--- a/src/rag_results.xlsx
+++ b/src/rag_results.xlsx
@@ -2,15 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="4300" yWindow="880" windowWidth="29900" windowHeight="20240" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Results" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -19,17 +18,28 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="新細明體"/>
+      <charset val="136"/>
+      <family val="1"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="新細明體"/>
+      <charset val="136"/>
+      <family val="3"/>
+      <sz val="9"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -41,7 +51,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
+        <fgColor rgb="FF1F4E78"/>
       </patternFill>
     </fill>
   </fills>
@@ -54,9 +64,13 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="FFD9D9D9"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -75,7 +89,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -438,21 +452,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:M84"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
     <col width="48" customWidth="1" min="3" max="3"/>
     <col width="36" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="6" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="11" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
@@ -526,29 +537,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SC1</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>保戶在114/1/10投保樂鍾溢，如果他在115/3/30罹患特定傷病的話，他在115/1/9會領到無理賠回饋保險金嗎?</t>
+          <t>保障範圍包括哪些項目？</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>回答：  
-1. 樂鍾溢保單包含「無理賠回饋保險金」的條款，依據第十四條規定，若被保險人在保險單年度末仍生存且未曾申領「特定傷病保險金」，可獲得「無理賠回饋保險金」。  
-2. 115/1/9屬於保險單年度末，需確認被保險人在該日期前是否符合條件。由於被保險人在115/3/30罹患特定傷病，且診斷日期晚於115/1/9，因此115/1/9時未曾申領「特定傷病保險金」，符合給付條件。  
-3. 115/3/30罹患特定傷病不影響115/1/9的「無理賠回饋保險金」給付資格，但若事後發現被保險人不符條件，保險公司有權要求返還或扣回該保險金。  
-4. 保單生效日期為114/1/10，等待期為30日，故114/2/9起保單進入有效期間，與本問題無直接影響。  
-條文依據：  
-- [第十四條 無理賠回饋保險金的給付]  
-- [第十二條 特定傷病保險金的給付]</t>
+保障範圍包括：住院醫療保險金、加護病房或燒燙傷病房保險金、祝壽保險金、身故保險金或喪葬費用保險金，以及所繳保險費的退還。
+條文依據：  
+- [第五條 保險範圍]</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>第十四條 無理賠回饋保險金的給付 | payout_items | 第二十條 無理賠回饋保險金的申領 | 第十二條 特定傷病保險金的給付 | other_metadata</t>
+          <t>payout_items | summary | 第五條 保險範圍 | 第二條 名詞定義 | 第十八條 除外責任（一）</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -559,34 +566,4740 @@
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>回答：  
-1. 樂鍾溢保單包含「無理賠回饋保險金」的條款，依據第十四條規定，若被保險人在保險單年度末仍生存且未曾申領「特定傷病保險金」，可獲得「無理賠回饋保險金」。  
-2. 115/1/9屬於保險單年度末，需確認被保險人在該日期前是否符合條件。由於被保險人在115/3/30罹患特定傷病，且診斷日期晚於115/1/9，因此115/1/9時未曾申領「特定傷病保險金」，符合給付條件。  
-3. 115/3/30罹患特定傷病不影響115/1/9的「無理賠回饋保險金」給付資格，但若事後發現被保險人不符條件，保險公司有權要求返還或扣回該保險金。  
-4. 保單生效日期為114/1/10，等待期為30日，故114/2/9起保單進入有效期間，與本問題無直接影響。  
-條文依據：  
-- [第十四條 無理賠回饋保險金的給付]  
-- [第十二條 特定傷病保險金的給付]</t>
+保障範圍包括：住院醫療保險金、加護病房或燒燙傷病房保險金、祝壽保險金、身故保險金或喪葬費用保險金，以及所繳保險費的退還。
+條文依據：  
+- [第五條 保險範圍]</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>{"points": [{"id": "1", "point": "確認樂鍾溢保單是否包含無理賠回饋保險金的條款", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認115/1/9是否符合無理賠回饋保險金的給付條件", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認115/3/30罹患特定傷病是否影響無理賠回饋保險金的給付資格", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認保單的生效日期及相關等待期規定", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.930912, "neutral": 0.061623, "contradiction": 0.007465, "factuality": 0.992535, "C_fact": 0.992535}, "C_conf": 0.9955}</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>0.9925349999999999</v>
-      </c>
-      <c r="L2" s="3" t="n">
-        <v>0.9955000000000001</v>
-      </c>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="n"/>
+      <c r="K2" s="3" t="n"/>
+      <c r="L2" s="3" t="n"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-15 11:33:12</t>
+          <t>2026-03-15 15:55:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>住院日數計算有什麼特殊規則？</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院日數的計算規則如下：  
+1. 住院日數是按被保險人同一次住院的實際全日住進急性病房或慢性病房（包括加護病房及燒燙傷病房）的住院日數計算，包含住院當日及出院當日。  
+2. 若被保險人出院後於同一日再次入院診療，該日不得重複計入住院日數。  
+條文依據：  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第十二條 住院醫療保險金的給付 | 第二條 名詞定義 | 第十三條 加護病房或燒燙傷病房保險金的給付 | 第二十八條 住院醫療保險金日額之減少</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院日數的計算規則如下：  
+1. 住院日數是按被保險人同一次住院的實際全日住進急性病房或慢性病房（包括加護病房及燒燙傷病房）的住院日數計算，包含住院當日及出院當日。  
+2. 若被保險人出院後於同一日再次入院診療，該日不得重複計入住院日數。  
+條文依據：  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="n"/>
+      <c r="K3" s="3" t="n"/>
+      <c r="L3" s="3" t="n"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2026-03-15 15:55:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>住院醫療保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院醫療保險金的給付規定如下：  
+被保險人於本契約有效期間內因疾病或傷害而住院治療時，本公司將依保險單上所記載的「住院醫療保險金日額」，乘以入院日當年度的「增額係數」，再乘以被保險人住院日數，給付「住院醫療保險金」。同一保單年度內，同一次住院的住院日數給付上限為三百六十五日。  
+條文依據：  
+- [第十二條 住院醫療保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 住院醫療保險金的給付 | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第十三條 加護病房或燒燙傷病房保險金的給付 | 第十四條 醫療保險金給付總額之上限 | 第二十八條 住院醫療保險金日額之減少</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院醫療保險金的給付規定如下：  
+被保險人於本契約有效期間內因疾病或傷害而住院治療時，本公司將依保險單上所記載的「住院醫療保險金日額」，乘以入院日當年度的「增額係數」，再乘以被保險人住院日數，給付「住院醫療保險金」。同一保單年度內，同一次住院的住院日數給付上限為三百六十五日。  
+條文依據：  
+- [第十二條 住院醫療保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="n"/>
+      <c r="K4" s="3" t="n"/>
+      <c r="L4" s="3" t="n"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2026-03-15 15:55:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>加護病房或燒燙傷病房保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+加護病房或燒燙傷病房保險金的給付規定如下：  
+被保險人於本契約有效期間內因疾病或傷害而在醫院的加護病房或燒燙傷病房接受治療時，除住院醫療保險金外，保險公司將依保險單上所記載的「住院醫療保險金日額」，乘以入院日當年度的「增額係數」，再乘以實際住進加護病房或燒燙傷病房的日數（含轉入及轉出當日）的二倍，給付「加護病房或燒燙傷病房保險金」。  
+同一保單年度內，同一次住院的加護病房及燒燙傷病房住院日數合計給付最高以365日為限，但同一日內僅給付其中一種病房的保險金。
+條文依據：  
+- [第十三條 加護病房或燒燙傷病房保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 加護病房或燒燙傷病房保險金的給付 | payout_items | 第二十三條 醫療保險金的申領 | 第五條 保險範圍 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+加護病房或燒燙傷病房保險金的給付規定如下：  
+被保險人於本契約有效期間內因疾病或傷害而在醫院的加護病房或燒燙傷病房接受治療時，除住院醫療保險金外，保險公司將依保險單上所記載的「住院醫療保險金日額」，乘以入院日當年度的「增額係數」，再乘以實際住進加護病房或燒燙傷病房的日數（含轉入及轉出當日）的二倍，給付「加護病房或燒燙傷病房保險金」。  
+同一保單年度內，同一次住院的加護病房及燒燙傷病房住院日數合計給付最高以365日為限，但同一日內僅給付其中一種病房的保險金。
+條文依據：  
+- [第十三條 加護病房或燒燙傷病房保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="n"/>
+      <c r="K5" s="3" t="n"/>
+      <c r="L5" s="3" t="n"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2026-03-15 15:55:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>醫療保險金給付總額之上限</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+醫療保險金給付總額之上限為保險單上所記載之「住院醫療保險金日額」的二千五百倍。
+條文依據：  
+- [第十四條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 醫療保險金給付總額之上限 | 第十二條 住院醫療保險金的給付 | 第五條 保險範圍 | 第十三條 加護病房或燒燙傷病房保險金的給付 | payout_items</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+醫療保險金給付總額之上限為保險單上所記載之「住院醫療保險金日額」的二千五百倍。
+條文依據：  
+- [第十四條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="n"/>
+      <c r="K6" s="3" t="n"/>
+      <c r="L6" s="3" t="n"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2026-03-15 15:56:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>祝壽保險金的給付規定為何?</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+祝壽保險金的給付規定為：被保險人在本契約有效期間內，且於保險年齡到達99歲的保險單週年日仍生存時，本公司將依「當年度保險金額」給付祝壽保險金。
+條文依據：  
+- [第十五條 祝壽保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>第十五條 祝壽保險金的給付 | 第十二條至第十三條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | 第二十四條 祝壽保險金的申領 | payout_items | 第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+祝壽保險金的給付規定為：被保險人在本契約有效期間內，且於保險年齡到達99歲的保險單週年日仍生存時，本公司將依「當年度保險金額」給付祝壽保險金。
+條文依據：  
+- [第十五條 祝壽保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="n"/>
+      <c r="K7" s="3" t="n"/>
+      <c r="L7" s="3" t="n"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2026-03-15 15:56:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>有效期間內身故，保險金如何給付?</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於本契約有效期間內身故時，本公司按「當年度保險金額」給付「身故保險金」。若被保險人於繳費期間內身故，當期已繳付之未到期保險費將不予退還，亦不併入身故保險金內給付。若被保險人於有效期間內且實際年齡未滿十五足歲身故，本公司將按「所繳保險費」退還要保人，不適用前述規定。此外，若被保險人為受監護宣告尚未撤銷者，其身故保險金變更為喪葬費用保險金，且喪葬費用保險金額不得超過遺產稅喪葬費扣除額之半數，超過部分不負給付責任，但本公司應無息退還該超過部分之已繳保險費。
+條文依據：  
+- [第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付 | 第十條 契約的終止（二） | 第五條 保險範圍 | 第二十二條 失蹤處理 | 第十五條 祝壽保險金的給付</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於本契約有效期間內身故時，本公司按「當年度保險金額」給付「身故保險金」。若被保險人於繳費期間內身故，當期已繳付之未到期保險費將不予退還，亦不併入身故保險金內給付。若被保險人於有效期間內且實際年齡未滿十五足歲身故，本公司將按「所繳保險費」退還要保人，不適用前述規定。此外，若被保險人為受監護宣告尚未撤銷者，其身故保險金變更為喪葬費用保險金，且喪葬費用保險金額不得超過遺產稅喪葬費扣除額之半數，超過部分不負給付責任，但本公司應無息退還該超過部分之已繳保險費。
+條文依據：  
+- [第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="n"/>
+      <c r="K8" s="3" t="n"/>
+      <c r="L8" s="3" t="n"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-03-15 15:56:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>健康促進保險費折減規定</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+健康促進保險費折減規定如下：  
+1. 被保險人年齡需達20歲（含）以上，並使用保險公司指定程式加入健康計劃。  
+2. 若於「指定日期」會員等級符合標準，則次一保險單年度保險費可依會員等級折減：  
+   - 進階會員：折減2%。  
+   - 菁英會員或更高等級：折減3%。  
+3. 折減僅適用於主契約保險費，不包含其他附約、附加條款或批註條款，且豁免或復效的保險費不適用折減。  
+4. 被保險人需完成指定程式的註冊程序，並授權保險公司取得健康促進相關電子紀錄，保險公司將依此計算會員等級。
+條文依據：  
+- [第十七條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>第十七條 健康促進保險費折減 | 第二十八條 住院醫療保險金日額之減少 | 第三十條 投保年齡的計算及錯誤的處理 | 第二條 名詞定義 | 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+健康促進保險費折減規定如下：  
+1. 被保險人年齡需達20歲（含）以上，並使用保險公司指定程式加入健康計劃。  
+2. 若於「指定日期」會員等級符合標準，則次一保險單年度保險費可依會員等級折減：  
+   - 進階會員：折減2%。  
+   - 菁英會員或更高等級：折減3%。  
+3. 折減僅適用於主契約保險費，不包含其他附約、附加條款或批註條款，且豁免或復效的保險費不適用折減。  
+4. 被保險人需完成指定程式的註冊程序，並授權保險公司取得健康促進相關電子紀錄，保險公司將依此計算會員等級。
+條文依據：  
+- [第十七條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="n"/>
+      <c r="K9" s="3" t="n"/>
+      <c r="L9" s="3" t="n"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-03-15 15:56:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>除外責任的解釋?</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據保險條款，除外責任是指保險公司對於某些特定情況下發生的疾病、傷害或死亡，不負給付保險金的責任。以下為主要除外責任的內容：  
+1. **疾病或傷害住院診療的除外責任**：  
+   - 因被保險人故意行為（如自殺、自殺未遂）、犯罪行為或非法施用毒品所致的疾病或傷害。  
+   - 因美容手術或外科整型住院，但若為重建基本功能的必要整型則不在此限。  
+   - 因外觀可見的天生畸形、健康檢查、療養、靜養、戒毒、戒酒、護理或養老等非直接診治病人的目的住院。  
+   - 因懷孕、流產或分娩及其併發症住院，但以下情形不在此限：  
+     （一）懷孕相關疾病（如子宮外孕、葡萄胎等）。  
+     （二）因醫療行為必要的流產（如因遺傳性疾病或生命危險等）。  
+     （三）醫療行為必要的剖腹產，且符合特定情況（如胎位不正、多胞胎等）。  
+2. **身故保險金或喪葬費用保險金的除外責任**：  
+   - 要保人故意致被保險人於死。  
+   - 被保險人故意自殺，但若自契約訂立或復效之日起滿二年後自殺致死，保險公司仍負給付責任。  
+   - 被保險人因犯罪處死、拒捕或越獄致死。  
+條文依據：  
+- [第十八條 除外責任（一）]  
+- [第十九條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第十九條 除外責任（二） | 第八條 告知義務與本契約的解除 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據保險條款，除外責任是指保險公司對於某些特定情況下發生的疾病、傷害或死亡，不負給付保險金的責任。以下為主要除外責任的內容：  
+1. **疾病或傷害住院診療的除外責任**：  
+   - 因被保險人故意行為（如自殺、自殺未遂）、犯罪行為或非法施用毒品所致的疾病或傷害。  
+   - 因美容手術或外科整型住院，但若為重建基本功能的必要整型則不在此限。  
+   - 因外觀可見的天生畸形、健康檢查、療養、靜養、戒毒、戒酒、護理或養老等非直接診治病人的目的住院。  
+   - 因懷孕、流產或分娩及其併發症住院，但以下情形不在此限：  
+     （一）懷孕相關疾病（如子宮外孕、葡萄胎等）。  
+     （二）因醫療行為必要的流產（如因遺傳性疾病或生命危險等）。  
+     （三）醫療行為必要的剖腹產，且符合特定情況（如胎位不正、多胞胎等）。  
+2. **身故保險金或喪葬費用保險金的除外責任**：  
+   - 要保人故意致被保險人於死。  
+   - 被保險人故意自殺，但若自契約訂立或復效之日起滿二年後自殺致死，保險公司仍負給付責任。  
+   - 被保險人因犯罪處死、拒捕或越獄致死。  
+條文依據：  
+- [第十八條 除外責任（一）]  
+- [第十九條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="n"/>
+      <c r="K10" s="3" t="n"/>
+      <c r="L10" s="3" t="n"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-03-15 15:56:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>哪些疾病被含在除外責任?</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款，被保險人因以下原因所致之疾病或傷害，保險公司不負給付保險金的責任：  
+1. 被保險人之故意行為（包括自殺及自殺未遂）。  
+2. 被保險人之犯罪行為。  
+3. 被保險人非法施用毒品。  
+4. 美容手術、外科整型（但為重建基本功能所作之必要整型不在此限）。  
+5. 外觀可見之天生畸形。  
+6. 健康檢查、療養、靜養、戒毒、戒酒、護理或養老等非以直接診治病人為目的者。  
+7. 懷孕、流產或分娩及其併發症（但特定情形如子宮外孕、葡萄胎等懷孕相關疾病，或醫療行為必要之流產及剖腹產不在此限）。  
+8. 不孕症、人工受孕或非以治療為目的之避孕及絕育手術。  
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第二條 名詞定義 | 第十九條 除外責任（二）</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款，被保險人因以下原因所致之疾病或傷害，保險公司不負給付保險金的責任：  
+1. 被保險人之故意行為（包括自殺及自殺未遂）。  
+2. 被保險人之犯罪行為。  
+3. 被保險人非法施用毒品。  
+4. 美容手術、外科整型（但為重建基本功能所作之必要整型不在此限）。  
+5. 外觀可見之天生畸形。  
+6. 健康檢查、療養、靜養、戒毒、戒酒、護理或養老等非以直接診治病人為目的者。  
+7. 懷孕、流產或分娩及其併發症（但特定情形如子宮外孕、葡萄胎等懷孕相關疾病，或醫療行為必要之流產及剖腹產不在此限）。  
+8. 不孕症、人工受孕或非以治療為目的之避孕及絕育手術。  
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="n"/>
+      <c r="K11" s="3" t="n"/>
+      <c r="L11" s="3" t="n"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-03-15 15:57:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>進行美容手術住院可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，因美容手術住院無法申請理賠。但若美容手術是為了重建基本功能所作之必要整型，則不在此限，可以申請理賠。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第十三條 加護病房或燒燙傷病房保險金的給付 | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第二條 名詞定義 | payout_items</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，因美容手術住院無法申請理賠。但若美容手術是為了重建基本功能所作之必要整型，則不在此限，可以申請理賠。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="n"/>
+      <c r="K12" s="3" t="n"/>
+      <c r="L12" s="3" t="n"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-03-15 15:57:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>因胎兒染色體異常進行手術而住院可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以申請理賠。根據條款，被保險人因「胎兒染色體異常之手術」住院診療，不屬於除外責任範圍，因此本公司應負給付保險金的責任。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第二條 名詞定義 | payout_items | 第十三條 加護病房或燒燙傷病房保險金的給付</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以申請理賠。根據條款，被保險人因「胎兒染色體異常之手術」住院診療，不屬於除外責任範圍，因此本公司應負給付保險金的責任。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="n"/>
+      <c r="K13" s="3" t="n"/>
+      <c r="L13" s="3" t="n"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-03-15 15:57:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>因胎位不正進行手術而住院可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以申請理賠。根據條文，雖然懷孕、流產或分娩及其併發症一般屬於除外責任，但若因「醫療行為必要之剖腹產」而住院，且符合條文中列舉的情況，則不在除外責任範圍內。其中，「胎位不正」屬於符合條件的情況之一，因此可以申請理賠。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第二條 名詞定義 | payout_items | 第十三條 加護病房或燒燙傷病房保險金的給付</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以申請理賠。根據條文，雖然懷孕、流產或分娩及其併發症一般屬於除外責任，但若因「醫療行為必要之剖腹產」而住院，且符合條文中列舉的情況，則不在除外責任範圍內。其中，「胎位不正」屬於符合條件的情況之一，因此可以申請理賠。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="n"/>
+      <c r="K14" s="3" t="n"/>
+      <c r="L14" s="3" t="n"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2026-03-15 15:57:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>因自殺未遂導致住院可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條文規定，若被保險人因自殺未遂導致住院診療，屬於「被保險人之故意行為」，本公司不負給付第十二條至第十三條保險金的責任，因此無法申請理賠。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 除外責任（二） | 第十八條 除外責任（一） | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | payout_items | 第十條 契約的終止（二）</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條文規定，若被保險人因自殺未遂導致住院診療，屬於「被保險人之故意行為」，本公司不負給付第十二條至第十三條保險金的責任，因此無法申請理賠。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="n"/>
+      <c r="K15" s="3" t="n"/>
+      <c r="L15" s="3" t="n"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2026-03-15 15:57:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>被保險人在投保一年內故意自殺者，可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人在投保一年內故意自殺者，本公司不負給付身故保險金或喪葬費用保險金的責任。只有在契約訂立或復效之日起滿二年後，因故意自殺致死者，本公司才負給付責任。
+條文依據：  
+- [第十九條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 除外責任（二） | 第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付 | 第十條 契約的終止（二） | 第三十條 投保年齡的計算及錯誤的處理 | 第十八條 除外責任（一）</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人在投保一年內故意自殺者，本公司不負給付身故保險金或喪葬費用保險金的責任。只有在契約訂立或復效之日起滿二年後，因故意自殺致死者，本公司才負給付責任。
+條文依據：  
+- [第十九條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="n"/>
+      <c r="K16" s="3" t="n"/>
+      <c r="L16" s="3" t="n"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2026-03-15 15:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>申請理賠有什麼時間規定嗎?</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申請理賠的時間規定如下：要保人、被保險人或受益人應於知悉保險公司應負保險責任之事故後十日內通知保險公司，並於通知後儘速檢具所需文件向保險公司申請給付保險金。保險公司應於收齊所需文件後十五日內完成給付。但若因保險公司可歸責的原因未能在上述期限內完成給付，則應按年利一分加計利息給付。
+條文依據：  
+- [第二十一條 保險事故的通知與保險金的申請時間]</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>第二十一條 保險事故的通知與保險金的申請時間 | 第六條 第二期以後保險費的交付、寬限期間及契約效力的停止 | 第七條 本契約效力的恢復 | 第三條 契約撤銷權 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申請理賠的時間規定如下：要保人、被保險人或受益人應於知悉保險公司應負保險責任之事故後十日內通知保險公司，並於通知後儘速檢具所需文件向保險公司申請給付保險金。保險公司應於收齊所需文件後十五日內完成給付。但若因保險公司可歸責的原因未能在上述期限內完成給付，則應按年利一分加計利息給付。
+條文依據：  
+- [第二十一條 保險事故的通知與保險金的申請時間]</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="n"/>
+      <c r="K17" s="3" t="n"/>
+      <c r="L17" s="3" t="n"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2026-03-15 15:58:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>燒燙傷病房保險金怎麼申領?</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申請燒燙傷病房保險金時，受益人需依約定檢附以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 醫療診斷書或住院證明，且需列明進、出燒燙傷病房的日期。（但若要保人或被保險人為醫師時，不得為被保險人出具診斷書或住院證明。）  
+4. 受益人的身分證明。  
+此外，保險公司基於審核保險金的需要，得徵詢其他醫師的醫學專業意見，並經受益人同意後調閱被保險人的就醫相關資料，相關費用由保險公司負擔。  
+條文依據：  
+- [第二十三條 醫療保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>第二十三條 醫療保險金的申領 | 第十三條 加護病房或燒燙傷病房保險金的給付 | payout_items | 第二條 名詞定義 | 第二十一條 保險事故的通知與保險金的申請時間</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申請燒燙傷病房保險金時，受益人需依約定檢附以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 醫療診斷書或住院證明，且需列明進、出燒燙傷病房的日期。（但若要保人或被保險人為醫師時，不得為被保險人出具診斷書或住院證明。）  
+4. 受益人的身分證明。  
+此外，保險公司基於審核保險金的需要，得徵詢其他醫師的醫學專業意見，並經受益人同意後調閱被保險人的就醫相關資料，相關費用由保險公司負擔。  
+條文依據：  
+- [第二十三條 醫療保險金的申領]</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="n"/>
+      <c r="K18" s="3" t="n"/>
+      <c r="L18" s="3" t="n"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2026-03-15 15:58:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>活到99歲怎麼申請祝壽金?</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申請祝壽保險金時，受益人需檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 受益人的身分證明。  
+條文依據：  
+- [第二十四條 祝壽保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>第十五條 祝壽保險金的給付 | 第二十四條 祝壽保險金的申領 | 第五條 保險範圍 | 第十二條至第十三條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | announcement_history</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申請祝壽保險金時，受益人需檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 受益人的身分證明。  
+條文依據：  
+- [第二十四條 祝壽保險金的申領]</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="n"/>
+      <c r="K19" s="3" t="n"/>
+      <c r="L19" s="3" t="n"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2026-03-15 15:58:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>被保人身故怎麼申請理賠</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+受益人申請「身故保險金」或「喪葬費用保險金」時，應檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 被保險人死亡證明書及除戶戶籍謄本。  
+4. 受益人的身分證明。  
+條文依據：  
+- [第二十五條 身故保險金或喪葬費用保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付 | 第十二條至第十三條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | 第二十二條 失蹤處理 | 第二十五條 身故保險金或喪葬費用保險金的申領 | 第十九條 除外責任（二）</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+受益人申請「身故保險金」或「喪葬費用保險金」時，應檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 被保險人死亡證明書及除戶戶籍謄本。  
+4. 受益人的身分證明。  
+條文依據：  
+- [第二十五條 身故保險金或喪葬費用保險金的申領]</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="n"/>
+      <c r="K20" s="3" t="n"/>
+      <c r="L20" s="3" t="n"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2026-03-15 15:58:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>投保15年後，因手術住院3天，住院日額為2500元，請問可以申請多少理賠?</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款，被保險人因手術住院3天，住院醫療保險金的計算方式為「住院醫療保險金日額」乘以「增額係數」再乘以住院日數。假設「增額係數」為1（條文未提供具體數值），則理賠金額為：  
+2500元 × 1 × 3天 = 7500元。
+條文依據：  
+- [第十二條 住院醫療保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 住院醫療保險金的給付 | 第二條 名詞定義 | 第二十八條 住院醫療保險金日額之減少 | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第十三條 加護病房或燒燙傷病房保險金的給付</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款，被保險人因手術住院3天，住院醫療保險金的計算方式為「住院醫療保險金日額」乘以「增額係數」再乘以住院日數。假設「增額係數」為1（條文未提供具體數值），則理賠金額為：  
+2500元 × 1 × 3天 = 7500元。
+條文依據：  
+- [第十二條 住院醫療保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="n"/>
+      <c r="K21" s="3" t="n"/>
+      <c r="L21" s="3" t="n"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2026-03-15 15:58:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>保障範圍包括哪些項目？</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括：住院手術醫療保險金、門診手術醫療保險金、特定處置保險金、意外創傷縫合處置保險金、意外住院手術醫療保險金、祝壽保險金、所繳保險費的退還、身故保險金或喪葬費用保險金。
+條文依據：  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>payout_items | 第五條 保險範圍 | summary | 第四條 名詞定義 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括：住院手術醫療保險金、門診手術醫療保險金、特定處置保險金、意外創傷縫合處置保險金、意外住院手術醫療保險金、祝壽保險金、所繳保險費的退還、身故保險金或喪葬費用保險金。
+條文依據：  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="n"/>
+      <c r="K22" s="3" t="n"/>
+      <c r="L22" s="3" t="n"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2026-03-15 15:59:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>保險金額是否有上限?</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+有，保險金額的給付總額上限為保險單上所記載「保險金額」的一千五百倍，且不包含其他附約、附加條款或批註條款。
+條文依據：  
+- [第十六條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 醫療保險金給付總額之上限 | 第三十條 保險金額之減少 | 第五條 保險範圍 | 第十九條 健康促進保險費折減 | 第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+有，保險金額的給付總額上限為保險單上所記載「保險金額」的一千五百倍，且不包含其他附約、附加條款或批註條款。
+條文依據：  
+- [第十六條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="n"/>
+      <c r="K23" s="3" t="n"/>
+      <c r="L23" s="3" t="n"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2026-03-15 15:59:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>投保後5天發生手術，是否可以申請理賠?</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+找不到相關內容  
+條文依據：  
+找不到相關內容</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第十一條 住院手術醫療保險金 | 第二十條 除外責任（一） | 第十二條 門診手術醫療保險金 | 第十三條 意外住院手術醫療保險金 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+找不到相關內容  
+條文依據：  
+找不到相關內容</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="n"/>
+      <c r="K24" s="3" t="n"/>
+      <c r="L24" s="3" t="n"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2026-03-15 16:00:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>住院手術醫療保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院手術醫療保險金的給付規定如下：  
+1. 被保險人於本契約有效期間內因疾病或傷害，經醫師診斷必須於醫院住院接受附表一的手術治療且已實際接受手術者，本公司將依保險單所記載之「保險金額」，乘以手術日當年度之「增額係數」，再乘以手術給付倍數，給付「住院手術醫療保險金」。  
+2. 若同一次手術中於同一手術位置接受二項以上手術項目，僅給付手術給付倍數最高的手術項目。  
+3. 未載明於附表一的手術項目，將與被保險人協議比照附表內程度相當的手術項目，決定給付倍數。  
+4. 以下情形不負給付責任：  
+   - 屬於除外責任條款規定的情形。  
+   - 不屬於全民健康保險醫療服務給付項目及支付標準第二部第二章第七節或第三部第三章第四節第三項所列舉的手術。  
+條文依據：  
+- [第十一條 住院手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 住院手術醫療保險金 | 第十三條 意外住院手術醫療保險金 | 第十二條 門診手術醫療保險金 | payout_items | 第二十條 除外責任（一） | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院手術醫療保險金的給付規定如下：  
+1. 被保險人於本契約有效期間內因疾病或傷害，經醫師診斷必須於醫院住院接受附表一的手術治療且已實際接受手術者，本公司將依保險單所記載之「保險金額」，乘以手術日當年度之「增額係數」，再乘以手術給付倍數，給付「住院手術醫療保險金」。  
+2. 若同一次手術中於同一手術位置接受二項以上手術項目，僅給付手術給付倍數最高的手術項目。  
+3. 未載明於附表一的手術項目，將與被保險人協議比照附表內程度相當的手術項目，決定給付倍數。  
+4. 以下情形不負給付責任：  
+   - 屬於除外責任條款規定的情形。  
+   - 不屬於全民健康保險醫療服務給付項目及支付標準第二部第二章第七節或第三部第三章第四節第三項所列舉的手術。  
+條文依據：  
+- [第十一條 住院手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="n"/>
+      <c r="K25" s="3" t="n"/>
+      <c r="L25" s="3" t="n"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>2026-03-15 16:00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>門診手術醫療保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+門診手術醫療保險金的給付規定如下：  
+1. 被保險人於本契約有效期間內因疾病或傷害，經醫師診斷必須於醫院或診所門診接受附表一的手術治療且已實際接受手術者，本公司將依保險單所記載的「保險金額」，乘以手術日當年度的「增額係數」，再乘以手術給付倍數，給付「門診手術醫療保險金」。  
+2. 同一次手術中，於同一手術位置接受二項以上手術項目時，僅給付手術給付倍數最高的手術項目。  
+3. 同一保險單年度內，門診手術醫療保險金的給付以十次為限。  
+4. 未載明於附表一的手術項目，將與被保險人協議比照附表內的手術項目決定給付倍數。  
+5. 以下情形不負給付責任：  
+   - 依據本契約除外責任條款的規定不在給付範圍內。  
+   - 不屬於全民健康保險醫療服務給付項目及支付標準第二部第二章第七節或第三部第三章第四節第三項所列舉的手術。  
+條文依據：  
+- [第十二條 門診手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 門診手術醫療保險金 | 第十一條 住院手術醫療保險金 | payout_items | 第十三條 意外住院手術醫療保險金 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+門診手術醫療保險金的給付規定如下：  
+1. 被保險人於本契約有效期間內因疾病或傷害，經醫師診斷必須於醫院或診所門診接受附表一的手術治療且已實際接受手術者，本公司將依保險單所記載的「保險金額」，乘以手術日當年度的「增額係數」，再乘以手術給付倍數，給付「門診手術醫療保險金」。  
+2. 同一次手術中，於同一手術位置接受二項以上手術項目時，僅給付手術給付倍數最高的手術項目。  
+3. 同一保險單年度內，門診手術醫療保險金的給付以十次為限。  
+4. 未載明於附表一的手術項目，將與被保險人協議比照附表內的手術項目決定給付倍數。  
+5. 以下情形不負給付責任：  
+   - 依據本契約除外責任條款的規定不在給付範圍內。  
+   - 不屬於全民健康保險醫療服務給付項目及支付標準第二部第二章第七節或第三部第三章第四節第三項所列舉的手術。  
+條文依據：  
+- [第十二條 門診手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="n"/>
+      <c r="K26" s="3" t="n"/>
+      <c r="L26" s="3" t="n"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2026-03-15 16:00:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>意外住院手術醫療保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外住院手術醫療保險金的給付規定如下：  
+1. 被保險人需於本契約有效期間內，且保險年齡未滿七十歲。  
+2. 因傷害經醫師診斷在住院期間必須接受手術治療且已接受手術者。  
+3. 給付金額為保險單上所記載之「保險金額」的三倍，乘以手術日當年度之「增額係數」。  
+4. 若同一次手術中於同一手術位置接受二項以上手術項目，僅給付一次意外住院手術醫療保險金。
+條文依據：  
+- [第十三條 意外住院手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 意外住院手術醫療保險金 | 第十一條 住院手術醫療保險金 | 第十五條 意外創傷縫合處置保險金 | 第二十條 除外責任（一） | 第十二條 門診手術醫療保險金 | 附表三：意外創傷縫合處置項目及給付倍數表 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外住院手術醫療保險金的給付規定如下：  
+1. 被保險人需於本契約有效期間內，且保險年齡未滿七十歲。  
+2. 因傷害經醫師診斷在住院期間必須接受手術治療且已接受手術者。  
+3. 給付金額為保險單上所記載之「保險金額」的三倍，乘以手術日當年度之「增額係數」。  
+4. 若同一次手術中於同一手術位置接受二項以上手術項目，僅給付一次意外住院手術醫療保險金。
+條文依據：  
+- [第十三條 意外住院手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="n"/>
+      <c r="K27" s="3" t="n"/>
+      <c r="L27" s="3" t="n"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2026-03-15 16:00:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>特定處置保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+特定處置保險金的給付規定如下：  
+1. 被保險人於保險契約有效期間內，因疾病或傷害經醫師診斷需接受附表二所列之特定處置治療，且已實際接受處置者，本公司將依保險單所載「保險金額」，乘以特定處置日當年度之「增額係數」，再乘以特定處置給付倍數，給付「特定處置保險金」。  
+2. 若同一次處置治療中，於同一治療位置接受兩項以上特定處置項目，僅給付特定處置給付倍數最高的項目。  
+3. 若被保險人接受的處置未列於附表二所列之特定處置項目，本公司不負給付特定處置保險金的責任。  
+4. 同一保險單年度內，特定處置保險金的給付次數以十次為限。
+條文依據：  
+- [第十四條 特定處置保險金]</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 特定處置保險金 | 第十五條 意外創傷縫合處置保險金 | 附表二：特定處置項目及給付倍數表 | 第五條 保險範圍 | 附表三：意外創傷縫合處置項目及給付倍數表</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+特定處置保險金的給付規定如下：  
+1. 被保險人於保險契約有效期間內，因疾病或傷害經醫師診斷需接受附表二所列之特定處置治療，且已實際接受處置者，本公司將依保險單所載「保險金額」，乘以特定處置日當年度之「增額係數」，再乘以特定處置給付倍數，給付「特定處置保險金」。  
+2. 若同一次處置治療中，於同一治療位置接受兩項以上特定處置項目，僅給付特定處置給付倍數最高的項目。  
+3. 若被保險人接受的處置未列於附表二所列之特定處置項目，本公司不負給付特定處置保險金的責任。  
+4. 同一保險單年度內，特定處置保險金的給付次數以十次為限。
+條文依據：  
+- [第十四條 特定處置保險金]</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="n"/>
+      <c r="K28" s="3" t="n"/>
+      <c r="L28" s="3" t="n"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2026-03-15 16:00:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>意外創傷縫合處置保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外創傷縫合處置保險金的給付規定如下：  
+1. 被保險人於本契約有效期間內，因意外傷害事故在醫院或診所接受附表三所列的意外創傷縫合處置治療者，本公司將依保險單所記載的「保險金額」，乘以意外創傷縫合處置日當年度的「增額係數」，再乘以意外創傷縫合處置給付倍數，給付「意外創傷縫合處置保險金」。  
+2. 同一次意外傷害事故，本公司僅就被保險人接受創傷縫合處置的傷口最大者給付，且以給付一次為限。  
+3. 若被保險人因同一意外傷害事故，已申領第十一條「住院手術醫療保險金」或第十二條「門診手術醫療保險金」，本公司將不再給付本條之「意外創傷縫合處置保險金」。  
+條文依據：  
+- [第十五條 意外創傷縫合處置保險金]</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>第十五條 意外創傷縫合處置保險金 | 附表三：意外創傷縫合處置項目及給付倍數表 | 第十四條 特定處置保險金 | 第二十條 除外責任（一） | 第十三條 意外住院手術醫療保險金 | 附表二：特定處置項目及給付倍數表</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外創傷縫合處置保險金的給付規定如下：  
+1. 被保險人於本契約有效期間內，因意外傷害事故在醫院或診所接受附表三所列的意外創傷縫合處置治療者，本公司將依保險單所記載的「保險金額」，乘以意外創傷縫合處置日當年度的「增額係數」，再乘以意外創傷縫合處置給付倍數，給付「意外創傷縫合處置保險金」。  
+2. 同一次意外傷害事故，本公司僅就被保險人接受創傷縫合處置的傷口最大者給付，且以給付一次為限。  
+3. 若被保險人因同一意外傷害事故，已申領第十一條「住院手術醫療保險金」或第十二條「門診手術醫療保險金」，本公司將不再給付本條之「意外創傷縫合處置保險金」。  
+條文依據：  
+- [第十五條 意外創傷縫合處置保險金]</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="n"/>
+      <c r="K29" s="3" t="n"/>
+      <c r="L29" s="3" t="n"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2026-03-15 16:00:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>醫療保險金給付總額之上限</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+醫療保險金給付總額之上限為保險單上所記載「保險金額」的一千五百倍，且不包含其他附約、附加條款或批註條款。
+條文依據：  
+- [第十六條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 醫療保險金給付總額之上限 | 第十二條 門診手術醫療保險金 | 第五條 保險範圍 | 第十一條 住院手術醫療保險金 | 第十三條 意外住院手術醫療保險金 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+醫療保險金給付總額之上限為保險單上所記載「保險金額」的一千五百倍，且不包含其他附約、附加條款或批註條款。
+條文依據：  
+- [第十六條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="n"/>
+      <c r="K30" s="3" t="n"/>
+      <c r="L30" s="3" t="n"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>2026-03-15 16:01:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>祝壽保險金的領取規定為何?</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+祝壽保險金的領取規定如下：  
+1. 被保險人需於本契約有效期間內，且保險年齡到達九十九歲之保險單週年日仍生存，方可領取祝壽保險金。  
+2. 受益人申領祝壽保險金時，需檢具以下文件：  
+   - 保險單或其謄本  
+   - 保險金申請書  
+   - 受益人的身分證明  
+條文依據：  
+- [第十七條 祝壽保險金]  
+- [第二十六條 祝壽保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>第十七條 祝壽保險金 | 第二十六條 祝壽保險金的申領 | 第十一條至第十五條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | 第二十三條 保險事故的通知與保險金的申請時間 | 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+祝壽保險金的領取規定如下：  
+1. 被保險人需於本契約有效期間內，且保險年齡到達九十九歲之保險單週年日仍生存，方可領取祝壽保險金。  
+2. 受益人申領祝壽保險金時，需檢具以下文件：  
+   - 保險單或其謄本  
+   - 保險金申請書  
+   - 受益人的身分證明  
+條文依據：  
+- [第十七條 祝壽保險金]  
+- [第二十六條 祝壽保險金的申領]</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="n"/>
+      <c r="K31" s="3" t="n"/>
+      <c r="L31" s="3" t="n"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>2026-03-15 16:01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>身故時領取保險金有什麼規則?</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+身故時領取保險金的規則如下：  
+1. 若被保險人於本契約有效期間內身故，本公司按「當年度保險金額」給付「身故保險金」。  
+2. 若被保險人於本契約有效期間且實際年齡未滿十五足歲身故，本公司退還「所繳保險費」予要保人，不適用「當年度保險金額」的約定。  
+3. 若被保險人於訂立本契約時為受監護宣告尚未撤銷者，其身故保險金變更為喪葬費用保險金，且喪葬費用保險金額不得超過遺產稅喪葬費扣除額之半數，超過部分本公司不負給付責任，並退還超過部分的已繳保險費。  
+4. 若有多家保險公司或多個保險契約，喪葬費用保險金額超過限額時，依要保時間先後順序給付，若無法區分時間則按比例分擔責任。  
+條文依據：  
+- [第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金]  
+此外，受益人申領身故保險金或喪葬費用保險金時，需檢具相關文件，包括保險單、死亡證明書、保險金申請書及受益人身分證明。  
+條文依據：  
+- [第二十七條 身故保險金或喪葬費用保險金的申領]  
+若發生除外責任的情形（如要保人故意致被保險人於死、被保險人故意自殺於契約訂立或復效後兩年內等），本公司不負給付責任，但被保險人未滿十五足歲時，則退還所繳保險費予要保人或應得之人。  
+條文依據：  
+- [第二十一條 除外責任（二)]</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金 | 第二十七條 身故保險金或喪葬費用保險金的申領 | 第十一條至第十五條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | 第二十一條 除外責任（二） | 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+身故時領取保險金的規則如下：  
+1. 若被保險人於本契約有效期間內身故，本公司按「當年度保險金額」給付「身故保險金」。  
+2. 若被保險人於本契約有效期間且實際年齡未滿十五足歲身故，本公司退還「所繳保險費」予要保人，不適用「當年度保險金額」的約定。  
+3. 若被保險人於訂立本契約時為受監護宣告尚未撤銷者，其身故保險金變更為喪葬費用保險金，且喪葬費用保險金額不得超過遺產稅喪葬費扣除額之半數，超過部分本公司不負給付責任，並退還超過部分的已繳保險費。  
+4. 若有多家保險公司或多個保險契約，喪葬費用保險金額超過限額時，依要保時間先後順序給付，若無法區分時間則按比例分擔責任。  
+條文依據：  
+- [第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金]  
+此外，受益人申領身故保險金或喪葬費用保險金時，需檢具相關文件，包括保險單、死亡證明書、保險金申請書及受益人身分證明。  
+條文依據：  
+- [第二十七條 身故保險金或喪葬費用保險金的申領]  
+若發生除外責任的情形（如要保人故意致被保險人於死、被保險人故意自殺於契約訂立或復效後兩年內等），本公司不負給付責任，但被保險人未滿十五足歲時，則退還所繳保險費予要保人或應得之人。  
+條文依據：  
+- [第二十一條 除外責任（二)]</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="n"/>
+      <c r="K32" s="3" t="n"/>
+      <c r="L32" s="3" t="n"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>2026-03-15 16:01:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>什麼情況下可以保費折減?</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人年齡滿20歲（含）以上，並在保單有效期間內使用保險公司指定的程式，加入指定的健康計劃，且於「指定日期」的會員等級符合進階會員或菁英會員（或更高等級）標準之一者，可享有次一保險單年度的保費折減。折減比例為進階會員2%，菁英會員或更高等級3%。但豁免或復效的保險費不適用此折減規定。
+條文依據：  
+- [第十九條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 健康促進保險費折減 | 第三十條 保險金額之減少 | 第二十條 除外責任（一） | 第三十一條 投保年齡的計算及錯誤的處理 | 第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人年齡滿20歲（含）以上，並在保單有效期間內使用保險公司指定的程式，加入指定的健康計劃，且於「指定日期」的會員等級符合進階會員或菁英會員（或更高等級）標準之一者，可享有次一保險單年度的保費折減。折減比例為進階會員2%，菁英會員或更高等級3%。但豁免或復效的保險費不適用此折減規定。
+條文依據：  
+- [第十九條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="n"/>
+      <c r="K33" s="3" t="n"/>
+      <c r="L33" s="3" t="n"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>2026-03-15 16:01:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>角膜切除術是否可以申請理賠?</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+角膜切除術可以申請理賠，其對應的給付倍數為5倍。
+條文依據：  
+- [附表一：手術項目與給付倍數 - 1305 角膜切除術]</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+角膜切除術可以申請理賠，其對應的給付倍數為5倍。
+條文依據：  
+- [附表一：手術項目與給付倍數 - 1305 角膜切除術]</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="n"/>
+      <c r="K34" s="3" t="n"/>
+      <c r="L34" s="3" t="n"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2026-03-15 16:01:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>白內障手術是否可以申請理賠?</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+白內障手術是否可以申請理賠，需視手術是否符合以下條件：  
+1. 手術項目需列於附表一中，並有對應的手術給付倍數。  
+2. 手術需屬於全民健康保險醫療服務給付項目及支付標準第二部第二章第七節或第三部第三章第四節第三項所列舉的手術。  
+3. 手術不屬於第二十條「除外責任」中所列的排除範圍。  
+若白內障手術符合上述條件，則可申請理賠。若不符合，則無法申請理賠。
+條文依據：  
+- [第十二條 門診手術醫療保險金]  
+- [第二十條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 門診手術醫療保險金 | 第二十條 除外責任（一） | 附表一：手術項目與給付倍數 | payout_items | 第十一條 住院手術醫療保險金</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+白內障手術是否可以申請理賠，需視手術是否符合以下條件：  
+1. 手術項目需列於附表一中，並有對應的手術給付倍數。  
+2. 手術需屬於全民健康保險醫療服務給付項目及支付標準第二部第二章第七節或第三部第三章第四節第三項所列舉的手術。  
+3. 手術不屬於第二十條「除外責任」中所列的排除範圍。  
+若白內障手術符合上述條件，則可申請理賠。若不符合，則無法申請理賠。
+條文依據：  
+- [第十二條 門診手術醫療保險金]  
+- [第二十條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="n"/>
+      <c r="K35" s="3" t="n"/>
+      <c r="L35" s="3" t="n"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2026-03-15 16:02:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>保障範圍包括哪些項目？</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括：意外事故身故保險金或喪葬費用保險金、意外事故失能保險金、每月生活照護保險金、重大燒燙傷保險金、意外骨折保險金、傷害醫療日額保險金、意外創傷縫合處置保險金。
+條文依據：  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>payout_items | 第五條 保險範圍 | 第十五條 每月生活照護保險金的給付 | 第三十條 不保事項 | 附表二：失能程度與保險金給付表</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括：意外事故身故保險金或喪葬費用保險金、意外事故失能保險金、每月生活照護保險金、重大燒燙傷保險金、意外骨折保險金、傷害醫療日額保險金、意外創傷縫合處置保險金。
+條文依據：  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="n"/>
+      <c r="K36" s="3" t="n"/>
+      <c r="L36" s="3" t="n"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2026-03-15 19:01:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>發生意外事故身故，理賠內容為何?</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外事故身故的理賠內容如下：  
+1. 若屬「一般意外傷害事故」，給付金額為「傷害醫療保險金日額」的五百倍。  
+2. 若屬「特定意外傷害事故」，給付金額為「傷害醫療保險金日額」的一千倍。  
+3. 若被保險人於意外傷害事故發生後超過一百八十日身故，但受益人能證明身故與該意外傷害事故具有因果關係，本公司仍依上述金額給付。  
+4. 若被保險人於訂立契約時為受監護宣告尚未撤銷者，其理賠內容為「喪葬費用保險金」，且金額不得超過遺產稅喪葬費扣除額之半數，超過部分不負給付責任，並退還超過部分的已繳保險費。  
+條文依據：  
+- [第十二條 意外事故身故保險金或喪葬費用保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 意外事故身故保險金或喪葬費用保險金的給付 | 第十四條 保險給付的限制 | payout_items | 第十一條 契約的終止（二） | 第二十一條 失蹤處理</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外事故身故的理賠內容如下：  
+1. 若屬「一般意外傷害事故」，給付金額為「傷害醫療保險金日額」的五百倍。  
+2. 若屬「特定意外傷害事故」，給付金額為「傷害醫療保險金日額」的一千倍。  
+3. 若被保險人於意外傷害事故發生後超過一百八十日身故，但受益人能證明身故與該意外傷害事故具有因果關係，本公司仍依上述金額給付。  
+4. 若被保險人於訂立契約時為受監護宣告尚未撤銷者，其理賠內容為「喪葬費用保險金」，且金額不得超過遺產稅喪葬費扣除額之半數，超過部分不負給付責任，並退還超過部分的已繳保險費。  
+條文依據：  
+- [第十二條 意外事故身故保險金或喪葬費用保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="n"/>
+      <c r="K37" s="3" t="n"/>
+      <c r="L37" s="3" t="n"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2026-03-15 19:02:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>意外事故失能保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外事故失能保險金的給付條件如下：  
+1. 被保險人於本契約有效期間內遭受「意外傷害事故」，自意外傷害事故發生之日起一百八十日以內致成附表二所列失能程度之一者，本公司依該意外傷害事故之種類及其致成被保險人之失能程度，按以下方式給付：  
+   - 一般意外傷害事故：「傷害醫療保險金日額」的五百倍乘以附表二給付比例。  
+   - 特定意外傷害事故：「傷害醫療保險金日額」的一千倍乘以附表二給付比例。  
+2. 若被保險人自意外傷害事故發生之日起超過一百八十日致成附表二所列失能程度之一，且受益人能證明該失能與意外傷害事故具有因果關係者，本公司仍依上述規定給付，不受一百八十日限制。  
+3. 同一意外傷害事故致成附表二所列二項以上失能程度時，給付各該項失能保險金之和，但以該意外傷害事故種類的以下金額為上限：  
+   - 一般意外傷害事故：「傷害醫療保險金日額」的五百倍。  
+   - 特定意外傷害事故：「傷害醫療保險金日額」的一千倍。  
+   若不同失能項目屬於同一手或同一足，僅給付一項失能保險金；若失能等級不同，給付較嚴重項目之失能保險金。  
+4. 被保險人因本次意外傷害事故所致失能，若合併以前的失能，可領附表二所列較嚴重項目之失能保險金，但以前的失能視同已給付，應扣除之。若扣除後金額低於單獨請領金額者，不適用合併約定。  
+5. 同一保險單年度內不同意外傷害事故的失能保險金累計給付金額最高以以下金額為限：  
+   - 一般意外傷害事故：「傷害醫療保險金日額」的五百倍。  
+   - 特定意外傷害事故：「傷害醫療保險金日額」的一千倍。  
+6. 不同保險單年度內不同意外傷害事故的失能保險金累計給付金額最高以「傷害醫療保險金日額」的一千二百倍為限。
+條文依據：  
+- [第十三條 意外事故失能保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 意外事故失能保險金的給付 | 第十五條 每月生活照護保險金的給付 | 第十四條 保險給付的限制 | 第十二條 意外事故身故保險金或喪葬費用保險金的給付 | 第二十三條 意外事故失能保險金的申領 | 附表二：失能程度與保險金給付表</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外事故失能保險金的給付條件如下：  
+1. 被保險人於本契約有效期間內遭受「意外傷害事故」，自意外傷害事故發生之日起一百八十日以內致成附表二所列失能程度之一者，本公司依該意外傷害事故之種類及其致成被保險人之失能程度，按以下方式給付：  
+   - 一般意外傷害事故：「傷害醫療保險金日額」的五百倍乘以附表二給付比例。  
+   - 特定意外傷害事故：「傷害醫療保險金日額」的一千倍乘以附表二給付比例。  
+2. 若被保險人自意外傷害事故發生之日起超過一百八十日致成附表二所列失能程度之一，且受益人能證明該失能與意外傷害事故具有因果關係者，本公司仍依上述規定給付，不受一百八十日限制。  
+3. 同一意外傷害事故致成附表二所列二項以上失能程度時，給付各該項失能保險金之和，但以該意外傷害事故種類的以下金額為上限：  
+   - 一般意外傷害事故：「傷害醫療保險金日額」的五百倍。  
+   - 特定意外傷害事故：「傷害醫療保險金日額」的一千倍。  
+   若不同失能項目屬於同一手或同一足，僅給付一項失能保險金；若失能等級不同，給付較嚴重項目之失能保險金。  
+4. 被保險人因本次意外傷害事故所致失能，若合併以前的失能，可領附表二所列較嚴重項目之失能保險金，但以前的失能視同已給付，應扣除之。若扣除後金額低於單獨請領金額者，不適用合併約定。  
+5. 同一保險單年度內不同意外傷害事故的失能保險金累計給付金額最高以以下金額為限：  
+   - 一般意外傷害事故：「傷害醫療保險金日額」的五百倍。  
+   - 特定意外傷害事故：「傷害醫療保險金日額」的一千倍。  
+6. 不同保險單年度內不同意外傷害事故的失能保險金累計給付金額最高以「傷害醫療保險金日額」的一千二百倍為限。
+條文依據：  
+- [第十三條 意外事故失能保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="n"/>
+      <c r="K38" s="3" t="n"/>
+      <c r="L38" s="3" t="n"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2026-03-15 19:02:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>每月生活照護保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+每月生活照護保險金的給付條件如下：  
+1. 被保險人於本契約有效期間內因「意外傷害事故」，自事故發生之日起一百八十日內，導致附表二所列第一級至第六級失能程度之一，且失能診斷確定後，本公司將自失能診斷確定當日起，按「傷害醫療保險金日額」的二十倍乘以附表二給付比例所得之金額，按月給付，最多給付十二個月。  
+2. 若於該項失能的前四個「失能診斷確定週年日」，本契約有效且被保險人仍生存，本公司自各該週年日起，依相同計算方式按月給付，最多給付十二個月。  
+3. 若被保險人自意外傷害事故發生之日起超過一百八十日才達到附表二所列第一級至第六級失能程度之一，受益人需證明該失能與意外傷害事故具有因果關係，本公司仍依上述規定給付。  
+4. 若因同一意外傷害事故導致附表二所列兩項以上第一級至第六級失能程度，本公司給付各該項「每月生活照護保險金」之和，最高以「傷害醫療保險金日額」的二十倍為限。但若不同失能項目屬於同一手或同一足，僅給付一項，且以較嚴重項目為準。  
+5. 若合併以前的失能，按較嚴重項目給付，但以前的失能視同已給付，應扣除之。若扣除後金額低於單獨請領金額者，不適用合併約定。  
+6. 每月給付金額最高以「傷害醫療保險金日額」的二十倍為限，累計給付金額最高以「傷害醫療保險金日額」的一千二百倍為限。  
+7. 若被保險人在給付期間內身故，未支領的部分將貼現後一次性給付予法定繼承人，貼現年利率為1.85%。
+條文依據：  
+- [第十五條 每月生活照護保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>第二十四條 每月生活照護保險金的申領 | 第十五條 每月生活照護保險金的給付 | payout_items | 第十八條 傷害醫療日額保險金的給付 | 第五條 保險範圍 | 附表二：失能程度與保險金給付表 | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+每月生活照護保險金的給付條件如下：  
+1. 被保險人於本契約有效期間內因「意外傷害事故」，自事故發生之日起一百八十日內，導致附表二所列第一級至第六級失能程度之一，且失能診斷確定後，本公司將自失能診斷確定當日起，按「傷害醫療保險金日額」的二十倍乘以附表二給付比例所得之金額，按月給付，最多給付十二個月。  
+2. 若於該項失能的前四個「失能診斷確定週年日」，本契約有效且被保險人仍生存，本公司自各該週年日起，依相同計算方式按月給付，最多給付十二個月。  
+3. 若被保險人自意外傷害事故發生之日起超過一百八十日才達到附表二所列第一級至第六級失能程度之一，受益人需證明該失能與意外傷害事故具有因果關係，本公司仍依上述規定給付。  
+4. 若因同一意外傷害事故導致附表二所列兩項以上第一級至第六級失能程度，本公司給付各該項「每月生活照護保險金」之和，最高以「傷害醫療保險金日額」的二十倍為限。但若不同失能項目屬於同一手或同一足，僅給付一項，且以較嚴重項目為準。  
+5. 若合併以前的失能，按較嚴重項目給付，但以前的失能視同已給付，應扣除之。若扣除後金額低於單獨請領金額者，不適用合併約定。  
+6. 每月給付金額最高以「傷害醫療保險金日額」的二十倍為限，累計給付金額最高以「傷害醫療保險金日額」的一千二百倍為限。  
+7. 若被保險人在給付期間內身故，未支領的部分將貼現後一次性給付予法定繼承人，貼現年利率為1.85%。
+條文依據：  
+- [第十五條 每月生活照護保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="n"/>
+      <c r="K39" s="3" t="n"/>
+      <c r="L39" s="3" t="n"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2026-03-15 19:02:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>重大燒燙傷保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+重大燒燙傷保險金的給付條件為：被保險人在本契約有效期間內因「意外傷害事故」導致燒燙傷，且經診斷符合「重大燒燙傷」的定義時，本公司將按「傷害醫療保險金日額」的二百五十倍給付「重大燒燙傷保險金」。該保險金的給付以一次為限。
+條文依據：  
+- [第十六條 重大燒燙傷保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 重大燒燙傷保險金的給付 | 第二十五條 重大燒燙傷保險金的申領 | 第五條 保險範圍 | payout_items | 第二十九條 除外責任（原因）</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+重大燒燙傷保險金的給付條件為：被保險人在本契約有效期間內因「意外傷害事故」導致燒燙傷，且經診斷符合「重大燒燙傷」的定義時，本公司將按「傷害醫療保險金日額」的二百五十倍給付「重大燒燙傷保險金」。該保險金的給付以一次為限。
+條文依據：  
+- [第十六條 重大燒燙傷保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="n"/>
+      <c r="K40" s="3" t="n"/>
+      <c r="L40" s="3" t="n"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2026-03-15 19:02:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>意外骨折保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外骨折保險金的給付條件如下：  
+1. 被保險人於本契約有效期間內遭受「意外傷害事故」，並於事故發生後一百八十日內經合格醫院或診所診斷為附表三骨折別表所列骨折項目之一（含不完全骨折及骨骼龜裂），本公司按「傷害醫療保險金日額」的二倍給付意外骨折保險金。  
+2. 若被保險人於事故發生後超過一百八十日才確診骨折，但能證明骨折與該意外傷害事故具有因果關係，本公司仍依上述規定給付意外骨折保險金，不受一百八十日的限制。  
+3. 同一意外傷害事故僅給付一次意外骨折保險金。  
+4. 若骨折部位不屬於附表三骨折別表所列項目，則由本公司與被保險人協議核付意外骨折保險金。  
+5. 若骨折部位為骨折別表內明訂不給付之部位，則本公司不負給付保險金之責。
+條文依據：  
+- [第十七條 意外骨折保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>第十七條 意外骨折保險金的給付 | 第十八條 傷害醫療日額保險金的給付 | 第二十六條 意外骨折保險金的申領 | 第十三條 意外事故失能保險金的給付 | 第十九條 意外創傷縫合處置保險金的給付 | 附表二：失能程度與保險金給付表 | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外骨折保險金的給付條件如下：  
+1. 被保險人於本契約有效期間內遭受「意外傷害事故」，並於事故發生後一百八十日內經合格醫院或診所診斷為附表三骨折別表所列骨折項目之一（含不完全骨折及骨骼龜裂），本公司按「傷害醫療保險金日額」的二倍給付意外骨折保險金。  
+2. 若被保險人於事故發生後超過一百八十日才確診骨折，但能證明骨折與該意外傷害事故具有因果關係，本公司仍依上述規定給付意外骨折保險金，不受一百八十日的限制。  
+3. 同一意外傷害事故僅給付一次意外骨折保險金。  
+4. 若骨折部位不屬於附表三骨折別表所列項目，則由本公司與被保險人協議核付意外骨折保險金。  
+5. 若骨折部位為骨折別表內明訂不給付之部位，則本公司不負給付保險金之責。
+條文依據：  
+- [第十七條 意外骨折保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="n"/>
+      <c r="K41" s="3" t="n"/>
+      <c r="L41" s="3" t="n"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2026-03-15 19:02:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>傷害醫療日額保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+傷害醫療日額保險金的給付條件如下：  
+1. 被保險人於保險契約有效期間內遭受「意外傷害事故」，並於事故發生後180日內在「醫院」接受住院治療者，本公司按「傷害醫療保險金日額」乘以實際住院日數給付，但每次事故最高給付日數為90日。  
+2. 若事故發生後超過180日仍需繼續治療，且受益人能證明治療與事故具有因果關係者，本公司仍依上述規定給付，不受180日限制。  
+3. 若因意外事故骨折但未住院，或住院日數未達附表三骨折別表所訂日數，則未住院部分按骨折別表所訂日數乘以「傷害醫療保險金日額」的二分之一給付，合計給付日數以骨折別表所訂日數為上限。  
+4. 骨折類型的給付：完全骨折按骨折別表日數給付；不完全骨折按完全骨折日數的二分之一給付；骨骼龜裂按完全骨折日數的四分之一給付。同時發生多項骨折時，僅給付一項較高等級的保險金。
+條文依據：  
+- [第十八條 傷害醫療日額保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 傷害醫療日額保險金的給付 | 第二十七條 傷害醫療日額保險金的申領 | 第十五條 每月生活照護保險金的給付 | 第三十四條 傷害醫療保險金日額之減少 | 第十九條 意外創傷縫合處置保險金的給付 | 附表二：失能程度與保險金給付表 | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+傷害醫療日額保險金的給付條件如下：  
+1. 被保險人於保險契約有效期間內遭受「意外傷害事故」，並於事故發生後180日內在「醫院」接受住院治療者，本公司按「傷害醫療保險金日額」乘以實際住院日數給付，但每次事故最高給付日數為90日。  
+2. 若事故發生後超過180日仍需繼續治療，且受益人能證明治療與事故具有因果關係者，本公司仍依上述規定給付，不受180日限制。  
+3. 若因意外事故骨折但未住院，或住院日數未達附表三骨折別表所訂日數，則未住院部分按骨折別表所訂日數乘以「傷害醫療保險金日額」的二分之一給付，合計給付日數以骨折別表所訂日數為上限。  
+4. 骨折類型的給付：完全骨折按骨折別表日數給付；不完全骨折按完全骨折日數的二分之一給付；骨骼龜裂按完全骨折日數的四分之一給付。同時發生多項骨折時，僅給付一項較高等級的保險金。
+條文依據：  
+- [第十八條 傷害醫療日額保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="n"/>
+      <c r="K42" s="3" t="n"/>
+      <c r="L42" s="3" t="n"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2026-03-15 19:03:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>意外創傷縫合處置保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外創傷縫合處置保險金的給付條件為：被保險人在本契約有效期間內因「意外傷害事故」，於「醫院」或「診所」經醫師診斷必須接受創傷縫合處置治療且已接受縫合處置者，本公司按「傷害醫療保險金日額」給付「意外創傷縫合處置保險金」。同一意外傷害事故僅給付一次。
+條文依據：  
+- [第十九條 意外創傷縫合處置保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 意外創傷縫合處置保險金的給付 | 第二十八條 意外創傷縫合處置保險金的申領 | 第五條 保險範圍 | 第十七條 意外骨折保險金的給付 | payout_items | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外創傷縫合處置保險金的給付條件為：被保險人在本契約有效期間內因「意外傷害事故」，於「醫院」或「診所」經醫師診斷必須接受創傷縫合處置治療且已接受縫合處置者，本公司按「傷害醫療保險金日額」給付「意外創傷縫合處置保險金」。同一意外傷害事故僅給付一次。
+條文依據：  
+- [第十九條 意外創傷縫合處置保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr"/>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="n"/>
+      <c r="K43" s="3" t="n"/>
+      <c r="L43" s="3" t="n"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2026-03-15 19:03:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>因意外導致視力衰退，是否能申請理賠?</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若因意外導致視力衰退，需符合以下條件才能申請理賠：  
+1. 視力永久在萬國式視力表0.02以下，或眼球喪失、摘出，或僅能辨明暗、辨眼前一公尺以內手動、或辨眼前五公分以內指數者，視為「失明」。  
+2. 以自傷害之日起經過六個月的治療為判定原則，但若為眼球摘出等明顯無法復原的情況，則不受此六個月限制。  
+條文依據：  
+- 註2</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>第二十三條 意外事故失能保險金的申領 | 第十三條 意外事故失能保險金的給付 | 註2： | 第三十條 不保事項 | 第二十六條 意外骨折保險金的申領 | 附表二：失能程度與保險金給付表</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若因意外導致視力衰退，需符合以下條件才能申請理賠：  
+1. 視力永久在萬國式視力表0.02以下，或眼球喪失、摘出，或僅能辨明暗、辨眼前一公尺以內手動、或辨眼前五公分以內指數者，視為「失明」。  
+2. 以自傷害之日起經過六個月的治療為判定原則，但若為眼球摘出等明顯無法復原的情況，則不受此六個月限制。  
+條文依據：  
+- 註2</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr"/>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="n"/>
+      <c r="K44" s="3" t="n"/>
+      <c r="L44" s="3" t="n"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2026-03-15 19:03:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>肋骨骨折是否可以申請理賠?理賠金額為多少?</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+肋骨骨折可以申請理賠，理賠金額需依據以下情況計算：  
+1. 若被保險人因意外傷害事故導致肋骨完全骨折且未住院治療，則按附表三骨折別表所訂日數（20天）乘以「傷害醫療保險金日額」的二分之一給付。  
+2. 若為不完全骨折，則按完全骨折日數的二分之一（10天）給付；若為骨骼龜裂，則按完全骨折日數的四分之一（5天）給付。  
+3. 若被保險人住院治療，則按實際住院日數乘以「傷害醫療保險金日額」給付，但每次意外傷害事故的給付日數最高以90日為限。
+條文依據：  
+- [第十八條 傷害醫療日額保險金的給付]  
+- [附表三：骨折別表]</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 傷害醫療日額保險金的給付 | 第十七條 意外骨折保險金的給付 | 第二十六條 意外骨折保險金的申領 | 第三十條 不保事項 | 第五條 保險範圍 | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+肋骨骨折可以申請理賠，理賠金額需依據以下情況計算：  
+1. 若被保險人因意外傷害事故導致肋骨完全骨折且未住院治療，則按附表三骨折別表所訂日數（20天）乘以「傷害醫療保險金日額」的二分之一給付。  
+2. 若為不完全骨折，則按完全骨折日數的二分之一（10天）給付；若為骨骼龜裂，則按完全骨折日數的四分之一（5天）給付。  
+3. 若被保險人住院治療，則按實際住院日數乘以「傷害醫療保險金日額」給付，但每次意外傷害事故的給付日數最高以90日為限。
+條文依據：  
+- [第十八條 傷害醫療日額保險金的給付]  
+- [附表三：骨折別表]</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr"/>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="n"/>
+      <c r="K45" s="3" t="n"/>
+      <c r="L45" s="3" t="n"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2026-03-15 19:03:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>投保新鍾心滿福後，假設投保保額為100萬元，於第二保單年度接受「移植器官」，這樣可以領多少保險金?</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在第二保單年度接受「移植器官」，符合「特定重大傷病」的定義，保險公司將給付「重大傷病保險金」及「特定重大傷病保險金」。其中，「特定重大傷病保險金」為保險金額的20%。假設投保保額為100萬元，則「特定重大傷病保險金」為20萬元。  
+條文依據：  
+- [第十三條 特定重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>附表一：全民健康保險重大傷病項目 | 第二條 名詞定義 | 第十三條 特定重大傷病保險金的給付 | 第十五條 滿期保險金的給付 | 附表二：完全失能程度表</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在第二保單年度接受「移植器官」，符合「特定重大傷病」的定義，保險公司將給付「重大傷病保險金」及「特定重大傷病保險金」。其中，「特定重大傷病保險金」為保險金額的20%。假設投保保額為100萬元，則「特定重大傷病保險金」為20萬元。  
+條文依據：  
+- [第十三條 特定重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr"/>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="n"/>
+      <c r="K46" s="3" t="n"/>
+      <c r="L46" s="3" t="n"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2026-03-15 19:04:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>投保新鍾心滿福後，若要理賠重大傷病保險金，一定要檢附全民健保開立的重大傷病證明才能拿到保險金嗎?</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不一定需要檢附全民健保開立的重大傷病證明。若被保險人已取得一家「區域醫院」層級以上（含）之醫療院所開立且符合投保當時「重大傷病範圍」的診斷書及當次「重大傷病」病歷摘要，亦可作為重大傷病證明文件，免向全民健康保險保險人申請。此外，若因全民健康保險保險人變更或調整重大傷病項目，導致無法取得重大傷病證明文件時，也可依條款規定以其他文件替代。  
+條文依據：  
+- [第二十二條 重大傷病保險金、特定重大傷病保險金的申領]  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>第二十二條 重大傷病保險金、特定重大傷病保險金的申領 | 第十二條 重大傷病保險金的給付 | 第三十條 不保事項 | 第二條 名詞定義 | other_metadata | 附表一：全民健康保險重大傷病項目</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不一定需要檢附全民健保開立的重大傷病證明。若被保險人已取得一家「區域醫院」層級以上（含）之醫療院所開立且符合投保當時「重大傷病範圍」的診斷書及當次「重大傷病」病歷摘要，亦可作為重大傷病證明文件，免向全民健康保險保險人申請。此外，若因全民健康保險保險人變更或調整重大傷病項目，導致無法取得重大傷病證明文件時，也可依條款規定以其他文件替代。  
+條文依據：  
+- [第二十二條 重大傷病保險金、特定重大傷病保險金的申領]  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr"/>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="n"/>
+      <c r="K47" s="3" t="n"/>
+      <c r="L47" s="3" t="n"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2026-03-15 19:05:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>一定要有健保身分才能申請重大傷病理賠嗎？</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，被保險人需具備全民健康保險被保險人資格，並取得重大傷病證明，才能申請重大傷病保險金。然而，若被保險人喪失全民健康保險被保險人資格，需先重新申請加保全民健康保險後，方可申請重大傷病保險金的給付。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>第二十二條 重大傷病保險金、特定重大傷病保險金的申領 | 第十二條 重大傷病保險金的給付 | other_metadata | 第三十條 不保事項 | 第二條 名詞定義 | 附表一：全民健康保險重大傷病項目</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，被保險人需具備全民健康保險被保險人資格，並取得重大傷病證明，才能申請重大傷病保險金。然而，若被保險人喪失全民健康保險被保險人資格，需先重新申請加保全民健康保險後，方可申請重大傷病保險金的給付。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="n"/>
+      <c r="K48" s="3" t="n"/>
+      <c r="L48" s="3" t="n"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2026-03-15 19:05:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>重大傷病的項目如果在投保後有新增，可以從優申請理賠嗎？</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以從優申請理賠。根據條款，重大傷病的範圍包含「全民健康保險重大傷病項目及其證明有效期限」，且明確指出「包含本契約『訂立時』及『有效期間內被保險人診斷確定當時』由中央衛生主管機關公告之重大傷病項目」。因此，若投保後重大傷病項目有新增，且被保險人於有效期間內診斷確定符合新增項目，則可依新增項目申請理賠。
+條文依據：  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>附表一：全民健康保險重大傷病項目 | 第二條 名詞定義 | payout_items</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以從優申請理賠。根據條款，重大傷病的範圍包含「全民健康保險重大傷病項目及其證明有效期限」，且明確指出「包含本契約『訂立時』及『有效期間內被保險人診斷確定當時』由中央衛生主管機關公告之重大傷病項目」。因此，若投保後重大傷病項目有新增，且被保險人於有效期間內診斷確定符合新增項目，則可依新增項目申請理賠。
+條文依據：  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr"/>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="n"/>
+      <c r="K49" s="3" t="n"/>
+      <c r="L49" s="3" t="n"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2026-03-15 19:05:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>我的保單之前有停效，在復效後五天被診斷出重大疾病是否可申請理賠？</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以申請理賠，但需符合以下條件：  
+1. 復效後的契約有效期間內，被保險人經醫師診斷確定罹患「重大傷病」。  
+2. 若重大傷病是因意外傷害事故所致，則不受等待期間限制；若非因意外傷害事故，則需等待期間屆滿翌日後才可申請理賠。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 重大傷病保險金的給付 | 第八條 本契約效力的恢復 | 第二條 名詞定義 | 第三十條 不保事項 | 附表一：全民健康保險重大傷病項目</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以申請理賠，但需符合以下條件：  
+1. 復效後的契約有效期間內，被保險人經醫師診斷確定罹患「重大傷病」。  
+2. 若重大傷病是因意外傷害事故所致，則不受等待期間限制；若非因意外傷害事故，則需等待期間屆滿翌日後才可申請理賠。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="n"/>
+      <c r="K50" s="3" t="n"/>
+      <c r="L50" s="3" t="n"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2026-03-15 19:06:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>領完重大傷病保險金，主約終止後，附約可以繼續有效嗎?</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以。根據條文規定，若主約因重大傷病診斷確定而終止時，要保人於附約的有效期間內，仍可繼續繳交附約的保險費，以延續附約的效力。
+條文依據：  
+- [第十一條 契約的終止（二）]</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 契約的終止（二） | 第十二條 重大傷病保險金的給付 | 第三十條 不保事項 | 第五條 保險範圍 | payout_items | 附表一：全民健康保險重大傷病項目</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以。根據條文規定，若主約因重大傷病診斷確定而終止時，要保人於附約的有效期間內，仍可繼續繳交附約的保險費，以延續附約的效力。
+條文依據：  
+- [第十一條 契約的終止（二）]</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="n"/>
+      <c r="K51" s="3" t="n"/>
+      <c r="L51" s="3" t="n"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2026-03-15 19:07:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Q1：因為慢性精神病的保險給付僅有保額的20%，我可以先不申請給付，等之後發生其他重大傷病後，再申請重大傷病保險金嗎?Q2：但如果我不申請，保險公司不會知道我有罹患慢性精神病阿，所以我就可以領之後的重大傷病100%保額嗎?</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+Q1：根據條款規定，若被保險人同時或先後罹患兩項以上的重大傷病，保險公司僅給付一項「重大傷病保險金」。因此，即使您選擇不立即申請慢性精神病的保險金，未來若發生其他重大傷病，保險公司仍只會給付其中一項的保險金，且金額將依條款規定計算，並不會因未申請慢性精神病的保險金而影響給付金額。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]
+Q2：即使您未申請慢性精神病的保險金，保險公司在審核未來的重大傷病保險金申請時，仍會依據相關醫療紀錄及診斷書進行審核。如果發現您已罹患慢性精神病，則仍會依條款規定，僅給付一項「重大傷病保險金」，並按條款中對慢性精神病的給付比例計算。因此，未申請慢性精神病保險金並不會使您在未來的重大傷病保險金申請中獲得100%保額。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第二十二條 重大傷病保險金、特定重大傷病保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 重大傷病保險金的給付 | 第十三條 特定重大傷病保險金的給付 | 附表一：全民健康保險重大傷病項目 | 第二十二條 重大傷病保險金、特定重大傷病保險金的申領 | 第三十條 不保事項</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+Q1：根據條款規定，若被保險人同時或先後罹患兩項以上的重大傷病，保險公司僅給付一項「重大傷病保險金」。因此，即使您選擇不立即申請慢性精神病的保險金，未來若發生其他重大傷病，保險公司仍只會給付其中一項的保險金，且金額將依條款規定計算，並不會因未申請慢性精神病的保險金而影響給付金額。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]
+Q2：即使您未申請慢性精神病的保險金，保險公司在審核未來的重大傷病保險金申請時，仍會依據相關醫療紀錄及診斷書進行審核。如果發現您已罹患慢性精神病，則仍會依條款規定，僅給付一項「重大傷病保險金」，並按條款中對慢性精神病的給付比例計算。因此，未申請慢性精神病保險金並不會使您在未來的重大傷病保險金申請中獲得100%保額。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第二十二條 重大傷病保險金、特定重大傷病保險金的申領]</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr"/>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="n"/>
+      <c r="K52" s="3" t="n"/>
+      <c r="L52" s="3" t="n"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2026-03-15 19:07:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>失智症會賠嗎？賠多少？</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條文內容，失智症是否賠付需視其是否符合「重大傷病」的範圍。若失智症被中央衛生主管機關公告為「全民健康保險重大傷病項目」且取得相關重大傷病證明，或符合投保當時「重大傷病範圍」的診斷書及病歷摘要，則可申請「重大傷病保險金」。賠付金額依初次診斷確定罹患重大傷病時的保險單年度計算，具體如下：  
+1. 第一保險單年度：「年繳應繳保險費總額」的1.05倍。  
+2. 第二保險單年度（含）以後：  
+   - 若屬於「慢性精神病」範圍：「保險金額的20%」或「年繳應繳保險費總額的1.05倍」，取其大者。  
+   - 若不屬於「慢性精神病」範圍：「保險金額」或「年繳應繳保險費總額的1.05倍」，取其大者。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [附表一：全民健康保險重大傷病項目]</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>第十七條 完全失能保險金的給付 | 第二十九條 除外責任（二） | payout_items | 第十二條 重大傷病保險金的給付 | 第三十條 不保事項 | 附表二：完全失能程度表 | 附表一：全民健康保險重大傷病項目</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條文內容，失智症是否賠付需視其是否符合「重大傷病」的範圍。若失智症被中央衛生主管機關公告為「全民健康保險重大傷病項目」且取得相關重大傷病證明，或符合投保當時「重大傷病範圍」的診斷書及病歷摘要，則可申請「重大傷病保險金」。賠付金額依初次診斷確定罹患重大傷病時的保險單年度計算，具體如下：  
+1. 第一保險單年度：「年繳應繳保險費總額」的1.05倍。  
+2. 第二保險單年度（含）以後：  
+   - 若屬於「慢性精神病」範圍：「保險金額的20%」或「年繳應繳保險費總額的1.05倍」，取其大者。  
+   - 若不屬於「慢性精神病」範圍：「保險金額」或「年繳應繳保險費總額的1.05倍」，取其大者。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [附表一：全民健康保險重大傷病項目]</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr"/>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="n"/>
+      <c r="K53" s="3" t="n"/>
+      <c r="L53" s="3" t="n"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2026-03-15 19:08:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>投保新鍾心滿福後，於第二保單年度罹患子宮頸惡性腫瘤，且已給付重大傷病保險金。第五保單年度時又罹患慢性腎衰竭，這樣還可以申領重大傷病保險金的給付嗎?</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以申領重大傷病保險金，但僅限給付一項「重大傷病保險金」。根據條文，被保險人同時或先後罹患兩項以上「重大傷病」時，本公司僅給付一項「重大傷病保險金」。因此，若已於第二保單年度因子宮頸惡性腫瘤獲得重大傷病保險金，第五保單年度罹患慢性腎衰竭則無法再次申領。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 重大傷病保險金的給付 | 附表一：全民健康保險重大傷病項目 | 第二條 名詞定義 | 第二十二條 重大傷病保險金、特定重大傷病保險金的申領</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以申領重大傷病保險金，但僅限給付一項「重大傷病保險金」。根據條文，被保險人同時或先後罹患兩項以上「重大傷病」時，本公司僅給付一項「重大傷病保險金」。因此，若已於第二保單年度因子宮頸惡性腫瘤獲得重大傷病保險金，第五保單年度罹患慢性腎衰竭則無法再次申領。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr"/>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="n"/>
+      <c r="K54" s="3" t="n"/>
+      <c r="L54" s="3" t="n"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2026-03-15 19:08:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>12歲的被保險人可以有健康促進保險費折減嗎？</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+12歲的被保險人無法享有健康促進保險費折減，因為根據條款規定，健康促進保險費折減的適用對象為「實際年齡達十八歲（含）以上之被保險人」。
+條文依據：  
+- [第十九條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 健康促進保險費折減 | 第三十八條 投保年齡的計算及錯誤的處理 | 第三十四條 減額繳清保險 | 第二條 名詞定義 | 第十六條 所繳保險費加計利息的退還、身故保險金或喪葬費用保險金的給付 | 附表二：完全失能程度表</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+12歲的被保險人無法享有健康促進保險費折減，因為根據條款規定，健康促進保險費折減的適用對象為「實際年齡達十八歲（含）以上之被保險人」。
+條文依據：  
+- [第十九條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr"/>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="n"/>
+      <c r="K55" s="3" t="n"/>
+      <c r="L55" s="3" t="n"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2026-03-15 19:09:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>ZDN</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>被保險人於投保鍾心滿溢後的第10天就罹患慢性腎衰竭，請問可以申領重大傷病保險金嗎？</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不可以申領重大傷病保險金。根據條款，慢性腎衰竭屬於重大傷病範圍，但若被保險人於等待期間內（本契約生效日起30日內）罹患重大傷病，且非因意外傷害事故所致，則本契約自始無效，本公司僅退還已繳保險費，且不給付重大傷病保險金。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第三十條 不保事項]</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>第二十二條 重大傷病保險金、特定重大傷病保險金的申領 | 第二條 名詞定義 | 第十二條 重大傷病保險金的給付 | 第三十條 不保事項 | 附表一：全民健康保險重大傷病項目</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不可以申領重大傷病保險金。根據條款，慢性腎衰竭屬於重大傷病範圍，但若被保險人於等待期間內（本契約生效日起30日內）罹患重大傷病，且非因意外傷害事故所致，則本契約自始無效，本公司僅退還已繳保險費，且不給付重大傷病保險金。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第三十條 不保事項]</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr"/>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="n"/>
+      <c r="K56" s="3" t="n"/>
+      <c r="L56" s="3" t="n"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2026-03-15 19:09:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>CFE</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>投保自由配重大傷病後，若在契約生效後80天罹患第一期乳癌，會拿到理賠金嗎?</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不會拿到理賠金。根據條款，第一期乳癌屬於「需積極或長期治療之癌症」範圍，等待期間為契約生效日起90天。若被保險人在等待期間內（如本例的80天）罹患重大傷病，則契約自始無效，本公司無息退還已繳保險費予要保人。
+條文依據：  
+- [第二條 名詞定義]  
+- [第十一條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>第二條 名詞定義 | 附表一：全民健康保險重大傷病項目 | 第十一條 重大傷病保險金的給付 | 第十五條 不保事項 | 第十四條 除外責任</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不會拿到理賠金。根據條款，第一期乳癌屬於「需積極或長期治療之癌症」範圍，等待期間為契約生效日起90天。若被保險人在等待期間內（如本例的80天）罹患重大傷病，則契約自始無效，本公司無息退還已繳保險費予要保人。
+條文依據：  
+- [第二條 名詞定義]  
+- [第十一條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr"/>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="n"/>
+      <c r="K57" s="3" t="n"/>
+      <c r="L57" s="3" t="n"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2026-03-15 19:10:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>CFE</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>要保人想要終止國泰人壽自由配CFE契約，能否退保費?</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+要保人可以終止契約，並退還未到期保險費。根據條款規定，契約終止後，本公司會從當期已繳保險費中扣除按短期費率計算已經過期間的保險費，將剩餘的未到期保險費無息退還給要保人。
+條文依據：  
+- [第九條 契約的終止（一）]</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>第九條 契約的終止（一） | 第十五條 不保事項 | 第五條 契約有效期間及保證續保 | 第七條 本契約效力的恢復 | 第六條 續保保險費的交付、寬限期間及契約效力的停止 | 附表二：短期費率表</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+要保人可以終止契約，並退還未到期保險費。根據條款規定，契約終止後，本公司會從當期已繳保險費中扣除按短期費率計算已經過期間的保險費，將剩餘的未到期保險費無息退還給要保人。
+條文依據：  
+- [第九條 契約的終止（一）]</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr"/>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="n"/>
+      <c r="K58" s="3" t="n"/>
+      <c r="L58" s="3" t="n"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2026-03-15 19:11:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>CFE</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>投保國泰人壽自由配CFE，若在等待期間內罹患重大傷病，要如何給付?</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在等待期間內罹患「重大傷病」，且該重大傷病並非因意外傷害事故所致，則本契約自始無效，本公司將無息退還已繳保險費予要保人。然而，若重大傷病係因意外傷害事故所致，則不受等待期間限制，本公司仍會依約給付「重大傷病保險金」。
+條文依據：  
+- [第十一條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 重大傷病保險金的給付 | 第十五條 不保事項 | 第十四條 除外責任 | payout_items | 附表一：全民健康保險重大傷病項目</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在等待期間內罹患「重大傷病」，且該重大傷病並非因意外傷害事故所致，則本契約自始無效，本公司將無息退還已繳保險費予要保人。然而，若重大傷病係因意外傷害事故所致，則不受等待期間限制，本公司仍會依約給付「重大傷病保險金」。
+條文依據：  
+- [第十一條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr"/>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="n"/>
+      <c r="K59" s="3" t="n"/>
+      <c r="L59" s="3" t="n"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>2026-03-15 19:11:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>CFE</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>投保自由配一年定期初次罹患重大傷病健康保險後，於第三年罹患先天性肌肉萎縮症，可以申領重大傷病保險金嗎？</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不可以申領重大傷病保險金。根據條款，先天性肌肉萎縮症（Congenital muscular dystrophy）不屬於「全民健康保險重大傷病項目」中列為符合給付條件的疾病，因此不符合重大傷病保險金的給付範圍。
+條文依據：  
+- [附表一：全民健康保險重大傷病項目]</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 重大傷病保險金的給付 | 第十三條 重大傷病保險金的申領 | 附表一：全民健康保險重大傷病項目 | 第十五條 不保事項 | other_metadata</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不可以申領重大傷病保險金。根據條款，先天性肌肉萎縮症（Congenital muscular dystrophy）不屬於「全民健康保險重大傷病項目」中列為符合給付條件的疾病，因此不符合重大傷病保險金的給付範圍。
+條文依據：  
+- [附表一：全民健康保險重大傷病項目]</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr"/>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="n"/>
+      <c r="K60" s="3" t="n"/>
+      <c r="L60" s="3" t="n"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>2026-03-15 19:12:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>CFG</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>自由配重大疾病(甲型)保障的重大疾病有哪些疾病?</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+自由配重大疾病(甲型)保障的重大疾病包括以下疾病：  
+1. 腦中風後障礙(重度)  
+2. 癱瘓(重度)  
+3. 癌症(重度)  
+4. 急性心肌梗塞(重度)  
+5. 冠狀動脈繞道手術  
+6. 末期腎病變  
+7. 重大器官移植或造血幹細胞移植  
+條文依據：  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>國泰人壽自由配一年定期初次罹患重大疾病健康保險(甲型)年繳費率表 | payout_items | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+自由配重大疾病(甲型)保障的重大疾病包括以下疾病：  
+1. 腦中風後障礙(重度)  
+2. 癱瘓(重度)  
+3. 癌症(重度)  
+4. 急性心肌梗塞(重度)  
+5. 冠狀動脈繞道手術  
+6. 末期腎病變  
+7. 重大器官移植或造血幹細胞移植  
+條文依據：  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr"/>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J61" s="3" t="n"/>
+      <c r="K61" s="3" t="n"/>
+      <c r="L61" s="3" t="n"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>2026-03-15 19:13:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>被保險人領了2次癌症(重度)追蹤照護金後身故，是否還有尚未給付的保險金供受益人領取?</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條文，被保險人若已領取2次「癌症(重度)追蹤照護保險金」後身故，則無其他尚未給付的「癌症(重度)追蹤照護保險金」可供受益人領取。因為「癌症(重度)追蹤照護保險金」的給付條件為被保險人於保險單週年日仍生存，且最多給付5年，若被保險人已身故，則不再符合給付條件。
+條文依據：  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用) | 第二十三條 癌症保險金或罹癌基因檢測服務的申領 | 第十三條 初次罹患癌症(重度)保險金的給付 | 第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用) | 第二十二條 保險事故的通知與保險給付的申請時間</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條文，被保險人若已領取2次「癌症(重度)追蹤照護保險金」後身故，則無其他尚未給付的「癌症(重度)追蹤照護保險金」可供受益人領取。因為「癌症(重度)追蹤照護保險金」的給付條件為被保險人於保險單週年日仍生存，且最多給付5年，若被保險人已身故，則不再符合給付條件。
+條文依據：  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr"/>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="n"/>
+      <c r="K62" s="3" t="n"/>
+      <c r="L62" s="3" t="n"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>2026-03-15 19:13:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>保險金額2萬元，「罹癌基因檢測服務」費用8萬元，還會給付多少「癌症(重度)追蹤照護保險金」？</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若「罹癌基因檢測服務」費用高於「罹癌基因檢測服務額度」（附件一中補償金額為新臺幣1,000元），則被保險人僅能申領「癌症(重度)追蹤照護保險金」。因此，若保險金額為2萬元，則「癌症(重度)追蹤照護保險金」的給付金額為2萬元的12倍，即24萬元。
+條文依據：  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]  
+- [附件一：罹癌基因檢測服務之項目、服務費用及補償金額表]</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用) | 第二十三條 癌症保險金或罹癌基因檢測服務的申領 | 附件一：罹癌基因檢測服務之項目、服務費用及補償金額表 | 第十三條 初次罹患癌症(重度)保險金的給付 | 第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用)</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若「罹癌基因檢測服務」費用高於「罹癌基因檢測服務額度」（附件一中補償金額為新臺幣1,000元），則被保險人僅能申領「癌症(重度)追蹤照護保險金」。因此，若保險金額為2萬元，則「癌症(重度)追蹤照護保險金」的給付金額為2萬元的12倍，即24萬元。
+條文依據：  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]  
+- [附件一：罹癌基因檢測服務之項目、服務費用及補償金額表]</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr"/>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J63" s="3" t="n"/>
+      <c r="K63" s="3" t="n"/>
+      <c r="L63" s="3" t="n"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>2026-03-15 19:14:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>投保後1個月罹患重度癌症，會給付哪些保險金？契約還會持續有效嗎？</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 若被保險人在投保後1個月內診斷確定罹患「癌症(重度)」，符合「初次診斷確定罹患癌症(重度)」的條件，則可申領「初次罹患癌症(重度)保險金」。依條文規定，診斷確定日在第一保險單年度內，給付金額為「年繳應繳保險費」的一點零六倍。  
+2. 契約仍會持續有效，但當期已繳付之未到期保險費將不予退還，且續期保險費不會豁免，因豁免條款僅適用於第二保險單年度(含)以後。
+條文依據：  
+- [第十三條 初次罹患癌症(重度)保險金的給付]  
+- [第十六條 癌症(重度)豁免保險費(第二保險單年度起適用)]</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 癌症(重度)豁免保險費(第二保險單年度起適用) | 第十三條 初次罹患癌症(重度)保險金的給付 | 第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用) | 第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付 | 第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用)</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 若被保險人在投保後1個月內診斷確定罹患「癌症(重度)」，符合「初次診斷確定罹患癌症(重度)」的條件，則可申領「初次罹患癌症(重度)保險金」。依條文規定，診斷確定日在第一保險單年度內，給付金額為「年繳應繳保險費」的一點零六倍。  
+2. 契約仍會持續有效，但當期已繳付之未到期保險費將不予退還，且續期保險費不會豁免，因豁免條款僅適用於第二保險單年度(含)以後。
+條文依據：  
+- [第十三條 初次罹患癌症(重度)保險金的給付]  
+- [第十六條 癌症(重度)豁免保險費(第二保險單年度起適用)]</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr"/>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="n"/>
+      <c r="K64" s="3" t="n"/>
+      <c r="L64" s="3" t="n"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>2026-03-15 19:14:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>投保後10個月罹患重度癌症，會給付哪些保險金？契約還會持續有效嗎？</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 若被保險人在投保後10個月（即第一保險單年度內）診斷確定罹患重度癌症，依據條款規定，本公司將給付「初次罹患癌症(重度)保險金」，金額為「年繳應繳保險費」的一點零六倍。  
+2. 契約將持續有效，因條款中未提及此情況下契約會終止的規定。
+條文依據：  
+- [第十三條 初次罹患癌症(重度)保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 癌症(重度)豁免保險費(第二保險單年度起適用) | 第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用) | 第十條 契約的終止（二） | 第十三條 初次罹患癌症(重度)保險金的給付 | 第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 若被保險人在投保後10個月（即第一保險單年度內）診斷確定罹患重度癌症，依據條款規定，本公司將給付「初次罹患癌症(重度)保險金」，金額為「年繳應繳保險費」的一點零六倍。  
+2. 契約將持續有效，因條款中未提及此情況下契約會終止的規定。
+條文依據：  
+- [第十三條 初次罹患癌症(重度)保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr"/>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J65" s="3" t="n"/>
+      <c r="K65" s="3" t="n"/>
+      <c r="L65" s="3" t="n"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>2026-03-15 19:15:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>投保醫心康愛，罹患肺癌一期，可領什麼保險金？</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人罹患肺癌一期，屬於「癌症(初期)或癌症(輕度)」，可申領「初次罹患癌症(初期)或癌症(輕度)保險金」。給付金額依診斷確定日所在的保險單年度而定：  
+1. 若診斷確定日在第一保險單年度內，給付「年繳應繳保險費」的1.06倍。  
+2. 若診斷確定日在第二保險單年度(含)以後，給付「保險金額」的5倍。  
+條文依據：  
+- [第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付 | 第十三條 初次罹患癌症(重度)保險金的給付 | payout_items | 第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用) | 第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人罹患肺癌一期，屬於「癌症(初期)或癌症(輕度)」，可申領「初次罹患癌症(初期)或癌症(輕度)保險金」。給付金額依診斷確定日所在的保險單年度而定：  
+1. 若診斷確定日在第一保險單年度內，給付「年繳應繳保險費」的1.06倍。  
+2. 若診斷確定日在第二保險單年度(含)以後，給付「保險金額」的5倍。  
+條文依據：  
+- [第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr"/>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J66" s="3" t="n"/>
+      <c r="K66" s="3" t="n"/>
+      <c r="L66" s="3" t="n"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>2026-03-15 19:15:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>PX5</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>若被保險人身故有何給付?</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人身故，且本附約保險金尚未給付或未完全給付，則該部分保險金的受益人為被保險人的法定繼承人，並依據被保險人身故時的法定繼承人順序及應得比例，適用民法繼承編的相關規定。
+條文依據：  
+- [第二十條 受益人]</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>第二十條 受益人 | 第十二條 重大疾病保險金的給付 | 第十一條 輕度重大疾病保險金的給付 | 第十四條 保險事故的通知與保險金的申請時間 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人身故，且本附約保險金尚未給付或未完全給付，則該部分保險金的受益人為被保險人的法定繼承人，並依據被保險人身故時的法定繼承人順序及應得比例，適用民法繼承編的相關規定。
+條文依據：  
+- [第二十條 受益人]</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr"/>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J67" s="3" t="n"/>
+      <c r="K67" s="3" t="n"/>
+      <c r="L67" s="3" t="n"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>2026-03-15 19:15:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>PX5</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>投保鍾溢祝福後，請問在第二年經醫院醫師初次診斷罹患「輕度重大疾病」中的癌症(輕度)者，可以領到輕度重大疾病保險金嗎?可以領到保險金額的百分之多少?</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以領到輕度重大疾病保險金，保險金額為保險金額的百分之二十。根據條款規定，若被保險人在續保年度內經醫院醫師初次診斷罹患「輕度重大疾病」中的「癌症(輕度)」，可獲得保險金額的百分之二十。
+條文依據：  
+- [第十一條 輕度重大疾病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 輕度重大疾病保險金的給付 | 第十二條 重大疾病保險金的給付 | payout_items | other_metadata | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以領到輕度重大疾病保險金，保險金額為保險金額的百分之二十。根據條款規定，若被保險人在續保年度內經醫院醫師初次診斷罹患「輕度重大疾病」中的「癌症(輕度)」，可獲得保險金額的百分之二十。
+條文依據：  
+- [第十一條 輕度重大疾病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr"/>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J68" s="3" t="n"/>
+      <c r="K68" s="3" t="n"/>
+      <c r="L68" s="3" t="n"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>2026-03-15 19:16:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>PX5</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>請問如果在投保後的第三年經醫院醫師初次診斷罹患「重大疾病」者，可以領到重大疾病保險金嗎?可以領到保險金額的百分之多少?那後續又在第四年經醫院醫師初次診斷罹患「輕度重大疾病」者，可以領到輕度重大疾病保險金嗎?可以領到保險金額的百分之多少?</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 在投保後的第三年經醫院醫師初次診斷罹患「重大疾病」者，可以領到重大疾病保險金，給付金額為保險金額的1.3倍。  
+2. 在第四年經醫院醫師初次診斷罹患「輕度重大疾病」者，可以領到輕度重大疾病保險金，給付金額為保險金額的20%。  
+條文依據：  
+- [第十二條 重大疾病保險金的給付]  
+- [第十一條 輕度重大疾病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 重大疾病保險金的給付 | 第十一條 輕度重大疾病保險金的給付 | payout_items | 第十六條 除外責任 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 在投保後的第三年經醫院醫師初次診斷罹患「重大疾病」者，可以領到重大疾病保險金，給付金額為保險金額的1.3倍。  
+2. 在第四年經醫院醫師初次診斷罹患「輕度重大疾病」者，可以領到輕度重大疾病保險金，給付金額為保險金額的20%。  
+條文依據：  
+- [第十二條 重大疾病保險金的給付]  
+- [第十一條 輕度重大疾病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr"/>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J69" s="3" t="n"/>
+      <c r="K69" s="3" t="n"/>
+      <c r="L69" s="3" t="n"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>2026-03-15 19:16:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>PX5</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>請問如果在投保後的第三年經醫院醫師初次診斷罹患「輕度重大疾病」者，可以領到重大疾病保險金嗎?可以領到保險金額的百分之多少?那後續又在第四年經醫院醫師初次診斷罹患「重大疾病」者，可以領到輕度重大疾病保險金嗎?可以領到保險金額的百分之多少?</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 在投保後的第三年經醫院醫師初次診斷罹患「輕度重大疾病」者，可以領到「輕度重大疾病保險金」，而非「重大疾病保險金」。根據條文，診斷確定日於續保年度，給付保險金額的百分之二十。  
+2. 在第四年經醫院醫師初次診斷罹患「重大疾病」者，無法再領取「輕度重大疾病保險金」。根據條文，若被保險人於本附約有效期間內已申領過「輕度重大疾病保險金」，則「重大疾病保險金」需扣除已給付的「輕度重大疾病保險金」，且「輕度重大疾病保險金」終身最多以給付一次為限。
+條文依據：  
+- [第十一條 輕度重大疾病保險金的給付]  
+- [第十二條 重大疾病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 重大疾病保險金的給付 | 第十一條 輕度重大疾病保險金的給付 | payout_items | 第十六條 除外責任 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 在投保後的第三年經醫院醫師初次診斷罹患「輕度重大疾病」者，可以領到「輕度重大疾病保險金」，而非「重大疾病保險金」。根據條文，診斷確定日於續保年度，給付保險金額的百分之二十。  
+2. 在第四年經醫院醫師初次診斷罹患「重大疾病」者，無法再領取「輕度重大疾病保險金」。根據條文，若被保險人於本附約有效期間內已申領過「輕度重大疾病保險金」，則「重大疾病保險金」需扣除已給付的「輕度重大疾病保險金」，且「輕度重大疾病保險金」終身最多以給付一次為限。
+條文依據：  
+- [第十一條 輕度重大疾病保險金的給付]  
+- [第十二條 重大疾病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr"/>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J70" s="3" t="n"/>
+      <c r="K70" s="3" t="n"/>
+      <c r="L70" s="3" t="n"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>2026-03-15 19:17:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>PX5</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>請問主約效力終止(因身故以外情形)，PX5還能持續有效嗎？</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+當主約效力因身故以外的情形終止時，若非因「累計申領的各項保險給付已達上限」或「遭強制執行」的情形，PX5附約效力可持續至當期已繳保險費期滿時終止。若主約效力因上述兩種情形之一終止，則PX5附約效力可於附約保險期間屆滿時，透過要保人繼續繳交附約保險費而延續，並得續保至主約原保險期間屆滿或附約最高續保年齡（80歲），以較早屆至之日為準。
+條文依據：  
+- [第十條 附約的終止（二）]</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>第十條 附約的終止（二） | 第七條 保險費的墊繳、附約的停效及復效 | 第五條 附約的保險期間及保證續保 | 第十三條 健康促進保險費折減 | 第九條 附約的終止（一）</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+當主約效力因身故以外的情形終止時，若非因「累計申領的各項保險給付已達上限」或「遭強制執行」的情形，PX5附約效力可持續至當期已繳保險費期滿時終止。若主約效力因上述兩種情形之一終止，則PX5附約效力可於附約保險期間屆滿時，透過要保人繼續繳交附約保險費而延續，並得續保至主約原保險期間屆滿或附約最高續保年齡（80歲），以較早屆至之日為準。
+條文依據：  
+- [第十條 附約的終止（二）]</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr"/>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J71" s="3" t="n"/>
+      <c r="K71" s="3" t="n"/>
+      <c r="L71" s="3" t="n"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>2026-03-15 19:18:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>請問如果於「無理賠紀錄期間」屆滿日以內罹患特定傷病，會給付多少錢?這筆錢會給付給誰?</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在「無理賠紀錄期間」屆滿日以內罹患特定傷病，保險公司將給付的金額為「保險金額」加上「年繳應繳保險費總額」乘以1.02的加總。這筆「特定傷病保險金」的受益人為被保險人本人，且不得指定或變更。
+條文依據：  
+- [第十一條 特定傷病保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第十二條 無理賠關懷保險金的給付 | 第十一條 特定傷病保險金的給付 | payout_items | 第二十七條 受益人的指定及變更</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在「無理賠紀錄期間」屆滿日以內罹患特定傷病，保險公司將給付的金額為「保險金額」加上「年繳應繳保險費總額」乘以1.02的加總。這筆「特定傷病保險金」的受益人為被保險人本人，且不得指定或變更。
+條文依據：  
+- [第十一條 特定傷病保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr"/>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J72" s="3" t="n"/>
+      <c r="K72" s="3" t="n"/>
+      <c r="L72" s="3" t="n"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>2026-03-15 19:18:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>請問如果要保人與被保險人為同一人，被保險人於「無理賠紀錄期間」屆滿日以內身故，會給付多少錢?這筆錢會給付給誰?</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若要保人與被保險人為同一人，且被保險人於「無理賠紀錄期間」屆滿日以內身故，依條款規定，本公司將給付「無理賠關懷保險金」，金額為「年繳應繳保險費總額」乘以1.02。由於無理賠關懷保險金的受益人為要保人本人，而此情況下要保人與被保險人為同一人，因此該筆保險金將給付給被保險人的法定繼承人。
+條文依據：  
+- [第十二條 無理賠關懷保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 無理賠關懷保險金的給付 | 第五條 保險範圍 | 第十一條 特定傷病保險金的給付 | 第十九條 失蹤處理 | 第二十七條 受益人的指定及變更</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若要保人與被保險人為同一人，且被保險人於「無理賠紀錄期間」屆滿日以內身故，依條款規定，本公司將給付「無理賠關懷保險金」，金額為「年繳應繳保險費總額」乘以1.02。由於無理賠關懷保險金的受益人為要保人本人，而此情況下要保人與被保險人為同一人，因此該筆保險金將給付給被保險人的法定繼承人。
+條文依據：  
+- [第十二條 無理賠關懷保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr"/>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J73" s="3" t="n"/>
+      <c r="K73" s="3" t="n"/>
+      <c r="L73" s="3" t="n"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>2026-03-15 19:19:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>請問如果要保人與被保險人為不同人，被保險人於「無理賠紀錄期間」屆滿日以內生存，且被保險人未罹患特定傷病，會給付多少錢?這筆錢會給付給誰?</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人於「無理賠紀錄期間」屆滿日以內生存，且未罹患特定傷病，則本公司將按「年繳應繳保險費總額」乘以1.02，給付「無理賠關懷保險金」。此筆保險金的受益人為要保人本人。
+條文依據：  
+- [第十二條 無理賠關懷保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 無理賠關懷保險金的給付 | 第十一條 特定傷病保險金的給付 | 第五條 保險範圍 | 第二十七條 受益人的指定及變更 | 第十九條 失蹤處理</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人於「無理賠紀錄期間」屆滿日以內生存，且未罹患特定傷病，則本公司將按「年繳應繳保險費總額」乘以1.02，給付「無理賠關懷保險金」。此筆保險金的受益人為要保人本人。
+條文依據：  
+- [第十二條 無理賠關懷保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr"/>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J74" s="3" t="n"/>
+      <c r="K74" s="3" t="n"/>
+      <c r="L74" s="3" t="n"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>2026-03-15 19:19:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>保戶如果身故，會給保險金嗎?</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保戶（被保險人）若於本契約有效期間內身故，是否給付保險金需視具體情況而定。例如：  
+1. 若被保險人於「無理賠紀錄期間」內身故，本公司依約定給付保險金。  
+2. 若被保險人因犯罪處死、拒捕或越獄致死，或要保人故意致被保險人於死，則本公司不負給付保險金的責任。  
+3. 若被保險人故意自殺，則於契約訂立或復效之日起二年內不給付保險金，但二年後故意自殺致死者，本公司仍負給付保險金的責任。  
+條文依據：  
+- [第五條 保險範圍]  
+- [第十七條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第二十八條 本契約受益人死亡或失蹤的處理 | 第十七條 除外責任（二） | 第二十三條 受益人受益權之喪失 | 第十九條 失蹤處理</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保戶（被保險人）若於本契約有效期間內身故，是否給付保險金需視具體情況而定。例如：  
+1. 若被保險人於「無理賠紀錄期間」內身故，本公司依約定給付保險金。  
+2. 若被保險人因犯罪處死、拒捕或越獄致死，或要保人故意致被保險人於死，則本公司不負給付保險金的責任。  
+3. 若被保險人故意自殺，則於契約訂立或復效之日起二年內不給付保險金，但二年後故意自殺致死者，本公司仍負給付保險金的責任。  
+條文依據：  
+- [第五條 保險範圍]  
+- [第十七條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr"/>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J75" s="3" t="n"/>
+      <c r="K75" s="3" t="n"/>
+      <c r="L75" s="3" t="n"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>2026-03-15 19:20:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>保戶如果身故，身故申領的保險金會給誰?</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人身故，身故保險金的受益人為被保險人之法定繼承人。若有其他受益人，則依原約定比例分配保險金。若受益人故意致被保險人於死或雖未致死，該受益人喪失受益權，其應得部分將按其他受益人原約定比例分配給其他受益人；若無其他受益人，保險金將作為被保險人遺產處理。
+條文依據：  
+- [第二十三條 受益人受益權之喪失]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第二十三條 受益人受益權之喪失 | 第二十七條 受益人的指定及變更 | 第二十八條 本契約受益人死亡或失蹤的處理 | 第二十二條 分期定期保險金給付申領文件、給付期限及未依限給付之效果</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人身故，身故保險金的受益人為被保險人之法定繼承人。若有其他受益人，則依原約定比例分配保險金。若受益人故意致被保險人於死或雖未致死，該受益人喪失受益權，其應得部分將按其他受益人原約定比例分配給其他受益人；若無其他受益人，保險金將作為被保險人遺產處理。
+條文依據：  
+- [第二十三條 受益人受益權之喪失]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr"/>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J76" s="3" t="n"/>
+      <c r="K76" s="3" t="n"/>
+      <c r="L76" s="3" t="n"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>2026-03-15 19:20:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>如果保戶投保繳費年期20年的滿溢寶，然後在第20保單年度身故的話，可以領到多少錢?</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+找不到相關內容  
+條文依據：  
+找不到相關內容</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>第二十六條 投保年齡的計算及錯誤的處理 | other_metadata | 第五條 保險範圍 | 第二十二條 分期定期保險金給付申領文件、給付期限及未依限給付之效果 | 第十九條 失蹤處理</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+找不到相關內容  
+條文依據：  
+找不到相關內容</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr"/>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J77" s="3" t="n"/>
+      <c r="K77" s="3" t="n"/>
+      <c r="L77" s="3" t="n"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>2026-03-15 19:21:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>被保險人為60歲女性，投保繳費期間20年期之滿溢寶特定傷病定期健康保險（定期給付型）（外溢型）100萬元，年繳應繳保險費為83,500元，年繳實繳保險費為78,490元。若被保險人於第二保險單年度自殺身故，則無理賠關懷保險金可以領到多少錢？</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人於第二保險單年度內自殺身故，根據條款規定，自契約訂立或復效之日起二年內，因被保險人故意自殺致死者，本公司不負給付無理賠關懷保險金的責任。因此，在此情況下，無理賠關懷保險金無法領取。
+條文依據：  
+- [第十七條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 無理賠關懷保險金的給付 | 第十七條 除外責任（二） | 第二十七條 受益人的指定及變更 | 第二十一條 無理賠關懷保險金的申領 | 第十九條 失蹤處理</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人於第二保險單年度內自殺身故，根據條款規定，自契約訂立或復效之日起二年內，因被保險人故意自殺致死者，本公司不負給付無理賠關懷保險金的責任。因此，在此情況下，無理賠關懷保險金無法領取。
+條文依據：  
+- [第十七條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr"/>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J78" s="3" t="n"/>
+      <c r="K78" s="3" t="n"/>
+      <c r="L78" s="3" t="n"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2026-03-15 19:22:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>請問如果第2保單年度罹患特定傷病，可以給付多少錢?給付給誰?未來還有其他保險金嗎?</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在第2保單年度罹患特定傷病，依條款規定：  
+1. **給付金額**：保險公司將依「保險金額」給付「特定傷病保險金」。  
+2. **給付對象**：保險金給付予被保險人或其指定受益人。  
+3. **未來保險金**：自初次診斷確定罹患特定傷病的次一個保險單週年日起，每逢各保險單週年日仍生存者，保險公司將按「保險金額」的36%給付「生活補助保險金」，最多給付10次。此外，保險公司將自診斷確定日起豁免續期保險費，但當期已繳付之未到期保險費不予退還。
+條文依據：  
+- [第十二條 特定傷病保險金的給付]  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]  
+- [第十五條 保險費豁免（第二保險單年度起適用）]</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 特定傷病保險金的給付 | 第五條 保險範圍 | 第十三條 生活補助保險金的給付（第二保險單年度起適用） | 第二條 名詞定義 | 第十五條 保險費豁免（第二保險單年度起適用）</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在第2保單年度罹患特定傷病，依條款規定：  
+1. **給付金額**：保險公司將依「保險金額」給付「特定傷病保險金」。  
+2. **給付對象**：保險金給付予被保險人或其指定受益人。  
+3. **未來保險金**：自初次診斷確定罹患特定傷病的次一個保險單週年日起，每逢各保險單週年日仍生存者，保險公司將按「保險金額」的36%給付「生活補助保險金」，最多給付10次。此外，保險公司將自診斷確定日起豁免續期保險費，但當期已繳付之未到期保險費不予退還。
+條文依據：  
+- [第十二條 特定傷病保險金的給付]  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]  
+- [第十五條 保險費豁免（第二保險單年度起適用）]</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr"/>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J79" s="3" t="n"/>
+      <c r="K79" s="3" t="n"/>
+      <c r="L79" s="3" t="n"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>2026-03-15 19:22:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>請問我115年1月1日投保，怎麼得到健康促進保險費折減?</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+要獲得健康促進保險費折減，您需要在保單有效期間內完成以下步驟：  
+1. 使用保險公司指定的程式並加入指定的健康計劃。  
+2. 在「指定日期」時，您的會員等級需符合以下標準之一：  
+   - 實踐家：次一保險單年度保險費折減比例為3%。  
+   - 樂享家或高於樂享家的會員等級：次一保險單年度保險費折減比例為10%。  
+3. 您需完成指定程式的註冊程序，並授權保險公司取得與健康促進相關的電子紀錄。保險公司將根據成功傳輸的電子紀錄，依其訂定的辦法計算您的會員等級。  
+條文依據：  
+- [第十六條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 健康促進保險費折減 | 第二十三條 投保年齡的計算及錯誤的處理 | 第十五條 保險費豁免（第二保險單年度起適用） | 第五條 保險範圍 | payout_items</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+要獲得健康促進保險費折減，您需要在保單有效期間內完成以下步驟：  
+1. 使用保險公司指定的程式並加入指定的健康計劃。  
+2. 在「指定日期」時，您的會員等級需符合以下標準之一：  
+   - 實踐家：次一保險單年度保險費折減比例為3%。  
+   - 樂享家或高於樂享家的會員等級：次一保險單年度保險費折減比例為10%。  
+3. 您需完成指定程式的註冊程序，並授權保險公司取得與健康促進相關的電子紀錄。保險公司將根據成功傳輸的電子紀錄，依其訂定的辦法計算您的會員等級。  
+條文依據：  
+- [第十六條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr"/>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J80" s="3" t="n"/>
+      <c r="K80" s="3" t="n"/>
+      <c r="L80" s="3" t="n"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>2026-03-15 19:22:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>保戶在114/1/10投保樂鍾溢，如果他在115/3/30罹患特定傷病的話，在什麼時候可以領取生活補助保險金?</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保戶在114/1/10投保，保險單週年日為每年的1月10日。根據條款，生活補助保險金的給付條件為：被保險人在第二保險單年度（含）以後的有效期間內初次診斷確定罹患特定傷病，並自初次診斷確定罹患特定傷病的次一個保險單週年日起，每逢保險單週年日仍生存者，方可領取生活補助保險金。
+保戶於115/3/30診斷確定罹患特定傷病，該日期已屬於第二保險單年度（114/1/10至115/1/9為第一保險單年度，115/1/10起為第二保險單年度）。因此，保戶可於診斷確定的次一個保險單週年日，即116/1/10起，若仍生存，開始領取生活補助保險金。
+條文依據：  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 生活補助保險金的給付（第二保險單年度起適用） | other_metadata | 第十二條 特定傷病保險金的給付 | 第十一條 契約的終止（三） | 第十條 契約的終止（二）</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保戶在114/1/10投保，保險單週年日為每年的1月10日。根據條款，生活補助保險金的給付條件為：被保險人在第二保險單年度（含）以後的有效期間內初次診斷確定罹患特定傷病，並自初次診斷確定罹患特定傷病的次一個保險單週年日起，每逢保險單週年日仍生存者，方可領取生活補助保險金。
+保戶於115/3/30診斷確定罹患特定傷病，該日期已屬於第二保險單年度（114/1/10至115/1/9為第一保險單年度，115/1/10起為第二保險單年度）。因此，保戶可於診斷確定的次一個保險單週年日，即116/1/10起，若仍生存，開始領取生活補助保險金。
+條文依據：  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr"/>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J81" s="3" t="n"/>
+      <c r="K81" s="3" t="n"/>
+      <c r="L81" s="3" t="n"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>2026-03-15 19:23:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>保戶在114/1/10投保樂鍾溢，如果他在115/3/30罹患特定傷病的話，他在115/1/9會領到無理賠回饋保險金嗎?</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保戶在115/1/9無法領取無理賠回饋保險金。根據條款規定，無理賠回饋保險金的給付條件之一是被保險人在保險單年度末未曾因罹患特定傷病而申領特定傷病保險金。然而，保戶於115/3/30罹患特定傷病，且該診斷日屬於第二保險單年度（114/1/10至115/1/9為第一保險單年度，115/1/10起為第二保險單年度）。因此，保戶在115/1/9時尚未符合條件，無法領取無理賠回饋保險金。
+條文依據：  
+- [第十四條 無理賠回饋保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 無理賠回饋保險金的給付 | payout_items | 第二十條 無理賠回饋保險金的申領 | 第十二條 特定傷病保險金的給付 | other_metadata</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保戶在115/1/9無法領取無理賠回饋保險金。根據條款規定，無理賠回饋保險金的給付條件之一是被保險人在保險單年度末未曾因罹患特定傷病而申領特定傷病保險金。然而，保戶於115/3/30罹患特定傷病，且該診斷日屬於第二保險單年度（114/1/10至115/1/9為第一保險單年度，115/1/10起為第二保險單年度）。因此，保戶在115/1/9時尚未符合條件，無法領取無理賠回饋保險金。
+條文依據：  
+- [第十四條 無理賠回饋保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr"/>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J82" s="3" t="n"/>
+      <c r="K82" s="3" t="n"/>
+      <c r="L82" s="3" t="n"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>2026-03-15 19:23:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>被保險人於第一保險單年度罹患急性心肌梗塞（重度），生活補助保險金最多可以領取幾次？</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於第一保險單年度罹患急性心肌梗塞（重度），無法申領生活補助保險金，因為根據條款規定，生活補助保險金的給付僅適用於第二保險單年度（含）以後的有效期間內初次診斷確定罹患特定傷病的情況。
+條文依據：  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 契約的終止（三） | 第十三條 生活補助保險金的給付（第二保險單年度起適用） | 第二條 名詞定義 | 第十二條 特定傷病保險金的給付 | 第十九條 特定傷病保險金、生活補助保險金或保險費豁免的申領</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於第一保險單年度罹患急性心肌梗塞（重度），無法申領生活補助保險金，因為根據條款規定，生活補助保險金的給付僅適用於第二保險單年度（含）以後的有效期間內初次診斷確定罹患特定傷病的情況。
+條文依據：  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr"/>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J83" s="3" t="n"/>
+      <c r="K83" s="3" t="n"/>
+      <c r="L83" s="3" t="n"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>2026-03-15 19:24:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>被保險人為60歲女性，投保繳費期間20年期之樂鍾心特定傷病定期健康保險（外溢型）5單位，每單位年繳應繳保險費為1675元，則每逢保險單年度末生存者，可以領取多少無理賠關懷保險金？</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+每逢保險單年度末生存且未曾因罹患特定傷病申領「特定傷病保險金」者，可以領取的「無理賠回饋保險金」計算方式為：每單位年繳應繳保險費的10%（元以下無條件進位）乘以單位數。  
+計算如下：  
+每單位年繳應繳保險費為1675元，10%為167.5元，無條件進位後為168元。  
+5單位的「無理賠回饋保險金」為168元 × 5 = 840元。  
+因此，每逢保險單年度末生存者，可以領取840元的「無理賠回饋保險金」。
+條文依據：  
+- [第十四條 無理賠回饋保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 無理賠回饋保險金的給付 | 第五條 保險範圍 | 第十三條 生活補助保險金的給付（第二保險單年度起適用） | other_metadata | 第十二條 特定傷病保險金的給付</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+每逢保險單年度末生存且未曾因罹患特定傷病申領「特定傷病保險金」者，可以領取的「無理賠回饋保險金」計算方式為：每單位年繳應繳保險費的10%（元以下無條件進位）乘以單位數。  
+計算如下：  
+每單位年繳應繳保險費為1675元，10%為167.5元，無條件進位後為168元。  
+5單位的「無理賠回饋保險金」為168元 × 5 = 840元。  
+因此，每逢保險單年度末生存者，可以領取840元的「無理賠回饋保險金」。
+條文依據：  
+- [第十四條 無理賠回饋保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr"/>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J84" s="3" t="n"/>
+      <c r="K84" s="3" t="n"/>
+      <c r="L84" s="3" t="n"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>2026-03-15 19:25:39</t>
         </is>
       </c>
     </row>

--- a/src/rag_results.xlsx
+++ b/src/rag_results.xlsx
@@ -1,47 +1,107 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yiting/Desktop/rag 2/src/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFC9C7FD-2FCA-C44C-A12C-D32C5039023F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="4300" yWindow="880" windowWidth="29900" windowHeight="20240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Results" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+  <si>
+    <t>商品代號</t>
+  </si>
+  <si>
+    <t>問題（original)</t>
+  </si>
+  <si>
+    <t>回答(final)</t>
+  </si>
+  <si>
+    <t>檢索條款(final)</t>
+  </si>
+  <si>
+    <t>是否 reAct</t>
+  </si>
+  <si>
+    <t>initial answer</t>
+  </si>
+  <si>
+    <t>reviseAnswer1</t>
+  </si>
+  <si>
+    <t>reviseAnswer2</t>
+  </si>
+  <si>
+    <t>評估結果(final)</t>
+  </si>
+  <si>
+    <t>coverage_score(final)</t>
+  </si>
+  <si>
+    <t>C_fact(final)</t>
+  </si>
+  <si>
+    <t>C_conf(final)</t>
+  </si>
+  <si>
+    <t>timestamp</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="176" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
-      <name val="Calibri"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="新細明體"/>
+      <family val="3"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
+        <fgColor rgb="FF1F4E78"/>
       </patternFill>
     </fill>
   </fills>
@@ -54,98 +114,43 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="FFD9D9D9"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -433,164 +438,77 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="36" customWidth="1"/>
+    <col min="3" max="3" width="48" customWidth="1"/>
+    <col min="4" max="4" width="36" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="8" width="40" customWidth="1"/>
+    <col min="9" max="9" width="24" customWidth="1"/>
+    <col min="10" max="10" width="18" customWidth="1"/>
+    <col min="11" max="12" width="16" customWidth="1"/>
+    <col min="13" max="13" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>商品代號</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>問題（original)</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>回答(final)</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>檢索條款(final)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>是否 reAct</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>initial answer</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>reviseAnswer1</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>reviseAnswer2</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>評估結果(final)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>coverage_score(final)</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>C_fact(final)</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>C_conf(final)</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>timestamp</t>
-        </is>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>SC1</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>保戶在114/1/10投保樂鍾溢，如果他在115/3/30罹患特定傷病的話，他在115/1/9會領到無理賠回饋保險金嗎?</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>回答：  
-1. 樂鍾溢保單包含「無理賠回饋保險金」的條款，依據第十四條規定，若被保險人在保險單年度末仍生存且未曾申領「特定傷病保險金」，可獲得「無理賠回饋保險金」。  
-2. 115/1/9屬於保險單年度末，需確認被保險人在該日期前是否符合條件。由於被保險人在115/3/30罹患特定傷病，且診斷日期晚於115/1/9，因此115/1/9時未曾申領「特定傷病保險金」，符合給付條件。  
-3. 115/3/30罹患特定傷病不影響115/1/9的「無理賠回饋保險金」給付資格，但若事後發現被保險人不符條件，保險公司有權要求返還或扣回該保險金。  
-4. 保單生效日期為114/1/10，等待期為30日，故114/2/9起保單進入有效期間，與本問題無直接影響。  
-條文依據：  
-- [第十四條 無理賠回饋保險金的給付]  
-- [第十二條 特定傷病保險金的給付]</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>第十四條 無理賠回饋保險金的給付 | payout_items | 第二十條 無理賠回饋保險金的申領 | 第十二條 特定傷病保險金的給付 | other_metadata</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>回答：  
-1. 樂鍾溢保單包含「無理賠回饋保險金」的條款，依據第十四條規定，若被保險人在保險單年度末仍生存且未曾申領「特定傷病保險金」，可獲得「無理賠回饋保險金」。  
-2. 115/1/9屬於保險單年度末，需確認被保險人在該日期前是否符合條件。由於被保險人在115/3/30罹患特定傷病，且診斷日期晚於115/1/9，因此115/1/9時未曾申領「特定傷病保險金」，符合給付條件。  
-3. 115/3/30罹患特定傷病不影響115/1/9的「無理賠回饋保險金」給付資格，但若事後發現被保險人不符條件，保險公司有權要求返還或扣回該保險金。  
-4. 保單生效日期為114/1/10，等待期為30日，故114/2/9起保單進入有效期間，與本問題無直接影響。  
-條文依據：  
-- [第十四條 無理賠回饋保險金的給付]  
-- [第十二條 特定傷病保險金的給付]</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>{"points": [{"id": "1", "point": "確認樂鍾溢保單是否包含無理賠回饋保險金的條款", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認115/1/9是否符合無理賠回饋保險金的給付條件", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認115/3/30罹患特定傷病是否影響無理賠回饋保險金的給付資格", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認保單的生效日期及相關等待期規定", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.930912, "neutral": 0.061623, "contradiction": 0.007465, "factuality": 0.992535, "C_fact": 0.992535}, "C_conf": 0.9955}</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>0.9925349999999999</v>
-      </c>
-      <c r="L2" s="3" t="n">
-        <v>0.9955000000000001</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2026-03-15 11:33:12</t>
-        </is>
-      </c>
+    <row r="2" spans="1:13">
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/src/rag_results.xlsx
+++ b/src/rag_results.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -590,6 +590,65 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>保障範圍包括哪些？</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括：住院醫療保險金、加護病房或燒燙傷病房保險金、祝壽保險金、身故保險金或喪葬費用保險金，以及所繳保險費的退還。
+條文依據：  
+- [第五條 保險範圍]  
+- [摘要]</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>payout_items | 第五條 保險範圍 | 第二條 名詞定義 | summary | 第十八條 除外責任（一）</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括：住院醫療保險金、加護病房或燒燙傷病房保險金、祝壽保險金、身故保險金或喪葬費用保險金，以及所繳保險費的退還。
+條文依據：  
+- [第五條 保險範圍]  
+- [摘要]</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.299185, "neutral": 0.699514, "contradiction": 0.0013, "factuality": 0.9987, "C_fact": 0.9987}, "C_conf": 0.9987}</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="n"/>
+      <c r="K3" s="3" t="n">
+        <v>0.9987</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>0.9987</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2026-03-21 17:26:45</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/rag_results.xlsx
+++ b/src/rag_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yiting/Desktop/rag 2/src/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFC9C7FD-2FCA-C44C-A12C-D32C5039023F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{826580C4-1189-6349-8618-73CBF4E4F74D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4300" yWindow="880" windowWidth="29900" windowHeight="20240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="436">
   <si>
     <t>商品代號</t>
   </si>
@@ -59,6 +59,1764 @@
   </si>
   <si>
     <t>timestamp</t>
+  </si>
+  <si>
+    <t>AGG</t>
+  </si>
+  <si>
+    <t>保障範圍包括哪些項目？</t>
+  </si>
+  <si>
+    <t>回答：  
+保障範圍包括：住院醫療保險金、加護病房或燒燙傷病房保險金、祝壽保險金、身故保險金或喪葬費用保險金，以及所繳保險費的退還。
+條文依據：  
+- 第五條 保險範圍</t>
+  </si>
+  <si>
+    <t>payout_items | summary | 第五條 保險範圍 | 第二條 名詞定義 | 第十八條 除外責任（一）</t>
+  </si>
+  <si>
+    <t>否</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "Q", "point": "保障範圍包括哪些項目？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:28:22</t>
+  </si>
+  <si>
+    <t>住院日數計算有什麼特殊規則？</t>
+  </si>
+  <si>
+    <t>回答：  
+住院日數的計算規則如下：  
+1. 住院日數是按被保險人同一次住院的實際全日住進急性病房或慢性病房（含加護病房及燒燙傷病房）的日數計算，包含住院當日及出院當日。  
+2. 若被保險人出院後於同一日再次入院診療，該日不得重複計入住院日數。  
+條文依據：  
+- [第二條 名詞定義]</t>
+  </si>
+  <si>
+    <t>第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第十二條 住院醫療保險金的給付 | 第二條 名詞定義 | 第十三條 加護病房或燒燙傷病房保險金的給付 | 第二十八條 住院醫療保險金日額之減少</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "Q", "point": "住院日數計算有什麼特殊規則？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:28:27</t>
+  </si>
+  <si>
+    <t>住院醫療保險金的給付規定</t>
+  </si>
+  <si>
+    <t>回答：  
+住院醫療保險金的給付規定如下：  
+1. 被保險人於本契約有效期間內因疾病或傷害住院治療時，本公司將依保險單上記載的「住院醫療保險金日額」，乘以入院日當年度的「增額係數」，再乘以住院日數，給付「住院醫療保險金」。  
+2. 同一保單年度內，同一次住院的住院日數給付上限為365日。  
+條文依據：  
+- [第十二條 住院醫療保險金的給付]</t>
+  </si>
+  <si>
+    <t>第十二條 住院醫療保險金的給付 | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第十三條 加護病房或燒燙傷病房保險金的給付 | 第十四條 醫療保險金給付總額之上限 | 第二十八條 住院醫療保險金日額之減少</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "Q", "point": "住院醫療保險金的給付規定", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:28:33</t>
+  </si>
+  <si>
+    <t>加護病房或燒燙傷病房保險金的給付規定</t>
+  </si>
+  <si>
+    <t>回答：  
+加護病房或燒燙傷病房保險金的給付規定如下：  
+被保險人於本契約有效期間內因疾病或傷害而在醫院的加護病房或燒燙傷病房接受治療時，除住院醫療保險金外，保險公司將依保險單上記載的「住院醫療保險金日額」，乘以入院日當年度的「增額係數」，再乘以實際住進加護病房或燒燙傷病房的日數（含轉入及轉出當日）的二倍，給付「加護病房或燒燙傷病房保險金」。  
+同一保單年度內，同一次住院的加護病房及燒燙傷病房住院日數合計給付上限為365日，但同一日內僅給付其中一種病房的保險金。
+條文依據：  
+- [第十三條 加護病房或燒燙傷病房保險金的給付]</t>
+  </si>
+  <si>
+    <t>第十三條 加護病房或燒燙傷病房保險金的給付 | payout_items | 第二十三條 醫療保險金的申領 | 第五條 保險範圍 | 第二條 名詞定義</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "Q", "point": "加護病房或燒燙傷病房保險金的給付規定", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:28:52</t>
+  </si>
+  <si>
+    <t>醫療保險金給付總額之上限</t>
+  </si>
+  <si>
+    <t>回答：  
+醫療保險金給付總額之上限為保險單上所記載之「住院醫療保險金日額」的二千五百倍，並適用於第十二條至第十三條所列的各項保險金累計給付總額。
+條文依據：  
+- [第十四條 醫療保險金給付總額之上限]</t>
+  </si>
+  <si>
+    <t>第十四條 醫療保險金給付總額之上限 | 第十二條 住院醫療保險金的給付 | 第五條 保險範圍 | 第十三條 加護病房或燒燙傷病房保險金的給付 | payout_items</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "Q", "point": "醫療保險金給付總額之上限", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:29:03</t>
+  </si>
+  <si>
+    <t>祝壽保險金的給付規定為何?</t>
+  </si>
+  <si>
+    <t>回答：  
+祝壽保險金的給付規定如下：  
+1. 被保險人需於本契約有效期間內，且保險年齡到達99歲之保險單週年日仍生存。  
+2. 本公司將按「當年度保險金額」給付祝壽保險金。
+條文依據：  
+- [第十五條 祝壽保險金的給付]</t>
+  </si>
+  <si>
+    <t>第十五條 祝壽保險金的給付 | 第十二條至第十三條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | 第二十四條 祝壽保險金的申領 | payout_items | 第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "Q", "point": "祝壽保險金的給付規定為何?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:29:12</t>
+  </si>
+  <si>
+    <t>有效期間內身故，保險金如何給付?</t>
+  </si>
+  <si>
+    <t>回答：  
+被保險人於本契約有效期間內身故時，本公司依以下情況給付保險金：  
+1. 若被保險人於繳費期間內身故，已繳付之未到期保險費不予退還，亦不併入身故保險金內給付。  
+2. 若被保險人於實際年齡未滿十五足歲時身故，本公司將退還「所繳保險費」予要保人，而不適用身故保險金的給付規定。  
+3. 若被保險人為受監護宣告尚未撤銷者，其身故保險金變更為喪葬費用保險金。  
+條文依據：  
+- [第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付]</t>
+  </si>
+  <si>
+    <t>第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付 | 第十條 契約的終止（二） | 第五條 保險範圍 | 第二十二條 失蹤處理 | 第十五條 祝壽保險金的給付</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "Q", "point": "有效期間內身故，保險金如何給付?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:29:30</t>
+  </si>
+  <si>
+    <t>健康促進保險費折減規定</t>
+  </si>
+  <si>
+    <t>回答：  
+健康促進保險費折減規定如下：  
+1. 被保險人年齡需達20歲（含）以上，並需使用保險公司指定程式及加入指定健康計劃。  
+2. 若於「指定日期」會員等級符合標準，則次一保險單年度保險費可依會員等級享有折減：  
+   - 進階會員：折減2%。  
+   - 菁英會員或更高等級：折減3%。  
+3. 折減僅適用於主契約保險費，不包含其他附約、附加條款或批註條款，且豁免或復效的保險費不適用折減。  
+4. 被保險人需完成指定程式的註冊程序，並授權保險公司取得健康促進相關電子紀錄，保險公司將依此計算會員等級。
+條文依據：  
+- [第十七條 健康促進保險費折減]</t>
+  </si>
+  <si>
+    <t>第十七條 健康促進保險費折減 | 第二十八條 住院醫療保險金日額之減少 | 第三十條 投保年齡的計算及錯誤的處理 | 第二條 名詞定義 | 第五條 保險範圍</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "Q", "point": "健康促進保險費折減規定", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:29:39</t>
+  </si>
+  <si>
+    <t>除外責任的解釋?</t>
+  </si>
+  <si>
+    <t>回答：  
+除外責任是指保險公司對於某些特定原因或情況下所發生的疾病、傷害或死亡，不負給付保險金的責任。以下為條文中提及的主要除外責任範圍：  
+1. **疾病或傷害相關**：  
+   - 被保險人因故意行為（如自殺、自殺未遂）、犯罪行為或非法施用毒品所致的疾病或傷害。  
+   - 美容手術或外科整型（但為重建基本功能的必要整型不在此限）。  
+   - 健康檢查、療養、靜養等非直接診治病人的行為。  
+   - 懷孕、流產或分娩及其併發症（但特定情況如子宮外孕、葡萄胎等不在此限）。  
+2. **身故相關**：  
+   - 要保人故意致被保險人於死。  
+   - 被保險人故意自殺（但契約訂立或復效滿兩年後的自殺不在此限）。  
+   - 被保險人因犯罪處死、拒捕或越獄致死。  
+條文依據：  
+- [第十八條 除外責任（一）]  
+- [第十九條 除外責任（二）]</t>
+  </si>
+  <si>
+    <t>第十八條 除外責任（一） | 第十九條 除外責任（二） | 第八條 告知義務與本契約的解除 | 第二條 名詞定義</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "Q", "point": "除外責任的解釋?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:29:49</t>
+  </si>
+  <si>
+    <t>哪些疾病被含在除外責任?</t>
+  </si>
+  <si>
+    <t>回答：  
+根據條款，以下疾病或情況被列為除外責任，不在保險金給付範圍內：  
+1. 被保險人因故意行為（包括自殺及自殺未遂）所致之疾病或傷害。  
+2. 被保險人因犯罪行為所致之疾病或傷害。  
+3. 被保險人非法施用毒品所致之疾病或傷害。  
+4. 美容手術或外科整型，但為重建基本功能所需的必要整型不在此限。  
+5. 外觀可見的天生畸形。  
+6. 健康檢查、療養、靜養、戒毒、戒酒、護理或養老等非以直接診治病人為目的的行為。  
+7. 懷孕、流產或分娩及其併發症，但以下情況不在此限：  
+   （1）懷孕相關疾病（如子宮外孕、葡萄胎等）。  
+   （2）因醫療行為所必要的流產（如因遺傳性疾病或精神疾病等原因）。  
+   （3）醫療行為必要的剖腹產，且符合特定醫學條件（如胎位不正、多胞胎等）。  
+8. 不孕症、人工受孕或非以治療為目的的避孕及絕育手術。  
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+  </si>
+  <si>
+    <t>第十八條 除外責任（一） | 第二條 名詞定義 | 第十九條 除外責任（二）</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "Q", "point": "哪些疾病被含在除外責任?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:29:58</t>
+  </si>
+  <si>
+    <t>進行美容手術住院可以申請理賠嗎?</t>
+  </si>
+  <si>
+    <t>回答：  
+一般情況下，因美容手術或外科整型住院診療者，保險公司不負給付保險金的責任。但若該整型手術是為了重建基本功能所作的必要整型，則不在此限，保險公司仍需給付保險金。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+  </si>
+  <si>
+    <t>第十八條 除外責任（一） | 第十三條 加護病房或燒燙傷病房保險金的給付 | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第二條 名詞定義 | payout_items</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "Q", "point": "進行美容手術住院可以申請理賠嗎?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:30:06</t>
+  </si>
+  <si>
+    <t>因胎兒染色體異常進行手術而住院可以申請理賠嗎?</t>
+  </si>
+  <si>
+    <t>回答：  
+可以申請理賠。根據條款，因「胎兒染色體異常」進行手術屬於懷孕相關疾病的例外情形，不在除外責任範圍內，因此符合理賠條件。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+  </si>
+  <si>
+    <t>第十八條 除外責任（一） | 第二條 名詞定義 | payout_items | 第十三條 加護病房或燒燙傷病房保險金的給付</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "Q", "point": "因胎兒染色體異常進行手術而住院可以申請理賠嗎?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:30:12</t>
+  </si>
+  <si>
+    <t>因胎位不正進行手術而住院可以申請理賠嗎?</t>
+  </si>
+  <si>
+    <t>回答：  
+一般情況下，因胎位不正進行手術而住院屬於除外責任範圍內的「懷孕、流產或分娩及其併發症」。但若符合第十八條中所列的例外情況，例如「醫療行為必要之剖腹產」，且符合胎位不正的條件，則不在除外責任範圍內，可以申請理賠。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+  </si>
+  <si>
+    <t>第十八條 除外責任（一） | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第二條 名詞定義 | payout_items | 第十三條 加護病房或燒燙傷病房保險金的給付</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "Q", "point": "因胎位不正進行手術而住院可以申請理賠嗎?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:30:17</t>
+  </si>
+  <si>
+    <t>因自殺未遂導致住院可以申請理賠嗎?</t>
+  </si>
+  <si>
+    <t>回答：  
+被保險人因自殺未遂導致住院，本公司不負給付住院相關保險金的責任，因其屬於被保險人之故意行為。  
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+  </si>
+  <si>
+    <t>第十九條 除外責任（二） | 第十八條 除外責任（一） | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | payout_items | 第十條 契約的終止（二）</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "Q", "point": "因自殺未遂導致住院可以申請理賠嗎?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:30:26</t>
+  </si>
+  <si>
+    <t>被保險人在投保一年內故意自殺者，可以申請理賠嗎?</t>
+  </si>
+  <si>
+    <t>回答：  
+被保險人在投保一年內故意自殺者，保險公司不負給付身故保險金或喪葬費用保險金的責任。只有在契約訂立或復效之日起滿二年後，故意自殺致死的情況下，保險公司才負給付責任。
+條文依據：  
+- [第十九條 除外責任（二）]</t>
+  </si>
+  <si>
+    <t>第十九條 除外責任（二） | 第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付 | 第十條 契約的終止（二） | 第三十條 投保年齡的計算及錯誤的處理 | 第十八條 除外責任（一）</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "Q", "point": "被保險人在投保一年內故意自殺者，可以申請理賠嗎?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:30:33</t>
+  </si>
+  <si>
+    <t>申請理賠有什麼時間規定嗎?</t>
+  </si>
+  <si>
+    <t>回答：  
+申請理賠的時間規定如下：  
+1. 要保人、被保險人或受益人應於知悉保險事故後十日內通知保險公司。  
+2. 通知後應儘速檢具所需文件向保險公司申請給付保險金。  
+3. 保險公司應於收齊文件後十五日內完成給付。若因保險公司可歸責的原因未能在期限內給付，應按年利一分加計利息給付。
+條文依據：  
+- [第二十一條 保險事故的通知與保險金的申請時間]</t>
+  </si>
+  <si>
+    <t>第二十一條 保險事故的通知與保險金的申請時間 | 第六條 第二期以後保險費的交付、寬限期間及契約效力的停止 | 第七條 本契約效力的恢復 | 第三條 契約撤銷權 | 第二條 名詞定義</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "Q", "point": "申請理賠有什麼時間規定嗎?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:30:38</t>
+  </si>
+  <si>
+    <t>燒燙傷病房保險金怎麼申領?</t>
+  </si>
+  <si>
+    <t>回答：  
+申領燒燙傷病房保險金時，受益人需依規定檢附以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 醫療診斷書或住院證明，且需列明進、出燒燙傷病房的日期。（但若要保人或被保險人為醫師時，不得為被保險人出具診斷書或住院證明。）  
+4. 受益人的身分證明。  
+此外，保險公司可基於審核保險金的需要，徵詢其他醫師的醫學專業意見，並經受益人同意後調閱被保險人的就醫相關資料，相關費用由保險公司負擔。
+條文依據：  
+- [第二十三條 醫療保險金的申領]</t>
+  </si>
+  <si>
+    <t>第二十三條 醫療保險金的申領 | 第十三條 加護病房或燒燙傷病房保險金的給付 | payout_items | 第二條 名詞定義 | 第二十一條 保險事故的通知與保險金的申請時間</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "Q", "point": "燒燙傷病房保險金怎麼申領?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:30:45</t>
+  </si>
+  <si>
+    <t>活到99歲怎麼申請祝壽金?</t>
+  </si>
+  <si>
+    <t>回答：  
+申請祝壽保險金時，受益人需檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 受益人的身分證明。  
+條文依據：  
+- [第二十四條 祝壽保險金的申領]</t>
+  </si>
+  <si>
+    <t>第十五條 祝壽保險金的給付 | 第二十四條 祝壽保險金的申領 | 第五條 保險範圍 | 第十二條至第十三條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | announcement_history</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "Q", "point": "活到99歲怎麼申請祝壽金?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:30:50</t>
+  </si>
+  <si>
+    <t>被保人身故怎麼申請理賠</t>
+  </si>
+  <si>
+    <t>回答：  
+受益人申請「身故保險金」或「喪葬費用保險金」時，應檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 被保險人死亡證明書及除戶戶籍謄本。  
+4. 受益人的身分證明。  
+條文依據：  
+- [第二十五條 身故保險金或喪葬費用保險金的申領]</t>
+  </si>
+  <si>
+    <t>第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付 | 第十二條至第十三條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | 第二十二條 失蹤處理 | 第二十五條 身故保險金或喪葬費用保險金的申領 | 第十九條 除外責任（二）</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "Q", "point": "被保人身故怎麼申請理賠", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:30:55</t>
+  </si>
+  <si>
+    <t>投保15年後，因手術住院3天，住院日額為2500元，請問可以申請多少理賠?</t>
+  </si>
+  <si>
+    <t>回答：  
+根據條款規定，住院醫療保險金的計算方式為「住院醫療保險金日額」乘以「增額係數」，再乘以住院日數。假設增額係數為1（條文未提及具體增額係數，故以1計算），則理賠金額為：  
+2500元 × 1 × 3天 = 7500元。手術並未影響住院日額理賠條件。
+條文依據：  
+- [第十二條 住院醫療保險金的給付]  
+- [第二條 名詞定義]</t>
+  </si>
+  <si>
+    <t>第十二條 住院醫療保險金的給付 | 第二條 名詞定義 | 第二十八條 住院醫療保險金日額之減少 | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第十三條 加護病房或燒燙傷病房保險金的給付</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "1", "point": "確認住院日額保險金為每日2500元", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認住院天數為3天", "must_have": true, "分數": 1.0}, {"id": "3", "point": "計算住院日額保險金總理賠金額", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認手術是否影響住院日額理賠條件", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:31:33</t>
+  </si>
+  <si>
+    <t>L66</t>
+  </si>
+  <si>
+    <t>回答：  
+保障範圍包括：住院手術醫療保險金、門診手術醫療保險金、特定處置保險金、意外創傷縫合處置保險金、意外住院手術醫療保險金、祝壽保險金、所繳保險費的退還、身故保險金或喪葬費用保險金。
+條文依據：  
+- [第五條 保險範圍]</t>
+  </si>
+  <si>
+    <t>payout_items | 第五條 保險範圍 | summary | 第四條 名詞定義 | 附表一：手術項目與給付倍數</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:31:53</t>
+  </si>
+  <si>
+    <t>保險金額是否有上限?</t>
+  </si>
+  <si>
+    <t>回答：  
+有，保險金額有上限。本公司於本契約有效期間內，依第十一條至第十五條所給付之各項保險金，其累計給付總額上限為保險單上所記載「保險金額」的一千五百倍。
+條文依據：  
+- [第十六條 醫療保險金給付總額之上限]</t>
+  </si>
+  <si>
+    <t>第十六條 醫療保險金給付總額之上限 | 第三十條 保險金額之減少 | 第五條 保險範圍 | 第十九條 健康促進保險費折減 | 第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "Q", "point": "保險金額是否有上限?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:31:59</t>
+  </si>
+  <si>
+    <t>投保後5天發生手術，是否可以申請理賠?</t>
+  </si>
+  <si>
+    <t>回答：  
+依據第五條及第十一條，若被保險人在保險契約有效期間內因疾病或傷害接受手術治療，且手術項目符合附表一所列，並不屬於第二十條所規定的除外責任範圍，則可申請理賠。  
+條款未明確規定等待期間，因此投保後5天是否符合理賠條件，需進一步確認保單內容或相關附加條款。  
+條文依據：  
+[第五條 保險範圍]  
+[第十一條 住院手術醫療保險金]  
+[第二十條 除外責任（一）]</t>
+  </si>
+  <si>
+    <t>第二十條 除外責任（一） | 第十三條 意外住院手術醫療保險金 | 第五條 保險範圍 | 第十一條 住院手術醫療保險金 | 第十二條 門診手術醫療保險金 | 附表一：手術項目與給付倍數</t>
+  </si>
+  <si>
+    <t>是</t>
+  </si>
+  <si>
+    <t>回答：  
+找不到相關內容  
+條文依據：  
+找不到相關內容</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "Q", "point": "投保後5天發生手術，是否可以申請理賠?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:32:50</t>
+  </si>
+  <si>
+    <t>住院手術醫療保險金的給付規定</t>
+  </si>
+  <si>
+    <t>回答：  
+住院手術醫療保險金的給付規定如下：  
+1. 被保險人需於本契約有效期間內，因疾病或傷害經醫師診斷必須在醫院住院接受附表一所列的手術治療，且已實際接受手術者，方可申請給付。  
+2. 給付金額計算方式為：保險單上所記載的「保險金額」乘以手術日當年度的「增額係數」，再乘以手術給付倍數。  
+3. 若同一次手術中於同一手術位置接受兩項以上手術項目，僅給付手術給付倍數最高的手術項目。  
+4. 未載明於附表一的手術項目，將與被保險人協議比照附表內程度相當的手術項目，決定給付倍數。  
+5. 以下情形不予給付：  
+   - 屬於除外責任條款規定的情形。  
+   - 不屬於全民健康保險醫療服務給付項目及支付標準第二部第二章第七節或第三部第三章第四節第三項所列舉的手術。  
+條文依據：  
+- [第十一條 住院手術醫療保險金]</t>
+  </si>
+  <si>
+    <t>第十一條 住院手術醫療保險金 | 第十三條 意外住院手術醫療保險金 | 第十二條 門診手術醫療保險金 | payout_items | 第二十條 除外責任（一） | 附表一：手術項目與給付倍數</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "Q", "point": "住院手術醫療保險金的給付規定", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:33:20</t>
+  </si>
+  <si>
+    <t>門診手術醫療保險金的給付規定</t>
+  </si>
+  <si>
+    <t>回答：  
+門診手術醫療保險金的給付規定如下：  
+1. 被保險人需於本契約有效期間內，因疾病或傷害經醫師診斷必須於醫院或診所門診接受附表一所列的手術治療，且已實際接受手術。  
+2. 給付金額計算方式為：保險單上所記載的「保險金額」乘以手術日當年度的「增額係數」，再乘以手術給付倍數。  
+3. 同一次手術中，若於同一手術位置接受兩項以上手術項目，僅給付手術給付倍數最高的手術項目。  
+4. 同一保險單年度內，門診手術醫療保險金的給付以十次為限。  
+5. 若手術項目未載明於附表一，本公司將與被保險人協議比照附表內的手術項目決定給付倍數。  
+6. 以下情形不負給付責任：  
+   - 屬於本契約除外責任條款規定的項目。  
+   - 不屬於全民健康保險醫療服務給付項目及支付標準第二部第二章第七節或第三部第三章第四節第三項所列舉的手術。  
+條文依據：  
+- [第十二條 門診手術醫療保險金]</t>
+  </si>
+  <si>
+    <t>第十二條 門診手術醫療保險金 | 第十一條 住院手術醫療保險金 | payout_items | 第十三條 意外住院手術醫療保險金 | 附表一：手術項目與給付倍數</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "Q", "point": "門診手術醫療保險金的給付規定", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:33:28</t>
+  </si>
+  <si>
+    <t>意外住院手術醫療保險金的給付規定</t>
+  </si>
+  <si>
+    <t>回答：  
+意外住院手術醫療保險金的給付規定如下：  
+1. 被保險人需於本契約有效期間內，且保險年齡未滿七十歲。  
+2. 因傷害經醫師診斷，在住院期間必須接受手術治療且已實際接受手術。  
+3. 給付金額為保險單所記載的「保險金額」的三倍，乘以手術日當年度的「增額係數」。  
+4. 同一次手術中，於同一手術位置接受兩項以上手術項目時，僅給付一次意外住院手術醫療保險金。
+條文依據：  
+- [第十三條 意外住院手術醫療保險金]</t>
+  </si>
+  <si>
+    <t>第十三條 意外住院手術醫療保險金 | 第十一條 住院手術醫療保險金 | 第十五條 意外創傷縫合處置保險金 | 第二十條 除外責任（一） | 第十二條 門診手術醫療保險金 | 附表三：意外創傷縫合處置項目及給付倍數表 | 附表一：手術項目與給付倍數</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "Q", "point": "意外住院手術醫療保險金的給付規定", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:33:33</t>
+  </si>
+  <si>
+    <t>特定處置保險金的給付規定</t>
+  </si>
+  <si>
+    <t>回答：  
+特定處置保險金的給付規定如下：  
+1. 被保險人於保險有效期間內，因疾病或傷害經醫師診斷需接受附表二所列的特定處置治療，且已完成處置者，保險公司將依保險單所載的「保險金額」，乘以特定處置日當年度的「增額係數」，再乘以特定處置給付倍數，給付「特定處置保險金」。  
+2. 若同一次處置治療中，在同一治療位置接受兩項以上特定處置項目時，僅給付特定處置給付倍數最高的項目。  
+3. 若被保險人接受的處置未列於附表二的特定處置項目中，保險公司不負給付特定處置保險金的責任。  
+4. 同一保險單年度內，特定處置保險金的給付次數以十次為限。
+條文依據：  
+- [第十四條 特定處置保險金]</t>
+  </si>
+  <si>
+    <t>第十四條 特定處置保險金 | 第十五條 意外創傷縫合處置保險金 | 附表二：特定處置項目及給付倍數表 | 第五條 保險範圍 | 附表三：意外創傷縫合處置項目及給付倍數表</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "Q", "point": "特定處置保險金的給付規定", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:33:39</t>
+  </si>
+  <si>
+    <t>意外創傷縫合處置保險金的給付規定</t>
+  </si>
+  <si>
+    <t>回答：  
+意外創傷縫合處置保險金的給付規定如下：  
+1. 被保險人因意外傷害事故，於醫院或診所接受附表三所列的意外創傷縫合處置治療者，本公司將依保險單所記載的「保險金額」，乘以當年度的「增額係數」及「意外創傷縫合處置給付倍數」計算給付金額。  
+2. 同一次意外傷害事故中，本公司僅就傷口最大者給付，且僅給付一次。  
+3. 若被保險人因同一意外傷害事故已申領「住院手術醫療保險金」或「門診手術醫療保險金」，則不再給付「意外創傷縫合處置保險金」。  
+條文依據：  
+- [第十五條 意外創傷縫合處置保險金]</t>
+  </si>
+  <si>
+    <t>第十五條 意外創傷縫合處置保險金 | 附表三：意外創傷縫合處置項目及給付倍數表 | 第十四條 特定處置保險金 | 第二十條 除外責任（一） | 第十三條 意外住院手術醫療保險金 | 附表二：特定處置項目及給付倍數表</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "Q", "point": "意外創傷縫合處置保險金的給付規定", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:33:46</t>
+  </si>
+  <si>
+    <t>回答：  
+醫療保險金給付總額之上限為保險單上所記載「保險金額」的一千五百倍，此上限不包含其他附約、附加條款或批註條款。
+條文依據：  
+- [第十六條 醫療保險金給付總額之上限]</t>
+  </si>
+  <si>
+    <t>第十六條 醫療保險金給付總額之上限 | 第十二條 門診手術醫療保險金 | 第五條 保險範圍 | 第十一條 住院手術醫療保險金 | 第十三條 意外住院手術醫療保險金 | 附表一：手術項目與給付倍數</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:33:53</t>
+  </si>
+  <si>
+    <t>祝壽保險金的領取規定為何?</t>
+  </si>
+  <si>
+    <t>回答：  
+祝壽保險金的領取規定如下：  
+1. 被保險人需於本契約有效期間內，且保險年齡到達九十九歲之保險單週年日仍生存，方可領取祝壽保險金。  
+2. 受益人申領祝壽保險金時，需檢具以下文件：  
+   - 保險單或其謄本  
+   - 保險金申請書  
+   - 受益人的身分證明  
+條文依據：  
+- [第十七條 祝壽保險金]  
+- [第二十六條 祝壽保險金的申領]</t>
+  </si>
+  <si>
+    <t>第十七條 祝壽保險金 | 第二十六條 祝壽保險金的申領 | 第十一條至第十五條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | 第二十三條 保險事故的通知與保險金的申請時間 | 第五條 保險範圍</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "Q", "point": "祝壽保險金的領取規定為何?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:34:05</t>
+  </si>
+  <si>
+    <t>身故時領取保險金有什麼規則?</t>
+  </si>
+  <si>
+    <t>回答：  
+身故時領取保險金的規則如下：  
+1. **一般情況**：被保險人於本契約有效期間內身故，本公司按「當年度保險金額」給付「身故保險金」。  
+2. **未滿十五足歲**：若被保險人身故時實際年齡未滿十五足歲，本公司僅退還「所繳保險費」，不適用「當年度保險金額」。  
+3. **受監護宣告者**：若被保險人於訂立契約時受監護宣告且尚未撤銷，其身故保險金改為喪葬費用保險金，且金額不得超過遺產稅喪葬費扣除額之半數，超過部分不予給付，並退還超過部分的已繳保險費。  
+4. **除外責任**：若身故原因屬於以下情形，本公司不負給付責任：  
+   - 要保人故意致被保險人於死。  
+   - 被保險人故意自殺，但自契約訂立或復效之日起滿二年後故意自殺者，本公司仍負給付責任。  
+   - 被保險人因犯罪處死、拒捕或越獄致死。  
+   若被保險人未滿十五足歲且因上述原因身故，本公司僅退還「所繳保險費」。  
+條文依據：  
+- [第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金]  
+- [第二十一條 除外責任（二）]</t>
+  </si>
+  <si>
+    <t>第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金 | 第二十七條 身故保險金或喪葬費用保險金的申領 | 第十一條至第十五條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | 第二十一條 除外責任（二） | 第五條 保險範圍</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "Q", "point": "身故時領取保險金有什麼規則?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:34:17</t>
+  </si>
+  <si>
+    <t>什麼情況下可以保費折減?</t>
+  </si>
+  <si>
+    <t>回答：  
+被保險人年滿20歲（含）以上，並使用保險公司指定程式加入健康計劃，於「指定日期」達到符合會員等級標準者，可享有次一保險單年度的保費折減。折減比例依會員等級而定：進階會員為2%，菁英會員或更高等級為3%。但豁免或復效的保險費不適用此折減規定。此外，被保險人需完成程式註冊並授權保險公司取得健康相關電子紀錄，保險公司將依此計算會員等級。
+條文依據：  
+- [第十九條 健康促進保險費折減]</t>
+  </si>
+  <si>
+    <t>第十九條 健康促進保險費折減 | 第三十條 保險金額之減少 | 第二十條 除外責任（一） | 第三十一條 投保年齡的計算及錯誤的處理 | 第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "Q", "point": "什麼情況下可以保費折減?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:34:25</t>
+  </si>
+  <si>
+    <t>角膜切除術是否可以申請理賠?</t>
+  </si>
+  <si>
+    <t>回答：  
+角膜切除術可以申請理賠，其對應的給付倍數為5倍。
+條文依據：  
+- [附表一：手術項目與給付倍數 - 1305 角膜切除術]</t>
+  </si>
+  <si>
+    <t>附表一：手術項目與給付倍數</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "Q", "point": "角膜切除術是否可以申請理賠?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:34:30</t>
+  </si>
+  <si>
+    <t>白內障手術是否可以申請理賠?</t>
+  </si>
+  <si>
+    <t>回答：  
+白內障手術是否可以申請理賠，需視手術是否符合保單條款中的給付條件。根據條文，若白內障手術屬於附表一所列的手術項目，且不屬於除外責任條款規定的情形，則可申請理賠。若手術項目未列於附表一，保險公司將與被保險人協議比照附表內程度相當的手術項目決定給付倍數。
+條文依據：  
+- [第十二條 門診手術醫療保險金]  
+- [第十一條 住院手術醫療保險金]  
+- [第二十條 除外責任（一）]</t>
+  </si>
+  <si>
+    <t>第十二條 門診手術醫療保險金 | 第二十條 除外責任（一） | 附表一：手術項目與給付倍數 | payout_items | 第十一條 住院手術醫療保險金</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "Q", "point": "白內障手術是否可以申請理賠?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:34:37</t>
+  </si>
+  <si>
+    <t>GI1</t>
+  </si>
+  <si>
+    <t>回答：  
+保障範圍包括以下項目：  
+1. 意外事故身故保險金或喪葬費用保險金  
+2. 意外事故失能保險金  
+3. 每月生活照護保險金  
+4. 重大燒燙傷保險金  
+5. 意外骨折保險金  
+6. 傷害醫療日額保險金  
+7. 意外創傷縫合處置保險金  
+條文依據：  
+- [第五條 保險範圍]</t>
+  </si>
+  <si>
+    <t>payout_items | 第五條 保險範圍 | 第十五條 每月生活照護保險金的給付 | 第三十條 不保事項 | 附表二：失能程度與保險金給付表</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:34:41</t>
+  </si>
+  <si>
+    <t>發生意外事故身故，理賠內容為何?</t>
+  </si>
+  <si>
+    <t>回答：  
+發生意外事故身故，理賠內容如下：  
+1. 若被保險人於本契約有效期間內因「意外傷害事故」自事故發生之日起一百八十日以內身故，本公司依該意外傷害事故之種類給付「意外事故身故保險金」：  
+   - 一般意外傷害事故：給付「傷害醫療保險金日額」的五百倍。  
+   - 特定意外傷害事故：給付「傷害醫療保險金日額」的一千倍。  
+2. 若被保險人於事故發生後超過一百八十日身故，但受益人能證明身故與該意外傷害事故具有因果關係，本公司仍依上述約定給付「意外事故身故保險金」，不受一百八十日限制。  
+3. 若被保險人於訂立契約時為受監護宣告尚未撤銷者，其「意外事故身故保險金」變更為「喪葬費用保險金」。  
+條文依據：  
+- [第十二條 意外事故身故保險金或喪葬費用保險金的給付]</t>
+  </si>
+  <si>
+    <t>第十二條 意外事故身故保險金或喪葬費用保險金的給付 | 第十四條 保險給付的限制 | payout_items | 第十一條 契約的終止（二） | 第二十一條 失蹤處理</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "Q", "point": "發生意外事故身故，理賠內容為何?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:34:48</t>
+  </si>
+  <si>
+    <t>意外事故失能保險金的給付為何?</t>
+  </si>
+  <si>
+    <t>回答：  
+意外事故失能保險金的給付條件如下：  
+1. 被保險人於契約有效期間內遭受「意外傷害事故」，並自事故發生之日起 180 日內致成附表二所列失能程度之一者，本公司依事故種類及失能程度，按以下方式計算給付金額：  
+   - 一般意外傷害事故：「傷害醫療保險金日額」的 500 倍乘以附表二給付比例。  
+   - 特定意外傷害事故：「傷害醫療保險金日額」的 1000 倍乘以附表二給付比例。  
+2. 若超過 180 日致成失能，受益人需證明失能與事故具有因果關係，本公司仍依上述規定給付保險金，不受 180 日限制。  
+3. 同一事故導致多項失能時，僅給付同一手或同一足中較嚴重項目的失能保險金，且總金額以事故種類的上限為限：  
+   - 一般意外傷害事故：「傷害醫療保險金日額」的 500 倍。  
+   - 特定意外傷害事故：「傷害醫療保險金日額」的 1000 倍。  
+4. 不同事故導致的失能，累計給付金額最高以「傷害醫療保險金日額」的 1200 倍為限。  
+條文依據：  
+- [第十三條 意外事故失能保險金的給付]</t>
+  </si>
+  <si>
+    <t>第十三條 意外事故失能保險金的給付 | 第十五條 每月生活照護保險金的給付 | 第十四條 保險給付的限制 | 第十二條 意外事故身故保險金或喪葬費用保險金的給付 | 第二十三條 意外事故失能保險金的申領 | 附表二：失能程度與保險金給付表</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "Q", "point": "意外事故失能保險金的給付為何?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:34:55</t>
+  </si>
+  <si>
+    <t>每月生活照護保險金的給付為何?</t>
+  </si>
+  <si>
+    <t>回答：  
+每月生活照護保險金的給付條件如下：  
+1. 被保險人需於保險契約有效期間內因「意外傷害事故」，自事故發生之日起一百八十日內，致成附表二所列第一級至第六級失能程度之一。  
+2. 若被保險人自事故發生之日起超過一百八十日才達到上述失能程度，但能證明失能與該事故具有因果關係，仍可申請給付。  
+3. 給付金額為「傷害醫療保險金日額」的二十倍，乘以附表二給付比例所得之金額，按月給付，以十二個月為限。  
+4. 若於失能的前四個「失能診斷確定週年日」，契約有效且被保險人仍生存，則自各該週年日起，按相同方式給付，以十二個月為限。  
+5. 同一事故若導致多項失能，僅給付較嚴重項目，且最高給付金額以「傷害醫療保險金日額」的二十倍為限。  
+6. 累計給付金額最高以「傷害醫療保險金日額」的一千二百倍為限。  
+條文依據：  
+- [第十五條 每月生活照護保險金的給付]</t>
+  </si>
+  <si>
+    <t>第二十四條 每月生活照護保險金的申領 | 第十五條 每月生活照護保險金的給付 | payout_items | 第十八條 傷害醫療日額保險金的給付 | 第五條 保險範圍 | 附表二：失能程度與保險金給付表 | 附表三：骨折別表</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "Q", "point": "每月生活照護保險金的給付為何?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:35:03</t>
+  </si>
+  <si>
+    <t>重大燒燙傷保險金的給付為何?</t>
+  </si>
+  <si>
+    <t>回答：  
+重大燒燙傷保險金的給付條件為：被保險人於保險契約有效期間內因「意外傷害事故」導致燒燙傷，且經診斷符合「重大燒燙傷」的定義時，本公司將按「傷害醫療保險金日額」的二百五十倍給付「重大燒燙傷保險金」。該保險金的給付以一次為限。
+條文依據：  
+- [第十六條 重大燒燙傷保險金的給付]</t>
+  </si>
+  <si>
+    <t>第十六條 重大燒燙傷保險金的給付 | 第二十五條 重大燒燙傷保險金的申領 | 第五條 保險範圍 | payout_items | 第二十九條 除外責任（原因）</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "Q", "point": "重大燒燙傷保險金的給付為何?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:35:09</t>
+  </si>
+  <si>
+    <t>意外骨折保險金的給付為何?</t>
+  </si>
+  <si>
+    <t>回答：  
+意外骨折保險金的給付條件如下：  
+1. 被保險人於保險契約有效期間內因「意外傷害事故」導致骨折，且骨折項目屬於附表三骨折別表所列者（含不完全骨折及骨骼龜裂），本公司按「傷害醫療保險金日額」的二倍給付「意外骨折保險金」。  
+2. 骨折需於意外傷害事故發生之日起一百八十日內經醫院或診所診斷確定；若超過一百八十日，受益人需證明骨折與該意外傷害事故具有因果關係，仍可獲得保險金給付。  
+3. 同一意外傷害事故僅給付一次「意外骨折保險金」。  
+4. 若骨折部位不屬於附表三骨折別表所列項目，則由本公司與被保險人協議核付保險金；但若骨折部位為骨折別表內明訂不給付之部位，則本公司不負給付保險金之責。  
+條文依據：  
+- [第十七條 意外骨折保險金的給付]</t>
+  </si>
+  <si>
+    <t>第十七條 意外骨折保險金的給付 | 第十八條 傷害醫療日額保險金的給付 | 第二十六條 意外骨折保險金的申領 | 第十三條 意外事故失能保險金的給付 | 第十九條 意外創傷縫合處置保險金的給付 | 附表二：失能程度與保險金給付表 | 附表三：骨折別表</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "Q", "point": "意外骨折保險金的給付為何?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:35:15</t>
+  </si>
+  <si>
+    <t>傷害醫療日額保險金的給付為何?</t>
+  </si>
+  <si>
+    <t>回答：  
+傷害醫療日額保險金的給付條件如下：  
+1. 被保險人於保險契約有效期間內遭受「意外傷害事故」，並於事故發生後 180 日內在「醫院」接受住院治療，本公司將依「傷害醫療保險金日額」乘以實際住院日數給付保險金，但每次事故最高給付日數為 90 日。  
+2. 若治療超過 180 日，且受益人能證明治療與該意外傷害事故具有因果關係，本公司仍會依上述規定給付保險金，不受 180 日限制。  
+3. 若因意外事故骨折但未住院，或住院日數未達附表三骨折別表所訂日數，則按骨折別表所訂日數乘以「傷害醫療保險金日額」的二分之一給付，合計給付日數以骨折別表所訂日數為上限。  
+4. 骨折類型的給付標準：  
+   - 完全骨折：按骨折別表所訂日數給付。  
+   - 不完全骨折：按完全骨折日數的二分之一給付。  
+   - 骨骼龜裂：按完全骨折日數的四分之一給付。  
+5. 若同時發生多項骨折，僅給付一項較高等級的保險金。
+條文依據：  
+- [第十八條 傷害醫療日額保險金的給付]</t>
+  </si>
+  <si>
+    <t>第十八條 傷害醫療日額保險金的給付 | 第二十七條 傷害醫療日額保險金的申領 | 第十五條 每月生活照護保險金的給付 | 第三十四條 傷害醫療保險金日額之減少 | 第十九條 意外創傷縫合處置保險金的給付 | 附表二：失能程度與保險金給付表 | 附表三：骨折別表</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "Q", "point": "傷害醫療日額保險金的給付為何?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:35:23</t>
+  </si>
+  <si>
+    <t>意外創傷縫合處置保險金的給付為何?</t>
+  </si>
+  <si>
+    <t>回答：  
+意外創傷縫合處置保險金的給付條件為：被保險人於保險契約有效期間內，因遭受「意外傷害事故」，在「醫院」或「診所」經醫師診斷必須接受創傷縫合處置治療，且已完成縫合處置者，本公司將按「傷害醫療保險金日額」給付該保險金。同一意外傷害事故僅給付一次。
+條文依據：  
+- [第十九條 意外創傷縫合處置保險金的給付]</t>
+  </si>
+  <si>
+    <t>第十九條 意外創傷縫合處置保險金的給付 | 第二十八條 意外創傷縫合處置保險金的申領 | 第五條 保險範圍 | 第十七條 意外骨折保險金的給付 | payout_items | 附表三：骨折別表</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "Q", "point": "意外創傷縫合處置保險金的給付為何?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:35:30</t>
+  </si>
+  <si>
+    <t>因意外導致視力衰退，是否能申請理賠?</t>
+  </si>
+  <si>
+    <t>回答：  
+可以申請理賠，但需符合以下條件：  
+1. 視力永久衰退需達到「萬國式視力表0.02以下」的標準，或符合其他失明定義（如眼球喪失、摘出等）。  
+2. 視力障害的測定需經過六個月的治療期判定，除非是眼球摘出等明顯無法復原的情況。  
+條文依據：  
+- 註2 2-2.「失明」係指視力永久在萬國式視力表0.02以下而言，並包括眼球喪失、摘出、僅能辨明暗或辨眼前一公尺以內手動或辨眼前五公分以內指數者。  
+- 註2 2-3.以自傷害之日起經過六個月的治療為判定原則，但眼球摘出等明顯無法復原之情況，不在此限。</t>
+  </si>
+  <si>
+    <t>第二十三條 意外事故失能保險金的申領 | 第十三條 意外事故失能保險金的給付 | 註2： | 第三十條 不保事項 | 第二十六條 意外骨折保險金的申領 | 附表二：失能程度與保險金給付表</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "Q", "point": "因意外導致視力衰退，是否能申請理賠?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:35:37</t>
+  </si>
+  <si>
+    <t>肋骨骨折是否可以申請理賠?理賠金額為多少?</t>
+  </si>
+  <si>
+    <t>回答：  
+肋骨骨折可以申請理賠，理賠金額需依據骨折的情況計算：  
+1. 若肋骨完全骨折且未住院治療，按附表三所訂的20天乘以「傷害醫療保險金日額」的二分之一給付，即10天的日額保險金。  
+2. 若肋骨不完全骨折，按完全骨折日數的二分之一計算，即20天的二分之一再乘以「傷害醫療保險金日額」的二分之一，最終為5天的日額保險金。  
+3. 若肋骨為骨骼龜裂，按完全骨折日數的四分之一計算，即20天的四分之一再乘以「傷害醫療保險金日額」的二分之一，最終為2.5天的日額保險金。  
+條文依據：  
+- [第十八條 傷害醫療日額保險金的給付]  
+- [附表三：骨折別表]</t>
+  </si>
+  <si>
+    <t>第十八條 傷害醫療日額保險金的給付 | 第十七條 意外骨折保險金的給付 | 第二十六條 意外骨折保險金的申領 | 第三十條 不保事項 | 第五條 保險範圍 | 附表三：骨折別表</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "Q", "point": "肋骨骨折是否可以申請理賠?理賠金額為多少?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:35:44</t>
+  </si>
+  <si>
+    <t>ZCN</t>
+  </si>
+  <si>
+    <t>投保新鍾心滿福後，假設投保保額為100萬元，於第二保單年度接受「移植器官」，這樣可以領多少保險金?</t>
+  </si>
+  <si>
+    <t>回答：  
+新鍾心滿福保險涵蓋器官移植手術保障，且於第二保單年度接受「移植器官」符合保險金給付條件。根據條款，若被保險人於第二保單年度（含）以後的有效期間內，經初次診斷確定罹患「特定重大傷病」（包括器官移植），本公司將給付重大傷病保險金，並按「保險金額的百分之二十」額外給付「特定重大傷病保險金」。因此，若投保保額為100萬元，則可領取的保險金為：  
+1. 重大傷病保險金：100萬元  
+2. 特定重大傷病保險金：100萬元 × 20% = 20萬元  
+合計：120萬元。
+條文依據：  
+- [第十三條 特定重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+  </si>
+  <si>
+    <t>附表一：全民健康保險重大傷病項目 | 第二條 名詞定義 | 第十三條 特定重大傷病保險金的給付 | 第十五條 滿期保險金的給付 | 附表二：完全失能程度表</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "1", "point": "確認新鍾心滿福保險是否涵蓋器官移植手術保障", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認器官移植手術的保險金給付條件及計算方式", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認第二保單年度的保障範圍是否有影響", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認投保保額100萬元對保險金計算的影響", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:36:13</t>
+  </si>
+  <si>
+    <t>投保新鍾心滿福後，若要理賠重大傷病保險金，一定要檢附全民健保開立的重大傷病證明才能拿到保險金嗎?</t>
+  </si>
+  <si>
+    <t>回答：  
+申請重大傷病保險金時，並非一定需要檢附全民健保開立的重大傷病證明。若被保險人已取得一家「區域醫院」層級以上（含）之醫療院所開立且符合投保當時「重大傷病範圍」的診斷書及當次病歷摘要，亦可作為重大傷病證明文件，免向全民健康保險保險人申請。此外，若因全民健康保險保險人變更或調整重大傷病項目，導致無法取得重大傷病證明文件時，也可依條款規定以其他文件替代。  
+條文依據：  
+- [第二十二條 重大傷病保險金、特定重大傷病保險金的申領]  
+- [第十二條 重大傷病保險金的給付]</t>
+  </si>
+  <si>
+    <t>第二十二條 重大傷病保險金、特定重大傷病保險金的申領 | 第十二條 重大傷病保險金的給付 | 第三十條 不保事項 | 第二條 名詞定義 | other_metadata | 附表一：全民健康保險重大傷病項目</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "1", "point": "確認重大傷病保險金的理賠條件", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認是否需要檢附全民健保開立的重大傷病證明", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認新鍾心滿福保險的相關理賠規定", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:37:05</t>
+  </si>
+  <si>
+    <t>一定要有健保身分才能申請重大傷病理賠嗎？</t>
+  </si>
+  <si>
+    <t>回答：  
+不一定需要有健保身分才能申請重大傷病理賠。若被保險人喪失全民健康保險被保險人資格，需先申請加保全民健康保險後，始得申領「重大傷病保險金」之給付。但若因意外傷害事故導致重大傷病，則不受等待期間及健保資格限制。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+  </si>
+  <si>
+    <t>第二十二條 重大傷病保險金、特定重大傷病保險金的申領 | 第十二條 重大傷病保險金的給付 | other_metadata | 第三十條 不保事項 | 第二條 名詞定義 | 附表一：全民健康保險重大傷病項目</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "Q", "point": "一定要有健保身分才能申請重大傷病理賠嗎？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:37:26</t>
+  </si>
+  <si>
+    <t>重大傷病的項目如果在投保後有新增，可以從優申請理賠嗎？</t>
+  </si>
+  <si>
+    <t>回答：  
+可以從優申請理賠。根據條款，重大傷病的範圍包含「全民健康保險重大傷病項目及其證明有效期限」，且若該項目於保險契約有效期間內新增，則以中央衛生主管機關最新公告的項目為準。因此，新增的重大傷病項目在契約有效期間內確診，符合條件者可申請理賠。
+條文依據：  
+- [第二條 名詞定義]</t>
+  </si>
+  <si>
+    <t>附表一：全民健康保險重大傷病項目 | 第二條 名詞定義 | payout_items</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "Q", "point": "重大傷病的項目如果在投保後有新增，可以從優申請理賠嗎？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:37:33</t>
+  </si>
+  <si>
+    <t>我的保單之前有停效，在復效後五天被診斷出重大疾病是否可申請理賠？</t>
+  </si>
+  <si>
+    <t>回答：  
+若保單已成功復效，且重大疾病的診斷符合保單理賠條件，則可申請理賠。然而，需注意復效後是否有等待期的規定。根據條款，若重大疾病是因意外傷害事故所致，則不受等待期間限制；但若非因意外傷害事故，則需確認等待期間是否已屆滿。若等待期間內罹患重大疾病，保單將自始無效，僅退還已繳保險費。
+條文依據：  
+- [第八條 本契約效力的恢復]  
+- [第十二條 重大傷病保險金的給付]  
+- [第二條 名詞定義]  
+- [第三十條 不保事項]</t>
+  </si>
+  <si>
+    <t>第十二條 重大傷病保險金的給付 | 第八條 本契約效力的恢復 | 第二條 名詞定義 | 第三十條 不保事項 | 附表一：全民健康保險重大傷病項目</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "1", "point": "確認保單是否已成功復效", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認重大疾病是否符合保單理賠條件", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認復效後是否有等待期規定", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認重大疾病診斷日期是否符合保單條款", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:38:05</t>
+  </si>
+  <si>
+    <t>領完重大傷病保險金，主約終止後，附約可以繼續有效嗎?</t>
+  </si>
+  <si>
+    <t>回答：  
+可以。根據條文規定，若因重大傷病診斷確定而導致主約終止時，要保人仍可於附約的有效期間內繼續繳交附約保險費，以延續附約效力。
+條文依據：  
+- [第十一條 契約的終止（二）]</t>
+  </si>
+  <si>
+    <t>第十一條 契約的終止（二） | 第十二條 重大傷病保險金的給付 | 第三十條 不保事項 | 第五條 保險範圍 | payout_items | 附表一：全民健康保險重大傷病項目</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "Q", "point": "領完重大傷病保險金，主約終止後，附約可以繼續有效嗎?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:38:27</t>
+  </si>
+  <si>
+    <t>Q1：因為慢性精神病的保險給付僅有保額的20%，我可以先不申請給付，等之後發生其他重大傷病後，再申請重大傷病保險金嗎?Q2：但如果我不申請，保險公司不會知道我有罹患慢性精神病阿，所以我就可以領之後的重大傷病100%保額嗎?</t>
+  </si>
+  <si>
+    <t>回答：  
+Q1：慢性精神病的保險給付比例確實為保額的20%，但是否可以延後申請給付，條文中未明確規定可延後申請，因此建議直接向保險公司確認。  
+Q2：若未申請慢性精神病的保險金，條文中未提及保險公司是否會因此不知情，但根據條文第十二條規定，若被保險人同時或先後罹患兩項以上重大傷病，保險公司僅給付一項重大傷病保險金。因此，即使未申請慢性精神病的保險金，後續罹患其他重大傷病時，保險公司仍可能依條文規定僅給付一次，且金額將依條件計算，並非自動給付100%保額。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第三十條 不保事項]</t>
+  </si>
+  <si>
+    <t>第十二條 重大傷病保險金的給付 | 第十三條 特定重大傷病保險金的給付 | 附表一：全民健康保險重大傷病項目 | 第二十二條 重大傷病保險金、特定重大傷病保險金的申領 | 第三十條 不保事項</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "1", "point": "確認慢性精神病保險給付比例是否為保額的20%", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認是否可以延後申請慢性精神病保險給付", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認重大傷病保險金是否可在未申請慢性精神病給付的情況下領取100%保額", "must_have": true, "分數": 1.0}, {"id": "4", "point": "了解保險公司是否需要知悉慢性精神病的罹患情況以影響後續理賠", "must_have": false, "分數": 0.5}, {"id": "5", "point": "確認重大傷病保險金的申請條件與慢性精神病的影響關係", "must_have": false, "分數": 1.0}], "coverage_score": 0.9643, "C_conf": 0.9643}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:39:15</t>
+  </si>
+  <si>
+    <t>失智症會賠嗎？賠多少？</t>
+  </si>
+  <si>
+    <t>回答：  
+失智症是否理賠及賠償金額，需視保險契約條款而定。若失智症導致符合附表二所列「完全失能程度」之一，例如中樞神經系統機能遺存極度障害，終身不能從事任何工作且經常需醫療護理或專人周密照護者，則可申請「完全失能保險金」。賠償金額依以下方式計算：  
+1. 當年度保險金額。  
+2. 年繳應繳保險費總額的一點零五倍。  
+條款未明確規定失智症是否屬於重大傷病保險金的給付範圍。  
+條文依據：  
+[第十七條 完全失能保險金的給付]  
+[附表二：完全失能程度表]</t>
+  </si>
+  <si>
+    <t>附表一：全民健康保險重大傷病項目 | 第十七條 完全失能保險金的給付 | 附表二：完全失能程度表 | payout_items</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "Q", "point": "失智症會賠嗎？賠多少？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:40:00</t>
+  </si>
+  <si>
+    <t>投保新鍾心滿福後，於第二保單年度罹患子宮頸惡性腫瘤，且已給付重大傷病保險金。第五保單年度時又罹患慢性腎衰竭，這樣還可以申領重大傷病保險金的給付嗎?</t>
+  </si>
+  <si>
+    <t>回答：  
+根據條款規定，重大傷病保險金僅能給付一次，即使被保險人同時或先後罹患兩項以上的重大傷病，本公司僅給付一項重大傷病保險金。因此，雖然慢性腎衰竭符合重大傷病保險金的給付條件，但因已於第二保單年度因子宮頸惡性腫瘤申領過重大傷病保險金，無法再次申領。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+  </si>
+  <si>
+    <t>第十二條 重大傷病保險金的給付 | 附表一：全民健康保險重大傷病項目 | 第二條 名詞定義 | 第二十二條 重大傷病保險金、特定重大傷病保險金的申領</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "1", "point": "確認重大傷病保險金是否可重複申領", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認慢性腎衰竭是否符合重大傷病保險金的給付條件", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認保單條款中重大傷病保險金的申領次數限制", "must_have": false, "分數": 1.0}, {"id": "4", "point": "確認保單年度與疾病發生時間的影響", "must_have": false, "分數": 0.5}], "coverage_score": 0.95, "C_conf": 0.95}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:40:48</t>
+  </si>
+  <si>
+    <t>12歲的被保險人可以有健康促進保險費折減嗎？</t>
+  </si>
+  <si>
+    <t>回答：  
+12歲的被保險人無法享有健康促進保險費折減，因為根據條款規定，健康促進保險費折減僅適用於實際年齡達18歲（含）以上的被保險人。
+條文依據：  
+- [第十九條 健康促進保險費折減]</t>
+  </si>
+  <si>
+    <t>第十九條 健康促進保險費折減 | 第三十八條 投保年齡的計算及錯誤的處理 | 第三十四條 減額繳清保險 | 第二條 名詞定義 | 第十六條 所繳保險費加計利息的退還、身故保險金或喪葬費用保險金的給付 | 附表二：完全失能程度表</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "Q", "point": "12歲的被保險人可以有健康促進保險費折減嗎？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:41:22</t>
+  </si>
+  <si>
+    <t>ZDN</t>
+  </si>
+  <si>
+    <t>被保險人於投保鍾心滿溢後的第10天就罹患慢性腎衰竭，請問可以申領重大傷病保險金嗎？</t>
+  </si>
+  <si>
+    <t>回答：  
+被保險人於投保後第10天罹患慢性腎衰竭，無法申領重大傷病保險金。根據條款規定，重大傷病保險金的給付需符合等待期間的要求，而慢性腎衰竭屬於需等待90日的項目。若於等待期間內罹患重大傷病，契約自始無效，本公司僅退還已繳保險費。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+  </si>
+  <si>
+    <t>第二十二條 重大傷病保險金、特定重大傷病保險金的申領 | 第二條 名詞定義 | 第十二條 重大傷病保險金的給付 | 第三十條 不保事項 | 附表一：全民健康保險重大傷病項目</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "1", "point": "確認重大傷病保險金是否涵蓋慢性腎衰竭", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認重大傷病保險金的申領條件", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認慢性腎衰竭是否符合保單中的重大傷病定義", "must_have": false, "分數": 1.0}, {"id": "4", "point": "確認保單是否有等待期規定及其影響", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:41:53</t>
+  </si>
+  <si>
+    <t>CFE</t>
+  </si>
+  <si>
+    <t>投保自由配重大傷病後，若在契約生效後80天罹患第一期乳癌，會拿到理賠金嗎?</t>
+  </si>
+  <si>
+    <t>回答：  
+1. 自由配重大傷病保險涵蓋第一期乳癌，屬於「需積極或長期治療之癌症」範圍，且在附表一中明確列為保障項目。  
+2. 契約生效後的等待期間為90天，針對「需積極或長期治療之癌症」適用。因此，若在生效後80天罹患第一期乳癌，尚未超過等待期間，依條款規定，本契約自始無效，保險公司將無息退還已繳保險費。  
+條文依據：  
+- [第二條 名詞定義]  
+- [第十一條 重大傷病保險金的給付]</t>
+  </si>
+  <si>
+    <t>第二條 名詞定義 | 附表一：全民健康保險重大傷病項目 | 第十一條 重大傷病保險金的給付 | 第十五條 不保事項 | 第十四條 除外責任</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "1", "point": "確認自由配重大傷病保險是否涵蓋第一期乳癌", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認契約生效後的等待期規定是否影響理賠", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認理賠金額及相關條件是否符合保單規定", "must_have": false, "分數": 0.5}], "coverage_score": 0.9444, "C_conf": 0.9444}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:42:45</t>
+  </si>
+  <si>
+    <t>要保人想要終止國泰人壽自由配CFE契約，能否退保費?</t>
+  </si>
+  <si>
+    <t>回答：  
+要保人可以終止契約，並退還未到期保險費。本公司會從已繳保險費中扣除按短期費率計算的已經過期間保險費後，將未到期保險費無息退還給要保人。
+條文依據：  
+- [第九條 契約的終止（一）]</t>
+  </si>
+  <si>
+    <t>第九條 契約的終止（一） | 第十五條 不保事項 | 第五條 契約有效期間及保證續保 | 第七條 本契約效力的恢復 | 第六條 續保保險費的交付、寬限期間及契約效力的停止 | 附表二：短期費率表</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "Q", "point": "要保人想要終止國泰人壽自由配CFE契約，能否退保費?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:43:13</t>
+  </si>
+  <si>
+    <t>投保國泰人壽自由配CFE，若在等待期間內罹患重大傷病，要如何給付?</t>
+  </si>
+  <si>
+    <t>回答：  
+1. 國泰人壽自由配CFE保險涵蓋重大傷病保障，並提供「重大傷病保險金」的給付。  
+2. 若被保險人在等待期間內罹患重大傷病，依條款規定，若該重大傷病是因意外傷害事故所致，則不受等待期間限制，仍可申請重大傷病保險金；但若因其他原因（非意外傷害事故）罹患重大傷病，則本契約自始無效，本公司將無息退還已繳保險費予要保人。
+條文依據：  
+- [第十一條 重大傷病保險金的給付]  
+- [第十五條 不保事項]</t>
+  </si>
+  <si>
+    <t>第十一條 重大傷病保險金的給付 | 第十五條 不保事項 | 第十四條 除外責任 | payout_items | 附表一：全民健康保險重大傷病項目</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "1", "point": "確認國泰人壽自由配CFE保險是否涵蓋重大傷病保障", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認等待期間內重大傷病的給付條件", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認重大傷病的定義及範圍", "must_have": false, "分數": 0.5}], "coverage_score": 0.9444, "C_conf": 0.9444}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:43:41</t>
+  </si>
+  <si>
+    <t>投保自由配一年定期初次罹患重大傷病健康保險後，於第三年罹患先天性肌肉萎縮症，可以申領重大傷病保險金嗎？</t>
+  </si>
+  <si>
+    <t>回答：  
+1. 自由配一年定期重大傷病健康保險的保障範圍不包含「先天性肌肉萎縮症」，因其在附表一中標註為「否」，不屬於全民健康保險重大傷病項目。  
+2. 由於「先天性肌肉萎縮症」不在保障範圍內，即使於第三年罹患，也無法申領重大傷病保險金。  
+條文依據：  
+- [第十一條 重大傷病保險金的給付]  
+- [附表一：全民健康保險重大傷病項目]</t>
+  </si>
+  <si>
+    <t>第十一條 重大傷病保險金的給付 | 第十三條 重大傷病保險金的申領 | 附表一：全民健康保險重大傷病項目 | 第十五條 不保事項 | other_metadata</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "1", "point": "確認自由配一年定期重大傷病健康保險的保障範圍是否包含先天性肌肉萎縮症。", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認重大傷病保險金的申領條件是否適用於第三年罹患的情況。", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認保險條款中是否有關於先天性疾病的除外責任或限制。", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:44:28</t>
+  </si>
+  <si>
+    <t>CFG</t>
+  </si>
+  <si>
+    <t>自由配重大疾病(甲型)保障的重大疾病有哪些疾病?</t>
+  </si>
+  <si>
+    <t>回答：  
+自由配重大疾病(甲型)保障的重大疾病包括以下疾病：  
+1. 腦中風後障礙(重度)  
+2. 癱瘓(重度)  
+3. 癌症(重度)  
+4. 急性心肌梗塞(重度)  
+5. 冠狀動脈繞道手術  
+6. 末期腎病變  
+7. 重大器官移植或造血幹細胞移植  
+條文依據：  
+- [第二條 名詞定義]</t>
+  </si>
+  <si>
+    <t>國泰人壽自由配一年定期初次罹患重大疾病健康保險(甲型)年繳費率表 | payout_items | 第二條 名詞定義</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "Q", "point": "自由配重大疾病(甲型)保障的重大疾病有哪些疾病?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:44:46</t>
+  </si>
+  <si>
+    <t>DPA</t>
+  </si>
+  <si>
+    <t>被保險人領了2次癌症(重度)追蹤照護金後身故，是否還有尚未給付的保險金供受益人領取?</t>
+  </si>
+  <si>
+    <t>回答：  
+1. 癌症(重度)追蹤照護金的給付次數不影響其他保險金的領取資格，因為條文中未提及該項給付次數會限制其他保險金的申領。  
+2. 身故後是否有其他保險金可供受益人領取，需檢視保單是否包含身故保險金或其他相關保障。根據第二十八條，若被保險人身故時仍有未給付或未完全給付的保險金，則該部分保險金的受益人為被保險人身故時之法定繼承人。然而，提供的條文中未明確提及身故保險金或其他相關保障，因此無法確認是否有尚未給付的保險金供受益人領取。  
+條文依據：  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供]  
+- [第二十八條 受益人]</t>
+  </si>
+  <si>
+    <t>第二十八條 受益人 | 第十一條 契約的終止（三） | 第二十三條 癌症保險金或罹癌基因檢測服務的申領 | 第二十二條 保險事故的通知與保險給付的申請時間 | 第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)</t>
+  </si>
+  <si>
+    <t>回答：  
+1. 癌症(重度)追蹤照護金的給付次數不影響其他保險金的領取資格，因為條文中未提及該項給付次數會限制其他保險金的申領。  
+2. 身故後是否有其他保險金可供受益人領取，需檢視保單是否包含身故保險金或其他相關保障。然而，提供的條文中未提及身故保險金或其他相關保障，因此無法確認。  
+條文依據：  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供]  
+- [第十三條 初次罹患癌症(重度)保險金的給付]  
+- [第二十三條 癌症保險金或罹癌基因檢測服務的申領]</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "1", "point": "確認癌症(重度)追蹤照護金的給付次數是否影響其他保險金的領取資格", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認身故後是否有其他保險金可供受益人領取", "must_have": true, "分數": 0.8}, {"id": "3", "point": "確認保單中是否包含身故保險金或其他相關保障", "must_have": false, "分數": 1.0}, {"id": "4", "point": "確認保險金給付條件是否已完全符合保單約定", "must_have": false, "分數": 0.5}], "coverage_score": 0.87, "C_conf": 0.87}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:45:48</t>
+  </si>
+  <si>
+    <t>保險金額2萬元，「罹癌基因檢測服務」費用8萬元，還會給付多少「癌症(重度)追蹤照護保險金」？</t>
+  </si>
+  <si>
+    <t>回答：  
+根據條款，若被保險人選擇申領「罹癌基因檢測服務」，且該服務費用（8萬元）高於「罹癌基因檢測服務額度」（1,000元），則被保險人僅能申領「癌症(重度)追蹤照護保險金」。因此，保險公司將依「癌症(重度)追蹤照護保險金」的計算方式給付，金額為保險金額（2萬元）的12倍，即24萬元。  
+條文依據：  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]  
+- [附件一：罹癌基因檢測服務之項目、服務費用及補償金額表]</t>
+  </si>
+  <si>
+    <t>第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用) | 第二十三條 癌症保險金或罹癌基因檢測服務的申領 | 附件一：罹癌基因檢測服務之項目、服務費用及補償金額表 | 第十三條 初次罹患癌症(重度)保險金的給付 | 第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用)</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "1", "point": "確認癌症(重度)追蹤照護保險金的給付條件與計算方式", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認罹癌基因檢測服務費用是否影響保險金額計算", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認保險金額2萬元是否為總額或部分給付", "must_have": false, "分數": 0.5}], "coverage_score": 0.9444, "C_conf": 0.9444}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:46:24</t>
+  </si>
+  <si>
+    <t>投保後1個月罹患重度癌症，會給付哪些保險金？契約還會持續有效嗎？</t>
+  </si>
+  <si>
+    <t>回答：  
+1. 若被保險人在投保後1個月內診斷確定罹患「癌症(重度)」，因診斷確定日屬於第一保險單年度內，僅可申領「初次罹患癌症(重度)保險金」，給付金額為「年繳應繳保險費」的1.06倍。  
+2. 契約仍會持續有效，但當期已繳付之未到期保險費不予退還，且續期保險費不會豁免。
+條文依據：  
+- [第十三條 初次罹患癌症(重度)保險金的給付]  
+- [第十六條 癌症(重度)豁免保險費(第二保險單年度起適用)]</t>
+  </si>
+  <si>
+    <t>第十六條 癌症(重度)豁免保險費(第二保險單年度起適用) | 第十三條 初次罹患癌症(重度)保險金的給付 | 第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用) | 第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付 | 第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用)</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "Q", "point": "投保後1個月罹患重度癌症，會給付哪些保險金？契約還會持續有效嗎？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:46:45</t>
+  </si>
+  <si>
+    <t>投保後10個月罹患重度癌症，會給付哪些保險金？契約還會持續有效嗎？</t>
+  </si>
+  <si>
+    <t>回答：  
+1. 若被保險人在投保後10個月（即第一保險單年度內）診斷確定罹患重度癌症，依第十三條規定，本公司將給付「初次罹患癌症(重度)保險金」，金額為「年繳應繳保險費」的一點零六倍。  
+2. 契約將繼續有效，因第十條所述的契約終止條件僅適用於生效日起九十日內診斷確定罹患癌症的情況，超過九十日後不適用該條款。
+條文依據：  
+- [第十三條 初次罹患癌症(重度)保險金的給付]  
+- [第十條 契約的終止（二）]</t>
+  </si>
+  <si>
+    <t>第十六條 癌症(重度)豁免保險費(第二保險單年度起適用) | 第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用) | 第十條 契約的終止（二） | 第十三條 初次罹患癌症(重度)保險金的給付 | 第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "Q", "point": "投保後10個月罹患重度癌症，會給付哪些保險金？契約還會持續有效嗎？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:46:51</t>
+  </si>
+  <si>
+    <t>投保醫心康愛，罹患肺癌一期，可領什麼保險金？</t>
+  </si>
+  <si>
+    <t>回答：  
+若被保險人於本契約有效期間內，初次診斷確定罹患肺癌一期，屬於「癌症(初期)或癌症(輕度)」，可申領「初次罹患癌症(初期)或癌症(輕度)保險金」。給付金額依診斷確定日所在的保險單年度而定：  
+1. 若診斷確定日在第一保險單年度內，給付「年繳應繳保險費」的1.06倍。  
+2. 若診斷確定日在第二保險單年度(含)以後，給付「保險金額」的5倍。  
+此保險金最多給付一次。
+條文依據：  
+- [第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付]</t>
+  </si>
+  <si>
+    <t>第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付 | 第十三條 初次罹患癌症(重度)保險金的給付 | payout_items | 第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用) | 第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "Q", "point": "投保醫心康愛，罹患肺癌一期，可領什麼保險金？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:46:57</t>
+  </si>
+  <si>
+    <t>PX5</t>
+  </si>
+  <si>
+    <t>若被保險人身故有何給付?</t>
+  </si>
+  <si>
+    <t>回答：  
+被保險人身故時，若本附約保險金尚未給付或未完全給付，則該部分保險金的受益人為被保險人的法定繼承人，並依被保險人身故時的法定繼承人順序及應得比例，適用民法繼承編的相關規定。
+條文依據：  
+- [第二十條 受益人]</t>
+  </si>
+  <si>
+    <t>第二十條 受益人 | 第十二條 重大疾病保險金的給付 | 第十一條 輕度重大疾病保險金的給付 | 第十四條 保險事故的通知與保險金的申請時間 | 第二條 名詞定義</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "Q", "point": "若被保險人身故有何給付?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:47:05</t>
+  </si>
+  <si>
+    <t>投保鍾溢祝福後，請問在第二年經醫院醫師初次診斷罹患「輕度重大疾病」中的癌症(輕度)者，可以領到輕度重大疾病保險金嗎?可以領到保險金額的百分之多少?</t>
+  </si>
+  <si>
+    <t>回答：  
+1. 輕度重大疾病保險金的給付範圍涵蓋「輕度癌症」，包括符合條件的第一期癌症（如第一期乳癌、第一期子宮頸癌等），但不包括原位癌、零期癌及其他條款中明確列出的排除項目。  
+2. 若被保險人在第二年（即續保年度）經醫院醫師初次診斷罹患「輕度癌症」，且診斷確定日位於續保年度內，則符合輕度重大疾病保險金的理賠條件。  
+3. 在續保年度內，輕度重大疾病保險金的給付比例為保險金額的20%。  
+4. 保單中對於「輕度癌症」的例外條款包括：原位癌、零期癌、第一期惡性類癌，以及第二期（含）以下且非惡性黑色素瘤的皮膚癌等，這些情況不屬於理賠範圍。
+條文依據：  
+- [第十一條 輕度重大疾病保險金的給付]  
+- [第二條 名詞定義]</t>
+  </si>
+  <si>
+    <t>第十一條 輕度重大疾病保險金的給付 | 第十二條 重大疾病保險金的給付 | payout_items | other_metadata | 第二條 名詞定義</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "1", "point": "確認輕度重大疾病保險金是否涵蓋輕度癌症", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認第二年投保後是否符合輕度重大疾病保險金的理賠條件", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認輕度重大疾病保險金額的給付比例", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認保單中是否有特定輕度癌症的例外條款", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:47:34</t>
+  </si>
+  <si>
+    <t>請問如果在投保後的第三年經醫院醫師初次診斷罹患「重大疾病」者，可以領到重大疾病保險金嗎?可以領到保險金額的百分之多少?那後續又在第四年經醫院醫師初次診斷罹患「輕度重大疾病」者，可以領到輕度重大疾病保險金嗎?可以領到保險金額的百分之多少?</t>
+  </si>
+  <si>
+    <t>回答：  
+1. 在投保後的第三年經醫院醫師初次診斷罹患「重大疾病」者，符合重大疾病保險金的給付條件，因診斷確定日位於續保年度內，可領取保險金額的1.3倍。  
+2. 在第四年經醫院醫師初次診斷罹患「輕度重大疾病」者，符合輕度重大疾病保險金的給付條件，因診斷確定日位於續保年度內，可領取保險金額的20%。  
+條文依據：  
+- [第十二條 重大疾病保險金的給付]  
+- [第十一條 輕度重大疾病保險金的給付]</t>
+  </si>
+  <si>
+    <t>第十二條 重大疾病保險金的給付 | 第十一條 輕度重大疾病保險金的給付 | payout_items | 第十六條 除外責任 | 第二條 名詞定義</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "1", "point": "確認重大疾病保險金的給付條件是否符合第三年初次診斷重大疾病的情況", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認重大疾病保險金額的給付比例", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認輕度重大疾病保險金的給付條件是否符合第四年初次診斷輕度重大疾病的情況", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認輕度重大疾病保險金額的給付比例", "must_have": true, "分數": 1.0}, {"id": "5", "point": "確認重大疾病與輕度重大疾病的定義及區分標準", "must_have": false, "分數": 0.0}], "coverage_score": 0.9412, "C_conf": 0.9412}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:48:27</t>
+  </si>
+  <si>
+    <t>請問如果在投保後的第三年經醫院醫師初次診斷罹患「輕度重大疾病」者，可以領到重大疾病保險金嗎?可以領到保險金額的百分之多少?那後續又在第四年經醫院醫師初次診斷罹患「重大疾病」者，可以領到輕度重大疾病保險金嗎?可以領到保險金額的百分之多少?</t>
+  </si>
+  <si>
+    <t>回答：  
+1. 在投保後的第三年，若經醫院醫師初次診斷罹患「輕度重大疾病」，符合保險金給付條件，可領取「輕度重大疾病保險金」，給付比例為保險金額的20%。  
+2. 在第四年，若經醫院醫師初次診斷罹患「重大疾病」，符合保險金給付條件，但因已領取過「輕度重大疾病保險金」，需扣除已給付的金額，最終可領取的「重大疾病保險金」為保險金額的130%減去已給付的20%，即保險金額的110%。  
+條文依據：  
+- [第十一條 輕度重大疾病保險金的給付]  
+- [第十二條 重大疾病保險金的給付]</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "1", "point": "確認輕度重大疾病是否符合保險金給付條件", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認重大疾病是否符合保險金給付條件", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認輕度重大疾病保險金額的給付比例", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認重大疾病保險金額的給付比例", "must_have": true, "分數": 1.0}, {"id": "5", "point": "確認輕度重大疾病與重大疾病保險金是否有重疊或影響", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:49:36</t>
+  </si>
+  <si>
+    <t>請問主約效力終止(因身故以外情形)，PX5還能持續有效嗎？</t>
+  </si>
+  <si>
+    <t>回答：  
+主約效力若因「身故以外情形」終止，PX5附約仍可持續有效，但需符合以下條件：  
+1. 附約保險期間屆滿時，要保人需繼續繳交附約保險費。  
+2. 附約效力可延續至主契約原保險期間屆滿或附約最高續保年齡（以二者較早屆至之日為準）。  
+條文依據：  
+- [第十條 附約的終止（二）]</t>
+  </si>
+  <si>
+    <t>第十條 附約的終止（二） | 第七條 保險費的墊繳、附約的停效及復效 | 第五條 附約的保險期間及保證續保 | 第十三條 健康促進保險費折減 | 第九條 附約的終止（一）</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "Q", "point": "請問主約效力終止(因身故以外情形)，PX5還能持續有效嗎？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:49:55</t>
+  </si>
+  <si>
+    <t>FSAFSB</t>
+  </si>
+  <si>
+    <t>請問如果於「無理賠紀錄期間」屆滿日以內罹患特定傷病，會給付多少錢?這筆錢會給付給誰?</t>
+  </si>
+  <si>
+    <t>回答：  
+若被保險人在「無理賠紀錄期間」屆滿日以內罹患特定傷病，保險公司將給付的金額為「保險金額」加上「年繳應繳保險費總額」乘以1.02的加總。這筆「特定傷病保險金」的受益人為被保險人本人，且不得指定或變更受益人。
+條文依據：  
+- [第十一條 特定傷病保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+  </si>
+  <si>
+    <t>第五條 保險範圍 | 第十二條 無理賠關懷保險金的給付 | 第十一條 特定傷病保險金的給付 | payout_items | 第二十七條 受益人的指定及變更</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "Q", "point": "請問如果於「無理賠紀錄期間」屆滿日以內罹患特定傷病，會給付多少錢?這筆錢會給付給誰?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:50:02</t>
+  </si>
+  <si>
+    <t>請問如果要保人與被保險人為同一人，被保險人於「無理賠紀錄期間」屆滿日以內身故，會給付多少錢?這筆錢會給付給誰?</t>
+  </si>
+  <si>
+    <t>回答：  
+若要保人與被保險人為同一人，且被保險人於「無理賠紀錄期間」屆滿日以內身故，依據條款規定，本公司將給付「無理賠關懷保險金」，其金額為「年繳應繳保險費總額」乘以1.02。該筆保險金的受益人為要保人本人，若要保人與被保險人為同一人，則受益人為被保險人本人；若被保險人已身故，則受益人為被保險人的法定繼承人。
+條文依據：  
+- [第十二條 無理賠關懷保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+  </si>
+  <si>
+    <t>第十二條 無理賠關懷保險金的給付 | 第五條 保險範圍 | 第十一條 特定傷病保險金的給付 | 第十九條 失蹤處理 | 第二十七條 受益人的指定及變更</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "1", "point": "確認保險契約中身故保險金的給付金額計算方式", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認身故保險金的受益人為誰", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認「無理賠紀錄期間」屆滿日的定義及影響", "must_have": false, "分數": 0.5}], "coverage_score": 0.9444, "C_conf": 0.9444}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:50:25</t>
+  </si>
+  <si>
+    <t>請問如果要保人與被保險人為不同人，被保險人於「無理賠紀錄期間」屆滿日以內生存，且被保險人未罹患特定傷病，會給付多少錢?這筆錢會給付給誰?</t>
+  </si>
+  <si>
+    <t>回答：  
+若被保險人在「無理賠紀錄期間」屆滿日以內生存，且未罹患特定傷病，符合條件可給付「無理賠關懷保險金」。給付金額為「年繳應繳保險費總額」乘以1.02。此筆保險金的受益人為要保人本人，若要保人已身故，則以被保險人為受益人；若被保險人也已身故，則以被保險人之法定繼承人為受益人。
+條文依據：  
+- [第十二條 無理賠關懷保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+  </si>
+  <si>
+    <t>第十二條 無理賠關懷保險金的給付 | 第十一條 特定傷病保險金的給付 | 第五條 保險範圍 | 第二十七條 受益人的指定及變更 | 第十九條 失蹤處理</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "1", "point": "確認被保險人於無理賠紀錄期間屆滿日以內生存的條件", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認被保險人未罹患特定傷病的條件", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認給付金額的計算方式或標準", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認給付金的受益人為誰", "must_have": true, "分數": 1.0}, {"id": "5", "point": "確認保險契約中是否有相關條款限制或附加條件", "must_have": false, "分數": 0.8}], "coverage_score": 0.9882, "C_conf": 0.9882}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:51:02</t>
+  </si>
+  <si>
+    <t>保戶如果身故，會給保險金嗎?</t>
+  </si>
+  <si>
+    <t>回答：  
+保戶（被保險人）若於契約有效期間內身故，是否給付保險金需視具體情況而定。例如：  
+1. 若被保險人於「無理賠紀錄期間」內身故，本公司依第五條約定給付保險金。  
+2. 若被保險人因除外責任中的情形（如故意自殺於契約訂立或復效未滿二年內）身故，則本公司不負給付責任，但契約訂立或復效滿二年後故意自殺致死者，仍給付保險金。  
+條文依據：  
+- [第五條 保險範圍]  
+- [第十七條 除外責任（二）]</t>
+  </si>
+  <si>
+    <t>第五條 保險範圍 | 第二十八條 本契約受益人死亡或失蹤的處理 | 第十七條 除外責任（二） | 第二十三條 受益人受益權之喪失 | 第十九條 失蹤處理</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "Q", "point": "保戶如果身故，會給保險金嗎?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:51:24</t>
+  </si>
+  <si>
+    <t>保戶如果身故，身故申領的保險金會給誰?</t>
+  </si>
+  <si>
+    <t>回答：  
+保戶身故後，身故保險金的受益人依以下情況處理：  
+1. 若受益人已指定，則由指定的受益人領取。  
+2. 若受益人未指定或受益人喪失受益權，則保險金作為被保險人的遺產，由其法定繼承人依民法繼承編相關規定分配。  
+3. 若特定傷病保險金尚未給付或未完全給付，則該部分保險金的受益人為被保險人的法定繼承人。  
+條文依據：  
+- [第二十三條 受益人受益權之喪失]  
+- [第二十七條 受益人的指定及變更]</t>
+  </si>
+  <si>
+    <t>第五條 保險範圍 | 第二十三條 受益人受益權之喪失 | 第二十七條 受益人的指定及變更 | 第二十八條 本契約受益人死亡或失蹤的處理 | 第二十二條 分期定期保險金給付申領文件、給付期限及未依限給付之效果</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "Q", "point": "保戶如果身故，身故申領的保險金會給誰?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:51:31</t>
+  </si>
+  <si>
+    <t>如果保戶投保繳費年期20年的滿溢寶，然後在第20保單年度身故的話，可以領到多少錢?</t>
+  </si>
+  <si>
+    <t>回答：  
+根據條款，滿溢寶保險的身故給付條款規定，被保險人在「無理賠紀錄期間」內身故，本公司將依約定給付保險金。保單繳費年期20年並未明確影響身故給付金額，且條款中未提及第20保單年度的身故有任何特別條件或額外給付。
+條文依據：  
+- [第五條 保險範圍]</t>
+  </si>
+  <si>
+    <t>第二十六條 投保年齡的計算及錯誤的處理 | other_metadata | 第五條 保險範圍 | 第二十二條 分期定期保險金給付申領文件、給付期限及未依限給付之效果 | 第十九條 失蹤處理</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "1", "point": "確認滿溢寶保險的身故給付條款", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認保單繳費年期20年是否影響身故給付金額", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認第20保單年度的身故是否有特別條件或額外給付", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:51:53</t>
+  </si>
+  <si>
+    <t>被保險人為60歲女性，投保繳費期間20年期之滿溢寶特定傷病定期健康保險（定期給付型）（外溢型）100萬元，年繳應繳保險費為83,500元，年繳實繳保險費為78,490元。若被保險人於第二保險單年度自殺身故，則無理賠關懷保險金可以領到多少錢？</t>
+  </si>
+  <si>
+    <t>回答：  
+被保險人於第二保險單年度自殺身故，根據條款規定，自契約訂立或復效之日起二年內因故意自殺致死者，本公司不負給付無理賠關懷保險金的責任。因此，無理賠關懷保險金無法領取。
+條文依據：  
+- [第十七條 除外責任（二)]  
+- [第十二條 無理賠關懷保險金的給付]</t>
+  </si>
+  <si>
+    <t>第十二條 無理賠關懷保險金的給付 | 第十七條 除外責任（二） | 第二十七條 受益人的指定及變更 | 第二十一條 無理賠關懷保險金的申領 | 第十九條 失蹤處理</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "1", "point": "確認保險契約中自殺身故的理賠條款", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認第二保險單年度是否屬於等待期內", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認關懷保險金的計算方式及適用條件", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認年繳實繳保險費是否影響理賠金額", "must_have": false, "分數": 0.0}, {"id": "5", "point": "確認保險金額100萬元是否為理賠上限", "must_have": false, "分數": 0.0}], "coverage_score": 0.8571, "C_conf": 0.8571}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:52:29</t>
+  </si>
+  <si>
+    <t>SC1</t>
+  </si>
+  <si>
+    <t>請問如果第2保單年度罹患特定傷病，可以給付多少錢?給付給誰?未來還有其他保險金嗎?</t>
+  </si>
+  <si>
+    <t>回答：  
+若被保險人在第二保險單年度（含）以後罹患特定傷病，依條款規定：  
+1. **給付金額**：本公司將依「保險金額」給付「特定傷病保險金」。  
+2. **給付對象**：保險金給付予被保險人或其指定受益人。  
+3. **未來保險金**：自初次診斷確定罹患特定傷病的次一個保險單週年日起，每逢保險單週年日仍生存者，本公司將按「保險金額」的36%給付「生活補助保險金」，最多給付10次。此外，自診斷確定日起，續期保險費將豁免，但當期已繳付之未到期保險費不予退還。
+條文依據：  
+- [第十二條 特定傷病保險金的給付]  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]  
+- [第十五條 保險費豁免（第二保險單年度起適用）]</t>
+  </si>
+  <si>
+    <t>第十二條 特定傷病保險金的給付 | 第五條 保險範圍 | 第十三條 生活補助保險金的給付（第二保險單年度起適用） | 第二條 名詞定義 | 第十五條 保險費豁免（第二保險單年度起適用）</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "Q", "point": "請問如果第2保單年度罹患特定傷病，可以給付多少錢?給付給誰?未來還有其他保險金嗎?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:52:55</t>
+  </si>
+  <si>
+    <t>請問我115年1月1日投保，怎麼得到健康促進保險費折減?</t>
+  </si>
+  <si>
+    <t>回答：  
+要獲得健康促進保險費折減，您需要在保單有效期間內完成以下步驟：  
+1. 使用保險公司指定的程式並加入指定的健康計劃。  
+2. 完成程式註冊程序，並授權保險公司取得與健康促進相關的電子紀錄。  
+3. 根據成功傳輸的電子紀錄，保險公司將依其辦法計算您的會員等級。  
+4. 若於「指定日期」的會員等級符合標準，則次一保險單年度的保險費可按以下比例折減：  
+   - 實踐家：3%  
+   - 樂享家或高於樂享家的會員等級：10%  
+注意：復效或豁免的保險費不適用此折減約定。
+條文依據：  
+- [第十六條 健康促進保險費折減]</t>
+  </si>
+  <si>
+    <t>第十六條 健康促進保險費折減 | 第二十三條 投保年齡的計算及錯誤的處理 | 第十五條 保險費豁免（第二保險單年度起適用） | 第五條 保險範圍 | payout_items</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "Q", "point": "請問我115年1月1日投保，怎麼得到健康促進保險費折減?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:53:13</t>
+  </si>
+  <si>
+    <t>保戶在114/1/10投保樂鍾溢，如果他在115/3/30罹患特定傷病的話，在什麼時候可以領取生活補助保險金?</t>
+  </si>
+  <si>
+    <t>回答：  
+1. 樂鍾溢保險包含生活補助保險金保障，依據第十三條規定，生活補助保險金的給付條件為被保險人在第二保險單年度（含）以後的有效期間內，初次診斷確定罹患特定傷病，並自初次診斷確定罹患特定傷病的次一個保險單週年日起，每逢保險單週年日仍生存者，給付生活補助保險金。  
+2. 該保戶於115/3/30診斷確定罹患特定傷病，符合生活補助保險金的理賠條件，因其診斷日已超過等待期間（30日），且發生於第二保險單年度內。  
+3. 生活補助保險金的給付時間為初次診斷確定罹患特定傷病的次一個保險單週年日開始，並於每逢保險單週年日仍生存時給付。該保戶的保險單生效日為114/1/10，因此保險單週年日為每年的1月10日。由於診斷日為115/3/30，次一個保險單週年日為116/1/10，該保戶可於此日起領取第一筆生活補助保險金。  
+條文依據：  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]  
+- [第十二條 特定傷病保險金的給付]  
+- [國泰人壽樂鍾心特定傷病定期健康保險（外溢型）]</t>
+  </si>
+  <si>
+    <t>第十三條 生活補助保險金的給付（第二保險單年度起適用） | other_metadata | 第十二條 特定傷病保險金的給付 | 第十一條 契約的終止（三） | 第十條 契約的終止（二）</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "1", "point": "確認樂鍾溢保險是否包含生活補助保險金保障", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認特定傷病是否符合生活補助保險金的理賠條件", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認生活補助保險金的給付時間或條件", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認保單生效日與特定傷病發生日的關聯性", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:53:39</t>
+  </si>
+  <si>
+    <t>保戶在114/1/10投保樂鍾溢，如果他在115/3/30罹患特定傷病的話，他在115/1/9會領到無理賠回饋保險金嗎?</t>
+  </si>
+  <si>
+    <t>回答：  
+保戶在115/1/9無法領取無理賠回饋保險金，原因如下：  
+1. 根據第十四條，無理賠回饋保險金的條件為「被保險人於保險單年度末未曾因罹患特定傷病而申領特定傷病保險金，且仍生存」。  
+2. 保戶於114/1/10投保，保險單年度末為115/1/9。根據第十二條，特定傷病的等待期間為30日，且保戶在115/3/30罹患特定傷病，並未於115/1/9前申領特定傷病保險金，因此符合未申領條件。  
+3. 然而，無理賠回饋保險金需於保險單年度末（115/1/9）仍生存，並由受益人申領（第十四條及第二十條）。題目未提及保戶是否於115/1/9申領相關保險金，且未提供是否已提交申領所需文件，因此無法確認是否符合完整申領程序。
+條文依據：  
+- [第十四條 無理賠回饋保險金的給付]  
+- [第十二條 特定傷病保險金的給付]  
+- [第二十條 無理賠回饋保險金的申領]</t>
+  </si>
+  <si>
+    <t>第十四條 無理賠回饋保險金的給付 | payout_items | 第二十條 無理賠回饋保險金的申領 | 第十二條 特定傷病保險金的給付 | other_metadata</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "1", "point": "確認樂鍾溢保險的無理賠回饋保險金條件", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認保戶在115/1/9是否符合無理賠回饋保險金的領取資格", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認特定傷病是否影響無理賠回饋保險金的領取資格", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:54:26</t>
+  </si>
+  <si>
+    <t>被保險人於第一保險單年度罹患急性心肌梗塞（重度），生活補助保險金最多可以領取幾次？</t>
+  </si>
+  <si>
+    <t>回答：  
+被保險人於第一保險單年度罹患急性心肌梗塞（重度），無法申領生活補助保險金，因為生活補助保險金僅適用於第二保險單年度（含）以後的有效期間內。  
+條文依據：  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]  
+- [第二條 名詞定義]</t>
+  </si>
+  <si>
+    <t>第十一條 契約的終止（三） | 第十三條 生活補助保險金的給付（第二保險單年度起適用） | 第二條 名詞定義 | 第十二條 特定傷病保險金的給付 | 第十九條 特定傷病保險金、生活補助保險金或保險費豁免的申領</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "1", "point": "確認生活補助保險金是否涵蓋急性心肌梗塞（重度）", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認第一保險單年度內生活補助保險金的給付次數上限", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認生活補助保險金的申請條件與限制", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:55:30</t>
+  </si>
+  <si>
+    <t>被保險人為60歲女性，投保繳費期間20年期之樂鍾心特定傷病定期健康保險（外溢型）5單位，每單位年繳應繳保險費為1675元，則每逢保險單年度末生存者，可以領取多少無理賠關懷保險金？</t>
+  </si>
+  <si>
+    <t>回答：  
+1. 樂鍾心特定傷病定期健康保險（外溢型）包含無理賠回饋保險金的保障內容，條件為被保險人於保險單年度末仍生存，且未曾因罹患特定傷病申領特定傷病保險金。  
+2. 每逢保險單年度末生存者，可領取的無理賠回饋保險金金額為：每單位年繳應繳保險費的10%（元以下無條件進位）乘以單位數。計算如下：  
+   - 每單位年繳應繳保險費為1675元，10%為167.5元，無條件進位後為168元。  
+   - 單位數為5單位，因此168元 × 5 = 840元。  
+   - 每逢保險單年度末生存者，可領取840元的無理賠回饋保險金。
+條文依據：  
+- [第十四條 無理賠回饋保險金的給付]</t>
+  </si>
+  <si>
+    <t>第十四條 無理賠回饋保險金的給付 | 第五條 保險範圍 | 第十三條 生活補助保險金的給付（第二保險單年度起適用） | other_metadata | 第十二條 特定傷病保險金的給付</t>
+  </si>
+  <si>
+    <t>{"points": [{"id": "1", "point": "確認樂鍾心特定傷病定期健康保險（外溢型）是否包含無理賠關懷保險金的保障內容", "must_have": true, "分數": 1.0}, {"id": "2", "point": "計算每逢保險單年度末生存者可領取的無理賠關懷保險金金額", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認5單位保險的年繳保險費與無理賠關懷保險金的計算方式之關聯", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:56:17</t>
   </si>
 </sst>
 </file>
@@ -439,7 +2197,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:N84"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -454,7 +2212,7 @@
     <col min="13" max="13" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -495,17 +2253,3165 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="F2" s="2"/>
+    <row r="2" spans="1:14" ht="120">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="3"/>
+      <c r="I2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="3">
+        <v>1</v>
+      </c>
       <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
+      <c r="L2" s="3">
+        <v>1</v>
+      </c>
+      <c r="M2" t="s">
+        <v>19</v>
+      </c>
+      <c r="N2" s="3">
+        <v>15.08</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="165">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" s="3">
+        <v>1</v>
+      </c>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3">
+        <v>1</v>
+      </c>
+      <c r="M3" t="s">
+        <v>24</v>
+      </c>
+      <c r="N3" s="3">
+        <v>5.81</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="195">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J4" s="3">
+        <v>1</v>
+      </c>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3">
+        <v>1</v>
+      </c>
+      <c r="M4" t="s">
+        <v>29</v>
+      </c>
+      <c r="N4" s="3">
+        <v>5.13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="300">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J5" s="3">
+        <v>1</v>
+      </c>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3">
+        <v>1</v>
+      </c>
+      <c r="M5" t="s">
+        <v>34</v>
+      </c>
+      <c r="N5" s="3">
+        <v>19.16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="120">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J6" s="3">
+        <v>1</v>
+      </c>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3">
+        <v>1</v>
+      </c>
+      <c r="M6" t="s">
+        <v>39</v>
+      </c>
+      <c r="N6" s="3">
+        <v>11.32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="150">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J7" s="3">
+        <v>1</v>
+      </c>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3">
+        <v>1</v>
+      </c>
+      <c r="M7" t="s">
+        <v>44</v>
+      </c>
+      <c r="N7" s="3">
+        <v>8.08</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="255">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="J8" s="3">
+        <v>1</v>
+      </c>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3">
+        <v>1</v>
+      </c>
+      <c r="M8" t="s">
+        <v>49</v>
+      </c>
+      <c r="N8" s="3">
+        <v>18.28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="300">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="J9" s="3">
+        <v>1</v>
+      </c>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3">
+        <v>1</v>
+      </c>
+      <c r="M9" t="s">
+        <v>54</v>
+      </c>
+      <c r="N9" s="3">
+        <v>8.4600000000000009</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="398">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E10" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="J10" s="3">
+        <v>1</v>
+      </c>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3">
+        <v>1</v>
+      </c>
+      <c r="M10" t="s">
+        <v>59</v>
+      </c>
+      <c r="N10" s="3">
+        <v>10.38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="409.6">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="J11" s="3">
+        <v>1</v>
+      </c>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3">
+        <v>1</v>
+      </c>
+      <c r="M11" t="s">
+        <v>64</v>
+      </c>
+      <c r="N11" s="3">
+        <v>9.1300000000000008</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="135">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E12" t="s">
+        <v>17</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="J12" s="3">
+        <v>1</v>
+      </c>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3">
+        <v>1</v>
+      </c>
+      <c r="M12" t="s">
+        <v>69</v>
+      </c>
+      <c r="N12" s="3">
+        <v>7.49</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="120">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="J13" s="3">
+        <v>1</v>
+      </c>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3">
+        <v>1</v>
+      </c>
+      <c r="M13" t="s">
+        <v>74</v>
+      </c>
+      <c r="N13" s="3">
+        <v>5.81</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="165">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="J14" s="3">
+        <v>1</v>
+      </c>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3">
+        <v>1</v>
+      </c>
+      <c r="M14" t="s">
+        <v>79</v>
+      </c>
+      <c r="N14" s="3">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="105">
+      <c r="A15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E15" t="s">
+        <v>17</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="J15" s="3">
+        <v>1</v>
+      </c>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3">
+        <v>1</v>
+      </c>
+      <c r="M15" t="s">
+        <v>84</v>
+      </c>
+      <c r="N15" s="3">
+        <v>8.75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="135">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E16" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="J16" s="3">
+        <v>1</v>
+      </c>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3">
+        <v>1</v>
+      </c>
+      <c r="M16" t="s">
+        <v>89</v>
+      </c>
+      <c r="N16" s="3">
+        <v>6.62</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="210">
+      <c r="A17" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E17" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="J17" s="3">
+        <v>1</v>
+      </c>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3">
+        <v>1</v>
+      </c>
+      <c r="M17" t="s">
+        <v>94</v>
+      </c>
+      <c r="N17" s="3">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="270">
+      <c r="A18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E18" t="s">
+        <v>17</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="J18" s="3">
+        <v>1</v>
+      </c>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3">
+        <v>1</v>
+      </c>
+      <c r="M18" t="s">
+        <v>99</v>
+      </c>
+      <c r="N18" s="3">
+        <v>6.73</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="135">
+      <c r="A19" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="J19" s="3">
+        <v>1</v>
+      </c>
+      <c r="K19" s="3"/>
+      <c r="L19" s="3">
+        <v>1</v>
+      </c>
+      <c r="M19" t="s">
+        <v>104</v>
+      </c>
+      <c r="N19" s="3">
+        <v>4.78</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="180">
+      <c r="A20" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="J20" s="3">
+        <v>1</v>
+      </c>
+      <c r="K20" s="3"/>
+      <c r="L20" s="3">
+        <v>1</v>
+      </c>
+      <c r="M20" t="s">
+        <v>109</v>
+      </c>
+      <c r="N20" s="3">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="255">
+      <c r="A21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E21" t="s">
+        <v>17</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="J21" s="3">
+        <v>1</v>
+      </c>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3">
+        <v>1</v>
+      </c>
+      <c r="M21" t="s">
+        <v>114</v>
+      </c>
+      <c r="N21" s="3">
+        <v>38.369999999999997</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="150">
+      <c r="A22" t="s">
+        <v>115</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E22" t="s">
+        <v>17</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J22" s="3">
+        <v>1</v>
+      </c>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3">
+        <v>1</v>
+      </c>
+      <c r="M22" t="s">
+        <v>118</v>
+      </c>
+      <c r="N22" s="3">
+        <v>19.3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="135">
+      <c r="A23" t="s">
+        <v>115</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E23" t="s">
+        <v>17</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="J23" s="3">
+        <v>1</v>
+      </c>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3">
+        <v>1</v>
+      </c>
+      <c r="M23" t="s">
+        <v>123</v>
+      </c>
+      <c r="N23" s="3">
+        <v>5.78</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="225">
+      <c r="A24" t="s">
+        <v>115</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E24" t="s">
+        <v>127</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="J24" s="3">
+        <v>1</v>
+      </c>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3">
+        <v>1</v>
+      </c>
+      <c r="M24" t="s">
+        <v>130</v>
+      </c>
+      <c r="N24" s="3">
+        <v>51.61</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="356">
+      <c r="A25" t="s">
+        <v>115</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E25" t="s">
+        <v>17</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="J25" s="3">
+        <v>1</v>
+      </c>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3">
+        <v>1</v>
+      </c>
+      <c r="M25" t="s">
+        <v>135</v>
+      </c>
+      <c r="N25" s="3">
+        <v>29.35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="398">
+      <c r="A26" t="s">
+        <v>115</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="E26" t="s">
+        <v>17</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="J26" s="3">
+        <v>1</v>
+      </c>
+      <c r="K26" s="3"/>
+      <c r="L26" s="3">
+        <v>1</v>
+      </c>
+      <c r="M26" t="s">
+        <v>140</v>
+      </c>
+      <c r="N26" s="3">
+        <v>8.2200000000000006</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="240">
+      <c r="A27" t="s">
+        <v>115</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E27" t="s">
+        <v>17</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="J27" s="3">
+        <v>1</v>
+      </c>
+      <c r="K27" s="3"/>
+      <c r="L27" s="3">
+        <v>1</v>
+      </c>
+      <c r="M27" t="s">
+        <v>145</v>
+      </c>
+      <c r="N27" s="3">
+        <v>5.39</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="300">
+      <c r="A28" t="s">
+        <v>115</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E28" t="s">
+        <v>17</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="J28" s="3">
+        <v>1</v>
+      </c>
+      <c r="K28" s="3"/>
+      <c r="L28" s="3">
+        <v>1</v>
+      </c>
+      <c r="M28" t="s">
+        <v>150</v>
+      </c>
+      <c r="N28" s="3">
+        <v>5.98</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="270">
+      <c r="A29" t="s">
+        <v>115</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E29" t="s">
+        <v>17</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="J29" s="3">
+        <v>1</v>
+      </c>
+      <c r="K29" s="3"/>
+      <c r="L29" s="3">
+        <v>1</v>
+      </c>
+      <c r="M29" t="s">
+        <v>155</v>
+      </c>
+      <c r="N29" s="3">
+        <v>6.22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="120">
+      <c r="A30" t="s">
+        <v>115</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="E30" t="s">
+        <v>17</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J30" s="3">
+        <v>1</v>
+      </c>
+      <c r="K30" s="3"/>
+      <c r="L30" s="3">
+        <v>1</v>
+      </c>
+      <c r="M30" t="s">
+        <v>158</v>
+      </c>
+      <c r="N30" s="3">
+        <v>6.72</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="210">
+      <c r="A31" t="s">
+        <v>115</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E31" t="s">
+        <v>17</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="J31" s="3">
+        <v>1</v>
+      </c>
+      <c r="K31" s="3"/>
+      <c r="L31" s="3">
+        <v>1</v>
+      </c>
+      <c r="M31" t="s">
+        <v>163</v>
+      </c>
+      <c r="N31" s="3">
+        <v>12.11</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="409.6">
+      <c r="A32" t="s">
+        <v>115</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E32" t="s">
+        <v>17</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="J32" s="3">
+        <v>1</v>
+      </c>
+      <c r="K32" s="3"/>
+      <c r="L32" s="3">
+        <v>1</v>
+      </c>
+      <c r="M32" t="s">
+        <v>168</v>
+      </c>
+      <c r="N32" s="3">
+        <v>12.23</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" ht="210">
+      <c r="A33" t="s">
+        <v>115</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E33" t="s">
+        <v>17</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="J33" s="3">
+        <v>1</v>
+      </c>
+      <c r="K33" s="3"/>
+      <c r="L33" s="3">
+        <v>1</v>
+      </c>
+      <c r="M33" t="s">
+        <v>173</v>
+      </c>
+      <c r="N33" s="3">
+        <v>7.63</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" ht="105">
+      <c r="A34" t="s">
+        <v>115</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E34" t="s">
+        <v>17</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="J34" s="3">
+        <v>1</v>
+      </c>
+      <c r="K34" s="3"/>
+      <c r="L34" s="3">
+        <v>1</v>
+      </c>
+      <c r="M34" t="s">
+        <v>178</v>
+      </c>
+      <c r="N34" s="3">
+        <v>5.41</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" ht="210">
+      <c r="A35" t="s">
+        <v>115</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="E35" t="s">
+        <v>17</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="J35" s="3">
+        <v>1</v>
+      </c>
+      <c r="K35" s="3"/>
+      <c r="L35" s="3">
+        <v>1</v>
+      </c>
+      <c r="M35" t="s">
+        <v>183</v>
+      </c>
+      <c r="N35" s="3">
+        <v>7.02</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" ht="195">
+      <c r="A36" t="s">
+        <v>184</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="E36" t="s">
+        <v>17</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J36" s="3">
+        <v>1</v>
+      </c>
+      <c r="K36" s="3"/>
+      <c r="L36" s="3">
+        <v>1</v>
+      </c>
+      <c r="M36" t="s">
+        <v>187</v>
+      </c>
+      <c r="N36" s="3">
+        <v>4.2699999999999996</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" ht="342">
+      <c r="A37" t="s">
+        <v>184</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E37" t="s">
+        <v>17</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="J37" s="3">
+        <v>1</v>
+      </c>
+      <c r="K37" s="3"/>
+      <c r="L37" s="3">
+        <v>1</v>
+      </c>
+      <c r="M37" t="s">
+        <v>192</v>
+      </c>
+      <c r="N37" s="3">
+        <v>6.73</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" ht="409.6">
+      <c r="A38" t="s">
+        <v>184</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="E38" t="s">
+        <v>17</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="J38" s="3">
+        <v>1</v>
+      </c>
+      <c r="K38" s="3"/>
+      <c r="L38" s="3">
+        <v>1</v>
+      </c>
+      <c r="M38" t="s">
+        <v>197</v>
+      </c>
+      <c r="N38" s="3">
+        <v>7.04</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" ht="370">
+      <c r="A39" t="s">
+        <v>184</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="E39" t="s">
+        <v>17</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="J39" s="3">
+        <v>1</v>
+      </c>
+      <c r="K39" s="3"/>
+      <c r="L39" s="3">
+        <v>1</v>
+      </c>
+      <c r="M39" t="s">
+        <v>202</v>
+      </c>
+      <c r="N39" s="3">
+        <v>7.32</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" ht="165">
+      <c r="A40" t="s">
+        <v>184</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="E40" t="s">
+        <v>17</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="J40" s="3">
+        <v>1</v>
+      </c>
+      <c r="K40" s="3"/>
+      <c r="L40" s="3">
+        <v>1</v>
+      </c>
+      <c r="M40" t="s">
+        <v>207</v>
+      </c>
+      <c r="N40" s="3">
+        <v>6.79</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" ht="342">
+      <c r="A41" t="s">
+        <v>184</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="E41" t="s">
+        <v>17</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="J41" s="3">
+        <v>1</v>
+      </c>
+      <c r="K41" s="3"/>
+      <c r="L41" s="3">
+        <v>1</v>
+      </c>
+      <c r="M41" t="s">
+        <v>212</v>
+      </c>
+      <c r="N41" s="3">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" ht="409.6">
+      <c r="A42" t="s">
+        <v>184</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E42" t="s">
+        <v>17</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="J42" s="3">
+        <v>1</v>
+      </c>
+      <c r="K42" s="3"/>
+      <c r="L42" s="3">
+        <v>1</v>
+      </c>
+      <c r="M42" t="s">
+        <v>217</v>
+      </c>
+      <c r="N42" s="3">
+        <v>7.65</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" ht="195">
+      <c r="A43" t="s">
+        <v>184</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="E43" t="s">
+        <v>17</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="J43" s="3">
+        <v>1</v>
+      </c>
+      <c r="K43" s="3"/>
+      <c r="L43" s="3">
+        <v>1</v>
+      </c>
+      <c r="M43" t="s">
+        <v>222</v>
+      </c>
+      <c r="N43" s="3">
+        <v>7.03</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" ht="255">
+      <c r="A44" t="s">
+        <v>184</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="E44" t="s">
+        <v>17</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="J44" s="3">
+        <v>1</v>
+      </c>
+      <c r="K44" s="3"/>
+      <c r="L44" s="3">
+        <v>1</v>
+      </c>
+      <c r="M44" t="s">
+        <v>227</v>
+      </c>
+      <c r="N44" s="3">
+        <v>6.62</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" ht="285">
+      <c r="A45" t="s">
+        <v>184</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="E45" t="s">
+        <v>17</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="J45" s="3">
+        <v>1</v>
+      </c>
+      <c r="K45" s="3"/>
+      <c r="L45" s="3">
+        <v>1</v>
+      </c>
+      <c r="M45" t="s">
+        <v>232</v>
+      </c>
+      <c r="N45" s="3">
+        <v>7.23</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" ht="300">
+      <c r="A46" t="s">
+        <v>233</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="E46" t="s">
+        <v>17</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="J46" s="3">
+        <v>1</v>
+      </c>
+      <c r="K46" s="3"/>
+      <c r="L46" s="3">
+        <v>1</v>
+      </c>
+      <c r="M46" t="s">
+        <v>238</v>
+      </c>
+      <c r="N46" s="3">
+        <v>28.64</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" ht="255">
+      <c r="A47" t="s">
+        <v>233</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="E47" t="s">
+        <v>17</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="J47" s="3">
+        <v>1</v>
+      </c>
+      <c r="K47" s="3"/>
+      <c r="L47" s="3">
+        <v>1</v>
+      </c>
+      <c r="M47" t="s">
+        <v>243</v>
+      </c>
+      <c r="N47" s="3">
+        <v>52.36</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" ht="165">
+      <c r="A48" t="s">
+        <v>233</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="E48" t="s">
+        <v>17</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="J48" s="3">
+        <v>1</v>
+      </c>
+      <c r="K48" s="3"/>
+      <c r="L48" s="3">
+        <v>1</v>
+      </c>
+      <c r="M48" t="s">
+        <v>248</v>
+      </c>
+      <c r="N48" s="3">
+        <v>21.02</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" ht="165">
+      <c r="A49" t="s">
+        <v>233</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="E49" t="s">
+        <v>17</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="J49" s="3">
+        <v>1</v>
+      </c>
+      <c r="K49" s="3"/>
+      <c r="L49" s="3">
+        <v>1</v>
+      </c>
+      <c r="M49" t="s">
+        <v>253</v>
+      </c>
+      <c r="N49" s="3">
+        <v>6.91</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" ht="270">
+      <c r="A50" t="s">
+        <v>233</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="E50" t="s">
+        <v>17</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="J50" s="3">
+        <v>1</v>
+      </c>
+      <c r="K50" s="3"/>
+      <c r="L50" s="3">
+        <v>1</v>
+      </c>
+      <c r="M50" t="s">
+        <v>258</v>
+      </c>
+      <c r="N50" s="3">
+        <v>30.37</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" ht="120">
+      <c r="A51" t="s">
+        <v>233</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="E51" t="s">
+        <v>17</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="J51" s="3">
+        <v>1</v>
+      </c>
+      <c r="K51" s="3"/>
+      <c r="L51" s="3">
+        <v>1</v>
+      </c>
+      <c r="M51" t="s">
+        <v>263</v>
+      </c>
+      <c r="N51" s="3">
+        <v>21.68</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" ht="398">
+      <c r="A52" t="s">
+        <v>233</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="E52" t="s">
+        <v>17</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="J52" s="3">
+        <v>0.96430000000000005</v>
+      </c>
+      <c r="K52" s="3"/>
+      <c r="L52" s="3">
+        <v>0.96430000000000005</v>
+      </c>
+      <c r="M52" t="s">
+        <v>268</v>
+      </c>
+      <c r="N52" s="3">
+        <v>48.62</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" ht="255">
+      <c r="A53" t="s">
+        <v>233</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="E53" t="s">
+        <v>127</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="H53" s="2"/>
+      <c r="I53" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="J53" s="3">
+        <v>1</v>
+      </c>
+      <c r="K53" s="3"/>
+      <c r="L53" s="3">
+        <v>1</v>
+      </c>
+      <c r="M53" t="s">
+        <v>273</v>
+      </c>
+      <c r="N53" s="3">
+        <v>44.4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" ht="300">
+      <c r="A54" t="s">
+        <v>233</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="E54" t="s">
+        <v>17</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="G54" s="2"/>
+      <c r="H54" s="2"/>
+      <c r="I54" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="J54" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="K54" s="3"/>
+      <c r="L54" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="M54" t="s">
+        <v>278</v>
+      </c>
+      <c r="N54" s="3">
+        <v>47.82</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" ht="120">
+      <c r="A55" t="s">
+        <v>233</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="E55" t="s">
+        <v>17</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="G55" s="2"/>
+      <c r="H55" s="2"/>
+      <c r="I55" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="J55" s="3">
+        <v>1</v>
+      </c>
+      <c r="K55" s="3"/>
+      <c r="L55" s="3">
+        <v>1</v>
+      </c>
+      <c r="M55" t="s">
+        <v>283</v>
+      </c>
+      <c r="N55" s="3">
+        <v>33.19</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" ht="285">
+      <c r="A56" t="s">
+        <v>284</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="E56" t="s">
+        <v>17</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="G56" s="2"/>
+      <c r="H56" s="2"/>
+      <c r="I56" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="J56" s="3">
+        <v>1</v>
+      </c>
+      <c r="K56" s="3"/>
+      <c r="L56" s="3">
+        <v>1</v>
+      </c>
+      <c r="M56" t="s">
+        <v>289</v>
+      </c>
+      <c r="N56" s="3">
+        <v>31.69</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" ht="225">
+      <c r="A57" t="s">
+        <v>290</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="E57" t="s">
+        <v>17</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="G57" s="2"/>
+      <c r="H57" s="2"/>
+      <c r="I57" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="J57" s="3">
+        <v>0.94440000000000002</v>
+      </c>
+      <c r="K57" s="3"/>
+      <c r="L57" s="3">
+        <v>0.94440000000000002</v>
+      </c>
+      <c r="M57" t="s">
+        <v>295</v>
+      </c>
+      <c r="N57" s="3">
+        <v>51.6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" ht="120">
+      <c r="A58" t="s">
+        <v>290</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="E58" t="s">
+        <v>17</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="G58" s="2"/>
+      <c r="H58" s="2"/>
+      <c r="I58" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="J58" s="3">
+        <v>1</v>
+      </c>
+      <c r="K58" s="3"/>
+      <c r="L58" s="3">
+        <v>1</v>
+      </c>
+      <c r="M58" t="s">
+        <v>300</v>
+      </c>
+      <c r="N58" s="3">
+        <v>27.8</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" ht="225">
+      <c r="A59" t="s">
+        <v>290</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="E59" t="s">
+        <v>17</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="G59" s="2"/>
+      <c r="H59" s="2"/>
+      <c r="I59" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="J59" s="3">
+        <v>0.94440000000000002</v>
+      </c>
+      <c r="K59" s="3"/>
+      <c r="L59" s="3">
+        <v>0.94440000000000002</v>
+      </c>
+      <c r="M59" t="s">
+        <v>305</v>
+      </c>
+      <c r="N59" s="3">
+        <v>27.99</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" ht="285">
+      <c r="A60" t="s">
+        <v>290</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="E60" t="s">
+        <v>17</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="G60" s="2"/>
+      <c r="H60" s="2"/>
+      <c r="I60" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="J60" s="3">
+        <v>1</v>
+      </c>
+      <c r="K60" s="3"/>
+      <c r="L60" s="3">
+        <v>1</v>
+      </c>
+      <c r="M60" t="s">
+        <v>310</v>
+      </c>
+      <c r="N60" s="3">
+        <v>46.1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" ht="195">
+      <c r="A61" t="s">
+        <v>311</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="E61" t="s">
+        <v>17</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="G61" s="2"/>
+      <c r="H61" s="2"/>
+      <c r="I61" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="J61" s="3">
+        <v>1</v>
+      </c>
+      <c r="K61" s="3"/>
+      <c r="L61" s="3">
+        <v>1</v>
+      </c>
+      <c r="M61" t="s">
+        <v>316</v>
+      </c>
+      <c r="N61" s="3">
+        <v>18.79</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" ht="314">
+      <c r="A62" t="s">
+        <v>317</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="E62" t="s">
+        <v>127</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="H62" s="2"/>
+      <c r="I62" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="J62" s="3">
+        <v>0.87</v>
+      </c>
+      <c r="K62" s="3"/>
+      <c r="L62" s="3">
+        <v>0.87</v>
+      </c>
+      <c r="M62" t="s">
+        <v>323</v>
+      </c>
+      <c r="N62" s="3">
+        <v>61.38</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" ht="240">
+      <c r="A63" t="s">
+        <v>317</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="E63" t="s">
+        <v>17</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="G63" s="2"/>
+      <c r="H63" s="2"/>
+      <c r="I63" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="J63" s="3">
+        <v>0.94440000000000002</v>
+      </c>
+      <c r="K63" s="3"/>
+      <c r="L63" s="3">
+        <v>0.94440000000000002</v>
+      </c>
+      <c r="M63" t="s">
+        <v>328</v>
+      </c>
+      <c r="N63" s="3">
+        <v>35.79</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" ht="225">
+      <c r="A64" t="s">
+        <v>317</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="E64" t="s">
+        <v>17</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="G64" s="2"/>
+      <c r="H64" s="2"/>
+      <c r="I64" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="J64" s="3">
+        <v>1</v>
+      </c>
+      <c r="K64" s="3"/>
+      <c r="L64" s="3">
+        <v>1</v>
+      </c>
+      <c r="M64" t="s">
+        <v>333</v>
+      </c>
+      <c r="N64" s="3">
+        <v>21.08</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" ht="225">
+      <c r="A65" t="s">
+        <v>317</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="E65" t="s">
+        <v>17</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="G65" s="2"/>
+      <c r="H65" s="2"/>
+      <c r="I65" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="J65" s="3">
+        <v>1</v>
+      </c>
+      <c r="K65" s="3"/>
+      <c r="L65" s="3">
+        <v>1</v>
+      </c>
+      <c r="M65" t="s">
+        <v>338</v>
+      </c>
+      <c r="N65" s="3">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" ht="240">
+      <c r="A66" t="s">
+        <v>317</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="E66" t="s">
+        <v>17</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="G66" s="2"/>
+      <c r="H66" s="2"/>
+      <c r="I66" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="J66" s="3">
+        <v>1</v>
+      </c>
+      <c r="K66" s="3"/>
+      <c r="L66" s="3">
+        <v>1</v>
+      </c>
+      <c r="M66" t="s">
+        <v>343</v>
+      </c>
+      <c r="N66" s="3">
+        <v>5.69</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" ht="135">
+      <c r="A67" t="s">
+        <v>344</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="E67" t="s">
+        <v>17</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="G67" s="2"/>
+      <c r="H67" s="2"/>
+      <c r="I67" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="J67" s="3">
+        <v>1</v>
+      </c>
+      <c r="K67" s="3"/>
+      <c r="L67" s="3">
+        <v>1</v>
+      </c>
+      <c r="M67" t="s">
+        <v>349</v>
+      </c>
+      <c r="N67" s="3">
+        <v>7.35</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" ht="314">
+      <c r="A68" t="s">
+        <v>344</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="E68" t="s">
+        <v>17</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="G68" s="2"/>
+      <c r="H68" s="2"/>
+      <c r="I68" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="J68" s="3">
+        <v>1</v>
+      </c>
+      <c r="K68" s="3"/>
+      <c r="L68" s="3">
+        <v>1</v>
+      </c>
+      <c r="M68" t="s">
+        <v>354</v>
+      </c>
+      <c r="N68" s="3">
+        <v>29.86</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" ht="398">
+      <c r="A69" t="s">
+        <v>344</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="E69" t="s">
+        <v>17</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="G69" s="2"/>
+      <c r="H69" s="2"/>
+      <c r="I69" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="J69" s="3">
+        <v>0.94120000000000004</v>
+      </c>
+      <c r="K69" s="3"/>
+      <c r="L69" s="3">
+        <v>0.94120000000000004</v>
+      </c>
+      <c r="M69" t="s">
+        <v>359</v>
+      </c>
+      <c r="N69" s="3">
+        <v>52.2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" ht="342">
+      <c r="A70" t="s">
+        <v>344</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="E70" t="s">
+        <v>17</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="G70" s="2"/>
+      <c r="H70" s="2"/>
+      <c r="I70" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="J70" s="3">
+        <v>1</v>
+      </c>
+      <c r="K70" s="3"/>
+      <c r="L70" s="3">
+        <v>1</v>
+      </c>
+      <c r="M70" t="s">
+        <v>363</v>
+      </c>
+      <c r="N70" s="3">
+        <v>68.88</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" ht="180">
+      <c r="A71" t="s">
+        <v>344</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="E71" t="s">
+        <v>17</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="G71" s="2"/>
+      <c r="H71" s="2"/>
+      <c r="I71" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="J71" s="3">
+        <v>1</v>
+      </c>
+      <c r="K71" s="3"/>
+      <c r="L71" s="3">
+        <v>1</v>
+      </c>
+      <c r="M71" t="s">
+        <v>368</v>
+      </c>
+      <c r="N71" s="3">
+        <v>19.100000000000001</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" ht="165">
+      <c r="A72" t="s">
+        <v>369</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="E72" t="s">
+        <v>17</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="G72" s="2"/>
+      <c r="H72" s="2"/>
+      <c r="I72" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="J72" s="3">
+        <v>1</v>
+      </c>
+      <c r="K72" s="3"/>
+      <c r="L72" s="3">
+        <v>1</v>
+      </c>
+      <c r="M72" t="s">
+        <v>374</v>
+      </c>
+      <c r="N72" s="3">
+        <v>6.69</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" ht="240">
+      <c r="A73" t="s">
+        <v>369</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="E73" t="s">
+        <v>17</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="G73" s="2"/>
+      <c r="H73" s="2"/>
+      <c r="I73" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="J73" s="3">
+        <v>0.94440000000000002</v>
+      </c>
+      <c r="K73" s="3"/>
+      <c r="L73" s="3">
+        <v>0.94440000000000002</v>
+      </c>
+      <c r="M73" t="s">
+        <v>379</v>
+      </c>
+      <c r="N73" s="3">
+        <v>22.63</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" ht="342">
+      <c r="A74" t="s">
+        <v>369</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="E74" t="s">
+        <v>17</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="G74" s="2"/>
+      <c r="H74" s="2"/>
+      <c r="I74" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="J74" s="3">
+        <v>0.98819999999999997</v>
+      </c>
+      <c r="K74" s="3"/>
+      <c r="L74" s="3">
+        <v>0.98819999999999997</v>
+      </c>
+      <c r="M74" t="s">
+        <v>384</v>
+      </c>
+      <c r="N74" s="3">
+        <v>37.049999999999997</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" ht="240">
+      <c r="A75" t="s">
+        <v>369</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="E75" t="s">
+        <v>17</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="G75" s="2"/>
+      <c r="H75" s="2"/>
+      <c r="I75" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="J75" s="3">
+        <v>1</v>
+      </c>
+      <c r="K75" s="3"/>
+      <c r="L75" s="3">
+        <v>1</v>
+      </c>
+      <c r="M75" t="s">
+        <v>389</v>
+      </c>
+      <c r="N75" s="3">
+        <v>21.57</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" ht="240">
+      <c r="A76" t="s">
+        <v>369</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="E76" t="s">
+        <v>17</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="G76" s="2"/>
+      <c r="H76" s="2"/>
+      <c r="I76" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="J76" s="3">
+        <v>1</v>
+      </c>
+      <c r="K76" s="3"/>
+      <c r="L76" s="3">
+        <v>1</v>
+      </c>
+      <c r="M76" t="s">
+        <v>394</v>
+      </c>
+      <c r="N76" s="3">
+        <v>7.42</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" ht="240">
+      <c r="A77" t="s">
+        <v>369</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="E77" t="s">
+        <v>17</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="G77" s="2"/>
+      <c r="H77" s="2"/>
+      <c r="I77" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="J77" s="3">
+        <v>1</v>
+      </c>
+      <c r="K77" s="3"/>
+      <c r="L77" s="3">
+        <v>1</v>
+      </c>
+      <c r="M77" t="s">
+        <v>399</v>
+      </c>
+      <c r="N77" s="3">
+        <v>22.34</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" ht="342">
+      <c r="A78" t="s">
+        <v>369</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="E78" t="s">
+        <v>17</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="G78" s="2"/>
+      <c r="H78" s="2"/>
+      <c r="I78" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="J78" s="3">
+        <v>0.85709999999999997</v>
+      </c>
+      <c r="K78" s="3"/>
+      <c r="L78" s="3">
+        <v>0.85709999999999997</v>
+      </c>
+      <c r="M78" t="s">
+        <v>404</v>
+      </c>
+      <c r="N78" s="3">
+        <v>35.520000000000003</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" ht="314">
+      <c r="A79" t="s">
+        <v>405</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="E79" t="s">
+        <v>17</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="G79" s="2"/>
+      <c r="H79" s="2"/>
+      <c r="I79" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="J79" s="3">
+        <v>1</v>
+      </c>
+      <c r="K79" s="3"/>
+      <c r="L79" s="3">
+        <v>1</v>
+      </c>
+      <c r="M79" t="s">
+        <v>410</v>
+      </c>
+      <c r="N79" s="3">
+        <v>25.98</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" ht="314">
+      <c r="A80" t="s">
+        <v>405</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="E80" t="s">
+        <v>17</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="G80" s="2"/>
+      <c r="H80" s="2"/>
+      <c r="I80" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="J80" s="3">
+        <v>1</v>
+      </c>
+      <c r="K80" s="3"/>
+      <c r="L80" s="3">
+        <v>1</v>
+      </c>
+      <c r="M80" t="s">
+        <v>415</v>
+      </c>
+      <c r="N80" s="3">
+        <v>17.3</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" ht="409.6">
+      <c r="A81" t="s">
+        <v>405</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="E81" t="s">
+        <v>17</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="G81" s="2"/>
+      <c r="H81" s="2"/>
+      <c r="I81" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="J81" s="3">
+        <v>1</v>
+      </c>
+      <c r="K81" s="3"/>
+      <c r="L81" s="3">
+        <v>1</v>
+      </c>
+      <c r="M81" t="s">
+        <v>420</v>
+      </c>
+      <c r="N81" s="3">
+        <v>25.71</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" ht="342">
+      <c r="A82" t="s">
+        <v>405</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="E82" t="s">
+        <v>17</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="G82" s="2"/>
+      <c r="H82" s="2"/>
+      <c r="I82" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="J82" s="3">
+        <v>1</v>
+      </c>
+      <c r="K82" s="3"/>
+      <c r="L82" s="3">
+        <v>1</v>
+      </c>
+      <c r="M82" t="s">
+        <v>425</v>
+      </c>
+      <c r="N82" s="3">
+        <v>47.35</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" ht="240">
+      <c r="A83" t="s">
+        <v>405</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="E83" t="s">
+        <v>17</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="G83" s="2"/>
+      <c r="H83" s="2"/>
+      <c r="I83" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="J83" s="3">
+        <v>1</v>
+      </c>
+      <c r="K83" s="3"/>
+      <c r="L83" s="3">
+        <v>1</v>
+      </c>
+      <c r="M83" t="s">
+        <v>430</v>
+      </c>
+      <c r="N83" s="3">
+        <v>63.51</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" ht="285">
+      <c r="A84" t="s">
+        <v>405</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="E84" t="s">
+        <v>17</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="G84" s="2"/>
+      <c r="H84" s="2"/>
+      <c r="I84" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="J84" s="3">
+        <v>1</v>
+      </c>
+      <c r="K84" s="3"/>
+      <c r="L84" s="3">
+        <v>1</v>
+      </c>
+      <c r="M84" t="s">
+        <v>435</v>
+      </c>
+      <c r="N84" s="3">
+        <v>46.9</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/src/rag_results.xlsx
+++ b/src/rag_results.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N167"/>
+  <dimension ref="A1:N250"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11155,6 +11155,5287 @@
         <v>68.72</v>
       </c>
     </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>保障範圍包括哪些項目？</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括住院醫療保險金、加護病房或燒燙傷病房保險金、祝壽保險金、身故保險金或喪葬費用保險金，以及所繳保險費的退還。
+條文依據：  
+- 摘要</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>payout_items | summary | 第五條 保險範圍 | 第二條 名詞定義 | 第十八條 除外責任（一）</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括住院醫療保險金、加護病房或燒燙傷病房保險金、祝壽保險金、身故保險金或喪葬費用保險金，以及所繳保險費的退還。
+條文依據：  
+- 摘要</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr"/>
+      <c r="H168" s="2" t="inlineStr"/>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.983647, "neutral": 0.012178, "contradiction": 0.004175, "factuality": 0.995825, "C_fact": 0.995825}, "C_conf": 0.9958}</t>
+        </is>
+      </c>
+      <c r="J168" s="5" t="n"/>
+      <c r="K168" s="5" t="n">
+        <v>0.995825</v>
+      </c>
+      <c r="L168" s="5" t="n">
+        <v>0.9958</v>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:17:45</t>
+        </is>
+      </c>
+      <c r="N168" s="5" t="n">
+        <v>16.33</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>住院日數計算有什麼特殊規則？</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院日數計算的特殊規則包括：  
+1. 住院日數以被保險人同一次住院的實際全日住進急性病房或慢性病房（含加護病房及燒燙傷病房）的住院日數計算，包含住院及出院當日。  
+2. 若被保險人出院後又於同一日入院診療，該日不得重複計入住院日數。  
+條文依據：  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第十二條 住院醫療保險金的給付 | 第二條 名詞定義 | 第十三條 加護病房或燒燙傷病房保險金的給付 | 第二十八條 住院醫療保險金日額之減少</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院日數計算的特殊規則包括：  
+1. 住院日數以被保險人同一次住院的實際全日住進急性病房或慢性病房（含加護病房及燒燙傷病房）的住院日數計算，包含住院及出院當日。  
+2. 若被保險人出院後又於同一日入院診療，該日不得重複計入住院日數。  
+條文依據：  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr"/>
+      <c r="H169" s="2" t="inlineStr"/>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.996412, "neutral": 0.003364, "contradiction": 0.000225, "factuality": 0.999775, "C_fact": 0.999775}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J169" s="5" t="n"/>
+      <c r="K169" s="5" t="n">
+        <v>0.999775</v>
+      </c>
+      <c r="L169" s="5" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:17:58</t>
+        </is>
+      </c>
+      <c r="N169" s="5" t="n">
+        <v>12.59</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>住院醫療保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院醫療保險金的給付規定如下：  
+被保險人於契約有效期間內因疾病或傷害住院治療時，保險公司將依保險單所記載的「住院醫療保險金日額」，乘以入院日當年度的「增額係數」，再乘以住院日數，給付「住院醫療保險金」。同一保單年度內，同一次住院的住院日數給付上限為365日。
+條文依據：  
+- [第十二條 住院醫療保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 住院醫療保險金的給付 | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第十三條 加護病房或燒燙傷病房保險金的給付 | 第十四條 醫療保險金給付總額之上限 | 第二十八條 住院醫療保險金日額之減少</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院醫療保險金的給付規定如下：  
+被保險人於契約有效期間內因疾病或傷害住院治療時，保險公司將依保險單所記載的「住院醫療保險金日額」，乘以入院日當年度的「增額係數」，再乘以住院日數，給付「住院醫療保險金」。同一保單年度內，同一次住院的住院日數給付上限為365日。
+條文依據：  
+- [第十二條 住院醫療保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr"/>
+      <c r="H170" s="2" t="inlineStr"/>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.993554, "neutral": 0.003772, "contradiction": 0.002674, "factuality": 0.997326, "C_fact": 0.997326}, "C_conf": 0.9973}</t>
+        </is>
+      </c>
+      <c r="J170" s="5" t="n"/>
+      <c r="K170" s="5" t="n">
+        <v>0.997326</v>
+      </c>
+      <c r="L170" s="5" t="n">
+        <v>0.9973</v>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:18:04</t>
+        </is>
+      </c>
+      <c r="N170" s="5" t="n">
+        <v>5.34</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>加護病房或燒燙傷病房保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+加護病房或燒燙傷病房保險金的給付規定如下：  
+被保險人於契約有效期間內因疾病或傷害住院，並於醫院的加護病房或燒燙傷病房接受治療者，除住院醫療保險金外，保險公司將依保險單所記載的「住院醫療保險金日額」，乘以入院日當年度的「增額係數」，再乘以實際住進加護病房或燒燙傷病房的日數（含轉入及轉出當日）的二倍，給付「加護病房或燒燙傷病房保險金」。  
+同一保單年度內，同一次住院的加護病房及燒燙傷病房住院日數合計給付上限為365日，但同一日僅能就其中一種病房給付。
+條文依據：  
+- [第十三條 加護病房或燒燙傷病房保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 加護病房或燒燙傷病房保險金的給付 | payout_items | 第二十三條 醫療保險金的申領 | 第五條 保險範圍 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+加護病房或燒燙傷病房保險金的給付規定如下：  
+被保險人於契約有效期間內因疾病或傷害住院，並於醫院的加護病房或燒燙傷病房接受治療者，除住院醫療保險金外，保險公司將依保險單所記載的「住院醫療保險金日額」，乘以入院日當年度的「增額係數」，再乘以實際住進加護病房或燒燙傷病房的日數（含轉入及轉出當日）的二倍，給付「加護病房或燒燙傷病房保險金」。  
+同一保單年度內，同一次住院的加護病房及燒燙傷病房住院日數合計給付上限為365日，但同一日僅能就其中一種病房給付。
+條文依據：  
+- [第十三條 加護病房或燒燙傷病房保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr"/>
+      <c r="H171" s="2" t="inlineStr"/>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.996367, "neutral": 0.003026, "contradiction": 0.000607, "factuality": 0.999393, "C_fact": 0.999393}, "C_conf": 0.9994}</t>
+        </is>
+      </c>
+      <c r="J171" s="5" t="n"/>
+      <c r="K171" s="5" t="n">
+        <v>0.999393</v>
+      </c>
+      <c r="L171" s="5" t="n">
+        <v>0.9994</v>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:18:08</t>
+        </is>
+      </c>
+      <c r="N171" s="5" t="n">
+        <v>4.72</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>醫療保險金給付總額之上限</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+醫療保險金給付總額之上限為保險單上所記載之「住院醫療保險金日額」的二千五百倍，且此上限適用於本契約有效期間內依第十二條至第十三條所給付之各項保險金的累計總額。
+條文依據：  
+- [第十四條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 醫療保險金給付總額之上限 | 第十二條 住院醫療保險金的給付 | 第五條 保險範圍 | 第十三條 加護病房或燒燙傷病房保險金的給付 | payout_items</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+醫療保險金給付總額之上限為保險單上所記載之「住院醫療保險金日額」的二千五百倍，且此上限適用於本契約有效期間內依第十二條至第十三條所給付之各項保險金的累計總額。
+條文依據：  
+- [第十四條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr"/>
+      <c r="H172" s="2" t="inlineStr"/>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.995968, "neutral": 0.003732, "contradiction": 0.0003, "factuality": 0.9997, "C_fact": 0.9997}, "C_conf": 0.9997}</t>
+        </is>
+      </c>
+      <c r="J172" s="5" t="n"/>
+      <c r="K172" s="5" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="L172" s="5" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:18:11</t>
+        </is>
+      </c>
+      <c r="N172" s="5" t="n">
+        <v>2.58</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>祝壽保險金的給付規定為何?</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+祝壽保險金的給付規定為：被保險人於本契約有效期間且保險年齡到達九十九歲之保險單週年日仍生存時，本公司按「當年度保險金額」給付「祝壽保險金」。
+條文依據：  
+- [第十五條 祝壽保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>第十五條 祝壽保險金的給付 | 第十二條至第十三條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | 第二十四條 祝壽保險金的申領 | payout_items | 第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+祝壽保險金的給付規定為：被保險人於本契約有效期間且保險年齡到達九十九歲之保險單週年日仍生存時，本公司按「當年度保險金額」給付「祝壽保險金」。
+條文依據：  
+- [第十五條 祝壽保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr"/>
+      <c r="H173" s="2" t="inlineStr"/>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.997653, "neutral": 0.002173, "contradiction": 0.000174, "factuality": 0.999826, "C_fact": 0.999826}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J173" s="5" t="n"/>
+      <c r="K173" s="5" t="n">
+        <v>0.999826</v>
+      </c>
+      <c r="L173" s="5" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:18:14</t>
+        </is>
+      </c>
+      <c r="N173" s="5" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>有效期間內身故，保險金如何給付?</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於本契約有效期間內身故者，本公司按「當年度保險金額」給付「身故保險金」。若被保險人於繳費期間內身故，當期已繳付之未到期保險費將不予退還，亦不併入身故保險金內給付。若被保險人於有效期間且實際年齡未滿十五足歲身故者，本公司按「所繳保險費」退還要保人，不適用前述規定。此外，若被保險人為受監護宣告尚未撤銷者，其身故保險金變更為喪葬費用保險金，並受遺產稅喪葬費扣除額之半數限制，超過部分不負給付責任。  
+條文依據：  
+- [第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付 | 第十條 契約的終止（二） | 第五條 保險範圍 | 第二十二條 失蹤處理 | 第十五條 祝壽保險金的給付</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於本契約有效期間內身故者，本公司按「當年度保險金額」給付「身故保險金」。若被保險人於繳費期間內身故，當期已繳付之未到期保險費將不予退還，亦不併入身故保險金內給付。若被保險人於有效期間且實際年齡未滿十五足歲身故者，本公司按「所繳保險費」退還要保人，不適用前述規定。此外，若被保險人為受監護宣告尚未撤銷者，其身故保險金變更為喪葬費用保險金，並受遺產稅喪葬費扣除額之半數限制，超過部分不負給付責任。  
+條文依據：  
+- [第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr"/>
+      <c r="H174" s="2" t="inlineStr"/>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.458867, "neutral": 0.540053, "contradiction": 0.00108, "factuality": 0.99892, "C_fact": 0.99892}, "C_conf": 0.9989}</t>
+        </is>
+      </c>
+      <c r="J174" s="5" t="n"/>
+      <c r="K174" s="5" t="n">
+        <v>0.99892</v>
+      </c>
+      <c r="L174" s="5" t="n">
+        <v>0.9989</v>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:18:19</t>
+        </is>
+      </c>
+      <c r="N174" s="5" t="n">
+        <v>4.59</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>健康促進保險費折減規定</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+健康促進保險費折減規定如下：  
+被保險人年齡達20歲（含）以上，使用保險公司指定程式並加入健康計劃，於「指定日期」的會員等級符合標準者，可享次一保險單年度保險費折減。折減比例依會員等級分為：進階會員折減2%，菁英會員或更高等級折減3%。豁免或復效的保險費不適用折減規定。被保險人需完成程式註冊並授權保險公司取得健康相關電子紀錄，保險公司將依紀錄計算會員等級。  
+條文依據：  
+- [第十七條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>第十七條 健康促進保險費折減 | 第二十八條 住院醫療保險金日額之減少 | 第三十條 投保年齡的計算及錯誤的處理 | 第二條 名詞定義 | 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+健康促進保險費折減規定如下：  
+被保險人年齡達20歲（含）以上，使用保險公司指定程式並加入健康計劃，於「指定日期」的會員等級符合標準者，可享次一保險單年度保險費折減。折減比例依會員等級分為：進階會員折減2%，菁英會員或更高等級折減3%。豁免或復效的保險費不適用折減規定。被保險人需完成程式註冊並授權保險公司取得健康相關電子紀錄，保險公司將依紀錄計算會員等級。  
+條文依據：  
+- [第十七條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr"/>
+      <c r="H175" s="2" t="inlineStr"/>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.99729, "neutral": 0.002091, "contradiction": 0.000619, "factuality": 0.999381, "C_fact": 0.999381}, "C_conf": 0.9994}</t>
+        </is>
+      </c>
+      <c r="J175" s="5" t="n"/>
+      <c r="K175" s="5" t="n">
+        <v>0.999381</v>
+      </c>
+      <c r="L175" s="5" t="n">
+        <v>0.9994</v>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:18:24</t>
+        </is>
+      </c>
+      <c r="N175" s="5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>除外責任的解釋?</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+除外責任是指保險公司不負給付保險金責任的情形，包含以下幾類：  
+1. 因被保險人故意行為（如自殺、自殺未遂）、犯罪行為或非法施用毒品所致的疾病或傷害。  
+2. 因美容手術或外科整型住院，但若為重建基本功能所需的整型則不在此限。  
+3. 因外觀可見的天生畸形住院。  
+4. 因健康檢查、療養、靜養、戒毒、戒酒、護理或養老等非直接診治病人目的住院。  
+5. 因懷孕、流產或分娩及其併發症住院，但以下情形不在此限：  
+   - 懷孕相關疾病（如子宮外孕、葡萄胎等）。  
+   - 因醫療行為必要的流產（如因遺傳性疾病或精神疾病等）。  
+   - 醫療行為必要的剖腹產（如胎位不正、多胞胎等）。  
+條文依據：  
+- [第十八條 除外責任（一)]</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第十九條 除外責任（二） | 第八條 告知義務與本契約的解除 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+除外責任是指保險公司不負給付保險金責任的情形，包含以下幾類：  
+1. 因被保險人故意行為（如自殺、自殺未遂）、犯罪行為或非法施用毒品所致的疾病或傷害。  
+2. 因美容手術或外科整型住院，但若為重建基本功能所需的整型則不在此限。  
+3. 因外觀可見的天生畸形住院。  
+4. 因健康檢查、療養、靜養、戒毒、戒酒、護理或養老等非直接診治病人目的住院。  
+5. 因懷孕、流產或分娩及其併發症住院，但以下情形不在此限：  
+   - 懷孕相關疾病（如子宮外孕、葡萄胎等）。  
+   - 因醫療行為必要的流產（如因遺傳性疾病或精神疾病等）。  
+   - 醫療行為必要的剖腹產（如胎位不正、多胞胎等）。  
+條文依據：  
+- [第十八條 除外責任（一)]</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr"/>
+      <c r="H176" s="2" t="inlineStr"/>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.997021, "neutral": 0.002662, "contradiction": 0.000317, "factuality": 0.999683, "C_fact": 0.999683}, "C_conf": 0.9997}</t>
+        </is>
+      </c>
+      <c r="J176" s="5" t="n"/>
+      <c r="K176" s="5" t="n">
+        <v>0.999683</v>
+      </c>
+      <c r="L176" s="5" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:18:29</t>
+        </is>
+      </c>
+      <c r="N176" s="5" t="n">
+        <v>5.73</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>哪些疾病被含在除外責任?</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+以下疾病被列為除外責任，保險公司不負給付第十二條至第十三條保險金的責任：  
+1. 美容手術、外科整型（但為重建基本功能所作之必要整型不在此限）。  
+2. 外觀可見之天生畸形。  
+3. 健康檢查、療養、靜養、戒毒、戒酒、護理或養老之非以直接診治病人為目的者。  
+4. 懷孕、流產或分娩及其併發症（但特定懷孕相關疾病、醫療行為必要之流產及剖腹產不在此限）。  
+5. 不孕症、人工受孕或非以治療為目的之避孕及絕育手術。
+條文依據：  
+- [第十八條 除外責任（一)]</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第二條 名詞定義 | 第十九條 除外責任（二）</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+以下疾病被列為除外責任，保險公司不負給付第十二條至第十三條保險金的責任：  
+1. 美容手術、外科整型（但為重建基本功能所作之必要整型不在此限）。  
+2. 外觀可見之天生畸形。  
+3. 健康檢查、療養、靜養、戒毒、戒酒、護理或養老之非以直接診治病人為目的者。  
+4. 懷孕、流產或分娩及其併發症（但特定懷孕相關疾病、醫療行為必要之流產及剖腹產不在此限）。  
+5. 不孕症、人工受孕或非以治療為目的之避孕及絕育手術。
+條文依據：  
+- [第十八條 除外責任（一)]</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr"/>
+      <c r="H177" s="2" t="inlineStr"/>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.9986, "neutral": 0.001184, "contradiction": 0.000215, "factuality": 0.999785, "C_fact": 0.999785}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J177" s="5" t="n"/>
+      <c r="K177" s="5" t="n">
+        <v>0.999785</v>
+      </c>
+      <c r="L177" s="5" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:18:35</t>
+        </is>
+      </c>
+      <c r="N177" s="5" t="n">
+        <v>3.36</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>進行美容手術住院可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，因美容手術住院診療者，本公司不負給付保險金的責任。但若美容手術是為重建基本功能所作之必要整型，則不在此限，可以申請理賠。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第十三條 加護病房或燒燙傷病房保險金的給付 | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第二條 名詞定義 | payout_items</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，因美容手術住院診療者，本公司不負給付保險金的責任。但若美容手術是為重建基本功能所作之必要整型，則不在此限，可以申請理賠。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr"/>
+      <c r="H178" s="2" t="inlineStr"/>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.474019, "neutral": 0.524983, "contradiction": 0.000999, "factuality": 0.999001, "C_fact": 0.999001}, "C_conf": 0.999}</t>
+        </is>
+      </c>
+      <c r="J178" s="5" t="n"/>
+      <c r="K178" s="5" t="n">
+        <v>0.999001</v>
+      </c>
+      <c r="L178" s="5" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:18:39</t>
+        </is>
+      </c>
+      <c r="N178" s="5" t="n">
+        <v>4.52</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>因胎兒染色體異常進行手術而住院可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以申請理賠。根據條款，懷孕相關疾病中的「胎兒染色體異常之手術」屬於例外情形，不在除外責任範圍內，因此符合理賠條件。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第二條 名詞定義 | payout_items | 第十三條 加護病房或燒燙傷病房保險金的給付</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以申請理賠。根據條款，懷孕相關疾病中的「胎兒染色體異常之手術」屬於例外情形，不在除外責任範圍內，因此符合理賠條件。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr"/>
+      <c r="H179" s="2" t="inlineStr"/>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.977264, "neutral": 0.022465, "contradiction": 0.00027, "factuality": 0.99973, "C_fact": 0.99973}, "C_conf": 0.9997}</t>
+        </is>
+      </c>
+      <c r="J179" s="5" t="n"/>
+      <c r="K179" s="5" t="n">
+        <v>0.99973</v>
+      </c>
+      <c r="L179" s="5" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:18:42</t>
+        </is>
+      </c>
+      <c r="N179" s="5" t="n">
+        <v>2.96</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>因胎位不正進行手術而住院可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，因胎位不正進行手術而住院屬於「懷孕、流產或分娩及其併發症」的除外責任範圍，保險公司不負給付保險金的責任。但若手術屬於「醫療行為必要之剖腹產」且符合胎位不正的情形，則不在除外責任範圍內，可以申請理賠。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第二條 名詞定義 | payout_items | 第十三條 加護病房或燒燙傷病房保險金的給付</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，因胎位不正進行手術而住院屬於「懷孕、流產或分娩及其併發症」的除外責任範圍，保險公司不負給付保險金的責任。但若手術屬於「醫療行為必要之剖腹產」且符合胎位不正的情形，則不在除外責任範圍內，可以申請理賠。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr"/>
+      <c r="H180" s="2" t="inlineStr"/>
+      <c r="I180" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.619191, "neutral": 0.375582, "contradiction": 0.005227, "factuality": 0.994773, "C_fact": 0.994773}, "C_conf": 0.9948}</t>
+        </is>
+      </c>
+      <c r="J180" s="5" t="n"/>
+      <c r="K180" s="5" t="n">
+        <v>0.994773</v>
+      </c>
+      <c r="L180" s="5" t="n">
+        <v>0.9948</v>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:18:45</t>
+        </is>
+      </c>
+      <c r="N180" s="5" t="n">
+        <v>3.03</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>因自殺未遂導致住院可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，因被保險人故意行為（包括自殺及自殺未遂）導致住院診療者，本公司不負給付住院醫療保險金的責任。  
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 除外責任（二） | 第十八條 除外責任（一） | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | payout_items | 第十條 契約的終止（二）</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，因被保險人故意行為（包括自殺及自殺未遂）導致住院診療者，本公司不負給付住院醫療保險金的責任。  
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr"/>
+      <c r="H181" s="2" t="inlineStr"/>
+      <c r="I181" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.983569, "neutral": 0.016184, "contradiction": 0.000247, "factuality": 0.999753, "C_fact": 0.999753}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J181" s="5" t="n"/>
+      <c r="K181" s="5" t="n">
+        <v>0.999753</v>
+      </c>
+      <c r="L181" s="5" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:18:48</t>
+        </is>
+      </c>
+      <c r="N181" s="5" t="n">
+        <v>2.81</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>被保險人在投保一年內故意自殺者，可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人在投保一年內故意自殺者，依條款規定，本公司不負給付身故保險金或喪葬費用保險金的責任。但若自契約訂立或復效之日起滿二年後故意自殺致死者，本公司仍負給付責任。
+條文依據：  
+- [第十九條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 除外責任（二） | 第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付 | 第十條 契約的終止（二） | 第三十條 投保年齡的計算及錯誤的處理 | 第十八條 除外責任（一）</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人在投保一年內故意自殺者，依條款規定，本公司不負給付身故保險金或喪葬費用保險金的責任。但若自契約訂立或復效之日起滿二年後故意自殺致死者，本公司仍負給付責任。
+條文依據：  
+- [第十九條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr"/>
+      <c r="H182" s="2" t="inlineStr"/>
+      <c r="I182" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.997445, "neutral": 0.002388, "contradiction": 0.000167, "factuality": 0.999833, "C_fact": 0.999833}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J182" s="5" t="n"/>
+      <c r="K182" s="5" t="n">
+        <v>0.999833</v>
+      </c>
+      <c r="L182" s="5" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:18:52</t>
+        </is>
+      </c>
+      <c r="N182" s="5" t="n">
+        <v>3.96</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>申請理賠有什麼時間規定嗎?</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申請理賠的時間規定如下：要保人、被保險人或受益人應於知悉本公司應負保險責任之事故後十日內通知本公司，並於通知後儘速檢具所需文件向本公司申請給付保險金。本公司應於收齊所需文件後十五日內完成保險金給付。若因可歸責於本公司之事由未能在約定期限內給付，則應按年利一分加計利息給付。  
+條文依據：  
+- [第二十一條 保險事故的通知與保險金的申請時間]</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>第二十一條 保險事故的通知與保險金的申請時間 | 第六條 第二期以後保險費的交付、寬限期間及契約效力的停止 | 第七條 本契約效力的恢復 | 第三條 契約撤銷權 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申請理賠的時間規定如下：要保人、被保險人或受益人應於知悉本公司應負保險責任之事故後十日內通知本公司，並於通知後儘速檢具所需文件向本公司申請給付保險金。本公司應於收齊所需文件後十五日內完成保險金給付。若因可歸責於本公司之事由未能在約定期限內給付，則應按年利一分加計利息給付。  
+條文依據：  
+- [第二十一條 保險事故的通知與保險金的申請時間]</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr"/>
+      <c r="H183" s="2" t="inlineStr"/>
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.997385, "neutral": 0.002516, "contradiction": 9.9e-05, "factuality": 0.999901, "C_fact": 0.999901}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J183" s="5" t="n"/>
+      <c r="K183" s="5" t="n">
+        <v>0.999901</v>
+      </c>
+      <c r="L183" s="5" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:18:57</t>
+        </is>
+      </c>
+      <c r="N183" s="5" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>燒燙傷病房保險金怎麼申領?</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申領燒燙傷病房保險金時，受益人需檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 醫療診斷書或住院證明，並列明進、出燒燙傷病房的日期。（但要保人或被保險人為醫師時，不得為被保險人出具診斷書或住院證明。）  
+4. 受益人的身分證明。  
+此外，本公司基於審核保險金之需要，得徵詢其他醫師的醫學專業意見，並經受益人同意調閱被保險人之就醫相關資料，相關費用由本公司負擔。
+條文依據：  
+- [第二十三條 醫療保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>第二十三條 醫療保險金的申領 | 第十三條 加護病房或燒燙傷病房保險金的給付 | payout_items | 第二條 名詞定義 | 第二十一條 保險事故的通知與保險金的申請時間</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申領燒燙傷病房保險金時，受益人需檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 醫療診斷書或住院證明，並列明進、出燒燙傷病房的日期。（但要保人或被保險人為醫師時，不得為被保險人出具診斷書或住院證明。）  
+4. 受益人的身分證明。  
+此外，本公司基於審核保險金之需要，得徵詢其他醫師的醫學專業意見，並經受益人同意調閱被保險人之就醫相關資料，相關費用由本公司負擔。
+條文依據：  
+- [第二十三條 醫療保險金的申領]</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr"/>
+      <c r="H184" s="2" t="inlineStr"/>
+      <c r="I184" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.99806, "neutral": 0.001825, "contradiction": 0.000115, "factuality": 0.999885, "C_fact": 0.999885}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J184" s="5" t="n"/>
+      <c r="K184" s="5" t="n">
+        <v>0.999885</v>
+      </c>
+      <c r="L184" s="5" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:19:04</t>
+        </is>
+      </c>
+      <c r="N184" s="5" t="n">
+        <v>6.81</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>活到99歲怎麼申請祝壽金?</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申請祝壽保險金時，受益人需檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 受益人的身分證明。  
+條文依據：  
+- [第二十四條 祝壽保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>第十五條 祝壽保險金的給付 | 第二十四條 祝壽保險金的申領 | 第五條 保險範圍 | 第十二條至第十三條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | announcement_history</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申請祝壽保險金時，受益人需檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 受益人的身分證明。  
+條文依據：  
+- [第二十四條 祝壽保險金的申領]</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr"/>
+      <c r="H185" s="2" t="inlineStr"/>
+      <c r="I185" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.99803, "neutral": 0.001868, "contradiction": 0.000103, "factuality": 0.999897, "C_fact": 0.999897}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J185" s="5" t="n"/>
+      <c r="K185" s="5" t="n">
+        <v>0.999897</v>
+      </c>
+      <c r="L185" s="5" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:19:08</t>
+        </is>
+      </c>
+      <c r="N185" s="5" t="n">
+        <v>3.68</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>被保人身故怎麼申請理賠</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+受益人申請「身故保險金」或「喪葬費用保險金」時，需檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 被保險人死亡證明書及除戶戶籍謄本。  
+4. 受益人的身分證明。  
+條文依據：  
+- [第二十五條 身故保險金或喪葬費用保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付 | 第十二條至第十三條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | 第二十二條 失蹤處理 | 第二十五條 身故保險金或喪葬費用保險金的申領 | 第十九條 除外責任（二）</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+受益人申請「身故保險金」或「喪葬費用保險金」時，需檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 被保險人死亡證明書及除戶戶籍謄本。  
+4. 受益人的身分證明。  
+條文依據：  
+- [第二十五條 身故保險金或喪葬費用保險金的申領]</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr"/>
+      <c r="H186" s="2" t="inlineStr"/>
+      <c r="I186" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.996283, "neutral": 0.003565, "contradiction": 0.000152, "factuality": 0.999848, "C_fact": 0.999848}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J186" s="5" t="n"/>
+      <c r="K186" s="5" t="n">
+        <v>0.999848</v>
+      </c>
+      <c r="L186" s="5" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:19:11</t>
+        </is>
+      </c>
+      <c r="N186" s="5" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>投保15年後，因手術住院3天，住院日額為2500元，請問可以申請多少理賠?</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+依據條款，被保險人因手術住院3天，住院醫療保險金的計算公式為「住院醫療保險金日額」乘以「增額係數」再乘以住院日數。假設「增額係數」為1（條文未提供具體數值），則理賠金額為：2500元 × 1 × 3天 = 7500元。
+條文依據：  
+- [第十二條 住院醫療保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 住院醫療保險金的給付 | 第二條 名詞定義 | 第二十八條 住院醫療保險金日額之減少 | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第十三條 加護病房或燒燙傷病房保險金的給付 | 第五條 保險範圍 | payout_items | 第二十一條 保險事故的通知與保險金的申請時間</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+依據條款，被保險人因手術住院3天，住院醫療保險金的計算公式為「住院醫療保險金日額」乘以「增額係數」再乘以住院日數。假設「增額係數」為1（條文未提供具體數值），則理賠金額為：2500元 × 1 × 3天 = 7500元。
+條文依據：  
+- [第十二條 住院醫療保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr"/>
+      <c r="H187" s="2" t="inlineStr"/>
+      <c r="I187" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.176316, "neutral": 0.797901, "contradiction": 0.025783, "factuality": 0.974217, "C_fact": 0.974217}, "C_conf": 0.9742}</t>
+        </is>
+      </c>
+      <c r="J187" s="5" t="n"/>
+      <c r="K187" s="5" t="n">
+        <v>0.974217</v>
+      </c>
+      <c r="L187" s="5" t="n">
+        <v>0.9742</v>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:19:54</t>
+        </is>
+      </c>
+      <c r="N187" s="5" t="n">
+        <v>42.03</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>保障範圍包括哪些項目？</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括：住院手術醫療保險金、門診手術醫療保險金、特定處置保險金、意外創傷縫合處置保險金、意外住院手術醫療保險金、祝壽保險金、所繳保險費的退還、身故保險金或喪葬費用保險金。
+條文依據：  
+- [第五條 保險範圍]  
+- [給付項目]</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>payout_items | 第五條 保險範圍 | summary | 第四條 名詞定義 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括：住院手術醫療保險金、門診手術醫療保險金、特定處置保險金、意外創傷縫合處置保險金、意外住院手術醫療保險金、祝壽保險金、所繳保險費的退還、身故保險金或喪葬費用保險金。
+條文依據：  
+- [第五條 保險範圍]  
+- [給付項目]</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr"/>
+      <c r="H188" s="2" t="inlineStr"/>
+      <c r="I188" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.998103, "neutral": 0.001736, "contradiction": 0.000161, "factuality": 0.999839, "C_fact": 0.999839}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J188" s="5" t="n"/>
+      <c r="K188" s="5" t="n">
+        <v>0.999839</v>
+      </c>
+      <c r="L188" s="5" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:20:23</t>
+        </is>
+      </c>
+      <c r="N188" s="5" t="n">
+        <v>29.12</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>保險金額是否有上限?</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+有，保險金額的累計給付總額上限為保險單上所記載「保險金額」的一千五百倍，且不包含其他附約、附加條款或批註條款。
+條文依據：  
+- [第十六條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 醫療保險金給付總額之上限 | 第三十條 保險金額之減少 | 第五條 保險範圍 | 第十九條 健康促進保險費折減 | 第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+有，保險金額的累計給付總額上限為保險單上所記載「保險金額」的一千五百倍，且不包含其他附約、附加條款或批註條款。
+條文依據：  
+- [第十六條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="G189" s="2" t="inlineStr"/>
+      <c r="H189" s="2" t="inlineStr"/>
+      <c r="I189" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.997554, "neutral": 0.002322, "contradiction": 0.000124, "factuality": 0.999876, "C_fact": 0.999876}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J189" s="5" t="n"/>
+      <c r="K189" s="5" t="n">
+        <v>0.999876</v>
+      </c>
+      <c r="L189" s="5" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:20:30</t>
+        </is>
+      </c>
+      <c r="N189" s="5" t="n">
+        <v>6.88</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>投保後5天發生手術，是否可以申請理賠?</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+投保後5天發生手術是否可以申請理賠，需視保險契約中是否有等待期間的規定。然而，提供的條款中未提及等待期間的相關內容，因此無法判斷是否符合理賠條件。
+條文依據：  
+[第五條 保險範圍]  
+[第十一條 住院手術醫療保險金]  
+[第二十條 除外責任（一)]</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第十一條 住院手術醫療保險金 | 第二十條 除外責任（一） | 第十二條 門診手術醫療保險金 | 第十三條 意外住院手術醫療保險金 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+投保後5天發生手術是否可以申請理賠，需視保險契約中是否有等待期間的規定。然而，提供的條款中未提及等待期間的相關內容，因此無法判斷是否符合理賠條件。
+條文依據：  
+找不到相關內容</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+投保後5天發生手術是否可以申請理賠，需視保險契約中是否有等待期間的規定。然而，提供的條款中未提及等待期間的相關內容，因此無法判斷是否符合理賠條件。
+條文依據：  
+[第五條 保險範圍]  
+[第十一條 住院手術醫療保險金]  
+[第二十條 除外責任（一)]</t>
+        </is>
+      </c>
+      <c r="H190" s="2" t="inlineStr"/>
+      <c r="I190" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.062334, "neutral": 0.926352, "contradiction": 0.011314, "factuality": 0.988686, "C_fact": 0.988686}, "C_conf": 0.9887}</t>
+        </is>
+      </c>
+      <c r="J190" s="5" t="n"/>
+      <c r="K190" s="5" t="n">
+        <v>0.988686</v>
+      </c>
+      <c r="L190" s="5" t="n">
+        <v>0.9887</v>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:20:37</t>
+        </is>
+      </c>
+      <c r="N190" s="5" t="n">
+        <v>6.42</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>住院手術醫療保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院手術醫療保險金的給付規定如下：  
+1. 被保險人於契約有效期間內因疾病或傷害，經醫師診斷必須住院接受附表一所列的手術治療且已實際接受手術者，本公司依保險單記載的「保險金額」乘以手術日當年度的「增額係數」，再乘以手術給付倍數，給付住院手術醫療保險金。  
+2. 若同一次手術中於同一手術位置接受二項以上手術項目，僅給付手術給付倍數最高的手術項目。  
+3. 未載明於附表一的手術項目，將比照附表一內程度相當的手術項目決定給付倍數。  
+4. 以下情形不負給付責任：  
+   - 依據除外責任條款規定不在給付範圍內。  
+   - 不屬全民健康保險醫療服務給付項目及支付標準第二部第二章第七節或第三部第三章第四節第三項所列舉的手術。  
+條文依據：  
+- [第十一條 住院手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 住院手術醫療保險金 | 第十三條 意外住院手術醫療保險金 | 第十二條 門診手術醫療保險金 | payout_items | 第二十條 除外責任（一） | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院手術醫療保險金的給付規定如下：  
+1. 被保險人於契約有效期間內因疾病或傷害，經醫師診斷必須住院接受附表一所列的手術治療且已實際接受手術者，本公司依保險單記載的「保險金額」乘以手術日當年度的「增額係數」，再乘以手術給付倍數，給付住院手術醫療保險金。  
+2. 若同一次手術中於同一手術位置接受二項以上手術項目，僅給付手術給付倍數最高的手術項目。  
+3. 未載明於附表一的手術項目，將比照附表一內程度相當的手術項目決定給付倍數。  
+4. 以下情形不負給付責任：  
+   - 依據除外責任條款規定不在給付範圍內。  
+   - 不屬全民健康保險醫療服務給付項目及支付標準第二部第二章第七節或第三部第三章第四節第三項所列舉的手術。  
+條文依據：  
+- [第十一條 住院手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr"/>
+      <c r="H191" s="2" t="inlineStr"/>
+      <c r="I191" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.994507, "neutral": 0.00473, "contradiction": 0.000763, "factuality": 0.999237, "C_fact": 0.999237}, "C_conf": 0.9992}</t>
+        </is>
+      </c>
+      <c r="J191" s="5" t="n"/>
+      <c r="K191" s="5" t="n">
+        <v>0.999237</v>
+      </c>
+      <c r="L191" s="5" t="n">
+        <v>0.9992</v>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:20:44</t>
+        </is>
+      </c>
+      <c r="N191" s="5" t="n">
+        <v>6.87</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>門診手術醫療保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+門診手術醫療保險金的給付規定如下：  
+1. 被保險人因疾病或傷害，經醫師診斷必須於醫院或診所門診接受附表一的手術治療且已實際接受手術者，本公司依保險單所記載之「保險金額」乘以手術日當年度之「增額係數」，再乘以手術給付倍數，給付「門診手術醫療保險金」。  
+2. 同一次手術中，若於同一手術位置接受二項以上手術項目，僅給付手術給付倍數最高的手術項目。  
+3. 同一保險單年度內，門診手術醫療保險金的給付以十次為限。  
+4. 未載明於附表一所列的手術項目，將與被保險人協議比照該表內之手術項目，決定給付倍數。  
+5. 以下情形不負給付責任：  
+   - 依據本契約除外責任條款的規定不在給付範圍內。  
+   - 不屬全民健康保險醫療服務給付項目及支付標準第二部第二章第七節或第三部第三章第四節第三項所列舉的手術。  
+條文依據：  
+- [第十二條 門診手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 門診手術醫療保險金 | 第十一條 住院手術醫療保險金 | payout_items | 第十三條 意外住院手術醫療保險金 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+門診手術醫療保險金的給付規定如下：  
+1. 被保險人因疾病或傷害，經醫師診斷必須於醫院或診所門診接受附表一的手術治療且已實際接受手術者，本公司依保險單所記載之「保險金額」乘以手術日當年度之「增額係數」，再乘以手術給付倍數，給付「門診手術醫療保險金」。  
+2. 同一次手術中，若於同一手術位置接受二項以上手術項目，僅給付手術給付倍數最高的手術項目。  
+3. 同一保險單年度內，門診手術醫療保險金的給付以十次為限。  
+4. 未載明於附表一所列的手術項目，將與被保險人協議比照該表內之手術項目，決定給付倍數。  
+5. 以下情形不負給付責任：  
+   - 依據本契約除外責任條款的規定不在給付範圍內。  
+   - 不屬全民健康保險醫療服務給付項目及支付標準第二部第二章第七節或第三部第三章第四節第三項所列舉的手術。  
+條文依據：  
+- [第十二條 門診手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr"/>
+      <c r="H192" s="2" t="inlineStr"/>
+      <c r="I192" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.904984, "neutral": 0.092394, "contradiction": 0.002622, "factuality": 0.997378, "C_fact": 0.997378}, "C_conf": 0.9974}</t>
+        </is>
+      </c>
+      <c r="J192" s="5" t="n"/>
+      <c r="K192" s="5" t="n">
+        <v>0.997378</v>
+      </c>
+      <c r="L192" s="5" t="n">
+        <v>0.9974</v>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:20:49</t>
+        </is>
+      </c>
+      <c r="N192" s="5" t="n">
+        <v>4.78</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>意外住院手術醫療保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外住院手術醫療保險金的給付規定如下：  
+1. 被保險人於契約有效期間內且保險年齡未滿七十歲，因傷害經醫師診斷在住院期間必須接受手術治療且已接受手術者，本公司按保險單所記載之「保險金額」的三倍，乘以手術日當年度之「增額係數」，給付「意外住院手術醫療保險金」。  
+2. 若被保險人於同一次手術中，於同一手術位置接受二項以上手術項目時，僅給付一次「意外住院手術醫療保險金」。  
+條文依據：  
+- [第十三條 意外住院手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 意外住院手術醫療保險金 | 第十一條 住院手術醫療保險金 | 第十五條 意外創傷縫合處置保險金 | 第二十條 除外責任（一） | 第十二條 門診手術醫療保險金 | 附表三：意外創傷縫合處置項目及給付倍數表 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外住院手術醫療保險金的給付規定如下：  
+1. 被保險人於契約有效期間內且保險年齡未滿七十歲，因傷害經醫師診斷在住院期間必須接受手術治療且已接受手術者，本公司按保險單所記載之「保險金額」的三倍，乘以手術日當年度之「增額係數」，給付「意外住院手術醫療保險金」。  
+2. 若被保險人於同一次手術中，於同一手術位置接受二項以上手術項目時，僅給付一次「意外住院手術醫療保險金」。  
+條文依據：  
+- [第十三條 意外住院手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="inlineStr"/>
+      <c r="H193" s="2" t="inlineStr"/>
+      <c r="I193" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.992892, "neutral": 0.006516, "contradiction": 0.000591, "factuality": 0.999409, "C_fact": 0.999409}, "C_conf": 0.9994}</t>
+        </is>
+      </c>
+      <c r="J193" s="5" t="n"/>
+      <c r="K193" s="5" t="n">
+        <v>0.999409</v>
+      </c>
+      <c r="L193" s="5" t="n">
+        <v>0.9994</v>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:20:52</t>
+        </is>
+      </c>
+      <c r="N193" s="5" t="n">
+        <v>3.44</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>特定處置保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+特定處置保險金的給付規定如下：  
+1. 被保險人因疾病或傷害，經醫師診斷必須於醫院或診所接受附表二所列之特定處置治療且已接受處置者，保險公司將依保險單所記載的「保險金額」，乘以特定處置日當年度的「增額係數」，再乘以特定處置給付倍數，給付「特定處置保險金」。  
+2. 同一次處置治療中，若於同一治療位置接受二項以上特定處置項目，僅給付特定處置給付倍數最高的特定處置項目。  
+3. 若被保險人所接受的處置未載明於附表二所列之特定處置項目，保險公司不負給付特定處置保險金的責任。  
+4. 同一保險單年度的「特定處置保險金」給付次數以十次為限。
+條文依據：  
+- [第十四條 特定處置保險金]</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 特定處置保險金 | 第十五條 意外創傷縫合處置保險金 | 附表二：特定處置項目及給付倍數表 | 第五條 保險範圍 | 附表三：意外創傷縫合處置項目及給付倍數表</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+特定處置保險金的給付規定如下：  
+1. 被保險人因疾病或傷害，經醫師診斷必須於醫院或診所接受附表二所列之特定處置治療且已接受處置者，保險公司將依保險單所記載的「保險金額」，乘以特定處置日當年度的「增額係數」，再乘以特定處置給付倍數，給付「特定處置保險金」。  
+2. 同一次處置治療中，若於同一治療位置接受二項以上特定處置項目，僅給付特定處置給付倍數最高的特定處置項目。  
+3. 若被保險人所接受的處置未載明於附表二所列之特定處置項目，保險公司不負給付特定處置保險金的責任。  
+4. 同一保險單年度的「特定處置保險金」給付次數以十次為限。
+條文依據：  
+- [第十四條 特定處置保險金]</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr"/>
+      <c r="H194" s="2" t="inlineStr"/>
+      <c r="I194" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.988805, "neutral": 0.010095, "contradiction": 0.0011, "factuality": 0.9989, "C_fact": 0.9989}, "C_conf": 0.9989}</t>
+        </is>
+      </c>
+      <c r="J194" s="5" t="n"/>
+      <c r="K194" s="5" t="n">
+        <v>0.9989</v>
+      </c>
+      <c r="L194" s="5" t="n">
+        <v>0.9989</v>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:20:57</t>
+        </is>
+      </c>
+      <c r="N194" s="5" t="n">
+        <v>4.35</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>意外創傷縫合處置保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外創傷縫合處置保險金的給付規定如下：  
+1. 被保險人因意外傷害事故，於醫院或診所接受附表三所列的意外創傷縫合處置治療者，本公司將依保險單記載的「保險金額」，乘以當年度的「增額係數」，再乘以意外創傷縫合處置給付倍數，給付保險金。  
+2. 同一次意外傷害事故，僅就傷口最大者給付保險金，且以給付一次為限。  
+3. 若被保險人因同一意外傷害事故，已申領住院手術醫療保險金或門診手術醫療保險金者，則不再給付意外創傷縫合處置保險金。
+條文依據：  
+- [第十五條 意外創傷縫合處置保險金]</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>第十五條 意外創傷縫合處置保險金 | 附表三：意外創傷縫合處置項目及給付倍數表 | 第十四條 特定處置保險金 | 第二十條 除外責任（一） | 第十三條 意外住院手術醫療保險金 | 附表二：特定處置項目及給付倍數表</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外創傷縫合處置保險金的給付規定如下：  
+1. 被保險人因意外傷害事故，於醫院或診所接受附表三所列的意外創傷縫合處置治療者，本公司將依保險單記載的「保險金額」，乘以當年度的「增額係數」，再乘以意外創傷縫合處置給付倍數，給付保險金。  
+2. 同一次意外傷害事故，僅就傷口最大者給付保險金，且以給付一次為限。  
+3. 若被保險人因同一意外傷害事故，已申領住院手術醫療保險金或門診手術醫療保險金者，則不再給付意外創傷縫合處置保險金。
+條文依據：  
+- [第十五條 意外創傷縫合處置保險金]</t>
+        </is>
+      </c>
+      <c r="G195" s="2" t="inlineStr"/>
+      <c r="H195" s="2" t="inlineStr"/>
+      <c r="I195" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.991842, "neutral": 0.007354, "contradiction": 0.000804, "factuality": 0.999196, "C_fact": 0.999196}, "C_conf": 0.9992}</t>
+        </is>
+      </c>
+      <c r="J195" s="5" t="n"/>
+      <c r="K195" s="5" t="n">
+        <v>0.999196</v>
+      </c>
+      <c r="L195" s="5" t="n">
+        <v>0.9992</v>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:21:01</t>
+        </is>
+      </c>
+      <c r="N195" s="5" t="n">
+        <v>4.01</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>醫療保險金給付總額之上限</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+醫療保險金給付總額之上限為保險單上所記載的「保險金額」的一千五百倍，且僅限於本契約有效期間內依第十一條至第十五條所給付的各項保險金，不包含其他附約、附加條款或批註條款。
+條文依據：  
+- [第十六條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 醫療保險金給付總額之上限 | 第十二條 門診手術醫療保險金 | 第五條 保險範圍 | 第十一條 住院手術醫療保險金 | 第十三條 意外住院手術醫療保險金 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+醫療保險金給付總額之上限為保險單上所記載的「保險金額」的一千五百倍，且僅限於本契約有效期間內依第十一條至第十五條所給付的各項保險金，不包含其他附約、附加條款或批註條款。
+條文依據：  
+- [第十六條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr"/>
+      <c r="H196" s="2" t="inlineStr"/>
+      <c r="I196" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.99341, "neutral": 0.006378, "contradiction": 0.000212, "factuality": 0.999788, "C_fact": 0.999788}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J196" s="5" t="n"/>
+      <c r="K196" s="5" t="n">
+        <v>0.999788</v>
+      </c>
+      <c r="L196" s="5" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:21:04</t>
+        </is>
+      </c>
+      <c r="N196" s="5" t="n">
+        <v>2.87</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>祝壽保險金的領取規定為何?</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+祝壽保險金的領取規定如下：  
+1. 被保險人需於本契約有效期間且保險年齡到達九十九歲之保險單週年日仍生存，方可申領祝壽保險金。  
+2. 受益人申領祝壽保險金時，需檢具以下文件：  
+   - 保險單或其謄本  
+   - 保險金申請書  
+   - 受益人的身分證明  
+條文依據：  
+- [第十七條 祝壽保險金]  
+- [第二十六條 祝壽保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>第十七條 祝壽保險金 | 第二十六條 祝壽保險金的申領 | 第十一條至第十五條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | 第二十三條 保險事故的通知與保險金的申請時間 | 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+祝壽保險金的領取規定如下：  
+1. 被保險人需於本契約有效期間且保險年齡到達九十九歲之保險單週年日仍生存，方可申領祝壽保險金。  
+2. 受益人申領祝壽保險金時，需檢具以下文件：  
+   - 保險單或其謄本  
+   - 保險金申請書  
+   - 受益人的身分證明  
+條文依據：  
+- [第十七條 祝壽保險金]  
+- [第二十六條 祝壽保險金的申領]</t>
+        </is>
+      </c>
+      <c r="G197" s="2" t="inlineStr"/>
+      <c r="H197" s="2" t="inlineStr"/>
+      <c r="I197" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.998662, "neutral": 0.001196, "contradiction": 0.000141, "factuality": 0.999859, "C_fact": 0.999859}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J197" s="5" t="n"/>
+      <c r="K197" s="5" t="n">
+        <v>0.9998590000000001</v>
+      </c>
+      <c r="L197" s="5" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:21:06</t>
+        </is>
+      </c>
+      <c r="N197" s="5" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>身故時領取保險金有什麼規則?</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+身故時領取保險金的規則如下：  
+1. 被保險人於契約有效期間內身故，本公司按「當年度保險金額」給付「身故保險金」。  
+2. 若被保險人身故時實際年齡未滿十五足歲，本公司退還「所繳保險費」予要保人，不適用「當年度保險金額」的約定。  
+3. 若被保險人於訂立契約時受監護宣告尚未撤銷，其身故保險金改為喪葬費用保險金，且喪葬費用保險金額不得超過遺產稅喪葬費扣除額之半數，超過部分不負給付責任。  
+4. 受益人申領身故保險金或喪葬費用保險金時，需提供保險單、死亡證明書及除戶戶籍謄本、保險金申請書及受益人身分證明。  
+條文依據：  
+- [第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金]  
+- [第二十七條 身故保險金或喪葬費用保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金 | 第二十七條 身故保險金或喪葬費用保險金的申領 | 第十一條至第十五條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | 第二十一條 除外責任（二） | 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+身故時領取保險金的規則如下：  
+1. 被保險人於契約有效期間內身故，本公司按「當年度保險金額」給付「身故保險金」。  
+2. 若被保險人身故時實際年齡未滿十五足歲，本公司退還「所繳保險費」予要保人，不適用「當年度保險金額」的約定。  
+3. 若被保險人於訂立契約時受監護宣告尚未撤銷，其身故保險金改為喪葬費用保險金，且喪葬費用保險金額不得超過遺產稅喪葬費扣除額之半數，超過部分不負給付責任。  
+4. 受益人申領身故保險金或喪葬費用保險金時，需提供保險單、死亡證明書及除戶戶籍謄本、保險金申請書及受益人身分證明。  
+條文依據：  
+- [第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金]  
+- [第二十七條 身故保險金或喪葬費用保險金的申領]</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr"/>
+      <c r="H198" s="2" t="inlineStr"/>
+      <c r="I198" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.499941, "neutral": 0.497298, "contradiction": 0.002761, "factuality": 0.997239, "C_fact": 0.997239}, "C_conf": 0.9972}</t>
+        </is>
+      </c>
+      <c r="J198" s="5" t="n"/>
+      <c r="K198" s="5" t="n">
+        <v>0.997239</v>
+      </c>
+      <c r="L198" s="5" t="n">
+        <v>0.9972</v>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:21:10</t>
+        </is>
+      </c>
+      <c r="N198" s="5" t="n">
+        <v>3.66</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>什麼情況下可以保費折減?</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人年齡滿20歲（含）以上，並使用保險公司指定程式加入健康計劃，於「指定日期」的會員等級符合進階會員或菁英會員（或更高等級）標準者，可享次一保險單年度的保費折減。折減比例為進階會員2%，菁英會員或更高等級3%。但豁免或復效的保險費不適用折減約定。
+條文依據：  
+- [第十九條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 健康促進保險費折減 | 第三十條 保險金額之減少 | 第二十條 除外責任（一） | 第三十一條 投保年齡的計算及錯誤的處理 | 第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人年齡滿20歲（含）以上，並使用保險公司指定程式加入健康計劃，於「指定日期」的會員等級符合進階會員或菁英會員（或更高等級）標準者，可享次一保險單年度的保費折減。折減比例為進階會員2%，菁英會員或更高等級3%。但豁免或復效的保險費不適用折減約定。
+條文依據：  
+- [第十九條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="inlineStr"/>
+      <c r="H199" s="2" t="inlineStr"/>
+      <c r="I199" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.995552, "neutral": 0.004211, "contradiction": 0.000237, "factuality": 0.999763, "C_fact": 0.999763}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J199" s="5" t="n"/>
+      <c r="K199" s="5" t="n">
+        <v>0.999763</v>
+      </c>
+      <c r="L199" s="5" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:21:13</t>
+        </is>
+      </c>
+      <c r="N199" s="5" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>角膜切除術是否可以申請理賠?</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+角膜切除術可以申請理賠，其手術項目編號為1305，給付倍數為5。  
+條文依據：  
+- 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+角膜切除術可以申請理賠，其手術項目編號為1305，給付倍數為5。  
+條文依據：  
+- 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="G200" s="2" t="inlineStr"/>
+      <c r="H200" s="2" t="inlineStr"/>
+      <c r="I200" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.106276, "neutral": 0.887582, "contradiction": 0.006142, "factuality": 0.993858, "C_fact": 0.993858}, "C_conf": 0.9939}</t>
+        </is>
+      </c>
+      <c r="J200" s="5" t="n"/>
+      <c r="K200" s="5" t="n">
+        <v>0.993858</v>
+      </c>
+      <c r="L200" s="5" t="n">
+        <v>0.9939</v>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:21:16</t>
+        </is>
+      </c>
+      <c r="N200" s="5" t="n">
+        <v>3.27</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>白內障手術是否可以申請理賠?</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+白內障手術是否可以申請理賠需視手術是否符合附表一所列的手術項目及其給付倍數。如果白內障手術屬於附表一中所列的手術項目，例如「晶體切除術合併玻璃體切除術」（項目編號1367，給付倍數30），則可申請理賠。此外，手術需符合全民健康保險醫療服務給付項目及支付標準，並不屬於除外責任條款所規定的排除範圍。若手術不在附表一中，則需與保險公司協議比照附表一內的手術項目決定給付倍數。
+條文依據：  
+- [第十二條 門診手術醫療保險金]  
+- [附表一：手術項目與給付倍數]</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 門診手術醫療保險金 | 第二十條 除外責任（一） | 附表一：手術項目與給付倍數 | payout_items | 第十一條 住院手術醫療保險金</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+白內障手術是否可以申請理賠需視手術是否符合附表一所列的手術項目及其給付倍數。如果白內障手術屬於附表一中所列的手術項目，例如「晶體切除術合併玻璃體切除術」（項目編號1367，給付倍數30），則可申請理賠。此外，手術需符合全民健康保險醫療服務給付項目及支付標準，並不屬於除外責任條款所規定的排除範圍。若手術不在附表一中，則需與保險公司協議比照附表一內的手術項目決定給付倍數。
+條文依據：  
+- [第十二條 門診手術醫療保險金]  
+- [附表一：手術項目與給付倍數]</t>
+        </is>
+      </c>
+      <c r="G201" s="2" t="inlineStr"/>
+      <c r="H201" s="2" t="inlineStr"/>
+      <c r="I201" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.02805, "neutral": 0.969831, "contradiction": 0.002119, "factuality": 0.997881, "C_fact": 0.997881}, "C_conf": 0.9979}</t>
+        </is>
+      </c>
+      <c r="J201" s="5" t="n"/>
+      <c r="K201" s="5" t="n">
+        <v>0.997881</v>
+      </c>
+      <c r="L201" s="5" t="n">
+        <v>0.9979</v>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:21:20</t>
+        </is>
+      </c>
+      <c r="N201" s="5" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>保障範圍包括哪些項目？</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括：意外事故身故保險金或喪葬費用保險金、意外事故失能保險金、每月生活照護保險金、重大燒燙傷保險金、意外骨折保險金、傷害醫療日額保險金、意外創傷縫合處置保險金。
+條文依據：  
+- 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>payout_items | 第五條 保險範圍 | 第十五條 每月生活照護保險金的給付 | 第三十條 不保事項 | 附表二：失能程度與保險金給付表</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括：意外事故身故保險金或喪葬費用保險金、意外事故失能保險金、每月生活照護保險金、重大燒燙傷保險金、意外骨折保險金、傷害醫療日額保險金、意外創傷縫合處置保險金。
+條文依據：  
+- 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="G202" s="2" t="inlineStr"/>
+      <c r="H202" s="2" t="inlineStr"/>
+      <c r="I202" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.998144, "neutral": 0.001643, "contradiction": 0.000214, "factuality": 0.999786, "C_fact": 0.999786}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J202" s="5" t="n"/>
+      <c r="K202" s="5" t="n">
+        <v>0.999786</v>
+      </c>
+      <c r="L202" s="5" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:21:22</t>
+        </is>
+      </c>
+      <c r="N202" s="5" t="n">
+        <v>2.24</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>發生意外事故身故，理賠內容為何?</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外事故身故的理賠內容包括「意外事故身故保險金」或「喪葬費用保險金」，其金額依意外傷害事故的種類而定：  
+1. 一般意外傷害事故：「傷害醫療保險金日額」的五百倍。  
+2. 特定意外傷害事故：「傷害醫療保險金日額」的一千倍。  
+若被保險人於意外傷害事故發生後超過一百八十日身故，但受益人能證明身故與該事故具有因果關係，本公司仍依上述約定給付保險金。此外，若被保險人受監護宣告尚未撤銷，其理賠內容改為「喪葬費用保險金」，且喪葬費用保險金額不得超過遺產稅喪葬費扣除額之半數，超過部分不予理賠。  
+條文依據：  
+- [第十二條 意外事故身故保險金或喪葬費用保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 意外事故身故保險金或喪葬費用保險金的給付 | 第十四條 保險給付的限制 | payout_items | 第十一條 契約的終止（二） | 第二十一條 失蹤處理</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外事故身故的理賠內容包括「意外事故身故保險金」或「喪葬費用保險金」，其金額依意外傷害事故的種類而定：  
+1. 一般意外傷害事故：「傷害醫療保險金日額」的五百倍。  
+2. 特定意外傷害事故：「傷害醫療保險金日額」的一千倍。  
+若被保險人於意外傷害事故發生後超過一百八十日身故，但受益人能證明身故與該事故具有因果關係，本公司仍依上述約定給付保險金。此外，若被保險人受監護宣告尚未撤銷，其理賠內容改為「喪葬費用保險金」，且喪葬費用保險金額不得超過遺產稅喪葬費扣除額之半數，超過部分不予理賠。  
+條文依據：  
+- [第十二條 意外事故身故保險金或喪葬費用保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G203" s="2" t="inlineStr"/>
+      <c r="H203" s="2" t="inlineStr"/>
+      <c r="I203" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.963749, "neutral": 0.035863, "contradiction": 0.000388, "factuality": 0.999612, "C_fact": 0.999612}, "C_conf": 0.9996}</t>
+        </is>
+      </c>
+      <c r="J203" s="5" t="n"/>
+      <c r="K203" s="5" t="n">
+        <v>0.9996119999999999</v>
+      </c>
+      <c r="L203" s="5" t="n">
+        <v>0.9996</v>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:21:26</t>
+        </is>
+      </c>
+      <c r="N203" s="5" t="n">
+        <v>3.44</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>意外事故失能保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外事故失能保險金的給付條件為：被保險人於契約有效期間內遭受意外傷害事故，並於事故發生後一百八十日內致成附表二所列失能程度之一者，本公司依意外傷害事故種類及失能程度，按以下約定金額給付：  
+1. 一般意外傷害事故：傷害醫療保險金日額的五百倍乘以附表二給付比例。  
+2. 特定意外傷害事故：傷害醫療保險金日額的一千倍乘以附表二給付比例。  
+若被保險人超過一百八十日後才致成失能，但受益人能證明失能與事故具有因果關係者，仍可依上述規定申領保險金，不受一百八十日限制。  
+此外，若因同一事故致成附表二所列多項失能程度，保險金給付以該事故種類的上限金額為限；若失能項目屬於同一手或足，僅給付一項保險金，且依較嚴重項目計算。  
+條文依據：  
+- [第十三條 意外事故失能保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 意外事故失能保險金的給付 | 第十五條 每月生活照護保險金的給付 | 第十四條 保險給付的限制 | 第十二條 意外事故身故保險金或喪葬費用保險金的給付 | 第二十三條 意外事故失能保險金的申領 | 附表二：失能程度與保險金給付表</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外事故失能保險金的給付條件為：被保險人於契約有效期間內遭受意外傷害事故，並於事故發生後一百八十日內致成附表二所列失能程度之一者，本公司依意外傷害事故種類及失能程度，按以下約定金額給付：  
+1. 一般意外傷害事故：傷害醫療保險金日額的五百倍乘以附表二給付比例。  
+2. 特定意外傷害事故：傷害醫療保險金日額的一千倍乘以附表二給付比例。  
+若被保險人超過一百八十日後才致成失能，但受益人能證明失能與事故具有因果關係者，仍可依上述規定申領保險金，不受一百八十日限制。  
+此外，若因同一事故致成附表二所列多項失能程度，保險金給付以該事故種類的上限金額為限；若失能項目屬於同一手或足，僅給付一項保險金，且依較嚴重項目計算。  
+條文依據：  
+- [第十三條 意外事故失能保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="inlineStr"/>
+      <c r="H204" s="2" t="inlineStr"/>
+      <c r="I204" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.007472, "neutral": 0.98085, "contradiction": 0.011678, "factuality": 0.988322, "C_fact": 0.988322}, "C_conf": 0.9883}</t>
+        </is>
+      </c>
+      <c r="J204" s="5" t="n"/>
+      <c r="K204" s="5" t="n">
+        <v>0.988322</v>
+      </c>
+      <c r="L204" s="5" t="n">
+        <v>0.9883</v>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:21:31</t>
+        </is>
+      </c>
+      <c r="N204" s="5" t="n">
+        <v>4.81</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>每月生活照護保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+每月生活照護保險金的給付條件如下：  
+1. 被保險人於契約有效期間內遭受意外傷害事故，並於事故發生後180日內致成附表二所列第一級至第六級失能程度之一時，本公司自失能診斷確定當日起，按「傷害醫療保險金日額」的20倍乘以附表二給付比例所得之金額，按月給付，最多以12個月為限。  
+2. 若失能診斷確定後的前四個「失能診斷確定週年日」，契約仍有效且被保險人仍生存，本公司自各該週年日起，依相同計算方式按月給付，最多以12個月為限。  
+3. 若被保險人於事故發生後超過180日致成失能，受益人能證明失能與事故具有因果關係者，本公司仍依上述規定給付，不受180日限制。  
+4. 同一事故若致成多項失能，僅給付較嚴重項目，且最高以「傷害醫療保險金日額」的20倍為限。  
+5. 累計給付金額最高以「傷害醫療保險金日額」的1200倍為限。  
+條文依據：  
+- [第十五條 每月生活照護保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>第二十四條 每月生活照護保險金的申領 | 第十五條 每月生活照護保險金的給付 | payout_items | 第十八條 傷害醫療日額保險金的給付 | 第五條 保險範圍 | 附表二：失能程度與保險金給付表 | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+每月生活照護保險金的給付條件如下：  
+1. 被保險人於契約有效期間內遭受意外傷害事故，並於事故發生後180日內致成附表二所列第一級至第六級失能程度之一時，本公司自失能診斷確定當日起，按「傷害醫療保險金日額」的20倍乘以附表二給付比例所得之金額，按月給付，最多以12個月為限。  
+2. 若失能診斷確定後的前四個「失能診斷確定週年日」，契約仍有效且被保險人仍生存，本公司自各該週年日起，依相同計算方式按月給付，最多以12個月為限。  
+3. 若被保險人於事故發生後超過180日致成失能，受益人能證明失能與事故具有因果關係者，本公司仍依上述規定給付，不受180日限制。  
+4. 同一事故若致成多項失能，僅給付較嚴重項目，且最高以「傷害醫療保險金日額」的20倍為限。  
+5. 累計給付金額最高以「傷害醫療保險金日額」的1200倍為限。  
+條文依據：  
+- [第十五條 每月生活照護保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G205" s="2" t="inlineStr"/>
+      <c r="H205" s="2" t="inlineStr"/>
+      <c r="I205" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.283533, "neutral": 0.699171, "contradiction": 0.017296, "factuality": 0.982704, "C_fact": 0.982704}, "C_conf": 0.9827}</t>
+        </is>
+      </c>
+      <c r="J205" s="5" t="n"/>
+      <c r="K205" s="5" t="n">
+        <v>0.982704</v>
+      </c>
+      <c r="L205" s="5" t="n">
+        <v>0.9827</v>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:21:36</t>
+        </is>
+      </c>
+      <c r="N205" s="5" t="n">
+        <v>5.44</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>重大燒燙傷保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+重大燒燙傷保險金的給付條件為：被保險人於契約有效期間內遭受意外傷害事故，導致燒燙傷並經診斷符合重大燒燙傷的標準時，本公司將按傷害醫療保險金日額的二百五十倍給付重大燒燙傷保險金。此保險金的給付以一次為限。
+條文依據：  
+- [第十六條 重大燒燙傷保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 重大燒燙傷保險金的給付 | 第二十五條 重大燒燙傷保險金的申領 | 第五條 保險範圍 | payout_items | 第二十九條 除外責任（原因）</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+重大燒燙傷保險金的給付條件為：被保險人於契約有效期間內遭受意外傷害事故，導致燒燙傷並經診斷符合重大燒燙傷的標準時，本公司將按傷害醫療保險金日額的二百五十倍給付重大燒燙傷保險金。此保險金的給付以一次為限。
+條文依據：  
+- [第十六條 重大燒燙傷保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G206" s="2" t="inlineStr"/>
+      <c r="H206" s="2" t="inlineStr"/>
+      <c r="I206" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.99779, "neutral": 0.002089, "contradiction": 0.000121, "factuality": 0.999879, "C_fact": 0.999879}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J206" s="5" t="n"/>
+      <c r="K206" s="5" t="n">
+        <v>0.999879</v>
+      </c>
+      <c r="L206" s="5" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:21:39</t>
+        </is>
+      </c>
+      <c r="N206" s="5" t="n">
+        <v>2.86</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>意外骨折保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外骨折保險金的給付條件如下：  
+1. 被保險人於契約有效期間內遭受「意外傷害事故」，自事故發生日起一百八十日內，經合格醫院或診所診斷為附表三骨折別表所列骨折項目之一（含不完全骨折及骨骼龜裂），本公司按「傷害醫療保險金日額」的二倍給付。  
+2. 若超過一百八十日診斷確定骨折，受益人需證明骨折與事故具有因果關係，本公司仍給付保險金，不受一百八十日限制。  
+3. 同一意外傷害事故僅給付一次意外骨折保險金。  
+4. 若骨折非屬附表三骨折別表所列項目，需由本公司與被保險人協議核付；但若骨折部位為骨折別表內明訂不給付之部位，本公司不負給付責任。
+條文依據：  
+- [第十七條 意外骨折保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>第十七條 意外骨折保險金的給付 | 第十八條 傷害醫療日額保險金的給付 | 第二十六條 意外骨折保險金的申領 | 第十三條 意外事故失能保險金的給付 | 第十九條 意外創傷縫合處置保險金的給付 | 附表二：失能程度與保險金給付表 | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外骨折保險金的給付條件如下：  
+1. 被保險人於契約有效期間內遭受「意外傷害事故」，自事故發生日起一百八十日內，經合格醫院或診所診斷為附表三骨折別表所列骨折項目之一（含不完全骨折及骨骼龜裂），本公司按「傷害醫療保險金日額」的二倍給付。  
+2. 若超過一百八十日診斷確定骨折，受益人需證明骨折與事故具有因果關係，本公司仍給付保險金，不受一百八十日限制。  
+3. 同一意外傷害事故僅給付一次意外骨折保險金。  
+4. 若骨折非屬附表三骨折別表所列項目，需由本公司與被保險人協議核付；但若骨折部位為骨折別表內明訂不給付之部位，本公司不負給付責任。
+條文依據：  
+- [第十七條 意外骨折保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G207" s="2" t="inlineStr"/>
+      <c r="H207" s="2" t="inlineStr"/>
+      <c r="I207" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.992297, "neutral": 0.007132, "contradiction": 0.00057, "factuality": 0.99943, "C_fact": 0.99943}, "C_conf": 0.9994}</t>
+        </is>
+      </c>
+      <c r="J207" s="5" t="n"/>
+      <c r="K207" s="5" t="n">
+        <v>0.99943</v>
+      </c>
+      <c r="L207" s="5" t="n">
+        <v>0.9994</v>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:21:44</t>
+        </is>
+      </c>
+      <c r="N207" s="5" t="n">
+        <v>4.71</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>傷害醫療日額保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+傷害醫療日額保險金的給付條件如下：  
+1. 被保險人於契約有效期間內遭受「意外傷害事故」，自事故發生日起一百八十日內於「醫院」接受住院治療者，本公司按「傷害醫療保險金日額」乘以實際住院日數給付，最高以九十日為限。  
+2. 若治療超過一百八十日，受益人能證明治療與事故具有因果關係者，仍可依上述規定給付，不受一百八十日限制。  
+3. 若因骨折未住院或住院日數未達附表三骨折別表所訂日數，未住院部分按骨折別表日數乘以「傷害醫療保險金日額」的二分之一給付，合計給付日數以骨折別表所訂日數為上限。  
+4. 骨折類型的給付依骨骼損傷程度區分：完全骨折按骨折別表日數給付；不完全骨折按完全骨折日數二分之一給付；骨骼龜裂按完全骨折日數四分之一給付。同時發生多項骨折時，僅給付較高等級的保險金。
+條文依據：  
+- [第十八條 傷害醫療日額保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 傷害醫療日額保險金的給付 | 第二十七條 傷害醫療日額保險金的申領 | 第十五條 每月生活照護保險金的給付 | 第三十四條 傷害醫療保險金日額之減少 | 第十九條 意外創傷縫合處置保險金的給付 | 附表二：失能程度與保險金給付表 | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+傷害醫療日額保險金的給付條件如下：  
+1. 被保險人於契約有效期間內遭受「意外傷害事故」，自事故發生日起一百八十日內於「醫院」接受住院治療者，本公司按「傷害醫療保險金日額」乘以實際住院日數給付，最高以九十日為限。  
+2. 若治療超過一百八十日，受益人能證明治療與事故具有因果關係者，仍可依上述規定給付，不受一百八十日限制。  
+3. 若因骨折未住院或住院日數未達附表三骨折別表所訂日數，未住院部分按骨折別表日數乘以「傷害醫療保險金日額」的二分之一給付，合計給付日數以骨折別表所訂日數為上限。  
+4. 骨折類型的給付依骨骼損傷程度區分：完全骨折按骨折別表日數給付；不完全骨折按完全骨折日數二分之一給付；骨骼龜裂按完全骨折日數四分之一給付。同時發生多項骨折時，僅給付較高等級的保險金。
+條文依據：  
+- [第十八條 傷害醫療日額保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G208" s="2" t="inlineStr"/>
+      <c r="H208" s="2" t="inlineStr"/>
+      <c r="I208" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.963785, "neutral": 0.035792, "contradiction": 0.000422, "factuality": 0.999578, "C_fact": 0.999578}, "C_conf": 0.9996}</t>
+        </is>
+      </c>
+      <c r="J208" s="5" t="n"/>
+      <c r="K208" s="5" t="n">
+        <v>0.999578</v>
+      </c>
+      <c r="L208" s="5" t="n">
+        <v>0.9996</v>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:21:49</t>
+        </is>
+      </c>
+      <c r="N208" s="5" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>意外創傷縫合處置保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外創傷縫合處置保險金的給付條件為：被保險人於契約有效期間內遭受「意外傷害事故」，並於「醫院」或「診所」經醫師診斷必須接受創傷縫合處置治療且已接受縫合處置者，本公司按「傷害醫療保險金日額」給付該保險金。同一意外傷害事故僅給付一次。
+條文依據：  
+- [第十九條 意外創傷縫合處置保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 意外創傷縫合處置保險金的給付 | 第二十八條 意外創傷縫合處置保險金的申領 | 第五條 保險範圍 | 第十七條 意外骨折保險金的給付 | payout_items | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外創傷縫合處置保險金的給付條件為：被保險人於契約有效期間內遭受「意外傷害事故」，並於「醫院」或「診所」經醫師診斷必須接受創傷縫合處置治療且已接受縫合處置者，本公司按「傷害醫療保險金日額」給付該保險金。同一意外傷害事故僅給付一次。
+條文依據：  
+- [第十九條 意外創傷縫合處置保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G209" s="2" t="inlineStr"/>
+      <c r="H209" s="2" t="inlineStr"/>
+      <c r="I209" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.996712, "neutral": 0.003178, "contradiction": 0.000111, "factuality": 0.999889, "C_fact": 0.999889}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J209" s="5" t="n"/>
+      <c r="K209" s="5" t="n">
+        <v>0.999889</v>
+      </c>
+      <c r="L209" s="5" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:21:52</t>
+        </is>
+      </c>
+      <c r="N209" s="5" t="n">
+        <v>2.85</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>因意外導致視力衰退，是否能申請理賠?</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+因意外導致視力衰退是否能申請理賠，需符合以下條件：  
+1. 視力永久在萬國式視力表0.02以下，或眼球喪失、摘出、僅能辨明暗或辨眼前一公尺以內手動或辨眼前五公分以內指數者。  
+2. 以自傷害之日起經過六個月的治療為判定原則，但若屬眼球摘出等明顯無法復原之情況，則不受六個月治療期間限制。  
+若符合上述條件，則可申請理賠。  
+條文依據：  
+- 註2</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>第二十三條 意外事故失能保險金的申領 | 第十三條 意外事故失能保險金的給付 | 註2： | 第三十條 不保事項 | 第二十六條 意外骨折保險金的申領 | 附表二：失能程度與保險金給付表</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+因意外導致視力衰退是否能申請理賠，需符合以下條件：  
+1. 視力永久在萬國式視力表0.02以下，或眼球喪失、摘出、僅能辨明暗或辨眼前一公尺以內手動或辨眼前五公分以內指數者。  
+2. 以自傷害之日起經過六個月的治療為判定原則，但若屬眼球摘出等明顯無法復原之情況，則不受六個月治療期間限制。  
+若符合上述條件，則可申請理賠。  
+條文依據：  
+- 註2</t>
+        </is>
+      </c>
+      <c r="G210" s="2" t="inlineStr"/>
+      <c r="H210" s="2" t="inlineStr"/>
+      <c r="I210" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.90648, "neutral": 0.089724, "contradiction": 0.003796, "factuality": 0.996204, "C_fact": 0.996204}, "C_conf": 0.9962}</t>
+        </is>
+      </c>
+      <c r="J210" s="5" t="n"/>
+      <c r="K210" s="5" t="n">
+        <v>0.996204</v>
+      </c>
+      <c r="L210" s="5" t="n">
+        <v>0.9962</v>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:21:55</t>
+        </is>
+      </c>
+      <c r="N210" s="5" t="n">
+        <v>2.67</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>肋骨骨折是否可以申請理賠?理賠金額為多少?</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+肋骨骨折可以申請理賠，理賠金額需依肋骨骨折的情形判定：  
+1. 若肋骨完全骨折且未住院治療，依附表三骨折別表所訂完全骨折日數（20天）乘以「傷害醫療保險金日額」的二分之一給付。  
+2. 若肋骨完全骨折且住院治療，依實際住院日數乘以「傷害醫療保險金日額」給付，但最高給付日數以附表三骨折別表所訂日數（20天）為上限。  
+3. 若肋骨不完全骨折，按完全骨折日數（20天）的二分之一給付；若肋骨龜裂，按完全骨折日數的四分之一給付。  
+條文依據：  
+- [第十八條 傷害醫療日額保險金的給付]  
+- [附表三：骨折別表]</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 傷害醫療日額保險金的給付 | 第十七條 意外骨折保險金的給付 | 第二十六條 意外骨折保險金的申領 | 第三十條 不保事項 | 第五條 保險範圍 | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+肋骨骨折可以申請理賠，理賠金額需依肋骨骨折的情形判定：  
+1. 若肋骨完全骨折且未住院治療，依附表三骨折別表所訂完全骨折日數（20天）乘以「傷害醫療保險金日額」的二分之一給付。  
+2. 若肋骨完全骨折且住院治療，依實際住院日數乘以「傷害醫療保險金日額」給付，但最高給付日數以附表三骨折別表所訂日數（20天）為上限。  
+3. 若肋骨不完全骨折，按完全骨折日數（20天）的二分之一給付；若肋骨龜裂，按完全骨折日數的四分之一給付。  
+條文依據：  
+- [第十八條 傷害醫療日額保險金的給付]  
+- [附表三：骨折別表]</t>
+        </is>
+      </c>
+      <c r="G211" s="2" t="inlineStr"/>
+      <c r="H211" s="2" t="inlineStr"/>
+      <c r="I211" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.896895, "neutral": 0.092865, "contradiction": 0.01024, "factuality": 0.98976, "C_fact": 0.98976}, "C_conf": 0.9898}</t>
+        </is>
+      </c>
+      <c r="J211" s="5" t="n"/>
+      <c r="K211" s="5" t="n">
+        <v>0.98976</v>
+      </c>
+      <c r="L211" s="5" t="n">
+        <v>0.9898</v>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:21:59</t>
+        </is>
+      </c>
+      <c r="N211" s="5" t="n">
+        <v>4.28</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>投保新鍾心滿福後，假設投保保額為100萬元，於第二保單年度接受「移植器官」，這樣可以領多少保險金?</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人於第二保險單年度(含)以後的有效期間內接受「移植器官」，符合「特定重大傷病」的定義，則可獲得「重大傷病保險金」及「特定重大傷病保險金」。其中，「特定重大傷病保險金」的給付金額為保險金額的20%。假設投保保額為100萬元，則「特定重大傷病保險金」為20萬元。此外，重大傷病保險金的具體金額需依保單條款進一步確認。
+條文依據：  
+- [第十三條 特定重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>附表一：全民健康保險重大傷病項目 | 第二條 名詞定義 | 第十三條 特定重大傷病保險金的給付 | 第十五條 滿期保險金的給付 | 附表三：各保險單年度可借金額上限表 | payout_items | 第十七條 完全失能保險金的給付 | 附表二：完全失能程度表</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人於第二保險單年度(含)以後的有效期間內接受「移植器官」，符合「特定重大傷病」的定義，則可獲得「重大傷病保險金」及「特定重大傷病保險金」。其中，「特定重大傷病保險金」的給付金額為保險金額的20%。假設投保保額為100萬元，則「特定重大傷病保險金」為20萬元。此外，重大傷病保險金的具體金額需依保單條款進一步確認。
+條文依據：  
+- [第十三條 特定重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G212" s="2" t="inlineStr"/>
+      <c r="H212" s="2" t="inlineStr"/>
+      <c r="I212" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.002961, "neutral": 0.994008, "contradiction": 0.003032, "factuality": 0.996968, "C_fact": 0.996968}, "C_conf": 0.997}</t>
+        </is>
+      </c>
+      <c r="J212" s="5" t="n"/>
+      <c r="K212" s="5" t="n">
+        <v>0.996968</v>
+      </c>
+      <c r="L212" s="5" t="n">
+        <v>0.997</v>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:22:23</t>
+        </is>
+      </c>
+      <c r="N212" s="5" t="n">
+        <v>23.66</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>投保新鍾心滿福後，若要理賠重大傷病保險金，一定要檢附全民健保開立的重大傷病證明才能拿到保險金嗎?</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不一定需要檢附全民健保開立的重大傷病證明。若被保險人已取得一家「區域醫院」層級以上（含）之醫療院所開立且符合投保當時「重大傷病範圍」的診斷書及當次「重大傷病」病歷摘要，亦可視為「重大傷病」證明文件，免向全民健康保險保險人申請重大傷病證明。  
+條文依據：  
+- [第二十二條 重大傷病保險金、特定重大傷病保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>第二十二條 重大傷病保險金、特定重大傷病保險金的申領 | 第十二條 重大傷病保險金的給付 | 第三十條 不保事項 | 第二條 名詞定義 | other_metadata | 附表一：全民健康保險重大傷病項目</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不一定需要檢附全民健保開立的重大傷病證明。若被保險人已取得一家「區域醫院」層級以上（含）之醫療院所開立且符合投保當時「重大傷病範圍」的診斷書及當次「重大傷病」病歷摘要，亦可視為「重大傷病」證明文件，免向全民健康保險保險人申請重大傷病證明。  
+條文依據：  
+- [第二十二條 重大傷病保險金、特定重大傷病保險金的申領]</t>
+        </is>
+      </c>
+      <c r="G213" s="2" t="inlineStr"/>
+      <c r="H213" s="2" t="inlineStr"/>
+      <c r="I213" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.976706, "neutral": 0.008421, "contradiction": 0.014873, "factuality": 0.985127, "C_fact": 0.985127}, "C_conf": 0.9851}</t>
+        </is>
+      </c>
+      <c r="J213" s="5" t="n"/>
+      <c r="K213" s="5" t="n">
+        <v>0.985127</v>
+      </c>
+      <c r="L213" s="5" t="n">
+        <v>0.9851</v>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:23:08</t>
+        </is>
+      </c>
+      <c r="N213" s="5" t="n">
+        <v>44.45</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>一定要有健保身分才能申請重大傷病理賠嗎？</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，被保險人若喪失全民健康保險被保險人資格，需先申請加保全民健康保險後，才能申領重大傷病保險金。然而，若重大傷病係因意外傷害事故所致，則不受此限制。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>第二十二條 重大傷病保險金、特定重大傷病保險金的申領 | 第十二條 重大傷病保險金的給付 | other_metadata | 第三十條 不保事項 | 第二條 名詞定義 | 附表一：全民健康保險重大傷病項目</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，被保險人若喪失全民健康保險被保險人資格，需先申請加保全民健康保險後，才能申領重大傷病保險金。然而，若重大傷病係因意外傷害事故所致，則不受此限制。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G214" s="2" t="inlineStr"/>
+      <c r="H214" s="2" t="inlineStr"/>
+      <c r="I214" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.001115, "neutral": 0.9981, "contradiction": 0.000785, "factuality": 0.999215, "C_fact": 0.999215}, "C_conf": 0.9992}</t>
+        </is>
+      </c>
+      <c r="J214" s="5" t="n"/>
+      <c r="K214" s="5" t="n">
+        <v>0.999215</v>
+      </c>
+      <c r="L214" s="5" t="n">
+        <v>0.9992</v>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:23:30</t>
+        </is>
+      </c>
+      <c r="N214" s="5" t="n">
+        <v>22.53</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>重大傷病的項目如果在投保後有新增，可以從優申請理賠嗎？</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以申請理賠，但需符合以下條件：重大傷病項目若在投保後新增，理賠範圍以「訂立時」及「有效期間內被保險人診斷確定當時」由中央衛生主管機關公告之重大傷病項目為準。因此，只要新增項目在被保險人診斷確定時已被中央衛生主管機關公告為重大傷病項目，即可申請理賠。
+條文依據：  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t>附表一：全民健康保險重大傷病項目 | 第二條 名詞定義 | payout_items</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F215" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以申請理賠，但需符合以下條件：重大傷病項目若在投保後新增，理賠範圍以「訂立時」及「有效期間內被保險人診斷確定當時」由中央衛生主管機關公告之重大傷病項目為準。因此，只要新增項目在被保險人診斷確定時已被中央衛生主管機關公告為重大傷病項目，即可申請理賠。
+條文依據：  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G215" s="2" t="inlineStr"/>
+      <c r="H215" s="2" t="inlineStr"/>
+      <c r="I215" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.992373, "neutral": 0.006742, "contradiction": 0.000885, "factuality": 0.999115, "C_fact": 0.999115}, "C_conf": 0.9991}</t>
+        </is>
+      </c>
+      <c r="J215" s="5" t="n"/>
+      <c r="K215" s="5" t="n">
+        <v>0.999115</v>
+      </c>
+      <c r="L215" s="5" t="n">
+        <v>0.9991</v>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:23:36</t>
+        </is>
+      </c>
+      <c r="N215" s="5" t="n">
+        <v>5.57</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>我的保單之前有停效，在復效後五天被診斷出重大疾病是否可申請理賠？</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以申請理賠，但需符合以下條件：  
+1. 復效後的契約有效期間內，被保險人經醫院醫師初次診斷確定罹患「重大傷病」，並取得符合規定的重大傷病證明文件。  
+2. 若重大傷病係因意外傷害事故所致，則不受等待期間限制；若非因意外傷害事故，則需等待期間屆滿翌日後方可申請理賠。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第八條 本契約效力的恢復]</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 重大傷病保險金的給付 | 第八條 本契約效力的恢復 | 第二條 名詞定義 | 第三十條 不保事項 | 第五條 保險範圍 | 第二十二條 重大傷病保險金、特定重大傷病保險金的申領 | other_metadata | 附表一：全民健康保險重大傷病項目</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F216" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以申請理賠，但需符合以下條件：  
+1. 復效後的契約有效期間內，被保險人經醫院醫師初次診斷確定罹患「重大傷病」，並取得符合規定的重大傷病證明文件。  
+2. 若重大傷病係因意外傷害事故所致，則不受等待期間限制；若非因意外傷害事故，則需等待期間屆滿翌日後方可申請理賠。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第八條 本契約效力的恢復]</t>
+        </is>
+      </c>
+      <c r="G216" s="2" t="inlineStr"/>
+      <c r="H216" s="2" t="inlineStr"/>
+      <c r="I216" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.956518, "neutral": 0.041583, "contradiction": 0.0019, "factuality": 0.9981, "C_fact": 0.9981}, "C_conf": 0.9981}</t>
+        </is>
+      </c>
+      <c r="J216" s="5" t="n"/>
+      <c r="K216" s="5" t="n">
+        <v>0.9981</v>
+      </c>
+      <c r="L216" s="5" t="n">
+        <v>0.9981</v>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:24:01</t>
+        </is>
+      </c>
+      <c r="N216" s="5" t="n">
+        <v>25.24</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>領完重大傷病保險金，主約終止後，附約可以繼續有效嗎?</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以。依據條文，若主約因重大傷病診斷確定而終止時，要保人於附約的有效期間內，仍可繼續繳交附約保險費，以延續附約效力。
+條文依據：  
+- [第十一條 契約的終止（二）]</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 契約的終止（二） | 第十二條 重大傷病保險金的給付 | 第三十條 不保事項 | 第五條 保險範圍 | payout_items | 附表一：全民健康保險重大傷病項目</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F217" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以。依據條文，若主約因重大傷病診斷確定而終止時，要保人於附約的有效期間內，仍可繼續繳交附約保險費，以延續附約效力。
+條文依據：  
+- [第十一條 契約的終止（二）]</t>
+        </is>
+      </c>
+      <c r="G217" s="2" t="inlineStr"/>
+      <c r="H217" s="2" t="inlineStr"/>
+      <c r="I217" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.986316, "neutral": 0.013525, "contradiction": 0.000159, "factuality": 0.999841, "C_fact": 0.999841}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J217" s="5" t="n"/>
+      <c r="K217" s="5" t="n">
+        <v>0.999841</v>
+      </c>
+      <c r="L217" s="5" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:24:13</t>
+        </is>
+      </c>
+      <c r="N217" s="5" t="n">
+        <v>11.46</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>Q1：因為慢性精神病的保險給付僅有保額的20%，我可以先不申請給付，等之後發生其他重大傷病後，再申請重大傷病保險金嗎?Q2：但如果我不申請，保險公司不會知道我有罹患慢性精神病阿，所以我就可以領之後的重大傷病100%保額嗎?</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+Q1：依據條款規定，若被保險人同時或先後罹患二項以上「重大傷病」，保險公司僅給付一項「重大傷病保險金」。因此，即使您選擇不申請慢性精神病的保險給付，之後罹患其他重大傷病時，保險公司仍僅會給付其中一項的保險金，並不會因未申請慢性精神病的保險金而影響給付比例。  
+Q2：條款未明確規定保險公司是否會因未申請慢性精神病保險金而不知情，但依據條款，若被保險人罹患慢性精神病且符合重大傷病範圍，保險公司有權依診斷書及病歷摘要審核是否符合給付條件。若之後罹患其他重大傷病，保險公司仍僅會依條款規定給付一項保險金，並不會因未申請慢性精神病保險金而給付100%保額。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 重大傷病保險金的給付 | 第十三條 特定重大傷病保險金的給付 | 附表一：全民健康保險重大傷病項目 | 第二十二條 重大傷病保險金、特定重大傷病保險金的申領 | 第三十條 不保事項 | 第二十八條 除外責任（一） | payout_items | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F218" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+Q1：依據條款規定，若被保險人同時或先後罹患二項以上「重大傷病」，保險公司僅給付一項「重大傷病保險金」。因此，即使您選擇不申請慢性精神病的保險給付，之後罹患其他重大傷病時，保險公司仍僅會給付其中一項的保險金，並不會因未申請慢性精神病的保險金而影響給付比例。  
+Q2：條款未明確規定保險公司是否會因未申請慢性精神病保險金而不知情，但依據條款，若被保險人罹患慢性精神病且符合重大傷病範圍，保險公司有權依診斷書及病歷摘要審核是否符合給付條件。若之後罹患其他重大傷病，保險公司仍僅會依條款規定給付一項保險金，並不會因未申請慢性精神病保險金而給付100%保額。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G218" s="2" t="inlineStr"/>
+      <c r="H218" s="2" t="inlineStr"/>
+      <c r="I218" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.982661, "neutral": 0.016538, "contradiction": 0.000801, "factuality": 0.999199, "C_fact": 0.999199}, "C_conf": 0.9992}</t>
+        </is>
+      </c>
+      <c r="J218" s="5" t="n"/>
+      <c r="K218" s="5" t="n">
+        <v>0.9991989999999999</v>
+      </c>
+      <c r="L218" s="5" t="n">
+        <v>0.9992</v>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:24:39</t>
+        </is>
+      </c>
+      <c r="N218" s="5" t="n">
+        <v>25.6</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>失智症會賠嗎？賠多少？</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+失智症是否理賠及賠償金額需視其是否符合「重大傷病」的範圍。根據條款，若失智症屬於附表一所載「重大傷病」範圍，且被保險人於等待期間屆滿翌日或復效日起的契約有效期間內，經醫院醫師初次診斷確定罹患，並取得符合規定的重大傷病證明或診斷書，則可申請「重大傷病保險金」。賠償金額依初次診斷確定罹患重大傷病時之保險單年度計算，分為以下情況：  
+1. 第一保險單年度：「年繳應繳保險費總額」的一點零五倍。  
+2. 第二保險單年度（含）以後：  
+   - 若屬附表一所載「六、慢性精神病」：「保險金額的百分之二十」或「年繳應繳保險費總額」的一點零五倍，二者取其大者。  
+   - 若屬其他「重大傷病範圍」項目：「保險金額」或「年繳應繳保險費總額」的一點零五倍，二者取其大者。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [附表一：全民健康保險重大傷病項目]</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
+        <is>
+          <t>第十七條 完全失能保險金的給付 | 第二十九條 除外責任（二） | payout_items | 第十二條 重大傷病保險金的給付 | 第三十條 不保事項 | 附表二：完全失能程度表 | 附表一：全民健康保險重大傷病項目</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F219" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+失智症是否理賠及賠償金額需視其是否符合「重大傷病」的範圍。根據條款，若失智症屬於附表一所載「重大傷病」範圍，且被保險人於等待期間屆滿翌日或復效日起的契約有效期間內，經醫院醫師初次診斷確定罹患，並取得符合規定的重大傷病證明或診斷書，則可申請「重大傷病保險金」。賠償金額依初次診斷確定罹患重大傷病時之保險單年度計算，分為以下情況：  
+1. 第一保險單年度：「年繳應繳保險費總額」的一點零五倍。  
+2. 第二保險單年度（含）以後：  
+   - 若屬附表一所載「六、慢性精神病」：「保險金額的百分之二十」或「年繳應繳保險費總額」的一點零五倍，二者取其大者。  
+   - 若屬其他「重大傷病範圍」項目：「保險金額」或「年繳應繳保險費總額」的一點零五倍，二者取其大者。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [附表一：全民健康保險重大傷病項目]</t>
+        </is>
+      </c>
+      <c r="G219" s="2" t="inlineStr"/>
+      <c r="H219" s="2" t="inlineStr"/>
+      <c r="I219" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.996819, "neutral": 0.00289, "contradiction": 0.00029, "factuality": 0.99971, "C_fact": 0.99971}, "C_conf": 0.9997}</t>
+        </is>
+      </c>
+      <c r="J219" s="5" t="n"/>
+      <c r="K219" s="5" t="n">
+        <v>0.99971</v>
+      </c>
+      <c r="L219" s="5" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:25:01</t>
+        </is>
+      </c>
+      <c r="N219" s="5" t="n">
+        <v>21.74</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>投保新鍾心滿福後，於第二保單年度罹患子宮頸惡性腫瘤，且已給付重大傷病保險金。第五保單年度時又罹患慢性腎衰竭，這樣還可以申領重大傷病保險金的給付嗎?</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不可以再次申領重大傷病保險金。根據條款規定，被保險人同時或先後罹患二項以上「重大傷病」時，本公司僅給付一項「重大傷病保險金」。因此，即使於第五保單年度罹患慢性腎衰竭，因已於第二保單年度因子宮頸惡性腫瘤申領過重大傷病保險金，無法再次申領。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 重大傷病保險金的給付 | 附表一：全民健康保險重大傷病項目 | 第二條 名詞定義 | 第二十二條 重大傷病保險金、特定重大傷病保險金的申領 | 第五條 保險範圍 | payout_items</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F220" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不可以再次申領重大傷病保險金。根據條款規定，被保險人同時或先後罹患二項以上「重大傷病」時，本公司僅給付一項「重大傷病保險金」。因此，即使於第五保單年度罹患慢性腎衰竭，因已於第二保單年度因子宮頸惡性腫瘤申領過重大傷病保險金，無法再次申領。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G220" s="2" t="inlineStr"/>
+      <c r="H220" s="2" t="inlineStr"/>
+      <c r="I220" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.960141, "neutral": 0.039248, "contradiction": 0.000611, "factuality": 0.999389, "C_fact": 0.999389}, "C_conf": 0.9994}</t>
+        </is>
+      </c>
+      <c r="J220" s="5" t="n"/>
+      <c r="K220" s="5" t="n">
+        <v>0.999389</v>
+      </c>
+      <c r="L220" s="5" t="n">
+        <v>0.9994</v>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:25:31</t>
+        </is>
+      </c>
+      <c r="N220" s="5" t="n">
+        <v>30.46</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>12歲的被保險人可以有健康促進保險費折減嗎？</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+12歲的被保險人無法享有健康促進保險費折減，因為第十九條明確規定，只有實際年齡達十八歲（含）以上的被保險人才符合使用指定程式並加入健康計劃以折減保險費的資格。
+條文依據：  
+- [第十九條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 健康促進保險費折減 | 第三十八條 投保年齡的計算及錯誤的處理 | 第三十四條 減額繳清保險 | 第二條 名詞定義 | 第十六條 所繳保險費加計利息的退還、身故保險金或喪葬費用保險金的給付 | 附表二：完全失能程度表</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F221" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+12歲的被保險人無法享有健康促進保險費折減，因為第十九條明確規定，只有實際年齡達十八歲（含）以上的被保險人才符合使用指定程式並加入健康計劃以折減保險費的資格。
+條文依據：  
+- [第十九條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="G221" s="2" t="inlineStr"/>
+      <c r="H221" s="2" t="inlineStr"/>
+      <c r="I221" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.939516, "neutral": 0.059363, "contradiction": 0.001121, "factuality": 0.998879, "C_fact": 0.998879}, "C_conf": 0.9989}</t>
+        </is>
+      </c>
+      <c r="J221" s="5" t="n"/>
+      <c r="K221" s="5" t="n">
+        <v>0.998879</v>
+      </c>
+      <c r="L221" s="5" t="n">
+        <v>0.9989</v>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:25:53</t>
+        </is>
+      </c>
+      <c r="N221" s="5" t="n">
+        <v>21.7</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>ZDN</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>被保險人於投保鍾心滿溢後的第10天就罹患慢性腎衰竭，請問可以申領重大傷病保險金嗎？</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不可以申領重大傷病保險金。根據條款規定，慢性腎衰竭屬於「重大傷病」範圍，但需符合等待期間的要求。等待期間為自契約生效日起持續有效三十日，慢性腎衰竭並非因意外傷害事故所致，因此在等待期間內罹患「重大傷病」者，契約自始無效，本公司僅退還已繳保險費且不給付保險金。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
+        <is>
+          <t>第二十二條 重大傷病保險金、特定重大傷病保險金的申領 | 第二條 名詞定義 | 第十二條 重大傷病保險金的給付 | 第三十條 不保事項 | 附表一：全民健康保險重大傷病項目</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不可以申領重大傷病保險金。根據條款規定，慢性腎衰竭屬於「重大傷病」範圍，但需符合等待期間的要求。等待期間為自契約生效日起持續有效三十日，慢性腎衰竭並非因意外傷害事故所致，因此在等待期間內罹患「重大傷病」者，契約自始無效，本公司僅退還已繳保險費且不給付保險金。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G222" s="2" t="inlineStr"/>
+      <c r="H222" s="2" t="inlineStr"/>
+      <c r="I222" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.00203, "neutral": 0.984574, "contradiction": 0.013397, "factuality": 0.986603, "C_fact": 0.986603}, "C_conf": 0.9866}</t>
+        </is>
+      </c>
+      <c r="J222" s="5" t="n"/>
+      <c r="K222" s="5" t="n">
+        <v>0.986603</v>
+      </c>
+      <c r="L222" s="5" t="n">
+        <v>0.9866</v>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:26:27</t>
+        </is>
+      </c>
+      <c r="N222" s="5" t="n">
+        <v>33.62</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>CFE</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>投保自由配重大傷病後，若在契約生效後80天罹患第一期乳癌，會拿到理賠金嗎?</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不會拿到理賠金。根據條款，第一期乳癌屬於「需積極或長期治療之癌症」範圍，其等待期間為契約生效日起90天。若被保險人在等待期間內罹患重大傷病，契約自始無效，保險公司僅退還已繳保險費且不支付理賠金。
+條文依據：  
+- [第二條 名詞定義]  
+- [第十一條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
+        <is>
+          <t>第二條 名詞定義 | 附表一：全民健康保險重大傷病項目 | 第十一條 重大傷病保險金的給付 | 第十五條 不保事項 | 第十四條 除外責任 | other_metadata | 第五條 契約有效期間及保證續保</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F223" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不會拿到理賠金。根據條款，第一期乳癌屬於「需積極或長期治療之癌症」範圍，其等待期間為契約生效日起90天。若被保險人在等待期間內罹患重大傷病，契約自始無效，保險公司僅退還已繳保險費且不支付理賠金。
+條文依據：  
+- [第二條 名詞定義]  
+- [第十一條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G223" s="2" t="inlineStr"/>
+      <c r="H223" s="2" t="inlineStr"/>
+      <c r="I223" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.003285, "neutral": 0.99561, "contradiction": 0.001105, "factuality": 0.998895, "C_fact": 0.998895}, "C_conf": 0.9989}</t>
+        </is>
+      </c>
+      <c r="J223" s="5" t="n"/>
+      <c r="K223" s="5" t="n">
+        <v>0.998895</v>
+      </c>
+      <c r="L223" s="5" t="n">
+        <v>0.9989</v>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:27:06</t>
+        </is>
+      </c>
+      <c r="N223" s="5" t="n">
+        <v>39.03</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>CFE</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>要保人想要終止國泰人壽自由配CFE契約，能否退保費?</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+要保人可以終止契約，並退還未到期保險費。本公司會從已繳保險費中扣除按短期費率計算的已經過期間保險費後，將未到期保險費無息退還給要保人。
+條文依據：  
+- [第九條 契約的終止（一）]</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t>第九條 契約的終止（一） | 第十五條 不保事項 | 第五條 契約有效期間及保證續保 | 第七條 本契約效力的恢復 | 第六條 續保保險費的交付、寬限期間及契約效力的停止 | 附表二：短期費率表</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F224" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+要保人可以終止契約，並退還未到期保險費。本公司會從已繳保險費中扣除按短期費率計算的已經過期間保險費後，將未到期保險費無息退還給要保人。
+條文依據：  
+- [第九條 契約的終止（一）]</t>
+        </is>
+      </c>
+      <c r="G224" s="2" t="inlineStr"/>
+      <c r="H224" s="2" t="inlineStr"/>
+      <c r="I224" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.997835, "neutral": 0.002071, "contradiction": 9.4e-05, "factuality": 0.999906, "C_fact": 0.999906}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J224" s="5" t="n"/>
+      <c r="K224" s="5" t="n">
+        <v>0.999906</v>
+      </c>
+      <c r="L224" s="5" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:27:27</t>
+        </is>
+      </c>
+      <c r="N224" s="5" t="n">
+        <v>20.74</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>CFE</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>投保國泰人壽自由配CFE，若在等待期間內罹患重大傷病，要如何給付?</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在等待期間內罹患重大傷病，且該重大傷病非因意外傷害事故所致，則本契約自始無效，本公司僅無息退還已繳保險費予要保人。若重大傷病係因意外傷害事故所致，則不受等待期間限制，可依約給付重大傷病保險金。
+條文依據：  
+- [第十一條 重大傷病保險金的給付]  
+- [第十五條 不保事項]</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 重大傷病保險金的給付 | 第十五條 不保事項 | 第十四條 除外責任 | payout_items | 附表一：全民健康保險重大傷病項目 | other_metadata</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F225" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在等待期間內罹患重大傷病，且該重大傷病非因意外傷害事故所致，則本契約自始無效，本公司僅無息退還已繳保險費予要保人。若重大傷病係因意外傷害事故所致，則不受等待期間限制，可依約給付重大傷病保險金。
+條文依據：  
+- [第十一條 重大傷病保險金的給付]  
+- [第十五條 不保事項]</t>
+        </is>
+      </c>
+      <c r="G225" s="2" t="inlineStr"/>
+      <c r="H225" s="2" t="inlineStr"/>
+      <c r="I225" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.945941, "neutral": 0.031935, "contradiction": 0.022124, "factuality": 0.977876, "C_fact": 0.977876}, "C_conf": 0.9779}</t>
+        </is>
+      </c>
+      <c r="J225" s="5" t="n"/>
+      <c r="K225" s="5" t="n">
+        <v>0.977876</v>
+      </c>
+      <c r="L225" s="5" t="n">
+        <v>0.9779</v>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:27:56</t>
+        </is>
+      </c>
+      <c r="N225" s="5" t="n">
+        <v>28.48</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>CFE</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>投保自由配一年定期初次罹患重大傷病健康保險後，於第三年罹患先天性肌肉萎縮症，可以申領重大傷病保險金嗎？</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不可以申領重大傷病保險金。根據附表一，「先天性肌肉萎縮症」不屬於重大傷病範圍，且該項目已明確標示為「否」，表示不符合重大傷病保險金的給付條件。
+條文依據：  
+- [附表一：全民健康保險重大傷病項目]</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 重大傷病保險金的給付 | 第十三條 重大傷病保險金的申領 | 附表一：全民健康保險重大傷病項目 | 第十五條 不保事項</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F226" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不可以申領重大傷病保險金。根據條款，被保險人罹患「先天性肌肉萎縮症」不屬於重大傷病範圍，且附表一已明確標示該項目為「否」，表示不符合重大傷病保險金的給付條件。
+條文依據：  
+- [附表一：全民健康保險重大傷病項目]</t>
+        </is>
+      </c>
+      <c r="G226" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不可以申領重大傷病保險金。根據附表一，「先天性肌肉萎縮症」不屬於重大傷病範圍，且該項目已明確標示為「否」，表示不符合重大傷病保險金的給付條件。
+條文依據：  
+- [附表一：全民健康保險重大傷病項目]</t>
+        </is>
+      </c>
+      <c r="H226" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不可以申領重大傷病保險金。根據附表一，「先天性肌肉萎縮症」不屬於重大傷病範圍，且該項目已明確標示為「否」，表示不符合重大傷病保險金的給付條件。
+條文依據：  
+- [附表一：全民健康保險重大傷病項目]</t>
+        </is>
+      </c>
+      <c r="I226" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.104573, "neutral": 0.031146, "contradiction": 0.864281, "factuality": 0.135719, "C_fact": 0.135719}, "C_conf": 0.1357}</t>
+        </is>
+      </c>
+      <c r="J226" s="5" t="n"/>
+      <c r="K226" s="7" t="n">
+        <v>0.135719</v>
+      </c>
+      <c r="L226" s="7" t="n">
+        <v>0.1357</v>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:28:54</t>
+        </is>
+      </c>
+      <c r="N226" s="5" t="n">
+        <v>58.29</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>CFG</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>自由配重大疾病(甲型)保障的重大疾病有哪些疾病?</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+自由配重大疾病(甲型)保障的重大疾病包括以下疾病：  
+1. 腦中風後障礙(重度)  
+2. 癱瘓(重度)  
+3. 癌症(重度)  
+4. 急性心肌梗塞(重度)  
+5. 冠狀動脈繞道手術  
+6. 末期腎病變  
+7. 重大器官移植或造血幹細胞移植  
+條文依據：  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
+        <is>
+          <t>國泰人壽自由配一年定期初次罹患重大疾病健康保險(甲型)年繳費率表 | payout_items | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F227" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+自由配重大疾病(甲型)保障的重大疾病包括以下疾病：  
+1. 腦中風後障礙(重度)  
+2. 癱瘓(重度)  
+3. 癌症(重度)  
+4. 急性心肌梗塞(重度)  
+5. 冠狀動脈繞道手術  
+6. 末期腎病變  
+7. 重大器官移植或造血幹細胞移植  
+條文依據：  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G227" s="2" t="inlineStr"/>
+      <c r="H227" s="2" t="inlineStr"/>
+      <c r="I227" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.435646, "neutral": 0.534641, "contradiction": 0.029713, "factuality": 0.970287, "C_fact": 0.970287}, "C_conf": 0.9703}</t>
+        </is>
+      </c>
+      <c r="J227" s="5" t="n"/>
+      <c r="K227" s="5" t="n">
+        <v>0.970287</v>
+      </c>
+      <c r="L227" s="5" t="n">
+        <v>0.9703000000000001</v>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:29:16</t>
+        </is>
+      </c>
+      <c r="N227" s="5" t="n">
+        <v>21.36</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>被保險人領了2次癌症(重度)追蹤照護金後身故，是否還有尚未給付的保險金供受益人領取?</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人已領取2次「癌症(重度)追蹤照護保險金」後身故，則不再有尚未給付的「癌症(重度)追蹤照護保險金」可供受益人申領，因該保險金的給付最長以五年為限，且需被保險人於各保險單週年日仍生存才能申領。此外，條文未提及其他相關保險金可因身故而補充給付。  
+條文依據：  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用) | 第二十三條 癌症保險金或罹癌基因檢測服務的申領 | 第十三條 初次罹患癌症(重度)保險金的給付 | 第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用) | 第二十二條 保險事故的通知與保險給付的申請時間 | 第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付 | 第十六條 癌症(重度)豁免保險費(第二保險單年度起適用) | payout_items</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F228" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人已領取2次「癌症(重度)追蹤照護保險金」後身故，則不再有尚未給付的「癌症(重度)追蹤照護保險金」可供受益人申領，因該保險金的給付最長以五年為限，且需被保險人於各保險單週年日仍生存才能申領。此外，條文未提及其他相關保險金可因身故而補充給付。  
+條文依據：  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]</t>
+        </is>
+      </c>
+      <c r="G228" s="2" t="inlineStr"/>
+      <c r="H228" s="2" t="inlineStr"/>
+      <c r="I228" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.069178, "neutral": 0.903651, "contradiction": 0.027171, "factuality": 0.972829, "C_fact": 0.972829}, "C_conf": 0.9728}</t>
+        </is>
+      </c>
+      <c r="J228" s="5" t="n"/>
+      <c r="K228" s="5" t="n">
+        <v>0.9728290000000001</v>
+      </c>
+      <c r="L228" s="5" t="n">
+        <v>0.9728</v>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:29:44</t>
+        </is>
+      </c>
+      <c r="N228" s="5" t="n">
+        <v>27.95</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>保險金額2萬元，「罹癌基因檢測服務」費用8萬元，還會給付多少「癌症(重度)追蹤照護保險金」？</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人選擇申領「罹癌基因檢測服務」，因服務費用（8萬元）高於「罹癌基因檢測服務額度」（1,000元），則僅能申領「癌症(重度)追蹤照護保險金」。依條款規定，「癌症(重度)追蹤照護保險金」的給付金額為保險金額的12倍，即2萬元 × 12 = 24萬元。  
+條文依據：  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用) | 第二十三條 癌症保險金或罹癌基因檢測服務的申領 | 附件一：罹癌基因檢測服務之項目、服務費用及補償金額表 | 第十三條 初次罹患癌症(重度)保險金的給付 | 第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用) | 第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付 | other_metadata | payout_items</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F229" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人選擇申領「罹癌基因檢測服務」，因服務費用（8萬元）高於「罹癌基因檢測服務額度」（1,000元），則僅能申領「癌症(重度)追蹤照護保險金」。依條款規定，「癌症(重度)追蹤照護保險金」的給付金額為保險金額的12倍，即2萬元 × 12 = 24萬元。  
+條文依據：  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]</t>
+        </is>
+      </c>
+      <c r="G229" s="2" t="inlineStr"/>
+      <c r="H229" s="2" t="inlineStr"/>
+      <c r="I229" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.646965, "neutral": 0.228045, "contradiction": 0.12499, "factuality": 0.87501, "C_fact": 0.87501}, "C_conf": 0.875}</t>
+        </is>
+      </c>
+      <c r="J229" s="5" t="n"/>
+      <c r="K229" s="5" t="n">
+        <v>0.87501</v>
+      </c>
+      <c r="L229" s="5" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:30:40</t>
+        </is>
+      </c>
+      <c r="N229" s="5" t="n">
+        <v>55.56</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>投保後1個月罹患重度癌症，會給付哪些保險金？契約還會持續有效嗎？</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在投保後1個月罹患重度癌症，因診斷確定日屬於第一保險單年度內，符合「初次診斷確定罹患癌症(重度)」的條件，本公司將給付「初次罹患癌症(重度)保險金」，金額為「年繳應繳保險費」的一點零六倍。契約仍會持續有效，但當期已繳付之未到期保險費不予退還。  
+條文依據：  
+- [第十三條 初次罹患癌症(重度)保險金的給付]  
+- [第十六條 癌症(重度)豁免保險費(第二保險單年度起適用)]</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 癌症(重度)豁免保險費(第二保險單年度起適用) | 第十三條 初次罹患癌症(重度)保險金的給付 | 第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用) | 第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付 | 第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用)</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F230" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在投保後1個月罹患重度癌症，因診斷確定日屬於第一保險單年度內，符合「初次診斷確定罹患癌症(重度)」的條件，本公司將給付「初次罹患癌症(重度)保險金」，金額為「年繳應繳保險費」的一點零六倍。契約仍會持續有效，但當期已繳付之未到期保險費不予退還。  
+條文依據：  
+- [第十三條 初次罹患癌症(重度)保險金的給付]  
+- [第十六條 癌症(重度)豁免保險費(第二保險單年度起適用)]</t>
+        </is>
+      </c>
+      <c r="G230" s="2" t="inlineStr"/>
+      <c r="H230" s="2" t="inlineStr"/>
+      <c r="I230" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.996249, "neutral": 0.003286, "contradiction": 0.000465, "factuality": 0.999535, "C_fact": 0.999535}, "C_conf": 0.9995}</t>
+        </is>
+      </c>
+      <c r="J230" s="5" t="n"/>
+      <c r="K230" s="5" t="n">
+        <v>0.999535</v>
+      </c>
+      <c r="L230" s="5" t="n">
+        <v>0.9995000000000001</v>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:31:10</t>
+        </is>
+      </c>
+      <c r="N230" s="5" t="n">
+        <v>27.26</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>投保後10個月罹患重度癌症，會給付哪些保險金？契約還會持續有效嗎？</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人於投保後10個月（即第二保險單年度內）診斷確定罹患重度癌症，符合「初次診斷確定罹患癌症(重度)」的條件，本公司將給付「初次罹患癌症(重度)保險金」，金額為「保險金額」的十二倍。此外，契約仍會持續有效，並且自診斷確定日起豁免續期保險費，但當期已繳付之未到期保險費不予退還。  
+條文依據：  
+- [第十三條 初次罹患癌症(重度)保險金的給付]  
+- [第十六條 癌症(重度)豁免保險費(第二保險單年度起適用)]</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 癌症(重度)豁免保險費(第二保險單年度起適用) | 第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用) | 第十條 契約的終止（二） | 第十三條 初次罹患癌症(重度)保險金的給付 | 第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F231" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人於投保後10個月（即第二保險單年度內）診斷確定罹患重度癌症，符合「初次診斷確定罹患癌症(重度)」的條件，本公司將給付「初次罹患癌症(重度)保險金」，金額為「保險金額」的十二倍。此外，契約仍會持續有效，並且自診斷確定日起豁免續期保險費，但當期已繳付之未到期保險費不予退還。  
+條文依據：  
+- [第十三條 初次罹患癌症(重度)保險金的給付]  
+- [第十六條 癌症(重度)豁免保險費(第二保險單年度起適用)]</t>
+        </is>
+      </c>
+      <c r="G231" s="2" t="inlineStr"/>
+      <c r="H231" s="2" t="inlineStr"/>
+      <c r="I231" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.996463, "neutral": 0.003388, "contradiction": 0.000149, "factuality": 0.999851, "C_fact": 0.999851}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J231" s="5" t="n"/>
+      <c r="K231" s="5" t="n">
+        <v>0.999851</v>
+      </c>
+      <c r="L231" s="5" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:31:21</t>
+        </is>
+      </c>
+      <c r="N231" s="5" t="n">
+        <v>10.98</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>投保醫心康愛，罹患肺癌一期，可領什麼保險金？</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+罹患肺癌一期屬於「癌症(初期)或癌症(輕度)」，可申領「初次罹患癌症(初期)或癌症(輕度)保險金」。若診斷確定日是在第一保險單年度內，可領「年繳應繳保險費」的一點零六倍；若診斷確定日是在第二保險單年度(含)以後，可領「保險金額」的五倍。此保險金最多給付一次。
+條文依據：  
+- [第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付 | 第十三條 初次罹患癌症(重度)保險金的給付 | payout_items | 第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用) | 第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F232" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+罹患肺癌一期屬於「癌症(初期)或癌症(輕度)」，可申領「初次罹患癌症(初期)或癌症(輕度)保險金」。若診斷確定日是在第一保險單年度內，可領「年繳應繳保險費」的一點零六倍；若診斷確定日是在第二保險單年度(含)以後，可領「保險金額」的五倍。此保險金最多給付一次。
+條文依據：  
+- [第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G232" s="2" t="inlineStr"/>
+      <c r="H232" s="2" t="inlineStr"/>
+      <c r="I232" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.896883, "neutral": 0.102936, "contradiction": 0.000181, "factuality": 0.999819, "C_fact": 0.999819}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J232" s="5" t="n"/>
+      <c r="K232" s="5" t="n">
+        <v>0.999819</v>
+      </c>
+      <c r="L232" s="5" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:31:28</t>
+        </is>
+      </c>
+      <c r="N232" s="5" t="n">
+        <v>6.31</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>PX5</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>若被保險人身故有何給付?</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人身故，保險金的受益人為被保險人的法定繼承人，並依民法繼承編的相關規定分配受益順序及比例。若本附約保險金尚未給付或未完全給付，則由法定繼承人申領該部分保險金。
+條文依據：  
+- [第二十條 受益人]</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="inlineStr">
+        <is>
+          <t>第二十條 受益人 | 第十二條 重大疾病保險金的給付 | 第十一條 輕度重大疾病保險金的給付 | 第十四條 保險事故的通知與保險金的申請時間 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F233" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人身故，保險金的受益人為被保險人的法定繼承人，並依民法繼承編的相關規定分配受益順序及比例。若本附約保險金尚未給付或未完全給付，則由法定繼承人申領該部分保險金。
+條文依據：  
+- [第二十條 受益人]</t>
+        </is>
+      </c>
+      <c r="G233" s="2" t="inlineStr"/>
+      <c r="H233" s="2" t="inlineStr"/>
+      <c r="I233" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.99676, "neutral": 0.002597, "contradiction": 0.000642, "factuality": 0.999358, "C_fact": 0.999358}, "C_conf": 0.9994}</t>
+        </is>
+      </c>
+      <c r="J233" s="5" t="n"/>
+      <c r="K233" s="5" t="n">
+        <v>0.999358</v>
+      </c>
+      <c r="L233" s="5" t="n">
+        <v>0.9994</v>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:31:31</t>
+        </is>
+      </c>
+      <c r="N233" s="5" t="n">
+        <v>3.11</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>PX5</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>投保鍾溢祝福後，請問在第二年經醫院醫師初次診斷罹患「輕度重大疾病」中的癌症(輕度)者，可以領到輕度重大疾病保險金嗎?可以領到保險金額的百分之多少?</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以領到輕度重大疾病保險金，保險金額的百分之二十。根據條款，被保險人在續保年度內初次診斷罹患「輕度重大疾病」中的癌症(輕度)，符合給付條件。
+條文依據：  
+- [第十一條 輕度重大疾病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 輕度重大疾病保險金的給付 | 第十二條 重大疾病保險金的給付 | payout_items | other_metadata | 第二條 名詞定義 | 國泰人壽鍾溢祝福重大疾病健康保險附約(乙型) (外溢型)年繳費率表</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F234" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以領到輕度重大疾病保險金，保險金額的百分之二十。根據條款，被保險人在續保年度內初次診斷罹患「輕度重大疾病」中的癌症(輕度)，符合給付條件。
+條文依據：  
+- [第十一條 輕度重大疾病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G234" s="2" t="inlineStr"/>
+      <c r="H234" s="2" t="inlineStr"/>
+      <c r="I234" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.98913, "neutral": 0.010751, "contradiction": 0.000119, "factuality": 0.999881, "C_fact": 0.999881}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J234" s="5" t="n"/>
+      <c r="K234" s="5" t="n">
+        <v>0.999881</v>
+      </c>
+      <c r="L234" s="5" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:32:04</t>
+        </is>
+      </c>
+      <c r="N234" s="5" t="n">
+        <v>32.39</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>PX5</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>請問如果在投保後的第三年經醫院醫師初次診斷罹患「重大疾病」者，可以領到重大疾病保險金嗎?可以領到保險金額的百分之多少?那後續又在第四年經醫院醫師初次診斷罹患「輕度重大疾病」者，可以領到輕度重大疾病保險金嗎?可以領到保險金額的百分之多少?</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+在投保後的第三年初次診斷罹患「重大疾病」者，可以領到重大疾病保險金，給付比例為保險金額的1.3倍。  
+在第四年初次診斷罹患「輕度重大疾病」者，可以領到輕度重大疾病保險金，給付比例為保險金額的20%。  
+條文依據：  
+- [第十二條 重大疾病保險金的給付]  
+- [第十一條 輕度重大疾病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 重大疾病保險金的給付 | 第十一條 輕度重大疾病保險金的給付 | payout_items | 第十六條 除外責任 | 第二條 名詞定義 | 第四條 保險範圍 | other_metadata | 國泰人壽鍾溢祝福重大疾病健康保險附約(乙型) (外溢型)年繳費率表</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F235" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+在投保後的第三年初次診斷罹患「重大疾病」者，可以領到重大疾病保險金，給付比例為保險金額的1.3倍。  
+在第四年初次診斷罹患「輕度重大疾病」者，可以領到輕度重大疾病保險金，給付比例為保險金額的20%。  
+條文依據：  
+- [第十二條 重大疾病保險金的給付]  
+- [第十一條 輕度重大疾病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G235" s="2" t="inlineStr"/>
+      <c r="H235" s="2" t="inlineStr"/>
+      <c r="I235" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.584049, "neutral": 0.385322, "contradiction": 0.030629, "factuality": 0.969371, "C_fact": 0.969371}, "C_conf": 0.9694}</t>
+        </is>
+      </c>
+      <c r="J235" s="5" t="n"/>
+      <c r="K235" s="5" t="n">
+        <v>0.969371</v>
+      </c>
+      <c r="L235" s="5" t="n">
+        <v>0.9694</v>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:32:45</t>
+        </is>
+      </c>
+      <c r="N235" s="5" t="n">
+        <v>40.96</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>PX5</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>請問如果在投保後的第三年經醫院醫師初次診斷罹患「輕度重大疾病」者，可以領到重大疾病保險金嗎?可以領到保險金額的百分之多少?那後續又在第四年經醫院醫師初次診斷罹患「重大疾病」者，可以領到輕度重大疾病保險金嗎?可以領到保險金額的百分之多少?</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+在投保後的第三年初次診斷罹患「輕度重大疾病」者，可以領到「輕度重大疾病保險金」，給付比例為保險金額的百分之二十。  
+後續在第四年初次診斷罹患「重大疾病」者，因已申領過「輕度重大疾病保險金」，可領到「重大疾病保險金」，但需扣除已領取的「輕度重大疾病保險金」，給付比例為保險金額的一點三倍。
+條文依據：  
+- [第十一條 輕度重大疾病保險金的給付]  
+- [第十二條 重大疾病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 重大疾病保險金的給付 | 第十一條 輕度重大疾病保險金的給付 | payout_items | 第十六條 除外責任 | 第二條 名詞定義 | 第四條 保險範圍 | other_metadata | 第十五條 各項保險金的申領</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F236" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+在投保後的第三年初次診斷罹患「輕度重大疾病」者，可以領到「輕度重大疾病保險金」，給付比例為保險金額的百分之二十。  
+後續在第四年初次診斷罹患「重大疾病」者，因已申領過「輕度重大疾病保險金」，可領到「重大疾病保險金」，但需扣除已領取的「輕度重大疾病保險金」，給付比例為保險金額的一點三倍。
+條文依據：  
+- [第十一條 輕度重大疾病保險金的給付]  
+- [第十二條 重大疾病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G236" s="2" t="inlineStr"/>
+      <c r="H236" s="2" t="inlineStr"/>
+      <c r="I236" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.913698, "neutral": 0.052866, "contradiction": 0.033436, "factuality": 0.966564, "C_fact": 0.966564}, "C_conf": 0.9666}</t>
+        </is>
+      </c>
+      <c r="J236" s="5" t="n"/>
+      <c r="K236" s="5" t="n">
+        <v>0.966564</v>
+      </c>
+      <c r="L236" s="5" t="n">
+        <v>0.9666</v>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:33:25</t>
+        </is>
+      </c>
+      <c r="N236" s="5" t="n">
+        <v>39.64</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>PX5</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>請問主約效力終止(因身故以外情形)，PX5還能持續有效嗎？</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+主約效力因身故以外情形終止時，PX5附約效力可持續至附約當期已繳保險費期滿即行終止，並不再延續。  
+條文依據：  
+- [第十條 附約的終止（二）]</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
+        <is>
+          <t>第十條 附約的終止（二） | 第七條 保險費的墊繳、附約的停效及復效 | 第五條 附約的保險期間及保證續保 | 第十三條 健康促進保險費折減 | 第九條 附約的終止（一）</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F237" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+主約效力因身故以外情形終止時，PX5附約效力可持續至附約當期已繳保險費期滿即行終止，並不再延續。  
+條文依據：  
+- [第十條 附約的終止（二）]</t>
+        </is>
+      </c>
+      <c r="G237" s="2" t="inlineStr"/>
+      <c r="H237" s="2" t="inlineStr"/>
+      <c r="I237" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.792572, "neutral": 0.011362, "contradiction": 0.196066, "factuality": 0.803934, "C_fact": 0.803934}, "C_conf": 0.8039}</t>
+        </is>
+      </c>
+      <c r="J237" s="5" t="n"/>
+      <c r="K237" s="5" t="n">
+        <v>0.803934</v>
+      </c>
+      <c r="L237" s="5" t="n">
+        <v>0.8038999999999999</v>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:33:49</t>
+        </is>
+      </c>
+      <c r="N237" s="5" t="n">
+        <v>23.44</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>請問如果於「無理賠紀錄期間」屆滿日以內罹患特定傷病，會給付多少錢?這筆錢會給付給誰?</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人於「無理賠紀錄期間」屆滿日以內罹患特定傷病，保險公司將給付「保險金額」加上「年繳應繳保險費總額」乘以1.02的金額作為「特定傷病保險金」。這筆保險金的受益人為被保險人本人，保險公司不受理其指定及變更。
+條文依據：  
+- [第十一條 特定傷病保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第十二條 無理賠關懷保險金的給付 | 第十一條 特定傷病保險金的給付 | payout_items | 第二十七條 受益人的指定及變更</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F238" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人於「無理賠紀錄期間」屆滿日以內罹患特定傷病，保險公司將給付「保險金額」加上「年繳應繳保險費總額」乘以1.02的金額作為「特定傷病保險金」。這筆保險金的受益人為被保險人本人，保險公司不受理其指定及變更。
+條文依據：  
+- [第十一條 特定傷病保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="G238" s="2" t="inlineStr"/>
+      <c r="H238" s="2" t="inlineStr"/>
+      <c r="I238" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.996837, "neutral": 0.00284, "contradiction": 0.000322, "factuality": 0.999678, "C_fact": 0.999678}, "C_conf": 0.9997}</t>
+        </is>
+      </c>
+      <c r="J238" s="5" t="n"/>
+      <c r="K238" s="5" t="n">
+        <v>0.999678</v>
+      </c>
+      <c r="L238" s="5" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:33:58</t>
+        </is>
+      </c>
+      <c r="N238" s="5" t="n">
+        <v>8.85</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>請問如果要保人與被保險人為同一人，被保險人於「無理賠紀錄期間」屆滿日以內身故，會給付多少錢?這筆錢會給付給誰?</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若要保人與被保險人為同一人，被保險人於「無理賠紀錄期間」屆滿日以內身故，符合第十二條的條件，本公司將給付「無理賠關懷保險金」，金額為「年繳應繳保險費總額」乘以1.02。根據第二十七條，無理賠關懷保險金的受益人為要保人本人。由於要保人與被保險人為同一人，若被保險人已身故，則該保險金的受益人為被保險人的法定繼承人。
+條文依據：  
+- [第十二條 無理賠關懷保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 無理賠關懷保險金的給付 | 第五條 保險範圍 | 第十一條 特定傷病保險金的給付 | 第十九條 失蹤處理 | 第二十七條 受益人的指定及變更 | 第十七條 除外責任（二） | 第二十一條 無理賠關懷保險金的申領 | payout_items</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F239" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若要保人與被保險人為同一人，被保險人於「無理賠紀錄期間」屆滿日以內身故，符合第十二條的條件，本公司將給付「無理賠關懷保險金」，金額為「年繳應繳保險費總額」乘以1.02。根據第二十七條，無理賠關懷保險金的受益人為要保人本人。由於要保人與被保險人為同一人，若被保險人已身故，則該保險金的受益人為被保險人的法定繼承人。
+條文依據：  
+- [第十二條 無理賠關懷保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="G239" s="2" t="inlineStr"/>
+      <c r="H239" s="2" t="inlineStr"/>
+      <c r="I239" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.996213, "neutral": 0.003491, "contradiction": 0.000295, "factuality": 0.999705, "C_fact": 0.999705}, "C_conf": 0.9997}</t>
+        </is>
+      </c>
+      <c r="J239" s="5" t="n"/>
+      <c r="K239" s="5" t="n">
+        <v>0.999705</v>
+      </c>
+      <c r="L239" s="5" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:34:26</t>
+        </is>
+      </c>
+      <c r="N239" s="5" t="n">
+        <v>28.19</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>請問如果要保人與被保險人為不同人，被保險人於「無理賠紀錄期間」屆滿日以內生存，且被保險人未罹患特定傷病，會給付多少錢?這筆錢會給付給誰?</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人於「無理賠紀錄期間」屆滿日以內生存，且未罹患特定傷病，本公司將按「年繳應繳保險費總額」乘以1.02，給付「無理賠關懷保險金」。此筆保險金的受益人為要保人本人。本公司不受理受益人指定及變更。
+條文依據：  
+- [第十二條 無理賠關懷保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 無理賠關懷保險金的給付 | 第十一條 特定傷病保險金的給付 | 第五條 保險範圍 | 第二十七條 受益人的指定及變更 | 第十九條 失蹤處理 | payout_items | 第十七條 除外責任（二） | 第二十一條 無理賠關懷保險金的申領</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F240" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人於「無理賠紀錄期間」屆滿日以內生存，且未罹患特定傷病，本公司將按「年繳應繳保險費總額」乘以1.02，給付「無理賠關懷保險金」。此筆保險金的受益人為要保人本人。本公司不受理受益人指定及變更。
+條文依據：  
+- [第十二條 無理賠關懷保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="G240" s="2" t="inlineStr"/>
+      <c r="H240" s="2" t="inlineStr"/>
+      <c r="I240" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.997076, "neutral": 0.002684, "contradiction": 0.00024, "factuality": 0.99976, "C_fact": 0.99976}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J240" s="5" t="n"/>
+      <c r="K240" s="5" t="n">
+        <v>0.99976</v>
+      </c>
+      <c r="L240" s="5" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:35:02</t>
+        </is>
+      </c>
+      <c r="N240" s="5" t="n">
+        <v>35.47</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>保戶如果身故，會給保險金嗎?</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保戶身故時，若符合保險契約約定的條件，本公司會依相關條款給付保險金。例如：若被保險人在「無理賠紀錄期間」內身故，或因法院宣告死亡，則可依約給付保險金。此外，若受益人在分期定期保險金給付期間內死亡，尚未領取的保險金也會一次貼現給付予法定繼承人。
+條文依據：  
+- [第五條 保險範圍]  
+- [第二十八條 本契約受益人死亡或失蹤的處理]  
+- [第十九條 失蹤處理]</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第二十八條 本契約受益人死亡或失蹤的處理 | 第十七條 除外責任（二） | 第二十三條 受益人受益權之喪失 | 第十九條 失蹤處理</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F241" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保戶身故時，若符合保險契約約定的條件，本公司會依相關條款給付保險金。例如：若被保險人在「無理賠紀錄期間」內身故，或因法院宣告死亡，則可依約給付保險金。此外，若受益人在分期定期保險金給付期間內死亡，尚未領取的保險金也會一次貼現給付予法定繼承人。
+條文依據：  
+- [第五條 保險範圍]  
+- [第二十八條 本契約受益人死亡或失蹤的處理]  
+- [第十九條 失蹤處理]</t>
+        </is>
+      </c>
+      <c r="G241" s="2" t="inlineStr"/>
+      <c r="H241" s="2" t="inlineStr"/>
+      <c r="I241" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.995086, "neutral": 0.004429, "contradiction": 0.000485, "factuality": 0.999515, "C_fact": 0.999515}, "C_conf": 0.9995}</t>
+        </is>
+      </c>
+      <c r="J241" s="5" t="n"/>
+      <c r="K241" s="5" t="n">
+        <v>0.999515</v>
+      </c>
+      <c r="L241" s="5" t="n">
+        <v>0.9995000000000001</v>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:35:31</t>
+        </is>
+      </c>
+      <c r="N241" s="5" t="n">
+        <v>29.49</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>保戶如果身故，身故申領的保險金會給誰?</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保戶身故後，若有尚未給付或未完全給付的保險金，則該部分保險金的受益人為保戶的法定繼承人。若契約受益人為法定繼承人，其受益順序及應得比例適用民法繼承編相關規定。
+條文依據：  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第二十三條 受益人受益權之喪失 | 第二十七條 受益人的指定及變更 | 第二十八條 本契約受益人死亡或失蹤的處理 | 第二十二條 分期定期保險金給付申領文件、給付期限及未依限給付之效果</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F242" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保戶身故後，若有尚未給付或未完全給付的保險金，則該部分保險金的受益人為保戶的法定繼承人。若契約受益人為法定繼承人，其受益順序及應得比例適用民法繼承編相關規定。
+條文依據：  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="G242" s="2" t="inlineStr"/>
+      <c r="H242" s="2" t="inlineStr"/>
+      <c r="I242" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.993794, "neutral": 0.00568, "contradiction": 0.000525, "factuality": 0.999475, "C_fact": 0.999475}, "C_conf": 0.9995}</t>
+        </is>
+      </c>
+      <c r="J242" s="5" t="n"/>
+      <c r="K242" s="5" t="n">
+        <v>0.999475</v>
+      </c>
+      <c r="L242" s="5" t="n">
+        <v>0.9995000000000001</v>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:35:38</t>
+        </is>
+      </c>
+      <c r="N242" s="5" t="n">
+        <v>6.51</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>如果保戶投保繳費年期20年的滿溢寶，然後在第20保單年度身故的話，可以領到多少錢?</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若保戶於第20保單年度身故，且符合「無理賠紀錄期間」屆滿時仍生存的條件，則可依契約約定領取保險金。具體金額需依保險契約中「保險金額」的約定計算。  
+條文依據：  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
+        <is>
+          <t>第二十六條 投保年齡的計算及錯誤的處理 | other_metadata | 第五條 保險範圍 | 第二十二條 分期定期保險金給付申領文件、給付期限及未依限給付之效果 | 第十九條 失蹤處理 | 第二十八條 本契約受益人死亡或失蹤的處理 | 第十一條 特定傷病保險金的給付 | 第十五條 健康促進保險費折減</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F243" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若保戶於第20保單年度身故，且符合「無理賠紀錄期間」屆滿時仍生存的條件，則可依契約約定領取保險金。具體金額需依保險契約中「保險金額」的約定計算。  
+條文依據：  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="G243" s="2" t="inlineStr"/>
+      <c r="H243" s="2" t="inlineStr"/>
+      <c r="I243" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.014401, "neutral": 0.985345, "contradiction": 0.000254, "factuality": 0.999746, "C_fact": 0.999746}, "C_conf": 0.9997}</t>
+        </is>
+      </c>
+      <c r="J243" s="5" t="n"/>
+      <c r="K243" s="5" t="n">
+        <v>0.999746</v>
+      </c>
+      <c r="L243" s="5" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:35:59</t>
+        </is>
+      </c>
+      <c r="N243" s="5" t="n">
+        <v>20.46</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>被保險人為60歲女性，投保繳費期間20年期之滿溢寶特定傷病定期健康保險（定期給付型）（外溢型）100萬元，年繳應繳保險費為83,500元，年繳實繳保險費為78,490元。若被保險人於第二保險單年度自殺身故，則無理賠關懷保險金可以領到多少錢？</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人於第二保險單年度自殺身故，依條款規定，自契約訂立或復效之日起二年後故意自殺致死者，本公司仍負給付第十二條保險金之責任。因此，無理賠關懷保險金仍可領取，金額為「年繳應繳保險費總額」乘以1.02，即83,500元 × 1.02 = 85,170元。
+條文依據：  
+- [第十七條 除外責任（二)]  
+- [第十二條 無理賠關懷保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 無理賠關懷保險金的給付 | 第十七條 除外責任（二） | 第二十七條 受益人的指定及變更 | 第二十一條 無理賠關懷保險金的申領 | 第十九條 失蹤處理 | 第五條 保險範圍 | 第十一條 特定傷病保險金的給付 | other_metadata</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F244" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人於第二保險單年度自殺身故，依條款規定，自契約訂立或復效之日起二年後故意自殺致死者，本公司仍負給付第十二條保險金之責任。因此，無理賠關懷保險金仍可領取，金額為「年繳應繳保險費總額」乘以1.02，即83,500元 × 1.02 = 85,170元。
+條文依據：  
+- [第十七條 除外責任（二)]  
+- [第十二條 無理賠關懷保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G244" s="2" t="inlineStr"/>
+      <c r="H244" s="2" t="inlineStr"/>
+      <c r="I244" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.966433, "neutral": 0.029022, "contradiction": 0.004544, "factuality": 0.995456, "C_fact": 0.995456}, "C_conf": 0.9955}</t>
+        </is>
+      </c>
+      <c r="J244" s="5" t="n"/>
+      <c r="K244" s="5" t="n">
+        <v>0.995456</v>
+      </c>
+      <c r="L244" s="5" t="n">
+        <v>0.9955000000000001</v>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:36:38</t>
+        </is>
+      </c>
+      <c r="N244" s="5" t="n">
+        <v>39.21</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>請問如果第2保單年度罹患特定傷病，可以給付多少錢?給付給誰?未來還有其他保險金嗎?</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在第二保險單年度（含）以後罹患特定傷病，依條款規定，本公司將給付以下保險金：  
+1. **特定傷病保險金**：金額為「保險金額」。  
+2. **生活補助保險金**：自初次診斷確定罹患特定傷病的次一個保險單週年日起，每逢各保險單週年日仍生存者，按「保險金額」的百分之三十六給付，最高給付次數為十次。  
+保險金的受益人依保險契約所載明的受益人為準。  
+條文依據：  
+- [第十二條 特定傷病保險金的給付]  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 特定傷病保險金的給付 | 第五條 保險範圍 | 第十三條 生活補助保險金的給付（第二保險單年度起適用） | 第二條 名詞定義 | 第十五條 保險費豁免（第二保險單年度起適用）</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F245" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在第二保險單年度（含）以後罹患特定傷病，依條款規定，本公司將給付以下保險金：  
+1. **特定傷病保險金**：金額為「保險金額」。  
+2. **生活補助保險金**：自初次診斷確定罹患特定傷病的次一個保險單週年日起，每逢各保險單週年日仍生存者，按「保險金額」的百分之三十六給付，最高給付次數為十次。  
+保險金的受益人依保險契約所載明的受益人為準。  
+條文依據：  
+- [第十二條 特定傷病保險金的給付]  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]</t>
+        </is>
+      </c>
+      <c r="G245" s="2" t="inlineStr"/>
+      <c r="H245" s="2" t="inlineStr"/>
+      <c r="I245" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.986355, "neutral": 0.010888, "contradiction": 0.002758, "factuality": 0.997242, "C_fact": 0.997242}, "C_conf": 0.9972}</t>
+        </is>
+      </c>
+      <c r="J245" s="5" t="n"/>
+      <c r="K245" s="5" t="n">
+        <v>0.997242</v>
+      </c>
+      <c r="L245" s="5" t="n">
+        <v>0.9972</v>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:36:57</t>
+        </is>
+      </c>
+      <c r="N245" s="5" t="n">
+        <v>19.23</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>請問我115年1月1日投保，怎麼得到健康促進保險費折減?</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+要獲得健康促進保險費折減，您需在保險契約有效期間內完成以下步驟：  
+1. 使用保險公司指定的程式並加入指定的健康計劃。  
+2. 完成程式註冊程序，執行該程式並授權保險公司取得與健康促進相關的電子紀錄。  
+3. 在「指定日期」時，您的會員等級需符合以下標準之一：  
+   - 實踐家：次一保險單年度保險費折減比例為3%。  
+   - 樂享家或高於樂享家的會員等級：次一保險單年度保險費折減比例為10%。  
+此外，復效或豁免的保險費不適用折減約定。折減比例將依成功傳輸的電子紀錄及保險公司所訂辦法計算。
+條文依據：  
+- [第十六條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 健康促進保險費折減 | 第二十三條 投保年齡的計算及錯誤的處理 | 第十五條 保險費豁免（第二保險單年度起適用） | 第五條 保險範圍 | payout_items</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F246" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+要獲得健康促進保險費折減，您需在保險契約有效期間內完成以下步驟：  
+1. 使用保險公司指定的程式並加入指定的健康計劃。  
+2. 完成程式註冊程序，執行該程式並授權保險公司取得與健康促進相關的電子紀錄。  
+3. 在「指定日期」時，您的會員等級需符合以下標準之一：  
+   - 實踐家：次一保險單年度保險費折減比例為3%。  
+   - 樂享家或高於樂享家的會員等級：次一保險單年度保險費折減比例為10%。  
+此外，復效或豁免的保險費不適用折減約定。折減比例將依成功傳輸的電子紀錄及保險公司所訂辦法計算。
+條文依據：  
+- [第十六條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="G246" s="2" t="inlineStr"/>
+      <c r="H246" s="2" t="inlineStr"/>
+      <c r="I246" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.995796, "neutral": 0.003842, "contradiction": 0.000363, "factuality": 0.999637, "C_fact": 0.999637}, "C_conf": 0.9996}</t>
+        </is>
+      </c>
+      <c r="J246" s="5" t="n"/>
+      <c r="K246" s="5" t="n">
+        <v>0.999637</v>
+      </c>
+      <c r="L246" s="5" t="n">
+        <v>0.9996</v>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:37:05</t>
+        </is>
+      </c>
+      <c r="N246" s="5" t="n">
+        <v>7.67</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>保戶在114/1/10投保樂鍾溢，如果他在115/3/30罹患特定傷病的話，在什麼時候可以領取生活補助保險金?</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保戶在115/3/30初次診斷確定罹患特定傷病，根據第十三條規定，生活補助保險金的給付需從初次診斷確定罹患特定傷病的次一個保險單週年日開始計算。保單週年日為每年1月10日，因此保戶可於116/1/10起，每逢保險單週年日仍生存者，領取生活補助保險金。
+條文依據：  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 生活補助保險金的給付（第二保險單年度起適用） | other_metadata | 第十二條 特定傷病保險金的給付 | 第十一條 契約的終止（三） | 第十條 契約的終止（二） | 第五條 保險範圍 | payout_items | 第十五條 保險費豁免（第二保險單年度起適用）</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F247" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保戶在115/3/30初次診斷確定罹患特定傷病，根據第十三條規定，生活補助保險金的給付需從初次診斷確定罹患特定傷病的次一個保險單週年日開始計算。保單週年日為每年1月10日，因此保戶可於116/1/10起，每逢保險單週年日仍生存者，領取生活補助保險金。
+條文依據：  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]</t>
+        </is>
+      </c>
+      <c r="G247" s="2" t="inlineStr"/>
+      <c r="H247" s="2" t="inlineStr"/>
+      <c r="I247" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.981293, "neutral": 0.01049, "contradiction": 0.008216, "factuality": 0.991784, "C_fact": 0.991784}, "C_conf": 0.9918}</t>
+        </is>
+      </c>
+      <c r="J247" s="5" t="n"/>
+      <c r="K247" s="5" t="n">
+        <v>0.991784</v>
+      </c>
+      <c r="L247" s="5" t="n">
+        <v>0.9918</v>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:37:30</t>
+        </is>
+      </c>
+      <c r="N247" s="5" t="n">
+        <v>24.7</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>保戶在114/1/10投保樂鍾溢，如果他在115/3/30罹患特定傷病的話，他在115/1/9會領到無理賠回饋保險金嗎?</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不會領到無理賠回饋保險金。根據條款，保戶需於保險單年度末仍生存且未曾因罹患特定傷病申領「特定傷病保險金」才能獲得「無理賠回饋保險金」。保戶在115/3/30罹患特定傷病，符合申領「特定傷病保險金」的條件，因此不符合「無理賠回饋保險金」的給付條件。
+條文依據：  
+- [第十四條 無理賠回饋保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 無理賠回饋保險金的給付 | payout_items | 第二十條 無理賠回饋保險金的申領 | 第十二條 特定傷病保險金的給付 | other_metadata | 第十條 契約的終止（二） | 第五條 保險範圍 | 第十五條 保險費豁免（第二保險單年度起適用）</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F248" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不會領到無理賠回饋保險金。根據條款，保戶需於保險單年度末仍生存且未曾因罹患特定傷病申領「特定傷病保險金」才能獲得「無理賠回饋保險金」。保戶在115/3/30罹患特定傷病，符合申領「特定傷病保險金」的條件，因此不符合「無理賠回饋保險金」的給付條件。
+條文依據：  
+- [第十四條 無理賠回饋保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G248" s="2" t="inlineStr"/>
+      <c r="H248" s="2" t="inlineStr"/>
+      <c r="I248" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.168406, "neutral": 0.787462, "contradiction": 0.044131, "factuality": 0.955869, "C_fact": 0.955869}, "C_conf": 0.9559}</t>
+        </is>
+      </c>
+      <c r="J248" s="5" t="n"/>
+      <c r="K248" s="5" t="n">
+        <v>0.955869</v>
+      </c>
+      <c r="L248" s="5" t="n">
+        <v>0.9559</v>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:38:14</t>
+        </is>
+      </c>
+      <c r="N248" s="5" t="n">
+        <v>44.02</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>被保險人於第一保險單年度罹患急性心肌梗塞（重度），生活補助保險金最多可以領取幾次？</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於第一保險單年度罹患急性心肌梗塞（重度），無法申領「生活補助保險金」，因該保險金僅適用於第二保險單年度（含）以後的有效期間內初次診斷確定罹患特定傷病者。
+條文依據：  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 契約的終止（三） | 第十三條 生活補助保險金的給付（第二保險單年度起適用） | 第二條 名詞定義 | 第十二條 特定傷病保險金的給付 | 第十九條 特定傷病保險金、生活補助保險金或保險費豁免的申領 | 第五條 保險範圍 | 第十四條 無理賠回饋保險金的給付 | payout_items</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F249" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於第一保險單年度罹患急性心肌梗塞（重度），無法申領「生活補助保險金」，因該保險金僅適用於第二保險單年度（含）以後的有效期間內初次診斷確定罹患特定傷病者。
+條文依據：  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]</t>
+        </is>
+      </c>
+      <c r="G249" s="2" t="inlineStr"/>
+      <c r="H249" s="2" t="inlineStr"/>
+      <c r="I249" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.10923, "neutral": 0.776435, "contradiction": 0.114336, "factuality": 0.885664, "C_fact": 0.885664}, "C_conf": 0.8857}</t>
+        </is>
+      </c>
+      <c r="J249" s="5" t="n"/>
+      <c r="K249" s="5" t="n">
+        <v>0.885664</v>
+      </c>
+      <c r="L249" s="5" t="n">
+        <v>0.8857</v>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:38:56</t>
+        </is>
+      </c>
+      <c r="N249" s="5" t="n">
+        <v>40.94</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>被保險人為60歲女性，投保繳費期間20年期之樂鍾心特定傷病定期健康保險（外溢型）5單位，每單位年繳應繳保險費為1675元，則每逢保險單年度末生存者，可以領取多少無理賠關懷保險金？</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人每逢保險單年度末生存且未曾申領「特定傷病保險金」者，可領取的「無理賠回饋保險金」金額為：每單位年繳應繳保險費的百分之十乘以單位數。依題目提供的資訊計算如下：  
+每單位年繳應繳保險費為1675元，百分之十為167.5元（元以下無條件進位為168元）。  
+單位數為5單位，因此168元 × 5 = 840元。  
+故每逢保險單年度末生存者，可領取的「無理賠回饋保險金」金額為840元。
+條文依據：  
+- [第十四條 無理賠回饋保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 無理賠回饋保險金的給付 | 第五條 保險範圍 | 第十三條 生活補助保險金的給付（第二保險單年度起適用） | other_metadata | 第十二條 特定傷病保險金的給付 | payout_items | 第二十條 無理賠回饋保險金的申領 | 第十五條 保險費豁免（第二保險單年度起適用）</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F250" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人每逢保險單年度末生存且未曾申領「特定傷病保險金」者，可領取的「無理賠回饋保險金」金額為：每單位年繳應繳保險費的百分之十乘以單位數。依題目提供的資訊計算如下：  
+每單位年繳應繳保險費為1675元，百分之十為167.5元（元以下無條件進位為168元）。  
+單位數為5單位，因此168元 × 5 = 840元。  
+故每逢保險單年度末生存者，可領取的「無理賠回饋保險金」金額為840元。
+條文依據：  
+- [第十四條 無理賠回饋保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G250" s="2" t="inlineStr"/>
+      <c r="H250" s="2" t="inlineStr"/>
+      <c r="I250" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.99493, "neutral": 0.004556, "contradiction": 0.000514, "factuality": 0.999486, "C_fact": 0.999486}, "C_conf": 0.9995}</t>
+        </is>
+      </c>
+      <c r="J250" s="5" t="n"/>
+      <c r="K250" s="5" t="n">
+        <v>0.999486</v>
+      </c>
+      <c r="L250" s="5" t="n">
+        <v>0.9995000000000001</v>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:39:37</t>
+        </is>
+      </c>
+      <c r="N250" s="5" t="n">
+        <v>41.62</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/rag_results.xlsx
+++ b/src/rag_results.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N250"/>
+  <dimension ref="A1:N333"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -16436,6 +16436,5295 @@
         <v>41.62</v>
       </c>
     </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>保障範圍包括哪些項目？</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括住院醫療保險金、加護病房或燒燙傷病房保險金、祝壽保險金、身故保險金或喪葬費用保險金，以及所繳保險費的退還。
+條文依據：  
+- 摘要</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
+        <is>
+          <t>payout_items | summary | 第五條 保險範圍 | 第二條 名詞定義 | 第十八條 除外責任（一）</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F251" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括住院醫療保險金、加護病房或燒燙傷病房保險金、祝壽保險金、身故保險金或喪葬費用保險金，以及所繳保險費的退還。
+條文依據：  
+- 摘要</t>
+        </is>
+      </c>
+      <c r="G251" s="2" t="inlineStr"/>
+      <c r="H251" s="2" t="inlineStr"/>
+      <c r="I251" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.983647, "neutral": 0.012178, "contradiction": 0.004175, "factuality": 0.995825, "C_fact": 0.995825}, "C_conf": 0.9958}</t>
+        </is>
+      </c>
+      <c r="J251" s="5" t="n"/>
+      <c r="K251" s="5" t="n">
+        <v>0.995825</v>
+      </c>
+      <c r="L251" s="5" t="n">
+        <v>0.9958</v>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:06:34</t>
+        </is>
+      </c>
+      <c r="N251" s="5" t="n">
+        <v>18.58</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>住院日數計算有什麼特殊規則？</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院日數計算的特殊規則包括：  
+1. 住院日數是按被保險人同一次住院的實際全日住進急性病房或慢性病房（含加護病房及燒燙傷病房）的住院日數計算，包含住院及出院當日。  
+2. 若被保險人出院後又於同一日入院診療，該日不得重複計入住院日數。  
+條文依據：  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第十二條 住院醫療保險金的給付 | 第二條 名詞定義 | 第十三條 加護病房或燒燙傷病房保險金的給付 | 第二十八條 住院醫療保險金日額之減少</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F252" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院日數計算的特殊規則包括：  
+1. 住院日數是按被保險人同一次住院的實際全日住進急性病房或慢性病房（含加護病房及燒燙傷病房）的住院日數計算，包含住院及出院當日。  
+2. 若被保險人出院後又於同一日入院診療，該日不得重複計入住院日數。  
+條文依據：  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G252" s="2" t="inlineStr"/>
+      <c r="H252" s="2" t="inlineStr"/>
+      <c r="I252" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.996115, "neutral": 0.003676, "contradiction": 0.000209, "factuality": 0.999791, "C_fact": 0.999791}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J252" s="5" t="n"/>
+      <c r="K252" s="5" t="n">
+        <v>0.999791</v>
+      </c>
+      <c r="L252" s="5" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:06:47</t>
+        </is>
+      </c>
+      <c r="N252" s="5" t="n">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>住院醫療保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院醫療保險金的給付規定如下：  
+被保險人於契約有效期間內因疾病或傷害住院治療時，保險公司將依保險單所記載的「住院醫療保險金日額」，乘以入院日當年度的「增額係數」，再乘以住院日數，給付「住院醫療保險金」。同一保單年度內，同一次住院的住院日數給付上限為三百六十五日。
+條文依據：  
+- [第十二條 住院醫療保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 住院醫療保險金的給付 | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第十三條 加護病房或燒燙傷病房保險金的給付 | 第十四條 醫療保險金給付總額之上限 | 第二十八條 住院醫療保險金日額之減少</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F253" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院醫療保險金的給付規定如下：  
+被保險人於契約有效期間內因疾病或傷害住院治療時，保險公司將依保險單所記載的「住院醫療保險金日額」，乘以入院日當年度的「增額係數」，再乘以住院日數，給付「住院醫療保險金」。同一保單年度內，同一次住院的住院日數給付上限為三百六十五日。
+條文依據：  
+- [第十二條 住院醫療保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G253" s="2" t="inlineStr"/>
+      <c r="H253" s="2" t="inlineStr"/>
+      <c r="I253" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.998183, "neutral": 0.001694, "contradiction": 0.000123, "factuality": 0.999877, "C_fact": 0.999877}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J253" s="5" t="n"/>
+      <c r="K253" s="5" t="n">
+        <v>0.999877</v>
+      </c>
+      <c r="L253" s="5" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:06:57</t>
+        </is>
+      </c>
+      <c r="N253" s="5" t="n">
+        <v>10.22</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>加護病房或燒燙傷病房保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+加護病房或燒燙傷病房保險金的給付規定如下：  
+被保險人於契約有效期間內因疾病或傷害住院，並接受加護病房或燒燙傷病房治療者，除住院醫療保險金外，保險公司將依保險單記載的「住院醫療保險金日額」，乘以入院日當年度的「增額係數」，再乘以實際住進加護病房或燒燙傷病房的日數（含轉入及轉出當日）的二倍，給付「加護病房或燒燙傷病房保險金」。同一保單年度內，同一次住院的加護病房及燒燙傷病房住院日數合計給付上限為365日，但同一日僅能就其中一種病房給付。
+條文依據：  
+- [第十三條 加護病房或燒燙傷病房保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 加護病房或燒燙傷病房保險金的給付 | payout_items | 第二十三條 醫療保險金的申領 | 第五條 保險範圍 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F254" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+加護病房或燒燙傷病房保險金的給付規定如下：  
+被保險人於契約有效期間內因疾病或傷害住院，並接受加護病房或燒燙傷病房治療者，除住院醫療保險金外，保險公司將依保險單記載的「住院醫療保險金日額」，乘以入院日當年度的「增額係數」，再乘以實際住進加護病房或燒燙傷病房的日數（含轉入及轉出當日）的二倍，給付「加護病房或燒燙傷病房保險金」。同一保單年度內，同一次住院的加護病房及燒燙傷病房住院日數合計給付上限為365日，但同一日僅能就其中一種病房給付。
+條文依據：  
+- [第十三條 加護病房或燒燙傷病房保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G254" s="2" t="inlineStr"/>
+      <c r="H254" s="2" t="inlineStr"/>
+      <c r="I254" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.996658, "neutral": 0.002854, "contradiction": 0.000488, "factuality": 0.999512, "C_fact": 0.999512}, "C_conf": 0.9995}</t>
+        </is>
+      </c>
+      <c r="J254" s="5" t="n"/>
+      <c r="K254" s="5" t="n">
+        <v>0.999512</v>
+      </c>
+      <c r="L254" s="5" t="n">
+        <v>0.9995000000000001</v>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:07:03</t>
+        </is>
+      </c>
+      <c r="N254" s="5" t="n">
+        <v>5.47</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>醫療保險金給付總額之上限</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+醫療保險金給付總額之上限為保險單上所記載之「住院醫療保險金日額」的二千五百倍，並適用於本契約有效期間內依第十二條至第十三條所給付之各項保險金的累計總額。
+條文依據：  
+- [第十四條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 醫療保險金給付總額之上限 | 第十二條 住院醫療保險金的給付 | 第五條 保險範圍 | 第十三條 加護病房或燒燙傷病房保險金的給付 | payout_items</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F255" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+醫療保險金給付總額之上限為保險單上所記載之「住院醫療保險金日額」的二千五百倍，並適用於本契約有效期間內依第十二條至第十三條所給付之各項保險金的累計總額。
+條文依據：  
+- [第十四條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="G255" s="2" t="inlineStr"/>
+      <c r="H255" s="2" t="inlineStr"/>
+      <c r="I255" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.996196, "neutral": 0.003514, "contradiction": 0.00029, "factuality": 0.99971, "C_fact": 0.99971}, "C_conf": 0.9997}</t>
+        </is>
+      </c>
+      <c r="J255" s="5" t="n"/>
+      <c r="K255" s="5" t="n">
+        <v>0.99971</v>
+      </c>
+      <c r="L255" s="5" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:07:05</t>
+        </is>
+      </c>
+      <c r="N255" s="5" t="n">
+        <v>2.18</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>祝壽保險金的給付規定為何?</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+祝壽保險金的給付規定為：被保險人於本契約有效期間且保險年齡到達九十九歲之保險單週年日仍生存時，本公司按「當年度保險金額」給付「祝壽保險金」。
+條文依據：  
+- [第十五條 祝壽保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
+        <is>
+          <t>第十五條 祝壽保險金的給付 | 第十二條至第十三條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | 第二十四條 祝壽保險金的申領 | payout_items | 第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F256" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+祝壽保險金的給付規定為：被保險人於本契約有效期間且保險年齡到達九十九歲之保險單週年日仍生存時，本公司按「當年度保險金額」給付「祝壽保險金」。
+條文依據：  
+- [第十五條 祝壽保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G256" s="2" t="inlineStr"/>
+      <c r="H256" s="2" t="inlineStr"/>
+      <c r="I256" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.997653, "neutral": 0.002173, "contradiction": 0.000174, "factuality": 0.999826, "C_fact": 0.999826}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J256" s="5" t="n"/>
+      <c r="K256" s="5" t="n">
+        <v>0.999826</v>
+      </c>
+      <c r="L256" s="5" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:07:07</t>
+        </is>
+      </c>
+      <c r="N256" s="5" t="n">
+        <v>1.91</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>有效期間內身故，保險金如何給付?</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於本契約有效期間內身故者，本公司按「當年度保險金額」給付「身故保險金」。若被保險人於繳費期間內身故，當期已繳付之未到期保險費將不予退還，亦不併入身故保險金內給付。若被保險人於有效期間且實際年齡未滿十五足歲身故者，本公司按「所繳保險費」退還要保人，不適用前述規定。此外，若被保險人為受監護宣告尚未撤銷者，其身故保險金變更為喪葬費用保險金，並受遺產稅喪葬費扣除額之半數限制，超過部分不負給付責任。  
+條文依據：  
+- [第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付 | 第十條 契約的終止（二） | 第五條 保險範圍 | 第二十二條 失蹤處理 | 第十五條 祝壽保險金的給付</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F257" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於本契約有效期間內身故者，本公司按「當年度保險金額」給付「身故保險金」。若被保險人於繳費期間內身故，當期已繳付之未到期保險費將不予退還，亦不併入身故保險金內給付。若被保險人於有效期間且實際年齡未滿十五足歲身故者，本公司按「所繳保險費」退還要保人，不適用前述規定。此外，若被保險人為受監護宣告尚未撤銷者，其身故保險金變更為喪葬費用保險金，並受遺產稅喪葬費扣除額之半數限制，超過部分不負給付責任。  
+條文依據：  
+- [第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G257" s="2" t="inlineStr"/>
+      <c r="H257" s="2" t="inlineStr"/>
+      <c r="I257" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.458867, "neutral": 0.540053, "contradiction": 0.00108, "factuality": 0.99892, "C_fact": 0.99892}, "C_conf": 0.9989}</t>
+        </is>
+      </c>
+      <c r="J257" s="5" t="n"/>
+      <c r="K257" s="5" t="n">
+        <v>0.99892</v>
+      </c>
+      <c r="L257" s="5" t="n">
+        <v>0.9989</v>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:07:12</t>
+        </is>
+      </c>
+      <c r="N257" s="5" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>健康促進保險費折減規定</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+健康促進保險費折減規定如下：  
+被保險人年齡達20歲（含）以上，使用保險公司指定程式並加入健康計劃，於「指定日期」的會員等級符合標準者，可享次一保險單年度的保險費折減。折減比例依會員等級分為：進階會員折減2%，菁英會員或更高等級折減3%。豁免或復效的保險費不適用折減規定。被保險人需完成程式註冊並授權保險公司取得健康相關電子紀錄，保險公司將依紀錄計算會員等級。  
+條文依據：  
+- [第十七條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
+        <is>
+          <t>第十七條 健康促進保險費折減 | 第二十八條 住院醫療保險金日額之減少 | 第三十條 投保年齡的計算及錯誤的處理 | 第二條 名詞定義 | 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F258" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+健康促進保險費折減規定如下：  
+被保險人年齡達20歲（含）以上，使用保險公司指定程式並加入健康計劃，於「指定日期」的會員等級符合標準者，可享次一保險單年度的保險費折減。折減比例依會員等級分為：進階會員折減2%，菁英會員或更高等級折減3%。豁免或復效的保險費不適用折減規定。被保險人需完成程式註冊並授權保險公司取得健康相關電子紀錄，保險公司將依紀錄計算會員等級。  
+條文依據：  
+- [第十七條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="G258" s="2" t="inlineStr"/>
+      <c r="H258" s="2" t="inlineStr"/>
+      <c r="I258" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.997354, "neutral": 0.002066, "contradiction": 0.00058, "factuality": 0.99942, "C_fact": 0.99942}, "C_conf": 0.9994}</t>
+        </is>
+      </c>
+      <c r="J258" s="5" t="n"/>
+      <c r="K258" s="5" t="n">
+        <v>0.99942</v>
+      </c>
+      <c r="L258" s="5" t="n">
+        <v>0.9994</v>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:07:18</t>
+        </is>
+      </c>
+      <c r="N258" s="5" t="n">
+        <v>4.17</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>除外責任的解釋?</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+除外責任是指保險公司不負給付保險金責任的情形，包含被保險人因故意行為、犯罪行為、非法施用毒品等原因所致的疾病或傷害，以及因美容手術、健康檢查、懷孕、流產或分娩等特定事故住院診療的情況。但部分情形有例外，例如重建基本功能的必要整型手術、特定懷孕相關疾病、醫療行為必要的流產或剖腹產等，保險公司仍負給付責任。
+條文依據：  
+- [第十八條 除外責任（一)]  
+- [第十九條 除外責任（二)]</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第十九條 除外責任（二） | 第八條 告知義務與本契約的解除 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F259" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+除外責任是指保險公司不負給付保險金責任的情形，包含被保險人因故意行為、犯罪行為、非法施用毒品等原因所致的疾病或傷害，以及因美容手術、健康檢查、懷孕、流產或分娩等特定事故住院診療的情況。但部分情形有例外，例如重建基本功能的必要整型手術、特定懷孕相關疾病、醫療行為必要的流產或剖腹產等，保險公司仍負給付責任。
+條文依據：  
+- [第十八條 除外責任（一)]  
+- [第十九條 除外責任（二)]</t>
+        </is>
+      </c>
+      <c r="G259" s="2" t="inlineStr"/>
+      <c r="H259" s="2" t="inlineStr"/>
+      <c r="I259" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.978546, "neutral": 0.021227, "contradiction": 0.000227, "factuality": 0.999773, "C_fact": 0.999773}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J259" s="5" t="n"/>
+      <c r="K259" s="5" t="n">
+        <v>0.999773</v>
+      </c>
+      <c r="L259" s="5" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:07:23</t>
+        </is>
+      </c>
+      <c r="N259" s="5" t="n">
+        <v>4.69</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>哪些疾病被含在除外責任?</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+以下疾病被列為除外責任，保險公司不負給付第十二條至第十三條保險金的責任：  
+1. 美容手術、外科整型（但為重建基本功能所作之必要整型不在此限）。  
+2. 外觀可見之天生畸形。  
+3. 健康檢查、療養、靜養、戒毒、戒酒、護理或養老之非以直接診治病人為目的者。  
+4. 懷孕、流產或分娩及其併發症（但特定懷孕相關疾病、醫療行為必要之流產及剖腹產不在此限）。  
+5. 不孕症、人工受孕或非以治療為目的之避孕及絕育手術。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第二條 名詞定義 | 第十九條 除外責任（二）</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F260" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+以下疾病被列為除外責任，保險公司不負給付第十二條至第十三條保險金的責任：  
+1. 美容手術、外科整型（但為重建基本功能所作之必要整型不在此限）。  
+2. 外觀可見之天生畸形。  
+3. 健康檢查、療養、靜養、戒毒、戒酒、護理或養老之非以直接診治病人為目的者。  
+4. 懷孕、流產或分娩及其併發症（但特定懷孕相關疾病、醫療行為必要之流產及剖腹產不在此限）。  
+5. 不孕症、人工受孕或非以治療為目的之避孕及絕育手術。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="G260" s="2" t="inlineStr"/>
+      <c r="H260" s="2" t="inlineStr"/>
+      <c r="I260" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.9986, "neutral": 0.001184, "contradiction": 0.000215, "factuality": 0.999785, "C_fact": 0.999785}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J260" s="5" t="n"/>
+      <c r="K260" s="5" t="n">
+        <v>0.999785</v>
+      </c>
+      <c r="L260" s="5" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:07:27</t>
+        </is>
+      </c>
+      <c r="N260" s="5" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>進行美容手術住院可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，因美容手術住院診療者，本公司不負給付保險金的責任。但若美容手術是為重建基本功能所作之必要整型，則不在此限，可以申請理賠。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D261" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第十三條 加護病房或燒燙傷病房保險金的給付 | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第二條 名詞定義 | payout_items</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F261" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，因美容手術住院診療者，本公司不負給付保險金的責任。但若美容手術是為重建基本功能所作之必要整型，則不在此限，可以申請理賠。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="G261" s="2" t="inlineStr"/>
+      <c r="H261" s="2" t="inlineStr"/>
+      <c r="I261" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.474019, "neutral": 0.524983, "contradiction": 0.000999, "factuality": 0.999001, "C_fact": 0.999001}, "C_conf": 0.999}</t>
+        </is>
+      </c>
+      <c r="J261" s="5" t="n"/>
+      <c r="K261" s="5" t="n">
+        <v>0.999001</v>
+      </c>
+      <c r="L261" s="5" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:07:30</t>
+        </is>
+      </c>
+      <c r="N261" s="5" t="n">
+        <v>3.45</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>因胎兒染色體異常進行手術而住院可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以申請理賠。根據條款，被保險人因「胎兒染色體異常之手術」住院診療不屬於除外責任範圍，因此本公司負有給付保險金的責任。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第二條 名詞定義 | payout_items | 第十三條 加護病房或燒燙傷病房保險金的給付</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F262" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以申請理賠。根據條款，被保險人因「胎兒染色體異常之手術」住院診療不屬於除外責任範圍，因此本公司負有給付保險金的責任。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="G262" s="2" t="inlineStr"/>
+      <c r="H262" s="2" t="inlineStr"/>
+      <c r="I262" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.97883, "neutral": 0.013511, "contradiction": 0.007658, "factuality": 0.992342, "C_fact": 0.992342}, "C_conf": 0.9923}</t>
+        </is>
+      </c>
+      <c r="J262" s="5" t="n"/>
+      <c r="K262" s="5" t="n">
+        <v>0.9923419999999999</v>
+      </c>
+      <c r="L262" s="5" t="n">
+        <v>0.9923</v>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:07:33</t>
+        </is>
+      </c>
+      <c r="N262" s="5" t="n">
+        <v>2.95</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>因胎位不正進行手術而住院可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，因懷孕、流產或分娩及其併發症住院診療，本公司不負給付保險金的責任。然而，若因胎位不正進行手術屬於「醫療行為必要之剖腹產」的情形，則不在此限，可以申請理賠。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第二條 名詞定義 | payout_items | 第十三條 加護病房或燒燙傷病房保險金的給付</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F263" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，因懷孕、流產或分娩及其併發症住院診療，本公司不負給付保險金的責任。然而，若因胎位不正進行手術屬於「醫療行為必要之剖腹產」的情形，則不在此限，可以申請理賠。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="G263" s="2" t="inlineStr"/>
+      <c r="H263" s="2" t="inlineStr"/>
+      <c r="I263" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.542911, "neutral": 0.4556, "contradiction": 0.001489, "factuality": 0.998511, "C_fact": 0.998511}, "C_conf": 0.9985}</t>
+        </is>
+      </c>
+      <c r="J263" s="5" t="n"/>
+      <c r="K263" s="5" t="n">
+        <v>0.998511</v>
+      </c>
+      <c r="L263" s="5" t="n">
+        <v>0.9985000000000001</v>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:07:37</t>
+        </is>
+      </c>
+      <c r="N263" s="5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>因自殺未遂導致住院可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，因被保險人故意行為（包括自殺及自殺未遂）導致住院診療者，本公司不負給付住院醫療保險金的責任。  
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 除外責任（二） | 第十八條 除外責任（一） | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | payout_items | 第十條 契約的終止（二）</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F264" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，因被保險人故意行為（包括自殺及自殺未遂）導致住院診療者，本公司不負給付住院醫療保險金的責任。  
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="G264" s="2" t="inlineStr"/>
+      <c r="H264" s="2" t="inlineStr"/>
+      <c r="I264" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.983569, "neutral": 0.016184, "contradiction": 0.000247, "factuality": 0.999753, "C_fact": 0.999753}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J264" s="5" t="n"/>
+      <c r="K264" s="5" t="n">
+        <v>0.999753</v>
+      </c>
+      <c r="L264" s="5" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:07:39</t>
+        </is>
+      </c>
+      <c r="N264" s="5" t="n">
+        <v>2.76</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>被保險人在投保一年內故意自殺者，可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人在投保一年內故意自殺者，依條款規定，本公司不負給付身故保險金或喪葬費用保險金的責任。唯若自契約訂立或復效之日起滿二年後故意自殺致死者，本公司仍負給付責任。
+條文依據：  
+- [第十九條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="D265" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 除外責任（二） | 第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付 | 第十條 契約的終止（二） | 第三十條 投保年齡的計算及錯誤的處理 | 第十八條 除外責任（一）</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F265" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人在投保一年內故意自殺者，依條款規定，本公司不負給付身故保險金或喪葬費用保險金的責任。唯若自契約訂立或復效之日起滿二年後故意自殺致死者，本公司仍負給付責任。
+條文依據：  
+- [第十九條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="G265" s="2" t="inlineStr"/>
+      <c r="H265" s="2" t="inlineStr"/>
+      <c r="I265" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.997423, "neutral": 0.002395, "contradiction": 0.000182, "factuality": 0.999818, "C_fact": 0.999818}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J265" s="5" t="n"/>
+      <c r="K265" s="5" t="n">
+        <v>0.999818</v>
+      </c>
+      <c r="L265" s="5" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:07:43</t>
+        </is>
+      </c>
+      <c r="N265" s="5" t="n">
+        <v>3.38</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>申請理賠有什麼時間規定嗎?</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申請理賠的時間規定如下：要保人、被保險人或受益人應於知悉本公司應負保險責任之事故後十日內通知本公司，並於通知後儘速檢具所需文件向本公司申請給付保險金。本公司應於收齊所需文件後十五日內完成保險金給付。但若因可歸責於本公司之事由導致未在約定期限內給付者，應按年利一分加計利息給付。
+條文依據：  
+- [第二十一條 保險事故的通知與保險金的申請時間]</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
+        <is>
+          <t>第二十一條 保險事故的通知與保險金的申請時間 | 第六條 第二期以後保險費的交付、寬限期間及契約效力的停止 | 第七條 本契約效力的恢復 | 第三條 契約撤銷權 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F266" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申請理賠的時間規定如下：要保人、被保險人或受益人應於知悉本公司應負保險責任之事故後十日內通知本公司，並於通知後儘速檢具所需文件向本公司申請給付保險金。本公司應於收齊所需文件後十五日內完成保險金給付。但若因可歸責於本公司之事由導致未在約定期限內給付者，應按年利一分加計利息給付。
+條文依據：  
+- [第二十一條 保險事故的通知與保險金的申請時間]</t>
+        </is>
+      </c>
+      <c r="G266" s="2" t="inlineStr"/>
+      <c r="H266" s="2" t="inlineStr"/>
+      <c r="I266" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.997047, "neutral": 0.002872, "contradiction": 8.1e-05, "factuality": 0.999919, "C_fact": 0.999919}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J266" s="5" t="n"/>
+      <c r="K266" s="5" t="n">
+        <v>0.999919</v>
+      </c>
+      <c r="L266" s="5" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:07:48</t>
+        </is>
+      </c>
+      <c r="N266" s="5" t="n">
+        <v>4.29</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>燒燙傷病房保險金怎麼申領?</t>
+        </is>
+      </c>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申領燒燙傷病房保險金時，受益人需依約定檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 醫療診斷書或住院證明，並列明進、出燒燙傷病房的日期。（但要保人或被保險人為醫師時，不得為被保險人出具診斷書或住院證明。）  
+4. 受益人的身分證明。  
+此外，保險公司基於審核保險金的需要，得徵詢其他醫師的醫學專業意見，並經受益人同意調閱被保險人的就醫相關資料，相關費用由保險公司負擔。
+條文依據：  
+- [第二十三條 醫療保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="inlineStr">
+        <is>
+          <t>第二十三條 醫療保險金的申領 | 第十三條 加護病房或燒燙傷病房保險金的給付 | payout_items | 第二條 名詞定義 | 第二十一條 保險事故的通知與保險金的申請時間</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F267" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申領燒燙傷病房保險金時，受益人需依約定檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 醫療診斷書或住院證明，並列明進、出燒燙傷病房的日期。（但要保人或被保險人為醫師時，不得為被保險人出具診斷書或住院證明。）  
+4. 受益人的身分證明。  
+此外，保險公司基於審核保險金的需要，得徵詢其他醫師的醫學專業意見，並經受益人同意調閱被保險人的就醫相關資料，相關費用由保險公司負擔。
+條文依據：  
+- [第二十三條 醫療保險金的申領]</t>
+        </is>
+      </c>
+      <c r="G267" s="2" t="inlineStr"/>
+      <c r="H267" s="2" t="inlineStr"/>
+      <c r="I267" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.998221, "neutral": 0.001605, "contradiction": 0.000174, "factuality": 0.999826, "C_fact": 0.999826}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J267" s="5" t="n"/>
+      <c r="K267" s="5" t="n">
+        <v>0.999826</v>
+      </c>
+      <c r="L267" s="5" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:07:52</t>
+        </is>
+      </c>
+      <c r="N267" s="5" t="n">
+        <v>4.23</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>活到99歲怎麼申請祝壽金?</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申請祝壽保險金時，受益人需檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 受益人的身分證明。  
+條文依據：  
+- [第二十四條 祝壽保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
+        <is>
+          <t>第十五條 祝壽保險金的給付 | 第二十四條 祝壽保險金的申領 | 第五條 保險範圍 | 第十二條至第十三條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | announcement_history</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F268" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申請祝壽保險金時，受益人需檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 受益人的身分證明。  
+條文依據：  
+- [第二十四條 祝壽保險金的申領]</t>
+        </is>
+      </c>
+      <c r="G268" s="2" t="inlineStr"/>
+      <c r="H268" s="2" t="inlineStr"/>
+      <c r="I268" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.99803, "neutral": 0.001868, "contradiction": 0.000103, "factuality": 0.999897, "C_fact": 0.999897}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J268" s="5" t="n"/>
+      <c r="K268" s="5" t="n">
+        <v>0.999897</v>
+      </c>
+      <c r="L268" s="5" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:07:55</t>
+        </is>
+      </c>
+      <c r="N268" s="5" t="n">
+        <v>2.43</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>被保人身故怎麼申請理賠</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+受益人申領「身故保險金」或「喪葬費用保險金」時，需檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 被保險人死亡證明書及除戶戶籍謄本。  
+4. 受益人的身分證明。  
+條文依據：  
+- [第二十五條 身故保險金或喪葬費用保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D269" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付 | 第十二條至第十三條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | 第二十二條 失蹤處理 | 第二十五條 身故保險金或喪葬費用保險金的申領 | 第十九條 除外責任（二）</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F269" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+受益人申領「身故保險金」或「喪葬費用保險金」時，需檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 被保險人死亡證明書及除戶戶籍謄本。  
+4. 受益人的身分證明。  
+條文依據：  
+- [第二十五條 身故保險金或喪葬費用保險金的申領]</t>
+        </is>
+      </c>
+      <c r="G269" s="2" t="inlineStr"/>
+      <c r="H269" s="2" t="inlineStr"/>
+      <c r="I269" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.996062, "neutral": 0.003782, "contradiction": 0.000155, "factuality": 0.999845, "C_fact": 0.999845}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J269" s="5" t="n"/>
+      <c r="K269" s="5" t="n">
+        <v>0.999845</v>
+      </c>
+      <c r="L269" s="5" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:07:57</t>
+        </is>
+      </c>
+      <c r="N269" s="5" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>投保15年後，因手術住院3天，住院日額為2500元，請問可以申請多少理賠?</t>
+        </is>
+      </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+依據第十二條，住院醫療保險金的計算公式為「住院醫療保險金日額」乘以「增額係數」再乘以住院日數。假設增額係數未提供具體數值，僅能以住院日額直接計算。住院日額為2500元，住院日數為3天，因此理賠金額為：2500元 × 3天 = 7500元。
+條文依據：  
+- [第十二條 住院醫療保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D270" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 住院醫療保險金的給付 | 第十三條 加護病房或燒燙傷病房保險金的給付 | 第二十八條 住院醫療保險金日額之減少 | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | payout_items | 第五條 保險範圍 | 第二條 名詞定義 | 第二十一條 保險事故的通知與保險金的申請時間</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F270" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+依據第十二條，住院醫療保險金的計算公式為「住院醫療保險金日額」乘以「增額係數」再乘以住院日數。假設增額係數未提供具體數值，僅能以住院日額直接計算。住院日額為2500元，住院日數為3天，因此理賠金額為：2500元 × 3天 = 7500元。
+條文依據：  
+- [第十二條 住院醫療保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G270" s="2" t="inlineStr"/>
+      <c r="H270" s="2" t="inlineStr"/>
+      <c r="I270" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.118618, "neutral": 0.871817, "contradiction": 0.009565, "factuality": 0.990435, "C_fact": 0.990435}, "C_conf": 0.9904}</t>
+        </is>
+      </c>
+      <c r="J270" s="5" t="n"/>
+      <c r="K270" s="5" t="n">
+        <v>0.990435</v>
+      </c>
+      <c r="L270" s="5" t="n">
+        <v>0.9903999999999999</v>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:08:00</t>
+        </is>
+      </c>
+      <c r="N270" s="5" t="n">
+        <v>2.54</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>保障範圍包括哪些項目？</t>
+        </is>
+      </c>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括：住院手術醫療保險金、門診手術醫療保險金、特定處置保險金、意外創傷縫合處置保險金、意外住院手術醫療保險金、祝壽保險金、所繳保險費的退還、身故保險金或喪葬費用保險金。
+條文依據：  
+- 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="D271" s="2" t="inlineStr">
+        <is>
+          <t>payout_items | 第五條 保險範圍 | summary | 第四條 名詞定義 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F271" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括：住院手術醫療保險金、門診手術醫療保險金、特定處置保險金、意外創傷縫合處置保險金、意外住院手術醫療保險金、祝壽保險金、所繳保險費的退還、身故保險金或喪葬費用保險金。
+條文依據：  
+- 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="G271" s="2" t="inlineStr"/>
+      <c r="H271" s="2" t="inlineStr"/>
+      <c r="I271" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.997972, "neutral": 0.001773, "contradiction": 0.000255, "factuality": 0.999745, "C_fact": 0.999745}, "C_conf": 0.9997}</t>
+        </is>
+      </c>
+      <c r="J271" s="5" t="n"/>
+      <c r="K271" s="5" t="n">
+        <v>0.999745</v>
+      </c>
+      <c r="L271" s="5" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:08:03</t>
+        </is>
+      </c>
+      <c r="N271" s="5" t="n">
+        <v>2.86</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="inlineStr">
+        <is>
+          <t>保險金額是否有上限?</t>
+        </is>
+      </c>
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+有上限。本契約有效期間內，依第十一條至第十五條所給付之各項保險金，其累計給付總額上限為保險單上所記載「保險金額」的一千五百倍。
+條文依據：  
+- [第十六條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="D272" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 醫療保險金給付總額之上限 | 第三十條 保險金額之減少 | 第五條 保險範圍 | 第十九條 健康促進保險費折減 | 第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F272" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+有上限。本契約有效期間內，依第十一條至第十五條所給付之各項保險金，其累計給付總額上限為保險單上所記載「保險金額」的一千五百倍。
+條文依據：  
+- [第十六條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="G272" s="2" t="inlineStr"/>
+      <c r="H272" s="2" t="inlineStr"/>
+      <c r="I272" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.996057, "neutral": 0.003784, "contradiction": 0.000159, "factuality": 0.999841, "C_fact": 0.999841}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J272" s="5" t="n"/>
+      <c r="K272" s="5" t="n">
+        <v>0.999841</v>
+      </c>
+      <c r="L272" s="5" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:08:05</t>
+        </is>
+      </c>
+      <c r="N272" s="5" t="n">
+        <v>1.79</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="inlineStr">
+        <is>
+          <t>投保後5天發生手術，是否可以申請理賠?</t>
+        </is>
+      </c>
+      <c r="C273" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+條款未明確規定／資料不足</t>
+        </is>
+      </c>
+      <c r="D273" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第十一條 住院手術醫療保險金 | 第二十條 除外責任（一） | 第十二條 門診手術醫療保險金 | 第十三條 意外住院手術醫療保險金 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F273" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款內容，是否可以申請理賠需視保險契約中是否有等待期間的規定。然而，提供的條款中未提及等待期間的相關規定，因此無法判斷投保後5天是否符合理賠條件。
+條文依據：  
+找不到相關內容</t>
+        </is>
+      </c>
+      <c r="G273" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+條款未明確規定／資料不足</t>
+        </is>
+      </c>
+      <c r="H273" s="2" t="inlineStr"/>
+      <c r="I273" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.108859, "neutral": 0.77934, "contradiction": 0.111801, "factuality": 0.888199, "C_fact": 0.888199}, "C_conf": 0.8882}</t>
+        </is>
+      </c>
+      <c r="J273" s="5" t="n"/>
+      <c r="K273" s="5" t="n">
+        <v>0.888199</v>
+      </c>
+      <c r="L273" s="5" t="n">
+        <v>0.8882</v>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:08:11</t>
+        </is>
+      </c>
+      <c r="N273" s="5" t="n">
+        <v>6.77</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <t>住院手術醫療保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院手術醫療保險金的給付規定如下：  
+1. 被保險人於契約有效期間內因疾病或傷害，經醫師診斷必須於醫院住院接受附表一所列的手術治療且已實際接受手術者，本公司依保險單記載的「保險金額」乘以手術日當年度的「增額係數」，再乘以手術給付倍數，給付住院手術醫療保險金。  
+2. 若同一次手術中於同一手術位置接受二項以上手術項目，僅給付手術給付倍數最高的手術項目。  
+3. 未載明於附表一的手術項目，將與被保險人協議比照附表一內程度相當的手術項目決定給付倍數。  
+4. 以下情形不負給付責任：  
+   - 依據除外責任條款規定不在給付範圍內。  
+   - 不屬全民健康保險醫療服務給付項目及支付標準第二部第二章第七節或第三部第三章第四節第三項所列舉的手術。  
+條文依據：  
+- [第十一條 住院手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="D274" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 住院手術醫療保險金 | 第十三條 意外住院手術醫療保險金 | 第十二條 門診手術醫療保險金 | payout_items | 第二十條 除外責任（一） | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F274" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院手術醫療保險金的給付規定如下：  
+1. 被保險人於契約有效期間內因疾病或傷害，經醫師診斷必須於醫院住院接受附表一所列的手術治療且已實際接受手術者，本公司依保險單記載的「保險金額」乘以手術日當年度的「增額係數」，再乘以手術給付倍數，給付住院手術醫療保險金。  
+2. 若同一次手術中於同一手術位置接受二項以上手術項目，僅給付手術給付倍數最高的手術項目。  
+3. 未載明於附表一的手術項目，將與被保險人協議比照附表一內程度相當的手術項目決定給付倍數。  
+4. 以下情形不負給付責任：  
+   - 依據除外責任條款規定不在給付範圍內。  
+   - 不屬全民健康保險醫療服務給付項目及支付標準第二部第二章第七節或第三部第三章第四節第三項所列舉的手術。  
+條文依據：  
+- [第十一條 住院手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="G274" s="2" t="inlineStr"/>
+      <c r="H274" s="2" t="inlineStr"/>
+      <c r="I274" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.993185, "neutral": 0.005888, "contradiction": 0.000927, "factuality": 0.999073, "C_fact": 0.999073}, "C_conf": 0.9991}</t>
+        </is>
+      </c>
+      <c r="J274" s="5" t="n"/>
+      <c r="K274" s="5" t="n">
+        <v>0.999073</v>
+      </c>
+      <c r="L274" s="5" t="n">
+        <v>0.9991</v>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:08:18</t>
+        </is>
+      </c>
+      <c r="N274" s="5" t="n">
+        <v>5.92</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B275" s="2" t="inlineStr">
+        <is>
+          <t>門診手術醫療保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C275" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+門診手術醫療保險金的給付規定如下：  
+1. 被保險人因疾病或傷害，經醫師診斷必須於醫院或診所門診接受附表一的手術治療且已實際接受手術者，本公司依保險單所記載之「保險金額」乘以手術日當年度之「增額係數」，再乘以手術給付倍數，給付「門診手術醫療保險金」。  
+2. 同一次手術中，於同一手術位置接受二項以上手術項目時，僅給付手術給付倍數最高的手術項目。  
+3. 同一保險單年度內，門診手術醫療保險金的給付以十次為限。  
+4. 未載明於附表一所列的手術項目，將與被保險人協議比照該表內之手術項目，決定給付倍數。  
+5. 以下情形不負給付責任：  
+   - 依據本契約除外責任條款的規定不在給付範圍內。  
+   - 不屬全民健康保險醫療服務給付項目及支付標準第二部第二章第七節或第三部第三章第四節第三項所列舉的手術。  
+條文依據：  
+- [第十二條 門診手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="D275" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 門診手術醫療保險金 | 第十一條 住院手術醫療保險金 | payout_items | 第十三條 意外住院手術醫療保險金 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F275" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+門診手術醫療保險金的給付規定如下：  
+1. 被保險人因疾病或傷害，經醫師診斷必須於醫院或診所門診接受附表一的手術治療且已實際接受手術者，本公司依保險單所記載之「保險金額」乘以手術日當年度之「增額係數」，再乘以手術給付倍數，給付「門診手術醫療保險金」。  
+2. 同一次手術中，於同一手術位置接受二項以上手術項目時，僅給付手術給付倍數最高的手術項目。  
+3. 同一保險單年度內，門診手術醫療保險金的給付以十次為限。  
+4. 未載明於附表一所列的手術項目，將與被保險人協議比照該表內之手術項目，決定給付倍數。  
+5. 以下情形不負給付責任：  
+   - 依據本契約除外責任條款的規定不在給付範圍內。  
+   - 不屬全民健康保險醫療服務給付項目及支付標準第二部第二章第七節或第三部第三章第四節第三項所列舉的手術。  
+條文依據：  
+- [第十二條 門診手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="G275" s="2" t="inlineStr"/>
+      <c r="H275" s="2" t="inlineStr"/>
+      <c r="I275" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.887881, "neutral": 0.109427, "contradiction": 0.002692, "factuality": 0.997308, "C_fact": 0.997308}, "C_conf": 0.9973}</t>
+        </is>
+      </c>
+      <c r="J275" s="5" t="n"/>
+      <c r="K275" s="5" t="n">
+        <v>0.997308</v>
+      </c>
+      <c r="L275" s="5" t="n">
+        <v>0.9973</v>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:08:22</t>
+        </is>
+      </c>
+      <c r="N275" s="5" t="n">
+        <v>4.06</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B276" s="2" t="inlineStr">
+        <is>
+          <t>意外住院手術醫療保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C276" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外住院手術醫療保險金的給付規定如下：  
+1. 被保險人需於本契約有效期間內且保險年齡未滿七十歲。  
+2. 因傷害經醫師診斷在住院期間必須接受手術治療且已接受手術者，保險公司按保險單所記載之「保險金額」的三倍，乘以手術日當年度之「增額係數」，給付「意外住院手術醫療保險金」。  
+3. 若被保險人於同一次手術中，於同一手術位置接受二項以上手術項目，僅給付一次「意外住院手術醫療保險金」。  
+條文依據：  
+- [第十三條 意外住院手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="D276" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 意外住院手術醫療保險金 | 第十一條 住院手術醫療保險金 | 第十五條 意外創傷縫合處置保險金 | 第二十條 除外責任（一） | 第十二條 門診手術醫療保險金 | 附表三：意外創傷縫合處置項目及給付倍數表 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F276" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外住院手術醫療保險金的給付規定如下：  
+1. 被保險人需於本契約有效期間內且保險年齡未滿七十歲。  
+2. 因傷害經醫師診斷在住院期間必須接受手術治療且已接受手術者，保險公司按保險單所記載之「保險金額」的三倍，乘以手術日當年度之「增額係數」，給付「意外住院手術醫療保險金」。  
+3. 若被保險人於同一次手術中，於同一手術位置接受二項以上手術項目，僅給付一次「意外住院手術醫療保險金」。  
+條文依據：  
+- [第十三條 意外住院手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="G276" s="2" t="inlineStr"/>
+      <c r="H276" s="2" t="inlineStr"/>
+      <c r="I276" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.996051, "neutral": 0.003505, "contradiction": 0.000443, "factuality": 0.999557, "C_fact": 0.999557}, "C_conf": 0.9996}</t>
+        </is>
+      </c>
+      <c r="J276" s="5" t="n"/>
+      <c r="K276" s="5" t="n">
+        <v>0.999557</v>
+      </c>
+      <c r="L276" s="5" t="n">
+        <v>0.9996</v>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:08:25</t>
+        </is>
+      </c>
+      <c r="N276" s="5" t="n">
+        <v>3.17</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B277" s="2" t="inlineStr">
+        <is>
+          <t>特定處置保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C277" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+特定處置保險金的給付規定如下：  
+1. 被保險人因疾病或傷害，經醫師診斷必須於醫院或診所接受附表二所列之特定處置治療且已接受處置者，保險公司將依保險單記載的「保險金額」，乘以特定處置日當年度的「增額係數」，再乘以特定處置給付倍數，給付「特定處置保險金」。  
+2. 同一次處置治療中，若於同一治療位置接受二項以上特定處置項目，僅給付特定處置給付倍數最高的特定處置項目。  
+3. 若被保險人所接受的處置未載明於附表二所列之特定處置項目，保險公司不負給付特定處置保險金的責任。  
+4. 同一保險單年度的「特定處置保險金」給付次數以十次為限。
+條文依據：  
+- [第十四條 特定處置保險金]</t>
+        </is>
+      </c>
+      <c r="D277" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 特定處置保險金 | 第十五條 意外創傷縫合處置保險金 | 附表二：特定處置項目及給付倍數表 | 第五條 保險範圍 | 附表三：意外創傷縫合處置項目及給付倍數表</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F277" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+特定處置保險金的給付規定如下：  
+1. 被保險人因疾病或傷害，經醫師診斷必須於醫院或診所接受附表二所列之特定處置治療且已接受處置者，保險公司將依保險單記載的「保險金額」，乘以特定處置日當年度的「增額係數」，再乘以特定處置給付倍數，給付「特定處置保險金」。  
+2. 同一次處置治療中，若於同一治療位置接受二項以上特定處置項目，僅給付特定處置給付倍數最高的特定處置項目。  
+3. 若被保險人所接受的處置未載明於附表二所列之特定處置項目，保險公司不負給付特定處置保險金的責任。  
+4. 同一保險單年度的「特定處置保險金」給付次數以十次為限。
+條文依據：  
+- [第十四條 特定處置保險金]</t>
+        </is>
+      </c>
+      <c r="G277" s="2" t="inlineStr"/>
+      <c r="H277" s="2" t="inlineStr"/>
+      <c r="I277" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.989582, "neutral": 0.00941, "contradiction": 0.001008, "factuality": 0.998992, "C_fact": 0.998992}, "C_conf": 0.999}</t>
+        </is>
+      </c>
+      <c r="J277" s="5" t="n"/>
+      <c r="K277" s="5" t="n">
+        <v>0.998992</v>
+      </c>
+      <c r="L277" s="5" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:08:29</t>
+        </is>
+      </c>
+      <c r="N277" s="5" t="n">
+        <v>3.56</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B278" s="2" t="inlineStr">
+        <is>
+          <t>意外創傷縫合處置保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C278" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外創傷縫合處置保險金的給付規定如下：  
+1. 被保險人因意外傷害事故，於醫院或診所接受附表三所列的意外創傷縫合處置治療者，本公司將依保險單所記載的「保險金額」，乘以意外創傷縫合處置日當年度的「增額係數」，再乘以意外創傷縫合處置給付倍數，給付保險金。  
+2. 同一次意外傷害事故，僅就被保險人接受創傷縫合處置的傷口最大者給付保險金，且以給付一次為限。  
+3. 若被保險人因同一意外傷害事故，已申領「住院手術醫療保險金」或「門診手術醫療保險金」，則不再給付意外創傷縫合處置保險金。
+條文依據：  
+- [第十五條 意外創傷縫合處置保險金]</t>
+        </is>
+      </c>
+      <c r="D278" s="2" t="inlineStr">
+        <is>
+          <t>第十五條 意外創傷縫合處置保險金 | 附表三：意外創傷縫合處置項目及給付倍數表 | 第十四條 特定處置保險金 | 第二十條 除外責任（一） | 第十三條 意外住院手術醫療保險金 | 附表二：特定處置項目及給付倍數表</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F278" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外創傷縫合處置保險金的給付規定如下：  
+1. 被保險人因意外傷害事故，於醫院或診所接受附表三所列的意外創傷縫合處置治療者，本公司將依保險單所記載的「保險金額」，乘以意外創傷縫合處置日當年度的「增額係數」，再乘以意外創傷縫合處置給付倍數，給付保險金。  
+2. 同一次意外傷害事故，僅就被保險人接受創傷縫合處置的傷口最大者給付保險金，且以給付一次為限。  
+3. 若被保險人因同一意外傷害事故，已申領「住院手術醫療保險金」或「門診手術醫療保險金」，則不再給付意外創傷縫合處置保險金。
+條文依據：  
+- [第十五條 意外創傷縫合處置保險金]</t>
+        </is>
+      </c>
+      <c r="G278" s="2" t="inlineStr"/>
+      <c r="H278" s="2" t="inlineStr"/>
+      <c r="I278" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.990107, "neutral": 0.009035, "contradiction": 0.000859, "factuality": 0.999141, "C_fact": 0.999141}, "C_conf": 0.9991}</t>
+        </is>
+      </c>
+      <c r="J278" s="5" t="n"/>
+      <c r="K278" s="5" t="n">
+        <v>0.9991409999999999</v>
+      </c>
+      <c r="L278" s="5" t="n">
+        <v>0.9991</v>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:08:33</t>
+        </is>
+      </c>
+      <c r="N278" s="5" t="n">
+        <v>3.76</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B279" s="2" t="inlineStr">
+        <is>
+          <t>醫療保險金給付總額之上限</t>
+        </is>
+      </c>
+      <c r="C279" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+醫療保險金給付總額之上限為保險單上所記載的「保險金額」之一千五百倍，且不包含其他附約、附加條款及批註條款。  
+條文依據：  
+- [第十六條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="D279" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 醫療保險金給付總額之上限 | 第十二條 門診手術醫療保險金 | 第五條 保險範圍 | 第十一條 住院手術醫療保險金 | 第十三條 意外住院手術醫療保險金 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F279" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+醫療保險金給付總額之上限為保險單上所記載的「保險金額」之一千五百倍，且不包含其他附約、附加條款及批註條款。  
+條文依據：  
+- [第十六條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="G279" s="2" t="inlineStr"/>
+      <c r="H279" s="2" t="inlineStr"/>
+      <c r="I279" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.996964, "neutral": 0.002863, "contradiction": 0.000174, "factuality": 0.999826, "C_fact": 0.999826}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J279" s="5" t="n"/>
+      <c r="K279" s="5" t="n">
+        <v>0.999826</v>
+      </c>
+      <c r="L279" s="5" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:08:35</t>
+        </is>
+      </c>
+      <c r="N279" s="5" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B280" s="2" t="inlineStr">
+        <is>
+          <t>祝壽保險金的領取規定為何?</t>
+        </is>
+      </c>
+      <c r="C280" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+祝壽保險金的領取規定如下：  
+1. 被保險人需於本契約有效期間且保險年齡到達九十九歲之保險單週年日仍生存，方可申領祝壽保險金。  
+2. 受益人申領祝壽保險金時，需檢具以下文件：  
+   - 保險單或其謄本  
+   - 保險金申請書  
+   - 受益人的身分證明  
+條文依據：  
+- [第十七條 祝壽保險金]  
+- [第二十六條 祝壽保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D280" s="2" t="inlineStr">
+        <is>
+          <t>第十七條 祝壽保險金 | 第二十六條 祝壽保險金的申領 | 第十一條至第十五條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | 第二十三條 保險事故的通知與保險金的申請時間 | 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F280" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+祝壽保險金的領取規定如下：  
+1. 被保險人需於本契約有效期間且保險年齡到達九十九歲之保險單週年日仍生存，方可申領祝壽保險金。  
+2. 受益人申領祝壽保險金時，需檢具以下文件：  
+   - 保險單或其謄本  
+   - 保險金申請書  
+   - 受益人的身分證明  
+條文依據：  
+- [第十七條 祝壽保險金]  
+- [第二十六條 祝壽保險金的申領]</t>
+        </is>
+      </c>
+      <c r="G280" s="2" t="inlineStr"/>
+      <c r="H280" s="2" t="inlineStr"/>
+      <c r="I280" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.998662, "neutral": 0.001196, "contradiction": 0.000141, "factuality": 0.999859, "C_fact": 0.999859}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J280" s="5" t="n"/>
+      <c r="K280" s="5" t="n">
+        <v>0.9998590000000001</v>
+      </c>
+      <c r="L280" s="5" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:08:38</t>
+        </is>
+      </c>
+      <c r="N280" s="5" t="n">
+        <v>2.62</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B281" s="2" t="inlineStr">
+        <is>
+          <t>身故時領取保險金有什麼規則?</t>
+        </is>
+      </c>
+      <c r="C281" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+身故時領取保險金的規則如下：  
+1. 被保險人於本契約有效期間內身故者，本公司按「當年度保險金額」給付「身故保險金」。  
+2. 若被保險人於本契約有效期間且實際年齡未滿十五足歲身故者，本公司退還「所繳保險費」予要保人，不適用「身故保險金」的約定。  
+3. 若被保險人於訂立契約時受監護宣告尚未撤銷，其身故保險金變更為喪葬費用保險金，且喪葬費用保險金額不得超過遺產稅喪葬費扣除額之半數，超過部分本公司不負給付責任，並退還超過部分的已繳保險費。  
+4. 若投保多家保險公司或多個保險契約，喪葬費用保險金額合計超過限額時，各保險公司依比例分擔責任。  
+條文依據：  
+- [第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金]</t>
+        </is>
+      </c>
+      <c r="D281" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金 | 第二十七條 身故保險金或喪葬費用保險金的申領 | 第十一條至第十五條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | 第二十一條 除外責任（二） | 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F281" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+身故時領取保險金的規則如下：  
+1. 被保險人於本契約有效期間內身故者，本公司按「當年度保險金額」給付「身故保險金」。  
+2. 若被保險人於本契約有效期間且實際年齡未滿十五足歲身故者，本公司退還「所繳保險費」予要保人，不適用「身故保險金」的約定。  
+3. 若被保險人於訂立契約時受監護宣告尚未撤銷，其身故保險金變更為喪葬費用保險金，且喪葬費用保險金額不得超過遺產稅喪葬費扣除額之半數，超過部分本公司不負給付責任，並退還超過部分的已繳保險費。  
+4. 若投保多家保險公司或多個保險契約，喪葬費用保險金額合計超過限額時，各保險公司依比例分擔責任。  
+條文依據：  
+- [第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金]</t>
+        </is>
+      </c>
+      <c r="G281" s="2" t="inlineStr"/>
+      <c r="H281" s="2" t="inlineStr"/>
+      <c r="I281" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.952356, "neutral": 0.046949, "contradiction": 0.000695, "factuality": 0.999305, "C_fact": 0.999305}, "C_conf": 0.9993}</t>
+        </is>
+      </c>
+      <c r="J281" s="5" t="n"/>
+      <c r="K281" s="5" t="n">
+        <v>0.999305</v>
+      </c>
+      <c r="L281" s="5" t="n">
+        <v>0.9993</v>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:08:42</t>
+        </is>
+      </c>
+      <c r="N281" s="5" t="n">
+        <v>4.31</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B282" s="2" t="inlineStr">
+        <is>
+          <t>什麼情況下可以保費折減?</t>
+        </is>
+      </c>
+      <c r="C282" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人年齡達20歲（含）以上，使用保險公司指定程式並加入指定健康計劃，且於「指定日期」的會員等級符合進階會員或菁英會員（或更高等級）標準之一者，可享次一保險單年度的保費折減。折減比例為進階會員2%，菁英會員或更高等級3%。但豁免或復效的保險費不適用此折減約定。
+條文依據：  
+- [第十九條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="D282" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 健康促進保險費折減 | 第三十條 保險金額之減少 | 第二十條 除外責任（一） | 第三十一條 投保年齡的計算及錯誤的處理 | 第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F282" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人年齡達20歲（含）以上，使用保險公司指定程式並加入指定健康計劃，且於「指定日期」的會員等級符合進階會員或菁英會員（或更高等級）標準之一者，可享次一保險單年度的保費折減。折減比例為進階會員2%，菁英會員或更高等級3%。但豁免或復效的保險費不適用此折減約定。
+條文依據：  
+- [第十九條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="G282" s="2" t="inlineStr"/>
+      <c r="H282" s="2" t="inlineStr"/>
+      <c r="I282" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.994624, "neutral": 0.005154, "contradiction": 0.000222, "factuality": 0.999778, "C_fact": 0.999778}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J282" s="5" t="n"/>
+      <c r="K282" s="5" t="n">
+        <v>0.9997779999999999</v>
+      </c>
+      <c r="L282" s="5" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:08:46</t>
+        </is>
+      </c>
+      <c r="N282" s="5" t="n">
+        <v>3.57</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B283" s="2" t="inlineStr">
+        <is>
+          <t>角膜切除術是否可以申請理賠?</t>
+        </is>
+      </c>
+      <c r="C283" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+角膜切除術可以申請理賠，其手術項目編號為1305，給付倍數為5。  
+條文依據：  
+- 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="D283" s="2" t="inlineStr">
+        <is>
+          <t>附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F283" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+角膜切除術可以申請理賠，其手術項目編號為1305，給付倍數為5。  
+條文依據：  
+- 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="G283" s="2" t="inlineStr"/>
+      <c r="H283" s="2" t="inlineStr"/>
+      <c r="I283" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.106276, "neutral": 0.887582, "contradiction": 0.006142, "factuality": 0.993858, "C_fact": 0.993858}, "C_conf": 0.9939}</t>
+        </is>
+      </c>
+      <c r="J283" s="5" t="n"/>
+      <c r="K283" s="5" t="n">
+        <v>0.993858</v>
+      </c>
+      <c r="L283" s="5" t="n">
+        <v>0.9939</v>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:08:50</t>
+        </is>
+      </c>
+      <c r="N283" s="5" t="n">
+        <v>3.71</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B284" s="2" t="inlineStr">
+        <is>
+          <t>白內障手術是否可以申請理賠?</t>
+        </is>
+      </c>
+      <c r="C284" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+白內障手術是否可以申請理賠需視手術是否符合附表一所列的手術項目及相關條件。若白內障手術屬於附表一中「晶體切除術合併玻璃體切除術」（項目編號1367，給付倍數30）或「移位晶體摘除合併玻璃體切除術」（項目編號1368，給付倍數30），且不屬於除外責任條款規定的範圍，則可申請理賠。若手術不在附表一中，則需與保險公司協議比照附表一內的手術項目決定給付倍數。
+條文依據：  
+- [第十二條 門診手術醫療保險金]  
+- [附表一：手術項目與給付倍數]</t>
+        </is>
+      </c>
+      <c r="D284" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 門診手術醫療保險金 | 第二十條 除外責任（一） | 附表一：手術項目與給付倍數 | payout_items | 第十一條 住院手術醫療保險金</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F284" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+白內障手術是否可以申請理賠需視手術是否符合附表一所列的手術項目及相關條件。若白內障手術屬於附表一中「晶體切除術合併玻璃體切除術」（項目編號1367，給付倍數30）或「移位晶體摘除合併玻璃體切除術」（項目編號1368，給付倍數30），且不屬於除外責任條款規定的範圍，則可申請理賠。若手術不在附表一中，則需與保險公司協議比照附表一內的手術項目決定給付倍數。
+條文依據：  
+- [第十二條 門診手術醫療保險金]  
+- [附表一：手術項目與給付倍數]</t>
+        </is>
+      </c>
+      <c r="G284" s="2" t="inlineStr"/>
+      <c r="H284" s="2" t="inlineStr"/>
+      <c r="I284" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.199207, "neutral": 0.747607, "contradiction": 0.053186, "factuality": 0.946814, "C_fact": 0.946814}, "C_conf": 0.9468}</t>
+        </is>
+      </c>
+      <c r="J284" s="5" t="n"/>
+      <c r="K284" s="5" t="n">
+        <v>0.946814</v>
+      </c>
+      <c r="L284" s="5" t="n">
+        <v>0.9468</v>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:08:54</t>
+        </is>
+      </c>
+      <c r="N284" s="5" t="n">
+        <v>3.82</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B285" s="2" t="inlineStr">
+        <is>
+          <t>保障範圍包括哪些項目？</t>
+        </is>
+      </c>
+      <c r="C285" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括：意外事故身故保險金或喪葬費用保險金、意外事故失能保險金、每月生活照護保險金、重大燒燙傷保險金、意外骨折保險金、傷害醫療日額保險金、意外創傷縫合處置保險金。
+條文依據：  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="D285" s="2" t="inlineStr">
+        <is>
+          <t>payout_items | 第五條 保險範圍 | 第十五條 每月生活照護保險金的給付 | 第三十條 不保事項 | 附表二：失能程度與保險金給付表</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F285" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括：意外事故身故保險金或喪葬費用保險金、意外事故失能保險金、每月生活照護保險金、重大燒燙傷保險金、意外骨折保險金、傷害醫療日額保險金、意外創傷縫合處置保險金。
+條文依據：  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="G285" s="2" t="inlineStr"/>
+      <c r="H285" s="2" t="inlineStr"/>
+      <c r="I285" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.997935, "neutral": 0.001907, "contradiction": 0.000158, "factuality": 0.999842, "C_fact": 0.999842}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J285" s="5" t="n"/>
+      <c r="K285" s="5" t="n">
+        <v>0.999842</v>
+      </c>
+      <c r="L285" s="5" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:08:56</t>
+        </is>
+      </c>
+      <c r="N285" s="5" t="n">
+        <v>2.73</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B286" s="2" t="inlineStr">
+        <is>
+          <t>發生意外事故身故，理賠內容為何?</t>
+        </is>
+      </c>
+      <c r="C286" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外事故身故的理賠內容包括「意外事故身故保險金」或「喪葬費用保險金」，依意外傷害事故的種類給付以下金額：  
+1. 一般意外傷害事故：「傷害醫療保險金日額」的五百倍。  
+2. 特定意外傷害事故：「傷害醫療保險金日額」的一千倍。  
+若被保險人於意外傷害事故發生後超過一百八十日身故，但受益人能證明身故與該事故具有因果關係，本公司仍依約給付「意外事故身故保險金」，不受一百八十日限制。此外，若被保險人受監護宣告尚未撤銷，其理賠內容改為「喪葬費用保險金」，且喪葬費用保險金額不得超過遺產稅喪葬費扣除額之半數，超過部分不負給付責任。  
+條文依據：  
+- [第十二條 意外事故身故保險金或喪葬費用保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D286" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 意外事故身故保險金或喪葬費用保險金的給付 | 第十四條 保險給付的限制 | payout_items | 第十一條 契約的終止（二） | 第二十一條 失蹤處理</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F286" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外事故身故的理賠內容包括「意外事故身故保險金」或「喪葬費用保險金」，依意外傷害事故的種類給付以下金額：  
+1. 一般意外傷害事故：「傷害醫療保險金日額」的五百倍。  
+2. 特定意外傷害事故：「傷害醫療保險金日額」的一千倍。  
+若被保險人於意外傷害事故發生後超過一百八十日身故，但受益人能證明身故與該事故具有因果關係，本公司仍依約給付「意外事故身故保險金」，不受一百八十日限制。此外，若被保險人受監護宣告尚未撤銷，其理賠內容改為「喪葬費用保險金」，且喪葬費用保險金額不得超過遺產稅喪葬費扣除額之半數，超過部分不負給付責任。  
+條文依據：  
+- [第十二條 意外事故身故保險金或喪葬費用保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G286" s="2" t="inlineStr"/>
+      <c r="H286" s="2" t="inlineStr"/>
+      <c r="I286" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.995318, "neutral": 0.004491, "contradiction": 0.000192, "factuality": 0.999808, "C_fact": 0.999808}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J286" s="5" t="n"/>
+      <c r="K286" s="5" t="n">
+        <v>0.999808</v>
+      </c>
+      <c r="L286" s="5" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:09:01</t>
+        </is>
+      </c>
+      <c r="N286" s="5" t="n">
+        <v>4.65</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B287" s="2" t="inlineStr">
+        <is>
+          <t>意外事故失能保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C287" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外事故失能保險金的給付條件如下：  
+1. 被保險人於契約有效期間內遭受意外傷害事故，並自事故發生之日起一百八十日內致成附表二所列失能程度之一者，本公司依意外傷害事故種類及失能程度，按以下約定金額給付：  
+   - 一般意外傷害事故：「傷害醫療保險金日額」的五百倍乘以附表二給付比例。  
+   - 特定意外傷害事故：「傷害醫療保險金日額」的一千倍乘以附表二給付比例。  
+2. 若被保險人自事故發生之日起超過一百八十日致成失能，受益人能證明失能與事故具有因果關係者，本公司仍依上述規定給付，不受一百八十日限制。  
+3. 同一事故致成附表二所列二項以上失能程度時，給付各項失能保險金之和以事故種類的以下金額為上限：  
+   - 一般意外傷害事故：「傷害醫療保險金日額」的五百倍。  
+   - 特定意外傷害事故：「傷害醫療保險金日額」的一千倍。  
+   若不同失能項目屬於同一手或同一足，僅給付一項失能保險金；失能等級不同時，給付較嚴重項目。  
+4. 若合併以前失能，僅按較嚴重項目給付，但以前失能視同已給付，應扣除之。若扣除後金額低於單獨請領金額者，不適用合併約定。  
+5. 同一保險單年度內不同事故申領失能保險金時，累計給付金額最高以以下金額為限：  
+   - 一般意外傷害事故：「傷害醫療保險金日額」的五百倍。  
+   - 特定意外傷害事故：「傷害醫療保險金日額」的一千倍。  
+6. 不同事故申領失能保險金時，累計給付金額最高以「傷害醫療保險金日額」的一千二百倍為限。
+條文依據：  
+- [第十三條 意外事故失能保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D287" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 意外事故失能保險金的給付 | 第十五條 每月生活照護保險金的給付 | 第十四條 保險給付的限制 | 第十二條 意外事故身故保險金或喪葬費用保險金的給付 | 第二十三條 意外事故失能保險金的申領 | 附表二：失能程度與保險金給付表</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F287" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外事故失能保險金的給付條件如下：  
+1. 被保險人於契約有效期間內遭受意外傷害事故，並自事故發生之日起一百八十日內致成附表二所列失能程度之一者，本公司依意外傷害事故種類及失能程度，按以下約定金額給付：  
+   - 一般意外傷害事故：「傷害醫療保險金日額」的五百倍乘以附表二給付比例。  
+   - 特定意外傷害事故：「傷害醫療保險金日額」的一千倍乘以附表二給付比例。  
+2. 若被保險人自事故發生之日起超過一百八十日致成失能，受益人能證明失能與事故具有因果關係者，本公司仍依上述規定給付，不受一百八十日限制。  
+3. 同一事故致成附表二所列二項以上失能程度時，給付各項失能保險金之和以事故種類的以下金額為上限：  
+   - 一般意外傷害事故：「傷害醫療保險金日額」的五百倍。  
+   - 特定意外傷害事故：「傷害醫療保險金日額」的一千倍。  
+   若不同失能項目屬於同一手或同一足，僅給付一項失能保險金；失能等級不同時，給付較嚴重項目。  
+4. 若合併以前失能，僅按較嚴重項目給付，但以前失能視同已給付，應扣除之。若扣除後金額低於單獨請領金額者，不適用合併約定。  
+5. 同一保險單年度內不同事故申領失能保險金時，累計給付金額最高以以下金額為限：  
+   - 一般意外傷害事故：「傷害醫療保險金日額」的五百倍。  
+   - 特定意外傷害事故：「傷害醫療保險金日額」的一千倍。  
+6. 不同事故申領失能保險金時，累計給付金額最高以「傷害醫療保險金日額」的一千二百倍為限。
+條文依據：  
+- [第十三條 意外事故失能保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G287" s="2" t="inlineStr"/>
+      <c r="H287" s="2" t="inlineStr"/>
+      <c r="I287" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.594904, "neutral": 0.399708, "contradiction": 0.005387, "factuality": 0.994613, "C_fact": 0.994613}, "C_conf": 0.9946}</t>
+        </is>
+      </c>
+      <c r="J287" s="5" t="n"/>
+      <c r="K287" s="5" t="n">
+        <v>0.994613</v>
+      </c>
+      <c r="L287" s="5" t="n">
+        <v>0.9946</v>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:09:09</t>
+        </is>
+      </c>
+      <c r="N287" s="5" t="n">
+        <v>7.67</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B288" s="2" t="inlineStr">
+        <is>
+          <t>每月生活照護保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C288" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+每月生活照護保險金的給付條件如下：  
+1. 被保險人於契約有效期間內遭受「意外傷害事故」，並於事故發生後180日內致成附表二所列第一級至第六級失能程度之一時，本公司自失能診斷確定當日起，按「傷害醫療保險金日額」的20倍乘以附表二給付比例所得之金額，按月給付，最多以12個月為限。  
+2. 若失能診斷確定後的前四個「失能診斷確定週年日」，契約仍有效且被保險人仍生存，本公司自各該週年日起，依相同計算方式再給付，最多以12個月為限。  
+3. 若被保險人於事故發生後超過180日才致成失能，受益人需證明失能與事故具有因果關係，本公司仍可依上述規定給付，不受180日限制。  
+4. 同一事故若導致多項失能，僅給付較嚴重項目，且最高以「傷害醫療保險金日額」的20倍為限。  
+5. 累計給付金額最高以「傷害醫療保險金日額」的1200倍為限。  
+條文依據：  
+- [第十五條 每月生活照護保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D288" s="2" t="inlineStr">
+        <is>
+          <t>第二十四條 每月生活照護保險金的申領 | 第十五條 每月生活照護保險金的給付 | payout_items | 第十八條 傷害醫療日額保險金的給付 | 第五條 保險範圍 | 附表二：失能程度與保險金給付表 | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F288" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+每月生活照護保險金的給付條件如下：  
+1. 被保險人於契約有效期間內遭受「意外傷害事故」，並於事故發生後180日內致成附表二所列第一級至第六級失能程度之一時，本公司自失能診斷確定當日起，按「傷害醫療保險金日額」的20倍乘以附表二給付比例所得之金額，按月給付，最多以12個月為限。  
+2. 若失能診斷確定後的前四個「失能診斷確定週年日」，契約仍有效且被保險人仍生存，本公司自各該週年日起，依相同計算方式再給付，最多以12個月為限。  
+3. 若被保險人於事故發生後超過180日才致成失能，受益人需證明失能與事故具有因果關係，本公司仍可依上述規定給付，不受180日限制。  
+4. 同一事故若導致多項失能，僅給付較嚴重項目，且最高以「傷害醫療保險金日額」的20倍為限。  
+5. 累計給付金額最高以「傷害醫療保險金日額」的1200倍為限。  
+條文依據：  
+- [第十五條 每月生活照護保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G288" s="2" t="inlineStr"/>
+      <c r="H288" s="2" t="inlineStr"/>
+      <c r="I288" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.410767, "neutral": 0.561789, "contradiction": 0.027444, "factuality": 0.972556, "C_fact": 0.972556}, "C_conf": 0.9726}</t>
+        </is>
+      </c>
+      <c r="J288" s="5" t="n"/>
+      <c r="K288" s="5" t="n">
+        <v>0.972556</v>
+      </c>
+      <c r="L288" s="5" t="n">
+        <v>0.9726</v>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:09:18</t>
+        </is>
+      </c>
+      <c r="N288" s="5" t="n">
+        <v>8.380000000000001</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B289" s="2" t="inlineStr">
+        <is>
+          <t>重大燒燙傷保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C289" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+重大燒燙傷保險金的給付條件為：被保險人於契約有效期間內因「意外傷害事故」導致燒燙傷，且經診斷符合「重大燒燙傷」標準者，本公司將按「傷害醫療保險金日額」的二百五十倍給付「重大燒燙傷保險金」。此保險金的給付以一次為限。
+條文依據：  
+- [第十六條 重大燒燙傷保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D289" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 重大燒燙傷保險金的給付 | 第二十五條 重大燒燙傷保險金的申領 | 第五條 保險範圍 | payout_items | 第二十九條 除外責任（原因）</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F289" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+重大燒燙傷保險金的給付條件為：被保險人於契約有效期間內因「意外傷害事故」導致燒燙傷，且經診斷符合「重大燒燙傷」標準者，本公司將按「傷害醫療保險金日額」的二百五十倍給付「重大燒燙傷保險金」。此保險金的給付以一次為限。
+條文依據：  
+- [第十六條 重大燒燙傷保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G289" s="2" t="inlineStr"/>
+      <c r="H289" s="2" t="inlineStr"/>
+      <c r="I289" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.997119, "neutral": 0.002757, "contradiction": 0.000125, "factuality": 0.999875, "C_fact": 0.999875}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J289" s="5" t="n"/>
+      <c r="K289" s="5" t="n">
+        <v>0.999875</v>
+      </c>
+      <c r="L289" s="5" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:09:24</t>
+        </is>
+      </c>
+      <c r="N289" s="5" t="n">
+        <v>5.74</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B290" s="2" t="inlineStr">
+        <is>
+          <t>意外骨折保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C290" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外骨折保險金的給付條件如下：  
+1. 被保險人於契約有效期間內遭受「意外傷害事故」，自事故發生日起一百八十日內，經合格醫院或診所診斷為附表三骨折別表所列骨折項目之一（含不完全骨折及骨骼龜裂），本公司按「傷害醫療保險金日額」的二倍給付意外骨折保險金。  
+2. 若超過一百八十日診斷確定骨折，受益人需證明骨折與事故具有因果關係，仍可依上述規定給付。  
+3. 同一意外傷害事故僅給付一次意外骨折保險金。  
+4. 若骨折非屬附表三骨折別表所列項目，需由本公司與被保險人協議核付；但若骨折部位為骨折別表內明訂不給付之部位，則本公司不負給付責任。
+條文依據：  
+- [第十七條 意外骨折保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D290" s="2" t="inlineStr">
+        <is>
+          <t>第十七條 意外骨折保險金的給付 | 第十八條 傷害醫療日額保險金的給付 | 第二十六條 意外骨折保險金的申領 | 第十三條 意外事故失能保險金的給付 | 第十九條 意外創傷縫合處置保險金的給付 | 附表二：失能程度與保險金給付表 | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F290" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外骨折保險金的給付條件如下：  
+1. 被保險人於契約有效期間內遭受「意外傷害事故」，自事故發生日起一百八十日內，經合格醫院或診所診斷為附表三骨折別表所列骨折項目之一（含不完全骨折及骨骼龜裂），本公司按「傷害醫療保險金日額」的二倍給付意外骨折保險金。  
+2. 若超過一百八十日診斷確定骨折，受益人需證明骨折與事故具有因果關係，仍可依上述規定給付。  
+3. 同一意外傷害事故僅給付一次意外骨折保險金。  
+4. 若骨折非屬附表三骨折別表所列項目，需由本公司與被保險人協議核付；但若骨折部位為骨折別表內明訂不給付之部位，則本公司不負給付責任。
+條文依據：  
+- [第十七條 意外骨折保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G290" s="2" t="inlineStr"/>
+      <c r="H290" s="2" t="inlineStr"/>
+      <c r="I290" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.994522, "neutral": 0.005088, "contradiction": 0.00039, "factuality": 0.99961, "C_fact": 0.99961}, "C_conf": 0.9996}</t>
+        </is>
+      </c>
+      <c r="J290" s="5" t="n"/>
+      <c r="K290" s="5" t="n">
+        <v>0.99961</v>
+      </c>
+      <c r="L290" s="5" t="n">
+        <v>0.9996</v>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:09:28</t>
+        </is>
+      </c>
+      <c r="N290" s="5" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B291" s="2" t="inlineStr">
+        <is>
+          <t>傷害醫療日額保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C291" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+傷害醫療日額保險金的給付條件如下：  
+1. 被保險人於契約有效期間內遭受「意外傷害事故」，自事故發生日起一百八十日內於「醫院」接受住院治療者，本公司按「傷害醫療保險金日額」乘以實際住院日數給付，最高以九十日為限。  
+2. 若治療超過一百八十日，受益人能證明治療與事故具有因果關係者，仍可依規定給付，不受一百八十日限制。  
+3. 若因骨折未住院或住院日數未達附表三骨折別表所訂日數，未住院部分按骨折別表所訂日數乘以「傷害醫療保險金日額」的二分之一給付，合計給付日數以骨折別表所訂日數為上限。  
+4. 骨折類型給付：完全骨折按骨折別表日數給付；不完全骨折按完全骨折日數二分之一給付；骨骼龜裂按完全骨折日數四分之一給付。同時蒙受多項骨折時，僅給付較高等級的保險金。
+條文依據：  
+- [第十八條 傷害醫療日額保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D291" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 傷害醫療日額保險金的給付 | 第二十七條 傷害醫療日額保險金的申領 | 第十五條 每月生活照護保險金的給付 | 第三十四條 傷害醫療保險金日額之減少 | 第十九條 意外創傷縫合處置保險金的給付 | 附表二：失能程度與保險金給付表 | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F291" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+傷害醫療日額保險金的給付條件如下：  
+1. 被保險人於契約有效期間內遭受「意外傷害事故」，自事故發生日起一百八十日內於「醫院」接受住院治療者，本公司按「傷害醫療保險金日額」乘以實際住院日數給付，最高以九十日為限。  
+2. 若治療超過一百八十日，受益人能證明治療與事故具有因果關係者，仍可依規定給付，不受一百八十日限制。  
+3. 若因骨折未住院或住院日數未達附表三骨折別表所訂日數，未住院部分按骨折別表所訂日數乘以「傷害醫療保險金日額」的二分之一給付，合計給付日數以骨折別表所訂日數為上限。  
+4. 骨折類型給付：完全骨折按骨折別表日數給付；不完全骨折按完全骨折日數二分之一給付；骨骼龜裂按完全骨折日數四分之一給付。同時蒙受多項骨折時，僅給付較高等級的保險金。
+條文依據：  
+- [第十八條 傷害醫療日額保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G291" s="2" t="inlineStr"/>
+      <c r="H291" s="2" t="inlineStr"/>
+      <c r="I291" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.908464, "neutral": 0.090943, "contradiction": 0.000593, "factuality": 0.999407, "C_fact": 0.999407}, "C_conf": 0.9994}</t>
+        </is>
+      </c>
+      <c r="J291" s="5" t="n"/>
+      <c r="K291" s="5" t="n">
+        <v>0.999407</v>
+      </c>
+      <c r="L291" s="5" t="n">
+        <v>0.9994</v>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:09:35</t>
+        </is>
+      </c>
+      <c r="N291" s="5" t="n">
+        <v>5.36</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B292" s="2" t="inlineStr">
+        <is>
+          <t>意外創傷縫合處置保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C292" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外創傷縫合處置保險金的給付條件為：被保險人於契約有效期間內遭受「意外傷害事故」，並於「醫院」或「診所」經醫師診斷必須接受創傷縫合處置治療且已接受縫合處置者，本公司按「傷害醫療保險金日額」給付該保險金。同一意外傷害事故僅給付一次。
+條文依據：  
+- [第十九條 意外創傷縫合處置保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D292" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 意外創傷縫合處置保險金的給付 | 第二十八條 意外創傷縫合處置保險金的申領 | 第五條 保險範圍 | 第十七條 意外骨折保險金的給付 | payout_items | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F292" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外創傷縫合處置保險金的給付條件為：被保險人於契約有效期間內遭受「意外傷害事故」，並於「醫院」或「診所」經醫師診斷必須接受創傷縫合處置治療且已接受縫合處置者，本公司按「傷害醫療保險金日額」給付該保險金。同一意外傷害事故僅給付一次。
+條文依據：  
+- [第十九條 意外創傷縫合處置保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G292" s="2" t="inlineStr"/>
+      <c r="H292" s="2" t="inlineStr"/>
+      <c r="I292" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.996712, "neutral": 0.003178, "contradiction": 0.000111, "factuality": 0.999889, "C_fact": 0.999889}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J292" s="5" t="n"/>
+      <c r="K292" s="5" t="n">
+        <v>0.999889</v>
+      </c>
+      <c r="L292" s="5" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:09:38</t>
+        </is>
+      </c>
+      <c r="N292" s="5" t="n">
+        <v>3.39</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B293" s="2" t="inlineStr">
+        <is>
+          <t>因意外導致視力衰退，是否能申請理賠?</t>
+        </is>
+      </c>
+      <c r="C293" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+因意外導致視力衰退是否能申請理賠，需符合以下條件：  
+1. 視力永久在萬國式視力表0.02以下，或符合失明的定義（包括眼球喪失、摘出、僅能辨明暗或辨眼前一公尺以內手動或辨眼前五公分以內指數）。  
+2. 以自傷害之日起經過六個月的治療為判定原則，但若屬眼球摘出等明顯無法復原的情況，則不受此限。  
+若符合上述條件，則可申請理賠。  
+條文依據：  
+- 註2</t>
+        </is>
+      </c>
+      <c r="D293" s="2" t="inlineStr">
+        <is>
+          <t>第二十三條 意外事故失能保險金的申領 | 第十三條 意外事故失能保險金的給付 | 註2： | 第三十條 不保事項 | 第二十六條 意外骨折保險金的申領 | 附表二：失能程度與保險金給付表</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F293" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+因意外導致視力衰退是否能申請理賠，需符合以下條件：  
+1. 視力永久在萬國式視力表0.02以下，或符合失明的定義（包括眼球喪失、摘出、僅能辨明暗或辨眼前一公尺以內手動或辨眼前五公分以內指數）。  
+2. 以自傷害之日起經過六個月的治療為判定原則，但若屬眼球摘出等明顯無法復原的情況，則不受此限。  
+若符合上述條件，則可申請理賠。  
+條文依據：  
+- 註2</t>
+        </is>
+      </c>
+      <c r="G293" s="2" t="inlineStr"/>
+      <c r="H293" s="2" t="inlineStr"/>
+      <c r="I293" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.884295, "neutral": 0.112349, "contradiction": 0.003356, "factuality": 0.996644, "C_fact": 0.996644}, "C_conf": 0.9966}</t>
+        </is>
+      </c>
+      <c r="J293" s="5" t="n"/>
+      <c r="K293" s="5" t="n">
+        <v>0.996644</v>
+      </c>
+      <c r="L293" s="5" t="n">
+        <v>0.9966</v>
+      </c>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:09:42</t>
+        </is>
+      </c>
+      <c r="N293" s="5" t="n">
+        <v>3.93</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B294" s="2" t="inlineStr">
+        <is>
+          <t>肋骨骨折是否可以申請理賠?理賠金額為多少?</t>
+        </is>
+      </c>
+      <c r="C294" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+肋骨骨折可以申請理賠，理賠金額需依肋骨骨折的情形判定：  
+1. 若肋骨完全骨折且未住院治療，依附表三骨折別表所訂日數（20天）乘以「傷害醫療保險金日額」的二分之一給付。  
+2. 若肋骨完全骨折且住院治療，依實際住院日數乘以「傷害醫療保險金日額」給付，但最高給付日數以附表三骨折別表所訂日數（20天）為限。  
+3. 若肋骨不完全骨折，按完全骨折日數（20天）的二分之一給付；若肋骨龜裂，按完全骨折日數的四分之一給付。  
+條文依據：  
+- [第十八條 傷害醫療日額保險金的給付]  
+- [附表三：骨折別表]</t>
+        </is>
+      </c>
+      <c r="D294" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 傷害醫療日額保險金的給付 | 第十七條 意外骨折保險金的給付 | 第二十六條 意外骨折保險金的申領 | 第三十條 不保事項 | 第五條 保險範圍 | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F294" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+肋骨骨折可以申請理賠，理賠金額需依肋骨骨折的情形判定：  
+1. 若肋骨完全骨折且未住院治療，依附表三骨折別表所訂日數（20天）乘以「傷害醫療保險金日額」的二分之一給付。  
+2. 若肋骨完全骨折且住院治療，依實際住院日數乘以「傷害醫療保險金日額」給付，但最高給付日數以附表三骨折別表所訂日數（20天）為限。  
+3. 若肋骨不完全骨折，按完全骨折日數（20天）的二分之一給付；若肋骨龜裂，按完全骨折日數的四分之一給付。  
+條文依據：  
+- [第十八條 傷害醫療日額保險金的給付]  
+- [附表三：骨折別表]</t>
+        </is>
+      </c>
+      <c r="G294" s="2" t="inlineStr"/>
+      <c r="H294" s="2" t="inlineStr"/>
+      <c r="I294" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.91254, "neutral": 0.079938, "contradiction": 0.007522, "factuality": 0.992478, "C_fact": 0.992478}, "C_conf": 0.9925}</t>
+        </is>
+      </c>
+      <c r="J294" s="5" t="n"/>
+      <c r="K294" s="5" t="n">
+        <v>0.992478</v>
+      </c>
+      <c r="L294" s="5" t="n">
+        <v>0.9925</v>
+      </c>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:09:47</t>
+        </is>
+      </c>
+      <c r="N294" s="5" t="n">
+        <v>4.37</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B295" s="2" t="inlineStr">
+        <is>
+          <t>投保新鍾心滿福後，假設投保保額為100萬元，於第二保單年度接受「移植器官」，這樣可以領多少保險金?</t>
+        </is>
+      </c>
+      <c r="C295" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人於第二保險單年度（含）以後的有效期間內，初次診斷確定罹患「特定重大傷病」並接受「移植器官」，可獲得「重大傷病保險金」及「特定重大傷病保險金」。其中，「特定重大傷病保險金」的給付金額為保險金額的20%，即100萬元 × 20% = 20萬元。重大傷病保險金的具體金額則需依保險契約條款進一步確認。
+條文依據：  
+- [第十三條 特定重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D295" s="2" t="inlineStr">
+        <is>
+          <t>第十五條 滿期保險金的給付 | 第二條 名詞定義 | 附表一：全民健康保險重大傷病項目 | 第十三條 特定重大傷病保險金的給付 | 附表三：各保險單年度可借金額上限表 | payout_items | 第十七條 完全失能保險金的給付 | 附表二：完全失能程度表</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F295" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人於第二保險單年度（含）以後的有效期間內，初次診斷確定罹患「特定重大傷病」並接受「移植器官」，可獲得「重大傷病保險金」及「特定重大傷病保險金」。其中，「特定重大傷病保險金」的給付金額為保險金額的20%，即100萬元 × 20% = 20萬元。重大傷病保險金的具體金額則需依保險契約條款進一步確認。
+條文依據：  
+- [第十三條 特定重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G295" s="2" t="inlineStr"/>
+      <c r="H295" s="2" t="inlineStr"/>
+      <c r="I295" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.060211, "neutral": 0.829693, "contradiction": 0.110096, "factuality": 0.889904, "C_fact": 0.889904}, "C_conf": 0.8899}</t>
+        </is>
+      </c>
+      <c r="J295" s="5" t="n"/>
+      <c r="K295" s="5" t="n">
+        <v>0.889904</v>
+      </c>
+      <c r="L295" s="5" t="n">
+        <v>0.8899</v>
+      </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:09:52</t>
+        </is>
+      </c>
+      <c r="N295" s="5" t="n">
+        <v>4.47</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B296" s="2" t="inlineStr">
+        <is>
+          <t>投保新鍾心滿福後，若要理賠重大傷病保險金，一定要檢附全民健保開立的重大傷病證明才能拿到保險金嗎?</t>
+        </is>
+      </c>
+      <c r="C296" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不一定。若被保險人已取得一家「區域醫院」層級以上（含）之醫療院所開立且符合投保當時「重大傷病範圍」的診斷書及當次「重大傷病」病歷摘要，視為重大傷病證明文件，免向全民健康保險保險人申請重大傷病證明即可申領保險金。此外，若因全民健康保險保險人變更或調整重大傷病項目導致無法取得重大傷病證明文件，或被保險人於重大傷病證明文件核發前身故，也可依條款規定檢附替代文件申領保險金。  
+條文依據：  
+- [第二十二條 重大傷病保險金、特定重大傷病保險金的申領]  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D296" s="2" t="inlineStr">
+        <is>
+          <t>第二十二條 重大傷病保險金、特定重大傷病保險金的申領 | other_metadata | 第十二條 重大傷病保險金的給付 | 附表一：全民健康保險重大傷病項目 | 第二條 名詞定義 | 第三十條 不保事項</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F296" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不一定。若被保險人已取得一家「區域醫院」層級以上（含）之醫療院所開立且符合投保當時「重大傷病範圍」的診斷書及當次「重大傷病」病歷摘要，視為重大傷病證明文件，免向全民健康保險保險人申請重大傷病證明即可申領保險金。此外，若因全民健康保險保險人變更或調整重大傷病項目導致無法取得重大傷病證明文件，或被保險人於重大傷病證明文件核發前身故，也可依條款規定檢附替代文件申領保險金。  
+條文依據：  
+- [第二十二條 重大傷病保險金、特定重大傷病保險金的申領]  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G296" s="2" t="inlineStr"/>
+      <c r="H296" s="2" t="inlineStr"/>
+      <c r="I296" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.019288, "neutral": 0.980193, "contradiction": 0.000519, "factuality": 0.999481, "C_fact": 0.999481}, "C_conf": 0.9995}</t>
+        </is>
+      </c>
+      <c r="J296" s="5" t="n"/>
+      <c r="K296" s="5" t="n">
+        <v>0.999481</v>
+      </c>
+      <c r="L296" s="5" t="n">
+        <v>0.9995000000000001</v>
+      </c>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:09:57</t>
+        </is>
+      </c>
+      <c r="N296" s="5" t="n">
+        <v>4.78</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B297" s="2" t="inlineStr">
+        <is>
+          <t>一定要有健保身分才能申請重大傷病理賠嗎？</t>
+        </is>
+      </c>
+      <c r="C297" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，被保險人若喪失全民健康保險被保險人資格，需先申請加保全民健康保險後，才能申領重大傷病保險金。然而，若重大傷病係因意外傷害事故所致，則不受此限制。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D297" s="2" t="inlineStr">
+        <is>
+          <t>第二十二條 重大傷病保險金、特定重大傷病保險金的申領 | 第十二條 重大傷病保險金的給付 | other_metadata | 第三十條 不保事項 | 第二條 名詞定義 | 附表一：全民健康保險重大傷病項目</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F297" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，被保險人若喪失全民健康保險被保險人資格，需先申請加保全民健康保險後，才能申領重大傷病保險金。然而，若重大傷病係因意外傷害事故所致，則不受此限制。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G297" s="2" t="inlineStr"/>
+      <c r="H297" s="2" t="inlineStr"/>
+      <c r="I297" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.001115, "neutral": 0.9981, "contradiction": 0.000785, "factuality": 0.999215, "C_fact": 0.999215}, "C_conf": 0.9992}</t>
+        </is>
+      </c>
+      <c r="J297" s="5" t="n"/>
+      <c r="K297" s="5" t="n">
+        <v>0.999215</v>
+      </c>
+      <c r="L297" s="5" t="n">
+        <v>0.9992</v>
+      </c>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:10:00</t>
+        </is>
+      </c>
+      <c r="N297" s="5" t="n">
+        <v>3.24</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B298" s="2" t="inlineStr">
+        <is>
+          <t>重大傷病的項目如果在投保後有新增，可以從優申請理賠嗎？</t>
+        </is>
+      </c>
+      <c r="C298" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以申請理賠，但需符合以下條件：重大傷病項目若在投保後新增，理賠範圍以「訂立時」及「有效期間內被保險人診斷確定當時」由中央衛生主管機關公告之最新項目為準。因此，新增項目若在被保險人診斷確定時已被公告，則可納入理賠範圍。
+條文依據：  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D298" s="2" t="inlineStr">
+        <is>
+          <t>附表一：全民健康保險重大傷病項目 | 第二條 名詞定義 | payout_items</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F298" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以申請理賠，但需符合以下條件：重大傷病項目若在投保後新增，理賠範圍以「訂立時」及「有效期間內被保險人診斷確定當時」由中央衛生主管機關公告之最新項目為準。因此，新增項目若在被保險人診斷確定時已被公告，則可納入理賠範圍。
+條文依據：  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G298" s="2" t="inlineStr"/>
+      <c r="H298" s="2" t="inlineStr"/>
+      <c r="I298" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.996639, "neutral": 0.003094, "contradiction": 0.000267, "factuality": 0.999733, "C_fact": 0.999733}, "C_conf": 0.9997}</t>
+        </is>
+      </c>
+      <c r="J298" s="5" t="n"/>
+      <c r="K298" s="5" t="n">
+        <v>0.999733</v>
+      </c>
+      <c r="L298" s="5" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:10:04</t>
+        </is>
+      </c>
+      <c r="N298" s="5" t="n">
+        <v>4.11</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B299" s="2" t="inlineStr">
+        <is>
+          <t>我的保單之前有停效，在復效後五天被診斷出重大疾病是否可申請理賠？</t>
+        </is>
+      </c>
+      <c r="C299" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以申請理賠，但需符合以下條件：  
+1. 復效後的契約有效期間內，被保險人經醫院醫師初次診斷確定罹患「重大傷病」。  
+2. 若重大傷病係因意外傷害事故所致，則不受等待期間限制；若非因意外傷害事故，則需等待期間屆滿翌日或復效日起才能申請理賠。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D299" s="2" t="inlineStr">
+        <is>
+          <t>第八條 本契約效力的恢復 | 第三十條 不保事項 | 第五條 保險範圍 | other_metadata | 第二條 名詞定義 | 第十二條 重大傷病保險金的給付 | 第二十二條 重大傷病保險金、特定重大傷病保險金的申領 | 附表一：全民健康保險重大傷病項目</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F299" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以申請理賠，但需符合以下條件：  
+1. 復效後的契約有效期間內，被保險人經醫院醫師初次診斷確定罹患「重大傷病」。  
+2. 若重大傷病係因意外傷害事故所致，則不受等待期間限制；若非因意外傷害事故，則需等待期間屆滿翌日或復效日起才能申請理賠。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G299" s="2" t="inlineStr"/>
+      <c r="H299" s="2" t="inlineStr"/>
+      <c r="I299" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.492903, "neutral": 0.476144, "contradiction": 0.030953, "factuality": 0.969047, "C_fact": 0.969047}, "C_conf": 0.969}</t>
+        </is>
+      </c>
+      <c r="J299" s="5" t="n"/>
+      <c r="K299" s="5" t="n">
+        <v>0.969047</v>
+      </c>
+      <c r="L299" s="5" t="n">
+        <v>0.969</v>
+      </c>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:10:08</t>
+        </is>
+      </c>
+      <c r="N299" s="5" t="n">
+        <v>4.05</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B300" s="2" t="inlineStr">
+        <is>
+          <t>領完重大傷病保險金，主約終止後，附約可以繼續有效嗎?</t>
+        </is>
+      </c>
+      <c r="C300" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以。根據條文規定，若主約因重大傷病診斷確定而終止時，要保人於附約的有效期間內，仍可繼續繳交附約保險費，以延續附約效力。
+條文依據：  
+- [第十一條 契約的終止（二）]</t>
+        </is>
+      </c>
+      <c r="D300" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 契約的終止（二） | 第十二條 重大傷病保險金的給付 | 第三十條 不保事項 | 第五條 保險範圍 | payout_items | 附表一：全民健康保險重大傷病項目</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F300" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以。根據條文規定，若主約因重大傷病診斷確定而終止時，要保人於附約的有效期間內，仍可繼續繳交附約保險費，以延續附約效力。
+條文依據：  
+- [第十一條 契約的終止（二）]</t>
+        </is>
+      </c>
+      <c r="G300" s="2" t="inlineStr"/>
+      <c r="H300" s="2" t="inlineStr"/>
+      <c r="I300" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.993389, "neutral": 0.006487, "contradiction": 0.000124, "factuality": 0.999876, "C_fact": 0.999876}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J300" s="5" t="n"/>
+      <c r="K300" s="5" t="n">
+        <v>0.999876</v>
+      </c>
+      <c r="L300" s="5" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:10:12</t>
+        </is>
+      </c>
+      <c r="N300" s="5" t="n">
+        <v>3.46</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B301" s="2" t="inlineStr">
+        <is>
+          <t>Q1：因為慢性精神病的保險給付僅有保額的20%，我可以先不申請給付，等之後發生其他重大傷病後，再申請重大傷病保險金嗎?Q2：但如果我不申請，保險公司不會知道我有罹患慢性精神病阿，所以我就可以領之後的重大傷病100%保額嗎?</t>
+        </is>
+      </c>
+      <c r="C301" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+Q1：依據條款，被保險人同時或先後罹患二項以上重大傷病時，保險公司僅給付一項重大傷病保險金。因此，即使您選擇不申請慢性精神病的保險給付，之後若罹患其他重大傷病，保險公司仍僅會給付其中一項的重大傷病保險金，並依條款規定計算金額。  
+Q2：保險公司是否知悉您罹患慢性精神病並不影響重大傷病保險金的給付規則。條款明確規定，若罹患慢性精神病，重大傷病保險金的給付金額僅為保險金額的20%或年繳應繳保險費總額的1.05倍，二者取其大者。因此，即使您未申請慢性精神病的保險給付，之後罹患其他重大傷病，保險公司仍會依條款規定計算給付金額，並不會因未申請慢性精神病給付而改為給付100%保額。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D301" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 重大傷病保險金的給付 | 第十三條 特定重大傷病保險金的給付 | 第三十條 不保事項 | 第二十八條 除外責任（一） | 第二十二條 重大傷病保險金、特定重大傷病保險金的申領 | 第二條 名詞定義 | 附表一：全民健康保險重大傷病項目 | payout_items</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F301" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+Q1：依據條款，被保險人同時或先後罹患二項以上重大傷病時，保險公司僅給付一項重大傷病保險金。因此，即使您選擇不申請慢性精神病的保險給付，之後若罹患其他重大傷病，保險公司仍僅會給付其中一項的重大傷病保險金，並依條款規定計算金額。  
+Q2：保險公司是否知悉您罹患慢性精神病並不影響重大傷病保險金的給付規則。條款明確規定，若罹患慢性精神病，重大傷病保險金的給付金額僅為保險金額的20%或年繳應繳保險費總額的1.05倍，二者取其大者。因此，即使您未申請慢性精神病的保險給付，之後罹患其他重大傷病，保險公司仍會依條款規定計算給付金額，並不會因未申請慢性精神病給付而改為給付100%保額。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G301" s="2" t="inlineStr"/>
+      <c r="H301" s="2" t="inlineStr"/>
+      <c r="I301" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.890406, "neutral": 0.107468, "contradiction": 0.002126, "factuality": 0.997874, "C_fact": 0.997874}, "C_conf": 0.9979}</t>
+        </is>
+      </c>
+      <c r="J301" s="5" t="n"/>
+      <c r="K301" s="5" t="n">
+        <v>0.997874</v>
+      </c>
+      <c r="L301" s="5" t="n">
+        <v>0.9979</v>
+      </c>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:10:31</t>
+        </is>
+      </c>
+      <c r="N301" s="5" t="n">
+        <v>18.42</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B302" s="2" t="inlineStr">
+        <is>
+          <t>失智症會賠嗎？賠多少？</t>
+        </is>
+      </c>
+      <c r="C302" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+失智症是否理賠及賠償金額需視其是否符合「重大傷病」的範圍及診斷條件。根據條款，若失智症屬於附表一所載「重大傷病」範圍，且被保險人取得符合規定的重大傷病證明或診斷書，則可申請「重大傷病保險金」。賠償金額依初次診斷確定罹患重大傷病時的保險單年度計算：  
+1. 第一保險單年度：「年繳應繳保險費總額」的一點零五倍。  
+2. 第二保險單年度（含）以後：  
+   - 若屬「慢性精神病」：給付「保險金額的百分之二十」或「年繳應繳保險費總額的一點零五倍」，二者取其大者。  
+   - 若屬其他重大傷病範圍：給付「保險金額」或「年繳應繳保險費總額的一點零五倍」，二者取其大者。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [附表一：全民健康保險重大傷病項目]</t>
+        </is>
+      </c>
+      <c r="D302" s="2" t="inlineStr">
+        <is>
+          <t>第十七條 完全失能保險金的給付 | 第二十九條 除外責任（二） | payout_items | 第十二條 重大傷病保險金的給付 | 第三十條 不保事項 | 附表二：完全失能程度表 | 附表一：全民健康保險重大傷病項目</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F302" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+失智症是否理賠及賠償金額需視其是否符合「重大傷病」的範圍及診斷條件。根據條款，若失智症屬於附表一所載「重大傷病」範圍，且被保險人取得符合規定的重大傷病證明或診斷書，則可申請「重大傷病保險金」。賠償金額依初次診斷確定罹患重大傷病時的保險單年度計算：  
+1. 第一保險單年度：「年繳應繳保險費總額」的一點零五倍。  
+2. 第二保險單年度（含）以後：  
+   - 若屬「慢性精神病」：給付「保險金額的百分之二十」或「年繳應繳保險費總額的一點零五倍」，二者取其大者。  
+   - 若屬其他重大傷病範圍：給付「保險金額」或「年繳應繳保險費總額的一點零五倍」，二者取其大者。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [附表一：全民健康保險重大傷病項目]</t>
+        </is>
+      </c>
+      <c r="G302" s="2" t="inlineStr"/>
+      <c r="H302" s="2" t="inlineStr"/>
+      <c r="I302" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.994636, "neutral": 0.005014, "contradiction": 0.00035, "factuality": 0.99965, "C_fact": 0.99965}, "C_conf": 0.9997}</t>
+        </is>
+      </c>
+      <c r="J302" s="5" t="n"/>
+      <c r="K302" s="5" t="n">
+        <v>0.99965</v>
+      </c>
+      <c r="L302" s="5" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:10:39</t>
+        </is>
+      </c>
+      <c r="N302" s="5" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B303" s="2" t="inlineStr">
+        <is>
+          <t>投保新鍾心滿福後，於第二保單年度罹患子宮頸惡性腫瘤，且已給付重大傷病保險金。第五保單年度時又罹患慢性腎衰竭，這樣還可以申領重大傷病保險金的給付嗎?</t>
+        </is>
+      </c>
+      <c r="C303" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不可以再次申領重大傷病保險金。根據條款規定，被保險人同時或先後罹患二項以上「重大傷病」時，本公司僅給付一項「重大傷病保險金」。因此，即使於第五保單年度罹患慢性腎衰竭，因已於第二保單年度因子宮頸惡性腫瘤申領過重大傷病保險金，無法再次申領。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D303" s="2" t="inlineStr">
+        <is>
+          <t>附表一：全民健康保險重大傷病項目 | 第十二條 重大傷病保險金的給付 | 第五條 保險範圍 | 第二條 名詞定義 | payout_items | 第二十二條 重大傷病保險金、特定重大傷病保險金的申領</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F303" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不可以再次申領重大傷病保險金。根據條款規定，被保險人同時或先後罹患二項以上「重大傷病」時，本公司僅給付一項「重大傷病保險金」。因此，即使於第五保單年度罹患慢性腎衰竭，因已於第二保單年度因子宮頸惡性腫瘤申領過重大傷病保險金，無法再次申領。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G303" s="2" t="inlineStr"/>
+      <c r="H303" s="2" t="inlineStr"/>
+      <c r="I303" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.960141, "neutral": 0.039248, "contradiction": 0.000611, "factuality": 0.999389, "C_fact": 0.999389}, "C_conf": 0.9994}</t>
+        </is>
+      </c>
+      <c r="J303" s="5" t="n"/>
+      <c r="K303" s="5" t="n">
+        <v>0.999389</v>
+      </c>
+      <c r="L303" s="5" t="n">
+        <v>0.9994</v>
+      </c>
+      <c r="M303" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:10:44</t>
+        </is>
+      </c>
+      <c r="N303" s="5" t="n">
+        <v>4.72</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B304" s="2" t="inlineStr">
+        <is>
+          <t>12歲的被保險人可以有健康促進保險費折減嗎？</t>
+        </is>
+      </c>
+      <c r="C304" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+12歲的被保險人無法享有健康促進保險費折減，因為該條款明確規定只有實際年齡達十八歲（含）以上的被保險人才符合資格。  
+條文依據：  
+- [第十九條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="D304" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 健康促進保險費折減 | 第三十八條 投保年齡的計算及錯誤的處理 | 第三十四條 減額繳清保險 | 第二條 名詞定義 | 第十六條 所繳保險費加計利息的退還、身故保險金或喪葬費用保險金的給付 | 附表二：完全失能程度表</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F304" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+12歲的被保險人無法享有健康促進保險費折減，因為該條款明確規定只有實際年齡達十八歲（含）以上的被保險人才符合資格。  
+條文依據：  
+- [第十九條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="G304" s="2" t="inlineStr"/>
+      <c r="H304" s="2" t="inlineStr"/>
+      <c r="I304" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.919166, "neutral": 0.079112, "contradiction": 0.001722, "factuality": 0.998278, "C_fact": 0.998278}, "C_conf": 0.9983}</t>
+        </is>
+      </c>
+      <c r="J304" s="5" t="n"/>
+      <c r="K304" s="5" t="n">
+        <v>0.998278</v>
+      </c>
+      <c r="L304" s="5" t="n">
+        <v>0.9983</v>
+      </c>
+      <c r="M304" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:10:47</t>
+        </is>
+      </c>
+      <c r="N304" s="5" t="n">
+        <v>2.93</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>ZDN</t>
+        </is>
+      </c>
+      <c r="B305" s="2" t="inlineStr">
+        <is>
+          <t>被保險人於投保鍾心滿溢後的第10天就罹患慢性腎衰竭，請問可以申領重大傷病保險金嗎？</t>
+        </is>
+      </c>
+      <c r="C305" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不可以申領重大傷病保險金。根據條款規定，被保險人因意外傷害事故以外原因，於等待期間內罹患「重大傷病」者，本契約自始無效，本公司僅退還已繳保險費且不給付重大傷病保險金。等待期間為契約生效日起持續有效三十日，因此第10天仍屬等待期間內。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D305" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 重大傷病保險金的給付 | 附表一：全民健康保險重大傷病項目 | 第三十條 不保事項 | 第二條 名詞定義 | 第二十二條 重大傷病保險金、特定重大傷病保險金的申領</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F305" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不可以申領重大傷病保險金。根據條款規定，慢性腎衰竭屬於「重大傷病範圍」中的項目，但若被保險人於等待期間內罹患重大傷病（非因意外傷害事故所致），則契約自始無效，本公司僅退還已繳保險費且不給付重大傷病保險金。等待期間為契約生效日起持續有效三十日，因此第10天仍屬等待期間內。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G305" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不可以申領重大傷病保險金。根據條款規定，被保險人因意外傷害事故以外原因，於等待期間內罹患「重大傷病」者，本契約自始無效，本公司僅退還已繳保險費且不給付重大傷病保險金。等待期間為契約生效日起持續有效三十日，因此第10天仍屬等待期間內。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="H305" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不可以申領重大傷病保險金。根據條款規定，被保險人因意外傷害事故以外原因，於等待期間內罹患「重大傷病」者，本契約自始無效，本公司僅退還已繳保險費且不給付重大傷病保險金。等待期間為契約生效日起持續有效三十日，因此第10天仍屬等待期間內。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="I305" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.033904, "neutral": 0.086416, "contradiction": 0.87968, "factuality": 0.12032, "C_fact": 0.12032}, "C_conf": 0.1203}</t>
+        </is>
+      </c>
+      <c r="J305" s="5" t="n"/>
+      <c r="K305" s="7" t="n">
+        <v>0.12032</v>
+      </c>
+      <c r="L305" s="7" t="n">
+        <v>0.1203</v>
+      </c>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:10:58</t>
+        </is>
+      </c>
+      <c r="N305" s="5" t="n">
+        <v>11.45</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>CFE</t>
+        </is>
+      </c>
+      <c r="B306" s="2" t="inlineStr">
+        <is>
+          <t>投保自由配重大傷病後，若在契約生效後80天罹患第一期乳癌，會拿到理賠金嗎?</t>
+        </is>
+      </c>
+      <c r="C306" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不會拿到理賠金。根據條款，第一期乳癌屬於「需積極或長期治療之癌症」範圍，等待期間為契約生效日起90天。若在等待期間內罹患重大傷病，契約自始無效，本公司僅退還已繳保險費且無息。
+條文依據：  
+- [第二條 名詞定義]  
+- [第十一條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D306" s="2" t="inlineStr">
+        <is>
+          <t>附表一：全民健康保險重大傷病項目 | 第十一條 重大傷病保險金的給付 | 第十五條 不保事項 | 第二條 名詞定義 | other_metadata | 第五條 契約有效期間及保證續保 | 第十四條 除外責任</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F306" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不會拿到理賠金。根據條款，第一期乳癌屬於「需積極或長期治療之癌症」範圍，等待期間為契約生效日起90天。若在等待期間內罹患重大傷病，契約自始無效，本公司僅退還已繳保險費且無息。
+條文依據：  
+- [第二條 名詞定義]  
+- [第十一條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G306" s="2" t="inlineStr"/>
+      <c r="H306" s="2" t="inlineStr"/>
+      <c r="I306" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.728417, "neutral": 0.142745, "contradiction": 0.128839, "factuality": 0.871161, "C_fact": 0.871161}, "C_conf": 0.8712}</t>
+        </is>
+      </c>
+      <c r="J306" s="5" t="n"/>
+      <c r="K306" s="5" t="n">
+        <v>0.871161</v>
+      </c>
+      <c r="L306" s="5" t="n">
+        <v>0.8712</v>
+      </c>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:11:02</t>
+        </is>
+      </c>
+      <c r="N306" s="5" t="n">
+        <v>3.72</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>CFE</t>
+        </is>
+      </c>
+      <c r="B307" s="2" t="inlineStr">
+        <is>
+          <t>要保人想要終止國泰人壽自由配CFE契約，能否退保費?</t>
+        </is>
+      </c>
+      <c r="C307" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+要保人可以終止契約，並退還未到期保險費。本公司會從已繳保險費中扣除按短期費率計算的已經過期間保險費後，將未到期保險費無息退還給要保人。
+條文依據：  
+- [第九條 契約的終止（一）]</t>
+        </is>
+      </c>
+      <c r="D307" s="2" t="inlineStr">
+        <is>
+          <t>第九條 契約的終止（一） | 第十五條 不保事項 | 第五條 契約有效期間及保證續保 | 第七條 本契約效力的恢復 | 第六條 續保保險費的交付、寬限期間及契約效力的停止 | 附表二：短期費率表</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F307" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+要保人可以終止契約，並退還未到期保險費。本公司會從已繳保險費中扣除按短期費率計算的已經過期間保險費後，將未到期保險費無息退還給要保人。
+條文依據：  
+- [第九條 契約的終止（一）]</t>
+        </is>
+      </c>
+      <c r="G307" s="2" t="inlineStr"/>
+      <c r="H307" s="2" t="inlineStr"/>
+      <c r="I307" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.997835, "neutral": 0.002071, "contradiction": 9.4e-05, "factuality": 0.999906, "C_fact": 0.999906}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J307" s="5" t="n"/>
+      <c r="K307" s="5" t="n">
+        <v>0.999906</v>
+      </c>
+      <c r="L307" s="5" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:11:06</t>
+        </is>
+      </c>
+      <c r="N307" s="5" t="n">
+        <v>3.48</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>CFE</t>
+        </is>
+      </c>
+      <c r="B308" s="2" t="inlineStr">
+        <is>
+          <t>投保國泰人壽自由配CFE，若在等待期間內罹患重大傷病，要如何給付?</t>
+        </is>
+      </c>
+      <c r="C308" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在等待期間內罹患重大傷病，且該重大傷病並非因意外傷害事故所致，則本契約自始無效，本公司僅無息退還已繳保險費予要保人。若重大傷病係因意外傷害事故所致，則不受等待期間限制，可依約給付重大傷病保險金。
+條文依據：  
+- [第十一條 重大傷病保險金的給付]  
+- [第十五條 不保事項]</t>
+        </is>
+      </c>
+      <c r="D308" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 重大傷病保險金的給付 | 附表一：全民健康保險重大傷病項目 | 第十五條 不保事項 | 第十四條 除外責任 | payout_items | other_metadata</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F308" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在等待期間內罹患重大傷病，且該重大傷病並非因意外傷害事故所致，則本契約自始無效，本公司僅無息退還已繳保險費予要保人。若重大傷病係因意外傷害事故所致，則不受等待期間限制，可依約給付重大傷病保險金。
+條文依據：  
+- [第十一條 重大傷病保險金的給付]  
+- [第十五條 不保事項]</t>
+        </is>
+      </c>
+      <c r="G308" s="2" t="inlineStr"/>
+      <c r="H308" s="2" t="inlineStr"/>
+      <c r="I308" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.944735, "neutral": 0.030208, "contradiction": 0.025056, "factuality": 0.974944, "C_fact": 0.974944}, "C_conf": 0.9749}</t>
+        </is>
+      </c>
+      <c r="J308" s="5" t="n"/>
+      <c r="K308" s="5" t="n">
+        <v>0.974944</v>
+      </c>
+      <c r="L308" s="5" t="n">
+        <v>0.9749</v>
+      </c>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:11:09</t>
+        </is>
+      </c>
+      <c r="N308" s="5" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>CFE</t>
+        </is>
+      </c>
+      <c r="B309" s="2" t="inlineStr">
+        <is>
+          <t>投保自由配一年定期初次罹患重大傷病健康保險後，於第三年罹患先天性肌肉萎縮症，可以申領重大傷病保險金嗎？</t>
+        </is>
+      </c>
+      <c r="C309" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不可以申領重大傷病保險金。根據條款，先天性肌肉萎縮症不屬於「重大傷病」範圍，因此不符合申領條件。
+條文依據：  
+- 附表一：全民健康保險重大傷病項目</t>
+        </is>
+      </c>
+      <c r="D309" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 重大傷病保險金的給付 | other_metadata | 附表一：全民健康保險重大傷病項目 | 第十三條 重大傷病保險金的申領 | 第十五條 不保事項</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F309" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不可以申領重大傷病保險金。根據條款，先天性肌肉萎縮症不屬於「重大傷病」範圍，因此不符合申領條件。
+條文依據：  
+- 附表一：全民健康保險重大傷病項目</t>
+        </is>
+      </c>
+      <c r="G309" s="2" t="inlineStr"/>
+      <c r="H309" s="2" t="inlineStr"/>
+      <c r="I309" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.012166, "neutral": 0.951748, "contradiction": 0.036087, "factuality": 0.963913, "C_fact": 0.963913}, "C_conf": 0.9639}</t>
+        </is>
+      </c>
+      <c r="J309" s="5" t="n"/>
+      <c r="K309" s="5" t="n">
+        <v>0.963913</v>
+      </c>
+      <c r="L309" s="5" t="n">
+        <v>0.9639</v>
+      </c>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:11:17</t>
+        </is>
+      </c>
+      <c r="N309" s="5" t="n">
+        <v>6.79</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>CFG</t>
+        </is>
+      </c>
+      <c r="B310" s="2" t="inlineStr">
+        <is>
+          <t>自由配重大疾病(甲型)保障的重大疾病有哪些疾病?</t>
+        </is>
+      </c>
+      <c r="C310" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+自由配重大疾病(甲型)保障的重大疾病包括以下疾病：  
+1. 腦中風後障礙(重度)  
+2. 癱瘓(重度)  
+3. 癌症(重度)  
+4. 急性心肌梗塞(重度)  
+5. 冠狀動脈繞道手術  
+6. 末期腎病變  
+7. 重大器官移植或造血幹細胞移植  
+條文依據：  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D310" s="2" t="inlineStr">
+        <is>
+          <t>國泰人壽自由配一年定期初次罹患重大疾病健康保險(甲型)年繳費率表 | payout_items | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F310" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+自由配重大疾病(甲型)保障的重大疾病包括以下疾病：  
+1. 腦中風後障礙(重度)  
+2. 癱瘓(重度)  
+3. 癌症(重度)  
+4. 急性心肌梗塞(重度)  
+5. 冠狀動脈繞道手術  
+6. 末期腎病變  
+7. 重大器官移植或造血幹細胞移植  
+條文依據：  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G310" s="2" t="inlineStr"/>
+      <c r="H310" s="2" t="inlineStr"/>
+      <c r="I310" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.435646, "neutral": 0.534641, "contradiction": 0.029713, "factuality": 0.970287, "C_fact": 0.970287}, "C_conf": 0.9703}</t>
+        </is>
+      </c>
+      <c r="J310" s="5" t="n"/>
+      <c r="K310" s="5" t="n">
+        <v>0.970287</v>
+      </c>
+      <c r="L310" s="5" t="n">
+        <v>0.9703000000000001</v>
+      </c>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:11:22</t>
+        </is>
+      </c>
+      <c r="N310" s="5" t="n">
+        <v>5.12</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B311" s="2" t="inlineStr">
+        <is>
+          <t>被保險人領了2次癌症(重度)追蹤照護金後身故，是否還有尚未給付的保險金供受益人領取?</t>
+        </is>
+      </c>
+      <c r="C311" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人已領取2次「癌症(重度)追蹤照護保險金」後身故，受益人無法再申領尚未給付的「癌症(重度)追蹤照護保險金」，因該保險金的給付條件為被保險人於保險單週年日仍生存，且最多給付5年。被保險人身故後，該保險金的給付責任即終止。
+條文依據：  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]</t>
+        </is>
+      </c>
+      <c r="D311" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用) | 第十三條 初次罹患癌症(重度)保險金的給付 | payout_items | 第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用) | 第二十三條 癌症保險金或罹癌基因檢測服務的申領 | 第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付 | 第十六條 癌症(重度)豁免保險費(第二保險單年度起適用) | 第二十二條 保險事故的通知與保險給付的申請時間</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F311" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人已領取2次「癌症(重度)追蹤照護保險金」後身故，受益人無法再申領尚未給付的「癌症(重度)追蹤照護保險金」，因該保險金的給付條件為被保險人於保險單週年日仍生存，且最多給付5年。被保險人身故後，該保險金的給付責任即終止。
+條文依據：  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]</t>
+        </is>
+      </c>
+      <c r="G311" s="2" t="inlineStr"/>
+      <c r="H311" s="2" t="inlineStr"/>
+      <c r="I311" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.959271, "neutral": 0.027372, "contradiction": 0.013357, "factuality": 0.986643, "C_fact": 0.986643}, "C_conf": 0.9866}</t>
+        </is>
+      </c>
+      <c r="J311" s="5" t="n"/>
+      <c r="K311" s="5" t="n">
+        <v>0.986643</v>
+      </c>
+      <c r="L311" s="5" t="n">
+        <v>0.9866</v>
+      </c>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:11:27</t>
+        </is>
+      </c>
+      <c r="N311" s="5" t="n">
+        <v>5.16</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B312" s="2" t="inlineStr">
+        <is>
+          <t>保險金額2萬元，「罹癌基因檢測服務」費用8萬元，還會給付多少「癌症(重度)追蹤照護保險金」？</t>
+        </is>
+      </c>
+      <c r="C312" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人選擇申領「罹癌基因檢測服務」，因服務費用（8萬元）高於「罹癌基因檢測服務額度」（1,000元），則僅能申領「癌症(重度)追蹤照護保險金」。依條款規定，「癌症(重度)追蹤照護保險金」的給付金額為保險金額的12倍，故給付金額為 2萬元 × 12 = 24萬元。
+條文依據：  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]</t>
+        </is>
+      </c>
+      <c r="D312" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用) | 附件一：罹癌基因檢測服務之項目、服務費用及補償金額表 | 第二十三條 癌症保險金或罹癌基因檢測服務的申領 | 第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用) | payout_items | 第十三條 初次罹患癌症(重度)保險金的給付 | other_metadata | 第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F312" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人選擇申領「罹癌基因檢測服務」，因服務費用（8萬元）高於「罹癌基因檢測服務額度」（1,000元），則僅能申領「癌症(重度)追蹤照護保險金」。依條款規定，「癌症(重度)追蹤照護保險金」的給付金額為保險金額的12倍，故給付金額為 2萬元 × 12 = 24萬元。
+條文依據：  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]</t>
+        </is>
+      </c>
+      <c r="G312" s="2" t="inlineStr"/>
+      <c r="H312" s="2" t="inlineStr"/>
+      <c r="I312" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.557082, "neutral": 0.243222, "contradiction": 0.199696, "factuality": 0.800304, "C_fact": 0.800304}, "C_conf": 0.8003}</t>
+        </is>
+      </c>
+      <c r="J312" s="5" t="n"/>
+      <c r="K312" s="5" t="n">
+        <v>0.800304</v>
+      </c>
+      <c r="L312" s="5" t="n">
+        <v>0.8003</v>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:11:31</t>
+        </is>
+      </c>
+      <c r="N312" s="5" t="n">
+        <v>3.57</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B313" s="2" t="inlineStr">
+        <is>
+          <t>投保後1個月罹患重度癌症，會給付哪些保險金？契約還會持續有效嗎？</t>
+        </is>
+      </c>
+      <c r="C313" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在投保後1個月罹患重度癌症，因診斷確定日屬於第一保險單年度內，符合「初次診斷確定罹患癌症(重度)」的條件，本公司將給付「初次罹患癌症(重度)保險金」，金額為「年繳應繳保險費」的一點零六倍。契約仍會持續有效，但當期已繳付之未到期保險費不予退還。  
+條文依據：  
+- [第十三條 初次罹患癌症(重度)保險金的給付]  
+- [第十六條 癌症(重度)豁免保險費(第二保險單年度起適用)]</t>
+        </is>
+      </c>
+      <c r="D313" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 癌症(重度)豁免保險費(第二保險單年度起適用) | 第十三條 初次罹患癌症(重度)保險金的給付 | 第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用) | 第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付 | 第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用)</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F313" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在投保後1個月罹患重度癌症，因診斷確定日屬於第一保險單年度內，符合「初次診斷確定罹患癌症(重度)」的條件，本公司將給付「初次罹患癌症(重度)保險金」，金額為「年繳應繳保險費」的一點零六倍。契約仍會持續有效，但當期已繳付之未到期保險費不予退還。  
+條文依據：  
+- [第十三條 初次罹患癌症(重度)保險金的給付]  
+- [第十六條 癌症(重度)豁免保險費(第二保險單年度起適用)]</t>
+        </is>
+      </c>
+      <c r="G313" s="2" t="inlineStr"/>
+      <c r="H313" s="2" t="inlineStr"/>
+      <c r="I313" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.996249, "neutral": 0.003286, "contradiction": 0.000465, "factuality": 0.999535, "C_fact": 0.999535}, "C_conf": 0.9995}</t>
+        </is>
+      </c>
+      <c r="J313" s="5" t="n"/>
+      <c r="K313" s="5" t="n">
+        <v>0.999535</v>
+      </c>
+      <c r="L313" s="5" t="n">
+        <v>0.9995000000000001</v>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:11:35</t>
+        </is>
+      </c>
+      <c r="N313" s="5" t="n">
+        <v>3.67</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B314" s="2" t="inlineStr">
+        <is>
+          <t>投保後10個月罹患重度癌症，會給付哪些保險金？契約還會持續有效嗎？</t>
+        </is>
+      </c>
+      <c r="C314" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人於投保後10個月（即第一保險單年度內）診斷確定罹患重度癌症，依條款規定，本公司將給付「初次罹患癌症(重度)保險金」，金額為「年繳應繳保險費」的一點零六倍。契約仍會持續有效，並不因罹患重度癌症而終止。  
+條文依據：  
+- [第十三條 初次罹患癌症(重度)保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D314" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 癌症(重度)豁免保險費(第二保險單年度起適用) | 第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用) | 第十條 契約的終止（二） | 第十三條 初次罹患癌症(重度)保險金的給付 | 第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F314" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人於投保後10個月（即第一保險單年度內）診斷確定罹患重度癌症，依條款規定，本公司將給付「初次罹患癌症(重度)保險金」，金額為「年繳應繳保險費」的一點零六倍。契約仍會持續有效，並不因罹患重度癌症而終止。  
+條文依據：  
+- [第十三條 初次罹患癌症(重度)保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G314" s="2" t="inlineStr"/>
+      <c r="H314" s="2" t="inlineStr"/>
+      <c r="I314" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.855158, "neutral": 0.035276, "contradiction": 0.109566, "factuality": 0.890434, "C_fact": 0.890434}, "C_conf": 0.8904}</t>
+        </is>
+      </c>
+      <c r="J314" s="5" t="n"/>
+      <c r="K314" s="5" t="n">
+        <v>0.8904339999999999</v>
+      </c>
+      <c r="L314" s="5" t="n">
+        <v>0.8904</v>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:11:37</t>
+        </is>
+      </c>
+      <c r="N314" s="5" t="n">
+        <v>2.44</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B315" s="2" t="inlineStr">
+        <is>
+          <t>投保醫心康愛，罹患肺癌一期，可領什麼保險金？</t>
+        </is>
+      </c>
+      <c r="C315" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+罹患肺癌一期屬於「癌症(初期)」，符合「初次診斷確定罹患癌症(初期)或癌症(輕度)」的條件，可申領「初次罹患癌症(初期)或癌症(輕度)保險金」。若診斷確定日是在第一保險單年度內，可領「年繳應繳保險費」的一點零六倍；若診斷確定日是在第二保險單年度(含)以後，可領「保險金額」的五倍。此保險金最多僅給付一次。
+條文依據：  
+- [第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D315" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付 | 第十三條 初次罹患癌症(重度)保險金的給付 | payout_items | 第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用) | 第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F315" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+罹患肺癌一期屬於「癌症(初期)」，符合「初次診斷確定罹患癌症(初期)或癌症(輕度)」的條件，可申領「初次罹患癌症(初期)或癌症(輕度)保險金」。若診斷確定日是在第一保險單年度內，可領「年繳應繳保險費」的一點零六倍；若診斷確定日是在第二保險單年度(含)以後，可領「保險金額」的五倍。此保險金最多僅給付一次。
+條文依據：  
+- [第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G315" s="2" t="inlineStr"/>
+      <c r="H315" s="2" t="inlineStr"/>
+      <c r="I315" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.917225, "neutral": 0.082601, "contradiction": 0.000174, "factuality": 0.999826, "C_fact": 0.999826}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J315" s="5" t="n"/>
+      <c r="K315" s="5" t="n">
+        <v>0.999826</v>
+      </c>
+      <c r="L315" s="5" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:11:41</t>
+        </is>
+      </c>
+      <c r="N315" s="5" t="n">
+        <v>3.03</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>PX5</t>
+        </is>
+      </c>
+      <c r="B316" s="2" t="inlineStr">
+        <is>
+          <t>若被保險人身故有何給付?</t>
+        </is>
+      </c>
+      <c r="C316" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人身故，保險金的受益人為被保險人的法定繼承人，並依民法繼承編的相關規定分配。若本附約保險金尚未給付或未完全給付，則由法定繼承人申領該部分保險金。
+條文依據：  
+- [第二十條 受益人]</t>
+        </is>
+      </c>
+      <c r="D316" s="2" t="inlineStr">
+        <is>
+          <t>第二十條 受益人 | 第十二條 重大疾病保險金的給付 | 第十一條 輕度重大疾病保險金的給付 | 第十四條 保險事故的通知與保險金的申請時間 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F316" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人身故，保險金的受益人為被保險人的法定繼承人，並依民法繼承編的相關規定分配。若本附約保險金尚未給付或未完全給付，則由法定繼承人申領該部分保險金。
+條文依據：  
+- [第二十條 受益人]</t>
+        </is>
+      </c>
+      <c r="G316" s="2" t="inlineStr"/>
+      <c r="H316" s="2" t="inlineStr"/>
+      <c r="I316" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.997035, "neutral": 0.002326, "contradiction": 0.000639, "factuality": 0.999361, "C_fact": 0.999361}, "C_conf": 0.9994}</t>
+        </is>
+      </c>
+      <c r="J316" s="5" t="n"/>
+      <c r="K316" s="5" t="n">
+        <v>0.9993610000000001</v>
+      </c>
+      <c r="L316" s="5" t="n">
+        <v>0.9994</v>
+      </c>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:11:44</t>
+        </is>
+      </c>
+      <c r="N316" s="5" t="n">
+        <v>3.14</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>PX5</t>
+        </is>
+      </c>
+      <c r="B317" s="2" t="inlineStr">
+        <is>
+          <t>投保鍾溢祝福後，請問在第二年經醫院醫師初次診斷罹患「輕度重大疾病」中的癌症(輕度)者，可以領到輕度重大疾病保險金嗎?可以領到保險金額的百分之多少?</t>
+        </is>
+      </c>
+      <c r="C317" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以領到輕度重大疾病保險金，保險金額的百分之二十。根據條款，被保險人在第二年（續保年度）經醫院醫師初次診斷罹患「輕度重大疾病」中的癌症(輕度)，符合給付條件，且等待期間已屆滿。
+條文依據：  
+- [第十一條 輕度重大疾病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D317" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 輕度重大疾病保險金的給付 | 第十二條 重大疾病保險金的給付 | other_metadata | payout_items | 國泰人壽鍾溢祝福重大疾病健康保險附約(乙型) (外溢型)年繳費率表 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F317" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以領到輕度重大疾病保險金，保險金額的百分之二十。根據條款，被保險人在第二年（續保年度）經醫院醫師初次診斷罹患「輕度重大疾病」中的癌症(輕度)，符合給付條件，且等待期間已屆滿。
+條文依據：  
+- [第十一條 輕度重大疾病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G317" s="2" t="inlineStr"/>
+      <c r="H317" s="2" t="inlineStr"/>
+      <c r="I317" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.997094, "neutral": 0.002516, "contradiction": 0.00039, "factuality": 0.99961, "C_fact": 0.99961}, "C_conf": 0.9996}</t>
+        </is>
+      </c>
+      <c r="J317" s="5" t="n"/>
+      <c r="K317" s="5" t="n">
+        <v>0.99961</v>
+      </c>
+      <c r="L317" s="5" t="n">
+        <v>0.9996</v>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:11:47</t>
+        </is>
+      </c>
+      <c r="N317" s="5" t="n">
+        <v>3.19</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>PX5</t>
+        </is>
+      </c>
+      <c r="B318" s="2" t="inlineStr">
+        <is>
+          <t>請問如果在投保後的第三年經醫院醫師初次診斷罹患「重大疾病」者，可以領到重大疾病保險金嗎?可以領到保險金額的百分之多少?那後續又在第四年經醫院醫師初次診斷罹患「輕度重大疾病」者，可以領到輕度重大疾病保險金嗎?可以領到保險金額的百分之多少?</t>
+        </is>
+      </c>
+      <c r="C318" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+在投保後的第三年初次診斷罹患「重大疾病」者，可以領到重大疾病保險金，給付比例為保險金額的1.3倍。後續在第四年初次診斷罹患「輕度重大疾病」者，因「輕度重大疾病保險金」終身最多以給付一次為限，且條款未明確規定是否可在已申領重大疾病保險金後再申領輕度重大疾病保險金，故資料不足。
+條文依據：  
+- [第十二條 重大疾病保險金的給付]  
+- [第十一條 輕度重大疾病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D318" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 輕度重大疾病保險金的給付 | 第十二條 重大疾病保險金的給付 | 第十六條 除外責任 | 第二條 名詞定義 | 第四條 保險範圍 | 國泰人壽鍾溢祝福重大疾病健康保險附約(乙型) (外溢型)年繳費率表</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F318" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+在投保後的第三年初次診斷罹患「重大疾病」者，可以領到重大疾病保險金，給付比例為保險金額的1.3倍。後續在第四年初次診斷罹患「輕度重大疾病」者，因已申領過重大疾病保險金，依條款規定「輕度重大疾病保險金」終身最多以給付一次為限，故無法再領取輕度重大疾病保險金。
+條文依據：  
+- [第十二條 重大疾病保險金的給付]  
+- [第十一條 輕度重大疾病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G318" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+在投保後的第三年初次診斷罹患「重大疾病」者，可以領到重大疾病保險金，給付比例為保險金額的1.3倍。後續在第四年初次診斷罹患「輕度重大疾病」者，因「輕度重大疾病保險金」終身最多以給付一次為限，且條款未明確規定是否可在已申領重大疾病保險金後再申領輕度重大疾病保險金，故資料不足。
+條文依據：  
+- [第十二條 重大疾病保險金的給付]  
+- [第十一條 輕度重大疾病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="H318" s="2" t="inlineStr"/>
+      <c r="I318" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.422005, "neutral": 0.503978, "contradiction": 0.074016, "factuality": 0.925984, "C_fact": 0.925984}, "C_conf": 0.926}</t>
+        </is>
+      </c>
+      <c r="J318" s="5" t="n"/>
+      <c r="K318" s="5" t="n">
+        <v>0.925984</v>
+      </c>
+      <c r="L318" s="5" t="n">
+        <v>0.926</v>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:11:55</t>
+        </is>
+      </c>
+      <c r="N318" s="5" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>PX5</t>
+        </is>
+      </c>
+      <c r="B319" s="2" t="inlineStr">
+        <is>
+          <t>請問如果在投保後的第三年經醫院醫師初次診斷罹患「輕度重大疾病」者，可以領到重大疾病保險金嗎?可以領到保險金額的百分之多少?那後續又在第四年經醫院醫師初次診斷罹患「重大疾病」者，可以領到輕度重大疾病保險金嗎?可以領到保險金額的百分之多少?</t>
+        </is>
+      </c>
+      <c r="C319" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+在投保後的第三年初次診斷罹患「輕度重大疾病」者，無法領取「重大疾病保險金」，只能領取「輕度重大疾病保險金」，給付比例為保險金額的百分之二十。  
+若後續在第四年初次診斷罹患「重大疾病」，無法再領取「輕度重大疾病保險金」，但可以領取「重大疾病保險金」，給付比例為保險金額的一點三倍，且需扣除已領取的「輕度重大疾病保險金」。  
+條文依據：  
+- [第十一條 輕度重大疾病保險金的給付]  
+- [第十二條 重大疾病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D319" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 輕度重大疾病保險金的給付 | 第十二條 重大疾病保險金的給付 | 第十六條 除外責任 | payout_items | 第二條 名詞定義 | 第四條 保險範圍 | other_metadata | 第十五條 各項保險金的申領</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F319" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+在投保後的第三年初次診斷罹患「輕度重大疾病」者，無法領取「重大疾病保險金」，只能領取「輕度重大疾病保險金」，給付比例為保險金額的百分之二十。  
+若後續在第四年初次診斷罹患「重大疾病」，無法再領取「輕度重大疾病保險金」，但可以領取「重大疾病保險金」，給付比例為保險金額的一點三倍，且需扣除已領取的「輕度重大疾病保險金」。  
+條文依據：  
+- [第十一條 輕度重大疾病保險金的給付]  
+- [第十二條 重大疾病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G319" s="2" t="inlineStr"/>
+      <c r="H319" s="2" t="inlineStr"/>
+      <c r="I319" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.92374, "neutral": 0.067375, "contradiction": 0.008886, "factuality": 0.991114, "C_fact": 0.991114}, "C_conf": 0.9911}</t>
+        </is>
+      </c>
+      <c r="J319" s="5" t="n"/>
+      <c r="K319" s="5" t="n">
+        <v>0.9911140000000001</v>
+      </c>
+      <c r="L319" s="5" t="n">
+        <v>0.9911</v>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:12:02</t>
+        </is>
+      </c>
+      <c r="N319" s="5" t="n">
+        <v>5.78</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>PX5</t>
+        </is>
+      </c>
+      <c r="B320" s="2" t="inlineStr">
+        <is>
+          <t>請問主約效力終止(因身故以外情形)，PX5還能持續有效嗎？</t>
+        </is>
+      </c>
+      <c r="C320" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+主約效力因身故以外情形終止時，PX5附約效力可持續至附約當期已繳保險費期滿即行終止，並不再延續。  
+條文依據：  
+- [第十條 附約的終止（二）]</t>
+        </is>
+      </c>
+      <c r="D320" s="2" t="inlineStr">
+        <is>
+          <t>第十條 附約的終止（二） | 第七條 保險費的墊繳、附約的停效及復效 | 第五條 附約的保險期間及保證續保 | 第十三條 健康促進保險費折減 | 第九條 附約的終止（一）</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F320" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+主約效力因身故以外情形終止時，PX5附約效力可持續至附約當期已繳保險費期滿即行終止，並不再延續。  
+條文依據：  
+- [第十條 附約的終止（二）]</t>
+        </is>
+      </c>
+      <c r="G320" s="2" t="inlineStr"/>
+      <c r="H320" s="2" t="inlineStr"/>
+      <c r="I320" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.792572, "neutral": 0.011362, "contradiction": 0.196066, "factuality": 0.803934, "C_fact": 0.803934}, "C_conf": 0.8039}</t>
+        </is>
+      </c>
+      <c r="J320" s="5" t="n"/>
+      <c r="K320" s="5" t="n">
+        <v>0.803934</v>
+      </c>
+      <c r="L320" s="5" t="n">
+        <v>0.8038999999999999</v>
+      </c>
+      <c r="M320" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:12:05</t>
+        </is>
+      </c>
+      <c r="N320" s="5" t="n">
+        <v>3.15</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B321" s="2" t="inlineStr">
+        <is>
+          <t>請問如果於「無理賠紀錄期間」屆滿日以內罹患特定傷病，會給付多少錢?這筆錢會給付給誰?</t>
+        </is>
+      </c>
+      <c r="C321" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在「無理賠紀錄期間」屆滿日以內罹患特定傷病，保險公司將給付「特定傷病保險金」，其金額為「保險金額」加上「年繳應繳保險費總額」乘以1.02的加總。這筆保險金的受益人為被保險人本人，保險公司不受理其指定及變更。
+條文依據：  
+- [第十一條 特定傷病保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="D321" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第十二條 無理賠關懷保險金的給付 | 第十一條 特定傷病保險金的給付 | payout_items | 第二十七條 受益人的指定及變更</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F321" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在「無理賠紀錄期間」屆滿日以內罹患特定傷病，保險公司將給付「特定傷病保險金」，其金額為「保險金額」加上「年繳應繳保險費總額」乘以1.02的加總。這筆保險金的受益人為被保險人本人，保險公司不受理其指定及變更。
+條文依據：  
+- [第十一條 特定傷病保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="G321" s="2" t="inlineStr"/>
+      <c r="H321" s="2" t="inlineStr"/>
+      <c r="I321" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.99722, "neutral": 0.00245, "contradiction": 0.00033, "factuality": 0.99967, "C_fact": 0.99967}, "C_conf": 0.9997}</t>
+        </is>
+      </c>
+      <c r="J321" s="5" t="n"/>
+      <c r="K321" s="5" t="n">
+        <v>0.9996699999999999</v>
+      </c>
+      <c r="L321" s="5" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:12:09</t>
+        </is>
+      </c>
+      <c r="N321" s="5" t="n">
+        <v>3.18</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B322" s="2" t="inlineStr">
+        <is>
+          <t>請問如果要保人與被保險人為同一人，被保險人於「無理賠紀錄期間」屆滿日以內身故，會給付多少錢?這筆錢會給付給誰?</t>
+        </is>
+      </c>
+      <c r="C322" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若要保人與被保險人為同一人，被保險人於「無理賠紀錄期間」屆滿日以內身故，符合「無理賠關懷保險金」的給付條件，保險公司將按「年繳應繳保險費總額」乘以1.02給付「無理賠關懷保險金」。此筆保險金的受益人為要保人本人。  
+條文依據：  
+- [第十二條 無理賠關懷保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="D322" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第十二條 無理賠關懷保險金的給付 | 第十一條 特定傷病保險金的給付 | payout_items | 第十九條 失蹤處理 | 第二十一條 無理賠關懷保險金的申領 | 第二十七條 受益人的指定及變更 | 第十七條 除外責任（二）</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F322" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若要保人與被保險人為同一人，被保險人於「無理賠紀錄期間」屆滿日以內身故，符合「無理賠關懷保險金」的給付條件，保險公司將按「年繳應繳保險費總額」乘以1.02給付「無理賠關懷保險金」。此筆保險金的受益人為要保人本人。  
+條文依據：  
+- [第十二條 無理賠關懷保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="G322" s="2" t="inlineStr"/>
+      <c r="H322" s="2" t="inlineStr"/>
+      <c r="I322" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.976941, "neutral": 0.022376, "contradiction": 0.000683, "factuality": 0.999317, "C_fact": 0.999317}, "C_conf": 0.9993}</t>
+        </is>
+      </c>
+      <c r="J322" s="5" t="n"/>
+      <c r="K322" s="5" t="n">
+        <v>0.999317</v>
+      </c>
+      <c r="L322" s="5" t="n">
+        <v>0.9993</v>
+      </c>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:12:13</t>
+        </is>
+      </c>
+      <c r="N322" s="5" t="n">
+        <v>3.86</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B323" s="2" t="inlineStr">
+        <is>
+          <t>請問如果要保人與被保險人為不同人，被保險人於「無理賠紀錄期間」屆滿日以內生存，且被保險人未罹患特定傷病，會給付多少錢?這筆錢會給付給誰?</t>
+        </is>
+      </c>
+      <c r="C323" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在「無理賠紀錄期間」屆滿日以內生存，且未罹患特定傷病，則本公司將給付「無理賠關懷保險金」，金額為「年繳應繳保險費總額」乘以1.02。此筆保險金的受益人為要保人本人，且不得指定或變更受益人。
+條文依據：  
+- [第十二條 無理賠關懷保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="D323" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第十二條 無理賠關懷保險金的給付 | 第十一條 特定傷病保險金的給付 | payout_items | 第二十七條 受益人的指定及變更 | 第十九條 失蹤處理 | 第二十一條 無理賠關懷保險金的申領 | 第十七條 除外責任（二）</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F323" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在「無理賠紀錄期間」屆滿日以內生存，且未罹患特定傷病，則本公司將給付「無理賠關懷保險金」，金額為「年繳應繳保險費總額」乘以1.02。此筆保險金的受益人為要保人本人，且不得指定或變更受益人。
+條文依據：  
+- [第十二條 無理賠關懷保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="G323" s="2" t="inlineStr"/>
+      <c r="H323" s="2" t="inlineStr"/>
+      <c r="I323" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.996538, "neutral": 0.003188, "contradiction": 0.000274, "factuality": 0.999726, "C_fact": 0.999726}, "C_conf": 0.9997}</t>
+        </is>
+      </c>
+      <c r="J323" s="5" t="n"/>
+      <c r="K323" s="5" t="n">
+        <v>0.999726</v>
+      </c>
+      <c r="L323" s="5" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:12:16</t>
+        </is>
+      </c>
+      <c r="N323" s="5" t="n">
+        <v>3.21</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B324" s="2" t="inlineStr">
+        <is>
+          <t>保戶如果身故，會給保險金嗎?</t>
+        </is>
+      </c>
+      <c r="C324" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保戶身故時，若符合保險契約約定的條件，本公司會依照相關條款給付保險金。例如，若被保險人在「無理賠紀錄期間」內身故，或於「無理賠紀錄期間」屆滿時仍生存，本公司將依第五條約定給付保險金。此外，若受益人在分期定期保險金給付期間內死亡，尚未領取的分期定期保險金將一次貼現給付予受益人之法定繼承人，依第二十八條規定處理。
+條文依據：  
+- [第五條 保險範圍]  
+- [第二十八條 本契約受益人死亡或失蹤的處理]</t>
+        </is>
+      </c>
+      <c r="D324" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第二十八條 本契約受益人死亡或失蹤的處理 | 第十七條 除外責任（二） | 第二十三條 受益人受益權之喪失 | 第十九條 失蹤處理</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F324" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保戶身故時，若符合保險契約約定的條件，本公司會依照相關條款給付保險金。例如，若被保險人在「無理賠紀錄期間」內身故，或於「無理賠紀錄期間」屆滿時仍生存，本公司將依第五條約定給付保險金。此外，若受益人在分期定期保險金給付期間內死亡，尚未領取的分期定期保險金將一次貼現給付予受益人之法定繼承人，依第二十八條規定處理。
+條文依據：  
+- [第五條 保險範圍]  
+- [第二十八條 本契約受益人死亡或失蹤的處理]</t>
+        </is>
+      </c>
+      <c r="G324" s="2" t="inlineStr"/>
+      <c r="H324" s="2" t="inlineStr"/>
+      <c r="I324" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.989447, "neutral": 0.010323, "contradiction": 0.00023, "factuality": 0.99977, "C_fact": 0.99977}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J324" s="5" t="n"/>
+      <c r="K324" s="5" t="n">
+        <v>0.99977</v>
+      </c>
+      <c r="L324" s="5" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:12:20</t>
+        </is>
+      </c>
+      <c r="N324" s="5" t="n">
+        <v>3.81</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B325" s="2" t="inlineStr">
+        <is>
+          <t>保戶如果身故，身故申領的保險金會給誰?</t>
+        </is>
+      </c>
+      <c r="C325" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保戶身故後，若有尚未給付或未完全給付的保險金，該部分保險金的受益人為保戶的法定繼承人。法定繼承人的受益順序及應得比例依民法繼承編相關規定處理。  
+條文依據：  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="D325" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第二十三條 受益人受益權之喪失 | 第二十七條 受益人的指定及變更 | 第二十八條 本契約受益人死亡或失蹤的處理 | 第二十二條 分期定期保險金給付申領文件、給付期限及未依限給付之效果</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F325" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保戶身故後，若有尚未給付或未完全給付的保險金，該部分保險金的受益人為保戶的法定繼承人。法定繼承人的受益順序及應得比例依民法繼承編相關規定處理。  
+條文依據：  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="G325" s="2" t="inlineStr"/>
+      <c r="H325" s="2" t="inlineStr"/>
+      <c r="I325" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.996624, "neutral": 0.003149, "contradiction": 0.000227, "factuality": 0.999773, "C_fact": 0.999773}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J325" s="5" t="n"/>
+      <c r="K325" s="5" t="n">
+        <v>0.999773</v>
+      </c>
+      <c r="L325" s="5" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M325" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:12:23</t>
+        </is>
+      </c>
+      <c r="N325" s="5" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B326" s="2" t="inlineStr">
+        <is>
+          <t>如果保戶投保繳費年期20年的滿溢寶，然後在第20保單年度身故的話，可以領到多少錢?</t>
+        </is>
+      </c>
+      <c r="C326" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若保戶在第20保單年度身故，依據條款規定，若未曾罹患特定傷病且於「無理賠紀錄期間」內身故，本公司將依契約約定給付保險金。具體金額需依保險單所載的保險金額及相關條件計算。
+條文依據：  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="D326" s="2" t="inlineStr">
+        <is>
+          <t>other_metadata | 第二十八條 本契約受益人死亡或失蹤的處理 | 第二十六條 投保年齡的計算及錯誤的處理 | 第十一條 特定傷病保險金的給付 | 第二十二條 分期定期保險金給付申領文件、給付期限及未依限給付之效果 | 第五條 保險範圍 | 第十五條 健康促進保險費折減 | 第十九條 失蹤處理</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F326" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若保戶在第20保單年度身故，依據條款規定，若未曾罹患特定傷病且於「無理賠紀錄期間」內身故，本公司將依契約約定給付保險金。具體金額需依保險單所載的保險金額及相關條件計算。
+條文依據：  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="G326" s="2" t="inlineStr"/>
+      <c r="H326" s="2" t="inlineStr"/>
+      <c r="I326" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.018647, "neutral": 0.981021, "contradiction": 0.000333, "factuality": 0.999667, "C_fact": 0.999667}, "C_conf": 0.9997}</t>
+        </is>
+      </c>
+      <c r="J326" s="5" t="n"/>
+      <c r="K326" s="5" t="n">
+        <v>0.999667</v>
+      </c>
+      <c r="L326" s="5" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:12:25</t>
+        </is>
+      </c>
+      <c r="N326" s="5" t="n">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B327" s="2" t="inlineStr">
+        <is>
+          <t>被保險人為60歲女性，投保繳費期間20年期之滿溢寶特定傷病定期健康保險（定期給付型）（外溢型）100萬元，年繳應繳保險費為83,500元，年繳實繳保險費為78,490元。若被保險人於第二保險單年度自殺身故，則無理賠關懷保險金可以領到多少錢？</t>
+        </is>
+      </c>
+      <c r="C327" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人於第二保險單年度自殺身故，因契約訂立或復效之日起未滿二年，屬於除外責任範圍內，本公司不負給付無理賠關懷保險金的責任。因此，無理賠關懷保險金無法領取。
+條文依據：  
+- [第十七條 除外責任（二)]</t>
+        </is>
+      </c>
+      <c r="D327" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 無理賠關懷保險金的給付 | 第十七條 除外責任（二） | 第十一條 特定傷病保險金的給付 | other_metadata | 第十九條 失蹤處理 | 第五條 保險範圍 | 第二十一條 無理賠關懷保險金的申領 | 第二十七條 受益人的指定及變更</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F327" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人於第二保險單年度自殺身故，因契約訂立或復效之日起未滿二年，屬於除外責任範圍內，本公司不負給付無理賠關懷保險金的責任。因此，無理賠關懷保險金無法領取。
+條文依據：  
+- [第十七條 除外責任（二)]</t>
+        </is>
+      </c>
+      <c r="G327" s="2" t="inlineStr"/>
+      <c r="H327" s="2" t="inlineStr"/>
+      <c r="I327" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.799427, "neutral": 0.062743, "contradiction": 0.13783, "factuality": 0.86217, "C_fact": 0.86217}, "C_conf": 0.8622}</t>
+        </is>
+      </c>
+      <c r="J327" s="5" t="n"/>
+      <c r="K327" s="5" t="n">
+        <v>0.86217</v>
+      </c>
+      <c r="L327" s="5" t="n">
+        <v>0.8622</v>
+      </c>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:12:27</t>
+        </is>
+      </c>
+      <c r="N327" s="5" t="n">
+        <v>2.17</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B328" s="2" t="inlineStr">
+        <is>
+          <t>請問如果第2保單年度罹患特定傷病，可以給付多少錢?給付給誰?未來還有其他保險金嗎?</t>
+        </is>
+      </c>
+      <c r="C328" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在第二保險單年度（含）以後罹患特定傷病，依條款規定可獲以下給付：  
+1. **特定傷病保險金**：給付金額為「保險金額」，且僅給付一次。  
+2. **生活補助保險金**：自初次診斷確定罹患特定傷病的次一個保險單週年日起，每逢保險單週年日仍生存者，按「保險金額」的36%給付，最高給付次數為10次。  
+3. **保險費豁免**：自診斷確定日起豁免續期保險費，但當期已繳付之未到期保險費不予退還。  
+給付對象為被保險人本人。  
+條文依據：  
+- [第十二條 特定傷病保險金的給付]  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]  
+- [第十五條 保險費豁免（第二保險單年度起適用）]</t>
+        </is>
+      </c>
+      <c r="D328" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 特定傷病保險金的給付 | 第五條 保險範圍 | 第十三條 生活補助保險金的給付（第二保險單年度起適用） | 第二條 名詞定義 | 第十五條 保險費豁免（第二保險單年度起適用）</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F328" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在第二保險單年度（含）以後罹患特定傷病，依條款規定可獲以下給付：  
+1. **特定傷病保險金**：給付金額為「保險金額」，且僅給付一次。  
+2. **生活補助保險金**：自初次診斷確定罹患特定傷病的次一個保險單週年日起，每逢保險單週年日仍生存者，按「保險金額」的36%給付，最高給付次數為10次。  
+3. **保險費豁免**：自診斷確定日起豁免續期保險費，但當期已繳付之未到期保險費不予退還。  
+給付對象為被保險人本人。  
+條文依據：  
+- [第十二條 特定傷病保險金的給付]  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]  
+- [第十五條 保險費豁免（第二保險單年度起適用）]</t>
+        </is>
+      </c>
+      <c r="G328" s="2" t="inlineStr"/>
+      <c r="H328" s="2" t="inlineStr"/>
+      <c r="I328" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.106964, "neutral": 0.883063, "contradiction": 0.009973, "factuality": 0.990027, "C_fact": 0.990027}, "C_conf": 0.99}</t>
+        </is>
+      </c>
+      <c r="J328" s="5" t="n"/>
+      <c r="K328" s="5" t="n">
+        <v>0.990027</v>
+      </c>
+      <c r="L328" s="5" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:12:31</t>
+        </is>
+      </c>
+      <c r="N328" s="5" t="n">
+        <v>3.56</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B329" s="2" t="inlineStr">
+        <is>
+          <t>請問我115年1月1日投保，怎麼得到健康促進保險費折減?</t>
+        </is>
+      </c>
+      <c r="C329" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+要獲得健康促進保險費折減，您需完成以下步驟：  
+1. 使用保險公司指定的程式並加入指定的健康計劃。  
+2. 完成程式註冊程序，執行該程式並授權保險公司取得與健康促進相關的電子紀錄。  
+3. 在「指定日期」時，您的會員等級需符合以下標準之一：  
+   - 實踐家：折減次一保險單年度保險費3%。  
+   - 樂享家或高於樂享家：折減次一保險單年度保險費10%。  
+注意：復效或豁免的保險費不適用折減約定。
+條文依據：  
+- [第十六條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="D329" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 健康促進保險費折減 | 第二十三條 投保年齡的計算及錯誤的處理 | 第十五條 保險費豁免（第二保險單年度起適用） | 第五條 保險範圍 | payout_items</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F329" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+要獲得健康促進保險費折減，您需完成以下步驟：  
+1. 使用保險公司指定的程式並加入指定的健康計劃。  
+2. 完成程式註冊程序，執行該程式並授權保險公司取得與健康促進相關的電子紀錄。  
+3. 在「指定日期」時，您的會員等級需符合以下標準之一：  
+   - 實踐家：折減次一保險單年度保險費3%。  
+   - 樂享家或高於樂享家：折減次一保險單年度保險費10%。  
+注意：復效或豁免的保險費不適用折減約定。
+條文依據：  
+- [第十六條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="G329" s="2" t="inlineStr"/>
+      <c r="H329" s="2" t="inlineStr"/>
+      <c r="I329" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.997202, "neutral": 0.001778, "contradiction": 0.00102, "factuality": 0.99898, "C_fact": 0.99898}, "C_conf": 0.999}</t>
+        </is>
+      </c>
+      <c r="J329" s="5" t="n"/>
+      <c r="K329" s="5" t="n">
+        <v>0.99898</v>
+      </c>
+      <c r="L329" s="5" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="M329" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:12:36</t>
+        </is>
+      </c>
+      <c r="N329" s="5" t="n">
+        <v>4.12</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B330" s="2" t="inlineStr">
+        <is>
+          <t>保戶在114/1/10投保樂鍾溢，如果他在115/3/30罹患特定傷病的話，在什麼時候可以領取生活補助保險金?</t>
+        </is>
+      </c>
+      <c r="C330" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保戶在114/1/10投保，保險單週年日為每年的1月10日。根據條款，生活補助保險金的給付需符合以下條件：  
+1. 被保險人於第二保險單年度（含）以後的有效期間內初次診斷確定罹患特定傷病。  
+2. 自初次診斷確定罹患特定傷病的次一個保險單週年日起，每逢各保險單週年日仍生存者，方可領取生活補助保險金。  
+保戶於115/3/30罹患特定傷病，符合第二保險單年度的條件。其初次診斷確定罹患特定傷病的次一個保險單週年日為116/1/10，因此保戶可於116/1/10起，每逢保險單週年日仍生存時，領取生活補助保險金。
+條文依據：  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]</t>
+        </is>
+      </c>
+      <c r="D330" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 生活補助保險金的給付（第二保險單年度起適用） | other_metadata | 第十一條 契約的終止（三） | payout_items | 第十二條 特定傷病保險金的給付 | 第五條 保險範圍 | 第十五條 保險費豁免（第二保險單年度起適用） | 第十條 契約的終止（二）</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F330" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保戶在114/1/10投保，保險單週年日為每年的1月10日。根據條款，生活補助保險金的給付需符合以下條件：  
+1. 被保險人於第二保險單年度（含）以後的有效期間內初次診斷確定罹患特定傷病。  
+2. 自初次診斷確定罹患特定傷病的次一個保險單週年日起，每逢各保險單週年日仍生存者，方可領取生活補助保險金。  
+保戶於115/3/30罹患特定傷病，符合第二保險單年度的條件。其初次診斷確定罹患特定傷病的次一個保險單週年日為116/1/10，因此保戶可於116/1/10起，每逢保險單週年日仍生存時，領取生活補助保險金。
+條文依據：  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]</t>
+        </is>
+      </c>
+      <c r="G330" s="2" t="inlineStr"/>
+      <c r="H330" s="2" t="inlineStr"/>
+      <c r="I330" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.974128, "neutral": 0.021456, "contradiction": 0.004416, "factuality": 0.995584, "C_fact": 0.995584}, "C_conf": 0.9956}</t>
+        </is>
+      </c>
+      <c r="J330" s="5" t="n"/>
+      <c r="K330" s="5" t="n">
+        <v>0.995584</v>
+      </c>
+      <c r="L330" s="5" t="n">
+        <v>0.9956</v>
+      </c>
+      <c r="M330" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:12:40</t>
+        </is>
+      </c>
+      <c r="N330" s="5" t="n">
+        <v>4.52</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B331" s="2" t="inlineStr">
+        <is>
+          <t>保戶在114/1/10投保樂鍾溢，如果他在115/3/30罹患特定傷病的話，他在115/1/9會領到無理賠回饋保險金嗎?</t>
+        </is>
+      </c>
+      <c r="C331" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不會領到無理賠回饋保險金。根據條款，無理賠回饋保險金的給付條件是被保險人在保險單年度末仍生存且未曾因罹患特定傷病申領「特定傷病保險金」。保戶在115/3/30罹患特定傷病，符合申領「特定傷病保險金」的條件，因此不符合無理賠回饋保險金的給付條件。
+條文依據：  
+- [第十四條 無理賠回饋保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D331" s="2" t="inlineStr">
+        <is>
+          <t>payout_items | 第十四條 無理賠回饋保險金的給付 | other_metadata | 第十二條 特定傷病保險金的給付 | 第二十條 無理賠回饋保險金的申領 | 第十條 契約的終止（二） | 第五條 保險範圍 | 第十五條 保險費豁免（第二保險單年度起適用）</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F331" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不會領到無理賠回饋保險金。根據條款，無理賠回饋保險金的給付條件是被保險人在保險單年度末仍生存且未曾因罹患特定傷病申領「特定傷病保險金」。保戶在115/3/30罹患特定傷病，符合申領「特定傷病保險金」的條件，因此不符合無理賠回饋保險金的給付條件。
+條文依據：  
+- [第十四條 無理賠回饋保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G331" s="2" t="inlineStr"/>
+      <c r="H331" s="2" t="inlineStr"/>
+      <c r="I331" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.792157, "neutral": 0.194897, "contradiction": 0.012945, "factuality": 0.987055, "C_fact": 0.987055}, "C_conf": 0.9871}</t>
+        </is>
+      </c>
+      <c r="J331" s="5" t="n"/>
+      <c r="K331" s="5" t="n">
+        <v>0.987055</v>
+      </c>
+      <c r="L331" s="5" t="n">
+        <v>0.9871</v>
+      </c>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:12:44</t>
+        </is>
+      </c>
+      <c r="N331" s="5" t="n">
+        <v>3.23</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B332" s="2" t="inlineStr">
+        <is>
+          <t>被保險人於第一保險單年度罹患急性心肌梗塞（重度），生活補助保險金最多可以領取幾次？</t>
+        </is>
+      </c>
+      <c r="C332" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於第一保險單年度罹患急性心肌梗塞（重度），無法申領生活補助保險金。根據條款規定，生活補助保險金的給付僅適用於第二保險單年度（含）以後的有效期間內初次診斷確定罹患特定傷病者。
+條文依據：  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]</t>
+        </is>
+      </c>
+      <c r="D332" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 生活補助保險金的給付（第二保險單年度起適用） | 第十二條 特定傷病保險金的給付 | 第十一條 契約的終止（三） | 第五條 保險範圍 | 第二條 名詞定義 | payout_items | 第十四條 無理賠回饋保險金的給付 | 第十九條 特定傷病保險金、生活補助保險金或保險費豁免的申領</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F332" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於第一保險單年度罹患急性心肌梗塞（重度），無法申領生活補助保險金。根據條款規定，生活補助保險金的給付僅適用於第二保險單年度（含）以後的有效期間內初次診斷確定罹患特定傷病者。
+條文依據：  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]</t>
+        </is>
+      </c>
+      <c r="G332" s="2" t="inlineStr"/>
+      <c r="H332" s="2" t="inlineStr"/>
+      <c r="I332" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.435759, "neutral": 0.557938, "contradiction": 0.006303, "factuality": 0.993697, "C_fact": 0.993697}, "C_conf": 0.9937}</t>
+        </is>
+      </c>
+      <c r="J332" s="5" t="n"/>
+      <c r="K332" s="5" t="n">
+        <v>0.9936970000000001</v>
+      </c>
+      <c r="L332" s="5" t="n">
+        <v>0.9937</v>
+      </c>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:12:47</t>
+        </is>
+      </c>
+      <c r="N332" s="5" t="n">
+        <v>2.81</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B333" s="2" t="inlineStr">
+        <is>
+          <t>被保險人為60歲女性，投保繳費期間20年期之樂鍾心特定傷病定期健康保險（外溢型）5單位，每單位年繳應繳保險費為1675元，則每逢保險單年度末生存者，可以領取多少無理賠關懷保險金？</t>
+        </is>
+      </c>
+      <c r="C333" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人每逢保險單年度末仍生存且未曾因罹患特定傷病申領「特定傷病保險金」者，可領取的「無理賠回饋保險金」金額為：每單位年繳應繳保險費的百分之十乘以單位數。計算如下：  
+每單位年繳應繳保險費為1675元，百分之十為167.5元，元以下無條件進位為168元。  
+5單位的金額為168元 × 5 = 840元。  
+因此，每逢保險單年度末生存者，可領取840元的「無理賠回饋保險金」。
+條文依據：  
+- [第十四條 無理賠回饋保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D333" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 無理賠回饋保險金的給付 | other_metadata | payout_items | 第二十條 無理賠回饋保險金的申領 | 第十二條 特定傷病保險金的給付 | 第十三條 生活補助保險金的給付（第二保險單年度起適用） | 第五條 保險範圍 | 第十五條 保險費豁免（第二保險單年度起適用）</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F333" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人每逢保險單年度末仍生存且未曾因罹患特定傷病申領「特定傷病保險金」者，可領取的「無理賠回饋保險金」金額為：每單位年繳應繳保險費的百分之十乘以單位數。計算如下：  
+每單位年繳應繳保險費為1675元，百分之十為167.5元，元以下無條件進位為168元。  
+5單位的金額為168元 × 5 = 840元。  
+因此，每逢保險單年度末生存者，可領取840元的「無理賠回饋保險金」。
+條文依據：  
+- [第十四條 無理賠回饋保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G333" s="2" t="inlineStr"/>
+      <c r="H333" s="2" t="inlineStr"/>
+      <c r="I333" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.993663, "neutral": 0.005904, "contradiction": 0.000433, "factuality": 0.999567, "C_fact": 0.999567}, "C_conf": 0.9996}</t>
+        </is>
+      </c>
+      <c r="J333" s="5" t="n"/>
+      <c r="K333" s="5" t="n">
+        <v>0.999567</v>
+      </c>
+      <c r="L333" s="5" t="n">
+        <v>0.9996</v>
+      </c>
+      <c r="M333" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:12:59</t>
+        </is>
+      </c>
+      <c r="N333" s="5" t="n">
+        <v>12.27</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/rag_results.xlsx
+++ b/src/rag_results.xlsx
@@ -32,7 +32,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +42,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -62,7 +67,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -71,6 +76,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
@@ -438,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -590,6 +598,5348 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>保障範圍包括哪些項目？</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括：住院醫療保險金、加護病房或燒燙傷病房保險金、祝壽保險金、身故保險金或喪葬費用保險金，以及所繳保險費的退還。
+條文依據：  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>payout_items | summary | 第五條 保險範圍 | 第二條 名詞定義 | 第十八條 除外責任（一）</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括：住院醫療保險金、加護病房或燒燙傷病房保險金、祝壽保險金、身故保險金或喪葬費用保險金，以及所繳保險費的退還。
+條文依據：  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "保障範圍包括哪些項目？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.998507, "neutral": 0.001349, "contradiction": 0.000145, "factuality": 0.999855, "C_fact": 0.999855}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>0.999855</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:13:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>住院日數計算有什麼特殊規則？</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院日數的計算規則如下：  
+1. 住院日數是按被保險人同一次住院的實際全日住進急性病房或慢性病房（含加護病房及燒燙傷病房）的日數計算，包含住院當日及出院當日。  
+2. 若被保險人出院後於同一日再次入院診療，該日不得重複計入住院日數。  
+條文依據：  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第十二條 住院醫療保險金的給付 | 第二條 名詞定義 | 第十三條 加護病房或燒燙傷病房保險金的給付 | 第二十八條 住院醫療保險金日額之減少</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院日數的計算規則如下：  
+1. 住院日數是按被保險人同一次住院的實際全日住進急性病房或慢性病房（含加護病房及燒燙傷病房）的日數計算，包含住院當日及出院當日。  
+2. 若被保險人出院後於同一日再次入院診療，該日不得重複計入住院日數。  
+條文依據：  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "住院日數計算有什麼特殊規則？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.997897, "neutral": 0.001923, "contradiction": 0.00018, "factuality": 0.99982, "C_fact": 0.99982}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>0.99982</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:13:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>住院醫療保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院醫療保險金的給付規定如下：  
+1. 被保險人於契約有效期間內因疾病或傷害住院治療時，保險公司將依保險單所載的「住院醫療保險金日額」，乘以入院日當年度的「增額係數」，再乘以住院日數，給付住院醫療保險金。  
+2. 同一保單年度內，同一次住院的住院醫療保險金給付日數，最高以365日為限。  
+條文依據：  
+- [第十二條 住院醫療保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 住院醫療保險金的給付 | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第十三條 加護病房或燒燙傷病房保險金的給付 | 第十四條 醫療保險金給付總額之上限 | 第二十八條 住院醫療保險金日額之減少</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院醫療保險金的給付規定如下：  
+1. 被保險人於契約有效期間內因疾病或傷害住院治療時，保險公司將依保險單所載的「住院醫療保險金日額」，乘以入院日當年度的「增額係數」，再乘以住院日數，給付住院醫療保險金。  
+2. 同一保單年度內，同一次住院的住院醫療保險金給付日數，最高以365日為限。  
+條文依據：  
+- [第十二條 住院醫療保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "住院醫療保險金的給付規定", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.996683, "neutral": 0.002892, "contradiction": 0.000425, "factuality": 0.999575, "C_fact": 0.999575}, "C_conf": 0.9997}</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>0.999575</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:13:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>加護病房或燒燙傷病房保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+加護病房或燒燙傷病房保險金的給付規定如下：  
+被保險人於本契約有效期間內因疾病或傷害而在醫院的加護病房或燒燙傷病房接受治療時，除住院醫療保險金外，保險公司將依保險單上記載的「住院醫療保險金日額」，乘以入院日當年度的「增額係數」，再乘以實際住進加護病房或燒燙傷病房的日數（含轉入及轉出當日）的二倍，給付「加護病房或燒燙傷病房保險金」。  
+同一保單年度內，同一次住院的加護病房及燒燙傷病房住院日數合計最高以365日為限，但同一日內僅給付其中一種病房的保險金。
+條文依據：  
+- [第十三條 加護病房或燒燙傷病房保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 加護病房或燒燙傷病房保險金的給付 | payout_items | 第二十三條 醫療保險金的申領 | 第五條 保險範圍 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+加護病房或燒燙傷病房保險金的給付規定如下：  
+被保險人於本契約有效期間內因疾病或傷害而在醫院的加護病房或燒燙傷病房接受治療時，除住院醫療保險金外，保險公司將依保險單上記載的「住院醫療保險金日額」，乘以入院日當年度的「增額係數」，再乘以實際住進加護病房或燒燙傷病房的日數（含轉入及轉出當日）的二倍，給付「加護病房或燒燙傷病房保險金」。  
+同一保單年度內，同一次住院的加護病房及燒燙傷病房住院日數合計最高以365日為限，但同一日內僅給付其中一種病房的保險金。
+條文依據：  
+- [第十三條 加護病房或燒燙傷病房保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "加護病房或燒燙傷病房保險金的給付規定", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.99608, "neutral": 0.0033, "contradiction": 0.00062, "factuality": 0.99938, "C_fact": 0.99938}, "C_conf": 0.9996}</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0.99938</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0.9996</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:14:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>醫療保險金給付總額之上限</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+醫療保險金給付總額之上限為保險單上所記載之「住院醫療保險金日額」的二千五百倍，並適用於本契約有效期間內依第十二條至第十三條所給付之各項保險金的累計總額。
+條文依據：  
+- [第十四條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 醫療保險金給付總額之上限 | 第十二條 住院醫療保險金的給付 | 第五條 保險範圍 | 第十三條 加護病房或燒燙傷病房保險金的給付 | payout_items</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+醫療保險金給付總額之上限為保險單上所記載之「住院醫療保險金日額」的二千五百倍，並適用於本契約有效期間內依第十二條至第十三條所給付之各項保險金的累計總額。
+條文依據：  
+- [第十四條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "醫療保險金給付總額之上限", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.996196, "neutral": 0.003514, "contradiction": 0.00029, "factuality": 0.99971, "C_fact": 0.99971}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>0.99971</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:14:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>祝壽保險金的給付規定為何?</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+祝壽保險金的給付規定如下：  
+被保險人於本契約有效期間內，且保險年齡到達九十九歲之保險單週年日仍生存時，本公司將按「當年度保險金額」給付「祝壽保險金」。
+條文依據：  
+- [第十五條 祝壽保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>第十五條 祝壽保險金的給付 | 第十二條至第十三條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | 第二十四條 祝壽保險金的申領 | payout_items | 第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+祝壽保險金的給付規定如下：  
+被保險人於本契約有效期間內，且保險年齡到達九十九歲之保險單週年日仍生存時，本公司將按「當年度保險金額」給付「祝壽保險金」。
+條文依據：  
+- [第十五條 祝壽保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "祝壽保險金的給付規定為何?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.998014, "neutral": 0.001828, "contradiction": 0.000157, "factuality": 0.999843, "C_fact": 0.999843}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>0.999843</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:14:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>有效期間內身故，保險金如何給付?</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於本契約有效期間內身故時，本公司依以下情況給付保險金：  
+1. 若被保險人於繳費期間內身故，已繳付之未到期保險費不予退還，亦不併入身故保險金內給付。  
+2. 若被保險人於實際年齡未滿十五足歲時身故，本公司退還「所繳保險費」，不適用身故保險金的約定。  
+3. 若被保險人為受監護宣告尚未撤銷者，其身故保險金變更為喪葬費用保險金，且喪葬費用保險金額不得超過遺產稅喪葬費扣除額之半數，超過部分不負給付責任，並退還超過部分的已繳保險費。
+條文依據：  
+- [第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付 | 第十條 契約的終止（二） | 第五條 保險範圍 | 第二十二條 失蹤處理 | 第十五條 祝壽保險金的給付</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於本契約有效期間內身故時，本公司依以下情況給付保險金：  
+1. 若被保險人於繳費期間內身故，已繳付之未到期保險費不予退還，亦不併入身故保險金內給付。  
+2. 若被保險人於實際年齡未滿十五足歲時身故，本公司退還「所繳保險費」，不適用身故保險金的約定。  
+3. 若被保險人為受監護宣告尚未撤銷者，其身故保險金變更為喪葬費用保險金，且喪葬費用保險金額不得超過遺產稅喪葬費扣除額之半數，超過部分不負給付責任，並退還超過部分的已繳保險費。
+條文依據：  
+- [第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "有效期間內身故，保險金如何給付?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.984315, "neutral": 0.014334, "contradiction": 0.001351, "factuality": 0.998649, "C_fact": 0.998649}, "C_conf": 0.9992}</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>0.998649</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>0.9992</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:14:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>健康促進保險費折減規定</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+健康促進保險費折減規定如下：  
+1. 被保險人年齡需達20歲（含）以上，並使用保險公司指定程式加入健康計劃。  
+2. 若於「指定日期」會員等級符合標準，可享次一保險單年度保險費折減：  
+   - 進階會員：折減2%。  
+   - 菁英會員或更高等級：折減3%。  
+3. 折減僅適用於主契約保險費，不包含附約、附加條款或批註條款，且豁免或復效的保險費不適用折減。  
+4. 被保險人需完成程式註冊並授權保險公司取得健康相關電子紀錄，保險公司將依紀錄計算會員等級。
+條文依據：  
+- [第十七條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>第十七條 健康促進保險費折減 | 第二十八條 住院醫療保險金日額之減少 | 第三十條 投保年齡的計算及錯誤的處理 | 第二條 名詞定義 | 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+健康促進保險費折減規定如下：  
+1. 被保險人年齡需達20歲（含）以上，並使用保險公司指定程式加入健康計劃。  
+2. 若於「指定日期」會員等級符合標準，可享次一保險單年度保險費折減：  
+   - 進階會員：折減2%。  
+   - 菁英會員或更高等級：折減3%。  
+3. 折減僅適用於主契約保險費，不包含附約、附加條款或批註條款，且豁免或復效的保險費不適用折減。  
+4. 被保險人需完成程式註冊並授權保險公司取得健康相關電子紀錄，保險公司將依紀錄計算會員等級。
+條文依據：  
+- [第十七條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "健康促進保險費折減規定", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.993294, "neutral": 0.006042, "contradiction": 0.000664, "factuality": 0.999336, "C_fact": 0.999336}, "C_conf": 0.9996}</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>0.999336</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>0.9996</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:14:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>除外責任的解釋?</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+除外責任是指保險公司對於某些特定原因或情況下所發生的疾病、傷害或死亡，不負給付保險金的責任。以下為相關條文中的主要除外責任內容：  
+1. **一般除外責任**：  
+   - 被保險人因故意行為（如自殺、自殺未遂）、犯罪行為或非法施用毒品所致疾病或傷害，保險公司不負給付責任。  
+   - 因美容手術、外科整型（非重建基本功能所需者）、健康檢查、療養等非直接診治病人目的的行為，保險公司不負給付責任。  
+2. **懷孕相關除外責任**：  
+   - 懷孕、流產或分娩及其併發症一般不在保障範圍內，但以下情況例外：  
+     （一）特定懷孕相關疾病（如子宮外孕、葡萄胎等）。  
+     （二）因醫療行為必要的流產（如因遺傳性疾病或懷孕危及生命等）。  
+     （三）符合醫療行為必要的剖腹產（如胎位不正、多胞胎等）。  
+條文依據：  
+- [第十八條 除外責任（一）]  
+- [第十九條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第十九條 除外責任（二） | 第八條 告知義務與本契約的解除 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+除外責任是指保險公司對於某些特定原因或情況下所發生的疾病、傷害或死亡，不負給付保險金的責任。以下為相關條文中的主要除外責任內容：  
+1. **一般除外責任**：  
+   - 被保險人因故意行為（如自殺、自殺未遂）、犯罪行為或非法施用毒品所致疾病或傷害，保險公司不負給付責任。  
+   - 因美容手術、外科整型（非重建基本功能所需者）、健康檢查、療養等非直接診治病人目的的行為，保險公司不負給付責任。  
+2. **懷孕相關除外責任**：  
+   - 懷孕、流產或分娩及其併發症一般不在保障範圍內，但以下情況例外：  
+     （一）特定懷孕相關疾病（如子宮外孕、葡萄胎等）。  
+     （二）因醫療行為必要的流產（如因遺傳性疾病或懷孕危及生命等）。  
+     （三）符合醫療行為必要的剖腹產（如胎位不正、多胞胎等）。  
+條文依據：  
+- [第十八條 除外責任（一）]  
+- [第十九條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "除外責任的解釋?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.941516, "neutral": 0.056707, "contradiction": 0.001777, "factuality": 0.998223, "C_fact": 0.998223}, "C_conf": 0.9989}</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>0.998223</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>0.9989</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:15:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>哪些疾病被含在除外責任?</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人因以下原因所致之疾病或傷害，屬於除外責任，本公司不負給付保險金的責任：  
+1. 被保險人之故意行為（包括自殺及自殺未遂）。  
+2. 被保險人之犯罪行為。  
+3. 被保險人非法施用毒品。  
+4. 美容手術、外科整型（但為重建基本功能所作之必要整型不在此限）。  
+5. 外觀可見之天生畸形。  
+6. 健康檢查、療養、靜養、戒毒、戒酒、護理或養老等非以直接診治病人為目的者。  
+7. 懷孕、流產或分娩及其併發症（但特定情形如子宮外孕、葡萄胎等不在此限）。  
+8. 不孕症、人工受孕或非以治療為目的之避孕及絕育手術。  
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第二條 名詞定義 | 第十九條 除外責任（二）</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人因以下原因所致之疾病或傷害，屬於除外責任，本公司不負給付保險金的責任：  
+1. 被保險人之故意行為（包括自殺及自殺未遂）。  
+2. 被保險人之犯罪行為。  
+3. 被保險人非法施用毒品。  
+4. 美容手術、外科整型（但為重建基本功能所作之必要整型不在此限）。  
+5. 外觀可見之天生畸形。  
+6. 健康檢查、療養、靜養、戒毒、戒酒、護理或養老等非以直接診治病人為目的者。  
+7. 懷孕、流產或分娩及其併發症（但特定情形如子宮外孕、葡萄胎等不在此限）。  
+8. 不孕症、人工受孕或非以治療為目的之避孕及絕育手術。  
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "哪些疾病被含在除外責任?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.998033, "neutral": 0.00171, "contradiction": 0.000257, "factuality": 0.999743, "C_fact": 0.999743}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>0.999743</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:15:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>進行美容手術住院可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，因美容手術住院無法申請理賠。但若美容手術是為了重建基本功能所作之必要整型，則不在此限，可以申請理賠。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第十三條 加護病房或燒燙傷病房保險金的給付 | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第二條 名詞定義 | payout_items</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，因美容手術住院無法申請理賠。但若美容手術是為了重建基本功能所作之必要整型，則不在此限，可以申請理賠。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "進行美容手術住院可以申請理賠嗎?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.845325, "neutral": 0.152107, "contradiction": 0.002569, "factuality": 0.997431, "C_fact": 0.997431}, "C_conf": 0.9985}</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>0.997431</v>
+      </c>
+      <c r="L13" s="3" t="n">
+        <v>0.9985000000000001</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:15:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>因胎兒染色體異常進行手術而住院可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以申請理賠。根據條款，因「胎兒染色體異常之手術」住院診療不屬於除外責任範圍，因此符合理賠條件。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第二條 名詞定義 | payout_items | 第十三條 加護病房或燒燙傷病房保險金的給付</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以申請理賠。根據條款，因「胎兒染色體異常之手術」住院診療不屬於除外責任範圍，因此符合理賠條件。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "因胎兒染色體異常進行手術而住院可以申請理賠嗎?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.988765, "neutral": 0.01088, "contradiction": 0.000355, "factuality": 0.999645, "C_fact": 0.999645}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>0.999645</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:15:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>因胎位不正進行手術而住院可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，因胎位不正進行手術而住院屬於除外責任範圍內，但若該手術為醫療行為必要之剖腹產，且符合條款中列明的情況（如胎位不正），則不在除外責任之列，可申請理賠。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第二條 名詞定義 | payout_items | 第十三條 加護病房或燒燙傷病房保險金的給付</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，因胎位不正進行手術而住院屬於除外責任範圍內，但若該手術為醫療行為必要之剖腹產，且符合條款中列明的情況（如胎位不正），則不在除外責任之列，可申請理賠。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "因胎位不正進行手術而住院可以申請理賠嗎?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.726287, "neutral": 0.271228, "contradiction": 0.002485, "factuality": 0.997515, "C_fact": 0.997515}, "C_conf": 0.9985}</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>0.997515</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>0.9985000000000001</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:15:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>因自殺未遂導致住院可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人因自殺未遂導致住院，本公司不負給付住院相關保險金的責任，因其屬於被保險人之故意行為。但若條文中未提及例外情況，則無其他補充說明。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 除外責任（二） | 第十八條 除外責任（一） | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | payout_items | 第十條 契約的終止（二）</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人因自殺未遂導致住院，本公司不負給付住院相關保險金的責任，因其屬於被保險人之故意行為。但若條文中未提及例外情況，則無其他補充說明。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "因自殺未遂導致住院可以申請理賠嗎?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.924045, "neutral": 0.06981, "contradiction": 0.006145, "factuality": 0.993855, "C_fact": 0.993855}, "C_conf": 0.9963}</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>0.993855</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>0.9963</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:15:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>被保險人在投保一年內故意自殺者，可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人在投保一年內故意自殺者，保險公司不負給付身故保險金或喪葬費用保險金的責任。只有在契約訂立或復效之日起滿二年後，故意自殺致死的情況下，保險公司才負給付責任。
+條文依據：  
+- [第十九條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 除外責任（二） | 第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付 | 第十條 契約的終止（二） | 第三十條 投保年齡的計算及錯誤的處理 | 第十八條 除外責任（一）</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人在投保一年內故意自殺者，保險公司不負給付身故保險金或喪葬費用保險金的責任。只有在契約訂立或復效之日起滿二年後，故意自殺致死的情況下，保險公司才負給付責任。
+條文依據：  
+- [第十九條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "被保險人在投保一年內故意自殺者，可以申請理賠嗎?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.997769, "neutral": 0.00196, "contradiction": 0.000271, "factuality": 0.999729, "C_fact": 0.999729}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>0.999729</v>
+      </c>
+      <c r="L17" s="3" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:16:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>申請理賠有什麼時間規定嗎?</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申請理賠的時間規定如下：要保人、被保險人或受益人應於知悉保險事故後十日內通知保險公司，並於通知後儘速檢具所需文件向保險公司申請給付保險金。保險公司應於收齊文件後十五日內完成給付。如因保險公司可歸責的原因未能在期限內給付，應按年利一分加計利息給付。
+條文依據：  
+- [第二十一條 保險事故的通知與保險金的申請時間]</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>第二十一條 保險事故的通知與保險金的申請時間 | 第六條 第二期以後保險費的交付、寬限期間及契約效力的停止 | 第七條 本契約效力的恢復 | 第三條 契約撤銷權 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申請理賠的時間規定如下：要保人、被保險人或受益人應於知悉保險事故後十日內通知保險公司，並於通知後儘速檢具所需文件向保險公司申請給付保險金。保險公司應於收齊文件後十五日內完成給付。如因保險公司可歸責的原因未能在期限內給付，應按年利一分加計利息給付。
+條文依據：  
+- [第二十一條 保險事故的通知與保險金的申請時間]</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "申請理賠有什麼時間規定嗎?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.997906, "neutral": 0.001938, "contradiction": 0.000157, "factuality": 0.999843, "C_fact": 0.999843}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>0.999843</v>
+      </c>
+      <c r="L18" s="3" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:16:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>燒燙傷病房保險金怎麼申領?</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申領燒燙傷病房保險金時，受益人需檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 醫療診斷書或住院證明，且需列明進、出燒燙傷病房的日期。（但要保人或被保險人為醫師時，不得為被保險人出具診斷書或住院證明。）  
+4. 受益人的身分證明。  
+此外，保險公司基於審核保險金的需要，得徵詢其他醫師的醫學專業意見，並經受益人同意調閱被保險人的就醫相關資料，相關費用由保險公司負擔。
+條文依據：  
+- [第二十三條 醫療保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>第二十三條 醫療保險金的申領 | 第十三條 加護病房或燒燙傷病房保險金的給付 | payout_items | 第二條 名詞定義 | 第二十一條 保險事故的通知與保險金的申請時間</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申領燒燙傷病房保險金時，受益人需檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 醫療診斷書或住院證明，且需列明進、出燒燙傷病房的日期。（但要保人或被保險人為醫師時，不得為被保險人出具診斷書或住院證明。）  
+4. 受益人的身分證明。  
+此外，保險公司基於審核保險金的需要，得徵詢其他醫師的醫學專業意見，並經受益人同意調閱被保險人的就醫相關資料，相關費用由保險公司負擔。
+條文依據：  
+- [第二十三條 醫療保險金的申領]</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "燒燙傷病房保險金怎麼申領?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.998148, "neutral": 0.001672, "contradiction": 0.00018, "factuality": 0.99982, "C_fact": 0.99982}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>0.99982</v>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:16:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>活到99歲怎麼申請祝壽金?</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申請祝壽保險金時，受益人需檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 受益人的身分證明。  
+條文依據：  
+- [第二十四條 祝壽保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>第十五條 祝壽保險金的給付 | 第二十四條 祝壽保險金的申領 | 第五條 保險範圍 | 第十二條至第十三條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | announcement_history</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申請祝壽保險金時，受益人需檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 受益人的身分證明。  
+條文依據：  
+- [第二十四條 祝壽保險金的申領]</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "活到99歲怎麼申請祝壽金?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.99803, "neutral": 0.001868, "contradiction": 0.000103, "factuality": 0.999897, "C_fact": 0.999897}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>0.999897</v>
+      </c>
+      <c r="L20" s="3" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:16:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>被保人身故怎麼申請理賠</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+受益人申請「身故保險金」或「喪葬費用保險金」時，需檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 被保險人死亡證明書及除戶戶籍謄本。  
+4. 受益人的身分證明。  
+條文依據：  
+- [第二十五條 身故保險金或喪葬費用保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付 | 第十二條至第十三條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | 第二十二條 失蹤處理 | 第二十五條 身故保險金或喪葬費用保險金的申領 | 第十九條 除外責任（二）</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+受益人申請「身故保險金」或「喪葬費用保險金」時，需檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 被保險人死亡證明書及除戶戶籍謄本。  
+4. 受益人的身分證明。  
+條文依據：  
+- [第二十五條 身故保險金或喪葬費用保險金的申領]</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "被保人身故怎麼申請理賠", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.996283, "neutral": 0.003565, "contradiction": 0.000152, "factuality": 0.999848, "C_fact": 0.999848}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>0.999848</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:16:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>投保15年後，因手術住院3天，住院日額為2500元，請問可以申請多少理賠?</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款，被保險人住院3天且住院日額為每日2500元，住院保險金總額為2500元 × 3天 = 7500元。手術並未影響住院保險金的申請條件，因此可申請7500元的理賠。
+條文依據：  
+- [第十二條 住院醫療保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 住院醫療保險金的給付 | 第十三條 加護病房或燒燙傷病房保險金的給付 | 第二十八條 住院醫療保險金日額之減少 | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | payout_items | 第五條 保險範圍 | 第二條 名詞定義 | 第二十一條 保險事故的通知與保險金的申請時間</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款，被保險人住院3天且住院日額為每日2500元，住院保險金總額為2500元 × 3天 = 7500元。手術並未影響住院保險金的申請條件，因此可申請7500元的理賠。
+條文依據：  
+- [第十二條 住院醫療保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認住院日額保險金為每日2500元", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認住院天數為3天", "must_have": true, "分數": 1.0}, {"id": "3", "point": "計算住院保險金總額", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認手術是否影響住院保險金申請條件", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.992518, "neutral": 0.007219, "contradiction": 0.000262, "factuality": 0.999738, "C_fact": 0.999738}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>0.999738</v>
+      </c>
+      <c r="L22" s="3" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:16:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>保障範圍包括哪些項目？</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括：住院手術醫療保險金、門診手術醫療保險金、特定處置保險金、意外創傷縫合處置保險金、意外住院手術醫療保險金、祝壽保險金、所繳保險費的退還、身故保險金或喪葬費用保險金。
+條文依據：  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>payout_items | 第五條 保險範圍 | summary | 第四條 名詞定義 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括：住院手術醫療保險金、門診手術醫療保險金、特定處置保險金、意外創傷縫合處置保險金、意外住院手術醫療保險金、祝壽保險金、所繳保險費的退還、身故保險金或喪葬費用保險金。
+條文依據：  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "保障範圍包括哪些項目？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.998072, "neutral": 0.001746, "contradiction": 0.000182, "factuality": 0.999818, "C_fact": 0.999818}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" s="3" t="n">
+        <v>0.999818</v>
+      </c>
+      <c r="L23" s="3" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:16:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>保險金額是否有上限?</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+有，保險金額的給付總額上限為保險單上所記載「保險金額」的一千五百倍，且不包含其他附約、附加條款或批註條款。
+條文依據：  
+- [第十六條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 醫療保險金給付總額之上限 | 第三十條 保險金額之減少 | 第五條 保險範圍 | 第十九條 健康促進保險費折減 | 第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+有，保險金額的給付總額上限為保險單上所記載「保險金額」的一千五百倍，且不包含其他附約、附加條款或批註條款。
+條文依據：  
+- [第十六條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "保險金額是否有上限?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.997606, "neutral": 0.00227, "contradiction": 0.000124, "factuality": 0.999876, "C_fact": 0.999876}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>0.999876</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:17:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>投保後5天發生手術，是否可以申請理賠?</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款，被保險人於保險契約有效期間內因疾病或傷害接受手術，符合附表一所列手術項目且不屬除外責任範圍者，可申請理賠。然而，若疾病發生於契約生效日起持續有效第三十一日之前，則不符合理賠條件，除非屬特定疾病不適用等待期間的情形。投保後5天發生手術，是否符合理賠條件需視疾病是否屬等待期間限制及手術是否符合附表一所列項目而定。  
+條款依據：  
+[第五條 保險範圍]  
+[第十一條 住院手術醫療保險金]  
+[第四條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第十一條 住院手術醫療保險金 | 第二十條 除外責任（一） | 第十二條 門診手術醫療保險金 | 第十三條 意外住院手術醫療保險金 | 第二十三條 保險事故的通知與保險金的申請時間 | 第四條 名詞定義 | 第十五條 意外創傷縫合處置保險金 | 附表三：意外創傷縫合處置項目及給付倍數表 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+找不到相關內容  
+條文依據：  
+找不到相關內容</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款，被保險人於保險契約有效期間內因疾病或傷害接受手術，符合附表一所列手術項目且不屬除外責任範圍者，可申請理賠。然而，若疾病發生於契約生效日起持續有效第三十一日之前，則不符合理賠條件，除非屬特定疾病不適用等待期間的情形。投保後5天發生手術，是否符合理賠條件需視疾病是否屬等待期間限制及手術是否符合附表一所列項目而定。  
+條款依據：  
+[第五條 保險範圍]  
+[第十一條 住院手術醫療保險金]  
+[第四條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "投保後5天發生手術，是否可以申請理賠?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.909678, "neutral": 0.070288, "contradiction": 0.020034, "factuality": 0.979966, "C_fact": 0.979966}, "C_conf": 0.9879}</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>0.979966</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>0.9879</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:17:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>住院手術醫療保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院手術醫療保險金的給付規定如下：  
+1. 被保險人需於保險契約有效期間內，因疾病或傷害經醫師診斷必須住院接受附表一所列的手術治療，且已實際接受手術。  
+2. 給付金額計算方式為：保險單所載「保險金額」乘以手術日當年度的「增額係數」，再乘以手術給付倍數。  
+3. 若同一次手術中於同一手術位置接受兩項以上手術項目，僅給付手術給付倍數最高的手術項目。  
+4. 未載明於附表一的手術項目，將與被保險人協議比照附表內程度相當的手術項目決定給付倍數。  
+5. 以下情形不予給付：  
+   - 屬於除外責任條款規定的情形。  
+   - 不屬於全民健康保險醫療服務給付項目及支付標準第二部第二章第七節或第三部第三章第四節第三項所列舉的手術。  
+條文依據：  
+- [第十一條 住院手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 住院手術醫療保險金 | 第十三條 意外住院手術醫療保險金 | 第十二條 門診手術醫療保險金 | payout_items | 第二十條 除外責任（一） | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院手術醫療保險金的給付規定如下：  
+1. 被保險人需於保險契約有效期間內，因疾病或傷害經醫師診斷必須住院接受附表一所列的手術治療，且已實際接受手術。  
+2. 給付金額計算方式為：保險單所載「保險金額」乘以手術日當年度的「增額係數」，再乘以手術給付倍數。  
+3. 若同一次手術中於同一手術位置接受兩項以上手術項目，僅給付手術給付倍數最高的手術項目。  
+4. 未載明於附表一的手術項目，將與被保險人協議比照附表內程度相當的手術項目決定給付倍數。  
+5. 以下情形不予給付：  
+   - 屬於除外責任條款規定的情形。  
+   - 不屬於全民健康保險醫療服務給付項目及支付標準第二部第二章第七節或第三部第三章第四節第三項所列舉的手術。  
+條文依據：  
+- [第十一條 住院手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "住院手術醫療保險金的給付規定", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.995344, "neutral": 0.004265, "contradiction": 0.00039, "factuality": 0.99961, "C_fact": 0.99961}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>0.99961</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:17:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>門診手術醫療保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+門診手術醫療保險金的給付規定如下：  
+1. 被保險人需於本契約有效期間內，因疾病或傷害經醫師診斷必須於醫院或診所門診接受附表一所列的手術治療，且已實際接受手術。  
+2. 給付金額計算方式為：保險單所記載的「保險金額」乘以手術日當年度的「增額係數」，再乘以手術給付倍數。  
+3. 同一次手術中，若於同一手術位置接受兩項以上手術項目，僅給付手術給付倍數最高的手術項目。  
+4. 同一保險單年度內，門診手術醫療保險金的給付以十次為限。  
+5. 若手術項目未載明於附表一，本公司將與被保險人協議比照附表內的手術項目決定給付倍數。  
+6. 以下情形不負給付責任：  
+   - 屬於本契約除外責任條款規定的情形。  
+   - 不屬於全民健康保險醫療服務給付項目及支付標準第二部第二章第七節或第三部第三章第四節第三項所列舉的手術。  
+條文依據：  
+- [第十二條 門診手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 門診手術醫療保險金 | 第十一條 住院手術醫療保險金 | payout_items | 第十三條 意外住院手術醫療保險金 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+門診手術醫療保險金的給付規定如下：  
+1. 被保險人需於本契約有效期間內，因疾病或傷害經醫師診斷必須於醫院或診所門診接受附表一所列的手術治療，且已實際接受手術。  
+2. 給付金額計算方式為：保險單所記載的「保險金額」乘以手術日當年度的「增額係數」，再乘以手術給付倍數。  
+3. 同一次手術中，若於同一手術位置接受兩項以上手術項目，僅給付手術給付倍數最高的手術項目。  
+4. 同一保險單年度內，門診手術醫療保險金的給付以十次為限。  
+5. 若手術項目未載明於附表一，本公司將與被保險人協議比照附表內的手術項目決定給付倍數。  
+6. 以下情形不負給付責任：  
+   - 屬於本契約除外責任條款規定的情形。  
+   - 不屬於全民健康保險醫療服務給付項目及支付標準第二部第二章第七節或第三部第三章第四節第三項所列舉的手術。  
+條文依據：  
+- [第十二條 門診手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "門診手術醫療保險金的給付規定", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.984771, "neutral": 0.014813, "contradiction": 0.000416, "factuality": 0.999584, "C_fact": 0.999584}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>0.999584</v>
+      </c>
+      <c r="L27" s="3" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:17:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>意外住院手術醫療保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外住院手術醫療保險金的給付規定如下：  
+1. 被保險人需於本契約有效期間內，且保險年齡未滿七十歲。  
+2. 因傷害經醫師診斷，在住院期間必須接受手術治療且已接受手術者。  
+3. 給付金額為保險單所記載之「保險金額」的三倍，乘以手術日當年度之「增額係數」。  
+4. 同一次手術中，於同一手術位置接受二項以上手術項目時，僅給付一次意外住院手術醫療保險金。
+條文依據：  
+- [第十三條 意外住院手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 意外住院手術醫療保險金 | 第十一條 住院手術醫療保險金 | 第十五條 意外創傷縫合處置保險金 | 第二十條 除外責任（一） | 第十二條 門診手術醫療保險金 | 附表三：意外創傷縫合處置項目及給付倍數表 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外住院手術醫療保險金的給付規定如下：  
+1. 被保險人需於本契約有效期間內，且保險年齡未滿七十歲。  
+2. 因傷害經醫師診斷，在住院期間必須接受手術治療且已接受手術者。  
+3. 給付金額為保險單所記載之「保險金額」的三倍，乘以手術日當年度之「增額係數」。  
+4. 同一次手術中，於同一手術位置接受二項以上手術項目時，僅給付一次意外住院手術醫療保險金。
+條文依據：  
+- [第十三條 意外住院手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "意外住院手術醫療保險金的給付規定", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.997756, "neutral": 0.002026, "contradiction": 0.000218, "factuality": 0.999782, "C_fact": 0.999782}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>0.9997819999999999</v>
+      </c>
+      <c r="L28" s="3" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:17:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>特定處置保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+特定處置保險金的給付規定如下：  
+1. 被保險人需於保險契約有效期間內，因疾病或傷害經醫師診斷必須接受附表二所列的特定處置治療，且實際完成處置後，保險公司才會給付特定處置保險金。  
+2. 給付金額計算方式為：保險單上記載的「保險金額」× 特定處置日當年度的「增額係數」× 特定處置給付倍數。  
+3. 同一次處置治療中，若於同一治療位置接受兩項以上特定處置項目，僅給付特定處置給付倍數最高的項目。  
+4. 若接受的處置未列於附表二，保險公司不負給付責任。  
+5. 同一保險單年度內，特定處置保險金的給付次數以十次為限。
+條文依據：  
+- [第十四條 特定處置保險金]</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 特定處置保險金 | 第十五條 意外創傷縫合處置保險金 | 附表二：特定處置項目及給付倍數表 | 第五條 保險範圍 | 附表三：意外創傷縫合處置項目及給付倍數表</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+特定處置保險金的給付規定如下：  
+1. 被保險人需於保險契約有效期間內，因疾病或傷害經醫師診斷必須接受附表二所列的特定處置治療，且實際完成處置後，保險公司才會給付特定處置保險金。  
+2. 給付金額計算方式為：保險單上記載的「保險金額」× 特定處置日當年度的「增額係數」× 特定處置給付倍數。  
+3. 同一次處置治療中，若於同一治療位置接受兩項以上特定處置項目，僅給付特定處置給付倍數最高的項目。  
+4. 若接受的處置未列於附表二，保險公司不負給付責任。  
+5. 同一保險單年度內，特定處置保險金的給付次數以十次為限。
+條文依據：  
+- [第十四條 特定處置保險金]</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "特定處置保險金的給付規定", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.995824, "neutral": 0.003812, "contradiction": 0.000364, "factuality": 0.999636, "C_fact": 0.999636}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" s="3" t="n">
+        <v>0.999636</v>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:18:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>意外創傷縫合處置保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外創傷縫合處置保險金的給付規定如下：  
+1. 被保險人需於保險契約有效期間內，因意外傷害事故在醫院或診所接受附表三所列的意外創傷縫合處置治療。  
+2. 給付金額計算方式為：保險單所載「保險金額」× 當年度「增額係數」× 給付倍數。  
+3. 同一次意外傷害事故中，僅針對傷口最大者給付，且每次事故僅給付一次。  
+4. 若已申領「住院手術醫療保險金」或「門診手術醫療保險金」，則不再給付此保險金。
+條文依據：  
+- [第十五條 意外創傷縫合處置保險金]</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>第十五條 意外創傷縫合處置保險金 | 附表三：意外創傷縫合處置項目及給付倍數表 | 第十四條 特定處置保險金 | 第二十條 除外責任（一） | 第十三條 意外住院手術醫療保險金 | 附表二：特定處置項目及給付倍數表</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外創傷縫合處置保險金的給付規定如下：  
+1. 被保險人需於保險契約有效期間內，因意外傷害事故在醫院或診所接受附表三所列的意外創傷縫合處置治療。  
+2. 給付金額計算方式為：保險單所載「保險金額」× 當年度「增額係數」× 給付倍數。  
+3. 同一次意外傷害事故中，僅針對傷口最大者給付，且每次事故僅給付一次。  
+4. 若已申領「住院手術醫療保險金」或「門診手術醫療保險金」，則不再給付此保險金。
+條文依據：  
+- [第十五條 意外創傷縫合處置保險金]</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "意外創傷縫合處置保險金的給付規定", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.997747, "neutral": 0.001976, "contradiction": 0.000277, "factuality": 0.999723, "C_fact": 0.999723}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" s="3" t="n">
+        <v>0.999723</v>
+      </c>
+      <c r="L30" s="3" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:18:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>醫療保險金給付總額之上限</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+醫療保險金給付總額之上限為保險單上所記載「保險金額」的一千五百倍，此上限僅適用於本契約有效期間內，且不包含其他附約、附加條款或批註條款的金額。
+條文依據：  
+- [第十六條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 醫療保險金給付總額之上限 | 第十二條 門診手術醫療保險金 | 第五條 保險範圍 | 第十一條 住院手術醫療保險金 | 第十三條 意外住院手術醫療保險金 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+醫療保險金給付總額之上限為保險單上所記載「保險金額」的一千五百倍，此上限僅適用於本契約有效期間內，且不包含其他附約、附加條款或批註條款的金額。
+條文依據：  
+- [第十六條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "醫療保險金給付總額之上限", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.996204, "neutral": 0.003618, "contradiction": 0.000178, "factuality": 0.999822, "C_fact": 0.999822}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v>0.999822</v>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:18:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>祝壽保險金的領取規定為何?</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+祝壽保險金的領取規定如下：  
+1. 被保險人需於本契約有效期間內，且保險年齡到達九十九歲之保險單週年日仍生存，方可領取祝壽保險金。  
+2. 受益人申領祝壽保險金時，需檢具以下文件：  
+   - 保險單或其謄本  
+   - 保險金申請書  
+   - 受益人的身分證明  
+條文依據：  
+- [第十七條 祝壽保險金]  
+- [第二十六條 祝壽保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>第十七條 祝壽保險金 | 第二十六條 祝壽保險金的申領 | 第十一條至第十五條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | 第二十三條 保險事故的通知與保險金的申請時間 | 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+祝壽保險金的領取規定如下：  
+1. 被保險人需於本契約有效期間內，且保險年齡到達九十九歲之保險單週年日仍生存，方可領取祝壽保險金。  
+2. 受益人申領祝壽保險金時，需檢具以下文件：  
+   - 保險單或其謄本  
+   - 保險金申請書  
+   - 受益人的身分證明  
+條文依據：  
+- [第十七條 祝壽保險金]  
+- [第二十六條 祝壽保險金的申領]</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "祝壽保險金的領取規定為何?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.998692, "neutral": 0.001171, "contradiction": 0.000137, "factuality": 0.999863, "C_fact": 0.999863}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>0.9998629999999999</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:18:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>身故時領取保險金有什麼規則?</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+身故時領取保險金的規則如下：  
+1. **一般規則**：被保險人於本契約有效期間內身故，本公司按「當年度保險金額」給付「身故保險金」。  
+2. **未滿十五足歲規則**：若被保險人於本契約有效期間且實際年齡未滿十五足歲身故，本公司僅退還「所繳保險費」，不適用一般規則。  
+3. **受監護宣告者**：若被保險人於訂立契約時為受監護宣告尚未撤銷者，其身故保險金變更為喪葬費用保險金，且金額不得超過遺產稅喪葬費扣除額之半數，超過部分不負給付責任，並退還超過部分的已繳保險費。  
+4. **除外責任**：若身故原因屬於要保人故意致死、被保險人故意自殺（但契約訂立或復效後滿兩年者除外）、犯罪處死、拒捕或越獄致死等情形，本公司不負給付責任。未滿十五足歲者因上述原因身故，僅退還所繳保險費。  
+5. **申領文件**：受益人申領保險金時，需提供保險單、死亡證明書及除戶戶籍謄本、保險金申請書及受益人身分證明等文件。
+條文依據：  
+- [第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金]  
+- [第二十七條 身故保險金或喪葬費用保險金的申領]  
+- [第二十一條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金 | 第二十七條 身故保險金或喪葬費用保險金的申領 | 第十一條至第十五條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | 第二十一條 除外責任（二） | 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+身故時領取保險金的規則如下：  
+1. **一般規則**：被保險人於本契約有效期間內身故，本公司按「當年度保險金額」給付「身故保險金」。  
+2. **未滿十五足歲規則**：若被保險人於本契約有效期間且實際年齡未滿十五足歲身故，本公司僅退還「所繳保險費」，不適用一般規則。  
+3. **受監護宣告者**：若被保險人於訂立契約時為受監護宣告尚未撤銷者，其身故保險金變更為喪葬費用保險金，且金額不得超過遺產稅喪葬費扣除額之半數，超過部分不負給付責任，並退還超過部分的已繳保險費。  
+4. **除外責任**：若身故原因屬於要保人故意致死、被保險人故意自殺（但契約訂立或復效後滿兩年者除外）、犯罪處死、拒捕或越獄致死等情形，本公司不負給付責任。未滿十五足歲者因上述原因身故，僅退還所繳保險費。  
+5. **申領文件**：受益人申領保險金時，需提供保險單、死亡證明書及除戶戶籍謄本、保險金申請書及受益人身分證明等文件。
+條文依據：  
+- [第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金]  
+- [第二十七條 身故保險金或喪葬費用保險金的申領]  
+- [第二十一條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "身故時領取保險金有什麼規則?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.827296, "neutral": 0.164287, "contradiction": 0.008417, "factuality": 0.991583, "C_fact": 0.991583}, "C_conf": 0.9949}</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" s="3" t="n">
+        <v>0.991583</v>
+      </c>
+      <c r="L33" s="3" t="n">
+        <v>0.9949</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:18:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>什麼情況下可以保費折減?</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人年齡滿20歲（含）以上，並使用保險公司指定的程式加入健康計劃，且於「指定日期」的會員等級符合進階會員或菁英會員（或更高等級）標準之一者，可享次一保險單年度的保費折減。折減比例為進階會員2%，菁英會員或更高等級3%。但豁免或復效的保險費不適用此折減規定。此外，被保險人需完成程式註冊並授權保險公司取得健康相關電子紀錄，保險公司將依此計算會員等級。
+條文依據：  
+- [第十九條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 健康促進保險費折減 | 第三十條 保險金額之減少 | 第二十條 除外責任（一） | 第三十一條 投保年齡的計算及錯誤的處理 | 第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人年齡滿20歲（含）以上，並使用保險公司指定的程式加入健康計劃，且於「指定日期」的會員等級符合進階會員或菁英會員（或更高等級）標準之一者，可享次一保險單年度的保費折減。折減比例為進階會員2%，菁英會員或更高等級3%。但豁免或復效的保險費不適用此折減規定。此外，被保險人需完成程式註冊並授權保險公司取得健康相關電子紀錄，保險公司將依此計算會員等級。
+條文依據：  
+- [第十九條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "什麼情況下可以保費折減?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.997054, "neutral": 0.002743, "contradiction": 0.000203, "factuality": 0.999797, "C_fact": 0.999797}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" s="3" t="n">
+        <v>0.999797</v>
+      </c>
+      <c r="L34" s="3" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:19:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>角膜切除術是否可以申請理賠?</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+角膜切除術可以申請理賠，其對應的給付倍數為5倍。
+條文依據：  
+- [附表一：手術項目與給付倍數 - 1305 角膜切除術]</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+角膜切除術可以申請理賠，其對應的給付倍數為5倍。
+條文依據：  
+- [附表一：手術項目與給付倍數 - 1305 角膜切除術]</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "角膜切除術是否可以申請理賠?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.053763, "neutral": 0.940966, "contradiction": 0.005271, "factuality": 0.994729, "C_fact": 0.994729}, "C_conf": 0.9968}</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" s="3" t="n">
+        <v>0.994729</v>
+      </c>
+      <c r="L35" s="3" t="n">
+        <v>0.9968</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:19:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>白內障手術是否可以申請理賠?</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+白內障手術是否可以申請理賠需視以下條件而定：  
+1. 若白內障手術屬於附表一所列的手術項目，且符合保單條件，則可申請理賠。  
+2. 若手術不在附表一所列，則需與保險公司協議比照附表內相當手術項目決定給付倍數。  
+3. 若手術屬於除外責任條款中所列情形（如美容手術或非全民健康保險支付項目等），則不予理賠。
+條文依據：  
+- [第十二條 門診手術醫療保險金]  
+- [第十一條 住院手術醫療保險金]  
+- [第二十條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 門診手術醫療保險金 | 第二十條 除外責任（一） | 附表一：手術項目與給付倍數 | payout_items | 第十一條 住院手術醫療保險金</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+白內障手術是否可以申請理賠需視以下條件而定：  
+1. 若白內障手術屬於附表一所列的手術項目，且符合保單條件，則可申請理賠。  
+2. 若手術不在附表一所列，則需與保險公司協議比照附表內相當手術項目決定給付倍數。  
+3. 若手術屬於除外責任條款中所列情形（如美容手術或非全民健康保險支付項目等），則不予理賠。
+條文依據：  
+- [第十二條 門診手術醫療保險金]  
+- [第十一條 住院手術醫療保險金]  
+- [第二十條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "白內障手術是否可以申請理賠?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.007725, "neutral": 0.988301, "contradiction": 0.003974, "factuality": 0.996026, "C_fact": 0.996026}, "C_conf": 0.9976}</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" s="3" t="n">
+        <v>0.996026</v>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>0.9976</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:19:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>保障範圍包括哪些項目？</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括：意外事故身故保險金或喪葬費用保險金、意外事故失能保險金、每月生活照護保險金、重大燒燙傷保險金、意外骨折保險金、傷害醫療日額保險金，以及意外創傷縫合處置保險金。
+條文依據：  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>payout_items | 第五條 保險範圍 | 第十五條 每月生活照護保險金的給付 | 第三十條 不保事項 | 附表二：失能程度與保險金給付表</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括：意外事故身故保險金或喪葬費用保險金、意外事故失能保險金、每月生活照護保險金、重大燒燙傷保險金、意外骨折保險金、傷害醫療日額保險金，以及意外創傷縫合處置保險金。
+條文依據：  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "保障範圍包括哪些項目？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.9981, "neutral": 0.001737, "contradiction": 0.000164, "factuality": 0.999836, "C_fact": 0.999836}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K37" s="3" t="n">
+        <v>0.9998359999999999</v>
+      </c>
+      <c r="L37" s="3" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:19:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>發生意外事故身故，理賠內容為何?</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外事故身故的理賠內容如下：  
+1. 若被保險人於意外傷害事故發生之日起 180 日內身故，本公司依意外傷害事故種類給付：  
+   - 一般意外傷害事故：「傷害醫療保險金日額」的 500 倍。  
+   - 特定意外傷害事故：「傷害醫療保險金日額」的 1000 倍。  
+2. 若被保險人於意外傷害事故發生後超過 180 日身故，但受益人能證明身故與該事故具有因果關係，本公司仍依上述金額給付。  
+3. 若被保險人於訂立契約時為受監護宣告尚未撤銷者，其理賠內容為「喪葬費用保險金」，且喪葬費用保險金額不得超過遺產稅喪葬費扣除額之半數，超過部分不負給付責任，並退還超額部分的已繳保險費。  
+條文依據：  
+- [第十二條 意外事故身故保險金或喪葬費用保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 意外事故身故保險金或喪葬費用保險金的給付 | 第十四條 保險給付的限制 | payout_items | 第十一條 契約的終止（二） | 第二十一條 失蹤處理</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外事故身故的理賠內容如下：  
+1. 若被保險人於意外傷害事故發生之日起 180 日內身故，本公司依意外傷害事故種類給付：  
+   - 一般意外傷害事故：「傷害醫療保險金日額」的 500 倍。  
+   - 特定意外傷害事故：「傷害醫療保險金日額」的 1000 倍。  
+2. 若被保險人於意外傷害事故發生後超過 180 日身故，但受益人能證明身故與該事故具有因果關係，本公司仍依上述金額給付。  
+3. 若被保險人於訂立契約時為受監護宣告尚未撤銷者，其理賠內容為「喪葬費用保險金」，且喪葬費用保險金額不得超過遺產稅喪葬費扣除額之半數，超過部分不負給付責任，並退還超額部分的已繳保險費。  
+條文依據：  
+- [第十二條 意外事故身故保險金或喪葬費用保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "發生意外事故身故，理賠內容為何?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.995376, "neutral": 0.004087, "contradiction": 0.000537, "factuality": 0.999463, "C_fact": 0.999463}, "C_conf": 0.9997}</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>0.999463</v>
+      </c>
+      <c r="L38" s="3" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:19:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>意外事故失能保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外事故失能保險金的給付條件如下：  
+1. 被保險人於契約有效期間內遭受「意外傷害事故」，並於事故發生後180日內致成附表二所列失能程度之一者，本公司依事故種類及失能程度，按以下方式計算給付金額：  
+   - 一般意外傷害事故：「傷害醫療保險金日額」的500倍乘以附表二給付比例。  
+   - 特定意外傷害事故：「傷害醫療保險金日額」的1000倍乘以附表二給付比例。  
+2. 若超過180日致成失能，但能證明失能與事故具有因果關係者，仍可申請給付，不受180日限制。  
+3. 同一事故導致多項失能時，僅給付同一手或足中較嚴重項目的失能保險金，且總金額以事故種類的上限為限：  
+   - 一般意外傷害事故：「傷害醫療保險金日額」的500倍。  
+   - 特定意外傷害事故：「傷害醫療保險金日額」的1000倍。  
+4. 不同事故導致失能時，累計給付金額最高以「傷害醫療保險金日額」的1200倍為限。  
+條文依據：  
+- [第十三條 意外事故失能保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 意外事故失能保險金的給付 | 第十五條 每月生活照護保險金的給付 | 第十四條 保險給付的限制 | 第十二條 意外事故身故保險金或喪葬費用保險金的給付 | 第二十三條 意外事故失能保險金的申領 | 附表二：失能程度與保險金給付表</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外事故失能保險金的給付條件如下：  
+1. 被保險人於契約有效期間內遭受「意外傷害事故」，並於事故發生後180日內致成附表二所列失能程度之一者，本公司依事故種類及失能程度，按以下方式計算給付金額：  
+   - 一般意外傷害事故：「傷害醫療保險金日額」的500倍乘以附表二給付比例。  
+   - 特定意外傷害事故：「傷害醫療保險金日額」的1000倍乘以附表二給付比例。  
+2. 若超過180日致成失能，但能證明失能與事故具有因果關係者，仍可申請給付，不受180日限制。  
+3. 同一事故導致多項失能時，僅給付同一手或足中較嚴重項目的失能保險金，且總金額以事故種類的上限為限：  
+   - 一般意外傷害事故：「傷害醫療保險金日額」的500倍。  
+   - 特定意外傷害事故：「傷害醫療保險金日額」的1000倍。  
+4. 不同事故導致失能時，累計給付金額最高以「傷害醫療保險金日額」的1200倍為限。  
+條文依據：  
+- [第十三條 意外事故失能保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "意外事故失能保險金的給付為何?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.424701, "neutral": 0.535887, "contradiction": 0.039412, "factuality": 0.960588, "C_fact": 0.960588}, "C_conf": 0.9762}</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K39" s="3" t="n">
+        <v>0.960588</v>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>0.9762</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:20:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>每月生活照護保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+每月生活照護保險金的給付條件如下：  
+1. 被保險人於保險契約有效期間內因「意外傷害事故」，自事故發生之日起180日內，致成附表二所列第1級至第6級失能程度之一時，本公司自失能診斷確定當日起，按「傷害醫療保險金日額」的20倍乘以附表二給付比例所得之金額，按月給付，最多給付12個月。  
+2. 若該失能的前四個「失能診斷確定週年日」時，契約仍有效且被保險人仍生存，本公司自各該週年日起，按相同計算方式再給付，最多給付12個月。  
+3. 若被保險人自事故發生之日起超過180日才致成附表二所列第1級至第6級失能程度之一，但能證明該失能與事故具有因果關係者，本公司仍依上述規定給付，不受180日限制。  
+4. 同一事故若導致多項第1級至第6級失能，僅給付一項較嚴重失能的保險金，且最高以「傷害醫療保險金日額」的20倍為限。  
+5. 若失能合併以前的失能，僅給付較嚴重項目的保險金，但以前的失能視同已給付，應扣除之。  
+6. 每月給付金額最高以「傷害醫療保險金日額」的20倍為限，累計給付金額最高以「傷害醫療保險金日額」的1200倍為限。  
+條文依據：  
+- [第十五條 每月生活照護保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>第二十四條 每月生活照護保險金的申領 | 第十五條 每月生活照護保險金的給付 | payout_items | 第十八條 傷害醫療日額保險金的給付 | 第五條 保險範圍 | 附表二：失能程度與保險金給付表 | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+每月生活照護保險金的給付條件如下：  
+1. 被保險人於保險契約有效期間內因「意外傷害事故」，自事故發生之日起180日內，致成附表二所列第1級至第6級失能程度之一時，本公司自失能診斷確定當日起，按「傷害醫療保險金日額」的20倍乘以附表二給付比例所得之金額，按月給付，最多給付12個月。  
+2. 若該失能的前四個「失能診斷確定週年日」時，契約仍有效且被保險人仍生存，本公司自各該週年日起，按相同計算方式再給付，最多給付12個月。  
+3. 若被保險人自事故發生之日起超過180日才致成附表二所列第1級至第6級失能程度之一，但能證明該失能與事故具有因果關係者，本公司仍依上述規定給付，不受180日限制。  
+4. 同一事故若導致多項第1級至第6級失能，僅給付一項較嚴重失能的保險金，且最高以「傷害醫療保險金日額」的20倍為限。  
+5. 若失能合併以前的失能，僅給付較嚴重項目的保險金，但以前的失能視同已給付，應扣除之。  
+6. 每月給付金額最高以「傷害醫療保險金日額」的20倍為限，累計給付金額最高以「傷害醫療保險金日額」的1200倍為限。  
+條文依據：  
+- [第十五條 每月生活照護保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "每月生活照護保險金的給付為何?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.418886, "neutral": 0.56193, "contradiction": 0.019183, "factuality": 0.980817, "C_fact": 0.980817}, "C_conf": 0.9884}</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K40" s="3" t="n">
+        <v>0.980817</v>
+      </c>
+      <c r="L40" s="3" t="n">
+        <v>0.9883999999999999</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:20:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>重大燒燙傷保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+重大燒燙傷保險金的給付條件為：被保險人於保險契約有效期間內因「意外傷害事故」導致燒燙傷，且經診斷符合「重大燒燙傷」的定義時，本公司將按「傷害醫療保險金日額」的二百五十倍給付「重大燒燙傷保險金」。該保險金的給付以一次為限。
+條文依據：  
+- [第十六條 重大燒燙傷保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 重大燒燙傷保險金的給付 | 第二十五條 重大燒燙傷保險金的申領 | 第五條 保險範圍 | payout_items | 第二十九條 除外責任（原因）</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+重大燒燙傷保險金的給付條件為：被保險人於保險契約有效期間內因「意外傷害事故」導致燒燙傷，且經診斷符合「重大燒燙傷」的定義時，本公司將按「傷害醫療保險金日額」的二百五十倍給付「重大燒燙傷保險金」。該保險金的給付以一次為限。
+條文依據：  
+- [第十六條 重大燒燙傷保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "重大燒燙傷保險金的給付為何?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.997013, "neutral": 0.002858, "contradiction": 0.000129, "factuality": 0.999871, "C_fact": 0.999871}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" s="3" t="n">
+        <v>0.999871</v>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:20:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>意外骨折保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外骨折保險金的給付條件如下：  
+1. 被保險人於保險契約有效期間內遭受「意外傷害事故」，並於事故發生後180日內經合格醫院或診所診斷為附表三骨折別表所列骨折項目之一（含不完全骨折及骨骼龜裂），本公司按「傷害醫療保險金日額」的二倍給付意外骨折保險金。  
+2. 若超過180日診斷確定骨折，受益人需證明骨折與該意外傷害事故具有因果關係，仍可獲得保險金給付，不受180日限制。  
+3. 同一意外傷害事故僅給付一次意外骨折保險金。  
+4. 若骨折部位不屬於附表三骨折別表所列項目，需由本公司與被保險人協議核付；但若骨折部位為骨折別表內明訂不給付之部位，則不負給付責任。
+條文依據：  
+- [第十七條 意外骨折保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>第十七條 意外骨折保險金的給付 | 第十八條 傷害醫療日額保險金的給付 | 第二十六條 意外骨折保險金的申領 | 第十三條 意外事故失能保險金的給付 | 第十九條 意外創傷縫合處置保險金的給付 | 附表二：失能程度與保險金給付表 | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外骨折保險金的給付條件如下：  
+1. 被保險人於保險契約有效期間內遭受「意外傷害事故」，並於事故發生後180日內經合格醫院或診所診斷為附表三骨折別表所列骨折項目之一（含不完全骨折及骨骼龜裂），本公司按「傷害醫療保險金日額」的二倍給付意外骨折保險金。  
+2. 若超過180日診斷確定骨折，受益人需證明骨折與該意外傷害事故具有因果關係，仍可獲得保險金給付，不受180日限制。  
+3. 同一意外傷害事故僅給付一次意外骨折保險金。  
+4. 若骨折部位不屬於附表三骨折別表所列項目，需由本公司與被保險人協議核付；但若骨折部位為骨折別表內明訂不給付之部位，則不負給付責任。
+條文依據：  
+- [第十七條 意外骨折保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "意外骨折保險金的給付為何?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.992497, "neutral": 0.007209, "contradiction": 0.000294, "factuality": 0.999706, "C_fact": 0.999706}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K42" s="3" t="n">
+        <v>0.999706</v>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:20:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>傷害醫療日額保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+傷害醫療日額保險金的給付條件如下：  
+1. 被保險人於保險契約有效期間內因「意外傷害事故」住院治療，且住院日數在意外發生後 180 日內，本公司按「傷害醫療保險金日額」乘以實際住院日數給付，但每次事故最高給付日數為 90 日。  
+2. 若治療超過 180 日，受益人需證明治療與該意外事故具因果關係，本公司仍依上述規定給付，不受 180 日限制。  
+3. 若因意外事故骨折但未住院，或住院日數未達附表三骨折別表所訂日數，則按骨折別表所訂日數乘以「傷害醫療保險金日額」的二分之一給付，合計給付日數以骨折別表所訂日數為上限。  
+4. 骨折類型的給付：  
+   - 完全骨折按骨折別表所訂日數給付。  
+   - 不完全骨折按完全骨折日數的二分之一給付。  
+   - 骨骼龜裂按完全骨折日數的四分之一給付。  
+5. 同時發生多項骨折時，僅給付一項較高等級的傷害醫療日額保險金。
+條文依據：  
+- [第十八條 傷害醫療日額保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 傷害醫療日額保險金的給付 | 第二十七條 傷害醫療日額保險金的申領 | 第十五條 每月生活照護保險金的給付 | 第三十四條 傷害醫療保險金日額之減少 | 第十九條 意外創傷縫合處置保險金的給付 | 附表二：失能程度與保險金給付表 | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+傷害醫療日額保險金的給付條件如下：  
+1. 被保險人於保險契約有效期間內因「意外傷害事故」住院治療，且住院日數在意外發生後 180 日內，本公司按「傷害醫療保險金日額」乘以實際住院日數給付，但每次事故最高給付日數為 90 日。  
+2. 若治療超過 180 日，受益人需證明治療與該意外事故具因果關係，本公司仍依上述規定給付，不受 180 日限制。  
+3. 若因意外事故骨折但未住院，或住院日數未達附表三骨折別表所訂日數，則按骨折別表所訂日數乘以「傷害醫療保險金日額」的二分之一給付，合計給付日數以骨折別表所訂日數為上限。  
+4. 骨折類型的給付：  
+   - 完全骨折按骨折別表所訂日數給付。  
+   - 不完全骨折按完全骨折日數的二分之一給付。  
+   - 骨骼龜裂按完全骨折日數的四分之一給付。  
+5. 同時發生多項骨折時，僅給付一項較高等級的傷害醫療日額保險金。
+條文依據：  
+- [第十八條 傷害醫療日額保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr"/>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "傷害醫療日額保險金的給付為何?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.961568, "neutral": 0.036602, "contradiction": 0.00183, "factuality": 0.99817, "C_fact": 0.99817}, "C_conf": 0.9989}</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K43" s="3" t="n">
+        <v>0.99817</v>
+      </c>
+      <c r="L43" s="3" t="n">
+        <v>0.9989</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:20:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>意外創傷縫合處置保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外創傷縫合處置保險金的給付條件為：被保險人於保險契約有效期間內，因遭受「意外傷害事故」，在「醫院」或「診所」經醫師診斷必須接受創傷縫合處置治療，且已完成縫合處置者，本公司將按「傷害醫療保險金日額」給付該保險金。同一意外傷害事故僅給付一次。
+條文依據：  
+- [第十九條 意外創傷縫合處置保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 意外創傷縫合處置保險金的給付 | 第二十八條 意外創傷縫合處置保險金的申領 | 第五條 保險範圍 | 第十七條 意外骨折保險金的給付 | payout_items | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外創傷縫合處置保險金的給付條件為：被保險人於保險契約有效期間內，因遭受「意外傷害事故」，在「醫院」或「診所」經醫師診斷必須接受創傷縫合處置治療，且已完成縫合處置者，本公司將按「傷害醫療保險金日額」給付該保險金。同一意外傷害事故僅給付一次。
+條文依據：  
+- [第十九條 意外創傷縫合處置保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr"/>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "意外創傷縫合處置保險金的給付為何?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.997496, "neutral": 0.002397, "contradiction": 0.000107, "factuality": 0.999893, "C_fact": 0.999893}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K44" s="3" t="n">
+        <v>0.999893</v>
+      </c>
+      <c r="L44" s="3" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:21:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>因意外導致視力衰退，是否能申請理賠?</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若因意外導致視力衰退，需符合附表二中「失能程度與保險金給付表」的相關條件，才能申請理賠。例如，視力永久在萬國式視力表0.02以下，或眼球摘出等情況，屬於「失明」的定義，則可申請意外事故失能保險金。此外，視力障害的測定需經過六個月治療後判定，但若為眼球摘出等明顯無法復原的情況，則不受此限制。
+條文依據：  
+- [註2]  
+- [第十三條 意外事故失能保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>第二十三條 意外事故失能保險金的申領 | 第十三條 意外事故失能保險金的給付 | 註2： | 第三十條 不保事項 | 第二十六條 意外骨折保險金的申領 | 附表二：失能程度與保險金給付表</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若因意外導致視力衰退，需符合附表二中「失能程度與保險金給付表」的相關條件，才能申請理賠。例如，視力永久在萬國式視力表0.02以下，或眼球摘出等情況，屬於「失明」的定義，則可申請意外事故失能保險金。此外，視力障害的測定需經過六個月治療後判定，但若為眼球摘出等明顯無法復原的情況，則不受此限制。
+條文依據：  
+- [註2]  
+- [第十三條 意外事故失能保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr"/>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "因意外導致視力衰退，是否能申請理賠?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.018808, "neutral": 0.979883, "contradiction": 0.001308, "factuality": 0.998692, "C_fact": 0.998692}, "C_conf": 0.9992}</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K45" s="3" t="n">
+        <v>0.998692</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>0.9992</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:21:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>肋骨骨折是否可以申請理賠?理賠金額為多少?</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+肋骨骨折可以申請理賠，理賠金額需依據骨折的情況計算：  
+1. 若肋骨完全骨折且未住院治療，按附表三所訂的完全骨折日數20天乘以「傷害醫療保險金日額」的二分之一給付，即10天的日額保險金。  
+2. 若肋骨不完全骨折，按完全骨折日數的二分之一計算，即20天的二分之一為10天，再乘以「傷害醫療保險金日額」的二分之一給付，即5天的日額保險金。  
+3. 若肋骨為骨骼龜裂，按完全骨折日數的四分之一計算，即20天的四分之一為5天，再乘以「傷害醫療保險金日額」的二分之一給付，即2.5天的日額保險金。  
+條文依據：  
+- [第十八條 傷害醫療日額保險金的給付]  
+- [附表三：骨折別表]</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 傷害醫療日額保險金的給付 | 第十七條 意外骨折保險金的給付 | 第二十六條 意外骨折保險金的申領 | 第三十條 不保事項 | 第五條 保險範圍 | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+肋骨骨折可以申請理賠，理賠金額需依據骨折的情況計算：  
+1. 若肋骨完全骨折且未住院治療，按附表三所訂的完全骨折日數20天乘以「傷害醫療保險金日額」的二分之一給付，即10天的日額保險金。  
+2. 若肋骨不完全骨折，按完全骨折日數的二分之一計算，即20天的二分之一為10天，再乘以「傷害醫療保險金日額」的二分之一給付，即5天的日額保險金。  
+3. 若肋骨為骨骼龜裂，按完全骨折日數的四分之一計算，即20天的四分之一為5天，再乘以「傷害醫療保險金日額」的二分之一給付，即2.5天的日額保險金。  
+條文依據：  
+- [第十八條 傷害醫療日額保險金的給付]  
+- [附表三：骨折別表]</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr"/>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "肋骨骨折是否可以申請理賠?理賠金額為多少?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.948394, "neutral": 0.03876, "contradiction": 0.012846, "factuality": 0.987154, "C_fact": 0.987154}, "C_conf": 0.9923}</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>0.987154</v>
+      </c>
+      <c r="L46" s="3" t="n">
+        <v>0.9923</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:21:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>投保新鍾心滿福後，假設投保保額為100萬元，於第二保單年度接受「移植器官」，這樣可以領多少保險金?</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+新鍾心滿福保險涵蓋「移植器官」的保障，並將其列為「特定重大傷病」之一。若被保險人在第二保單年度接受器官移植手術，符合條件時，保險公司將給付「特定重大傷病保險金」，其金額為保險金額的20%。假設投保保額為100萬元，則可領取的保險金為20萬元。  
+條文依據：  
+- [第十三條 特定重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>第十五條 滿期保險金的給付 | 第二條 名詞定義 | 附表一：全民健康保險重大傷病項目 | 第十三條 特定重大傷病保險金的給付 | 附表三：各保險單年度可借金額上限表 | payout_items | 第十七條 完全失能保險金的給付 | 附表二：完全失能程度表</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+新鍾心滿福保險涵蓋「移植器官」的保障，並將其列為「特定重大傷病」之一。若被保險人在第二保單年度接受器官移植手術，符合條件時，保險公司將給付「特定重大傷病保險金」，其金額為保險金額的20%。假設投保保額為100萬元，則可領取的保險金為20萬元。  
+條文依據：  
+- [第十三條 特定重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr"/>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認新鍾心滿福保險是否涵蓋器官移植手術保障", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認器官移植手術的保險金給付條件及計算方式", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認第二保單年度的保險金給付規則", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認投保保額100萬元對保險金計算的影響", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.006577, "neutral": 0.990706, "contradiction": 0.002717, "factuality": 0.997283, "C_fact": 0.997283}, "C_conf": 0.9984}</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K47" s="3" t="n">
+        <v>0.997283</v>
+      </c>
+      <c r="L47" s="3" t="n">
+        <v>0.9984</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:21:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>投保新鍾心滿福後，若要理賠重大傷病保險金，一定要檢附全民健保開立的重大傷病證明才能拿到保險金嗎?</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申請重大傷病保險金時，並非一定需要檢附全民健保開立的重大傷病證明。若被保險人已取得一家「區域醫院」層級以上（含）之醫療院所開立且符合投保當時「重大傷病範圍」的診斷書及當次病歷摘要，亦可作為重大傷病證明文件，免向全民健保申請相關證明。此外，若因全民健保重大傷病項目變更導致無法取得證明，或被保險人於證明核發前身故，亦可依條款規定以其他文件替代。  
+條文依據：  
+- [第二十二條 重大傷病保險金、特定重大傷病保險金的申領]  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>第二十二條 重大傷病保險金、特定重大傷病保險金的申領 | other_metadata | 第十二條 重大傷病保險金的給付 | 附表一：全民健康保險重大傷病項目 | 第二條 名詞定義 | 第三十條 不保事項</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申請重大傷病保險金時，並非一定需要檢附全民健保開立的重大傷病證明。若被保險人已取得一家「區域醫院」層級以上（含）之醫療院所開立且符合投保當時「重大傷病範圍」的診斷書及當次病歷摘要，亦可作為重大傷病證明文件，免向全民健保申請相關證明。此外，若因全民健保重大傷病項目變更導致無法取得證明，或被保險人於證明核發前身故，亦可依條款規定以其他文件替代。  
+條文依據：  
+- [第二十二條 重大傷病保險金、特定重大傷病保險金的申領]  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認重大傷病保險金的理賠條件", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認是否需要檢附全民健保開立的重大傷病證明", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認新鍾心滿福保險的相關理賠規定", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.359661, "neutral": 0.638857, "contradiction": 0.001482, "factuality": 0.998518, "C_fact": 0.998518}, "C_conf": 0.9991}</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K48" s="3" t="n">
+        <v>0.998518</v>
+      </c>
+      <c r="L48" s="3" t="n">
+        <v>0.9991</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:22:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>一定要有健保身分才能申請重大傷病理賠嗎？</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不一定需要有健保身分才能申請重大傷病理賠。若被保險人喪失全民健康保險被保險人資格，需先申請加保全民健康保險後，始得申領重大傷病保險金。此外，若被保險人已取得符合投保當時重大傷病範圍的診斷書及病歷摘要，亦可作為申請理賠的替代文件。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>第二十二條 重大傷病保險金、特定重大傷病保險金的申領 | 第十二條 重大傷病保險金的給付 | other_metadata | 第三十條 不保事項 | 第二條 名詞定義 | 附表一：全民健康保險重大傷病項目</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不一定需要有健保身分才能申請重大傷病理賠。若被保險人喪失全民健康保險被保險人資格，需先申請加保全民健康保險後，始得申領重大傷病保險金。此外，若被保險人已取得符合投保當時重大傷病範圍的診斷書及病歷摘要，亦可作為申請理賠的替代文件。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr"/>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "一定要有健保身分才能申請重大傷病理賠嗎？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.133944, "neutral": 0.856681, "contradiction": 0.009375, "factuality": 0.990625, "C_fact": 0.990625}, "C_conf": 0.9944}</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K49" s="3" t="n">
+        <v>0.990625</v>
+      </c>
+      <c r="L49" s="3" t="n">
+        <v>0.9944</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:22:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>重大傷病的項目如果在投保後有新增，可以從優申請理賠嗎？</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以從優申請理賠。根據條款，重大傷病的範圍包含「全民健康保險重大傷病項目及其證明有效期限」，且若該項目於保單訂立後或有效期間內新增，則以中央衛生主管機關最新公告的項目為準。因此，新增的重大傷病項目在符合條件下可申請理賠。
+條文依據：  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>附表一：全民健康保險重大傷病項目 | 第二條 名詞定義 | payout_items</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以從優申請理賠。根據條款，重大傷病的範圍包含「全民健康保險重大傷病項目及其證明有效期限」，且若該項目於保單訂立後或有效期間內新增，則以中央衛生主管機關最新公告的項目為準。因此，新增的重大傷病項目在符合條件下可申請理賠。
+條文依據：  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "重大傷病的項目如果在投保後有新增，可以從優申請理賠嗎？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.993441, "neutral": 0.006381, "contradiction": 0.000179, "factuality": 0.999821, "C_fact": 0.999821}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K50" s="3" t="n">
+        <v>0.999821</v>
+      </c>
+      <c r="L50" s="3" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:22:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>我的保單之前有停效，在復效後五天被診斷出重大疾病是否可申請理賠？</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若保單已成功復效，且重大疾病符合保單理賠範圍，則可申請理賠。根據條款，復效後的理賠條件需注意等待期間的限制。若重大疾病是在復效後的等待期間內（如30天或90天，依疾病類型而定）被診斷，則保單自始無效，僅退還已繳保險費。若重大疾病因意外傷害事故所致，則不受等待期間限制。
+條文依據：  
+- [第八條 本契約效力的恢復]  
+- [第十二條 重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>第八條 本契約效力的恢復 | 第三十條 不保事項 | 第五條 保險範圍 | other_metadata | 第二條 名詞定義 | 第十二條 重大傷病保險金的給付 | 第二十二條 重大傷病保險金、特定重大傷病保險金的申領 | 附表一：全民健康保險重大傷病項目</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若保單已成功復效，且重大疾病符合保單理賠範圍，則可申請理賠。根據條款，復效後的理賠條件需注意等待期間的限制。若重大疾病是在復效後的等待期間內（如30天或90天，依疾病類型而定）被診斷，則保單自始無效，僅退還已繳保險費。若重大疾病因意外傷害事故所致，則不受等待期間限制。
+條文依據：  
+- [第八條 本契約效力的恢復]  
+- [第十二條 重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認保單是否已成功復效", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認重大疾病是否符合保單理賠範圍", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認復效後的理賠條件是否有相關限制", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認重大疾病診斷日期是否影響理賠資格", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.000966, "neutral": 0.987608, "contradiction": 0.011426, "factuality": 0.988574, "C_fact": 0.988574}, "C_conf": 0.9931}</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K51" s="3" t="n">
+        <v>0.988574</v>
+      </c>
+      <c r="L51" s="3" t="n">
+        <v>0.9931</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:22:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>領完重大傷病保險金，主約終止後，附約可以繼續有效嗎?</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以。根據條款規定，若因重大傷病診斷確定而導致主約終止時，要保人仍可於附約有效期間內繼續繳交附約保險費，以延續附約效力。
+條文依據：  
+- [第十一條 契約的終止（二）]</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 契約的終止（二） | 第十二條 重大傷病保險金的給付 | 第三十條 不保事項 | 第五條 保險範圍 | payout_items | 附表一：全民健康保險重大傷病項目</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以。根據條款規定，若因重大傷病診斷確定而導致主約終止時，要保人仍可於附約有效期間內繼續繳交附約保險費，以延續附約效力。
+條文依據：  
+- [第十一條 契約的終止（二）]</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr"/>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "領完重大傷病保險金，主約終止後，附約可以繼續有效嗎?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.996247, "neutral": 0.003631, "contradiction": 0.000122, "factuality": 0.999878, "C_fact": 0.999878}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K52" s="3" t="n">
+        <v>0.999878</v>
+      </c>
+      <c r="L52" s="3" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:22:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Q1：因為慢性精神病的保險給付僅有保額的20%，我可以先不申請給付，等之後發生其他重大傷病後，再申請重大傷病保險金嗎?Q2：但如果我不申請，保險公司不會知道我有罹患慢性精神病阿，所以我就可以領之後的重大傷病100%保額嗎?</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+Q1：慢性精神病的保險給付比例為保額的20%，但若「年繳應繳保險費總額」的一點零五倍高於保額的20%，則取其大者。您可以選擇延後申請慢性精神病保險給付，但需注意條款中未明確規定延後申請的影響，且保險公司僅給付一項重大傷病保險金。  
+Q2：即使您不申請慢性精神病保險給付，保險公司仍可能依據診斷記錄或其他資料得知您已罹患慢性精神病，並依條款規定僅給付一次重大傷病保險金，且金額將依慢性精神病的給付比例計算。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 重大傷病保險金的給付 | 第十三條 特定重大傷病保險金的給付 | 第三十條 不保事項 | 第二十八條 除外責任（一） | 第二十二條 重大傷病保險金、特定重大傷病保險金的申領 | 第二條 名詞定義 | 附表一：全民健康保險重大傷病項目 | payout_items</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+Q1：慢性精神病的保險給付比例為保額的20%，但若「年繳應繳保險費總額」的一點零五倍高於保額的20%，則取其大者。您可以選擇延後申請慢性精神病保險給付，但需注意條款中未明確規定延後申請的影響，且保險公司僅給付一項重大傷病保險金。  
+Q2：即使您不申請慢性精神病保險給付，保險公司仍可能依據診斷記錄或其他資料得知您已罹患慢性精神病，並依條款規定僅給付一次重大傷病保險金，且金額將依慢性精神病的給付比例計算。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr"/>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認慢性精神病保險給付比例是否為保額的20%", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認是否可以延後申請慢性精神病保險給付", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認重大傷病保險金是否可申請100%保額", "must_have": true, "分數": 1.0}, {"id": "4", "point": "了解不申請慢性精神病保險給付是否影響後續重大傷病保險金申請", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.788645, "neutral": 0.150959, "contradiction": 0.060396, "factuality": 0.939604, "C_fact": 0.939604}, "C_conf": 0.9633}</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K53" s="3" t="n">
+        <v>0.939604</v>
+      </c>
+      <c r="L53" s="3" t="n">
+        <v>0.9633</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:23:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>失智症會賠嗎？賠多少？</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+失智症是否理賠及理賠金額需視其是否符合保單條款中「重大傷病」或「完全失能」的定義。  
+1. 若失智症導致符合附表二所列「完全失能程度」之一，例如中樞神經系統機能遺存極度障害，終身需專人照護，則可依第十七條規定給付「完全失能保險金」，金額為「當年度保險金額」或「年繳應繳保險費總額的一點零五倍」，取其較大者。[第十七條 完全失能保險金的給付]  
+2. 若失智症屬於附表一所列「重大傷病」範圍，例如慢性精神病，則可依第十二條規定給付「重大傷病保險金」，金額依初次診斷確定罹患重大傷病時的保險單年度計算，若屬慢性精神病，則為「保險金額的百分之二十」或「年繳應繳保險費總額的一點零五倍」，取其較大者。[第十二條 重大傷病保險金的給付]  
+條款依據：  
+[第十七條 完全失能保險金的給付]  
+[第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>第十七條 完全失能保險金的給付 | 第二十九條 除外責任（二） | 第十二條 重大傷病保險金的給付 | 第三十條 不保事項 | 附表一：全民健康保險重大傷病項目 | 第二十一條 失蹤處理 | 第十六條 所繳保險費加計利息的退還、身故保險金或喪葬費用保險金的給付 | 附表二：完全失能程度表</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+找不到相關內容  
+條文依據：  
+找不到相關內容</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+失智症是否理賠及理賠金額需視其是否符合保單條款中「重大傷病」或「完全失能」的定義。  
+1. 若失智症導致符合附表二所列「完全失能程度」之一，例如中樞神經系統機能遺存極度障害，終身需專人照護，則可依第十七條規定給付「完全失能保險金」，金額為「當年度保險金額」或「年繳應繳保險費總額的一點零五倍」，取其較大者。[第十七條 完全失能保險金的給付]  
+2. 若失智症屬於附表一所列「重大傷病」範圍，例如慢性精神病，則可依第十二條規定給付「重大傷病保險金」，金額依初次診斷確定罹患重大傷病時的保險單年度計算，若屬慢性精神病，則為「保險金額的百分之二十」或「年繳應繳保險費總額的一點零五倍」，取其較大者。[第十二條 重大傷病保險金的給付]  
+條款依據：  
+[第十七條 完全失能保險金的給付]  
+[第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr"/>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "失智症會賠嗎？賠多少？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.022447, "neutral": 0.965011, "contradiction": 0.012543, "factuality": 0.987457, "C_fact": 0.987457}, "C_conf": 0.9925}</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K54" s="3" t="n">
+        <v>0.987457</v>
+      </c>
+      <c r="L54" s="3" t="n">
+        <v>0.9925</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:23:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>投保新鍾心滿福後，於第二保單年度罹患子宮頸惡性腫瘤，且已給付重大傷病保險金。第五保單年度時又罹患慢性腎衰竭，這樣還可以申領重大傷病保險金的給付嗎?</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款規定，重大傷病保險金僅能給付一次，即使被保險人同時或先後罹患多項重大傷病，本公司僅給付一項重大傷病保險金。因此，雖然慢性腎衰竭符合重大傷病保險金的給付條件，但因已於第二保單年度因子宮頸惡性腫瘤申領過重大傷病保險金，無法再次申領。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>附表一：全民健康保險重大傷病項目 | 第十二條 重大傷病保險金的給付 | 第五條 保險範圍 | 第二條 名詞定義 | payout_items | 第二十二條 重大傷病保險金、特定重大傷病保險金的申領</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款規定，重大傷病保險金僅能給付一次，即使被保險人同時或先後罹患多項重大傷病，本公司僅給付一項重大傷病保險金。因此，雖然慢性腎衰竭符合重大傷病保險金的給付條件，但因已於第二保單年度因子宮頸惡性腫瘤申領過重大傷病保險金，無法再次申領。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr"/>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認重大傷病保險金是否可重複申領", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認慢性腎衰竭是否符合重大傷病保險金的給付條件", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認保單條款中對於重大傷病保險金的申領次數限制", "must_have": false, "分數": 1.0}, {"id": "4", "point": "確認保單年度與疾病發生時間的影響是否相關", "must_have": false, "分數": 0.5}], "coverage_score": 0.95, "nli": {"entailment": 0.651249, "neutral": 0.346323, "contradiction": 0.002428, "factuality": 0.997572, "C_fact": 0.997572}, "C_conf": 0.9486}</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K55" s="3" t="n">
+        <v>0.997572</v>
+      </c>
+      <c r="L55" s="3" t="n">
+        <v>0.9486</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:23:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>12歲的被保險人可以有健康促進保險費折減嗎？</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+12歲的被保險人無法享有健康促進保險費折減，因為該條款明確規定，只有實際年齡達18歲（含）以上的被保險人才能參與健康促進計劃並獲得保險費折減。
+條文依據：  
+- [第十九條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 健康促進保險費折減 | 第三十八條 投保年齡的計算及錯誤的處理 | 第三十四條 減額繳清保險 | 第二條 名詞定義 | 第十六條 所繳保險費加計利息的退還、身故保險金或喪葬費用保險金的給付 | 附表二：完全失能程度表</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+12歲的被保險人無法享有健康促進保險費折減，因為該條款明確規定，只有實際年齡達18歲（含）以上的被保險人才能參與健康促進計劃並獲得保險費折減。
+條文依據：  
+- [第十九條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr"/>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "12歲的被保險人可以有健康促進保險費折減嗎？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.98138, "neutral": 0.018084, "contradiction": 0.000536, "factuality": 0.999464, "C_fact": 0.999464}, "C_conf": 0.9997}</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K56" s="3" t="n">
+        <v>0.999464</v>
+      </c>
+      <c r="L56" s="3" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:24:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>ZDN</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>被保險人於投保鍾心滿溢後的第10天就罹患慢性腎衰竭，請問可以申領重大傷病保險金嗎？</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於投保後第10天罹患慢性腎衰竭，無法申領重大傷病保險金。原因如下：  
+1. 慢性腎衰竭屬於重大傷病範圍，需符合附表一中「慢性腎衰竭〔尿毒症〕，必須接受定期透析治療者」的條件，方可申領重大傷病保險金。  
+2. 根據條款，重大傷病保險金的給付需等待期間屆滿翌日或復效日起的契約有效期間內發生。等待期間為自契約生效日起持續有效30日，屬癌症者則為90日。被保險人於等待期間內罹患慢性腎衰竭，契約自始無效，本公司僅退還已繳保險費。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第三十條 不保事項]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 重大傷病保險金的給付 | 附表一：全民健康保險重大傷病項目 | 第三十條 不保事項 | 第二條 名詞定義 | 第二十二條 重大傷病保險金、特定重大傷病保險金的申領</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於投保後第10天罹患慢性腎衰竭，無法申領重大傷病保險金。原因如下：  
+1. 慢性腎衰竭屬於重大傷病範圍，需符合附表一中「慢性腎衰竭〔尿毒症〕，必須接受定期透析治療者」的條件，方可申領重大傷病保險金。  
+2. 根據條款，重大傷病保險金的給付需等待期間屆滿翌日或復效日起的契約有效期間內發生。等待期間為自契約生效日起持續有效30日，屬癌症者則為90日。被保險人於等待期間內罹患慢性腎衰竭，契約自始無效，本公司僅退還已繳保險費。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第三十條 不保事項]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr"/>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認重大傷病保險金是否涵蓋慢性腎衰竭", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認重大傷病保險金的申領條件是否符合第10天罹患疾病的情況", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認保單是否有等待期規定及其適用範圍", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.002078, "neutral": 0.97258, "contradiction": 0.025342, "factuality": 0.974658, "C_fact": 0.974658}, "C_conf": 0.9847}</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K57" s="3" t="n">
+        <v>0.974658</v>
+      </c>
+      <c r="L57" s="3" t="n">
+        <v>0.9847</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:24:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>CFE</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>投保自由配重大傷病後，若在契約生效後80天罹患第一期乳癌，會拿到理賠金嗎?</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人在契約生效後80天罹患第一期乳癌，因癌症的等待期間為90天，80天尚未滿等待期間，因此不符合理賠條件。  
+條文依據：  
+- [第二條 名詞定義]  
+- [第十一條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>附表一：全民健康保險重大傷病項目 | 第十一條 重大傷病保險金的給付 | 第十五條 不保事項 | 第二條 名詞定義 | 第五條 契約有效期間及保證續保 | 第十四條 除外責任</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人在契約生效後80天罹患第一期乳癌，符合理賠條件，可獲得理賠金。  
+1. 第一期乳癌屬於「重大傷病範圍」中的「需積極或長期治療之癌症」，且未被排除在保障範圍之外。  
+2. 根據等待期間的規定，癌症的等待期間為90天，80天尚未滿等待期間，因此不符合理賠條件。  
+條文依據：  
+- [第二條 名詞定義]  
+- [第十一條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人在契約生效後80天罹患第一期乳癌，因癌症的等待期間為90天，80天尚未滿等待期間，因此不符合理賠條件。  
+條文依據：  
+- [第二條 名詞定義]  
+- [第十一條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr"/>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認自由配重大傷病保險是否涵蓋第一期乳癌", "must_have": true, "分數": 0.8}, {"id": "2", "point": "確認契約生效後80天是否符合等待期規定", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認理賠金的給付條件是否包含第一期乳癌", "must_have": true, "分數": 0.8}, {"id": "4", "point": "確認保險契約中重大傷病的定義與範圍", "must_have": false, "分數": 0.5}], "coverage_score": 0.8385, "nli": {"entailment": 0.011587, "neutral": 0.977199, "contradiction": 0.011213, "factuality": 0.988787, "C_fact": 0.988787}, "C_conf": 0.8328}</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="n">
+        <v>0.8385</v>
+      </c>
+      <c r="K58" s="3" t="n">
+        <v>0.988787</v>
+      </c>
+      <c r="L58" s="3" t="n">
+        <v>0.8328</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:24:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>CFE</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>要保人想要終止國泰人壽自由配CFE契約，能否退保費?</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+要保人可以終止契約，並退還未到期保險費。根據條款規定，當要保人終止契約時，本公司會從已繳保險費中扣除按短期費率計算的已經過期間保險費後，將未到期保險費無息退還給要保人。
+條文依據：  
+- [第九條 契約的終止（一）]</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>第九條 契約的終止（一） | 第十五條 不保事項 | 第五條 契約有效期間及保證續保 | 第七條 本契約效力的恢復 | 第六條 續保保險費的交付、寬限期間及契約效力的停止 | 附表二：短期費率表</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+要保人可以終止契約，並退還未到期保險費。根據條款規定，當要保人終止契約時，本公司會從已繳保險費中扣除按短期費率計算的已經過期間保險費後，將未到期保險費無息退還給要保人。
+條文依據：  
+- [第九條 契約的終止（一）]</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr"/>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "要保人想要終止國泰人壽自由配CFE契約，能否退保費?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.998035, "neutral": 0.00188, "contradiction": 8.5e-05, "factuality": 0.999915, "C_fact": 0.999915}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K59" s="3" t="n">
+        <v>0.999915</v>
+      </c>
+      <c r="L59" s="3" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:25:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>CFE</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>投保國泰人壽自由配CFE，若在等待期間內罹患重大傷病，要如何給付?</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在等待期間內罹患重大傷病，依條款規定，因意外傷害事故所致的重大傷病不受等待期間限制，仍可申請重大傷病保險金。但若因其他原因（非意外傷害事故）罹患重大傷病，則本契約自始無效，保險公司僅退還已繳保險費且不計利息。  
+條文依據：  
+- [第十一條 重大傷病保險金的給付]  
+- [第十五條 不保事項]</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 重大傷病保險金的給付 | 附表一：全民健康保險重大傷病項目 | 第十五條 不保事項 | 第十四條 除外責任 | payout_items | other_metadata</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在等待期間內罹患重大傷病，依條款規定，因意外傷害事故所致的重大傷病不受等待期間限制，仍可申請重大傷病保險金。但若因其他原因（非意外傷害事故）罹患重大傷病，則本契約自始無效，保險公司僅退還已繳保險費且不計利息。  
+條文依據：  
+- [第十一條 重大傷病保險金的給付]  
+- [第十五條 不保事項]</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr"/>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認國泰人壽自由配CFE的等待期間規定", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認重大傷病是否符合保單條款中的保障範圍", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認等待期間內重大傷病的給付條件或限制", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認是否有例外條款適用於等待期間內的重大傷病", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.90598, "neutral": 0.08627, "contradiction": 0.007751, "factuality": 0.992249, "C_fact": 0.992249}, "C_conf": 0.9953}</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K60" s="3" t="n">
+        <v>0.992249</v>
+      </c>
+      <c r="L60" s="3" t="n">
+        <v>0.9953</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:25:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>CFE</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>投保自由配一年定期初次罹患重大傷病健康保險後，於第三年罹患先天性肌肉萎縮症，可以申領重大傷病保險金嗎？</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於第三年罹患先天性肌肉萎縮症，無法申領重大傷病保險金，原因如下：  
+1. 先天性肌肉萎縮症不屬於保單所涵蓋的重大傷病範圍，根據附表一，該疾病標註為「否」。  
+2. 保單條款第十五條明確規定，若被保險人於投保前已符合重大傷病項目或屬於先天性疾病，則屬於除外責任範圍，保險契約自始無效。
+條文依據：  
+- [附表一：全民健康保險重大傷病項目]  
+- [第十五條 不保事項]</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 重大傷病保險金的給付 | other_metadata | 附表一：全民健康保險重大傷病項目 | 第十三條 重大傷病保險金的申領 | 第十五條 不保事項</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於第三年罹患先天性肌肉萎縮症，無法申領重大傷病保險金，原因如下：  
+1. 先天性肌肉萎縮症不屬於保單所涵蓋的重大傷病範圍，根據附表一，該疾病標註為「否」。  
+2. 保單條款第十五條明確規定，若被保險人於投保前已符合重大傷病項目或屬於先天性疾病，則屬於除外責任範圍，保險契約自始無效。
+條文依據：  
+- [附表一：全民健康保險重大傷病項目]  
+- [第十五條 不保事項]</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr"/>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認自由配一年定期重大傷病健康保險是否涵蓋先天性肌肉萎縮症", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認保險條款中重大傷病保險金的申領條件", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認先天性疾病是否屬於保單的除外責任範圍", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認保險是否仍在有效期間內", "must_have": false, "分數": 0.0}, {"id": "5", "point": "確認是否已完成相關診斷及申請程序", "must_have": false, "分數": 0.0}], "coverage_score": 0.8571, "nli": {"entailment": 0.957879, "neutral": 0.041818, "contradiction": 0.000303, "factuality": 0.999697, "C_fact": 0.999697}, "C_conf": 0.8569}</t>
+        </is>
+      </c>
+      <c r="J61" s="3" t="n">
+        <v>0.8571</v>
+      </c>
+      <c r="K61" s="3" t="n">
+        <v>0.9996969999999999</v>
+      </c>
+      <c r="L61" s="3" t="n">
+        <v>0.8569</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:25:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>CFG</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>自由配重大疾病(甲型)保障的重大疾病有哪些疾病?</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+自由配重大疾病(甲型)保障的重大疾病包括以下疾病：  
+1. 腦中風後障礙(重度)  
+2. 癱瘓(重度)  
+3. 癌症(重度)  
+4. 急性心肌梗塞(重度)  
+5. 冠狀動脈繞道手術  
+6. 末期腎病變  
+7. 重大器官移植或造血幹細胞移植  
+條文依據：  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>國泰人壽自由配一年定期初次罹患重大疾病健康保險(甲型)年繳費率表 | payout_items | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+自由配重大疾病(甲型)保障的重大疾病包括以下疾病：  
+1. 腦中風後障礙(重度)  
+2. 癱瘓(重度)  
+3. 癌症(重度)  
+4. 急性心肌梗塞(重度)  
+5. 冠狀動脈繞道手術  
+6. 末期腎病變  
+7. 重大器官移植或造血幹細胞移植  
+條文依據：  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr"/>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "自由配重大疾病(甲型)保障的重大疾病有哪些疾病?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.435646, "neutral": 0.534641, "contradiction": 0.029713, "factuality": 0.970287, "C_fact": 0.970287}, "C_conf": 0.9821}</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K62" s="3" t="n">
+        <v>0.970287</v>
+      </c>
+      <c r="L62" s="3" t="n">
+        <v>0.9821</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:25:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>被保險人領了2次癌症(重度)追蹤照護金後身故，是否還有尚未給付的保險金供受益人領取?</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 根據條款第十四條，「癌症(重度)追蹤照護保險金」的給付以被保險人仍生存為前提，且最長以五年為限。被保險人已領取2次，尚未達到給付上限，但因被保險人已身故，該保險金不再適用。  
+2. 條款未明確規定是否存在專屬的身故保險金供受益人申領。  
+3. 條款第二十八條規定，若被保險人身故時仍有未完全給付的保險金，該部分保險金之受益人為法定繼承人，但未明確指出是否包含其他附加保障或特定身故保險金。  
+條文依據：  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]  
+- [第二十八條 受益人]</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>第二十八條 受益人 | 第十一條 契約的終止（三） | 第二十二條 保險事故的通知與保險給付的申請時間 | 第二十三條 癌症保險金或罹癌基因檢測服務的申領 | 第十三條 初次罹患癌症(重度)保險金的給付 | 第五條 保險範圍 | 第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用) | 第十條 契約的終止（二） | 第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 根據條款，第十四條規定「癌症(重度)追蹤照護保險金」的給付最長以五年為限，且每年給付一次。被保險人已領取2次，尚未達到給付上限，因此仍有剩餘的「癌症(重度)追蹤照護保險金」未給付，但因被保險人已身故，該保險金不再適用。  
+2. 條款中未提及身故保險金的保障，因此無法確認是否有此項保險金供受益人領取。  
+3. 條款中未提及其他相關保險金（如附加保障）是否適用於此情況。  
+條文依據：  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]  
+- 找不到相關內容</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 根據條款第十四條，「癌症(重度)追蹤照護保險金」的給付以被保險人仍生存為前提，且最長以五年為限。被保險人已領取2次，尚未達到給付上限，但因被保險人已身故，該保險金不再適用。  
+2. 條款第十三條、第十二條等內容提及「初次罹患癌症(重度)保險金」及「初次罹患癌症(初期)或癌症(輕度)保險金」的給付，但未明確規定是否存在專屬的身故保險金供受益人申領。  
+3. 條款第二十八條規定，若被保險人身故時仍有未完全給付的保險金，該部分保險金之受益人為法定繼承人，但未明確指出是否包含其他附加保障或特定身故保險金。  
+條文依據：  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]  
+- [第二十八條 受益人]  
+- [第十三條 初次罹患癌症(重度)保險金的給付]  
+- [第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付]</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 根據條款第十四條，「癌症(重度)追蹤照護保險金」的給付以被保險人仍生存為前提，且最長以五年為限。被保險人已領取2次，尚未達到給付上限，但因被保險人已身故，該保險金不再適用。  
+2. 條款未明確規定是否存在專屬的身故保險金供受益人申領。  
+3. 條款第二十八條規定，若被保險人身故時仍有未完全給付的保險金，該部分保險金之受益人為法定繼承人，但未明確指出是否包含其他附加保障或特定身故保險金。  
+條文依據：  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]  
+- [第二十八條 受益人]</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認癌症(重度)追蹤照護金的給付次數及條件是否已達上限", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認保險契約中是否有身故保險金的保障", "must_have": true, "分數": 0.5}, {"id": "3", "point": "確認其他相關保險金（如未領取的附加保障）是否適用", "must_have": false, "分數": 0.5}], "coverage_score": 0.7222, "nli": {"entailment": 0.986089, "neutral": 0.013223, "contradiction": 0.000688, "factuality": 0.999312, "C_fact": 0.999312}, "C_conf": 0.7219}</t>
+        </is>
+      </c>
+      <c r="J63" s="4" t="n">
+        <v>0.7222</v>
+      </c>
+      <c r="K63" s="3" t="n">
+        <v>0.999312</v>
+      </c>
+      <c r="L63" s="4" t="n">
+        <v>0.7219</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:26:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>保險金額2萬元，「罹癌基因檢測服務」費用8萬元，還會給付多少「癌症(重度)追蹤照護保險金」？</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款，若被保險人選擇申領「罹癌基因檢測服務」，且該服務費用（8萬元）高於「罹癌基因檢測服務額度」（1,000元），則被保險人僅能申領「癌症(重度)追蹤照護保險金」。因此，保險公司將不提供罹癌基因檢測服務，而是依「癌症(重度)追蹤照護保險金」的計算方式給付。  
+「癌症(重度)追蹤照護保險金」的計算方式為：保險金額的12倍，即2萬元 × 12 = 24萬元。  
+條文依據：  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用) | 附件一：罹癌基因檢測服務之項目、服務費用及補償金額表 | 第二十三條 癌症保險金或罹癌基因檢測服務的申領 | 第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用) | payout_items | 第十三條 初次罹患癌症(重度)保險金的給付 | other_metadata | 第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款，若被保險人選擇申領「罹癌基因檢測服務」，且該服務費用（8萬元）高於「罹癌基因檢測服務額度」（1,000元），則被保險人僅能申領「癌症(重度)追蹤照護保險金」。因此，保險公司將不提供罹癌基因檢測服務，而是依「癌症(重度)追蹤照護保險金」的計算方式給付。  
+「癌症(重度)追蹤照護保險金」的計算方式為：保險金額的12倍，即2萬元 × 12 = 24萬元。  
+條文依據：  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr"/>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認罹癌基因檢測服務費用是否已從保險金額中扣除", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認癌症(重度)追蹤照護保險金的給付條件與計算方式", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認保險金額2萬元是否為總額或部分額度", "must_have": false, "分數": 0.5}], "coverage_score": 0.9444, "nli": {"entailment": 0.295541, "neutral": 0.666661, "contradiction": 0.037798, "factuality": 0.962202, "C_fact": 0.962202}, "C_conf": 0.9228}</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="n">
+        <v>0.9444</v>
+      </c>
+      <c r="K64" s="3" t="n">
+        <v>0.962202</v>
+      </c>
+      <c r="L64" s="3" t="n">
+        <v>0.9228</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:26:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>投保後1個月罹患重度癌症，會給付哪些保險金？契約還會持續有效嗎？</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 若被保險人在投保後1個月內（即第一保險單年度內）診斷確定罹患重度癌症，符合「初次診斷確定罹患癌症(重度)」條件，本公司將給付「初次罹患癌症(重度)保險金」，金額為「年繳應繳保險費」的1.06倍。  
+2. 契約仍會持續有效，但當期已繳付之未到期保險費將不予退還。
+條文依據：  
+- [第十三條 初次罹患癌症(重度)保險金的給付]  
+- [第十六條 癌症(重度)豁免保險費(第二保險單年度起適用)]</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 癌症(重度)豁免保險費(第二保險單年度起適用) | 第十三條 初次罹患癌症(重度)保險金的給付 | 第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用) | 第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付 | 第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用)</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 若被保險人在投保後1個月內（即第一保險單年度內）診斷確定罹患重度癌症，符合「初次診斷確定罹患癌症(重度)」條件，本公司將給付「初次罹患癌症(重度)保險金」，金額為「年繳應繳保險費」的1.06倍。  
+2. 契約仍會持續有效，但當期已繳付之未到期保險費將不予退還。
+條文依據：  
+- [第十三條 初次罹患癌症(重度)保險金的給付]  
+- [第十六條 癌症(重度)豁免保險費(第二保險單年度起適用)]</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr"/>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "投保後1個月罹患重度癌症，會給付哪些保險金？契約還會持續有效嗎？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.99617, "neutral": 0.003275, "contradiction": 0.000556, "factuality": 0.999444, "C_fact": 0.999444}, "C_conf": 0.9997}</t>
+        </is>
+      </c>
+      <c r="J65" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K65" s="3" t="n">
+        <v>0.999444</v>
+      </c>
+      <c r="L65" s="3" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:26:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>投保後10個月罹患重度癌症，會給付哪些保險金？契約還會持續有效嗎？</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 若被保險人於投保後10個月（即第一保險單年度內）診斷確定罹患重度癌症，符合「初次診斷確定罹患癌症(重度)」條件，本公司將給付「初次罹患癌症(重度)保險金」，金額為「年繳應繳保險費」的1.06倍。  
+2. 契約仍會持續有效，並不會因給付該保險金而終止。
+條文依據：  
+- [第十三條 初次罹患癌症(重度)保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 癌症(重度)豁免保險費(第二保險單年度起適用) | 第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用) | 第十條 契約的終止（二） | 第十三條 初次罹患癌症(重度)保險金的給付 | 第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 若被保險人於投保後10個月（即第一保險單年度內）診斷確定罹患重度癌症，符合「初次診斷確定罹患癌症(重度)」條件，本公司將給付「初次罹患癌症(重度)保險金」，金額為「年繳應繳保險費」的1.06倍。  
+2. 契約仍會持續有效，並不會因給付該保險金而終止。
+條文依據：  
+- [第十三條 初次罹患癌症(重度)保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr"/>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "投保後10個月罹患重度癌症，會給付哪些保險金？契約還會持續有效嗎？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.7816, "neutral": 0.060202, "contradiction": 0.158197, "factuality": 0.841803, "C_fact": 0.841803}, "C_conf": 0.9018}</t>
+        </is>
+      </c>
+      <c r="J66" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K66" s="3" t="n">
+        <v>0.841803</v>
+      </c>
+      <c r="L66" s="3" t="n">
+        <v>0.9018</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:27:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>投保醫心康愛，罹患肺癌一期，可領什麼保險金？</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人罹患肺癌一期，符合「初次診斷確定罹患癌症(初期)」的定義，可申領「初次罹患癌症(初期)或癌症(輕度)保險金」。給付金額依診斷確定日所在的保險單年度而定：  
+1. 若診斷確定日在第一保險單年度內，給付「年繳應繳保險費」的1.06倍。  
+2. 若診斷確定日在第二保險單年度(含)以後，給付「保險金額」的5倍。  
+條文依據：  
+- [第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付 | 第十三條 初次罹患癌症(重度)保險金的給付 | payout_items | 第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用) | 第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人罹患肺癌一期，符合「初次診斷確定罹患癌症(初期)」的定義，可申領「初次罹患癌症(初期)或癌症(輕度)保險金」。給付金額依診斷確定日所在的保險單年度而定：  
+1. 若診斷確定日在第一保險單年度內，給付「年繳應繳保險費」的1.06倍。  
+2. 若診斷確定日在第二保險單年度(含)以後，給付「保險金額」的5倍。  
+條文依據：  
+- [第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr"/>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "投保醫心康愛，罹患肺癌一期，可領什麼保險金？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.018148, "neutral": 0.981599, "contradiction": 0.000253, "factuality": 0.999747, "C_fact": 0.999747}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J67" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K67" s="3" t="n">
+        <v>0.9997470000000001</v>
+      </c>
+      <c r="L67" s="3" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:27:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>PX5</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>若被保險人身故有何給付?</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人身故時，若本附約保險金尚未給付或未完全給付，則該部分保險金的受益人為被保險人的法定繼承人，並依被保險人身故時的法定繼承人順序及應得比例，適用民法繼承編的相關規定。
+條文依據：  
+- [第二十條 受益人]</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>第二十條 受益人 | 第十二條 重大疾病保險金的給付 | 第十一條 輕度重大疾病保險金的給付 | 第十四條 保險事故的通知與保險金的申請時間 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人身故時，若本附約保險金尚未給付或未完全給付，則該部分保險金的受益人為被保險人的法定繼承人，並依被保險人身故時的法定繼承人順序及應得比例，適用民法繼承編的相關規定。
+條文依據：  
+- [第二十條 受益人]</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr"/>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "若被保險人身故有何給付?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.990448, "neutral": 0.007011, "contradiction": 0.002541, "factuality": 0.997459, "C_fact": 0.997459}, "C_conf": 0.9985}</t>
+        </is>
+      </c>
+      <c r="J68" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K68" s="3" t="n">
+        <v>0.997459</v>
+      </c>
+      <c r="L68" s="3" t="n">
+        <v>0.9985000000000001</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:27:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>PX5</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>投保鍾溢祝福後，請問在第二年經醫院醫師初次診斷罹患「輕度重大疾病」中的癌症(輕度)者，可以領到輕度重大疾病保險金嗎?可以領到保險金額的百分之多少?</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+在第二年經醫院醫師初次診斷罹患「輕度重大疾病」中的癌症(輕度)者，可以領取輕度重大疾病保險金，給付比例為保險金額的百分之二十。此情況符合理賠條件，因診斷確定日位於續保年度內，且輕度癌症屬於輕度重大疾病的保障範圍。  
+條文依據：  
+- [第十一條 輕度重大疾病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 輕度重大疾病保險金的給付 | 第十二條 重大疾病保險金的給付 | other_metadata | payout_items | 國泰人壽鍾溢祝福重大疾病健康保險附約(乙型) (外溢型)年繳費率表 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+在第二年經醫院醫師初次診斷罹患「輕度重大疾病」中的癌症(輕度)者，可以領取輕度重大疾病保險金，給付比例為保險金額的百分之二十。此情況符合理賠條件，因診斷確定日位於續保年度內，且輕度癌症屬於輕度重大疾病的保障範圍。  
+條文依據：  
+- [第十一條 輕度重大疾病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr"/>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認輕度重大疾病保險金是否涵蓋輕度癌症", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認第二年投保後是否符合輕度重大疾病保險金的理賠條件", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認輕度重大疾病保險金額的給付比例", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認保單中是否有特定輕度癌症的理賠限制或條件", "must_have": false, "分數": 0.8}], "coverage_score": 0.9846, "nli": {"entailment": 0.68115, "neutral": 0.313859, "contradiction": 0.004991, "factuality": 0.995009, "C_fact": 0.995009}, "C_conf": 0.9816}</t>
+        </is>
+      </c>
+      <c r="J69" s="3" t="n">
+        <v>0.9846</v>
+      </c>
+      <c r="K69" s="3" t="n">
+        <v>0.995009</v>
+      </c>
+      <c r="L69" s="3" t="n">
+        <v>0.9816</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:27:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>PX5</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>請問如果在投保後的第三年經醫院醫師初次診斷罹患「重大疾病」者，可以領到重大疾病保險金嗎?可以領到保險金額的百分之多少?那後續又在第四年經醫院醫師初次診斷罹患「輕度重大疾病」者，可以領到輕度重大疾病保險金嗎?可以領到保險金額的百分之多少?</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 在投保後的第三年經醫院醫師初次診斷罹患「重大疾病」者，符合重大疾病保險金的給付條件，可領取保險金額的1.3倍。  
+2. 在第四年經醫院醫師初次診斷罹患「輕度重大疾病」者，符合輕度重大疾病保險金的給付條件，但因條款規定「輕度重大疾病保險金」終身最多給付一次，且已於第三年領取重大疾病保險金時扣除過輕度重大疾病保險金，因此無法再次領取輕度重大疾病保險金。
+條文依據：  
+- [第十二條 重大疾病保險金的給付]  
+- [第十一條 輕度重大疾病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 輕度重大疾病保險金的給付 | 第十二條 重大疾病保險金的給付 | 第十六條 除外責任 | payout_items | 第二條 名詞定義 | 第四條 保險範圍 | other_metadata | 國泰人壽鍾溢祝福重大疾病健康保險附約(乙型) (外溢型)年繳費率表</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 在投保後的第三年經醫院醫師初次診斷罹患「重大疾病」者，符合重大疾病保險金的給付條件，可領取保險金額的1.3倍。  
+2. 在第四年經醫院醫師初次診斷罹患「輕度重大疾病」者，符合輕度重大疾病保險金的給付條件，但因條款規定「輕度重大疾病保險金」終身最多給付一次，且已於第三年領取重大疾病保險金時扣除過輕度重大疾病保險金，因此無法再次領取輕度重大疾病保險金。
+條文依據：  
+- [第十二條 重大疾病保險金的給付]  
+- [第十一條 輕度重大疾病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr"/>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認重大疾病保險金的給付條件是否符合第三年初次診斷重大疾病的情況", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認重大疾病保險金額的給付比例", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認輕度重大疾病保險金的給付條件是否符合第四年初次診斷輕度重大疾病的情況", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認輕度重大疾病保險金額的給付比例", "must_have": true, "分數": 1.0}, {"id": "5", "point": "確認重大疾病與輕度重大疾病的定義及區分標準", "must_have": false, "分數": 0.5}], "coverage_score": 0.9706, "nli": {"entailment": 0.653292, "neutral": 0.166783, "contradiction": 0.179925, "factuality": 0.820075, "C_fact": 0.820075}, "C_conf": 0.8617}</t>
+        </is>
+      </c>
+      <c r="J70" s="3" t="n">
+        <v>0.9706</v>
+      </c>
+      <c r="K70" s="3" t="n">
+        <v>0.820075</v>
+      </c>
+      <c r="L70" s="3" t="n">
+        <v>0.8617</v>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:27:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>PX5</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>請問如果在投保後的第三年經醫院醫師初次診斷罹患「輕度重大疾病」者，可以領到重大疾病保險金嗎?可以領到保險金額的百分之多少?那後續又在第四年經醫院醫師初次診斷罹患「重大疾病」者，可以領到輕度重大疾病保險金嗎?可以領到保險金額的百分之多少?</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 在投保後的第三年，若經醫院醫師初次診斷罹患「輕度重大疾病」，符合保險金給付條件，可領取「輕度重大疾病保險金」，給付比例為保險金額的20%。  
+2. 在第四年，若經醫院醫師初次診斷罹患「重大疾病」，符合保險金給付條件，但因已於第三年申領過「輕度重大疾病保險金」，依條款規定，重大疾病保險金的給付金額需扣除已給付的輕度重大疾病保險金，最終給付比例為保險金額的130%減去20%，即保險金額的110%。  
+條文依據：  
+- [第十一條 輕度重大疾病保險金的給付]  
+- [第十二條 重大疾病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 輕度重大疾病保險金的給付 | 第十二條 重大疾病保險金的給付 | 第十六條 除外責任 | payout_items | 第二條 名詞定義 | 第四條 保險範圍 | other_metadata | 第十五條 各項保險金的申領</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 在投保後的第三年，若經醫院醫師初次診斷罹患「輕度重大疾病」，符合保險金給付條件，可領取「輕度重大疾病保險金」，給付比例為保險金額的20%。  
+2. 在第四年，若經醫院醫師初次診斷罹患「重大疾病」，符合保險金給付條件，但因已於第三年申領過「輕度重大疾病保險金」，依條款規定，重大疾病保險金的給付金額需扣除已給付的輕度重大疾病保險金，最終給付比例為保險金額的130%減去20%，即保險金額的110%。  
+條文依據：  
+- [第十一條 輕度重大疾病保險金的給付]  
+- [第十二條 重大疾病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr"/>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認輕度重大疾病是否符合保險金給付條件", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認輕度重大疾病保險金額的給付比例", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認重大疾病是否符合保險金給付條件", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認重大疾病保險金額的給付比例", "must_have": true, "分數": 1.0}, {"id": "5", "point": "確認輕度重大疾病保險金是否在重大疾病診斷後仍可申請", "must_have": false, "分數": 0.0}], "coverage_score": 0.9412, "nli": {"entailment": 0.975595, "neutral": 0.018349, "contradiction": 0.006056, "factuality": 0.993944, "C_fact": 0.993944}, "C_conf": 0.9378}</t>
+        </is>
+      </c>
+      <c r="J71" s="3" t="n">
+        <v>0.9412</v>
+      </c>
+      <c r="K71" s="3" t="n">
+        <v>0.993944</v>
+      </c>
+      <c r="L71" s="3" t="n">
+        <v>0.9378</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:28:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>PX5</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>請問主約效力終止(因身故以外情形)，PX5還能持續有效嗎？</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+主約效力因身故以外情形終止時，PX5附約仍可持續有效，但需符合以下條件：  
+1. 要保人需繼續繳交附約保險費。  
+2. 附約效力可延續至主約原保險期間屆滿或附約最高續保年齡（80歲），以較早者為準。  
+條文依據：  
+- [第十條 附約的終止（二）]</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>第十條 附約的終止（二） | 第七條 保險費的墊繳、附約的停效及復效 | 第五條 附約的保險期間及保證續保 | 第十三條 健康促進保險費折減 | 第九條 附約的終止（一）</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+主約效力因身故以外情形終止時，PX5附約仍可持續有效，但需符合以下條件：  
+1. 要保人需繼續繳交附約保險費。  
+2. 附約效力可延續至主約原保險期間屆滿或附約最高續保年齡（80歲），以較早者為準。  
+條文依據：  
+- [第十條 附約的終止（二）]</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr"/>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "請問主約效力終止(因身故以外情形)，PX5還能持續有效嗎？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.051754, "neutral": 0.947283, "contradiction": 0.000964, "factuality": 0.999036, "C_fact": 0.999036}, "C_conf": 0.9994}</t>
+        </is>
+      </c>
+      <c r="J72" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K72" s="3" t="n">
+        <v>0.999036</v>
+      </c>
+      <c r="L72" s="3" t="n">
+        <v>0.9994</v>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:28:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>請問如果於「無理賠紀錄期間」屆滿日以內罹患特定傷病，會給付多少錢?這筆錢會給付給誰?</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在「無理賠紀錄期間」屆滿日以內罹患特定傷病，保險公司將給付的金額為「保險金額」加上「年繳應繳保險費總額」乘以1.02的加總。這筆「特定傷病保險金」的受益人為被保險人本人，且不得指定或變更。
+條文依據：  
+- [第十一條 特定傷病保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第十二條 無理賠關懷保險金的給付 | 第十一條 特定傷病保險金的給付 | payout_items | 第二十七條 受益人的指定及變更</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在「無理賠紀錄期間」屆滿日以內罹患特定傷病，保險公司將給付的金額為「保險金額」加上「年繳應繳保險費總額」乘以1.02的加總。這筆「特定傷病保險金」的受益人為被保險人本人，且不得指定或變更。
+條文依據：  
+- [第十一條 特定傷病保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr"/>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "請問如果於「無理賠紀錄期間」屆滿日以內罹患特定傷病，會給付多少錢?這筆錢會給付給誰?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.996866, "neutral": 0.00284, "contradiction": 0.000294, "factuality": 0.999706, "C_fact": 0.999706}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J73" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K73" s="3" t="n">
+        <v>0.999706</v>
+      </c>
+      <c r="L73" s="3" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:28:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>請問如果要保人與被保險人為同一人，被保險人於「無理賠紀錄期間」屆滿日以內身故，會給付多少錢?這筆錢會給付給誰?</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若要保人與被保險人為同一人，且被保險人於「無理賠紀錄期間」屆滿日以內身故，依第十二條規定，本公司將給付「無理賠關懷保險金」，金額為「年繳應繳保險費總額」乘以1.02。該筆保險金的受益人為要保人本人，若要保人已身故，則以被保險人之法定繼承人為受益人。
+條文依據：  
+- [第十二條 無理賠關懷保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第十二條 無理賠關懷保險金的給付 | 第十一條 特定傷病保險金的給付 | payout_items | 第十九條 失蹤處理 | 第二十一條 無理賠關懷保險金的申領 | 第二十七條 受益人的指定及變更 | 第十七條 除外責任（二）</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若要保人與被保險人為同一人，且被保險人於「無理賠紀錄期間」屆滿日以內身故，依第十二條規定，本公司將給付「無理賠關懷保險金」，金額為「年繳應繳保險費總額」乘以1.02。該筆保險金的受益人為要保人本人，若要保人已身故，則以被保險人之法定繼承人為受益人。
+條文依據：  
+- [第十二條 無理賠關懷保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr"/>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認保險契約中身故保險金的給付金額", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認身故保險金的受益人為誰", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認「無理賠紀錄期間」屆滿日的定義及影響", "must_have": false, "分數": 0.5}], "coverage_score": 0.9444, "nli": {"entailment": 0.993496, "neutral": 0.005585, "contradiction": 0.000919, "factuality": 0.999081, "C_fact": 0.999081}, "C_conf": 0.9439}</t>
+        </is>
+      </c>
+      <c r="J74" s="3" t="n">
+        <v>0.9444</v>
+      </c>
+      <c r="K74" s="3" t="n">
+        <v>0.999081</v>
+      </c>
+      <c r="L74" s="3" t="n">
+        <v>0.9439</v>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:28:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>請問如果要保人與被保險人為不同人，被保險人於「無理賠紀錄期間」屆滿日以內生存，且被保險人未罹患特定傷病，會給付多少錢?這筆錢會給付給誰?</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若要保人與被保險人為不同人，且被保險人於「無理賠紀錄期間」屆滿日以內生存，並未罹患特定傷病，則符合「無理賠關懷保險金」的給付條件。本公司將按「年繳應繳保險費總額」乘以1.02計算給付金額。此筆保險金的受益人為要保人本人。
+條文依據：  
+- [第十二條 無理賠關懷保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第十二條 無理賠關懷保險金的給付 | 第十一條 特定傷病保險金的給付 | payout_items | 第二十七條 受益人的指定及變更 | 第十九條 失蹤處理 | 第二十一條 無理賠關懷保險金的申領 | 第十七條 除外責任（二）</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若要保人與被保險人為不同人，且被保險人於「無理賠紀錄期間」屆滿日以內生存，並未罹患特定傷病，則符合「無理賠關懷保險金」的給付條件。本公司將按「年繳應繳保險費總額」乘以1.02計算給付金額。此筆保險金的受益人為要保人本人。
+條文依據：  
+- [第十二條 無理賠關懷保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr"/>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認被保險人於無理賠紀錄期間屆滿日以內生存的條件", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認被保險人未罹患特定傷病的條件", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認給付金額的計算方式或金額", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認給付金的受益人為誰", "must_have": true, "分數": 1.0}, {"id": "5", "point": "確認保險契約中是否有相關條款限制或附加條件", "must_have": false, "分數": 0.8}], "coverage_score": 0.9882, "nli": {"entailment": 0.993115, "neutral": 0.00625, "contradiction": 0.000635, "factuality": 0.999365, "C_fact": 0.999365}, "C_conf": 0.9878}</t>
+        </is>
+      </c>
+      <c r="J75" s="3" t="n">
+        <v>0.9882</v>
+      </c>
+      <c r="K75" s="3" t="n">
+        <v>0.9993649999999999</v>
+      </c>
+      <c r="L75" s="3" t="n">
+        <v>0.9878</v>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:29:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>保戶如果身故，會給保險金嗎?</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保戶（被保險人）若於契約有效期間內身故，是否給付保險金需視具體情況而定。例如：  
+1. 若被保險人於「無理賠紀錄期間」內身故，本公司依第五條約定給付保險金。  
+2. 若被保險人因除外責任中的情形（如故意自殺於契約訂立或復效未滿二年內）身故，則本公司不負給付責任。  
+條文依據：  
+- [第五條 保險範圍]  
+- [第十七條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第二十八條 本契約受益人死亡或失蹤的處理 | 第十七條 除外責任（二） | 第二十三條 受益人受益權之喪失 | 第十九條 失蹤處理</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保戶（被保險人）若於契約有效期間內身故，是否給付保險金需視具體情況而定。例如：  
+1. 若被保險人於「無理賠紀錄期間」內身故，本公司依第五條約定給付保險金。  
+2. 若被保險人因除外責任中的情形（如故意自殺於契約訂立或復效未滿二年內）身故，則本公司不負給付責任。  
+條文依據：  
+- [第五條 保險範圍]  
+- [第十七條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr"/>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "保戶如果身故，會給保險金嗎?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.993931, "neutral": 0.005652, "contradiction": 0.000418, "factuality": 0.999582, "C_fact": 0.999582}, "C_conf": 0.9997}</t>
+        </is>
+      </c>
+      <c r="J76" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K76" s="3" t="n">
+        <v>0.999582</v>
+      </c>
+      <c r="L76" s="3" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:29:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>保戶如果身故，身故申領的保險金會給誰?</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人身故，身故保險金的受益人依以下情況處理：  
+1. 若受益人已指定，則由指定的受益人領取。  
+2. 若受益人未指定或受益人喪失受益權，則保險金作為被保險人的遺產，由其法定繼承人依民法繼承編相關規定分配。  
+條文依據：  
+- [第二十三條 受益人受益權之喪失]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第二十三條 受益人受益權之喪失 | 第二十七條 受益人的指定及變更 | 第二十八條 本契約受益人死亡或失蹤的處理 | 第二十二條 分期定期保險金給付申領文件、給付期限及未依限給付之效果</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人身故，身故保險金的受益人依以下情況處理：  
+1. 若受益人已指定，則由指定的受益人領取。  
+2. 若受益人未指定或受益人喪失受益權，則保險金作為被保險人的遺產，由其法定繼承人依民法繼承編相關規定分配。  
+條文依據：  
+- [第二十三條 受益人受益權之喪失]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr"/>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "保戶如果身故，身故申領的保險金會給誰?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.993739, "neutral": 0.005837, "contradiction": 0.000425, "factuality": 0.999575, "C_fact": 0.999575}, "C_conf": 0.9997}</t>
+        </is>
+      </c>
+      <c r="J77" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K77" s="3" t="n">
+        <v>0.999575</v>
+      </c>
+      <c r="L77" s="3" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:29:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>如果保戶投保繳費年期20年的滿溢寶，然後在第20保單年度身故的話，可以領到多少錢?</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+條款未明確規定／資料不足</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第十條 契約的終止（二） | 第二十六條 投保年齡的計算及錯誤的處理 | 第十一條 特定傷病保險金的給付 | 第十五條 健康促進保險費折減 | 第二十條 特定傷病保險金的申領 | 第十三條 分期定期保險金給付 | 第二十八條 本契約受益人死亡或失蹤的處理 | 第十九條 失蹤處理 | 第十八條 保險事故的通知與保險金的申請時間 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款內容，滿溢寶保險的身故保障內容僅限於「特定傷病」或「無理賠紀錄期間」內的身故情形。若保戶在第20保單年度身故，條款中並未提及該情況下的理賠金額計算方式。此外，滿溢寶保險為不分紅保險單，無紅利或附加利益影響理賠金額。  
+條文依據：  
+- [第五條 保險範圍]  
+- [第十一條 特定傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+條款未明確規定／資料不足</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+條款未明確規定／資料不足</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認滿溢寶保險的身故保障內容", "must_have": true, "分數": 0.5}, {"id": "2", "point": "確認保單繳費年期20年對身故理賠的影響", "must_have": true, "分數": 0.0}, {"id": "3", "point": "確認第20保單年度身故的理賠金額計算方式", "must_have": true, "分數": 0.0}, {"id": "4", "point": "確認是否有額外的紅利或附加利益影響理賠金額", "must_have": false, "分數": 0.0}], "coverage_score": 0.1538, "nli": {"entailment": 0.025091, "neutral": 0.018455, "contradiction": 0.956453, "factuality": 0.043547, "C_fact": 0.043547}, "C_conf": 0.0235}</t>
+        </is>
+      </c>
+      <c r="J78" s="4" t="n">
+        <v>0.1538</v>
+      </c>
+      <c r="K78" s="4" t="n">
+        <v>0.043547</v>
+      </c>
+      <c r="L78" s="4" t="n">
+        <v>0.0235</v>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:30:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>被保險人為60歲女性，投保繳費期間20年期之滿溢寶特定傷病定期健康保險（定期給付型）（外溢型）100萬元，年繳應繳保險費為83,500元，年繳實繳保險費為78,490元。若被保險人於第二保險單年度自殺身故，則無理賠關懷保險金可以領到多少錢？</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於第二保險單年度自殺身故，根據條款規定，自契約訂立或復效之日起二年內因故意自殺致死者，本公司不負給付無理賠關懷保險金的責任。因此，本案例中無理賠關懷保險金無法領取。
+條文依據：  
+- [第十七條 除外責任（二）]  
+- [第十二條 無理賠關懷保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 無理賠關懷保險金的給付 | 第十七條 除外責任（二） | 第十一條 特定傷病保險金的給付 | other_metadata | 第十九條 失蹤處理 | 第五條 保險範圍 | 第二十一條 無理賠關懷保險金的申領 | 第二十七條 受益人的指定及變更</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於第二保險單年度自殺身故，根據條款規定，自契約訂立或復效之日起二年內因故意自殺致死者，本公司不負給付無理賠關懷保險金的責任。因此，本案例中無理賠關懷保險金無法領取。
+條文依據：  
+- [第十七條 除外責任（二）]  
+- [第十二條 無理賠關懷保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr"/>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認保險契約中自殺身故的理賠條款", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認第二保險單年度是否屬於等待期內", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認關懷保險金的計算方式及適用條件", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認年繳實繳保險費與年繳應繳保險費的差異是否影響理賠金額", "must_have": false, "分數": 0.0}], "coverage_score": 0.9231, "nli": {"entailment": 0.878905, "neutral": 0.10412, "contradiction": 0.016975, "factuality": 0.983025, "C_fact": 0.983025}, "C_conf": 0.9137}</t>
+        </is>
+      </c>
+      <c r="J79" s="3" t="n">
+        <v>0.9231</v>
+      </c>
+      <c r="K79" s="3" t="n">
+        <v>0.983025</v>
+      </c>
+      <c r="L79" s="3" t="n">
+        <v>0.9137</v>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:30:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>請問如果第2保單年度罹患特定傷病，可以給付多少錢?給付給誰?未來還有其他保險金嗎?</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. **給付金額**：若於第二保險單年度（含）以後罹患特定傷病，將依「保險金額」給付「特定傷病保險金」。  
+2. **給付對象**：保險金給付予被保險人或其指定受益人。  
+3. **未來保險金**：自初次診斷確定罹患特定傷病的次一個保險單週年日起，每逢保險單週年日仍生存者，可按「保險金額」的36%給付「生活補助保險金」，最多給付10次。  
+條文依據：  
+- [第十二條 特定傷病保險金的給付]  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 特定傷病保險金的給付 | 第五條 保險範圍 | 第十三條 生活補助保險金的給付（第二保險單年度起適用） | 第二條 名詞定義 | 第十五條 保險費豁免（第二保險單年度起適用）</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. **給付金額**：若於第二保險單年度（含）以後罹患特定傷病，將依「保險金額」給付「特定傷病保險金」。  
+2. **給付對象**：保險金給付予被保險人或其指定受益人。  
+3. **未來保險金**：自初次診斷確定罹患特定傷病的次一個保險單週年日起，每逢保險單週年日仍生存者，可按「保險金額」的36%給付「生活補助保險金」，最多給付10次。  
+條文依據：  
+- [第十二條 特定傷病保險金的給付]  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr"/>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "請問如果第2保單年度罹患特定傷病，可以給付多少錢?給付給誰?未來還有其他保險金嗎?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.876558, "neutral": 0.063392, "contradiction": 0.06005, "factuality": 0.93995, "C_fact": 0.93995}, "C_conf": 0.9635}</t>
+        </is>
+      </c>
+      <c r="J80" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K80" s="3" t="n">
+        <v>0.93995</v>
+      </c>
+      <c r="L80" s="3" t="n">
+        <v>0.9635</v>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:30:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>請問我115年1月1日投保，怎麼得到健康促進保險費折減?</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+要獲得健康促進保險費折減，您需要在保單有效期間內完成以下步驟：  
+1. 使用保險公司指定的程式並加入指定的健康計劃。  
+2. 完成程式註冊程序，並授權保險公司取得與健康促進相關的電子紀錄。  
+3. 在「指定日期」時，您的會員等級需符合以下標準之一：  
+   - 實踐家：次一保險單年度保險費折減3%。  
+   - 樂享家或更高等級：次一保險單年度保險費折減10%。  
+注意：復效或豁免的保險費不適用此折減規定。
+條文依據：  
+- [第十六條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 健康促進保險費折減 | 第二十三條 投保年齡的計算及錯誤的處理 | 第十五條 保險費豁免（第二保險單年度起適用） | 第五條 保險範圍 | payout_items</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+要獲得健康促進保險費折減，您需要在保單有效期間內完成以下步驟：  
+1. 使用保險公司指定的程式並加入指定的健康計劃。  
+2. 完成程式註冊程序，並授權保險公司取得與健康促進相關的電子紀錄。  
+3. 在「指定日期」時，您的會員等級需符合以下標準之一：  
+   - 實踐家：次一保險單年度保險費折減3%。  
+   - 樂享家或更高等級：次一保險單年度保險費折減10%。  
+注意：復效或豁免的保險費不適用此折減規定。
+條文依據：  
+- [第十六條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr"/>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "請問我115年1月1日投保，怎麼得到健康促進保險費折減?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.996803, "neutral": 0.001782, "contradiction": 0.001414, "factuality": 0.998586, "C_fact": 0.998586}, "C_conf": 0.9992}</t>
+        </is>
+      </c>
+      <c r="J81" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K81" s="3" t="n">
+        <v>0.998586</v>
+      </c>
+      <c r="L81" s="3" t="n">
+        <v>0.9992</v>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:30:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>保戶在114/1/10投保樂鍾溢，如果他在115/3/30罹患特定傷病的話，在什麼時候可以領取生活補助保險金?</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 樂鍾溢保險包含生活補助保險金保障，並於第二保險單年度起適用。  
+2. 保戶於115/3/30初次診斷確定罹患特定傷病，符合生活補助保險金的理賠條件，因該診斷日已超過等待期間（30日）且發生於第二保險單年度內。  
+3. 根據條款規定，生活補助保險金的給付自初次診斷確定罹患特定傷病的次一個保險單週年日起開始，並於每逢保險單週年日仍生存時給付。因此，保戶可於116/1/10（次一個保險單週年日）起申請並領取生活補助保險金。  
+條文依據：  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]  
+- [國泰人壽樂鍾心特定傷病定期健康保險（外溢型）]</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 生活補助保險金的給付（第二保險單年度起適用） | other_metadata | 第十一條 契約的終止（三） | payout_items | 第十二條 特定傷病保險金的給付 | 第五條 保險範圍 | 第十五條 保險費豁免（第二保險單年度起適用） | 第十條 契約的終止（二）</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 樂鍾溢保險包含生活補助保險金保障，並於第二保險單年度起適用。  
+2. 保戶於115/3/30初次診斷確定罹患特定傷病，符合生活補助保險金的理賠條件，因該診斷日已超過等待期間（30日）且發生於第二保險單年度內。  
+3. 根據條款規定，生活補助保險金的給付自初次診斷確定罹患特定傷病的次一個保險單週年日起開始，並於每逢保險單週年日仍生存時給付。因此，保戶可於116/1/10（次一個保險單週年日）起申請並領取生活補助保險金。  
+條文依據：  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]  
+- [國泰人壽樂鍾心特定傷病定期健康保險（外溢型）]</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr"/>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認樂鍾溢保險是否包含生活補助保險金保障", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認特定傷病是否符合生活補助保險金的理賠條件", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認生活補助保險金的申請及給付時間規定", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認保單生效日與特定傷病發生日的關聯性", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.567407, "neutral": 0.431772, "contradiction": 0.000822, "factuality": 0.999178, "C_fact": 0.999178}, "C_conf": 0.9995}</t>
+        </is>
+      </c>
+      <c r="J82" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K82" s="3" t="n">
+        <v>0.999178</v>
+      </c>
+      <c r="L82" s="3" t="n">
+        <v>0.9995000000000001</v>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:31:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>保戶在114/1/10投保樂鍾溢，如果他在115/3/30罹患特定傷病的話，他在115/1/9會領到無理賠回饋保險金嗎?</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保單包含無理賠回饋保險金的條款，但保戶在115/1/9不符合領取條件，因為其於115/3/30罹患特定傷病，根據條款規定，若被保險人於保險單年度內罹患特定傷病並申領特定傷病保險金，則無法領取無理賠回饋保險金。此外，條款明確指出，若已給付無理賠回饋保險金後發現不符條件，保險公司有權要求返還或從其他保險金中扣回。
+條文依據：  
+- [第十四條 無理賠回饋保險金的給付]  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>payout_items | 第十四條 無理賠回饋保險金的給付 | other_metadata | 第十二條 特定傷病保險金的給付 | 第二十條 無理賠回饋保險金的申領 | 第十條 契約的終止（二） | 第五條 保險範圍 | 第十五條 保險費豁免（第二保險單年度起適用）</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保單包含無理賠回饋保險金的條款，但保戶在115/1/9不符合領取條件，因為其於115/3/30罹患特定傷病，根據條款規定，若被保險人於保險單年度內罹患特定傷病並申領特定傷病保險金，則無法領取無理賠回饋保險金。此外，條款明確指出，若已給付無理賠回饋保險金後發現不符條件，保險公司有權要求返還或從其他保險金中扣回。
+條文依據：  
+- [第十四條 無理賠回饋保險金的給付]  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr"/>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認保單是否包含無理賠回饋保險金的條款", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認保戶在115/1/9是否符合無理賠回饋保險金的領取條件", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認特定傷病是否影響無理賠回饋保險金的領取資格", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.146699, "neutral": 0.850684, "contradiction": 0.002617, "factuality": 0.997383, "C_fact": 0.997383}, "C_conf": 0.9984}</t>
+        </is>
+      </c>
+      <c r="J83" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K83" s="3" t="n">
+        <v>0.997383</v>
+      </c>
+      <c r="L83" s="3" t="n">
+        <v>0.9984</v>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:31:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>被保險人於第一保險單年度罹患急性心肌梗塞（重度），生活補助保險金最多可以領取幾次？</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於第一保險單年度罹患急性心肌梗塞（重度），無法申領生活補助保險金，因為生活補助保險金僅適用於第二保險單年度（含）以後的有效期間內。  
+條文依據：  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 生活補助保險金的給付（第二保險單年度起適用） | 第十二條 特定傷病保險金的給付 | 第十一條 契約的終止（三） | 第五條 保險範圍 | 第二條 名詞定義 | payout_items | 第十四條 無理賠回饋保險金的給付 | 第十九條 特定傷病保險金、生活補助保險金或保險費豁免的申領</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於第一保險單年度罹患急性心肌梗塞（重度），無法申領生活補助保險金，因為生活補助保險金僅適用於第二保險單年度（含）以後的有效期間內。  
+條文依據：  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr"/>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認生活補助保險金是否涵蓋急性心肌梗塞（重度）", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認第一保險單年度內生活補助保險金的給付次數上限", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認急性心肌梗塞（重度）是否符合生活補助保險金的理賠條件", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.040638, "neutral": 0.953771, "contradiction": 0.005591, "factuality": 0.994409, "C_fact": 0.994409}, "C_conf": 0.9966}</t>
+        </is>
+      </c>
+      <c r="J84" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K84" s="3" t="n">
+        <v>0.994409</v>
+      </c>
+      <c r="L84" s="3" t="n">
+        <v>0.9966</v>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:31:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>被保險人為60歲女性，投保繳費期間20年期之樂鍾心特定傷病定期健康保險（外溢型）5單位，每單位年繳應繳保險費為1675元，則每逢保險單年度末生存者，可以領取多少無理賠關懷保險金？</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+每逢保險單年度末生存者，可以領取的無理賠回饋保險金為：  
+1675元 × 10% × 5單位 = 837.5元（元以下無條件進位為838元）。  
+條文依據：  
+- [第十四條 無理賠回饋保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 無理賠回饋保險金的給付 | other_metadata | payout_items | 第二十條 無理賠回饋保險金的申領 | 第十二條 特定傷病保險金的給付 | 第十三條 生活補助保險金的給付（第二保險單年度起適用） | 第五條 保險範圍 | 第十五條 保險費豁免（第二保險單年度起適用）</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+每逢保險單年度末生存者，可以領取的無理賠回饋保險金為：  
+1675元 × 10% × 5單位 = 837.5元（元以下無條件進位為838元）。  
+條文依據：  
+- [第十四條 無理賠回饋保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr"/>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認保險商品名稱為樂鍾心特定傷病定期健康保險（外溢型）", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認投保單位數為5單位", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認每單位年繳保險費為1675元", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認無理賠關懷保險金的計算方式或公式", "must_have": false, "分數": 1.0}, {"id": "5", "point": "確認保險單年度末生存者的定義及條件", "must_have": false, "分數": 0.0}], "coverage_score": 0.9286, "nli": {"entailment": 0.87892, "neutral": 0.11885, "contradiction": 0.00223, "factuality": 0.99777, "C_fact": 0.99777}, "C_conf": 0.9274}</t>
+        </is>
+      </c>
+      <c r="J85" s="3" t="n">
+        <v>0.9286</v>
+      </c>
+      <c r="K85" s="3" t="n">
+        <v>0.99777</v>
+      </c>
+      <c r="L85" s="3" t="n">
+        <v>0.9274</v>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>2026-03-30 20:31:58</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/rag_results.xlsx
+++ b/src/rag_results.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N84"/>
+  <dimension ref="A1:N167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4768,6 +4768,4217 @@
         <v>10.47</v>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>保障範圍包括哪些項目？</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括：住院醫療保險金、加護病房或燒燙傷病房保險金、祝壽保險金、身故保險金或喪葬費用保險金，以及所繳保險費的退還。
+條文依據：  
+- 摘要</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>payout_items | summary | 第五條 保險範圍 | 第二條 名詞定義 | 第十八條 除外責任（一）</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr"/>
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr"/>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J85" s="3" t="n"/>
+      <c r="K85" s="3" t="n"/>
+      <c r="L85" s="3" t="n"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:01:26</t>
+        </is>
+      </c>
+      <c r="N85" s="3" t="n">
+        <v>18.18</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>住院日數計算有什麼特殊規則？</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院日數計算的特殊規則包括：  
+1. 住院日數以被保險人同一次住院的實際全日住進急性病房或慢性病房（含加護病房及燒燙傷病房）的住院日數計算，包含住院及出院當日。  
+2. 若被保險人出院後又於同一日入院診療，該日不得重複計入住院日數。  
+條文依據：  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第十二條 住院醫療保險金的給付 | 第二條 名詞定義 | 第十三條 加護病房或燒燙傷病房保險金的給付 | 第二十八條 住院醫療保險金日額之減少</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr"/>
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr"/>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J86" s="3" t="n"/>
+      <c r="K86" s="3" t="n"/>
+      <c r="L86" s="3" t="n"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:01:30</t>
+        </is>
+      </c>
+      <c r="N86" s="3" t="n">
+        <v>4.32</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>住院醫療保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院醫療保險金的給付規定如下：  
+被保險人於契約有效期間內因疾病或傷害住院治療，本公司依保險單記載之「住院醫療保險金日額」，乘以入院日當年度之「增額係數」，再乘以住院日數計算給付金額。同一保單年度內，同一次住院的住院日數給付上限為三百六十五日。若因同一疾病或傷害於出院後十四日內再次住院，視為同一次住院處理。若契約有效期間屆滿後出院，再次住院部分則不予給付保險金。  
+條文依據：  
+- [第十二條 住院醫療保險金的給付]  
+- [第十一條 住院次數之計算及契約有效期間屆滿後住院之處理]</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 住院醫療保險金的給付 | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第十三條 加護病房或燒燙傷病房保險金的給付 | 第十四條 醫療保險金給付總額之上限 | 第二十八條 住院醫療保險金日額之減少</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr"/>
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr"/>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J87" s="3" t="n"/>
+      <c r="K87" s="3" t="n"/>
+      <c r="L87" s="3" t="n"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:01:37</t>
+        </is>
+      </c>
+      <c r="N87" s="3" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>加護病房或燒燙傷病房保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+加護病房或燒燙傷病房保險金的給付規定如下：  
+被保險人於契約有效期間內因疾病或傷害住院，並於醫院的加護病房或燒燙傷病房接受治療者，除住院醫療保險金外，保險公司將依保險單所記載的「住院醫療保險金日額」，乘以入院日當年度的「增額係數」，再乘以實際住進加護病房或燒燙傷病房的日數（含轉入及轉出當日）的二倍，給付「加護病房或燒燙傷病房保險金」。  
+同一保單年度內，同一次住院的加護病房及燒燙傷病房住院日數合計給付最高以365日為限。同一日內，保險公司僅就加護病房或燒燙傷病房其中一種病房給付。
+條文依據：  
+- [第十三條 加護病房或燒燙傷病房保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 加護病房或燒燙傷病房保險金的給付 | payout_items | 第二十三條 醫療保險金的申領 | 第五條 保險範圍 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr"/>
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr"/>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J88" s="3" t="n"/>
+      <c r="K88" s="3" t="n"/>
+      <c r="L88" s="3" t="n"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:01:43</t>
+        </is>
+      </c>
+      <c r="N88" s="3" t="n">
+        <v>6.42</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>醫療保險金給付總額之上限</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+醫療保險金給付總額之上限為保險單上所記載之「住院醫療保險金日額」的二千五百倍，且僅限於本契約有效期間內依第十二條至第十三條所給付之各項保險金的累計總額。
+條文依據：  
+- [第十四條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 醫療保險金給付總額之上限 | 第十二條 住院醫療保險金的給付 | 第五條 保險範圍 | 第十三條 加護病房或燒燙傷病房保險金的給付 | payout_items</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr"/>
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr"/>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J89" s="3" t="n"/>
+      <c r="K89" s="3" t="n"/>
+      <c r="L89" s="3" t="n"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:01:46</t>
+        </is>
+      </c>
+      <c r="N89" s="3" t="n">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>祝壽保險金的給付規定為何?</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+祝壽保險金的給付規定為：被保險人於本契約有效期間且保險年齡到達九十九歲之保險單週年日仍生存時，本公司按「當年度保險金額」給付「祝壽保險金」。
+條文依據：  
+- [第十五條 祝壽保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>第十五條 祝壽保險金的給付 | 第十二條至第十三條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | 第二十四條 祝壽保險金的申領 | payout_items | 第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr"/>
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr"/>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J90" s="3" t="n"/>
+      <c r="K90" s="3" t="n"/>
+      <c r="L90" s="3" t="n"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:01:49</t>
+        </is>
+      </c>
+      <c r="N90" s="3" t="n">
+        <v>2.66</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>有效期間內身故，保險金如何給付?</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於本契約有效期間內身故者，本公司按「當年度保險金額」給付「身故保險金」。若被保險人於繳費期間內身故，當期已繳付之未到期保險費將不予退還，亦不併入身故保險金內給付。若被保險人於有效期間且實際年齡未滿十五足歲身故者，本公司按「所繳保險費」退還要保人，不適用前述約定。此外，若被保險人為受監護宣告尚未撤銷者，其身故保險金變更為喪葬費用保險金，並受相關限額規定約束。  
+條文依據：  
+- [第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付 | 第十條 契約的終止（二） | 第五條 保險範圍 | 第二十二條 失蹤處理 | 第十五條 祝壽保險金的給付</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr"/>
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr"/>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J91" s="3" t="n"/>
+      <c r="K91" s="3" t="n"/>
+      <c r="L91" s="3" t="n"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:01:54</t>
+        </is>
+      </c>
+      <c r="N91" s="3" t="n">
+        <v>4.78</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>健康促進保險費折減規定</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+健康促進保險費折減規定如下：  
+1. 被保險人需年滿20歲（含）以上，並使用保險公司指定程式加入健康計劃。  
+2. 若於「指定日期」的會員等級符合進階會員或菁英會員（或更高等級），次一保險單年度的保險費可分別折減2%或3%。  
+3. 折減僅適用於主契約保險費，不包含附約、附加條款及批註條款。  
+4. 豁免或復效的保險費不適用折減規定。  
+5. 被保險人需完成程式註冊並授權保險公司取得健康相關電子紀錄，保險公司將依紀錄計算會員等級。
+條文依據：  
+- [第十七條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>第十七條 健康促進保險費折減 | 第二十八條 住院醫療保險金日額之減少 | 第三十條 投保年齡的計算及錯誤的處理 | 第二條 名詞定義 | 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr"/>
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr"/>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J92" s="3" t="n"/>
+      <c r="K92" s="3" t="n"/>
+      <c r="L92" s="3" t="n"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:02:07</t>
+        </is>
+      </c>
+      <c r="N92" s="3" t="n">
+        <v>12.97</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>除外責任的解釋?</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+除外責任是指保險公司不負給付保險金責任的情形。根據條款，以下為主要除外責任的範圍：  
+1. 因被保險人故意行為（如自殺、自殺未遂）、犯罪行為或非法施用毒品所致的疾病或傷害。  
+2. 因美容手術或外科整型住院，但若為重建基本功能所需的整型則不在此限。  
+3. 因健康檢查、療養、靜養、戒毒、戒酒、護理或養老等非直接診治病人目的的住院。  
+4. 因懷孕、流產或分娩及其併發症住院，但若符合特定醫療行為必要的情形（如子宮外孕、葡萄胎、胎盤早期剝離等）則不在此限。  
+5. 因不孕症、人工受孕或非治療目的的避孕及絕育手術住院。  
+條文依據：  
+- [第十八條 除外責任（一)]  
+- [第十九條 除外責任（二)]</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第十九條 除外責任（二） | 第八條 告知義務與本契約的解除 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr"/>
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr"/>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J93" s="3" t="n"/>
+      <c r="K93" s="3" t="n"/>
+      <c r="L93" s="3" t="n"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:02:13</t>
+        </is>
+      </c>
+      <c r="N93" s="3" t="n">
+        <v>6.49</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>哪些疾病被含在除外責任?</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+以下疾病被列為除外責任，保險公司不負給付第十二條至第十三條保險金的責任：  
+1. 美容手術、外科整型（但為重建基本功能所作之必要整型不在此限）。  
+2. 外觀可見之天生畸形。  
+3. 健康檢查、療養、靜養、戒毒、戒酒、護理或養老之非以直接診治病人為目的者。  
+4. 懷孕、流產或分娩及其併發症（但特定懷孕相關疾病、醫療行為必要之流產及剖腹產不在此限）。  
+5. 不孕症、人工受孕或非以治療為目的之避孕及絕育手術。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第二條 名詞定義 | 第十九條 除外責任（二）</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr"/>
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr"/>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J94" s="3" t="n"/>
+      <c r="K94" s="3" t="n"/>
+      <c r="L94" s="3" t="n"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:02:17</t>
+        </is>
+      </c>
+      <c r="N94" s="3" t="n">
+        <v>3.53</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>進行美容手術住院可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，因美容手術住院診療者，本公司不負給付保險金的責任。但若美容手術是為重建基本功能所作之必要整型，則不在此限，可以申請理賠。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第十三條 加護病房或燒燙傷病房保險金的給付 | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第二條 名詞定義 | payout_items</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr"/>
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr"/>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J95" s="3" t="n"/>
+      <c r="K95" s="3" t="n"/>
+      <c r="L95" s="3" t="n"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:02:20</t>
+        </is>
+      </c>
+      <c r="N95" s="3" t="n">
+        <v>3.54</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>因胎兒染色體異常進行手術而住院可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以申請理賠。根據條款，懷孕相關疾病中「胎兒染色體異常之手術」屬於例外情形，不在除外責任範圍內，因此符合理賠條件。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第二條 名詞定義 | payout_items | 第十三條 加護病房或燒燙傷病房保險金的給付</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr"/>
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr"/>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J96" s="3" t="n"/>
+      <c r="K96" s="3" t="n"/>
+      <c r="L96" s="3" t="n"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:02:23</t>
+        </is>
+      </c>
+      <c r="N96" s="3" t="n">
+        <v>2.51</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>因胎位不正進行手術而住院可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，因懷孕、流產或分娩及其併發症住院診療，本公司不負給付保險金的責任。然而，若因胎位不正進行手術屬於醫療行為必要之剖腹產，則不在此限，符合理賠條件。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第二條 名詞定義 | payout_items | 第十三條 加護病房或燒燙傷病房保險金的給付</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr"/>
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr"/>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J97" s="3" t="n"/>
+      <c r="K97" s="3" t="n"/>
+      <c r="L97" s="3" t="n"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:02:26</t>
+        </is>
+      </c>
+      <c r="N97" s="3" t="n">
+        <v>3.02</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>因自殺未遂導致住院可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，因被保險人故意行為（包括自殺及自殺未遂）導致住院診療者，本公司不負給付住院醫療保險金的責任。  
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 除外責任（二） | 第十八條 除外責任（一） | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | payout_items | 第十條 契約的終止（二）</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr"/>
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr"/>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J98" s="3" t="n"/>
+      <c r="K98" s="3" t="n"/>
+      <c r="L98" s="3" t="n"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:02:29</t>
+        </is>
+      </c>
+      <c r="N98" s="3" t="n">
+        <v>2.72</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>被保險人在投保一年內故意自殺者，可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人在投保一年內故意自殺者，依條款規定，本公司不負給付身故保險金或喪葬費用保險金的責任。但若故意自殺發生於契約訂立或復效之日起二年後，本公司仍負給付責任。
+條文依據：  
+- [第十九條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 除外責任（二） | 第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付 | 第十條 契約的終止（二） | 第三十條 投保年齡的計算及錯誤的處理 | 第十八條 除外責任（一）</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr"/>
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr"/>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J99" s="3" t="n"/>
+      <c r="K99" s="3" t="n"/>
+      <c r="L99" s="3" t="n"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:02:32</t>
+        </is>
+      </c>
+      <c r="N99" s="3" t="n">
+        <v>3.14</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>申請理賠有什麼時間規定嗎?</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申請理賠的時間規定如下：要保人、被保險人或受益人應於知悉本公司應負保險責任之事故後十日內通知本公司，並於通知後儘速檢具所需文件向本公司申請給付保險金。本公司應於收齊所需文件後十五日內完成給付。但若因可歸責於本公司之事由導致未在約定期限內給付者，應按年利一分加計利息給付。
+條文依據：  
+- [第二十一條 保險事故的通知與保險金的申請時間]</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>第二十一條 保險事故的通知與保險金的申請時間 | 第六條 第二期以後保險費的交付、寬限期間及契約效力的停止 | 第七條 本契約效力的恢復 | 第三條 契約撤銷權 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr"/>
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr"/>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J100" s="3" t="n"/>
+      <c r="K100" s="3" t="n"/>
+      <c r="L100" s="3" t="n"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:02:35</t>
+        </is>
+      </c>
+      <c r="N100" s="3" t="n">
+        <v>3.03</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>燒燙傷病房保險金怎麼申領?</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申領燒燙傷病房保險金時，受益人需依約定檢具以下文件：保險單或其謄本、保險金申請書、醫療診斷書或住院證明（需列明進出燒燙傷病房日期，且要保人或被保險人若為醫師，不得自行出具診斷書或住院證明）、受益人的身分證明。本公司可徵詢其他醫師的醫學專業意見並調閱被保險人就醫相關資料，相關費用由本公司負擔。
+條文依據：  
+- [第二十三條 醫療保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>第二十三條 醫療保險金的申領 | 第十三條 加護病房或燒燙傷病房保險金的給付 | payout_items | 第二條 名詞定義 | 第二十一條 保險事故的通知與保險金的申請時間</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr"/>
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr"/>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J101" s="3" t="n"/>
+      <c r="K101" s="3" t="n"/>
+      <c r="L101" s="3" t="n"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:02:40</t>
+        </is>
+      </c>
+      <c r="N101" s="3" t="n">
+        <v>4.67</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>活到99歲怎麼申請祝壽金?</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申請祝壽保險金時，受益人需檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 受益人的身分證明。  
+條文依據：  
+- [第二十四條 祝壽保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>第十五條 祝壽保險金的給付 | 第二十四條 祝壽保險金的申領 | 第五條 保險範圍 | 第十二條至第十三條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | announcement_history</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr"/>
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr"/>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J102" s="3" t="n"/>
+      <c r="K102" s="3" t="n"/>
+      <c r="L102" s="3" t="n"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:02:42</t>
+        </is>
+      </c>
+      <c r="N102" s="3" t="n">
+        <v>2.66</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>被保人身故怎麼申請理賠</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+受益人申請「身故保險金」或「喪葬費用保險金」時，需檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 被保險人死亡證明書及除戶戶籍謄本。  
+4. 受益人的身分證明。  
+條文依據：  
+- [第二十五條 身故保險金或喪葬費用保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付 | 第十二條至第十三條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | 第二十二條 失蹤處理 | 第二十五條 身故保險金或喪葬費用保險金的申領 | 第十九條 除外責任（二）</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr"/>
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr"/>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J103" s="3" t="n"/>
+      <c r="K103" s="3" t="n"/>
+      <c r="L103" s="3" t="n"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:02:44</t>
+        </is>
+      </c>
+      <c r="N103" s="3" t="n">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>投保15年後，因手術住院3天，住院日額為2500元，請問可以申請多少理賠?</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+依據條款，被保險人因手術住院3天，可申請住院醫療保險金。理賠金額計算方式為「住院醫療保險金日額」乘以「增額係數」再乘以住院日數。假設增額係數為1（未提供具體增額係數），則理賠金額為：2500元 × 1 × 3天 = 7500元。
+條文依據：  
+- [第十二條 住院醫療保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 住院醫療保險金的給付 | 第十三條 加護病房或燒燙傷病房保險金的給付 | 第二十八條 住院醫療保險金日額之減少 | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | payout_items | 第五條 保險範圍 | 第二條 名詞定義 | 第二十一條 保險事故的通知與保險金的申請時間</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr"/>
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr"/>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J104" s="3" t="n"/>
+      <c r="K104" s="3" t="n"/>
+      <c r="L104" s="3" t="n"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:02:51</t>
+        </is>
+      </c>
+      <c r="N104" s="3" t="n">
+        <v>4.77</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>保障範圍包括哪些項目？</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括：住院手術醫療保險金、門診手術醫療保險金、特定處置保險金、意外創傷縫合處置保險金、意外住院手術醫療保險金、祝壽保險金、所繳保險費的退還、身故保險金或喪葬費用保險金。
+條文依據：  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>payout_items | 第五條 保險範圍 | summary | 第四條 名詞定義 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr"/>
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr"/>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J105" s="3" t="n"/>
+      <c r="K105" s="3" t="n"/>
+      <c r="L105" s="3" t="n"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:02:55</t>
+        </is>
+      </c>
+      <c r="N105" s="3" t="n">
+        <v>3.98</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>保險金額是否有上限?</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+有，保險金額的累計給付總額上限為保險單上所記載「保險金額」的一千五百倍，且不包含其他附約、附加條款或批註條款。
+條文依據：  
+- [第十六條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 醫療保險金給付總額之上限 | 第三十條 保險金額之減少 | 第五條 保險範圍 | 第十九條 健康促進保險費折減 | 第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr"/>
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr"/>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J106" s="3" t="n"/>
+      <c r="K106" s="3" t="n"/>
+      <c r="L106" s="3" t="n"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:03:00</t>
+        </is>
+      </c>
+      <c r="N106" s="3" t="n">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>投保後5天發生手術，是否可以申請理賠?</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款內容，是否可以申請理賠需視保險契約中是否有等待期間的規定。然而，提供的條款中未提及等待期間的相關規定，因此無法判斷投保後5天是否符合理賠條件。
+條文依據：  
+找不到相關內容</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第十一條 住院手術醫療保險金 | 第二十條 除外責任（一） | 第十二條 門診手術醫療保險金 | 第十三條 意外住院手術醫療保險金 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr"/>
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr"/>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J107" s="3" t="n"/>
+      <c r="K107" s="3" t="n"/>
+      <c r="L107" s="3" t="n"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:03:03</t>
+        </is>
+      </c>
+      <c r="N107" s="3" t="n">
+        <v>3.14</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>住院手術醫療保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院手術醫療保險金的給付規定如下：  
+1. 被保險人於契約有效期間內因疾病或傷害，經醫師診斷必須住院接受附表一所列的手術治療且已實際接受手術者，本公司依保險單記載的「保險金額」乘以手術日當年度的「增額係數」，再乘以手術給付倍數，給付住院手術醫療保險金。  
+2. 同一次手術中，若於同一手術位置接受二項以上手術項目，僅給付手術給付倍數最高的手術項目。  
+3. 未載明於附表一的手術項目，將與被保險人協議比照附表一內程度相當的手術項目，決定給付倍數。  
+4. 以下情形不負給付責任：  
+   - 依據除外責任條款規定不在給付範圍內。  
+   - 不屬全民健康保險醫療服務給付項目及支付標準第二部第二章第七節或第三部第三章第四節第三項所列舉的手術。  
+條文依據：  
+- [第十一條 住院手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 住院手術醫療保險金 | 第十三條 意外住院手術醫療保險金 | 第十二條 門診手術醫療保險金 | payout_items | 第二十條 除外責任（一） | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr"/>
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr"/>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J108" s="3" t="n"/>
+      <c r="K108" s="3" t="n"/>
+      <c r="L108" s="3" t="n"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:03:09</t>
+        </is>
+      </c>
+      <c r="N108" s="3" t="n">
+        <v>5.31</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>門診手術醫療保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+門診手術醫療保險金的給付規定如下：  
+1. 被保險人因疾病或傷害，經醫師診斷必須於醫院或診所門診接受附表一的手術治療且已實際接受手術者，本公司依保險單所記載之「保險金額」乘以手術日當年度之「增額係數」，再乘以手術給付倍數，給付「門診手術醫療保險金」。  
+2. 同一次手術中，若於同一手術位置接受二項以上手術項目，僅給付手術給付倍數最高的手術項目。  
+3. 同一保險單年度內，門診手術醫療保險金的給付以十次為限。  
+4. 未載明於附表一所列的手術項目，將與被保險人協議比照該表內手術項目決定給付倍數。  
+5. 以下情形不負給付責任：  
+   - 依據本契約除外責任條款的規定不在給付範圍內。  
+   - 不屬全民健康保險醫療服務給付項目及支付標準第二部第二章第七節或第三部第三章第四節第三項所列舉的手術。  
+條文依據：  
+- [第十二條 門診手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 門診手術醫療保險金 | 第十一條 住院手術醫療保險金 | payout_items | 第十三條 意外住院手術醫療保險金 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr"/>
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr"/>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J109" s="3" t="n"/>
+      <c r="K109" s="3" t="n"/>
+      <c r="L109" s="3" t="n"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:03:12</t>
+        </is>
+      </c>
+      <c r="N109" s="3" t="n">
+        <v>3.81</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>意外住院手術醫療保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外住院手術醫療保險金的給付規定如下：  
+1. 被保險人於契約有效期間內且保險年齡未滿七十歲，因傷害經醫師診斷在住院期間必須接受手術治療且已接受手術者，保險公司按保險單所記載之「保險金額」的三倍，乘以手術日當年度之「增額係數」，給付「意外住院手術醫療保險金」。  
+2. 若被保險人在同一次手術中於同一手術位置接受二項以上手術項目，僅給付一次「意外住院手術醫療保險金」。
+條文依據：  
+- [第十三條 意外住院手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 意外住院手術醫療保險金 | 第十一條 住院手術醫療保險金 | 第十五條 意外創傷縫合處置保險金 | 第二十條 除外責任（一） | 第十二條 門診手術醫療保險金 | 附表三：意外創傷縫合處置項目及給付倍數表 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr"/>
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr"/>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J110" s="3" t="n"/>
+      <c r="K110" s="3" t="n"/>
+      <c r="L110" s="3" t="n"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:03:16</t>
+        </is>
+      </c>
+      <c r="N110" s="3" t="n">
+        <v>3.74</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>特定處置保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+特定處置保險金的給付規定如下：  
+1. 被保險人因疾病或傷害，經醫師診斷必須於醫院或診所接受附表二所列之特定處置治療且已接受處置者，保險公司將依保險單記載的「保險金額」，乘以特定處置日當年度的「增額係數」，再乘以特定處置給付倍數，給付「特定處置保險金」。  
+2. 同一次處置治療中，若於同一治療位置接受二項以上特定處置項目，僅給付特定處置給付倍數最高的特定處置項目。  
+3. 若被保險人所接受的處置未載明於附表二所列之特定處置項目，保險公司不負給付特定處置保險金的責任。  
+4. 同一保險單年度的「特定處置保險金」給付次數以十次為限。
+條文依據：  
+- [第十四條 特定處置保險金]</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 特定處置保險金 | 第十五條 意外創傷縫合處置保險金 | 附表二：特定處置項目及給付倍數表 | 第五條 保險範圍 | 附表三：意外創傷縫合處置項目及給付倍數表</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr"/>
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr"/>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J111" s="3" t="n"/>
+      <c r="K111" s="3" t="n"/>
+      <c r="L111" s="3" t="n"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:03:20</t>
+        </is>
+      </c>
+      <c r="N111" s="3" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>意外創傷縫合處置保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外創傷縫合處置保險金的給付規定如下：  
+1. 被保險人因意外傷害事故，於醫院或診所接受附表三所列的意外創傷縫合處置治療者，本公司將依保險單所記載的「保險金額」，乘以當年度的「增額係數」，再乘以意外創傷縫合處置給付倍數，給付保險金。  
+2. 同一次意外傷害事故，僅就傷口最大者給付保險金，且以給付一次為限。  
+3. 若被保險人因同一意外傷害事故，已申領住院手術醫療保險金或門診手術醫療保險金者，則不再給付意外創傷縫合處置保險金。
+條文依據：  
+- [第十五條 意外創傷縫合處置保險金]</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>第十五條 意外創傷縫合處置保險金 | 附表三：意外創傷縫合處置項目及給付倍數表 | 第十四條 特定處置保險金 | 第二十條 除外責任（一） | 第十三條 意外住院手術醫療保險金 | 附表二：特定處置項目及給付倍數表</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr"/>
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr"/>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J112" s="3" t="n"/>
+      <c r="K112" s="3" t="n"/>
+      <c r="L112" s="3" t="n"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:03:23</t>
+        </is>
+      </c>
+      <c r="N112" s="3" t="n">
+        <v>3.13</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>醫療保險金給付總額之上限</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+醫療保險金給付總額之上限為保險單上所記載的「保險金額」之一千五百倍，且不包含其他附約、附加條款及批註條款。
+條文依據：  
+- [第十六條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 醫療保險金給付總額之上限 | 第十二條 門診手術醫療保險金 | 第五條 保險範圍 | 第十一條 住院手術醫療保險金 | 第十三條 意外住院手術醫療保險金 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr"/>
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr"/>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J113" s="3" t="n"/>
+      <c r="K113" s="3" t="n"/>
+      <c r="L113" s="3" t="n"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:03:27</t>
+        </is>
+      </c>
+      <c r="N113" s="3" t="n">
+        <v>3.23</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>祝壽保險金的領取規定為何?</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+祝壽保險金的領取規定如下：  
+1. 被保險人需於本契約有效期間且保險年齡到達九十九歲之保險單週年日仍生存，方可申領祝壽保險金。  
+2. 受益人申領祝壽保險金時，需檢具以下文件：  
+   - 保險單或其謄本  
+   - 保險金申請書  
+   - 受益人的身分證明  
+條文依據：  
+- [第十七條 祝壽保險金]  
+- [第二十六條 祝壽保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>第十七條 祝壽保險金 | 第二十六條 祝壽保險金的申領 | 第十一條至第十五條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | 第二十三條 保險事故的通知與保險金的申請時間 | 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr"/>
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr"/>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J114" s="3" t="n"/>
+      <c r="K114" s="3" t="n"/>
+      <c r="L114" s="3" t="n"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:03:29</t>
+        </is>
+      </c>
+      <c r="N114" s="3" t="n">
+        <v>2.74</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>身故時領取保險金有什麼規則?</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+身故時領取保險金的規則如下：  
+1. 被保險人於契約有效期間內身故者，本公司按「當年度保險金額」給付「身故保險金」。  
+2. 若被保險人身故時實際年齡未滿十五足歲，本公司退還「所繳保險費」予要保人，不適用「當年度保險金額」的約定。  
+3. 若被保險人於訂立契約時受監護宣告尚未撤銷，其身故保險金改為喪葬費用保險金，且喪葬費用保險金額不得超過遺產稅喪葬費扣除額之半數，超過部分不負給付責任。  
+4. 受益人申領身故保險金或喪葬費用保險金時，需提供保險單、死亡證明書及除戶戶籍謄本、保險金申請書及受益人身分證明等文件。  
+條文依據：  
+- [第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金]  
+- [第二十七條 身故保險金或喪葬費用保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金 | 第二十七條 身故保險金或喪葬費用保險金的申領 | 第十一條至第十五條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | 第二十一條 除外責任（二） | 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr"/>
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr"/>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J115" s="3" t="n"/>
+      <c r="K115" s="3" t="n"/>
+      <c r="L115" s="3" t="n"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:03:35</t>
+        </is>
+      </c>
+      <c r="N115" s="3" t="n">
+        <v>5.76</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>什麼情況下可以保費折減?</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人年齡滿20歲（含）以上，並使用保險公司指定程式加入健康計劃，於「指定日期」的會員等級符合進階會員或菁英會員（或更高等級）標準者，可享次一保險單年度的保費折減。折減比例為進階會員2%，菁英會員或更高等級3%。但豁免或復效的保險費不適用此折減約定。
+條文依據：  
+- [第十九條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 健康促進保險費折減 | 第三十條 保險金額之減少 | 第二十條 除外責任（一） | 第三十一條 投保年齡的計算及錯誤的處理 | 第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr"/>
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr"/>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J116" s="3" t="n"/>
+      <c r="K116" s="3" t="n"/>
+      <c r="L116" s="3" t="n"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:03:39</t>
+        </is>
+      </c>
+      <c r="N116" s="3" t="n">
+        <v>3.67</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>角膜切除術是否可以申請理賠?</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+角膜切除術可以申請理賠，其手術項目編號為1305，給付倍數為5。  
+條文依據：  
+- 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr"/>
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr"/>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J117" s="3" t="n"/>
+      <c r="K117" s="3" t="n"/>
+      <c r="L117" s="3" t="n"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:03:41</t>
+        </is>
+      </c>
+      <c r="N117" s="3" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>白內障手術是否可以申請理賠?</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+白內障手術是否可以申請理賠需視手術是否符合附表一所列的手術項目及給付倍數。如果白內障手術屬於附表一中所列的手術項目，例如「晶體切除術合併玻璃體切除術」（項目編號1367，給付倍數30），則可申請理賠。若手術未列於附表一，則需與保險公司協議比照附表一內的手術項目決定給付倍數。此外，若手術屬於除外責任條款所列的情形，則不予理賠。
+條文依據：  
+- [第十二條 門診手術醫療保險金]  
+- [附表一：手術項目與給付倍數]  
+- [第二十條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 門診手術醫療保險金 | 第二十條 除外責任（一） | 附表一：手術項目與給付倍數 | payout_items | 第十一條 住院手術醫療保險金</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr"/>
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr"/>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J118" s="3" t="n"/>
+      <c r="K118" s="3" t="n"/>
+      <c r="L118" s="3" t="n"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:03:45</t>
+        </is>
+      </c>
+      <c r="N118" s="3" t="n">
+        <v>4.05</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>保障範圍包括哪些項目？</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括：意外事故身故保險金或喪葬費用保險金、意外事故失能保險金、每月生活照護保險金、重大燒燙傷保險金、意外骨折保險金、傷害醫療日額保險金、意外創傷縫合處置保險金。
+條文依據：  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>payout_items | 第五條 保險範圍 | 第十五條 每月生活照護保險金的給付 | 第三十條 不保事項 | 附表二：失能程度與保險金給付表</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr"/>
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr"/>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J119" s="3" t="n"/>
+      <c r="K119" s="3" t="n"/>
+      <c r="L119" s="3" t="n"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:03:48</t>
+        </is>
+      </c>
+      <c r="N119" s="3" t="n">
+        <v>2.52</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>發生意外事故身故，理賠內容為何?</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外事故身故的理賠內容包括「意外事故身故保險金」或「喪葬費用保險金」，依意外傷害事故的種類給付以下金額：  
+1. 一般意外傷害事故：「傷害醫療保險金日額」的五百倍。  
+2. 特定意外傷害事故：「傷害醫療保險金日額」的一千倍。  
+若被保險人於意外傷害事故發生後超過一百八十日身故，但受益人能證明身故與該事故具有因果關係，本公司仍依上述約定給付保險金，不受一百八十日限制。此外，若被保險人受監護宣告尚未撤銷，其理賠內容變更為「喪葬費用保險金」，且喪葬費用保險金額不得超過遺產稅喪葬費扣除額之半數，超過部分不負給付責任。  
+條文依據：  
+- [第十二條 意外事故身故保險金或喪葬費用保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 意外事故身故保險金或喪葬費用保險金的給付 | 第十四條 保險給付的限制 | payout_items | 第十一條 契約的終止（二） | 第二十一條 失蹤處理</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr"/>
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr"/>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J120" s="3" t="n"/>
+      <c r="K120" s="3" t="n"/>
+      <c r="L120" s="3" t="n"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:03:55</t>
+        </is>
+      </c>
+      <c r="N120" s="3" t="n">
+        <v>7.63</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>意外事故失能保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外事故失能保險金的給付條件如下：  
+1. 被保險人於契約有效期間內遭受意外傷害事故，並於事故發生後180日內致成附表二所列失能程度之一者，本公司依意外事故種類及失能程度，按以下約定金額給付：  
+   - 一般意外傷害事故：傷害醫療保險金日額的500倍乘以附表二給付比例。  
+   - 特定意外傷害事故：傷害醫療保險金日額的1000倍乘以附表二給付比例。  
+2. 若被保險人超過180日後致成失能，受益人能證明失能與事故具有因果關係者，本公司仍依上述規定給付，不受180日限制。  
+3. 同一事故致成多項失能時，僅給付同一手或足中較嚴重失能項目之保險金；不同事故累計給付金額以契約規定的上限為限。  
+4. 若合併以前失能，僅給付較嚴重項目之保險金，但以前失能視同已給付，應扣除之。  
+條文依據：  
+- [第十三條 意外事故失能保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 意外事故失能保險金的給付 | 第十五條 每月生活照護保險金的給付 | 第十四條 保險給付的限制 | 第十二條 意外事故身故保險金或喪葬費用保險金的給付 | 第二十三條 意外事故失能保險金的申領 | 附表二：失能程度與保險金給付表</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr"/>
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr"/>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J121" s="3" t="n"/>
+      <c r="K121" s="3" t="n"/>
+      <c r="L121" s="3" t="n"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:04:02</t>
+        </is>
+      </c>
+      <c r="N121" s="3" t="n">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>每月生活照護保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+每月生活照護保險金的給付條件如下：  
+1. 被保險人於契約有效期間內遭受意外傷害事故，並於事故發生後180日內致成附表二所列第一級至第六級失能程度之一時，本公司自失能診斷確定當日起，按「傷害醫療保險金日額」的20倍乘以附表二給付比例所得之金額，按月給付，以12個月為限。  
+2. 若失能診斷確定後的前四個週年日，被保險人仍生存且契約有效，本公司自各該週年日起，依相同方式按月給付，以12個月為限。  
+3. 若被保險人於事故發生後超過180日致成失能，受益人能證明失能與事故具有因果關係者，本公司仍依上述規定給付，不受180日限制。  
+4. 同一事故若致成多項失能，僅給付較嚴重項目，且最高以「傷害醫療保險金日額」的20倍為限。  
+5. 累計給付金額最高以「傷害醫療保險金日額」的1200倍為限。  
+條文依據：  
+- [第十五條 每月生活照護保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>第二十四條 每月生活照護保險金的申領 | 第十五條 每月生活照護保險金的給付 | payout_items | 第十八條 傷害醫療日額保險金的給付 | 第五條 保險範圍 | 附表二：失能程度與保險金給付表 | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr"/>
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr"/>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J122" s="3" t="n"/>
+      <c r="K122" s="3" t="n"/>
+      <c r="L122" s="3" t="n"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:04:12</t>
+        </is>
+      </c>
+      <c r="N122" s="3" t="n">
+        <v>9.619999999999999</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>重大燒燙傷保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+重大燒燙傷保險金的給付條件為：被保險人於本契約有效期間內遭受「意外傷害事故」，蒙受燒燙傷之傷害，經診斷符合「重大燒燙傷」者，本公司按「傷害醫療保險金日額」的二百五十倍給付「重大燒燙傷保險金」。此保險金的給付以一次為限。
+條文依據：  
+- [第十六條 重大燒燙傷保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 重大燒燙傷保險金的給付 | 第二十五條 重大燒燙傷保險金的申領 | 第五條 保險範圍 | payout_items | 第二十九條 除外責任（原因）</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr"/>
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr"/>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J123" s="3" t="n"/>
+      <c r="K123" s="3" t="n"/>
+      <c r="L123" s="3" t="n"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:04:15</t>
+        </is>
+      </c>
+      <c r="N123" s="3" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>意外骨折保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外骨折保險金的給付條件如下：  
+1. 被保險人於契約有效期間內遭受「意外傷害事故」，自事故發生日起一百八十日內，經合格醫院或診所診斷為附表三骨折別表所列骨折項目之一（含不完全骨折及骨骼龜裂），本公司按「傷害醫療保險金日額」的二倍給付。  
+2. 若超過一百八十日診斷確定骨折，受益人需證明骨折與事故具有因果關係，本公司仍給付保險金，不受一百八十日限制。  
+3. 同一意外傷害事故僅給付一次意外骨折保險金。  
+4. 若骨折非屬附表三骨折別表所列項目，需由本公司與被保險人協議核付；但若骨折部位為骨折別表內明訂不給付之部位，則不負給付責任。
+條文依據：  
+- [第十七條 意外骨折保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>第十七條 意外骨折保險金的給付 | 第十八條 傷害醫療日額保險金的給付 | 第二十六條 意外骨折保險金的申領 | 第十三條 意外事故失能保險金的給付 | 第十九條 意外創傷縫合處置保險金的給付 | 附表二：失能程度與保險金給付表 | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr"/>
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr"/>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J124" s="3" t="n"/>
+      <c r="K124" s="3" t="n"/>
+      <c r="L124" s="3" t="n"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:04:21</t>
+        </is>
+      </c>
+      <c r="N124" s="3" t="n">
+        <v>5.34</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>傷害醫療日額保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+傷害醫療日額保險金的給付條件如下：  
+1. 被保險人於契約有效期間內遭受「意外傷害事故」，自事故發生日起一百八十日內於「醫院」接受住院治療者，本公司按「傷害醫療保險金日額」乘以實際住院日數給付，最高以九十日為限。  
+2. 若治療超過一百八十日，受益人能證明治療與事故具有因果關係者，仍可依規定給付，不受一百八十日限制。  
+3. 若因骨折未住院或住院日數未達附表三骨折別表所訂日數，未住院部分按骨折別表所訂日數乘以「傷害醫療保險金日額」的二分之一給付，合計給付日數以骨折別表所訂日數為上限。  
+4. 骨折給付依骨骼損傷程度分為完全骨折、不完全骨折及骨骼龜裂，分別按完全骨折日數的二分之一及四分之一給付。若同時有多項骨折，僅給付較高等級的保險金。
+條文依據：  
+- [第十八條 傷害醫療日額保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 傷害醫療日額保險金的給付 | 第二十七條 傷害醫療日額保險金的申領 | 第十五條 每月生活照護保險金的給付 | 第三十四條 傷害醫療保險金日額之減少 | 第十九條 意外創傷縫合處置保險金的給付 | 附表二：失能程度與保險金給付表 | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr"/>
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr"/>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J125" s="3" t="n"/>
+      <c r="K125" s="3" t="n"/>
+      <c r="L125" s="3" t="n"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:04:28</t>
+        </is>
+      </c>
+      <c r="N125" s="3" t="n">
+        <v>7.41</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>意外創傷縫合處置保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外創傷縫合處置保險金的給付條件為：被保險人於契約有效期間內遭受「意外傷害事故」，並於「醫院」或「診所」經醫師診斷必須接受創傷縫合處置治療且已接受縫合處置者，本公司按「傷害醫療保險金日額」給付該保險金。同一意外傷害事故僅給付一次。
+條文依據：  
+- [第十九條 意外創傷縫合處置保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 意外創傷縫合處置保險金的給付 | 第二十八條 意外創傷縫合處置保險金的申領 | 第五條 保險範圍 | 第十七條 意外骨折保險金的給付 | payout_items | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr"/>
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr"/>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J126" s="3" t="n"/>
+      <c r="K126" s="3" t="n"/>
+      <c r="L126" s="3" t="n"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:04:32</t>
+        </is>
+      </c>
+      <c r="N126" s="3" t="n">
+        <v>3.71</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>因意外導致視力衰退，是否能申請理賠?</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+因意外導致視力衰退是否能申請理賠，需符合以下條件：  
+1. 視力永久在萬國式視力表0.02以下，或眼球喪失、摘出、僅能辨明暗或辨眼前一公尺以內手動或辨眼前五公分以內指數者。  
+2. 以自傷害之日起經過六個月的治療為判定原則，但若屬眼球摘出等明顯無法復原的情況，則不受六個月治療期間的限制。  
+若符合上述條件，則可申請理賠。  
+條文依據：  
+- 註2</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>第二十三條 意外事故失能保險金的申領 | 第十三條 意外事故失能保險金的給付 | 註2： | 第三十條 不保事項 | 第二十六條 意外骨折保險金的申領 | 附表二：失能程度與保險金給付表</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr"/>
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr"/>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J127" s="3" t="n"/>
+      <c r="K127" s="3" t="n"/>
+      <c r="L127" s="3" t="n"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:04:36</t>
+        </is>
+      </c>
+      <c r="N127" s="3" t="n">
+        <v>3.74</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>肋骨骨折是否可以申請理賠?理賠金額為多少?</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+肋骨骨折可以申請理賠，理賠金額需依肋骨骨折的情形判定：  
+1. 若肋骨完全骨折且未住院治療，依附表三骨折別表所訂日數（20天）乘以「傷害醫療保險金日額」的二分之一給付。  
+2. 若肋骨完全骨折且住院治療，依實際住院日數乘以「傷害醫療保險金日額」給付，但最高以附表三骨折別表所訂日數（20天）為上限。  
+3. 若肋骨不完全骨折，按完全骨折日數（20天）的二分之一給付；若肋骨龜裂，按完全骨折日數的四分之一給付。  
+條文依據：  
+- [第十八條 傷害醫療日額保險金的給付]  
+- [附表三：骨折別表]</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 傷害醫療日額保險金的給付 | 第十七條 意外骨折保險金的給付 | 第二十六條 意外骨折保險金的申領 | 第三十條 不保事項 | 第五條 保險範圍 | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr"/>
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr"/>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J128" s="3" t="n"/>
+      <c r="K128" s="3" t="n"/>
+      <c r="L128" s="3" t="n"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:04:41</t>
+        </is>
+      </c>
+      <c r="N128" s="3" t="n">
+        <v>5.07</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>投保新鍾心滿福後，假設投保保額為100萬元，於第二保單年度接受「移植器官」，這樣可以領多少保險金?</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人於第二保險單年度（含）以後的有效期間內，初次診斷確定罹患「特定重大傷病」並接受「移植器官」，可獲得「重大傷病保險金」及額外的「特定重大傷病保險金」。其中，「特定重大傷病保險金」的給付金額為保險金額的20%，即100萬元的20%，為20萬元。重大傷病保險金的具體金額則需依保險契約中其他相關條款計算。
+條文依據：  
+- [第十三條 特定重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>第十五條 滿期保險金的給付 | 第二條 名詞定義 | 附表一：全民健康保險重大傷病項目 | 第十三條 特定重大傷病保險金的給付 | 附表三：各保險單年度可借金額上限表 | payout_items | 第十七條 完全失能保險金的給付 | 附表二：完全失能程度表</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr"/>
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr"/>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J129" s="3" t="n"/>
+      <c r="K129" s="3" t="n"/>
+      <c r="L129" s="3" t="n"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:04:47</t>
+        </is>
+      </c>
+      <c r="N129" s="3" t="n">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>投保新鍾心滿福後，若要理賠重大傷病保險金，一定要檢附全民健保開立的重大傷病證明才能拿到保險金嗎?</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不一定需要檢附全民健保開立的重大傷病證明。若被保險人已取得一家「區域醫院」層級以上（含）之醫療院所開立且符合投保當時「重大傷病範圍」的診斷書及當次「重大傷病」病歷摘要，則可視為重大傷病證明文件，免向全民健康保險保險人申請。此外，若因全民健康保險保險人變更或調整重大傷病項目導致無法取得重大傷病證明文件，或被保險人於重大傷病證明文件核發前身故，也可依條款規定以其他文件替代。  
+條文依據：  
+- [第二十二條 重大傷病保險金、特定重大傷病保險金的申領]  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>第二十二條 重大傷病保險金、特定重大傷病保險金的申領 | other_metadata | 第十二條 重大傷病保險金的給付 | 附表一：全民健康保險重大傷病項目 | 第二條 名詞定義 | 第三十條 不保事項</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr"/>
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr"/>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J130" s="3" t="n"/>
+      <c r="K130" s="3" t="n"/>
+      <c r="L130" s="3" t="n"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:04:53</t>
+        </is>
+      </c>
+      <c r="N130" s="3" t="n">
+        <v>5.48</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>一定要有健保身分才能申請重大傷病理賠嗎？</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，被保險人若喪失全民健康保險被保險人資格，需先申請加保全民健康保險後，才能申領重大傷病保險金。然而，若重大傷病係因意外傷害事故所致，則不受此限制。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>第二十二條 重大傷病保險金、特定重大傷病保險金的申領 | 第十二條 重大傷病保險金的給付 | other_metadata | 第三十條 不保事項 | 第二條 名詞定義 | 附表一：全民健康保險重大傷病項目</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr"/>
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr"/>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J131" s="3" t="n"/>
+      <c r="K131" s="3" t="n"/>
+      <c r="L131" s="3" t="n"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:04:56</t>
+        </is>
+      </c>
+      <c r="N131" s="3" t="n">
+        <v>3.51</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>重大傷病的項目如果在投保後有新增，可以從優申請理賠嗎？</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以申請理賠，但需符合以下條件：重大傷病項目若在投保後新增，理賠範圍以「訂立時」及「有效期間內被保險人診斷確定當時」由中央衛生主管機關公告之重大傷病項目為準。因此，只要新增項目在被保險人診斷確定時已被中央主管機關公告為重大傷病項目，即可申請理賠。
+條文依據：  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>附表一：全民健康保險重大傷病項目 | 第二條 名詞定義 | payout_items</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr"/>
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr"/>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J132" s="3" t="n"/>
+      <c r="K132" s="3" t="n"/>
+      <c r="L132" s="3" t="n"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:05:01</t>
+        </is>
+      </c>
+      <c r="N132" s="3" t="n">
+        <v>4.19</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>我的保單之前有停效，在復效後五天被診斷出重大疾病是否可申請理賠？</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以申請理賠，但需符合以下條件：  
+1. 復效後的契約有效期間內，被保險人經醫院醫師初次診斷確定罹患「重大傷病」。  
+2. 若重大傷病係因意外傷害事故所致，則不受等待期間限制；若非意外傷害事故，則需等待期間屆滿翌日或復效日起才符合理賠條件。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>第八條 本契約效力的恢復 | 第三十條 不保事項 | 第五條 保險範圍 | other_metadata | 第二條 名詞定義 | 第十二條 重大傷病保險金的給付 | 第二十二條 重大傷病保險金、特定重大傷病保險金的申領 | 附表一：全民健康保險重大傷病項目</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr"/>
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr"/>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J133" s="3" t="n"/>
+      <c r="K133" s="3" t="n"/>
+      <c r="L133" s="3" t="n"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:05:04</t>
+        </is>
+      </c>
+      <c r="N133" s="3" t="n">
+        <v>3.31</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>領完重大傷病保險金，主約終止後，附約可以繼續有效嗎?</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以。根據條文規定，若主約因重大傷病診斷確定日而終止時，要保人於附約的有效期間內，仍可繼續繳交附約保險費，以延續附約效力。
+條文依據：  
+- [第十一條 契約的終止（二)]</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 契約的終止（二） | 第十二條 重大傷病保險金的給付 | 第三十條 不保事項 | 第五條 保險範圍 | payout_items | 附表一：全民健康保險重大傷病項目</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr"/>
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr"/>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J134" s="3" t="n"/>
+      <c r="K134" s="3" t="n"/>
+      <c r="L134" s="3" t="n"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:05:07</t>
+        </is>
+      </c>
+      <c r="N134" s="3" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>Q1：因為慢性精神病的保險給付僅有保額的20%，我可以先不申請給付，等之後發生其他重大傷病後，再申請重大傷病保險金嗎?Q2：但如果我不申請，保險公司不會知道我有罹患慢性精神病阿，所以我就可以領之後的重大傷病100%保額嗎?</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+Q1：依據條款，被保險人同時或先後罹患二項以上重大傷病時，保險公司僅給付一項重大傷病保險金。因此，即使您選擇不申請慢性精神病的保險給付，未來若罹患其他重大傷病，保險公司仍僅會給付其中一項的保險金，並依條款規定計算金額。  
+Q2：保險公司是否給付重大傷病保險金，需依條款規定進行審核。若您未申請慢性精神病的保險給付，保險公司可能無法得知您已罹患慢性精神病，但未來若申請其他重大傷病保險金，保險公司仍會依條款進行審核，並可能要求提供相關病歷摘要或診斷書等文件。若審核過程中發現您已罹患慢性精神病，則保險公司仍僅會給付一項重大傷病保險金，並依條款規定計算金額。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 重大傷病保險金的給付 | 第十三條 特定重大傷病保險金的給付 | 第三十條 不保事項 | 第二十八條 除外責任（一） | 第二十二條 重大傷病保險金、特定重大傷病保險金的申領 | 第二條 名詞定義 | 附表一：全民健康保險重大傷病項目 | payout_items</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr"/>
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr"/>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J135" s="3" t="n"/>
+      <c r="K135" s="3" t="n"/>
+      <c r="L135" s="3" t="n"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:05:18</t>
+        </is>
+      </c>
+      <c r="N135" s="3" t="n">
+        <v>10.62</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>失智症會賠嗎？賠多少？</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+失智症是否賠付及賠付金額需視其是否符合「重大傷病」或「完全失能」的定義。若失智症導致符合附表二「完全失能程度」中的第七項（中樞神經系統機能遺存極度障害，終身不能從事任何工作，經常需醫療護理或專人周密照護者），則可申請「完全失能保險金」，賠付金額依第十七條規定，按「當年度保險金額」或「年繳應繳保險費總額的一點零五倍」取其較大者給付。若失智症符合「重大傷病」範圍，則可申請「重大傷病保險金」，賠付金額依第十二條規定，按初次診斷確定罹患重大傷病時之保險單年度計算。
+條文依據：  
+- [第十七條 完全失能保險金的給付]  
+- [第十二條 重大傷病保險金的給付]  
+- [附表二：完全失能程度表]  
+- [附表一：全民健康保險重大傷病項目]</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>第十七條 完全失能保險金的給付 | 第二十九條 除外責任（二） | payout_items | 第十二條 重大傷病保險金的給付 | 第三十條 不保事項 | 附表二：完全失能程度表 | 附表一：全民健康保險重大傷病項目</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr"/>
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr"/>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J136" s="3" t="n"/>
+      <c r="K136" s="3" t="n"/>
+      <c r="L136" s="3" t="n"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:05:29</t>
+        </is>
+      </c>
+      <c r="N136" s="3" t="n">
+        <v>11.13</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>投保新鍾心滿福後，於第二保單年度罹患子宮頸惡性腫瘤，且已給付重大傷病保險金。第五保單年度時又罹患慢性腎衰竭，這樣還可以申領重大傷病保險金的給付嗎?</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不可以再次申領重大傷病保險金。根據條款規定，被保險人同時或先後罹患二項以上「重大傷病」時，本公司僅給付一項「重大傷病保險金」。因此，即使於第五保單年度罹患慢性腎衰竭，因已於第二保單年度因子宮頸惡性腫瘤申領過重大傷病保險金，無法再次申領。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>附表一：全民健康保險重大傷病項目 | 第十二條 重大傷病保險金的給付 | 第五條 保險範圍 | 第二條 名詞定義 | payout_items | 第二十二條 重大傷病保險金、特定重大傷病保險金的申領</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr"/>
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr"/>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J137" s="3" t="n"/>
+      <c r="K137" s="3" t="n"/>
+      <c r="L137" s="3" t="n"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:05:34</t>
+        </is>
+      </c>
+      <c r="N137" s="3" t="n">
+        <v>4.73</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>12歲的被保險人可以有健康促進保險費折減嗎？</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+12歲的被保險人無法享有健康促進保險費折減，因為第十九條明確規定，只有實際年齡達十八歲（含）以上的被保險人才符合使用指定程式並加入健康計劃以折減保險費的資格。
+條文依據：  
+- [第十九條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 健康促進保險費折減 | 第三十八條 投保年齡的計算及錯誤的處理 | 第三十四條 減額繳清保險 | 第二條 名詞定義 | 第十六條 所繳保險費加計利息的退還、身故保險金或喪葬費用保險金的給付 | 附表二：完全失能程度表</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr"/>
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr"/>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J138" s="3" t="n"/>
+      <c r="K138" s="3" t="n"/>
+      <c r="L138" s="3" t="n"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:05:37</t>
+        </is>
+      </c>
+      <c r="N138" s="3" t="n">
+        <v>2.81</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>ZDN</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>被保險人於投保鍾心滿溢後的第10天就罹患慢性腎衰竭，請問可以申領重大傷病保險金嗎？</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不可以申領重大傷病保險金。根據條款，被保險人因意外傷害事故以外原因，於等待期間內罹患「重大傷病」者，本契約自始無效，本公司僅無息退還已繳保險費予要保人。慢性腎衰竭屬於重大傷病範圍，但因其非意外傷害事故所致，且發生於等待期間內（投保後第10天），因此不符合申領條件。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第三十條 不保事項]</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 重大傷病保險金的給付 | 附表一：全民健康保險重大傷病項目 | 第三十條 不保事項 | 第二條 名詞定義 | 第二十二條 重大傷病保險金、特定重大傷病保險金的申領</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr"/>
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr"/>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J139" s="3" t="n"/>
+      <c r="K139" s="3" t="n"/>
+      <c r="L139" s="3" t="n"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:05:41</t>
+        </is>
+      </c>
+      <c r="N139" s="3" t="n">
+        <v>3.95</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>CFE</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>投保自由配重大傷病後，若在契約生效後80天罹患第一期乳癌，會拿到理賠金嗎?</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不會拿到理賠金。根據條款，第一期乳癌屬於「需積極或長期治療之癌症」範圍，等待期間為契約生效日起90天。若在等待期間內罹患重大傷病，契約自始無效，本公司僅退還已繳保險費且不計利息。
+條文依據：  
+- [第二條 名詞定義]  
+- [第十一條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>附表一：全民健康保險重大傷病項目 | 第十一條 重大傷病保險金的給付 | 第十五條 不保事項 | 第二條 名詞定義 | other_metadata | 第五條 契約有效期間及保證續保 | 第十四條 除外責任</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr"/>
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr"/>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J140" s="3" t="n"/>
+      <c r="K140" s="3" t="n"/>
+      <c r="L140" s="3" t="n"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:05:47</t>
+        </is>
+      </c>
+      <c r="N140" s="3" t="n">
+        <v>5.89</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>CFE</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>要保人想要終止國泰人壽自由配CFE契約，能否退保費?</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+要保人可以終止契約，並退還未到期保險費。本公司會從已繳保險費中扣除按短期費率計算的已經過期間保險費後，將未到期保險費無息退還給要保人。
+條文依據：  
+- [第九條 契約的終止（一）]</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>第九條 契約的終止（一） | 第十五條 不保事項 | 第五條 契約有效期間及保證續保 | 第七條 本契約效力的恢復 | 第六條 續保保險費的交付、寬限期間及契約效力的停止 | 附表二：短期費率表</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr"/>
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr"/>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J141" s="3" t="n"/>
+      <c r="K141" s="3" t="n"/>
+      <c r="L141" s="3" t="n"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:05:50</t>
+        </is>
+      </c>
+      <c r="N141" s="3" t="n">
+        <v>2.81</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>CFE</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>投保國泰人壽自由配CFE，若在等待期間內罹患重大傷病，要如何給付?</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在等待期間內罹患重大傷病，且該重大傷病並非因意外傷害事故所致，則本契約自始無效，本公司僅無息退還已繳保險費予要保人。若重大傷病係因意外傷害事故所致，則不受等待期間限制，可依約給付重大傷病保險金。
+條文依據：  
+- [第十一條 重大傷病保險金的給付]  
+- [第十五條 不保事項]</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 重大傷病保險金的給付 | 附表一：全民健康保險重大傷病項目 | 第十五條 不保事項 | 第十四條 除外責任 | payout_items | other_metadata</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr"/>
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr"/>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J142" s="3" t="n"/>
+      <c r="K142" s="3" t="n"/>
+      <c r="L142" s="3" t="n"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:05:54</t>
+        </is>
+      </c>
+      <c r="N142" s="3" t="n">
+        <v>4.28</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>CFE</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>投保自由配一年定期初次罹患重大傷病健康保險後，於第三年罹患先天性肌肉萎縮症，可以申領重大傷病保險金嗎？</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不可以申領重大傷病保險金。根據條款，先天性肌肉萎縮症不屬於「重大傷病」範圍，因此不符合申領條件。
+條文依據：  
+- 附表一：全民健康保險重大傷病項目</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 重大傷病保險金的給付 | other_metadata | 附表一：全民健康保險重大傷病項目 | 第十三條 重大傷病保險金的申領 | 第十五條 不保事項</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr"/>
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr"/>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J143" s="3" t="n"/>
+      <c r="K143" s="3" t="n"/>
+      <c r="L143" s="3" t="n"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:05:57</t>
+        </is>
+      </c>
+      <c r="N143" s="3" t="n">
+        <v>3.04</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>CFG</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>自由配重大疾病(甲型)保障的重大疾病有哪些疾病?</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+自由配重大疾病(甲型)保障的重大疾病包括以下疾病：  
+1. 腦中風後障礙(重度)  
+2. 癱瘓(重度)  
+3. 癌症(重度)  
+4. 急性心肌梗塞(重度)  
+5. 冠狀動脈繞道手術  
+6. 末期腎病變  
+7. 重大器官移植或造血幹細胞移植  
+條文依據：  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>國泰人壽自由配一年定期初次罹患重大疾病健康保險(甲型)年繳費率表 | payout_items | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr"/>
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr"/>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J144" s="3" t="n"/>
+      <c r="K144" s="3" t="n"/>
+      <c r="L144" s="3" t="n"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:06:00</t>
+        </is>
+      </c>
+      <c r="N144" s="3" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>被保險人領了2次癌症(重度)追蹤照護金後身故，是否還有尚未給付的保險金供受益人領取?</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人已領取2次「癌症(重度)追蹤照護保險金」後身故，受益人無法再申領尚未給付的「癌症(重度)追蹤照護保險金」，因該保險金的給付條件為被保險人於保險單週年日仍生存，且最多僅能給付5次。被保險人身故後，該保險金的給付責任即終止。
+條文依據：  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用) | 第十三條 初次罹患癌症(重度)保險金的給付 | payout_items | 第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用) | 第二十三條 癌症保險金或罹癌基因檢測服務的申領 | 第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付 | 第十六條 癌症(重度)豁免保險費(第二保險單年度起適用) | 第二十二條 保險事故的通知與保險給付的申請時間</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr"/>
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr"/>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J145" s="3" t="n"/>
+      <c r="K145" s="3" t="n"/>
+      <c r="L145" s="3" t="n"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:06:04</t>
+        </is>
+      </c>
+      <c r="N145" s="3" t="n">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>保險金額2萬元，「罹癌基因檢測服務」費用8萬元，還會給付多少「癌症(重度)追蹤照護保險金」？</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若「罹癌基因檢測服務額度」低於附件一所列「罹癌基因檢測服務」的服務費用，被保險人僅能申領「癌症(重度)追蹤照護保險金」。因此，若服務費用為新臺幣8萬元，而補償金額僅為新臺幣1,000元，則被保險人無法申領「罹癌基因檢測服務」，僅能申領「癌症(重度)追蹤照護保險金」。依條款規定，「癌症(重度)追蹤照護保險金」的給付金額為保險金額的12倍，即新臺幣24萬元。  
+條文依據：  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]  
+- [附件一：罹癌基因檢測服務之項目、服務費用及補償金額表]</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用) | 附件一：罹癌基因檢測服務之項目、服務費用及補償金額表 | 第二十三條 癌症保險金或罹癌基因檢測服務的申領 | 第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用) | payout_items | 第十三條 初次罹患癌症(重度)保險金的給付 | other_metadata | 第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr"/>
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr"/>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J146" s="3" t="n"/>
+      <c r="K146" s="3" t="n"/>
+      <c r="L146" s="3" t="n"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:06:09</t>
+        </is>
+      </c>
+      <c r="N146" s="3" t="n">
+        <v>4.76</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>投保後1個月罹患重度癌症，會給付哪些保險金？契約還會持續有效嗎？</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在投保後1個月罹患重度癌症，因診斷確定日屬於第一保險單年度內，符合「初次診斷確定罹患癌症(重度)」的條件，本公司將給付「初次罹患癌症(重度)保險金」，金額為「年繳應繳保險費」的一點零六倍。契約仍會持續有效，但當期已繳付之未到期保險費不予退還。  
+條文依據：  
+- [第十三條 初次罹患癌症(重度)保險金的給付]  
+- [第十六條 癌症(重度)豁免保險費(第二保險單年度起適用)]</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 癌症(重度)豁免保險費(第二保險單年度起適用) | 第十三條 初次罹患癌症(重度)保險金的給付 | 第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用) | 第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付 | 第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用)</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr"/>
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr"/>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J147" s="3" t="n"/>
+      <c r="K147" s="3" t="n"/>
+      <c r="L147" s="3" t="n"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:06:13</t>
+        </is>
+      </c>
+      <c r="N147" s="3" t="n">
+        <v>4.01</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>投保後10個月罹患重度癌症，會給付哪些保險金？契約還會持續有效嗎？</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人於投保後10個月（即第二保險單年度內）診斷確定罹患重度癌症，符合「初次診斷確定罹患癌症(重度)」的條件，本公司將給付「初次罹患癌症(重度)保險金」，金額為「保險金額」的十二倍。此外，契約仍會持續有效，並豁免續期保險費，但當期已繳付之未到期保險費不予退還。  
+條文依據：  
+- [第十三條 初次罹患癌症(重度)保險金的給付]  
+- [第十六條 癌症(重度)豁免保險費(第二保險單年度起適用)]</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 癌症(重度)豁免保險費(第二保險單年度起適用) | 第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用) | 第十條 契約的終止（二） | 第十三條 初次罹患癌症(重度)保險金的給付 | 第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr"/>
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr"/>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J148" s="3" t="n"/>
+      <c r="K148" s="3" t="n"/>
+      <c r="L148" s="3" t="n"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:06:18</t>
+        </is>
+      </c>
+      <c r="N148" s="3" t="n">
+        <v>4.78</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>投保醫心康愛，罹患肺癌一期，可領什麼保險金？</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+罹患肺癌一期屬於「癌症(初期)或癌症(輕度)」，可申領「初次罹患癌症(初期)或癌症(輕度)保險金」。若診斷確定日是在第一保險單年度內，可領「年繳應繳保險費」的一點零六倍；若診斷確定日是在第二保險單年度(含)以後，可領「保險金額」的五倍。此保險金最多僅給付一次。
+條文依據：  
+- [第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付 | 第十三條 初次罹患癌症(重度)保險金的給付 | payout_items | 第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用) | 第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr"/>
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr"/>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J149" s="3" t="n"/>
+      <c r="K149" s="3" t="n"/>
+      <c r="L149" s="3" t="n"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:06:23</t>
+        </is>
+      </c>
+      <c r="N149" s="3" t="n">
+        <v>4.53</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>PX5</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>若被保險人身故有何給付?</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人身故，保險金的受益人為被保險人的法定繼承人，並依民法繼承編的相關規定分配。若本附約保險金尚未給付或未完全給付，則由法定繼承人申領該部分保險金。
+條文依據：  
+- [第二十條 受益人]</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>第二十條 受益人 | 第十二條 重大疾病保險金的給付 | 第十一條 輕度重大疾病保險金的給付 | 第十四條 保險事故的通知與保險金的申請時間 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr"/>
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr"/>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J150" s="3" t="n"/>
+      <c r="K150" s="3" t="n"/>
+      <c r="L150" s="3" t="n"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:06:27</t>
+        </is>
+      </c>
+      <c r="N150" s="3" t="n">
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>PX5</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>投保鍾溢祝福後，請問在第二年經醫院醫師初次診斷罹患「輕度重大疾病」中的癌症(輕度)者，可以領到輕度重大疾病保險金嗎?可以領到保險金額的百分之多少?</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以領到輕度重大疾病保險金，保險金額的百分之二十。根據條款，被保險人於續保年度內初次診斷罹患「輕度重大疾病」中的癌症(輕度)，符合給付條件，且等待期間屆滿後即可申領。
+條文依據：  
+- [第十一條 輕度重大疾病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 輕度重大疾病保險金的給付 | 第十二條 重大疾病保險金的給付 | other_metadata | payout_items | 國泰人壽鍾溢祝福重大疾病健康保險附約(乙型) (外溢型)年繳費率表 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr"/>
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr"/>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J151" s="3" t="n"/>
+      <c r="K151" s="3" t="n"/>
+      <c r="L151" s="3" t="n"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:06:36</t>
+        </is>
+      </c>
+      <c r="N151" s="3" t="n">
+        <v>9.130000000000001</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>PX5</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>請問如果在投保後的第三年經醫院醫師初次診斷罹患「重大疾病」者，可以領到重大疾病保險金嗎?可以領到保險金額的百分之多少?那後續又在第四年經醫院醫師初次診斷罹患「輕度重大疾病」者，可以領到輕度重大疾病保險金嗎?可以領到保險金額的百分之多少?</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+在投保後的第三年初次診斷罹患「重大疾病」者，可以領到重大疾病保險金，給付比例為保險金額的1.3倍。  
+後續於第四年初次診斷罹患「輕度重大疾病」者，因已申領過重大疾病保險金，根據條款規定，輕度重大疾病保險金不再給付。
+條文依據：  
+- [第十二條 重大疾病保險金的給付]  
+- [第十一條 輕度重大疾病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 輕度重大疾病保險金的給付 | 第十二條 重大疾病保險金的給付 | 第十六條 除外責任 | payout_items | 第二條 名詞定義 | 第四條 保險範圍 | other_metadata | 國泰人壽鍾溢祝福重大疾病健康保險附約(乙型) (外溢型)年繳費率表</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr"/>
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr"/>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J152" s="3" t="n"/>
+      <c r="K152" s="3" t="n"/>
+      <c r="L152" s="3" t="n"/>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:06:40</t>
+        </is>
+      </c>
+      <c r="N152" s="3" t="n">
+        <v>4.42</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>PX5</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>請問如果在投保後的第三年經醫院醫師初次診斷罹患「輕度重大疾病」者，可以領到重大疾病保險金嗎?可以領到保險金額的百分之多少?那後續又在第四年經醫院醫師初次診斷罹患「重大疾病」者，可以領到輕度重大疾病保險金嗎?可以領到保險金額的百分之多少?</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+在投保後的第三年初次診斷罹患「輕度重大疾病」者，無法領取「重大疾病保險金」，只能領取「輕度重大疾病保險金」，給付比例為保險金額的百分之二十。  
+若後續在第四年初次診斷罹患「重大疾病」者，無法再領取「輕度重大疾病保險金」，但可以領取「重大疾病保險金」，給付比例為保險金額的一點三倍，且需扣除已領取的「輕度重大疾病保險金」。  
+條文依據：  
+- [第十一條 輕度重大疾病保險金的給付]  
+- [第十二條 重大疾病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 輕度重大疾病保險金的給付 | 第十二條 重大疾病保險金的給付 | 第十六條 除外責任 | payout_items | 第二條 名詞定義 | 第四條 保險範圍 | other_metadata | 第十五條 各項保險金的申領</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr"/>
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr"/>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J153" s="3" t="n"/>
+      <c r="K153" s="3" t="n"/>
+      <c r="L153" s="3" t="n"/>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:06:44</t>
+        </is>
+      </c>
+      <c r="N153" s="3" t="n">
+        <v>3.79</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>PX5</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>請問主約效力終止(因身故以外情形)，PX5還能持續有效嗎？</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+主約效力因身故以外情形終止時，PX5附約效力可持續至附約當期已繳保險費期滿即行終止，並不再延續。  
+條文依據：  
+- [第十條 附約的終止（二）]</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>第十條 附約的終止（二） | 第七條 保險費的墊繳、附約的停效及復效 | 第五條 附約的保險期間及保證續保 | 第十三條 健康促進保險費折減 | 第九條 附約的終止（一）</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr"/>
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr"/>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J154" s="3" t="n"/>
+      <c r="K154" s="3" t="n"/>
+      <c r="L154" s="3" t="n"/>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:06:47</t>
+        </is>
+      </c>
+      <c r="N154" s="3" t="n">
+        <v>2.91</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>請問如果於「無理賠紀錄期間」屆滿日以內罹患特定傷病，會給付多少錢?這筆錢會給付給誰?</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若於「無理賠紀錄期間」屆滿日以內罹患特定傷病，保險公司將給付「保險金額」加上「年繳應繳保險費總額」乘以1.02的金額作為「特定傷病保險金」。這筆保險金的受益人為被保險人本人，且不得指定或變更。
+條文依據：  
+- [第十一條 特定傷病保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第十二條 無理賠關懷保險金的給付 | 第十一條 特定傷病保險金的給付 | payout_items | 第二十七條 受益人的指定及變更</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr"/>
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr"/>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J155" s="3" t="n"/>
+      <c r="K155" s="3" t="n"/>
+      <c r="L155" s="3" t="n"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:06:51</t>
+        </is>
+      </c>
+      <c r="N155" s="3" t="n">
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>請問如果要保人與被保險人為同一人，被保險人於「無理賠紀錄期間」屆滿日以內身故，會給付多少錢?這筆錢會給付給誰?</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若要保人與被保險人為同一人，被保險人於「無理賠紀錄期間」屆滿日以內身故，符合「無理賠關懷保險金」的給付條件，保險公司將按「年繳應繳保險費總額」乘以1.02給付「無理賠關懷保險金」。此筆保險金的受益人為要保人本人，因要保人與被保險人為同一人，則改由被保險人的法定繼承人作為受益人。
+條文依據：  
+- [第十二條 無理賠關懷保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第十二條 無理賠關懷保險金的給付 | 第十一條 特定傷病保險金的給付 | payout_items | 第十九條 失蹤處理 | 第二十一條 無理賠關懷保險金的申領 | 第二十七條 受益人的指定及變更 | 第十七條 除外責任（二）</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr"/>
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr"/>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J156" s="3" t="n"/>
+      <c r="K156" s="3" t="n"/>
+      <c r="L156" s="3" t="n"/>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:06:56</t>
+        </is>
+      </c>
+      <c r="N156" s="3" t="n">
+        <v>4.94</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>請問如果要保人與被保險人為不同人，被保險人於「無理賠紀錄期間」屆滿日以內生存，且被保險人未罹患特定傷病，會給付多少錢?這筆錢會給付給誰?</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人於「無理賠紀錄期間」屆滿日以內生存，且未罹患特定傷病，本公司將給付「無理賠關懷保險金」，金額為「年繳應繳保險費總額」乘以1.02。此筆保險金的受益人為要保人本人。
+條文依據：  
+- [第十二條 無理賠關懷保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第十二條 無理賠關懷保險金的給付 | 第十一條 特定傷病保險金的給付 | payout_items | 第二十七條 受益人的指定及變更 | 第十九條 失蹤處理 | 第二十一條 無理賠關懷保險金的申領 | 第十七條 除外責任（二）</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr"/>
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr"/>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J157" s="3" t="n"/>
+      <c r="K157" s="3" t="n"/>
+      <c r="L157" s="3" t="n"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:07:02</t>
+        </is>
+      </c>
+      <c r="N157" s="3" t="n">
+        <v>5.34</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>保戶如果身故，會給保險金嗎?</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保戶身故時，若符合保險契約約定的條件，本公司會依照相關條款給付保險金。例如，若被保險人在「無理賠紀錄期間」內身故，或因特定情形如法院宣告死亡，則可依約定給付保險金。此外，若受益人在分期定期保險金給付期間內死亡，尚未領取的保險金也會一次貼現給付予法定繼承人。
+條文依據：  
+- [第五條 保險範圍]  
+- [第二十八條 本契約受益人死亡或失蹤的處理]  
+- [第十九條 失蹤處理]</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第二十八條 本契約受益人死亡或失蹤的處理 | 第十七條 除外責任（二） | 第二十三條 受益人受益權之喪失 | 第十九條 失蹤處理</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr"/>
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr"/>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J158" s="3" t="n"/>
+      <c r="K158" s="3" t="n"/>
+      <c r="L158" s="3" t="n"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:07:06</t>
+        </is>
+      </c>
+      <c r="N158" s="3" t="n">
+        <v>3.95</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>保戶如果身故，身故申領的保險金會給誰?</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保戶身故後，若有尚未給付或未完全給付的保險金，該部分保險金的受益人為保戶的法定繼承人。若契約受益人為法定繼承人，其受益順序及應得比例適用民法繼承編相關規定。
+條文依據：  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第二十三條 受益人受益權之喪失 | 第二十七條 受益人的指定及變更 | 第二十八條 本契約受益人死亡或失蹤的處理 | 第二十二條 分期定期保險金給付申領文件、給付期限及未依限給付之效果</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr"/>
+      <c r="G159" s="2" t="inlineStr"/>
+      <c r="H159" s="2" t="inlineStr"/>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J159" s="3" t="n"/>
+      <c r="K159" s="3" t="n"/>
+      <c r="L159" s="3" t="n"/>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:07:11</t>
+        </is>
+      </c>
+      <c r="N159" s="3" t="n">
+        <v>5.15</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>如果保戶投保繳費年期20年的滿溢寶，然後在第20保單年度身故的話，可以領到多少錢?</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若保戶在第20保單年度身故，依據條款規定，若未曾罹患特定傷病且於「無理賠紀錄期間」內身故，本公司將依照契約約定給付保險金。具體金額需依保險單所載的保險金額計算，條款未提供具體金額計算方式。
+條文依據：  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>other_metadata | 第二十八條 本契約受益人死亡或失蹤的處理 | 第二十六條 投保年齡的計算及錯誤的處理 | 第十一條 特定傷病保險金的給付 | 第二十二條 分期定期保險金給付申領文件、給付期限及未依限給付之效果 | 第五條 保險範圍 | 第十五條 健康促進保險費折減 | 第十九條 失蹤處理</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr"/>
+      <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr"/>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J160" s="3" t="n"/>
+      <c r="K160" s="3" t="n"/>
+      <c r="L160" s="3" t="n"/>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:07:20</t>
+        </is>
+      </c>
+      <c r="N160" s="3" t="n">
+        <v>8.529999999999999</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>被保險人為60歲女性，投保繳費期間20年期之滿溢寶特定傷病定期健康保險（定期給付型）（外溢型）100萬元，年繳應繳保險費為83,500元，年繳實繳保險費為78,490元。若被保險人於第二保險單年度自殺身故，則無理賠關懷保險金可以領到多少錢？</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人於第二保險單年度自殺身故，根據第十七條「除外責任（二）」的規定，故意自殺致死的情形，若發生於契約訂立或復效之日起二年內，本公司不負給付無理賠關懷保險金的責任。因此，無理賠關懷保險金無法領取。
+條文依據：  
+- [第十七條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 無理賠關懷保險金的給付 | 第十七條 除外責任（二） | 第十一條 特定傷病保險金的給付 | other_metadata | 第十九條 失蹤處理 | 第五條 保險範圍 | 第二十一條 無理賠關懷保險金的申領 | 第二十七條 受益人的指定及變更</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr"/>
+      <c r="G161" s="2" t="inlineStr"/>
+      <c r="H161" s="2" t="inlineStr"/>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J161" s="3" t="n"/>
+      <c r="K161" s="3" t="n"/>
+      <c r="L161" s="3" t="n"/>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:07:29</t>
+        </is>
+      </c>
+      <c r="N161" s="3" t="n">
+        <v>8.83</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>請問如果第2保單年度罹患特定傷病，可以給付多少錢?給付給誰?未來還有其他保險金嗎?</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在第二保險單年度（含）以後罹患特定傷病，依條款規定，本公司將給付以下保險金：  
+1. **特定傷病保險金**：給付金額為「保險金額」，且僅給付一次。  
+2. **生活補助保險金**：自初次診斷確定罹患特定傷病的次一個保險單週年日起，每逢保險單週年日仍生存者，按「保險金額」的36%給付，最高給付次數為10次。  
+給付對象為被保險人。  
+條文依據：  
+- [第十二條 特定傷病保險金的給付]  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 特定傷病保險金的給付 | 第五條 保險範圍 | 第十三條 生活補助保險金的給付（第二保險單年度起適用） | 第二條 名詞定義 | 第十五條 保險費豁免（第二保險單年度起適用）</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr"/>
+      <c r="G162" s="2" t="inlineStr"/>
+      <c r="H162" s="2" t="inlineStr"/>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J162" s="3" t="n"/>
+      <c r="K162" s="3" t="n"/>
+      <c r="L162" s="3" t="n"/>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:07:35</t>
+        </is>
+      </c>
+      <c r="N162" s="3" t="n">
+        <v>6.53</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>請問我115年1月1日投保，怎麼得到健康促進保險費折減?</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+要獲得健康促進保險費折減，您需在本契約有效期間內完成以下步驟：  
+1. 使用本公司指定的程式並加入指定的健康計劃。  
+2. 完成程式註冊程序，執行該程式並授權本公司取得您的裝置或程式內與健康促進相關的電子紀錄。  
+3. 在「指定日期」時，您的會員等級需符合以下標準之一：  
+   - 實踐家：次一保險單年度保險費折減比例為3%。  
+   - 樂享家或高於樂享家的會員等級：次一保險單年度保險費折減比例為10%。  
+此外，復效或豁免的保險費不適用折減約定。  
+條文依據：  
+- [第十六條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 健康促進保險費折減 | 第二十三條 投保年齡的計算及錯誤的處理 | 第十五條 保險費豁免（第二保險單年度起適用） | 第五條 保險範圍 | payout_items</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr"/>
+      <c r="G163" s="2" t="inlineStr"/>
+      <c r="H163" s="2" t="inlineStr"/>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J163" s="3" t="n"/>
+      <c r="K163" s="3" t="n"/>
+      <c r="L163" s="3" t="n"/>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:07:41</t>
+        </is>
+      </c>
+      <c r="N163" s="3" t="n">
+        <v>5.24</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>保戶在114/1/10投保樂鍾溢，如果他在115/3/30罹患特定傷病的話，在什麼時候可以領取生活補助保險金?</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保戶在114/1/10投保，保險單週年日為每年的1月10日。根據條款，生活補助保險金的給付需符合以下條件：  
+1. 被保險人於第二保險單年度（含）以後的有效期間內初次診斷確定罹患特定傷病。  
+2. 自初次診斷確定罹患特定傷病的次一個保險單週年日起，每逢各保險單週年日仍生存者，方可領取生活補助保險金。  
+保戶於115/3/30罹患特定傷病，屬於第二保險單年度（114/1/10至115/1/9為第一保險單年度，115/1/10起為第二保險單年度）。因此，保戶可於初次診斷確定罹患特定傷病的次一個保險單週年日，即116/1/10起，每逢保險單週年日仍生存者，開始領取生活補助保險金。
+條文依據：  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 生活補助保險金的給付（第二保險單年度起適用） | other_metadata | 第十一條 契約的終止（三） | payout_items | 第十二條 特定傷病保險金的給付 | 第五條 保險範圍 | 第十五條 保險費豁免（第二保險單年度起適用） | 第十條 契約的終止（二）</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr"/>
+      <c r="G164" s="2" t="inlineStr"/>
+      <c r="H164" s="2" t="inlineStr"/>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J164" s="3" t="n"/>
+      <c r="K164" s="3" t="n"/>
+      <c r="L164" s="3" t="n"/>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:07:47</t>
+        </is>
+      </c>
+      <c r="N164" s="3" t="n">
+        <v>6.34</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>保戶在114/1/10投保樂鍾溢，如果他在115/3/30罹患特定傷病的話，他在115/1/9會領到無理賠回饋保險金嗎?</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不會領到無理賠回饋保險金。根據條款，申領「無理賠回饋保險金」的條件是被保險人在保險單年度末仍生存且未曾因罹患特定傷病申領「特定傷病保險金」。保戶於115/3/30罹患特定傷病，符合申領「特定傷病保險金」的條件，因此不符合「無理賠回饋保險金」的給付條件。
+條文依據：  
+- [第十四條 無理賠回饋保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>payout_items | 第十四條 無理賠回饋保險金的給付 | other_metadata | 第十二條 特定傷病保險金的給付 | 第二十條 無理賠回饋保險金的申領 | 第十條 契約的終止（二） | 第五條 保險範圍 | 第十五條 保險費豁免（第二保險單年度起適用）</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr"/>
+      <c r="G165" s="2" t="inlineStr"/>
+      <c r="H165" s="2" t="inlineStr"/>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J165" s="3" t="n"/>
+      <c r="K165" s="3" t="n"/>
+      <c r="L165" s="3" t="n"/>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:07:51</t>
+        </is>
+      </c>
+      <c r="N165" s="3" t="n">
+        <v>4.45</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>被保險人於第一保險單年度罹患急性心肌梗塞（重度），生活補助保險金最多可以領取幾次？</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於第一保險單年度罹患急性心肌梗塞（重度），無法申領生活補助保險金。根據條款規定，生活補助保險金的給付僅適用於第二保險單年度（含）以後的有效期間內初次診斷確定罹患特定傷病者。
+條文依據：  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 生活補助保險金的給付（第二保險單年度起適用） | 第十二條 特定傷病保險金的給付 | 第十一條 契約的終止（三） | 第五條 保險範圍 | 第二條 名詞定義 | payout_items | 第十四條 無理賠回饋保險金的給付 | 第十九條 特定傷病保險金、生活補助保險金或保險費豁免的申領</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr"/>
+      <c r="G166" s="2" t="inlineStr"/>
+      <c r="H166" s="2" t="inlineStr"/>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J166" s="3" t="n"/>
+      <c r="K166" s="3" t="n"/>
+      <c r="L166" s="3" t="n"/>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:07:57</t>
+        </is>
+      </c>
+      <c r="N166" s="3" t="n">
+        <v>5.16</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>被保險人為60歲女性，投保繳費期間20年期之樂鍾心特定傷病定期健康保險（外溢型）5單位，每單位年繳應繳保險費為1675元，則每逢保險單年度末生存者，可以領取多少無理賠關懷保險金？</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人每逢保險單年度末仍生存且未曾因罹患特定傷病申領「特定傷病保險金」者，可領取「無理賠回饋保險金」。計算方式為：每單位年繳應繳保險費的百分之十（元以下無條件進位）乘以單位數。  
+計算如下：  
+每單位年繳應繳保險費 = 1675元  
+百分之十 = 167.5元（元以下無條件進位為168元）  
+單位數 = 5單位  
+168元 × 5單位 = 840元  
+因此，每逢保險單年度末生存者，可領取840元的「無理賠回饋保險金」。  
+條文依據：  
+- [第十四條 無理賠回饋保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 無理賠回饋保險金的給付 | other_metadata | payout_items | 第二十條 無理賠回饋保險金的申領 | 第十二條 特定傷病保險金的給付 | 第十三條 生活補助保險金的給付（第二保險單年度起適用） | 第五條 保險範圍 | 第十五條 保險費豁免（第二保險單年度起適用）</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr"/>
+      <c r="G167" s="2" t="inlineStr"/>
+      <c r="H167" s="2" t="inlineStr"/>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J167" s="3" t="n"/>
+      <c r="K167" s="3" t="n"/>
+      <c r="L167" s="3" t="n"/>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:08:10</t>
+        </is>
+      </c>
+      <c r="N167" s="3" t="n">
+        <v>13.47</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/rag_results.xlsx
+++ b/src/rag_results.xlsx
@@ -42,7 +42,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -52,6 +52,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -76,7 +81,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -88,6 +93,9 @@
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
@@ -455,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N167"/>
+  <dimension ref="A1:N250"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11470,6 +11478,5481 @@
         <v>37.62</v>
       </c>
     </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>保障範圍包括哪些項目？</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障項目包含：住院醫療保險金、加護病房或燒燙傷病房保險金、祝壽保險金、身故保險金或喪葬費用保險金，以及所繳保險費的退還。
+條文依據：  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>payout_items | summary | 第五條 保險範圍 | 第二條 名詞定義 | 第十八條 除外責任（一）</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障項目包含：住院醫療保險金、加護病房或燒燙傷病房保險金、祝壽保險金、身故保險金或喪葬費用保險金，以及所繳保險費的退還。
+條文依據：  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr"/>
+      <c r="H168" s="2" t="inlineStr"/>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "保障範圍包括哪些項目？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J168" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K168" s="4" t="n"/>
+      <c r="L168" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:46:37</t>
+        </is>
+      </c>
+      <c r="N168" s="4" t="n">
+        <v>31.25</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>住院日數計算有什麼特殊規則？</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院日數的計算規則如下：  
+1. 住院日數是按被保險人同一次住院的實際全日住進急性病房或慢性病房（含加護病房及燒燙傷病房）的日數計算，包含住院當日及出院當日。  
+2. 若被保險人出院後於同一日再次入院診療，該日不得重複計入住院日數。  
+條文依據：  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第十二條 住院醫療保險金的給付 | 第二條 名詞定義 | 第十三條 加護病房或燒燙傷病房保險金的給付 | 第二十八條 住院醫療保險金日額之減少</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院日數的計算規則如下：  
+1. 住院日數是按被保險人同一次住院的實際全日住進急性病房或慢性病房（含加護病房及燒燙傷病房）的日數計算，包含住院當日及出院當日。  
+2. 若被保險人出院後於同一日再次入院診療，該日不得重複計入住院日數。  
+條文依據：  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr"/>
+      <c r="H169" s="2" t="inlineStr"/>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "住院日數計算有什麼特殊規則？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J169" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K169" s="4" t="n"/>
+      <c r="L169" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:46:46</t>
+        </is>
+      </c>
+      <c r="N169" s="4" t="n">
+        <v>9.220000000000001</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>住院醫療保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院醫療保險金的給付規定如下：  
+1. 被保險人於本契約有效期間內因疾病或傷害住院治療時，本公司將依保險單上記載的「住院醫療保險金日額」，乘以入院日當年度的「增額係數」，再乘以住院日數，給付「住院醫療保險金」。  
+2. 同一保單年度內，同一次住院的住院日數給付上限為365日。  
+條文依據：  
+- [第十二條 住院醫療保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 住院醫療保險金的給付 | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第十三條 加護病房或燒燙傷病房保險金的給付 | 第十四條 醫療保險金給付總額之上限 | 第二十八條 住院醫療保險金日額之減少</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院醫療保險金的給付規定如下：  
+1. 被保險人於本契約有效期間內因疾病或傷害住院治療時，本公司將依保險單上記載的「住院醫療保險金日額」，乘以入院日當年度的「增額係數」，再乘以住院日數，給付「住院醫療保險金」。  
+2. 同一保單年度內，同一次住院的住院日數給付上限為365日。  
+條文依據：  
+- [第十二條 住院醫療保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr"/>
+      <c r="H170" s="2" t="inlineStr"/>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "住院醫療保險金的給付規定", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J170" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K170" s="4" t="n"/>
+      <c r="L170" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:46:55</t>
+        </is>
+      </c>
+      <c r="N170" s="4" t="n">
+        <v>8.58</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>加護病房或燒燙傷病房保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+加護病房或燒燙傷病房保險金的給付規定如下：  
+被保險人於本契約有效期間內因疾病或傷害而在醫院的加護病房或燒燙傷病房接受治療時，除住院醫療保險金外，本公司將依保險單所載「住院醫療保險金日額」，乘以入院日當年度的「增額係數」，再乘以實際住進加護病房或燒燙傷病房的日數（含轉入及轉出當日）的二倍，給付「加護病房或燒燙傷病房保險金」。  
+同一保單年度內，同一次住院的加護病房及燒燙傷病房住院日數合計最高以365日為限。同一日內，本公司僅就加護病房或燒燙傷病房其中一種病房給付。
+條文依據：  
+- [第十三條 加護病房或燒燙傷病房保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 加護病房或燒燙傷病房保險金的給付 | payout_items | 第二十三條 醫療保險金的申領 | 第五條 保險範圍 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+加護病房或燒燙傷病房保險金的給付規定如下：  
+被保險人於本契約有效期間內因疾病或傷害而在醫院的加護病房或燒燙傷病房接受治療時，除住院醫療保險金外，本公司將依保險單所載「住院醫療保險金日額」，乘以入院日當年度的「增額係數」，再乘以實際住進加護病房或燒燙傷病房的日數（含轉入及轉出當日）的二倍，給付「加護病房或燒燙傷病房保險金」。  
+同一保單年度內，同一次住院的加護病房及燒燙傷病房住院日數合計最高以365日為限。同一日內，本公司僅就加護病房或燒燙傷病房其中一種病房給付。
+條文依據：  
+- [第十三條 加護病房或燒燙傷病房保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr"/>
+      <c r="H171" s="2" t="inlineStr"/>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "加護病房或燒燙傷病房保險金的給付規定", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J171" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K171" s="4" t="n"/>
+      <c r="L171" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:47:05</t>
+        </is>
+      </c>
+      <c r="N171" s="4" t="n">
+        <v>10.26</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>醫療保險金給付總額之上限</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+醫療保險金給付總額之上限為保險單上所記載之「住院醫療保險金日額」的二千五百倍。
+條文依據：  
+- [第十四條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 醫療保險金給付總額之上限 | 第十二條 住院醫療保險金的給付 | 第五條 保險範圍 | 第十三條 加護病房或燒燙傷病房保險金的給付 | payout_items</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+醫療保險金給付總額之上限為保險單上所記載之「住院醫療保險金日額」的二千五百倍。
+條文依據：  
+- [第十四條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr"/>
+      <c r="H172" s="2" t="inlineStr"/>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "醫療保險金給付總額之上限", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J172" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K172" s="4" t="n"/>
+      <c r="L172" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:47:12</t>
+        </is>
+      </c>
+      <c r="N172" s="4" t="n">
+        <v>7.43</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>祝壽保險金的給付規定為何?</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+祝壽保險金的給付規定如下：  
+被保險人於本契約有效期間內，且保險年齡到達九十九歲之保險單週年日仍生存時，本公司將按「當年度保險金額」給付「祝壽保險金」。
+條文依據：  
+- [第十五條 祝壽保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>第十五條 祝壽保險金的給付 | 第十二條至第十三條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | 第二十四條 祝壽保險金的申領 | payout_items | 第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+祝壽保險金的給付規定如下：  
+被保險人於本契約有效期間內，且保險年齡到達九十九歲之保險單週年日仍生存時，本公司將按「當年度保險金額」給付「祝壽保險金」。
+條文依據：  
+- [第十五條 祝壽保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr"/>
+      <c r="H173" s="2" t="inlineStr"/>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "祝壽保險金的給付規定為何?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J173" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K173" s="4" t="n"/>
+      <c r="L173" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:47:22</t>
+        </is>
+      </c>
+      <c r="N173" s="4" t="n">
+        <v>9.609999999999999</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>有效期間內身故，保險金如何給付?</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於本契約有效期間內身故時，本公司依以下情況給付保險金：  
+1. 一般情況：按「當年度保險金額」給付「身故保險金」。  
+2. 若被保險人於繳費期間內身故，當期已繳付之未到期保險費不予退還，亦不併入身故保險金內給付。  
+3. 若被保險人於有效期間內且實際年齡未滿十五足歲身故，本公司退還「所繳保險費」，不適用上述一般情況。  
+4. 若被保險人為受監護宣告尚未撤銷者，其身故保險金變更為喪葬費用保險金，且喪葬費用保險金額不得超過遺產稅喪葬費扣除額之半數，超過部分不負給付責任，並退還超過部分之已繳保險費。
+條文依據：  
+- [第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付 | 第十條 契約的終止（二） | 第五條 保險範圍 | 第二十二條 失蹤處理 | 第十五條 祝壽保險金的給付</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於本契約有效期間內身故時，本公司依以下情況給付保險金：  
+1. 一般情況：按「當年度保險金額」給付「身故保險金」。  
+2. 若被保險人於繳費期間內身故，當期已繳付之未到期保險費不予退還，亦不併入身故保險金內給付。  
+3. 若被保險人於有效期間內且實際年齡未滿十五足歲身故，本公司退還「所繳保險費」，不適用上述一般情況。  
+4. 若被保險人為受監護宣告尚未撤銷者，其身故保險金變更為喪葬費用保險金，且喪葬費用保險金額不得超過遺產稅喪葬費扣除額之半數，超過部分不負給付責任，並退還超過部分之已繳保險費。
+條文依據：  
+- [第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr"/>
+      <c r="H174" s="2" t="inlineStr"/>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "有效期間內身故，保險金如何給付?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J174" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K174" s="4" t="n"/>
+      <c r="L174" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:47:33</t>
+        </is>
+      </c>
+      <c r="N174" s="4" t="n">
+        <v>10.68</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>健康促進保險費折減規定</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+健康促進保險費折減規定如下：  
+1. 被保險人年齡需達20歲（含）以上，並使用保險公司指定程式加入健康計劃。  
+2. 若於「指定日期」會員等級符合以下標準，則可享次一保險單年度保險費折減：  
+   - 進階會員：折減比例為2%。  
+   - 菁英會員或更高等級：折減比例為3%。  
+3. 折減僅適用於主契約保險費，不包含其他附約、附加條款或批註條款，且豁免或復效的保險費不適用折減。  
+4. 被保險人需完成指定程式的註冊程序，並授權保險公司取得健康促進相關電子紀錄，保險公司將依此計算會員等級。
+條文依據：  
+- [第十七條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>第十七條 健康促進保險費折減 | 第二十八條 住院醫療保險金日額之減少 | 第三十條 投保年齡的計算及錯誤的處理 | 第二條 名詞定義 | 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+健康促進保險費折減規定如下：  
+1. 被保險人年齡需達20歲（含）以上，並使用保險公司指定程式加入健康計劃。  
+2. 若於「指定日期」會員等級符合以下標準，則可享次一保險單年度保險費折減：  
+   - 進階會員：折減比例為2%。  
+   - 菁英會員或更高等級：折減比例為3%。  
+3. 折減僅適用於主契約保險費，不包含其他附約、附加條款或批註條款，且豁免或復效的保險費不適用折減。  
+4. 被保險人需完成指定程式的註冊程序，並授權保險公司取得健康促進相關電子紀錄，保險公司將依此計算會員等級。
+條文依據：  
+- [第十七條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr"/>
+      <c r="H175" s="2" t="inlineStr"/>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "健康促進保險費折減規定", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J175" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K175" s="4" t="n"/>
+      <c r="L175" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:47:42</t>
+        </is>
+      </c>
+      <c r="N175" s="4" t="n">
+        <v>9.220000000000001</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>除外責任的解釋?</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+除外責任是指保險公司對於某些特定原因或情況下所發生的疾病、傷害或死亡，不負給付保險金的責任。以下為條文中提及的主要除外責任範圍：  
+1. **疾病或傷害相關除外責任**：  
+   - 被保險人因故意行為（如自殺、自殺未遂）、犯罪行為或非法施用毒品所致的疾病或傷害。  
+   - 美容手術或外科整型（但為重建基本功能的必要整型不在此限）。  
+   - 健康檢查、療養、靜養等非直接診治病人的行為。  
+   - 懷孕、流產或分娩及其併發症（但特定情況如子宮外孕、葡萄胎等不在此限）。  
+2. **身故相關除外責任**：  
+   - 要保人故意致被保險人於死。  
+   - 被保險人故意自殺（但契約訂立或復效滿兩年後的自殺不在此限）。  
+   - 被保險人因犯罪處死、拒捕或越獄致死。  
+條文依據：  
+- [第十八條 除外責任（一）]  
+- [第十九條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第十九條 除外責任（二） | 第八條 告知義務與本契約的解除 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+除外責任是指保險公司對於某些特定原因或情況下所發生的疾病、傷害或死亡，不負給付保險金的責任。以下為條文中提及的主要除外責任範圍：  
+1. **疾病或傷害相關除外責任**：  
+   - 被保險人因故意行為（如自殺、自殺未遂）、犯罪行為或非法施用毒品所致的疾病或傷害。  
+   - 美容手術或外科整型（但為重建基本功能的必要整型不在此限）。  
+   - 健康檢查、療養、靜養等非直接診治病人的行為。  
+   - 懷孕、流產或分娩及其併發症（但特定情況如子宮外孕、葡萄胎等不在此限）。  
+2. **身故相關除外責任**：  
+   - 要保人故意致被保險人於死。  
+   - 被保險人故意自殺（但契約訂立或復效滿兩年後的自殺不在此限）。  
+   - 被保險人因犯罪處死、拒捕或越獄致死。  
+條文依據：  
+- [第十八條 除外責任（一）]  
+- [第十九條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr"/>
+      <c r="H176" s="2" t="inlineStr"/>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "除外責任的解釋?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J176" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K176" s="4" t="n"/>
+      <c r="L176" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:47:53</t>
+        </is>
+      </c>
+      <c r="N176" s="4" t="n">
+        <v>11.09</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>哪些疾病被含在除外責任?</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人因以下原因所致之疾病或傷害，屬於除外責任，本公司不負給付保險金的責任：  
+1. 被保險人之故意行為（包括自殺及自殺未遂）。  
+2. 被保險人之犯罪行為。  
+3. 被保險人非法施用毒品。  
+4. 美容手術、外科整型（但為重建基本功能所作之必要整型不在此限）。  
+5. 外觀可見之天生畸形。  
+6. 健康檢查、療養、靜養、戒毒、戒酒、護理或養老之非以直接診治病人為目的者。  
+7. 懷孕、流產或分娩及其併發症（但特定懷孕相關疾病、醫療行為必要之流產及剖腹產情形不在此限）。  
+8. 不孕症、人工受孕或非以治療為目的之避孕及絕育手術。  
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第二條 名詞定義 | 第十九條 除外責任（二）</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人因以下原因所致之疾病或傷害，屬於除外責任，本公司不負給付保險金的責任：  
+1. 被保險人之故意行為（包括自殺及自殺未遂）。  
+2. 被保險人之犯罪行為。  
+3. 被保險人非法施用毒品。  
+4. 美容手術、外科整型（但為重建基本功能所作之必要整型不在此限）。  
+5. 外觀可見之天生畸形。  
+6. 健康檢查、療養、靜養、戒毒、戒酒、護理或養老之非以直接診治病人為目的者。  
+7. 懷孕、流產或分娩及其併發症（但特定懷孕相關疾病、醫療行為必要之流產及剖腹產情形不在此限）。  
+8. 不孕症、人工受孕或非以治療為目的之避孕及絕育手術。  
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr"/>
+      <c r="H177" s="2" t="inlineStr"/>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "哪些疾病被含在除外責任?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J177" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K177" s="4" t="n"/>
+      <c r="L177" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:48:00</t>
+        </is>
+      </c>
+      <c r="N177" s="4" t="n">
+        <v>6.58</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>進行美容手術住院可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，因美容手術住院無法申請理賠。但若該美容手術是為了重建基本功能所作之必要整型，則不在此限，仍可申請理賠。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第十三條 加護病房或燒燙傷病房保險金的給付 | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第二條 名詞定義 | payout_items</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，因美容手術住院無法申請理賠。但若該美容手術是為了重建基本功能所作之必要整型，則不在此限，仍可申請理賠。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr"/>
+      <c r="H178" s="2" t="inlineStr"/>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "進行美容手術住院可以申請理賠嗎?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J178" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K178" s="4" t="n"/>
+      <c r="L178" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:48:07</t>
+        </is>
+      </c>
+      <c r="N178" s="4" t="n">
+        <v>6.46</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>因胎兒染色體異常進行手術而住院可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以申請理賠。根據條款，因「胎兒染色體異常之手術」住院診療不屬於除外責任範圍，因此符合理賠條件。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第二條 名詞定義 | payout_items | 第十三條 加護病房或燒燙傷病房保險金的給付</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以申請理賠。根據條款，因「胎兒染色體異常之手術」住院診療不屬於除外責任範圍，因此符合理賠條件。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr"/>
+      <c r="H179" s="2" t="inlineStr"/>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "因胎兒染色體異常進行手術而住院可以申請理賠嗎?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J179" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K179" s="4" t="n"/>
+      <c r="L179" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:48:14</t>
+        </is>
+      </c>
+      <c r="N179" s="4" t="n">
+        <v>5.56</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>因胎位不正進行手術而住院可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以申請理賠。根據條款，雖然懷孕、分娩及其併發症一般屬於除外責任，但若因胎位不正而進行醫療行為必要之剖腹產，則不在除外責任範圍內，因此符合理賠條件。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第二條 名詞定義 | payout_items | 第十三條 加護病房或燒燙傷病房保險金的給付</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以申請理賠。根據條款，雖然懷孕、分娩及其併發症一般屬於除外責任，但若因胎位不正而進行醫療行為必要之剖腹產，則不在除外責任範圍內，因此符合理賠條件。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr"/>
+      <c r="H180" s="2" t="inlineStr"/>
+      <c r="I180" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "因胎位不正進行手術而住院可以申請理賠嗎?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J180" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K180" s="4" t="n"/>
+      <c r="L180" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:48:22</t>
+        </is>
+      </c>
+      <c r="N180" s="4" t="n">
+        <v>8.210000000000001</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>因自殺未遂導致住院可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人因自殺未遂導致住院，本公司不負給付住院相關保險金的責任，因其屬於被保險人之故意行為。  
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 除外責任（二） | 第十八條 除外責任（一） | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | payout_items | 第十條 契約的終止（二）</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人因自殺未遂導致住院，本公司不負給付住院相關保險金的責任，因其屬於被保險人之故意行為。  
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr"/>
+      <c r="H181" s="2" t="inlineStr"/>
+      <c r="I181" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "因自殺未遂導致住院可以申請理賠嗎?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J181" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K181" s="4" t="n"/>
+      <c r="L181" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:48:29</t>
+        </is>
+      </c>
+      <c r="N181" s="4" t="n">
+        <v>6.97</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>被保險人在投保一年內故意自殺者，可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人在投保一年內故意自殺者，保險公司不負給付身故保險金或喪葬費用保險金的責任。只有在契約訂立或復效之日起滿二年後，故意自殺致死的情況下，保險公司才負給付責任。
+條文依據：  
+- [第十九條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 除外責任（二） | 第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付 | 第十條 契約的終止（二） | 第三十條 投保年齡的計算及錯誤的處理 | 第十八條 除外責任（一）</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人在投保一年內故意自殺者，保險公司不負給付身故保險金或喪葬費用保險金的責任。只有在契約訂立或復效之日起滿二年後，故意自殺致死的情況下，保險公司才負給付責任。
+條文依據：  
+- [第十九條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr"/>
+      <c r="H182" s="2" t="inlineStr"/>
+      <c r="I182" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "被保險人在投保一年內故意自殺者，可以申請理賠嗎?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J182" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K182" s="4" t="n"/>
+      <c r="L182" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:48:36</t>
+        </is>
+      </c>
+      <c r="N182" s="4" t="n">
+        <v>6.56</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>申請理賠有什麼時間規定嗎?</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申請理賠的時間規定如下：要保人、被保險人或受益人應於知悉保險事故後十日內通知保險公司，並於通知後儘速檢具所需文件申請保險金。保險公司應於收到完整文件後十五日內給付保險金。如因保險公司可歸責的原因未能在期限內給付，應按年利一分加計利息給付。
+條文依據：  
+- [第二十一條 保險事故的通知與保險金的申請時間]</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>第二十一條 保險事故的通知與保險金的申請時間 | 第六條 第二期以後保險費的交付、寬限期間及契約效力的停止 | 第七條 本契約效力的恢復 | 第三條 契約撤銷權 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申請理賠的時間規定如下：要保人、被保險人或受益人應於知悉保險事故後十日內通知保險公司，並於通知後儘速檢具所需文件申請保險金。保險公司應於收到完整文件後十五日內給付保險金。如因保險公司可歸責的原因未能在期限內給付，應按年利一分加計利息給付。
+條文依據：  
+- [第二十一條 保險事故的通知與保險金的申請時間]</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr"/>
+      <c r="H183" s="2" t="inlineStr"/>
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "申請理賠有什麼時間規定嗎?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J183" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K183" s="4" t="n"/>
+      <c r="L183" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:48:44</t>
+        </is>
+      </c>
+      <c r="N183" s="4" t="n">
+        <v>8.52</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>燒燙傷病房保險金怎麼申領?</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申領燒燙傷病房保險金時，受益人需檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 醫療診斷書或住院證明，並需列明進、出燒燙傷病房的日期。（但要保人或被保險人為醫師時，不得為被保險人出具診斷書或住院證明。）  
+4. 受益人的身分證明。  
+此外，保險公司可基於審核需要，徵詢其他醫師的專業意見，並經受益人同意調閱被保險人的就醫相關資料，相關費用由保險公司負擔。
+條文依據：  
+- [第二十三條 醫療保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>第二十三條 醫療保險金的申領 | 第十三條 加護病房或燒燙傷病房保險金的給付 | payout_items | 第二條 名詞定義 | 第二十一條 保險事故的通知與保險金的申請時間</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申領燒燙傷病房保險金時，受益人需檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 醫療診斷書或住院證明，並需列明進、出燒燙傷病房的日期。（但要保人或被保險人為醫師時，不得為被保險人出具診斷書或住院證明。）  
+4. 受益人的身分證明。  
+此外，保險公司可基於審核需要，徵詢其他醫師的專業意見，並經受益人同意調閱被保險人的就醫相關資料，相關費用由保險公司負擔。
+條文依據：  
+- [第二十三條 醫療保險金的申領]</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr"/>
+      <c r="H184" s="2" t="inlineStr"/>
+      <c r="I184" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "燒燙傷病房保險金怎麼申領?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J184" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K184" s="4" t="n"/>
+      <c r="L184" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:48:54</t>
+        </is>
+      </c>
+      <c r="N184" s="4" t="n">
+        <v>9.550000000000001</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>活到99歲怎麼申請祝壽金?</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申請祝壽保險金時，受益人需檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 受益人的身分證明。  
+條文依據：  
+- [第二十四條 祝壽保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>第十五條 祝壽保險金的給付 | 第二十四條 祝壽保險金的申領 | 第五條 保險範圍 | 第十二條至第十三條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | announcement_history</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申請祝壽保險金時，受益人需檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 受益人的身分證明。  
+條文依據：  
+- [第二十四條 祝壽保險金的申領]</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr"/>
+      <c r="H185" s="2" t="inlineStr"/>
+      <c r="I185" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "活到99歲怎麼申請祝壽金?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J185" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K185" s="4" t="n"/>
+      <c r="L185" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:48:59</t>
+        </is>
+      </c>
+      <c r="N185" s="4" t="n">
+        <v>5.35</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>被保人身故怎麼申請理賠</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+受益人申請「身故保險金」或「喪葬費用保險金」時，需檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 被保險人死亡證明書及除戶戶籍謄本。  
+4. 受益人的身分證明。  
+條文依據：  
+- [第二十五條 身故保險金或喪葬費用保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付 | 第十二條至第十三條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | 第二十二條 失蹤處理 | 第二十五條 身故保險金或喪葬費用保險金的申領 | 第十九條 除外責任（二）</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+受益人申請「身故保險金」或「喪葬費用保險金」時，需檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 被保險人死亡證明書及除戶戶籍謄本。  
+4. 受益人的身分證明。  
+條文依據：  
+- [第二十五條 身故保險金或喪葬費用保險金的申領]</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr"/>
+      <c r="H186" s="2" t="inlineStr"/>
+      <c r="I186" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "被保人身故怎麼申請理賠", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J186" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K186" s="4" t="n"/>
+      <c r="L186" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:49:07</t>
+        </is>
+      </c>
+      <c r="N186" s="4" t="n">
+        <v>8.119999999999999</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>投保15年後，因手術住院3天，住院日額為2500元，請問可以申請多少理賠?</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 住院日額為2500元的保險條款適用，因被保險人於契約有效期間內因手術住院，符合第十二條規定的住院醫療保險金給付條件。  
+2. 理賠金額計算方式為：住院醫療保險金日額（2500元） × 增額係數（假設為1，因題目未提供具體年度增額係數） × 住院天數（3天），因此理賠金額為2500 × 1 × 3 = 7500元。  
+3. 無其他條文提及影響理賠金額的條件或限制，且住院天數未超過第十二條規定的365天上限。
+條文依據：  
+- [第十二條 住院醫療保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 住院醫療保險金的給付 | 第十三條 加護病房或燒燙傷病房保險金的給付 | 第二十八條 住院醫療保險金日額之減少 | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | payout_items | 第五條 保險範圍 | 第二條 名詞定義 | 第二十一條 保險事故的通知與保險金的申請時間</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 住院日額為2500元的保險條款適用，因被保險人於契約有效期間內因手術住院，符合第十二條規定的住院醫療保險金給付條件。  
+2. 理賠金額計算方式為：住院醫療保險金日額（2500元） × 增額係數（假設為1，因題目未提供具體年度增額係數） × 住院天數（3天），因此理賠金額為2500 × 1 × 3 = 7500元。  
+3. 無其他條文提及影響理賠金額的條件或限制，且住院天數未超過第十二條規定的365天上限。
+條文依據：  
+- [第十二條 住院醫療保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr"/>
+      <c r="H187" s="2" t="inlineStr"/>
+      <c r="I187" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認住院日額為2500元的保險條款是否適用", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認住院天數為3天的理賠計算方式", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認是否有其他影響理賠金額的條件或限制", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J187" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K187" s="4" t="n"/>
+      <c r="L187" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:49:21</t>
+        </is>
+      </c>
+      <c r="N187" s="4" t="n">
+        <v>13.86</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>保障範圍包括哪些項目？</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括：住院手術醫療保險金、門診手術醫療保險金、特定處置保險金、意外創傷縫合處置保險金、意外住院手術醫療保險金、祝壽保險金、所繳保險費的退還、身故保險金或喪葬費用保險金。
+條文依據：  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>payout_items | 第五條 保險範圍 | summary | 第四條 名詞定義 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括：住院手術醫療保險金、門診手術醫療保險金、特定處置保險金、意外創傷縫合處置保險金、意外住院手術醫療保險金、祝壽保險金、所繳保險費的退還、身故保險金或喪葬費用保險金。
+條文依據：  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr"/>
+      <c r="H188" s="2" t="inlineStr"/>
+      <c r="I188" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "保障範圍包括哪些項目？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J188" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K188" s="4" t="n"/>
+      <c r="L188" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:49:28</t>
+        </is>
+      </c>
+      <c r="N188" s="4" t="n">
+        <v>6.94</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>保險金額是否有上限?</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+有，保險金額的給付總額上限為保險單上所記載「保險金額」的一千五百倍，且不包含其他附約、附加條款或批註條款。
+條文依據：  
+- [第十六條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 醫療保險金給付總額之上限 | 第三十條 保險金額之減少 | 第五條 保險範圍 | 第十九條 健康促進保險費折減 | 第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+有，保險金額的給付總額上限為保險單上所記載「保險金額」的一千五百倍，且不包含其他附約、附加條款或批註條款。
+條文依據：  
+- [第十六條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="G189" s="2" t="inlineStr"/>
+      <c r="H189" s="2" t="inlineStr"/>
+      <c r="I189" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "保險金額是否有上限?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J189" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K189" s="4" t="n"/>
+      <c r="L189" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:49:34</t>
+        </is>
+      </c>
+      <c r="N189" s="4" t="n">
+        <v>5.55</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>投保後5天發生手術，是否可以申請理賠?</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款，被保險人於本契約有效期間內因疾病或傷害接受手術，符合附表一所列手術項目且不屬除外責任範圍者，可申請理賠。但若疾病發生於契約生效日起持續有效第三十一日之前，則不在理賠範圍內，除非屬於等待期間不適用的特定疾病。若手術因意外傷害事故而進行，則無等待期間限制。  
+條文依據：  
+[第五條 保險範圍]  
+[第十一條 住院手術醫療保險金]  
+[第四條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第十一條 住院手術醫療保險金 | 第二十條 除外責任（一） | 第十二條 門診手術醫療保險金 | 第十三條 意外住院手術醫療保險金 | 第二十三條 保險事故的通知與保險金的申請時間 | 第四條 名詞定義 | 第十五條 意外創傷縫合處置保險金 | 附表三：意外創傷縫合處置項目及給付倍數表 | 附表一：手術項目與給付倍數 | payout_items</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+找不到相關內容  
+條文依據：  
+找不到相關內容</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款，被保險人於本契約有效期間內因疾病或傷害接受手術，符合附表一所列手術項目且不屬除外責任範圍者，可申請理賠。但若疾病發生於契約生效日起持續有效第三十一日之前，則不在理賠範圍內，除非屬於等待期間不適用的特定疾病。若手術因意外傷害事故而進行，則無等待期間限制。  
+條文依據：  
+[第五條 保險範圍]  
+[第十一條 住院手術醫療保險金]  
+[第四條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="H190" s="2" t="inlineStr"/>
+      <c r="I190" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "投保後5天發生手術，是否可以申請理賠?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J190" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K190" s="4" t="n"/>
+      <c r="L190" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:49:49</t>
+        </is>
+      </c>
+      <c r="N190" s="4" t="n">
+        <v>14.48</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>住院手術醫療保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院手術醫療保險金的給付規定如下：  
+1. 被保險人需於保險契約有效期間內，因疾病或傷害經醫師診斷必須住院接受附表一所列的手術治療，且已實際接受手術。  
+2. 給付金額計算方式為：保險單上記載的「保險金額」乘以手術日當年度的「增額係數」，再乘以手術給付倍數。  
+3. 若同一次手術中於同一手術位置接受兩項以上手術項目，僅給付手術給付倍數最高的手術項目。  
+4. 未載明於附表一的手術項目，將與被保險人協議比照附表內程度相當的手術項目，決定給付倍數。  
+5. 以下情形不予給付：  
+   - 屬於除外責任條款規定的情形。  
+   - 不屬於全民健康保險醫療服務給付項目及支付標準第二部第二章第七節或第三部第三章第四節第三項所列舉的手術。  
+條文依據：  
+- [第十一條 住院手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 住院手術醫療保險金 | 第十三條 意外住院手術醫療保險金 | 第十二條 門診手術醫療保險金 | payout_items | 第二十條 除外責任（一） | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院手術醫療保險金的給付規定如下：  
+1. 被保險人需於保險契約有效期間內，因疾病或傷害經醫師診斷必須住院接受附表一所列的手術治療，且已實際接受手術。  
+2. 給付金額計算方式為：保險單上記載的「保險金額」乘以手術日當年度的「增額係數」，再乘以手術給付倍數。  
+3. 若同一次手術中於同一手術位置接受兩項以上手術項目，僅給付手術給付倍數最高的手術項目。  
+4. 未載明於附表一的手術項目，將與被保險人協議比照附表內程度相當的手術項目，決定給付倍數。  
+5. 以下情形不予給付：  
+   - 屬於除外責任條款規定的情形。  
+   - 不屬於全民健康保險醫療服務給付項目及支付標準第二部第二章第七節或第三部第三章第四節第三項所列舉的手術。  
+條文依據：  
+- [第十一條 住院手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr"/>
+      <c r="H191" s="2" t="inlineStr"/>
+      <c r="I191" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "住院手術醫療保險金的給付規定", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J191" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K191" s="4" t="n"/>
+      <c r="L191" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:50:10</t>
+        </is>
+      </c>
+      <c r="N191" s="4" t="n">
+        <v>21.6</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>門診手術醫療保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+門診手術醫療保險金的給付規定如下：  
+1. 被保險人需於本契約有效期間內，因疾病或傷害經醫師診斷必須於醫院或診所門診接受附表一所列的手術治療，且已實際接受手術。  
+2. 給付金額計算方式為：保險單上所記載的「保險金額」乘以手術日當年度的「增額係數」，再乘以手術給付倍數。  
+3. 同一次手術中，若於同一手術位置接受兩項以上手術項目，僅給付手術給付倍數最高的手術項目。  
+4. 同一保險單年度內，門診手術醫療保險金的給付以十次為限。  
+5. 若手術項目未載明於附表一，本公司將與被保險人協議比照附表內的手術項目決定給付倍數。  
+6. 以下情形不予給付：  
+   - 屬於本契約除外責任條款規定的項目。  
+   - 不屬於全民健康保險醫療服務給付項目及支付標準第二部第二章第七節或第三部第三章第四節第三項所列舉的手術。  
+條文依據：  
+- [第十二條 門診手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 門診手術醫療保險金 | 第十一條 住院手術醫療保險金 | payout_items | 第十三條 意外住院手術醫療保險金 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+門診手術醫療保險金的給付規定如下：  
+1. 被保險人需於本契約有效期間內，因疾病或傷害經醫師診斷必須於醫院或診所門診接受附表一所列的手術治療，且已實際接受手術。  
+2. 給付金額計算方式為：保險單上所記載的「保險金額」乘以手術日當年度的「增額係數」，再乘以手術給付倍數。  
+3. 同一次手術中，若於同一手術位置接受兩項以上手術項目，僅給付手術給付倍數最高的手術項目。  
+4. 同一保險單年度內，門診手術醫療保險金的給付以十次為限。  
+5. 若手術項目未載明於附表一，本公司將與被保險人協議比照附表內的手術項目決定給付倍數。  
+6. 以下情形不予給付：  
+   - 屬於本契約除外責任條款規定的項目。  
+   - 不屬於全民健康保險醫療服務給付項目及支付標準第二部第二章第七節或第三部第三章第四節第三項所列舉的手術。  
+條文依據：  
+- [第十二條 門診手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr"/>
+      <c r="H192" s="2" t="inlineStr"/>
+      <c r="I192" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "門診手術醫療保險金的給付規定", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J192" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K192" s="4" t="n"/>
+      <c r="L192" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:50:25</t>
+        </is>
+      </c>
+      <c r="N192" s="4" t="n">
+        <v>14.52</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>意外住院手術醫療保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外住院手術醫療保險金的給付規定如下：  
+1. 被保險人需於本契約有效期間內，且保險年齡未滿七十歲。  
+2. 因傷害經醫師診斷，在住院期間必須接受手術治療且已實際接受手術者。  
+3. 給付金額為保險單所記載之「保險金額」的三倍，乘以手術日當年度的「增額係數」。  
+4. 若同一次手術中於同一手術位置接受兩項以上手術項目，僅給付一次意外住院手術醫療保險金。
+條文依據：  
+- [第十三條 意外住院手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 意外住院手術醫療保險金 | 第十一條 住院手術醫療保險金 | 第十五條 意外創傷縫合處置保險金 | 第二十條 除外責任（一） | 第十二條 門診手術醫療保險金 | 附表三：意外創傷縫合處置項目及給付倍數表 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外住院手術醫療保險金的給付規定如下：  
+1. 被保險人需於本契約有效期間內，且保險年齡未滿七十歲。  
+2. 因傷害經醫師診斷，在住院期間必須接受手術治療且已實際接受手術者。  
+3. 給付金額為保險單所記載之「保險金額」的三倍，乘以手術日當年度的「增額係數」。  
+4. 若同一次手術中於同一手術位置接受兩項以上手術項目，僅給付一次意外住院手術醫療保險金。
+條文依據：  
+- [第十三條 意外住院手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="inlineStr"/>
+      <c r="H193" s="2" t="inlineStr"/>
+      <c r="I193" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "意外住院手術醫療保險金的給付規定", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J193" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K193" s="4" t="n"/>
+      <c r="L193" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:50:38</t>
+        </is>
+      </c>
+      <c r="N193" s="4" t="n">
+        <v>12.34</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>特定處置保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+特定處置保險金的給付規定如下：  
+1. 被保險人需於保險契約有效期間內，因疾病或傷害經醫師診斷必須接受附表二所列的特定處置治療，且實際完成處置後，保險公司才會給付特定處置保險金。  
+2. 給付金額計算方式為：保險單上記載的「保險金額」× 特定處置日當年度的「增額係數」× 特定處置給付倍數。  
+3. 同一次處置治療中，若於同一治療位置接受兩項以上特定處置項目，僅給付特定處置給付倍數最高的項目。  
+4. 若被保險人接受的處置未列於附表二，保險公司不負給付責任。  
+5. 同一保險單年度內，特定處置保險金的給付次數以十次為限。
+條文依據：  
+- [第十四條 特定處置保險金]</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 特定處置保險金 | 第十五條 意外創傷縫合處置保險金 | 附表二：特定處置項目及給付倍數表 | 第五條 保險範圍 | 附表三：意外創傷縫合處置項目及給付倍數表</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+特定處置保險金的給付規定如下：  
+1. 被保險人需於保險契約有效期間內，因疾病或傷害經醫師診斷必須接受附表二所列的特定處置治療，且實際完成處置後，保險公司才會給付特定處置保險金。  
+2. 給付金額計算方式為：保險單上記載的「保險金額」× 特定處置日當年度的「增額係數」× 特定處置給付倍數。  
+3. 同一次處置治療中，若於同一治療位置接受兩項以上特定處置項目，僅給付特定處置給付倍數最高的項目。  
+4. 若被保險人接受的處置未列於附表二，保險公司不負給付責任。  
+5. 同一保險單年度內，特定處置保險金的給付次數以十次為限。
+條文依據：  
+- [第十四條 特定處置保險金]</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr"/>
+      <c r="H194" s="2" t="inlineStr"/>
+      <c r="I194" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "特定處置保險金的給付規定", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J194" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K194" s="4" t="n"/>
+      <c r="L194" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:50:49</t>
+        </is>
+      </c>
+      <c r="N194" s="4" t="n">
+        <v>10.91</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>意外創傷縫合處置保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外創傷縫合處置保險金的給付規定如下：  
+1. 被保險人因意外傷害事故，在醫院或診所接受附表三所列的意外創傷縫合處置治療者，本公司將依保險單所記載的「保險金額」，乘以當年度的「增額係數」及「意外創傷縫合處置給付倍數」計算給付金額。  
+2. 同一次意外傷害事故，僅就傷口最大者給付，且以給付一次為限。  
+3. 若被保險人因同一意外傷害事故已申領「住院手術醫療保險金」或「門診手術醫療保險金」，則不再給付「意外創傷縫合處置保險金」。  
+條文依據：  
+- [第十五條 意外創傷縫合處置保險金]</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>第十五條 意外創傷縫合處置保險金 | 附表三：意外創傷縫合處置項目及給付倍數表 | 第十四條 特定處置保險金 | 第二十條 除外責任（一） | 第十三條 意外住院手術醫療保險金 | 附表二：特定處置項目及給付倍數表</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外創傷縫合處置保險金的給付規定如下：  
+1. 被保險人因意外傷害事故，在醫院或診所接受附表三所列的意外創傷縫合處置治療者，本公司將依保險單所記載的「保險金額」，乘以當年度的「增額係數」及「意外創傷縫合處置給付倍數」計算給付金額。  
+2. 同一次意外傷害事故，僅就傷口最大者給付，且以給付一次為限。  
+3. 若被保險人因同一意外傷害事故已申領「住院手術醫療保險金」或「門診手術醫療保險金」，則不再給付「意外創傷縫合處置保險金」。  
+條文依據：  
+- [第十五條 意外創傷縫合處置保險金]</t>
+        </is>
+      </c>
+      <c r="G195" s="2" t="inlineStr"/>
+      <c r="H195" s="2" t="inlineStr"/>
+      <c r="I195" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "意外創傷縫合處置保險金的給付規定", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J195" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K195" s="4" t="n"/>
+      <c r="L195" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:51:11</t>
+        </is>
+      </c>
+      <c r="N195" s="4" t="n">
+        <v>22.25</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>醫療保險金給付總額之上限</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+醫療保險金給付總額之上限為保險單上所記載「保險金額」的一千五百倍，此上限不包含其他附約、附加條款或批註條款。
+條文依據：  
+- [第十六條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 醫療保險金給付總額之上限 | 第十二條 門診手術醫療保險金 | 第五條 保險範圍 | 第十一條 住院手術醫療保險金 | 第十三條 意外住院手術醫療保險金 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+醫療保險金給付總額之上限為保險單上所記載「保險金額」的一千五百倍，此上限不包含其他附約、附加條款或批註條款。
+條文依據：  
+- [第十六條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr"/>
+      <c r="H196" s="2" t="inlineStr"/>
+      <c r="I196" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "醫療保險金給付總額之上限", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J196" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K196" s="4" t="n"/>
+      <c r="L196" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:51:20</t>
+        </is>
+      </c>
+      <c r="N196" s="4" t="n">
+        <v>8.630000000000001</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>祝壽保險金的領取規定為何?</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+祝壽保險金的領取規定如下：  
+1. 被保險人需於本契約有效期間內，且保險年齡到達99歲之保險單週年日仍生存，方可領取祝壽保險金。  
+2. 受益人申領祝壽保險金時，需檢具以下文件：  
+   - 保險單或其謄本  
+   - 保險金申請書  
+   - 受益人的身分證明  
+條文依據：  
+- [第十七條 祝壽保險金]  
+- [第二十六條 祝壽保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>第十七條 祝壽保險金 | 第二十六條 祝壽保險金的申領 | 第十一條至第十五條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | 第二十三條 保險事故的通知與保險金的申請時間 | 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+祝壽保險金的領取規定如下：  
+1. 被保險人需於本契約有效期間內，且保險年齡到達99歲之保險單週年日仍生存，方可領取祝壽保險金。  
+2. 受益人申領祝壽保險金時，需檢具以下文件：  
+   - 保險單或其謄本  
+   - 保險金申請書  
+   - 受益人的身分證明  
+條文依據：  
+- [第十七條 祝壽保險金]  
+- [第二十六條 祝壽保險金的申領]</t>
+        </is>
+      </c>
+      <c r="G197" s="2" t="inlineStr"/>
+      <c r="H197" s="2" t="inlineStr"/>
+      <c r="I197" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "祝壽保險金的領取規定為何?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J197" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K197" s="4" t="n"/>
+      <c r="L197" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:51:28</t>
+        </is>
+      </c>
+      <c r="N197" s="4" t="n">
+        <v>8.57</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>身故時領取保險金有什麼規則?</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+身故時領取保險金的規則如下：  
+1. **一般規則**：被保險人於本契約有效期間內身故，本公司按「當年度保險金額」給付「身故保險金」。  
+2. **未滿十五足歲規則**：若被保險人於有效期間內且實際年齡未滿十五足歲身故，本公司僅退還「所繳保險費」，不適用一般規則。  
+3. **受監護宣告者**：若被保險人於訂立契約時受監護宣告且尚未撤銷，其身故保險金變更為喪葬費用保險金，並受相關金額上限規範。  
+4. **喪葬費用保險金上限**：若被保險人於民國99年2月3日（含）以後投保，其喪葬費用保險金額總和不得超過遺產稅喪葬費扣除額之半數，超過部分不予給付，並退還已繳保險費。  
+5. **除外責任**：若身故原因屬於要保人故意致死、被保險人故意自殺（契約訂立或復效後兩年內）、犯罪處死、拒捕或越獄致死等情形，本公司不負給付責任。未滿十五足歲者因上述原因身故，僅退還所繳保險費。
+條文依據：  
+- [第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金]  
+- [第二十一條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金 | 第二十七條 身故保險金或喪葬費用保險金的申領 | 第十一條至第十五條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | 第二十一條 除外責任（二） | 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+身故時領取保險金的規則如下：  
+1. **一般規則**：被保險人於本契約有效期間內身故，本公司按「當年度保險金額」給付「身故保險金」。  
+2. **未滿十五足歲規則**：若被保險人於有效期間內且實際年齡未滿十五足歲身故，本公司僅退還「所繳保險費」，不適用一般規則。  
+3. **受監護宣告者**：若被保險人於訂立契約時受監護宣告且尚未撤銷，其身故保險金變更為喪葬費用保險金，並受相關金額上限規範。  
+4. **喪葬費用保險金上限**：若被保險人於民國99年2月3日（含）以後投保，其喪葬費用保險金額總和不得超過遺產稅喪葬費扣除額之半數，超過部分不予給付，並退還已繳保險費。  
+5. **除外責任**：若身故原因屬於要保人故意致死、被保險人故意自殺（契約訂立或復效後兩年內）、犯罪處死、拒捕或越獄致死等情形，本公司不負給付責任。未滿十五足歲者因上述原因身故，僅退還所繳保險費。
+條文依據：  
+- [第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金]  
+- [第二十一條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr"/>
+      <c r="H198" s="2" t="inlineStr"/>
+      <c r="I198" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "身故時領取保險金有什麼規則?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J198" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K198" s="4" t="n"/>
+      <c r="L198" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:51:47</t>
+        </is>
+      </c>
+      <c r="N198" s="4" t="n">
+        <v>18.09</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>什麼情況下可以保費折減?</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人年齡滿20歲（含）以上，並使用保險公司指定的程式加入健康計劃，於「指定日期」的會員等級符合進階會員或菁英會員（或更高等級）標準之一者，可享次一保險單年度的保費折減。折減比例為進階會員2%，菁英會員或更高等級3%。但豁免或復效的保險費不適用此折減規定。此外，被保險人需完成程式註冊並授權保險公司取得健康相關電子紀錄，保險公司將依此計算會員等級。
+條文依據：  
+- [第十九條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 健康促進保險費折減 | 第三十條 保險金額之減少 | 第二十條 除外責任（一） | 第三十一條 投保年齡的計算及錯誤的處理 | 第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人年齡滿20歲（含）以上，並使用保險公司指定的程式加入健康計劃，於「指定日期」的會員等級符合進階會員或菁英會員（或更高等級）標準之一者，可享次一保險單年度的保費折減。折減比例為進階會員2%，菁英會員或更高等級3%。但豁免或復效的保險費不適用此折減規定。此外，被保險人需完成程式註冊並授權保險公司取得健康相關電子紀錄，保險公司將依此計算會員等級。
+條文依據：  
+- [第十九條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="inlineStr"/>
+      <c r="H199" s="2" t="inlineStr"/>
+      <c r="I199" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "什麼情況下可以保費折減?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J199" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K199" s="4" t="n"/>
+      <c r="L199" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:51:55</t>
+        </is>
+      </c>
+      <c r="N199" s="4" t="n">
+        <v>8.85</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>角膜切除術是否可以申請理賠?</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+角膜切除術可以申請理賠，其對應的給付倍數為5倍。
+條文依據：  
+- [附表一：手術項目與給付倍數 - 1305 角膜切除術]</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+角膜切除術可以申請理賠，其對應的給付倍數為5倍。
+條文依據：  
+- [附表一：手術項目與給付倍數 - 1305 角膜切除術]</t>
+        </is>
+      </c>
+      <c r="G200" s="2" t="inlineStr"/>
+      <c r="H200" s="2" t="inlineStr"/>
+      <c r="I200" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "角膜切除術是否可以申請理賠?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J200" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K200" s="4" t="n"/>
+      <c r="L200" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:52:03</t>
+        </is>
+      </c>
+      <c r="N200" s="4" t="n">
+        <v>7.21</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>白內障手術是否可以申請理賠?</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+白內障手術是否可以申請理賠需視手術是否符合附表一所列的手術項目及相關條件。若白內障手術未載明於附表一，則需與保險公司協議比照附表內程度相當的手術項目決定給付倍數。此外，若手術屬於除外責任條款中所列的情形，則不在理賠範圍內。
+條文依據：  
+- [第十二條 門診手術醫療保險金]  
+- [第十一條 住院手術醫療保險金]  
+- [第二十條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 門診手術醫療保險金 | 第二十條 除外責任（一） | 附表一：手術項目與給付倍數 | payout_items | 第十一條 住院手術醫療保險金</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+白內障手術是否可以申請理賠需視手術是否符合附表一所列的手術項目及相關條件。若白內障手術未載明於附表一，則需與保險公司協議比照附表內程度相當的手術項目決定給付倍數。此外，若手術屬於除外責任條款中所列的情形，則不在理賠範圍內。
+條文依據：  
+- [第十二條 門診手術醫療保險金]  
+- [第十一條 住院手術醫療保險金]  
+- [第二十條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="G201" s="2" t="inlineStr"/>
+      <c r="H201" s="2" t="inlineStr"/>
+      <c r="I201" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "白內障手術是否可以申請理賠?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J201" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K201" s="4" t="n"/>
+      <c r="L201" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:52:24</t>
+        </is>
+      </c>
+      <c r="N201" s="4" t="n">
+        <v>21.04</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>保障範圍包括哪些項目？</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括：意外事故身故保險金或喪葬費用保險金、意外事故失能保險金、每月生活照護保險金、重大燒燙傷保險金、意外骨折保險金、傷害醫療日額保險金、意外創傷縫合處置保險金。
+條文依據：  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>payout_items | 第五條 保險範圍 | 第十五條 每月生活照護保險金的給付 | 第三十條 不保事項 | 附表二：失能程度與保險金給付表</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括：意外事故身故保險金或喪葬費用保險金、意外事故失能保險金、每月生活照護保險金、重大燒燙傷保險金、意外骨折保險金、傷害醫療日額保險金、意外創傷縫合處置保險金。
+條文依據：  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="G202" s="2" t="inlineStr"/>
+      <c r="H202" s="2" t="inlineStr"/>
+      <c r="I202" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "保障範圍包括哪些項目？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J202" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K202" s="4" t="n"/>
+      <c r="L202" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:52:31</t>
+        </is>
+      </c>
+      <c r="N202" s="4" t="n">
+        <v>6.45</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>發生意外事故身故，理賠內容為何?</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外事故身故的理賠內容如下：  
+1. 若被保險人於意外傷害事故發生之日起 180 日內身故，本公司依意外傷害事故種類給付以下金額：  
+   - 一般意外傷害事故：「傷害醫療保險金日額」的 500 倍。  
+   - 特定意外傷害事故：「傷害醫療保險金日額」的 1000 倍。  
+2. 若被保險人於意外傷害事故發生後超過 180 日身故，但受益人能證明身故與該事故具有因果關係，本公司仍依上述金額給付。  
+3. 若被保險人為受監護宣告尚未撤銷者，其理賠內容變更為喪葬費用保險金，且喪葬費用保險金額不得超過遺產稅喪葬費扣除額之半數，超過部分不負給付責任。  
+條文依據：  
+- [第十二條 意外事故身故保險金或喪葬費用保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 意外事故身故保險金或喪葬費用保險金的給付 | 第十四條 保險給付的限制 | payout_items | 第十一條 契約的終止（二） | 第二十一條 失蹤處理</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外事故身故的理賠內容如下：  
+1. 若被保險人於意外傷害事故發生之日起 180 日內身故，本公司依意外傷害事故種類給付以下金額：  
+   - 一般意外傷害事故：「傷害醫療保險金日額」的 500 倍。  
+   - 特定意外傷害事故：「傷害醫療保險金日額」的 1000 倍。  
+2. 若被保險人於意外傷害事故發生後超過 180 日身故，但受益人能證明身故與該事故具有因果關係，本公司仍依上述金額給付。  
+3. 若被保險人為受監護宣告尚未撤銷者，其理賠內容變更為喪葬費用保險金，且喪葬費用保險金額不得超過遺產稅喪葬費扣除額之半數，超過部分不負給付責任。  
+條文依據：  
+- [第十二條 意外事故身故保險金或喪葬費用保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G203" s="2" t="inlineStr"/>
+      <c r="H203" s="2" t="inlineStr"/>
+      <c r="I203" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "發生意外事故身故，理賠內容為何?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J203" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K203" s="4" t="n"/>
+      <c r="L203" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:52:42</t>
+        </is>
+      </c>
+      <c r="N203" s="4" t="n">
+        <v>11.24</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>意外事故失能保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外事故失能保險金的給付條件如下：  
+1. 被保險人於保險契約有效期間內遭受「意外傷害事故」，並於事故發生後180日內致成附表二所列失能程度之一者，本公司依事故種類及失能程度，按以下方式計算給付金額：  
+   - 一般意外傷害事故：「傷害醫療保險金日額」的500倍乘以附表二給付比例。  
+   - 特定意外傷害事故：「傷害醫療保險金日額」的1000倍乘以附表二給付比例。  
+2. 若超過180日致成失能，但能證明失能與事故具有因果關係者，仍可申請給付，不受180日限制。  
+3. 同一事故導致多項失能時，僅給付同一手或足中較嚴重項目的失能保險金，且總金額以事故種類的上限為限：  
+   - 一般意外傷害事故：「傷害醫療保險金日額」的500倍。  
+   - 特定意外傷害事故：「傷害醫療保險金日額」的1000倍。  
+4. 不同事故導致的失能，累計給付金額最高以「傷害醫療保險金日額」的1200倍為限。  
+條文依據：  
+- [第十三條 意外事故失能保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 意外事故失能保險金的給付 | 第十五條 每月生活照護保險金的給付 | 第十四條 保險給付的限制 | 第十二條 意外事故身故保險金或喪葬費用保險金的給付 | 第二十三條 意外事故失能保險金的申領 | 附表二：失能程度與保險金給付表</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外事故失能保險金的給付條件如下：  
+1. 被保險人於保險契約有效期間內遭受「意外傷害事故」，並於事故發生後180日內致成附表二所列失能程度之一者，本公司依事故種類及失能程度，按以下方式計算給付金額：  
+   - 一般意外傷害事故：「傷害醫療保險金日額」的500倍乘以附表二給付比例。  
+   - 特定意外傷害事故：「傷害醫療保險金日額」的1000倍乘以附表二給付比例。  
+2. 若超過180日致成失能，但能證明失能與事故具有因果關係者，仍可申請給付，不受180日限制。  
+3. 同一事故導致多項失能時，僅給付同一手或足中較嚴重項目的失能保險金，且總金額以事故種類的上限為限：  
+   - 一般意外傷害事故：「傷害醫療保險金日額」的500倍。  
+   - 特定意外傷害事故：「傷害醫療保險金日額」的1000倍。  
+4. 不同事故導致的失能，累計給付金額最高以「傷害醫療保險金日額」的1200倍為限。  
+條文依據：  
+- [第十三條 意外事故失能保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="inlineStr"/>
+      <c r="H204" s="2" t="inlineStr"/>
+      <c r="I204" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "意外事故失能保險金的給付為何?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J204" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K204" s="4" t="n"/>
+      <c r="L204" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:53:07</t>
+        </is>
+      </c>
+      <c r="N204" s="4" t="n">
+        <v>24.8</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>每月生活照護保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+每月生活照護保險金的給付條件如下：  
+1. 被保險人於保險契約有效期間內因「意外傷害事故」，自事故發生之日起180日內，致成附表二所列第1級至第6級失能程度之一時，本公司自失能診斷確定當日起，按「傷害醫療保險金日額」的20倍乘以附表二給付比例所得之金額，按月給付，最多給付12個月。  
+2. 若於該失能的前四個「失能診斷確定週年日」，保險契約仍有效且被保險人仍生存，本公司自各該週年日起，按相同計算方式再給付，最多給付12個月。  
+3. 若被保險人自事故發生之日起超過180日才致成附表二所列第1級至第6級失能程度之一，但能證明失能與該事故具有因果關係者，本公司仍依上述規定給付，不受180日限制。  
+4. 同一事故若導致多項第1級至第6級失能，僅給付一項較嚴重失能的保險金，且最高以「傷害醫療保險金日額」的20倍為限。  
+5. 若失能合併以前的失能，僅給付較嚴重項目，但需扣除以前已給付的金額。  
+6. 每月給付金額最高以「傷害醫療保險金日額」的20倍為限，累計給付金額最高以「傷害醫療保險金日額」的1200倍為限。  
+條文依據：  
+- [第十五條 每月生活照護保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>第二十四條 每月生活照護保險金的申領 | 第十五條 每月生活照護保險金的給付 | payout_items | 第十八條 傷害醫療日額保險金的給付 | 第五條 保險範圍 | 附表二：失能程度與保險金給付表 | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+每月生活照護保險金的給付條件如下：  
+1. 被保險人於保險契約有效期間內因「意外傷害事故」，自事故發生之日起180日內，致成附表二所列第1級至第6級失能程度之一時，本公司自失能診斷確定當日起，按「傷害醫療保險金日額」的20倍乘以附表二給付比例所得之金額，按月給付，最多給付12個月。  
+2. 若於該失能的前四個「失能診斷確定週年日」，保險契約仍有效且被保險人仍生存，本公司自各該週年日起，按相同計算方式再給付，最多給付12個月。  
+3. 若被保險人自事故發生之日起超過180日才致成附表二所列第1級至第6級失能程度之一，但能證明失能與該事故具有因果關係者，本公司仍依上述規定給付，不受180日限制。  
+4. 同一事故若導致多項第1級至第6級失能，僅給付一項較嚴重失能的保險金，且最高以「傷害醫療保險金日額」的20倍為限。  
+5. 若失能合併以前的失能，僅給付較嚴重項目，但需扣除以前已給付的金額。  
+6. 每月給付金額最高以「傷害醫療保險金日額」的20倍為限，累計給付金額最高以「傷害醫療保險金日額」的1200倍為限。  
+條文依據：  
+- [第十五條 每月生活照護保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G205" s="2" t="inlineStr"/>
+      <c r="H205" s="2" t="inlineStr"/>
+      <c r="I205" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "每月生活照護保險金的給付為何?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J205" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K205" s="4" t="n"/>
+      <c r="L205" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:53:18</t>
+        </is>
+      </c>
+      <c r="N205" s="4" t="n">
+        <v>11.48</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>重大燒燙傷保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+重大燒燙傷保險金的給付條件為：被保險人於保險契約有效期間內，因「意外傷害事故」導致燒燙傷，且經診斷符合「重大燒燙傷」的定義時，本公司將按「傷害醫療保險金日額」的二百五十倍給付「重大燒燙傷保險金」。該保險金的給付以一次為限。
+條文依據：  
+- [第十六條 重大燒燙傷保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 重大燒燙傷保險金的給付 | 第二十五條 重大燒燙傷保險金的申領 | 第五條 保險範圍 | payout_items | 第二十九條 除外責任（原因）</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+重大燒燙傷保險金的給付條件為：被保險人於保險契約有效期間內，因「意外傷害事故」導致燒燙傷，且經診斷符合「重大燒燙傷」的定義時，本公司將按「傷害醫療保險金日額」的二百五十倍給付「重大燒燙傷保險金」。該保險金的給付以一次為限。
+條文依據：  
+- [第十六條 重大燒燙傷保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G206" s="2" t="inlineStr"/>
+      <c r="H206" s="2" t="inlineStr"/>
+      <c r="I206" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "重大燒燙傷保險金的給付為何?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J206" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K206" s="4" t="n"/>
+      <c r="L206" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:53:27</t>
+        </is>
+      </c>
+      <c r="N206" s="4" t="n">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>意外骨折保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外骨折保險金的給付條件如下：  
+1. 被保險人於契約有效期間內遭受「意外傷害事故」，並於事故發生後180日內經合格醫院或診所診斷為附表三骨折別表所列骨折項目之一（含不完全骨折及骨骼龜裂），本公司按「傷害醫療保險金日額」的二倍給付意外骨折保險金。  
+2. 若超過180日診斷確定骨折，受益人需證明骨折與該意外傷害事故具有因果關係，仍可依上述規定給付。  
+3. 同一意外傷害事故僅給付一次意外骨折保險金。  
+4. 若骨折不屬於附表三骨折別表所列項目，需由本公司與被保險人協議核付；但若骨折為骨折別表內明訂不給付之部位，則不負給付責任。
+條文依據：  
+- [第十七條 意外骨折保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>第十七條 意外骨折保險金的給付 | 第十八條 傷害醫療日額保險金的給付 | 第二十六條 意外骨折保險金的申領 | 第十三條 意外事故失能保險金的給付 | 第十九條 意外創傷縫合處置保險金的給付 | 附表二：失能程度與保險金給付表 | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外骨折保險金的給付條件如下：  
+1. 被保險人於契約有效期間內遭受「意外傷害事故」，並於事故發生後180日內經合格醫院或診所診斷為附表三骨折別表所列骨折項目之一（含不完全骨折及骨骼龜裂），本公司按「傷害醫療保險金日額」的二倍給付意外骨折保險金。  
+2. 若超過180日診斷確定骨折，受益人需證明骨折與該意外傷害事故具有因果關係，仍可依上述規定給付。  
+3. 同一意外傷害事故僅給付一次意外骨折保險金。  
+4. 若骨折不屬於附表三骨折別表所列項目，需由本公司與被保險人協議核付；但若骨折為骨折別表內明訂不給付之部位，則不負給付責任。
+條文依據：  
+- [第十七條 意外骨折保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G207" s="2" t="inlineStr"/>
+      <c r="H207" s="2" t="inlineStr"/>
+      <c r="I207" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "意外骨折保險金的給付為何?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J207" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K207" s="4" t="n"/>
+      <c r="L207" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:53:42</t>
+        </is>
+      </c>
+      <c r="N207" s="4" t="n">
+        <v>14.99</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>傷害醫療日額保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+傷害醫療日額保險金的給付條件如下：  
+1. 被保險人於保險契約有效期間內因「意外傷害事故」住院治療，且住院日數在意外發生後 180 日內，本公司按「傷害醫療保險金日額」乘以實際住院日數給付，但每次事故最高給付日數為 90 日。  
+2. 若治療超過 180 日，受益人需證明治療與該意外事故具因果關係，本公司仍依上述規定給付，不受 180 日限制。  
+3. 若因骨折未住院或住院日數未達附表三骨折別表所訂日數，未住院部分按骨折別表所訂日數的二分之一乘以「傷害醫療保險金日額」給付，合計給付日數以骨折別表所訂日數為上限。  
+4. 骨折類型的給付：  
+   - 完全骨折按骨折別表所訂日數給付。  
+   - 不完全骨折按完全骨折日數的二分之一給付。  
+   - 骨骼龜裂按完全骨折日數的四分之一給付。  
+5. 同時發生多項骨折時，僅給付一項較高等級的「傷害醫療日額保險金」。
+條文依據：  
+- [第十八條 傷害醫療日額保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 傷害醫療日額保險金的給付 | 第二十七條 傷害醫療日額保險金的申領 | 第十五條 每月生活照護保險金的給付 | 第三十四條 傷害醫療保險金日額之減少 | 第十九條 意外創傷縫合處置保險金的給付 | 附表二：失能程度與保險金給付表 | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+傷害醫療日額保險金的給付條件如下：  
+1. 被保險人於保險契約有效期間內因「意外傷害事故」住院治療，且住院日數在意外發生後 180 日內，本公司按「傷害醫療保險金日額」乘以實際住院日數給付，但每次事故最高給付日數為 90 日。  
+2. 若治療超過 180 日，受益人需證明治療與該意外事故具因果關係，本公司仍依上述規定給付，不受 180 日限制。  
+3. 若因骨折未住院或住院日數未達附表三骨折別表所訂日數，未住院部分按骨折別表所訂日數的二分之一乘以「傷害醫療保險金日額」給付，合計給付日數以骨折別表所訂日數為上限。  
+4. 骨折類型的給付：  
+   - 完全骨折按骨折別表所訂日數給付。  
+   - 不完全骨折按完全骨折日數的二分之一給付。  
+   - 骨骼龜裂按完全骨折日數的四分之一給付。  
+5. 同時發生多項骨折時，僅給付一項較高等級的「傷害醫療日額保險金」。
+條文依據：  
+- [第十八條 傷害醫療日額保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G208" s="2" t="inlineStr"/>
+      <c r="H208" s="2" t="inlineStr"/>
+      <c r="I208" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "傷害醫療日額保險金的給付為何?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J208" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K208" s="4" t="n"/>
+      <c r="L208" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:53:56</t>
+        </is>
+      </c>
+      <c r="N208" s="4" t="n">
+        <v>13.91</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>意外創傷縫合處置保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外創傷縫合處置保險金的給付條件為：被保險人於保險契約有效期間內，因遭受「意外傷害事故」，在「醫院」或「診所」經醫師診斷必須接受創傷縫合處置治療，且已完成縫合處置者，本公司將按「傷害醫療保險金日額」給付該保險金。同一意外傷害事故僅給付一次。
+條文依據：  
+- [第十九條 意外創傷縫合處置保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 意外創傷縫合處置保險金的給付 | 第二十八條 意外創傷縫合處置保險金的申領 | 第五條 保險範圍 | 第十七條 意外骨折保險金的給付 | payout_items | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外創傷縫合處置保險金的給付條件為：被保險人於保險契約有效期間內，因遭受「意外傷害事故」，在「醫院」或「診所」經醫師診斷必須接受創傷縫合處置治療，且已完成縫合處置者，本公司將按「傷害醫療保險金日額」給付該保險金。同一意外傷害事故僅給付一次。
+條文依據：  
+- [第十九條 意外創傷縫合處置保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G209" s="2" t="inlineStr"/>
+      <c r="H209" s="2" t="inlineStr"/>
+      <c r="I209" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "意外創傷縫合處置保險金的給付為何?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J209" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K209" s="4" t="n"/>
+      <c r="L209" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:54:04</t>
+        </is>
+      </c>
+      <c r="N209" s="4" t="n">
+        <v>7.32</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>因意外導致視力衰退，是否能申請理賠?</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以申請理賠，但需符合以下條件：  
+1. 視力衰退需達到「失明」的定義，即矯正後視力永久在萬國式視力表0.02以下，或符合其他失明標準（如眼球摘出、僅能辨明暗等）。  
+2. 必須經過自傷害日起六個月的治療後判定為永久性視力損害，但若屬眼球摘出等明顯無法復原的情況，則不受此六個月限制。  
+條文依據：  
+- 註2</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>第二十三條 意外事故失能保險金的申領 | 第十三條 意外事故失能保險金的給付 | 註2： | 第三十條 不保事項 | 第二十六條 意外骨折保險金的申領 | 附表二：失能程度與保險金給付表</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以申請理賠，但需符合以下條件：  
+1. 視力衰退需達到「失明」的定義，即矯正後視力永久在萬國式視力表0.02以下，或符合其他失明標準（如眼球摘出、僅能辨明暗等）。  
+2. 必須經過自傷害日起六個月的治療後判定為永久性視力損害，但若屬眼球摘出等明顯無法復原的情況，則不受此六個月限制。  
+條文依據：  
+- 註2</t>
+        </is>
+      </c>
+      <c r="G210" s="2" t="inlineStr"/>
+      <c r="H210" s="2" t="inlineStr"/>
+      <c r="I210" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "因意外導致視力衰退，是否能申請理賠?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J210" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K210" s="4" t="n"/>
+      <c r="L210" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:54:12</t>
+        </is>
+      </c>
+      <c r="N210" s="4" t="n">
+        <v>8.02</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>肋骨骨折是否可以申請理賠?理賠金額為多少?</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+肋骨骨折可以申請理賠，理賠金額需依據骨折的情況計算：  
+1. 若肋骨完全骨折且未住院治療，按附表三所訂的20天乘以「傷害醫療保險金日額」的二分之一給付。  
+2. 若肋骨完全骨折且住院治療，則按實際住院日數乘以「傷害醫療保險金日額」給付，但最高以90日為限。  
+3. 若為不完全骨折，按完全骨折日數的二分之一（即10天）給付；若為骨骼龜裂，按完全骨折日數的四分之一（即5天）給付。  
+條文依據：  
+- [第十八條 傷害醫療日額保險金的給付]  
+- [附表三：骨折別表]</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 傷害醫療日額保險金的給付 | 第十七條 意外骨折保險金的給付 | 第二十六條 意外骨折保險金的申領 | 第三十條 不保事項 | 第五條 保險範圍 | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+肋骨骨折可以申請理賠，理賠金額需依據骨折的情況計算：  
+1. 若肋骨完全骨折且未住院治療，按附表三所訂的20天乘以「傷害醫療保險金日額」的二分之一給付。  
+2. 若肋骨完全骨折且住院治療，則按實際住院日數乘以「傷害醫療保險金日額」給付，但最高以90日為限。  
+3. 若為不完全骨折，按完全骨折日數的二分之一（即10天）給付；若為骨骼龜裂，按完全骨折日數的四分之一（即5天）給付。  
+條文依據：  
+- [第十八條 傷害醫療日額保險金的給付]  
+- [附表三：骨折別表]</t>
+        </is>
+      </c>
+      <c r="G211" s="2" t="inlineStr"/>
+      <c r="H211" s="2" t="inlineStr"/>
+      <c r="I211" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "肋骨骨折是否可以申請理賠?理賠金額為多少?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J211" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K211" s="4" t="n"/>
+      <c r="L211" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:54:22</t>
+        </is>
+      </c>
+      <c r="N211" s="4" t="n">
+        <v>9.76</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>投保新鍾心滿福後，假設投保保額為100萬元，於第二保單年度接受「移植器官」，這樣可以領多少保險金?</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+新鍾心滿福保險涵蓋器官移植手術的保障，並將其列為「特定重大傷病」之一。於第二保單年度接受器官移植手術時，保險公司將按保險金額的20%給付「特定重大傷病保險金」。若投保保額為100萬元，實際給付金額為20萬元。第二保單年度符合條件，且不影響保險金的給付。
+條文依據：  
+- [第十三條 特定重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>第十五條 滿期保險金的給付 | 第二條 名詞定義 | 附表一：全民健康保險重大傷病項目 | 第十三條 特定重大傷病保險金的給付 | 附表三：各保險單年度可借金額上限表 | payout_items | 第十七條 完全失能保險金的給付 | 附表二：完全失能程度表</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+新鍾心滿福保險涵蓋器官移植手術的保障，並將其列為「特定重大傷病」之一。於第二保單年度接受器官移植手術時，保險公司將按保險金額的20%給付「特定重大傷病保險金」。若投保保額為100萬元，實際給付金額為20萬元。第二保單年度符合條件，且不影響保險金的給付。
+條文依據：  
+- [第十三條 特定重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G212" s="2" t="inlineStr"/>
+      <c r="H212" s="2" t="inlineStr"/>
+      <c r="I212" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認新鍾心滿福保險是否涵蓋器官移植手術的保障", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認保單條款中器官移植手術的保險金給付標準", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認保額為100萬元的情況下，器官移植手術的實際給付金額", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認第二保單年度是否影響保險金的給付條件", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J212" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K212" s="4" t="n"/>
+      <c r="L212" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:54:36</t>
+        </is>
+      </c>
+      <c r="N212" s="4" t="n">
+        <v>13.93</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>投保新鍾心滿福後，若要理賠重大傷病保險金，一定要檢附全民健保開立的重大傷病證明才能拿到保險金嗎?</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申請重大傷病保險金時，並非一定要檢附全民健保開立的重大傷病證明。若被保險人已取得一家「區域醫院」層級以上（含）之醫療院所開立且符合投保當時「重大傷病範圍」的診斷書及當次病歷摘要，亦可作為重大傷病證明文件，免向全民健康保險保險人申請重大傷病證明。  
+條文依據：  
+- [第二十二條 重大傷病保險金、特定重大傷病保險金的申領]  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>第二十二條 重大傷病保險金、特定重大傷病保險金的申領 | other_metadata | 第十二條 重大傷病保險金的給付 | 附表一：全民健康保險重大傷病項目 | 第二條 名詞定義 | 第三十條 不保事項</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申請重大傷病保險金時，並非一定要檢附全民健保開立的重大傷病證明。若被保險人已取得一家「區域醫院」層級以上（含）之醫療院所開立且符合投保當時「重大傷病範圍」的診斷書及當次病歷摘要，亦可作為重大傷病證明文件，免向全民健康保險保險人申請重大傷病證明。  
+條文依據：  
+- [第二十二條 重大傷病保險金、特定重大傷病保險金的申領]  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G213" s="2" t="inlineStr"/>
+      <c r="H213" s="2" t="inlineStr"/>
+      <c r="I213" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認重大傷病保險金的理賠條件", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認是否需要檢附全民健保開立的重大傷病證明", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認新鍾心滿福保單條款中對重大傷病理賠的相關規定", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J213" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K213" s="4" t="n"/>
+      <c r="L213" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:54:49</t>
+        </is>
+      </c>
+      <c r="N213" s="4" t="n">
+        <v>12.92</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>一定要有健保身分才能申請重大傷病理賠嗎？</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不一定需要有健保身分才能申請重大傷病理賠。若被保險人喪失全民健康保險被保險人資格，需先申請加保全民健康保險後，始得申領「重大傷病保險金」之給付。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>第二十二條 重大傷病保險金、特定重大傷病保險金的申領 | 第十二條 重大傷病保險金的給付 | other_metadata | 第三十條 不保事項 | 第二條 名詞定義 | 附表一：全民健康保險重大傷病項目</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不一定需要有健保身分才能申請重大傷病理賠。若被保險人喪失全民健康保險被保險人資格，需先申請加保全民健康保險後，始得申領「重大傷病保險金」之給付。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G214" s="2" t="inlineStr"/>
+      <c r="H214" s="2" t="inlineStr"/>
+      <c r="I214" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "一定要有健保身分才能申請重大傷病理賠嗎？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J214" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K214" s="4" t="n"/>
+      <c r="L214" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:54:55</t>
+        </is>
+      </c>
+      <c r="N214" s="4" t="n">
+        <v>5.85</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>重大傷病的項目如果在投保後有新增，可以從優申請理賠嗎？</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以從優申請理賠，若重大傷病項目於保險契約有效期間內新增，則以中央衛生主管機關最新公告的重大傷病項目為準，並適用於被保險人於有效期間內診斷確定的情形。
+條文依據：  
+- [第二條 名詞定義]：「全民健康保險重大傷病項目及其證明有效期限」，包含本契約「訂立時」及「有效期間內被保險人診斷確定當時」由中央衛生主管機關公告之重大傷病項目。</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t>附表一：全民健康保險重大傷病項目 | 第二條 名詞定義 | payout_items</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F215" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以從優申請理賠，若重大傷病項目於保險契約有效期間內新增，則以中央衛生主管機關最新公告的重大傷病項目為準，並適用於被保險人於有效期間內診斷確定的情形。
+條文依據：  
+- [第二條 名詞定義]：「全民健康保險重大傷病項目及其證明有效期限」，包含本契約「訂立時」及「有效期間內被保險人診斷確定當時」由中央衛生主管機關公告之重大傷病項目。</t>
+        </is>
+      </c>
+      <c r="G215" s="2" t="inlineStr"/>
+      <c r="H215" s="2" t="inlineStr"/>
+      <c r="I215" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "重大傷病的項目如果在投保後有新增，可以從優申請理賠嗎？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J215" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K215" s="4" t="n"/>
+      <c r="L215" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:55:03</t>
+        </is>
+      </c>
+      <c r="N215" s="4" t="n">
+        <v>7.95</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>我的保單之前有停效，在復效後五天被診斷出重大疾病是否可申請理賠？</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若保單已成功復效，且重大疾病屬於保單保障範圍內，則可申請理賠。但需注意，復效後的理賠條件需符合以下規定：重大疾病的診斷需發生於復效後的有效期間內，且若該疾病屬於等待期間限制範圍，則需等待期間屆滿後方可理賠。若重大疾病因意外傷害事故所致，則不受等待期間限制。  
+條文依據：  
+- [第八條 本契約效力的恢復]  
+- [第十二條 重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>第八條 本契約效力的恢復 | 第三十條 不保事項 | 第五條 保險範圍 | other_metadata | 第二條 名詞定義 | 第十二條 重大傷病保險金的給付 | 第二十二條 重大傷病保險金、特定重大傷病保險金的申領 | 附表一：全民健康保險重大傷病項目</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F216" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若保單已成功復效，且重大疾病屬於保單保障範圍內，則可申請理賠。但需注意，復效後的理賠條件需符合以下規定：重大疾病的診斷需發生於復效後的有效期間內，且若該疾病屬於等待期間限制範圍，則需等待期間屆滿後方可理賠。若重大疾病因意外傷害事故所致，則不受等待期間限制。  
+條文依據：  
+- [第八條 本契約效力的恢復]  
+- [第十二條 重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G216" s="2" t="inlineStr"/>
+      <c r="H216" s="2" t="inlineStr"/>
+      <c r="I216" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認保單是否已成功復效", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認重大疾病是否在保單保障範圍內", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認復效後的理賠條件或限制", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認重大疾病診斷日期是否符合理賠條件", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J216" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K216" s="4" t="n"/>
+      <c r="L216" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:55:15</t>
+        </is>
+      </c>
+      <c r="N216" s="4" t="n">
+        <v>12.18</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>領完重大傷病保險金，主約終止後，附約可以繼續有效嗎?</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以。根據條文規定，若因重大傷病診斷確定而導致主約終止時，要保人仍可於附約有效期間內繼續繳交附約保險費，以延續附約效力。
+條文依據：  
+- [第十一條 契約的終止（二）]</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 契約的終止（二） | 第十二條 重大傷病保險金的給付 | 第三十條 不保事項 | 第五條 保險範圍 | payout_items | 附表一：全民健康保險重大傷病項目</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F217" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以。根據條文規定，若因重大傷病診斷確定而導致主約終止時，要保人仍可於附約有效期間內繼續繳交附約保險費，以延續附約效力。
+條文依據：  
+- [第十一條 契約的終止（二）]</t>
+        </is>
+      </c>
+      <c r="G217" s="2" t="inlineStr"/>
+      <c r="H217" s="2" t="inlineStr"/>
+      <c r="I217" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "領完重大傷病保險金，主約終止後，附約可以繼續有效嗎?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J217" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K217" s="4" t="n"/>
+      <c r="L217" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:55:22</t>
+        </is>
+      </c>
+      <c r="N217" s="4" t="n">
+        <v>7.09</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>Q1：因為慢性精神病的保險給付僅有保額的20%，我可以先不申請給付，等之後發生其他重大傷病後，再申請重大傷病保險金嗎?Q2：但如果我不申請，保險公司不會知道我有罹患慢性精神病阿，所以我就可以領之後的重大傷病100%保額嗎?</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 慢性精神病的保險給付確實僅有保額的20%，或「年繳應繳保險費總額」的1.05倍，二者取其大者。  
+2. 可以延後申請慢性精神病的保險給付，但需注意條款中未提及延後申請是否有時間限制，建議確認保單細節或與保險公司聯繫。  
+3. 延後申請慢性精神病的保險給付不會影響其他重大傷病保險金的申請資格，但條款明確規定「同時或先後罹患二項以上重大傷病時，本公司僅給付一項重大傷病保險金」，因此若已罹患慢性精神病，之後再罹患其他重大傷病，仍僅能選擇其中一項進行理賠。  
+4. 保險公司是否知曉慢性精神病的病情，取決於被保險人是否主動申報或提供相關診斷證明，條款中未明確提及保險公司是否會主動調查。  
+5. 若罹患的重大傷病不屬於慢性精神病，則重大傷病保險金可按保險金額或「年繳應繳保險費總額」的1.05倍，二者取其大者進行給付。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第十三條 特定重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 重大傷病保險金的給付 | 第十三條 特定重大傷病保險金的給付 | 第三十條 不保事項 | 第二十八條 除外責任（一） | 第二十二條 重大傷病保險金、特定重大傷病保險金的申領 | 第二條 名詞定義 | 附表一：全民健康保險重大傷病項目 | payout_items</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F218" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 慢性精神病的保險給付確實僅有保額的20%，或「年繳應繳保險費總額」的1.05倍，二者取其大者。  
+2. 可以延後申請慢性精神病的保險給付，但需注意條款中未提及延後申請是否有時間限制，建議確認保單細節或與保險公司聯繫。  
+3. 延後申請慢性精神病的保險給付不會影響其他重大傷病保險金的申請資格，但條款明確規定「同時或先後罹患二項以上重大傷病時，本公司僅給付一項重大傷病保險金」，因此若已罹患慢性精神病，之後再罹患其他重大傷病，仍僅能選擇其中一項進行理賠。  
+4. 保險公司是否知曉慢性精神病的病情，取決於被保險人是否主動申報或提供相關診斷證明，條款中未明確提及保險公司是否會主動調查。  
+5. 若罹患的重大傷病不屬於慢性精神病，則重大傷病保險金可按保險金額或「年繳應繳保險費總額」的1.05倍，二者取其大者進行給付。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第十三條 特定重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G218" s="2" t="inlineStr"/>
+      <c r="H218" s="2" t="inlineStr"/>
+      <c r="I218" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認慢性精神病保險給付是否僅有保額的20%", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認是否可以延後申請慢性精神病的保險給付", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認延後申請是否影響重大傷病保險金的申請資格", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認保險公司是否會因未申請而不知曉慢性精神病的病情", "must_have": false, "分數": 1.0}, {"id": "5", "point": "確認重大傷病保險金是否能領取100%保額", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J218" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K218" s="4" t="n"/>
+      <c r="L218" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:55:44</t>
+        </is>
+      </c>
+      <c r="N218" s="4" t="n">
+        <v>21.71</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>失智症會賠嗎？賠多少？</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+失智症是否理賠及理賠金額需視保險契約內容而定。若失智症符合附表二所列「完全失能程度」或附表一所載「重大傷病範圍」中的相關項目，則可能符合理賠條件。  
+1. 若失智症導致「中樞神經系統機能遺存極度障害，終身不能從事任何工作，經常需醫療護理或專人周密照護」，可依第十七條規定申請「完全失能保險金」，理賠金額為「當年度保險金額」或「年繳應繳保險費總額的一點零五倍」，取其較大者 [第十七條 完全失能保險金的給付]。  
+2. 若失智症屬於附表一所載「重大傷病範圍」中的「慢性精神病」或其他符合「重大傷病」項目，則可依第十二條規定申請「重大傷病保險金」，理賠金額依保險單年度及病症類型計算 [第十二條 重大傷病保險金的給付]。  
+條款未明確規定失智症是否涵蓋於其他保險項目。</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
+        <is>
+          <t>第十七條 完全失能保險金的給付 | 第二十九條 除外責任（二） | 第十二條 重大傷病保險金的給付 | 第三十條 不保事項 | 附表一：全民健康保險重大傷病項目 | 第二十一條 失蹤處理 | 第十六條 所繳保險費加計利息的退還、身故保險金或喪葬費用保險金的給付 | 附表二：完全失能程度表 | payout_items</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F219" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+找不到相關內容  
+條文依據：  
+找不到相關內容</t>
+        </is>
+      </c>
+      <c r="G219" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+失智症是否理賠及理賠金額需視保險契約內容而定。若失智症符合附表二所列「完全失能程度」或附表一所載「重大傷病範圍」中的相關項目，則可能符合理賠條件。  
+1. 若失智症導致「中樞神經系統機能遺存極度障害，終身不能從事任何工作，經常需醫療護理或專人周密照護」，可依第十七條規定申請「完全失能保險金」，理賠金額為「當年度保險金額」或「年繳應繳保險費總額的一點零五倍」，取其較大者 [第十七條 完全失能保險金的給付]。  
+2. 若失智症屬於附表一所載「重大傷病範圍」中的「慢性精神病」或其他符合「重大傷病」項目，則可依第十二條規定申請「重大傷病保險金」，理賠金額依保險單年度及病症類型計算 [第十二條 重大傷病保險金的給付]。  
+條款未明確規定失智症是否涵蓋於其他保險項目。</t>
+        </is>
+      </c>
+      <c r="H219" s="2" t="inlineStr"/>
+      <c r="I219" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "失智症會賠嗎？賠多少？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J219" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K219" s="4" t="n"/>
+      <c r="L219" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:56:09</t>
+        </is>
+      </c>
+      <c r="N219" s="4" t="n">
+        <v>24.99</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>投保新鍾心滿福後，於第二保單年度罹患子宮頸惡性腫瘤，且已給付重大傷病保險金。第五保單年度時又罹患慢性腎衰竭，這樣還可以申領重大傷病保險金的給付嗎?</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款規定，重大傷病保險金僅能給付一次，即使被保險人於不同保單年度內先後罹患多項重大傷病，本公司僅給付一項重大傷病保險金。因此，於第二保單年度已因子宮頸惡性腫瘤申領重大傷病保險金後，第五保單年度罹患慢性腎衰竭將無法再次申領重大傷病保險金。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
+        <is>
+          <t>附表一：全民健康保險重大傷病項目 | 第二條 名詞定義 | 第十二條 重大傷病保險金的給付 | 第二十二條 重大傷病保險金、特定重大傷病保險金的申領</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F220" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款規定，重大傷病保險金僅能給付一次，即使被保險人於不同保單年度內先後罹患多項重大傷病，本公司僅給付一項重大傷病保險金。因此，於第二保單年度已因子宮頸惡性腫瘤申領重大傷病保險金後，第五保單年度罹患慢性腎衰竭將無法再次申領重大傷病保險金。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G220" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款規定，重大傷病保險金僅能給付一次，即使被保險人於不同保單年度內先後罹患多項重大傷病，本公司僅給付一項重大傷病保險金。因此，於第二保單年度已因子宮頸惡性腫瘤申領重大傷病保險金後，第五保單年度罹患慢性腎衰竭將無法再次申領重大傷病保險金。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="H220" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款規定，重大傷病保險金僅能給付一次，即使被保險人於不同保單年度內先後罹患多項重大傷病，本公司僅給付一項重大傷病保險金。因此，於第二保單年度已因子宮頸惡性腫瘤申領重大傷病保險金後，第五保單年度罹患慢性腎衰竭將無法再次申領重大傷病保險金。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="I220" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認重大傷病保險金是否可重複申領", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認重大傷病保險金的申領條件是否涵蓋慢性腎衰竭", "must_have": true, "分數": 0.5}, {"id": "3", "point": "確認保單條款中對於不同保單年度內多次罹患重大疾病的規定", "must_have": false, "分數": 1.0}], "coverage_score": 0.7778, "C_conf": 0.7778}</t>
+        </is>
+      </c>
+      <c r="J220" s="5" t="n">
+        <v>0.7778</v>
+      </c>
+      <c r="K220" s="4" t="n"/>
+      <c r="L220" s="5" t="n">
+        <v>0.7778</v>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:56:46</t>
+        </is>
+      </c>
+      <c r="N220" s="4" t="n">
+        <v>36.64</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>12歲的被保險人可以有健康促進保險費折減嗎？</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+12歲的被保險人無法享有健康促進保險費折減，因為該條款明確規定，只有實際年齡達18歲（含）以上的被保險人才符合資格。
+條文依據：  
+- [第十九條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 健康促進保險費折減 | 第三十八條 投保年齡的計算及錯誤的處理 | 第三十四條 減額繳清保險 | 第二條 名詞定義 | 第十六條 所繳保險費加計利息的退還、身故保險金或喪葬費用保險金的給付 | 附表二：完全失能程度表</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F221" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+12歲的被保險人無法享有健康促進保險費折減，因為該條款明確規定，只有實際年齡達18歲（含）以上的被保險人才符合資格。
+條文依據：  
+- [第十九條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="G221" s="2" t="inlineStr"/>
+      <c r="H221" s="2" t="inlineStr"/>
+      <c r="I221" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "12歲的被保險人可以有健康促進保險費折減嗎？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J221" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K221" s="4" t="n"/>
+      <c r="L221" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:56:58</t>
+        </is>
+      </c>
+      <c r="N221" s="4" t="n">
+        <v>11.78</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>ZDN</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>被保險人於投保鍾心滿溢後的第10天就罹患慢性腎衰竭，請問可以申領重大傷病保險金嗎？</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於投保後第10天罹患慢性腎衰竭，無法申領重大傷病保險金。根據條款，慢性腎衰竭屬於重大傷病範圍，但因非因意外傷害事故所致，需符合等待期間規定。等待期間為契約生效日起持續有效90日，於等待期間內罹患重大傷病者，契約自始無效，本公司僅退還已繳保險費。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第二條 名詞定義]  
+- [第三十條 不保事項]</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 重大傷病保險金的給付 | 附表一：全民健康保險重大傷病項目 | 第三十條 不保事項 | 第二條 名詞定義 | 第二十二條 重大傷病保險金、特定重大傷病保險金的申領</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於投保後第10天罹患慢性腎衰竭，無法申領重大傷病保險金。根據條款，慢性腎衰竭屬於重大傷病範圍，但因非因意外傷害事故所致，需符合等待期間規定。等待期間為契約生效日起持續有效90日，於等待期間內罹患重大傷病者，契約自始無效，本公司僅退還已繳保險費。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第二條 名詞定義]  
+- [第三十條 不保事項]</t>
+        </is>
+      </c>
+      <c r="G222" s="2" t="inlineStr"/>
+      <c r="H222" s="2" t="inlineStr"/>
+      <c r="I222" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認重大傷病保險金是否涵蓋慢性腎衰竭", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認保單是否已生效並符合理賠條件", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認慢性腎衰竭的診斷是否符合重大傷病的定義", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認保單是否有針對重大傷病的特定等待期規定", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J222" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K222" s="4" t="n"/>
+      <c r="L222" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:57:18</t>
+        </is>
+      </c>
+      <c r="N222" s="4" t="n">
+        <v>19.73</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>CFE</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>投保自由配重大傷病後，若在契約生效後80天罹患第一期乳癌，會拿到理賠金嗎?</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人在契約生效後80天罹患第一期乳癌，符合理賠條件，可獲得理賠金。理由如下：  
+1. 第一期乳癌屬於「重大傷病範圍」中「需積極或長期治療之癌症」的項目，且未被排除。  
+2. 保單等待期間針對癌症為90天，80天尚未滿等待期間，因此不符合理賠條件。  
+條文依據：  
+- [附表一：全民健康保險重大傷病項目]  
+- [第二條 名詞定義]  
+- [第十一條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
+        <is>
+          <t>附表一：全民健康保險重大傷病項目 | 第十一條 重大傷病保險金的給付 | 第十五條 不保事項 | 第二條 名詞定義 | other_metadata | 第五條 契約有效期間及保證續保 | 第十四條 除外責任</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F223" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人在契約生效後80天罹患第一期乳癌，符合理賠條件，可獲得理賠金。理由如下：  
+1. 第一期乳癌屬於「重大傷病範圍」中「需積極或長期治療之癌症」的項目，且未被排除。  
+2. 保單等待期間針對癌症為90天，80天尚未滿等待期間，因此不符合理賠條件。  
+條文依據：  
+- [附表一：全民健康保險重大傷病項目]  
+- [第二條 名詞定義]  
+- [第十一條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G223" s="2" t="inlineStr"/>
+      <c r="H223" s="2" t="inlineStr"/>
+      <c r="I223" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認自由配重大傷病保險是否涵蓋第一期乳癌", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認契約生效後80天是否符合保單等待期規定", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認第一期乳癌是否符合理賠條件", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認保單是否有特別條款或除外責任針對乳癌", "must_have": false, "分數": 0.0}], "coverage_score": 0.9231, "C_conf": 0.9231}</t>
+        </is>
+      </c>
+      <c r="J223" s="4" t="n">
+        <v>0.9231</v>
+      </c>
+      <c r="K223" s="4" t="n"/>
+      <c r="L223" s="4" t="n">
+        <v>0.9231</v>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:57:33</t>
+        </is>
+      </c>
+      <c r="N223" s="4" t="n">
+        <v>14.83</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>CFE</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>要保人想要終止國泰人壽自由配CFE契約，能否退保費?</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+要保人可以終止契約，並可退還未到期保險費。本公司會從已繳保險費中扣除按短期費率計算的已經過期間保險費後，將剩餘未到期保險費無息退還給要保人。
+條文依據：  
+- [第九條 契約的終止（一）]</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t>第九條 契約的終止（一） | 第十五條 不保事項 | 第五條 契約有效期間及保證續保 | 第七條 本契約效力的恢復 | 第六條 續保保險費的交付、寬限期間及契約效力的停止 | 附表二：短期費率表</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F224" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+要保人可以終止契約，並可退還未到期保險費。本公司會從已繳保險費中扣除按短期費率計算的已經過期間保險費後，將剩餘未到期保險費無息退還給要保人。
+條文依據：  
+- [第九條 契約的終止（一）]</t>
+        </is>
+      </c>
+      <c r="G224" s="2" t="inlineStr"/>
+      <c r="H224" s="2" t="inlineStr"/>
+      <c r="I224" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "要保人想要終止國泰人壽自由配CFE契約，能否退保費?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J224" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K224" s="4" t="n"/>
+      <c r="L224" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:57:41</t>
+        </is>
+      </c>
+      <c r="N224" s="4" t="n">
+        <v>8.300000000000001</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>CFE</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>投保國泰人壽自由配CFE，若在等待期間內罹患重大傷病，要如何給付?</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在等待期間內罹患重大傷病，依條款規定，因意外傷害事故所致的重大傷病不受等待期間限制，仍可申請給付重大傷病保險金。但若因其他原因（非意外傷害事故）罹患重大傷病，則本契約自始無效，保險公司僅退還已繳保險費且不計利息。  
+條文依據：  
+- [第十一條 重大傷病保險金的給付]  
+- [第十五條 不保事項]</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 重大傷病保險金的給付 | 附表一：全民健康保險重大傷病項目 | 第十五條 不保事項 | 第十四條 除外責任 | payout_items | other_metadata</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F225" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在等待期間內罹患重大傷病，依條款規定，因意外傷害事故所致的重大傷病不受等待期間限制，仍可申請給付重大傷病保險金。但若因其他原因（非意外傷害事故）罹患重大傷病，則本契約自始無效，保險公司僅退還已繳保險費且不計利息。  
+條文依據：  
+- [第十一條 重大傷病保險金的給付]  
+- [第十五條 不保事項]</t>
+        </is>
+      </c>
+      <c r="G225" s="2" t="inlineStr"/>
+      <c r="H225" s="2" t="inlineStr"/>
+      <c r="I225" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認國泰人壽自由配CFE的等待期間規定", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認重大傷病是否符合保單條款中的定義", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認等待期間內重大傷病的給付條件或限制", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認是否有其他附加條款影響給付", "must_have": false, "分數": 0.8}], "coverage_score": 0.9846, "C_conf": 0.9846}</t>
+        </is>
+      </c>
+      <c r="J225" s="4" t="n">
+        <v>0.9846</v>
+      </c>
+      <c r="K225" s="4" t="n"/>
+      <c r="L225" s="4" t="n">
+        <v>0.9846</v>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:57:57</t>
+        </is>
+      </c>
+      <c r="N225" s="4" t="n">
+        <v>15.69</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>CFE</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>投保自由配一年定期初次罹患重大傷病健康保險後，於第三年罹患先天性肌肉萎縮症，可以申領重大傷病保險金嗎？</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款內容，先天性肌肉萎縮症屬於「重大傷病範圍」的排除項目，因此無法申領重大傷病保險金。此外，保險期間為一年，若要保人已按規定交付續保保險費且契約仍在有效期間內，本公司仍負保險責任。  
+條文依據：  
+- [第二條 名詞定義]  
+- [第五條 契約有效期間及保證續保]</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
+        <is>
+          <t>第五條 契約有效期間及保證續保 | 第二條 名詞定義 | 第六條 續保保險費的交付、寬限期間及契約效力的停止 | 第十條 契約的終止（二） | 附表一：全民健康保險重大傷病項目 | 第四條 保險範圍 | 第十八條 投保年齡的計算及錯誤的處理 | 第十一條 重大傷病保險金的給付 | 第九條 契約的終止（一） | 附表二：短期費率表 | other_metadata</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F226" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款內容，先天性肌肉萎縮症不屬於「全民健康保險重大傷病項目」的保障範圍，因此無法申領重大傷病保險金。此外，條款中未提及對先天性疾病的特別除外責任或限制，但因該疾病不在保障範圍內，仍無法申領保險金。
+條文依據：  
+- [附表一：全民健康保險重大傷病項目]</t>
+        </is>
+      </c>
+      <c r="G226" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款內容，先天性肌肉萎縮症屬於「重大傷病範圍」的排除項目，因此無法申領重大傷病保險金。此外，保險期間為一年，若要保人已按規定交付續保保險費且契約仍在有效期間內，本公司仍負保險責任。  
+條文依據：  
+- [第二條 名詞定義]  
+- [第五條 契約有效期間及保證續保]</t>
+        </is>
+      </c>
+      <c r="H226" s="2" t="inlineStr"/>
+      <c r="I226" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認自由配一年定期重大傷病健康保險的保障範圍是否包含先天性肌肉萎縮症", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認保單是否對先天性疾病有除外責任或限制", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認保險是否仍在有效期間內", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認重大傷病保險金的申領條件與程序", "must_have": false, "分數": 0.5}], "coverage_score": 0.9615, "C_conf": 0.9615}</t>
+        </is>
+      </c>
+      <c r="J226" s="4" t="n">
+        <v>0.9615</v>
+      </c>
+      <c r="K226" s="4" t="n"/>
+      <c r="L226" s="4" t="n">
+        <v>0.9615</v>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:58:27</t>
+        </is>
+      </c>
+      <c r="N226" s="4" t="n">
+        <v>29.5</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>CFG</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>自由配重大疾病(甲型)保障的重大疾病有哪些疾病?</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+自由配重大疾病(甲型)保障的重大疾病包括以下疾病：  
+1. 腦中風後障礙(重度)  
+2. 癱瘓(重度)  
+3. 癌症(重度)  
+4. 急性心肌梗塞(重度)  
+5. 冠狀動脈繞道手術  
+6. 末期腎病變  
+7. 重大器官移植或造血幹細胞移植  
+條文依據：  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
+        <is>
+          <t>國泰人壽自由配一年定期初次罹患重大疾病健康保險(甲型)年繳費率表 | payout_items | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F227" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+自由配重大疾病(甲型)保障的重大疾病包括以下疾病：  
+1. 腦中風後障礙(重度)  
+2. 癱瘓(重度)  
+3. 癌症(重度)  
+4. 急性心肌梗塞(重度)  
+5. 冠狀動脈繞道手術  
+6. 末期腎病變  
+7. 重大器官移植或造血幹細胞移植  
+條文依據：  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G227" s="2" t="inlineStr"/>
+      <c r="H227" s="2" t="inlineStr"/>
+      <c r="I227" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "自由配重大疾病(甲型)保障的重大疾病有哪些疾病?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J227" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K227" s="4" t="n"/>
+      <c r="L227" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:58:34</t>
+        </is>
+      </c>
+      <c r="N227" s="4" t="n">
+        <v>6.86</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>被保險人領了2次癌症(重度)追蹤照護金後身故，是否還有尚未給付的保險金供受益人領取?</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 被保險人已領取2次「癌症(重度)追蹤照護保險金」，根據第十四條規定，此項保險金最多給付5年，因此尚有3次的給付額度未使用，但因被保險人已身故，該項保險金的給付責任即終止。  
+2. 條款未明確規定是否包含身故保險金保障，無法確認是否有此項保障。  
+3. 條款中其他可能尚未給付的保險金項目包括：  
+   - 「初次罹患癌症(重度)保險金」（第十三條），但此項保險金僅限給付一次，需確認是否已申領過。  
+   - 「癌症(重度)標靶藥物治療輔助保險金」（第十五條），需確認是否符合條件並已申領。  
+   - 「癌症(重度)豁免保險費」（第十六條），此項豁免僅適用於被保險人生存期間，身故後不適用。  
+條文依據：  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]  
+- [第十三條 初次罹患癌症(重度)保險金的給付]  
+- [第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用)]  
+- [第十六條 癌症(重度)豁免保險費(第二保險單年度起適用)]  
+- [第二十八條 受益人]  
+- [第十一條 契約的終止（三)]</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
+        <is>
+          <t>第二十八條 受益人 | 第十一條 契約的終止（三） | 第二十三條 癌症保險金或罹癌基因檢測服務的申領 | 第二十二條 保險事故的通知與保險給付的申請時間 | 第五條 保險範圍 | 第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用) | 第十三條 初次罹患癌症(重度)保險金的給付 | 附件一：罹癌基因檢測服務之項目、服務費用及補償金額表 | payout_items | other_metadata</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F228" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 被保險人已領取2次「癌症(重度)追蹤照護保險金」，根據第十四條規定，此項保險金最多給付5年，因此尚有3次的給付額度未使用，但因被保險人已身故，該項保險金的給付責任即終止。  
+2. 提供的條款中未提及身故保險金保障，因此無法確認是否有此項保障。  
+3. 條款中其他可能尚未給付的保險金項目包括：  
+   - 「初次罹患癌症(重度)保險金」（第十三條），但此項保險金僅限給付一次，需確認是否已申領過。  
+   - 「癌症(重度)標靶藥物治療輔助保險金」（第十五條），需確認是否符合條件並已申領。  
+   - 「癌症(重度)豁免保險費」（第十六條），此項豁免僅適用於被保險人生存期間，身故後不適用。  
+條文依據：  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]  
+- [第十三條 初次罹患癌症(重度)保險金的給付]  
+- [第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用)]  
+- [第十六條 癌症(重度)豁免保險費(第二保險單年度起適用)]  
+- [第二十三條 癌症保險金或罹癌基因檢測服務的申領]</t>
+        </is>
+      </c>
+      <c r="G228" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 被保險人已領取2次「癌症(重度)追蹤照護保險金」，根據第十四條規定，此項保險金最多給付5年，因此尚有3次的給付額度未使用，但因被保險人已身故，該項保險金的給付責任即終止。  
+2. 條款未明確規定是否包含身故保險金保障，無法確認是否有此項保障。  
+3. 條款中其他可能尚未給付的保險金項目包括：  
+   - 「初次罹患癌症(重度)保險金」（第十三條），但此項保險金僅限給付一次，需確認是否已申領過。  
+   - 「癌症(重度)標靶藥物治療輔助保險金」（第十五條），需確認是否符合條件並已申領。  
+   - 「癌症(重度)豁免保險費」（第十六條），此項豁免僅適用於被保險人生存期間，身故後不適用。  
+條文依據：  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]  
+- [第十三條 初次罹患癌症(重度)保險金的給付]  
+- [第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用)]  
+- [第十六條 癌症(重度)豁免保險費(第二保險單年度起適用)]  
+- [第二十八條 受益人]  
+- [第十一條 契約的終止（三)]</t>
+        </is>
+      </c>
+      <c r="H228" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 被保險人已領取2次「癌症(重度)追蹤照護保險金」，根據第十四條規定，此項保險金最多給付5年，因此尚有3次的給付額度未使用，但因被保險人已身故，該項保險金的給付責任即終止。  
+2. 條款未明確規定是否包含身故保險金保障，無法確認是否有此項保障。  
+3. 條款中其他可能尚未給付的保險金項目包括：  
+   - 「初次罹患癌症(重度)保險金」（第十三條），但此項保險金僅限給付一次，需確認是否已申領過。  
+   - 「癌症(重度)標靶藥物治療輔助保險金」（第十五條），需確認是否符合條件並已申領。  
+   - 「癌症(重度)豁免保險費」（第十六條），此項豁免僅適用於被保險人生存期間，身故後不適用。  
+條文依據：  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]  
+- [第十三條 初次罹患癌症(重度)保險金的給付]  
+- [第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用)]  
+- [第十六條 癌症(重度)豁免保險費(第二保險單年度起適用)]  
+- [第二十八條 受益人]  
+- [第十一條 契約的終止（三)]</t>
+        </is>
+      </c>
+      <c r="I228" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認被保險人已領取的癌症(重度)追蹤照護金次數及金額", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認保單是否包含身故保險金保障", "must_have": true, "分數": 0.5}, {"id": "3", "point": "確認保單條款中其他可能尚未給付的保險金項目", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認保單是否有針對癌症相關保障的累計給付上限", "must_have": false, "分數": 0.5}, {"id": "5", "point": "確認受益人是否符合領取保險金的資格", "must_have": false, "分數": 0.0}], "coverage_score": 0.75, "C_conf": 0.75}</t>
+        </is>
+      </c>
+      <c r="J228" s="5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K228" s="4" t="n"/>
+      <c r="L228" s="5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:59:21</t>
+        </is>
+      </c>
+      <c r="N228" s="4" t="n">
+        <v>47.75</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>保險金額2萬元，「罹癌基因檢測服務」費用8萬元，還會給付多少「癌症(重度)追蹤照護保險金」？</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款，若被保險人選擇申領「罹癌基因檢測服務」，且該服務費用（8萬元）高於「罹癌基因檢測服務額度」（1,000元），則被保險人僅能申領「癌症(重度)追蹤照護保險金」。因此，保險公司將依保險金額的12倍給付「癌症(重度)追蹤照護保險金」，即2萬元 × 12 = 24萬元。  
+條文依據：  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用) | 附件一：罹癌基因檢測服務之項目、服務費用及補償金額表 | 第二十三條 癌症保險金或罹癌基因檢測服務的申領 | 第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用) | payout_items | 第十三條 初次罹患癌症(重度)保險金的給付 | other_metadata | 第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F229" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款，若被保險人選擇申領「罹癌基因檢測服務」，且該服務費用（8萬元）高於「罹癌基因檢測服務額度」（1,000元），則被保險人僅能申領「癌症(重度)追蹤照護保險金」。因此，保險公司將依保險金額的12倍給付「癌症(重度)追蹤照護保險金」，即2萬元 × 12 = 24萬元。  
+條文依據：  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]</t>
+        </is>
+      </c>
+      <c r="G229" s="2" t="inlineStr"/>
+      <c r="H229" s="2" t="inlineStr"/>
+      <c r="I229" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認癌症(重度)追蹤照護保險金的保險金額為2萬元", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認罹癌基因檢測服務費用為8萬元", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認罹癌基因檢測服務是否屬於癌症(重度)追蹤照護保險金的給付範圍", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認保險條款中是否有其他扣除或限制規定", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J229" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K229" s="4" t="n"/>
+      <c r="L229" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:00:04</t>
+        </is>
+      </c>
+      <c r="N229" s="4" t="n">
+        <v>42.84</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>投保後1個月罹患重度癌症，會給付哪些保險金？契約還會持續有效嗎？</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 若被保險人在投保後1個月內診斷確定罹患重度癌症，因診斷確定日屬於第一保險單年度內，僅可申領「初次罹患癌症(重度)保險金」，給付金額為「年繳應繳保險費」的1.06倍。  
+2. 契約仍會持續有效，但當期已繳付之未到期保險費將不予退還，且續期保險費不會豁免。
+條文依據：  
+- [第十三條 初次罹患癌症(重度)保險金的給付]  
+- [第十六條 癌症(重度)豁免保險費(第二保險單年度起適用)]</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 癌症(重度)豁免保險費(第二保險單年度起適用) | 第十三條 初次罹患癌症(重度)保險金的給付 | 第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用) | 第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付 | 第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用)</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F230" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 若被保險人在投保後1個月內診斷確定罹患重度癌症，因診斷確定日屬於第一保險單年度內，僅可申領「初次罹患癌症(重度)保險金」，給付金額為「年繳應繳保險費」的1.06倍。  
+2. 契約仍會持續有效，但當期已繳付之未到期保險費將不予退還，且續期保險費不會豁免。
+條文依據：  
+- [第十三條 初次罹患癌症(重度)保險金的給付]  
+- [第十六條 癌症(重度)豁免保險費(第二保險單年度起適用)]</t>
+        </is>
+      </c>
+      <c r="G230" s="2" t="inlineStr"/>
+      <c r="H230" s="2" t="inlineStr"/>
+      <c r="I230" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "投保後1個月罹患重度癌症，會給付哪些保險金？契約還會持續有效嗎？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J230" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K230" s="4" t="n"/>
+      <c r="L230" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:00:14</t>
+        </is>
+      </c>
+      <c r="N230" s="4" t="n">
+        <v>9.300000000000001</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>投保後10個月罹患重度癌症，會給付哪些保險金？契約還會持續有效嗎？</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 投保後10個月罹患重度癌症，若符合「初次診斷確定罹患癌症(重度)」，可獲得「初次罹患癌症(重度)保險金」，金額為「保險金額」的十二倍。  
+2. 契約仍會持續有效，且自診斷確定日起，續期保險費將被豁免，但當期已繳付之未到期保險費不予退還。
+條文依據：  
+- [第十三條 初次罹患癌症(重度)保險金的給付]  
+- [第十六條 癌症(重度)豁免保險費(第二保險單年度起適用)]</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 癌症(重度)豁免保險費(第二保險單年度起適用) | 第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用) | 第十條 契約的終止（二） | 第十三條 初次罹患癌症(重度)保險金的給付 | 第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F231" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 投保後10個月罹患重度癌症，若符合「初次診斷確定罹患癌症(重度)」，可獲得「初次罹患癌症(重度)保險金」，金額為「保險金額」的十二倍。  
+2. 契約仍會持續有效，且自診斷確定日起，續期保險費將被豁免，但當期已繳付之未到期保險費不予退還。
+條文依據：  
+- [第十三條 初次罹患癌症(重度)保險金的給付]  
+- [第十六條 癌症(重度)豁免保險費(第二保險單年度起適用)]</t>
+        </is>
+      </c>
+      <c r="G231" s="2" t="inlineStr"/>
+      <c r="H231" s="2" t="inlineStr"/>
+      <c r="I231" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "投保後10個月罹患重度癌症，會給付哪些保險金？契約還會持續有效嗎？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J231" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K231" s="4" t="n"/>
+      <c r="L231" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:00:22</t>
+        </is>
+      </c>
+      <c r="N231" s="4" t="n">
+        <v>7.89</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>投保醫心康愛，罹患肺癌一期，可領什麼保險金？</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人於本契約有效期間內，初次診斷確定罹患肺癌一期，屬於「癌症(初期)或癌症(輕度)」，可申領「初次罹患癌症(初期)或癌症(輕度)保險金」。給付金額依診斷確定日所在的保險單年度而定：  
+1. 若診斷確定日在第一保險單年度內，給付「年繳應繳保險費」的1.06倍。  
+2. 若診斷確定日在第二保險單年度(含)以後，給付「保險金額」的5倍。  
+條文依據：  
+- [第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付 | 第十三條 初次罹患癌症(重度)保險金的給付 | payout_items | 第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用) | 第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F232" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人於本契約有效期間內，初次診斷確定罹患肺癌一期，屬於「癌症(初期)或癌症(輕度)」，可申領「初次罹患癌症(初期)或癌症(輕度)保險金」。給付金額依診斷確定日所在的保險單年度而定：  
+1. 若診斷確定日在第一保險單年度內，給付「年繳應繳保險費」的1.06倍。  
+2. 若診斷確定日在第二保險單年度(含)以後，給付「保險金額」的5倍。  
+條文依據：  
+- [第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G232" s="2" t="inlineStr"/>
+      <c r="H232" s="2" t="inlineStr"/>
+      <c r="I232" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "投保醫心康愛，罹患肺癌一期，可領什麼保險金？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J232" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K232" s="4" t="n"/>
+      <c r="L232" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:00:31</t>
+        </is>
+      </c>
+      <c r="N232" s="4" t="n">
+        <v>7.78</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>PX5</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>若被保險人身故有何給付?</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人身故時，若本附約保險金尚未給付或未完全給付，則該部分保險金的受益人為被保險人的法定繼承人，並依民法繼承編的相關規定確定受益順序及應得比例。
+條文依據：  
+- [第二十條 受益人]</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="inlineStr">
+        <is>
+          <t>第二十條 受益人 | 第十二條 重大疾病保險金的給付 | 第十一條 輕度重大疾病保險金的給付 | 第十四條 保險事故的通知與保險金的申請時間 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F233" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人身故時，若本附約保險金尚未給付或未完全給付，則該部分保險金的受益人為被保險人的法定繼承人，並依民法繼承編的相關規定確定受益順序及應得比例。
+條文依據：  
+- [第二十條 受益人]</t>
+        </is>
+      </c>
+      <c r="G233" s="2" t="inlineStr"/>
+      <c r="H233" s="2" t="inlineStr"/>
+      <c r="I233" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "若被保險人身故有何給付?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J233" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K233" s="4" t="n"/>
+      <c r="L233" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:00:38</t>
+        </is>
+      </c>
+      <c r="N233" s="4" t="n">
+        <v>7.11</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>PX5</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>投保鍾溢祝福後，請問在第二年經醫院醫師初次診斷罹患「輕度重大疾病」中的癌症(輕度)者，可以領到輕度重大疾病保險金嗎?可以領到保險金額的百分之多少?</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+投保鍾溢祝福後，若在第二年經醫院醫師初次診斷罹患「輕度重大疾病」中的癌症(輕度)，可以領取輕度重大疾病保險金，給付比例為保險金額的百分之二十。
+條文依據：  
+- [第十一條 輕度重大疾病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 輕度重大疾病保險金的給付 | 第十二條 重大疾病保險金的給付 | other_metadata | payout_items | 國泰人壽鍾溢祝福重大疾病健康保險附約(乙型) (外溢型)年繳費率表 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F234" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+投保鍾溢祝福後，若在第二年經醫院醫師初次診斷罹患「輕度重大疾病」中的癌症(輕度)，可以領取輕度重大疾病保險金，給付比例為保險金額的百分之二十。
+條文依據：  
+- [第十一條 輕度重大疾病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G234" s="2" t="inlineStr"/>
+      <c r="H234" s="2" t="inlineStr"/>
+      <c r="I234" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認保單是否涵蓋輕度重大疾病保障", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認輕度重大疾病保障是否包含輕度癌症", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認輕度重大疾病保險金的給付比例或金額", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認是否符合第二年初次診斷的理賠條件", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J234" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K234" s="4" t="n"/>
+      <c r="L234" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:00:50</t>
+        </is>
+      </c>
+      <c r="N234" s="4" t="n">
+        <v>11.89</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>PX5</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>請問如果在投保後的第三年經醫院醫師初次診斷罹患「重大疾病」者，可以領到重大疾病保險金嗎?可以領到保險金額的百分之多少?那後續又在第四年經醫院醫師初次診斷罹患「輕度重大疾病」者，可以領到輕度重大疾病保險金嗎?可以領到保險金額的百分之多少?</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 在投保後的第三年，若經醫院醫師初次診斷罹患「重大疾病」，可以領取重大疾病保險金，給付比例為保險金額的1.3倍。  
+2. 在第四年，若經醫院醫師初次診斷罹患「輕度重大疾病」，可以領取輕度重大疾病保險金，給付比例為保險金額的20%。  
+條文依據：  
+- [第十二條 重大疾病保險金的給付]  
+- [第十一條 輕度重大疾病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 輕度重大疾病保險金的給付 | 第十二條 重大疾病保險金的給付 | 第十六條 除外責任 | payout_items | 第二條 名詞定義 | 第四條 保險範圍 | other_metadata | 國泰人壽鍾溢祝福重大疾病健康保險附約(乙型) (外溢型)年繳費率表</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F235" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 在投保後的第三年，若經醫院醫師初次診斷罹患「重大疾病」，可以領取重大疾病保險金，給付比例為保險金額的1.3倍。  
+2. 在第四年，若經醫院醫師初次診斷罹患「輕度重大疾病」，可以領取輕度重大疾病保險金，給付比例為保險金額的20%。  
+條文依據：  
+- [第十二條 重大疾病保險金的給付]  
+- [第十一條 輕度重大疾病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G235" s="2" t="inlineStr"/>
+      <c r="H235" s="2" t="inlineStr"/>
+      <c r="I235" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認重大疾病保險金是否涵蓋第三年初次診斷的重大疾病", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認重大疾病保險金額的給付比例", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認輕度重大疾病保險金是否涵蓋第四年初次診斷的輕度重大疾病", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認輕度重大疾病保險金額的給付比例", "must_have": true, "分數": 1.0}, {"id": "5", "point": "確認重大疾病與輕度重大疾病的定義及區分標準", "must_have": false, "分數": 0.0}], "coverage_score": 0.9412, "C_conf": 0.9412}</t>
+        </is>
+      </c>
+      <c r="J235" s="4" t="n">
+        <v>0.9412</v>
+      </c>
+      <c r="K235" s="4" t="n"/>
+      <c r="L235" s="4" t="n">
+        <v>0.9412</v>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:01:03</t>
+        </is>
+      </c>
+      <c r="N235" s="4" t="n">
+        <v>12.6</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>PX5</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>請問如果在投保後的第三年經醫院醫師初次診斷罹患「輕度重大疾病」者，可以領到重大疾病保險金嗎?可以領到保險金額的百分之多少?那後續又在第四年經醫院醫師初次診斷罹患「重大疾病」者，可以領到輕度重大疾病保險金嗎?可以領到保險金額的百分之多少?</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 在投保後的第三年，若被保險人經醫院醫師初次診斷罹患「輕度重大疾病」，符合條款中的理賠條件，可領取「輕度重大疾病保險金」，給付比例為保險金額的20%。  
+2. 在第四年，若被保險人經醫院醫師初次診斷罹患「重大疾病」，符合條款中的理賠條件，但因條款規定「重大疾病保險金」需扣除已領取的「輕度重大疾病保險金」，因此可領取的比例為保險金額的130%減去已領取的20%，即保險金額的110%。  
+3. 條款規定「輕度重大疾病保險金」終身最多給付一次，因此在第四年罹患「重大疾病」後，無法再領取「輕度重大疾病保險金」。
+條文依據：  
+- [第十一條 輕度重大疾病保險金的給付]  
+- [第十二條 重大疾病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 輕度重大疾病保險金的給付 | 第十二條 重大疾病保險金的給付 | 第十六條 除外責任 | payout_items | 第二條 名詞定義 | 第四條 保險範圍 | other_metadata | 第十五條 各項保險金的申領</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F236" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 在投保後的第三年，若被保險人經醫院醫師初次診斷罹患「輕度重大疾病」，符合條款中的理賠條件，可領取「輕度重大疾病保險金」，給付比例為保險金額的20%。  
+2. 在第四年，若被保險人經醫院醫師初次診斷罹患「重大疾病」，符合條款中的理賠條件，但因條款規定「重大疾病保險金」需扣除已領取的「輕度重大疾病保險金」，因此可領取的比例為保險金額的130%減去已領取的20%，即保險金額的110%。  
+3. 條款規定「輕度重大疾病保險金」終身最多給付一次，因此在第四年罹患「重大疾病」後，無法再領取「輕度重大疾病保險金」。
+條文依據：  
+- [第十一條 輕度重大疾病保險金的給付]  
+- [第十二條 重大疾病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G236" s="2" t="inlineStr"/>
+      <c r="H236" s="2" t="inlineStr"/>
+      <c r="I236" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認輕度重大疾病是否符合保單條款中的理賠條件", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認輕度重大疾病保險金的給付比例或金額", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認重大疾病是否符合保單條款中的理賠條件", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認重大疾病保險金的給付比例或金額", "must_have": true, "分數": 1.0}, {"id": "5", "point": "確認罹患重大疾病後是否仍可領取輕度重大疾病保險金", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J236" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K236" s="4" t="n"/>
+      <c r="L236" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:01:28</t>
+        </is>
+      </c>
+      <c r="N236" s="4" t="n">
+        <v>24.78</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>PX5</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>請問主約效力終止(因身故以外情形)，PX5還能持續有效嗎？</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+主約效力因身故以外的情形終止時，PX5附約仍可持續有效，但需符合以下條件：  
+1. 要保人需繼續繳交附約保險費。  
+2. 附約效力可延續至主約原保險期間屆滿或附約最高續保年齡（以較早者為準）。  
+條文依據：  
+- [第十條 附約的終止（二）]</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
+        <is>
+          <t>第十條 附約的終止（二） | 第七條 保險費的墊繳、附約的停效及復效 | 第五條 附約的保險期間及保證續保 | 第十三條 健康促進保險費折減 | 第九條 附約的終止（一）</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F237" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+主約效力因身故以外的情形終止時，PX5附約仍可持續有效，但需符合以下條件：  
+1. 要保人需繼續繳交附約保險費。  
+2. 附約效力可延續至主約原保險期間屆滿或附約最高續保年齡（以較早者為準）。  
+條文依據：  
+- [第十條 附約的終止（二）]</t>
+        </is>
+      </c>
+      <c r="G237" s="2" t="inlineStr"/>
+      <c r="H237" s="2" t="inlineStr"/>
+      <c r="I237" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "請問主約效力終止(因身故以外情形)，PX5還能持續有效嗎？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J237" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K237" s="4" t="n"/>
+      <c r="L237" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:01:40</t>
+        </is>
+      </c>
+      <c r="N237" s="4" t="n">
+        <v>12.26</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>請問如果於「無理賠紀錄期間」屆滿日以內罹患特定傷病，會給付多少錢?這筆錢會給付給誰?</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在「無理賠紀錄期間」屆滿日以內罹患特定傷病，保險公司將給付的金額為「保險金額」加上「年繳應繳保險費總額」乘以1.02的加總。這筆「特定傷病保險金」的受益人為被保險人本人，且不得指定或變更。
+條文依據：  
+- [第十一條 特定傷病保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第十二條 無理賠關懷保險金的給付 | 第十一條 特定傷病保險金的給付 | payout_items | 第二十七條 受益人的指定及變更</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F238" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在「無理賠紀錄期間」屆滿日以內罹患特定傷病，保險公司將給付的金額為「保險金額」加上「年繳應繳保險費總額」乘以1.02的加總。這筆「特定傷病保險金」的受益人為被保險人本人，且不得指定或變更。
+條文依據：  
+- [第十一條 特定傷病保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="G238" s="2" t="inlineStr"/>
+      <c r="H238" s="2" t="inlineStr"/>
+      <c r="I238" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "請問如果於「無理賠紀錄期間」屆滿日以內罹患特定傷病，會給付多少錢?這筆錢會給付給誰?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J238" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K238" s="4" t="n"/>
+      <c r="L238" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:01:51</t>
+        </is>
+      </c>
+      <c r="N238" s="4" t="n">
+        <v>10.46</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>請問如果要保人與被保險人為同一人，被保險人於「無理賠紀錄期間」屆滿日以內身故，會給付多少錢?這筆錢會給付給誰?</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若要保人與被保險人為同一人，且被保險人在「無理賠紀錄期間」屆滿日以內身故，依第十二條規定，本公司將給付「無理賠關懷保險金」，金額為「年繳應繳保險費總額」乘以1.02。根據第二十七條，無理賠關懷保險金的受益人為要保人本人，但因要保人與被保險人為同一人，且被保險人已身故，則受益人為被保險人的法定繼承人。
+條文依據：  
+- [第十二條 無理賠關懷保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第十二條 無理賠關懷保險金的給付 | 第十一條 特定傷病保險金的給付 | payout_items | 第十九條 失蹤處理 | 第二十一條 無理賠關懷保險金的申領 | 第二十七條 受益人的指定及變更 | 第十七條 除外責任（二）</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F239" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若要保人與被保險人為同一人，且被保險人在「無理賠紀錄期間」屆滿日以內身故，依第十二條規定，本公司將給付「無理賠關懷保險金」，金額為「年繳應繳保險費總額」乘以1.02。根據第二十七條，無理賠關懷保險金的受益人為要保人本人，但因要保人與被保險人為同一人，且被保險人已身故，則受益人為被保險人的法定繼承人。
+條文依據：  
+- [第十二條 無理賠關懷保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="G239" s="2" t="inlineStr"/>
+      <c r="H239" s="2" t="inlineStr"/>
+      <c r="I239" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認要保人與被保險人為同一人時的理賠規定", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認被保險人在無理賠紀錄期間屆滿日以內身故的保險金額", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認身故保險金的受益人為何人", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認無理賠紀錄期間的定義與適用條件", "must_have": false, "分數": 0.8}], "coverage_score": 0.9846, "C_conf": 0.9846}</t>
+        </is>
+      </c>
+      <c r="J239" s="4" t="n">
+        <v>0.9846</v>
+      </c>
+      <c r="K239" s="4" t="n"/>
+      <c r="L239" s="4" t="n">
+        <v>0.9846</v>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:02:09</t>
+        </is>
+      </c>
+      <c r="N239" s="4" t="n">
+        <v>18.33</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>請問如果要保人與被保險人為不同人，被保險人於「無理賠紀錄期間」屆滿日以內生存，且被保險人未罹患特定傷病，會給付多少錢?這筆錢會給付給誰?</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若要保人與被保險人為不同人，且被保險人在「無理賠紀錄期間」屆滿日以內生存，並未罹患特定傷病，則本公司將給付「無理賠關懷保險金」。該金額為「年繳應繳保險費總額」乘以1.02。此筆保險金的受益人為要保人本人。
+條文依據：  
+- [第十二條 無理賠關懷保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第十二條 無理賠關懷保險金的給付 | 第十一條 特定傷病保險金的給付 | payout_items | 第二十七條 受益人的指定及變更 | 第十九條 失蹤處理 | 第二十一條 無理賠關懷保險金的申領 | 第十七條 除外責任（二）</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F240" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若要保人與被保險人為不同人，且被保險人在「無理賠紀錄期間」屆滿日以內生存，並未罹患特定傷病，則本公司將給付「無理賠關懷保險金」。該金額為「年繳應繳保險費總額」乘以1.02。此筆保險金的受益人為要保人本人。
+條文依據：  
+- [第十二條 無理賠關懷保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="G240" s="2" t="inlineStr"/>
+      <c r="H240" s="2" t="inlineStr"/>
+      <c r="I240" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認要保人與被保險人為不同人時的保險條款適用", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認無理賠紀錄期間屆滿日以內生存的給付金額", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認被保險人未罹患特定傷病的條件下的給付金額", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認該筆給付金的受益人為何人", "must_have": true, "分數": 1.0}, {"id": "5", "point": "確認特定傷病的定義與範圍", "must_have": false, "分數": 0.0}], "coverage_score": 0.9412, "C_conf": 0.9412}</t>
+        </is>
+      </c>
+      <c r="J240" s="4" t="n">
+        <v>0.9412</v>
+      </c>
+      <c r="K240" s="4" t="n"/>
+      <c r="L240" s="4" t="n">
+        <v>0.9412</v>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:02:22</t>
+        </is>
+      </c>
+      <c r="N240" s="4" t="n">
+        <v>13.21</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>保戶如果身故，會給保險金嗎?</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保戶（被保險人）若於契約有效期間內身故，是否給付保險金需視具體情況而定。例如：  
+1. 若被保險人於「無理賠紀錄期間」內身故，本公司依約定給付保險金。  
+2. 若被保險人因犯罪處死、拒捕或越獄致死，或要保人故意致被保險人於死，則本公司不負給付保險金的責任。  
+3. 若被保險人故意自殺，則需契約訂立或復效滿二年後，本公司才負給付保險金的責任。  
+條文依據：  
+- [第五條 保險範圍]  
+- [第十七條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第二十八條 本契約受益人死亡或失蹤的處理 | 第十七條 除外責任（二） | 第二十三條 受益人受益權之喪失 | 第十九條 失蹤處理</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F241" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保戶（被保險人）若於契約有效期間內身故，是否給付保險金需視具體情況而定。例如：  
+1. 若被保險人於「無理賠紀錄期間」內身故，本公司依約定給付保險金。  
+2. 若被保險人因犯罪處死、拒捕或越獄致死，或要保人故意致被保險人於死，則本公司不負給付保險金的責任。  
+3. 若被保險人故意自殺，則需契約訂立或復效滿二年後，本公司才負給付保險金的責任。  
+條文依據：  
+- [第五條 保險範圍]  
+- [第十七條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="G241" s="2" t="inlineStr"/>
+      <c r="H241" s="2" t="inlineStr"/>
+      <c r="I241" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "保戶如果身故，會給保險金嗎?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J241" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K241" s="4" t="n"/>
+      <c r="L241" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:02:31</t>
+        </is>
+      </c>
+      <c r="N241" s="4" t="n">
+        <v>8.41</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>保戶如果身故，身故申領的保險金會給誰?</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人身故，身故保險金的受益人依以下情況處理：  
+1. 若受益人已指定，則由指定的受益人領取。  
+2. 若受益人未指定或受益人喪失受益權，則保險金作為被保險人的遺產，由其法定繼承人依民法繼承編相關規定分配。  
+條文依據：  
+- [第二十三條 受益人受益權之喪失]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第二十三條 受益人受益權之喪失 | 第二十七條 受益人的指定及變更 | 第二十八條 本契約受益人死亡或失蹤的處理 | 第二十二條 分期定期保險金給付申領文件、給付期限及未依限給付之效果</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F242" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人身故，身故保險金的受益人依以下情況處理：  
+1. 若受益人已指定，則由指定的受益人領取。  
+2. 若受益人未指定或受益人喪失受益權，則保險金作為被保險人的遺產，由其法定繼承人依民法繼承編相關規定分配。  
+條文依據：  
+- [第二十三條 受益人受益權之喪失]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="G242" s="2" t="inlineStr"/>
+      <c r="H242" s="2" t="inlineStr"/>
+      <c r="I242" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "保戶如果身故，身故申領的保險金會給誰?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J242" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K242" s="4" t="n"/>
+      <c r="L242" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:02:42</t>
+        </is>
+      </c>
+      <c r="N242" s="4" t="n">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>如果保戶投保繳費年期20年的滿溢寶，然後在第20保單年度身故的話，可以領到多少錢?</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款內容，若保戶於第20保單年度身故，且符合「無理賠紀錄期間」內身故的條件，則本公司將依照契約約定給付保險金。具體金額需依保單內的保險金額及相關條件計算。條款中未明確提及第20保單年度身故的特定金額計算方式，因此需參考保單詳細內容進一步確認。
+條文依據：  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
+        <is>
+          <t>other_metadata | 第二十八條 本契約受益人死亡或失蹤的處理 | 第二十六條 投保年齡的計算及錯誤的處理 | 第十一條 特定傷病保險金的給付 | 第二十二條 分期定期保險金給付申領文件、給付期限及未依限給付之效果 | 第五條 保險範圍 | 第十五條 健康促進保險費折減 | 第十九條 失蹤處理</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F243" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款內容，若保戶於第20保單年度身故，且符合「無理賠紀錄期間」內身故的條件，則本公司將依照契約約定給付保險金。具體金額需依保單內的保險金額及相關條件計算。條款中未明確提及第20保單年度身故的特定金額計算方式，因此需參考保單詳細內容進一步確認。
+條文依據：  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="G243" s="2" t="inlineStr"/>
+      <c r="H243" s="2" t="inlineStr"/>
+      <c r="I243" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認滿溢寶的保險內容與保障範圍", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認第20保單年度身故的保險金給付規則", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認保戶已完成20年繳費年期的狀況", "must_have": false, "分數": 0.5}], "coverage_score": 0.9444, "C_conf": 0.9444}</t>
+        </is>
+      </c>
+      <c r="J243" s="4" t="n">
+        <v>0.9444</v>
+      </c>
+      <c r="K243" s="4" t="n"/>
+      <c r="L243" s="4" t="n">
+        <v>0.9444</v>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:02:57</t>
+        </is>
+      </c>
+      <c r="N243" s="4" t="n">
+        <v>14.41</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>被保險人為60歲女性，投保繳費期間20年期之滿溢寶特定傷病定期健康保險（定期給付型）（外溢型）100萬元，年繳應繳保險費為83,500元，年繳實繳保險費為78,490元。若被保險人於第二保險單年度自殺身故，則無理賠關懷保險金可以領到多少錢？</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於第二保險單年度內自殺身故，根據條款規定，自契約訂立或復效之日起二年內因故意自殺致死者，本公司不負給付無理賠關懷保險金的責任。因此，本案例中無理賠關懷保險金無法領取。
+條文依據：  
+- [第十七條 除外責任（二）]  
+- [第十二條 無理賠關懷保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 無理賠關懷保險金的給付 | 第十七條 除外責任（二） | 第十一條 特定傷病保險金的給付 | other_metadata | 第十九條 失蹤處理 | 第五條 保險範圍 | 第二十一條 無理賠關懷保險金的申領 | 第二十七條 受益人的指定及變更</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F244" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於第二保險單年度內自殺身故，根據條款規定，自契約訂立或復效之日起二年內因故意自殺致死者，本公司不負給付無理賠關懷保險金的責任。因此，本案例中無理賠關懷保險金無法領取。
+條文依據：  
+- [第十七條 除外責任（二）]  
+- [第十二條 無理賠關懷保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G244" s="2" t="inlineStr"/>
+      <c r="H244" s="2" t="inlineStr"/>
+      <c r="I244" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認保險商品是否涵蓋自殺身故的理賠條款", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認第二保險單年度內自殺身故的理賠規定或限制", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認無理賠關懷保險金的計算方式或適用條件", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認年繳實繳保險費是否影響無理賠關懷保險金的金額", "must_have": false, "分數": 0.0}], "coverage_score": 0.9231, "C_conf": 0.9231}</t>
+        </is>
+      </c>
+      <c r="J244" s="4" t="n">
+        <v>0.9231</v>
+      </c>
+      <c r="K244" s="4" t="n"/>
+      <c r="L244" s="4" t="n">
+        <v>0.9231</v>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:03:10</t>
+        </is>
+      </c>
+      <c r="N244" s="4" t="n">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>請問如果第2保單年度罹患特定傷病，可以給付多少錢?給付給誰?未來還有其他保險金嗎?</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在第2保單年度罹患特定傷病，依條款規定，本公司將給付以下金額與保險金：  
+1. **特定傷病保險金**：按「保險金額」給付，且僅給付一次。  
+2. **生活補助保險金**：自診斷確定罹患特定傷病的次一個保險單週年日起，每逢保險單週年日仍生存者，按「保險金額」的36%給付，最多給付10次。  
+3. **保險費豁免**：自診斷確定日起，豁免本契約的續期保險費，但當期已繳付之未到期保險費不予退還。  
+給付對象為保險契約的受益人。  
+條文依據：  
+- [第十二條 特定傷病保險金的給付]  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]  
+- [第十五條 保險費豁免（第二保險單年度起適用）]</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 特定傷病保險金的給付 | 第五條 保險範圍 | 第十三條 生活補助保險金的給付（第二保險單年度起適用） | 第二條 名詞定義 | 第十五條 保險費豁免（第二保險單年度起適用）</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F245" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在第2保單年度罹患特定傷病，依條款規定，本公司將給付以下金額與保險金：  
+1. **特定傷病保險金**：按「保險金額」給付，且僅給付一次。  
+2. **生活補助保險金**：自診斷確定罹患特定傷病的次一個保險單週年日起，每逢保險單週年日仍生存者，按「保險金額」的36%給付，最多給付10次。  
+3. **保險費豁免**：自診斷確定日起，豁免本契約的續期保險費，但當期已繳付之未到期保險費不予退還。  
+給付對象為保險契約的受益人。  
+條文依據：  
+- [第十二條 特定傷病保險金的給付]  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]  
+- [第十五條 保險費豁免（第二保險單年度起適用）]</t>
+        </is>
+      </c>
+      <c r="G245" s="2" t="inlineStr"/>
+      <c r="H245" s="2" t="inlineStr"/>
+      <c r="I245" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "請問如果第2保單年度罹患特定傷病，可以給付多少錢?給付給誰?未來還有其他保險金嗎?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J245" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K245" s="4" t="n"/>
+      <c r="L245" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:03:29</t>
+        </is>
+      </c>
+      <c r="N245" s="4" t="n">
+        <v>19.25</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>請問我115年1月1日投保，怎麼得到健康促進保險費折減?</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+要獲得健康促進保險費折減，您需要在保單有效期間內完成以下步驟：  
+1. 使用保險公司指定的程式並加入指定的健康計劃。  
+2. 在「指定日期」時，您的會員等級需符合以下標準之一：  
+   - 實踐家：次一保險單年度保險費折減3%。  
+   - 樂享家或高於樂享家的會員等級：次一保險單年度保險費折減10%。  
+3. 完成指定程式的註冊程序，並授權保險公司取得與健康促進相關的電子紀錄。保險公司將依據成功傳輸的電子紀錄計算您的會員等級。  
+條文依據：  
+- [第十六條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 健康促進保險費折減 | 第二十三條 投保年齡的計算及錯誤的處理 | 第十五條 保險費豁免（第二保險單年度起適用） | 第五條 保險範圍 | payout_items</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F246" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+要獲得健康促進保險費折減，您需要在保單有效期間內完成以下步驟：  
+1. 使用保險公司指定的程式並加入指定的健康計劃。  
+2. 在「指定日期」時，您的會員等級需符合以下標準之一：  
+   - 實踐家：次一保險單年度保險費折減3%。  
+   - 樂享家或高於樂享家的會員等級：次一保險單年度保險費折減10%。  
+3. 完成指定程式的註冊程序，並授權保險公司取得與健康促進相關的電子紀錄。保險公司將依據成功傳輸的電子紀錄計算您的會員等級。  
+條文依據：  
+- [第十六條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="G246" s="2" t="inlineStr"/>
+      <c r="H246" s="2" t="inlineStr"/>
+      <c r="I246" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "請問我115年1月1日投保，怎麼得到健康促進保險費折減?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J246" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K246" s="4" t="n"/>
+      <c r="L246" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:03:38</t>
+        </is>
+      </c>
+      <c r="N246" s="4" t="n">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>保戶在114/1/10投保樂鍾溢，如果他在115/3/30罹患特定傷病的話，在什麼時候可以領取生活補助保險金?</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保戶於114/1/10投保樂鍾溢，根據條款，生活補助保險金的給付條件需滿足以下幾點：  
+1. 保單需進入第二保險單年度（即115/1/10起）。  
+2. 被保險人需於第二保險單年度內初次診斷確定罹患特定傷病（115/3/30符合此條件）。  
+3. 生活補助保險金的給付自初次診斷確定罹患特定傷病的次一個保險單週年日（116/1/10）起，每逢保險單週年日仍生存者給付。  
+因此，保戶可於116/1/10首次領取生活補助保險金，並於每年保險單週年日（如117/1/10、118/1/10等）持續領取，最高給付次數為十次。
+條文依據：  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]  
+- [第十一條 契約的終止（三）]  
+- [第十二條 特定傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 生活補助保險金的給付（第二保險單年度起適用） | other_metadata | 第十一條 契約的終止（三） | payout_items | 第十二條 特定傷病保險金的給付 | 第五條 保險範圍 | 第十五條 保險費豁免（第二保險單年度起適用） | 第十條 契約的終止（二）</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F247" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保戶於114/1/10投保樂鍾溢，根據條款，生活補助保險金的給付條件需滿足以下幾點：  
+1. 保單需進入第二保險單年度（即115/1/10起）。  
+2. 被保險人需於第二保險單年度內初次診斷確定罹患特定傷病（115/3/30符合此條件）。  
+3. 生活補助保險金的給付自初次診斷確定罹患特定傷病的次一個保險單週年日（116/1/10）起，每逢保險單週年日仍生存者給付。  
+因此，保戶可於116/1/10首次領取生活補助保險金，並於每年保險單週年日（如117/1/10、118/1/10等）持續領取，最高給付次數為十次。
+條文依據：  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]  
+- [第十一條 契約的終止（三）]  
+- [第十二條 特定傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G247" s="2" t="inlineStr"/>
+      <c r="H247" s="2" t="inlineStr"/>
+      <c r="I247" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認樂鍾溢保單是否包含生活補助保險金保障", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認生活補助保險金的給付條件與特定傷病的適用性", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認保單生效日與115/3/30之間的時間是否符合保險條件", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認保單是否有針對特定傷病的等待期規定", "must_have": false, "分數": 1.0}, {"id": "5", "point": "確認生活補助保險金的申請流程與所需文件", "must_have": false, "分數": 0.0}], "coverage_score": 0.9286, "C_conf": 0.9286}</t>
+        </is>
+      </c>
+      <c r="J247" s="4" t="n">
+        <v>0.9286</v>
+      </c>
+      <c r="K247" s="4" t="n"/>
+      <c r="L247" s="4" t="n">
+        <v>0.9286</v>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:03:57</t>
+        </is>
+      </c>
+      <c r="N247" s="4" t="n">
+        <v>19.65</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>保戶在114/1/10投保樂鍾溢，如果他在115/3/30罹患特定傷病的話，他在115/1/9會領到無理賠回饋保險金嗎?</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 樂鍾溢保單包含「無理賠回饋保險金」的條款。  
+2. 無理賠回饋保險金的給付條件為：被保險人在保險單年度末仍生存，且未曾因罹患特定傷病申領「特定傷病保險金」。  
+3. 保戶在115/1/9符合無理賠回饋保險金的給付條件，因為截至該日為止，保戶尚未於保險單年度內罹患特定傷病或申領相關保險金。  
+4. 保戶於115/3/30罹患特定傷病不影響其115/1/9的無理賠回饋保險金給付資格，因該日期已屬上一保險單年度的結束日，且條款未規定事後罹患特定傷病會追溯影響已給付的無理賠回饋保險金。
+條文依據：  
+- [第十四條 無理賠回饋保險金的給付]  
+- [第二十條 無理賠回饋保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
+        <is>
+          <t>payout_items | 第十四條 無理賠回饋保險金的給付 | other_metadata | 第十二條 特定傷病保險金的給付 | 第二十條 無理賠回饋保險金的申領 | 第十條 契約的終止（二） | 第五條 保險範圍 | 第十五條 保險費豁免（第二保險單年度起適用）</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F248" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 樂鍾溢保單包含「無理賠回饋保險金」的條款。  
+2. 無理賠回饋保險金的給付條件為：被保險人在保險單年度末仍生存，且未曾因罹患特定傷病申領「特定傷病保險金」。  
+3. 保戶在115/1/9符合無理賠回饋保險金的給付條件，因為截至該日為止，保戶尚未於保險單年度內罹患特定傷病或申領相關保險金。  
+4. 保戶於115/3/30罹患特定傷病不影響其115/1/9的無理賠回饋保險金給付資格，因該日期已屬上一保險單年度的結束日，且條款未規定事後罹患特定傷病會追溯影響已給付的無理賠回饋保險金。
+條文依據：  
+- [第十四條 無理賠回饋保險金的給付]  
+- [第二十條 無理賠回饋保險金的申領]</t>
+        </is>
+      </c>
+      <c r="G248" s="2" t="inlineStr"/>
+      <c r="H248" s="2" t="inlineStr"/>
+      <c r="I248" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認樂鍾溢保單是否包含無理賠回饋保險金的條款", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認無理賠回饋保險金的給付條件", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認保戶在115/1/9是否符合無理賠回饋保險金的給付條件", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認保戶在115/3/30罹患特定傷病是否影響無理賠回饋保險金的給付資格", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J248" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K248" s="4" t="n"/>
+      <c r="L248" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:04:14</t>
+        </is>
+      </c>
+      <c r="N248" s="4" t="n">
+        <v>16.4</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>被保險人於第一保險單年度罹患急性心肌梗塞（重度），生活補助保險金最多可以領取幾次？</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於第一保險單年度罹患急性心肌梗塞（重度），無法申領生活補助保險金，因為生活補助保險金僅適用於第二保險單年度（含）以後的有效期間內。  
+條文依據：  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 生活補助保險金的給付（第二保險單年度起適用） | 第十二條 特定傷病保險金的給付 | 第十一條 契約的終止（三） | 第五條 保險範圍 | 第二條 名詞定義 | payout_items | 第十四條 無理賠回饋保險金的給付 | 第十九條 特定傷病保險金、生活補助保險金或保險費豁免的申領</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F249" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於第一保險單年度罹患急性心肌梗塞（重度），無法申領生活補助保險金，因為生活補助保險金僅適用於第二保險單年度（含）以後的有效期間內。  
+條文依據：  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]</t>
+        </is>
+      </c>
+      <c r="G249" s="2" t="inlineStr"/>
+      <c r="H249" s="2" t="inlineStr"/>
+      <c r="I249" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認生活補助保險金是否涵蓋急性心肌梗塞（重度）", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認第一保險單年度內生活補助保險金的給付次數限制", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認急性心肌梗塞（重度）是否符合保單條款中的重度疾病定義", "must_have": false, "分數": 0.0}], "coverage_score": 0.8889, "C_conf": 0.8889}</t>
+        </is>
+      </c>
+      <c r="J249" s="4" t="n">
+        <v>0.8889</v>
+      </c>
+      <c r="K249" s="4" t="n"/>
+      <c r="L249" s="4" t="n">
+        <v>0.8889</v>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:04:25</t>
+        </is>
+      </c>
+      <c r="N249" s="4" t="n">
+        <v>11.53</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>被保險人為60歲女性，投保繳費期間20年期之樂鍾心特定傷病定期健康保險（外溢型）5單位，每單位年繳應繳保險費為1675元，則每逢保險單年度末生存者，可以領取多少無理賠關懷保險金？</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款規定，無理賠回饋保險金的計算方式為「每單位年繳應繳保險費」的10%乘以「單位數」。本案例中，每單位年繳應繳保險費為1675元，投保5單位，因此計算如下：  
+1675元 × 10% × 5單位 = 837.5元（元以下無條件進位為838元）。  
+因此，每逢保險單年度末生存者，可以領取838元的無理賠回饋保險金。
+條文依據：  
+- [第十四條 無理賠回饋保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 無理賠回饋保險金的給付 | other_metadata | payout_items | 第二十條 無理賠回饋保險金的申領 | 第十二條 特定傷病保險金的給付 | 第十三條 生活補助保險金的給付（第二保險單年度起適用） | 第五條 保險範圍 | 第十五條 保險費豁免（第二保險單年度起適用）</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F250" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款規定，無理賠回饋保險金的計算方式為「每單位年繳應繳保險費」的10%乘以「單位數」。本案例中，每單位年繳應繳保險費為1675元，投保5單位，因此計算如下：  
+1675元 × 10% × 5單位 = 837.5元（元以下無條件進位為838元）。  
+因此，每逢保險單年度末生存者，可以領取838元的無理賠回饋保險金。
+條文依據：  
+- [第十四條 無理賠回饋保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G250" s="2" t="inlineStr"/>
+      <c r="H250" s="2" t="inlineStr"/>
+      <c r="I250" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認樂鍾心特定傷病定期健康保險（外溢型）的無理賠關懷保險金計算方式", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認每單位年繳保險費為1675元的相關條件", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認投保5單位對無理賠關懷保險金的影響", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認保險單年度末生存者的定義與條件", "must_have": false, "分數": 0.8}], "coverage_score": 0.9846, "C_conf": 0.9846}</t>
+        </is>
+      </c>
+      <c r="J250" s="4" t="n">
+        <v>0.9846</v>
+      </c>
+      <c r="K250" s="4" t="n"/>
+      <c r="L250" s="4" t="n">
+        <v>0.9846</v>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:04:40</t>
+        </is>
+      </c>
+      <c r="N250" s="4" t="n">
+        <v>14.39</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/rag_results.xlsx
+++ b/src/rag_results.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N333"/>
+  <dimension ref="A1:N416"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -21725,6 +21725,5287 @@
         <v>12.27</v>
       </c>
     </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B334" s="2" t="inlineStr">
+        <is>
+          <t>保障範圍包括哪些項目？</t>
+        </is>
+      </c>
+      <c r="C334" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括住院醫療保險金、加護病房或燒燙傷病房保險金、祝壽保險金、身故保險金或喪葬費用保險金，以及所繳保險費的退還。
+條文依據：  
+- 摘要</t>
+        </is>
+      </c>
+      <c r="D334" s="2" t="inlineStr">
+        <is>
+          <t>payout_items | summary | 第五條 保險範圍 | 第二條 名詞定義 | 第十八條 除外責任（一）</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F334" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括住院醫療保險金、加護病房或燒燙傷病房保險金、祝壽保險金、身故保險金或喪葬費用保險金，以及所繳保險費的退還。
+條文依據：  
+- 摘要</t>
+        </is>
+      </c>
+      <c r="G334" s="2" t="inlineStr"/>
+      <c r="H334" s="2" t="inlineStr"/>
+      <c r="I334" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.983647, "neutral": 0.012178, "contradiction": 0.004175, "factuality": 0.995825, "C_fact": 0.995825}, "C_conf": 0.9958}</t>
+        </is>
+      </c>
+      <c r="J334" s="5" t="n"/>
+      <c r="K334" s="5" t="n">
+        <v>0.995825</v>
+      </c>
+      <c r="L334" s="5" t="n">
+        <v>0.9958</v>
+      </c>
+      <c r="M334" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:38:56</t>
+        </is>
+      </c>
+      <c r="N334" s="5" t="n">
+        <v>23.33</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B335" s="2" t="inlineStr">
+        <is>
+          <t>住院日數計算有什麼特殊規則？</t>
+        </is>
+      </c>
+      <c r="C335" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院日數計算的特殊規則包括：  
+1. 住院日數是按被保險人同一次住院的實際全日住進急性病房或慢性病房（含加護病房及燒燙傷病房）的住院日數計算，包含住院及出院當日。  
+2. 若被保險人出院後又於同一日入院診療，該日不得重複計入住院日數。  
+條文依據：  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D335" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第十二條 住院醫療保險金的給付 | 第二條 名詞定義 | 第十三條 加護病房或燒燙傷病房保險金的給付 | 第二十八條 住院醫療保險金日額之減少</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F335" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院日數計算的特殊規則包括：  
+1. 住院日數是按被保險人同一次住院的實際全日住進急性病房或慢性病房（含加護病房及燒燙傷病房）的住院日數計算，包含住院及出院當日。  
+2. 若被保險人出院後又於同一日入院診療，該日不得重複計入住院日數。  
+條文依據：  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G335" s="2" t="inlineStr"/>
+      <c r="H335" s="2" t="inlineStr"/>
+      <c r="I335" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.996115, "neutral": 0.003676, "contradiction": 0.000209, "factuality": 0.999791, "C_fact": 0.999791}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J335" s="5" t="n"/>
+      <c r="K335" s="5" t="n">
+        <v>0.999791</v>
+      </c>
+      <c r="L335" s="5" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M335" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:39:20</t>
+        </is>
+      </c>
+      <c r="N335" s="5" t="n">
+        <v>23.4</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B336" s="2" t="inlineStr">
+        <is>
+          <t>住院醫療保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C336" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院醫療保險金的給付規定如下：  
+被保險人於契約有效期間內因疾病或傷害住院治療，本公司依保險單所記載之「住院醫療保險金日額」，乘以入院日當年度之「增額係數」，再乘以住院日數，給付「住院醫療保險金」。同一保單年度內，同一次住院的住院日數給付上限為三百六十五日。  
+條文依據：  
+- [第十二條 住院醫療保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D336" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 住院醫療保險金的給付 | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第十三條 加護病房或燒燙傷病房保險金的給付 | 第十四條 醫療保險金給付總額之上限 | 第二十八條 住院醫療保險金日額之減少</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F336" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院醫療保險金的給付規定如下：  
+被保險人於契約有效期間內因疾病或傷害住院治療，本公司依保險單所記載之「住院醫療保險金日額」，乘以入院日當年度之「增額係數」，再乘以住院日數，給付「住院醫療保險金」。同一保單年度內，同一次住院的住院日數給付上限為三百六十五日。  
+條文依據：  
+- [第十二條 住院醫療保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G336" s="2" t="inlineStr"/>
+      <c r="H336" s="2" t="inlineStr"/>
+      <c r="I336" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.997861, "neutral": 0.002008, "contradiction": 0.00013, "factuality": 0.99987, "C_fact": 0.99987}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J336" s="5" t="n"/>
+      <c r="K336" s="5" t="n">
+        <v>0.99987</v>
+      </c>
+      <c r="L336" s="5" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M336" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:39:33</t>
+        </is>
+      </c>
+      <c r="N336" s="5" t="n">
+        <v>12.73</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B337" s="2" t="inlineStr">
+        <is>
+          <t>加護病房或燒燙傷病房保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C337" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+加護病房或燒燙傷病房保險金的給付規定如下：  
+被保險人於契約有效期間內因疾病或傷害住院，並在醫院的加護病房或燒燙傷病房接受治療者，除住院醫療保險金外，保險公司將依保險單所記載的「住院醫療保險金日額」，乘以入院日當年度的「增額係數」，再乘以實際住進加護病房或燒燙傷病房的日數（含轉入及轉出當日）的二倍，給付「加護病房或燒燙傷病房保險金」。  
+同一保單年度內，同一次住院的加護病房及燒燙傷病房住院日數合計給付最高以365日為限。同一日內，保險公司僅就加護病房或燒燙傷病房其中一種病房給付。
+條文依據：  
+- [第十三條 加護病房或燒燙傷病房保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D337" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 加護病房或燒燙傷病房保險金的給付 | payout_items | 第二十三條 醫療保險金的申領 | 第五條 保險範圍 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F337" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+加護病房或燒燙傷病房保險金的給付規定如下：  
+被保險人於契約有效期間內因疾病或傷害住院，並在醫院的加護病房或燒燙傷病房接受治療者，除住院醫療保險金外，保險公司將依保險單所記載的「住院醫療保險金日額」，乘以入院日當年度的「增額係數」，再乘以實際住進加護病房或燒燙傷病房的日數（含轉入及轉出當日）的二倍，給付「加護病房或燒燙傷病房保險金」。  
+同一保單年度內，同一次住院的加護病房及燒燙傷病房住院日數合計給付最高以365日為限。同一日內，保險公司僅就加護病房或燒燙傷病房其中一種病房給付。
+條文依據：  
+- [第十三條 加護病房或燒燙傷病房保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G337" s="2" t="inlineStr"/>
+      <c r="H337" s="2" t="inlineStr"/>
+      <c r="I337" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.993512, "neutral": 0.005062, "contradiction": 0.001427, "factuality": 0.998573, "C_fact": 0.998573}, "C_conf": 0.9986}</t>
+        </is>
+      </c>
+      <c r="J337" s="5" t="n"/>
+      <c r="K337" s="5" t="n">
+        <v>0.998573</v>
+      </c>
+      <c r="L337" s="5" t="n">
+        <v>0.9986</v>
+      </c>
+      <c r="M337" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:39:43</t>
+        </is>
+      </c>
+      <c r="N337" s="5" t="n">
+        <v>9.98</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B338" s="2" t="inlineStr">
+        <is>
+          <t>醫療保險金給付總額之上限</t>
+        </is>
+      </c>
+      <c r="C338" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+醫療保險金給付總額之上限為保險單上所記載之「住院醫療保險金日額」的二千五百倍，且此上限適用於本契約有效期間內依第十二條至第十三條所給付之各項保險金的累計總額。
+條文依據：  
+- [第十四條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="D338" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 醫療保險金給付總額之上限 | 第十二條 住院醫療保險金的給付 | 第五條 保險範圍 | 第十三條 加護病房或燒燙傷病房保險金的給付 | payout_items</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F338" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+醫療保險金給付總額之上限為保險單上所記載之「住院醫療保險金日額」的二千五百倍，且此上限適用於本契約有效期間內依第十二條至第十三條所給付之各項保險金的累計總額。
+條文依據：  
+- [第十四條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="G338" s="2" t="inlineStr"/>
+      <c r="H338" s="2" t="inlineStr"/>
+      <c r="I338" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.995968, "neutral": 0.003732, "contradiction": 0.0003, "factuality": 0.9997, "C_fact": 0.9997}, "C_conf": 0.9997}</t>
+        </is>
+      </c>
+      <c r="J338" s="5" t="n"/>
+      <c r="K338" s="5" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="L338" s="5" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="M338" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:39:48</t>
+        </is>
+      </c>
+      <c r="N338" s="5" t="n">
+        <v>4.27</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B339" s="2" t="inlineStr">
+        <is>
+          <t>祝壽保險金的給付規定為何?</t>
+        </is>
+      </c>
+      <c r="C339" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+祝壽保險金的給付規定為：被保險人於本契約有效期間且保險年齡到達九十九歲之保險單週年日仍生存時，本公司按「當年度保險金額」給付「祝壽保險金」。
+條文依據：  
+- [第十五條 祝壽保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D339" s="2" t="inlineStr">
+        <is>
+          <t>第十五條 祝壽保險金的給付 | 第十二條至第十三條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | 第二十四條 祝壽保險金的申領 | payout_items | 第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F339" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+祝壽保險金的給付規定為：被保險人於本契約有效期間且保險年齡到達九十九歲之保險單週年日仍生存時，本公司按「當年度保險金額」給付「祝壽保險金」。
+條文依據：  
+- [第十五條 祝壽保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G339" s="2" t="inlineStr"/>
+      <c r="H339" s="2" t="inlineStr"/>
+      <c r="I339" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.997653, "neutral": 0.002173, "contradiction": 0.000174, "factuality": 0.999826, "C_fact": 0.999826}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J339" s="5" t="n"/>
+      <c r="K339" s="5" t="n">
+        <v>0.999826</v>
+      </c>
+      <c r="L339" s="5" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M339" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:39:51</t>
+        </is>
+      </c>
+      <c r="N339" s="5" t="n">
+        <v>3.34</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B340" s="2" t="inlineStr">
+        <is>
+          <t>有效期間內身故，保險金如何給付?</t>
+        </is>
+      </c>
+      <c r="C340" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於本契約有效期間內身故者，本公司按「當年度保險金額」給付「身故保險金」。若被保險人於有效期間且實際年齡未滿十五足歲身故者，本公司則按「所繳保險費」退還要保人，不適用「身故保險金」的約定。此外，若被保險人訂立契約時受監護宣告尚未撤銷，其身故保險金將變更為喪葬費用保險金，且喪葬費用保險金額不得超過遺產稅喪葬費扣除額之半數，超過部分不負給付責任。  
+條文依據：  
+- [第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D340" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付 | 第十條 契約的終止（二） | 第五條 保險範圍 | 第二十二條 失蹤處理 | 第十五條 祝壽保險金的給付</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F340" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於本契約有效期間內身故者，本公司按「當年度保險金額」給付「身故保險金」。若被保險人於有效期間且實際年齡未滿十五足歲身故者，本公司則按「所繳保險費」退還要保人，不適用「身故保險金」的約定。此外，若被保險人訂立契約時受監護宣告尚未撤銷，其身故保險金將變更為喪葬費用保險金，且喪葬費用保險金額不得超過遺產稅喪葬費扣除額之半數，超過部分不負給付責任。  
+條文依據：  
+- [第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G340" s="2" t="inlineStr"/>
+      <c r="H340" s="2" t="inlineStr"/>
+      <c r="I340" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.984274, "neutral": 0.015419, "contradiction": 0.000307, "factuality": 0.999693, "C_fact": 0.999693}, "C_conf": 0.9997}</t>
+        </is>
+      </c>
+      <c r="J340" s="5" t="n"/>
+      <c r="K340" s="5" t="n">
+        <v>0.9996930000000001</v>
+      </c>
+      <c r="L340" s="5" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="M340" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:40:07</t>
+        </is>
+      </c>
+      <c r="N340" s="5" t="n">
+        <v>13.05</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B341" s="2" t="inlineStr">
+        <is>
+          <t>健康促進保險費折減規定</t>
+        </is>
+      </c>
+      <c r="C341" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+健康促進保險費折減規定如下：  
+1. 被保險人需年滿20歲（含）以上，並使用保險公司指定程式加入健康計劃。  
+2. 若於「指定日期」的會員等級符合進階會員或菁英會員（或更高等級），可享次一保險單年度保險費折減：進階會員折減2%，菁英會員或更高等級折減3%。  
+3. 豁免或復效的保險費不適用折減規定。  
+4. 被保險人需完成程式註冊並授權保險公司取得健康促進相關電子紀錄，折減比例依成功傳輸的電子紀錄計算。
+條文依據：  
+- [第十七條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="D341" s="2" t="inlineStr">
+        <is>
+          <t>第十七條 健康促進保險費折減 | 第二十八條 住院醫療保險金日額之減少 | 第三十條 投保年齡的計算及錯誤的處理 | 第二條 名詞定義 | 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F341" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+健康促進保險費折減規定如下：  
+1. 被保險人需年滿20歲（含）以上，並使用保險公司指定程式加入健康計劃。  
+2. 若於「指定日期」的會員等級符合進階會員或菁英會員（或更高等級），可享次一保險單年度保險費折減：進階會員折減2%，菁英會員或更高等級折減3%。  
+3. 豁免或復效的保險費不適用折減規定。  
+4. 被保險人需完成程式註冊並授權保險公司取得健康促進相關電子紀錄，折減比例依成功傳輸的電子紀錄計算。
+條文依據：  
+- [第十七條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="G341" s="2" t="inlineStr"/>
+      <c r="H341" s="2" t="inlineStr"/>
+      <c r="I341" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.995281, "neutral": 0.003863, "contradiction": 0.000856, "factuality": 0.999144, "C_fact": 0.999144}, "C_conf": 0.9991}</t>
+        </is>
+      </c>
+      <c r="J341" s="5" t="n"/>
+      <c r="K341" s="5" t="n">
+        <v>0.999144</v>
+      </c>
+      <c r="L341" s="5" t="n">
+        <v>0.9991</v>
+      </c>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:40:25</t>
+        </is>
+      </c>
+      <c r="N341" s="5" t="n">
+        <v>18.3</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B342" s="2" t="inlineStr">
+        <is>
+          <t>除外責任的解釋?</t>
+        </is>
+      </c>
+      <c r="C342" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+除外責任是指保險公司不負給付保險金責任的情形，包含被保險人因故意行為、犯罪行為、非法施用毒品等原因所致的疾病或傷害，以及因美容手術、健康檢查、懷孕、流產或分娩等特定事故住院診療的情況。但部分情形如重建基本功能的整型手術、特定懷孕相關疾病、醫療行為必要的流產或剖腹產等，則不在此限。  
+條文依據：  
+- [第十八條 除外責任（一）]  
+- [第十九條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="D342" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第十九條 除外責任（二） | 第八條 告知義務與本契約的解除 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F342" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+除外責任是指保險公司不負給付保險金責任的情形，包含被保險人因故意行為、犯罪行為、非法施用毒品等原因所致的疾病或傷害，以及因美容手術、健康檢查、懷孕、流產或分娩等特定事故住院診療的情況。但部分情形如重建基本功能的整型手術、特定懷孕相關疾病、醫療行為必要的流產或剖腹產等，則不在此限。  
+條文依據：  
+- [第十八條 除外責任（一）]  
+- [第十九條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="G342" s="2" t="inlineStr"/>
+      <c r="H342" s="2" t="inlineStr"/>
+      <c r="I342" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.998031, "neutral": 0.001868, "contradiction": 0.000102, "factuality": 0.999898, "C_fact": 0.999898}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J342" s="5" t="n"/>
+      <c r="K342" s="5" t="n">
+        <v>0.999898</v>
+      </c>
+      <c r="L342" s="5" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:40:51</t>
+        </is>
+      </c>
+      <c r="N342" s="5" t="n">
+        <v>24.9</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B343" s="2" t="inlineStr">
+        <is>
+          <t>哪些疾病被含在除外責任?</t>
+        </is>
+      </c>
+      <c r="C343" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+以下疾病被列為除外責任，保險公司不負給付第十二條至第十三條保險金的責任：  
+1. 美容手術、外科整型（但為重建基本功能所作之必要整型不在此限）。  
+2. 外觀可見之天生畸形。  
+3. 健康檢查、療養、靜養、戒毒、戒酒、護理或養老之非以直接診治病人為目的者。  
+4. 懷孕、流產或分娩及其併發症（但特定懷孕相關疾病、醫療行為必要之流產及剖腹產不在此限）。  
+5. 不孕症、人工受孕或非以治療為目的之避孕及絕育手術。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D343" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第二條 名詞定義 | 第十九條 除外責任（二）</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F343" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+以下疾病被列為除外責任，保險公司不負給付第十二條至第十三條保險金的責任：  
+1. 美容手術、外科整型（但為重建基本功能所作之必要整型不在此限）。  
+2. 外觀可見之天生畸形。  
+3. 健康檢查、療養、靜養、戒毒、戒酒、護理或養老之非以直接診治病人為目的者。  
+4. 懷孕、流產或分娩及其併發症（但特定懷孕相關疾病、醫療行為必要之流產及剖腹產不在此限）。  
+5. 不孕症、人工受孕或非以治療為目的之避孕及絕育手術。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="G343" s="2" t="inlineStr"/>
+      <c r="H343" s="2" t="inlineStr"/>
+      <c r="I343" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.9986, "neutral": 0.001184, "contradiction": 0.000215, "factuality": 0.999785, "C_fact": 0.999785}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J343" s="5" t="n"/>
+      <c r="K343" s="5" t="n">
+        <v>0.999785</v>
+      </c>
+      <c r="L343" s="5" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:41:10</t>
+        </is>
+      </c>
+      <c r="N343" s="5" t="n">
+        <v>18.88</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B344" s="2" t="inlineStr">
+        <is>
+          <t>進行美容手術住院可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C344" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，因美容手術住院診療者，本公司不負給付保險金的責任。但若美容手術是為重建基本功能所作之必要整型，則不在此限，可以申請理賠。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D344" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第十三條 加護病房或燒燙傷病房保險金的給付 | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第二條 名詞定義 | payout_items</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F344" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，因美容手術住院診療者，本公司不負給付保險金的責任。但若美容手術是為重建基本功能所作之必要整型，則不在此限，可以申請理賠。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="G344" s="2" t="inlineStr"/>
+      <c r="H344" s="2" t="inlineStr"/>
+      <c r="I344" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.474019, "neutral": 0.524983, "contradiction": 0.000999, "factuality": 0.999001, "C_fact": 0.999001}, "C_conf": 0.999}</t>
+        </is>
+      </c>
+      <c r="J344" s="5" t="n"/>
+      <c r="K344" s="5" t="n">
+        <v>0.999001</v>
+      </c>
+      <c r="L344" s="5" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="M344" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:41:19</t>
+        </is>
+      </c>
+      <c r="N344" s="5" t="n">
+        <v>9.44</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B345" s="2" t="inlineStr">
+        <is>
+          <t>因胎兒染色體異常進行手術而住院可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C345" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以申請理賠。根據條款，因「胎兒染色體異常之手術」屬於懷孕相關疾病的例外情形，不在除外責任範圍內，因此符合理賠條件。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D345" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第二條 名詞定義 | payout_items | 第十三條 加護病房或燒燙傷病房保險金的給付</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F345" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以申請理賠。根據條款，因「胎兒染色體異常之手術」屬於懷孕相關疾病的例外情形，不在除外責任範圍內，因此符合理賠條件。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="G345" s="2" t="inlineStr"/>
+      <c r="H345" s="2" t="inlineStr"/>
+      <c r="I345" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.982538, "neutral": 0.017186, "contradiction": 0.000276, "factuality": 0.999724, "C_fact": 0.999724}, "C_conf": 0.9997}</t>
+        </is>
+      </c>
+      <c r="J345" s="5" t="n"/>
+      <c r="K345" s="5" t="n">
+        <v>0.9997239999999999</v>
+      </c>
+      <c r="L345" s="5" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="M345" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:41:33</t>
+        </is>
+      </c>
+      <c r="N345" s="5" t="n">
+        <v>13.72</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B346" s="2" t="inlineStr">
+        <is>
+          <t>因胎位不正進行手術而住院可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C346" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，因懷孕、流產或分娩及其併發症住院診療，本公司不負給付保險金的責任。然而，若因胎位不正進行手術屬於醫療行為必要之剖腹產，則不在此限，符合理賠條件。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D346" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第二條 名詞定義 | payout_items | 第十三條 加護病房或燒燙傷病房保險金的給付</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F346" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，因懷孕、流產或分娩及其併發症住院診療，本公司不負給付保險金的責任。然而，若因胎位不正進行手術屬於醫療行為必要之剖腹產，則不在此限，符合理賠條件。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="G346" s="2" t="inlineStr"/>
+      <c r="H346" s="2" t="inlineStr"/>
+      <c r="I346" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.90418, "neutral": 0.095138, "contradiction": 0.000682, "factuality": 0.999318, "C_fact": 0.999318}, "C_conf": 0.9993}</t>
+        </is>
+      </c>
+      <c r="J346" s="5" t="n"/>
+      <c r="K346" s="5" t="n">
+        <v>0.999318</v>
+      </c>
+      <c r="L346" s="5" t="n">
+        <v>0.9993</v>
+      </c>
+      <c r="M346" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:41:40</t>
+        </is>
+      </c>
+      <c r="N346" s="5" t="n">
+        <v>6.68</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B347" s="2" t="inlineStr">
+        <is>
+          <t>因自殺未遂導致住院可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C347" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+因自殺未遂導致住院，本公司不負給付住院醫療保險金的責任，因為此屬被保險人之故意行為。但若有其他符合保險條款的例外情形，則需依具體條件判定。  
+條文依據：  
+- [第十八條 除外責任（一)]</t>
+        </is>
+      </c>
+      <c r="D347" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 除外責任（二） | 第十八條 除外責任（一） | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | payout_items | 第十條 契約的終止（二）</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F347" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+因自殺未遂導致住院，本公司不負給付住院醫療保險金的責任，因為此屬被保險人之故意行為。但若有其他符合保險條款的例外情形，則需依具體條件判定。  
+條文依據：  
+- [第十八條 除外責任（一)]</t>
+        </is>
+      </c>
+      <c r="G347" s="2" t="inlineStr"/>
+      <c r="H347" s="2" t="inlineStr"/>
+      <c r="I347" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.984608, "neutral": 0.015018, "contradiction": 0.000374, "factuality": 0.999626, "C_fact": 0.999626}, "C_conf": 0.9996}</t>
+        </is>
+      </c>
+      <c r="J347" s="5" t="n"/>
+      <c r="K347" s="5" t="n">
+        <v>0.999626</v>
+      </c>
+      <c r="L347" s="5" t="n">
+        <v>0.9996</v>
+      </c>
+      <c r="M347" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:41:46</t>
+        </is>
+      </c>
+      <c r="N347" s="5" t="n">
+        <v>6.02</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B348" s="2" t="inlineStr">
+        <is>
+          <t>被保險人在投保一年內故意自殺者，可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C348" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人在投保一年內故意自殺者，依條款規定，本公司不負給付身故保險金或喪葬費用保險金的責任。但若故意自殺發生於契約訂立或復效之日起二年後，本公司仍負給付責任。
+條文依據：  
+- [第十九條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="D348" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 除外責任（二） | 第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付 | 第十條 契約的終止（二） | 第三十條 投保年齡的計算及錯誤的處理 | 第十八條 除外責任（一）</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F348" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人在投保一年內故意自殺者，依條款規定，本公司不負給付身故保險金或喪葬費用保險金的責任。但若故意自殺發生於契約訂立或復效之日起二年後，本公司仍負給付責任。
+條文依據：  
+- [第十九條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="G348" s="2" t="inlineStr"/>
+      <c r="H348" s="2" t="inlineStr"/>
+      <c r="I348" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.997326, "neutral": 0.002554, "contradiction": 0.000119, "factuality": 0.999881, "C_fact": 0.999881}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J348" s="5" t="n"/>
+      <c r="K348" s="5" t="n">
+        <v>0.999881</v>
+      </c>
+      <c r="L348" s="5" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M348" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:41:52</t>
+        </is>
+      </c>
+      <c r="N348" s="5" t="n">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B349" s="2" t="inlineStr">
+        <is>
+          <t>申請理賠有什麼時間規定嗎?</t>
+        </is>
+      </c>
+      <c r="C349" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申請理賠的時間規定如下：要保人、被保險人或受益人應於知悉本公司應負保險責任之事故後十日內通知本公司，並於通知後儘速檢具所需文件向本公司申請給付保險金。本公司應於收齊所需文件後十五日內完成保險金給付。若因可歸責於本公司之事由未能在約定期限內給付，則應按年利一分加計利息給付。  
+條文依據：  
+- [第二十一條 保險事故的通知與保險金的申請時間]</t>
+        </is>
+      </c>
+      <c r="D349" s="2" t="inlineStr">
+        <is>
+          <t>第二十一條 保險事故的通知與保險金的申請時間 | 第六條 第二期以後保險費的交付、寬限期間及契約效力的停止 | 第七條 本契約效力的恢復 | 第三條 契約撤銷權 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F349" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申請理賠的時間規定如下：要保人、被保險人或受益人應於知悉本公司應負保險責任之事故後十日內通知本公司，並於通知後儘速檢具所需文件向本公司申請給付保險金。本公司應於收齊所需文件後十五日內完成保險金給付。若因可歸責於本公司之事由未能在約定期限內給付，則應按年利一分加計利息給付。  
+條文依據：  
+- [第二十一條 保險事故的通知與保險金的申請時間]</t>
+        </is>
+      </c>
+      <c r="G349" s="2" t="inlineStr"/>
+      <c r="H349" s="2" t="inlineStr"/>
+      <c r="I349" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.997385, "neutral": 0.002516, "contradiction": 9.9e-05, "factuality": 0.999901, "C_fact": 0.999901}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J349" s="5" t="n"/>
+      <c r="K349" s="5" t="n">
+        <v>0.999901</v>
+      </c>
+      <c r="L349" s="5" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M349" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:41:58</t>
+        </is>
+      </c>
+      <c r="N349" s="5" t="n">
+        <v>5.22</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B350" s="2" t="inlineStr">
+        <is>
+          <t>燒燙傷病房保險金怎麼申領?</t>
+        </is>
+      </c>
+      <c r="C350" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申領燒燙傷病房保險金時，受益人需檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 醫療診斷書或住院證明，並列明進、出燒燙傷病房的日期。（但要保人或被保險人為醫師時，不得為被保險人出具診斷書或住院證明。）  
+4. 受益人的身分證明。  
+此外，本公司基於審核保險金之需要，得徵詢其他醫師的醫學專業意見，並經受益人同意調閱被保險人之就醫相關資料，相關費用由本公司負擔。
+條文依據：  
+- [第二十三條 醫療保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D350" s="2" t="inlineStr">
+        <is>
+          <t>第二十三條 醫療保險金的申領 | 第十三條 加護病房或燒燙傷病房保險金的給付 | payout_items | 第二條 名詞定義 | 第二十一條 保險事故的通知與保險金的申請時間</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F350" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申領燒燙傷病房保險金時，受益人需檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 醫療診斷書或住院證明，並列明進、出燒燙傷病房的日期。（但要保人或被保險人為醫師時，不得為被保險人出具診斷書或住院證明。）  
+4. 受益人的身分證明。  
+此外，本公司基於審核保險金之需要，得徵詢其他醫師的醫學專業意見，並經受益人同意調閱被保險人之就醫相關資料，相關費用由本公司負擔。
+條文依據：  
+- [第二十三條 醫療保險金的申領]</t>
+        </is>
+      </c>
+      <c r="G350" s="2" t="inlineStr"/>
+      <c r="H350" s="2" t="inlineStr"/>
+      <c r="I350" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.99806, "neutral": 0.001825, "contradiction": 0.000115, "factuality": 0.999885, "C_fact": 0.999885}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J350" s="5" t="n"/>
+      <c r="K350" s="5" t="n">
+        <v>0.999885</v>
+      </c>
+      <c r="L350" s="5" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M350" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:42:07</t>
+        </is>
+      </c>
+      <c r="N350" s="5" t="n">
+        <v>9.140000000000001</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B351" s="2" t="inlineStr">
+        <is>
+          <t>活到99歲怎麼申請祝壽金?</t>
+        </is>
+      </c>
+      <c r="C351" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申請祝壽保險金時，受益人需準備以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 受益人的身分證明。  
+條文依據：  
+- [第二十四條 祝壽保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D351" s="2" t="inlineStr">
+        <is>
+          <t>第十五條 祝壽保險金的給付 | 第二十四條 祝壽保險金的申領 | 第五條 保險範圍 | 第十二條至第十三條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | announcement_history</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F351" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申請祝壽保險金時，受益人需準備以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 受益人的身分證明。  
+條文依據：  
+- [第二十四條 祝壽保險金的申領]</t>
+        </is>
+      </c>
+      <c r="G351" s="2" t="inlineStr"/>
+      <c r="H351" s="2" t="inlineStr"/>
+      <c r="I351" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.99841, "neutral": 0.001489, "contradiction": 0.0001, "factuality": 0.9999, "C_fact": 0.9999}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J351" s="5" t="n"/>
+      <c r="K351" s="5" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="L351" s="5" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M351" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:42:15</t>
+        </is>
+      </c>
+      <c r="N351" s="5" t="n">
+        <v>8.01</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B352" s="2" t="inlineStr">
+        <is>
+          <t>被保人身故怎麼申請理賠</t>
+        </is>
+      </c>
+      <c r="C352" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+受益人申領「身故保險金」或「喪葬費用保險金」時，需檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 被保險人死亡證明書及除戶戶籍謄本。  
+4. 受益人的身分證明。  
+條文依據：  
+- [第二十五條 身故保險金或喪葬費用保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D352" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付 | 第十二條至第十三條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | 第二十二條 失蹤處理 | 第二十五條 身故保險金或喪葬費用保險金的申領 | 第十九條 除外責任（二）</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F352" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+受益人申領「身故保險金」或「喪葬費用保險金」時，需檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 被保險人死亡證明書及除戶戶籍謄本。  
+4. 受益人的身分證明。  
+條文依據：  
+- [第二十五條 身故保險金或喪葬費用保險金的申領]</t>
+        </is>
+      </c>
+      <c r="G352" s="2" t="inlineStr"/>
+      <c r="H352" s="2" t="inlineStr"/>
+      <c r="I352" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.996062, "neutral": 0.003782, "contradiction": 0.000155, "factuality": 0.999845, "C_fact": 0.999845}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J352" s="5" t="n"/>
+      <c r="K352" s="5" t="n">
+        <v>0.999845</v>
+      </c>
+      <c r="L352" s="5" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M352" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:42:27</t>
+        </is>
+      </c>
+      <c r="N352" s="5" t="n">
+        <v>11.08</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B353" s="2" t="inlineStr">
+        <is>
+          <t>投保15年後，因手術住院3天，住院日額為2500元，請問可以申請多少理賠?</t>
+        </is>
+      </c>
+      <c r="C353" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+依據第十二條，住院醫療保險金的計算公式為「住院醫療保險金日額」乘以「增額係數」再乘以住院日數。假設增額係數未提供具體數值，僅以住院日額 2500 元計算，住院 3 天的理賠金額為：  
+2500 元 × 3 天 = 7500 元。  
+條文依據：  
+- [第十二條 住院醫療保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D353" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 住院醫療保險金的給付 | 第十三條 加護病房或燒燙傷病房保險金的給付 | 第二十八條 住院醫療保險金日額之減少 | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | payout_items | 第五條 保險範圍 | 第二條 名詞定義 | 第二十一條 保險事故的通知與保險金的申請時間</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F353" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+依據第十二條，住院醫療保險金的計算公式為「住院醫療保險金日額」乘以「增額係數」再乘以住院日數。假設增額係數未提供具體數值，僅以住院日額 2500 元計算，住院 3 天的理賠金額為：  
+2500 元 × 3 天 = 7500 元。  
+條文依據：  
+- [第十二條 住院醫療保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G353" s="2" t="inlineStr"/>
+      <c r="H353" s="2" t="inlineStr"/>
+      <c r="I353" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.990622, "neutral": 0.007599, "contradiction": 0.001779, "factuality": 0.998221, "C_fact": 0.998221}, "C_conf": 0.9982}</t>
+        </is>
+      </c>
+      <c r="J353" s="5" t="n"/>
+      <c r="K353" s="5" t="n">
+        <v>0.998221</v>
+      </c>
+      <c r="L353" s="5" t="n">
+        <v>0.9982</v>
+      </c>
+      <c r="M353" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:42:36</t>
+        </is>
+      </c>
+      <c r="N353" s="5" t="n">
+        <v>9.029999999999999</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B354" s="2" t="inlineStr">
+        <is>
+          <t>保障範圍包括哪些項目？</t>
+        </is>
+      </c>
+      <c r="C354" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括：住院手術醫療保險金、門診手術醫療保險金、特定處置保險金、意外創傷縫合處置保險金、意外住院手術醫療保險金、祝壽保險金、所繳保險費的退還、身故保險金或喪葬費用保險金。
+條文依據：  
+- [第五條 保險範圍]  
+- [給付項目]</t>
+        </is>
+      </c>
+      <c r="D354" s="2" t="inlineStr">
+        <is>
+          <t>payout_items | 第五條 保險範圍 | summary | 第四條 名詞定義 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F354" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括：住院手術醫療保險金、門診手術醫療保險金、特定處置保險金、意外創傷縫合處置保險金、意外住院手術醫療保險金、祝壽保險金、所繳保險費的退還、身故保險金或喪葬費用保險金。
+條文依據：  
+- [第五條 保險範圍]  
+- [給付項目]</t>
+        </is>
+      </c>
+      <c r="G354" s="2" t="inlineStr"/>
+      <c r="H354" s="2" t="inlineStr"/>
+      <c r="I354" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.998103, "neutral": 0.001736, "contradiction": 0.000161, "factuality": 0.999839, "C_fact": 0.999839}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J354" s="5" t="n"/>
+      <c r="K354" s="5" t="n">
+        <v>0.999839</v>
+      </c>
+      <c r="L354" s="5" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M354" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:42:40</t>
+        </is>
+      </c>
+      <c r="N354" s="5" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B355" s="2" t="inlineStr">
+        <is>
+          <t>保險金額是否有上限?</t>
+        </is>
+      </c>
+      <c r="C355" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+有，保險金額的累計給付總額上限為保險單上所記載「保險金額」的一千五百倍，且不包含其他附約、附加條款或批註條款。
+條文依據：  
+- [第十六條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="D355" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 醫療保險金給付總額之上限 | 第三十條 保險金額之減少 | 第五條 保險範圍 | 第十九條 健康促進保險費折減 | 第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F355" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+有，保險金額的累計給付總額上限為保險單上所記載「保險金額」的一千五百倍，且不包含其他附約、附加條款或批註條款。
+條文依據：  
+- [第十六條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="G355" s="2" t="inlineStr"/>
+      <c r="H355" s="2" t="inlineStr"/>
+      <c r="I355" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.997554, "neutral": 0.002322, "contradiction": 0.000124, "factuality": 0.999876, "C_fact": 0.999876}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J355" s="5" t="n"/>
+      <c r="K355" s="5" t="n">
+        <v>0.999876</v>
+      </c>
+      <c r="L355" s="5" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M355" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:42:45</t>
+        </is>
+      </c>
+      <c r="N355" s="5" t="n">
+        <v>4.67</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B356" s="2" t="inlineStr">
+        <is>
+          <t>投保後5天發生手術，是否可以申請理賠?</t>
+        </is>
+      </c>
+      <c r="C356" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+投保後5天發生手術是否可以申請理賠，需視保險契約中是否有等待期間的規定。然而，提供的條款中未提及等待期間的相關內容，因此無法判斷是否符合理賠條件。
+條文依據：  
+[第五條 保險範圍]  
+[第十一條 住院手術醫療保險金]  
+[第二十條 除外責任（一)]</t>
+        </is>
+      </c>
+      <c r="D356" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第十一條 住院手術醫療保險金 | 第二十條 除外責任（一） | 第十二條 門診手術醫療保險金 | 第十三條 意外住院手術醫療保險金 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F356" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+投保後5天發生手術是否可以申請理賠，需視保險契約中是否有等待期間的規定。然而，提供的條款中未提及等待期間的相關內容，因此無法判斷是否符合理賠條件。
+條文依據：  
+找不到相關內容</t>
+        </is>
+      </c>
+      <c r="G356" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+投保後5天發生手術是否可以申請理賠，需視保險契約中是否有等待期間的規定。然而，提供的條款中未提及等待期間的相關內容，因此無法判斷是否符合理賠條件。
+條文依據：  
+[第五條 保險範圍]  
+[第十一條 住院手術醫療保險金]  
+[第二十條 除外責任（一)]</t>
+        </is>
+      </c>
+      <c r="H356" s="2" t="inlineStr"/>
+      <c r="I356" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.062334, "neutral": 0.926352, "contradiction": 0.011314, "factuality": 0.988686, "C_fact": 0.988686}, "C_conf": 0.9887}</t>
+        </is>
+      </c>
+      <c r="J356" s="5" t="n"/>
+      <c r="K356" s="5" t="n">
+        <v>0.988686</v>
+      </c>
+      <c r="L356" s="5" t="n">
+        <v>0.9887</v>
+      </c>
+      <c r="M356" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:43:02</t>
+        </is>
+      </c>
+      <c r="N356" s="5" t="n">
+        <v>16.6</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B357" s="2" t="inlineStr">
+        <is>
+          <t>住院手術醫療保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C357" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院手術醫療保險金的給付規定如下：  
+1. 被保險人於契約有效期間內因疾病或傷害，經醫師診斷必須於醫院住院接受附表一所列的手術治療且已實際接受手術者，本公司依保險單記載的「保險金額」乘以手術日當年度的「增額係數」，再乘以手術給付倍數，給付住院手術醫療保險金。  
+2. 同一次手術中，若於同一手術位置接受二項以上手術項目，僅給付手術給付倍數最高的手術項目。  
+3. 未載明於附表一的手術項目，將比照附表一內程度相當的手術項目決定給付倍數。  
+4. 以下情形不負給付責任：  
+   - 依據除外責任條款規定不在給付範圍內。  
+   - 不屬全民健康保險醫療服務給付項目及支付標準第二部第二章第七節或第三部第三章第四節第三項所列舉的手術。  
+條文依據：  
+- [第十一條 住院手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="D357" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 住院手術醫療保險金 | 第十三條 意外住院手術醫療保險金 | 第十二條 門診手術醫療保險金 | payout_items | 第二十條 除外責任（一） | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F357" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院手術醫療保險金的給付規定如下：  
+1. 被保險人於契約有效期間內因疾病或傷害，經醫師診斷必須於醫院住院接受附表一所列的手術治療且已實際接受手術者，本公司依保險單記載的「保險金額」乘以手術日當年度的「增額係數」，再乘以手術給付倍數，給付住院手術醫療保險金。  
+2. 同一次手術中，若於同一手術位置接受二項以上手術項目，僅給付手術給付倍數最高的手術項目。  
+3. 未載明於附表一的手術項目，將比照附表一內程度相當的手術項目決定給付倍數。  
+4. 以下情形不負給付責任：  
+   - 依據除外責任條款規定不在給付範圍內。  
+   - 不屬全民健康保險醫療服務給付項目及支付標準第二部第二章第七節或第三部第三章第四節第三項所列舉的手術。  
+條文依據：  
+- [第十一條 住院手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="G357" s="2" t="inlineStr"/>
+      <c r="H357" s="2" t="inlineStr"/>
+      <c r="I357" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.995175, "neutral": 0.004181, "contradiction": 0.000645, "factuality": 0.999355, "C_fact": 0.999355}, "C_conf": 0.9994}</t>
+        </is>
+      </c>
+      <c r="J357" s="5" t="n"/>
+      <c r="K357" s="5" t="n">
+        <v>0.999355</v>
+      </c>
+      <c r="L357" s="5" t="n">
+        <v>0.9994</v>
+      </c>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:43:12</t>
+        </is>
+      </c>
+      <c r="N357" s="5" t="n">
+        <v>10.03</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B358" s="2" t="inlineStr">
+        <is>
+          <t>門診手術醫療保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C358" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+門診手術醫療保險金的給付規定如下：  
+1. 被保險人需於契約有效期間內因疾病或傷害，經醫師診斷必須於醫院或診所門診接受附表一所列的手術治療，且已實際接受手術。  
+2. 給付金額計算方式為：保險單記載的「保險金額」乘以手術日當年度的「增額係數」，再乘以手術給付倍數。  
+3. 同一次手術中，若於同一手術位置接受二項以上手術項目，僅給付手術給付倍數最高的手術項目。  
+4. 同一保險單年度內，門診手術醫療保險金的給付以十次為限。  
+5. 未載明於附表一的手術項目，將與被保險人協議比照附表內的手術項目決定給付倍數。  
+6. 以下情形不予給付：  
+   - 依據契約除外責任條款規定不在給付範圍內。  
+   - 不屬全民健康保險醫療服務給付項目及支付標準第二部第二章第七節或第三部第三章第四節第三項所列舉的手術。  
+條文依據：  
+- [第十二條 門診手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="D358" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 門診手術醫療保險金 | 第十一條 住院手術醫療保險金 | payout_items | 第十三條 意外住院手術醫療保險金 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F358" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+門診手術醫療保險金的給付規定如下：  
+1. 被保險人需於契約有效期間內因疾病或傷害，經醫師診斷必須於醫院或診所門診接受附表一所列的手術治療，且已實際接受手術。  
+2. 給付金額計算方式為：保險單記載的「保險金額」乘以手術日當年度的「增額係數」，再乘以手術給付倍數。  
+3. 同一次手術中，若於同一手術位置接受二項以上手術項目，僅給付手術給付倍數最高的手術項目。  
+4. 同一保險單年度內，門診手術醫療保險金的給付以十次為限。  
+5. 未載明於附表一的手術項目，將與被保險人協議比照附表內的手術項目決定給付倍數。  
+6. 以下情形不予給付：  
+   - 依據契約除外責任條款規定不在給付範圍內。  
+   - 不屬全民健康保險醫療服務給付項目及支付標準第二部第二章第七節或第三部第三章第四節第三項所列舉的手術。  
+條文依據：  
+- [第十二條 門診手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="G358" s="2" t="inlineStr"/>
+      <c r="H358" s="2" t="inlineStr"/>
+      <c r="I358" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.98184, "neutral": 0.017761, "contradiction": 0.000399, "factuality": 0.999601, "C_fact": 0.999601}, "C_conf": 0.9996}</t>
+        </is>
+      </c>
+      <c r="J358" s="5" t="n"/>
+      <c r="K358" s="5" t="n">
+        <v>0.999601</v>
+      </c>
+      <c r="L358" s="5" t="n">
+        <v>0.9996</v>
+      </c>
+      <c r="M358" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:43:22</t>
+        </is>
+      </c>
+      <c r="N358" s="5" t="n">
+        <v>9.460000000000001</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B359" s="2" t="inlineStr">
+        <is>
+          <t>意外住院手術醫療保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C359" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外住院手術醫療保險金的給付規定如下：  
+1. 被保險人需於契約有效期間內且保險年齡未滿七十歲。  
+2. 因傷害經醫師診斷在住院期間必須接受手術治療且已接受手術者，保險公司按保險單所記載之「保險金額」的三倍，乘以手術日當年度之「增額係數」，給付「意外住院手術醫療保險金」。  
+3. 若同一次手術中於同一手術位置接受二項以上手術項目，僅給付一次「意外住院手術醫療保險金」。  
+條文依據：  
+- [第十三條 意外住院手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="D359" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 意外住院手術醫療保險金 | 第十一條 住院手術醫療保險金 | 第十五條 意外創傷縫合處置保險金 | 第二十條 除外責任（一） | 第十二條 門診手術醫療保險金 | 附表三：意外創傷縫合處置項目及給付倍數表 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F359" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外住院手術醫療保險金的給付規定如下：  
+1. 被保險人需於契約有效期間內且保險年齡未滿七十歲。  
+2. 因傷害經醫師診斷在住院期間必須接受手術治療且已接受手術者，保險公司按保險單所記載之「保險金額」的三倍，乘以手術日當年度之「增額係數」，給付「意外住院手術醫療保險金」。  
+3. 若同一次手術中於同一手術位置接受二項以上手術項目，僅給付一次「意外住院手術醫療保險金」。  
+條文依據：  
+- [第十三條 意外住院手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="G359" s="2" t="inlineStr"/>
+      <c r="H359" s="2" t="inlineStr"/>
+      <c r="I359" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.996237, "neutral": 0.003322, "contradiction": 0.000441, "factuality": 0.999559, "C_fact": 0.999559}, "C_conf": 0.9996}</t>
+        </is>
+      </c>
+      <c r="J359" s="5" t="n"/>
+      <c r="K359" s="5" t="n">
+        <v>0.999559</v>
+      </c>
+      <c r="L359" s="5" t="n">
+        <v>0.9996</v>
+      </c>
+      <c r="M359" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:43:36</t>
+        </is>
+      </c>
+      <c r="N359" s="5" t="n">
+        <v>14.34</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B360" s="2" t="inlineStr">
+        <is>
+          <t>特定處置保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C360" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+特定處置保險金的給付規定如下：  
+1. 被保險人因疾病或傷害，經醫師診斷必須於醫院或診所接受附表二所列之特定處置治療且已接受處置者，保險公司將依保險單記載的「保險金額」，乘以特定處置日當年度的「增額係數」，再乘以特定處置給付倍數，給付「特定處置保險金」。  
+2. 同一次處置治療中，若於同一治療位置接受二項以上特定處置項目，僅給付特定處置給付倍數最高的特定處置項目。  
+3. 若被保險人接受的處置未載明於附表二所列之特定處置項目，保險公司不負給付特定處置保險金的責任。  
+4. 同一保險單年度的「特定處置保險金」給付次數以十次為限。
+條文依據：  
+- [第十四條 特定處置保險金]</t>
+        </is>
+      </c>
+      <c r="D360" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 特定處置保險金 | 第十五條 意外創傷縫合處置保險金 | 附表二：特定處置項目及給付倍數表 | 第五條 保險範圍 | 附表三：意外創傷縫合處置項目及給付倍數表</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F360" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+特定處置保險金的給付規定如下：  
+1. 被保險人因疾病或傷害，經醫師診斷必須於醫院或診所接受附表二所列之特定處置治療且已接受處置者，保險公司將依保險單記載的「保險金額」，乘以特定處置日當年度的「增額係數」，再乘以特定處置給付倍數，給付「特定處置保險金」。  
+2. 同一次處置治療中，若於同一治療位置接受二項以上特定處置項目，僅給付特定處置給付倍數最高的特定處置項目。  
+3. 若被保險人接受的處置未載明於附表二所列之特定處置項目，保險公司不負給付特定處置保險金的責任。  
+4. 同一保險單年度的「特定處置保險金」給付次數以十次為限。
+條文依據：  
+- [第十四條 特定處置保險金]</t>
+        </is>
+      </c>
+      <c r="G360" s="2" t="inlineStr"/>
+      <c r="H360" s="2" t="inlineStr"/>
+      <c r="I360" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.989904, "neutral": 0.009121, "contradiction": 0.000975, "factuality": 0.999025, "C_fact": 0.999025}, "C_conf": 0.999}</t>
+        </is>
+      </c>
+      <c r="J360" s="5" t="n"/>
+      <c r="K360" s="5" t="n">
+        <v>0.9990250000000001</v>
+      </c>
+      <c r="L360" s="5" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="M360" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:43:52</t>
+        </is>
+      </c>
+      <c r="N360" s="5" t="n">
+        <v>15.65</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B361" s="2" t="inlineStr">
+        <is>
+          <t>意外創傷縫合處置保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C361" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外創傷縫合處置保險金的給付規定如下：  
+1. 被保險人因意外傷害事故，於醫院或診所接受附表三所列的意外創傷縫合處置治療者，本公司將依保險單所記載的「保險金額」，乘以當年度的「增額係數」，再乘以意外創傷縫合處置給付倍數，給付保險金。  
+2. 同一次意外傷害事故，僅就傷口最大者給付保險金，且以給付一次為限。  
+3. 若被保險人因同一意外傷害事故已申領住院手術醫療保險金或門診手術醫療保險金者，則不再給付意外創傷縫合處置保險金。
+條文依據：  
+- [第十五條 意外創傷縫合處置保險金]</t>
+        </is>
+      </c>
+      <c r="D361" s="2" t="inlineStr">
+        <is>
+          <t>第十五條 意外創傷縫合處置保險金 | 附表三：意外創傷縫合處置項目及給付倍數表 | 第十四條 特定處置保險金 | 第二十條 除外責任（一） | 第十三條 意外住院手術醫療保險金 | 附表二：特定處置項目及給付倍數表</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F361" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外創傷縫合處置保險金的給付規定如下：  
+1. 被保險人因意外傷害事故，於醫院或診所接受附表三所列的意外創傷縫合處置治療者，本公司將依保險單所記載的「保險金額」，乘以當年度的「增額係數」，再乘以意外創傷縫合處置給付倍數，給付保險金。  
+2. 同一次意外傷害事故，僅就傷口最大者給付保險金，且以給付一次為限。  
+3. 若被保險人因同一意外傷害事故已申領住院手術醫療保險金或門診手術醫療保險金者，則不再給付意外創傷縫合處置保險金。
+條文依據：  
+- [第十五條 意外創傷縫合處置保險金]</t>
+        </is>
+      </c>
+      <c r="G361" s="2" t="inlineStr"/>
+      <c r="H361" s="2" t="inlineStr"/>
+      <c r="I361" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.991853, "neutral": 0.007355, "contradiction": 0.000792, "factuality": 0.999208, "C_fact": 0.999208}, "C_conf": 0.9992}</t>
+        </is>
+      </c>
+      <c r="J361" s="5" t="n"/>
+      <c r="K361" s="5" t="n">
+        <v>0.999208</v>
+      </c>
+      <c r="L361" s="5" t="n">
+        <v>0.9992</v>
+      </c>
+      <c r="M361" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:44:01</t>
+        </is>
+      </c>
+      <c r="N361" s="5" t="n">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B362" s="2" t="inlineStr">
+        <is>
+          <t>醫療保險金給付總額之上限</t>
+        </is>
+      </c>
+      <c r="C362" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+醫療保險金給付總額之上限為保險單上所記載的「保險金額」之一千五百倍，且不包含其他附約、附加條款及批註條款。
+條文依據：  
+- [第十六條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="D362" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 醫療保險金給付總額之上限 | 第十二條 門診手術醫療保險金 | 第五條 保險範圍 | 第十一條 住院手術醫療保險金 | 第十三條 意外住院手術醫療保險金 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F362" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+醫療保險金給付總額之上限為保險單上所記載的「保險金額」之一千五百倍，且不包含其他附約、附加條款及批註條款。
+條文依據：  
+- [第十六條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="G362" s="2" t="inlineStr"/>
+      <c r="H362" s="2" t="inlineStr"/>
+      <c r="I362" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.996964, "neutral": 0.002863, "contradiction": 0.000174, "factuality": 0.999826, "C_fact": 0.999826}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J362" s="5" t="n"/>
+      <c r="K362" s="5" t="n">
+        <v>0.999826</v>
+      </c>
+      <c r="L362" s="5" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M362" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:44:07</t>
+        </is>
+      </c>
+      <c r="N362" s="5" t="n">
+        <v>5.74</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B363" s="2" t="inlineStr">
+        <is>
+          <t>祝壽保險金的領取規定為何?</t>
+        </is>
+      </c>
+      <c r="C363" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+祝壽保險金的領取規定如下：  
+1. 被保險人需於本契約有效期間且保險年齡到達九十九歲之保險單週年日仍生存，方可申領祝壽保險金。  
+2. 受益人申領祝壽保險金時，需檢具以下文件：  
+   - 保險單或其謄本  
+   - 保險金申請書  
+   - 受益人的身分證明  
+條文依據：  
+- [第十七條 祝壽保險金]  
+- [第二十六條 祝壽保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D363" s="2" t="inlineStr">
+        <is>
+          <t>第十七條 祝壽保險金 | 第二十六條 祝壽保險金的申領 | 第十一條至第十五條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | 第二十三條 保險事故的通知與保險金的申請時間 | 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F363" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+祝壽保險金的領取規定如下：  
+1. 被保險人需於本契約有效期間且保險年齡到達九十九歲之保險單週年日仍生存，方可申領祝壽保險金。  
+2. 受益人申領祝壽保險金時，需檢具以下文件：  
+   - 保險單或其謄本  
+   - 保險金申請書  
+   - 受益人的身分證明  
+條文依據：  
+- [第十七條 祝壽保險金]  
+- [第二十六條 祝壽保險金的申領]</t>
+        </is>
+      </c>
+      <c r="G363" s="2" t="inlineStr"/>
+      <c r="H363" s="2" t="inlineStr"/>
+      <c r="I363" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.998662, "neutral": 0.001196, "contradiction": 0.000141, "factuality": 0.999859, "C_fact": 0.999859}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J363" s="5" t="n"/>
+      <c r="K363" s="5" t="n">
+        <v>0.9998590000000001</v>
+      </c>
+      <c r="L363" s="5" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M363" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:44:10</t>
+        </is>
+      </c>
+      <c r="N363" s="5" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B364" s="2" t="inlineStr">
+        <is>
+          <t>身故時領取保險金有什麼規則?</t>
+        </is>
+      </c>
+      <c r="C364" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+身故時領取保險金的規則如下：  
+1. 被保險人於契約有效期間內身故，本公司按「當年度保險金額」給付「身故保險金」。  
+2. 若被保險人身故時實際年齡未滿十五足歲，本公司退還「所繳保險費」予要保人，不適用「當年度保險金額」的約定。  
+3. 若被保險人於訂立契約時受監護宣告且尚未撤銷，其身故保險金改為喪葬費用保險金，且喪葬費用保險金額不得超過遺產稅喪葬費扣除額之半數，超過部分不負給付責任。  
+4. 受益人申領身故保險金或喪葬費用保險金時，需提供保險單、死亡證明書及除戶戶籍謄本、保險金申請書及受益人身分證明。  
+條文依據：  
+- [第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金]  
+- [第二十七條 身故保險金或喪葬費用保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D364" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金 | 第二十七條 身故保險金或喪葬費用保險金的申領 | 第十一條至第十五條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | 第二十一條 除外責任（二） | 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F364" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+身故時領取保險金的規則如下：  
+1. 被保險人於契約有效期間內身故，本公司按「當年度保險金額」給付「身故保險金」。  
+2. 若被保險人身故時實際年齡未滿十五足歲，本公司退還「所繳保險費」予要保人，不適用「當年度保險金額」的約定。  
+3. 若被保險人於訂立契約時受監護宣告且尚未撤銷，其身故保險金改為喪葬費用保險金，且喪葬費用保險金額不得超過遺產稅喪葬費扣除額之半數，超過部分不負給付責任。  
+4. 受益人申領身故保險金或喪葬費用保險金時，需提供保險單、死亡證明書及除戶戶籍謄本、保險金申請書及受益人身分證明。  
+條文依據：  
+- [第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金]  
+- [第二十七條 身故保險金或喪葬費用保險金的申領]</t>
+        </is>
+      </c>
+      <c r="G364" s="2" t="inlineStr"/>
+      <c r="H364" s="2" t="inlineStr"/>
+      <c r="I364" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.321265, "neutral": 0.676385, "contradiction": 0.00235, "factuality": 0.99765, "C_fact": 0.99765}, "C_conf": 0.9977}</t>
+        </is>
+      </c>
+      <c r="J364" s="5" t="n"/>
+      <c r="K364" s="5" t="n">
+        <v>0.99765</v>
+      </c>
+      <c r="L364" s="5" t="n">
+        <v>0.9977</v>
+      </c>
+      <c r="M364" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:44:19</t>
+        </is>
+      </c>
+      <c r="N364" s="5" t="n">
+        <v>8.220000000000001</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B365" s="2" t="inlineStr">
+        <is>
+          <t>什麼情況下可以保費折減?</t>
+        </is>
+      </c>
+      <c r="C365" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人年齡達20歲（含）以上，並使用保險公司指定程式加入健康計劃，於「指定日期」的會員等級符合進階會員或菁英會員（或更高等級）標準者，可享次一保險單年度的保費折減。折減比例為進階會員2%，菁英會員或更高等級3%。但豁免或復效的保險費不適用折減約定。
+條文依據：  
+- [第十九條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="D365" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 健康促進保險費折減 | 第三十條 保險金額之減少 | 第二十條 除外責任（一） | 第三十一條 投保年齡的計算及錯誤的處理 | 第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F365" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人年齡達20歲（含）以上，並使用保險公司指定程式加入健康計劃，於「指定日期」的會員等級符合進階會員或菁英會員（或更高等級）標準者，可享次一保險單年度的保費折減。折減比例為進階會員2%，菁英會員或更高等級3%。但豁免或復效的保險費不適用折減約定。
+條文依據：  
+- [第十九條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="G365" s="2" t="inlineStr"/>
+      <c r="H365" s="2" t="inlineStr"/>
+      <c r="I365" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.995136, "neutral": 0.00461, "contradiction": 0.000254, "factuality": 0.999746, "C_fact": 0.999746}, "C_conf": 0.9997}</t>
+        </is>
+      </c>
+      <c r="J365" s="5" t="n"/>
+      <c r="K365" s="5" t="n">
+        <v>0.999746</v>
+      </c>
+      <c r="L365" s="5" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="M365" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:44:30</t>
+        </is>
+      </c>
+      <c r="N365" s="5" t="n">
+        <v>11.36</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B366" s="2" t="inlineStr">
+        <is>
+          <t>角膜切除術是否可以申請理賠?</t>
+        </is>
+      </c>
+      <c r="C366" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+角膜切除術可以申請理賠，該手術項目已列於「手術項目表」中，給付倍數為5倍。
+條文依據：  
+- 附表一：手術項目與給付倍數 - 1305 角膜切除術</t>
+        </is>
+      </c>
+      <c r="D366" s="2" t="inlineStr">
+        <is>
+          <t>附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F366" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+角膜切除術可以申請理賠，該手術項目已列於「手術項目表」中，給付倍數為5倍。
+條文依據：  
+- 附表一：手術項目與給付倍數 - 1305 角膜切除術</t>
+        </is>
+      </c>
+      <c r="G366" s="2" t="inlineStr"/>
+      <c r="H366" s="2" t="inlineStr"/>
+      <c r="I366" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.866441, "neutral": 0.127973, "contradiction": 0.005586, "factuality": 0.994414, "C_fact": 0.994414}, "C_conf": 0.9944}</t>
+        </is>
+      </c>
+      <c r="J366" s="5" t="n"/>
+      <c r="K366" s="5" t="n">
+        <v>0.994414</v>
+      </c>
+      <c r="L366" s="5" t="n">
+        <v>0.9944</v>
+      </c>
+      <c r="M366" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:44:35</t>
+        </is>
+      </c>
+      <c r="N366" s="5" t="n">
+        <v>4.41</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B367" s="2" t="inlineStr">
+        <is>
+          <t>白內障手術是否可以申請理賠?</t>
+        </is>
+      </c>
+      <c r="C367" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+白內障手術是否可以申請理賠需視手術是否符合附表一所列的手術項目及給付倍數。如果白內障手術屬於附表一中所列的手術項目，且不屬於除外責任條款規定的範圍，則可申請理賠。若手術未載明於附表一，則需與保險公司協議比照附表一內的手術項目決定給付倍數。此外，若手術屬於全民健康保險醫療服務給付項目及支付標準所列舉的手術，則符合理賠條件；反之，若不屬於全民健康保險醫療服務給付項目，則不予理賠。
+條文依據：  
+- [第十二條 門診手術醫療保險金]  
+- [第十一條 住院手術醫療保險金]  
+- [第二十條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D367" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 門診手術醫療保險金 | 第二十條 除外責任（一） | 附表一：手術項目與給付倍數 | payout_items | 第十一條 住院手術醫療保險金</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F367" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+白內障手術是否可以申請理賠需視手術是否符合附表一所列的手術項目及給付倍數。如果白內障手術屬於附表一中所列的手術項目，且不屬於除外責任條款規定的範圍，則可申請理賠。若手術未載明於附表一，則需與保險公司協議比照附表一內的手術項目決定給付倍數。此外，若手術屬於全民健康保險醫療服務給付項目及支付標準所列舉的手術，則符合理賠條件；反之，若不屬於全民健康保險醫療服務給付項目，則不予理賠。
+條文依據：  
+- [第十二條 門診手術醫療保險金]  
+- [第十一條 住院手術醫療保險金]  
+- [第二十條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="G367" s="2" t="inlineStr"/>
+      <c r="H367" s="2" t="inlineStr"/>
+      <c r="I367" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.498378, "neutral": 0.493207, "contradiction": 0.008415, "factuality": 0.991585, "C_fact": 0.991585}, "C_conf": 0.9916}</t>
+        </is>
+      </c>
+      <c r="J367" s="5" t="n"/>
+      <c r="K367" s="5" t="n">
+        <v>0.991585</v>
+      </c>
+      <c r="L367" s="5" t="n">
+        <v>0.9916</v>
+      </c>
+      <c r="M367" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:44:44</t>
+        </is>
+      </c>
+      <c r="N367" s="5" t="n">
+        <v>8.630000000000001</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B368" s="2" t="inlineStr">
+        <is>
+          <t>保障範圍包括哪些項目？</t>
+        </is>
+      </c>
+      <c r="C368" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括：意外事故身故保險金或喪葬費用保險金、意外事故失能保險金、每月生活照護保險金、重大燒燙傷保險金、意外骨折保險金、傷害醫療日額保險金、意外創傷縫合處置保險金。
+條文依據：  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="D368" s="2" t="inlineStr">
+        <is>
+          <t>payout_items | 第五條 保險範圍 | 第十五條 每月生活照護保險金的給付 | 第三十條 不保事項 | 附表二：失能程度與保險金給付表</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F368" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括：意外事故身故保險金或喪葬費用保險金、意外事故失能保險金、每月生活照護保險金、重大燒燙傷保險金、意外骨折保險金、傷害醫療日額保險金、意外創傷縫合處置保險金。
+條文依據：  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="G368" s="2" t="inlineStr"/>
+      <c r="H368" s="2" t="inlineStr"/>
+      <c r="I368" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.997935, "neutral": 0.001907, "contradiction": 0.000158, "factuality": 0.999842, "C_fact": 0.999842}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J368" s="5" t="n"/>
+      <c r="K368" s="5" t="n">
+        <v>0.999842</v>
+      </c>
+      <c r="L368" s="5" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M368" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:44:57</t>
+        </is>
+      </c>
+      <c r="N368" s="5" t="n">
+        <v>12.88</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B369" s="2" t="inlineStr">
+        <is>
+          <t>發生意外事故身故，理賠內容為何?</t>
+        </is>
+      </c>
+      <c r="C369" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外事故身故的理賠內容包括「意外事故身故保險金」或「喪葬費用保險金」，其金額依意外傷害事故的種類而定：  
+1. 一般意外傷害事故：給付「傷害醫療保險金日額」的五百倍。  
+2. 特定意外傷害事故：給付「傷害醫療保險金日額」的一千倍。  
+若被保險人於意外傷害事故發生後超過一百八十日身故，但受益人能證明身故與該事故具有因果關係，本公司仍依上述約定給付保險金，不受一百八十日限制。此外，若被保險人受監護宣告尚未撤銷，其理賠內容改為「喪葬費用保險金」，且喪葬費用保險金額不得超過遺產稅喪葬費扣除額之半數，超過部分不負給付責任。  
+條文依據：  
+- [第十二條 意外事故身故保險金或喪葬費用保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D369" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 意外事故身故保險金或喪葬費用保險金的給付 | 第十四條 保險給付的限制 | payout_items | 第十一條 契約的終止（二） | 第二十一條 失蹤處理</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F369" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外事故身故的理賠內容包括「意外事故身故保險金」或「喪葬費用保險金」，其金額依意外傷害事故的種類而定：  
+1. 一般意外傷害事故：給付「傷害醫療保險金日額」的五百倍。  
+2. 特定意外傷害事故：給付「傷害醫療保險金日額」的一千倍。  
+若被保險人於意外傷害事故發生後超過一百八十日身故，但受益人能證明身故與該事故具有因果關係，本公司仍依上述約定給付保險金，不受一百八十日限制。此外，若被保險人受監護宣告尚未撤銷，其理賠內容改為「喪葬費用保險金」，且喪葬費用保險金額不得超過遺產稅喪葬費扣除額之半數，超過部分不負給付責任。  
+條文依據：  
+- [第十二條 意外事故身故保險金或喪葬費用保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G369" s="2" t="inlineStr"/>
+      <c r="H369" s="2" t="inlineStr"/>
+      <c r="I369" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.994583, "neutral": 0.005224, "contradiction": 0.000193, "factuality": 0.999807, "C_fact": 0.999807}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J369" s="5" t="n"/>
+      <c r="K369" s="5" t="n">
+        <v>0.999807</v>
+      </c>
+      <c r="L369" s="5" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M369" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:45:17</t>
+        </is>
+      </c>
+      <c r="N369" s="5" t="n">
+        <v>20.21</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B370" s="2" t="inlineStr">
+        <is>
+          <t>意外事故失能保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C370" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外事故失能保險金的給付條件如下：  
+1. 被保險人於契約有效期間內遭受意外傷害事故，並於事故發生後180日內致成附表二所列失能程度之一者，本公司依意外傷害事故種類及失能程度，按以下金額給付：  
+   - 一般意外傷害事故：「傷害醫療保險金日額」的500倍乘以附表二給付比例。  
+   - 特定意外傷害事故：「傷害醫療保險金日額」的1000倍乘以附表二給付比例。  
+2. 若被保險人超過180日後致成失能，受益人能證明失能與事故具有因果關係者，本公司仍依上述規定給付，不受180日限制。  
+3. 同一事故致成多項失能時，僅給付同一手或足中較嚴重項目的失能保險金，且給付金額以事故種類的上限為限。  
+4. 若失能合併以前的失能，僅給付較嚴重項目，但需扣除以前已給付的保險金。  
+條文依據：  
+- [第十三條 意外事故失能保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D370" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 意外事故失能保險金的給付 | 第十五條 每月生活照護保險金的給付 | 第十四條 保險給付的限制 | 第十二條 意外事故身故保險金或喪葬費用保險金的給付 | 第二十三條 意外事故失能保險金的申領 | 附表二：失能程度與保險金給付表</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F370" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外事故失能保險金的給付條件如下：  
+1. 被保險人於契約有效期間內遭受意外傷害事故，並於事故發生後180日內致成附表二所列失能程度之一者，本公司依意外傷害事故種類及失能程度，按以下金額給付：  
+   - 一般意外傷害事故：「傷害醫療保險金日額」的500倍乘以附表二給付比例。  
+   - 特定意外傷害事故：「傷害醫療保險金日額」的1000倍乘以附表二給付比例。  
+2. 若被保險人超過180日後致成失能，受益人能證明失能與事故具有因果關係者，本公司仍依上述規定給付，不受180日限制。  
+3. 同一事故致成多項失能時，僅給付同一手或足中較嚴重項目的失能保險金，且給付金額以事故種類的上限為限。  
+4. 若失能合併以前的失能，僅給付較嚴重項目，但需扣除以前已給付的保險金。  
+條文依據：  
+- [第十三條 意外事故失能保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G370" s="2" t="inlineStr"/>
+      <c r="H370" s="2" t="inlineStr"/>
+      <c r="I370" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.069361, "neutral": 0.92181, "contradiction": 0.008829, "factuality": 0.991171, "C_fact": 0.991171}, "C_conf": 0.9912}</t>
+        </is>
+      </c>
+      <c r="J370" s="5" t="n"/>
+      <c r="K370" s="5" t="n">
+        <v>0.991171</v>
+      </c>
+      <c r="L370" s="5" t="n">
+        <v>0.9912</v>
+      </c>
+      <c r="M370" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:45:44</t>
+        </is>
+      </c>
+      <c r="N370" s="5" t="n">
+        <v>26.36</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B371" s="2" t="inlineStr">
+        <is>
+          <t>每月生活照護保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C371" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+每月生活照護保險金的給付條件如下：  
+1. 被保險人於契約有效期間內遭受意外傷害事故，並於事故發生後180日內致成附表二所列第一級至第六級失能程度之一時，本公司自失能診斷確定當日起，按「傷害醫療保險金日額」的20倍乘以附表二給付比例所得之金額，按月給付，最多以12個月為限。  
+2. 若失能診斷確定後的前四個週年日，被保險人仍生存且契約有效，本公司自各該週年日起，依相同計算方式按月給付，最多以12個月為限。  
+3. 若被保險人於事故發生後超過180日才致成失能，受益人需證明失能與事故具有因果關係，本公司仍可依上述規定給付，不受180日限制。  
+4. 同一事故若致成多項失能，僅給付較嚴重項目，且最高以「傷害醫療保險金日額」的20倍為限。  
+5. 累計給付金額最高以「傷害醫療保險金日額」的1200倍為限。  
+條文依據：  
+- [第十五條 每月生活照護保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D371" s="2" t="inlineStr">
+        <is>
+          <t>第二十四條 每月生活照護保險金的申領 | 第十五條 每月生活照護保險金的給付 | payout_items | 第十八條 傷害醫療日額保險金的給付 | 第五條 保險範圍 | 附表二：失能程度與保險金給付表 | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F371" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+每月生活照護保險金的給付條件如下：  
+1. 被保險人於契約有效期間內遭受意外傷害事故，並於事故發生後180日內致成附表二所列第一級至第六級失能程度之一時，本公司自失能診斷確定當日起，按「傷害醫療保險金日額」的20倍乘以附表二給付比例所得之金額，按月給付，最多以12個月為限。  
+2. 若失能診斷確定後的前四個週年日，被保險人仍生存且契約有效，本公司自各該週年日起，依相同計算方式按月給付，最多以12個月為限。  
+3. 若被保險人於事故發生後超過180日才致成失能，受益人需證明失能與事故具有因果關係，本公司仍可依上述規定給付，不受180日限制。  
+4. 同一事故若致成多項失能，僅給付較嚴重項目，且最高以「傷害醫療保險金日額」的20倍為限。  
+5. 累計給付金額最高以「傷害醫療保險金日額」的1200倍為限。  
+條文依據：  
+- [第十五條 每月生活照護保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G371" s="2" t="inlineStr"/>
+      <c r="H371" s="2" t="inlineStr"/>
+      <c r="I371" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.263108, "neutral": 0.724936, "contradiction": 0.011955, "factuality": 0.988045, "C_fact": 0.988045}, "C_conf": 0.988}</t>
+        </is>
+      </c>
+      <c r="J371" s="5" t="n"/>
+      <c r="K371" s="5" t="n">
+        <v>0.988045</v>
+      </c>
+      <c r="L371" s="5" t="n">
+        <v>0.988</v>
+      </c>
+      <c r="M371" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:46:01</t>
+        </is>
+      </c>
+      <c r="N371" s="5" t="n">
+        <v>16.61</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B372" s="2" t="inlineStr">
+        <is>
+          <t>重大燒燙傷保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C372" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+重大燒燙傷保險金的給付條件為：被保險人於本契約有效期間內遭受「意外傷害事故」，蒙受燒燙傷之傷害，經診斷符合「重大燒燙傷」者，本公司按「傷害醫療保險金日額」的二百五十倍給付「重大燒燙傷保險金」。此保險金的給付以一次為限。
+條文依據：  
+- [第十六條 重大燒燙傷保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D372" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 重大燒燙傷保險金的給付 | 第二十五條 重大燒燙傷保險金的申領 | 第五條 保險範圍 | payout_items | 第二十九條 除外責任（原因）</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F372" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+重大燒燙傷保險金的給付條件為：被保險人於本契約有效期間內遭受「意外傷害事故」，蒙受燒燙傷之傷害，經診斷符合「重大燒燙傷」者，本公司按「傷害醫療保險金日額」的二百五十倍給付「重大燒燙傷保險金」。此保險金的給付以一次為限。
+條文依據：  
+- [第十六條 重大燒燙傷保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G372" s="2" t="inlineStr"/>
+      <c r="H372" s="2" t="inlineStr"/>
+      <c r="I372" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.996109, "neutral": 0.003767, "contradiction": 0.000124, "factuality": 0.999876, "C_fact": 0.999876}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J372" s="5" t="n"/>
+      <c r="K372" s="5" t="n">
+        <v>0.999876</v>
+      </c>
+      <c r="L372" s="5" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M372" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:46:06</t>
+        </is>
+      </c>
+      <c r="N372" s="5" t="n">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B373" s="2" t="inlineStr">
+        <is>
+          <t>意外骨折保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C373" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外骨折保險金的給付條件如下：  
+1. 被保險人於契約有效期間內遭受「意外傷害事故」，自事故發生之日起一百八十日內，經合格醫院或診所診斷為附表三骨折別表所列骨折項目之一（含不完全骨折及骨骼龜裂），本公司按「傷害醫療保險金日額」的二倍給付。  
+2. 若超過一百八十日診斷確定骨折，受益人需證明骨折與事故具有因果關係，本公司仍給付保險金，不受一百八十日限制。  
+3. 同一意外傷害事故僅給付一次意外骨折保險金。  
+4. 若骨折非屬附表三骨折別表所列項目，需由本公司與被保險人協議核付；但若骨折部位屬骨折別表內明訂不給付之部位，本公司不負給付責任。
+條文依據：  
+- [第十七條 意外骨折保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D373" s="2" t="inlineStr">
+        <is>
+          <t>第十七條 意外骨折保險金的給付 | 第十八條 傷害醫療日額保險金的給付 | 第二十六條 意外骨折保險金的申領 | 第十三條 意外事故失能保險金的給付 | 第十九條 意外創傷縫合處置保險金的給付 | 附表二：失能程度與保險金給付表 | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F373" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外骨折保險金的給付條件如下：  
+1. 被保險人於契約有效期間內遭受「意外傷害事故」，自事故發生之日起一百八十日內，經合格醫院或診所診斷為附表三骨折別表所列骨折項目之一（含不完全骨折及骨骼龜裂），本公司按「傷害醫療保險金日額」的二倍給付。  
+2. 若超過一百八十日診斷確定骨折，受益人需證明骨折與事故具有因果關係，本公司仍給付保險金，不受一百八十日限制。  
+3. 同一意外傷害事故僅給付一次意外骨折保險金。  
+4. 若骨折非屬附表三骨折別表所列項目，需由本公司與被保險人協議核付；但若骨折部位屬骨折別表內明訂不給付之部位，本公司不負給付責任。
+條文依據：  
+- [第十七條 意外骨折保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G373" s="2" t="inlineStr"/>
+      <c r="H373" s="2" t="inlineStr"/>
+      <c r="I373" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.992403, "neutral": 0.007022, "contradiction": 0.000575, "factuality": 0.999425, "C_fact": 0.999425}, "C_conf": 0.9994}</t>
+        </is>
+      </c>
+      <c r="J373" s="5" t="n"/>
+      <c r="K373" s="5" t="n">
+        <v>0.999425</v>
+      </c>
+      <c r="L373" s="5" t="n">
+        <v>0.9994</v>
+      </c>
+      <c r="M373" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:46:12</t>
+        </is>
+      </c>
+      <c r="N373" s="5" t="n">
+        <v>5.87</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B374" s="2" t="inlineStr">
+        <is>
+          <t>傷害醫療日額保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C374" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+傷害醫療日額保險金的給付條件如下：  
+1. 被保險人於契約有效期間內遭受意外傷害事故，並於事故發生後180日內在醫院接受住院治療者，本公司按傷害醫療保險金日額乘以實際住院日數給付，最高以90日為限。  
+2. 若治療超過180日，受益人能證明治療與事故具有因果關係者，仍可依上述規定給付，不受180日限制。  
+3. 若因骨折未住院或住院日數未達附表三骨折別表所訂日數，未住院部分按骨折別表所訂日數乘以傷害醫療保險金日額的二分之一給付，合計給付日數以骨折別表所訂日數為上限。  
+4. 骨折給付依骨骼損傷程度分為完全骨折、不完全骨折及骨骼龜裂，分別按完全骨折日數的100%、50%及25%給付。同時發生多項骨折時，僅給付較高等級的保險金。
+條文依據：  
+- [第十八條 傷害醫療日額保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D374" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 傷害醫療日額保險金的給付 | 第二十七條 傷害醫療日額保險金的申領 | 第十五條 每月生活照護保險金的給付 | 第三十四條 傷害醫療保險金日額之減少 | 第十九條 意外創傷縫合處置保險金的給付 | 附表二：失能程度與保險金給付表 | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F374" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+傷害醫療日額保險金的給付條件如下：  
+1. 被保險人於契約有效期間內遭受意外傷害事故，並於事故發生後180日內在醫院接受住院治療者，本公司按傷害醫療保險金日額乘以實際住院日數給付，最高以90日為限。  
+2. 若治療超過180日，受益人能證明治療與事故具有因果關係者，仍可依上述規定給付，不受180日限制。  
+3. 若因骨折未住院或住院日數未達附表三骨折別表所訂日數，未住院部分按骨折別表所訂日數乘以傷害醫療保險金日額的二分之一給付，合計給付日數以骨折別表所訂日數為上限。  
+4. 骨折給付依骨骼損傷程度分為完全骨折、不完全骨折及骨骼龜裂，分別按完全骨折日數的100%、50%及25%給付。同時發生多項骨折時，僅給付較高等級的保險金。
+條文依據：  
+- [第十八條 傷害醫療日額保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G374" s="2" t="inlineStr"/>
+      <c r="H374" s="2" t="inlineStr"/>
+      <c r="I374" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.678033, "neutral": 0.320251, "contradiction": 0.001716, "factuality": 0.998284, "C_fact": 0.998284}, "C_conf": 0.9983}</t>
+        </is>
+      </c>
+      <c r="J374" s="5" t="n"/>
+      <c r="K374" s="5" t="n">
+        <v>0.9982839999999999</v>
+      </c>
+      <c r="L374" s="5" t="n">
+        <v>0.9983</v>
+      </c>
+      <c r="M374" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:46:19</t>
+        </is>
+      </c>
+      <c r="N374" s="5" t="n">
+        <v>7.68</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B375" s="2" t="inlineStr">
+        <is>
+          <t>意外創傷縫合處置保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C375" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外創傷縫合處置保險金的給付條件為：被保險人於契約有效期間內遭受「意外傷害事故」，並於「醫院」或「診所」經醫師診斷必須接受創傷縫合處置治療且已接受縫合處置者，本公司按「傷害醫療保險金日額」給付「意外創傷縫合處置保險金」。同一意外傷害事故僅給付一次。
+條文依據：  
+- [第十九條 意外創傷縫合處置保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D375" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 意外創傷縫合處置保險金的給付 | 第二十八條 意外創傷縫合處置保險金的申領 | 第五條 保險範圍 | 第十七條 意外骨折保險金的給付 | payout_items | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F375" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外創傷縫合處置保險金的給付條件為：被保險人於契約有效期間內遭受「意外傷害事故」，並於「醫院」或「診所」經醫師診斷必須接受創傷縫合處置治療且已接受縫合處置者，本公司按「傷害醫療保險金日額」給付「意外創傷縫合處置保險金」。同一意外傷害事故僅給付一次。
+條文依據：  
+- [第十九條 意外創傷縫合處置保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G375" s="2" t="inlineStr"/>
+      <c r="H375" s="2" t="inlineStr"/>
+      <c r="I375" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.995573, "neutral": 0.004283, "contradiction": 0.000144, "factuality": 0.999856, "C_fact": 0.999856}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J375" s="5" t="n"/>
+      <c r="K375" s="5" t="n">
+        <v>0.999856</v>
+      </c>
+      <c r="L375" s="5" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M375" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:46:26</t>
+        </is>
+      </c>
+      <c r="N375" s="5" t="n">
+        <v>6.13</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B376" s="2" t="inlineStr">
+        <is>
+          <t>因意外導致視力衰退，是否能申請理賠?</t>
+        </is>
+      </c>
+      <c r="C376" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+因意外導致視力衰退是否能申請理賠，需符合以下條件：  
+1. 視力永久在萬國式視力表0.02以下，或眼球喪失、摘出、僅能辨明暗或辨眼前一公尺以內手動或辨眼前五公分以內指數者。  
+2. 以自傷害之日起經過六個月的治療為判定原則，但若屬眼球摘出等明顯無法復原的情況，則不受六個月治療期間限制。  
+若符合上述條件，則可申請理賠。  
+條文依據：  
+- 註2</t>
+        </is>
+      </c>
+      <c r="D376" s="2" t="inlineStr">
+        <is>
+          <t>第二十三條 意外事故失能保險金的申領 | 第十三條 意外事故失能保險金的給付 | 註2： | 第三十條 不保事項 | 第二十六條 意外骨折保險金的申領 | 附表二：失能程度與保險金給付表</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F376" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+因意外導致視力衰退是否能申請理賠，需符合以下條件：  
+1. 視力永久在萬國式視力表0.02以下，或眼球喪失、摘出、僅能辨明暗或辨眼前一公尺以內手動或辨眼前五公分以內指數者。  
+2. 以自傷害之日起經過六個月的治療為判定原則，但若屬眼球摘出等明顯無法復原的情況，則不受六個月治療期間限制。  
+若符合上述條件，則可申請理賠。  
+條文依據：  
+- 註2</t>
+        </is>
+      </c>
+      <c r="G376" s="2" t="inlineStr"/>
+      <c r="H376" s="2" t="inlineStr"/>
+      <c r="I376" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.903969, "neutral": 0.092263, "contradiction": 0.003768, "factuality": 0.996232, "C_fact": 0.996232}, "C_conf": 0.9962}</t>
+        </is>
+      </c>
+      <c r="J376" s="5" t="n"/>
+      <c r="K376" s="5" t="n">
+        <v>0.996232</v>
+      </c>
+      <c r="L376" s="5" t="n">
+        <v>0.9962</v>
+      </c>
+      <c r="M376" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:46:32</t>
+        </is>
+      </c>
+      <c r="N376" s="5" t="n">
+        <v>6.34</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B377" s="2" t="inlineStr">
+        <is>
+          <t>肋骨骨折是否可以申請理賠?理賠金額為多少?</t>
+        </is>
+      </c>
+      <c r="C377" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+肋骨骨折可以申請理賠，理賠金額需依肋骨骨折的情形判定：  
+1. 若肋骨完全骨折且未住院治療，依附表三骨折別表所訂完全骨折日數（20天）乘以「傷害醫療保險金日額」的二分之一給付。  
+2. 若肋骨完全骨折且住院治療，依實際住院日數乘以「傷害醫療保險金日額」給付，但最高給付日數以附表三骨折別表所訂日數（20天）為上限。  
+3. 若肋骨不完全骨折，按完全骨折日數（20天）的二分之一給付；若肋骨龜裂，按完全骨折日數的四分之一給付。  
+條文依據：  
+- [第十八條 傷害醫療日額保險金的給付]  
+- [附表三：骨折別表]</t>
+        </is>
+      </c>
+      <c r="D377" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 傷害醫療日額保險金的給付 | 第十七條 意外骨折保險金的給付 | 第二十六條 意外骨折保險金的申領 | 第三十條 不保事項 | 第五條 保險範圍 | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F377" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+肋骨骨折可以申請理賠，理賠金額需依肋骨骨折的情形判定：  
+1. 若肋骨完全骨折且未住院治療，依附表三骨折別表所訂完全骨折日數（20天）乘以「傷害醫療保險金日額」的二分之一給付。  
+2. 若肋骨完全骨折且住院治療，依實際住院日數乘以「傷害醫療保險金日額」給付，但最高給付日數以附表三骨折別表所訂日數（20天）為上限。  
+3. 若肋骨不完全骨折，按完全骨折日數（20天）的二分之一給付；若肋骨龜裂，按完全骨折日數的四分之一給付。  
+條文依據：  
+- [第十八條 傷害醫療日額保險金的給付]  
+- [附表三：骨折別表]</t>
+        </is>
+      </c>
+      <c r="G377" s="2" t="inlineStr"/>
+      <c r="H377" s="2" t="inlineStr"/>
+      <c r="I377" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.896895, "neutral": 0.092865, "contradiction": 0.01024, "factuality": 0.98976, "C_fact": 0.98976}, "C_conf": 0.9898}</t>
+        </is>
+      </c>
+      <c r="J377" s="5" t="n"/>
+      <c r="K377" s="5" t="n">
+        <v>0.98976</v>
+      </c>
+      <c r="L377" s="5" t="n">
+        <v>0.9898</v>
+      </c>
+      <c r="M377" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:46:41</t>
+        </is>
+      </c>
+      <c r="N377" s="5" t="n">
+        <v>9.19</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B378" s="2" t="inlineStr">
+        <is>
+          <t>投保新鍾心滿福後，假設投保保額為100萬元，於第二保單年度接受「移植器官」，這樣可以領多少保險金?</t>
+        </is>
+      </c>
+      <c r="C378" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人於第二保險單年度（含）以後的有效期間內，初次診斷確定罹患「特定重大傷病」並接受「移植器官」，可獲得「重大傷病保險金」及「特定重大傷病保險金」。其中，「特定重大傷病保險金」的給付金額為保險金額的20%，即100萬元 × 20% = 20萬元。重大傷病保險金的具體金額則需依保單條款進一步確認。
+條文依據：  
+- [第十三條 特定重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D378" s="2" t="inlineStr">
+        <is>
+          <t>第十五條 滿期保險金的給付 | 第二條 名詞定義 | 附表一：全民健康保險重大傷病項目 | 第十三條 特定重大傷病保險金的給付 | 附表三：各保險單年度可借金額上限表 | payout_items | 第十七條 完全失能保險金的給付 | 附表二：完全失能程度表</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F378" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人於第二保險單年度（含）以後的有效期間內，初次診斷確定罹患「特定重大傷病」並接受「移植器官」，可獲得「重大傷病保險金」及「特定重大傷病保險金」。其中，「特定重大傷病保險金」的給付金額為保險金額的20%，即100萬元 × 20% = 20萬元。重大傷病保險金的具體金額則需依保單條款進一步確認。
+條文依據：  
+- [第十三條 特定重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G378" s="2" t="inlineStr"/>
+      <c r="H378" s="2" t="inlineStr"/>
+      <c r="I378" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.09329, "neutral": 0.776254, "contradiction": 0.130456, "factuality": 0.869544, "C_fact": 0.869544}, "C_conf": 0.8695}</t>
+        </is>
+      </c>
+      <c r="J378" s="5" t="n"/>
+      <c r="K378" s="5" t="n">
+        <v>0.869544</v>
+      </c>
+      <c r="L378" s="5" t="n">
+        <v>0.8695000000000001</v>
+      </c>
+      <c r="M378" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:46:47</t>
+        </is>
+      </c>
+      <c r="N378" s="5" t="n">
+        <v>5.54</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B379" s="2" t="inlineStr">
+        <is>
+          <t>投保新鍾心滿福後，若要理賠重大傷病保險金，一定要檢附全民健保開立的重大傷病證明才能拿到保險金嗎?</t>
+        </is>
+      </c>
+      <c r="C379" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不一定需要檢附全民健保開立的重大傷病證明。若被保險人已取得一家「區域醫院」層級以上（含）之醫療院所開立且符合投保當時「重大傷病範圍」的診斷書及當次「重大傷病」病歷摘要，視為重大傷病證明文件，免向全民健康保險保險人申請重大傷病證明即可申領保險金。
+條文依據：  
+- [第二十二條 重大傷病保險金、特定重大傷病保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D379" s="2" t="inlineStr">
+        <is>
+          <t>第二十二條 重大傷病保險金、特定重大傷病保險金的申領 | other_metadata | 第十二條 重大傷病保險金的給付 | 附表一：全民健康保險重大傷病項目 | 第二條 名詞定義 | 第三十條 不保事項</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F379" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不一定需要檢附全民健保開立的重大傷病證明。若被保險人已取得一家「區域醫院」層級以上（含）之醫療院所開立且符合投保當時「重大傷病範圍」的診斷書及當次「重大傷病」病歷摘要，視為重大傷病證明文件，免向全民健康保險保險人申請重大傷病證明即可申領保險金。
+條文依據：  
+- [第二十二條 重大傷病保險金、特定重大傷病保險金的申領]</t>
+        </is>
+      </c>
+      <c r="G379" s="2" t="inlineStr"/>
+      <c r="H379" s="2" t="inlineStr"/>
+      <c r="I379" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.885506, "neutral": 0.023356, "contradiction": 0.091139, "factuality": 0.908861, "C_fact": 0.908861}, "C_conf": 0.9089}</t>
+        </is>
+      </c>
+      <c r="J379" s="5" t="n"/>
+      <c r="K379" s="5" t="n">
+        <v>0.908861</v>
+      </c>
+      <c r="L379" s="5" t="n">
+        <v>0.9089</v>
+      </c>
+      <c r="M379" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:46:56</t>
+        </is>
+      </c>
+      <c r="N379" s="5" t="n">
+        <v>7.45</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B380" s="2" t="inlineStr">
+        <is>
+          <t>一定要有健保身分才能申請重大傷病理賠嗎？</t>
+        </is>
+      </c>
+      <c r="C380" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，被保險人若喪失全民健康保險被保險人資格，需先申請加保全民健康保險後，才能申領重大傷病保險金。然而，若重大傷病係因意外傷害事故所致，則不受此限制。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D380" s="2" t="inlineStr">
+        <is>
+          <t>第二十二條 重大傷病保險金、特定重大傷病保險金的申領 | 第十二條 重大傷病保險金的給付 | other_metadata | 第三十條 不保事項 | 第二條 名詞定義 | 附表一：全民健康保險重大傷病項目</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F380" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，被保險人若喪失全民健康保險被保險人資格，需先申請加保全民健康保險後，才能申領重大傷病保險金。然而，若重大傷病係因意外傷害事故所致，則不受此限制。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G380" s="2" t="inlineStr"/>
+      <c r="H380" s="2" t="inlineStr"/>
+      <c r="I380" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.001115, "neutral": 0.9981, "contradiction": 0.000785, "factuality": 0.999215, "C_fact": 0.999215}, "C_conf": 0.9992}</t>
+        </is>
+      </c>
+      <c r="J380" s="5" t="n"/>
+      <c r="K380" s="5" t="n">
+        <v>0.999215</v>
+      </c>
+      <c r="L380" s="5" t="n">
+        <v>0.9992</v>
+      </c>
+      <c r="M380" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:47:03</t>
+        </is>
+      </c>
+      <c r="N380" s="5" t="n">
+        <v>6.58</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B381" s="2" t="inlineStr">
+        <is>
+          <t>重大傷病的項目如果在投保後有新增，可以從優申請理賠嗎？</t>
+        </is>
+      </c>
+      <c r="C381" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以從優申請理賠。依據條款，重大傷病的範圍包含「訂立時」及「有效期間內被保險人診斷確定當時」由中央衛生主管機關公告之重大傷病項目。因此，若投保後重大傷病項目有新增，且被保險人於有效期間內診斷確定符合新增項目，則可申請理賠。
+條文依據：  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D381" s="2" t="inlineStr">
+        <is>
+          <t>附表一：全民健康保險重大傷病項目 | 第二條 名詞定義 | payout_items</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F381" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以從優申請理賠。依據條款，重大傷病的範圍包含「訂立時」及「有效期間內被保險人診斷確定當時」由中央衛生主管機關公告之重大傷病項目。因此，若投保後重大傷病項目有新增，且被保險人於有效期間內診斷確定符合新增項目，則可申請理賠。
+條文依據：  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G381" s="2" t="inlineStr"/>
+      <c r="H381" s="2" t="inlineStr"/>
+      <c r="I381" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.989659, "neutral": 0.010127, "contradiction": 0.000214, "factuality": 0.999786, "C_fact": 0.999786}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J381" s="5" t="n"/>
+      <c r="K381" s="5" t="n">
+        <v>0.999786</v>
+      </c>
+      <c r="L381" s="5" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M381" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:47:08</t>
+        </is>
+      </c>
+      <c r="N381" s="5" t="n">
+        <v>5.54</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B382" s="2" t="inlineStr">
+        <is>
+          <t>我的保單之前有停效，在復效後五天被診斷出重大疾病是否可申請理賠？</t>
+        </is>
+      </c>
+      <c r="C382" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+條款未明確規定／資料不足</t>
+        </is>
+      </c>
+      <c r="D382" s="2" t="inlineStr">
+        <is>
+          <t>第八條 本契約效力的恢復 | 第三十條 不保事項 | 第五條 保險範圍 | 第二條 名詞定義 | 第十二條 重大傷病保險金的給付 | 第二十二條 重大傷病保險金、特定重大傷病保險金的申領 | 附表一：全民健康保險重大傷病項目</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F382" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以申請理賠，但需符合以下條件：若保單復效後，被保險人於契約有效期間內罹患重大疾病，且符合「重大傷病」的定義及相關文件要求，即可申請理賠。復效後的疾病不受等待期間限制，並且保險公司需依約給付重大傷病保險金。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G382" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+條款未明確規定／資料不足</t>
+        </is>
+      </c>
+      <c r="H382" s="2" t="inlineStr"/>
+      <c r="I382" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.403623, "neutral": 0.461499, "contradiction": 0.134878, "factuality": 0.865122, "C_fact": 0.865122}, "C_conf": 0.8651}</t>
+        </is>
+      </c>
+      <c r="J382" s="5" t="n"/>
+      <c r="K382" s="5" t="n">
+        <v>0.8651219999999999</v>
+      </c>
+      <c r="L382" s="5" t="n">
+        <v>0.8651</v>
+      </c>
+      <c r="M382" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:47:17</t>
+        </is>
+      </c>
+      <c r="N382" s="5" t="n">
+        <v>8.630000000000001</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B383" s="2" t="inlineStr">
+        <is>
+          <t>領完重大傷病保險金，主約終止後，附約可以繼續有效嗎?</t>
+        </is>
+      </c>
+      <c r="C383" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以。依據條文，若主約因重大傷病診斷確定日而終止時，要保人於附約的有效期間內，仍可繼續繳交附約保險費，以延續附約效力。
+條文依據：  
+- [第十一條 契約的終止（二）]</t>
+        </is>
+      </c>
+      <c r="D383" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 契約的終止（二） | 第十二條 重大傷病保險金的給付 | 第三十條 不保事項 | 第五條 保險範圍 | payout_items | 附表一：全民健康保險重大傷病項目</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F383" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以。依據條文，若主約因重大傷病診斷確定日而終止時，要保人於附約的有效期間內，仍可繼續繳交附約保險費，以延續附約效力。
+條文依據：  
+- [第十一條 契約的終止（二）]</t>
+        </is>
+      </c>
+      <c r="G383" s="2" t="inlineStr"/>
+      <c r="H383" s="2" t="inlineStr"/>
+      <c r="I383" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.984233, "neutral": 0.015595, "contradiction": 0.000171, "factuality": 0.999829, "C_fact": 0.999829}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J383" s="5" t="n"/>
+      <c r="K383" s="5" t="n">
+        <v>0.999829</v>
+      </c>
+      <c r="L383" s="5" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M383" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:47:23</t>
+        </is>
+      </c>
+      <c r="N383" s="5" t="n">
+        <v>5.47</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B384" s="2" t="inlineStr">
+        <is>
+          <t>Q1：因為慢性精神病的保險給付僅有保額的20%，我可以先不申請給付，等之後發生其他重大傷病後，再申請重大傷病保險金嗎?Q2：但如果我不申請，保險公司不會知道我有罹患慢性精神病阿，所以我就可以領之後的重大傷病100%保額嗎?</t>
+        </is>
+      </c>
+      <c r="C384" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+Q1：依據條款，被保險人同時或先後罹患二項以上「重大傷病」時，保險公司僅給付一項「重大傷病保險金」。因此，即使您選擇不申請慢性精神病的保險給付，未來若罹患其他重大傷病，保險公司仍僅會給付其中一項的保險金，並依條款規定計算金額。  
+Q2：保險公司是否知悉您罹患慢性精神病並不影響未來重大傷病保險金的給付比例。若您罹患的重大傷病屬於慢性精神病，保險公司將依條款規定給付「保險金額的百分之二十」或「年繳應繳保險費總額的一點零五倍」，二者取其大者。若罹患其他重大傷病，則依條款規定給付「保險金額」或「年繳應繳保險費總額的一點零五倍」，二者取其大者。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D384" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 重大傷病保險金的給付 | 第十三條 特定重大傷病保險金的給付 | 第三十條 不保事項 | 第二十八條 除外責任（一） | 第二十二條 重大傷病保險金、特定重大傷病保險金的申領 | 第二條 名詞定義 | 附表一：全民健康保險重大傷病項目 | payout_items</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F384" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+Q1：依據條款，被保險人同時或先後罹患二項以上「重大傷病」時，保險公司僅給付一項「重大傷病保險金」。因此，即使您選擇不申請慢性精神病的保險給付，未來若罹患其他重大傷病，保險公司仍僅會給付其中一項的保險金，並依條款規定計算金額。  
+Q2：保險公司是否知悉您罹患慢性精神病並不影響未來重大傷病保險金的給付比例。若您罹患的重大傷病屬於慢性精神病，保險公司將依條款規定給付「保險金額的百分之二十」或「年繳應繳保險費總額的一點零五倍」，二者取其大者。若罹患其他重大傷病，則依條款規定給付「保險金額」或「年繳應繳保險費總額的一點零五倍」，二者取其大者。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G384" s="2" t="inlineStr"/>
+      <c r="H384" s="2" t="inlineStr"/>
+      <c r="I384" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.975867, "neutral": 0.022918, "contradiction": 0.001215, "factuality": 0.998785, "C_fact": 0.998785}, "C_conf": 0.9988}</t>
+        </is>
+      </c>
+      <c r="J384" s="5" t="n"/>
+      <c r="K384" s="5" t="n">
+        <v>0.998785</v>
+      </c>
+      <c r="L384" s="5" t="n">
+        <v>0.9988</v>
+      </c>
+      <c r="M384" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:47:42</t>
+        </is>
+      </c>
+      <c r="N384" s="5" t="n">
+        <v>19.43</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B385" s="2" t="inlineStr">
+        <is>
+          <t>失智症會賠嗎？賠多少？</t>
+        </is>
+      </c>
+      <c r="C385" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+失智症是否理賠及賠償金額需視其是否符合「重大傷病」的範圍。根據條款，若失智症屬於附表一所載「重大傷病」範圍，且被保險人於等待期間屆滿翌日或復效日起的契約有效期間內，經醫院醫師初次診斷確定罹患，並取得符合規定的重大傷病證明或診斷書，本公司將依診斷確定罹患重大傷病時之保險單年度，以下列方式計算給付金額：  
+1. 第一保險單年度：「年繳應繳保險費總額」的一點零五倍。  
+2. 第二保險單年度（含）以後：  
+   - 若屬附表一所載「六、慢性精神病」：「保險金額的百分之二十」或「年繳應繳保險費總額」的一點零五倍，二者取其大者。  
+   - 若屬其他「重大傷病範圍」項目：「保險金額」或「年繳應繳保險費總額」的一點零五倍，二者取其大者。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [附表一：全民健康保險重大傷病項目]</t>
+        </is>
+      </c>
+      <c r="D385" s="2" t="inlineStr">
+        <is>
+          <t>第十七條 完全失能保險金的給付 | 第二十九條 除外責任（二） | payout_items | 第十二條 重大傷病保險金的給付 | 第三十條 不保事項 | 附表二：完全失能程度表 | 附表一：全民健康保險重大傷病項目</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F385" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+失智症是否理賠及賠償金額需視其是否符合「重大傷病」的範圍。根據條款，若失智症屬於附表一所載「重大傷病」範圍，且被保險人於等待期間屆滿翌日或復效日起的契約有效期間內，經醫院醫師初次診斷確定罹患，並取得符合規定的重大傷病證明或診斷書，本公司將依診斷確定罹患重大傷病時之保險單年度，以下列方式計算給付金額：  
+1. 第一保險單年度：「年繳應繳保險費總額」的一點零五倍。  
+2. 第二保險單年度（含）以後：  
+   - 若屬附表一所載「六、慢性精神病」：「保險金額的百分之二十」或「年繳應繳保險費總額」的一點零五倍，二者取其大者。  
+   - 若屬其他「重大傷病範圍」項目：「保險金額」或「年繳應繳保險費總額」的一點零五倍，二者取其大者。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [附表一：全民健康保險重大傷病項目]</t>
+        </is>
+      </c>
+      <c r="G385" s="2" t="inlineStr"/>
+      <c r="H385" s="2" t="inlineStr"/>
+      <c r="I385" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.996, "neutral": 0.00359, "contradiction": 0.00041, "factuality": 0.99959, "C_fact": 0.99959}, "C_conf": 0.9996}</t>
+        </is>
+      </c>
+      <c r="J385" s="5" t="n"/>
+      <c r="K385" s="5" t="n">
+        <v>0.99959</v>
+      </c>
+      <c r="L385" s="5" t="n">
+        <v>0.9996</v>
+      </c>
+      <c r="M385" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:47:54</t>
+        </is>
+      </c>
+      <c r="N385" s="5" t="n">
+        <v>11.84</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B386" s="2" t="inlineStr">
+        <is>
+          <t>投保新鍾心滿福後，於第二保單年度罹患子宮頸惡性腫瘤，且已給付重大傷病保險金。第五保單年度時又罹患慢性腎衰竭，這樣還可以申領重大傷病保險金的給付嗎?</t>
+        </is>
+      </c>
+      <c r="C386" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不可以再次申領重大傷病保險金。根據條款規定，被保險人同時或先後罹患二項以上「重大傷病」時，本公司僅給付一項「重大傷病保險金」。因此，即使於第五保單年度罹患慢性腎衰竭，已於第二保單年度因子宮頸惡性腫瘤申領過重大傷病保險金，無法再次申領。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D386" s="2" t="inlineStr">
+        <is>
+          <t>附表一：全民健康保險重大傷病項目 | 第十二條 重大傷病保險金的給付 | 第五條 保險範圍 | 第二條 名詞定義 | payout_items | 第二十二條 重大傷病保險金、特定重大傷病保險金的申領</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F386" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不可以再次申領重大傷病保險金。根據條款規定，被保險人同時或先後罹患二項以上「重大傷病」時，本公司僅給付一項「重大傷病保險金」。因此，即使於第五保單年度罹患慢性腎衰竭，已於第二保單年度因子宮頸惡性腫瘤申領過重大傷病保險金，無法再次申領。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G386" s="2" t="inlineStr"/>
+      <c r="H386" s="2" t="inlineStr"/>
+      <c r="I386" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.96529, "neutral": 0.03419, "contradiction": 0.00052, "factuality": 0.99948, "C_fact": 0.99948}, "C_conf": 0.9995}</t>
+        </is>
+      </c>
+      <c r="J386" s="5" t="n"/>
+      <c r="K386" s="5" t="n">
+        <v>0.99948</v>
+      </c>
+      <c r="L386" s="5" t="n">
+        <v>0.9995000000000001</v>
+      </c>
+      <c r="M386" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:48:12</t>
+        </is>
+      </c>
+      <c r="N386" s="5" t="n">
+        <v>17.92</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B387" s="2" t="inlineStr">
+        <is>
+          <t>12歲的被保險人可以有健康促進保險費折減嗎？</t>
+        </is>
+      </c>
+      <c r="C387" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+12歲的被保險人無法享有健康促進保險費折減，因為第十九條明確規定，只有實際年齡達十八歲（含）以上的被保險人才符合折減條件。
+條文依據：  
+- [第十九條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="D387" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 健康促進保險費折減 | 第三十八條 投保年齡的計算及錯誤的處理 | 第三十四條 減額繳清保險 | 第二條 名詞定義 | 第十六條 所繳保險費加計利息的退還、身故保險金或喪葬費用保險金的給付 | 附表二：完全失能程度表</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F387" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+12歲的被保險人無法享有健康促進保險費折減，因為第十九條明確規定，只有實際年齡達十八歲（含）以上的被保險人才符合折減條件。
+條文依據：  
+- [第十九條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="G387" s="2" t="inlineStr"/>
+      <c r="H387" s="2" t="inlineStr"/>
+      <c r="I387" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.936248, "neutral": 0.062415, "contradiction": 0.001337, "factuality": 0.998663, "C_fact": 0.998663}, "C_conf": 0.9987}</t>
+        </is>
+      </c>
+      <c r="J387" s="5" t="n"/>
+      <c r="K387" s="5" t="n">
+        <v>0.998663</v>
+      </c>
+      <c r="L387" s="5" t="n">
+        <v>0.9987</v>
+      </c>
+      <c r="M387" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:48:20</t>
+        </is>
+      </c>
+      <c r="N387" s="5" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>ZDN</t>
+        </is>
+      </c>
+      <c r="B388" s="2" t="inlineStr">
+        <is>
+          <t>被保險人於投保鍾心滿溢後的第10天就罹患慢性腎衰竭，請問可以申領重大傷病保險金嗎？</t>
+        </is>
+      </c>
+      <c r="C388" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不可以申領重大傷病保險金。根據條款，被保險人因意外傷害事故以外原因，於等待期間內罹患「重大傷病」者，本契約自始無效，本公司僅無息退還已繳保險費予要保人。慢性腎衰竭屬於重大傷病範圍，但因其非意外傷害事故所致，且發生於等待期間內（第10天），因此不符合申領條件。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第三十條 不保事項]</t>
+        </is>
+      </c>
+      <c r="D388" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 重大傷病保險金的給付 | 附表一：全民健康保險重大傷病項目 | 第三十條 不保事項 | 第二條 名詞定義 | 第二十二條 重大傷病保險金、特定重大傷病保險金的申領</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F388" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不可以申領重大傷病保險金。根據條款，被保險人因意外傷害事故以外原因，於等待期間內罹患「重大傷病」者，本契約自始無效，本公司僅無息退還已繳保險費予要保人。慢性腎衰竭屬於重大傷病範圍，但因其非意外傷害事故所致，且發生於等待期間內（第10天），因此不符合申領條件。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第三十條 不保事項]</t>
+        </is>
+      </c>
+      <c r="G388" s="2" t="inlineStr"/>
+      <c r="H388" s="2" t="inlineStr"/>
+      <c r="I388" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.000854, "neutral": 0.998759, "contradiction": 0.000387, "factuality": 0.999613, "C_fact": 0.999613}, "C_conf": 0.9996}</t>
+        </is>
+      </c>
+      <c r="J388" s="5" t="n"/>
+      <c r="K388" s="5" t="n">
+        <v>0.999613</v>
+      </c>
+      <c r="L388" s="5" t="n">
+        <v>0.9996</v>
+      </c>
+      <c r="M388" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:48:32</t>
+        </is>
+      </c>
+      <c r="N388" s="5" t="n">
+        <v>11.03</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>CFE</t>
+        </is>
+      </c>
+      <c r="B389" s="2" t="inlineStr">
+        <is>
+          <t>投保自由配重大傷病後，若在契約生效後80天罹患第一期乳癌，會拿到理賠金嗎?</t>
+        </is>
+      </c>
+      <c r="C389" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不會拿到理賠金。根據條款，第一期乳癌屬於「需積極或長期治療之癌症」範圍，等待期間為契約生效日起90天。若在等待期間內罹患重大傷病，契約自始無效，本公司僅退還已繳保險費且不計利息。
+條文依據：  
+- [第二條 名詞定義]  
+- [第十一條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D389" s="2" t="inlineStr">
+        <is>
+          <t>附表一：全民健康保險重大傷病項目 | 第十一條 重大傷病保險金的給付 | 第十五條 不保事項 | 第二條 名詞定義 | other_metadata | 第五條 契約有效期間及保證續保 | 第十四條 除外責任</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F389" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不會拿到理賠金。根據條款，第一期乳癌屬於「需積極或長期治療之癌症」範圍，等待期間為契約生效日起90天。若在等待期間內罹患重大傷病，契約自始無效，本公司僅退還已繳保險費且不計利息。
+條文依據：  
+- [第二條 名詞定義]  
+- [第十一條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G389" s="2" t="inlineStr"/>
+      <c r="H389" s="2" t="inlineStr"/>
+      <c r="I389" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.562159, "neutral": 0.254312, "contradiction": 0.183529, "factuality": 0.816471, "C_fact": 0.816471}, "C_conf": 0.8165}</t>
+        </is>
+      </c>
+      <c r="J389" s="5" t="n"/>
+      <c r="K389" s="5" t="n">
+        <v>0.8164709999999999</v>
+      </c>
+      <c r="L389" s="5" t="n">
+        <v>0.8165</v>
+      </c>
+      <c r="M389" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:48:38</t>
+        </is>
+      </c>
+      <c r="N389" s="5" t="n">
+        <v>6.16</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>CFE</t>
+        </is>
+      </c>
+      <c r="B390" s="2" t="inlineStr">
+        <is>
+          <t>要保人想要終止國泰人壽自由配CFE契約，能否退保費?</t>
+        </is>
+      </c>
+      <c r="C390" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+要保人可以終止契約，並退還未到期保險費。本公司會從已繳保險費中扣除按短期費率計算的已經過期間保險費後，將剩餘未到期保險費無息退還給要保人。
+條文依據：  
+- [第九條 契約的終止（一）]</t>
+        </is>
+      </c>
+      <c r="D390" s="2" t="inlineStr">
+        <is>
+          <t>第九條 契約的終止（一） | 第十五條 不保事項 | 第五條 契約有效期間及保證續保 | 第七條 本契約效力的恢復 | 第六條 續保保險費的交付、寬限期間及契約效力的停止 | 附表二：短期費率表</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F390" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+要保人可以終止契約，並退還未到期保險費。本公司會從已繳保險費中扣除按短期費率計算的已經過期間保險費後，將剩餘未到期保險費無息退還給要保人。
+條文依據：  
+- [第九條 契約的終止（一）]</t>
+        </is>
+      </c>
+      <c r="G390" s="2" t="inlineStr"/>
+      <c r="H390" s="2" t="inlineStr"/>
+      <c r="I390" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.997707, "neutral": 0.002201, "contradiction": 9.2e-05, "factuality": 0.999908, "C_fact": 0.999908}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J390" s="5" t="n"/>
+      <c r="K390" s="5" t="n">
+        <v>0.999908</v>
+      </c>
+      <c r="L390" s="5" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M390" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:48:43</t>
+        </is>
+      </c>
+      <c r="N390" s="5" t="n">
+        <v>4.55</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>CFE</t>
+        </is>
+      </c>
+      <c r="B391" s="2" t="inlineStr">
+        <is>
+          <t>投保國泰人壽自由配CFE，若在等待期間內罹患重大傷病，要如何給付?</t>
+        </is>
+      </c>
+      <c r="C391" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在等待期間內因意外傷害事故罹患重大傷病，則不受等待期間限制，本公司仍會給付重大傷病保險金。若因意外傷害事故以外的原因罹患重大傷病，則本契約自始無效，本公司僅無息退還已繳保險費予要保人。
+條文依據：  
+- [第十一條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D391" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 重大傷病保險金的給付 | 附表一：全民健康保險重大傷病項目 | 第十五條 不保事項 | 第十四條 除外責任 | payout_items | other_metadata</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F391" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在等待期間內因意外傷害事故罹患重大傷病，則不受等待期間限制，本公司仍會給付重大傷病保險金。若因意外傷害事故以外的原因罹患重大傷病，則本契約自始無效，本公司僅無息退還已繳保險費予要保人。
+條文依據：  
+- [第十一條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G391" s="2" t="inlineStr"/>
+      <c r="H391" s="2" t="inlineStr"/>
+      <c r="I391" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.965114, "neutral": 0.032758, "contradiction": 0.002128, "factuality": 0.997872, "C_fact": 0.997872}, "C_conf": 0.9979}</t>
+        </is>
+      </c>
+      <c r="J391" s="5" t="n"/>
+      <c r="K391" s="5" t="n">
+        <v>0.997872</v>
+      </c>
+      <c r="L391" s="5" t="n">
+        <v>0.9979</v>
+      </c>
+      <c r="M391" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:48:48</t>
+        </is>
+      </c>
+      <c r="N391" s="5" t="n">
+        <v>5.68</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>CFE</t>
+        </is>
+      </c>
+      <c r="B392" s="2" t="inlineStr">
+        <is>
+          <t>投保自由配一年定期初次罹患重大傷病健康保險後，於第三年罹患先天性肌肉萎縮症，可以申領重大傷病保險金嗎？</t>
+        </is>
+      </c>
+      <c r="C392" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不可以申領重大傷病保險金。根據條款附表一，先天性肌肉萎縮症（Congenital muscular dystrophy）在「全民健康保險重大傷病項目」中標示為「否」，不屬於重大傷病範圍，因此不符合重大傷病保險金的給付條件。
+條文依據：  
+- [附表一：全民健康保險重大傷病項目]</t>
+        </is>
+      </c>
+      <c r="D392" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 重大傷病保險金的給付 | 附表一：全民健康保險重大傷病項目 | 第十三條 重大傷病保險金的申領 | 第十五條 不保事項</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F392" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不可以申領重大傷病保險金。根據條款，先天性肌肉萎縮症不屬於「重大傷病」範圍，且條文附表一已明確標示此疾病為「否」，表示不符合重大傷病保險金的給付條件。
+條文依據：  
+- [附表一：全民健康保險重大傷病項目]</t>
+        </is>
+      </c>
+      <c r="G392" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不可以申領重大傷病保險金。根據條款附表一，先天性肌肉萎縮症（Congenital muscular dystrophy）在「全民健康保險重大傷病項目」中標示為「否」，不屬於重大傷病範圍，因此不符合重大傷病保險金的給付條件。
+條文依據：  
+- [附表一：全民健康保險重大傷病項目]</t>
+        </is>
+      </c>
+      <c r="H392" s="2" t="inlineStr"/>
+      <c r="I392" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.905722, "neutral": 0.042939, "contradiction": 0.051339, "factuality": 0.948661, "C_fact": 0.948661}, "C_conf": 0.9487}</t>
+        </is>
+      </c>
+      <c r="J392" s="5" t="n"/>
+      <c r="K392" s="5" t="n">
+        <v>0.948661</v>
+      </c>
+      <c r="L392" s="5" t="n">
+        <v>0.9487</v>
+      </c>
+      <c r="M392" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:49:04</t>
+        </is>
+      </c>
+      <c r="N392" s="5" t="n">
+        <v>15.55</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>CFG</t>
+        </is>
+      </c>
+      <c r="B393" s="2" t="inlineStr">
+        <is>
+          <t>自由配重大疾病(甲型)保障的重大疾病有哪些疾病?</t>
+        </is>
+      </c>
+      <c r="C393" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+自由配重大疾病(甲型)保障的重大疾病包括以下疾病：  
+1. 腦中風後障礙(重度)  
+2. 癱瘓(重度)  
+3. 癌症(重度)  
+4. 急性心肌梗塞(重度)  
+5. 冠狀動脈繞道手術  
+6. 末期腎病變  
+7. 重大器官移植或造血幹細胞移植  
+條文依據：  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D393" s="2" t="inlineStr">
+        <is>
+          <t>國泰人壽自由配一年定期初次罹患重大疾病健康保險(甲型)年繳費率表 | payout_items | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F393" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+自由配重大疾病(甲型)保障的重大疾病包括以下疾病：  
+1. 腦中風後障礙(重度)  
+2. 癱瘓(重度)  
+3. 癌症(重度)  
+4. 急性心肌梗塞(重度)  
+5. 冠狀動脈繞道手術  
+6. 末期腎病變  
+7. 重大器官移植或造血幹細胞移植  
+條文依據：  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G393" s="2" t="inlineStr"/>
+      <c r="H393" s="2" t="inlineStr"/>
+      <c r="I393" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.435646, "neutral": 0.534641, "contradiction": 0.029713, "factuality": 0.970287, "C_fact": 0.970287}, "C_conf": 0.9703}</t>
+        </is>
+      </c>
+      <c r="J393" s="5" t="n"/>
+      <c r="K393" s="5" t="n">
+        <v>0.970287</v>
+      </c>
+      <c r="L393" s="5" t="n">
+        <v>0.9703000000000001</v>
+      </c>
+      <c r="M393" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:49:28</t>
+        </is>
+      </c>
+      <c r="N393" s="5" t="n">
+        <v>23.24</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B394" s="2" t="inlineStr">
+        <is>
+          <t>被保險人領了2次癌症(重度)追蹤照護金後身故，是否還有尚未給付的保險金供受益人領取?</t>
+        </is>
+      </c>
+      <c r="C394" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人已領取2次「癌症(重度)追蹤照護保險金」後身故，則無其他尚未給付的「癌症(重度)追蹤照護保險金」可供受益人申領，因該保險金的給付最長以五年為限，且需被保險人於各保險單週年日仍生存才能給付。此外，條文未提及其他相關保險金在此情況下的額外給付。  
+條文依據：  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]</t>
+        </is>
+      </c>
+      <c r="D394" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用) | 第十三條 初次罹患癌症(重度)保險金的給付 | payout_items | 第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用) | 第二十三條 癌症保險金或罹癌基因檢測服務的申領 | 第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付 | 第十六條 癌症(重度)豁免保險費(第二保險單年度起適用) | 第二十二條 保險事故的通知與保險給付的申請時間</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F394" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人已領取2次「癌症(重度)追蹤照護保險金」後身故，則無其他尚未給付的「癌症(重度)追蹤照護保險金」可供受益人申領，因該保險金的給付最長以五年為限，且需被保險人於各保險單週年日仍生存才能給付。此外，條文未提及其他相關保險金在此情況下的額外給付。  
+條文依據：  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]</t>
+        </is>
+      </c>
+      <c r="G394" s="2" t="inlineStr"/>
+      <c r="H394" s="2" t="inlineStr"/>
+      <c r="I394" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.069284, "neutral": 0.923969, "contradiction": 0.006747, "factuality": 0.993253, "C_fact": 0.993253}, "C_conf": 0.9933}</t>
+        </is>
+      </c>
+      <c r="J394" s="5" t="n"/>
+      <c r="K394" s="5" t="n">
+        <v>0.9932530000000001</v>
+      </c>
+      <c r="L394" s="5" t="n">
+        <v>0.9933</v>
+      </c>
+      <c r="M394" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:49:36</t>
+        </is>
+      </c>
+      <c r="N394" s="5" t="n">
+        <v>8.130000000000001</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B395" s="2" t="inlineStr">
+        <is>
+          <t>保險金額2萬元，「罹癌基因檢測服務」費用8萬元，還會給付多少「癌症(重度)追蹤照護保險金」？</t>
+        </is>
+      </c>
+      <c r="C395" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人選擇申領「罹癌基因檢測服務」，因服務費用（8萬元）高於「罹癌基因檢測服務額度」（附件一補償金額1,000元），則僅能申領「癌症(重度)追蹤照護保險金」。依條款規定，「癌症(重度)追蹤照護保險金」的給付金額為保險金額的12倍，故給付金額為2萬元 × 12 = 24萬元。
+條文依據：  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]  
+- [附件一：罹癌基因檢測服務之項目、服務費用及補償金額表]</t>
+        </is>
+      </c>
+      <c r="D395" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用) | 附件一：罹癌基因檢測服務之項目、服務費用及補償金額表 | 第二十三條 癌症保險金或罹癌基因檢測服務的申領 | 第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用) | payout_items | 第十三條 初次罹患癌症(重度)保險金的給付 | other_metadata | 第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F395" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人選擇申領「罹癌基因檢測服務」，因服務費用（8萬元）高於「罹癌基因檢測服務額度」（附件一補償金額1,000元），則僅能申領「癌症(重度)追蹤照護保險金」。依條款規定，「癌症(重度)追蹤照護保險金」的給付金額為保險金額的12倍，故給付金額為2萬元 × 12 = 24萬元。
+條文依據：  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]  
+- [附件一：罹癌基因檢測服務之項目、服務費用及補償金額表]</t>
+        </is>
+      </c>
+      <c r="G395" s="2" t="inlineStr"/>
+      <c r="H395" s="2" t="inlineStr"/>
+      <c r="I395" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.81477, "neutral": 0.111481, "contradiction": 0.073749, "factuality": 0.926251, "C_fact": 0.926251}, "C_conf": 0.9263}</t>
+        </is>
+      </c>
+      <c r="J395" s="5" t="n"/>
+      <c r="K395" s="5" t="n">
+        <v>0.926251</v>
+      </c>
+      <c r="L395" s="5" t="n">
+        <v>0.9263</v>
+      </c>
+      <c r="M395" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:49:41</t>
+        </is>
+      </c>
+      <c r="N395" s="5" t="n">
+        <v>5.54</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B396" s="2" t="inlineStr">
+        <is>
+          <t>投保後1個月罹患重度癌症，會給付哪些保險金？契約還會持續有效嗎？</t>
+        </is>
+      </c>
+      <c r="C396" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在投保後1個月罹患重度癌症，因診斷確定日屬於第一保險單年度內，符合「初次診斷確定罹患癌症(重度)」的條件，本公司將給付「初次罹患癌症(重度)保險金」，金額為「年繳應繳保險費」的一點零六倍。契約仍會持續有效，但不適用「癌症(重度)豁免保險費」及其他第二保險單年度起適用的保障。  
+條文依據：  
+- [第十三條 初次罹患癌症(重度)保險金的給付]  
+- [第十六條 癌症(重度)豁免保險費(第二保險單年度起適用)]</t>
+        </is>
+      </c>
+      <c r="D396" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 癌症(重度)豁免保險費(第二保險單年度起適用) | 第十三條 初次罹患癌症(重度)保險金的給付 | 第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用) | 第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付 | 第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用)</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F396" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在投保後1個月罹患重度癌症，因診斷確定日屬於第一保險單年度內，符合「初次診斷確定罹患癌症(重度)」的條件，本公司將給付「初次罹患癌症(重度)保險金」，金額為「年繳應繳保險費」的一點零六倍。契約仍會持續有效，但不適用「癌症(重度)豁免保險費」及其他第二保險單年度起適用的保障。  
+條文依據：  
+- [第十三條 初次罹患癌症(重度)保險金的給付]  
+- [第十六條 癌症(重度)豁免保險費(第二保險單年度起適用)]</t>
+        </is>
+      </c>
+      <c r="G396" s="2" t="inlineStr"/>
+      <c r="H396" s="2" t="inlineStr"/>
+      <c r="I396" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.926599, "neutral": 0.029428, "contradiction": 0.043973, "factuality": 0.956027, "C_fact": 0.956027}, "C_conf": 0.956}</t>
+        </is>
+      </c>
+      <c r="J396" s="5" t="n"/>
+      <c r="K396" s="5" t="n">
+        <v>0.956027</v>
+      </c>
+      <c r="L396" s="5" t="n">
+        <v>0.956</v>
+      </c>
+      <c r="M396" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:49:48</t>
+        </is>
+      </c>
+      <c r="N396" s="5" t="n">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B397" s="2" t="inlineStr">
+        <is>
+          <t>投保後10個月罹患重度癌症，會給付哪些保險金？契約還會持續有效嗎？</t>
+        </is>
+      </c>
+      <c r="C397" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人於投保後10個月（即第二保險單年度內）診斷確定罹患重度癌症，符合「初次診斷確定罹患癌症(重度)」的條件，本公司將給付「初次罹患癌症(重度)保險金」，金額為「保險金額」的十二倍。此外，契約仍會持續有效，並豁免續期保險費，但當期已繳付之未到期保險費不予退還。  
+條文依據：  
+- [第十三條 初次罹患癌症(重度)保險金的給付]  
+- [第十六條 癌症(重度)豁免保險費(第二保險單年度起適用)]</t>
+        </is>
+      </c>
+      <c r="D397" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 癌症(重度)豁免保險費(第二保險單年度起適用) | 第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用) | 第十條 契約的終止（二） | 第十三條 初次罹患癌症(重度)保險金的給付 | 第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F397" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人於投保後10個月（即第二保險單年度內）診斷確定罹患重度癌症，符合「初次診斷確定罹患癌症(重度)」的條件，本公司將給付「初次罹患癌症(重度)保險金」，金額為「保險金額」的十二倍。此外，契約仍會持續有效，並豁免續期保險費，但當期已繳付之未到期保險費不予退還。  
+條文依據：  
+- [第十三條 初次罹患癌症(重度)保險金的給付]  
+- [第十六條 癌症(重度)豁免保險費(第二保險單年度起適用)]</t>
+        </is>
+      </c>
+      <c r="G397" s="2" t="inlineStr"/>
+      <c r="H397" s="2" t="inlineStr"/>
+      <c r="I397" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.996879, "neutral": 0.002957, "contradiction": 0.000164, "factuality": 0.999836, "C_fact": 0.999836}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J397" s="5" t="n"/>
+      <c r="K397" s="5" t="n">
+        <v>0.9998359999999999</v>
+      </c>
+      <c r="L397" s="5" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M397" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:49:53</t>
+        </is>
+      </c>
+      <c r="N397" s="5" t="n">
+        <v>4.83</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B398" s="2" t="inlineStr">
+        <is>
+          <t>投保醫心康愛，罹患肺癌一期，可領什麼保險金？</t>
+        </is>
+      </c>
+      <c r="C398" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+罹患肺癌一期屬於「癌症(初期)或癌症(輕度)」，可申領「初次罹患癌症(初期)或癌症(輕度)保險金」。若診斷確定日是在第一保險單年度內，可領「年繳應繳保險費」的一點零六倍；若診斷確定日是在第二保險單年度(含)以後，可領「保險金額」的五倍。此保險金最多僅給付一次。  
+條文依據：  
+- [第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D398" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付 | 第十三條 初次罹患癌症(重度)保險金的給付 | payout_items | 第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用) | 第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F398" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+罹患肺癌一期屬於「癌症(初期)或癌症(輕度)」，可申領「初次罹患癌症(初期)或癌症(輕度)保險金」。若診斷確定日是在第一保險單年度內，可領「年繳應繳保險費」的一點零六倍；若診斷確定日是在第二保險單年度(含)以後，可領「保險金額」的五倍。此保險金最多僅給付一次。  
+條文依據：  
+- [第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G398" s="2" t="inlineStr"/>
+      <c r="H398" s="2" t="inlineStr"/>
+      <c r="I398" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.889629, "neutral": 0.110202, "contradiction": 0.000169, "factuality": 0.999831, "C_fact": 0.999831}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J398" s="5" t="n"/>
+      <c r="K398" s="5" t="n">
+        <v>0.999831</v>
+      </c>
+      <c r="L398" s="5" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M398" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:49:58</t>
+        </is>
+      </c>
+      <c r="N398" s="5" t="n">
+        <v>3.87</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>PX5</t>
+        </is>
+      </c>
+      <c r="B399" s="2" t="inlineStr">
+        <is>
+          <t>若被保險人身故有何給付?</t>
+        </is>
+      </c>
+      <c r="C399" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人身故，且本附約保險金尚未給付或未完全給付，則以被保險人之法定繼承人為該部分保險金之受益人，並依民法繼承編之相關規定分配。  
+條文依據：  
+- [第二十條 受益人]</t>
+        </is>
+      </c>
+      <c r="D399" s="2" t="inlineStr">
+        <is>
+          <t>第二十條 受益人 | 第十二條 重大疾病保險金的給付 | 第十一條 輕度重大疾病保險金的給付 | 第十四條 保險事故的通知與保險金的申請時間 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F399" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人身故，且本附約保險金尚未給付或未完全給付，則以被保險人之法定繼承人為該部分保險金之受益人，並依民法繼承編之相關規定分配。  
+條文依據：  
+- [第二十條 受益人]</t>
+        </is>
+      </c>
+      <c r="G399" s="2" t="inlineStr"/>
+      <c r="H399" s="2" t="inlineStr"/>
+      <c r="I399" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.99027, "neutral": 0.007351, "contradiction": 0.002379, "factuality": 0.997621, "C_fact": 0.997621}, "C_conf": 0.9976}</t>
+        </is>
+      </c>
+      <c r="J399" s="5" t="n"/>
+      <c r="K399" s="5" t="n">
+        <v>0.997621</v>
+      </c>
+      <c r="L399" s="5" t="n">
+        <v>0.9976</v>
+      </c>
+      <c r="M399" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:50:03</t>
+        </is>
+      </c>
+      <c r="N399" s="5" t="n">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>PX5</t>
+        </is>
+      </c>
+      <c r="B400" s="2" t="inlineStr">
+        <is>
+          <t>投保鍾溢祝福後，請問在第二年經醫院醫師初次診斷罹患「輕度重大疾病」中的癌症(輕度)者，可以領到輕度重大疾病保險金嗎?可以領到保險金額的百分之多少?</t>
+        </is>
+      </c>
+      <c r="C400" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以領到輕度重大疾病保險金，保險金額的百分之二十。根據條款，被保險人於續保年度內初次診斷罹患「輕度重大疾病」中的癌症(輕度)，符合給付條件，且等待期間屆滿後即可申領。
+條文依據：  
+- [第十一條 輕度重大疾病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D400" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 輕度重大疾病保險金的給付 | 第十二條 重大疾病保險金的給付 | other_metadata | payout_items | 國泰人壽鍾溢祝福重大疾病健康保險附約(乙型) (外溢型)年繳費率表 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F400" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以領到輕度重大疾病保險金，保險金額的百分之二十。根據條款，被保險人於續保年度內初次診斷罹患「輕度重大疾病」中的癌症(輕度)，符合給付條件，且等待期間屆滿後即可申領。
+條文依據：  
+- [第十一條 輕度重大疾病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G400" s="2" t="inlineStr"/>
+      <c r="H400" s="2" t="inlineStr"/>
+      <c r="I400" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.989904, "neutral": 0.008677, "contradiction": 0.001419, "factuality": 0.998581, "C_fact": 0.998581}, "C_conf": 0.9986}</t>
+        </is>
+      </c>
+      <c r="J400" s="5" t="n"/>
+      <c r="K400" s="5" t="n">
+        <v>0.9985810000000001</v>
+      </c>
+      <c r="L400" s="5" t="n">
+        <v>0.9986</v>
+      </c>
+      <c r="M400" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:50:10</t>
+        </is>
+      </c>
+      <c r="N400" s="5" t="n">
+        <v>6.44</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>PX5</t>
+        </is>
+      </c>
+      <c r="B401" s="2" t="inlineStr">
+        <is>
+          <t>請問如果在投保後的第三年經醫院醫師初次診斷罹患「重大疾病」者，可以領到重大疾病保險金嗎?可以領到保險金額的百分之多少?那後續又在第四年經醫院醫師初次診斷罹患「輕度重大疾病」者，可以領到輕度重大疾病保險金嗎?可以領到保險金額的百分之多少?</t>
+        </is>
+      </c>
+      <c r="C401" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+在投保後的第三年初次診斷罹患「重大疾病」者，可以領到重大疾病保險金，保險金額為保險金額的1.3倍。後續於第四年初次診斷罹患「輕度重大疾病」者，因已申領過重大疾病保險金，根據條款規定，輕度重大疾病保險金不再給付。
+條文依據：  
+- [第十二條 重大疾病保險金的給付]  
+- [第十一條 輕度重大疾病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D401" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 輕度重大疾病保險金的給付 | 第十二條 重大疾病保險金的給付 | 第十六條 除外責任 | payout_items | 第二條 名詞定義 | 第四條 保險範圍 | other_metadata | 國泰人壽鍾溢祝福重大疾病健康保險附約(乙型) (外溢型)年繳費率表</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F401" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+在投保後的第三年初次診斷罹患「重大疾病」者，可以領到重大疾病保險金，保險金額為保險金額的1.3倍。後續於第四年初次診斷罹患「輕度重大疾病」者，因已申領過重大疾病保險金，根據條款規定，輕度重大疾病保險金不再給付。
+條文依據：  
+- [第十二條 重大疾病保險金的給付]  
+- [第十一條 輕度重大疾病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G401" s="2" t="inlineStr"/>
+      <c r="H401" s="2" t="inlineStr"/>
+      <c r="I401" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.98523, "neutral": 0.012495, "contradiction": 0.002274, "factuality": 0.997726, "C_fact": 0.997726}, "C_conf": 0.9977}</t>
+        </is>
+      </c>
+      <c r="J401" s="5" t="n"/>
+      <c r="K401" s="5" t="n">
+        <v>0.997726</v>
+      </c>
+      <c r="L401" s="5" t="n">
+        <v>0.9977</v>
+      </c>
+      <c r="M401" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:50:15</t>
+        </is>
+      </c>
+      <c r="N401" s="5" t="n">
+        <v>4.96</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>PX5</t>
+        </is>
+      </c>
+      <c r="B402" s="2" t="inlineStr">
+        <is>
+          <t>請問如果在投保後的第三年經醫院醫師初次診斷罹患「輕度重大疾病」者，可以領到重大疾病保險金嗎?可以領到保險金額的百分之多少?那後續又在第四年經醫院醫師初次診斷罹患「重大疾病」者，可以領到輕度重大疾病保險金嗎?可以領到保險金額的百分之多少?</t>
+        </is>
+      </c>
+      <c r="C402" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+在投保後的第三年初次診斷罹患「輕度重大疾病」者，無法領取「重大疾病保險金」，只能領取「輕度重大疾病保險金」，給付比例為保險金額的百分之二十。  
+後續在第四年初次診斷罹患「重大疾病」者，無法再領取「輕度重大疾病保險金」，但可以領取「重大疾病保險金」，給付比例為保險金額的一點三倍，且需扣除已領取的「輕度重大疾病保險金」。  
+條文依據：  
+- [第十一條 輕度重大疾病保險金的給付]  
+- [第十二條 重大疾病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D402" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 輕度重大疾病保險金的給付 | 第十二條 重大疾病保險金的給付 | 第十六條 除外責任 | payout_items | 第二條 名詞定義 | 第四條 保險範圍 | other_metadata | 第十五條 各項保險金的申領</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F402" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+在投保後的第三年初次診斷罹患「輕度重大疾病」者，無法領取「重大疾病保險金」，只能領取「輕度重大疾病保險金」，給付比例為保險金額的百分之二十。  
+後續在第四年初次診斷罹患「重大疾病」者，無法再領取「輕度重大疾病保險金」，但可以領取「重大疾病保險金」，給付比例為保險金額的一點三倍，且需扣除已領取的「輕度重大疾病保險金」。  
+條文依據：  
+- [第十一條 輕度重大疾病保險金的給付]  
+- [第十二條 重大疾病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G402" s="2" t="inlineStr"/>
+      <c r="H402" s="2" t="inlineStr"/>
+      <c r="I402" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.909611, "neutral": 0.081394, "contradiction": 0.008995, "factuality": 0.991005, "C_fact": 0.991005}, "C_conf": 0.991}</t>
+        </is>
+      </c>
+      <c r="J402" s="5" t="n"/>
+      <c r="K402" s="5" t="n">
+        <v>0.991005</v>
+      </c>
+      <c r="L402" s="5" t="n">
+        <v>0.991</v>
+      </c>
+      <c r="M402" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:50:24</t>
+        </is>
+      </c>
+      <c r="N402" s="5" t="n">
+        <v>8.449999999999999</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>PX5</t>
+        </is>
+      </c>
+      <c r="B403" s="2" t="inlineStr">
+        <is>
+          <t>請問主約效力終止(因身故以外情形)，PX5還能持續有效嗎？</t>
+        </is>
+      </c>
+      <c r="C403" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+主約效力因身故以外情形終止時，PX5附約效力可持續至附約當期已繳保險費期滿即行終止，並不再延續。  
+條文依據：  
+- [第十條 附約的終止（二）]</t>
+        </is>
+      </c>
+      <c r="D403" s="2" t="inlineStr">
+        <is>
+          <t>第十條 附約的終止（二） | 第七條 保險費的墊繳、附約的停效及復效 | 第五條 附約的保險期間及保證續保 | 第十三條 健康促進保險費折減 | 第九條 附約的終止（一）</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F403" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+主約效力因身故以外情形終止時，PX5附約效力可持續至附約當期已繳保險費期滿即行終止，並不再延續。  
+條文依據：  
+- [第十條 附約的終止（二）]</t>
+        </is>
+      </c>
+      <c r="G403" s="2" t="inlineStr"/>
+      <c r="H403" s="2" t="inlineStr"/>
+      <c r="I403" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.792572, "neutral": 0.011362, "contradiction": 0.196066, "factuality": 0.803934, "C_fact": 0.803934}, "C_conf": 0.8039}</t>
+        </is>
+      </c>
+      <c r="J403" s="5" t="n"/>
+      <c r="K403" s="5" t="n">
+        <v>0.803934</v>
+      </c>
+      <c r="L403" s="5" t="n">
+        <v>0.8038999999999999</v>
+      </c>
+      <c r="M403" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:50:30</t>
+        </is>
+      </c>
+      <c r="N403" s="5" t="n">
+        <v>6.26</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B404" s="2" t="inlineStr">
+        <is>
+          <t>請問如果於「無理賠紀錄期間」屆滿日以內罹患特定傷病，會給付多少錢?這筆錢會給付給誰?</t>
+        </is>
+      </c>
+      <c r="C404" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在「無理賠紀錄期間」屆滿日以內罹患特定傷病，保險公司將給付「保險金額」及「年繳應繳保險費總額」乘以一點零二之加總作為「特定傷病保險金」。此筆保險金的受益人為被保險人本人，保險公司不受理其指定及變更。
+條文依據：  
+- [第十一條 特定傷病保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="D404" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第十二條 無理賠關懷保險金的給付 | 第十一條 特定傷病保險金的給付 | payout_items | 第二十七條 受益人的指定及變更</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F404" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在「無理賠紀錄期間」屆滿日以內罹患特定傷病，保險公司將給付「保險金額」及「年繳應繳保險費總額」乘以一點零二之加總作為「特定傷病保險金」。此筆保險金的受益人為被保險人本人，保險公司不受理其指定及變更。
+條文依據：  
+- [第十一條 特定傷病保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="G404" s="2" t="inlineStr"/>
+      <c r="H404" s="2" t="inlineStr"/>
+      <c r="I404" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.997279, "neutral": 0.00241, "contradiction": 0.000311, "factuality": 0.999689, "C_fact": 0.999689}, "C_conf": 0.9997}</t>
+        </is>
+      </c>
+      <c r="J404" s="5" t="n"/>
+      <c r="K404" s="5" t="n">
+        <v>0.999689</v>
+      </c>
+      <c r="L404" s="5" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="M404" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:50:36</t>
+        </is>
+      </c>
+      <c r="N404" s="5" t="n">
+        <v>5.48</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B405" s="2" t="inlineStr">
+        <is>
+          <t>請問如果要保人與被保險人為同一人，被保險人於「無理賠紀錄期間」屆滿日以內身故，會給付多少錢?這筆錢會給付給誰?</t>
+        </is>
+      </c>
+      <c r="C405" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若要保人與被保險人為同一人，被保險人於「無理賠紀錄期間」屆滿日以內身故，符合「無理賠關懷保險金」的給付條件，保險公司將給付「年繳應繳保險費總額」乘以1.02的金額。此筆保險金的受益人為要保人本人，因要保人與被保險人為同一人，該筆保險金將直接給付予被保險人本人。
+條文依據：  
+- [第十二條 無理賠關懷保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="D405" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第十二條 無理賠關懷保險金的給付 | 第十一條 特定傷病保險金的給付 | payout_items | 第十九條 失蹤處理 | 第二十一條 無理賠關懷保險金的申領 | 第二十七條 受益人的指定及變更 | 第十七條 除外責任（二）</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F405" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若要保人與被保險人為同一人，被保險人於「無理賠紀錄期間」屆滿日以內身故，符合「無理賠關懷保險金」的給付條件，保險公司將給付「年繳應繳保險費總額」乘以1.02的金額。此筆保險金的受益人為要保人本人，因要保人與被保險人為同一人，該筆保險金將直接給付予被保險人本人。
+條文依據：  
+- [第十二條 無理賠關懷保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="G405" s="2" t="inlineStr"/>
+      <c r="H405" s="2" t="inlineStr"/>
+      <c r="I405" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.9757, "neutral": 0.020755, "contradiction": 0.003545, "factuality": 0.996455, "C_fact": 0.996455}, "C_conf": 0.9965}</t>
+        </is>
+      </c>
+      <c r="J405" s="5" t="n"/>
+      <c r="K405" s="5" t="n">
+        <v>0.996455</v>
+      </c>
+      <c r="L405" s="5" t="n">
+        <v>0.9965000000000001</v>
+      </c>
+      <c r="M405" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:50:43</t>
+        </is>
+      </c>
+      <c r="N405" s="5" t="n">
+        <v>6.92</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B406" s="2" t="inlineStr">
+        <is>
+          <t>請問如果要保人與被保險人為不同人，被保險人於「無理賠紀錄期間」屆滿日以內生存，且被保險人未罹患特定傷病，會給付多少錢?這筆錢會給付給誰?</t>
+        </is>
+      </c>
+      <c r="C406" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人於「無理賠紀錄期間」屆滿日以內生存，且未罹患特定傷病，本公司將給付「無理賠關懷保險金」，金額為「年繳應繳保險費總額」乘以1.02。此筆保險金的受益人為要保人本人。
+條文依據：  
+- [第十二條 無理賠關懷保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="D406" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第十二條 無理賠關懷保險金的給付 | 第十一條 特定傷病保險金的給付 | payout_items | 第二十七條 受益人的指定及變更 | 第十九條 失蹤處理 | 第二十一條 無理賠關懷保險金的申領 | 第十七條 除外責任（二）</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F406" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人於「無理賠紀錄期間」屆滿日以內生存，且未罹患特定傷病，本公司將給付「無理賠關懷保險金」，金額為「年繳應繳保險費總額」乘以1.02。此筆保險金的受益人為要保人本人。
+條文依據：  
+- [第十二條 無理賠關懷保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="G406" s="2" t="inlineStr"/>
+      <c r="H406" s="2" t="inlineStr"/>
+      <c r="I406" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.996642, "neutral": 0.003076, "contradiction": 0.000282, "factuality": 0.999718, "C_fact": 0.999718}, "C_conf": 0.9997}</t>
+        </is>
+      </c>
+      <c r="J406" s="5" t="n"/>
+      <c r="K406" s="5" t="n">
+        <v>0.999718</v>
+      </c>
+      <c r="L406" s="5" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="M406" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:50:48</t>
+        </is>
+      </c>
+      <c r="N406" s="5" t="n">
+        <v>5.15</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B407" s="2" t="inlineStr">
+        <is>
+          <t>保戶如果身故，會給保險金嗎?</t>
+        </is>
+      </c>
+      <c r="C407" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保戶身故時，若符合保險契約約定的條件，本公司會依照相關條款給付保險金。例如，若被保險人在「無理賠紀錄期間」內身故，或於「無理賠紀錄期間」屆滿時仍生存，本公司將依第五條約定給付保險金。此外，若受益人在分期定期保險金給付期間內死亡，尚未領取的分期定期保險金會一次貼現給付予受益人之法定繼承人。  
+條文依據：  
+- [第五條 保險範圍]  
+- [第二十八條 本契約受益人死亡或失蹤的處理]</t>
+        </is>
+      </c>
+      <c r="D407" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第二十八條 本契約受益人死亡或失蹤的處理 | 第十七條 除外責任（二） | 第二十三條 受益人受益權之喪失 | 第十九條 失蹤處理</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F407" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保戶身故時，若符合保險契約約定的條件，本公司會依照相關條款給付保險金。例如，若被保險人在「無理賠紀錄期間」內身故，或於「無理賠紀錄期間」屆滿時仍生存，本公司將依第五條約定給付保險金。此外，若受益人在分期定期保險金給付期間內死亡，尚未領取的分期定期保險金會一次貼現給付予受益人之法定繼承人。  
+條文依據：  
+- [第五條 保險範圍]  
+- [第二十八條 本契約受益人死亡或失蹤的處理]</t>
+        </is>
+      </c>
+      <c r="G407" s="2" t="inlineStr"/>
+      <c r="H407" s="2" t="inlineStr"/>
+      <c r="I407" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.992444, "neutral": 0.007411, "contradiction": 0.000145, "factuality": 0.999855, "C_fact": 0.999855}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J407" s="5" t="n"/>
+      <c r="K407" s="5" t="n">
+        <v>0.999855</v>
+      </c>
+      <c r="L407" s="5" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M407" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:50:54</t>
+        </is>
+      </c>
+      <c r="N407" s="5" t="n">
+        <v>5.74</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B408" s="2" t="inlineStr">
+        <is>
+          <t>保戶如果身故，身故申領的保險金會給誰?</t>
+        </is>
+      </c>
+      <c r="C408" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保戶身故後，若有尚未給付或未完全給付的特定傷病保險金，則該部分保險金的受益人為保戶的法定繼承人。若涉及無理賠關懷保險金，受益人同樣為法定繼承人，並依民法繼承編相關規定分配。  
+條文依據：  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="D408" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第二十三條 受益人受益權之喪失 | 第二十七條 受益人的指定及變更 | 第二十八條 本契約受益人死亡或失蹤的處理 | 第二十二條 分期定期保險金給付申領文件、給付期限及未依限給付之效果</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F408" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保戶身故後，若有尚未給付或未完全給付的特定傷病保險金，則該部分保險金的受益人為保戶的法定繼承人。若涉及無理賠關懷保險金，受益人同樣為法定繼承人，並依民法繼承編相關規定分配。  
+條文依據：  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="G408" s="2" t="inlineStr"/>
+      <c r="H408" s="2" t="inlineStr"/>
+      <c r="I408" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.997007, "neutral": 0.002757, "contradiction": 0.000236, "factuality": 0.999764, "C_fact": 0.999764}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J408" s="5" t="n"/>
+      <c r="K408" s="5" t="n">
+        <v>0.999764</v>
+      </c>
+      <c r="L408" s="5" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M408" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:50:58</t>
+        </is>
+      </c>
+      <c r="N408" s="5" t="n">
+        <v>3.83</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B409" s="2" t="inlineStr">
+        <is>
+          <t>如果保戶投保繳費年期20年的滿溢寶，然後在第20保單年度身故的話，可以領到多少錢?</t>
+        </is>
+      </c>
+      <c r="C409" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若保戶在第20保單年度身故，依據條款規定，若未曾罹患特定傷病且於「無理賠紀錄期間」內身故，本公司將依照契約約定給付保險金。具體金額需依保險單所載的保險金額及相關條件計算。
+條文依據：  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="D409" s="2" t="inlineStr">
+        <is>
+          <t>other_metadata | 第二十八條 本契約受益人死亡或失蹤的處理 | 第二十六條 投保年齡的計算及錯誤的處理 | 第十一條 特定傷病保險金的給付 | 第二十二條 分期定期保險金給付申領文件、給付期限及未依限給付之效果 | 第五條 保險範圍 | 第十五條 健康促進保險費折減 | 第十九條 失蹤處理</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F409" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若保戶在第20保單年度身故，依據條款規定，若未曾罹患特定傷病且於「無理賠紀錄期間」內身故，本公司將依照契約約定給付保險金。具體金額需依保險單所載的保險金額及相關條件計算。
+條文依據：  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="G409" s="2" t="inlineStr"/>
+      <c r="H409" s="2" t="inlineStr"/>
+      <c r="I409" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.033004, "neutral": 0.966594, "contradiction": 0.000402, "factuality": 0.999598, "C_fact": 0.999598}, "C_conf": 0.9996}</t>
+        </is>
+      </c>
+      <c r="J409" s="5" t="n"/>
+      <c r="K409" s="5" t="n">
+        <v>0.999598</v>
+      </c>
+      <c r="L409" s="5" t="n">
+        <v>0.9996</v>
+      </c>
+      <c r="M409" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:51:01</t>
+        </is>
+      </c>
+      <c r="N409" s="5" t="n">
+        <v>3.56</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B410" s="2" t="inlineStr">
+        <is>
+          <t>被保險人為60歲女性，投保繳費期間20年期之滿溢寶特定傷病定期健康保險（定期給付型）（外溢型）100萬元，年繳應繳保險費為83,500元，年繳實繳保險費為78,490元。若被保險人於第二保險單年度自殺身故，則無理賠關懷保險金可以領到多少錢？</t>
+        </is>
+      </c>
+      <c r="C410" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+依第十七條規定，被保險人於契約訂立或復效之日起二年內故意自殺致死者，本公司不負給付無理賠關懷保險金的責任。因此，若被保險人於第二保險單年度自殺身故，無理賠關懷保險金無法領取。
+條文依據：  
+- [第十七條 除外責任（二)]</t>
+        </is>
+      </c>
+      <c r="D410" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 無理賠關懷保險金的給付 | 第十七條 除外責任（二） | 第十一條 特定傷病保險金的給付 | 第十九條 失蹤處理 | 第五條 保險範圍 | 第二十一條 無理賠關懷保險金的申領 | 第二十七條 受益人的指定及變更</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F410" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人於第二保險單年度自殺身故，依條款規定，自契約訂立或復效之日起二年內故意自殺致死者，本公司不負給付無理賠關懷保險金的責任。因此，無理賠關懷保險金無法領取。
+條文依據：  
+- [第十七條 除外責任（二)]</t>
+        </is>
+      </c>
+      <c r="G410" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+依第十七條規定，被保險人於契約訂立或復效之日起二年內故意自殺致死者，本公司不負給付無理賠關懷保險金的責任。因此，若被保險人於第二保險單年度自殺身故，無理賠關懷保險金無法領取。
+條文依據：  
+- [第十七條 除外責任（二)]</t>
+        </is>
+      </c>
+      <c r="H410" s="2" t="inlineStr"/>
+      <c r="I410" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.96674, "neutral": 0.032422, "contradiction": 0.000838, "factuality": 0.999162, "C_fact": 0.999162}, "C_conf": 0.9992}</t>
+        </is>
+      </c>
+      <c r="J410" s="5" t="n"/>
+      <c r="K410" s="5" t="n">
+        <v>0.999162</v>
+      </c>
+      <c r="L410" s="5" t="n">
+        <v>0.9992</v>
+      </c>
+      <c r="M410" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:51:07</t>
+        </is>
+      </c>
+      <c r="N410" s="5" t="n">
+        <v>5.91</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B411" s="2" t="inlineStr">
+        <is>
+          <t>請問如果第2保單年度罹患特定傷病，可以給付多少錢?給付給誰?未來還有其他保險金嗎?</t>
+        </is>
+      </c>
+      <c r="C411" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在第二保險單年度（含）以後罹患特定傷病，依條款規定可獲得以下給付：  
+1. **特定傷病保險金**：給付金額為「保險金額」，且僅給付一次。  
+2. **生活補助保險金**：自初次診斷確定罹患特定傷病的次一個保險單週年日起，每逢保險單週年日仍生存者，按「保險金額」的36%給付，最高可給付十次。  
+3. **保險費豁免**：自診斷確定日起豁免續期保險費，但當期已繳付之未到期保險費不予退還。  
+給付對象為被保險人。  
+條文依據：  
+- [第十二條 特定傷病保險金的給付]  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]  
+- [第十五條 保險費豁免（第二保險單年度起適用）]</t>
+        </is>
+      </c>
+      <c r="D411" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 特定傷病保險金的給付 | 第五條 保險範圍 | 第十三條 生活補助保險金的給付（第二保險單年度起適用） | 第二條 名詞定義 | 第十五條 保險費豁免（第二保險單年度起適用）</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F411" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在第二保險單年度（含）以後罹患特定傷病，依條款規定可獲得以下給付：  
+1. **特定傷病保險金**：給付金額為「保險金額」，且僅給付一次。  
+2. **生活補助保險金**：自初次診斷確定罹患特定傷病的次一個保險單週年日起，每逢保險單週年日仍生存者，按「保險金額」的36%給付，最高可給付十次。  
+3. **保險費豁免**：自診斷確定日起豁免續期保險費，但當期已繳付之未到期保險費不予退還。  
+給付對象為被保險人。  
+條文依據：  
+- [第十二條 特定傷病保險金的給付]  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]  
+- [第十五條 保險費豁免（第二保險單年度起適用）]</t>
+        </is>
+      </c>
+      <c r="G411" s="2" t="inlineStr"/>
+      <c r="H411" s="2" t="inlineStr"/>
+      <c r="I411" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.972963, "neutral": 0.025578, "contradiction": 0.001459, "factuality": 0.998541, "C_fact": 0.998541}, "C_conf": 0.9985}</t>
+        </is>
+      </c>
+      <c r="J411" s="5" t="n"/>
+      <c r="K411" s="5" t="n">
+        <v>0.998541</v>
+      </c>
+      <c r="L411" s="5" t="n">
+        <v>0.9985000000000001</v>
+      </c>
+      <c r="M411" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:51:15</t>
+        </is>
+      </c>
+      <c r="N411" s="5" t="n">
+        <v>7.11</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B412" s="2" t="inlineStr">
+        <is>
+          <t>請問我115年1月1日投保，怎麼得到健康促進保險費折減?</t>
+        </is>
+      </c>
+      <c r="C412" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+要獲得健康促進保險費折減，您需在本契約有效期間內完成以下步驟：  
+1. 使用本公司指定的程式並加入指定的健康計劃。  
+2. 完成程式註冊程序，並執行該程式。  
+3. 授權本公司取得您裝置或程式內與健康促進相關的電子紀錄。  
+4. 確保於「指定日期」的會員等級符合折減標準（如「實踐家」可折減3%，「樂享家」或更高等級可折減10%）。  
+本公司將根據成功傳輸的電子紀錄，依其辦法計算您的會員等級，並按表列比例折減次一保險單年度的保險費。  
+條文依據：  
+- [第十六條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="D412" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 健康促進保險費折減 | 第二十三條 投保年齡的計算及錯誤的處理 | 第十五條 保險費豁免（第二保險單年度起適用） | 第五條 保險範圍 | payout_items</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F412" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+要獲得健康促進保險費折減，您需在本契約有效期間內完成以下步驟：  
+1. 使用本公司指定的程式並加入指定的健康計劃。  
+2. 完成程式註冊程序，並執行該程式。  
+3. 授權本公司取得您裝置或程式內與健康促進相關的電子紀錄。  
+4. 確保於「指定日期」的會員等級符合折減標準（如「實踐家」可折減3%，「樂享家」或更高等級可折減10%）。  
+本公司將根據成功傳輸的電子紀錄，依其辦法計算您的會員等級，並按表列比例折減次一保險單年度的保險費。  
+條文依據：  
+- [第十六條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="G412" s="2" t="inlineStr"/>
+      <c r="H412" s="2" t="inlineStr"/>
+      <c r="I412" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.997531, "neutral": 0.002319, "contradiction": 0.00015, "factuality": 0.99985, "C_fact": 0.99985}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J412" s="5" t="n"/>
+      <c r="K412" s="5" t="n">
+        <v>0.99985</v>
+      </c>
+      <c r="L412" s="5" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M412" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:51:22</t>
+        </is>
+      </c>
+      <c r="N412" s="5" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B413" s="2" t="inlineStr">
+        <is>
+          <t>保戶在114/1/10投保樂鍾溢，如果他在115/3/30罹患特定傷病的話，在什麼時候可以領取生活補助保險金?</t>
+        </is>
+      </c>
+      <c r="C413" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保戶在114/1/10投保，保險單週年日為每年的1月10日。根據條款，生活補助保險金的給付需符合以下條件：  
+1. 被保險人於第二保險單年度（含）以後的有效期間內初次診斷確定罹患特定傷病。  
+2. 自初次診斷確定罹患特定傷病的次一個保險單週年日起，每逢保險單週年日仍生存者，方可領取生活補助保險金。  
+保戶於115/3/30診斷罹患特定傷病，屬於第二保險單年度（114/1/10至115/1/9之後）。因此，保戶可於診斷確定的次一個保險單週年日，即116/1/10起，每逢保險單週年日仍生存者，開始領取生活補助保險金。
+條文依據：  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]</t>
+        </is>
+      </c>
+      <c r="D413" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 生活補助保險金的給付（第二保險單年度起適用） | other_metadata | 第十一條 契約的終止（三） | payout_items | 第十二條 特定傷病保險金的給付 | 第五條 保險範圍 | 第十五條 保險費豁免（第二保險單年度起適用） | 第十條 契約的終止（二）</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F413" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保戶在114/1/10投保，保險單週年日為每年的1月10日。根據條款，生活補助保險金的給付需符合以下條件：  
+1. 被保險人於第二保險單年度（含）以後的有效期間內初次診斷確定罹患特定傷病。  
+2. 自初次診斷確定罹患特定傷病的次一個保險單週年日起，每逢保險單週年日仍生存者，方可領取生活補助保險金。  
+保戶於115/3/30診斷罹患特定傷病，屬於第二保險單年度（114/1/10至115/1/9之後）。因此，保戶可於診斷確定的次一個保險單週年日，即116/1/10起，每逢保險單週年日仍生存者，開始領取生活補助保險金。
+條文依據：  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]</t>
+        </is>
+      </c>
+      <c r="G413" s="2" t="inlineStr"/>
+      <c r="H413" s="2" t="inlineStr"/>
+      <c r="I413" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.934257, "neutral": 0.029707, "contradiction": 0.036036, "factuality": 0.963964, "C_fact": 0.963964}, "C_conf": 0.964}</t>
+        </is>
+      </c>
+      <c r="J413" s="5" t="n"/>
+      <c r="K413" s="5" t="n">
+        <v>0.963964</v>
+      </c>
+      <c r="L413" s="5" t="n">
+        <v>0.964</v>
+      </c>
+      <c r="M413" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:51:44</t>
+        </is>
+      </c>
+      <c r="N413" s="5" t="n">
+        <v>21.84</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B414" s="2" t="inlineStr">
+        <is>
+          <t>保戶在114/1/10投保樂鍾溢，如果他在115/3/30罹患特定傷病的話，他在115/1/9會領到無理賠回饋保險金嗎?</t>
+        </is>
+      </c>
+      <c r="C414" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不會領到無理賠回饋保險金。根據條款規定，無理賠回饋保險金的給付條件是被保險人在保險單年度末未曾因罹患特定傷病申領「特定傷病保險金」，且仍生存。由於保戶在115/3/30罹患特定傷病，並符合申領「特定傷病保險金」的條件，因此不符合無理賠回饋保險金的給付條件。
+條文依據：  
+- [第十四條 無理賠回饋保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D414" s="2" t="inlineStr">
+        <is>
+          <t>payout_items | 第十四條 無理賠回饋保險金的給付 | other_metadata | 第十二條 特定傷病保險金的給付 | 第二十條 無理賠回饋保險金的申領 | 第十條 契約的終止（二） | 第五條 保險範圍 | 第十五條 保險費豁免（第二保險單年度起適用）</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F414" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不會領到無理賠回饋保險金。根據條款規定，無理賠回饋保險金的給付條件是被保險人在保險單年度末未曾因罹患特定傷病申領「特定傷病保險金」，且仍生存。由於保戶在115/3/30罹患特定傷病，並符合申領「特定傷病保險金」的條件，因此不符合無理賠回饋保險金的給付條件。
+條文依據：  
+- [第十四條 無理賠回饋保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G414" s="2" t="inlineStr"/>
+      <c r="H414" s="2" t="inlineStr"/>
+      <c r="I414" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.021204, "neutral": 0.975938, "contradiction": 0.002858, "factuality": 0.997142, "C_fact": 0.997142}, "C_conf": 0.9971}</t>
+        </is>
+      </c>
+      <c r="J414" s="5" t="n"/>
+      <c r="K414" s="5" t="n">
+        <v>0.997142</v>
+      </c>
+      <c r="L414" s="5" t="n">
+        <v>0.9971</v>
+      </c>
+      <c r="M414" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:51:56</t>
+        </is>
+      </c>
+      <c r="N414" s="5" t="n">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B415" s="2" t="inlineStr">
+        <is>
+          <t>被保險人於第一保險單年度罹患急性心肌梗塞（重度），生活補助保險金最多可以領取幾次？</t>
+        </is>
+      </c>
+      <c r="C415" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於第一保險單年度罹患急性心肌梗塞（重度），無法申領生活補助保險金。根據條款規定，生活補助保險金的給付僅適用於第二保險單年度（含）以後的有效期間內初次診斷確定罹患特定傷病者。
+條文依據：  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]</t>
+        </is>
+      </c>
+      <c r="D415" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 生活補助保險金的給付（第二保險單年度起適用） | 第十二條 特定傷病保險金的給付 | 第十一條 契約的終止（三） | 第五條 保險範圍 | 第二條 名詞定義 | payout_items | 第十四條 無理賠回饋保險金的給付 | 第十九條 特定傷病保險金、生活補助保險金或保險費豁免的申領</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F415" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於第一保險單年度罹患急性心肌梗塞（重度），無法申領生活補助保險金。根據條款規定，生活補助保險金的給付僅適用於第二保險單年度（含）以後的有效期間內初次診斷確定罹患特定傷病者。
+條文依據：  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]</t>
+        </is>
+      </c>
+      <c r="G415" s="2" t="inlineStr"/>
+      <c r="H415" s="2" t="inlineStr"/>
+      <c r="I415" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.435759, "neutral": 0.557938, "contradiction": 0.006303, "factuality": 0.993697, "C_fact": 0.993697}, "C_conf": 0.9937}</t>
+        </is>
+      </c>
+      <c r="J415" s="5" t="n"/>
+      <c r="K415" s="5" t="n">
+        <v>0.9936970000000001</v>
+      </c>
+      <c r="L415" s="5" t="n">
+        <v>0.9937</v>
+      </c>
+      <c r="M415" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:52:02</t>
+        </is>
+      </c>
+      <c r="N415" s="5" t="n">
+        <v>4.53</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B416" s="2" t="inlineStr">
+        <is>
+          <t>被保險人為60歲女性，投保繳費期間20年期之樂鍾心特定傷病定期健康保險（外溢型）5單位，每單位年繳應繳保險費為1675元，則每逢保險單年度末生存者，可以領取多少無理賠關懷保險金？</t>
+        </is>
+      </c>
+      <c r="C416" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+每逢保險單年度末生存者，若符合條件，可領取的「無理賠回饋保險金」金額為：1675元 × 10% × 5單位 = 837元（元以下無條件進位）。  
+條文依據：  
+- [第十四條 無理賠回饋保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D416" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 無理賠回饋保險金的給付 | other_metadata | payout_items | 第二十條 無理賠回饋保險金的申領 | 第十二條 特定傷病保險金的給付 | 第十三條 生活補助保險金的給付（第二保險單年度起適用） | 第五條 保險範圍 | 第十五條 保險費豁免（第二保險單年度起適用）</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F416" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+每逢保險單年度末生存者，若符合條件，可領取的「無理賠回饋保險金」金額為：1675元 × 10% × 5單位 = 837元（元以下無條件進位）。  
+條文依據：  
+- [第十四條 無理賠回饋保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G416" s="2" t="inlineStr"/>
+      <c r="H416" s="2" t="inlineStr"/>
+      <c r="I416" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.499043, "neutral": 0.49712, "contradiction": 0.003837, "factuality": 0.996163, "C_fact": 0.996163}, "C_conf": 0.9962}</t>
+        </is>
+      </c>
+      <c r="J416" s="5" t="n"/>
+      <c r="K416" s="5" t="n">
+        <v>0.996163</v>
+      </c>
+      <c r="L416" s="5" t="n">
+        <v>0.9962</v>
+      </c>
+      <c r="M416" t="inlineStr">
+        <is>
+          <t>2026-03-31 21:52:16</t>
+        </is>
+      </c>
+      <c r="N416" s="5" t="n">
+        <v>13.72</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/rag_results.xlsx
+++ b/src/rag_results.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M85"/>
+  <dimension ref="A1:M191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5940,6 +5940,6993 @@
         </is>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>保障範圍包括哪些項目？</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括：住院醫療保險金、加護病房或燒燙傷病房保險金、祝壽保險金、身故保險金或喪葬費用保險金，以及所繳保險費的退還。
+條文依據：  
+- 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>payout_items | summary | 第五條 保險範圍 | 第二條 名詞定義 | 第十八條 除外責任（一）</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括：住院醫療保險金、加護病房或燒燙傷病房保險金、祝壽保險金、身故保險金或喪葬費用保險金，以及所繳保險費的退還。
+條文依據：  
+- 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr"/>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "保障範圍包括哪些項目？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.998507, "neutral": 0.001287, "contradiction": 0.000206, "factuality": 0.999794, "C_fact": 0.999794}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J86" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K86" s="3" t="n">
+        <v>0.999794</v>
+      </c>
+      <c r="L86" s="3" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:19:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>住院日數計算有什麼特殊規則？</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院日數的計算規則如下：  
+1. 住院日數是指被保險人同一次住院期間，實際全日住進急性病房或慢性病房（包括加護病房及燒燙傷病房）的日數，並包含住院當日及出院當日。  
+2. 若被保險人出院後於同一日再次入院診療，該日不得重複計入住院日數。  
+條文依據：  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第十二條 住院醫療保險金的給付 | 第二條 名詞定義 | 第十三條 加護病房或燒燙傷病房保險金的給付 | 第二十八條 住院醫療保險金日額之減少</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院日數的計算規則如下：  
+1. 住院日數是指被保險人同一次住院期間，實際全日住進急性病房或慢性病房（包括加護病房及燒燙傷病房）的日數，並包含住院當日及出院當日。  
+2. 若被保險人出院後於同一日再次入院診療，該日不得重複計入住院日數。  
+條文依據：  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr"/>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "住院日數計算有什麼特殊規則？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.998083, "neutral": 0.001733, "contradiction": 0.000184, "factuality": 0.999816, "C_fact": 0.999816}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J87" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K87" s="3" t="n">
+        <v>0.999816</v>
+      </c>
+      <c r="L87" s="3" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:20:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>住院醫療保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院醫療保險金的給付規定如下：  
+1. 被保險人於契約有效期間內因疾病或傷害住院治療時，保險公司將依保險單所載的「住院醫療保險金日額」，乘以入院日當年度的「增額係數」，再乘以住院日數，給付住院醫療保險金。  
+2. 同一保單年度內，同一次住院的住院醫療保險金給付日數，最高以365日為限。  
+條文依據：  
+- [第十二條 住院醫療保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 住院醫療保險金的給付 | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第十三條 加護病房或燒燙傷病房保險金的給付 | 第十四條 醫療保險金給付總額之上限 | 第二十八條 住院醫療保險金日額之減少</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院醫療保險金的給付規定如下：  
+1. 被保險人於契約有效期間內因疾病或傷害住院治療時，保險公司將依保險單所載的「住院醫療保險金日額」，乘以入院日當年度的「增額係數」，再乘以住院日數，給付住院醫療保險金。  
+2. 同一保單年度內，同一次住院的住院醫療保險金給付日數，最高以365日為限。  
+條文依據：  
+- [第十二條 住院醫療保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr"/>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "住院醫療保險金的給付規定", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.996683, "neutral": 0.002892, "contradiction": 0.000425, "factuality": 0.999575, "C_fact": 0.999575}, "C_conf": 0.9997}</t>
+        </is>
+      </c>
+      <c r="J88" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K88" s="3" t="n">
+        <v>0.999575</v>
+      </c>
+      <c r="L88" s="3" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:20:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>加護病房或燒燙傷病房保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+加護病房或燒燙傷病房保險金的給付規定如下：  
+1. 被保險人於本契約有效期間內因疾病或傷害住進醫院的加護病房或燒燙傷病房接受治療時，除住院醫療保險金外，保險公司將依保險單上記載的「住院醫療保險金日額」，乘以入院日當年度的「增額係數」，再乘以實際住進加護病房或燒燙傷病房的日數（含轉入及轉出當日）的二倍，給付「加護病房或燒燙傷病房保險金」。  
+2. 同一保單年度內，同一次住院的加護病房及燒燙傷病房住院日數合計給付上限為365日。  
+3. 同一日內，保險公司僅就加護病房或燒燙傷病房其中一種病房給付。
+條文依據：  
+- [第十三條 加護病房或燒燙傷病房保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 加護病房或燒燙傷病房保險金的給付 | payout_items | 第二十三條 醫療保險金的申領 | 第五條 保險範圍 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+加護病房或燒燙傷病房保險金的給付規定如下：  
+1. 被保險人於本契約有效期間內因疾病或傷害住進醫院的加護病房或燒燙傷病房接受治療時，除住院醫療保險金外，保險公司將依保險單上記載的「住院醫療保險金日額」，乘以入院日當年度的「增額係數」，再乘以實際住進加護病房或燒燙傷病房的日數（含轉入及轉出當日）的二倍，給付「加護病房或燒燙傷病房保險金」。  
+2. 同一保單年度內，同一次住院的加護病房及燒燙傷病房住院日數合計給付上限為365日。  
+3. 同一日內，保險公司僅就加護病房或燒燙傷病房其中一種病房給付。
+條文依據：  
+- [第十三條 加護病房或燒燙傷病房保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr"/>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "加護病房或燒燙傷病房保險金的給付規定", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.994475, "neutral": 0.004596, "contradiction": 0.000929, "factuality": 0.999071, "C_fact": 0.999071}, "C_conf": 0.9994}</t>
+        </is>
+      </c>
+      <c r="J89" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K89" s="3" t="n">
+        <v>0.999071</v>
+      </c>
+      <c r="L89" s="3" t="n">
+        <v>0.9994</v>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:20:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>醫療保險金給付總額之上限</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+醫療保險金給付總額之上限為保險單上所記載之「住院醫療保險金日額」的二千五百倍。
+條文依據：  
+- [第十四條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 醫療保險金給付總額之上限 | 第十二條 住院醫療保險金的給付 | 第五條 保險範圍 | 第十三條 加護病房或燒燙傷病房保險金的給付 | payout_items</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+醫療保險金給付總額之上限為保險單上所記載之「住院醫療保險金日額」的二千五百倍。
+條文依據：  
+- [第十四條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr"/>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "醫療保險金給付總額之上限", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.997331, "neutral": 0.002391, "contradiction": 0.000278, "factuality": 0.999722, "C_fact": 0.999722}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J90" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K90" s="3" t="n">
+        <v>0.999722</v>
+      </c>
+      <c r="L90" s="3" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:20:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>祝壽保險金的給付規定為何?</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+祝壽保險金的給付規定如下：  
+被保險人於本契約有效期間內，且保險年齡到達九十九歲之保險單週年日仍生存時，本公司將按「當年度保險金額」給付「祝壽保險金」。
+條文依據：  
+- [第十五條 祝壽保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>第十五條 祝壽保險金的給付 | 第十二條至第十三條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | 第二十四條 祝壽保險金的申領 | payout_items | 第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+祝壽保險金的給付規定如下：  
+被保險人於本契約有效期間內，且保險年齡到達九十九歲之保險單週年日仍生存時，本公司將按「當年度保險金額」給付「祝壽保險金」。
+條文依據：  
+- [第十五條 祝壽保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr"/>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "祝壽保險金的給付規定為何?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.998014, "neutral": 0.001828, "contradiction": 0.000157, "factuality": 0.999843, "C_fact": 0.999843}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J91" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K91" s="3" t="n">
+        <v>0.999843</v>
+      </c>
+      <c r="L91" s="3" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:21:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>有效期間內身故，保險金如何給付?</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於本契約有效期間內身故時，本公司按「當年度保險金額」給付「身故保險金」。若被保險人於繳費期間內身故，當期已繳付之未到期保險費將不予退還，亦不併入身故保險金內給付。若被保險人於有效期間內且實際年齡未滿十五足歲身故，本公司將按「所繳保險費」退還要保人，不適用前述規定。此外，若被保險人為受監護宣告尚未撤銷者，其身故保險金變更為喪葬費用保險金，並受相關限額規定約束。
+條文依據：  
+- [第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付 | 第十條 契約的終止（二） | 第五條 保險範圍 | 第二十二條 失蹤處理 | 第十五條 祝壽保險金的給付</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於本契約有效期間內身故時，本公司按「當年度保險金額」給付「身故保險金」。若被保險人於繳費期間內身故，當期已繳付之未到期保險費將不予退還，亦不併入身故保險金內給付。若被保險人於有效期間內且實際年齡未滿十五足歲身故，本公司將按「所繳保險費」退還要保人，不適用前述規定。此外，若被保險人為受監護宣告尚未撤銷者，其身故保險金變更為喪葬費用保險金，並受相關限額規定約束。
+條文依據：  
+- [第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr"/>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "有效期間內身故，保險金如何給付?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.591009, "neutral": 0.407278, "contradiction": 0.001713, "factuality": 0.998287, "C_fact": 0.998287}, "C_conf": 0.999}</t>
+        </is>
+      </c>
+      <c r="J92" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K92" s="3" t="n">
+        <v>0.998287</v>
+      </c>
+      <c r="L92" s="3" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:21:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>健康促進保險費折減規定</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+健康促進保險費折減規定如下：  
+1. 被保險人年齡需滿20歲（含）以上，並使用保險公司指定程式加入健康計劃。  
+2. 若於「指定日期」會員等級符合標準，次一保險單年度保險費可依會員等級折減：  
+   - 進階會員：折減2%。  
+   - 菁英會員或更高等級：折減3%。  
+3. 折減僅適用於主契約保險費，不包含附約、附加條款或批註條款，且豁免或復效的保險費不適用折減。  
+4. 被保險人需完成程式註冊並授權保險公司取得健康相關電子紀錄，保險公司將依紀錄計算會員等級。
+條文依據：  
+- [第十七條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>第十七條 健康促進保險費折減 | 第二十八條 住院醫療保險金日額之減少 | 第三十條 投保年齡的計算及錯誤的處理 | 第二條 名詞定義 | 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+健康促進保險費折減規定如下：  
+1. 被保險人年齡需滿20歲（含）以上，並使用保險公司指定程式加入健康計劃。  
+2. 若於「指定日期」會員等級符合標準，次一保險單年度保險費可依會員等級折減：  
+   - 進階會員：折減2%。  
+   - 菁英會員或更高等級：折減3%。  
+3. 折減僅適用於主契約保險費，不包含附約、附加條款或批註條款，且豁免或復效的保險費不適用折減。  
+4. 被保險人需完成程式註冊並授權保險公司取得健康相關電子紀錄，保險公司將依紀錄計算會員等級。
+條文依據：  
+- [第十七條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr"/>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "健康促進保險費折減規定", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.992653, "neutral": 0.006483, "contradiction": 0.000864, "factuality": 0.999136, "C_fact": 0.999136}, "C_conf": 0.9995}</t>
+        </is>
+      </c>
+      <c r="J93" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K93" s="3" t="n">
+        <v>0.999136</v>
+      </c>
+      <c r="L93" s="3" t="n">
+        <v>0.9995000000000001</v>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:21:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>除外責任的解釋?</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+除外責任是指保險公司對於某些特定原因或情況下所發生的疾病、傷害或事故，不負給付保險金的責任。以下為相關條文中的除外責任範圍：  
+1. **一般除外責任**：  
+   - 被保險人因故意行為（如自殺、自殺未遂）、犯罪行為或非法施用毒品所致疾病或傷害，保險公司不負責給付保險金。  
+   - 因美容手術、外科整型（但重建基本功能的必要整型不在此限）、健康檢查、療養等非直接診治病人目的的行為，保險公司不負責給付保險金。  
+   - 懷孕、流產或分娩及其併發症一般不在保障範圍內，但特定情況（如子宮外孕、葡萄胎等）不在此限。  
+2. **特定情況的例外**：  
+   - 若因醫療行為必要進行流產或剖腹產，且符合條文中列舉的醫學條件，則保險公司仍需負責給付保險金。  
+條文依據：  
+- [第十八條 除外責任（一）]  
+- [第十九條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第十九條 除外責任（二） | 第八條 告知義務與本契約的解除 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+除外責任是指保險公司對於某些特定原因或情況下所發生的疾病、傷害或事故，不負給付保險金的責任。以下為相關條文中的除外責任範圍：  
+1. **一般除外責任**：  
+   - 被保險人因故意行為（如自殺、自殺未遂）、犯罪行為或非法施用毒品所致疾病或傷害，保險公司不負責給付保險金。  
+   - 因美容手術、外科整型（但重建基本功能的必要整型不在此限）、健康檢查、療養等非直接診治病人目的的行為，保險公司不負責給付保險金。  
+   - 懷孕、流產或分娩及其併發症一般不在保障範圍內，但特定情況（如子宮外孕、葡萄胎等）不在此限。  
+2. **特定情況的例外**：  
+   - 若因醫療行為必要進行流產或剖腹產，且符合條文中列舉的醫學條件，則保險公司仍需負責給付保險金。  
+條文依據：  
+- [第十八條 除外責任（一）]  
+- [第十九條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr"/>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "除外責任的解釋?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.975044, "neutral": 0.023763, "contradiction": 0.001193, "factuality": 0.998807, "C_fact": 0.998807}, "C_conf": 0.9993}</t>
+        </is>
+      </c>
+      <c r="J94" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K94" s="3" t="n">
+        <v>0.998807</v>
+      </c>
+      <c r="L94" s="3" t="n">
+        <v>0.9993</v>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:21:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>哪些疾病被含在除外責任?</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人因以下原因所致之疾病或傷害，屬於除外責任範圍，本公司不負給付保險金的責任：  
+1. 被保險人之故意行為（包括自殺及自殺未遂）。  
+2. 被保險人之犯罪行為。  
+3. 被保險人非法施用毒品。  
+4. 美容手術、外科整型（但為重建基本功能所作之必要整型不在此限）。  
+5. 外觀可見之天生畸形。  
+6. 健康檢查、療養、靜養、戒毒、戒酒、護理或養老等非以直接診治病人為目的者。  
+7. 懷孕、流產或分娩及其併發症（但特定懷孕相關疾病、醫療行為必要之流產及剖腹產情形不在此限）。  
+8. 不孕症、人工受孕或非以治療為目的之避孕及絕育手術。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第二條 名詞定義 | 第十九條 除外責任（二）</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人因以下原因所致之疾病或傷害，屬於除外責任範圍，本公司不負給付保險金的責任：  
+1. 被保險人之故意行為（包括自殺及自殺未遂）。  
+2. 被保險人之犯罪行為。  
+3. 被保險人非法施用毒品。  
+4. 美容手術、外科整型（但為重建基本功能所作之必要整型不在此限）。  
+5. 外觀可見之天生畸形。  
+6. 健康檢查、療養、靜養、戒毒、戒酒、護理或養老等非以直接診治病人為目的者。  
+7. 懷孕、流產或分娩及其併發症（但特定懷孕相關疾病、醫療行為必要之流產及剖腹產情形不在此限）。  
+8. 不孕症、人工受孕或非以治療為目的之避孕及絕育手術。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr"/>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "哪些疾病被含在除外責任?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.998241, "neutral": 0.001506, "contradiction": 0.000253, "factuality": 0.999747, "C_fact": 0.999747}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J95" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K95" s="3" t="n">
+        <v>0.9997470000000001</v>
+      </c>
+      <c r="L95" s="3" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:22:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>進行美容手術住院可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，因美容手術住院無法申請理賠。但若該美容手術是為了重建基本功能所作之必要整型，則不在此限，仍可申請理賠。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第十三條 加護病房或燒燙傷病房保險金的給付 | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第二條 名詞定義 | payout_items</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，因美容手術住院無法申請理賠。但若該美容手術是為了重建基本功能所作之必要整型，則不在此限，仍可申請理賠。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr"/>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "進行美容手術住院可以申請理賠嗎?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.407922, "neutral": 0.588038, "contradiction": 0.004039, "factuality": 0.995961, "C_fact": 0.995961}, "C_conf": 0.9976}</t>
+        </is>
+      </c>
+      <c r="J96" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K96" s="3" t="n">
+        <v>0.995961</v>
+      </c>
+      <c r="L96" s="3" t="n">
+        <v>0.9976</v>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:22:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>因胎兒染色體異常進行手術而住院可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以申請理賠。根據條款，因胎兒染色體異常進行手術屬於懷孕相關疾病的例外情形，不在除外責任範圍內，因此符合理賠條件。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第二條 名詞定義 | payout_items | 第十三條 加護病房或燒燙傷病房保險金的給付</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以申請理賠。根據條款，因胎兒染色體異常進行手術屬於懷孕相關疾病的例外情形，不在除外責任範圍內，因此符合理賠條件。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr"/>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "因胎兒染色體異常進行手術而住院可以申請理賠嗎?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.977987, "neutral": 0.02171, "contradiction": 0.000303, "factuality": 0.999697, "C_fact": 0.999697}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J97" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K97" s="3" t="n">
+        <v>0.9996969999999999</v>
+      </c>
+      <c r="L97" s="3" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:22:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>因胎位不正進行手術而住院可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，因胎位不正進行手術而住院屬於除外責任範圍內的「懷孕、流產或分娩及其併發症」。但若符合「醫療行為必要之剖腹產」的條件，例如胎位不正，則不在除外責任範圍內，可以申請理賠。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第二條 名詞定義 | payout_items | 第十三條 加護病房或燒燙傷病房保險金的給付</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，因胎位不正進行手術而住院屬於除外責任範圍內的「懷孕、流產或分娩及其併發症」。但若符合「醫療行為必要之剖腹產」的條件，例如胎位不正，則不在除外責任範圍內，可以申請理賠。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr"/>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "因胎位不正進行手術而住院可以申請理賠嗎?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.409909, "neutral": 0.582227, "contradiction": 0.007864, "factuality": 0.992136, "C_fact": 0.992136}, "C_conf": 0.9953}</t>
+        </is>
+      </c>
+      <c r="J98" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K98" s="3" t="n">
+        <v>0.992136</v>
+      </c>
+      <c r="L98" s="3" t="n">
+        <v>0.9953</v>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:22:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>因自殺未遂導致住院可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人因自殺未遂導致住院，本公司不負給付住院相關保險金的責任，因其屬於被保險人之故意行為。  
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 除外責任（二） | 第十八條 除外責任（一） | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | payout_items | 第十條 契約的終止（二）</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人因自殺未遂導致住院，本公司不負給付住院相關保險金的責任，因其屬於被保險人之故意行為。  
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr"/>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "因自殺未遂導致住院可以申請理賠嗎?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.993764, "neutral": 0.005568, "contradiction": 0.000669, "factuality": 0.999331, "C_fact": 0.999331}, "C_conf": 0.9996}</t>
+        </is>
+      </c>
+      <c r="J99" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K99" s="3" t="n">
+        <v>0.999331</v>
+      </c>
+      <c r="L99" s="3" t="n">
+        <v>0.9996</v>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:22:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>被保險人在投保一年內故意自殺者，可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人在投保一年內故意自殺者，保險公司不負給付身故保險金或喪葬費用保險金的責任。只有在契約訂立或復效之日起滿二年後，因故意自殺致死的情況下，保險公司才負給付責任。
+條文依據：  
+- [第十九條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 除外責任（二） | 第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付 | 第十條 契約的終止（二） | 第三十條 投保年齡的計算及錯誤的處理 | 第十八條 除外責任（一）</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人在投保一年內故意自殺者，保險公司不負給付身故保險金或喪葬費用保險金的責任。只有在契約訂立或復效之日起滿二年後，因故意自殺致死的情況下，保險公司才負給付責任。
+條文依據：  
+- [第十九條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr"/>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "被保險人在投保一年內故意自殺者，可以申請理賠嗎?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.997826, "neutral": 0.001897, "contradiction": 0.000277, "factuality": 0.999723, "C_fact": 0.999723}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J100" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K100" s="3" t="n">
+        <v>0.999723</v>
+      </c>
+      <c r="L100" s="3" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:22:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>申請理賠有什麼時間規定嗎?</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申請理賠的時間規定如下：要保人、被保險人或受益人應於知悉保險事故後十日內通知保險公司，並於通知後儘速檢具所需文件申請保險金。保險公司應於收到完整文件後十五日內給付保險金。如因保險公司可歸責的原因未能在期限內給付，應按年利一分加計利息給付。
+條文依據：  
+- [第二十一條 保險事故的通知與保險金的申請時間]</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>第二十一條 保險事故的通知與保險金的申請時間 | 第六條 第二期以後保險費的交付、寬限期間及契約效力的停止 | 第七條 本契約效力的恢復 | 第三條 契約撤銷權 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申請理賠的時間規定如下：要保人、被保險人或受益人應於知悉保險事故後十日內通知保險公司，並於通知後儘速檢具所需文件申請保險金。保險公司應於收到完整文件後十五日內給付保險金。如因保險公司可歸責的原因未能在期限內給付，應按年利一分加計利息給付。
+條文依據：  
+- [第二十一條 保險事故的通知與保險金的申請時間]</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr"/>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "申請理賠有什麼時間規定嗎?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.998199, "neutral": 0.001674, "contradiction": 0.000127, "factuality": 0.999873, "C_fact": 0.999873}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J101" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K101" s="3" t="n">
+        <v>0.999873</v>
+      </c>
+      <c r="L101" s="3" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:23:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>燒燙傷病房保險金怎麼申領?</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申領燒燙傷病房保險金時，受益人需檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 醫療診斷書或住院證明，且需列明進、出燒燙傷病房的日期。（但要保人或被保險人為醫師時，不得為被保險人出具診斷書或住院證明。）  
+4. 受益人的身分證明。  
+此外，保險公司可基於審核需要，徵詢其他醫師的專業意見，並經受益人同意調閱被保險人的就醫相關資料，相關費用由保險公司負擔。
+條文依據：  
+- [第二十三條 醫療保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>第二十三條 醫療保險金的申領 | 第十三條 加護病房或燒燙傷病房保險金的給付 | payout_items | 第二條 名詞定義 | 第二十一條 保險事故的通知與保險金的申請時間</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申領燒燙傷病房保險金時，受益人需檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 醫療診斷書或住院證明，且需列明進、出燒燙傷病房的日期。（但要保人或被保險人為醫師時，不得為被保險人出具診斷書或住院證明。）  
+4. 受益人的身分證明。  
+此外，保險公司可基於審核需要，徵詢其他醫師的專業意見，並經受益人同意調閱被保險人的就醫相關資料，相關費用由保險公司負擔。
+條文依據：  
+- [第二十三條 醫療保險金的申領]</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr"/>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "燒燙傷病房保險金怎麼申領?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.998243, "neutral": 0.001573, "contradiction": 0.000184, "factuality": 0.999816, "C_fact": 0.999816}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J102" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K102" s="3" t="n">
+        <v>0.999816</v>
+      </c>
+      <c r="L102" s="3" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:23:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>活到99歲怎麼申請祝壽金?</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申請祝壽保險金時，受益人需檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 受益人的身分證明。  
+條文依據：  
+- [第二十四條 祝壽保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>第十五條 祝壽保險金的給付 | 第二十四條 祝壽保險金的申領 | 第五條 保險範圍 | 第十二條至第十三條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | announcement_history</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申請祝壽保險金時，受益人需檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 受益人的身分證明。  
+條文依據：  
+- [第二十四條 祝壽保險金的申領]</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr"/>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "活到99歲怎麼申請祝壽金?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.99803, "neutral": 0.001868, "contradiction": 0.000103, "factuality": 0.999897, "C_fact": 0.999897}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J103" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K103" s="3" t="n">
+        <v>0.999897</v>
+      </c>
+      <c r="L103" s="3" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:23:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>被保人身故怎麼申請理賠</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+受益人申請「身故保險金」或「喪葬費用保險金」時，需檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 被保險人死亡證明書及除戶戶籍謄本。  
+4. 受益人的身分證明。  
+條文依據：  
+- [第二十五條 身故保險金或喪葬費用保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付 | 第十二條至第十三條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | 第二十二條 失蹤處理 | 第二十五條 身故保險金或喪葬費用保險金的申領 | 第十九條 除外責任（二）</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+受益人申請「身故保險金」或「喪葬費用保險金」時，需檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 被保險人死亡證明書及除戶戶籍謄本。  
+4. 受益人的身分證明。  
+條文依據：  
+- [第二十五條 身故保險金或喪葬費用保險金的申領]</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr"/>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "被保人身故怎麼申請理賠", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.996283, "neutral": 0.003565, "contradiction": 0.000152, "factuality": 0.999848, "C_fact": 0.999848}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J104" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K104" s="3" t="n">
+        <v>0.999848</v>
+      </c>
+      <c r="L104" s="3" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:23:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>投保15年後，因手術住院3天，住院日額為2500元，請問可以申請多少理賠?</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 住院日額為2500元的保險條款適用，因被保險人於契約有效期間內因手術住院，符合第十二條規定的住院醫療保險金給付條件。  
+2. 理賠金額計算為：住院醫療保險金日額（2500元） × 增額係數（假設為1，因題目未提供具體增額係數） × 住院日數（3天） = 7500元。  
+3. 手術本身不影響住院醫療保險金的計算，因條文未提及手術為額外影響因素。
+條文依據：  
+- [第十二條 住院醫療保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 住院醫療保險金的給付 | 第十三條 加護病房或燒燙傷病房保險金的給付 | 第二十八條 住院醫療保險金日額之減少 | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | payout_items | 第五條 保險範圍 | 第二條 名詞定義 | 第二十一條 保險事故的通知與保險金的申請時間</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 住院日額為2500元的保險條款適用，因被保險人於契約有效期間內因手術住院，符合第十二條規定的住院醫療保險金給付條件。  
+2. 理賠金額計算為：住院醫療保險金日額（2500元） × 增額係數（假設為1，因題目未提供具體增額係數） × 住院日數（3天） = 7500元。  
+3. 手術本身不影響住院醫療保險金的計算，因條文未提及手術為額外影響因素。
+條文依據：  
+- [第十二條 住院醫療保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr"/>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認住院日額為2500元的保險條款是否適用", "must_have": true, "分數": 1.0}, {"id": "2", "point": "計算住院3天的理賠金額", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認手術是否影響理賠金額的計算", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.973499, "neutral": 0.021883, "contradiction": 0.004618, "factuality": 0.995382, "C_fact": 0.995382}, "C_conf": 0.9972}</t>
+        </is>
+      </c>
+      <c r="J105" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K105" s="3" t="n">
+        <v>0.995382</v>
+      </c>
+      <c r="L105" s="3" t="n">
+        <v>0.9972</v>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:23:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>保障範圍包括哪些項目？</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括：住院手術醫療保險金、門診手術醫療保險金、特定處置保險金、意外創傷縫合處置保險金、意外住院手術醫療保險金、祝壽保險金、所繳保險費的退還、身故保險金或喪葬費用保險金。
+條文依據：  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>payout_items | 第五條 保險範圍 | summary | 第四條 名詞定義 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括：住院手術醫療保險金、門診手術醫療保險金、特定處置保險金、意外創傷縫合處置保險金、意外住院手術醫療保險金、祝壽保險金、所繳保險費的退還、身故保險金或喪葬費用保險金。
+條文依據：  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr"/>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "保障範圍包括哪些項目？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.998072, "neutral": 0.001746, "contradiction": 0.000182, "factuality": 0.999818, "C_fact": 0.999818}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J106" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K106" s="3" t="n">
+        <v>0.999818</v>
+      </c>
+      <c r="L106" s="3" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:24:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>保險金額是否有上限?</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+有，保險金額的給付總額上限為保險單上所記載「保險金額」的一千五百倍，且不包含其他附約、附加條款或批註條款。
+條文依據：  
+- [第十六條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 醫療保險金給付總額之上限 | 第三十條 保險金額之減少 | 第五條 保險範圍 | 第十九條 健康促進保險費折減 | 第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+有，保險金額的給付總額上限為保險單上所記載「保險金額」的一千五百倍，且不包含其他附約、附加條款或批註條款。
+條文依據：  
+- [第十六條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr"/>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "保險金額是否有上限?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.997606, "neutral": 0.00227, "contradiction": 0.000124, "factuality": 0.999876, "C_fact": 0.999876}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J107" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K107" s="3" t="n">
+        <v>0.999876</v>
+      </c>
+      <c r="L107" s="3" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:24:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>投保後5天發生手術，是否可以申請理賠?</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款，被保險人於保險契約有效期間內因疾病或傷害接受手術，符合附表一所列手術項目且已實際接受手術者，可申請理賠。但若手術屬於除外責任條款所列情形，則不在理賠範圍內。此外，疾病的理賠需符合等待期間規定，即自契約生效日起持續有效第三十一日後發生的疾病才可申請理賠，除非屬於特定疾病不適用等待期間的情形。  
+條款依據：  
+[第五條 保險範圍]  
+[第十一條 住院手術醫療保險金]  
+[第四條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第十一條 住院手術醫療保險金 | 第二十條 除外責任（一） | 第十二條 門診手術醫療保險金 | 第十三條 意外住院手術醫療保險金 | 第二十三條 保險事故的通知與保險金的申請時間 | 第四條 名詞定義 | 第十五條 意外創傷縫合處置保險金 | 附表三：意外創傷縫合處置項目及給付倍數表 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+找不到相關內容  
+條文依據：  
+找不到相關內容</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款，被保險人於保險契約有效期間內因疾病或傷害接受手術，符合附表一所列手術項目且已實際接受手術者，可申請理賠。但若手術屬於除外責任條款所列情形，則不在理賠範圍內。此外，疾病的理賠需符合等待期間規定，即自契約生效日起持續有效第三十一日後發生的疾病才可申請理賠，除非屬於特定疾病不適用等待期間的情形。  
+條款依據：  
+[第五條 保險範圍]  
+[第十一條 住院手術醫療保險金]  
+[第四條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr"/>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "投保後5天發生手術，是否可以申請理賠?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.597166, "neutral": 0.394456, "contradiction": 0.008378, "factuality": 0.991622, "C_fact": 0.991622}, "C_conf": 0.995}</t>
+        </is>
+      </c>
+      <c r="J108" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K108" s="3" t="n">
+        <v>0.991622</v>
+      </c>
+      <c r="L108" s="3" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:24:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>住院手術醫療保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院手術醫療保險金的給付規定如下：  
+1. 被保險人需於保險契約有效期間內，因疾病或傷害經醫師診斷必須住院接受附表一所列的手術治療，且已實際接受手術。  
+2. 給付金額計算方式為：保險單上記載的「保險金額」乘以手術日當年度的「增額係數」，再乘以手術給付倍數。  
+3. 若同一次手術中於同一手術位置接受兩項以上手術項目，僅給付手術給付倍數最高的手術項目。  
+4. 未載明於附表一的手術項目，將與被保險人協議比照附表內程度相當的手術項目，決定給付倍數。  
+5. 以下情形不在給付範圍內：  
+   - 屬於除外責任條款規定的情形。  
+   - 不屬於全民健康保險醫療服務給付項目及支付標準第二部第二章第七節或第三部第三章第四節第三項所列舉的手術。  
+條文依據：  
+- [第十一條 住院手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 住院手術醫療保險金 | 第十三條 意外住院手術醫療保險金 | 第十二條 門診手術醫療保險金 | payout_items | 第二十條 除外責任（一） | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院手術醫療保險金的給付規定如下：  
+1. 被保險人需於保險契約有效期間內，因疾病或傷害經醫師診斷必須住院接受附表一所列的手術治療，且已實際接受手術。  
+2. 給付金額計算方式為：保險單上記載的「保險金額」乘以手術日當年度的「增額係數」，再乘以手術給付倍數。  
+3. 若同一次手術中於同一手術位置接受兩項以上手術項目，僅給付手術給付倍數最高的手術項目。  
+4. 未載明於附表一的手術項目，將與被保險人協議比照附表內程度相當的手術項目，決定給付倍數。  
+5. 以下情形不在給付範圍內：  
+   - 屬於除外責任條款規定的情形。  
+   - 不屬於全民健康保險醫療服務給付項目及支付標準第二部第二章第七節或第三部第三章第四節第三項所列舉的手術。  
+條文依據：  
+- [第十一條 住院手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr"/>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "住院手術醫療保險金的給付規定", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.994376, "neutral": 0.005055, "contradiction": 0.000569, "factuality": 0.999431, "C_fact": 0.999431}, "C_conf": 0.9997}</t>
+        </is>
+      </c>
+      <c r="J109" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K109" s="3" t="n">
+        <v>0.999431</v>
+      </c>
+      <c r="L109" s="3" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:24:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>門診手術醫療保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+門診手術醫療保險金的給付規定如下：  
+1. 被保險人需於本契約有效期間內，因疾病或傷害經醫師診斷必須於醫院或診所門診接受附表一所列的手術治療，且已實際接受手術。  
+2. 給付金額計算方式為：保險單上所記載的「保險金額」乘以手術日當年度的「增額係數」，再乘以手術給付倍數。  
+3. 同一次手術中，若於同一手術位置接受兩項以上手術項目，僅給付手術給付倍數最高的手術項目。  
+4. 同一保險單年度內，門診手術醫療保險金的給付以十次為限。  
+5. 若手術項目未載明於附表一，本公司將與被保險人協議比照附表內的手術項目決定給付倍數。  
+6. 以下情形不負給付責任：  
+   - 依據本契約除外責任條款的規定不在給付範圍內。  
+   - 不屬於全民健康保險醫療服務給付項目及支付標準第二部第二章第七節或第三部第三章第四節第三項所列舉的手術。  
+條文依據：  
+- [第十二條 門診手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 門診手術醫療保險金 | 第十一條 住院手術醫療保險金 | payout_items | 第十三條 意外住院手術醫療保險金 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+門診手術醫療保險金的給付規定如下：  
+1. 被保險人需於本契約有效期間內，因疾病或傷害經醫師診斷必須於醫院或診所門診接受附表一所列的手術治療，且已實際接受手術。  
+2. 給付金額計算方式為：保險單上所記載的「保險金額」乘以手術日當年度的「增額係數」，再乘以手術給付倍數。  
+3. 同一次手術中，若於同一手術位置接受兩項以上手術項目，僅給付手術給付倍數最高的手術項目。  
+4. 同一保險單年度內，門診手術醫療保險金的給付以十次為限。  
+5. 若手術項目未載明於附表一，本公司將與被保險人協議比照附表內的手術項目決定給付倍數。  
+6. 以下情形不負給付責任：  
+   - 依據本契約除外責任條款的規定不在給付範圍內。  
+   - 不屬於全民健康保險醫療服務給付項目及支付標準第二部第二章第七節或第三部第三章第四節第三項所列舉的手術。  
+條文依據：  
+- [第十二條 門診手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr"/>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "門診手術醫療保險金的給付規定", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.967156, "neutral": 0.032236, "contradiction": 0.000608, "factuality": 0.999392, "C_fact": 0.999392}, "C_conf": 0.9996}</t>
+        </is>
+      </c>
+      <c r="J110" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K110" s="3" t="n">
+        <v>0.9993919999999999</v>
+      </c>
+      <c r="L110" s="3" t="n">
+        <v>0.9996</v>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:24:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>意外住院手術醫療保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外住院手術醫療保險金的給付規定如下：  
+1. 被保險人需於本契約有效期間內，且保險年齡未滿七十歲。  
+2. 因傷害經醫師診斷在住院期間必須接受手術治療且已接受手術者，保險公司將按保險單所記載的「保險金額」的三倍，乘以手術日當年度的「增額係數」，給付「意外住院手術醫療保險金」。  
+3. 若同一次手術中於同一手術位置接受兩項以上手術項目，僅給付一次「意外住院手術醫療保險金」。  
+條文依據：  
+- [第十三條 意外住院手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 意外住院手術醫療保險金 | 第十一條 住院手術醫療保險金 | 第十五條 意外創傷縫合處置保險金 | 第二十條 除外責任（一） | 第十二條 門診手術醫療保險金 | 附表三：意外創傷縫合處置項目及給付倍數表 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外住院手術醫療保險金的給付規定如下：  
+1. 被保險人需於本契約有效期間內，且保險年齡未滿七十歲。  
+2. 因傷害經醫師診斷在住院期間必須接受手術治療且已接受手術者，保險公司將按保險單所記載的「保險金額」的三倍，乘以手術日當年度的「增額係數」，給付「意外住院手術醫療保險金」。  
+3. 若同一次手術中於同一手術位置接受兩項以上手術項目，僅給付一次「意外住院手術醫療保險金」。  
+條文依據：  
+- [第十三條 意外住院手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr"/>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "意外住院手術醫療保險金的給付規定", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.996891, "neutral": 0.002776, "contradiction": 0.000333, "factuality": 0.999667, "C_fact": 0.999667}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J111" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K111" s="3" t="n">
+        <v>0.999667</v>
+      </c>
+      <c r="L111" s="3" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:25:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>特定處置保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+特定處置保險金的給付規定如下：  
+1. 被保險人需於保險契約有效期間內，因疾病或傷害經醫師診斷必須接受附表二所列的特定處置治療，且實際完成處置後，保險公司才會給付特定處置保險金。  
+2. 給付金額計算方式為：保險單上記載的「保險金額」× 特定處置日當年度的「增額係數」× 特定處置給付倍數。  
+3. 同一次處置治療中，若於同一治療位置接受兩項以上特定處置項目，僅給付特定處置給付倍數最高的項目。  
+4. 若被保險人接受的處置未列於附表二，保險公司不負給付責任。  
+5. 同一保險單年度內，特定處置保險金的給付次數以十次為限。
+條文依據：  
+- [第十四條 特定處置保險金]</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 特定處置保險金 | 第十五條 意外創傷縫合處置保險金 | 附表二：特定處置項目及給付倍數表 | 第五條 保險範圍 | 附表三：意外創傷縫合處置項目及給付倍數表</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+特定處置保險金的給付規定如下：  
+1. 被保險人需於保險契約有效期間內，因疾病或傷害經醫師診斷必須接受附表二所列的特定處置治療，且實際完成處置後，保險公司才會給付特定處置保險金。  
+2. 給付金額計算方式為：保險單上記載的「保險金額」× 特定處置日當年度的「增額係數」× 特定處置給付倍數。  
+3. 同一次處置治療中，若於同一治療位置接受兩項以上特定處置項目，僅給付特定處置給付倍數最高的項目。  
+4. 若被保險人接受的處置未列於附表二，保險公司不負給付責任。  
+5. 同一保險單年度內，特定處置保險金的給付次數以十次為限。
+條文依據：  
+- [第十四條 特定處置保險金]</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr"/>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "特定處置保險金的給付規定", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.995616, "neutral": 0.003974, "contradiction": 0.000409, "factuality": 0.999591, "C_fact": 0.999591}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J112" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K112" s="3" t="n">
+        <v>0.999591</v>
+      </c>
+      <c r="L112" s="3" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:25:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>意外創傷縫合處置保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外創傷縫合處置保險金的給付規定如下：  
+1. 被保險人於保險有效期間內，因意外傷害事故在醫院或診所接受附表三所列的意外創傷縫合處置治療者，本公司將依保險單所載「保險金額」，乘以當年度「增額係數」及「意外創傷縫合處置給付倍數」計算給付金額。  
+2. 同一次意外傷害事故中，本公司僅針對傷口最大者給付一次保險金。  
+3. 若被保險人因同一意外傷害事故已申領「住院手術醫療保險金」或「門診手術醫療保險金」，則不再給付意外創傷縫合處置保險金。
+條文依據：  
+- [第十五條 意外創傷縫合處置保險金]</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>第十五條 意外創傷縫合處置保險金 | 附表三：意外創傷縫合處置項目及給付倍數表 | 第十四條 特定處置保險金 | 第二十條 除外責任（一） | 第十三條 意外住院手術醫療保險金 | 附表二：特定處置項目及給付倍數表</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外創傷縫合處置保險金的給付規定如下：  
+1. 被保險人於保險有效期間內，因意外傷害事故在醫院或診所接受附表三所列的意外創傷縫合處置治療者，本公司將依保險單所載「保險金額」，乘以當年度「增額係數」及「意外創傷縫合處置給付倍數」計算給付金額。  
+2. 同一次意外傷害事故中，本公司僅針對傷口最大者給付一次保險金。  
+3. 若被保險人因同一意外傷害事故已申領「住院手術醫療保險金」或「門診手術醫療保險金」，則不再給付意外創傷縫合處置保險金。
+條文依據：  
+- [第十五條 意外創傷縫合處置保險金]</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr"/>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "意外創傷縫合處置保險金的給付規定", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.995892, "neutral": 0.003827, "contradiction": 0.000281, "factuality": 0.999719, "C_fact": 0.999719}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J113" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K113" s="3" t="n">
+        <v>0.999719</v>
+      </c>
+      <c r="L113" s="3" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:25:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>醫療保險金給付總額之上限</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+醫療保險金給付總額之上限為保險單上所記載「保險金額」的一千五百倍，此上限僅適用於本契約有效期間內，且不包含其他附約、附加條款或批註條款的金額。
+條文依據：  
+- [第十六條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 醫療保險金給付總額之上限 | 第十二條 門診手術醫療保險金 | 第五條 保險範圍 | 第十一條 住院手術醫療保險金 | 第十三條 意外住院手術醫療保險金 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+醫療保險金給付總額之上限為保險單上所記載「保險金額」的一千五百倍，此上限僅適用於本契約有效期間內，且不包含其他附約、附加條款或批註條款的金額。
+條文依據：  
+- [第十六條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr"/>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "醫療保險金給付總額之上限", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.996204, "neutral": 0.003618, "contradiction": 0.000178, "factuality": 0.999822, "C_fact": 0.999822}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J114" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K114" s="3" t="n">
+        <v>0.999822</v>
+      </c>
+      <c r="L114" s="3" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:25:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>祝壽保險金的領取規定為何?</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+祝壽保險金的領取規定如下：  
+1. 被保險人需於本契約有效期間內，且保險年齡到達九十九歲之保險單週年日仍生存，方可領取祝壽保險金。  
+2. 受益人申領祝壽保險金時，需檢具以下文件：  
+   - 保險單或其謄本  
+   - 保險金申請書  
+   - 受益人的身分證明  
+條文依據：  
+- [第十七條 祝壽保險金]  
+- [第二十六條 祝壽保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>第十七條 祝壽保險金 | 第二十六條 祝壽保險金的申領 | 第十一條至第十五條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | 第二十三條 保險事故的通知與保險金的申請時間 | 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+祝壽保險金的領取規定如下：  
+1. 被保險人需於本契約有效期間內，且保險年齡到達九十九歲之保險單週年日仍生存，方可領取祝壽保險金。  
+2. 受益人申領祝壽保險金時，需檢具以下文件：  
+   - 保險單或其謄本  
+   - 保險金申請書  
+   - 受益人的身分證明  
+條文依據：  
+- [第十七條 祝壽保險金]  
+- [第二十六條 祝壽保險金的申領]</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr"/>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "祝壽保險金的領取規定為何?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.998692, "neutral": 0.001171, "contradiction": 0.000137, "factuality": 0.999863, "C_fact": 0.999863}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J115" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K115" s="3" t="n">
+        <v>0.9998629999999999</v>
+      </c>
+      <c r="L115" s="3" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:25:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>身故時領取保險金有什麼規則?</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+身故時領取保險金的規則如下：  
+1. **一般規則**：被保險人於本契約有效期間內身故，本公司按「當年度保險金額」給付「身故保險金」。  
+2. **未滿十五足歲規則**：若被保險人於本契約有效期間且實際年齡未滿十五足歲身故，本公司僅退還「所繳保險費」，不適用一般規則。  
+3. **受監護宣告者**：若被保險人於訂立契約時為受監護宣告尚未撤銷者，其身故保險金變更為喪葬費用保險金，且金額不得超過遺產稅喪葬費扣除額之半數，超過部分不負給付責任，並退還超過部分的已繳保險費。  
+4. **除外責任**：若身故原因屬於要保人故意致死、被保險人故意自殺（契約訂立或復效後兩年內）、犯罪處死、拒捕或越獄致死等情形，本公司不負給付責任。未滿十五足歲者因上述原因身故，僅退還所繳保險費。  
+5. **申領文件**：受益人申領保險金時，需提供保險單、死亡證明書及除戶戶籍謄本、保險金申請書及受益人身分證明等文件。
+條文依據：  
+- [第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金]  
+- [第二十七條 身故保險金或喪葬費用保險金的申領]  
+- [第二十一條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金 | 第二十七條 身故保險金或喪葬費用保險金的申領 | 第十一條至第十五條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | 第二十一條 除外責任（二） | 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+身故時領取保險金的規則如下：  
+1. **一般規則**：被保險人於本契約有效期間內身故，本公司按「當年度保險金額」給付「身故保險金」。  
+2. **未滿十五足歲規則**：若被保險人於本契約有效期間且實際年齡未滿十五足歲身故，本公司僅退還「所繳保險費」，不適用一般規則。  
+3. **受監護宣告者**：若被保險人於訂立契約時為受監護宣告尚未撤銷者，其身故保險金變更為喪葬費用保險金，且金額不得超過遺產稅喪葬費扣除額之半數，超過部分不負給付責任，並退還超過部分的已繳保險費。  
+4. **除外責任**：若身故原因屬於要保人故意致死、被保險人故意自殺（契約訂立或復效後兩年內）、犯罪處死、拒捕或越獄致死等情形，本公司不負給付責任。未滿十五足歲者因上述原因身故，僅退還所繳保險費。  
+5. **申領文件**：受益人申領保險金時，需提供保險單、死亡證明書及除戶戶籍謄本、保險金申請書及受益人身分證明等文件。
+條文依據：  
+- [第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金]  
+- [第二十七條 身故保險金或喪葬費用保險金的申領]  
+- [第二十一條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr"/>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "身故時領取保險金有什麼規則?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.756658, "neutral": 0.233401, "contradiction": 0.00994, "factuality": 0.99006, "C_fact": 0.99006}, "C_conf": 0.994}</t>
+        </is>
+      </c>
+      <c r="J116" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K116" s="3" t="n">
+        <v>0.9900600000000001</v>
+      </c>
+      <c r="L116" s="3" t="n">
+        <v>0.994</v>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:25:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>什麼情況下可以保費折減?</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人年齡滿20歲（含）以上，並使用保險公司指定的程式加入健康計劃，且於「指定日期」的會員等級符合進階會員或菁英會員（或更高等級）標準之一者，可享次一保險單年度的保費折減。折減比例為進階會員2%，菁英會員或更高等級3%。但豁免或復效的保險費不適用此折減規定。此外，被保險人需完成程式註冊並授權保險公司取得健康相關電子紀錄，保險公司將依此計算會員等級。
+條文依據：  
+- [第十九條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 健康促進保險費折減 | 第三十條 保險金額之減少 | 第二十條 除外責任（一） | 第三十一條 投保年齡的計算及錯誤的處理 | 第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人年齡滿20歲（含）以上，並使用保險公司指定的程式加入健康計劃，且於「指定日期」的會員等級符合進階會員或菁英會員（或更高等級）標準之一者，可享次一保險單年度的保費折減。折減比例為進階會員2%，菁英會員或更高等級3%。但豁免或復效的保險費不適用此折減規定。此外，被保險人需完成程式註冊並授權保險公司取得健康相關電子紀錄，保險公司將依此計算會員等級。
+條文依據：  
+- [第十九條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr"/>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "什麼情況下可以保費折減?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.997054, "neutral": 0.002743, "contradiction": 0.000203, "factuality": 0.999797, "C_fact": 0.999797}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J117" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K117" s="3" t="n">
+        <v>0.999797</v>
+      </c>
+      <c r="L117" s="3" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:26:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>角膜切除術是否可以申請理賠?</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+角膜切除術可以申請理賠，其對應的給付倍數為5倍。
+條文依據：  
+- [附表一：手術項目與給付倍數 - 1305 角膜切除術]</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+角膜切除術可以申請理賠，其對應的給付倍數為5倍。
+條文依據：  
+- [附表一：手術項目與給付倍數 - 1305 角膜切除術]</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr"/>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "角膜切除術是否可以申請理賠?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.053763, "neutral": 0.940966, "contradiction": 0.005271, "factuality": 0.994729, "C_fact": 0.994729}, "C_conf": 0.9968}</t>
+        </is>
+      </c>
+      <c r="J118" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K118" s="3" t="n">
+        <v>0.994729</v>
+      </c>
+      <c r="L118" s="3" t="n">
+        <v>0.9968</v>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:26:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>白內障手術是否可以申請理賠?</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+白內障手術是否可以申請理賠需視以下條件而定：  
+1. 若白內障手術屬於附表一所列的手術項目，則可依據手術給付倍數申請理賠。  
+2. 若手術項目未載明於附表一，保險公司將與被保險人協議比照附表內程度相當的手術項目，決定給付倍數。  
+3. 若手術屬於除外責任條款中所列的情形（如美容手術或非全民健康保險醫療服務給付項目等），則不在理賠範圍內。
+條文依據：  
+- [第十二條 門診手術醫療保險金]  
+- [第十一條 住院手術醫療保險金]  
+- [第二十條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 門診手術醫療保險金 | 第二十條 除外責任（一） | 附表一：手術項目與給付倍數 | payout_items | 第十一條 住院手術醫療保險金</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+白內障手術是否可以申請理賠需視以下條件而定：  
+1. 若白內障手術屬於附表一所列的手術項目，則可依據手術給付倍數申請理賠。  
+2. 若手術項目未載明於附表一，保險公司將與被保險人協議比照附表內程度相當的手術項目，決定給付倍數。  
+3. 若手術屬於除外責任條款中所列的情形（如美容手術或非全民健康保險醫療服務給付項目等），則不在理賠範圍內。
+條文依據：  
+- [第十二條 門診手術醫療保險金]  
+- [第十一條 住院手術醫療保險金]  
+- [第二十條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr"/>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "白內障手術是否可以申請理賠?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.006905, "neutral": 0.991751, "contradiction": 0.001344, "factuality": 0.998656, "C_fact": 0.998656}, "C_conf": 0.9992}</t>
+        </is>
+      </c>
+      <c r="J119" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K119" s="3" t="n">
+        <v>0.998656</v>
+      </c>
+      <c r="L119" s="3" t="n">
+        <v>0.9992</v>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:26:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>保障範圍包括哪些項目？</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括：意外事故身故保險金或喪葬費用保險金、意外事故失能保險金、每月生活照護保險金、重大燒燙傷保險金、意外骨折保險金、傷害醫療日額保險金，以及意外創傷縫合處置保險金。
+條文依據：  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>payout_items | 第五條 保險範圍 | 第十五條 每月生活照護保險金的給付 | 第三十條 不保事項 | 附表二：失能程度與保險金給付表</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括：意外事故身故保險金或喪葬費用保險金、意外事故失能保險金、每月生活照護保險金、重大燒燙傷保險金、意外骨折保險金、傷害醫療日額保險金，以及意外創傷縫合處置保險金。
+條文依據：  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr"/>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "保障範圍包括哪些項目？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.9981, "neutral": 0.001737, "contradiction": 0.000164, "factuality": 0.999836, "C_fact": 0.999836}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J120" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K120" s="3" t="n">
+        <v>0.9998359999999999</v>
+      </c>
+      <c r="L120" s="3" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:26:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>發生意外事故身故，理賠內容為何?</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外事故身故的理賠內容如下：  
+1. 若被保險人於意外傷害事故發生之日起 180 日內身故，本公司依意外傷害事故種類給付以下金額：  
+   - 一般意外傷害事故：「傷害醫療保險金日額」的 500 倍。  
+   - 特定意外傷害事故：「傷害醫療保險金日額」的 1000 倍。  
+2. 若被保險人於意外傷害事故發生後超過 180 日身故，但受益人能證明身故與該事故具有因果關係，本公司仍依上述金額給付。  
+3. 若被保險人為受監護宣告尚未撤銷者，其理賠內容變更為喪葬費用保險金，且喪葬費用保險金額不得超過遺產稅喪葬費扣除額之半數，超過部分不負給付責任，但已繳保險費將無息退還。  
+條文依據：  
+- [第十二條 意外事故身故保險金或喪葬費用保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 意外事故身故保險金或喪葬費用保險金的給付 | 第十四條 保險給付的限制 | payout_items | 第十一條 契約的終止（二） | 第二十一條 失蹤處理</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外事故身故的理賠內容如下：  
+1. 若被保險人於意外傷害事故發生之日起 180 日內身故，本公司依意外傷害事故種類給付以下金額：  
+   - 一般意外傷害事故：「傷害醫療保險金日額」的 500 倍。  
+   - 特定意外傷害事故：「傷害醫療保險金日額」的 1000 倍。  
+2. 若被保險人於意外傷害事故發生後超過 180 日身故，但受益人能證明身故與該事故具有因果關係，本公司仍依上述金額給付。  
+3. 若被保險人為受監護宣告尚未撤銷者，其理賠內容變更為喪葬費用保險金，且喪葬費用保險金額不得超過遺產稅喪葬費扣除額之半數，超過部分不負給付責任，但已繳保險費將無息退還。  
+條文依據：  
+- [第十二條 意外事故身故保險金或喪葬費用保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr"/>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "發生意外事故身故，理賠內容為何?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.996779, "neutral": 0.002857, "contradiction": 0.000364, "factuality": 0.999636, "C_fact": 0.999636}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J121" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K121" s="3" t="n">
+        <v>0.999636</v>
+      </c>
+      <c r="L121" s="3" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:26:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>意外事故失能保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外事故失能保險金的給付條件如下：  
+1. 被保險人於契約有效期間內遭受「意外傷害事故」，並於事故發生後180日內致成附表二所列失能程度之一者，本公司依事故種類及失能程度，按以下方式計算給付金額：  
+   - 一般意外傷害事故：「傷害醫療保險金日額」的500倍乘以附表二給付比例。  
+   - 特定意外傷害事故：「傷害醫療保險金日額」的1000倍乘以附表二給付比例。  
+2. 若超過180日致成失能，但能證明失能與事故具有因果關係者，仍可申請給付，不受180日限制。  
+3. 同一事故導致多項失能時，僅給付同一手或同一足中較嚴重項目的失能保險金，且總金額以事故種類的上限為限：  
+   - 一般意外傷害事故：「傷害醫療保險金日額」的500倍。  
+   - 特定意外傷害事故：「傷害醫療保險金日額」的1000倍。  
+4. 不同事故導致的失能，累計給付金額最高以「傷害醫療保險金日額」的1200倍為限。  
+條文依據：  
+- [第十三條 意外事故失能保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 意外事故失能保險金的給付 | 第十五條 每月生活照護保險金的給付 | 第十四條 保險給付的限制 | 第十二條 意外事故身故保險金或喪葬費用保險金的給付 | 第二十三條 意外事故失能保險金的申領 | 附表二：失能程度與保險金給付表</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外事故失能保險金的給付條件如下：  
+1. 被保險人於契約有效期間內遭受「意外傷害事故」，並於事故發生後180日內致成附表二所列失能程度之一者，本公司依事故種類及失能程度，按以下方式計算給付金額：  
+   - 一般意外傷害事故：「傷害醫療保險金日額」的500倍乘以附表二給付比例。  
+   - 特定意外傷害事故：「傷害醫療保險金日額」的1000倍乘以附表二給付比例。  
+2. 若超過180日致成失能，但能證明失能與事故具有因果關係者，仍可申請給付，不受180日限制。  
+3. 同一事故導致多項失能時，僅給付同一手或同一足中較嚴重項目的失能保險金，且總金額以事故種類的上限為限：  
+   - 一般意外傷害事故：「傷害醫療保險金日額」的500倍。  
+   - 特定意外傷害事故：「傷害醫療保險金日額」的1000倍。  
+4. 不同事故導致的失能，累計給付金額最高以「傷害醫療保險金日額」的1200倍為限。  
+條文依據：  
+- [第十三條 意外事故失能保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr"/>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "意外事故失能保險金的給付為何?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.32928, "neutral": 0.636318, "contradiction": 0.034402, "factuality": 0.965598, "C_fact": 0.965598}, "C_conf": 0.9792}</t>
+        </is>
+      </c>
+      <c r="J122" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K122" s="3" t="n">
+        <v>0.965598</v>
+      </c>
+      <c r="L122" s="3" t="n">
+        <v>0.9792</v>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:27:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>每月生活照護保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+每月生活照護保險金的給付條件如下：  
+1. 被保險人於保險契約有效期間內因「意外傷害事故」，自事故發生之日起180日內，致成附表二所列第1級至第6級失能程度之一時，自失能診斷確定當日起，按「傷害醫療保險金日額」的20倍乘以附表二給付比例所得之金額，按月給付，最多給付12個月。  
+2. 若於失能的前四個「失能診斷確定週年日」，契約仍有效且被保險人仍生存，則自各該週年日起，按相同計算方式再給付，最多給付12個月。  
+3. 若被保險人自事故發生之日起超過180日才致成附表二所列第1級至第6級失能程度之一，但能證明失能與事故具有因果關係，仍可依上述規定給付。  
+4. 同一事故若致成多項第1級至第6級失能，僅給付一項較嚴重失能的保險金，且最高以「傷害醫療保險金日額」的20倍為限。  
+5. 若失能合併以前的失能，按較嚴重項目給付，但以前的失能視同已給付，應扣除之。  
+條文依據：  
+- [第十五條 每月生活照護保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>第二十四條 每月生活照護保險金的申領 | 第十五條 每月生活照護保險金的給付 | payout_items | 第十八條 傷害醫療日額保險金的給付 | 第五條 保險範圍 | 附表二：失能程度與保險金給付表 | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+每月生活照護保險金的給付條件如下：  
+1. 被保險人於保險契約有效期間內因「意外傷害事故」，自事故發生之日起180日內，致成附表二所列第1級至第6級失能程度之一時，自失能診斷確定當日起，按「傷害醫療保險金日額」的20倍乘以附表二給付比例所得之金額，按月給付，最多給付12個月。  
+2. 若於失能的前四個「失能診斷確定週年日」，契約仍有效且被保險人仍生存，則自各該週年日起，按相同計算方式再給付，最多給付12個月。  
+3. 若被保險人自事故發生之日起超過180日才致成附表二所列第1級至第6級失能程度之一，但能證明失能與事故具有因果關係，仍可依上述規定給付。  
+4. 同一事故若致成多項第1級至第6級失能，僅給付一項較嚴重失能的保險金，且最高以「傷害醫療保險金日額」的20倍為限。  
+5. 若失能合併以前的失能，按較嚴重項目給付，但以前的失能視同已給付，應扣除之。  
+條文依據：  
+- [第十五條 每月生活照護保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr"/>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "每月生活照護保險金的給付為何?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.050297, "neutral": 0.943948, "contradiction": 0.005755, "factuality": 0.994245, "C_fact": 0.994245}, "C_conf": 0.9965}</t>
+        </is>
+      </c>
+      <c r="J123" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K123" s="3" t="n">
+        <v>0.994245</v>
+      </c>
+      <c r="L123" s="3" t="n">
+        <v>0.9965000000000001</v>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:27:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>重大燒燙傷保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+重大燒燙傷保險金的給付條件為：被保險人於保險契約有效期間內因「意外傷害事故」導致燒燙傷，且經診斷符合「重大燒燙傷」的定義時，本公司將按「傷害醫療保險金日額」的二百五十倍給付「重大燒燙傷保險金」。該保險金的給付以一次為限。
+條文依據：  
+- [第十六條 重大燒燙傷保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 重大燒燙傷保險金的給付 | 第二十五條 重大燒燙傷保險金的申領 | 第五條 保險範圍 | payout_items | 第二十九條 除外責任（原因）</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+重大燒燙傷保險金的給付條件為：被保險人於保險契約有效期間內因「意外傷害事故」導致燒燙傷，且經診斷符合「重大燒燙傷」的定義時，本公司將按「傷害醫療保險金日額」的二百五十倍給付「重大燒燙傷保險金」。該保險金的給付以一次為限。
+條文依據：  
+- [第十六條 重大燒燙傷保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr"/>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "重大燒燙傷保險金的給付為何?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.997013, "neutral": 0.002858, "contradiction": 0.000129, "factuality": 0.999871, "C_fact": 0.999871}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J124" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K124" s="3" t="n">
+        <v>0.999871</v>
+      </c>
+      <c r="L124" s="3" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:27:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>意外骨折保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外骨折保險金的給付條件如下：  
+1. 被保險人於保險契約有效期間內遭受「意外傷害事故」，並於事故發生後180日內經合格醫院或診所診斷為附表三骨折別表所列骨折項目之一（含不完全骨折及骨骼龜裂），本公司按「傷害醫療保險金日額」的二倍給付意外骨折保險金。  
+2. 若超過180日診斷確定骨折，受益人需證明骨折與該意外傷害事故具有因果關係，仍可依上述規定給付。  
+3. 同一意外傷害事故僅給付一次意外骨折保險金。  
+4. 若骨折不屬於附表三骨折別表所列項目，需由本公司與被保險人協議核付；但若骨折為骨折別表內明訂不給付之部位，則不負給付責任。
+條文依據：  
+- [第十七條 意外骨折保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>第十七條 意外骨折保險金的給付 | 第十八條 傷害醫療日額保險金的給付 | 第二十六條 意外骨折保險金的申領 | 第十三條 意外事故失能保險金的給付 | 第十九條 意外創傷縫合處置保險金的給付 | 附表二：失能程度與保險金給付表 | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外骨折保險金的給付條件如下：  
+1. 被保險人於保險契約有效期間內遭受「意外傷害事故」，並於事故發生後180日內經合格醫院或診所診斷為附表三骨折別表所列骨折項目之一（含不完全骨折及骨骼龜裂），本公司按「傷害醫療保險金日額」的二倍給付意外骨折保險金。  
+2. 若超過180日診斷確定骨折，受益人需證明骨折與該意外傷害事故具有因果關係，仍可依上述規定給付。  
+3. 同一意外傷害事故僅給付一次意外骨折保險金。  
+4. 若骨折不屬於附表三骨折別表所列項目，需由本公司與被保險人協議核付；但若骨折為骨折別表內明訂不給付之部位，則不負給付責任。
+條文依據：  
+- [第十七條 意外骨折保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr"/>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "意外骨折保險金的給付為何?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.994719, "neutral": 0.004902, "contradiction": 0.000378, "factuality": 0.999622, "C_fact": 0.999622}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J125" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K125" s="3" t="n">
+        <v>0.999622</v>
+      </c>
+      <c r="L125" s="3" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:27:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>傷害醫療日額保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+傷害醫療日額保險金的給付條件如下：  
+1. 被保險人於保險契約有效期間內遭受「意外傷害事故」，並於事故發生後一百八十日內在「醫院」接受住院治療者，本公司按「傷害醫療保險金日額」乘以實際住院日數給付，但每次事故最高給付日數為九十日。  
+2. 若治療超過一百八十日，且受益人能證明治療與該意外傷害事故具有因果關係者，本公司仍依上述規定給付，不受一百八十日限制。  
+3. 若因意外事故骨折但未住院，或住院日數未達附表三骨折別表所訂日數，則按骨折別表所訂日數乘以「傷害醫療保險金日額」的二分之一給付，合計給付日數以骨折別表所訂日數為上限。  
+4. 骨折類型的給付：  
+   - 完全骨折按骨折別表日數給付。  
+   - 不完全骨折按完全骨折日數的二分之一給付。  
+   - 骨骼龜裂按完全骨折日數的四分之一給付。  
+5. 同時發生多項骨折時，僅給付一項較高等級的保險金。
+條文依據：  
+- [第十八條 傷害醫療日額保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 傷害醫療日額保險金的給付 | 第二十七條 傷害醫療日額保險金的申領 | 第十五條 每月生活照護保險金的給付 | 第三十四條 傷害醫療保險金日額之減少 | 第十九條 意外創傷縫合處置保險金的給付 | 附表二：失能程度與保險金給付表 | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+傷害醫療日額保險金的給付條件如下：  
+1. 被保險人於保險契約有效期間內遭受「意外傷害事故」，並於事故發生後一百八十日內在「醫院」接受住院治療者，本公司按「傷害醫療保險金日額」乘以實際住院日數給付，但每次事故最高給付日數為九十日。  
+2. 若治療超過一百八十日，且受益人能證明治療與該意外傷害事故具有因果關係者，本公司仍依上述規定給付，不受一百八十日限制。  
+3. 若因意外事故骨折但未住院，或住院日數未達附表三骨折別表所訂日數，則按骨折別表所訂日數乘以「傷害醫療保險金日額」的二分之一給付，合計給付日數以骨折別表所訂日數為上限。  
+4. 骨折類型的給付：  
+   - 完全骨折按骨折別表日數給付。  
+   - 不完全骨折按完全骨折日數的二分之一給付。  
+   - 骨骼龜裂按完全骨折日數的四分之一給付。  
+5. 同時發生多項骨折時，僅給付一項較高等級的保險金。
+條文依據：  
+- [第十八條 傷害醫療日額保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr"/>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "傷害醫療日額保險金的給付為何?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.928389, "neutral": 0.067686, "contradiction": 0.003924, "factuality": 0.996076, "C_fact": 0.996076}, "C_conf": 0.9976}</t>
+        </is>
+      </c>
+      <c r="J126" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K126" s="3" t="n">
+        <v>0.996076</v>
+      </c>
+      <c r="L126" s="3" t="n">
+        <v>0.9976</v>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:28:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>意外創傷縫合處置保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外創傷縫合處置保險金的給付條件為：被保險人在保險契約有效期間內，因遭受意外傷害事故，於醫院或診所經醫師診斷必須接受創傷縫合處置治療，且已完成縫合處置者，本公司將按傷害醫療保險金日額給付意外創傷縫合處置保險金。同一意外傷害事故僅給付一次。
+條文依據：  
+- [第十九條 意外創傷縫合處置保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 意外創傷縫合處置保險金的給付 | 第二十八條 意外創傷縫合處置保險金的申領 | 第五條 保險範圍 | 第十七條 意外骨折保險金的給付 | payout_items | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外創傷縫合處置保險金的給付條件為：被保險人在保險契約有效期間內，因遭受意外傷害事故，於醫院或診所經醫師診斷必須接受創傷縫合處置治療，且已完成縫合處置者，本公司將按傷害醫療保險金日額給付意外創傷縫合處置保險金。同一意外傷害事故僅給付一次。
+條文依據：  
+- [第十九條 意外創傷縫合處置保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr"/>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "意外創傷縫合處置保險金的給付為何?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.997484, "neutral": 0.002412, "contradiction": 0.000104, "factuality": 0.999896, "C_fact": 0.999896}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J127" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K127" s="3" t="n">
+        <v>0.999896</v>
+      </c>
+      <c r="L127" s="3" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:28:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>因意外導致視力衰退，是否能申請理賠?</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若因意外導致視力衰退，需符合附表二中「失能程度與保險金給付表」的相關條件，才能申請理賠。例如，視力永久在萬國式視力表0.02以下，或眼球喪失、摘出等情況，屬於「失明」的定義，則可申請意外事故失能保險金。此外，視力障害的測定需經過六個月治療後判定，但若為眼球摘出等明顯無法復原的情況，則不受此限制。
+條文依據：  
+- [註2]  
+- [第十三條 意外事故失能保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>第二十三條 意外事故失能保險金的申領 | 第十三條 意外事故失能保險金的給付 | 註2： | 第三十條 不保事項 | 第二十六條 意外骨折保險金的申領 | 附表二：失能程度與保險金給付表</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若因意外導致視力衰退，需符合附表二中「失能程度與保險金給付表」的相關條件，才能申請理賠。例如，視力永久在萬國式視力表0.02以下，或眼球喪失、摘出等情況，屬於「失明」的定義，則可申請意外事故失能保險金。此外，視力障害的測定需經過六個月治療後判定，但若為眼球摘出等明顯無法復原的情況，則不受此限制。
+條文依據：  
+- [註2]  
+- [第十三條 意外事故失能保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr"/>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "因意外導致視力衰退，是否能申請理賠?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.017553, "neutral": 0.98112, "contradiction": 0.001327, "factuality": 0.998673, "C_fact": 0.998673}, "C_conf": 0.9992}</t>
+        </is>
+      </c>
+      <c r="J128" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K128" s="3" t="n">
+        <v>0.998673</v>
+      </c>
+      <c r="L128" s="3" t="n">
+        <v>0.9992</v>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:28:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>肋骨骨折是否可以申請理賠?理賠金額為多少?</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+肋骨骨折可以申請理賠，理賠金額需依據骨折的情況計算：  
+1. 若肋骨完全骨折且未住院治療，按附表三所訂的20天乘以「傷害醫療保險金日額」的二分之一給付。  
+2. 若肋骨不完全骨折，按完全骨折日數的二分之一（即10天）乘以「傷害醫療保險金日額」給付。  
+3. 若肋骨為骨骼龜裂，按完全骨折日數的四分之一（即5天）乘以「傷害醫療保險金日額」給付。  
+條文依據：  
+- [第十八條 傷害醫療日額保險金的給付]  
+- [附表三：骨折別表]</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 傷害醫療日額保險金的給付 | 第十七條 意外骨折保險金的給付 | 第二十六條 意外骨折保險金的申領 | 第三十條 不保事項 | 第五條 保險範圍 | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+肋骨骨折可以申請理賠，理賠金額需依據骨折的情況計算：  
+1. 若肋骨完全骨折且未住院治療，按附表三所訂的20天乘以「傷害醫療保險金日額」的二分之一給付。  
+2. 若肋骨不完全骨折，按完全骨折日數的二分之一（即10天）乘以「傷害醫療保險金日額」給付。  
+3. 若肋骨為骨骼龜裂，按完全骨折日數的四分之一（即5天）乘以「傷害醫療保險金日額」給付。  
+條文依據：  
+- [第十八條 傷害醫療日額保險金的給付]  
+- [附表三：骨折別表]</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr"/>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "肋骨骨折是否可以申請理賠?理賠金額為多少?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.729435, "neutral": 0.251208, "contradiction": 0.019357, "factuality": 0.980643, "C_fact": 0.980643}, "C_conf": 0.9883}</t>
+        </is>
+      </c>
+      <c r="J129" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K129" s="3" t="n">
+        <v>0.980643</v>
+      </c>
+      <c r="L129" s="3" t="n">
+        <v>0.9883</v>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:28:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>投保新鍾心滿福後，假設投保保額為100萬元，於第二保單年度接受「移植器官」，這樣可以領多少保險金?</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款，新鍾心滿福保險涵蓋「移植器官」的保險金給付，且於第二保單年度內，若被保險人接受器官移植，符合「特定重大傷病」的定義，保險公司將給付「特定重大傷病保險金」。該保險金為保險金額的20%。因此，若投保保額為100萬元，則可領取的保險金為20萬元。  
+條文依據：  
+- [第十三條 特定重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>第十五條 滿期保險金的給付 | 第二條 名詞定義 | 附表一：全民健康保險重大傷病項目 | 第十三條 特定重大傷病保險金的給付 | 附表三：各保險單年度可借金額上限表 | payout_items | 第十七條 完全失能保險金的給付 | 附表二：完全失能程度表</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款，新鍾心滿福保險涵蓋「移植器官」的保險金給付，且於第二保單年度內，若被保險人接受器官移植，符合「特定重大傷病」的定義，保險公司將給付「特定重大傷病保險金」。該保險金為保險金額的20%。因此，若投保保額為100萬元，則可領取的保險金為20萬元。  
+條文依據：  
+- [第十三條 特定重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr"/>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認新鍾心滿福保險是否涵蓋器官移植手術的保險金給付", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認保單條款中對於第二保單年度的保險金給付規定", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認投保保額100萬元對應的保險金計算方式", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認是否有其他附加條款或限制影響保險金給付", "must_have": false, "分數": 0.5}], "coverage_score": 0.9615, "nli": {"entailment": 0.009723, "neutral": 0.988206, "contradiction": 0.00207, "factuality": 0.99793, "C_fact": 0.99793}, "C_conf": 0.9603}</t>
+        </is>
+      </c>
+      <c r="J130" s="3" t="n">
+        <v>0.9615</v>
+      </c>
+      <c r="K130" s="3" t="n">
+        <v>0.99793</v>
+      </c>
+      <c r="L130" s="3" t="n">
+        <v>0.9603</v>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:29:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>投保新鍾心滿福後，若要理賠重大傷病保險金，一定要檢附全民健保開立的重大傷病證明才能拿到保險金嗎?</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 新鍾心滿福保單包含重大傷病保險金保障，依條款第二條名詞定義，重大傷病是指被保險人經醫院醫師診斷確定屬於「重大傷病範圍」項目之一者。  
+2. 理賠重大傷病保險金時，通常需要檢附全民健保開立的重大傷病證明，但條款中也明確說明，若被保險人已取得一家「區域醫院」層級以上（含）之醫療院所開立且符合投保當時「重大傷病範圍」的診斷書及病歷摘要，亦可視為重大傷病證明文件，免向全民健保申請。  
+3. 若無法取得全民健保重大傷病證明，條款提供其他替代文件，例如由區域醫院層級以上醫療院所開立的診斷書及病歷摘要，或其他符合條件的文件，具體情況需依條款規定辦理。
+條文依據：  
+- [第二條 名詞定義]  
+- [第二十二條 重大傷病保險金、特定重大傷病保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>第二十二條 重大傷病保險金、特定重大傷病保險金的申領 | other_metadata | 第十二條 重大傷病保險金的給付 | 附表一：全民健康保險重大傷病項目 | 第二條 名詞定義 | 第三十條 不保事項</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 新鍾心滿福保單包含重大傷病保險金保障，依條款第二條名詞定義，重大傷病是指被保險人經醫院醫師診斷確定屬於「重大傷病範圍」項目之一者。  
+2. 理賠重大傷病保險金時，通常需要檢附全民健保開立的重大傷病證明，但條款中也明確說明，若被保險人已取得一家「區域醫院」層級以上（含）之醫療院所開立且符合投保當時「重大傷病範圍」的診斷書及病歷摘要，亦可視為重大傷病證明文件，免向全民健保申請。  
+3. 若無法取得全民健保重大傷病證明，條款提供其他替代文件，例如由區域醫院層級以上醫療院所開立的診斷書及病歷摘要，或其他符合條件的文件，具體情況需依條款規定辦理。
+條文依據：  
+- [第二條 名詞定義]  
+- [第二十二條 重大傷病保險金、特定重大傷病保險金的申領]</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr"/>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認新鍾心滿福保單是否包含重大傷病保險金保障", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認理賠重大傷病保險金是否需要檢附全民健保開立的重大傷病證明", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認是否有其他文件可替代重大傷病證明進行理賠", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.877815, "neutral": 0.120729, "contradiction": 0.001457, "factuality": 0.998543, "C_fact": 0.998543}, "C_conf": 0.9991}</t>
+        </is>
+      </c>
+      <c r="J131" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K131" s="3" t="n">
+        <v>0.998543</v>
+      </c>
+      <c r="L131" s="3" t="n">
+        <v>0.9991</v>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:29:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>一定要有健保身分才能申請重大傷病理賠嗎？</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不一定需要有健保身分才能申請重大傷病理賠。若被保險人喪失全民健康保險被保險人資格，需先申請加保全民健康保險後，始得申領重大傷病保險金。此外，若被保險人已取得符合投保當時重大傷病範圍的診斷書及病歷摘要，亦可作為申請理賠的替代文件。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>第二十二條 重大傷病保險金、特定重大傷病保險金的申領 | 第十二條 重大傷病保險金的給付 | other_metadata | 第三十條 不保事項 | 第二條 名詞定義 | 附表一：全民健康保險重大傷病項目</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不一定需要有健保身分才能申請重大傷病理賠。若被保險人喪失全民健康保險被保險人資格，需先申請加保全民健康保險後，始得申領重大傷病保險金。此外，若被保險人已取得符合投保當時重大傷病範圍的診斷書及病歷摘要，亦可作為申請理賠的替代文件。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr"/>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "一定要有健保身分才能申請重大傷病理賠嗎？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.133944, "neutral": 0.856681, "contradiction": 0.009375, "factuality": 0.990625, "C_fact": 0.990625}, "C_conf": 0.9944}</t>
+        </is>
+      </c>
+      <c r="J132" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K132" s="3" t="n">
+        <v>0.990625</v>
+      </c>
+      <c r="L132" s="3" t="n">
+        <v>0.9944</v>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:30:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>重大傷病的項目如果在投保後有新增，可以從優申請理賠嗎？</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以從優申請理賠，若重大傷病項目於保單有效期間內新增，則以中央衛生主管機關最新公告的重大傷病項目為準，並適用於被保險人於有效期間內診斷確定的情形。
+條文依據：  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>附表一：全民健康保險重大傷病項目 | 第二條 名詞定義 | payout_items</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以從優申請理賠，若重大傷病項目於保單有效期間內新增，則以中央衛生主管機關最新公告的重大傷病項目為準，並適用於被保險人於有效期間內診斷確定的情形。
+條文依據：  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr"/>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "重大傷病的項目如果在投保後有新增，可以從優申請理賠嗎？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.992289, "neutral": 0.006987, "contradiction": 0.000724, "factuality": 0.999276, "C_fact": 0.999276}, "C_conf": 0.9996}</t>
+        </is>
+      </c>
+      <c r="J133" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K133" s="3" t="n">
+        <v>0.9992760000000001</v>
+      </c>
+      <c r="L133" s="3" t="n">
+        <v>0.9996</v>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:30:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>我的保單之前有停效，在復效後五天被診斷出重大疾病是否可申請理賠？</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若保單已成功復效，且重大疾病屬於保單保障範圍內，則可申請理賠。根據條款，重大疾病的理賠條件需符合以下規定：被保險人於復效日起的契約有效期間內，經醫院醫師初次診斷確定罹患重大疾病，並取得相關證明文件。若重大疾病因意外傷害事故所致，則不受等待期間限制；若非因意外傷害事故，則需確認是否符合等待期間的規定。
+條文依據：  
+- [第八條 本契約效力的恢復]  
+- [第十二條 重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>第八條 本契約效力的恢復 | 第三十條 不保事項 | 第五條 保險範圍 | other_metadata | 第二條 名詞定義 | 第十二條 重大傷病保險金的給付 | 第二十二條 重大傷病保險金、特定重大傷病保險金的申領 | 附表一：全民健康保險重大傷病項目</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若保單已成功復效，且重大疾病屬於保單保障範圍內，則可申請理賠。根據條款，重大疾病的理賠條件需符合以下規定：被保險人於復效日起的契約有效期間內，經醫院醫師初次診斷確定罹患重大疾病，並取得相關證明文件。若重大疾病因意外傷害事故所致，則不受等待期間限制；若非因意外傷害事故，則需確認是否符合等待期間的規定。
+條文依據：  
+- [第八條 本契約效力的恢復]  
+- [第十二條 重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr"/>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認保單是否已成功復效", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認重大疾病是否在保單保障範圍內", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認復效後的理賠條件是否符合重大疾病申請要求", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認重大疾病診斷日期是否符合保單復效後的理賠規定", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.375804, "neutral": 0.621215, "contradiction": 0.002981, "factuality": 0.997019, "C_fact": 0.997019}, "C_conf": 0.9982}</t>
+        </is>
+      </c>
+      <c r="J134" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K134" s="3" t="n">
+        <v>0.997019</v>
+      </c>
+      <c r="L134" s="3" t="n">
+        <v>0.9982</v>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:31:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>領完重大傷病保險金，主約終止後，附約可以繼續有效嗎?</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以。根據條款規定，若因重大傷病診斷確定而導致主約終止時，要保人仍可於附約有效期間內繼續繳交附約保險費，以延續附約效力。
+條文依據：  
+- [第十一條 契約的終止（二）]</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 契約的終止（二） | 第十二條 重大傷病保險金的給付 | 第三十條 不保事項 | 第五條 保險範圍 | payout_items | 附表一：全民健康保險重大傷病項目</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以。根據條款規定，若因重大傷病診斷確定而導致主約終止時，要保人仍可於附約有效期間內繼續繳交附約保險費，以延續附約效力。
+條文依據：  
+- [第十一條 契約的終止（二）]</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr"/>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "領完重大傷病保險金，主約終止後，附約可以繼續有效嗎?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.996247, "neutral": 0.003631, "contradiction": 0.000122, "factuality": 0.999878, "C_fact": 0.999878}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J135" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K135" s="3" t="n">
+        <v>0.999878</v>
+      </c>
+      <c r="L135" s="3" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:31:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>Q1：因為慢性精神病的保險給付僅有保額的20%，我可以先不申請給付，等之後發生其他重大傷病後，再申請重大傷病保險金嗎?Q2：但如果我不申請，保險公司不會知道我有罹患慢性精神病阿，所以我就可以領之後的重大傷病100%保額嗎?</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+Q1：慢性精神病的保險給付比例為保額的20%，且可以選擇延後申請，但需注意延後申請可能影響後續重大傷病保險金的申請資格或保額。根據條款規定，若被保險人同時或先後罹患兩項以上重大傷病，保險公司僅給付一項重大傷病保險金，且金額以「初次診斷確定罹患重大傷病時」的保險單年度計算，延後申請可能導致後續重大傷病的保險金額受限。  
+Q2：即使未申請慢性精神病保險金，保險公司仍可能透過其他方式得知被保險人罹患慢性精神病，且條款中未明確規定未申請即視為未罹患，因此無法保證後續重大傷病保險金能領取100%保額。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第十三條 特定重大傷病保險金的給付]  
+- [第二十二條 重大傷病保險金、特定重大傷病保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 重大傷病保險金的給付 | 第十三條 特定重大傷病保險金的給付 | 第三十條 不保事項 | 第二十八條 除外責任（一） | 第二十二條 重大傷病保險金、特定重大傷病保險金的申領 | 第二條 名詞定義 | 附表一：全民健康保險重大傷病項目 | payout_items</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+Q1：慢性精神病的保險給付比例為保額的20%，且可以選擇延後申請，但需注意延後申請可能影響後續重大傷病保險金的申請資格或保額。根據條款規定，若被保險人同時或先後罹患兩項以上重大傷病，保險公司僅給付一項重大傷病保險金，且金額以「初次診斷確定罹患重大傷病時」的保險單年度計算，延後申請可能導致後續重大傷病的保險金額受限。  
+Q2：即使未申請慢性精神病保險金，保險公司仍可能透過其他方式得知被保險人罹患慢性精神病，且條款中未明確規定未申請即視為未罹患，因此無法保證後續重大傷病保險金能領取100%保額。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第十三條 特定重大傷病保險金的給付]  
+- [第二十二條 重大傷病保險金、特定重大傷病保險金的申領]</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr"/>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認慢性精神病保險給付比例是否為保額的20%", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認是否可以延後申請慢性精神病保險給付", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認延後申請是否影響重大傷病保險金的申請資格或保額", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認保險公司是否會因未申請慢性精神病給付而不知情", "must_have": false, "分數": 1.0}, {"id": "5", "point": "確認重大傷病保險金是否能領取100%保額的條件", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.192858, "neutral": 0.804742, "contradiction": 0.0024, "factuality": 0.9976, "C_fact": 0.9976}, "C_conf": 0.9986}</t>
+        </is>
+      </c>
+      <c r="J136" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K136" s="3" t="n">
+        <v>0.9976</v>
+      </c>
+      <c r="L136" s="3" t="n">
+        <v>0.9986</v>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:32:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>失智症會賠嗎？賠多少？</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+失智症是否理賠及理賠金額需視其是否符合保單條款中「重大傷病」或「完全失能」的定義。  
+1. 若失智症導致符合附表二所列「完全失能程度」之一，例如中樞神經系統機能遺存極度障害，終身不能從事任何工作且需經常醫療護理或專人周密照護者，則可依第十七條規定給付「完全失能保險金」，金額為「當年度保險金額」或「年繳應繳保險費總額」的一點零五倍，取其較大者。[第十七條 完全失能保險金的給付]  
+2. 若失智症符合「重大傷病」範圍，例如附表一所列「慢性精神病」或其他符合中央衛生主管機關公告之重大傷病項目，且取得相關重大傷病證明，則可依第十二條規定給付「重大傷病保險金」。金額計算方式依初次診斷確定罹患重大傷病時的保險單年度而定，可能為「保險金額」或「年繳應繳保險費總額」的一點零五倍，取其較大者。[第十二條 重大傷病保險金的給付]  
+條款依據：  
+[第十七條 完全失能保險金的給付]  
+[第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>第十七條 完全失能保險金的給付 | 第二十九條 除外責任（二） | 第十二條 重大傷病保險金的給付 | 第三十條 不保事項 | 附表一：全民健康保險重大傷病項目 | 第二十一條 失蹤處理 | 第十六條 所繳保險費加計利息的退還、身故保險金或喪葬費用保險金的給付 | 附表二：完全失能程度表</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+找不到相關內容  
+條文依據：  
+找不到相關內容</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+失智症是否理賠及理賠金額需視其是否符合保單條款中「重大傷病」或「完全失能」的定義。  
+1. 若失智症導致符合附表二所列「完全失能程度」之一，例如中樞神經系統機能遺存極度障害，終身不能從事任何工作且需經常醫療護理或專人周密照護者，則可依第十七條規定給付「完全失能保險金」，金額為「當年度保險金額」或「年繳應繳保險費總額」的一點零五倍，取其較大者。[第十七條 完全失能保險金的給付]  
+2. 若失智症符合「重大傷病」範圍，例如附表一所列「慢性精神病」或其他符合中央衛生主管機關公告之重大傷病項目，且取得相關重大傷病證明，則可依第十二條規定給付「重大傷病保險金」。金額計算方式依初次診斷確定罹患重大傷病時的保險單年度而定，可能為「保險金額」或「年繳應繳保險費總額」的一點零五倍，取其較大者。[第十二條 重大傷病保險金的給付]  
+條款依據：  
+[第十七條 完全失能保險金的給付]  
+[第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr"/>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "失智症會賠嗎？賠多少？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.002882, "neutral": 0.994989, "contradiction": 0.002129, "factuality": 0.997871, "C_fact": 0.997871}, "C_conf": 0.9987}</t>
+        </is>
+      </c>
+      <c r="J137" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K137" s="3" t="n">
+        <v>0.997871</v>
+      </c>
+      <c r="L137" s="3" t="n">
+        <v>0.9987</v>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:32:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>投保新鍾心滿福後，於第二保單年度罹患子宮頸惡性腫瘤，且已給付重大傷病保險金。第五保單年度時又罹患慢性腎衰竭，這樣還可以申領重大傷病保險金的給付嗎?</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款規定，重大傷病保險金僅能給付一次，即使被保險人同時或先後罹患兩項以上的重大傷病，本公司僅給付一項重大傷病保險金。因此，雖然慢性腎衰竭屬於重大傷病範圍，但因已於第二保單年度因子宮頸惡性腫瘤申領過重大傷病保險金，無法再次申領。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>附表一：全民健康保險重大傷病項目 | 第十二條 重大傷病保險金的給付 | 第五條 保險範圍 | 第二條 名詞定義 | payout_items | 第二十二條 重大傷病保險金、特定重大傷病保險金的申領</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款規定，重大傷病保險金僅能給付一次，即使被保險人同時或先後罹患兩項以上的重大傷病，本公司僅給付一項重大傷病保險金。因此，雖然慢性腎衰竭屬於重大傷病範圍，但因已於第二保單年度因子宮頸惡性腫瘤申領過重大傷病保險金，無法再次申領。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr"/>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認重大傷病保險金是否可重複申領", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認重大傷病保險金的申領條件是否涵蓋慢性腎衰竭", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認保單條款中對於不同疾病的理賠規定", "must_have": false, "分數": 1.0}, {"id": "4", "point": "確認保單年度與理賠次數的限制規定", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.772543, "neutral": 0.225309, "contradiction": 0.002147, "factuality": 0.997853, "C_fact": 0.997853}, "C_conf": 0.9987}</t>
+        </is>
+      </c>
+      <c r="J138" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K138" s="3" t="n">
+        <v>0.997853</v>
+      </c>
+      <c r="L138" s="3" t="n">
+        <v>0.9987</v>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:33:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>12歲的被保險人可以有健康促進保險費折減嗎？</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+12歲的被保險人無法享有健康促進保險費折減，因為該條款明確規定，只有實際年齡達18歲（含）以上的被保險人才能參與健康促進計劃並獲得保險費折減。
+條文依據：  
+- [第十九條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 健康促進保險費折減 | 第三十八條 投保年齡的計算及錯誤的處理 | 第三十四條 減額繳清保險 | 第二條 名詞定義 | 第十六條 所繳保險費加計利息的退還、身故保險金或喪葬費用保險金的給付 | 附表二：完全失能程度表</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+12歲的被保險人無法享有健康促進保險費折減，因為該條款明確規定，只有實際年齡達18歲（含）以上的被保險人才能參與健康促進計劃並獲得保險費折減。
+條文依據：  
+- [第十九條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr"/>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "12歲的被保險人可以有健康促進保險費折減嗎？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.98138, "neutral": 0.018084, "contradiction": 0.000536, "factuality": 0.999464, "C_fact": 0.999464}, "C_conf": 0.9997}</t>
+        </is>
+      </c>
+      <c r="J139" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K139" s="3" t="n">
+        <v>0.999464</v>
+      </c>
+      <c r="L139" s="3" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:33:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>ZDN</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>被保險人於投保鍾心滿溢後的第10天就罹患慢性腎衰竭，請問可以申領重大傷病保險金嗎？</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於投保後第10天罹患慢性腎衰竭，無法申領重大傷病保險金。原因如下：  
+1. 慢性腎衰竭屬於重大傷病保險金涵蓋範圍，但需符合保單等待期間的規定。  
+2. 根據條款，重大傷病保險金的等待期間為自保單生效日起持續有效30日。被保險人因意外傷害事故以外原因於等待期間內罹患重大傷病者，本契約自始無效，本公司僅退還已繳保險費，且不給付重大傷病保險金。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 重大傷病保險金的給付 | 附表一：全民健康保險重大傷病項目 | 第三十條 不保事項 | 第二條 名詞定義 | 第二十二條 重大傷病保險金、特定重大傷病保險金的申領</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於投保後第10天罹患慢性腎衰竭，無法申領重大傷病保險金。原因如下：  
+1. 慢性腎衰竭屬於重大傷病保險金涵蓋範圍，但需符合保單等待期間的規定。  
+2. 根據條款，重大傷病保險金的等待期間為自保單生效日起持續有效30日。被保險人於等待期間內罹患慢性腎衰竭，依條款規定，本契約自始無效，本公司僅退還已繳保險費，且不給付重大傷病保險金。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第三十條 不保事項]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於投保後第10天罹患慢性腎衰竭，無法申領重大傷病保險金。原因如下：  
+1. 慢性腎衰竭屬於重大傷病保險金涵蓋範圍，但需符合保單等待期間的規定。  
+2. 根據條款，重大傷病保險金的等待期間為自保單生效日起持續有效30日。被保險人因意外傷害事故以外原因於等待期間內罹患重大傷病者，本契約自始無效，本公司僅退還已繳保險費，且不給付重大傷病保險金。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr"/>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認重大傷病保險金是否涵蓋慢性腎衰竭", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認保單是否已生效並符合理賠條件", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認慢性腎衰竭的診斷日期是否符合保單規定", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認保單是否有等待期規定及其影響", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.48216, "neutral": 0.501164, "contradiction": 0.016676, "factuality": 0.983324, "C_fact": 0.983324}, "C_conf": 0.99}</t>
+        </is>
+      </c>
+      <c r="J140" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K140" s="3" t="n">
+        <v>0.983324</v>
+      </c>
+      <c r="L140" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:33:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>CFE</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>投保自由配重大傷病後，若在契約生效後80天罹患第一期乳癌，會拿到理賠金嗎?</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 自由配重大傷病保險涵蓋第一期乳癌，屬於「需積極或長期治療之癌症」範圍內，且在附表一中明確列出 [附表一]。  
+2. 契約生效後的等待期為90天，您於生效後80天罹患第一期乳癌，尚未滿等待期，因此不符合理賠條件 [第二條 名詞定義]。  
+3. 根據條款，若被保險人因意外傷害事故以外原因於等待期間內罹患「重大傷病」，本契約自始無效，本公司將無息退還已繳保險費予要保人 [第十一條 重大傷病保險金的給付]。</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>附表一：全民健康保險重大傷病項目 | 第十一條 重大傷病保險金的給付 | 第十五條 不保事項 | 第二條 名詞定義 | 第五條 契約有效期間及保證續保 | 第十四條 除外責任</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 自由配重大傷病保險涵蓋第一期乳癌，屬於「需積極或長期治療之癌症」範圍內，且在附表一中明確列出。  
+2. 契約生效後的等待期為90天，您於生效後80天罹患第一期乳癌，尚未滿等待期，因此不符合理賠條件。  
+3. 根據條款，等待期間內罹患重大傷病，契約自始無效，本公司將無息退還已繳保險費。  
+條文依據：  
+- [第二條 名詞定義]  
+- [第十一條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 自由配重大傷病保險涵蓋第一期乳癌，屬於「需積極或長期治療之癌症」範圍內，且在附表一中明確列出。  
+2. 契約生效後的等待期為90天，您於生效後80天罹患第一期乳癌，尚未滿等待期，因此不符合理賠條件。  
+3. 根據條款，若被保險人因意外傷害事故以外原因於等待期間內罹患「重大傷病」，本契約自始無效，本公司將無息退還已繳保險費予要保人。  
+條文依據：  
+- [第二條 名詞定義]  
+- [第十一條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 自由配重大傷病保險涵蓋第一期乳癌，屬於「需積極或長期治療之癌症」範圍內，且在附表一中明確列出 [附表一]。  
+2. 契約生效後的等待期為90天，您於生效後80天罹患第一期乳癌，尚未滿等待期，因此不符合理賠條件 [第二條 名詞定義]。  
+3. 根據條款，若被保險人因意外傷害事故以外原因於等待期間內罹患「重大傷病」，本契約自始無效，本公司將無息退還已繳保險費予要保人 [第十一條 重大傷病保險金的給付]。</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認自由配重大傷病保險是否涵蓋第一期乳癌", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認契約生效後的等待期是否已滿", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認第一期乳癌是否符合理賠條件", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認理賠金額的計算方式或標準", "must_have": false, "分數": 0.0}], "coverage_score": 0.9231, "nli": {"entailment": 0.019702, "neutral": 0.701941, "contradiction": 0.278357, "factuality": 0.721643, "C_fact": 0.721643}, "C_conf": 0.759}</t>
+        </is>
+      </c>
+      <c r="J141" s="3" t="n">
+        <v>0.9231</v>
+      </c>
+      <c r="K141" s="4" t="n">
+        <v>0.721643</v>
+      </c>
+      <c r="L141" s="4" t="n">
+        <v>0.759</v>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:34:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>CFE</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>要保人想要終止國泰人壽自由配CFE契約，能否退保費?</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+要保人可以終止契約，並退還未到期保險費。本公司會從已繳保險費中扣除按短期費率計算的已經過期間保險費後，將未到期保險費無息退還給要保人。
+條文依據：  
+- [第九條 契約的終止（一）]</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>第九條 契約的終止（一） | 第十五條 不保事項 | 第五條 契約有效期間及保證續保 | 第七條 本契約效力的恢復 | 第六條 續保保險費的交付、寬限期間及契約效力的停止 | 附表二：短期費率表</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+要保人可以終止契約，並退還未到期保險費。本公司會從已繳保險費中扣除按短期費率計算的已經過期間保險費後，將未到期保險費無息退還給要保人。
+條文依據：  
+- [第九條 契約的終止（一）]</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr"/>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "要保人想要終止國泰人壽自由配CFE契約，能否退保費?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.997835, "neutral": 0.002071, "contradiction": 9.4e-05, "factuality": 0.999906, "C_fact": 0.999906}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J142" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K142" s="3" t="n">
+        <v>0.999906</v>
+      </c>
+      <c r="L142" s="3" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:34:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>CFE</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>投保國泰人壽自由配CFE，若在等待期間內罹患重大傷病，要如何給付?</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在等待期間內罹患重大傷病，依條款規定，因意外傷害事故所致的重大傷病不受等待期間限制，仍可申請給付重大傷病保險金。但若因其他原因（非意外傷害事故）罹患重大傷病，則本契約自始無效，保險公司僅退還已繳保險費且不計利息。  
+條文依據：  
+- [第十一條 重大傷病保險金的給付]  
+- [第十五條 不保事項]</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 重大傷病保險金的給付 | 附表一：全民健康保險重大傷病項目 | 第十五條 不保事項 | 第十四條 除外責任 | payout_items | other_metadata</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在等待期間內罹患重大傷病，依條款規定，因意外傷害事故所致的重大傷病不受等待期間限制，仍可申請給付重大傷病保險金。但若因其他原因（非意外傷害事故）罹患重大傷病，則本契約自始無效，保險公司僅退還已繳保險費且不計利息。  
+條文依據：  
+- [第十一條 重大傷病保險金的給付]  
+- [第十五條 不保事項]</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr"/>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認國泰人壽自由配CFE的等待期間規定", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認重大傷病是否符合保單條款中的定義", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認等待期間內重大傷病的給付條件或限制", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認是否有其他附加條款影響給付", "must_have": false, "分數": 0.5}], "coverage_score": 0.9615, "nli": {"entailment": 0.893848, "neutral": 0.098798, "contradiction": 0.007354, "factuality": 0.992646, "C_fact": 0.992646}, "C_conf": 0.9573}</t>
+        </is>
+      </c>
+      <c r="J143" s="3" t="n">
+        <v>0.9615</v>
+      </c>
+      <c r="K143" s="3" t="n">
+        <v>0.992646</v>
+      </c>
+      <c r="L143" s="3" t="n">
+        <v>0.9573</v>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:34:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>CFE</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>投保自由配一年定期初次罹患重大傷病健康保險後，於第三年罹患先天性肌肉萎縮症，可以申領重大傷病保險金嗎？</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人罹患「先天性肌肉萎縮症」無法申領重大傷病保險金，因該疾病屬於保單所列的重大傷病範圍排除項目之一。  
+此外，若於第三年罹患該疾病，需確認保險契約是否仍在有效期間內。根據條款，保險期間為一年，續保後始期以原契約屆滿日翌日為準，且續保需交付保險費並符合相關規定。若未交付續保保險費且超過寬限期間，契約效力將停止。  
+條文依據：  
+- [第二條 名詞定義]  
+- [第六條 續保保險費的交付、寬限期間及契約效力的停止]</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>第五條 契約有效期間及保證續保 | 第二條 名詞定義 | 第十八條 投保年齡的計算及錯誤的處理 | 第六條 續保保險費的交付、寬限期間及契約效力的停止 | 第十條 契約的終止（二） | 附表一：全民健康保險重大傷病項目 | 第十一條 重大傷病保險金的給付 | 第十三條 重大傷病保險金的申領 | 第三條 保險責任的開始及交付保險費</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人罹患「先天性肌肉萎縮症」無法申領重大傷病保險金，因該疾病不屬於保單所列的重大傷病保障範圍。  
+條文依據：  
+- [附表一：全民健康保險重大傷病項目]</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人罹患「先天性肌肉萎縮症」無法申領重大傷病保險金，因該疾病屬於保單所列的重大傷病範圍排除項目之一。  
+此外，若於第三年罹患該疾病，需確認保險契約是否仍在有效期間內。根據條款，保險期間為一年，續保後始期以原契約屆滿日翌日為準，且續保需交付保險費並符合相關規定。若未交付續保保險費且超過寬限期間，契約效力將停止。  
+條文依據：  
+- [第二條 名詞定義]  
+- [第六條 續保保險費的交付、寬限期間及契約效力的停止]</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr"/>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認自由配一年定期重大傷病健康保險的保障範圍是否包含先天性肌肉萎縮症", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認保單是否對先天性疾病有除外條款或限制", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認第三年是否仍在保險有效期間內", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認重大傷病保險金的申領條件是否已滿足", "must_have": false, "分數": 0.5}], "coverage_score": 0.9615, "nli": {"entailment": 0.836494, "neutral": 0.159651, "contradiction": 0.003854, "factuality": 0.996146, "C_fact": 0.996146}, "C_conf": 0.9593}</t>
+        </is>
+      </c>
+      <c r="J144" s="3" t="n">
+        <v>0.9615</v>
+      </c>
+      <c r="K144" s="3" t="n">
+        <v>0.996146</v>
+      </c>
+      <c r="L144" s="3" t="n">
+        <v>0.9593</v>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:35:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>CFG</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>自由配重大疾病(甲型)保障的重大疾病有哪些疾病?</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+自由配重大疾病(甲型)保障的重大疾病包括以下疾病：  
+1. 腦中風後障礙(重度)  
+2. 癱瘓(重度)  
+3. 癌症(重度)  
+4. 急性心肌梗塞(重度)  
+5. 冠狀動脈繞道手術  
+6. 末期腎病變  
+7. 重大器官移植或造血幹細胞移植  
+條文依據：  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>國泰人壽自由配一年定期初次罹患重大疾病健康保險(甲型)年繳費率表 | payout_items | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+自由配重大疾病(甲型)保障的重大疾病包括以下疾病：  
+1. 腦中風後障礙(重度)  
+2. 癱瘓(重度)  
+3. 癌症(重度)  
+4. 急性心肌梗塞(重度)  
+5. 冠狀動脈繞道手術  
+6. 末期腎病變  
+7. 重大器官移植或造血幹細胞移植  
+條文依據：  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr"/>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "自由配重大疾病(甲型)保障的重大疾病有哪些疾病?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.435646, "neutral": 0.534641, "contradiction": 0.029713, "factuality": 0.970287, "C_fact": 0.970287}, "C_conf": 0.9821}</t>
+        </is>
+      </c>
+      <c r="J145" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K145" s="3" t="n">
+        <v>0.970287</v>
+      </c>
+      <c r="L145" s="3" t="n">
+        <v>0.9821</v>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:35:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>被保險人領了2次癌症(重度)追蹤照護金後身故，是否還有尚未給付的保險金供受益人領取?</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 癌症(重度)追蹤照護金的給付次數不影響其他保險金的領取資格，因為條款中未提及該給付次數會限制其他保險金的申領。[第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]  
+2. 被保險人身故後，如本契約保險金尚未給付或未完全給付，則以被保險人身故時之法定繼承人為該部分保險金之受益人，並適用民法繼承編之相關規定。[第二十八條 受益人]  
+條文依據：  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]  
+- [第二十八條 受益人]</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>第二十八條 受益人 | 第二十二條 保險事故的通知與保險給付的申請時間 | 第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用) | 第二十三條 癌症保險金或罹癌基因檢測服務的申領 | 第五條 保險範圍 | 第十條 契約的終止（二） | 第十一條 契約的終止（三） | 第十三條 初次罹患癌症(重度)保險金的給付 | 第六條 第二期以後保險費的交付、寬限期間及契約效力的停止</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 癌症(重度)追蹤照護金的給付次數不影響其他保險金的領取資格，因為條款中未提及該給付次數會限制其他保險金的申領。  
+2. 被保險人身故後，條款中未提及與身故相關的保險金，因此無法確認是否有其他保險金可供受益人領取。  
+條文依據：  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]  
+- [找不到相關內容]</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 癌症(重度)追蹤照護金的給付次數不影響其他保險金的領取資格，因為條款中未提及該給付次數會限制其他保險金的申領。  
+2. 被保險人身故後，如本契約保險金尚未給付或未完全給付，則以被保險人身故時之法定繼承人為該部分保險金之受益人，並適用民法繼承編之相關規定。[第二十八條 受益人]  
+條文依據：  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]  
+- [第二十八條 受益人]</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 癌症(重度)追蹤照護金的給付次數不影響其他保險金的領取資格，因為條款中未提及該給付次數會限制其他保險金的申領。[第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]  
+2. 被保險人身故後，如本契約保險金尚未給付或未完全給付，則以被保險人身故時之法定繼承人為該部分保險金之受益人，並適用民法繼承編之相關規定。[第二十八條 受益人]  
+條文依據：  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]  
+- [第二十八條 受益人]</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認癌症(重度)追蹤照護金的給付次數是否影響其他保險金的領取資格", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認被保險人身故後是否有其他保險金可供受益人領取", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認保單中與身故相關的保險金條款", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.606978, "neutral": 0.361597, "contradiction": 0.031424, "factuality": 0.968576, "C_fact": 0.968576}, "C_conf": 0.981}</t>
+        </is>
+      </c>
+      <c r="J146" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K146" s="3" t="n">
+        <v>0.968576</v>
+      </c>
+      <c r="L146" s="3" t="n">
+        <v>0.981</v>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:36:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>保險金額2萬元，「罹癌基因檢測服務」費用8萬元，還會給付多少「癌症(重度)追蹤照護保險金」？</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款，若被保險人選擇申領「罹癌基因檢測服務」，且該服務費用（8萬元）高於「罹癌基因檢測服務額度」（1,000元），則被保險人僅能申領「癌症(重度)追蹤照護保險金」。在此情況下，保險金額為2萬元，依條款規定按「保險金額」的12倍計算，給付金額為24萬元。  
+條文依據：  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用) | 附件一：罹癌基因檢測服務之項目、服務費用及補償金額表 | 第二十三條 癌症保險金或罹癌基因檢測服務的申領 | 第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用) | payout_items | 第十三條 初次罹患癌症(重度)保險金的給付 | other_metadata | 第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款，若被保險人選擇申領「罹癌基因檢測服務」，且該服務費用（8萬元）高於「罹癌基因檢測服務額度」（1,000元），則被保險人僅能申領「癌症(重度)追蹤照護保險金」。在此情況下，保險金額為2萬元，依條款規定按「保險金額」的12倍計算，給付金額為24萬元。  
+條文依據：  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr"/>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認癌症(重度)追蹤照護保險金的給付條件與計算方式", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認罹癌基因檢測服務是否屬於保險範圍內的可理賠項目", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認保險金額2萬元是否為理賠上限或其他限制", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認是否有其他相關費用已影響保險金額的剩餘可用額度", "must_have": false, "分數": 0.5}], "coverage_score": 0.9615, "nli": {"entailment": 0.702828, "neutral": 0.125915, "contradiction": 0.171257, "factuality": 0.828743, "C_fact": 0.828743}, "C_conf": 0.859}</t>
+        </is>
+      </c>
+      <c r="J147" s="3" t="n">
+        <v>0.9615</v>
+      </c>
+      <c r="K147" s="3" t="n">
+        <v>0.828743</v>
+      </c>
+      <c r="L147" s="3" t="n">
+        <v>0.859</v>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:36:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>投保後1個月罹患重度癌症，會給付哪些保險金？契約還會持續有效嗎？</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 若被保險人在投保後1個月內（即第一保險單年度內）診斷確定罹患重度癌症，符合「初次診斷確定罹患癌症(重度)」條件，本公司將給付「初次罹患癌症(重度)保險金」，金額為「年繳應繳保險費」的1.06倍。  
+2. 契約仍會持續有效，但當期已繳付之未到期保險費不予退還，且續期保險費不會豁免，因豁免條款僅適用於第二保險單年度起。
+條文依據：  
+- [第十三條 初次罹患癌症(重度)保險金的給付]  
+- [第十六條 癌症(重度)豁免保險費(第二保險單年度起適用)]</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 癌症(重度)豁免保險費(第二保險單年度起適用) | 第十三條 初次罹患癌症(重度)保險金的給付 | 第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用) | 第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付 | 第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用)</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 若被保險人在投保後1個月內（即第一保險單年度內）診斷確定罹患重度癌症，符合「初次診斷確定罹患癌症(重度)」條件，本公司將給付「初次罹患癌症(重度)保險金」，金額為「年繳應繳保險費」的1.06倍。  
+2. 契約仍會持續有效，但當期已繳付之未到期保險費不予退還，且續期保險費不會豁免，因豁免條款僅適用於第二保險單年度起。
+條文依據：  
+- [第十三條 初次罹患癌症(重度)保險金的給付]  
+- [第十六條 癌症(重度)豁免保險費(第二保險單年度起適用)]</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr"/>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "投保後1個月罹患重度癌症，會給付哪些保險金？契約還會持續有效嗎？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.98353, "neutral": 0.012979, "contradiction": 0.003491, "factuality": 0.996509, "C_fact": 0.996509}, "C_conf": 0.9979}</t>
+        </is>
+      </c>
+      <c r="J148" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K148" s="3" t="n">
+        <v>0.996509</v>
+      </c>
+      <c r="L148" s="3" t="n">
+        <v>0.9979</v>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:37:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>投保後10個月罹患重度癌症，會給付哪些保險金？契約還會持續有效嗎？</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 若被保險人於投保後10個月（即第一保險單年度內）診斷確定罹患重度癌症，符合「初次診斷確定罹患癌症(重度)」條件，本公司將給付「初次罹患癌症(重度)保險金」，金額為「年繳應繳保險費」的一點零六倍。  
+2. 契約仍會持續有效，並不會因為罹患重度癌症而終止。
+條文依據：  
+- [第十三條 初次罹患癌症(重度)保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 癌症(重度)豁免保險費(第二保險單年度起適用) | 第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用) | 第十條 契約的終止（二） | 第十三條 初次罹患癌症(重度)保險金的給付 | 第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 若被保險人於投保後10個月（即第一保險單年度內）診斷確定罹患重度癌症，符合「初次診斷確定罹患癌症(重度)」條件，本公司將給付「初次罹患癌症(重度)保險金」，金額為「年繳應繳保險費」的一點零六倍。  
+2. 契約仍會持續有效，並不會因為罹患重度癌症而終止。
+條文依據：  
+- [第十三條 初次罹患癌症(重度)保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr"/>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "投保後10個月罹患重度癌症，會給付哪些保險金？契約還會持續有效嗎？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.799402, "neutral": 0.132515, "contradiction": 0.068083, "factuality": 0.931917, "C_fact": 0.931917}, "C_conf": 0.9586}</t>
+        </is>
+      </c>
+      <c r="J149" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K149" s="3" t="n">
+        <v>0.931917</v>
+      </c>
+      <c r="L149" s="3" t="n">
+        <v>0.9586</v>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:37:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>投保醫心康愛，罹患肺癌一期，可領什麼保險金？</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人於本契約有效期間內，初次診斷確定罹患肺癌一期，屬於「癌症(初期)或癌症(輕度)」，可申領「初次罹患癌症(初期)或癌症(輕度)保險金」。給付金額依診斷確定日所在的保險單年度而定：  
+1. 若診斷確定日在第一保險單年度內，給付「年繳應繳保險費」的1.06倍。  
+2. 若診斷確定日在第二保險單年度(含)以後，給付「保險金額」的5倍。  
+條文依據：  
+- [第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付 | 第十三條 初次罹患癌症(重度)保險金的給付 | payout_items | 第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用) | 第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人於本契約有效期間內，初次診斷確定罹患肺癌一期，屬於「癌症(初期)或癌症(輕度)」，可申領「初次罹患癌症(初期)或癌症(輕度)保險金」。給付金額依診斷確定日所在的保險單年度而定：  
+1. 若診斷確定日在第一保險單年度內，給付「年繳應繳保險費」的1.06倍。  
+2. 若診斷確定日在第二保險單年度(含)以後，給付「保險金額」的5倍。  
+條文依據：  
+- [第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr"/>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "投保醫心康愛，罹患肺癌一期，可領什麼保險金？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.993514, "neutral": 0.006274, "contradiction": 0.000212, "factuality": 0.999788, "C_fact": 0.999788}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J150" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K150" s="3" t="n">
+        <v>0.999788</v>
+      </c>
+      <c r="L150" s="3" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:37:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>PX5</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>若被保險人身故有何給付?</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人身故時，若本附約保險金尚未給付或未完全給付，則該部分保險金的受益人為被保險人的法定繼承人，並依民法繼承編的相關規定分配。  
+條文依據：  
+- [第二十條 受益人]</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>第二十條 受益人 | 第十二條 重大疾病保險金的給付 | 第十一條 輕度重大疾病保險金的給付 | 第十四條 保險事故的通知與保險金的申請時間 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人身故時，若本附約保險金尚未給付或未完全給付，則該部分保險金的受益人為被保險人的法定繼承人，並依民法繼承編的相關規定分配。  
+條文依據：  
+- [第二十條 受益人]</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr"/>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "若被保險人身故有何給付?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.993302, "neutral": 0.004892, "contradiction": 0.001806, "factuality": 0.998194, "C_fact": 0.998194}, "C_conf": 0.9989}</t>
+        </is>
+      </c>
+      <c r="J151" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K151" s="3" t="n">
+        <v>0.998194</v>
+      </c>
+      <c r="L151" s="3" t="n">
+        <v>0.9989</v>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:37:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>PX5</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>投保鍾溢祝福後，請問在第二年經醫院醫師初次診斷罹患「輕度重大疾病」中的癌症(輕度)者，可以領到輕度重大疾病保險金嗎?可以領到保險金額的百分之多少?</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+投保鍾溢祝福後，若在第二年經醫院醫師初次診斷罹患「輕度重大疾病」中的癌症(輕度)，可以領取輕度重大疾病保險金，給付比例為保險金額的百分之二十。此情況需符合以下條件：  
+1. 保單涵蓋輕度重大疾病保障，且輕度癌症屬於輕度重大疾病的範圍。  
+2. 第二年初次診斷罹患輕度癌症，且已超過等待期間（癌症等待期間為九十日）。  
+條文依據：  
+- [第十一條 輕度重大疾病保險金的給付]  
+- [第二條 名詞定義]  
+- [國泰人壽鍾溢祝福重大疾病健康保險附約（乙型）（外溢型）]</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 輕度重大疾病保險金的給付 | 第十二條 重大疾病保險金的給付 | other_metadata | payout_items | 國泰人壽鍾溢祝福重大疾病健康保險附約(乙型) (外溢型)年繳費率表 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+投保鍾溢祝福後，若在第二年經醫院醫師初次診斷罹患「輕度重大疾病」中的癌症(輕度)，可以領取輕度重大疾病保險金，給付比例為保險金額的百分之二十。此情況需符合以下條件：  
+1. 保單涵蓋輕度重大疾病保障，且輕度癌症屬於輕度重大疾病的範圍。  
+2. 第二年初次診斷罹患輕度癌症，且已超過等待期間（癌症等待期間為九十日）。  
+條文依據：  
+- [第十一條 輕度重大疾病保險金的給付]  
+- [第二條 名詞定義]  
+- [國泰人壽鍾溢祝福重大疾病健康保險附約（乙型）（外溢型）]</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr"/>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認保單是否涵蓋輕度重大疾病保障", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認輕度重大疾病保障是否包含輕度癌症", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認第二年初次診斷輕度癌症是否符合理賠條件", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認輕度重大疾病保險金的給付比例或金額", "must_have": true, "分數": 1.0}, {"id": "5", "point": "確認保單是否有特定條款影響理賠，例如等待期或除外責任", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.086488, "neutral": 0.911814, "contradiction": 0.001698, "factuality": 0.998302, "C_fact": 0.998302}, "C_conf": 0.999}</t>
+        </is>
+      </c>
+      <c r="J152" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K152" s="3" t="n">
+        <v>0.998302</v>
+      </c>
+      <c r="L152" s="3" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:38:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>PX5</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>請問如果在投保後的第三年經醫院醫師初次診斷罹患「重大疾病」者，可以領到重大疾病保險金嗎?可以領到保險金額的百分之多少?那後續又在第四年經醫院醫師初次診斷罹患「輕度重大疾病」者，可以領到輕度重大疾病保險金嗎?可以領到保險金額的百分之多少?</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 在投保後的第三年，若被保險人經醫院醫師初次診斷罹患「重大疾病」，符合條件者可領取重大疾病保險金，給付比例為保險金額的1.3倍。  
+2. 在第四年，若被保險人經醫院醫師初次診斷罹患「輕度重大疾病」，因第十二條規定「被保險人於續保前或本附約有效期間內曾得申領第十一條『輕度重大疾病保險金』者，應扣除之」，但條文未提及「重大疾病」的理賠會影響「輕度重大疾病」的給付，因此符合條件者仍可領取輕度重大疾病保險金，給付比例為保險金額的20%。  
+條文依據：  
+- [第十二條 重大疾病保險金的給付]  
+- [第十一條 輕度重大疾病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 輕度重大疾病保險金的給付 | 第十二條 重大疾病保險金的給付 | 第十六條 除外責任 | payout_items | 第二條 名詞定義 | 第四條 保險範圍 | other_metadata | 國泰人壽鍾溢祝福重大疾病健康保險附約(乙型) (外溢型)年繳費率表</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 在投保後的第三年，若被保險人經醫院醫師初次診斷罹患「重大疾病」，符合條件者可領取重大疾病保險金，給付比例為保險金額的1.3倍。  
+2. 在第四年，若被保險人經醫院醫師初次診斷罹患「輕度重大疾病」，因第十二條規定「被保險人於續保前或本附約有效期間內曾得申領第十一條『輕度重大疾病保險金』者，應扣除之」，但條文未提及「重大疾病」的理賠會影響「輕度重大疾病」的給付，因此符合條件者仍可領取輕度重大疾病保險金，給付比例為保險金額的20%。  
+條文依據：  
+- [第十二條 重大疾病保險金的給付]  
+- [第十一條 輕度重大疾病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr"/>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認重大疾病保險金的給付條件是否符合第三年初次診斷的情況", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認重大疾病保險金的給付比例或金額", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認輕度重大疾病保險金的給付條件是否符合第四年初次診斷的情況", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認輕度重大疾病保險金的給付比例或金額", "must_have": true, "分數": 1.0}, {"id": "5", "point": "確認重大疾病與輕度重大疾病是否屬於不同理賠範疇或是否影響後續理賠", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.826573, "neutral": 0.139177, "contradiction": 0.03425, "factuality": 0.96575, "C_fact": 0.96575}, "C_conf": 0.9793}</t>
+        </is>
+      </c>
+      <c r="J153" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K153" s="3" t="n">
+        <v>0.96575</v>
+      </c>
+      <c r="L153" s="3" t="n">
+        <v>0.9792999999999999</v>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:38:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>PX5</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>請問如果在投保後的第三年經醫院醫師初次診斷罹患「輕度重大疾病」者，可以領到重大疾病保險金嗎?可以領到保險金額的百分之多少?那後續又在第四年經醫院醫師初次診斷罹患「重大疾病」者，可以領到輕度重大疾病保險金嗎?可以領到保險金額的百分之多少?</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 在投保後的第三年，若經醫院醫師初次診斷罹患「輕度重大疾病」，符合保單保障範圍，可領取「輕度重大疾病保險金」，給付比例為保險金額的20%。  
+2. 在第四年，若經醫院醫師初次診斷罹患「重大疾病」，符合保單保障範圍，但因已於第三年申領過「輕度重大疾病保險金」，依條款規定，重大疾病保險金的給付金額需扣除已給付的輕度重大疾病保險金，最終給付比例為保險金額的130%減去20%，即保險金額的110%。
+條文依據：  
+- [第十一條 輕度重大疾病保險金的給付]  
+- [第十二條 重大疾病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 輕度重大疾病保險金的給付 | 第十二條 重大疾病保險金的給付 | 第十六條 除外責任 | payout_items | 第二條 名詞定義 | 第四條 保險範圍 | other_metadata | 第十五條 各項保險金的申領</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 在投保後的第三年，若經醫院醫師初次診斷罹患「輕度重大疾病」，符合保單保障範圍，可領取「輕度重大疾病保險金」，給付比例為保險金額的20%。  
+2. 在第四年，若經醫院醫師初次診斷罹患「重大疾病」，符合保單保障範圍，但因已於第三年申領過「輕度重大疾病保險金」，依條款規定，重大疾病保險金的給付金額需扣除已給付的輕度重大疾病保險金，最終給付比例為保險金額的130%減去20%，即保險金額的110%。
+條文依據：  
+- [第十一條 輕度重大疾病保險金的給付]  
+- [第十二條 重大疾病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr"/>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認輕度重大疾病是否符合保單保障範圍", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認輕度重大疾病保險金的給付比例", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認重大疾病是否符合保單保障範圍", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認重大疾病保險金的給付比例", "must_have": true, "分數": 1.0}, {"id": "5", "point": "確認輕度重大疾病與重大疾病之間的理賠關係或限制", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.977177, "neutral": 0.017204, "contradiction": 0.005619, "factuality": 0.994381, "C_fact": 0.994381}, "C_conf": 0.9966}</t>
+        </is>
+      </c>
+      <c r="J154" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K154" s="3" t="n">
+        <v>0.994381</v>
+      </c>
+      <c r="L154" s="3" t="n">
+        <v>0.9966</v>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:38:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>PX5</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>請問主約效力終止(因身故以外情形)，PX5還能持續有效嗎？</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+主約效力因身故以外的情形終止時，PX5附約仍可持續有效，但需符合以下條件：  
+1. 要保人需繼續繳交附約保險費。  
+2. 附約效力可延續至主約原保險期間屆滿或附約最高續保年齡（以較早者為準）。  
+條文依據：  
+- [第十條 附約的終止（二）]</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>第十條 附約的終止（二） | 第七條 保險費的墊繳、附約的停效及復效 | 第五條 附約的保險期間及保證續保 | 第十三條 健康促進保險費折減 | 第九條 附約的終止（一）</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+主約效力因身故以外的情形終止時，PX5附約仍可持續有效，但需符合以下條件：  
+1. 要保人需繼續繳交附約保險費。  
+2. 附約效力可延續至主約原保險期間屆滿或附約最高續保年齡（以較早者為準）。  
+條文依據：  
+- [第十條 附約的終止（二）]</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr"/>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "請問主約效力終止(因身故以外情形)，PX5還能持續有效嗎？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.992839, "neutral": 0.007012, "contradiction": 0.000149, "factuality": 0.999851, "C_fact": 0.999851}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J155" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K155" s="3" t="n">
+        <v>0.999851</v>
+      </c>
+      <c r="L155" s="3" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:38:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>請問如果於「無理賠紀錄期間」屆滿日以內罹患特定傷病，會給付多少錢?這筆錢會給付給誰?</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在「無理賠紀錄期間」屆滿日以內罹患特定傷病，保險公司將給付的金額為「保險金額」加上「年繳應繳保險費總額」乘以1.02的加總。這筆「特定傷病保險金」的受益人為被保險人本人，且不得指定或變更。
+條文依據：  
+- [第十一條 特定傷病保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第十二條 無理賠關懷保險金的給付 | 第十一條 特定傷病保險金的給付 | payout_items | 第二十七條 受益人的指定及變更</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在「無理賠紀錄期間」屆滿日以內罹患特定傷病，保險公司將給付的金額為「保險金額」加上「年繳應繳保險費總額」乘以1.02的加總。這筆「特定傷病保險金」的受益人為被保險人本人，且不得指定或變更。
+條文依據：  
+- [第十一條 特定傷病保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr"/>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "請問如果於「無理賠紀錄期間」屆滿日以內罹患特定傷病，會給付多少錢?這筆錢會給付給誰?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.996866, "neutral": 0.00284, "contradiction": 0.000294, "factuality": 0.999706, "C_fact": 0.999706}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J156" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K156" s="3" t="n">
+        <v>0.999706</v>
+      </c>
+      <c r="L156" s="3" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:39:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>請問如果要保人與被保險人為同一人，被保險人於「無理賠紀錄期間」屆滿日以內身故，會給付多少錢?這筆錢會給付給誰?</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若要保人與被保險人為同一人，且被保險人在「無理賠紀錄期間」屆滿日以內身故，依第十二條規定，本公司將給付「無理賠關懷保險金」，金額為「年繳應繳保險費總額」乘以1.02。根據第二十七條，無理賠關懷保險金的受益人為要保人本人，若要保人與被保險人為同一人，則受益人為被保險人的法定繼承人。
+條文依據：  
+- [第十二條 無理賠關懷保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第十二條 無理賠關懷保險金的給付 | 第十一條 特定傷病保險金的給付 | payout_items | 第十九條 失蹤處理 | 第二十一條 無理賠關懷保險金的申領 | 第二十七條 受益人的指定及變更 | 第十七條 除外責任（二）</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若要保人與被保險人為同一人，且被保險人在「無理賠紀錄期間」屆滿日以內身故，依第十二條規定，本公司將給付「無理賠關懷保險金」，金額為「年繳應繳保險費總額」乘以1.02。根據第二十七條，無理賠關懷保險金的受益人為要保人本人，若要保人與被保險人為同一人，則受益人為被保險人的法定繼承人。
+條文依據：  
+- [第十二條 無理賠關懷保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr"/>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認要保人與被保險人為同一人時的理賠規定", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認被保險人在無理賠紀錄期間屆滿日以內身故的保險金額", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認身故保險金的受益人為何人", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認無理賠紀錄期間的定義與適用條件", "must_have": false, "分數": 0.8}], "coverage_score": 0.9846, "nli": {"entailment": 0.994627, "neutral": 0.004864, "contradiction": 0.000508, "factuality": 0.999492, "C_fact": 0.999492}, "C_conf": 0.9843}</t>
+        </is>
+      </c>
+      <c r="J157" s="3" t="n">
+        <v>0.9846</v>
+      </c>
+      <c r="K157" s="3" t="n">
+        <v>0.999492</v>
+      </c>
+      <c r="L157" s="3" t="n">
+        <v>0.9843</v>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:39:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>請問如果要保人與被保險人為不同人，被保險人於「無理賠紀錄期間」屆滿日以內生存，且被保險人未罹患特定傷病，會給付多少錢?這筆錢會給付給誰?</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若要保人與被保險人為不同人，且被保險人在「無理賠紀錄期間」屆滿日以內生存，並未罹患特定傷病，則符合給付「無理賠關懷保險金」的條件。給付金額為「年繳應繳保險費總額」乘以1.02。該筆保險金的受益人為要保人本人。
+條文依據：  
+- [第十二條 無理賠關懷保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第十二條 無理賠關懷保險金的給付 | 第十一條 特定傷病保險金的給付 | payout_items | 第二十七條 受益人的指定及變更 | 第十九條 失蹤處理 | 第二十一條 無理賠關懷保險金的申領 | 第十七條 除外責任（二）</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若要保人與被保險人為不同人，且被保險人在「無理賠紀錄期間」屆滿日以內生存，並未罹患特定傷病，則符合給付「無理賠關懷保險金」的條件。給付金額為「年繳應繳保險費總額」乘以1.02。該筆保險金的受益人為要保人本人。
+條文依據：  
+- [第十二條 無理賠關懷保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr"/>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認要保人與被保險人為不同人時的保險條款適用", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認無理賠紀錄期間屆滿日生存的給付金額", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認被保險人未罹患特定傷病的條件對給付的影響", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認該筆給付金額的受益人為何人", "must_have": true, "分數": 1.0}, {"id": "5", "point": "確認特定傷病的定義與範圍", "must_have": false, "分數": 0.0}], "coverage_score": 0.9412, "nli": {"entailment": 0.987908, "neutral": 0.01156, "contradiction": 0.000532, "factuality": 0.999468, "C_fact": 0.999468}, "C_conf": 0.9409}</t>
+        </is>
+      </c>
+      <c r="J158" s="3" t="n">
+        <v>0.9412</v>
+      </c>
+      <c r="K158" s="3" t="n">
+        <v>0.999468</v>
+      </c>
+      <c r="L158" s="3" t="n">
+        <v>0.9409</v>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:40:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>保戶如果身故，會給保險金嗎?</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保戶（被保險人）若於契約有效期間內身故，是否給付保險金需視具體情況而定。例如：  
+1. 若被保險人於「無理賠紀錄期間」內身故，本公司依約給付保險金。  
+2. 若被保險人因除外責任中的情形（如故意自殺於契約訂立或復效未滿二年內）身故，則本公司不負給付保險金的責任。  
+條文依據：  
+- [第五條 保險範圍]  
+- [第十七條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第二十八條 本契約受益人死亡或失蹤的處理 | 第十七條 除外責任（二） | 第二十三條 受益人受益權之喪失 | 第十九條 失蹤處理</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保戶（被保險人）若於契約有效期間內身故，是否給付保險金需視具體情況而定。例如：  
+1. 若被保險人於「無理賠紀錄期間」內身故，本公司依約給付保險金。  
+2. 若被保險人因除外責任中的情形（如故意自殺於契約訂立或復效未滿二年內）身故，則本公司不負給付保險金的責任。  
+條文依據：  
+- [第五條 保險範圍]  
+- [第十七條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr"/>
+      <c r="H159" s="2" t="inlineStr"/>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "保戶如果身故，會給保險金嗎?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.994804, "neutral": 0.004758, "contradiction": 0.000438, "factuality": 0.999562, "C_fact": 0.999562}, "C_conf": 0.9997}</t>
+        </is>
+      </c>
+      <c r="J159" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K159" s="3" t="n">
+        <v>0.999562</v>
+      </c>
+      <c r="L159" s="3" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:40:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>保戶如果身故，身故申領的保險金會給誰?</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人身故，身故保險金的受益人依以下規定處理：  
+1. 若受益人已指定，則由指定的受益人領取。  
+2. 若受益人未指定或受益人喪失受益權，則保險金作為被保險人的遺產，由其法定繼承人依民法繼承編相關規定分配。  
+3. 若受益人為多數，喪失受益權的受益人原應得部分，按其他受益人原約定比例分配給其他受益人。
+條文依據：  
+- [第二十三條 受益人受益權之喪失]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第二十三條 受益人受益權之喪失 | 第二十七條 受益人的指定及變更 | 第二十八條 本契約受益人死亡或失蹤的處理 | 第二十二條 分期定期保險金給付申領文件、給付期限及未依限給付之效果</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人身故，身故保險金的受益人依以下規定處理：  
+1. 若受益人已指定，則由指定的受益人領取。  
+2. 若受益人未指定或受益人喪失受益權，則保險金作為被保險人的遺產，由其法定繼承人依民法繼承編相關規定分配。  
+3. 若受益人為多數，喪失受益權的受益人原應得部分，按其他受益人原約定比例分配給其他受益人。
+條文依據：  
+- [第二十三條 受益人受益權之喪失]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr"/>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "保戶如果身故，身故申領的保險金會給誰?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.972151, "neutral": 0.026813, "contradiction": 0.001036, "factuality": 0.998964, "C_fact": 0.998964}, "C_conf": 0.9994}</t>
+        </is>
+      </c>
+      <c r="J160" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K160" s="3" t="n">
+        <v>0.998964</v>
+      </c>
+      <c r="L160" s="3" t="n">
+        <v>0.9994</v>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:40:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>如果保戶投保繳費年期20年的滿溢寶，然後在第20保單年度身故的話，可以領到多少錢?</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款內容，滿溢寶的保險金給付條件為：被保險人在保險契約有效期間內，初次診斷確定罹患特定傷病，或於「無理賠紀錄期間」內身故，或於「無理賠紀錄期間」屆滿時仍生存者，本公司依約給付保險金。若保戶於第20保單年度身故，需確認是否符合「無理賠紀錄期間」內身故的條件，並依約給付相關保險金。條款中未提及額外的身故保險金或紅利給付，且本保險為不分紅保險單，無紅利分配。  
+條文依據：  
+- [第五條 保險範圍]  
+- [第十一條 特定傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>other_metadata | 第二十八條 本契約受益人死亡或失蹤的處理 | 第二十六條 投保年齡的計算及錯誤的處理 | 第十一條 特定傷病保險金的給付 | 第二十二條 分期定期保險金給付申領文件、給付期限及未依限給付之效果 | 第五條 保險範圍 | 第十五條 健康促進保險費折減 | 第十九條 失蹤處理</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款內容，滿溢寶的保險金給付條件為：被保險人在保險契約有效期間內，初次診斷確定罹患特定傷病，或於「無理賠紀錄期間」內身故，或於「無理賠紀錄期間」屆滿時仍生存者，本公司依約給付保險金。若保戶於第20保單年度身故，需確認是否符合「無理賠紀錄期間」內身故的條件，並依約給付相關保險金。條款中未提及額外的身故保險金或紅利給付，且本保險為不分紅保險單，無紅利分配。  
+條文依據：  
+- [第五條 保險範圍]  
+- [第十一條 特定傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr"/>
+      <c r="H161" s="2" t="inlineStr"/>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認滿溢寶的保險金給付條件", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認第20保單年度身故的保險金計算方式", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認是否有額外的身故保險金或紅利給付", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.811835, "neutral": 0.06448, "contradiction": 0.123685, "factuality": 0.876315, "C_fact": 0.876315}, "C_conf": 0.9238}</t>
+        </is>
+      </c>
+      <c r="J161" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K161" s="3" t="n">
+        <v>0.876315</v>
+      </c>
+      <c r="L161" s="3" t="n">
+        <v>0.9238</v>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:40:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>被保險人為60歲女性，投保繳費期間20年期之滿溢寶特定傷病定期健康保險（定期給付型）（外溢型）100萬元，年繳應繳保險費為83,500元，年繳實繳保險費為78,490元。若被保險人於第二保險單年度自殺身故，則無理賠關懷保險金可以領到多少錢？</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於第二保險單年度自殺身故，依第十七條規定，若自契約訂立或復效之日起未滿二年，屬於除外責任範圍，本公司不負給付無理賠關懷保險金的責任。因此，無理賠關懷保險金無法領取。
+條文依據：  
+- [第十七條 除外責任（二）]  
+- [第十二條 無理賠關懷保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 無理賠關懷保險金的給付 | 第十七條 除外責任（二） | 第十一條 特定傷病保險金的給付 | other_metadata | 第十九條 失蹤處理 | 第五條 保險範圍 | 第二十一條 無理賠關懷保險金的申領 | 第二十七條 受益人的指定及變更</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於第二保險單年度自殺身故，依第十七條規定，若自契約訂立或復效之日起未滿二年，屬於除外責任範圍，本公司不負給付無理賠關懷保險金的責任。因此，無理賠關懷保險金無法領取。
+條文依據：  
+- [第十七條 除外責任（二）]  
+- [第十二條 無理賠關懷保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr"/>
+      <c r="H162" s="2" t="inlineStr"/>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認保險商品為滿溢寶特定傷病定期健康保險（定期給付型）（外溢型）", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認被保險人於第二保險單年度自殺身故的理賠條件", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認無理賠關懷保險金的給付規定", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認年繳應繳與實繳保險費的差異是否影響理賠", "must_have": false, "分數": 0.0}, {"id": "5", "point": "確認保險商品是否有自殺除外條款", "must_have": false, "分數": 1.0}], "coverage_score": 0.9286, "nli": {"entailment": 0.966303, "neutral": 0.026736, "contradiction": 0.006961, "factuality": 0.993039, "C_fact": 0.993039}, "C_conf": 0.9247}</t>
+        </is>
+      </c>
+      <c r="J162" s="3" t="n">
+        <v>0.9286</v>
+      </c>
+      <c r="K162" s="3" t="n">
+        <v>0.993039</v>
+      </c>
+      <c r="L162" s="3" t="n">
+        <v>0.9247</v>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:41:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>請問如果第2保單年度罹患特定傷病，可以給付多少錢?給付給誰?未來還有其他保險金嗎?</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在第2保單年度罹患特定傷病，依條款規定：  
+1. **給付金額**：保險公司將依「保險金額」給付「特定傷病保險金」。  
+2. **給付對象**：保險金給付予被保險人或其合法受益人。  
+3. **未來保險金**：自診斷確定罹患特定傷病的次一個保險單週年日起，每逢保險單週年日仍生存者，保險公司將按「保險金額」的36%給付「生活補助保險金」，最多給付10次。此外，自診斷確定日起，保險公司將豁免續期保險費，但當期已繳付之未到期保險費不予退還。
+條文依據：  
+- [第十二條 特定傷病保險金的給付]  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]  
+- [第十五條 保險費豁免（第二保險單年度起適用）]</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 特定傷病保險金的給付 | 第五條 保險範圍 | 第十三條 生活補助保險金的給付（第二保險單年度起適用） | 第二條 名詞定義 | 第十五條 保險費豁免（第二保險單年度起適用）</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在第2保單年度罹患特定傷病，依條款規定：  
+1. **給付金額**：保險公司將依「保險金額」給付「特定傷病保險金」。  
+2. **給付對象**：保險金給付予被保險人或其合法受益人。  
+3. **未來保險金**：自診斷確定罹患特定傷病的次一個保險單週年日起，每逢保險單週年日仍生存者，保險公司將按「保險金額」的36%給付「生活補助保險金」，最多給付10次。此外，自診斷確定日起，保險公司將豁免續期保險費，但當期已繳付之未到期保險費不予退還。
+條文依據：  
+- [第十二條 特定傷病保險金的給付]  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]  
+- [第十五條 保險費豁免（第二保險單年度起適用）]</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr"/>
+      <c r="H163" s="2" t="inlineStr"/>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "請問如果第2保單年度罹患特定傷病，可以給付多少錢?給付給誰?未來還有其他保險金嗎?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.672909, "neutral": 0.323413, "contradiction": 0.003678, "factuality": 0.996322, "C_fact": 0.996322}, "C_conf": 0.9978}</t>
+        </is>
+      </c>
+      <c r="J163" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K163" s="3" t="n">
+        <v>0.996322</v>
+      </c>
+      <c r="L163" s="3" t="n">
+        <v>0.9978</v>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:41:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>請問我115年1月1日投保，怎麼得到健康促進保險費折減?</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+要獲得健康促進保險費折減，您需要在保單有效期間內完成以下步驟：  
+1. 使用保險公司指定的程式並加入指定的健康計劃。  
+2. 完成程式註冊程序，並授權保險公司取得與健康促進相關的電子紀錄。  
+3. 根據成功傳輸的電子紀錄，保險公司將依其辦法計算您的會員等級。  
+4. 若於「指定日期」的會員等級符合標準，則次一保險單年度的保險費可按以下比例折減：  
+   - 實踐家：3%  
+   - 樂享家或高於樂享家的會員等級：10%  
+注意：復效或豁免的保險費不適用此折減約定。
+條文依據：  
+- [第十六條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 健康促進保險費折減 | 第二十三條 投保年齡的計算及錯誤的處理 | 第十五條 保險費豁免（第二保險單年度起適用） | 第五條 保險範圍 | payout_items</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+要獲得健康促進保險費折減，您需要在保單有效期間內完成以下步驟：  
+1. 使用保險公司指定的程式並加入指定的健康計劃。  
+2. 完成程式註冊程序，並授權保險公司取得與健康促進相關的電子紀錄。  
+3. 根據成功傳輸的電子紀錄，保險公司將依其辦法計算您的會員等級。  
+4. 若於「指定日期」的會員等級符合標準，則次一保險單年度的保險費可按以下比例折減：  
+   - 實踐家：3%  
+   - 樂享家或高於樂享家的會員等級：10%  
+注意：復效或豁免的保險費不適用此折減約定。
+條文依據：  
+- [第十六條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr"/>
+      <c r="H164" s="2" t="inlineStr"/>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "請問我115年1月1日投保，怎麼得到健康促進保險費折減?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.997669, "neutral": 0.001902, "contradiction": 0.000428, "factuality": 0.999572, "C_fact": 0.999572}, "C_conf": 0.9997}</t>
+        </is>
+      </c>
+      <c r="J164" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K164" s="3" t="n">
+        <v>0.999572</v>
+      </c>
+      <c r="L164" s="3" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:41:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>保戶在114/1/10投保樂鍾溢，如果他在115/3/30罹患特定傷病的話，在什麼時候可以領取生活補助保險金?</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保戶於114/1/10投保樂鍾溢，根據條款，生活補助保險金的給付條件需滿足以下幾點：  
+1. 保單需進入第二保險單年度（含）後的有效期間。  
+2. 初次診斷確定罹患特定傷病後，從次一個保險單週年日起，每逢保險單週年日仍生存者，方可領取生活補助保險金。  
+保單生效日為114/1/10，第二保險單年度自115/1/10起算。保戶於115/3/30初次診斷確定罹患特定傷病，符合條件。根據條款，生活補助保險金的給付將從次一個保險單週年日（116/1/10）起開始計算，若保戶於該日仍生存，即可領取第一筆生活補助保險金。
+條文依據：  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]  
+- [第十一條 契約的終止（三）]</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 生活補助保險金的給付（第二保險單年度起適用） | other_metadata | 第十一條 契約的終止（三） | payout_items | 第十二條 特定傷病保險金的給付 | 第五條 保險範圍 | 第十五條 保險費豁免（第二保險單年度起適用） | 第十條 契約的終止（二）</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保戶於114/1/10投保樂鍾溢，根據條款，生活補助保險金的給付條件需滿足以下幾點：  
+1. 保單需進入第二保險單年度（含）後的有效期間。  
+2. 初次診斷確定罹患特定傷病後，從次一個保險單週年日起，每逢保險單週年日仍生存者，方可領取生活補助保險金。  
+保單生效日為114/1/10，第二保險單年度自115/1/10起算。保戶於115/3/30初次診斷確定罹患特定傷病，符合條件。根據條款，生活補助保險金的給付將從次一個保險單週年日（116/1/10）起開始計算，若保戶於該日仍生存，即可領取第一筆生活補助保險金。
+條文依據：  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]  
+- [第十一條 契約的終止（三）]</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr"/>
+      <c r="H165" s="2" t="inlineStr"/>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認樂鍾溢保單是否包含生活補助保險金保障", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認保單中針對特定傷病的生活補助保險金給付條件", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認保單生效日與等待期是否影響給付時間", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認115/3/30罹患特定傷病是否符合保單條件", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.927188, "neutral": 0.052961, "contradiction": 0.01985, "factuality": 0.98015, "C_fact": 0.98015}, "C_conf": 0.988}</t>
+        </is>
+      </c>
+      <c r="J165" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K165" s="3" t="n">
+        <v>0.98015</v>
+      </c>
+      <c r="L165" s="3" t="n">
+        <v>0.988</v>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:42:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>保戶在114/1/10投保樂鍾溢，如果他在115/3/30罹患特定傷病的話，他在115/1/9會領到無理賠回饋保險金嗎?</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 樂鍾溢保單包含無理賠回饋保險金的條款，條文中明確提到「無理賠回饋保險金」的給付與申領條件。  
+2. 無理賠回饋保險金的領取條件為：  
+   - 被保險人在保險單年度末仍生存，且未曾因罹患特定傷病而申領「特定傷病保險金」。  
+3. 保戶在115/1/9符合無理賠回饋保險金的領取資格，因為：  
+   - 115/1/9為第一保險單年度末，保戶在此日期前未曾申領「特定傷病保險金」（其於115/3/30才罹患特定傷病）。  
+4. 特定傷病的診斷日期（115/3/30）發生於115/1/9之後，因此不影響保戶在115/1/9領取無理賠回饋保險金的資格。
+條文依據：  
+- [第十四條 無理賠回饋保險金的給付]  
+- [第二十條 無理賠回饋保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>payout_items | 第十四條 無理賠回饋保險金的給付 | other_metadata | 第十二條 特定傷病保險金的給付 | 第二十條 無理賠回饋保險金的申領 | 第十條 契約的終止（二） | 第五條 保險範圍 | 第十五條 保險費豁免（第二保險單年度起適用）</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 樂鍾溢保單包含無理賠回饋保險金的條款，條文中明確提到「無理賠回饋保險金」的給付與申領條件。  
+2. 無理賠回饋保險金的領取條件為：  
+   - 被保險人在保險單年度末仍生存，且未曾因罹患特定傷病而申領「特定傷病保險金」。  
+3. 保戶在115/1/9符合無理賠回饋保險金的領取資格，因為：  
+   - 115/1/9為第一保險單年度末，保戶在此日期前未曾申領「特定傷病保險金」（其於115/3/30才罹患特定傷病）。  
+4. 特定傷病的診斷日期（115/3/30）發生於115/1/9之後，因此不影響保戶在115/1/9領取無理賠回饋保險金的資格。
+條文依據：  
+- [第十四條 無理賠回饋保險金的給付]  
+- [第二十條 無理賠回饋保險金的申領]</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr"/>
+      <c r="H166" s="2" t="inlineStr"/>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認樂鍾溢保單是否包含無理賠回饋保險金的條款", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認無理賠回饋保險金的領取條件", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認保戶在115/1/9是否符合無理賠回饋保險金的領取資格", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認特定傷病是否影響無理賠回饋保險金的領取資格", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.107323, "neutral": 0.874424, "contradiction": 0.018252, "factuality": 0.981748, "C_fact": 0.981748}, "C_conf": 0.989}</t>
+        </is>
+      </c>
+      <c r="J166" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K166" s="3" t="n">
+        <v>0.981748</v>
+      </c>
+      <c r="L166" s="3" t="n">
+        <v>0.989</v>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:42:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>被保險人於第一保險單年度罹患急性心肌梗塞（重度），生活補助保險金最多可以領取幾次？</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於第一保險單年度罹患急性心肌梗塞（重度），無法申領生活補助保險金，因為生活補助保險金僅適用於第二保險單年度（含）以後的有效期間內初次診斷確定罹患特定傷病的情況。
+條文依據：  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 生活補助保險金的給付（第二保險單年度起適用） | 第十二條 特定傷病保險金的給付 | 第十一條 契約的終止（三） | 第五條 保險範圍 | 第二條 名詞定義 | 第十四條 無理賠回饋保險金的給付 | 第十九條 特定傷病保險金、生活補助保險金或保險費豁免的申領</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於第一保險單年度罹患急性心肌梗塞（重度），無法申領生活補助保險金，因為生活補助保險金僅適用於第二保險單年度（含）以後的有效期間內初次診斷確定罹患特定傷病的情況。
+條文依據：  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於第一保險單年度罹患急性心肌梗塞（重度），無法申領生活補助保險金，因為生活補助保險金僅適用於第二保險單年度（含）以後的有效期間內初次診斷確定罹患特定傷病的情況。
+條文依據：  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr"/>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認生活補助保險金是否涵蓋急性心肌梗塞（重度）", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認第一保險單年度內生活補助保險金的給付次數限制", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認急性心肌梗塞（重度）是否符合保單條款中的重疾定義", "must_have": false, "分數": 0.5}], "coverage_score": 0.9444, "nli": {"entailment": 0.136136, "neutral": 0.844836, "contradiction": 0.019028, "factuality": 0.980972, "C_fact": 0.980972}, "C_conf": 0.9336}</t>
+        </is>
+      </c>
+      <c r="J167" s="3" t="n">
+        <v>0.9444</v>
+      </c>
+      <c r="K167" s="3" t="n">
+        <v>0.980972</v>
+      </c>
+      <c r="L167" s="3" t="n">
+        <v>0.9336</v>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:43:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>被保險人為60歲女性，投保繳費期間20年期之樂鍾心特定傷病定期健康保險（外溢型）5單位，每單位年繳應繳保險費為1675元，則每逢保險單年度末生存者，可以領取多少無理賠關懷保險金？</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款規定，無理賠回饋保險金的計算方式為「每單位年繳應繳保險費」的10%乘以「單位數」。本案例中，每單位年繳應繳保險費為1675元，投保單位數為5單位，因此計算如下：  
+1675元 × 10% × 5單位 = 837.5元（元以下無條件進位為838元）。  
+因此，每逢保險單年度末生存者，可以領取838元的無理賠回饋保險金。
+條文依據：  
+- [第十四條 無理賠回饋保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 無理賠回饋保險金的給付 | other_metadata | payout_items | 第二十條 無理賠回饋保險金的申領 | 第十二條 特定傷病保險金的給付 | 第十三條 生活補助保險金的給付（第二保險單年度起適用） | 第五條 保險範圍 | 第十五條 保險費豁免（第二保險單年度起適用）</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款規定，無理賠回饋保險金的計算方式為「每單位年繳應繳保險費」的10%乘以「單位數」。本案例中，每單位年繳應繳保險費為1675元，投保單位數為5單位，因此計算如下：  
+1675元 × 10% × 5單位 = 837.5元（元以下無條件進位為838元）。  
+因此，每逢保險單年度末生存者，可以領取838元的無理賠回饋保險金。
+條文依據：  
+- [第十四條 無理賠回饋保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr"/>
+      <c r="H168" s="2" t="inlineStr"/>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認樂鍾心特定傷病定期健康保險（外溢型）的無理賠關懷保險金計算方式", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認每單位保險金額與投保單位數（5單位）", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認保險單年度末生存者的定義與條件", "must_have": false, "分數": 0.8}], "coverage_score": 0.9778, "nli": {"entailment": 0.994236, "neutral": 0.005459, "contradiction": 0.000306, "factuality": 0.999694, "C_fact": 0.999694}, "C_conf": 0.9776}</t>
+        </is>
+      </c>
+      <c r="J168" s="3" t="n">
+        <v>0.9778</v>
+      </c>
+      <c r="K168" s="3" t="n">
+        <v>0.999694</v>
+      </c>
+      <c r="L168" s="3" t="n">
+        <v>0.9776</v>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:43:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>因同一疾病或傷害再次住院若間隔時間在出院後十四日內或因併發症導致的再次住院日數計算有什麼特殊規則？</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人因同一疾病或傷害，或因此引起之併發症，於出院後十四日內再次住院，其住院日數計算規則如下：  
+1. 該次住院將視為同一次住院處理，並適用第十二條至第十三條的保險金給付限制。  
+2. 若被保險人於契約有效期間屆滿後出院，則對於再次住院部分，本公司不予給付保險金。
+條文依據：  
+- [第十一條 住院次數之計算及契約有效期間屆滿後住院之處理]</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第十三條 加護病房或燒燙傷病房保險金的給付 | 第二條 名詞定義 | 第十二條 住院醫療保險金的給付 | 第十八條 除外責任（一） | 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人因同一疾病或傷害，或因此引起之併發症，於出院後十四日內再次住院，其住院日數計算規則如下：  
+1. 該次住院將視為同一次住院處理，並適用第十二條至第十三條的保險金給付限制。  
+2. 若被保險人於契約有效期間屆滿後出院，則對於再次住院部分，本公司不予給付保險金。
+條文依據：  
+- [第十一條 住院次數之計算及契約有效期間屆滿後住院之處理]</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr"/>
+      <c r="H169" s="2" t="inlineStr"/>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認同一疾病或傷害再次住院的間隔時間規定", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認因併發症導致的再次住院日數計算規則", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認是否有針對十四日內再次住院的特殊條款", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.997965, "neutral": 0.001862, "contradiction": 0.000174, "factuality": 0.999826, "C_fact": 0.999826}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J169" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K169" s="3" t="n">
+        <v>0.999826</v>
+      </c>
+      <c r="L169" s="3" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>2026-04-01 10:19:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>投保15年後，增額係數為多少？因手術住院3天，住院日額為2500元，請問可以申請多少理賠?</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 投保15年後，增額係數為1.05。  
+2. 手術住院3天的理賠計算方式為：住院日額 × 增額係數 × 住院日數。  
+3. 理賠金額計算為：2500元 × 1.05 × 3天 = 7875元。  
+4. 條款中未提及其他影響理賠金額的條件或限制，僅需注意住院日數的上限為365天。  
+條文依據：  
+- [附表：增額係數表]  
+- [第十二條 住院醫療保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>附表：增額係數表 | 第十二條 住院醫療保險金的給付 | 第十三條 加護病房或燒燙傷病房保險金的給付 | 第二十八條 住院醫療保險金日額之減少 | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第三十條 投保年齡的計算及錯誤的處理 | 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 投保15年後，增額係數為1.05。  
+2. 手術住院3天的理賠計算方式為：住院日額 × 增額係數 × 住院日數。  
+3. 理賠金額計算為：2500元 × 1.05 × 3天 = 7875元。  
+4. 條款中未提及其他影響理賠金額的條件或限制，僅需注意住院日數的上限為365天。
+條文依據：  
+- [附表：增額係數表]  
+- [第十二條 住院醫療保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 投保15年後，增額係數為1.05。  
+2. 手術住院3天的理賠計算方式為：住院日額 × 增額係數 × 住院日數。  
+3. 理賠金額計算為：2500元 × 1.05 × 3天 = 7875元。  
+4. 條款中未提及其他影響理賠金額的條件或限制，僅需注意住院日數的上限為365天。  
+條文依據：  
+- [附表：增額係數表]  
+- [第十二條 住院醫療保險金的給付]</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 投保15年後，增額係數為1.05。  
+2. 手術住院3天的理賠計算方式為：住院日額 × 增額係數 × 住院日數。  
+3. 理賠金額計算為：2500元 × 1.05 × 3天 = 7875元。  
+4. 條款中未提及其他影響理賠金額的條件或限制，僅需注意住院日數的上限為365天。  
+條文依據：  
+- [附表：增額係數表]  
+- [第十二條 住院醫療保險金的給付]</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認增額係數在投保15年後的數值", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認手術住院3天的理賠計算方式", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認住院日額為2500元的理賠金額計算", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認是否有其他影響理賠金額的條件或限制", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.207627, "neutral": 0.575744, "contradiction": 0.216629, "factuality": 0.783371, "C_fact": 0.783371}, "C_conf": 0.8637}</t>
+        </is>
+      </c>
+      <c r="J170" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K170" s="4" t="n">
+        <v>0.783371</v>
+      </c>
+      <c r="L170" s="3" t="n">
+        <v>0.8637</v>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>2026-04-01 10:28:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>祝壽保險金的領取規定為何?金額多少？</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+祝壽保險金的領取規定如下：  
+1. 被保險人需於本契約有效期間內，且保險年齡到達99歲之保險單週年日仍生存。  
+2. 金額為「當年度保險金額」。  
+條文依據：  
+- [第十七條 祝壽保險金]</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>第十七條 祝壽保險金 | 第二十六條 祝壽保險金的申領 | 第十一條至第十五條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | 第五條 保險範圍 | 第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+祝壽保險金的領取規定如下：  
+1. 被保險人需於本契約有效期間內，且保險年齡到達99歲之保險單週年日仍生存。  
+2. 金額為「當年度保險金額」。  
+條文依據：  
+- [第十七條 祝壽保險金]</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr"/>
+      <c r="H171" s="2" t="inlineStr"/>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "祝壽保險金的領取規定為何?金額多少？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.998844, "neutral": 0.001026, "contradiction": 0.00013, "factuality": 0.99987, "C_fact": 0.99987}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J171" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K171" s="3" t="n">
+        <v>0.99987</v>
+      </c>
+      <c r="L171" s="3" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>2026-04-01 11:18:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>白內障手術是否可以申請理賠?膜性白內障切開術、白內障線狀摘出術或白內障切囊術</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+白內障相關手術如膜性白內障切開術、白內障線狀摘出術及白內障切囊術均可申請理賠，且其給付倍數分別為5倍。  
+條文依據：  
+- [附表一：手術項目與給付倍數 - 1350 膜性白內障切開術 5]  
+- [附表一：手術項目與給付倍數 - 1351 白內障線狀摘出術 5]  
+- [附表一：手術項目與給付倍數 - 1352 白內障切囊術 5]</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>附表一：手術項目與給付倍數 | payout_items | 附表二：特定處置項目及給付倍數表</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+白內障相關手術如膜性白內障切開術、白內障線狀摘出術及白內障切囊術均可申請理賠，且其給付倍數分別為5倍。  
+條文依據：  
+- [附表一：手術項目與給付倍數 - 1350 膜性白內障切開術 5]  
+- [附表一：手術項目與給付倍數 - 1351 白內障線狀摘出術 5]  
+- [附表一：手術項目與給付倍數 - 1352 白內障切囊術 5]</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr"/>
+      <c r="H172" s="2" t="inlineStr"/>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "白內障手術是否可以申請理賠?膜性白內障切開術、白內障線狀摘出術或白內障切囊術", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.88905, "neutral": 0.108232, "contradiction": 0.002718, "factuality": 0.997282, "C_fact": 0.997282}, "C_conf": 0.9984}</t>
+        </is>
+      </c>
+      <c r="J172" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K172" s="3" t="n">
+        <v>0.997282</v>
+      </c>
+      <c r="L172" s="3" t="n">
+        <v>0.9984</v>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>2026-04-01 11:22:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>投保新鍾心滿福後，假設投保保額為100萬元，於第二保單年度接受「移植器官」，這樣可以領多少重大傷病保險金及特定重大傷病保險金?</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 新鍾心滿福保單涵蓋重大傷病保險金及特定重大傷病保險金。  
+2. 器官移植屬於「重大傷病範圍」及「特定重大傷病」的給付條件，符合保險金給付資格。  
+3. 若保額為100萬元，於第二保單年度接受器官移植，重大傷病保險金的給付金額為「保險金額」或「年繳應繳保險費總額的一點零五倍」，二者取其大者；特定重大傷病保險金則為「保險金額的百分之二十」，即20萬元。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第十三條 特定重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 特定重大傷病保險金的給付 | 第十二條 重大傷病保險金的給付 | 附表一：全民健康保險重大傷病項目 | payout_items | 第二條 名詞定義 | 附表二：完全失能程度表</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 新鍾心滿福保單涵蓋重大傷病保險金及特定重大傷病保險金。  
+2. 器官移植屬於「重大傷病範圍」及「特定重大傷病」的給付條件，符合保險金給付資格。  
+3. 若保額為100萬元，於第二保單年度接受器官移植，重大傷病保險金的給付金額為「保險金額」或「年繳應繳保險費總額的一點零五倍」，二者取其大者；特定重大傷病保險金則為「保險金額的百分之二十」，即20萬元。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第十三條 特定重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr"/>
+      <c r="H173" s="2" t="inlineStr"/>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認新鍾心滿福保單是否涵蓋重大傷病保險金及特定重大傷病保險金", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認重大傷病保險金及特定重大傷病保險金的給付條件是否包含器官移植", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認保額100萬元對應的重大傷病保險金及特定重大傷病保險金給付比例或金額", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認第二保單年度是否影響重大傷病保險金及特定重大傷病保險金的給付資格", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.079526, "neutral": 0.914244, "contradiction": 0.00623, "factuality": 0.99377, "C_fact": 0.99377}, "C_conf": 0.9963}</t>
+        </is>
+      </c>
+      <c r="J173" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K173" s="3" t="n">
+        <v>0.99377</v>
+      </c>
+      <c r="L173" s="3" t="n">
+        <v>0.9963</v>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>2026-04-01 11:32:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>要有健保身分才能申請重大傷病理賠嗎？</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+是的，若被保險人喪失全民健康保險被保險人資格，需先重新申請加入全民健康保險後，才能申請重大傷病保險金的給付。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>第二十二條 重大傷病保險金、特定重大傷病保險金的申領 | 第十二條 重大傷病保險金的給付 | 第三十條 不保事項 | other_metadata | 第二條 名詞定義 | 附表一：全民健康保險重大傷病項目</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+是的，若被保險人喪失全民健康保險被保險人資格，需先重新申請加入全民健康保險後，才能申請重大傷病保險金的給付。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr"/>
+      <c r="H174" s="2" t="inlineStr"/>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "要有健保身分才能申請重大傷病理賠嗎？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.95729, "neutral": 0.03243, "contradiction": 0.01028, "factuality": 0.98972, "C_fact": 0.98972}, "C_conf": 0.9938}</t>
+        </is>
+      </c>
+      <c r="J174" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K174" s="3" t="n">
+        <v>0.98972</v>
+      </c>
+      <c r="L174" s="3" t="n">
+        <v>0.9938</v>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>2026-04-01 11:35:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>zcn</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>失智症（具器質性病態）會賠嗎？賠多少？</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+失智症（具器質性病態）是否理賠及賠償金額，需視是否符合保險契約中「重大傷病」的定義及附表一所列範圍。若失智症未列入附表一「重大傷病」項目，則不符合理賠條件。  
+條款依據：  
+[第十二條 重大傷病保險金的給付]  
+[附表一：全民健康保險重大傷病項目]</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>第二十九條 除外責任（二） | 第十七條 完全失能保險金的給付 | 附表一：全民健康保險重大傷病項目 | 第十二條 重大傷病保險金的給付 | 第三十條 不保事項 | 第十六條 所繳保險費加計利息的退還、身故保險金或喪葬費用保險金的給付 | 附表二：完全失能程度表</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+找不到相關內容  
+條文依據：  
+找不到相關內容</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+失智症（具器質性病態）是否理賠及賠償金額，需視是否符合保險契約中「重大傷病」的定義及附表一所列範圍。若失智症未列入附表一「重大傷病」項目，則不符合理賠條件。  
+條款依據：  
+[第十二條 重大傷病保險金的給付]  
+[附表一：全民健康保險重大傷病項目]</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr"/>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "失智症（具器質性病態）會賠嗎？賠多少？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.014504, "neutral": 0.981674, "contradiction": 0.003822, "factuality": 0.996178, "C_fact": 0.996178}, "C_conf": 0.9977}</t>
+        </is>
+      </c>
+      <c r="J175" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K175" s="3" t="n">
+        <v>0.996178</v>
+      </c>
+      <c r="L175" s="3" t="n">
+        <v>0.9977</v>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>2026-04-01 11:40:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>zcn</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>慢性精神病失智症會賠嗎？賠多少？</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+慢性精神病（如失智症）屬於重大傷病範圍，若被保險人於等待期間屆滿翌日或復效日起的契約有效期間內，經醫師診斷確定罹患，並取得重大傷病證明或符合診斷書及病歷摘要的要求，本公司將依以下方式給付「重大傷病保險金」：  
+1. 若初次診斷確定罹患重大傷病時的保險單年度為第一保險單年度，給付金額為「年繳應繳保險費總額」的1.05倍。  
+2. 若初次診斷確定罹患重大傷病時的保險單年度為第二保險單年度（含）以後，給付金額為「保險金額的20%」或「年繳應繳保險費總額的1.05倍」，二者取其大者。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>附表一：全民健康保險重大傷病項目 | 第二十九條 除外責任（二） | 第十二條 重大傷病保險金的給付 | payout_items | 附表二：完全失能程度表</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+慢性精神病（如失智症）屬於重大傷病範圍，若被保險人於等待期間屆滿翌日或復效日起的契約有效期間內，經醫師診斷確定罹患，並取得重大傷病證明或符合診斷書及病歷摘要的要求，本公司將依以下方式給付「重大傷病保險金」：  
+1. 若初次診斷確定罹患重大傷病時的保險單年度為第一保險單年度，給付金額為「年繳應繳保險費總額」的1.05倍。  
+2. 若初次診斷確定罹患重大傷病時的保險單年度為第二保險單年度（含）以後，給付金額為「保險金額的20%」或「年繳應繳保險費總額的1.05倍」，二者取其大者。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr"/>
+      <c r="H176" s="2" t="inlineStr"/>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "慢性精神病失智症會賠嗎？賠多少？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.745203, "neutral": 0.253966, "contradiction": 0.000831, "factuality": 0.999169, "C_fact": 0.999169}, "C_conf": 0.9995}</t>
+        </is>
+      </c>
+      <c r="J176" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K176" s="3" t="n">
+        <v>0.999169</v>
+      </c>
+      <c r="L176" s="3" t="n">
+        <v>0.9995000000000001</v>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>2026-04-01 11:42:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>CFE</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>要保人想要終止國泰人壽自由配CFE契約，能否退保費?如何申請？</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+要保人可以隨時申請終止國泰人壽自由配CFE契約，並可退還未到期保險費。申請終止契約時，需以書面或其他約定方式通知保險公司，契約自保險公司收到通知時生效。退還的未到期保險費將依短期費率計算，扣除已經過期間的保險費後無息退還。
+條文依據：  
+- [第九條 契約的終止（一）]</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>第九條 契約的終止（一） | 第十五條 不保事項 | 第七條 本契約效力的恢復 | 第六條 續保保險費的交付、寬限期間及契約效力的停止 | 第十條 契約的終止（二） | 第五條 契約有效期間及保證續保 | 第八條 告知義務與本契約的解除 | 第十七條 保險金額之減少 | 附表二：短期費率表</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+要保人可以隨時申請終止國泰人壽自由配CFE契約，並可退還未到期保險費。申請終止契約時，需以書面或其他約定方式通知保險公司，契約自保險公司收到通知時生效。退還的未到期保險費將依短期費率計算，扣除已經過期間的保險費後無息退還。
+條文依據：  
+- [第九條 契約的終止（一）]</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr"/>
+      <c r="H177" s="2" t="inlineStr"/>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認終止國泰人壽自由配CFE契約是否可退保費", "must_have": true, "分數": 1.0}, {"id": "2", "point": "了解申請終止契約及退保費的流程", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認退保費的計算方式或條件", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.995977, "neutral": 0.003948, "contradiction": 7.5e-05, "factuality": 0.999925, "C_fact": 0.999925}, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J177" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K177" s="3" t="n">
+        <v>0.999925</v>
+      </c>
+      <c r="L177" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>2026-04-01 11:50:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>保險金額2萬元，「罹癌基因檢測服務」費用8萬元，還會給付多少「癌症(重度)追蹤照護保險金」？若選擇「罹癌基因檢測服務」，其費用會從當年度的「癌症(重度)追蹤照護保險金」中扣除嗎？這樣最後會給付多少錢？</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 癌症(重度)追蹤照護保險金的總額度為保險金額的12倍，即2萬元 × 12 = 24萬元。  
+2. 罹癌基因檢測服務費用為8萬元。  
+3. 根據條文，罹癌基因檢測服務與癌症(重度)追蹤照護保險金為擇一申領，無相互抵扣的規定。若罹癌基因檢測服務額度低於附件一所列服務費用，被保險人僅得申領癌症(重度)追蹤照護保險金，並可另行向合作機構購買罹癌基因檢測服務。  
+4. 若選擇罹癌基因檢測服務，則無法同時申領癌症(重度)追蹤照護保險金，因此最後給付金額為0元。若選擇癌症(重度)追蹤照護保險金，則給付金額為24萬元。  
+5. 條款未明確規定罹癌基因檢測服務費用是否會從癌症(重度)追蹤照護保險金中扣除。  
+條文依據：  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]  
+- [附件一：罹癌基因檢測服務之項目、服務費用及補償金額表]</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用) | 第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用) | 第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付 | 第十三條 初次罹患癌症(重度)保險金的給付 | 第二十三條 癌症保險金或罹癌基因檢測服務的申領 | 附件一：罹癌基因檢測服務之項目、服務費用及補償金額表 | 第十六條 癌症(重度)豁免保險費(第二保險單年度起適用) | 第二條 名詞定義 | 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 癌症(重度)追蹤照護保險金的總額度為保險金額的12倍，即2萬元 × 12 = 24萬元。  
+2. 罹癌基因檢測服務費用為8萬元。  
+3. 根據條文，罹癌基因檢測服務費用不會從癌症(重度)追蹤照護保險金中扣除，兩者為擇一申領，無相互抵扣的規定。  
+4. 若選擇罹癌基因檢測服務，則無法同時申領癌症(重度)追蹤照護保險金，因此最後給付金額為0元。若選擇癌症(重度)追蹤照護保險金，則給付金額為24萬元。  
+5. 條文未提及其他條件或限制影響癌症(重度)追蹤照護保險金的給付。
+條文依據：  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]  
+- [附件一：罹癌基因檢測服務之項目、服務費用及補償金額表]</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 癌症(重度)追蹤照護保險金的總額度為保險金額的12倍，即2萬元 × 12 = 24萬元。  
+2. 罹癌基因檢測服務費用為8萬元。  
+3. 根據條文，罹癌基因檢測服務與癌症(重度)追蹤照護保險金為擇一申領，無相互抵扣的規定。若罹癌基因檢測服務額度低於附件一所列服務費用，被保險人僅得申領癌症(重度)追蹤照護保險金，並可另行向合作機構購買罹癌基因檢測服務。  
+4. 若選擇罹癌基因檢測服務，則無法同時申領癌症(重度)追蹤照護保險金，因此最後給付金額為0元。若選擇癌症(重度)追蹤照護保險金，則給付金額為24萬元。  
+5. 條款未明確規定其他條件或限制影響癌症(重度)追蹤照護保險金的給付。
+條文依據：  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]  
+- [附件一：罹癌基因檢測服務之項目、服務費用及補償金額表]</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 癌症(重度)追蹤照護保險金的總額度為保險金額的12倍，即2萬元 × 12 = 24萬元。  
+2. 罹癌基因檢測服務費用為8萬元。  
+3. 根據條文，罹癌基因檢測服務與癌症(重度)追蹤照護保險金為擇一申領，無相互抵扣的規定。若罹癌基因檢測服務額度低於附件一所列服務費用，被保險人僅得申領癌症(重度)追蹤照護保險金，並可另行向合作機構購買罹癌基因檢測服務。  
+4. 若選擇罹癌基因檢測服務，則無法同時申領癌症(重度)追蹤照護保險金，因此最後給付金額為0元。若選擇癌症(重度)追蹤照護保險金，則給付金額為24萬元。  
+5. 條款未明確規定罹癌基因檢測服務費用是否會從癌症(重度)追蹤照護保險金中扣除。  
+條文依據：  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]  
+- [附件一：罹癌基因檢測服務之項目、服務費用及補償金額表]</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認癌症(重度)追蹤照護保險金的總額度為2萬元", "must_have": true, "分數": 0.0}, {"id": "2", "point": "確認罹癌基因檢測服務費用為8萬元", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認罹癌基因檢測服務費用是否會從癌症(重度)追蹤照護保險金中扣除", "must_have": true, "分數": 1.0}, {"id": "4", "point": "計算扣除罹癌基因檢測服務費用後剩餘的癌症(重度)追蹤照護保險金給付金額", "must_have": true, "分數": 1.0}, {"id": "5", "point": "確認是否有其他條件或限制影響癌症(重度)追蹤照護保險金的給付", "must_have": false, "分數": 1.0}], "coverage_score": 0.7647, "nli": {"entailment": 0.043625, "neutral": 0.029683, "contradiction": 0.926692, "factuality": 0.073308, "C_fact": 0.073308}, "C_conf": 0.1594}</t>
+        </is>
+      </c>
+      <c r="J178" s="4" t="n">
+        <v>0.7647</v>
+      </c>
+      <c r="K178" s="4" t="n">
+        <v>0.073308</v>
+      </c>
+      <c r="L178" s="4" t="n">
+        <v>0.1594</v>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>2026-04-01 14:33:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>投保後1個月罹患重度癌症，是否已過了等待期間？會給付哪些保險金？契約還會持續有效嗎？</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. **是否已超過等待期間**：等待期間為九十日，投保後一個月（約30天）罹患重度癌症，尚未超過等待期間。  
+2. **可申請的保險金種類與給付範圍**：因未超過等待期間，無法申請任何保險金。  
+3. **契約是否持續有效**：根據條款，若於生效日起九十日內罹患癌症，契約效力即行終止，保險公司將無息退還已繳保險費。因此，契約將不再有效。  
+條文依據：  
+- [第十條 契約的終止（二）]  
+- [第十三條 初次罹患癌症(重度)保險金的給付]  
+- （本保險「癌症」等待期間為九十日，詳請參閱契約條款）</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 癌症(重度)豁免保險費(第二保險單年度起適用) | 第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用) | 第十三條 初次罹患癌症(重度)保險金的給付 | other_metadata | 第十條 契約的終止（二） | 第十一條 契約的終止（三） | 第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付 | 第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用)</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. **是否已超過等待期間**：等待期間為九十日，投保後一個月（約30天）罹患重度癌症，尚未超過等待期間。  
+2. **可申請的保險金種類與給付範圍**：因未超過等待期間，無法申請任何保險金。  
+3. **契約是否持續有效**：根據條款，若於生效日起九十日內罹患癌症，契約效力即行終止，保險公司將無息退還已繳保險費。因此，契約將不再有效。  
+條文依據：  
+- [第十條 契約的終止（二）]  
+- [第十三條 初次罹患癌症(重度)保險金的給付]  
+- （本保險「癌症」等待期間為九十日，詳請參閱契約條款）</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr"/>
+      <c r="H179" s="2" t="inlineStr"/>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認重度癌症是否已超過等待期間", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認重度癌症可申請的保險金種類與給付範圍", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認保險契約是否因重度癌症診斷而持續有效", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認等待期間的具體天數及計算方式", "must_have": false, "分數": 1.0}, {"id": "5", "point": "確認是否需提供診斷證明文件以申請保險金", "must_have": false, "分數": 0.0}], "coverage_score": 0.9286, "nli": {"entailment": 0.94501, "neutral": 0.053317, "contradiction": 0.001673, "factuality": 0.998327, "C_fact": 0.998327}, "C_conf": 0.9277}</t>
+        </is>
+      </c>
+      <c r="J179" s="3" t="n">
+        <v>0.9286</v>
+      </c>
+      <c r="K179" s="3" t="n">
+        <v>0.998327</v>
+      </c>
+      <c r="L179" s="3" t="n">
+        <v>0.9277</v>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>2026-04-01 14:38:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>投保後10個月罹患重度癌症，是否已過了等待期間，會給付哪些保險金？契約還會終止嗎？</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. **是否已過等待期間**：等待期間為九十日（約三個月），投保後十個月已超過等待期間，因此符合等待期間的要求。  
+2. **可申請的保險金種類與範圍**：  
+   - 初次罹患癌症(重度)保險金：診斷確定日在第二保險單年度(含)以後，給付「保險金額」的十二倍。（依第十三條）  
+   - 癌症(重度)標靶藥物治療輔助保險金：若接受標靶治療，給付「保險金額」的十二倍。（依第十五條）  
+   - 癌症(重度)追蹤照護保險金：自診斷確定日的次一保險單週年日起，每年給付「保險金額」的十二倍，最長五年。（依第十四條）  
+3. **契約是否會終止**：罹患重度癌症後，契約不會立即終止。根據第十一條，若被保險人於第二保險單年度(含)以後申領完第十三條至第十五條的保險給付，契約才會終止。  
+條文依據：  
+- 第十條 契約的終止（二）  
+- 第十三條 初次罹患癌症(重度)保險金的給付  
+- 第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)  
+- 第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用)  
+- 第十一條 契約的終止（三）</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>第十條 契約的終止（二） | 第十六條 癌症(重度)豁免保險費(第二保險單年度起適用) | 第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用) | other_metadata | 第十三條 初次罹患癌症(重度)保險金的給付 | 第十一條 契約的終止（三） | 第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用) | 第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. **是否已過等待期間**：等待期間為九十日（約三個月），投保後十個月已超過等待期間，因此符合等待期間的要求。  
+2. **可申請的保險金種類與範圍**：  
+   - 初次罹患癌症(重度)保險金：診斷確定日在第二保險單年度(含)以後，給付「保險金額」的十二倍。（依第十三條）  
+   - 癌症(重度)標靶藥物治療輔助保險金：若接受標靶治療，給付「保險金額」的十二倍。（依第十五條）  
+   - 癌症(重度)追蹤照護保險金：自診斷確定日的次一保險單週年日起，每年給付「保險金額」的十二倍，最長五年。（依第十四條）  
+3. **契約是否會終止**：罹患重度癌症後，契約不會立即終止。根據第十一條，若被保險人於第二保險單年度(含)以後申領完第十三條至第十五條的保險給付，契約才會終止。  
+條文依據：  
+- 第十條 契約的終止（二）  
+- 第十三條 初次罹患癌症(重度)保險金的給付  
+- 第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)  
+- 第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用)  
+- 第十一條 契約的終止（三）</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr"/>
+      <c r="H180" s="2" t="inlineStr"/>
+      <c r="I180" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認重度癌症是否已過等待期間", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認重度癌症可申請的保險金種類與範圍", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認罹患重度癌症後契約是否會終止", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認保單中與癌症相關的理賠條款", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.728852, "neutral": 0.255522, "contradiction": 0.015626, "factuality": 0.984374, "C_fact": 0.984374}, "C_conf": 0.9906}</t>
+        </is>
+      </c>
+      <c r="J180" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K180" s="3" t="n">
+        <v>0.984374</v>
+      </c>
+      <c r="L180" s="3" t="n">
+        <v>0.9906</v>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>2026-04-01 14:40:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>dpa</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>投保後10個月罹患重度癌症（第一保單年度），是否已過了等待期間，會給付哪些保險金？契約還會終止嗎？</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. **重度癌症是否已過等待期間**：投保後10個月罹患重度癌症，已超過契約生效日起的90日等待期間，因此不受等待期間限制。  
+2. **可申請的保險金種類與給付範圍**：根據第十三條，診斷確定日位於第一保單年度內，符合「初次診斷確定罹患癌症（重度）」條件者，可申請「初次罹患癌症（重度）保險金」，給付金額為「年繳應繳保險費」的1.06倍。  
+3. **保險契約是否會終止**：根據第十一條，若被保險人在第一保單年度內符合「初次診斷確定罹患癌症（重度）」條件並申領保險金，契約效力即行終止。  
+條文依據：  
+- [第十條 契約的終止（二）]  
+- [第十三條 初次罹患癌症(重度)保險金的給付]  
+- [第十一條 契約的終止（三）]</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 初次罹患癌症(重度)保險金的給付 | 第十六條 癌症(重度)豁免保險費(第二保險單年度起適用) | 第十條 契約的終止（二） | 第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用) | 第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付 | 第十一條 契約的終止（三） | 第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用)</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. **重度癌症是否已過等待期間**：投保後10個月罹患重度癌症，已超過契約生效日起的90日等待期間，因此不受等待期間限制。  
+2. **可申請的保險金種類與給付範圍**：根據第十三條，診斷確定日位於第一保單年度內，符合「初次診斷確定罹患癌症（重度）」條件者，可申請「初次罹患癌症（重度）保險金」，給付金額為「年繳應繳保險費」的1.06倍。  
+3. **保險契約是否會終止**：根據第十一條，若被保險人在第一保單年度內符合「初次診斷確定罹患癌症（重度）」條件並申領保險金，契約效力即行終止。  
+條文依據：  
+- [第十條 契約的終止（二）]  
+- [第十三條 初次罹患癌症(重度)保險金的給付]  
+- [第十一條 契約的終止（三）]</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. **重度癌症是否已過等待期間**：投保後10個月罹患重度癌症，已超過契約生效日起的90日等待期間，因此不受等待期間限制。  
+2. **可申請的保險金種類與給付範圍**：根據第十三條，診斷確定日位於第一保單年度內，符合「初次診斷確定罹患癌症（重度）」條件者，可申請「初次罹患癌症（重度）保險金」，給付金額為「年繳應繳保險費」的1.06倍。  
+3. **保險契約是否會終止**：根據第十一條，若被保險人在第一保單年度內符合「初次診斷確定罹患癌症（重度）」條件並申領保險金，契約效力即行終止。  
+條文依據：  
+- [第十條 契約的終止（二）]  
+- [第十三條 初次罹患癌症(重度)保險金的給付]  
+- [第十一條 契約的終止（三）]</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. **重度癌症是否已過等待期間**：投保後10個月罹患重度癌症，已超過契約生效日起的90日等待期間，因此不受等待期間限制。  
+2. **可申請的保險金種類與給付範圍**：根據第十三條，診斷確定日位於第一保單年度內，符合「初次診斷確定罹患癌症（重度）」條件者，可申請「初次罹患癌症（重度）保險金」，給付金額為「年繳應繳保險費」的1.06倍。  
+3. **保險契約是否會終止**：根據第十一條，若被保險人在第一保單年度內符合「初次診斷確定罹患癌症（重度）」條件並申領保險金，契約效力即行終止。  
+條文依據：  
+- [第十條 契約的終止（二）]  
+- [第十三條 初次罹患癌症(重度)保險金的給付]  
+- [第十一條 契約的終止（三）]</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認重度癌症是否已過等待期間", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認重度癌症可申請的保險金種類與給付範圍", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認罹患重度癌症後保險契約是否會終止", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認第一保單年度對保險金給付的影響", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.034776, "neutral": 0.01468, "contradiction": 0.950544, "factuality": 0.049456, "C_fact": 0.049456}, "C_conf": 0.1646}</t>
+        </is>
+      </c>
+      <c r="J181" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K181" s="4" t="n">
+        <v>0.049456</v>
+      </c>
+      <c r="L181" s="4" t="n">
+        <v>0.1646</v>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>2026-04-01 14:43:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>dpa</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>投保醫心康愛，罹患肺癌一期(重度癌症)，可領什麼保險金？</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 醫心康愛保險涵蓋重度癌症保障，並於契約有效期間內提供相關保險金給付。  
+2. 肺癌一期屬於重度癌症，符合「初次診斷確定罹患癌症（重度）」的理賠條件。  
+3. 針對重度癌症的保險金給付項目包括：  
+   - 「初次罹患癌症(重度)保險金」：若診斷確定日在第二保險單年度(含)以後，給付「保險金額」的十二倍。  
+   - 「癌症(重度)標靶藥物治療輔助保險金」：若於第二保險單年度(含)以後接受標靶治療，給付「保險金額」的十二倍。  
+   - 「癌症(重度)追蹤照護保險金」：自診斷確定日次一保險單週年日起，每年給付「保險金額」的十二倍，最長五年。  
+   - 「癌症(重度)豁免保險費」：自診斷確定日起豁免續期保險費。  
+條文依據：  
+- [第五條 保險範圍]  
+- [第十三條 初次罹患癌症(重度)保險金的給付]  
+- [第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用)]  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]  
+- [第十六條 癌症(重度)豁免保險費(第二保險單年度起適用)]</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 初次罹患癌症(重度)保險金的給付 | 第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付 | payout_items | 第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用) | 第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用) | 第十六條 癌症(重度)豁免保險費(第二保險單年度起適用) | 第二十三條 癌症保險金或罹癌基因檢測服務的申領 | 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 醫心康愛保險涵蓋重度癌症保障，並於契約有效期間內提供相關保險金給付。  
+2. 肺癌一期屬於重度癌症，符合「初次診斷確定罹患癌症（重度）」的理賠條件。  
+3. 針對重度癌症的保險金給付項目包括：  
+   - 「初次罹患癌症(重度)保險金」：若診斷確定日在第二保險單年度(含)以後，給付「保險金額」的十二倍。  
+   - 「癌症(重度)標靶藥物治療輔助保險金」：若於第二保險單年度(含)以後接受標靶治療，給付「保險金額」的十二倍。  
+   - 「癌症(重度)追蹤照護保險金」：自診斷確定日次一保險單週年日起，每年給付「保險金額」的十二倍，最長五年。  
+   - 「癌症(重度)豁免保險費」：自診斷確定日起豁免續期保險費。  
+條文依據：  
+- [第五條 保險範圍]  
+- [第十三條 初次罹患癌症(重度)保險金的給付]  
+- [第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用)]  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]  
+- [第十六條 癌症(重度)豁免保險費(第二保險單年度起適用)]</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr"/>
+      <c r="H182" s="2" t="inlineStr"/>
+      <c r="I182" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認醫心康愛保險是否涵蓋重度癌症保障", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認肺癌一期是否符合重度癌症的理賠定義", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認醫心康愛保險針對重度癌症的保險金給付項目", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認是否有額外的住院或手術相關保險金保障", "must_have": false, "分數": 0.0}], "coverage_score": 0.9231, "nli": {"entailment": 0.002703, "neutral": 0.996785, "contradiction": 0.000512, "factuality": 0.999488, "C_fact": 0.999488}, "C_conf": 0.9228}</t>
+        </is>
+      </c>
+      <c r="J182" s="3" t="n">
+        <v>0.9231</v>
+      </c>
+      <c r="K182" s="3" t="n">
+        <v>0.999488</v>
+      </c>
+      <c r="L182" s="3" t="n">
+        <v>0.9228</v>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>2026-04-01 14:43:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>px5</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>若被保險人身故有何給付?未到期保險費如何處理？尚未給付或未完全給付的保險金如何處理？</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 被保險人身故時，若本附約保險金尚未給付或未完全給付，則以被保險人之法定繼承人為受益人，並依民法繼承編相關規定分配。  
+2. 未到期保險費應從當期已繳保險費中扣除按日數比例計算已經過期間之保險費後，將其未到期保險費無息退還要保人。  
+3. 尚未給付或未完全給付的保險金，應由被保險人之法定繼承人依民法繼承編相關規定分配。  
+條文依據：  
+- [第十條 附約的終止（二）]  
+- [第二十條 受益人]</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 保險事故的通知與保險金的申請時間 | 第二十條 受益人 | 第十二條 重大疾病保險金的給付 | 第十七條 欠繳保險費的扣除 | 第十一條 輕度重大疾病保險金的給付 | 第十條 附約的終止（二） | 第六條 第二期以後保險費及續保保險費的交付、寬限期間及附約效力的停止 | 第九條 附約的終止（一）</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 被保險人身故時，若本附約保險金尚未給付或未完全給付，則以被保險人之法定繼承人為受益人，並依民法繼承編相關規定分配。  
+2. 未到期保險費應從當期已繳保險費中扣除按日數比例計算已經過期間之保險費後，將其未到期保險費無息退還要保人。  
+3. 尚未給付或未完全給付的保險金，應由被保險人之法定繼承人依民法繼承編相關規定分配。  
+條文依據：  
+- [第十條 附約的終止（二）]  
+- [第二十條 受益人]</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr"/>
+      <c r="H183" s="2" t="inlineStr"/>
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認被保險人身故時的保險金給付內容", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認未到期保險費的處理方式", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認尚未給付或未完全給付的保險金處理方式", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認保險契約中相關條款的適用範圍", "must_have": false, "分數": 0.5}], "coverage_score": 0.9615, "nli": {"entailment": 0.994591, "neutral": 0.00497, "contradiction": 0.000439, "factuality": 0.999561, "C_fact": 0.999561}, "C_conf": 0.9612}</t>
+        </is>
+      </c>
+      <c r="J183" s="3" t="n">
+        <v>0.9615</v>
+      </c>
+      <c r="K183" s="3" t="n">
+        <v>0.999561</v>
+      </c>
+      <c r="L183" s="3" t="n">
+        <v>0.9612000000000001</v>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>2026-04-01 14:46:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>保戶如果身故，會給保險金嗎?身故保險金、特定傷病保險金及無理賠關懷保險金？</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 本保單條款中未提及「身故保險金」保障，無法確認是否包含此項保障。  
+2. 本保單包含「特定傷病保險金」保障，給付條件為被保險人在等待期間屆滿翌日或復效日起的契約有效期間內，經初次診斷確定罹患特定傷病，且符合第十一條規定的計算方式。  
+3. 本保單包含「無理賠關懷保險金」保障，給付條件為被保險人在「無理賠紀錄期間」內未曾申領特定傷病保險金，且於該期間內身故或屆滿時仍生存。  
+條文依據：  
+- [第十一條 特定傷病保險金的給付]  
+- [第十二條 無理賠關懷保險金的給付]  
+- 找不到相關條文提及「身故保險金」</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第十七條 除外責任（二） | 第二十七條 受益人的指定及變更 | 第十二條 無理賠關懷保險金的給付 | payout_items | 第十九條 失蹤處理 | 第十一條 特定傷病保險金的給付 | 第十六條 除外責任（一）</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 本保單條款中未提及「身故保險金」保障，無法確認是否包含此項保障。  
+2. 本保單包含「特定傷病保險金」保障，給付條件為被保險人在等待期間屆滿翌日或復效日起的契約有效期間內，經初次診斷確定罹患特定傷病，且符合第十一條規定的計算方式。  
+3. 本保單包含「無理賠關懷保險金」保障，給付條件為被保險人在「無理賠紀錄期間」內未曾申領特定傷病保險金，且於該期間內身故或屆滿時仍生存。  
+條文依據：  
+- [第十一條 特定傷病保險金的給付]  
+- [第十二條 無理賠關懷保險金的給付]  
+- 找不到相關條文提及「身故保險金」</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr"/>
+      <c r="H184" s="2" t="inlineStr"/>
+      <c r="I184" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認保單是否包含身故保險金保障", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認保單是否包含特定傷病保險金保障", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認保單是否包含無理賠關懷保險金保障", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認各項保險金的給付條件與範圍", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.951475, "neutral": 0.032748, "contradiction": 0.015777, "factuality": 0.984223, "C_fact": 0.984223}, "C_conf": 0.9905}</t>
+        </is>
+      </c>
+      <c r="J184" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K184" s="3" t="n">
+        <v>0.984223</v>
+      </c>
+      <c r="L184" s="3" t="n">
+        <v>0.9905</v>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>2026-04-01 14:54:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>保戶如果身故，身故申領的保險金會給誰?身故保險金的受益人是誰？</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+身故保險金的受益人定義如下：  
+1. 若保單上有指定受益人，則依保單指定的受益人為準。  
+2. 若無指定受益人，則以被保險人的法定繼承人為受益人，其受益順序及應得比例適用民法繼承編相關規定。  
+3. 特定傷病保險金及無理賠關懷保險金的受益人不得指定或變更，若被保險人身故且該保險金尚未給付，則以被保險人的法定繼承人為受益人。  
+條文依據：  
+- [第二十七條 受益人的指定及變更]  
+- [第二十二條 分期定期保險金給付申領文件、給付期限及未依限給付之效果]</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>第二十七條 受益人的指定及變更 | 第二十三條 受益人受益權之喪失 | 第二十八條 本契約受益人死亡或失蹤的處理 | 第五條 保險範圍 | 第二十二條 分期定期保險金給付申領文件、給付期限及未依限給付之效果 | 第十條 契約的終止（二） | 第二十條 特定傷病保險金的申領 | 第十七條 除外責任（二）</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+身故保險金的受益人定義如下：  
+1. 若保單上有指定受益人，則依保單指定的受益人為準。  
+2. 若無指定受益人，則以被保險人的法定繼承人為受益人，其受益順序及應得比例適用民法繼承編相關規定。  
+3. 特定傷病保險金及無理賠關懷保險金的受益人不得指定或變更，若被保險人身故且該保險金尚未給付，則以被保險人的法定繼承人為受益人。  
+條文依據：  
+- [第二十七條 受益人的指定及變更]  
+- [第二十二條 分期定期保險金給付申領文件、給付期限及未依限給付之效果]</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr"/>
+      <c r="H185" s="2" t="inlineStr"/>
+      <c r="I185" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認身故保險金的受益人定義與資格", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認保單上指定的受益人", "must_have": true, "分數": 1.0}, {"id": "3", "point": "若無指定受益人，確認法定繼承人是否為受益人", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認受益人變更的相關規定（如適用）", "must_have": false, "分數": 0.5}], "coverage_score": 0.9615, "nli": {"entailment": 0.986133, "neutral": 0.012239, "contradiction": 0.001628, "factuality": 0.998372, "C_fact": 0.998372}, "C_conf": 0.9606}</t>
+        </is>
+      </c>
+      <c r="J185" s="3" t="n">
+        <v>0.9615</v>
+      </c>
+      <c r="K185" s="3" t="n">
+        <v>0.998372</v>
+      </c>
+      <c r="L185" s="3" t="n">
+        <v>0.9606</v>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>2026-04-01 14:57:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>保戶如果身故，身故申領的保險金會給誰?要保人嗎？</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保戶（被保險人）身故後，身故保險金的受益人依以下情況處理：  
+1. 若保險金受益人已指定，則依指定的受益人給付。  
+2. 若未指定受益人，或受益人喪失受益權，則保險金作為被保險人的遺產，由其法定繼承人依民法繼承編相關規定分配。  
+條文依據：  
+- [第二十七條 受益人的指定及變更]  
+- [第二十三條 受益人受益權之喪失]</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>第二十七條 受益人的指定及變更 | 第二十三條 受益人受益權之喪失 | 第五條 保險範圍 | 第二十八條 本契約受益人死亡或失蹤的處理 | 第十七條 除外責任（二）</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保戶（被保險人）身故後，身故保險金的受益人依以下情況處理：  
+1. 若保險金受益人已指定，則依指定的受益人給付。  
+2. 若未指定受益人，或受益人喪失受益權，則保險金作為被保險人的遺產，由其法定繼承人依民法繼承編相關規定分配。  
+條文依據：  
+- [第二十七條 受益人的指定及變更]  
+- [第二十三條 受益人受益權之喪失]</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr"/>
+      <c r="H186" s="2" t="inlineStr"/>
+      <c r="I186" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "保戶如果身故，身故申領的保險金會給誰?要保人嗎？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.993347, "neutral": 0.005743, "contradiction": 0.00091, "factuality": 0.99909, "C_fact": 0.99909}, "C_conf": 0.9995}</t>
+        </is>
+      </c>
+      <c r="J186" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K186" s="3" t="n">
+        <v>0.99909</v>
+      </c>
+      <c r="L186" s="3" t="n">
+        <v>0.9995000000000001</v>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>2026-04-01 14:58:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>如果保戶投保繳費年期20年的滿溢寶，然後在第20保單年度身故的話，可以領到多少錢?無理賠關懷保險金?受益人為要保人嗎？</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 若保戶於第20保單年度身故，依條款規定，需確認是否符合「特定傷病保險金」或「無理賠關懷保險金」的給付條件。若符合「無理賠關懷保險金」條件，則可領取「年繳應繳保險費總額」乘以1.02的金額。  
+2. 是否包含無理賠關懷保險金，需確認被保險人在「無理賠紀錄期間」內未曾申領「特定傷病保險金」，且於該期間內身故或屆滿時仍生存。若符合條件，則包含無理賠關懷保險金。  
+3. 受益人是否為要保人，需依條款判定。若為「無理賠關懷保險金」，受益人為要保人本人；若要保人已身故，則以被保險人為受益人；若被保險人亦已身故，則以被保險人之法定繼承人為受益人。  
+條文依據：  
+- [第十二條 無理賠關懷保險金的給付]  
+- [第二十七條 受益人的指定及變更]  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>第二十七條 受益人的指定及變更 | 第十九條 失蹤處理 | 第十二條 無理賠關懷保險金的給付 | 第十七條 除外責任（二） | other_metadata | 第二十一條 無理賠關懷保險金的申領 | 第二十八條 本契約受益人死亡或失蹤的處理 | 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 若保戶於第20保單年度身故，依條款規定，需確認是否符合「特定傷病保險金」或「無理賠關懷保險金」的給付條件。若符合「無理賠關懷保險金」條件，則可領取「年繳應繳保險費總額」乘以1.02的金額。  
+2. 是否包含無理賠關懷保險金，需確認被保險人在「無理賠紀錄期間」內未曾申領「特定傷病保險金」，且於該期間內身故或屆滿時仍生存。若符合條件，則包含無理賠關懷保險金。  
+3. 受益人是否為要保人，需依條款判定。若為「無理賠關懷保險金」，受益人為要保人本人；若要保人已身故，則以被保險人為受益人；若被保險人亦已身故，則以被保險人之法定繼承人為受益人。  
+條文依據：  
+- [第十二條 無理賠關懷保險金的給付]  
+- [第二十七條 受益人的指定及變更]  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr"/>
+      <c r="H187" s="2" t="inlineStr"/>
+      <c r="I187" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認滿溢寶保單在第20保單年度身故的理賠金額", "must_have": true, "分數": 0.8}, {"id": "2", "point": "確認是否包含無理賠關懷保險金", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認受益人是否為要保人", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認滿溢寶保單的繳費年期與保障內容是否影響理賠金額", "must_have": false, "分數": 0.7}], "coverage_score": 0.9154, "nli": {"entailment": 0.578839, "neutral": 0.415412, "contradiction": 0.005748, "factuality": 0.994252, "C_fact": 0.994252}, "C_conf": 0.9122}</t>
+        </is>
+      </c>
+      <c r="J187" s="3" t="n">
+        <v>0.9154</v>
+      </c>
+      <c r="K187" s="3" t="n">
+        <v>0.994252</v>
+      </c>
+      <c r="L187" s="3" t="n">
+        <v>0.9122</v>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>2026-04-01 15:00:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>請問我115年1月1日投保，怎麼得到健康促進保險費折減?指定日期什麼時後？</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 健康促進保險費折減的申請條件為：被保險人需使用保險公司指定的程式並加入指定的健康計劃，於「指定日期」的會員等級符合標準（如「實踐家」或「樂享家」等級），即可享有次一保險單年度的保險費折減。折減比例為「實踐家」3%、「樂享家或更高等級」10%。  
+2. 115年1月1日投保者，若於保單生效後完成指定程式的註冊程序，並於「指定日期」達到符合的會員等級，即可符合折減資格。  
+3. 「指定日期」未在條文中明確定義，條款僅提及折減適用於次一保險單年度的保險費，需於該保險單年度前完成相關條件。  
+4. 被保險人需執行指定程式並授權保險公司取得健康促進相關的電子紀錄，無需額外提供健康相關證明文件。  
+條文依據：  
+- [第十六條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 健康促進保險費折減 | 第十五條 保險費豁免（第二保險單年度起適用） | 第五條 保險範圍 | 第二十三條 投保年齡的計算及錯誤的處理 | 第十二條 特定傷病保險金的給付 | 第十條 契約的終止（二） | 第十三條 生活補助保險金的給付（第二保險單年度起適用）</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 健康促進保險費折減的申請條件為：被保險人需使用保險公司指定的程式並加入指定的健康計劃，於「指定日期」的會員等級符合標準（如「實踐家」或「樂享家」等級），即可享有次一保險單年度的保險費折減。折減比例為「實踐家」3%、「樂享家或更高等級」10%。  
+2. 115年1月1日投保者，若於保單生效後完成指定程式的註冊程序，並於「指定日期」達到符合的會員等級，即可符合折減資格。  
+3. 「指定日期」未在條文中明確定義，但折減適用於次一保險單年度的保險費，需於該保險單年度前完成相關條件。  
+4. 被保險人需執行指定程式並授權保險公司取得健康促進相關的電子紀錄，無需額外提供健康相關證明文件。
+條文依據：  
+- [第十六條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 健康促進保險費折減的申請條件為：被保險人需使用保險公司指定的程式並加入指定的健康計劃，於「指定日期」的會員等級符合標準（如「實踐家」或「樂享家」等級），即可享有次一保險單年度的保險費折減。折減比例為「實踐家」3%、「樂享家或更高等級」10%。  
+2. 115年1月1日投保者，若於保單生效後完成指定程式的註冊程序，並於「指定日期」達到符合的會員等級，即可符合折減資格。  
+3. 「指定日期」未在條文中明確定義，條款僅提及折減適用於次一保險單年度的保險費，需於該保險單年度前完成相關條件。  
+4. 被保險人需執行指定程式並授權保險公司取得健康促進相關的電子紀錄，無需額外提供健康相關證明文件。
+條文依據：  
+- [第十六條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="H188" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 健康促進保險費折減的申請條件為：被保險人需使用保險公司指定的程式並加入指定的健康計劃，於「指定日期」的會員等級符合標準（如「實踐家」或「樂享家」等級），即可享有次一保險單年度的保險費折減。折減比例為「實踐家」3%、「樂享家或更高等級」10%。  
+2. 115年1月1日投保者，若於保單生效後完成指定程式的註冊程序，並於「指定日期」達到符合的會員等級，即可符合折減資格。  
+3. 「指定日期」未在條文中明確定義，條款僅提及折減適用於次一保險單年度的保險費，需於該保險單年度前完成相關條件。  
+4. 被保險人需執行指定程式並授權保險公司取得健康促進相關的電子紀錄，無需額外提供健康相關證明文件。  
+條文依據：  
+- [第十六條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="I188" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認健康促進保險費折減的申請條件", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認115年1月1日投保是否符合折減資格", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認健康促進保險費折減的指定日期及適用時間", "must_have": true, "分數": 0.8}, {"id": "4", "point": "確認是否需要提供健康相關證明文件以申請折減", "must_have": false, "分數": 1.0}], "coverage_score": 0.9385, "nli": {"entailment": 0.007652, "neutral": 0.22677, "contradiction": 0.765579, "factuality": 0.234421, "C_fact": 0.234421}, "C_conf": 0.393}</t>
+        </is>
+      </c>
+      <c r="J188" s="3" t="n">
+        <v>0.9385</v>
+      </c>
+      <c r="K188" s="4" t="n">
+        <v>0.234421</v>
+      </c>
+      <c r="L188" s="4" t="n">
+        <v>0.393</v>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>2026-04-01 15:04:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>保戶在114/1/10投保樂鍾溢，如果他在115/3/30罹患特定傷病的話，他在115/1/9會領到無理賠回饋保險金嗎?保險單週年日什麼時候？指定日期什麼時候？</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 保險單週年日為每年的1月10日，因為保戶於114/1/10投保，保險單週年日即為保單生效日的每年對應日期。  
+2. 115/1/9不符合無理賠回饋保險金的條件，因為被保險人在115/3/30已經確診罹患特定傷病，而第十四條規定，若被保險人不符條件（如罹患特定傷病），需返還已領取的無理賠回饋保險金。  
+3. 指定日期為每年的保險單年度末，即每年的1月9日。  
+4. 特定傷病的確診會影響無理賠回饋保險金的給付，因為第十四條明確規定，若被保險人罹患特定傷病並申領相關保險金，則不符合無理賠回饋保險金的條件。
+條文依據：  
+- [第十四條 無理賠回饋保險金的給付]  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>other_metadata | 第十四條 無理賠回饋保險金的給付 | payout_items | 第十二條 特定傷病保險金的給付 | 第十五條 保險費豁免（第二保險單年度起適用） | 第十條 契約的終止（二） | 第五條 保險範圍 | 第二十條 無理賠回饋保險金的申領</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 保險單週年日為每年的1月10日，因為保戶於114/1/10投保，保險單週年日即為保單生效日的每年對應日期。  
+2. 115/1/9不符合無理賠回饋保險金的條件，因為被保險人在115/3/30已經確診罹患特定傷病，而第十四條規定，若被保險人不符條件（如罹患特定傷病），需返還已領取的無理賠回饋保險金。  
+3. 指定日期為每年的保險單年度末，即每年的1月9日。  
+4. 特定傷病的確診會影響無理賠回饋保險金的給付，因為第十四條明確規定，若被保險人罹患特定傷病並申領相關保險金，則不符合無理賠回饋保險金的條件。
+條文依據：  
+- [第十四條 無理賠回饋保險金的給付]  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="G189" s="2" t="inlineStr"/>
+      <c r="H189" s="2" t="inlineStr"/>
+      <c r="I189" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認保險單週年日的日期", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認115/1/9是否符合無理賠回饋保險金的條件", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認指定日期的具體時間", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認特定傷病是否影響無理賠回饋保險金的給付", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.993819, "neutral": 0.005238, "contradiction": 0.000943, "factuality": 0.999057, "C_fact": 0.999057}, "C_conf": 0.9994}</t>
+        </is>
+      </c>
+      <c r="J189" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K189" s="3" t="n">
+        <v>0.999057</v>
+      </c>
+      <c r="L189" s="3" t="n">
+        <v>0.9994</v>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>2026-04-01 15:06:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>被保險人於第一保險單年度罹患急性心肌梗塞（重度），生活補助保險金最多可以領取幾次？契約會終止嗎？</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 生活補助保險金的給付次數上限為十次。  
+2. 急性心肌梗塞（重度）屬於「特定傷病」，但生活補助保險金的給付條件僅適用於第二保險單年度（含）以後，因此第一保險單年度內罹患急性心肌梗塞（重度）不符合生活補助保險金的給付條件。  
+3. 若被保險人於第一保險單年度內罹患特定傷病，契約將依第十二條規定給付特定傷病保險金，並依第十一條規定契約效力即行終止。  
+條文依據：  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]  
+- [第十二條 特定傷病保險金的給付]  
+- [第十一條 契約的終止（三）]</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 生活補助保險金的給付（第二保險單年度起適用） | 第十一條 契約的終止（三） | 第五條 保險範圍 | 第二條 名詞定義 | 第十二條 特定傷病保險金的給付 | 第十五條 保險費豁免（第二保險單年度起適用） | payout_items | 第十條 契約的終止（二）</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 生活補助保險金的給付次數上限為十次。  
+2. 急性心肌梗塞（重度）屬於「特定傷病」，但生活補助保險金的給付條件僅適用於第二保險單年度（含）以後，因此第一保險單年度內罹患急性心肌梗塞（重度）不符合生活補助保險金的給付條件。  
+3. 若被保險人於第一保險單年度內罹患特定傷病，契約將依第十二條規定給付特定傷病保險金，並依第十一條規定契約效力即行終止。  
+條文依據：  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]  
+- [第十二條 特定傷病保險金的給付]  
+- [第十一條 契約的終止（三）]</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr"/>
+      <c r="H190" s="2" t="inlineStr"/>
+      <c r="I190" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認生活補助保險金的給付次數上限", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認急性心肌梗塞（重度）是否符合生活補助保險金的給付條件", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認保險契約是否會因給付而終止", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認第一保險單年度內的相關條款限制", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.987078, "neutral": 0.01249, "contradiction": 0.000432, "factuality": 0.999568, "C_fact": 0.999568}, "C_conf": 0.9997}</t>
+        </is>
+      </c>
+      <c r="J190" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K190" s="3" t="n">
+        <v>0.999568</v>
+      </c>
+      <c r="L190" s="3" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>2026-04-01 15:08:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>sc1</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>被保險人為60歲女性，投保繳費期間20年期之樂鍾心特定傷病定期健康保險（外溢型）5單位，每單位年繳應繳保險費為1675元，則每逢保險單年度末生存者，可以領取多少無理賠關懷保險金？</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款規定，無理賠回饋保險金的計算方式為「每單位年繳應繳保險費」的10%（元以下無條件進位）乘以「單位數」。每單位年繳應繳保險費為1675元，10%為168元（167.5元無條件進位）。投保5單位，則無理賠回饋保險金為168元 × 5單位 = 840元。每逢保險單年度末，若被保險人仍生存且符合條件，即可領取840元的無理賠回饋保險金。
+條文依據：  
+- [第十四條 無理賠回饋保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 無理賠回饋保險金的給付 | other_metadata | payout_items | 第二十條 無理賠回饋保險金的申領 | 第十二條 特定傷病保險金的給付 | 第十三條 生活補助保險金的給付（第二保險單年度起適用） | 第五條 保險範圍 | 第十五條 保險費豁免（第二保險單年度起適用）</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款規定，無理賠回饋保險金的計算方式為「每單位年繳應繳保險費」的10%（元以下無條件進位）乘以「單位數」。每單位年繳應繳保險費為1675元，10%為168元（167.5元無條件進位）。投保5單位，則無理賠回饋保險金為168元 × 5單位 = 840元。每逢保險單年度末，若被保險人仍生存且符合條件，即可領取840元的無理賠回饋保險金。
+條文依據：  
+- [第十四條 無理賠回饋保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr"/>
+      <c r="H191" s="2" t="inlineStr"/>
+      <c r="I191" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認樂鍾心特定傷病定期健康保險（外溢型）的無理賠關懷保險金計算方式", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認每單位年繳保險費為1675元的相關條件", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認投保5單位對無理賠關懷保險金的影響", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認保險單年度末生存者的定義與條件", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.994587, "neutral": 0.005115, "contradiction": 0.000298, "factuality": 0.999702, "C_fact": 0.999702}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J191" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K191" s="3" t="n">
+        <v>0.999702</v>
+      </c>
+      <c r="L191" s="3" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>2026-04-01 15:53:49</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/rag_results.xlsx
+++ b/src/rag_results.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N250"/>
+  <dimension ref="A1:N337"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -16953,6 +16953,5765 @@
         <v>14.39</v>
       </c>
     </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>保障範圍包括哪些項目？</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包含：住院醫療保險金、加護病房或燒燙傷病房保險金、祝壽保險金、身故保險金或喪葬費用保險金，以及所繳保險費的退還。
+條文依據：  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
+        <is>
+          <t>payout_items | summary | 第五條 保險範圍 | 第二條 名詞定義 | 第十八條 除外責任（一）</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F251" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包含：住院醫療保險金、加護病房或燒燙傷病房保險金、祝壽保險金、身故保險金或喪葬費用保險金，以及所繳保險費的退還。
+條文依據：  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="G251" s="2" t="inlineStr"/>
+      <c r="H251" s="2" t="inlineStr"/>
+      <c r="I251" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "保障範圍包括哪些項目？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J251" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K251" s="4" t="n"/>
+      <c r="L251" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>2026-04-01 16:15:40</t>
+        </is>
+      </c>
+      <c r="N251" s="4" t="n">
+        <v>34.51</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>因同一疾病或傷害再次住院、若間隔時間在出院後十四日內或因併發症導致的再次住院日數計算有什麼特殊規則？</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人因同一疾病或傷害，或因此引起的併發症，在出院後十四日內再次住院，則該次住院的保險金給付限制（第十二條至第十三條）將視為同一次住院處理。  
+條文依據：  
+- [第十一條 住院次數之計算及契約有效期間屆滿後住院之處理]</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第十三條 加護病房或燒燙傷病房保險金的給付 | 第二條 名詞定義 | 第十二條 住院醫療保險金的給付 | 第十八條 除外責任（一） | 第二十八條 住院醫療保險金日額之減少</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F252" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人因同一疾病或傷害，或因此引起的併發症，在出院後十四日內再次住院，則該次住院的保險金給付限制（第十二條至第十三條）將視為同一次住院處理。  
+條文依據：  
+- [第十一條 住院次數之計算及契約有效期間屆滿後住院之處理]</t>
+        </is>
+      </c>
+      <c r="G252" s="2" t="inlineStr"/>
+      <c r="H252" s="2" t="inlineStr"/>
+      <c r="I252" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認同一疾病或傷害再次住院的間隔時間規則", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認因併發症導致的再次住院日數計算方式", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認是否有十四日內再次住院的特殊規定", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J252" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K252" s="4" t="n"/>
+      <c r="L252" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>2026-04-01 16:16:02</t>
+        </is>
+      </c>
+      <c r="N252" s="4" t="n">
+        <v>21.31</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>住院醫療保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院醫療保險金的給付規定如下：  
+1. 被保險人於本契約有效期間內因疾病或傷害住院治療時，本公司將依保險單上記載的「住院醫療保險金日額」，乘以入院日當年度的「增額係數」，再乘以住院日數，給付「住院醫療保險金」。  
+2. 同一保單年度內，同一次住院的住院日數給付上限為365日。  
+條文依據：  
+- [第十二條 住院醫療保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 住院醫療保險金的給付 | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第十三條 加護病房或燒燙傷病房保險金的給付 | 第十四條 醫療保險金給付總額之上限 | 第二十八條 住院醫療保險金日額之減少</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F253" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院醫療保險金的給付規定如下：  
+1. 被保險人於本契約有效期間內因疾病或傷害住院治療時，本公司將依保險單上記載的「住院醫療保險金日額」，乘以入院日當年度的「增額係數」，再乘以住院日數，給付「住院醫療保險金」。  
+2. 同一保單年度內，同一次住院的住院日數給付上限為365日。  
+條文依據：  
+- [第十二條 住院醫療保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G253" s="2" t="inlineStr"/>
+      <c r="H253" s="2" t="inlineStr"/>
+      <c r="I253" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "住院醫療保險金的給付規定", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J253" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K253" s="4" t="n"/>
+      <c r="L253" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>2026-04-01 16:16:26</t>
+        </is>
+      </c>
+      <c r="N253" s="4" t="n">
+        <v>23.35</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>加護病房或燒燙傷病房保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+加護病房或燒燙傷病房保險金的給付規定如下：  
+1. 被保險人於本契約有效期間內因疾病或傷害住進醫院的加護病房或燒燙傷病房接受治療時，除住院醫療保險金外，保險公司將依保險單上記載的「住院醫療保險金日額」，乘以入院日當年度的「增額係數」，再乘以實際住進加護病房或燒燙傷病房的日數（含轉入及轉出當日）的二倍，給付「加護病房或燒燙傷病房保險金」。  
+2. 同一保單年度內，同一次住院的加護病房及燒燙傷病房住院日數合計給付上限為365日。  
+3. 同一日內，保險公司僅就加護病房或燒燙傷病房其中一種病房給付。
+條文依據：  
+- [第十三條 加護病房或燒燙傷病房保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 加護病房或燒燙傷病房保險金的給付 | payout_items | 第二十三條 醫療保險金的申領 | 第五條 保險範圍 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F254" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+加護病房或燒燙傷病房保險金的給付規定如下：  
+1. 被保險人於本契約有效期間內因疾病或傷害住進醫院的加護病房或燒燙傷病房接受治療時，除住院醫療保險金外，保險公司將依保險單上記載的「住院醫療保險金日額」，乘以入院日當年度的「增額係數」，再乘以實際住進加護病房或燒燙傷病房的日數（含轉入及轉出當日）的二倍，給付「加護病房或燒燙傷病房保險金」。  
+2. 同一保單年度內，同一次住院的加護病房及燒燙傷病房住院日數合計給付上限為365日。  
+3. 同一日內，保險公司僅就加護病房或燒燙傷病房其中一種病房給付。
+條文依據：  
+- [第十三條 加護病房或燒燙傷病房保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G254" s="2" t="inlineStr"/>
+      <c r="H254" s="2" t="inlineStr"/>
+      <c r="I254" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "加護病房或燒燙傷病房保險金的給付規定", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J254" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K254" s="4" t="n"/>
+      <c r="L254" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>2026-04-01 16:17:20</t>
+        </is>
+      </c>
+      <c r="N254" s="4" t="n">
+        <v>53.61</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>保障範圍包括哪些項目？</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括：住院醫療保險金、加護病房或燒燙傷病房保險金、祝壽保險金、身故保險金或喪葬費用保險金，以及所繳保險費的退還。
+條文依據：  
+- 摘要  
+- 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
+        <is>
+          <t>payout_items | summary | 第五條 保險範圍 | 第二條 名詞定義 | 第十八條 除外責任（一）</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F255" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括：住院醫療保險金、加護病房或燒燙傷病房保險金、祝壽保險金、身故保險金或喪葬費用保險金，以及所繳保險費的退還。
+條文依據：  
+- 摘要  
+- 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="G255" s="2" t="inlineStr"/>
+      <c r="H255" s="2" t="inlineStr"/>
+      <c r="I255" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "保障範圍包括哪些項目？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J255" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K255" s="4" t="n"/>
+      <c r="L255" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:12:08</t>
+        </is>
+      </c>
+      <c r="N255" s="4" t="n">
+        <v>20.97</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>因同一疾病或傷害再次住院、若間隔時間在出院後十四日內或因併發症導致的再次住院日數計算有什麼特殊規則？</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 同一疾病或傷害再次住院的間隔時間規定為：若被保險人於出院後十四日內因同一疾病或傷害，或因此引起之併發症再次住院，則視為同一次住院。  
+2. 出院後十四日內再次住院的日數計算規則為：該次住院的保險金給付限制，均視為同一次住院辦理。  
+3. 因併發症導致的再次住院，若發生於出院後十四日內，亦視為同一次住院，並適用相同的保險金給付限制規則。  
+4. 若被保險人於本契約有效期間屆滿後出院，則再次住院部分不予給付保險金。
+條文依據：  
+- [第十一條 住院次數之計算及契約有效期間屆滿後住院之處理]</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第十三條 加護病房或燒燙傷病房保險金的給付 | 第二條 名詞定義 | 第十二條 住院醫療保險金的給付 | 第十八條 除外責任（一） | 第二十八條 住院醫療保險金日額之減少</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F256" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 同一疾病或傷害再次住院的間隔時間規定為：若被保險人於出院後十四日內因同一疾病或傷害，或因此引起之併發症再次住院，則視為同一次住院。  
+2. 出院後十四日內再次住院的日數計算規則為：該次住院的保險金給付限制，均視為同一次住院辦理。  
+3. 因併發症導致的再次住院，若發生於出院後十四日內，亦視為同一次住院，並適用相同的保險金給付限制規則。  
+4. 若被保險人於本契約有效期間屆滿後出院，則再次住院部分不予給付保險金。
+條文依據：  
+- [第十一條 住院次數之計算及契約有效期間屆滿後住院之處理]</t>
+        </is>
+      </c>
+      <c r="G256" s="2" t="inlineStr"/>
+      <c r="H256" s="2" t="inlineStr"/>
+      <c r="I256" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認同一疾病或傷害再次住院的間隔時間規定", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認出院後十四日內再次住院的日數計算規則", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認因併發症導致再次住院的日數計算規則", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認是否有其他特殊規則適用於再次住院的情況", "must_have": false, "分數": 0.5}], "coverage_score": 0.9615, "C_conf": 0.9615}</t>
+        </is>
+      </c>
+      <c r="J256" s="4" t="n">
+        <v>0.9615</v>
+      </c>
+      <c r="K256" s="4" t="n"/>
+      <c r="L256" s="4" t="n">
+        <v>0.9615</v>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:12:24</t>
+        </is>
+      </c>
+      <c r="N256" s="4" t="n">
+        <v>15.37</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>住院醫療保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院醫療保險金的給付規定如下：  
+1. 被保險人於本契約有效期間內因疾病或傷害住院治療時，本公司將依保險單上記載的「住院醫療保險金日額」，乘以入院日當年度的「增額係數」，再乘以住院日數，給付「住院醫療保險金」。  
+2. 同一保單年度內，同一次住院的住院日數給付上限為365日。  
+條文依據：  
+- [第十二條 住院醫療保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 住院醫療保險金的給付 | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第十三條 加護病房或燒燙傷病房保險金的給付 | 第十四條 醫療保險金給付總額之上限 | 第二十八條 住院醫療保險金日額之減少</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F257" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院醫療保險金的給付規定如下：  
+1. 被保險人於本契約有效期間內因疾病或傷害住院治療時，本公司將依保險單上記載的「住院醫療保險金日額」，乘以入院日當年度的「增額係數」，再乘以住院日數，給付「住院醫療保險金」。  
+2. 同一保單年度內，同一次住院的住院日數給付上限為365日。  
+條文依據：  
+- [第十二條 住院醫療保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G257" s="2" t="inlineStr"/>
+      <c r="H257" s="2" t="inlineStr"/>
+      <c r="I257" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "住院醫療保險金的給付規定", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J257" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K257" s="4" t="n"/>
+      <c r="L257" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:12:30</t>
+        </is>
+      </c>
+      <c r="N257" s="4" t="n">
+        <v>6.33</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>加護病房或燒燙傷病房保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+加護病房或燒燙傷病房保險金的給付規定如下：  
+被保險人於本契約有效期間內因疾病或傷害而在醫院的加護病房或燒燙傷病房接受治療時，除住院醫療保險金外，保險公司將依保險單上記載的「住院醫療保險金日額」，乘以入院日當年度的「增額係數」，再乘以實際住進加護病房或燒燙傷病房的日數（含轉入及轉出當日）的二倍，給付「加護病房或燒燙傷病房保險金」。  
+同一保單年度內，同一次住院的加護病房及燒燙傷病房住院日數合計給付上限為365日，但同一日內僅給付其中一種病房的保險金。
+條文依據：  
+- [第十三條 加護病房或燒燙傷病房保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 加護病房或燒燙傷病房保險金的給付 | payout_items | 第二十三條 醫療保險金的申領 | 第五條 保險範圍 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F258" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+加護病房或燒燙傷病房保險金的給付規定如下：  
+被保險人於本契約有效期間內因疾病或傷害而在醫院的加護病房或燒燙傷病房接受治療時，除住院醫療保險金外，保險公司將依保險單上記載的「住院醫療保險金日額」，乘以入院日當年度的「增額係數」，再乘以實際住進加護病房或燒燙傷病房的日數（含轉入及轉出當日）的二倍，給付「加護病房或燒燙傷病房保險金」。  
+同一保單年度內，同一次住院的加護病房及燒燙傷病房住院日數合計給付上限為365日，但同一日內僅給付其中一種病房的保險金。
+條文依據：  
+- [第十三條 加護病房或燒燙傷病房保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G258" s="2" t="inlineStr"/>
+      <c r="H258" s="2" t="inlineStr"/>
+      <c r="I258" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "加護病房或燒燙傷病房保險金的給付規定", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J258" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K258" s="4" t="n"/>
+      <c r="L258" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:12:38</t>
+        </is>
+      </c>
+      <c r="N258" s="4" t="n">
+        <v>7.69</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>醫療保險金給付總額之上限</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+醫療保險金給付總額之上限為保險單上所記載之「住院醫療保險金日額」的二千五百倍。
+條文依據：  
+- [第十四條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 醫療保險金給付總額之上限 | 第十二條 住院醫療保險金的給付 | 第五條 保險範圍 | 第十三條 加護病房或燒燙傷病房保險金的給付 | payout_items</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F259" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+醫療保險金給付總額之上限為保險單上所記載之「住院醫療保險金日額」的二千五百倍。
+條文依據：  
+- [第十四條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="G259" s="2" t="inlineStr"/>
+      <c r="H259" s="2" t="inlineStr"/>
+      <c r="I259" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "醫療保險金給付總額之上限", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J259" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K259" s="4" t="n"/>
+      <c r="L259" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:12:45</t>
+        </is>
+      </c>
+      <c r="N259" s="4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>祝壽保險金的給付規定為何?</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+祝壽保險金的給付規定如下：  
+1. 被保險人需於本契約有效期間內，且保險年齡到達99歲之保險單週年日仍生存。  
+2. 本公司將按「當年度保險金額」給付祝壽保險金。
+條文依據：  
+- [第十五條 祝壽保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
+        <is>
+          <t>第十五條 祝壽保險金的給付 | 第十二條至第十三條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | 第二十四條 祝壽保險金的申領 | payout_items | 第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F260" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+祝壽保險金的給付規定如下：  
+1. 被保險人需於本契約有效期間內，且保險年齡到達99歲之保險單週年日仍生存。  
+2. 本公司將按「當年度保險金額」給付祝壽保險金。
+條文依據：  
+- [第十五條 祝壽保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G260" s="2" t="inlineStr"/>
+      <c r="H260" s="2" t="inlineStr"/>
+      <c r="I260" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "祝壽保險金的給付規定為何?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J260" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K260" s="4" t="n"/>
+      <c r="L260" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:12:51</t>
+        </is>
+      </c>
+      <c r="N260" s="4" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>有效期間內身故，保險金如何給付?</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於本契約有效期間內身故時，本公司依以下情況給付保險金：  
+1. 一般情況：按「當年度保險金額」給付「身故保險金」。  
+2. 若被保險人於繳費期間內身故，當期已繳付之未到期保險費不予退還，亦不併入身故保險金內給付。  
+3. 若被保險人於有效期間內且實際年齡未滿十五足歲身故，本公司退還「所繳保險費」，不適用上述規定。  
+4. 若被保險人為受監護宣告尚未撤銷者，其身故保險金變更為喪葬費用保險金，且喪葬費用保險金額不得超過遺產稅喪葬費扣除額之半數，超過部分不負給付責任，並退還超過部分之已繳保險費。
+條文依據：  
+- [第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D261" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付 | 第十條 契約的終止（二） | 第五條 保險範圍 | 第二十二條 失蹤處理 | 第十五條 祝壽保險金的給付</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F261" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於本契約有效期間內身故時，本公司依以下情況給付保險金：  
+1. 一般情況：按「當年度保險金額」給付「身故保險金」。  
+2. 若被保險人於繳費期間內身故，當期已繳付之未到期保險費不予退還，亦不併入身故保險金內給付。  
+3. 若被保險人於有效期間內且實際年齡未滿十五足歲身故，本公司退還「所繳保險費」，不適用上述規定。  
+4. 若被保險人為受監護宣告尚未撤銷者，其身故保險金變更為喪葬費用保險金，且喪葬費用保險金額不得超過遺產稅喪葬費扣除額之半數，超過部分不負給付責任，並退還超過部分之已繳保險費。
+條文依據：  
+- [第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G261" s="2" t="inlineStr"/>
+      <c r="H261" s="2" t="inlineStr"/>
+      <c r="I261" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "有效期間內身故，保險金如何給付?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J261" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K261" s="4" t="n"/>
+      <c r="L261" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:13:05</t>
+        </is>
+      </c>
+      <c r="N261" s="4" t="n">
+        <v>13.94</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>健康促進保險費折減規定</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+健康促進保險費折減規定如下：  
+1. 被保險人年齡需達20歲（含）以上，並使用保險公司指定程式加入健康計劃。  
+2. 若於「指定日期」會員等級符合標準，次一保險單年度保險費可依會員等級折減：  
+   - 進階會員：折減2%。  
+   - 菁英會員或更高等級：折減3%。  
+3. 折減僅適用於主契約保險費，不包含附約、附加條款或批註條款，且豁免或復效的保險費不適用折減。  
+4. 被保險人需完成程式註冊並授權保險公司取得健康相關電子紀錄，保險公司將依紀錄計算會員等級。
+條文依據：  
+- [第十七條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="inlineStr">
+        <is>
+          <t>第十七條 健康促進保險費折減 | 第二十八條 住院醫療保險金日額之減少 | 第三十條 投保年齡的計算及錯誤的處理 | 第二條 名詞定義 | 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F262" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+健康促進保險費折減規定如下：  
+1. 被保險人年齡需達20歲（含）以上，並使用保險公司指定程式加入健康計劃。  
+2. 若於「指定日期」會員等級符合標準，次一保險單年度保險費可依會員等級折減：  
+   - 進階會員：折減2%。  
+   - 菁英會員或更高等級：折減3%。  
+3. 折減僅適用於主契約保險費，不包含附約、附加條款或批註條款，且豁免或復效的保險費不適用折減。  
+4. 被保險人需完成程式註冊並授權保險公司取得健康相關電子紀錄，保險公司將依紀錄計算會員等級。
+條文依據：  
+- [第十七條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="G262" s="2" t="inlineStr"/>
+      <c r="H262" s="2" t="inlineStr"/>
+      <c r="I262" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "健康促進保險費折減規定", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J262" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K262" s="4" t="n"/>
+      <c r="L262" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:13:14</t>
+        </is>
+      </c>
+      <c r="N262" s="4" t="n">
+        <v>8.460000000000001</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>除外責任的解釋?</t>
+        </is>
+      </c>
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+除外責任是指保險公司對於某些特定原因或情況下所發生的疾病、傷害或死亡，不負給付保險金的責任。以下為條文中提及的主要除外責任範圍：  
+1. **疾病或傷害相關除外責任**：  
+   - 被保險人因故意行為（如自殺、自殺未遂）、犯罪行為或非法施用毒品所致的疾病或傷害。  
+   - 美容手術或外科整型（但為重建基本功能的必要整型不在此限）。  
+   - 健康檢查、療養、靜養等非直接診治病人的行為。  
+   - 懷孕、流產或分娩及其併發症（但特定情況如子宮外孕、葡萄胎等不在此限）。  
+2. **身故相關除外責任**：  
+   - 要保人故意致被保險人於死。  
+   - 被保險人故意自殺（但契約訂立或復效滿兩年後自殺不在此限）。  
+   - 被保險人因犯罪處死、拒捕或越獄致死。  
+條文依據：  
+- [第十八條 除外責任（一）]  
+- [第十九條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第十九條 除外責任（二） | 第八條 告知義務與本契約的解除 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F263" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+除外責任是指保險公司對於某些特定原因或情況下所發生的疾病、傷害或死亡，不負給付保險金的責任。以下為條文中提及的主要除外責任範圍：  
+1. **疾病或傷害相關除外責任**：  
+   - 被保險人因故意行為（如自殺、自殺未遂）、犯罪行為或非法施用毒品所致的疾病或傷害。  
+   - 美容手術或外科整型（但為重建基本功能的必要整型不在此限）。  
+   - 健康檢查、療養、靜養等非直接診治病人的行為。  
+   - 懷孕、流產或分娩及其併發症（但特定情況如子宮外孕、葡萄胎等不在此限）。  
+2. **身故相關除外責任**：  
+   - 要保人故意致被保險人於死。  
+   - 被保險人故意自殺（但契約訂立或復效滿兩年後自殺不在此限）。  
+   - 被保險人因犯罪處死、拒捕或越獄致死。  
+條文依據：  
+- [第十八條 除外責任（一）]  
+- [第十九條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="G263" s="2" t="inlineStr"/>
+      <c r="H263" s="2" t="inlineStr"/>
+      <c r="I263" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "除外責任的解釋?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J263" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K263" s="4" t="n"/>
+      <c r="L263" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:13:25</t>
+        </is>
+      </c>
+      <c r="N263" s="4" t="n">
+        <v>9.880000000000001</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>哪些疾病被含在除外責任?</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人因以下原因所致之疾病或傷害，屬於除外責任範圍，本公司不負給付保險金的責任：  
+1. 被保險人之故意行為（包括自殺及自殺未遂）。  
+2. 被保險人之犯罪行為。  
+3. 被保險人非法施用毒品。  
+4. 美容手術、外科整型（但為重建基本功能所作之必要整型不在此限）。  
+5. 外觀可見之天生畸形。  
+6. 健康檢查、療養、靜養、戒毒、戒酒、護理或養老等非以直接診治病人為目的者。  
+7. 懷孕、流產或分娩及其併發症（但特定懷孕相關疾病、醫療行為必要之流產及剖腹產情形不在此限）。  
+8. 不孕症、人工受孕或非以治療為目的之避孕及絕育手術。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第二條 名詞定義 | 第十九條 除外責任（二）</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F264" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人因以下原因所致之疾病或傷害，屬於除外責任範圍，本公司不負給付保險金的責任：  
+1. 被保險人之故意行為（包括自殺及自殺未遂）。  
+2. 被保險人之犯罪行為。  
+3. 被保險人非法施用毒品。  
+4. 美容手術、外科整型（但為重建基本功能所作之必要整型不在此限）。  
+5. 外觀可見之天生畸形。  
+6. 健康檢查、療養、靜養、戒毒、戒酒、護理或養老等非以直接診治病人為目的者。  
+7. 懷孕、流產或分娩及其併發症（但特定懷孕相關疾病、醫療行為必要之流產及剖腹產情形不在此限）。  
+8. 不孕症、人工受孕或非以治療為目的之避孕及絕育手術。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="G264" s="2" t="inlineStr"/>
+      <c r="H264" s="2" t="inlineStr"/>
+      <c r="I264" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "哪些疾病被含在除外責任?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J264" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K264" s="4" t="n"/>
+      <c r="L264" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:13:35</t>
+        </is>
+      </c>
+      <c r="N264" s="4" t="n">
+        <v>9.289999999999999</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>進行美容手術住院可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，因美容手術住院無法申請理賠。但若該美容手術是為了重建基本功能所作之必要整型，則不在此限，仍可申請理賠。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D265" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第十三條 加護病房或燒燙傷病房保險金的給付 | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第二條 名詞定義 | payout_items</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F265" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，因美容手術住院無法申請理賠。但若該美容手術是為了重建基本功能所作之必要整型，則不在此限，仍可申請理賠。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="G265" s="2" t="inlineStr"/>
+      <c r="H265" s="2" t="inlineStr"/>
+      <c r="I265" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "進行美容手術住院可以申請理賠嗎?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J265" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K265" s="4" t="n"/>
+      <c r="L265" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:13:41</t>
+        </is>
+      </c>
+      <c r="N265" s="4" t="n">
+        <v>6.35</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>因胎兒染色體異常進行手術而住院可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以申請理賠。根據條款，因胎兒染色體異常進行手術屬於懷孕相關疾病的例外情形，不在除外責任範圍內，因此符合理賠條件。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第二條 名詞定義 | payout_items | 第十三條 加護病房或燒燙傷病房保險金的給付</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F266" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以申請理賠。根據條款，因胎兒染色體異常進行手術屬於懷孕相關疾病的例外情形，不在除外責任範圍內，因此符合理賠條件。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="G266" s="2" t="inlineStr"/>
+      <c r="H266" s="2" t="inlineStr"/>
+      <c r="I266" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "因胎兒染色體異常進行手術而住院可以申請理賠嗎?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J266" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K266" s="4" t="n"/>
+      <c r="L266" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:13:49</t>
+        </is>
+      </c>
+      <c r="N266" s="4" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>因胎位不正進行手術而住院可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，因胎位不正進行手術而住院屬於除外責任範圍，但若該手術為醫療行為必要之剖腹產，且符合條款中列明的情況（如胎位不正），則不在除外責任之列，可申請理賠。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第二條 名詞定義 | payout_items | 第十三條 加護病房或燒燙傷病房保險金的給付</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F267" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，因胎位不正進行手術而住院屬於除外責任範圍，但若該手術為醫療行為必要之剖腹產，且符合條款中列明的情況（如胎位不正），則不在除外責任之列，可申請理賠。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="G267" s="2" t="inlineStr"/>
+      <c r="H267" s="2" t="inlineStr"/>
+      <c r="I267" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "因胎位不正進行手術而住院可以申請理賠嗎?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J267" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K267" s="4" t="n"/>
+      <c r="L267" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:14:00</t>
+        </is>
+      </c>
+      <c r="N267" s="4" t="n">
+        <v>10.76</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>因自殺未遂導致住院可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人因自殺未遂導致住院，本公司不負給付住院相關保險金的責任，因其屬於被保險人之故意行為。  
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 除外責任（二） | 第十八條 除外責任（一） | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | payout_items | 第十條 契約的終止（二）</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F268" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人因自殺未遂導致住院，本公司不負給付住院相關保險金的責任，因其屬於被保險人之故意行為。  
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="G268" s="2" t="inlineStr"/>
+      <c r="H268" s="2" t="inlineStr"/>
+      <c r="I268" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "因自殺未遂導致住院可以申請理賠嗎?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J268" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K268" s="4" t="n"/>
+      <c r="L268" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:14:07</t>
+        </is>
+      </c>
+      <c r="N268" s="4" t="n">
+        <v>6.77</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>被保險人在投保一年內故意自殺者，可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人在投保一年內故意自殺者，保險公司不負給付身故保險金或喪葬費用保險金的責任。只有在契約訂立或復效之日起滿二年後，故意自殺致死的情況下，保險公司才會負給付責任。
+條文依據：  
+- [第十九條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="D269" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 除外責任（二） | 第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付 | 第十條 契約的終止（二） | 第三十條 投保年齡的計算及錯誤的處理 | 第十八條 除外責任（一）</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F269" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人在投保一年內故意自殺者，保險公司不負給付身故保險金或喪葬費用保險金的責任。只有在契約訂立或復效之日起滿二年後，故意自殺致死的情況下，保險公司才會負給付責任。
+條文依據：  
+- [第十九條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="G269" s="2" t="inlineStr"/>
+      <c r="H269" s="2" t="inlineStr"/>
+      <c r="I269" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "被保險人在投保一年內故意自殺者，可以申請理賠嗎?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J269" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K269" s="4" t="n"/>
+      <c r="L269" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:14:16</t>
+        </is>
+      </c>
+      <c r="N269" s="4" t="n">
+        <v>8.699999999999999</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>申請理賠有什麼時間規定嗎?</t>
+        </is>
+      </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申請理賠的時間規定如下：要保人、被保險人或受益人應於知悉保險事故後十日內通知保險公司，並儘速檢具所需文件申請保險金。保險公司應於收到完整文件後十五日內給付保險金。如因保險公司可歸責的原因未能在期限內給付，應按年利一分加計利息給付。
+條文依據：  
+- [第二十一條 保險事故的通知與保險金的申請時間]</t>
+        </is>
+      </c>
+      <c r="D270" s="2" t="inlineStr">
+        <is>
+          <t>第二十一條 保險事故的通知與保險金的申請時間 | 第六條 第二期以後保險費的交付、寬限期間及契約效力的停止 | 第七條 本契約效力的恢復 | 第三條 契約撤銷權 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F270" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申請理賠的時間規定如下：要保人、被保險人或受益人應於知悉保險事故後十日內通知保險公司，並儘速檢具所需文件申請保險金。保險公司應於收到完整文件後十五日內給付保險金。如因保險公司可歸責的原因未能在期限內給付，應按年利一分加計利息給付。
+條文依據：  
+- [第二十一條 保險事故的通知與保險金的申請時間]</t>
+        </is>
+      </c>
+      <c r="G270" s="2" t="inlineStr"/>
+      <c r="H270" s="2" t="inlineStr"/>
+      <c r="I270" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "申請理賠有什麼時間規定嗎?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J270" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K270" s="4" t="n"/>
+      <c r="L270" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:14:24</t>
+        </is>
+      </c>
+      <c r="N270" s="4" t="n">
+        <v>8.119999999999999</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>燒燙傷病房保險金怎麼申領?</t>
+        </is>
+      </c>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申領燒燙傷病房保險金時，受益人需檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 醫療診斷書或住院證明，且需列明進、出燒燙傷病房的日期。（但若要保人或被保險人為醫師時，不得為被保險人出具診斷書或住院證明。）  
+4. 受益人的身分證明。  
+此外，保險公司可基於審核需要，徵詢其他醫師的專業意見，並經受益人同意調閱被保險人的就醫相關資料，相關費用由保險公司負擔。
+條文依據：  
+- [第二十三條 醫療保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D271" s="2" t="inlineStr">
+        <is>
+          <t>第二十三條 醫療保險金的申領 | 第十三條 加護病房或燒燙傷病房保險金的給付 | payout_items | 第二條 名詞定義 | 第二十一條 保險事故的通知與保險金的申請時間</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F271" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申領燒燙傷病房保險金時，受益人需檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 醫療診斷書或住院證明，且需列明進、出燒燙傷病房的日期。（但若要保人或被保險人為醫師時，不得為被保險人出具診斷書或住院證明。）  
+4. 受益人的身分證明。  
+此外，保險公司可基於審核需要，徵詢其他醫師的專業意見，並經受益人同意調閱被保險人的就醫相關資料，相關費用由保險公司負擔。
+條文依據：  
+- [第二十三條 醫療保險金的申領]</t>
+        </is>
+      </c>
+      <c r="G271" s="2" t="inlineStr"/>
+      <c r="H271" s="2" t="inlineStr"/>
+      <c r="I271" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "燒燙傷病房保險金怎麼申領?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J271" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K271" s="4" t="n"/>
+      <c r="L271" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:14:32</t>
+        </is>
+      </c>
+      <c r="N271" s="4" t="n">
+        <v>7.64</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="inlineStr">
+        <is>
+          <t>活到99歲怎麼申請祝壽金?</t>
+        </is>
+      </c>
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申請祝壽保險金時，受益人需檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 受益人的身分證明。  
+條文依據：  
+- [第二十四條 祝壽保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D272" s="2" t="inlineStr">
+        <is>
+          <t>第十五條 祝壽保險金的給付 | 第二十四條 祝壽保險金的申領 | 第五條 保險範圍 | 第十二條至第十三條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | announcement_history</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F272" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申請祝壽保險金時，受益人需檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 受益人的身分證明。  
+條文依據：  
+- [第二十四條 祝壽保險金的申領]</t>
+        </is>
+      </c>
+      <c r="G272" s="2" t="inlineStr"/>
+      <c r="H272" s="2" t="inlineStr"/>
+      <c r="I272" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "活到99歲怎麼申請祝壽金?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J272" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K272" s="4" t="n"/>
+      <c r="L272" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:14:40</t>
+        </is>
+      </c>
+      <c r="N272" s="4" t="n">
+        <v>8.09</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="inlineStr">
+        <is>
+          <t>被保人身故怎麼申請理賠</t>
+        </is>
+      </c>
+      <c r="C273" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+受益人申請「身故保險金」或「喪葬費用保險金」時，需檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 被保險人死亡證明書及除戶戶籍謄本。  
+4. 受益人的身分證明。  
+條文依據：  
+- [第二十五條 身故保險金或喪葬費用保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D273" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付 | 第十二條至第十三條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | 第二十二條 失蹤處理 | 第二十五條 身故保險金或喪葬費用保險金的申領 | 第十九條 除外責任（二）</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F273" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+受益人申請「身故保險金」或「喪葬費用保險金」時，需檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 被保險人死亡證明書及除戶戶籍謄本。  
+4. 受益人的身分證明。  
+條文依據：  
+- [第二十五條 身故保險金或喪葬費用保險金的申領]</t>
+        </is>
+      </c>
+      <c r="G273" s="2" t="inlineStr"/>
+      <c r="H273" s="2" t="inlineStr"/>
+      <c r="I273" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "被保人身故怎麼申請理賠", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J273" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K273" s="4" t="n"/>
+      <c r="L273" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:14:48</t>
+        </is>
+      </c>
+      <c r="N273" s="4" t="n">
+        <v>7.44</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <t>投保15年後，增額係數為多少？因手術住院3天，住院日額為2500元，請問可以申請多少理賠?</t>
+        </is>
+      </c>
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 投保15年後的增額係數為1.05。  
+2. 理賠金額計算方式為：住院日額（2500元）× 增額係數（1.05）× 住院天數（3天）。計算結果為2500 × 1.05 × 3 = 7875元。  
+3. 手術住院3天的理賠天數即為3天，無額外扣減或限制。  
+4. 條文中未提及其他影響理賠金額的條件或限制，因此不影響上述計算結果。  
+條文依據：  
+- [附表：增額係數表]  
+- [第十二條 住院醫療保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D274" s="2" t="inlineStr">
+        <is>
+          <t>附表：增額係數表 | 第十二條 住院醫療保險金的給付 | 第十三條 加護病房或燒燙傷病房保險金的給付 | 第二十八條 住院醫療保險金日額之減少 | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第三十條 投保年齡的計算及錯誤的處理 | payout_items | 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F274" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 投保15年後的增額係數為1.05。  
+2. 理賠金額計算方式為：住院日額（2500元）× 增額係數（1.05）× 住院天數（3天）。計算結果為2500 × 1.05 × 3 = 7875元。  
+3. 手術住院3天的理賠天數即為3天，無額外扣減或限制。  
+4. 條文中未提及其他影響理賠金額的條件或限制，因此不影響上述計算結果。  
+條文依據：  
+- [附表：增額係數表]  
+- [第十二條 住院醫療保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G274" s="2" t="inlineStr"/>
+      <c r="H274" s="2" t="inlineStr"/>
+      <c r="I274" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認投保15年後的增額係數", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認住院日額為2500元的理賠計算方式", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認手術住院3天的理賠天數計算", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認是否有其他影響理賠金額的條件或限制", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J274" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K274" s="4" t="n"/>
+      <c r="L274" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:15:04</t>
+        </is>
+      </c>
+      <c r="N274" s="4" t="n">
+        <v>15.57</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B275" s="2" t="inlineStr">
+        <is>
+          <t>保障範圍包括哪些項目？</t>
+        </is>
+      </c>
+      <c r="C275" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括：住院手術醫療保險金、門診手術醫療保險金、特定處置保險金、意外創傷縫合處置保險金、意外住院手術醫療保險金、祝壽保險金、所繳保險費的退還、身故保險金或喪葬費用保險金。
+條文依據：  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="D275" s="2" t="inlineStr">
+        <is>
+          <t>payout_items | 第五條 保險範圍 | summary | 第四條 名詞定義 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F275" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括：住院手術醫療保險金、門診手術醫療保險金、特定處置保險金、意外創傷縫合處置保險金、意外住院手術醫療保險金、祝壽保險金、所繳保險費的退還、身故保險金或喪葬費用保險金。
+條文依據：  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="G275" s="2" t="inlineStr"/>
+      <c r="H275" s="2" t="inlineStr"/>
+      <c r="I275" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "保障範圍包括哪些項目？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J275" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K275" s="4" t="n"/>
+      <c r="L275" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:15:09</t>
+        </is>
+      </c>
+      <c r="N275" s="4" t="n">
+        <v>5.51</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B276" s="2" t="inlineStr">
+        <is>
+          <t>保險金額是否有上限?</t>
+        </is>
+      </c>
+      <c r="C276" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+有，保險金額的給付總額上限為保險單上所記載「保險金額」的一千五百倍，且不包含其他附約、附加條款或批註條款。
+條文依據：  
+- [第十六條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="D276" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 醫療保險金給付總額之上限 | 第三十條 保險金額之減少 | 第五條 保險範圍 | 第十九條 健康促進保險費折減 | 第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F276" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+有，保險金額的給付總額上限為保險單上所記載「保險金額」的一千五百倍，且不包含其他附約、附加條款或批註條款。
+條文依據：  
+- [第十六條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="G276" s="2" t="inlineStr"/>
+      <c r="H276" s="2" t="inlineStr"/>
+      <c r="I276" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "保險金額是否有上限?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J276" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K276" s="4" t="n"/>
+      <c r="L276" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:15:22</t>
+        </is>
+      </c>
+      <c r="N276" s="4" t="n">
+        <v>12.67</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B277" s="2" t="inlineStr">
+        <is>
+          <t>投保後5天發生手術，是否可以申請理賠?</t>
+        </is>
+      </c>
+      <c r="C277" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款，手術是否可以申請理賠需符合以下條件：  
+1. 被保險人需於保險契約有效期間內接受手術治療，且手術項目需符合附表一所列之手術項目或經協議比照附表一程度相當的手術項目。[第十一條 住院手術醫療保險金][第十二條 門診手術醫療保險金]  
+2. 若手術屬於除外責任條款所列情形之一，則不予理賠。[第二十條 除外責任（一)]  
+3. 若手術因疾病引起，需注意等待期間規定：疾病需自契約生效日起持續有效第三十一日後發生，方可申請理賠。[第四條 名詞定義]  
+因此，若投保後5天發生手術，需確認手術原因是否屬疾病或傷害：  
+- 若因疾病引起，則因未滿等待期間，無法申請理賠。  
+- 若因傷害引起，且符合其他條件，則可申請理賠。  
+條文依據：  
+[第十一條 住院手術醫療保險金]  
+[第十二條 門診手術醫療保險金]  
+[第二十條 除外責任（一)]  
+[第四條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D277" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第十一條 住院手術醫療保險金 | 第二十條 除外責任（一） | 第十二條 門診手術醫療保險金 | 第十三條 意外住院手術醫療保險金 | 第二十三條 保險事故的通知與保險金的申請時間 | 第四條 名詞定義 | 第十五條 意外創傷縫合處置保險金 | 附表三：意外創傷縫合處置項目及給付倍數表 | 附表一：手術項目與給付倍數 | payout_items</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F277" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+找不到相關內容  
+條文依據：  
+找不到相關內容</t>
+        </is>
+      </c>
+      <c r="G277" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款，手術是否可以申請理賠需符合以下條件：  
+1. 被保險人需於保險契約有效期間內接受手術治療，且手術項目需符合附表一所列之手術項目或經協議比照附表一程度相當的手術項目。[第十一條 住院手術醫療保險金][第十二條 門診手術醫療保險金]  
+2. 若手術屬於除外責任條款所列情形之一，則不予理賠。[第二十條 除外責任（一)]  
+3. 若手術因疾病引起，需注意等待期間規定：疾病需自契約生效日起持續有效第三十一日後發生，方可申請理賠。[第四條 名詞定義]  
+因此，若投保後5天發生手術，需確認手術原因是否屬疾病或傷害：  
+- 若因疾病引起，則因未滿等待期間，無法申請理賠。  
+- 若因傷害引起，且符合其他條件，則可申請理賠。  
+條文依據：  
+[第十一條 住院手術醫療保險金]  
+[第十二條 門診手術醫療保險金]  
+[第二十條 除外責任（一)]  
+[第四條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="H277" s="2" t="inlineStr"/>
+      <c r="I277" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "投保後5天發生手術，是否可以申請理賠?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J277" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K277" s="4" t="n"/>
+      <c r="L277" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:15:49</t>
+        </is>
+      </c>
+      <c r="N277" s="4" t="n">
+        <v>26.66</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B278" s="2" t="inlineStr">
+        <is>
+          <t>住院手術醫療保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C278" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院手術醫療保險金的給付規定如下：  
+1. 被保險人需於保險契約有效期間內，因疾病或傷害經醫師診斷必須住院接受附表一所列的手術治療，且已實際接受手術。  
+2. 給付金額計算方式為：保險單所記載的「保險金額」乘以手術日當年度的「增額係數」，再乘以手術給付倍數。  
+3. 若同一次手術中於同一手術位置接受兩項以上手術項目，僅給付手術給付倍數最高的手術項目。  
+4. 未載明於附表一的手術項目，將與被保險人協議比照附表內程度相當的手術項目，決定給付倍數。  
+5. 以下情形不予給付：  
+   - 屬於除外責任條款規定的情形。  
+   - 不屬於全民健康保險醫療服務給付項目及支付標準第二部第二章第七節或第三部第三章第四節第三項所列舉的手術。  
+條文依據：  
+- [第十一條 住院手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="D278" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 住院手術醫療保險金 | 第十三條 意外住院手術醫療保險金 | 第十二條 門診手術醫療保險金 | payout_items | 第二十條 除外責任（一） | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F278" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院手術醫療保險金的給付規定如下：  
+1. 被保險人需於保險契約有效期間內，因疾病或傷害經醫師診斷必須住院接受附表一所列的手術治療，且已實際接受手術。  
+2. 給付金額計算方式為：保險單所記載的「保險金額」乘以手術日當年度的「增額係數」，再乘以手術給付倍數。  
+3. 若同一次手術中於同一手術位置接受兩項以上手術項目，僅給付手術給付倍數最高的手術項目。  
+4. 未載明於附表一的手術項目，將與被保險人協議比照附表內程度相當的手術項目，決定給付倍數。  
+5. 以下情形不予給付：  
+   - 屬於除外責任條款規定的情形。  
+   - 不屬於全民健康保險醫療服務給付項目及支付標準第二部第二章第七節或第三部第三章第四節第三項所列舉的手術。  
+條文依據：  
+- [第十一條 住院手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="G278" s="2" t="inlineStr"/>
+      <c r="H278" s="2" t="inlineStr"/>
+      <c r="I278" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "住院手術醫療保險金的給付規定", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J278" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K278" s="4" t="n"/>
+      <c r="L278" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:15:58</t>
+        </is>
+      </c>
+      <c r="N278" s="4" t="n">
+        <v>8.880000000000001</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B279" s="2" t="inlineStr">
+        <is>
+          <t>門診手術醫療保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C279" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+門診手術醫療保險金的給付規定如下：  
+1. 被保險人需於本契約有效期間內，因疾病或傷害經醫師診斷必須於醫院或診所門診接受附表一所列的手術治療，且已實際接受手術。  
+2. 給付金額計算方式為：保險單上所記載的「保險金額」乘以手術日當年度的「增額係數」，再乘以手術給付倍數。  
+3. 同一次手術中，若於同一手術位置接受兩項以上手術項目，僅給付手術給付倍數最高的手術項目。  
+4. 同一保險單年度內，門診手術醫療保險金的給付以十次為限。  
+5. 若手術項目未載明於附表一，本公司將與被保險人協議比照附表內的手術項目決定給付倍數。  
+6. 以下情形不予給付：  
+   - 屬於本契約除外責任條款規定的項目。  
+   - 不屬於全民健康保險醫療服務給付項目及支付標準第二部第二章第七節或第三部第三章第四節第三項所列舉的手術。  
+條文依據：  
+- [第十二條 門診手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="D279" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 門診手術醫療保險金 | 第十一條 住院手術醫療保險金 | payout_items | 第十三條 意外住院手術醫療保險金 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F279" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+門診手術醫療保險金的給付規定如下：  
+1. 被保險人需於本契約有效期間內，因疾病或傷害經醫師診斷必須於醫院或診所門診接受附表一所列的手術治療，且已實際接受手術。  
+2. 給付金額計算方式為：保險單上所記載的「保險金額」乘以手術日當年度的「增額係數」，再乘以手術給付倍數。  
+3. 同一次手術中，若於同一手術位置接受兩項以上手術項目，僅給付手術給付倍數最高的手術項目。  
+4. 同一保險單年度內，門診手術醫療保險金的給付以十次為限。  
+5. 若手術項目未載明於附表一，本公司將與被保險人協議比照附表內的手術項目決定給付倍數。  
+6. 以下情形不予給付：  
+   - 屬於本契約除外責任條款規定的項目。  
+   - 不屬於全民健康保險醫療服務給付項目及支付標準第二部第二章第七節或第三部第三章第四節第三項所列舉的手術。  
+條文依據：  
+- [第十二條 門診手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="G279" s="2" t="inlineStr"/>
+      <c r="H279" s="2" t="inlineStr"/>
+      <c r="I279" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "門診手術醫療保險金的給付規定", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J279" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K279" s="4" t="n"/>
+      <c r="L279" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:16:08</t>
+        </is>
+      </c>
+      <c r="N279" s="4" t="n">
+        <v>10.1</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B280" s="2" t="inlineStr">
+        <is>
+          <t>意外住院手術醫療保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C280" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外住院手術醫療保險金的給付規定如下：  
+1. 被保險人需於本契約有效期間內，且保險年齡未滿七十歲。  
+2. 因傷害經醫師診斷，在住院期間必須接受手術治療且已實際接受手術者。  
+3. 給付金額為保險單所記載之「保險金額」的三倍，乘以手術日當年度之「增額係數」。  
+4. 同一次手術中，於同一手術位置接受二項以上手術項目時，僅給付一次意外住院手術醫療保險金。
+條文依據：  
+- [第十三條 意外住院手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="D280" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 意外住院手術醫療保險金 | 第十一條 住院手術醫療保險金 | 第十五條 意外創傷縫合處置保險金 | 第二十條 除外責任（一） | 第十二條 門診手術醫療保險金 | 附表三：意外創傷縫合處置項目及給付倍數表 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F280" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外住院手術醫療保險金的給付規定如下：  
+1. 被保險人需於本契約有效期間內，且保險年齡未滿七十歲。  
+2. 因傷害經醫師診斷，在住院期間必須接受手術治療且已實際接受手術者。  
+3. 給付金額為保險單所記載之「保險金額」的三倍，乘以手術日當年度之「增額係數」。  
+4. 同一次手術中，於同一手術位置接受二項以上手術項目時，僅給付一次意外住院手術醫療保險金。
+條文依據：  
+- [第十三條 意外住院手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="G280" s="2" t="inlineStr"/>
+      <c r="H280" s="2" t="inlineStr"/>
+      <c r="I280" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "意外住院手術醫療保險金的給付規定", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J280" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K280" s="4" t="n"/>
+      <c r="L280" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:16:15</t>
+        </is>
+      </c>
+      <c r="N280" s="4" t="n">
+        <v>6.52</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B281" s="2" t="inlineStr">
+        <is>
+          <t>特定處置保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C281" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+特定處置保險金的給付規定如下：  
+1. 被保險人於保險有效期間內，因疾病或傷害經醫師診斷需接受附表二所列的特定處置治療，且已完成處置者，保險公司將依保險單所載「保險金額」，乘以特定處置日當年度的「增額係數」，再乘以特定處置給付倍數，給付特定處置保險金。  
+2. 同一次處置治療中，若於同一治療位置接受兩項以上特定處置項目，僅給付特定處置給付倍數最高的項目。  
+3. 若接受的處置未列於附表二，保險公司不負給付責任。  
+4. 同一保險單年度內，特定處置保險金的給付次數以十次為限。
+條文依據：  
+- [第十四條 特定處置保險金]</t>
+        </is>
+      </c>
+      <c r="D281" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 特定處置保險金 | 第十五條 意外創傷縫合處置保險金 | 附表二：特定處置項目及給付倍數表 | 第五條 保險範圍 | 附表三：意外創傷縫合處置項目及給付倍數表</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F281" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+特定處置保險金的給付規定如下：  
+1. 被保險人於保險有效期間內，因疾病或傷害經醫師診斷需接受附表二所列的特定處置治療，且已完成處置者，保險公司將依保險單所載「保險金額」，乘以特定處置日當年度的「增額係數」，再乘以特定處置給付倍數，給付特定處置保險金。  
+2. 同一次處置治療中，若於同一治療位置接受兩項以上特定處置項目，僅給付特定處置給付倍數最高的項目。  
+3. 若接受的處置未列於附表二，保險公司不負給付責任。  
+4. 同一保險單年度內，特定處置保險金的給付次數以十次為限。
+條文依據：  
+- [第十四條 特定處置保險金]</t>
+        </is>
+      </c>
+      <c r="G281" s="2" t="inlineStr"/>
+      <c r="H281" s="2" t="inlineStr"/>
+      <c r="I281" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "特定處置保險金的給付規定", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J281" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K281" s="4" t="n"/>
+      <c r="L281" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:16:23</t>
+        </is>
+      </c>
+      <c r="N281" s="4" t="n">
+        <v>8.449999999999999</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B282" s="2" t="inlineStr">
+        <is>
+          <t>意外創傷縫合處置保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C282" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外創傷縫合處置保險金的給付規定如下：  
+1. 被保險人因意外傷害事故，於醫院或診所接受附表三所列的意外創傷縫合處置治療者，本公司將依保險單所記載的「保險金額」，乘以當年度的「增額係數」及「意外創傷縫合處置給付倍數」計算給付金額。  
+2. 同一次意外傷害事故中，本公司僅就傷口最大者給付，且僅給付一次。  
+3. 若被保險人因同一意外傷害事故已申領「住院手術醫療保險金」或「門診手術醫療保險金」，則不再給付「意外創傷縫合處置保險金」。  
+條文依據：  
+- [第十五條 意外創傷縫合處置保險金]</t>
+        </is>
+      </c>
+      <c r="D282" s="2" t="inlineStr">
+        <is>
+          <t>第十五條 意外創傷縫合處置保險金 | 附表三：意外創傷縫合處置項目及給付倍數表 | 第十四條 特定處置保險金 | 第二十條 除外責任（一） | 第十三條 意外住院手術醫療保險金 | 附表二：特定處置項目及給付倍數表</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F282" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外創傷縫合處置保險金的給付規定如下：  
+1. 被保險人因意外傷害事故，於醫院或診所接受附表三所列的意外創傷縫合處置治療者，本公司將依保險單所記載的「保險金額」，乘以當年度的「增額係數」及「意外創傷縫合處置給付倍數」計算給付金額。  
+2. 同一次意外傷害事故中，本公司僅就傷口最大者給付，且僅給付一次。  
+3. 若被保險人因同一意外傷害事故已申領「住院手術醫療保險金」或「門診手術醫療保險金」，則不再給付「意外創傷縫合處置保險金」。  
+條文依據：  
+- [第十五條 意外創傷縫合處置保險金]</t>
+        </is>
+      </c>
+      <c r="G282" s="2" t="inlineStr"/>
+      <c r="H282" s="2" t="inlineStr"/>
+      <c r="I282" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "意外創傷縫合處置保險金的給付規定", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J282" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K282" s="4" t="n"/>
+      <c r="L282" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:16:30</t>
+        </is>
+      </c>
+      <c r="N282" s="4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B283" s="2" t="inlineStr">
+        <is>
+          <t>醫療保險金給付總額之上限</t>
+        </is>
+      </c>
+      <c r="C283" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+醫療保險金給付總額之上限為保險單上所記載「保險金額」的一千五百倍，此上限僅適用於本契約有效期間內，且不包含其他附約、附加條款或批註條款的金額。
+條文依據：  
+- [第十六條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="D283" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 醫療保險金給付總額之上限 | 第十二條 門診手術醫療保險金 | 第五條 保險範圍 | 第十一條 住院手術醫療保險金 | 第十三條 意外住院手術醫療保險金 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F283" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+醫療保險金給付總額之上限為保險單上所記載「保險金額」的一千五百倍，此上限僅適用於本契約有效期間內，且不包含其他附約、附加條款或批註條款的金額。
+條文依據：  
+- [第十六條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="G283" s="2" t="inlineStr"/>
+      <c r="H283" s="2" t="inlineStr"/>
+      <c r="I283" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "醫療保險金給付總額之上限", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J283" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K283" s="4" t="n"/>
+      <c r="L283" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:16:38</t>
+        </is>
+      </c>
+      <c r="N283" s="4" t="n">
+        <v>8.07</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B284" s="2" t="inlineStr">
+        <is>
+          <t>祝壽保險金的領取規定為何?金額多少？</t>
+        </is>
+      </c>
+      <c r="C284" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+祝壽保險金的領取規定如下：  
+1. 被保險人需於本契約有效期間內，且保險年齡到達99歲之保險單週年日仍生存。  
+2. 金額為「當年度保險金額」。  
+條文依據：  
+- [第十七條 祝壽保險金]</t>
+        </is>
+      </c>
+      <c r="D284" s="2" t="inlineStr">
+        <is>
+          <t>第十七條 祝壽保險金 | 第二十六條 祝壽保險金的申領 | 第十一條至第十五條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | 第五條 保險範圍 | 第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F284" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+祝壽保險金的領取規定如下：  
+1. 被保險人需於本契約有效期間內，且保險年齡到達99歲之保險單週年日仍生存。  
+2. 金額為「當年度保險金額」。  
+條文依據：  
+- [第十七條 祝壽保險金]</t>
+        </is>
+      </c>
+      <c r="G284" s="2" t="inlineStr"/>
+      <c r="H284" s="2" t="inlineStr"/>
+      <c r="I284" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "祝壽保險金的領取規定為何?金額多少？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J284" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K284" s="4" t="n"/>
+      <c r="L284" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:16:45</t>
+        </is>
+      </c>
+      <c r="N284" s="4" t="n">
+        <v>6.61</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B285" s="2" t="inlineStr">
+        <is>
+          <t>身故時領取保險金有什麼規則?</t>
+        </is>
+      </c>
+      <c r="C285" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+身故時領取保險金的規則如下：  
+1. **一般規則**：被保險人於本契約有效期間內身故，本公司按「當年度保險金額」給付「身故保險金」。  
+2. **未滿十五足歲規則**：若被保險人於有效期間內且實際年齡未滿十五足歲身故，本公司僅退還「所繳保險費」，不適用一般規則。  
+3. **受監護宣告者**：若被保險人於訂立契約時受監護宣告且尚未撤銷，其身故保險金改為喪葬費用保險金，並受相關金額上限規範。  
+4. **喪葬費用保險金上限**：民國99年2月3日（含）以後投保的喪葬費用保險金總和不得超過遺產稅喪葬費扣除額之半數，超過部分不予給付，並退還已繳保險費。  
+5. **除外責任**：若身故原因屬於要保人故意致死、被保險人故意自殺（契約訂立或復效後兩年內）、犯罪處死、拒捕或越獄致死等情形，本公司不負給付責任。未滿十五足歲者因上述原因身故，僅退還所繳保險費。  
+條文依據：  
+- [第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金]  
+- [第二十一條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="D285" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金 | 第二十七條 身故保險金或喪葬費用保險金的申領 | 第十一條至第十五條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | 第二十一條 除外責任（二） | 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F285" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+身故時領取保險金的規則如下：  
+1. **一般規則**：被保險人於本契約有效期間內身故，本公司按「當年度保險金額」給付「身故保險金」。  
+2. **未滿十五足歲規則**：若被保險人於有效期間內且實際年齡未滿十五足歲身故，本公司僅退還「所繳保險費」，不適用一般規則。  
+3. **受監護宣告者**：若被保險人於訂立契約時受監護宣告且尚未撤銷，其身故保險金改為喪葬費用保險金，並受相關金額上限規範。  
+4. **喪葬費用保險金上限**：民國99年2月3日（含）以後投保的喪葬費用保險金總和不得超過遺產稅喪葬費扣除額之半數，超過部分不予給付，並退還已繳保險費。  
+5. **除外責任**：若身故原因屬於要保人故意致死、被保險人故意自殺（契約訂立或復效後兩年內）、犯罪處死、拒捕或越獄致死等情形，本公司不負給付責任。未滿十五足歲者因上述原因身故，僅退還所繳保險費。  
+條文依據：  
+- [第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金]  
+- [第二十一條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="G285" s="2" t="inlineStr"/>
+      <c r="H285" s="2" t="inlineStr"/>
+      <c r="I285" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "身故時領取保險金有什麼規則?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J285" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K285" s="4" t="n"/>
+      <c r="L285" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:16:57</t>
+        </is>
+      </c>
+      <c r="N285" s="4" t="n">
+        <v>11.82</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B286" s="2" t="inlineStr">
+        <is>
+          <t>什麼情況下可以保費折減?</t>
+        </is>
+      </c>
+      <c r="C286" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人年齡滿20歲（含）以上，並使用保險公司指定的程式加入健康計劃，於「指定日期」達到符合會員等級標準（進階會員或菁英會員等級）時，可享次一保險單年度的保費折減。折減比例為進階會員2%，菁英會員或更高等級3%。但豁免或復效的保險費不適用此折減規定。此外，被保險人需完成程式註冊並授權保險公司取得健康相關電子紀錄，保險公司將依此計算會員等級。
+條文依據：  
+- [第十九條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="D286" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 健康促進保險費折減 | 第三十條 保險金額之減少 | 第二十條 除外責任（一） | 第三十一條 投保年齡的計算及錯誤的處理 | 第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F286" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人年齡滿20歲（含）以上，並使用保險公司指定的程式加入健康計劃，於「指定日期」達到符合會員等級標準（進階會員或菁英會員等級）時，可享次一保險單年度的保費折減。折減比例為進階會員2%，菁英會員或更高等級3%。但豁免或復效的保險費不適用此折減規定。此外，被保險人需完成程式註冊並授權保險公司取得健康相關電子紀錄，保險公司將依此計算會員等級。
+條文依據：  
+- [第十九條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="G286" s="2" t="inlineStr"/>
+      <c r="H286" s="2" t="inlineStr"/>
+      <c r="I286" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "什麼情況下可以保費折減?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J286" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K286" s="4" t="n"/>
+      <c r="L286" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:17:08</t>
+        </is>
+      </c>
+      <c r="N286" s="4" t="n">
+        <v>10.97</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B287" s="2" t="inlineStr">
+        <is>
+          <t>角膜切除術是否可以申請理賠?</t>
+        </is>
+      </c>
+      <c r="C287" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+角膜切除術可以申請理賠，其對應的給付倍數為5倍。
+條文依據：  
+- [附表一：手術項目與給付倍數 - 1305 角膜切除術]</t>
+        </is>
+      </c>
+      <c r="D287" s="2" t="inlineStr">
+        <is>
+          <t>附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F287" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+角膜切除術可以申請理賠，其對應的給付倍數為5倍。
+條文依據：  
+- [附表一：手術項目與給付倍數 - 1305 角膜切除術]</t>
+        </is>
+      </c>
+      <c r="G287" s="2" t="inlineStr"/>
+      <c r="H287" s="2" t="inlineStr"/>
+      <c r="I287" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "角膜切除術是否可以申請理賠?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J287" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K287" s="4" t="n"/>
+      <c r="L287" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:17:21</t>
+        </is>
+      </c>
+      <c r="N287" s="4" t="n">
+        <v>11.18</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B288" s="2" t="inlineStr">
+        <is>
+          <t>白內障手術是否可以申請理賠?膜性白內障切開術、白內障線狀摘出術或白內障切囊術</t>
+        </is>
+      </c>
+      <c r="C288" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+白內障相關手術如膜性白內障切開術、白內障線狀摘出術及白內障切囊術均可申請理賠，且其給付倍數分別為5倍。  
+條文依據：  
+- [附表一：手術項目與給付倍數]</t>
+        </is>
+      </c>
+      <c r="D288" s="2" t="inlineStr">
+        <is>
+          <t>附表一：手術項目與給付倍數 | payout_items | 附表二：特定處置項目及給付倍數表</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F288" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+白內障相關手術如膜性白內障切開術、白內障線狀摘出術及白內障切囊術均可申請理賠，且其給付倍數分別為5倍。  
+條文依據：  
+- [附表一：手術項目與給付倍數]</t>
+        </is>
+      </c>
+      <c r="G288" s="2" t="inlineStr"/>
+      <c r="H288" s="2" t="inlineStr"/>
+      <c r="I288" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "白內障手術是否可以申請理賠?膜性白內障切開術、白內障線狀摘出術或白內障切囊術", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J288" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K288" s="4" t="n"/>
+      <c r="L288" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:17:30</t>
+        </is>
+      </c>
+      <c r="N288" s="4" t="n">
+        <v>8.93</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B289" s="2" t="inlineStr">
+        <is>
+          <t>保障範圍包括哪些項目？</t>
+        </is>
+      </c>
+      <c r="C289" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括：意外事故身故保險金或喪葬費用保險金、意外事故失能保險金、每月生活照護保險金、重大燒燙傷保險金、意外骨折保險金、傷害醫療日額保險金，以及意外創傷縫合處置保險金。
+條文依據：  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="D289" s="2" t="inlineStr">
+        <is>
+          <t>payout_items | 第五條 保險範圍 | 第十五條 每月生活照護保險金的給付 | 第三十條 不保事項 | 附表二：失能程度與保險金給付表</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F289" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括：意外事故身故保險金或喪葬費用保險金、意外事故失能保險金、每月生活照護保險金、重大燒燙傷保險金、意外骨折保險金、傷害醫療日額保險金，以及意外創傷縫合處置保險金。
+條文依據：  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="G289" s="2" t="inlineStr"/>
+      <c r="H289" s="2" t="inlineStr"/>
+      <c r="I289" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "保障範圍包括哪些項目？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J289" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K289" s="4" t="n"/>
+      <c r="L289" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:17:37</t>
+        </is>
+      </c>
+      <c r="N289" s="4" t="n">
+        <v>7.17</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B290" s="2" t="inlineStr">
+        <is>
+          <t>發生意外事故身故，理賠內容為何?</t>
+        </is>
+      </c>
+      <c r="C290" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外事故身故的理賠內容如下：  
+1. 若被保險人於意外傷害事故發生之日起 180 日內身故，本公司依意外傷害事故種類給付以下金額：  
+   - 一般意外傷害事故：「傷害醫療保險金日額」的 500 倍。  
+   - 特定意外傷害事故：「傷害醫療保險金日額」的 1000 倍。  
+2. 若被保險人於意外傷害事故發生後超過 180 日身故，但受益人能證明身故與該事故具有因果關係，本公司仍依上述金額給付。  
+3. 若被保險人為受監護宣告尚未撤銷者，其理賠內容變更為喪葬費用保險金，且喪葬費用保險金額不得超過遺產稅喪葬費扣除額之半數，超過部分不負給付責任。  
+條文依據：  
+- [第十二條 意外事故身故保險金或喪葬費用保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D290" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 意外事故身故保險金或喪葬費用保險金的給付 | 第十四條 保險給付的限制 | payout_items | 第十一條 契約的終止（二） | 第二十一條 失蹤處理</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F290" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外事故身故的理賠內容如下：  
+1. 若被保險人於意外傷害事故發生之日起 180 日內身故，本公司依意外傷害事故種類給付以下金額：  
+   - 一般意外傷害事故：「傷害醫療保險金日額」的 500 倍。  
+   - 特定意外傷害事故：「傷害醫療保險金日額」的 1000 倍。  
+2. 若被保險人於意外傷害事故發生後超過 180 日身故，但受益人能證明身故與該事故具有因果關係，本公司仍依上述金額給付。  
+3. 若被保險人為受監護宣告尚未撤銷者，其理賠內容變更為喪葬費用保險金，且喪葬費用保險金額不得超過遺產稅喪葬費扣除額之半數，超過部分不負給付責任。  
+條文依據：  
+- [第十二條 意外事故身故保險金或喪葬費用保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G290" s="2" t="inlineStr"/>
+      <c r="H290" s="2" t="inlineStr"/>
+      <c r="I290" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "發生意外事故身故，理賠內容為何?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J290" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K290" s="4" t="n"/>
+      <c r="L290" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:17:49</t>
+        </is>
+      </c>
+      <c r="N290" s="4" t="n">
+        <v>11.98</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B291" s="2" t="inlineStr">
+        <is>
+          <t>意外事故失能保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C291" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外事故失能保險金的給付條件如下：  
+1. 被保險人於契約有效期間內遭受「意外傷害事故」，並於事故發生後180日內致成附表二所列失能程度之一者，本公司依事故種類及失能程度，按以下方式計算給付金額：  
+   - 一般意外傷害事故：「傷害醫療保險金日額」的500倍乘以附表二給付比例。  
+   - 特定意外傷害事故：「傷害醫療保險金日額」的1000倍乘以附表二給付比例。  
+2. 若超過180日致成失能，但能證明失能與事故具有因果關係者，仍可申請給付，不受180日限制。  
+3. 同一事故導致多項失能時，僅給付同一手或同一足中較嚴重項目的失能保險金，且總金額以事故種類的上限為限：  
+   - 一般意外傷害事故：「傷害醫療保險金日額」的500倍。  
+   - 特定意外傷害事故：「傷害醫療保險金日額」的1000倍。  
+4. 不同事故導致的失能，累計給付金額最高以「傷害醫療保險金日額」的1200倍為限。  
+條文依據：  
+- [第十三條 意外事故失能保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D291" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 意外事故失能保險金的給付 | 第十五條 每月生活照護保險金的給付 | 第十四條 保險給付的限制 | 第十二條 意外事故身故保險金或喪葬費用保險金的給付 | 第二十三條 意外事故失能保險金的申領 | 附表二：失能程度與保險金給付表</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F291" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外事故失能保險金的給付條件如下：  
+1. 被保險人於契約有效期間內遭受「意外傷害事故」，並於事故發生後180日內致成附表二所列失能程度之一者，本公司依事故種類及失能程度，按以下方式計算給付金額：  
+   - 一般意外傷害事故：「傷害醫療保險金日額」的500倍乘以附表二給付比例。  
+   - 特定意外傷害事故：「傷害醫療保險金日額」的1000倍乘以附表二給付比例。  
+2. 若超過180日致成失能，但能證明失能與事故具有因果關係者，仍可申請給付，不受180日限制。  
+3. 同一事故導致多項失能時，僅給付同一手或同一足中較嚴重項目的失能保險金，且總金額以事故種類的上限為限：  
+   - 一般意外傷害事故：「傷害醫療保險金日額」的500倍。  
+   - 特定意外傷害事故：「傷害醫療保險金日額」的1000倍。  
+4. 不同事故導致的失能，累計給付金額最高以「傷害醫療保險金日額」的1200倍為限。  
+條文依據：  
+- [第十三條 意外事故失能保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G291" s="2" t="inlineStr"/>
+      <c r="H291" s="2" t="inlineStr"/>
+      <c r="I291" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "意外事故失能保險金的給付為何?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J291" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K291" s="4" t="n"/>
+      <c r="L291" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:18:01</t>
+        </is>
+      </c>
+      <c r="N291" s="4" t="n">
+        <v>11.31</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B292" s="2" t="inlineStr">
+        <is>
+          <t>每月生活照護保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C292" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+每月生活照護保險金的給付條件如下：  
+1. 被保險人於保險契約有效期間內因「意外傷害事故」，自事故發生之日起180日內，致成附表二所列第1級至第6級失能程度之一時，本公司自失能診斷確定當日起，按「傷害醫療保險金日額」的20倍乘以附表二給付比例所得之金額，按月給付，最多給付12個月。  
+2. 若該失能的前四個「失能診斷確定週年日」時，保險契約仍有效且被保險人仍生存，本公司自各該週年日起，按相同方式再給付，最多給付12個月。  
+3. 若被保險人自事故發生之日起超過180日才致成附表二所列第1級至第6級失能程度之一，但能證明該失能與事故具有因果關係者，本公司仍依上述規定給付，不受180日限制。  
+4. 同一事故若導致多項第1級至第6級失能，僅給付一項較嚴重失能的保險金，且最高以「傷害醫療保險金日額」的20倍為限。  
+5. 若失能合併以前的失能，按較嚴重項目給付，但以前的失能視同已給付，應扣除之。  
+條文依據：  
+- [第十五條 每月生活照護保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D292" s="2" t="inlineStr">
+        <is>
+          <t>第二十四條 每月生活照護保險金的申領 | 第十五條 每月生活照護保險金的給付 | payout_items | 第十八條 傷害醫療日額保險金的給付 | 第五條 保險範圍 | 附表二：失能程度與保險金給付表 | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F292" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+每月生活照護保險金的給付條件如下：  
+1. 被保險人於保險契約有效期間內因「意外傷害事故」，自事故發生之日起180日內，致成附表二所列第1級至第6級失能程度之一時，本公司自失能診斷確定當日起，按「傷害醫療保險金日額」的20倍乘以附表二給付比例所得之金額，按月給付，最多給付12個月。  
+2. 若該失能的前四個「失能診斷確定週年日」時，保險契約仍有效且被保險人仍生存，本公司自各該週年日起，按相同方式再給付，最多給付12個月。  
+3. 若被保險人自事故發生之日起超過180日才致成附表二所列第1級至第6級失能程度之一，但能證明該失能與事故具有因果關係者，本公司仍依上述規定給付，不受180日限制。  
+4. 同一事故若導致多項第1級至第6級失能，僅給付一項較嚴重失能的保險金，且最高以「傷害醫療保險金日額」的20倍為限。  
+5. 若失能合併以前的失能，按較嚴重項目給付，但以前的失能視同已給付，應扣除之。  
+條文依據：  
+- [第十五條 每月生活照護保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G292" s="2" t="inlineStr"/>
+      <c r="H292" s="2" t="inlineStr"/>
+      <c r="I292" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "每月生活照護保險金的給付為何?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J292" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K292" s="4" t="n"/>
+      <c r="L292" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:18:15</t>
+        </is>
+      </c>
+      <c r="N292" s="4" t="n">
+        <v>14.62</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B293" s="2" t="inlineStr">
+        <is>
+          <t>重大燒燙傷保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C293" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+重大燒燙傷保險金的給付條件為：被保險人於保險契約有效期間內，因「意外傷害事故」導致燒燙傷，且經診斷符合「重大燒燙傷」的定義時，本公司將按「傷害醫療保險金日額」的二百五十倍給付「重大燒燙傷保險金」。該保險金的給付以一次為限。
+條文依據：  
+- [第十六條 重大燒燙傷保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D293" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 重大燒燙傷保險金的給付 | 第二十五條 重大燒燙傷保險金的申領 | 第五條 保險範圍 | payout_items | 第二十九條 除外責任（原因）</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F293" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+重大燒燙傷保險金的給付條件為：被保險人於保險契約有效期間內，因「意外傷害事故」導致燒燙傷，且經診斷符合「重大燒燙傷」的定義時，本公司將按「傷害醫療保險金日額」的二百五十倍給付「重大燒燙傷保險金」。該保險金的給付以一次為限。
+條文依據：  
+- [第十六條 重大燒燙傷保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G293" s="2" t="inlineStr"/>
+      <c r="H293" s="2" t="inlineStr"/>
+      <c r="I293" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "重大燒燙傷保險金的給付為何?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J293" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K293" s="4" t="n"/>
+      <c r="L293" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:18:21</t>
+        </is>
+      </c>
+      <c r="N293" s="4" t="n">
+        <v>6.03</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B294" s="2" t="inlineStr">
+        <is>
+          <t>意外骨折保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C294" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外骨折保險金的給付條件如下：  
+1. 被保險人於契約有效期間內遭受「意外傷害事故」，並於事故發生後180日內經合格醫院或診所診斷為附表三骨折別表所列骨折項目之一（含不完全骨折及骨骼龜裂），本公司按「傷害醫療保險金日額」的二倍給付意外骨折保險金。  
+2. 若超過180日診斷確定骨折，受益人需證明骨折與該意外傷害事故具有因果關係，本公司仍依上述規定給付。  
+3. 同一意外傷害事故僅給付一次意外骨折保險金。  
+4. 若骨折不屬於附表三所列項目，需由本公司與被保險人協議核付；但若骨折為附表三內明訂不給付之部位，則不負給付責任。
+條文依據：  
+- [第十七條 意外骨折保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D294" s="2" t="inlineStr">
+        <is>
+          <t>第十七條 意外骨折保險金的給付 | 第十八條 傷害醫療日額保險金的給付 | 第二十六條 意外骨折保險金的申領 | 第十三條 意外事故失能保險金的給付 | 第十九條 意外創傷縫合處置保險金的給付 | 附表二：失能程度與保險金給付表 | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F294" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外骨折保險金的給付條件如下：  
+1. 被保險人於契約有效期間內遭受「意外傷害事故」，並於事故發生後180日內經合格醫院或診所診斷為附表三骨折別表所列骨折項目之一（含不完全骨折及骨骼龜裂），本公司按「傷害醫療保險金日額」的二倍給付意外骨折保險金。  
+2. 若超過180日診斷確定骨折，受益人需證明骨折與該意外傷害事故具有因果關係，本公司仍依上述規定給付。  
+3. 同一意外傷害事故僅給付一次意外骨折保險金。  
+4. 若骨折不屬於附表三所列項目，需由本公司與被保險人協議核付；但若骨折為附表三內明訂不給付之部位，則不負給付責任。
+條文依據：  
+- [第十七條 意外骨折保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G294" s="2" t="inlineStr"/>
+      <c r="H294" s="2" t="inlineStr"/>
+      <c r="I294" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "意外骨折保險金的給付為何?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J294" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K294" s="4" t="n"/>
+      <c r="L294" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:18:30</t>
+        </is>
+      </c>
+      <c r="N294" s="4" t="n">
+        <v>8.66</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B295" s="2" t="inlineStr">
+        <is>
+          <t>傷害醫療日額保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C295" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+傷害醫療日額保險金的給付條件如下：  
+1. 被保險人於保險契約有效期間內遭受「意外傷害事故」，並於事故發生後一百八十日內在「醫院」接受住院治療者，本公司按「傷害醫療保險金日額」乘以實際住院日數給付，但每次事故最高給付日數為九十日。  
+2. 若治療超過一百八十日，受益人需證明治療與事故具因果關係，本公司仍依上述規定給付，不受一百八十日限制。  
+3. 若因意外事故骨折但未住院，或住院日數未達附表三骨折別表所訂日數，未住院部分按骨折別表所訂日數乘以「傷害醫療保險金日額」的二分之一給付，合計給付日數以骨折別表所訂日數為上限。  
+4. 骨折類型的給付：  
+   - 完全骨折按骨折別表所訂日數給付。  
+   - 不完全骨折按完全骨折日數的二分之一給付。  
+   - 骨骼龜裂按完全骨折日數的四分之一給付。  
+5. 同時發生多項骨折時，僅給付一項較高等級的「傷害醫療日額保險金」。
+條文依據：  
+- [第十八條 傷害醫療日額保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D295" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 傷害醫療日額保險金的給付 | 第二十七條 傷害醫療日額保險金的申領 | 第十五條 每月生活照護保險金的給付 | 第三十四條 傷害醫療保險金日額之減少 | 第十九條 意外創傷縫合處置保險金的給付 | 附表二：失能程度與保險金給付表 | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F295" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+傷害醫療日額保險金的給付條件如下：  
+1. 被保險人於保險契約有效期間內遭受「意外傷害事故」，並於事故發生後一百八十日內在「醫院」接受住院治療者，本公司按「傷害醫療保險金日額」乘以實際住院日數給付，但每次事故最高給付日數為九十日。  
+2. 若治療超過一百八十日，受益人需證明治療與事故具因果關係，本公司仍依上述規定給付，不受一百八十日限制。  
+3. 若因意外事故骨折但未住院，或住院日數未達附表三骨折別表所訂日數，未住院部分按骨折別表所訂日數乘以「傷害醫療保險金日額」的二分之一給付，合計給付日數以骨折別表所訂日數為上限。  
+4. 骨折類型的給付：  
+   - 完全骨折按骨折別表所訂日數給付。  
+   - 不完全骨折按完全骨折日數的二分之一給付。  
+   - 骨骼龜裂按完全骨折日數的四分之一給付。  
+5. 同時發生多項骨折時，僅給付一項較高等級的「傷害醫療日額保險金」。
+條文依據：  
+- [第十八條 傷害醫療日額保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G295" s="2" t="inlineStr"/>
+      <c r="H295" s="2" t="inlineStr"/>
+      <c r="I295" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "傷害醫療日額保險金的給付為何?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J295" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K295" s="4" t="n"/>
+      <c r="L295" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:18:41</t>
+        </is>
+      </c>
+      <c r="N295" s="4" t="n">
+        <v>11.11</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B296" s="2" t="inlineStr">
+        <is>
+          <t>意外創傷縫合處置保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C296" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外創傷縫合處置保險金的給付條件為：被保險人於保險契約有效期間內，因遭受「意外傷害事故」，在「醫院」或「診所」經醫師診斷必須接受創傷縫合處置治療，且已完成縫合處置者，本公司將按「傷害醫療保險金日額」給付「意外創傷縫合處置保險金」。同一意外傷害事故僅給付一次。
+條文依據：  
+- [第十九條 意外創傷縫合處置保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D296" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 意外創傷縫合處置保險金的給付 | 第二十八條 意外創傷縫合處置保險金的申領 | 第五條 保險範圍 | 第十七條 意外骨折保險金的給付 | payout_items | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F296" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外創傷縫合處置保險金的給付條件為：被保險人於保險契約有效期間內，因遭受「意外傷害事故」，在「醫院」或「診所」經醫師診斷必須接受創傷縫合處置治療，且已完成縫合處置者，本公司將按「傷害醫療保險金日額」給付「意外創傷縫合處置保險金」。同一意外傷害事故僅給付一次。
+條文依據：  
+- [第十九條 意外創傷縫合處置保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G296" s="2" t="inlineStr"/>
+      <c r="H296" s="2" t="inlineStr"/>
+      <c r="I296" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "意外創傷縫合處置保險金的給付為何?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J296" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K296" s="4" t="n"/>
+      <c r="L296" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:18:48</t>
+        </is>
+      </c>
+      <c r="N296" s="4" t="n">
+        <v>6.71</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B297" s="2" t="inlineStr">
+        <is>
+          <t>因意外導致視力衰退，是否能申請理賠?</t>
+        </is>
+      </c>
+      <c r="C297" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以申請理賠，但需符合以下條件：  
+1. 視力永久衰退需達到「萬國式視力表0.02以下」的標準，或符合其他失明的定義（如眼球喪失、僅能辨明暗等）。  
+2. 必須經過自傷害日起六個月的治療後進行判定，但若屬於眼球摘出等明顯無法復原的情況，則不受此限制。  
+條文依據：  
+- 註2</t>
+        </is>
+      </c>
+      <c r="D297" s="2" t="inlineStr">
+        <is>
+          <t>第二十三條 意外事故失能保險金的申領 | 第十三條 意外事故失能保險金的給付 | 註2： | 第三十條 不保事項 | 第二十六條 意外骨折保險金的申領 | 附表二：失能程度與保險金給付表</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F297" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以申請理賠，但需符合以下條件：  
+1. 視力永久衰退需達到「萬國式視力表0.02以下」的標準，或符合其他失明的定義（如眼球喪失、僅能辨明暗等）。  
+2. 必須經過自傷害日起六個月的治療後進行判定，但若屬於眼球摘出等明顯無法復原的情況，則不受此限制。  
+條文依據：  
+- 註2</t>
+        </is>
+      </c>
+      <c r="G297" s="2" t="inlineStr"/>
+      <c r="H297" s="2" t="inlineStr"/>
+      <c r="I297" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "因意外導致視力衰退，是否能申請理賠?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J297" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K297" s="4" t="n"/>
+      <c r="L297" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:18:58</t>
+        </is>
+      </c>
+      <c r="N297" s="4" t="n">
+        <v>9.23</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B298" s="2" t="inlineStr">
+        <is>
+          <t>肋骨骨折是否可以申請理賠?理賠金額為多少?包含傷害醫療保險金日額跟意外骨折保險金嗎？</t>
+        </is>
+      </c>
+      <c r="C298" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+肋骨骨折可以申請理賠，理賠金額需視保單約定的「傷害醫療保險金日額」而定。若符合條件，可能包含「傷害醫療日額保險金」及「意外骨折保險金」。  
+1. **傷害醫療日額保險金**：若因肋骨骨折住院治療，依實際住院日數乘以「傷害醫療保險金日額」給付，但每次意外事故最高給付日數為90日。若未住院但符合骨折別表規定，按骨折別表所訂日數的二分之一給付。肋骨骨折的完全骨折日數為20天，因此未住院部分最高可給付10天的日額保險金。  
+2. **意外骨折保險金**：肋骨骨折屬於附表三骨折別表所列項目，若經診斷確定，按「傷害醫療保險金日額」的二倍給付一次性保險金。
+條文依據：  
+- [第十八條 傷害醫療日額保險金的給付]  
+- [第十七條 意外骨折保險金的給付]  
+- [附表三：骨折別表]</t>
+        </is>
+      </c>
+      <c r="D298" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 傷害醫療日額保險金的給付 | 第十七條 意外骨折保險金的給付 | 第二十六條 意外骨折保險金的申領 | payout_items | 第二十七條 傷害醫療日額保險金的申領 | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F298" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+肋骨骨折可以申請理賠，理賠金額需視保單約定的「傷害醫療保險金日額」而定。若符合條件，可能包含「傷害醫療日額保險金」及「意外骨折保險金」。  
+1. **傷害醫療日額保險金**：若因肋骨骨折住院治療，依實際住院日數乘以「傷害醫療保險金日額」給付，但每次意外事故最高給付日數為90日。若未住院但符合骨折別表規定，按骨折別表所訂日數的二分之一給付。肋骨骨折的完全骨折日數為20天，因此未住院部分最高可給付10天的日額保險金。  
+2. **意外骨折保險金**：肋骨骨折屬於附表三骨折別表所列項目，若經診斷確定，按「傷害醫療保險金日額」的二倍給付一次性保險金。
+條文依據：  
+- [第十八條 傷害醫療日額保險金的給付]  
+- [第十七條 意外骨折保險金的給付]  
+- [附表三：骨折別表]</t>
+        </is>
+      </c>
+      <c r="G298" s="2" t="inlineStr"/>
+      <c r="H298" s="2" t="inlineStr"/>
+      <c r="I298" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "肋骨骨折是否可以申請理賠?理賠金額為多少?包含傷害醫療保險金日額跟意外骨折保險金嗎？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J298" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K298" s="4" t="n"/>
+      <c r="L298" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:19:11</t>
+        </is>
+      </c>
+      <c r="N298" s="4" t="n">
+        <v>13.06</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B299" s="2" t="inlineStr">
+        <is>
+          <t>投保新鍾心滿福後，假設投保保額為100萬元，於第二保單年度接受「移植器官」，這樣可以領多少重大傷病保險金及特定重大傷病保險金?</t>
+        </is>
+      </c>
+      <c r="C299" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 新鍾心滿福保單涵蓋重大傷病保險金及特定重大傷病保險金。  
+2. 器官移植屬於「重大傷病範圍」及「特定重大傷病」的給付條件，符合保險金給付資格。  
+3. 若保額為100萬元，於第二保單年度接受器官移植，重大傷病保險金的給付金額為「保險金額」或「年繳應繳保險費總額的一點零五倍」，二者取其大者；特定重大傷病保險金則為「保險金額的百分之二十」，即20萬元。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第十三條 特定重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D299" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 特定重大傷病保險金的給付 | 第十二條 重大傷病保險金的給付 | 附表一：全民健康保險重大傷病項目 | payout_items | 第二條 名詞定義 | 附表二：完全失能程度表</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F299" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 新鍾心滿福保單涵蓋重大傷病保險金及特定重大傷病保險金。  
+2. 器官移植屬於「重大傷病範圍」及「特定重大傷病」的給付條件，符合保險金給付資格。  
+3. 若保額為100萬元，於第二保單年度接受器官移植，重大傷病保險金的給付金額為「保險金額」或「年繳應繳保險費總額的一點零五倍」，二者取其大者；特定重大傷病保險金則為「保險金額的百分之二十」，即20萬元。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第十三條 特定重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G299" s="2" t="inlineStr"/>
+      <c r="H299" s="2" t="inlineStr"/>
+      <c r="I299" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認新鍾心滿福保單是否涵蓋重大傷病保險金及特定重大傷病保險金", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認重大傷病保險金及特定重大傷病保險金的給付條件是否包含器官移植", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認保額100萬元對應的重大傷病保險金及特定重大傷病保險金給付比例或金額", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認第二保單年度是否影響重大傷病保險金及特定重大傷病保險金的給付資格", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J299" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K299" s="4" t="n"/>
+      <c r="L299" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:19:28</t>
+        </is>
+      </c>
+      <c r="N299" s="4" t="n">
+        <v>16.81</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B300" s="2" t="inlineStr">
+        <is>
+          <t>投保新鍾心滿福後，若要理賠重大傷病保險金，一定要檢附全民健保開立的重大傷病證明才能拿到保險金嗎?</t>
+        </is>
+      </c>
+      <c r="C300" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 新鍾心滿福包含重大傷病保險金保障，依條款第二條名詞定義及第十二條重大傷病保險金的給付規定，若被保險人符合重大傷病範圍並經診斷確定，可申請重大傷病保險金。  
+2. 理賠重大傷病保險金時，通常需要檢附全民健保開立的重大傷病證明，但條款中也明確規定，若被保險人已取得一家「區域醫院」層級以上（含）之醫療院所開立的診斷書及病歷摘要，且符合投保當時重大傷病範圍，亦可視為重大傷病證明文件，無需另行申請全民健保重大傷病證明。  
+3. 若因全民健保重大傷病項目變更或被保險人於重大傷病證明核發前身故等特殊情況，條款亦提供其他文件替代重大傷病證明進行理賠，例如區域醫院層級以上的診斷書及病歷摘要等。
+條文依據：  
+- [第二條 名詞定義]  
+- [第十二條 重大傷病保險金的給付]  
+- [第二十二條 重大傷病保險金、特定重大傷病保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D300" s="2" t="inlineStr">
+        <is>
+          <t>第二十二條 重大傷病保險金、特定重大傷病保險金的申領 | other_metadata | 第十二條 重大傷病保險金的給付 | 附表一：全民健康保險重大傷病項目 | 第二條 名詞定義 | 第三十條 不保事項</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F300" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 新鍾心滿福包含重大傷病保險金保障，依條款第二條名詞定義及第十二條重大傷病保險金的給付規定，若被保險人符合重大傷病範圍並經診斷確定，可申請重大傷病保險金。  
+2. 理賠重大傷病保險金時，通常需要檢附全民健保開立的重大傷病證明，但條款中也明確規定，若被保險人已取得一家「區域醫院」層級以上（含）之醫療院所開立的診斷書及病歷摘要，且符合投保當時重大傷病範圍，亦可視為重大傷病證明文件，無需另行申請全民健保重大傷病證明。  
+3. 若因全民健保重大傷病項目變更或被保險人於重大傷病證明核發前身故等特殊情況，條款亦提供其他文件替代重大傷病證明進行理賠，例如區域醫院層級以上的診斷書及病歷摘要等。
+條文依據：  
+- [第二條 名詞定義]  
+- [第十二條 重大傷病保險金的給付]  
+- [第二十二條 重大傷病保險金、特定重大傷病保險金的申領]</t>
+        </is>
+      </c>
+      <c r="G300" s="2" t="inlineStr"/>
+      <c r="H300" s="2" t="inlineStr"/>
+      <c r="I300" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認新鍾心滿福是否包含重大傷病保險金保障", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認理賠重大傷病保險金是否需要檢附全民健保開立的重大傷病證明", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認是否有其他文件可替代重大傷病證明進行理賠", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J300" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K300" s="4" t="n"/>
+      <c r="L300" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:19:45</t>
+        </is>
+      </c>
+      <c r="N300" s="4" t="n">
+        <v>16.95</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B301" s="2" t="inlineStr">
+        <is>
+          <t>要有健保身分才能申請重大傷病理賠嗎？</t>
+        </is>
+      </c>
+      <c r="C301" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+是的，若被保險人喪失全民健康保險被保險人資格，需先重新申請加入全民健康保險後，才能申請重大傷病保險金的給付。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D301" s="2" t="inlineStr">
+        <is>
+          <t>第二十二條 重大傷病保險金、特定重大傷病保險金的申領 | 第十二條 重大傷病保險金的給付 | 第三十條 不保事項 | other_metadata | 第二條 名詞定義 | 附表一：全民健康保險重大傷病項目</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F301" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+是的，若被保險人喪失全民健康保險被保險人資格，需先重新申請加入全民健康保險後，才能申請重大傷病保險金的給付。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G301" s="2" t="inlineStr"/>
+      <c r="H301" s="2" t="inlineStr"/>
+      <c r="I301" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "要有健保身分才能申請重大傷病理賠嗎？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J301" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K301" s="4" t="n"/>
+      <c r="L301" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:19:51</t>
+        </is>
+      </c>
+      <c r="N301" s="4" t="n">
+        <v>5.72</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B302" s="2" t="inlineStr">
+        <is>
+          <t>重大傷病的項目如果在投保後有新增，可以從優申請理賠嗎？</t>
+        </is>
+      </c>
+      <c r="C302" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以從優申請理賠。重大傷病的範圍包含「全民健康保險重大傷病項目及其證明有效期限」，且若該項目於保險契約有效期間內新增，則以中央衛生主管機關最新公告的項目為準，適用於理賠。
+條文依據：  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D302" s="2" t="inlineStr">
+        <is>
+          <t>附表一：全民健康保險重大傷病項目 | 第二條 名詞定義 | payout_items</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F302" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以從優申請理賠。重大傷病的範圍包含「全民健康保險重大傷病項目及其證明有效期限」，且若該項目於保險契約有效期間內新增，則以中央衛生主管機關最新公告的項目為準，適用於理賠。
+條文依據：  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G302" s="2" t="inlineStr"/>
+      <c r="H302" s="2" t="inlineStr"/>
+      <c r="I302" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "重大傷病的項目如果在投保後有新增，可以從優申請理賠嗎？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J302" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K302" s="4" t="n"/>
+      <c r="L302" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:19:58</t>
+        </is>
+      </c>
+      <c r="N302" s="4" t="n">
+        <v>6.67</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B303" s="2" t="inlineStr">
+        <is>
+          <t>我的保單之前有停效，在復效後五天被診斷出重大疾病是否可申請理賠？</t>
+        </is>
+      </c>
+      <c r="C303" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若保單已成功復效，且重大疾病屬於保單保障範圍內，並符合理賠條件，則可申請理賠。根據條款，重大疾病的理賠條件包括：  
+1. 被保險人於復效後的有效期間內，經醫院醫師初次診斷確定罹患重大疾病。  
+2. 已取得符合「重大傷病範圍」的診斷書及病歷摘要，或取得全民健康保險保險人核發的重大傷病證明。  
+此外，條款未提及復效後是否有等待期的規定，因此若無等待期限制，則診斷時間不影響理賠資格。
+條文依據：  
+- [第八條 本契約效力的恢復]  
+- [第十二條 重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D303" s="2" t="inlineStr">
+        <is>
+          <t>第八條 本契約效力的恢復 | 第三十條 不保事項 | 第五條 保險範圍 | other_metadata | 第二條 名詞定義 | 第十二條 重大傷病保險金的給付 | 第二十二條 重大傷病保險金、特定重大傷病保險金的申領 | 附表一：全民健康保險重大傷病項目</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F303" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若保單已成功復效，且重大疾病屬於保單保障範圍內，並符合理賠條件，則可申請理賠。根據條款，重大疾病的理賠條件包括：  
+1. 被保險人於復效後的有效期間內，經醫院醫師初次診斷確定罹患重大疾病。  
+2. 已取得符合「重大傷病範圍」的診斷書及病歷摘要，或取得全民健康保險保險人核發的重大傷病證明。  
+此外，條款未提及復效後是否有等待期的規定，因此若無等待期限制，則診斷時間不影響理賠資格。
+條文依據：  
+- [第八條 本契約效力的恢復]  
+- [第十二條 重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G303" s="2" t="inlineStr"/>
+      <c r="H303" s="2" t="inlineStr"/>
+      <c r="I303" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認保單是否已成功復效", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認重大疾病是否在保單保障範圍內", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認重大疾病診斷是否符合理賠條件", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認復效後是否有等待期的規定", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J303" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K303" s="4" t="n"/>
+      <c r="L303" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M303" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:20:25</t>
+        </is>
+      </c>
+      <c r="N303" s="4" t="n">
+        <v>27.58</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B304" s="2" t="inlineStr">
+        <is>
+          <t>領完重大傷病保險金，主約終止後，附約可以繼續有效嗎?</t>
+        </is>
+      </c>
+      <c r="C304" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以。根據條款規定，若因重大傷病診斷確定而導致主約終止時，要保人仍可於附約有效期間內繼續繳交附約保險費，以延續附約效力。
+條文依據：  
+- [第十一條 契約的終止（二）]</t>
+        </is>
+      </c>
+      <c r="D304" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 契約的終止（二） | 第十二條 重大傷病保險金的給付 | 第三十條 不保事項 | 第五條 保險範圍 | payout_items | 附表一：全民健康保險重大傷病項目</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F304" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以。根據條款規定，若因重大傷病診斷確定而導致主約終止時，要保人仍可於附約有效期間內繼續繳交附約保險費，以延續附約效力。
+條文依據：  
+- [第十一條 契約的終止（二）]</t>
+        </is>
+      </c>
+      <c r="G304" s="2" t="inlineStr"/>
+      <c r="H304" s="2" t="inlineStr"/>
+      <c r="I304" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "領完重大傷病保險金，主約終止後，附約可以繼續有效嗎?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J304" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K304" s="4" t="n"/>
+      <c r="L304" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M304" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:20:36</t>
+        </is>
+      </c>
+      <c r="N304" s="4" t="n">
+        <v>10.44</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B305" s="2" t="inlineStr">
+        <is>
+          <t>Q1：因為慢性精神病的保險給付僅有保額的20%，我可以先不申請給付，等之後發生其他重大傷病後，再申請重大傷病保險金嗎?Q2：但如果我不申請，保險公司不會知道我有罹患慢性精神病阿，所以我就可以領之後的重大傷病100%保額嗎?</t>
+        </is>
+      </c>
+      <c r="C305" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+Q1：慢性精神病的保險給付比例確實為保額的20%。根據條款規定，若罹患慢性精神病，保險公司僅給付「保險金額的百分之二十」或「年繳應繳保險費總額的一點零五倍」，二者取其大者。您可以選擇延後申請慢性精神病保險金，但條款中未明確限制延後申請的權利。  
+Q2：延後申請慢性精神病保險金並不會影響您之後申請其他重大傷病保險金的資格，但條款明確規定，若同時或先後罹患兩項以上重大傷病，保險公司僅給付一項重大傷病保險金。因此，即使您未申請慢性精神病保險金，保險公司仍可能依據診斷記錄或其他資料得知您已罹患慢性精神病，並據此計算給付金額，可能影響後續重大傷病保險金的給付比例。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第十三條 特定重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D305" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 重大傷病保險金的給付 | 第十三條 特定重大傷病保險金的給付 | 第三十條 不保事項 | 第二十八條 除外責任（一） | 第二十二條 重大傷病保險金、特定重大傷病保險金的申領 | 第二條 名詞定義 | 附表一：全民健康保險重大傷病項目 | payout_items</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F305" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+Q1：慢性精神病的保險給付比例確實為保額的20%。根據條款規定，若罹患慢性精神病，保險公司僅給付「保險金額的百分之二十」或「年繳應繳保險費總額的一點零五倍」，二者取其大者。您可以選擇延後申請慢性精神病保險金，但條款中未明確限制延後申請的權利。  
+Q2：延後申請慢性精神病保險金並不會影響您之後申請其他重大傷病保險金的資格，但條款明確規定，若同時或先後罹患兩項以上重大傷病，保險公司僅給付一項重大傷病保險金。因此，即使您未申請慢性精神病保險金，保險公司仍可能依據診斷記錄或其他資料得知您已罹患慢性精神病，並據此計算給付金額，可能影響後續重大傷病保險金的給付比例。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第十三條 特定重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G305" s="2" t="inlineStr"/>
+      <c r="H305" s="2" t="inlineStr"/>
+      <c r="I305" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認慢性精神病保險給付比例是否為保額的20%", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認是否可以延後申請慢性精神病保險給付", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認延後申請是否影響重大傷病保險金的申請資格", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認保險公司是否會因未申請慢性精神病給付而不知情", "must_have": false, "分數": 1.0}, {"id": "5", "point": "確認重大傷病保險金是否能領取100%保額", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J305" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K305" s="4" t="n"/>
+      <c r="L305" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:21:02</t>
+        </is>
+      </c>
+      <c r="N305" s="4" t="n">
+        <v>25.28</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B306" s="2" t="inlineStr">
+        <is>
+          <t>慢性精神病失智症會賠嗎？賠多少？</t>
+        </is>
+      </c>
+      <c r="C306" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+慢性精神病（如失智症）屬於重大傷病範圍，若被保險人於等待期間屆滿翌日或復效日起的契約有效期間內，經醫師診斷確定罹患，並取得重大傷病證明或符合診斷書及病歷摘要的要求，本公司將依以下方式給付重大傷病保險金：  
+1. 若初次診斷確定罹患重大傷病時的保險單年度為第一保險單年度，給付「年繳應繳保險費總額」的1.05倍。  
+2. 若初次診斷確定罹患重大傷病時的保險單年度為第二保險單年度（含）以後，屬於慢性精神病，給付「保險金額的20%」或「年繳應繳保險費總額的1.05倍」，二者取其大者。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D306" s="2" t="inlineStr">
+        <is>
+          <t>附表一：全民健康保險重大傷病項目 | 第二十九條 除外責任（二） | 第十二條 重大傷病保險金的給付 | payout_items | 附表二：完全失能程度表</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F306" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+慢性精神病（如失智症）屬於重大傷病範圍，若被保險人於等待期間屆滿翌日或復效日起的契約有效期間內，經醫師診斷確定罹患，並取得重大傷病證明或符合診斷書及病歷摘要的要求，本公司將依以下方式給付重大傷病保險金：  
+1. 若初次診斷確定罹患重大傷病時的保險單年度為第一保險單年度，給付「年繳應繳保險費總額」的1.05倍。  
+2. 若初次診斷確定罹患重大傷病時的保險單年度為第二保險單年度（含）以後，屬於慢性精神病，給付「保險金額的20%」或「年繳應繳保險費總額的1.05倍」，二者取其大者。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G306" s="2" t="inlineStr"/>
+      <c r="H306" s="2" t="inlineStr"/>
+      <c r="I306" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "慢性精神病失智症會賠嗎？賠多少？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J306" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K306" s="4" t="n"/>
+      <c r="L306" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:21:14</t>
+        </is>
+      </c>
+      <c r="N306" s="4" t="n">
+        <v>12.65</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B307" s="2" t="inlineStr">
+        <is>
+          <t>投保新鍾心滿福後，於第二保單年度罹患子宮頸惡性腫瘤，且已給付重大傷病保險金。第五保單年度時又罹患慢性腎衰竭，這樣還可以申領重大傷病保險金的給付嗎?</t>
+        </is>
+      </c>
+      <c r="C307" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款規定，被保險人同時或先後罹患二項以上「重大傷病」時，本公司僅給付一項「重大傷病保險金」。慢性腎衰竭〔尿毒症〕若符合需接受定期透析治療的條件，屬於「重大傷病範圍」項目之一 [第二條 名詞定義]。因此，於第二保單年度已因子宮頸惡性腫瘤申領重大傷病保險金後，第五保單年度罹患慢性腎衰竭將無法再次申領重大傷病保險金。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D307" s="2" t="inlineStr">
+        <is>
+          <t>附表一：全民健康保險重大傷病項目 | 第二條 名詞定義 | 第十二條 重大傷病保險金的給付 | 第二十二條 重大傷病保險金、特定重大傷病保險金的申領</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F307" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款規定，重大傷病保險金僅能給付一次，即使被保險人於不同保單年度內先後罹患多項重大傷病，本公司僅給付一項重大傷病保險金。因此，於第二保單年度已因子宮頸惡性腫瘤申領重大傷病保險金後，第五保單年度罹患慢性腎衰竭將無法再次申領重大傷病保險金。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G307" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款規定，被保險人同時或先後罹患二項以上「重大傷病」時，本公司僅給付一項「重大傷病保險金」。因此，於第二保單年度已因子宮頸惡性腫瘤申領重大傷病保險金後，第五保單年度罹患慢性腎衰竭將無法再次申領重大傷病保險金。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="H307" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款規定，被保險人同時或先後罹患二項以上「重大傷病」時，本公司僅給付一項「重大傷病保險金」。慢性腎衰竭〔尿毒症〕若符合需接受定期透析治療的條件，屬於「重大傷病範圍」項目之一 [第二條 名詞定義]。因此，於第二保單年度已因子宮頸惡性腫瘤申領重大傷病保險金後，第五保單年度罹患慢性腎衰竭將無法再次申領重大傷病保險金。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="I307" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認重大傷病保險金是否可重複申領", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認重大傷病保險金的申領條件是否涵蓋慢性腎衰竭", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認保單條款中對於不同保單年度內多次罹患重大傷病的規定", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認重大傷病保險金是否有累計上限或次數限制", "must_have": false, "分數": 1.0}, {"id": "5", "point": "確認慢性腎衰竭是否需符合特定診斷或治療條件才能申領", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J307" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K307" s="4" t="n"/>
+      <c r="L307" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:21:49</t>
+        </is>
+      </c>
+      <c r="N307" s="4" t="n">
+        <v>34.53</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B308" s="2" t="inlineStr">
+        <is>
+          <t>12歲的被保險人可以有健康促進保險費折減嗎？</t>
+        </is>
+      </c>
+      <c r="C308" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+12歲的被保險人無法享有健康促進保險費折減，因為該條款明確規定，只有實際年齡達18歲（含）以上的被保險人才能參與健康促進計劃並獲得保險費折減。
+條文依據：  
+- [第十九條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="D308" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 健康促進保險費折減 | 第三十八條 投保年齡的計算及錯誤的處理 | 第三十四條 減額繳清保險 | 第二條 名詞定義 | 第十六條 所繳保險費加計利息的退還、身故保險金或喪葬費用保險金的給付 | 附表二：完全失能程度表</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F308" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+12歲的被保險人無法享有健康促進保險費折減，因為該條款明確規定，只有實際年齡達18歲（含）以上的被保險人才能參與健康促進計劃並獲得保險費折減。
+條文依據：  
+- [第十九條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="G308" s="2" t="inlineStr"/>
+      <c r="H308" s="2" t="inlineStr"/>
+      <c r="I308" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "12歲的被保險人可以有健康促進保險費折減嗎？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J308" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K308" s="4" t="n"/>
+      <c r="L308" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:22:00</t>
+        </is>
+      </c>
+      <c r="N308" s="4" t="n">
+        <v>9.92</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>ZDN</t>
+        </is>
+      </c>
+      <c r="B309" s="2" t="inlineStr">
+        <is>
+          <t>被保險人於投保鍾心滿溢後的第10天就罹患慢性腎衰竭，請問可以申領重大傷病保險金嗎？</t>
+        </is>
+      </c>
+      <c r="C309" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於投保後第10天罹患慢性腎衰竭，無法申領重大傷病保險金。根據條款，慢性腎衰竭屬於重大傷病範圍，但因非因意外傷害事故所致，需經過等待期間（90天）後罹患才符合理賠條件。投保後第10天尚在等待期間內，因此本契約自始無效，本公司僅退還已繳保險費且不計利息。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第二條 名詞定義]  
+- [第三十條 不保事項]</t>
+        </is>
+      </c>
+      <c r="D309" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 重大傷病保險金的給付 | 附表一：全民健康保險重大傷病項目 | 第三十條 不保事項 | 第二條 名詞定義 | 第二十二條 重大傷病保險金、特定重大傷病保險金的申領</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F309" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於投保後第10天罹患慢性腎衰竭，無法申領重大傷病保險金。根據條款，慢性腎衰竭屬於重大傷病範圍，但因非因意外傷害事故所致，需經過等待期間（90天）後罹患才符合理賠條件。投保後第10天尚在等待期間內，因此本契約自始無效，本公司僅退還已繳保險費且不計利息。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第二條 名詞定義]  
+- [第三十條 不保事項]</t>
+        </is>
+      </c>
+      <c r="G309" s="2" t="inlineStr"/>
+      <c r="H309" s="2" t="inlineStr"/>
+      <c r="I309" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認重大傷病保險金是否涵蓋慢性腎衰竭", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認保單是否已生效並符合理賠條件", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認慢性腎衰竭的診斷日期是否符合保單規定", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認重大傷病保險金的理賠申請流程", "must_have": false, "分數": 0.5}], "coverage_score": 0.9615, "C_conf": 0.9615}</t>
+        </is>
+      </c>
+      <c r="J309" s="4" t="n">
+        <v>0.9615</v>
+      </c>
+      <c r="K309" s="4" t="n"/>
+      <c r="L309" s="4" t="n">
+        <v>0.9615</v>
+      </c>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:22:17</t>
+        </is>
+      </c>
+      <c r="N309" s="4" t="n">
+        <v>17.49</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>CFE</t>
+        </is>
+      </c>
+      <c r="B310" s="2" t="inlineStr">
+        <is>
+          <t>投保自由配重大傷病後，若在契約生效後80天罹患第一期乳癌，會拿到理賠金嗎?</t>
+        </is>
+      </c>
+      <c r="C310" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 自由配重大傷病保險涵蓋第一期乳癌，屬於「需積極或長期治療之癌症」範圍內，且在附表一中列明。  
+2. 第一期乳癌的等待期間為契約生效日起90天，您於生效後80天罹患，尚未滿等待期間，因此不符合理賠條件。  
+3. 因等待期間未滿，契約自始無效，保險公司將無息退還已繳保險費。  
+條文依據：  
+- [附表一：全民健康保險重大傷病項目]  
+- [第二條 名詞定義]  
+- [第十一條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D310" s="2" t="inlineStr">
+        <is>
+          <t>附表一：全民健康保險重大傷病項目 | 第十一條 重大傷病保險金的給付 | 第十五條 不保事項 | 第二條 名詞定義 | other_metadata | 第五條 契約有效期間及保證續保 | 第十四條 除外責任</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F310" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 自由配重大傷病保險涵蓋第一期乳癌，屬於「需積極或長期治療之癌症」範圍內，且在附表一中列明。  
+2. 第一期乳癌的等待期間為契約生效日起90天，您於生效後80天罹患，尚未滿等待期間，因此不符合理賠條件。  
+3. 因等待期間未滿，契約自始無效，保險公司將無息退還已繳保險費。  
+條文依據：  
+- [附表一：全民健康保險重大傷病項目]  
+- [第二條 名詞定義]  
+- [第十一條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G310" s="2" t="inlineStr"/>
+      <c r="H310" s="2" t="inlineStr"/>
+      <c r="I310" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認自由配重大傷病保險是否涵蓋第一期乳癌", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認契約生效後的等待期是否已滿", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認第一期乳癌是否符合理賠條件", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認理賠金額的計算方式或標準", "must_have": false, "分數": 0.5}], "coverage_score": 0.9615, "C_conf": 0.9615}</t>
+        </is>
+      </c>
+      <c r="J310" s="4" t="n">
+        <v>0.9615</v>
+      </c>
+      <c r="K310" s="4" t="n"/>
+      <c r="L310" s="4" t="n">
+        <v>0.9615</v>
+      </c>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:22:35</t>
+        </is>
+      </c>
+      <c r="N310" s="4" t="n">
+        <v>17.23</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>CFE</t>
+        </is>
+      </c>
+      <c r="B311" s="2" t="inlineStr">
+        <is>
+          <t>要保人想要終止國泰人壽自由配CFE契約，能否退保費?如何申請？</t>
+        </is>
+      </c>
+      <c r="C311" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+要保人可以隨時申請終止國泰人壽自由配CFE契約，並可退還未到期保險費。申請流程為向保險公司提交書面或其他約定方式的通知，契約自保險公司收到通知時生效。退還保費時，保險公司會從已繳保險費中扣除按短期費率計算的已經過期間保險費，剩餘部分無息退還給要保人。
+條文依據：  
+- [第九條 契約的終止（一）]</t>
+        </is>
+      </c>
+      <c r="D311" s="2" t="inlineStr">
+        <is>
+          <t>第九條 契約的終止（一） | 第十五條 不保事項 | 第七條 本契約效力的恢復 | 第六條 續保保險費的交付、寬限期間及契約效力的停止 | 第十條 契約的終止（二） | 第五條 契約有效期間及保證續保 | 第八條 告知義務與本契約的解除 | 第十七條 保險金額之減少 | 附表二：短期費率表</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F311" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+要保人可以隨時申請終止國泰人壽自由配CFE契約，並可退還未到期保險費。申請流程為向保險公司提交書面或其他約定方式的通知，契約自保險公司收到通知時生效。退還保費時，保險公司會從已繳保險費中扣除按短期費率計算的已經過期間保險費，剩餘部分無息退還給要保人。
+條文依據：  
+- [第九條 契約的終止（一）]</t>
+        </is>
+      </c>
+      <c r="G311" s="2" t="inlineStr"/>
+      <c r="H311" s="2" t="inlineStr"/>
+      <c r="I311" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認終止國泰人壽自由配CFE契約是否能退還保費", "must_have": true, "分數": 1.0}, {"id": "2", "point": "了解申請終止契約及退保費的流程", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認退保費是否有相關條件或限制", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J311" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K311" s="4" t="n"/>
+      <c r="L311" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:22:46</t>
+        </is>
+      </c>
+      <c r="N311" s="4" t="n">
+        <v>10.97</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>CFE</t>
+        </is>
+      </c>
+      <c r="B312" s="2" t="inlineStr">
+        <is>
+          <t>投保國泰人壽自由配CFE，若在等待期間內罹患重大傷病，要如何給付?</t>
+        </is>
+      </c>
+      <c r="C312" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在等待期間內罹患重大傷病，依條款規定，因意外傷害事故所致的重大傷病不受等待期間限制，仍可申請給付重大傷病保險金。但若因其他原因（非意外傷害事故）於等待期間內罹患重大傷病，則本契約自始無效，保險公司僅退還已繳保險費且不計利息。  
+條文依據：  
+- [第十一條 重大傷病保險金的給付]  
+- [第十五條 不保事項]</t>
+        </is>
+      </c>
+      <c r="D312" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 重大傷病保險金的給付 | 附表一：全民健康保險重大傷病項目 | 第十五條 不保事項 | 第十四條 除外責任 | payout_items | other_metadata</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F312" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在等待期間內罹患重大傷病，依條款規定，因意外傷害事故所致的重大傷病不受等待期間限制，仍可申請給付重大傷病保險金。但若因其他原因（非意外傷害事故）於等待期間內罹患重大傷病，則本契約自始無效，保險公司僅退還已繳保險費且不計利息。  
+條文依據：  
+- [第十一條 重大傷病保險金的給付]  
+- [第十五條 不保事項]</t>
+        </is>
+      </c>
+      <c r="G312" s="2" t="inlineStr"/>
+      <c r="H312" s="2" t="inlineStr"/>
+      <c r="I312" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認國泰人壽自由配CFE的等待期間規定", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認重大傷病是否符合保單條款中的定義", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認等待期間內重大傷病的給付條件或限制", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認是否有其他附加條款影響給付", "must_have": false, "分數": 0.5}], "coverage_score": 0.9615, "C_conf": 0.9615}</t>
+        </is>
+      </c>
+      <c r="J312" s="4" t="n">
+        <v>0.9615</v>
+      </c>
+      <c r="K312" s="4" t="n"/>
+      <c r="L312" s="4" t="n">
+        <v>0.9615</v>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:23:04</t>
+        </is>
+      </c>
+      <c r="N312" s="4" t="n">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>CFE</t>
+        </is>
+      </c>
+      <c r="B313" s="2" t="inlineStr">
+        <is>
+          <t>投保自由配一年定期初次罹患重大傷病健康保險後，於第三年罹患先天性肌肉萎縮症，可以申領重大傷病保險金嗎？</t>
+        </is>
+      </c>
+      <c r="C313" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於第三年罹患先天性肌肉萎縮症，無法申領重大傷病保險金，原因如下：  
+1. 自由配一年定期重大傷病健康保險的保障範圍中，先天性肌肉萎縮症不屬於「全民健康保險重大傷病項目」的保障範圍。  
+2. 保單條款中未明確提及對先天性疾病的除外責任，但因先天性肌肉萎縮症不在保障範圍內，仍不符合理賠條件。  
+3. 第三年罹患疾病的時間點雖已超過等待期間，但該疾病不屬於保單保障範圍，因此不符合理賠條件。
+條文依據：  
+- [附表一：全民健康保險重大傷病項目]  
+- [第十一條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D313" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 重大傷病保險金的給付 | other_metadata | 附表一：全民健康保險重大傷病項目 | 第十三條 重大傷病保險金的申領 | 第十五條 不保事項</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F313" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於第三年罹患先天性肌肉萎縮症，無法申領重大傷病保險金，原因如下：  
+1. 自由配一年定期重大傷病健康保險的保障範圍中，先天性肌肉萎縮症不屬於「全民健康保險重大傷病項目」的保障範圍。  
+2. 保單條款中未明確提及對先天性疾病的除外責任，但因先天性肌肉萎縮症不在保障範圍內，仍不符合理賠條件。  
+3. 第三年罹患疾病的時間點雖已超過等待期間，但該疾病不屬於保單保障範圍，因此不符合理賠條件。
+條文依據：  
+- [附表一：全民健康保險重大傷病項目]  
+- [第十一條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G313" s="2" t="inlineStr"/>
+      <c r="H313" s="2" t="inlineStr"/>
+      <c r="I313" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認自由配一年定期重大傷病健康保險的保障範圍是否包含先天性肌肉萎縮症", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認保單是否對先天性疾病有除外責任或限制", "must_have": true, "分數": 0.8}, {"id": "3", "point": "確認第三年罹患疾病是否符合保單的理賠條件", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認保單是否有針對重大傷病的等待期規定", "must_have": false, "分數": 0.8}, {"id": "5", "point": "確認是否需要提供相關醫療診斷證明文件", "must_have": false, "分數": 0.0}], "coverage_score": 0.8571, "C_conf": 0.8571}</t>
+        </is>
+      </c>
+      <c r="J313" s="4" t="n">
+        <v>0.8571</v>
+      </c>
+      <c r="K313" s="4" t="n"/>
+      <c r="L313" s="4" t="n">
+        <v>0.8571</v>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:23:26</t>
+        </is>
+      </c>
+      <c r="N313" s="4" t="n">
+        <v>21.46</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>CFG</t>
+        </is>
+      </c>
+      <c r="B314" s="2" t="inlineStr">
+        <is>
+          <t>自由配重大疾病(甲型)保障的重大疾病有哪些疾病?</t>
+        </is>
+      </c>
+      <c r="C314" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+自由配重大疾病(甲型)保障的重大疾病包括以下疾病：  
+1. 腦中風後障礙(重度)  
+2. 癱瘓(重度)  
+3. 癌症(重度)  
+4. 急性心肌梗塞(重度)  
+5. 冠狀動脈繞道手術  
+6. 末期腎病變  
+7. 重大器官移植或造血幹細胞移植  
+條文依據：  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D314" s="2" t="inlineStr">
+        <is>
+          <t>國泰人壽自由配一年定期初次罹患重大疾病健康保險(甲型)年繳費率表 | payout_items | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F314" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+自由配重大疾病(甲型)保障的重大疾病包括以下疾病：  
+1. 腦中風後障礙(重度)  
+2. 癱瘓(重度)  
+3. 癌症(重度)  
+4. 急性心肌梗塞(重度)  
+5. 冠狀動脈繞道手術  
+6. 末期腎病變  
+7. 重大器官移植或造血幹細胞移植  
+條文依據：  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G314" s="2" t="inlineStr"/>
+      <c r="H314" s="2" t="inlineStr"/>
+      <c r="I314" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "自由配重大疾病(甲型)保障的重大疾病有哪些疾病?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J314" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K314" s="4" t="n"/>
+      <c r="L314" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:23:35</t>
+        </is>
+      </c>
+      <c r="N314" s="4" t="n">
+        <v>8.82</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B315" s="2" t="inlineStr">
+        <is>
+          <t>被保險人領了2次癌症(重度)追蹤照護金後身故，是否還有尚未給付的保險金供受益人領取?</t>
+        </is>
+      </c>
+      <c r="C315" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 癌症(重度)追蹤照護金的給付次數不影響其他保險金的領取資格，因為條文中未提及該給付次數會限制其他保險金的申領。  
+2. 被保險人身故後，如本契約保險金尚未給付或未完全給付，則以被保險人身故時之法定繼承人為該部分保險金之受益人，並適用民法繼承編之相關規定。[第二十八條 受益人]  
+3. 被保險人身故後，如有「罹癌基因檢測服務未支領金額」，本公司應結算後給付予受益人或其他應得之人。[第十七條 罹癌基因檢測服務未支領金額]  
+條文依據：  
+- 第二十八條 受益人  
+- 第十七條 罹癌基因檢測服務未支領金額</t>
+        </is>
+      </c>
+      <c r="D315" s="2" t="inlineStr">
+        <is>
+          <t>第二十五條 欠繳保險費扣除 | 第二十二條 保險事故的通知與保險給付的申請時間 | 第二十八條 受益人 | 第十七條 罹癌基因檢測服務未支領金額 | 第二十四條 罹癌基因檢測服務未支領金額的申領 | 第六條 第二期以後保險費的交付、寬限期間及契約效力的停止 | 第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用) | 第十一條 契約的終止（三） | 第二十三條 癌症保險金或罹癌基因檢測服務的申領 | payout_items</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F315" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 癌症(重度)追蹤照護金的給付次數不影響其他保險金的領取資格，因為條文中未提及該給付次數會限制其他保險金的申領。  
+2. 被保險人身故後，條文中未提及與身故相關的保險金項目，因此無法確認是否有尚未給付的保險金供受益人領取。  
+條文依據：  
+- 第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供  
+- 找不到相關內容</t>
+        </is>
+      </c>
+      <c r="G315" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 癌症(重度)追蹤照護金的給付次數不影響其他保險金的領取資格，因為條文中未提及該給付次數會限制其他保險金的申領。  
+2. 被保險人身故後，如本契約保險金尚未給付或未完全給付，則以被保險人身故時之法定繼承人為該部分保險金之受益人，並適用民法繼承編之相關規定。[第二十八條 受益人]  
+3. 被保險人身故後，如有「罹癌基因檢測服務未支領金額」，本公司應結算後給付予受益人或其他應得之人。[第十七條 罹癌基因檢測服務未支領金額]  
+條文依據：  
+- 第二十八條 受益人  
+- 第十七條 罹癌基因檢測服務未支領金額</t>
+        </is>
+      </c>
+      <c r="H315" s="2" t="inlineStr"/>
+      <c r="I315" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認癌症(重度)追蹤照護金的給付次數是否影響其他保險金的領取資格", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認被保險人身故後是否有其他保險金項目尚未給付", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認保單中與身故相關的保險金條款", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J315" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K315" s="4" t="n"/>
+      <c r="L315" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:23:58</t>
+        </is>
+      </c>
+      <c r="N315" s="4" t="n">
+        <v>23.11</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B316" s="2" t="inlineStr">
+        <is>
+          <t>保險金額2萬元，「罹癌基因檢測服務」費用8萬元，還會給付多少「癌症(重度)追蹤照護保險金」？</t>
+        </is>
+      </c>
+      <c r="C316" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款，被保險人若選擇申領「罹癌基因檢測服務」，本公司僅提供新臺幣1,000元的補償金額，且無法同時申領「癌症(重度)追蹤照護保險金」。若選擇申領「癌症(重度)追蹤照護保險金」，則按保險金額的12倍給付，即新臺幣24萬元。條款明確指出，兩者不可同時申領，需擇一選擇。
+條文依據：  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]  
+- [附件一：罹癌基因檢測服務之項目、服務費用及補償金額表]</t>
+        </is>
+      </c>
+      <c r="D316" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用) | 第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用) | 第十三條 初次罹患癌症(重度)保險金的給付 | 第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付 | 第二十三條 癌症保險金或罹癌基因檢測服務的申領 | 第十六條 癌症(重度)豁免保險費(第二保險單年度起適用) | 第二條 名詞定義 | 第五條 保險範圍 | 附件一：罹癌基因檢測服務之項目、服務費用及補償金額表 | 第十七條 罹癌基因檢測服務未支領金額 | 第二十二條 保險事故的通知與保險給付的申請時間 | payout_items | other_metadata</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F316" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款，罹癌基因檢測服務費用為新臺幣8萬元，但本公司僅提供新臺幣1,000元的補償金額，且若被保險人選擇申領罹癌基因檢測服務，則無法同時申領癌症(重度)追蹤照護保險金。因此，若被保險人選擇罹癌基因檢測服務，將無法再獲得癌症(重度)追蹤照護保險金的給付。若選擇癌症(重度)追蹤照護保險金，則按保險金額的12倍給付，即新臺幣24萬元。
+條文依據：  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]  
+- [附件一：罹癌基因檢測服務之項目、服務費用及補償金額表]</t>
+        </is>
+      </c>
+      <c r="G316" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款，被保險人若選擇申領「罹癌基因檢測服務」，本公司僅提供新臺幣1,000元的補償金額，且無法同時申領「癌症(重度)追蹤照護保險金」。若選擇申領「癌症(重度)追蹤照護保險金」，則按保險金額的12倍給付，即新臺幣24萬元。條款明確指出，兩者不可同時申領，需擇一選擇。
+條文依據：  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]  
+- [附件一：罹癌基因檢測服務之項目、服務費用及補償金額表]</t>
+        </is>
+      </c>
+      <c r="H316" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款，被保險人若選擇申領「罹癌基因檢測服務」，本公司僅提供新臺幣1,000元的補償金額，且無法同時申領「癌症(重度)追蹤照護保險金」。若選擇申領「癌症(重度)追蹤照護保險金」，則按保險金額的12倍給付，即新臺幣24萬元。條款明確指出，兩者不可同時申領，需擇一選擇。
+條文依據：  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]  
+- [附件一：罹癌基因檢測服務之項目、服務費用及補償金額表]</t>
+        </is>
+      </c>
+      <c r="I316" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認癌症(重度)追蹤照護保險金的保險金額為2萬元", "must_have": true, "分數": 0.0}, {"id": "2", "point": "確認罹癌基因檢測服務費用為8萬元", "must_have": true, "分數": 0.0}, {"id": "3", "point": "確認罹癌基因檢測服務是否屬於癌症(重度)追蹤照護保險金的給付範圍", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認是否有其他相關保險金額或補助可用於支付罹癌基因檢測費用", "must_have": false, "分數": 1.0}], "coverage_score": 0.3846, "C_conf": 0.3846}</t>
+        </is>
+      </c>
+      <c r="J316" s="5" t="n">
+        <v>0.3846</v>
+      </c>
+      <c r="K316" s="4" t="n"/>
+      <c r="L316" s="5" t="n">
+        <v>0.3846</v>
+      </c>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:24:39</t>
+        </is>
+      </c>
+      <c r="N316" s="4" t="n">
+        <v>39.79</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B317" s="2" t="inlineStr">
+        <is>
+          <t>投保後1個月罹患重度癌症，是否已過了等待期間？會給付哪些保險金？契約還會持續有效嗎？</t>
+        </is>
+      </c>
+      <c r="C317" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. **是否已超過等待期間**：投保後1個月（約30天）罹患重度癌症，尚未超過等待期間，因本保險的等待期間為90日。  
+2. **可申請的保險金種類與給付範圍**：由於尚未超過等待期間，根據第十條規定，契約效力將終止，且本公司無息退還已收受之保險費，因此無法申請任何保險金。  
+3. **契約是否仍然有效**：契約將因未超過等待期間而終止，效力不再持續。  
+條文依據：  
+- [第十條 契約的終止（二）]  
+- （本保險「癌症」等待期間為九十日，詳請參閱契約條款）</t>
+        </is>
+      </c>
+      <c r="D317" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 癌症(重度)豁免保險費(第二保險單年度起適用) | 第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用) | 第十三條 初次罹患癌症(重度)保險金的給付 | other_metadata | 第十條 契約的終止（二） | 第十一條 契約的終止（三） | 第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付 | 第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用)</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F317" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. **是否已超過等待期間**：投保後1個月（約30天）罹患重度癌症，尚未超過等待期間，因本保險的等待期間為90日。  
+2. **可申請的保險金種類與給付範圍**：由於尚未超過等待期間，根據第十條規定，契約效力將終止，且本公司無息退還已收受之保險費，因此無法申請任何保險金。  
+3. **契約是否仍然有效**：契約將因未超過等待期間而終止，效力不再持續。  
+條文依據：  
+- [第十條 契約的終止（二）]  
+- （本保險「癌症」等待期間為九十日，詳請參閱契約條款）</t>
+        </is>
+      </c>
+      <c r="G317" s="2" t="inlineStr"/>
+      <c r="H317" s="2" t="inlineStr"/>
+      <c r="I317" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認重度癌症是否已超過等待期間", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認重度癌症可申請的保險金種類與給付範圍", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認罹患重度癌症後保險契約是否仍然有效", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認等待期間的具體規定與計算方式", "must_have": false, "分數": 1.0}, {"id": "5", "point": "確認保險金給付是否影響契約效力", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J317" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K317" s="4" t="n"/>
+      <c r="L317" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:24:56</t>
+        </is>
+      </c>
+      <c r="N317" s="4" t="n">
+        <v>16.44</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B318" s="2" t="inlineStr">
+        <is>
+          <t>投保後10個月罹患重度癌症（第一保單年度），是否已過了等待期間，會給付哪些保險金？契約還會終止嗎？</t>
+        </is>
+      </c>
+      <c r="C318" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. **是否已超過等待期間**：投保後10個月罹患重度癌症，已超過契約生效日起的90日等待期間，因此不受等待期間限制。  
+2. **可申請的保險金種類與給付範圍**：根據條款，被保險人於第一保單年度內初次診斷確定罹患重度癌症，可申請「初次罹患癌症(重度)保險金」，給付金額為「年繳應繳保險費」的1.06倍。  
+3. **保險契約是否會終止**：依條款規定，若被保險人在第一保單年度內符合「初次診斷確定罹患癌症（重度）」並申領保險金，契約效力即行終止。  
+條文依據：  
+- [第十條 契約的終止（二）]  
+- [第十三條 初次罹患癌症(重度)保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D318" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 初次罹患癌症(重度)保險金的給付 | 第十六條 癌症(重度)豁免保險費(第二保險單年度起適用) | 第十條 契約的終止（二） | 第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用) | 第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付 | 第十一條 契約的終止（三） | payout_items | 第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用)</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F318" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. **是否已超過等待期間**：投保後10個月罹患重度癌症，已超過契約生效日起的90日等待期間，因此不受等待期間限制。  
+2. **可申請的保險金種類與給付範圍**：根據條款，被保險人於第一保單年度內初次診斷確定罹患重度癌症，可申請「初次罹患癌症(重度)保險金」，給付金額為「年繳應繳保險費」的1.06倍。  
+3. **保險契約是否會終止**：依條款規定，若被保險人在第一保單年度內符合「初次診斷確定罹患癌症（重度）」並申領保險金，契約效力即行終止。  
+條文依據：  
+- [第十條 契約的終止（二）]  
+- [第十三條 初次罹患癌症(重度)保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G318" s="2" t="inlineStr"/>
+      <c r="H318" s="2" t="inlineStr"/>
+      <c r="I318" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認重度癌症是否已超過等待期間", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認重度癌症可申請的保險金種類與給付範圍", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認罹患重度癌症後保險契約是否會終止", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認第一保單年度內的相關理賠條件", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J318" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K318" s="4" t="n"/>
+      <c r="L318" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:25:16</t>
+        </is>
+      </c>
+      <c r="N318" s="4" t="n">
+        <v>20.55</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B319" s="2" t="inlineStr">
+        <is>
+          <t>投保醫心康愛，罹患肺癌一期(重度癌症)，可領什麼保險金？</t>
+        </is>
+      </c>
+      <c r="C319" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 醫心康愛保險涵蓋重度癌症保障，並於契約有效期間內提供相關保險金給付。  
+2. 肺癌一期屬於重度癌症，符合「初次診斷確定罹患癌症（重度）」的理賠條件。  
+3. 針對重度癌症的保險金給付項目包括：  
+   - 初次罹患癌症（重度）保險金：若診斷確定日在第二保險單年度（含）以後，給付「保險金額」的十二倍。  
+   - 癌症（重度）標靶藥物治療輔助保險金：若於第二保險單年度（含）以後接受標靶治療，給付「保險金額」的十二倍。  
+   - 癌症（重度）追蹤照護保險金：自診斷確定日次一保險單週年日起，每年給付「保險金額」的十二倍，最長五年。  
+   - 癌症（重度）豁免保險費：自診斷確定日起豁免續期保險費。  
+條文依據：  
+- [第十三條 初次罹患癌症(重度)保險金的給付]  
+- [第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用)]  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]  
+- [第十六條 癌症(重度)豁免保險費(第二保險單年度起適用)]  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="D319" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 初次罹患癌症(重度)保險金的給付 | 第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付 | payout_items | 第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用) | 第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用) | 第十六條 癌症(重度)豁免保險費(第二保險單年度起適用) | 第二十三條 癌症保險金或罹癌基因檢測服務的申領 | 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F319" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 醫心康愛保險涵蓋重度癌症保障，並於契約有效期間內提供相關保險金給付。  
+2. 肺癌一期屬於重度癌症，符合「初次診斷確定罹患癌症（重度）」的理賠條件。  
+3. 針對重度癌症的保險金給付項目包括：  
+   - 初次罹患癌症（重度）保險金：若診斷確定日在第二保險單年度（含）以後，給付「保險金額」的十二倍。  
+   - 癌症（重度）標靶藥物治療輔助保險金：若於第二保險單年度（含）以後接受標靶治療，給付「保險金額」的十二倍。  
+   - 癌症（重度）追蹤照護保險金：自診斷確定日次一保險單週年日起，每年給付「保險金額」的十二倍，最長五年。  
+   - 癌症（重度）豁免保險費：自診斷確定日起豁免續期保險費。  
+條文依據：  
+- [第十三條 初次罹患癌症(重度)保險金的給付]  
+- [第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用)]  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]  
+- [第十六條 癌症(重度)豁免保險費(第二保險單年度起適用)]  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="G319" s="2" t="inlineStr"/>
+      <c r="H319" s="2" t="inlineStr"/>
+      <c r="I319" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認醫心康愛保險是否涵蓋重度癌症保障", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認肺癌一期是否符合重度癌症的理賠定義", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認醫心康愛保險針對重度癌症的保險金給付項目", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認是否有額外的住院或手術相關保險金給付", "must_have": false, "分數": 0.0}], "coverage_score": 0.9231, "C_conf": 0.9231}</t>
+        </is>
+      </c>
+      <c r="J319" s="4" t="n">
+        <v>0.9231</v>
+      </c>
+      <c r="K319" s="4" t="n"/>
+      <c r="L319" s="4" t="n">
+        <v>0.9231</v>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:25:36</t>
+        </is>
+      </c>
+      <c r="N319" s="4" t="n">
+        <v>19.27</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>PX5</t>
+        </is>
+      </c>
+      <c r="B320" s="2" t="inlineStr">
+        <is>
+          <t>若被保險人身故有何給付?未到期保險費如何處理？尚未給付或未完全給付的保險金如何處理？</t>
+        </is>
+      </c>
+      <c r="C320" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 被保險人身故時，若本附約保險金尚未給付或未完全給付，則以被保險人之法定繼承人為受益人，並依民法繼承編相關規定分配。  
+2. 未到期保險費應從當期已繳保險費中扣除按日數比例計算已經過期間之保險費後，將其未到期保險費無息退還要保人。  
+3. 尚未給付或未完全給付的保險金，應由被保險人之法定繼承人依民法繼承編相關規定分配。  
+條文依據：  
+- [第十條 附約的終止（二）]  
+- [第二十條 受益人]</t>
+        </is>
+      </c>
+      <c r="D320" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 保險事故的通知與保險金的申請時間 | 第二十條 受益人 | 第十二條 重大疾病保險金的給付 | 第十七條 欠繳保險費的扣除 | 第十一條 輕度重大疾病保險金的給付 | 第十條 附約的終止（二） | 第六條 第二期以後保險費及續保保險費的交付、寬限期間及附約效力的停止 | 第九條 附約的終止（一）</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F320" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 被保險人身故時，若本附約保險金尚未給付或未完全給付，則以被保險人之法定繼承人為受益人，並依民法繼承編相關規定分配。  
+2. 未到期保險費應從當期已繳保險費中扣除按日數比例計算已經過期間之保險費後，將其未到期保險費無息退還要保人。  
+3. 尚未給付或未完全給付的保險金，應由被保險人之法定繼承人依民法繼承編相關規定分配。  
+條文依據：  
+- [第十條 附約的終止（二）]  
+- [第二十條 受益人]</t>
+        </is>
+      </c>
+      <c r="G320" s="2" t="inlineStr"/>
+      <c r="H320" s="2" t="inlineStr"/>
+      <c r="I320" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認被保險人身故時的保險金給付內容", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認未到期保險費的處理方式", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認尚未給付或未完全給付的保險金處理方式", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認保單條款中對相關給付的具體規定", "must_have": false, "分數": 0.5}], "coverage_score": 0.9615, "C_conf": 0.9615}</t>
+        </is>
+      </c>
+      <c r="J320" s="4" t="n">
+        <v>0.9615</v>
+      </c>
+      <c r="K320" s="4" t="n"/>
+      <c r="L320" s="4" t="n">
+        <v>0.9615</v>
+      </c>
+      <c r="M320" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:26:04</t>
+        </is>
+      </c>
+      <c r="N320" s="4" t="n">
+        <v>28.09</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>PX5</t>
+        </is>
+      </c>
+      <c r="B321" s="2" t="inlineStr">
+        <is>
+          <t>投保鍾溢祝福後，請問在第二年經醫院醫師初次診斷罹患「輕度重大疾病」中的癌症(輕度)者，可以領到輕度重大疾病保險金嗎?可以領到保險金額的百分之多少?</t>
+        </is>
+      </c>
+      <c r="C321" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+投保鍾溢祝福後，若在第二年經醫院醫師初次診斷罹患「輕度重大疾病」中的癌症(輕度)，可以領取輕度重大疾病保險金，給付比例為保險金額的百分之二十。  
+條文依據：  
+- [第十一條 輕度重大疾病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D321" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 輕度重大疾病保險金的給付 | 第十二條 重大疾病保險金的給付 | other_metadata | payout_items | 國泰人壽鍾溢祝福重大疾病健康保險附約(乙型) (外溢型)年繳費率表 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F321" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+投保鍾溢祝福後，若在第二年經醫院醫師初次診斷罹患「輕度重大疾病」中的癌症(輕度)，可以領取輕度重大疾病保險金，給付比例為保險金額的百分之二十。  
+條文依據：  
+- [第十一條 輕度重大疾病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G321" s="2" t="inlineStr"/>
+      <c r="H321" s="2" t="inlineStr"/>
+      <c r="I321" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認保單是否涵蓋輕度重大疾病保障", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認輕度重大疾病保障是否包含輕度癌症", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認第二年初次診斷是否符合保單理賠條件", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認輕度重大疾病保險金的給付比例或金額", "must_have": true, "分數": 1.0}, {"id": "5", "point": "確認保單是否有特定條款影響理賠比例", "must_have": false, "分數": 0.5}], "coverage_score": 0.9706, "C_conf": 0.9706}</t>
+        </is>
+      </c>
+      <c r="J321" s="4" t="n">
+        <v>0.9706</v>
+      </c>
+      <c r="K321" s="4" t="n"/>
+      <c r="L321" s="4" t="n">
+        <v>0.9706</v>
+      </c>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:26:25</t>
+        </is>
+      </c>
+      <c r="N321" s="4" t="n">
+        <v>21.17</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>PX5</t>
+        </is>
+      </c>
+      <c r="B322" s="2" t="inlineStr">
+        <is>
+          <t>請問如果在投保後的第三年經醫院醫師初次診斷罹患「重大疾病」者，可以領到重大疾病保險金嗎?可以領到保險金額的百分之多少?那後續又在第四年經醫院醫師初次診斷罹患「輕度重大疾病」者，可以領到輕度重大疾病保險金嗎?可以領到保險金額的百分之多少?</t>
+        </is>
+      </c>
+      <c r="C322" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 在投保後的第三年，若被保險人經醫院醫師初次診斷罹患「重大疾病」，符合條件者可領取重大疾病保險金，給付比例為保險金額的1.3倍。  
+2. 在第四年，若被保險人經醫院醫師初次診斷罹患「輕度重大疾病」，符合條件者可領取輕度重大疾病保險金，給付比例為保險金額的20%。  
+條文依據：  
+- [第十二條 重大疾病保險金的給付]  
+- [第十一條 輕度重大疾病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D322" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 輕度重大疾病保險金的給付 | 第十二條 重大疾病保險金的給付 | 第十六條 除外責任 | payout_items | 第二條 名詞定義 | 第四條 保險範圍 | other_metadata | 國泰人壽鍾溢祝福重大疾病健康保險附約(乙型) (外溢型)年繳費率表</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F322" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 在投保後的第三年，若被保險人經醫院醫師初次診斷罹患「重大疾病」，符合條件者可領取重大疾病保險金，給付比例為保險金額的1.3倍。  
+2. 在第四年，若被保險人經醫院醫師初次診斷罹患「輕度重大疾病」，符合條件者可領取輕度重大疾病保險金，給付比例為保險金額的20%。  
+條文依據：  
+- [第十二條 重大疾病保險金的給付]  
+- [第十一條 輕度重大疾病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G322" s="2" t="inlineStr"/>
+      <c r="H322" s="2" t="inlineStr"/>
+      <c r="I322" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認重大疾病保險金的給付條件是否符合第三年初次診斷的情況", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認重大疾病保險金的給付比例或金額", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認輕度重大疾病保險金的給付條件是否符合第四年初次診斷的情況", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認輕度重大疾病保險金的給付比例或金額", "must_have": true, "分數": 1.0}, {"id": "5", "point": "確認重大疾病與輕度重大疾病是否屬於同一保單範疇或不同保障範圍", "must_have": false, "分數": 0.0}], "coverage_score": 0.9412, "C_conf": 0.9412}</t>
+        </is>
+      </c>
+      <c r="J322" s="4" t="n">
+        <v>0.9412</v>
+      </c>
+      <c r="K322" s="4" t="n"/>
+      <c r="L322" s="4" t="n">
+        <v>0.9412</v>
+      </c>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:26:40</t>
+        </is>
+      </c>
+      <c r="N322" s="4" t="n">
+        <v>14.74</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>PX5</t>
+        </is>
+      </c>
+      <c r="B323" s="2" t="inlineStr">
+        <is>
+          <t>請問如果在投保後的第三年經醫院醫師初次診斷罹患「輕度重大疾病」者，可以領到重大疾病保險金嗎?可以領到保險金額的百分之多少?那後續又在第四年經醫院醫師初次診斷罹患「重大疾病」者，可以領到輕度重大疾病保險金嗎?可以領到保險金額的百分之多少?</t>
+        </is>
+      </c>
+      <c r="C323" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 在投保後的第三年經醫院醫師初次診斷罹患「輕度重大疾病」者，符合保單條款的理賠範圍，可領取「輕度重大疾病保險金」，給付比例為保險金額的20%。  
+2. 在第四年經醫院醫師初次診斷罹患「重大疾病」者，符合保單條款的理賠範圍，但因已於第三年申領過「輕度重大疾病保險金」，依第十二條規定，重大疾病保險金的給付金額需扣除已給付的輕度重大疾病保險金，最終給付比例為保險金額的130%減去20%，即保險金額的110%。
+條文依據：  
+- [第十一條 輕度重大疾病保險金的給付]  
+- [第十二條 重大疾病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D323" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 輕度重大疾病保險金的給付 | 第十二條 重大疾病保險金的給付 | 第十六條 除外責任 | payout_items | 第二條 名詞定義 | 第四條 保險範圍 | other_metadata | 第十五條 各項保險金的申領</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F323" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 在投保後的第三年經醫院醫師初次診斷罹患「輕度重大疾病」者，符合保單條款的理賠範圍，可領取「輕度重大疾病保險金」，給付比例為保險金額的20%。  
+2. 在第四年經醫院醫師初次診斷罹患「重大疾病」者，符合保單條款的理賠範圍，但因已於第三年申領過「輕度重大疾病保險金」，依第十二條規定，重大疾病保險金的給付金額需扣除已給付的輕度重大疾病保險金，最終給付比例為保險金額的130%減去20%，即保險金額的110%。
+條文依據：  
+- [第十一條 輕度重大疾病保險金的給付]  
+- [第十二條 重大疾病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G323" s="2" t="inlineStr"/>
+      <c r="H323" s="2" t="inlineStr"/>
+      <c r="I323" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認輕度重大疾病是否符合保單條款的理賠範圍", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認重大疾病是否符合保單條款的理賠範圍", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認輕度重大疾病保險金的給付比例或金額", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認重大疾病保險金的給付比例或金額", "must_have": true, "分數": 1.0}, {"id": "5", "point": "確認輕度重大疾病理賠後是否影響後續重大疾病的理賠資格或金額", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J323" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K323" s="4" t="n"/>
+      <c r="L323" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:26:59</t>
+        </is>
+      </c>
+      <c r="N323" s="4" t="n">
+        <v>18.58</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>PX5</t>
+        </is>
+      </c>
+      <c r="B324" s="2" t="inlineStr">
+        <is>
+          <t>請問主約效力終止(因身故以外情形)，PX5還能持續有效嗎？</t>
+        </is>
+      </c>
+      <c r="C324" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+主約效力因身故以外的情形終止時，PX5附約仍可持續有效，但需符合以下條件：  
+1. 要保人需繼續繳交附約保險費。  
+2. 附約效力可延續至主約原保險期間屆滿或附約最高續保年齡（以較早者為準）。  
+條文依據：  
+- [第十條 附約的終止（二）]</t>
+        </is>
+      </c>
+      <c r="D324" s="2" t="inlineStr">
+        <is>
+          <t>第十條 附約的終止（二） | 第七條 保險費的墊繳、附約的停效及復效 | 第五條 附約的保險期間及保證續保 | 第十三條 健康促進保險費折減 | 第九條 附約的終止（一）</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F324" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+主約效力因身故以外的情形終止時，PX5附約仍可持續有效，但需符合以下條件：  
+1. 要保人需繼續繳交附約保險費。  
+2. 附約效力可延續至主約原保險期間屆滿或附約最高續保年齡（以較早者為準）。  
+條文依據：  
+- [第十條 附約的終止（二）]</t>
+        </is>
+      </c>
+      <c r="G324" s="2" t="inlineStr"/>
+      <c r="H324" s="2" t="inlineStr"/>
+      <c r="I324" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "請問主約效力終止(因身故以外情形)，PX5還能持續有效嗎？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J324" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K324" s="4" t="n"/>
+      <c r="L324" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:27:10</t>
+        </is>
+      </c>
+      <c r="N324" s="4" t="n">
+        <v>11.13</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B325" s="2" t="inlineStr">
+        <is>
+          <t>請問如果於「無理賠紀錄期間」屆滿日以內罹患特定傷病，會給付多少錢?這筆錢會給付給誰?</t>
+        </is>
+      </c>
+      <c r="C325" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在「無理賠紀錄期間」屆滿日以內罹患特定傷病，保險公司將給付的金額為「保險金額」加上「年繳應繳保險費總額」乘以1.02的加總。這筆「特定傷病保險金」的受益人為被保險人本人，且不得指定或變更。
+條文依據：  
+- [第十一條 特定傷病保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="D325" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第十二條 無理賠關懷保險金的給付 | 第十一條 特定傷病保險金的給付 | payout_items | 第二十七條 受益人的指定及變更</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F325" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在「無理賠紀錄期間」屆滿日以內罹患特定傷病，保險公司將給付的金額為「保險金額」加上「年繳應繳保險費總額」乘以1.02的加總。這筆「特定傷病保險金」的受益人為被保險人本人，且不得指定或變更。
+條文依據：  
+- [第十一條 特定傷病保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="G325" s="2" t="inlineStr"/>
+      <c r="H325" s="2" t="inlineStr"/>
+      <c r="I325" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "請問如果於「無理賠紀錄期間」屆滿日以內罹患特定傷病，會給付多少錢?這筆錢會給付給誰?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J325" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K325" s="4" t="n"/>
+      <c r="L325" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M325" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:27:19</t>
+        </is>
+      </c>
+      <c r="N325" s="4" t="n">
+        <v>8.66</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B326" s="2" t="inlineStr">
+        <is>
+          <t>請問如果要保人與被保險人為同一人，被保險人於「無理賠紀錄期間」屆滿日以內身故，會給付多少錢?這筆錢會給付給誰?</t>
+        </is>
+      </c>
+      <c r="C326" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+在要保人與被保險人為同一人的情況下，若被保險人於「無理賠紀錄期間」屆滿日以內身故，依第十二條規定，本公司將給付「無理賠關懷保險金」，金額為「年繳應繳保險費總額」乘以1.02。根據第二十七條，無理賠關懷保險金的受益人為要保人本人，若要保人與被保險人為同一人，則受益人為被保險人的法定繼承人。
+條文依據：  
+- [第十二條 無理賠關懷保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="D326" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第十二條 無理賠關懷保險金的給付 | 第十一條 特定傷病保險金的給付 | payout_items | 第十九條 失蹤處理 | 第二十一條 無理賠關懷保險金的申領 | 第二十七條 受益人的指定及變更 | 第十七條 除外責任（二）</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F326" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+在要保人與被保險人為同一人的情況下，若被保險人於「無理賠紀錄期間」屆滿日以內身故，依第十二條規定，本公司將給付「無理賠關懷保險金」，金額為「年繳應繳保險費總額」乘以1.02。根據第二十七條，無理賠關懷保險金的受益人為要保人本人，若要保人與被保險人為同一人，則受益人為被保險人的法定繼承人。
+條文依據：  
+- [第十二條 無理賠關懷保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="G326" s="2" t="inlineStr"/>
+      <c r="H326" s="2" t="inlineStr"/>
+      <c r="I326" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認要保人與被保險人為同一人的情況下，身故保險金的給付金額", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認被保險人在無理賠紀錄期間屆滿日以內身故的保險金給付條件", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認身故保險金的受益人為何人", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認無理賠紀錄期間是否影響保險金額計算", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J326" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K326" s="4" t="n"/>
+      <c r="L326" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:27:34</t>
+        </is>
+      </c>
+      <c r="N326" s="4" t="n">
+        <v>14.26</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B327" s="2" t="inlineStr">
+        <is>
+          <t>請問如果要保人與被保險人為不同人，被保險人於「無理賠紀錄期間」屆滿日以內生存，且被保險人未罹患特定傷病，會給付多少錢?這筆錢會給付給誰?</t>
+        </is>
+      </c>
+      <c r="C327" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若要保人與被保險人為不同人，且被保險人在「無理賠紀錄期間」屆滿日以內生存，並未罹患特定傷病，則符合給付「無理賠關懷保險金」的條件。給付金額為「年繳應繳保險費總額」乘以1.02。該筆保險金的受益人為要保人本人。
+條文依據：  
+- [第十二條 無理賠關懷保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="D327" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第十二條 無理賠關懷保險金的給付 | 第十一條 特定傷病保險金的給付 | payout_items | 第二十七條 受益人的指定及變更 | 第十九條 失蹤處理 | 第二十一條 無理賠關懷保險金的申領 | 第十七條 除外責任（二）</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F327" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若要保人與被保險人為不同人，且被保險人在「無理賠紀錄期間」屆滿日以內生存，並未罹患特定傷病，則符合給付「無理賠關懷保險金」的條件。給付金額為「年繳應繳保險費總額」乘以1.02。該筆保險金的受益人為要保人本人。
+條文依據：  
+- [第十二條 無理賠關懷保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="G327" s="2" t="inlineStr"/>
+      <c r="H327" s="2" t="inlineStr"/>
+      <c r="I327" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認要保人與被保險人為不同人時的保險條款適用", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認無理賠紀錄期間屆滿日以內生存的給付金額", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認被保險人未罹患特定傷病的條件對給付的影響", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認該筆給付金的受益人為何人", "must_have": true, "分數": 1.0}, {"id": "5", "point": "確認特定傷病的定義與範圍", "must_have": false, "分數": 0.0}], "coverage_score": 0.9412, "C_conf": 0.9412}</t>
+        </is>
+      </c>
+      <c r="J327" s="4" t="n">
+        <v>0.9412</v>
+      </c>
+      <c r="K327" s="4" t="n"/>
+      <c r="L327" s="4" t="n">
+        <v>0.9412</v>
+      </c>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:27:48</t>
+        </is>
+      </c>
+      <c r="N327" s="4" t="n">
+        <v>14.53</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B328" s="2" t="inlineStr">
+        <is>
+          <t>保戶如果身故，會給保險金嗎?身故保險金、特定傷病保險金及無理賠關懷保險金？</t>
+        </is>
+      </c>
+      <c r="C328" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. **身故保險金**：條款未明確規定／資料不足。  
+2. **特定傷病保險金**：特定傷病保險金僅適用於被保險人於等待期間屆滿後，經診斷確定罹患特定傷病的情況，並不適用於單純的身故情況 [第十一條 特定傷病保險金的給付]。  
+3. **無理賠關懷保險金**：被保險人於「無理賠紀錄期間」內未曾因罹患特定傷病而申領特定傷病保險金，且於「無理賠紀錄期間」內身故或於「無理賠紀錄期間」屆滿時仍生存者，符合無理賠關懷保險金的給付條件 [第十二條 無理賠關懷保險金的給付]。</t>
+        </is>
+      </c>
+      <c r="D328" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第十條 契約的終止（二） | 第十九條 失蹤處理 | 第二十一條 無理賠關懷保險金的申領 | 第二十二條 分期定期保險金給付申領文件、給付期限及未依限給付之效果 | 第二十八條 本契約受益人死亡或失蹤的處理 | 第十一條 特定傷病保險金的給付 | 第十二條 無理賠關懷保險金的給付 | 第二十條 特定傷病保險金的申領 | 第十七條 除外責任（二）</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F328" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. **身故保險金**：條文中未提及「身故保險金」的給付條件，因此無法確認是否有此項保險金或其適用範圍。  
+2. **特定傷病保險金**：特定傷病保險金僅適用於被保險人於等待期間屆滿後，經診斷確定罹患特定傷病的情況，並不適用於單純的身故情況。  
+3. **無理賠關懷保險金**：若被保險人在「無理賠紀錄期間」內未曾申領特定傷病保險金，且於該期間內身故，則符合無理賠關懷保險金的給付條件。
+條文依據：  
+- [第十二條 無理賠關懷保險金的給付]  
+- [第十一條 特定傷病保險金的給付]  
+- 找不到相關條文提及「身故保險金」</t>
+        </is>
+      </c>
+      <c r="G328" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. **身故保險金**：條款未明確規定／資料不足。  
+2. **特定傷病保險金**：特定傷病保險金僅適用於被保險人於等待期間屆滿後，經診斷確定罹患特定傷病的情況，並不適用於單純的身故情況 [第十一條 特定傷病保險金的給付]。  
+3. **無理賠關懷保險金**：若被保險人在「無理賠紀錄期間」內未曾申領特定傷病保險金，且於該期間內身故，則符合無理賠關懷保險金的給付條件 [第十二條 無理賠關懷保險金的給付]。</t>
+        </is>
+      </c>
+      <c r="H328" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. **身故保險金**：條款未明確規定／資料不足。  
+2. **特定傷病保險金**：特定傷病保險金僅適用於被保險人於等待期間屆滿後，經診斷確定罹患特定傷病的情況，並不適用於單純的身故情況 [第十一條 特定傷病保險金的給付]。  
+3. **無理賠關懷保險金**：被保險人於「無理賠紀錄期間」內未曾因罹患特定傷病而申領特定傷病保險金，且於「無理賠紀錄期間」內身故或於「無理賠紀錄期間」屆滿時仍生存者，符合無理賠關懷保險金的給付條件 [第十二條 無理賠關懷保險金的給付]。</t>
+        </is>
+      </c>
+      <c r="I328" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認保戶身故是否符合保險金給付條件", "must_have": true, "分數": 0.5}, {"id": "2", "point": "確認身故保險金的給付條件與範圍", "must_have": true, "分數": 0.5}, {"id": "3", "point": "確認特定傷病保險金是否適用於身故情況", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認無理賠關懷保險金的適用條件", "must_have": false, "分數": 1.0}], "coverage_score": 0.6923, "C_conf": 0.6923}</t>
+        </is>
+      </c>
+      <c r="J328" s="5" t="n">
+        <v>0.6923</v>
+      </c>
+      <c r="K328" s="4" t="n"/>
+      <c r="L328" s="5" t="n">
+        <v>0.6923</v>
+      </c>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:28:24</t>
+        </is>
+      </c>
+      <c r="N328" s="4" t="n">
+        <v>35.29</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B329" s="2" t="inlineStr">
+        <is>
+          <t>保戶如果身故，身故申領的保險金會給誰?</t>
+        </is>
+      </c>
+      <c r="C329" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人身故，身故保險金的受益人依以下規定處理：  
+1. 若受益人已指定，則由指定的受益人領取。  
+2. 若受益人未指定或受益人喪失受益權，則保險金作為被保險人的遺產，由其法定繼承人依民法繼承編相關規定分配。  
+3. 若受益人為多數，且部分受益人喪失受益權，其應得部分按原約定比例分配給其他受益人。
+條文依據：  
+- [第二十三條 受益人受益權之喪失]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="D329" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第二十三條 受益人受益權之喪失 | 第二十七條 受益人的指定及變更 | 第二十八條 本契約受益人死亡或失蹤的處理 | 第二十二條 分期定期保險金給付申領文件、給付期限及未依限給付之效果</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F329" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人身故，身故保險金的受益人依以下規定處理：  
+1. 若受益人已指定，則由指定的受益人領取。  
+2. 若受益人未指定或受益人喪失受益權，則保險金作為被保險人的遺產，由其法定繼承人依民法繼承編相關規定分配。  
+3. 若受益人為多數，且部分受益人喪失受益權，其應得部分按原約定比例分配給其他受益人。
+條文依據：  
+- [第二十三條 受益人受益權之喪失]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="G329" s="2" t="inlineStr"/>
+      <c r="H329" s="2" t="inlineStr"/>
+      <c r="I329" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "保戶如果身故，身故申領的保險金會給誰?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J329" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K329" s="4" t="n"/>
+      <c r="L329" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M329" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:28:36</t>
+        </is>
+      </c>
+      <c r="N329" s="4" t="n">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B330" s="2" t="inlineStr">
+        <is>
+          <t>如果保戶投保繳費年期20年的滿溢寶，然後在第20保單年度身故的話，可以領到多少錢?無理賠關懷保險金?受益人為要保人嗎？</t>
+        </is>
+      </c>
+      <c r="C330" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 在第20保單年度身故，若符合條件，保險公司應依「特定傷病保險金」或「無理賠關懷保險金」的相關條款給付保險金。具體金額需依保單條款及實際情況計算。  
+2. 若被保險人在「無理賠紀錄期間」內未曾申領特定傷病保險金，且於該期間內身故，則符合無理賠關懷保險金的給付條件，金額為「年繳應繳保險費總額」乘以1.02。  
+3. 無理賠關懷保險金的受益人為要保人本人，保險公司不受理其指定及變更。若要保人已身故，則以被保險人為受益人；若被保險人也已身故，則以被保險人的法定繼承人為受益人。
+條文依據：  
+- [第二十七條 受益人的指定及變更]  
+- [第十二條 無理賠關懷保險金的給付]  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="D330" s="2" t="inlineStr">
+        <is>
+          <t>第二十七條 受益人的指定及變更 | 第十九條 失蹤處理 | 第十二條 無理賠關懷保險金的給付 | 第十七條 除外責任（二） | other_metadata | 第二十一條 無理賠關懷保險金的申領 | 第二十八條 本契約受益人死亡或失蹤的處理 | 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F330" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 在第20保單年度身故，若符合條件，保險公司應依「特定傷病保險金」或「無理賠關懷保險金」的相關條款給付保險金。具體金額需依保單條款及實際情況計算。  
+2. 若被保險人在「無理賠紀錄期間」內未曾申領特定傷病保險金，且於該期間內身故，則符合無理賠關懷保險金的給付條件，金額為「年繳應繳保險費總額」乘以1.02。  
+3. 無理賠關懷保險金的受益人為要保人本人，保險公司不受理其指定及變更。若要保人已身故，則以被保險人為受益人；若被保險人也已身故，則以被保險人的法定繼承人為受益人。
+條文依據：  
+- [第二十七條 受益人的指定及變更]  
+- [第十二條 無理賠關懷保險金的給付]  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="G330" s="2" t="inlineStr"/>
+      <c r="H330" s="2" t="inlineStr"/>
+      <c r="I330" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認滿溢寶在第20保單年度身故的保險金給付金額", "must_have": true, "分數": 0.8}, {"id": "2", "point": "確認是否包含無理賠關懷保險金的給付", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認受益人是否為要保人", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認滿溢寶的保險金計算方式或條件", "must_have": false, "分數": 0.7}], "coverage_score": 0.9154, "C_conf": 0.9154}</t>
+        </is>
+      </c>
+      <c r="J330" s="4" t="n">
+        <v>0.9154</v>
+      </c>
+      <c r="K330" s="4" t="n"/>
+      <c r="L330" s="4" t="n">
+        <v>0.9154</v>
+      </c>
+      <c r="M330" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:28:53</t>
+        </is>
+      </c>
+      <c r="N330" s="4" t="n">
+        <v>16.31</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B331" s="2" t="inlineStr">
+        <is>
+          <t>被保險人為60歲女性，投保繳費期間20年期之滿溢寶特定傷病定期健康保險（定期給付型）（外溢型）100萬元，年繳應繳保險費為83,500元，年繳實繳保險費為78,490元。若被保險人於第二保險單年度自殺身故，則無理賠關懷保險金可以領到多少錢？</t>
+        </is>
+      </c>
+      <c r="C331" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於第二保險單年度內自殺身故，根據條款規定，自契約訂立或復效之日起二年內因故意自殺致死者，本公司不負給付無理賠關懷保險金的責任。因此，本案例中無理賠關懷保險金無法領取。
+條文依據：  
+- [第十七條 除外責任（二）]  
+- [第十二條 無理賠關懷保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D331" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 無理賠關懷保險金的給付 | 第十七條 除外責任（二） | 第十一條 特定傷病保險金的給付 | other_metadata | 第十九條 失蹤處理 | 第五條 保險範圍 | 第二十一條 無理賠關懷保險金的申領 | 第二十七條 受益人的指定及變更</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F331" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於第二保險單年度內自殺身故，根據條款規定，自契約訂立或復效之日起二年內因故意自殺致死者，本公司不負給付無理賠關懷保險金的責任。因此，本案例中無理賠關懷保險金無法領取。
+條文依據：  
+- [第十七條 除外責任（二）]  
+- [第十二條 無理賠關懷保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G331" s="2" t="inlineStr"/>
+      <c r="H331" s="2" t="inlineStr"/>
+      <c r="I331" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認保險商品是否涵蓋自殺身故的理賠條款", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認第二保險單年度內自殺身故的理賠規定", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認無理賠關懷保險金的計算方式或金額", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認年繳實繳保險費是否影響無理賠關懷保險金的金額", "must_have": false, "分數": 0.0}], "coverage_score": 0.9231, "C_conf": 0.9231}</t>
+        </is>
+      </c>
+      <c r="J331" s="4" t="n">
+        <v>0.9231</v>
+      </c>
+      <c r="K331" s="4" t="n"/>
+      <c r="L331" s="4" t="n">
+        <v>0.9231</v>
+      </c>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:29:09</t>
+        </is>
+      </c>
+      <c r="N331" s="4" t="n">
+        <v>14.32</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B332" s="2" t="inlineStr">
+        <is>
+          <t>請問如果第2保單年度罹患特定傷病，可以給付多少錢?給付給誰?未來還有其他保險金嗎?</t>
+        </is>
+      </c>
+      <c r="C332" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. **給付金額**：若於第二保險單年度（含）以後罹患特定傷病，將依「保險金額」給付「特定傷病保險金」。  
+2. **給付對象**：保險金給付予被保險人或其指定受益人。  
+3. **未來保險金**：自初次診斷確定罹患特定傷病的次一個保險單週年日起，每逢保險單週年日仍生存者，可按「保險金額」的36%給付「生活補助保險金」，最多給付10次。此外，自診斷確定日起，豁免續期保險費，但當期已繳付之未到期保險費不予退還。
+條文依據：  
+- [第十二條 特定傷病保險金的給付]  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]  
+- [第十五條 保險費豁免（第二保險單年度起適用）]</t>
+        </is>
+      </c>
+      <c r="D332" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 特定傷病保險金的給付 | 第五條 保險範圍 | 第十三條 生活補助保險金的給付（第二保險單年度起適用） | 第二條 名詞定義 | 第十五條 保險費豁免（第二保險單年度起適用）</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F332" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. **給付金額**：若於第二保險單年度（含）以後罹患特定傷病，將依「保險金額」給付「特定傷病保險金」。  
+2. **給付對象**：保險金給付予被保險人或其指定受益人。  
+3. **未來保險金**：自初次診斷確定罹患特定傷病的次一個保險單週年日起，每逢保險單週年日仍生存者，可按「保險金額」的36%給付「生活補助保險金」，最多給付10次。此外，自診斷確定日起，豁免續期保險費，但當期已繳付之未到期保險費不予退還。
+條文依據：  
+- [第十二條 特定傷病保險金的給付]  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]  
+- [第十五條 保險費豁免（第二保險單年度起適用）]</t>
+        </is>
+      </c>
+      <c r="G332" s="2" t="inlineStr"/>
+      <c r="H332" s="2" t="inlineStr"/>
+      <c r="I332" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "請問如果第2保單年度罹患特定傷病，可以給付多少錢?給付給誰?未來還有其他保險金嗎?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J332" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K332" s="4" t="n"/>
+      <c r="L332" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:29:19</t>
+        </is>
+      </c>
+      <c r="N332" s="4" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B333" s="2" t="inlineStr">
+        <is>
+          <t>請問我115年1月1日投保，怎麼得到健康促進保險費折減?指定日期什麼時後？</t>
+        </is>
+      </c>
+      <c r="C333" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. **健康促進保險費折減的申請條件**：被保險人需使用保險公司指定的程式並加入指定的健康計劃，於「指定日期」達到符合會員等級標準（如「實踐家」或「樂享家」等級）。符合條件者，次一保險單年度的保險費可按會員等級享有折減比例（如實踐家3%、樂享家或更高等級10%）。  
+2. **115年1月1日投保是否符合折減資格**：115年1月1日投保後，需完成指定程式的註冊程序，並授權保險公司取得健康促進相關電子紀錄，保險公司將依據成功傳輸的紀錄計算會員等級。若於「指定日期」符合會員等級標準，則可享次一保險單年度的保險費折減。  
+3. **指定日期及適用時間**：條文未明確說明「指定日期」的具體定義，但折減適用於次一保險單年度的保險費。  
+條文依據：  
+- [第十六條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="D333" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 健康促進保險費折減 | 第十五條 保險費豁免（第二保險單年度起適用） | 第五條 保險範圍 | 第二十三條 投保年齡的計算及錯誤的處理 | 第十二條 特定傷病保險金的給付 | 第十條 契約的終止（二） | 第十三條 生活補助保險金的給付（第二保險單年度起適用） | payout_items</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F333" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. **健康促進保險費折減的申請條件**：被保險人需使用保險公司指定的程式並加入指定的健康計劃，於「指定日期」達到符合會員等級標準（如「實踐家」或「樂享家」等級）。符合條件者，次一保險單年度的保險費可按會員等級享有折減比例（如實踐家3%、樂享家或更高等級10%）。  
+2. **115年1月1日投保是否符合折減資格**：115年1月1日投保後，需完成指定程式的註冊程序，並授權保險公司取得健康促進相關電子紀錄，保險公司將依據成功傳輸的紀錄計算會員等級。若於「指定日期」符合會員等級標準，則可享次一保險單年度的保險費折減。  
+3. **指定日期及適用時間**：條文未明確說明「指定日期」的具體定義，但折減適用於次一保險單年度的保險費。  
+條文依據：  
+- [第十六條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="G333" s="2" t="inlineStr"/>
+      <c r="H333" s="2" t="inlineStr"/>
+      <c r="I333" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認健康促進保險費折減的申請條件", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認115年1月1日投保是否符合折減資格", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認健康促進保險費折減的指定日期及適用時間", "must_have": true, "分數": 0.8}, {"id": "4", "point": "確認健康促進保險費折減的申請流程", "must_have": false, "分數": 0.5}], "coverage_score": 0.9, "C_conf": 0.9}</t>
+        </is>
+      </c>
+      <c r="J333" s="4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K333" s="4" t="n"/>
+      <c r="L333" s="4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M333" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:29:34</t>
+        </is>
+      </c>
+      <c r="N333" s="4" t="n">
+        <v>14.49</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B334" s="2" t="inlineStr">
+        <is>
+          <t>保戶在114/1/10投保樂鍾溢，如果他在115/3/30罹患特定傷病的話，在什麼時候可以領取生活補助保險金?</t>
+        </is>
+      </c>
+      <c r="C334" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 樂鍾溢保單包含生活補助保險金保障，且該項保障於第二保險單年度（含）以後適用。  
+2. 根據條款，生活補助保險金的給付條件為：被保險人於第二保險單年度（含）以後初次診斷確定罹患特定傷病，並於初次診斷確定的次一個保險單週年日起，每逢保險單週年日仍生存者，保險公司將按保險金額的36%給付生活補助保險金。  
+3. 保單生效日為114/1/10，等待期為30日，等待期屆滿日為114/2/9。被保險人於115/3/30診斷確定罹患特定傷病，已超過等待期，符合條件。  
+4. 被保險人於115/3/30診斷確定後，次一個保險單週年日為116/1/10，若屆時仍生存，可於該日起申請第一筆生活補助保險金。
+條文依據：  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]  
+- [第十二條 特定傷病保險金的給付]  
+- [國泰人壽樂鍾心特定傷病定期健康保險（外溢型）]</t>
+        </is>
+      </c>
+      <c r="D334" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 生活補助保險金的給付（第二保險單年度起適用） | other_metadata | 第十一條 契約的終止（三） | payout_items | 第十二條 特定傷病保險金的給付 | 第五條 保險範圍 | 第十五條 保險費豁免（第二保險單年度起適用） | 第十條 契約的終止（二）</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F334" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 樂鍾溢保單包含生活補助保險金保障，且該項保障於第二保險單年度（含）以後適用。  
+2. 根據條款，生活補助保險金的給付條件為：被保險人於第二保險單年度（含）以後初次診斷確定罹患特定傷病，並於初次診斷確定的次一個保險單週年日起，每逢保險單週年日仍生存者，保險公司將按保險金額的36%給付生活補助保險金。  
+3. 保單生效日為114/1/10，等待期為30日，等待期屆滿日為114/2/9。被保險人於115/3/30診斷確定罹患特定傷病，已超過等待期，符合條件。  
+4. 被保險人於115/3/30診斷確定後，次一個保險單週年日為116/1/10，若屆時仍生存，可於該日起申請第一筆生活補助保險金。
+條文依據：  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]  
+- [第十二條 特定傷病保險金的給付]  
+- [國泰人壽樂鍾心特定傷病定期健康保險（外溢型）]</t>
+        </is>
+      </c>
+      <c r="G334" s="2" t="inlineStr"/>
+      <c r="H334" s="2" t="inlineStr"/>
+      <c r="I334" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認樂鍾溢保單是否包含生活補助保險金保障", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認保單中針對特定傷病的生活補助保險金給付條件", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認保單生效日與115/3/30之間是否符合等待期規定", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認生活補助保險金的申請流程與所需時間", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J334" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K334" s="4" t="n"/>
+      <c r="L334" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M334" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:29:49</t>
+        </is>
+      </c>
+      <c r="N334" s="4" t="n">
+        <v>15.25</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B335" s="2" t="inlineStr">
+        <is>
+          <t>保戶在114/1/10投保樂鍾溢，如果他在115/3/30罹患特定傷病的話，他在115/1/9會領到無理賠回饋保險金嗎?保險單週年日什麼時候？指定日期什麼時候？</t>
+        </is>
+      </c>
+      <c r="C335" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 保險單週年日為每年的1月10日，因為保戶於114/1/10投保，保險單週年日即為保單生效日的每年對應日期。  
+2. 115/1/9不符合無理賠回饋保險金的領取條件，因為被保險人在115/3/30已經罹患特定傷病，而第十四條規定，若被保險人不符條件（如罹患特定傷病），需返還已領取的無理賠回饋保險金或由保險金中扣回。  
+3. 指定日期為每年的保險單年度末，即每年的1月9日。  
+4. 特定傷病會影響無理賠回饋保險金的領取資格，因為第十四條明確規定，若被保險人於有效期間內罹患特定傷病並申領保險金，則不符合無理賠回饋保險金的條件。
+條文依據：  
+- [第十四條 無理賠回饋保險金的給付]  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="D335" s="2" t="inlineStr">
+        <is>
+          <t>other_metadata | 第十四條 無理賠回饋保險金的給付 | payout_items | 第十二條 特定傷病保險金的給付 | 第十五條 保險費豁免（第二保險單年度起適用） | 第十條 契約的終止（二） | 第五條 保險範圍 | 第二十條 無理賠回饋保險金的申領</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F335" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 保險單週年日為每年的1月10日，因為保戶於114/1/10投保，保險單週年日即為保單生效日的每年對應日期。  
+2. 115/1/9不符合無理賠回饋保險金的領取條件，因為被保險人在115/3/30已經罹患特定傷病，而第十四條規定，若被保險人不符條件（如罹患特定傷病），需返還已領取的無理賠回饋保險金或由保險金中扣回。  
+3. 指定日期為每年的保險單年度末，即每年的1月9日。  
+4. 特定傷病會影響無理賠回饋保險金的領取資格，因為第十四條明確規定，若被保險人於有效期間內罹患特定傷病並申領保險金，則不符合無理賠回饋保險金的條件。
+條文依據：  
+- [第十四條 無理賠回饋保險金的給付]  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="G335" s="2" t="inlineStr"/>
+      <c r="H335" s="2" t="inlineStr"/>
+      <c r="I335" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認保險單週年日的日期", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認115/1/9是否符合無理賠回饋保險金的領取條件", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認指定日期的具體時間", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認特定傷病是否影響無理賠回饋保險金的領取資格", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J335" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K335" s="4" t="n"/>
+      <c r="L335" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M335" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:30:02</t>
+        </is>
+      </c>
+      <c r="N335" s="4" t="n">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B336" s="2" t="inlineStr">
+        <is>
+          <t>被保險人於第一保險單年度罹患急性心肌梗塞（重度），生活補助保險金最多可以領取幾次？契約會終止嗎？</t>
+        </is>
+      </c>
+      <c r="C336" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 生活補助保險金的給付次數限制為最多十次，但僅適用於第二保險單年度（含）以後的有效期間內，且需符合條件。  
+2. 被保險人於第一保險單年度罹患急性心肌梗塞（重度），不符合生活補助保險金的給付條件，因該條款僅適用於第二保險單年度（含）以後。  
+3. 若被保險人於第一保險單年度罹患特定傷病（如急性心肌梗塞），契約將依第十一條第三款規定終止。  
+條文依據：  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]  
+- [第十一條 契約的終止（三）]  
+- [第十二條 特定傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D336" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 生活補助保險金的給付（第二保險單年度起適用） | 第十一條 契約的終止（三） | 第五條 保險範圍 | 第二條 名詞定義 | 第十二條 特定傷病保險金的給付 | 第十五條 保險費豁免（第二保險單年度起適用） | payout_items | 第十條 契約的終止（二）</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F336" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 生活補助保險金的給付次數限制為最多十次，但僅適用於第二保險單年度（含）以後的有效期間內，且需符合條件。  
+2. 被保險人於第一保險單年度罹患急性心肌梗塞（重度），不符合生活補助保險金的給付條件，因該條款僅適用於第二保險單年度（含）以後。  
+3. 若被保險人於第一保險單年度罹患特定傷病（如急性心肌梗塞），契約將依第十一條第三款規定終止。  
+條文依據：  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]  
+- [第十一條 契約的終止（三）]  
+- [第十二條 特定傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G336" s="2" t="inlineStr"/>
+      <c r="H336" s="2" t="inlineStr"/>
+      <c r="I336" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認生活補助保險金的給付次數限制", "must_have": true, "分數": 0.8}, {"id": "2", "point": "確認罹患急性心肌梗塞（重度）是否符合生活補助保險金的給付條件", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認保險契約是否會因給付而終止", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認第一保險單年度的定義及適用範圍", "must_have": false, "分數": 0.7}], "coverage_score": 0.9154, "C_conf": 0.9154}</t>
+        </is>
+      </c>
+      <c r="J336" s="4" t="n">
+        <v>0.9154</v>
+      </c>
+      <c r="K336" s="4" t="n"/>
+      <c r="L336" s="4" t="n">
+        <v>0.9154</v>
+      </c>
+      <c r="M336" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:30:22</t>
+        </is>
+      </c>
+      <c r="N336" s="4" t="n">
+        <v>19.44</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B337" s="2" t="inlineStr">
+        <is>
+          <t>被保險人為60歲女性，投保繳費期間20年期之樂鍾心特定傷病定期健康保險（外溢型）5單位，每單位年繳應繳保險費為1675元，則每逢保險單年度末生存者，可以領取多少無理賠關懷保險金？</t>
+        </is>
+      </c>
+      <c r="C337" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 樂鍾心特定傷病定期健康保險（外溢型）包含「無理賠回饋保險金」的條款。  
+2. 每單位無理賠回饋保險金的金額為每單位年繳應繳保險費的10%，即 1675 × 10% = 167.5 元，元以下無條件進位為 168 元。  
+3. 5 單位的總無理賠回饋保險金金額為 168 × 5 = 840 元。  
+條文依據：  
+- [第十四條 無理賠回饋保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D337" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 無理賠回饋保險金的給付 | other_metadata | payout_items | 第二十條 無理賠回饋保險金的申領 | 第十二條 特定傷病保險金的給付 | 第十三條 生活補助保險金的給付（第二保險單年度起適用） | 第五條 保險範圍 | 第十五條 保險費豁免（第二保險單年度起適用）</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F337" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 樂鍾心特定傷病定期健康保險（外溢型）包含「無理賠回饋保險金」的條款。  
+2. 每單位無理賠回饋保險金的金額為每單位年繳應繳保險費的10%，即 1675 × 10% = 167.5 元，元以下無條件進位為 168 元。  
+3. 5 單位的總無理賠回饋保險金金額為 168 × 5 = 840 元。  
+條文依據：  
+- [第十四條 無理賠回饋保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G337" s="2" t="inlineStr"/>
+      <c r="H337" s="2" t="inlineStr"/>
+      <c r="I337" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認樂鍾心特定傷病定期健康保險（外溢型）是否有無理賠關懷保險金的條款", "must_have": true, "分數": 1.0}, {"id": "2", "point": "計算每單位無理賠關懷保險金的金額", "must_have": true, "分數": 1.0}, {"id": "3", "point": "計算5單位的總無理賠關懷保險金金額", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認無理賠關懷保險金的給付條件是否與保險單年度末生存相關", "must_have": false, "分數": 0.0}], "coverage_score": 0.9231, "C_conf": 0.9231}</t>
+        </is>
+      </c>
+      <c r="J337" s="4" t="n">
+        <v>0.9231</v>
+      </c>
+      <c r="K337" s="4" t="n"/>
+      <c r="L337" s="4" t="n">
+        <v>0.9231</v>
+      </c>
+      <c r="M337" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:30:41</t>
+        </is>
+      </c>
+      <c r="N337" s="4" t="n">
+        <v>17.55</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/rag_results.xlsx
+++ b/src/rag_results.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N416"/>
+  <dimension ref="A1:N499"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -27006,6 +27006,5346 @@
         <v>13.72</v>
       </c>
     </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B417" s="2" t="inlineStr">
+        <is>
+          <t>保障範圍包括哪些項目？</t>
+        </is>
+      </c>
+      <c r="C417" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括住院醫療保險金、加護病房或燒燙傷病房保險金、祝壽保險金、身故保險金或喪葬費用保險金，以及所繳保險費的退還。
+條文依據：  
+- 摘要  
+- 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="D417" s="2" t="inlineStr">
+        <is>
+          <t>payout_items | summary | 第五條 保險範圍 | 第二條 名詞定義 | 第十八條 除外責任（一）</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F417" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括住院醫療保險金、加護病房或燒燙傷病房保險金、祝壽保險金、身故保險金或喪葬費用保險金，以及所繳保險費的退還。
+條文依據：  
+- 摘要  
+- 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="G417" s="2" t="inlineStr"/>
+      <c r="H417" s="2" t="inlineStr"/>
+      <c r="I417" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.989603, "neutral": 0.010147, "contradiction": 0.000251, "factuality": 0.999749, "C_fact": 0.999749}, "C_conf": 0.9997}</t>
+        </is>
+      </c>
+      <c r="J417" s="5" t="n"/>
+      <c r="K417" s="5" t="n">
+        <v>0.999749</v>
+      </c>
+      <c r="L417" s="5" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="M417" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:23:37</t>
+        </is>
+      </c>
+      <c r="N417" s="5" t="n">
+        <v>33.19</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B418" s="2" t="inlineStr">
+        <is>
+          <t>因同一疾病或傷害再次住院、若間隔時間在出院後十四日內或因併發症導致的再次住院日數計算有什麼特殊規則？</t>
+        </is>
+      </c>
+      <c r="C418" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人因同一疾病或傷害，或因此引起的併發症，於出院後十四日內再次住院，其住院日數計算將視為同一次住院處理，並適用第十二條至第十三條的各項保險金給付限制。
+條文依據：  
+- [第十一條 住院次數之計算及契約有效期間屆滿後住院之處理]</t>
+        </is>
+      </c>
+      <c r="D418" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第十三條 加護病房或燒燙傷病房保險金的給付 | 第二條 名詞定義 | 第十二條 住院醫療保險金的給付 | 第十八條 除外責任（一） | 第二十八條 住院醫療保險金日額之減少</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F418" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人因同一疾病或傷害，或因此引起的併發症，於出院後十四日內再次住院，其住院日數計算將視為同一次住院處理，並適用第十二條至第十三條的各項保險金給付限制。
+條文依據：  
+- [第十一條 住院次數之計算及契約有效期間屆滿後住院之處理]</t>
+        </is>
+      </c>
+      <c r="G418" s="2" t="inlineStr"/>
+      <c r="H418" s="2" t="inlineStr"/>
+      <c r="I418" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.996152, "neutral": 0.00368, "contradiction": 0.000168, "factuality": 0.999832, "C_fact": 0.999832}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J418" s="5" t="n"/>
+      <c r="K418" s="5" t="n">
+        <v>0.9998320000000001</v>
+      </c>
+      <c r="L418" s="5" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M418" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:23:57</t>
+        </is>
+      </c>
+      <c r="N418" s="5" t="n">
+        <v>20.37</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B419" s="2" t="inlineStr">
+        <is>
+          <t>住院醫療保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C419" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院醫療保險金的給付規定如下：  
+被保險人於契約有效期間內因疾病或傷害住院治療時，保險公司將依保險單上記載的「住院醫療保險金日額」，乘以入院日當年度的「增額係數」，再乘以住院日數，給付「住院醫療保險金」。同一保單年度內，同一次住院的住院日數給付上限為365日。
+條文依據：  
+- [第十二條 住院醫療保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D419" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 住院醫療保險金的給付 | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第十三條 加護病房或燒燙傷病房保險金的給付 | 第十四條 醫療保險金給付總額之上限 | 第二十八條 住院醫療保險金日額之減少</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F419" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院醫療保險金的給付規定如下：  
+被保險人於契約有效期間內因疾病或傷害住院治療時，保險公司將依保險單上記載的「住院醫療保險金日額」，乘以入院日當年度的「增額係數」，再乘以住院日數，給付「住院醫療保險金」。同一保單年度內，同一次住院的住院日數給付上限為365日。
+條文依據：  
+- [第十二條 住院醫療保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G419" s="2" t="inlineStr"/>
+      <c r="H419" s="2" t="inlineStr"/>
+      <c r="I419" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.993295, "neutral": 0.003922, "contradiction": 0.002783, "factuality": 0.997217, "C_fact": 0.997217}, "C_conf": 0.9972}</t>
+        </is>
+      </c>
+      <c r="J419" s="5" t="n"/>
+      <c r="K419" s="5" t="n">
+        <v>0.997217</v>
+      </c>
+      <c r="L419" s="5" t="n">
+        <v>0.9972</v>
+      </c>
+      <c r="M419" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:24:11</t>
+        </is>
+      </c>
+      <c r="N419" s="5" t="n">
+        <v>13.42</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B420" s="2" t="inlineStr">
+        <is>
+          <t>加護病房或燒燙傷病房保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C420" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+加護病房或燒燙傷病房保險金的給付規定如下：  
+被保險人於契約有效期間內因疾病或傷害住院，並在醫院的加護病房或燒燙傷病房接受治療者，除住院醫療保險金外，保險公司將依保險單所記載的「住院醫療保險金日額」，乘以入院日當年度的「增額係數」，再乘以實際住進加護病房或燒燙傷病房的日數（含轉入及轉出當日）的二倍，給付「加護病房或燒燙傷病房保險金」。  
+同一保單年度內，同一次住院的加護病房及燒燙傷病房住院日數合計給付上限為365日，但同一日內僅能就加護病房或燒燙傷病房其中一種病房給付。
+條文依據：  
+- [第十三條 加護病房或燒燙傷病房保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D420" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 加護病房或燒燙傷病房保險金的給付 | payout_items | 第二十三條 醫療保險金的申領 | 第五條 保險範圍 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F420" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+加護病房或燒燙傷病房保險金的給付規定如下：  
+被保險人於契約有效期間內因疾病或傷害住院，並在醫院的加護病房或燒燙傷病房接受治療者，除住院醫療保險金外，保險公司將依保險單所記載的「住院醫療保險金日額」，乘以入院日當年度的「增額係數」，再乘以實際住進加護病房或燒燙傷病房的日數（含轉入及轉出當日）的二倍，給付「加護病房或燒燙傷病房保險金」。  
+同一保單年度內，同一次住院的加護病房及燒燙傷病房住院日數合計給付上限為365日，但同一日內僅能就加護病房或燒燙傷病房其中一種病房給付。
+條文依據：  
+- [第十三條 加護病房或燒燙傷病房保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G420" s="2" t="inlineStr"/>
+      <c r="H420" s="2" t="inlineStr"/>
+      <c r="I420" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.995753, "neutral": 0.003493, "contradiction": 0.000753, "factuality": 0.999247, "C_fact": 0.999247}, "C_conf": 0.9992}</t>
+        </is>
+      </c>
+      <c r="J420" s="5" t="n"/>
+      <c r="K420" s="5" t="n">
+        <v>0.999247</v>
+      </c>
+      <c r="L420" s="5" t="n">
+        <v>0.9992</v>
+      </c>
+      <c r="M420" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:24:20</t>
+        </is>
+      </c>
+      <c r="N420" s="5" t="n">
+        <v>9.15</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B421" s="2" t="inlineStr">
+        <is>
+          <t>醫療保險金給付總額之上限</t>
+        </is>
+      </c>
+      <c r="C421" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+醫療保險金給付總額之上限為保險單上所記載之「住院醫療保險金日額」的二千五百倍，並適用於本契約有效期間內依第十二條至第十三條所給付之各項保險金的累計總額。
+條文依據：  
+- [第十四條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="D421" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 醫療保險金給付總額之上限 | 第十二條 住院醫療保險金的給付 | 第五條 保險範圍 | 第十三條 加護病房或燒燙傷病房保險金的給付 | payout_items</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F421" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+醫療保險金給付總額之上限為保險單上所記載之「住院醫療保險金日額」的二千五百倍，並適用於本契約有效期間內依第十二條至第十三條所給付之各項保險金的累計總額。
+條文依據：  
+- [第十四條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="G421" s="2" t="inlineStr"/>
+      <c r="H421" s="2" t="inlineStr"/>
+      <c r="I421" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.996196, "neutral": 0.003514, "contradiction": 0.00029, "factuality": 0.99971, "C_fact": 0.99971}, "C_conf": 0.9997}</t>
+        </is>
+      </c>
+      <c r="J421" s="5" t="n"/>
+      <c r="K421" s="5" t="n">
+        <v>0.99971</v>
+      </c>
+      <c r="L421" s="5" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="M421" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:24:30</t>
+        </is>
+      </c>
+      <c r="N421" s="5" t="n">
+        <v>6.38</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B422" s="2" t="inlineStr">
+        <is>
+          <t>祝壽保險金的給付規定為何?</t>
+        </is>
+      </c>
+      <c r="C422" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+祝壽保險金的給付規定為：被保險人於本契約有效期間且保險年齡到達九十九歲之保險單週年日仍生存時，本公司按「當年度保險金額」給付「祝壽保險金」。
+條文依據：  
+- [第十五條 祝壽保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D422" s="2" t="inlineStr">
+        <is>
+          <t>第十五條 祝壽保險金的給付 | 第十二條至第十三條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | 第二十四條 祝壽保險金的申領 | payout_items | 第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F422" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+祝壽保險金的給付規定為：被保險人於本契約有效期間且保險年齡到達九十九歲之保險單週年日仍生存時，本公司按「當年度保險金額」給付「祝壽保險金」。
+條文依據：  
+- [第十五條 祝壽保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G422" s="2" t="inlineStr"/>
+      <c r="H422" s="2" t="inlineStr"/>
+      <c r="I422" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.997653, "neutral": 0.002173, "contradiction": 0.000174, "factuality": 0.999826, "C_fact": 0.999826}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J422" s="5" t="n"/>
+      <c r="K422" s="5" t="n">
+        <v>0.999826</v>
+      </c>
+      <c r="L422" s="5" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M422" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:24:47</t>
+        </is>
+      </c>
+      <c r="N422" s="5" t="n">
+        <v>16.25</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B423" s="2" t="inlineStr">
+        <is>
+          <t>有效期間內身故，保險金如何給付?</t>
+        </is>
+      </c>
+      <c r="C423" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於本契約有效期間內身故者，本公司按「當年度保險金額」給付「身故保險金」。若被保險人於繳費期間內身故，當期已繳付之未到期保險費將不予退還，亦不併入身故保險金內給付。若被保險人於有效期間內且實際年齡未滿十五足歲身故者，本公司按「所繳保險費」退還要保人，不適用前述規定。此外，若被保險人訂立契約時受監護宣告尚未撤銷者，其身故保險金變更為喪葬費用保險金，並受遺產稅喪葬費扣除額之半數限制，超過部分不負給付責任。  
+條文依據：  
+- [第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D423" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付 | 第十條 契約的終止（二） | 第五條 保險範圍 | 第二十二條 失蹤處理 | 第十五條 祝壽保險金的給付</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F423" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於本契約有效期間內身故者，本公司按「當年度保險金額」給付「身故保險金」。若被保險人於繳費期間內身故，當期已繳付之未到期保險費將不予退還，亦不併入身故保險金內給付。若被保險人於有效期間內且實際年齡未滿十五足歲身故者，本公司按「所繳保險費」退還要保人，不適用前述規定。此外，若被保險人訂立契約時受監護宣告尚未撤銷者，其身故保險金變更為喪葬費用保險金，並受遺產稅喪葬費扣除額之半數限制，超過部分不負給付責任。  
+條文依據：  
+- [第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G423" s="2" t="inlineStr"/>
+      <c r="H423" s="2" t="inlineStr"/>
+      <c r="I423" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.510655, "neutral": 0.488265, "contradiction": 0.00108, "factuality": 0.99892, "C_fact": 0.99892}, "C_conf": 0.9989}</t>
+        </is>
+      </c>
+      <c r="J423" s="5" t="n"/>
+      <c r="K423" s="5" t="n">
+        <v>0.99892</v>
+      </c>
+      <c r="L423" s="5" t="n">
+        <v>0.9989</v>
+      </c>
+      <c r="M423" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:24:59</t>
+        </is>
+      </c>
+      <c r="N423" s="5" t="n">
+        <v>11.78</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B424" s="2" t="inlineStr">
+        <is>
+          <t>健康促進保險費折減規定</t>
+        </is>
+      </c>
+      <c r="C424" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+健康促進保險費折減規定如下：  
+1. 被保險人需年滿20歲（含）以上，並使用保險公司指定程式加入健康計劃。  
+2. 若於「指定日期」的會員等級符合進階會員或菁英會員（或更高等級），次一保險單年度的保險費可分別折減2%或3%。  
+3. 折減僅適用於主契約保險費，不包含附約、附加條款及批註條款。  
+4. 豁免或復效的保險費不適用折減規定。  
+5. 被保險人需完成程式註冊並授權保險公司取得健康相關電子紀錄，保險公司將依紀錄計算會員等級。
+條文依據：  
+- [第十七條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="D424" s="2" t="inlineStr">
+        <is>
+          <t>第十七條 健康促進保險費折減 | 第二十八條 住院醫療保險金日額之減少 | 第三十條 投保年齡的計算及錯誤的處理 | 第二條 名詞定義 | 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F424" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+健康促進保險費折減規定如下：  
+1. 被保險人需年滿20歲（含）以上，並使用保險公司指定程式加入健康計劃。  
+2. 若於「指定日期」的會員等級符合進階會員或菁英會員（或更高等級），次一保險單年度的保險費可分別折減2%或3%。  
+3. 折減僅適用於主契約保險費，不包含附約、附加條款及批註條款。  
+4. 豁免或復效的保險費不適用折減規定。  
+5. 被保險人需完成程式註冊並授權保險公司取得健康相關電子紀錄，保險公司將依紀錄計算會員等級。
+條文依據：  
+- [第十七條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="G424" s="2" t="inlineStr"/>
+      <c r="H424" s="2" t="inlineStr"/>
+      <c r="I424" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.984075, "neutral": 0.013375, "contradiction": 0.002549, "factuality": 0.997451, "C_fact": 0.997451}, "C_conf": 0.9975}</t>
+        </is>
+      </c>
+      <c r="J424" s="5" t="n"/>
+      <c r="K424" s="5" t="n">
+        <v>0.997451</v>
+      </c>
+      <c r="L424" s="5" t="n">
+        <v>0.9975000000000001</v>
+      </c>
+      <c r="M424" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:25:13</t>
+        </is>
+      </c>
+      <c r="N424" s="5" t="n">
+        <v>13.38</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B425" s="2" t="inlineStr">
+        <is>
+          <t>除外責任的解釋?</t>
+        </is>
+      </c>
+      <c r="C425" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+除外責任是指保險公司不負給付保險金責任的情形。根據條款內容，以下為主要除外責任的範圍：  
+1. 因被保險人故意行為（如自殺、自殺未遂）、犯罪行為或非法施用毒品所致的疾病或傷害。  
+2. 因美容手術或外科整型住院，但若為重建基本功能所需的整型則不在此限。  
+3. 因健康檢查、療養、靜養、戒毒、戒酒、護理或養老等非直接診治病人目的的住院。  
+4. 因懷孕、流產或分娩及其併發症住院，但若符合特定醫療行為必要的情形（如子宮外孕、葡萄胎、胎盤早期剝離等）則不在此限。  
+5. 因不孕症、人工受孕或非治療目的的避孕及絕育手術住院。  
+條文依據：  
+- [第十八條 除外責任（一)]  
+- [第十九條 除外責任（二)]</t>
+        </is>
+      </c>
+      <c r="D425" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第十九條 除外責任（二） | 第八條 告知義務與本契約的解除 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F425" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+除外責任是指保險公司不負給付保險金責任的情形。根據條款內容，以下為主要除外責任的範圍：  
+1. 因被保險人故意行為（如自殺、自殺未遂）、犯罪行為或非法施用毒品所致的疾病或傷害。  
+2. 因美容手術或外科整型住院，但若為重建基本功能所需的整型則不在此限。  
+3. 因健康檢查、療養、靜養、戒毒、戒酒、護理或養老等非直接診治病人目的的住院。  
+4. 因懷孕、流產或分娩及其併發症住院，但若符合特定醫療行為必要的情形（如子宮外孕、葡萄胎、胎盤早期剝離等）則不在此限。  
+5. 因不孕症、人工受孕或非治療目的的避孕及絕育手術住院。  
+條文依據：  
+- [第十八條 除外責任（一)]  
+- [第十九條 除外責任（二)]</t>
+        </is>
+      </c>
+      <c r="G425" s="2" t="inlineStr"/>
+      <c r="H425" s="2" t="inlineStr"/>
+      <c r="I425" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.997414, "neutral": 0.002467, "contradiction": 0.000119, "factuality": 0.999881, "C_fact": 0.999881}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J425" s="5" t="n"/>
+      <c r="K425" s="5" t="n">
+        <v>0.999881</v>
+      </c>
+      <c r="L425" s="5" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M425" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:25:28</t>
+        </is>
+      </c>
+      <c r="N425" s="5" t="n">
+        <v>14.76</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B426" s="2" t="inlineStr">
+        <is>
+          <t>哪些疾病被含在除外責任?</t>
+        </is>
+      </c>
+      <c r="C426" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+以下疾病被列為除外責任，保險公司不負給付第十二條至第十三條保險金的責任：  
+1. 美容手術、外科整型（但為重建基本功能所作之必要整型不在此限）。  
+2. 外觀可見之天生畸形。  
+3. 健康檢查、療養、靜養、戒毒、戒酒、護理或養老之非以直接診治病人為目的者。  
+4. 懷孕、流產或分娩及其併發症（但特定懷孕相關疾病、醫療行為必要之流產及剖腹產不在此限）。  
+5. 不孕症、人工受孕或非以治療為目的之避孕及絕育手術。
+條文依據：  
+- [第十八條 除外責任（一)]</t>
+        </is>
+      </c>
+      <c r="D426" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第二條 名詞定義 | 第十九條 除外責任（二）</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F426" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+以下疾病被列為除外責任，保險公司不負給付第十二條至第十三條保險金的責任：  
+1. 美容手術、外科整型（但為重建基本功能所作之必要整型不在此限）。  
+2. 外觀可見之天生畸形。  
+3. 健康檢查、療養、靜養、戒毒、戒酒、護理或養老之非以直接診治病人為目的者。  
+4. 懷孕、流產或分娩及其併發症（但特定懷孕相關疾病、醫療行為必要之流產及剖腹產不在此限）。  
+5. 不孕症、人工受孕或非以治療為目的之避孕及絕育手術。
+條文依據：  
+- [第十八條 除外責任（一)]</t>
+        </is>
+      </c>
+      <c r="G426" s="2" t="inlineStr"/>
+      <c r="H426" s="2" t="inlineStr"/>
+      <c r="I426" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.9986, "neutral": 0.001184, "contradiction": 0.000215, "factuality": 0.999785, "C_fact": 0.999785}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J426" s="5" t="n"/>
+      <c r="K426" s="5" t="n">
+        <v>0.999785</v>
+      </c>
+      <c r="L426" s="5" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M426" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:26:17</t>
+        </is>
+      </c>
+      <c r="N426" s="5" t="n">
+        <v>48.23</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B427" s="2" t="inlineStr">
+        <is>
+          <t>進行美容手術住院可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C427" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，因美容手術住院診療者，本公司不負給付保險金的責任。但若美容手術是為重建基本功能所作之必要整型，則不在此限，可以申請理賠。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D427" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第十三條 加護病房或燒燙傷病房保險金的給付 | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第二條 名詞定義 | payout_items</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F427" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，因美容手術住院診療者，本公司不負給付保險金的責任。但若美容手術是為重建基本功能所作之必要整型，則不在此限，可以申請理賠。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="G427" s="2" t="inlineStr"/>
+      <c r="H427" s="2" t="inlineStr"/>
+      <c r="I427" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.474019, "neutral": 0.524983, "contradiction": 0.000999, "factuality": 0.999001, "C_fact": 0.999001}, "C_conf": 0.999}</t>
+        </is>
+      </c>
+      <c r="J427" s="5" t="n"/>
+      <c r="K427" s="5" t="n">
+        <v>0.999001</v>
+      </c>
+      <c r="L427" s="5" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="M427" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:26:52</t>
+        </is>
+      </c>
+      <c r="N427" s="5" t="n">
+        <v>34.22</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B428" s="2" t="inlineStr">
+        <is>
+          <t>因胎兒染色體異常進行手術而住院可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C428" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以申請理賠。根據條款，被保險人因懷孕相關疾病（包括胎兒染色體異常之手術）住院診療，不屬於除外責任範圍，因此本公司負有給付保險金的責任。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D428" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第二條 名詞定義 | payout_items | 第十三條 加護病房或燒燙傷病房保險金的給付</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F428" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以申請理賠。根據條款，被保險人因懷孕相關疾病（包括胎兒染色體異常之手術）住院診療，不屬於除外責任範圍，因此本公司負有給付保險金的責任。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="G428" s="2" t="inlineStr"/>
+      <c r="H428" s="2" t="inlineStr"/>
+      <c r="I428" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.985211, "neutral": 0.007167, "contradiction": 0.007623, "factuality": 0.992377, "C_fact": 0.992377}, "C_conf": 0.9924}</t>
+        </is>
+      </c>
+      <c r="J428" s="5" t="n"/>
+      <c r="K428" s="5" t="n">
+        <v>0.992377</v>
+      </c>
+      <c r="L428" s="5" t="n">
+        <v>0.9923999999999999</v>
+      </c>
+      <c r="M428" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:27:16</t>
+        </is>
+      </c>
+      <c r="N428" s="5" t="n">
+        <v>23.59</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B429" s="2" t="inlineStr">
+        <is>
+          <t>因胎位不正進行手術而住院可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C429" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，因胎位不正進行手術而住院屬於除外責任範圍，保險公司不負給付保險金的責任。然而，若該手術屬於「醫療行為必要之剖腹產」且符合胎位不正的條件，則不在除外責任之列，可申請理賠。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D429" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第二條 名詞定義 | payout_items | 第十三條 加護病房或燒燙傷病房保險金的給付</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F429" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，因胎位不正進行手術而住院屬於除外責任範圍，保險公司不負給付保險金的責任。然而，若該手術屬於「醫療行為必要之剖腹產」且符合胎位不正的條件，則不在除外責任之列，可申請理賠。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="G429" s="2" t="inlineStr"/>
+      <c r="H429" s="2" t="inlineStr"/>
+      <c r="I429" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.124133, "neutral": 0.873344, "contradiction": 0.002523, "factuality": 0.997477, "C_fact": 0.997477}, "C_conf": 0.9975}</t>
+        </is>
+      </c>
+      <c r="J429" s="5" t="n"/>
+      <c r="K429" s="5" t="n">
+        <v>0.9974769999999999</v>
+      </c>
+      <c r="L429" s="5" t="n">
+        <v>0.9975000000000001</v>
+      </c>
+      <c r="M429" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:27:29</t>
+        </is>
+      </c>
+      <c r="N429" s="5" t="n">
+        <v>13.59</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B430" s="2" t="inlineStr">
+        <is>
+          <t>因自殺未遂導致住院可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C430" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，因被保險人故意行為（包括自殺及自殺未遂）導致住院診療者，本公司不負給付住院醫療保險金的責任。  
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D430" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 除外責任（二） | 第十八條 除外責任（一） | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | payout_items | 第十條 契約的終止（二）</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F430" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，因被保險人故意行為（包括自殺及自殺未遂）導致住院診療者，本公司不負給付住院醫療保險金的責任。  
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="G430" s="2" t="inlineStr"/>
+      <c r="H430" s="2" t="inlineStr"/>
+      <c r="I430" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.983569, "neutral": 0.016184, "contradiction": 0.000247, "factuality": 0.999753, "C_fact": 0.999753}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J430" s="5" t="n"/>
+      <c r="K430" s="5" t="n">
+        <v>0.999753</v>
+      </c>
+      <c r="L430" s="5" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M430" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:27:55</t>
+        </is>
+      </c>
+      <c r="N430" s="5" t="n">
+        <v>25.39</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B431" s="2" t="inlineStr">
+        <is>
+          <t>被保險人在投保一年內故意自殺者，可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C431" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人在投保一年內故意自殺者，依條款規定，本公司不負給付身故保險金或喪葬費用保險金的責任。但若自契約訂立或復效之日起滿二年後故意自殺致死者，本公司仍負給付責任。
+條文依據：  
+- [第十九條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="D431" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 除外責任（二） | 第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付 | 第十條 契約的終止（二） | 第三十條 投保年齡的計算及錯誤的處理 | 第十八條 除外責任（一）</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F431" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人在投保一年內故意自殺者，依條款規定，本公司不負給付身故保險金或喪葬費用保險金的責任。但若自契約訂立或復效之日起滿二年後故意自殺致死者，本公司仍負給付責任。
+條文依據：  
+- [第十九條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="G431" s="2" t="inlineStr"/>
+      <c r="H431" s="2" t="inlineStr"/>
+      <c r="I431" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.997445, "neutral": 0.002388, "contradiction": 0.000167, "factuality": 0.999833, "C_fact": 0.999833}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J431" s="5" t="n"/>
+      <c r="K431" s="5" t="n">
+        <v>0.999833</v>
+      </c>
+      <c r="L431" s="5" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M431" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:28:10</t>
+        </is>
+      </c>
+      <c r="N431" s="5" t="n">
+        <v>14.91</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B432" s="2" t="inlineStr">
+        <is>
+          <t>申請理賠有什麼時間規定嗎?</t>
+        </is>
+      </c>
+      <c r="C432" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申請理賠的時間規定如下：要保人、被保險人或受益人應於知悉本公司應負保險責任之事故後十日內通知本公司，並於通知後儘速檢具所需文件向本公司申請給付保險金。本公司應於收齊所需文件後十五日內給付保險金。但若因可歸責於本公司之事由導致未在約定期限內給付者，應按年利一分加計利息給付。
+條文依據：  
+- [第二十一條 保險事故的通知與保險金的申請時間]</t>
+        </is>
+      </c>
+      <c r="D432" s="2" t="inlineStr">
+        <is>
+          <t>第二十一條 保險事故的通知與保險金的申請時間 | 第六條 第二期以後保險費的交付、寬限期間及契約效力的停止 | 第七條 本契約效力的恢復 | 第三條 契約撤銷權 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F432" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申請理賠的時間規定如下：要保人、被保險人或受益人應於知悉本公司應負保險責任之事故後十日內通知本公司，並於通知後儘速檢具所需文件向本公司申請給付保險金。本公司應於收齊所需文件後十五日內給付保險金。但若因可歸責於本公司之事由導致未在約定期限內給付者，應按年利一分加計利息給付。
+條文依據：  
+- [第二十一條 保險事故的通知與保險金的申請時間]</t>
+        </is>
+      </c>
+      <c r="G432" s="2" t="inlineStr"/>
+      <c r="H432" s="2" t="inlineStr"/>
+      <c r="I432" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.996318, "neutral": 0.003601, "contradiction": 8.1e-05, "factuality": 0.999919, "C_fact": 0.999919}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J432" s="5" t="n"/>
+      <c r="K432" s="5" t="n">
+        <v>0.999919</v>
+      </c>
+      <c r="L432" s="5" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M432" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:28:20</t>
+        </is>
+      </c>
+      <c r="N432" s="5" t="n">
+        <v>9.92</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B433" s="2" t="inlineStr">
+        <is>
+          <t>燒燙傷病房保險金怎麼申領?</t>
+        </is>
+      </c>
+      <c r="C433" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申領燒燙傷病房保險金時，受益人需依約定檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 醫療診斷書或住院證明，並列明進、出燒燙傷病房的日期。（但要保人或被保險人為醫師時，不得為被保險人出具診斷書或住院證明。）  
+4. 受益人的身分證明。  
+此外，保險公司基於審核保險金的需要，得徵詢其他醫師的醫學專業意見，並經受益人同意調閱被保險人的就醫相關資料，相關費用由保險公司負擔。
+條文依據：  
+- [第二十三條 醫療保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D433" s="2" t="inlineStr">
+        <is>
+          <t>第二十三條 醫療保險金的申領 | 第十三條 加護病房或燒燙傷病房保險金的給付 | payout_items | 第二條 名詞定義 | 第二十一條 保險事故的通知與保險金的申請時間</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F433" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申領燒燙傷病房保險金時，受益人需依約定檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 醫療診斷書或住院證明，並列明進、出燒燙傷病房的日期。（但要保人或被保險人為醫師時，不得為被保險人出具診斷書或住院證明。）  
+4. 受益人的身分證明。  
+此外，保險公司基於審核保險金的需要，得徵詢其他醫師的醫學專業意見，並經受益人同意調閱被保險人的就醫相關資料，相關費用由保險公司負擔。
+條文依據：  
+- [第二十三條 醫療保險金的申領]</t>
+        </is>
+      </c>
+      <c r="G433" s="2" t="inlineStr"/>
+      <c r="H433" s="2" t="inlineStr"/>
+      <c r="I433" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.998221, "neutral": 0.001605, "contradiction": 0.000174, "factuality": 0.999826, "C_fact": 0.999826}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J433" s="5" t="n"/>
+      <c r="K433" s="5" t="n">
+        <v>0.999826</v>
+      </c>
+      <c r="L433" s="5" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M433" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:28:40</t>
+        </is>
+      </c>
+      <c r="N433" s="5" t="n">
+        <v>19.03</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B434" s="2" t="inlineStr">
+        <is>
+          <t>活到99歲怎麼申請祝壽金?</t>
+        </is>
+      </c>
+      <c r="C434" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申請祝壽保險金時，受益人需檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 受益人的身分證明。  
+條文依據：  
+- [第二十四條 祝壽保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D434" s="2" t="inlineStr">
+        <is>
+          <t>第十五條 祝壽保險金的給付 | 第二十四條 祝壽保險金的申領 | 第五條 保險範圍 | 第十二條至第十三條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | announcement_history</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F434" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申請祝壽保險金時，受益人需檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 受益人的身分證明。  
+條文依據：  
+- [第二十四條 祝壽保險金的申領]</t>
+        </is>
+      </c>
+      <c r="G434" s="2" t="inlineStr"/>
+      <c r="H434" s="2" t="inlineStr"/>
+      <c r="I434" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.99803, "neutral": 0.001868, "contradiction": 0.000103, "factuality": 0.999897, "C_fact": 0.999897}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J434" s="5" t="n"/>
+      <c r="K434" s="5" t="n">
+        <v>0.999897</v>
+      </c>
+      <c r="L434" s="5" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M434" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:28:50</t>
+        </is>
+      </c>
+      <c r="N434" s="5" t="n">
+        <v>10.08</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B435" s="2" t="inlineStr">
+        <is>
+          <t>被保人身故怎麼申請理賠</t>
+        </is>
+      </c>
+      <c r="C435" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+受益人申領「身故保險金」或「喪葬費用保險金」時，需檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 被保險人死亡證明書及除戶戶籍謄本。  
+4. 受益人的身分證明。  
+條文依據：  
+- [第二十五條 身故保險金或喪葬費用保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D435" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付 | 第十二條至第十三條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | 第二十二條 失蹤處理 | 第二十五條 身故保險金或喪葬費用保險金的申領 | 第十九條 除外責任（二）</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F435" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+受益人申領「身故保險金」或「喪葬費用保險金」時，需檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 被保險人死亡證明書及除戶戶籍謄本。  
+4. 受益人的身分證明。  
+條文依據：  
+- [第二十五條 身故保險金或喪葬費用保險金的申領]</t>
+        </is>
+      </c>
+      <c r="G435" s="2" t="inlineStr"/>
+      <c r="H435" s="2" t="inlineStr"/>
+      <c r="I435" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.996062, "neutral": 0.003782, "contradiction": 0.000155, "factuality": 0.999845, "C_fact": 0.999845}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J435" s="5" t="n"/>
+      <c r="K435" s="5" t="n">
+        <v>0.999845</v>
+      </c>
+      <c r="L435" s="5" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M435" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:29:03</t>
+        </is>
+      </c>
+      <c r="N435" s="5" t="n">
+        <v>12.91</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B436" s="2" t="inlineStr">
+        <is>
+          <t>投保15年後，增額係數為多少？因手術住院3天，住院日額為2500元，請問可以申請多少理賠?</t>
+        </is>
+      </c>
+      <c r="C436" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+投保15年後，增額係數為1.10。因手術住院3天，住院日額為2500元，理賠金額計算如下：  
+住院醫療保險金 = 住院日額 × 增額係數 × 住院日數  
+= 2500 × 1.10 × 3  
+= 8250元。  
+因此，可以申請理賠金額為8250元。
+條文依據：  
+- 附表：增額係數表 - 保險單年度第11~20年增額係數為1.10  
+- 第十二條 住院醫療保險金的給付</t>
+        </is>
+      </c>
+      <c r="D436" s="2" t="inlineStr">
+        <is>
+          <t>附表：增額係數表 | 第十二條 住院醫療保險金的給付 | 第十三條 加護病房或燒燙傷病房保險金的給付 | 第二十八條 住院醫療保險金日額之減少 | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第三十條 投保年齡的計算及錯誤的處理 | payout_items | 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F436" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+投保15年後，增額係數為1.10。因手術住院3天，住院日額為2500元，理賠金額計算如下：  
+住院醫療保險金 = 住院日額 × 增額係數 × 住院日數  
+= 2500 × 1.10 × 3  
+= 8250元。  
+因此，可以申請理賠金額為8250元。
+條文依據：  
+- 附表：增額係數表 - 保險單年度第11~20年增額係數為1.10  
+- 第十二條 住院醫療保險金的給付</t>
+        </is>
+      </c>
+      <c r="G436" s="2" t="inlineStr"/>
+      <c r="H436" s="2" t="inlineStr"/>
+      <c r="I436" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.993891, "neutral": 0.005735, "contradiction": 0.000374, "factuality": 0.999626, "C_fact": 0.999626}, "C_conf": 0.9996}</t>
+        </is>
+      </c>
+      <c r="J436" s="5" t="n"/>
+      <c r="K436" s="5" t="n">
+        <v>0.999626</v>
+      </c>
+      <c r="L436" s="5" t="n">
+        <v>0.9996</v>
+      </c>
+      <c r="M436" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:29:18</t>
+        </is>
+      </c>
+      <c r="N436" s="5" t="n">
+        <v>12.75</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B437" s="2" t="inlineStr">
+        <is>
+          <t>保障範圍包括哪些項目？</t>
+        </is>
+      </c>
+      <c r="C437" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括：住院手術醫療保險金、門診手術醫療保險金、特定處置保險金、意外創傷縫合處置保險金、意外住院手術醫療保險金、祝壽保險金、所繳保險費的退還、身故保險金或喪葬費用保險金。
+條文依據：  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="D437" s="2" t="inlineStr">
+        <is>
+          <t>payout_items | 第五條 保險範圍 | summary | 第四條 名詞定義 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F437" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括：住院手術醫療保險金、門診手術醫療保險金、特定處置保險金、意外創傷縫合處置保險金、意外住院手術醫療保險金、祝壽保險金、所繳保險費的退還、身故保險金或喪葬費用保險金。
+條文依據：  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="G437" s="2" t="inlineStr"/>
+      <c r="H437" s="2" t="inlineStr"/>
+      <c r="I437" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.998072, "neutral": 0.001746, "contradiction": 0.000182, "factuality": 0.999818, "C_fact": 0.999818}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J437" s="5" t="n"/>
+      <c r="K437" s="5" t="n">
+        <v>0.999818</v>
+      </c>
+      <c r="L437" s="5" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M437" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:29:44</t>
+        </is>
+      </c>
+      <c r="N437" s="5" t="n">
+        <v>25.37</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B438" s="2" t="inlineStr">
+        <is>
+          <t>保險金額是否有上限?</t>
+        </is>
+      </c>
+      <c r="C438" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+有，保險金額的累計給付總額上限為保險單上所記載「保險金額」的一千五百倍，且不包含其他附約、附加條款或批註條款。
+條文依據：  
+- [第十六條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="D438" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 醫療保險金給付總額之上限 | 第三十條 保險金額之減少 | 第五條 保險範圍 | 第十九條 健康促進保險費折減 | 第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F438" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+有，保險金額的累計給付總額上限為保險單上所記載「保險金額」的一千五百倍，且不包含其他附約、附加條款或批註條款。
+條文依據：  
+- [第十六條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="G438" s="2" t="inlineStr"/>
+      <c r="H438" s="2" t="inlineStr"/>
+      <c r="I438" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.997554, "neutral": 0.002322, "contradiction": 0.000124, "factuality": 0.999876, "C_fact": 0.999876}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J438" s="5" t="n"/>
+      <c r="K438" s="5" t="n">
+        <v>0.999876</v>
+      </c>
+      <c r="L438" s="5" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M438" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:29:53</t>
+        </is>
+      </c>
+      <c r="N438" s="5" t="n">
+        <v>9.16</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B439" s="2" t="inlineStr">
+        <is>
+          <t>投保後5天發生手術，是否可以申請理賠?</t>
+        </is>
+      </c>
+      <c r="C439" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+條款未明確規定／資料不足</t>
+        </is>
+      </c>
+      <c r="D439" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第十一條 住院手術醫療保險金 | 第二十條 除外責任（一） | 第十二條 門診手術醫療保險金 | 第十三條 意外住院手術醫療保險金 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F439" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款內容，是否可以申請理賠需視保險契約中是否有等待期間的規定。然而，提供的條款中未提及等待期間的相關規定，因此無法判斷投保後5天是否符合理賠條件。
+條文依據：  
+找不到相關內容</t>
+        </is>
+      </c>
+      <c r="G439" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+條款未明確規定／資料不足</t>
+        </is>
+      </c>
+      <c r="H439" s="2" t="inlineStr"/>
+      <c r="I439" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.108859, "neutral": 0.77934, "contradiction": 0.111801, "factuality": 0.888199, "C_fact": 0.888199}, "C_conf": 0.8882}</t>
+        </is>
+      </c>
+      <c r="J439" s="5" t="n"/>
+      <c r="K439" s="5" t="n">
+        <v>0.888199</v>
+      </c>
+      <c r="L439" s="5" t="n">
+        <v>0.8882</v>
+      </c>
+      <c r="M439" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:30:03</t>
+        </is>
+      </c>
+      <c r="N439" s="5" t="n">
+        <v>9.19</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B440" s="2" t="inlineStr">
+        <is>
+          <t>住院手術醫療保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C440" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院手術醫療保險金的給付規定如下：  
+1. 被保險人於契約有效期間內因疾病或傷害，經醫師診斷必須住院接受附表一所列的手術治療且已實際接受手術者，保險公司將依保險單所記載的「保險金額」乘以手術日當年度的「增額係數」，再乘以手術給付倍數，給付住院手術醫療保險金。  
+2. 若同一次手術中於同一手術位置接受二項以上手術項目，僅給付手術給付倍數最高的手術項目。  
+3. 未載明於附表一的手術項目，保險公司將與被保險人協議比照附表一內程度相當的手術項目，決定給付倍數。  
+4. 以下情形不負給付責任：  
+   - 依據契約除外責任條款的規定不在給付範圍內。  
+   - 不屬全民健康保險醫療服務給付項目及支付標準第二部第二章第七節或第三部第三章第四節第三項所列舉的手術。  
+條文依據：  
+- [第十一條 住院手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="D440" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 住院手術醫療保險金 | 第十三條 意外住院手術醫療保險金 | 第十二條 門診手術醫療保險金 | payout_items | 第二十條 除外責任（一） | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F440" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院手術醫療保險金的給付規定如下：  
+1. 被保險人於契約有效期間內因疾病或傷害，經醫師診斷必須住院接受附表一所列的手術治療且已實際接受手術者，保險公司將依保險單所記載的「保險金額」乘以手術日當年度的「增額係數」，再乘以手術給付倍數，給付住院手術醫療保險金。  
+2. 若同一次手術中於同一手術位置接受二項以上手術項目，僅給付手術給付倍數最高的手術項目。  
+3. 未載明於附表一的手術項目，保險公司將與被保險人協議比照附表一內程度相當的手術項目，決定給付倍數。  
+4. 以下情形不負給付責任：  
+   - 依據契約除外責任條款的規定不在給付範圍內。  
+   - 不屬全民健康保險醫療服務給付項目及支付標準第二部第二章第七節或第三部第三章第四節第三項所列舉的手術。  
+條文依據：  
+- [第十一條 住院手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="G440" s="2" t="inlineStr"/>
+      <c r="H440" s="2" t="inlineStr"/>
+      <c r="I440" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.986032, "neutral": 0.011841, "contradiction": 0.002127, "factuality": 0.997873, "C_fact": 0.997873}, "C_conf": 0.9979}</t>
+        </is>
+      </c>
+      <c r="J440" s="5" t="n"/>
+      <c r="K440" s="5" t="n">
+        <v>0.997873</v>
+      </c>
+      <c r="L440" s="5" t="n">
+        <v>0.9979</v>
+      </c>
+      <c r="M440" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:30:15</t>
+        </is>
+      </c>
+      <c r="N440" s="5" t="n">
+        <v>12.44</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B441" s="2" t="inlineStr">
+        <is>
+          <t>門診手術醫療保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C441" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+門診手術醫療保險金的給付規定如下：  
+1. 被保險人需於契約有效期間內因疾病或傷害，經醫師診斷必須於醫院或診所門診接受附表一所列的手術治療，且已實際接受手術。  
+2. 給付金額計算方式為保險單記載的「保險金額」乘以手術日當年度的「增額係數」，再乘以手術給付倍數。  
+3. 同一次手術中，若於同一手術位置接受二項以上手術項目，僅給付手術給付倍數最高的手術項目。  
+4. 同一保險單年度內，門診手術醫療保險金的給付以十次為限。  
+5. 未載明於附表一的手術項目，將與被保險人協議比照附表內手術項目決定給付倍數。  
+6. 以下情形不負給付責任：  
+   - 依據契約除外責任條款規定不在給付範圍內。  
+   - 不屬全民健康保險醫療服務給付項目及支付標準第二部第二章第七節或第三部第三章第四節第三項所列舉的手術。  
+條文依據：  
+- [第十二條 門診手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="D441" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 門診手術醫療保險金 | 第十一條 住院手術醫療保險金 | payout_items | 第十三條 意外住院手術醫療保險金 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F441" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+門診手術醫療保險金的給付規定如下：  
+1. 被保險人需於契約有效期間內因疾病或傷害，經醫師診斷必須於醫院或診所門診接受附表一所列的手術治療，且已實際接受手術。  
+2. 給付金額計算方式為保險單記載的「保險金額」乘以手術日當年度的「增額係數」，再乘以手術給付倍數。  
+3. 同一次手術中，若於同一手術位置接受二項以上手術項目，僅給付手術給付倍數最高的手術項目。  
+4. 同一保險單年度內，門診手術醫療保險金的給付以十次為限。  
+5. 未載明於附表一的手術項目，將與被保險人協議比照附表內手術項目決定給付倍數。  
+6. 以下情形不負給付責任：  
+   - 依據契約除外責任條款規定不在給付範圍內。  
+   - 不屬全民健康保險醫療服務給付項目及支付標準第二部第二章第七節或第三部第三章第四節第三項所列舉的手術。  
+條文依據：  
+- [第十二條 門診手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="G441" s="2" t="inlineStr"/>
+      <c r="H441" s="2" t="inlineStr"/>
+      <c r="I441" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.981508, "neutral": 0.017754, "contradiction": 0.000738, "factuality": 0.999262, "C_fact": 0.999262}, "C_conf": 0.9993}</t>
+        </is>
+      </c>
+      <c r="J441" s="5" t="n"/>
+      <c r="K441" s="5" t="n">
+        <v>0.999262</v>
+      </c>
+      <c r="L441" s="5" t="n">
+        <v>0.9993</v>
+      </c>
+      <c r="M441" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:30:35</t>
+        </is>
+      </c>
+      <c r="N441" s="5" t="n">
+        <v>19.64</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B442" s="2" t="inlineStr">
+        <is>
+          <t>意外住院手術醫療保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C442" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外住院手術醫療保險金的給付規定如下：  
+1. 被保險人需於本契約有效期間內且保險年齡未滿七十歲。  
+2. 因傷害經醫師診斷在住院期間必須接受手術治療且已接受手術者，保險公司按保險單所記載之「保險金額」的三倍，乘以手術日當年度之「增額係數」，給付「意外住院手術醫療保險金」。  
+3. 若被保險人於同一次手術中，於同一手術位置接受二項以上手術項目時，僅給付一次「意外住院手術醫療保險金」。  
+條文依據：  
+- [第十三條 意外住院手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="D442" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 意外住院手術醫療保險金 | 第十一條 住院手術醫療保險金 | 第十五條 意外創傷縫合處置保險金 | 第二十條 除外責任（一） | 第十二條 門診手術醫療保險金 | 附表三：意外創傷縫合處置項目及給付倍數表 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F442" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外住院手術醫療保險金的給付規定如下：  
+1. 被保險人需於本契約有效期間內且保險年齡未滿七十歲。  
+2. 因傷害經醫師診斷在住院期間必須接受手術治療且已接受手術者，保險公司按保險單所記載之「保險金額」的三倍，乘以手術日當年度之「增額係數」，給付「意外住院手術醫療保險金」。  
+3. 若被保險人於同一次手術中，於同一手術位置接受二項以上手術項目時，僅給付一次「意外住院手術醫療保險金」。  
+條文依據：  
+- [第十三條 意外住院手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="G442" s="2" t="inlineStr"/>
+      <c r="H442" s="2" t="inlineStr"/>
+      <c r="I442" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.995719, "neutral": 0.00384, "contradiction": 0.000441, "factuality": 0.999559, "C_fact": 0.999559}, "C_conf": 0.9996}</t>
+        </is>
+      </c>
+      <c r="J442" s="5" t="n"/>
+      <c r="K442" s="5" t="n">
+        <v>0.999559</v>
+      </c>
+      <c r="L442" s="5" t="n">
+        <v>0.9996</v>
+      </c>
+      <c r="M442" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:30:51</t>
+        </is>
+      </c>
+      <c r="N442" s="5" t="n">
+        <v>14.95</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B443" s="2" t="inlineStr">
+        <is>
+          <t>特定處置保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C443" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+特定處置保險金的給付規定如下：  
+1. 被保險人因疾病或傷害，經醫師診斷必須於醫院或診所接受附表二所列之特定處置治療且已接受處置者，保險公司將依保險單所記載的「保險金額」，乘以特定處置日當年度的「增額係數」，再乘以特定處置給付倍數，給付「特定處置保險金」。  
+2. 同一次處置治療中，若於同一治療位置接受二項以上特定處置項目，僅給付特定處置給付倍數最高的特定處置項目。  
+3. 若被保險人所接受的處置未載明於附表二所列之特定處置項目，保險公司不負給付特定處置保險金的責任。  
+4. 同一保險單年度的「特定處置保險金」給付次數以十次為限。
+條文依據：  
+- [第十四條 特定處置保險金]</t>
+        </is>
+      </c>
+      <c r="D443" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 特定處置保險金 | 第十五條 意外創傷縫合處置保險金 | 附表二：特定處置項目及給付倍數表 | 第五條 保險範圍 | 附表三：意外創傷縫合處置項目及給付倍數表</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F443" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+特定處置保險金的給付規定如下：  
+1. 被保險人因疾病或傷害，經醫師診斷必須於醫院或診所接受附表二所列之特定處置治療且已接受處置者，保險公司將依保險單所記載的「保險金額」，乘以特定處置日當年度的「增額係數」，再乘以特定處置給付倍數，給付「特定處置保險金」。  
+2. 同一次處置治療中，若於同一治療位置接受二項以上特定處置項目，僅給付特定處置給付倍數最高的特定處置項目。  
+3. 若被保險人所接受的處置未載明於附表二所列之特定處置項目，保險公司不負給付特定處置保險金的責任。  
+4. 同一保險單年度的「特定處置保險金」給付次數以十次為限。
+條文依據：  
+- [第十四條 特定處置保險金]</t>
+        </is>
+      </c>
+      <c r="G443" s="2" t="inlineStr"/>
+      <c r="H443" s="2" t="inlineStr"/>
+      <c r="I443" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.988805, "neutral": 0.010095, "contradiction": 0.0011, "factuality": 0.9989, "C_fact": 0.9989}, "C_conf": 0.9989}</t>
+        </is>
+      </c>
+      <c r="J443" s="5" t="n"/>
+      <c r="K443" s="5" t="n">
+        <v>0.9989</v>
+      </c>
+      <c r="L443" s="5" t="n">
+        <v>0.9989</v>
+      </c>
+      <c r="M443" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:31:00</t>
+        </is>
+      </c>
+      <c r="N443" s="5" t="n">
+        <v>9.51</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B444" s="2" t="inlineStr">
+        <is>
+          <t>意外創傷縫合處置保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C444" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外創傷縫合處置保險金的給付規定如下：  
+1. 被保險人因意外傷害事故，於醫院或診所接受附表三所列的意外創傷縫合處置治療者，本公司將依保險單所記載的「保險金額」，乘以意外創傷縫合處置日當年度的「增額係數」，再乘以意外創傷縫合處置給付倍數，給付保險金。  
+2. 同一次意外傷害事故，本公司僅就被保險人接受創傷縫合處置的傷口最大者給付保險金，且以給付一次為限。  
+3. 若被保險人因同一意外傷害事故，已申領第十一條「住院手術醫療保險金」或第十二條「門診手術醫療保險金」，則不再給付本條的「意外創傷縫合處置保險金」。  
+條文依據：  
+- [第十五條 意外創傷縫合處置保險金]</t>
+        </is>
+      </c>
+      <c r="D444" s="2" t="inlineStr">
+        <is>
+          <t>第十五條 意外創傷縫合處置保險金 | 附表三：意外創傷縫合處置項目及給付倍數表 | 第十四條 特定處置保險金 | 第二十條 除外責任（一） | 第十三條 意外住院手術醫療保險金 | 附表二：特定處置項目及給付倍數表</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F444" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外創傷縫合處置保險金的給付規定如下：  
+1. 被保險人因意外傷害事故，於醫院或診所接受附表三所列的意外創傷縫合處置治療者，本公司將依保險單所記載的「保險金額」，乘以意外創傷縫合處置日當年度的「增額係數」，再乘以意外創傷縫合處置給付倍數，給付保險金。  
+2. 同一次意外傷害事故，本公司僅就被保險人接受創傷縫合處置的傷口最大者給付保險金，且以給付一次為限。  
+3. 若被保險人因同一意外傷害事故，已申領第十一條「住院手術醫療保險金」或第十二條「門診手術醫療保險金」，則不再給付本條的「意外創傷縫合處置保險金」。  
+條文依據：  
+- [第十五條 意外創傷縫合處置保險金]</t>
+        </is>
+      </c>
+      <c r="G444" s="2" t="inlineStr"/>
+      <c r="H444" s="2" t="inlineStr"/>
+      <c r="I444" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.988778, "neutral": 0.010239, "contradiction": 0.000983, "factuality": 0.999017, "C_fact": 0.999017}, "C_conf": 0.999}</t>
+        </is>
+      </c>
+      <c r="J444" s="5" t="n"/>
+      <c r="K444" s="5" t="n">
+        <v>0.999017</v>
+      </c>
+      <c r="L444" s="5" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="M444" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:31:20</t>
+        </is>
+      </c>
+      <c r="N444" s="5" t="n">
+        <v>18.97</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B445" s="2" t="inlineStr">
+        <is>
+          <t>醫療保險金給付總額之上限</t>
+        </is>
+      </c>
+      <c r="C445" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+醫療保險金給付總額之上限為保險單上所記載的「保險金額」之一千五百倍，且僅包含第十一條至第十五條所給付的各項保險金，不包括其他附約、附加條款或批註條款。  
+條文依據：  
+- [第十六條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="D445" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 醫療保險金給付總額之上限 | 第十二條 門診手術醫療保險金 | 第五條 保險範圍 | 第十一條 住院手術醫療保險金 | 第十三條 意外住院手術醫療保險金 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F445" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+醫療保險金給付總額之上限為保險單上所記載的「保險金額」之一千五百倍，且僅包含第十一條至第十五條所給付的各項保險金，不包括其他附約、附加條款或批註條款。  
+條文依據：  
+- [第十六條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="G445" s="2" t="inlineStr"/>
+      <c r="H445" s="2" t="inlineStr"/>
+      <c r="I445" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.996805, "neutral": 0.003039, "contradiction": 0.000155, "factuality": 0.999845, "C_fact": 0.999845}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J445" s="5" t="n"/>
+      <c r="K445" s="5" t="n">
+        <v>0.999845</v>
+      </c>
+      <c r="L445" s="5" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M445" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:31:35</t>
+        </is>
+      </c>
+      <c r="N445" s="5" t="n">
+        <v>14.94</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B446" s="2" t="inlineStr">
+        <is>
+          <t>祝壽保險金的領取規定為何?金額多少？</t>
+        </is>
+      </c>
+      <c r="C446" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+祝壽保險金的領取規定如下：  
+1. 被保險人需於本契約有效期間內，且保險年齡到達九十九歲之保險單週年日仍生存。  
+2. 受益人申領祝壽保險金時，需檢具以下文件：  
+   - 保險單或其謄本  
+   - 保險金申請書  
+   - 受益人的身分證明  
+祝壽保險金的金額為「當年度保險金額」。  
+條文依據：  
+- [第十七條 祝壽保險金]  
+- [第二十六條 祝壽保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D446" s="2" t="inlineStr">
+        <is>
+          <t>第十七條 祝壽保險金 | 第二十六條 祝壽保險金的申領 | 第十一條至第十五條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | 第五條 保險範圍 | 第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F446" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+祝壽保險金的領取規定如下：  
+1. 被保險人需於本契約有效期間內，且保險年齡到達九十九歲之保險單週年日仍生存。  
+2. 受益人申領祝壽保險金時，需檢具以下文件：  
+   - 保險單或其謄本  
+   - 保險金申請書  
+   - 受益人的身分證明  
+祝壽保險金的金額為「當年度保險金額」。  
+條文依據：  
+- [第十七條 祝壽保險金]  
+- [第二十六條 祝壽保險金的申領]</t>
+        </is>
+      </c>
+      <c r="G446" s="2" t="inlineStr"/>
+      <c r="H446" s="2" t="inlineStr"/>
+      <c r="I446" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.998719, "neutral": 0.001131, "contradiction": 0.000149, "factuality": 0.999851, "C_fact": 0.999851}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J446" s="5" t="n"/>
+      <c r="K446" s="5" t="n">
+        <v>0.999851</v>
+      </c>
+      <c r="L446" s="5" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M446" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:31:44</t>
+        </is>
+      </c>
+      <c r="N446" s="5" t="n">
+        <v>9.08</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B447" s="2" t="inlineStr">
+        <is>
+          <t>身故時領取保險金有什麼規則?</t>
+        </is>
+      </c>
+      <c r="C447" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+身故時領取保險金的規則如下：  
+1. 被保險人於本契約有效期間內身故者，本公司按「當年度保險金額」給付「身故保險金」。  
+2. 若被保險人於本契約有效期間且實際年齡未滿十五足歲身故者，本公司退還「所繳保險費」予要保人，不適用「當年度保險金額」的約定。  
+3. 若被保險人於訂立契約時受監護宣告尚未撤銷，其身故保險金變更為喪葬費用保險金，且喪葬費用保險金額不得超過遺產稅喪葬費扣除額之半數，超過部分本公司不負給付責任，並退還超過部分的已繳保險費。  
+4. 若投保多家保險公司或多個保險契約，喪葬費用保險金額合計超過限額時，本公司僅依限額比例分擔責任。  
+條文依據：  
+- [第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金]</t>
+        </is>
+      </c>
+      <c r="D447" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金 | 第二十七條 身故保險金或喪葬費用保險金的申領 | 第十一條至第十五條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | 第二十一條 除外責任（二） | 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F447" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+身故時領取保險金的規則如下：  
+1. 被保險人於本契約有效期間內身故者，本公司按「當年度保險金額」給付「身故保險金」。  
+2. 若被保險人於本契約有效期間且實際年齡未滿十五足歲身故者，本公司退還「所繳保險費」予要保人，不適用「當年度保險金額」的約定。  
+3. 若被保險人於訂立契約時受監護宣告尚未撤銷，其身故保險金變更為喪葬費用保險金，且喪葬費用保險金額不得超過遺產稅喪葬費扣除額之半數，超過部分本公司不負給付責任，並退還超過部分的已繳保險費。  
+4. 若投保多家保險公司或多個保險契約，喪葬費用保險金額合計超過限額時，本公司僅依限額比例分擔責任。  
+條文依據：  
+- [第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金]</t>
+        </is>
+      </c>
+      <c r="G447" s="2" t="inlineStr"/>
+      <c r="H447" s="2" t="inlineStr"/>
+      <c r="I447" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.94375, "neutral": 0.055457, "contradiction": 0.000794, "factuality": 0.999206, "C_fact": 0.999206}, "C_conf": 0.9992}</t>
+        </is>
+      </c>
+      <c r="J447" s="5" t="n"/>
+      <c r="K447" s="5" t="n">
+        <v>0.999206</v>
+      </c>
+      <c r="L447" s="5" t="n">
+        <v>0.9992</v>
+      </c>
+      <c r="M447" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:31:53</t>
+        </is>
+      </c>
+      <c r="N447" s="5" t="n">
+        <v>9.109999999999999</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B448" s="2" t="inlineStr">
+        <is>
+          <t>什麼情況下可以保費折減?</t>
+        </is>
+      </c>
+      <c r="C448" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人年齡達20歲（含）以上，並使用保險公司指定程式加入健康計劃，於「指定日期」的會員等級符合進階會員或菁英會員（或更高等級）標準者，可享次一保險單年度的保費折減。折減比例為進階會員2%，菁英會員或更高等級3%。但豁免或復效的保險費不適用折減約定。
+條文依據：  
+- [第十九條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="D448" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 健康促進保險費折減 | 第三十條 保險金額之減少 | 第二十條 除外責任（一） | 第三十一條 投保年齡的計算及錯誤的處理 | 第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F448" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人年齡達20歲（含）以上，並使用保險公司指定程式加入健康計劃，於「指定日期」的會員等級符合進階會員或菁英會員（或更高等級）標準者，可享次一保險單年度的保費折減。折減比例為進階會員2%，菁英會員或更高等級3%。但豁免或復效的保險費不適用折減約定。
+條文依據：  
+- [第十九條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="G448" s="2" t="inlineStr"/>
+      <c r="H448" s="2" t="inlineStr"/>
+      <c r="I448" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.995136, "neutral": 0.00461, "contradiction": 0.000254, "factuality": 0.999746, "C_fact": 0.999746}, "C_conf": 0.9997}</t>
+        </is>
+      </c>
+      <c r="J448" s="5" t="n"/>
+      <c r="K448" s="5" t="n">
+        <v>0.999746</v>
+      </c>
+      <c r="L448" s="5" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="M448" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:32:07</t>
+        </is>
+      </c>
+      <c r="N448" s="5" t="n">
+        <v>12.79</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B449" s="2" t="inlineStr">
+        <is>
+          <t>角膜切除術是否可以申請理賠?</t>
+        </is>
+      </c>
+      <c r="C449" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+角膜切除術可以申請理賠，該手術項目已列於「手術項目表」中，給付倍數為5倍。
+條文依據：  
+- 附表一：手術項目與給付倍數 - 1305 角膜切除術</t>
+        </is>
+      </c>
+      <c r="D449" s="2" t="inlineStr">
+        <is>
+          <t>附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F449" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+角膜切除術可以申請理賠，該手術項目已列於「手術項目表」中，給付倍數為5倍。
+條文依據：  
+- 附表一：手術項目與給付倍數 - 1305 角膜切除術</t>
+        </is>
+      </c>
+      <c r="G449" s="2" t="inlineStr"/>
+      <c r="H449" s="2" t="inlineStr"/>
+      <c r="I449" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.866441, "neutral": 0.127973, "contradiction": 0.005586, "factuality": 0.994414, "C_fact": 0.994414}, "C_conf": 0.9944}</t>
+        </is>
+      </c>
+      <c r="J449" s="5" t="n"/>
+      <c r="K449" s="5" t="n">
+        <v>0.994414</v>
+      </c>
+      <c r="L449" s="5" t="n">
+        <v>0.9944</v>
+      </c>
+      <c r="M449" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:32:21</t>
+        </is>
+      </c>
+      <c r="N449" s="5" t="n">
+        <v>14.06</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B450" s="2" t="inlineStr">
+        <is>
+          <t>白內障手術是否可以申請理賠?膜性白內障切開術、白內障線狀摘出術或白內障切囊術</t>
+        </is>
+      </c>
+      <c r="C450" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+白內障手術可以申請理賠，包含膜性白內障切開術、白內障線狀摘出術及白內障切囊術。這些手術均列於附表一的手術項目中，並有對應的給付倍數。膜性白內障切開術的給付倍數為5，白內障線狀摘出術的給付倍數為5，白內障切囊術的給付倍數亦為5。
+條文依據：  
+- 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="D450" s="2" t="inlineStr">
+        <is>
+          <t>附表一：手術項目與給付倍數 | payout_items | 附表二：特定處置項目及給付倍數表</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F450" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+白內障手術可以申請理賠，包含膜性白內障切開術、白內障線狀摘出術及白內障切囊術。這些手術均列於附表一的手術項目中，並有對應的給付倍數。膜性白內障切開術的給付倍數為5，白內障線狀摘出術的給付倍數為5，白內障切囊術的給付倍數亦為5。
+條文依據：  
+- 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="G450" s="2" t="inlineStr"/>
+      <c r="H450" s="2" t="inlineStr"/>
+      <c r="I450" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.994174, "neutral": 0.005548, "contradiction": 0.000278, "factuality": 0.999722, "C_fact": 0.999722}, "C_conf": 0.9997}</t>
+        </is>
+      </c>
+      <c r="J450" s="5" t="n"/>
+      <c r="K450" s="5" t="n">
+        <v>0.999722</v>
+      </c>
+      <c r="L450" s="5" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="M450" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:32:40</t>
+        </is>
+      </c>
+      <c r="N450" s="5" t="n">
+        <v>17.46</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B451" s="2" t="inlineStr">
+        <is>
+          <t>保障範圍包括哪些項目？</t>
+        </is>
+      </c>
+      <c r="C451" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括：意外事故身故保險金或喪葬費用保險金、意外事故失能保險金、每月生活照護保險金、重大燒燙傷保險金、意外骨折保險金、傷害醫療日額保險金、意外創傷縫合處置保險金。
+條文依據：  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="D451" s="2" t="inlineStr">
+        <is>
+          <t>payout_items | 第五條 保險範圍 | 第十五條 每月生活照護保險金的給付 | 第三十條 不保事項 | 附表二：失能程度與保險金給付表</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F451" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括：意外事故身故保險金或喪葬費用保險金、意外事故失能保險金、每月生活照護保險金、重大燒燙傷保險金、意外骨折保險金、傷害醫療日額保險金、意外創傷縫合處置保險金。
+條文依據：  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="G451" s="2" t="inlineStr"/>
+      <c r="H451" s="2" t="inlineStr"/>
+      <c r="I451" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.997935, "neutral": 0.001907, "contradiction": 0.000158, "factuality": 0.999842, "C_fact": 0.999842}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J451" s="5" t="n"/>
+      <c r="K451" s="5" t="n">
+        <v>0.999842</v>
+      </c>
+      <c r="L451" s="5" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M451" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:32:55</t>
+        </is>
+      </c>
+      <c r="N451" s="5" t="n">
+        <v>14.44</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B452" s="2" t="inlineStr">
+        <is>
+          <t>發生意外事故身故，理賠內容為何?</t>
+        </is>
+      </c>
+      <c r="C452" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外事故身故的理賠內容包括「意外事故身故保險金」或「喪葬費用保險金」，其金額依意外傷害事故的種類而定：  
+1. 一般意外傷害事故：「傷害醫療保險金日額」的五百倍。  
+2. 特定意外傷害事故：「傷害醫療保險金日額」的一千倍。  
+若被保險人於意外傷害事故發生後超過一百八十日身故，但受益人能證明身故與該事故具有因果關係，本公司仍依上述約定給付保險金。此外，若被保險人受監護宣告尚未撤銷，其理賠內容變更為「喪葬費用保險金」，且喪葬費用保險金額不得超過遺產稅喪葬費扣除額之半數，超過部分不負給付責任。  
+條文依據：  
+- [第十二條 意外事故身故保險金或喪葬費用保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D452" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 意外事故身故保險金或喪葬費用保險金的給付 | 第十四條 保險給付的限制 | payout_items | 第十一條 契約的終止（二） | 第二十一條 失蹤處理</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F452" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外事故身故的理賠內容包括「意外事故身故保險金」或「喪葬費用保險金」，其金額依意外傷害事故的種類而定：  
+1. 一般意外傷害事故：「傷害醫療保險金日額」的五百倍。  
+2. 特定意外傷害事故：「傷害醫療保險金日額」的一千倍。  
+若被保險人於意外傷害事故發生後超過一百八十日身故，但受益人能證明身故與該事故具有因果關係，本公司仍依上述約定給付保險金。此外，若被保險人受監護宣告尚未撤銷，其理賠內容變更為「喪葬費用保險金」，且喪葬費用保險金額不得超過遺產稅喪葬費扣除額之半數，超過部分不負給付責任。  
+條文依據：  
+- [第十二條 意外事故身故保險金或喪葬費用保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G452" s="2" t="inlineStr"/>
+      <c r="H452" s="2" t="inlineStr"/>
+      <c r="I452" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.931662, "neutral": 0.067693, "contradiction": 0.000644, "factuality": 0.999356, "C_fact": 0.999356}, "C_conf": 0.9994}</t>
+        </is>
+      </c>
+      <c r="J452" s="5" t="n"/>
+      <c r="K452" s="5" t="n">
+        <v>0.999356</v>
+      </c>
+      <c r="L452" s="5" t="n">
+        <v>0.9994</v>
+      </c>
+      <c r="M452" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:33:03</t>
+        </is>
+      </c>
+      <c r="N452" s="5" t="n">
+        <v>8.529999999999999</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B453" s="2" t="inlineStr">
+        <is>
+          <t>意外事故失能保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C453" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外事故失能保險金的給付條件如下：  
+1. 被保險人於契約有效期間內遭受意外傷害事故，並於事故發生後180日內致成附表二所列失能程度之一者，本公司依意外傷害事故種類及失能程度，按以下約定金額給付：  
+   - 一般意外傷害事故：「傷害醫療保險金日額」的500倍乘以附表二給付比例。  
+   - 特定意外傷害事故：「傷害醫療保險金日額」的1000倍乘以附表二給付比例。  
+2. 若被保險人超過180日後致成失能，受益人能證明失能與事故具有因果關係者，本公司仍依上述規定給付，不受180日限制。  
+3. 同一事故致成多項失能時，僅給付同一手或足中較嚴重項目的失能保險金，且給付金額以事故種類的上限為限。  
+4. 若失能合併以前的失能，僅給付較嚴重項目，但需扣除以前已給付的金額。  
+條文依據：  
+- [第十三條 意外事故失能保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D453" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 意外事故失能保險金的給付 | 第十五條 每月生活照護保險金的給付 | 第十四條 保險給付的限制 | 第十二條 意外事故身故保險金或喪葬費用保險金的給付 | 第二十三條 意外事故失能保險金的申領 | 附表二：失能程度與保險金給付表</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F453" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外事故失能保險金的給付條件如下：  
+1. 被保險人於契約有效期間內遭受意外傷害事故，並於事故發生後180日內致成附表二所列失能程度之一者，本公司依意外傷害事故種類及失能程度，按以下約定金額給付：  
+   - 一般意外傷害事故：「傷害醫療保險金日額」的500倍乘以附表二給付比例。  
+   - 特定意外傷害事故：「傷害醫療保險金日額」的1000倍乘以附表二給付比例。  
+2. 若被保險人超過180日後致成失能，受益人能證明失能與事故具有因果關係者，本公司仍依上述規定給付，不受180日限制。  
+3. 同一事故致成多項失能時，僅給付同一手或足中較嚴重項目的失能保險金，且給付金額以事故種類的上限為限。  
+4. 若失能合併以前的失能，僅給付較嚴重項目，但需扣除以前已給付的金額。  
+條文依據：  
+- [第十三條 意外事故失能保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G453" s="2" t="inlineStr"/>
+      <c r="H453" s="2" t="inlineStr"/>
+      <c r="I453" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.171292, "neutral": 0.815996, "contradiction": 0.012712, "factuality": 0.987288, "C_fact": 0.987288}, "C_conf": 0.9873}</t>
+        </is>
+      </c>
+      <c r="J453" s="5" t="n"/>
+      <c r="K453" s="5" t="n">
+        <v>0.9872880000000001</v>
+      </c>
+      <c r="L453" s="5" t="n">
+        <v>0.9873</v>
+      </c>
+      <c r="M453" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:33:15</t>
+        </is>
+      </c>
+      <c r="N453" s="5" t="n">
+        <v>11.13</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B454" s="2" t="inlineStr">
+        <is>
+          <t>每月生活照護保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C454" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+每月生活照護保險金的給付條件如下：  
+1. 被保險人於契約有效期間內遭受意外傷害事故，並於事故發生後180日內致成附表二所列第一級至第六級失能程度之一時，本公司自失能診斷確定當日起，按「傷害醫療保險金日額」的20倍乘以附表二給付比例所得之金額，按月給付，最多以12個月為限。  
+2. 若失能診斷確定後的前四個「失能診斷確定週年日」，契約仍有效且被保險人仍生存，本公司自各該週年日起，依相同計算方式再給付最多12個月。  
+3. 若被保險人於事故發生後超過180日才致成失能，受益人需證明失能與事故具有因果關係，本公司仍可依上述規定給付，不受180日限制。  
+4. 同一事故若致成多項失能，僅給付較嚴重項目，且最高以「傷害醫療保險金日額」的20倍為限。  
+5. 累計給付金額最高以「傷害醫療保險金日額」的1200倍為限。  
+條文依據：  
+- [第十五條 每月生活照護保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D454" s="2" t="inlineStr">
+        <is>
+          <t>第二十四條 每月生活照護保險金的申領 | 第十五條 每月生活照護保險金的給付 | payout_items | 第十八條 傷害醫療日額保險金的給付 | 第五條 保險範圍 | 附表二：失能程度與保險金給付表 | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F454" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+每月生活照護保險金的給付條件如下：  
+1. 被保險人於契約有效期間內遭受意外傷害事故，並於事故發生後180日內致成附表二所列第一級至第六級失能程度之一時，本公司自失能診斷確定當日起，按「傷害醫療保險金日額」的20倍乘以附表二給付比例所得之金額，按月給付，最多以12個月為限。  
+2. 若失能診斷確定後的前四個「失能診斷確定週年日」，契約仍有效且被保險人仍生存，本公司自各該週年日起，依相同計算方式再給付最多12個月。  
+3. 若被保險人於事故發生後超過180日才致成失能，受益人需證明失能與事故具有因果關係，本公司仍可依上述規定給付，不受180日限制。  
+4. 同一事故若致成多項失能，僅給付較嚴重項目，且最高以「傷害醫療保險金日額」的20倍為限。  
+5. 累計給付金額最高以「傷害醫療保險金日額」的1200倍為限。  
+條文依據：  
+- [第十五條 每月生活照護保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G454" s="2" t="inlineStr"/>
+      <c r="H454" s="2" t="inlineStr"/>
+      <c r="I454" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.449201, "neutral": 0.5274, "contradiction": 0.0234, "factuality": 0.9766, "C_fact": 0.9766}, "C_conf": 0.9766}</t>
+        </is>
+      </c>
+      <c r="J454" s="5" t="n"/>
+      <c r="K454" s="5" t="n">
+        <v>0.9766</v>
+      </c>
+      <c r="L454" s="5" t="n">
+        <v>0.9766</v>
+      </c>
+      <c r="M454" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:33:25</t>
+        </is>
+      </c>
+      <c r="N454" s="5" t="n">
+        <v>9.75</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B455" s="2" t="inlineStr">
+        <is>
+          <t>重大燒燙傷保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C455" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+重大燒燙傷保險金的給付條件為：被保險人於本契約有效期間內因「意外傷害事故」導致燒燙傷，且經診斷符合「重大燒燙傷」的標準時，本公司將依「傷害醫療保險金日額」的二百五十倍給付「重大燒燙傷保險金」。此保險金的給付以一次為限。
+條文依據：  
+- [第十六條 重大燒燙傷保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D455" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 重大燒燙傷保險金的給付 | 第二十五條 重大燒燙傷保險金的申領 | 第五條 保險範圍 | payout_items | 第二十九條 除外責任（原因）</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F455" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+重大燒燙傷保險金的給付條件為：被保險人於本契約有效期間內因「意外傷害事故」導致燒燙傷，且經診斷符合「重大燒燙傷」的標準時，本公司將依「傷害醫療保險金日額」的二百五十倍給付「重大燒燙傷保險金」。此保險金的給付以一次為限。
+條文依據：  
+- [第十六條 重大燒燙傷保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G455" s="2" t="inlineStr"/>
+      <c r="H455" s="2" t="inlineStr"/>
+      <c r="I455" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.997102, "neutral": 0.002771, "contradiction": 0.000127, "factuality": 0.999873, "C_fact": 0.999873}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J455" s="5" t="n"/>
+      <c r="K455" s="5" t="n">
+        <v>0.999873</v>
+      </c>
+      <c r="L455" s="5" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M455" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:33:40</t>
+        </is>
+      </c>
+      <c r="N455" s="5" t="n">
+        <v>14.16</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B456" s="2" t="inlineStr">
+        <is>
+          <t>意外骨折保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C456" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外骨折保險金的給付條件如下：  
+1. 被保險人於契約有效期間內遭受「意外傷害事故」，自事故發生日起一百八十日內，經合格醫院或診所診斷為附表三骨折別表所列骨折項目之一（含不完全骨折及骨骼龜裂），本公司按「傷害醫療保險金日額」的二倍給付意外骨折保險金。  
+2. 若超過一百八十日診斷確定骨折，受益人能證明骨折與事故具有因果關係者，仍可依上述規定給付，不受一百八十日限制。  
+3. 同一意外傷害事故僅給付一次意外骨折保險金。  
+4. 若骨折非屬附表三骨折別表所列項目，需由本公司與被保險人協議核付；但若骨折部位為骨折別表內明訂不給付之部位，則本公司不負給付責任。
+條文依據：  
+- [第十七條 意外骨折保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D456" s="2" t="inlineStr">
+        <is>
+          <t>第十七條 意外骨折保險金的給付 | 第十八條 傷害醫療日額保險金的給付 | 第二十六條 意外骨折保險金的申領 | 第十三條 意外事故失能保險金的給付 | 第十九條 意外創傷縫合處置保險金的給付 | 附表二：失能程度與保險金給付表 | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F456" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外骨折保險金的給付條件如下：  
+1. 被保險人於契約有效期間內遭受「意外傷害事故」，自事故發生日起一百八十日內，經合格醫院或診所診斷為附表三骨折別表所列骨折項目之一（含不完全骨折及骨骼龜裂），本公司按「傷害醫療保險金日額」的二倍給付意外骨折保險金。  
+2. 若超過一百八十日診斷確定骨折，受益人能證明骨折與事故具有因果關係者，仍可依上述規定給付，不受一百八十日限制。  
+3. 同一意外傷害事故僅給付一次意外骨折保險金。  
+4. 若骨折非屬附表三骨折別表所列項目，需由本公司與被保險人協議核付；但若骨折部位為骨折別表內明訂不給付之部位，則本公司不負給付責任。
+條文依據：  
+- [第十七條 意外骨折保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G456" s="2" t="inlineStr"/>
+      <c r="H456" s="2" t="inlineStr"/>
+      <c r="I456" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.990871, "neutral": 0.008849, "contradiction": 0.00028, "factuality": 0.99972, "C_fact": 0.99972}, "C_conf": 0.9997}</t>
+        </is>
+      </c>
+      <c r="J456" s="5" t="n"/>
+      <c r="K456" s="5" t="n">
+        <v>0.9997200000000001</v>
+      </c>
+      <c r="L456" s="5" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="M456" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:33:50</t>
+        </is>
+      </c>
+      <c r="N456" s="5" t="n">
+        <v>9.91</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B457" s="2" t="inlineStr">
+        <is>
+          <t>傷害醫療日額保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C457" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+傷害醫療日額保險金的給付條件如下：  
+1. 被保險人於契約有效期間內遭受「意外傷害事故」，自事故發生日起一百八十日內於「醫院」接受住院治療者，本公司按「傷害醫療保險金日額」乘以實際住院日數給付，最高以九十日為限。  
+2. 若治療超過一百八十日，受益人能證明治療與事故具有因果關係者，仍可依規定給付，不受一百八十日限制。  
+3. 若因意外事故骨折未住院或住院未達附表三骨折別表所訂日數，未住院部分按骨折別表所訂日數乘以「傷害醫療保險金日額」的二分之一給付，合計給付日數以骨折別表所訂日數為上限。  
+4. 骨折給付依骨折程度分為完全骨折、不完全骨折及骨骼龜裂，分別按完全骨折日數的全額、二分之一及四分之一給付。若同時有多項骨折，僅給付較高等級的保險金。
+條文依據：  
+- [第十八條 傷害醫療日額保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D457" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 傷害醫療日額保險金的給付 | 第二十七條 傷害醫療日額保險金的申領 | 第十五條 每月生活照護保險金的給付 | 第三十四條 傷害醫療保險金日額之減少 | 第十九條 意外創傷縫合處置保險金的給付 | 附表二：失能程度與保險金給付表 | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F457" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+傷害醫療日額保險金的給付條件如下：  
+1. 被保險人於契約有效期間內遭受「意外傷害事故」，自事故發生日起一百八十日內於「醫院」接受住院治療者，本公司按「傷害醫療保險金日額」乘以實際住院日數給付，最高以九十日為限。  
+2. 若治療超過一百八十日，受益人能證明治療與事故具有因果關係者，仍可依規定給付，不受一百八十日限制。  
+3. 若因意外事故骨折未住院或住院未達附表三骨折別表所訂日數，未住院部分按骨折別表所訂日數乘以「傷害醫療保險金日額」的二分之一給付，合計給付日數以骨折別表所訂日數為上限。  
+4. 骨折給付依骨折程度分為完全骨折、不完全骨折及骨骼龜裂，分別按完全骨折日數的全額、二分之一及四分之一給付。若同時有多項骨折，僅給付較高等級的保險金。
+條文依據：  
+- [第十八條 傷害醫療日額保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G457" s="2" t="inlineStr"/>
+      <c r="H457" s="2" t="inlineStr"/>
+      <c r="I457" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.918414, "neutral": 0.080796, "contradiction": 0.00079, "factuality": 0.99921, "C_fact": 0.99921}, "C_conf": 0.9992}</t>
+        </is>
+      </c>
+      <c r="J457" s="5" t="n"/>
+      <c r="K457" s="5" t="n">
+        <v>0.99921</v>
+      </c>
+      <c r="L457" s="5" t="n">
+        <v>0.9992</v>
+      </c>
+      <c r="M457" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:33:56</t>
+        </is>
+      </c>
+      <c r="N457" s="5" t="n">
+        <v>6.23</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B458" s="2" t="inlineStr">
+        <is>
+          <t>意外創傷縫合處置保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C458" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外創傷縫合處置保險金的給付條件為：被保險人於契約有效期間內遭受「意外傷害事故」，並於「醫院」或「診所」經醫師診斷必須接受創傷縫合處置治療且已接受縫合處置者，本公司按「傷害醫療保險金日額」給付該保險金。同一意外傷害事故僅給付一次。
+條文依據：  
+- [第十九條 意外創傷縫合處置保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D458" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 意外創傷縫合處置保險金的給付 | 第二十八條 意外創傷縫合處置保險金的申領 | 第五條 保險範圍 | 第十七條 意外骨折保險金的給付 | payout_items | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F458" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外創傷縫合處置保險金的給付條件為：被保險人於契約有效期間內遭受「意外傷害事故」，並於「醫院」或「診所」經醫師診斷必須接受創傷縫合處置治療且已接受縫合處置者，本公司按「傷害醫療保險金日額」給付該保險金。同一意外傷害事故僅給付一次。
+條文依據：  
+- [第十九條 意外創傷縫合處置保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G458" s="2" t="inlineStr"/>
+      <c r="H458" s="2" t="inlineStr"/>
+      <c r="I458" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.996712, "neutral": 0.003178, "contradiction": 0.000111, "factuality": 0.999889, "C_fact": 0.999889}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J458" s="5" t="n"/>
+      <c r="K458" s="5" t="n">
+        <v>0.999889</v>
+      </c>
+      <c r="L458" s="5" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M458" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:34:01</t>
+        </is>
+      </c>
+      <c r="N458" s="5" t="n">
+        <v>4.34</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B459" s="2" t="inlineStr">
+        <is>
+          <t>因意外導致視力衰退，是否能申請理賠?</t>
+        </is>
+      </c>
+      <c r="C459" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+因意外導致視力衰退是否能申請理賠，需符合以下條件：  
+1. 視力永久在萬國式視力表0.02以下，或符合失明的定義（包括眼球喪失、摘出、僅能辨明暗或辨眼前一公尺以內手動或辨眼前五公分以內指數）。  
+2. 視力障害的測定需經過六個月的治療判定，但若屬眼球摘出等明顯無法復原的情況，則不受六個月治療期的限制。  
+條文依據：  
+- 註2</t>
+        </is>
+      </c>
+      <c r="D459" s="2" t="inlineStr">
+        <is>
+          <t>第二十三條 意外事故失能保險金的申領 | 第十三條 意外事故失能保險金的給付 | 註2： | 第三十條 不保事項 | 第二十六條 意外骨折保險金的申領 | 附表二：失能程度與保險金給付表</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F459" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+因意外導致視力衰退是否能申請理賠，需符合以下條件：  
+1. 視力永久在萬國式視力表0.02以下，或符合失明的定義（包括眼球喪失、摘出、僅能辨明暗或辨眼前一公尺以內手動或辨眼前五公分以內指數）。  
+2. 視力障害的測定需經過六個月的治療判定，但若屬眼球摘出等明顯無法復原的情況，則不受六個月治療期的限制。  
+條文依據：  
+- 註2</t>
+        </is>
+      </c>
+      <c r="G459" s="2" t="inlineStr"/>
+      <c r="H459" s="2" t="inlineStr"/>
+      <c r="I459" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.731819, "neutral": 0.187466, "contradiction": 0.080715, "factuality": 0.919285, "C_fact": 0.919285}, "C_conf": 0.9193}</t>
+        </is>
+      </c>
+      <c r="J459" s="5" t="n"/>
+      <c r="K459" s="5" t="n">
+        <v>0.919285</v>
+      </c>
+      <c r="L459" s="5" t="n">
+        <v>0.9193</v>
+      </c>
+      <c r="M459" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:34:07</t>
+        </is>
+      </c>
+      <c r="N459" s="5" t="n">
+        <v>6.14</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B460" s="2" t="inlineStr">
+        <is>
+          <t>肋骨骨折是否可以申請理賠?理賠金額為多少?包含傷害醫療保險金日額跟意外骨折保險金嗎？</t>
+        </is>
+      </c>
+      <c r="C460" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+肋骨骨折可以申請理賠，理賠金額包含「傷害醫療保險金日額」及「意外骨折保險金」。  
+1. 若被保險人因意外傷害事故導致肋骨骨折並住院治療，依「傷害醫療保險金日額」乘以實際住院日數給付，最高給付日數以附表三所訂完全骨折日數（20天）為上限。若未住院治療，則按附表三所訂完全骨折日數乘以「傷害醫療保險金日額」的二分之一給付。  
+2. 若被保險人因意外傷害事故導致肋骨骨折，且符合附表三骨折別表所列項目，則可申請「意外骨折保險金」，給付金額為「傷害醫療保險金日額」的二倍。  
+條文依據：  
+- [第十八條 傷害醫療日額保險金的給付]  
+- [第十七條 意外骨折保險金的給付]  
+- [附表三：骨折別表]</t>
+        </is>
+      </c>
+      <c r="D460" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 傷害醫療日額保險金的給付 | 第十七條 意外骨折保險金的給付 | 第二十六條 意外骨折保險金的申領 | payout_items | 第二十七條 傷害醫療日額保險金的申領 | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F460" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+肋骨骨折可以申請理賠，理賠金額包含「傷害醫療保險金日額」及「意外骨折保險金」。  
+1. 若被保險人因意外傷害事故導致肋骨骨折並住院治療，依「傷害醫療保險金日額」乘以實際住院日數給付，最高給付日數以附表三所訂完全骨折日數（20天）為上限。若未住院治療，則按附表三所訂完全骨折日數乘以「傷害醫療保險金日額」的二分之一給付。  
+2. 若被保險人因意外傷害事故導致肋骨骨折，且符合附表三骨折別表所列項目，則可申請「意外骨折保險金」，給付金額為「傷害醫療保險金日額」的二倍。  
+條文依據：  
+- [第十八條 傷害醫療日額保險金的給付]  
+- [第十七條 意外骨折保險金的給付]  
+- [附表三：骨折別表]</t>
+        </is>
+      </c>
+      <c r="G460" s="2" t="inlineStr"/>
+      <c r="H460" s="2" t="inlineStr"/>
+      <c r="I460" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.980725, "neutral": 0.014697, "contradiction": 0.004578, "factuality": 0.995422, "C_fact": 0.995422}, "C_conf": 0.9954}</t>
+        </is>
+      </c>
+      <c r="J460" s="5" t="n"/>
+      <c r="K460" s="5" t="n">
+        <v>0.995422</v>
+      </c>
+      <c r="L460" s="5" t="n">
+        <v>0.9954</v>
+      </c>
+      <c r="M460" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:34:18</t>
+        </is>
+      </c>
+      <c r="N460" s="5" t="n">
+        <v>10.19</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B461" s="2" t="inlineStr">
+        <is>
+          <t>投保新鍾心滿福後，假設投保保額為100萬元，於第二保單年度接受「移植器官」，這樣可以領多少重大傷病保險金及特定重大傷病保險金?</t>
+        </is>
+      </c>
+      <c r="C461" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人於第二保險單年度接受「移植器官」，符合重大傷病及特定重大傷病的定義，則可獲得以下保險金給付：  
+1. **重大傷病保險金**：依第十二條規定，第二保險單年度罹患重大傷病時，若屬「重大傷病範圍」中除慢性精神病外的項目，給付金額為「保險金額」或「年繳應繳保險費總額的一點零五倍」，二者取其大者。假設保額為100萬元，則重大傷病保險金為100萬元。  
+2. **特定重大傷病保險金**：依第十三條規定，於第二保險單年度（含）以後罹患「特定重大傷病」，可額外獲得「保險金額的百分之二十」作為特定重大傷病保險金。假設保額為100萬元，則特定重大傷病保險金為20萬元。  
+因此，總給付金額為：重大傷病保險金100萬元 + 特定重大傷病保險金20萬元 = **120萬元**。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第十三條 特定重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D461" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 特定重大傷病保險金的給付 | 第十二條 重大傷病保險金的給付 | 附表一：全民健康保險重大傷病項目 | payout_items | 第二條 名詞定義 | 附表二：完全失能程度表</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F461" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人於第二保險單年度接受「移植器官」，符合重大傷病及特定重大傷病的定義，則可獲得以下保險金給付：  
+1. **重大傷病保險金**：依第十二條規定，第二保險單年度罹患重大傷病時，若屬「重大傷病範圍」中除慢性精神病外的項目，給付金額為「保險金額」或「年繳應繳保險費總額的一點零五倍」，二者取其大者。假設保額為100萬元，則重大傷病保險金為100萬元。  
+2. **特定重大傷病保險金**：依第十三條規定，於第二保險單年度（含）以後罹患「特定重大傷病」，可額外獲得「保險金額的百分之二十」作為特定重大傷病保險金。假設保額為100萬元，則特定重大傷病保險金為20萬元。  
+因此，總給付金額為：重大傷病保險金100萬元 + 特定重大傷病保險金20萬元 = **120萬元**。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第十三條 特定重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G461" s="2" t="inlineStr"/>
+      <c r="H461" s="2" t="inlineStr"/>
+      <c r="I461" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.195488, "neutral": 0.785449, "contradiction": 0.019063, "factuality": 0.980937, "C_fact": 0.980937}, "C_conf": 0.9809}</t>
+        </is>
+      </c>
+      <c r="J461" s="5" t="n"/>
+      <c r="K461" s="5" t="n">
+        <v>0.9809369999999999</v>
+      </c>
+      <c r="L461" s="5" t="n">
+        <v>0.9809</v>
+      </c>
+      <c r="M461" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:34:28</t>
+        </is>
+      </c>
+      <c r="N461" s="5" t="n">
+        <v>10.47</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B462" s="2" t="inlineStr">
+        <is>
+          <t>投保新鍾心滿福後，若要理賠重大傷病保險金，一定要檢附全民健保開立的重大傷病證明才能拿到保險金嗎?</t>
+        </is>
+      </c>
+      <c r="C462" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不一定需要檢附全民健保開立的重大傷病證明。若被保險人之「重大傷病」係由診治醫師逕行認定，並已取得一家「區域醫院」層級以上（含）之醫療院所開立且符合投保當時「重大傷病範圍」之診斷書及當次「重大傷病」病歷摘要，則可視為「重大傷病」證明文件，免向全民健康保險保險人申請。  
+條文依據：  
+- [第二十二條 重大傷病保險金、特定重大傷病保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D462" s="2" t="inlineStr">
+        <is>
+          <t>第二十二條 重大傷病保險金、特定重大傷病保險金的申領 | other_metadata | 第十二條 重大傷病保險金的給付 | 附表一：全民健康保險重大傷病項目 | 第二條 名詞定義 | 第三十條 不保事項</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F462" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不一定需要檢附全民健保開立的重大傷病證明。若被保險人之「重大傷病」係由診治醫師逕行認定，並已取得一家「區域醫院」層級以上（含）之醫療院所開立且符合投保當時「重大傷病範圍」之診斷書及當次「重大傷病」病歷摘要，則可視為「重大傷病」證明文件，免向全民健康保險保險人申請。  
+條文依據：  
+- [第二十二條 重大傷病保險金、特定重大傷病保險金的申領]</t>
+        </is>
+      </c>
+      <c r="G462" s="2" t="inlineStr"/>
+      <c r="H462" s="2" t="inlineStr"/>
+      <c r="I462" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.787248, "neutral": 0.02054, "contradiction": 0.192212, "factuality": 0.807788, "C_fact": 0.807788}, "C_conf": 0.8078}</t>
+        </is>
+      </c>
+      <c r="J462" s="5" t="n"/>
+      <c r="K462" s="5" t="n">
+        <v>0.807788</v>
+      </c>
+      <c r="L462" s="5" t="n">
+        <v>0.8078</v>
+      </c>
+      <c r="M462" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:34:52</t>
+        </is>
+      </c>
+      <c r="N462" s="5" t="n">
+        <v>23.29</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B463" s="2" t="inlineStr">
+        <is>
+          <t>要有健保身分才能申請重大傷病理賠嗎？</t>
+        </is>
+      </c>
+      <c r="C463" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+是的，若被保險人喪失全民健康保險被保險人資格，需先申請加保全民健康保險後，才能申領重大傷病保險金的給付。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D463" s="2" t="inlineStr">
+        <is>
+          <t>第二十二條 重大傷病保險金、特定重大傷病保險金的申領 | 第十二條 重大傷病保險金的給付 | 第三十條 不保事項 | other_metadata | 第二條 名詞定義 | 附表一：全民健康保險重大傷病項目</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F463" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+是的，若被保險人喪失全民健康保險被保險人資格，需先申請加保全民健康保險後，才能申領重大傷病保險金的給付。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G463" s="2" t="inlineStr"/>
+      <c r="H463" s="2" t="inlineStr"/>
+      <c r="I463" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.854508, "neutral": 0.093947, "contradiction": 0.051545, "factuality": 0.948455, "C_fact": 0.948455}, "C_conf": 0.9485}</t>
+        </is>
+      </c>
+      <c r="J463" s="5" t="n"/>
+      <c r="K463" s="5" t="n">
+        <v>0.948455</v>
+      </c>
+      <c r="L463" s="5" t="n">
+        <v>0.9485</v>
+      </c>
+      <c r="M463" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:35:04</t>
+        </is>
+      </c>
+      <c r="N463" s="5" t="n">
+        <v>12.05</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B464" s="2" t="inlineStr">
+        <is>
+          <t>重大傷病的項目如果在投保後有新增，可以從優申請理賠嗎？</t>
+        </is>
+      </c>
+      <c r="C464" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以申請理賠，但需符合以下條件：重大傷病項目若在投保後新增，理賠範圍以「訂立時」及「有效期間內被保險人診斷確定當時」由中央衛生主管機關公告之最新項目為準。因此，只要新增項目在被保險人診斷確定時已被公告為重大傷病項目，即可申請理賠。
+條文依據：  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D464" s="2" t="inlineStr">
+        <is>
+          <t>附表一：全民健康保險重大傷病項目 | 第二條 名詞定義 | payout_items</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F464" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以申請理賠，但需符合以下條件：重大傷病項目若在投保後新增，理賠範圍以「訂立時」及「有效期間內被保險人診斷確定當時」由中央衛生主管機關公告之最新項目為準。因此，只要新增項目在被保險人診斷確定時已被公告為重大傷病項目，即可申請理賠。
+條文依據：  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G464" s="2" t="inlineStr"/>
+      <c r="H464" s="2" t="inlineStr"/>
+      <c r="I464" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.991177, "neutral": 0.007548, "contradiction": 0.001276, "factuality": 0.998724, "C_fact": 0.998724}, "C_conf": 0.9987}</t>
+        </is>
+      </c>
+      <c r="J464" s="5" t="n"/>
+      <c r="K464" s="5" t="n">
+        <v>0.9987239999999999</v>
+      </c>
+      <c r="L464" s="5" t="n">
+        <v>0.9987</v>
+      </c>
+      <c r="M464" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:35:26</t>
+        </is>
+      </c>
+      <c r="N464" s="5" t="n">
+        <v>18.21</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B465" s="2" t="inlineStr">
+        <is>
+          <t>我的保單之前有停效，在復效後五天被診斷出重大疾病是否可申請理賠？</t>
+        </is>
+      </c>
+      <c r="C465" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以申請理賠，但需符合以下條件：  
+1. 復效後的契約有效期間內，被保險人經醫院醫師初次診斷確定罹患「重大傷病」。  
+2. 被保險人已取得符合「重大傷病範圍」的診斷書及病歷摘要，或取得全民健康保險保險人核發的重大傷病證明。  
+3. 若重大傷病係因意外傷害事故所致，則不受等待期間限制；若非因意外傷害事故，則需等待期間屆滿翌日或復效日起方可申請理賠。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D465" s="2" t="inlineStr">
+        <is>
+          <t>第八條 本契約效力的恢復 | 第三十條 不保事項 | 第五條 保險範圍 | other_metadata | 第二條 名詞定義 | 第十二條 重大傷病保險金的給付 | 第二十二條 重大傷病保險金、特定重大傷病保險金的申領 | 附表一：全民健康保險重大傷病項目</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F465" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以申請理賠，但需符合以下條件：  
+1. 復效後的契約有效期間內，被保險人經醫院醫師初次診斷確定罹患「重大傷病」。  
+2. 被保險人已取得符合「重大傷病範圍」的診斷書及病歷摘要，或取得全民健康保險保險人核發的重大傷病證明。  
+3. 若重大傷病係因意外傷害事故所致，則不受等待期間限制；若非因意外傷害事故，則需等待期間屆滿翌日或復效日起方可申請理賠。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G465" s="2" t="inlineStr"/>
+      <c r="H465" s="2" t="inlineStr"/>
+      <c r="I465" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.017439, "neutral": 0.975275, "contradiction": 0.007286, "factuality": 0.992714, "C_fact": 0.992714}, "C_conf": 0.9927}</t>
+        </is>
+      </c>
+      <c r="J465" s="5" t="n"/>
+      <c r="K465" s="5" t="n">
+        <v>0.992714</v>
+      </c>
+      <c r="L465" s="5" t="n">
+        <v>0.9927</v>
+      </c>
+      <c r="M465" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:35:43</t>
+        </is>
+      </c>
+      <c r="N465" s="5" t="n">
+        <v>16.37</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B466" s="2" t="inlineStr">
+        <is>
+          <t>領完重大傷病保險金，主約終止後，附約可以繼續有效嗎?</t>
+        </is>
+      </c>
+      <c r="C466" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以。根據條文規定，若主約因重大傷病診斷確定日而終止時，要保人於附約的有效期間內，仍可繼續繳交附約保險費，以延續附約效力。
+條文依據：  
+- [第十一條 契約的終止（二）]</t>
+        </is>
+      </c>
+      <c r="D466" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 契約的終止（二） | 第十二條 重大傷病保險金的給付 | 第三十條 不保事項 | 第五條 保險範圍 | payout_items | 附表一：全民健康保險重大傷病項目</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F466" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以。根據條文規定，若主約因重大傷病診斷確定日而終止時，要保人於附約的有效期間內，仍可繼續繳交附約保險費，以延續附約效力。
+條文依據：  
+- [第十一條 契約的終止（二）]</t>
+        </is>
+      </c>
+      <c r="G466" s="2" t="inlineStr"/>
+      <c r="H466" s="2" t="inlineStr"/>
+      <c r="I466" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.992974, "neutral": 0.006899, "contradiction": 0.000127, "factuality": 0.999873, "C_fact": 0.999873}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J466" s="5" t="n"/>
+      <c r="K466" s="5" t="n">
+        <v>0.999873</v>
+      </c>
+      <c r="L466" s="5" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M466" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:35:51</t>
+        </is>
+      </c>
+      <c r="N466" s="5" t="n">
+        <v>7.19</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B467" s="2" t="inlineStr">
+        <is>
+          <t>Q1：因為慢性精神病的保險給付僅有保額的20%，我可以先不申請給付，等之後發生其他重大傷病後，再申請重大傷病保險金嗎?Q2：但如果我不申請，保險公司不會知道我有罹患慢性精神病阿，所以我就可以領之後的重大傷病100%保額嗎?</t>
+        </is>
+      </c>
+      <c r="C467" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+Q1：依據條款規定，若被保險人同時或先後罹患兩項以上重大傷病，本公司僅給付一項重大傷病保險金。因此，即使您選擇不申請慢性精神病的保險金，之後罹患其他重大傷病時，保險公司仍僅會給付一項重大傷病保險金，並依條款規定計算給付金額。  
+Q2：保險公司是否給付重大傷病保險金，需依條款規定進行審核。若您已罹患慢性精神病但未申請給付，之後罹患其他重大傷病時，保險公司仍會依據條款進行審核，並可能要求提供相關病歷摘要或診斷書等文件。條款中未提及未申請慢性精神病保險金是否影響後續重大傷病保險金的給付比例，因此保險公司仍可能依慢性精神病的規定進行計算。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D467" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 重大傷病保險金的給付 | 第十三條 特定重大傷病保險金的給付 | 第三十條 不保事項 | 第二十八條 除外責任（一） | 第二十二條 重大傷病保險金、特定重大傷病保險金的申領 | 第二條 名詞定義 | 附表一：全民健康保險重大傷病項目 | payout_items</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F467" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+Q1：依據條款規定，若被保險人同時或先後罹患兩項以上重大傷病，本公司僅給付一項重大傷病保險金。因此，即使您選擇不申請慢性精神病的保險金，之後罹患其他重大傷病時，保險公司仍僅會給付一項重大傷病保險金，並依條款規定計算給付金額。  
+Q2：保險公司是否給付重大傷病保險金，需依條款規定進行審核。若您已罹患慢性精神病但未申請給付，之後罹患其他重大傷病時，保險公司仍會依據條款進行審核，並可能要求提供相關病歷摘要或診斷書等文件。條款中未提及未申請慢性精神病保險金是否影響後續重大傷病保險金的給付比例，因此保險公司仍可能依慢性精神病的規定進行計算。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G467" s="2" t="inlineStr"/>
+      <c r="H467" s="2" t="inlineStr"/>
+      <c r="I467" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.821737, "neutral": 0.176679, "contradiction": 0.001584, "factuality": 0.998416, "C_fact": 0.998416}, "C_conf": 0.9984}</t>
+        </is>
+      </c>
+      <c r="J467" s="5" t="n"/>
+      <c r="K467" s="5" t="n">
+        <v>0.998416</v>
+      </c>
+      <c r="L467" s="5" t="n">
+        <v>0.9984</v>
+      </c>
+      <c r="M467" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:36:18</t>
+        </is>
+      </c>
+      <c r="N467" s="5" t="n">
+        <v>27.17</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B468" s="2" t="inlineStr">
+        <is>
+          <t>慢性精神病失智症會賠嗎？賠多少？</t>
+        </is>
+      </c>
+      <c r="C468" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+慢性精神病失智症屬於「重大傷病」範圍，若被保險人於等待期間屆滿翌日或復效日起的契約有效期間內，經醫院醫師初次診斷確定罹患此疾病，並取得符合規定的重大傷病證明或診斷書，本公司將依以下方式給付「重大傷病保險金」：  
+1. 初次診斷確定罹患重大傷病時之保險單年度為第一保險單年度：「年繳應繳保險費總額」的一點零五倍。  
+2. 初次診斷確定罹患重大傷病時之保險單年度為第二保險單年度（含）以後：「保險金額的百分之二十」或「年繳應繳保險費總額的一點零五倍」，二者取其大者。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [附表一：全民健康保險重大傷病項目 - 六、慢性精神病]</t>
+        </is>
+      </c>
+      <c r="D468" s="2" t="inlineStr">
+        <is>
+          <t>附表一：全民健康保險重大傷病項目 | 第二十九條 除外責任（二） | 第十二條 重大傷病保險金的給付 | payout_items | 附表二：完全失能程度表</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F468" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+慢性精神病失智症屬於「重大傷病」範圍，若被保險人於等待期間屆滿翌日或復效日起的契約有效期間內，經醫院醫師初次診斷確定罹患此疾病，並取得符合規定的重大傷病證明或診斷書，本公司將依以下方式給付「重大傷病保險金」：  
+1. 初次診斷確定罹患重大傷病時之保險單年度為第一保險單年度：「年繳應繳保險費總額」的一點零五倍。  
+2. 初次診斷確定罹患重大傷病時之保險單年度為第二保險單年度（含）以後：「保險金額的百分之二十」或「年繳應繳保險費總額的一點零五倍」，二者取其大者。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [附表一：全民健康保險重大傷病項目 - 六、慢性精神病]</t>
+        </is>
+      </c>
+      <c r="G468" s="2" t="inlineStr"/>
+      <c r="H468" s="2" t="inlineStr"/>
+      <c r="I468" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.926772, "neutral": 0.0727, "contradiction": 0.000528, "factuality": 0.999472, "C_fact": 0.999472}, "C_conf": 0.9995}</t>
+        </is>
+      </c>
+      <c r="J468" s="5" t="n"/>
+      <c r="K468" s="5" t="n">
+        <v>0.999472</v>
+      </c>
+      <c r="L468" s="5" t="n">
+        <v>0.9995000000000001</v>
+      </c>
+      <c r="M468" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:36:37</t>
+        </is>
+      </c>
+      <c r="N468" s="5" t="n">
+        <v>18.22</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B469" s="2" t="inlineStr">
+        <is>
+          <t>投保新鍾心滿福後，於第二保單年度罹患子宮頸惡性腫瘤，且已給付重大傷病保險金。第五保單年度時又罹患慢性腎衰竭，這樣還可以申領重大傷病保險金的給付嗎?</t>
+        </is>
+      </c>
+      <c r="C469" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不可以再次申領重大傷病保險金。根據條款規定，被保險人同時或先後罹患二項以上「重大傷病」時，本公司僅給付一項「重大傷病保險金」。因此，即使於第五保單年度罹患慢性腎衰竭，因已於第二保單年度因子宮頸惡性腫瘤申領過重大傷病保險金，無法再次申領。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D469" s="2" t="inlineStr">
+        <is>
+          <t>附表一：全民健康保險重大傷病項目 | 第十二條 重大傷病保險金的給付 | 第五條 保險範圍 | 第二條 名詞定義 | payout_items | 第二十二條 重大傷病保險金、特定重大傷病保險金的申領</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F469" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不可以再次申領重大傷病保險金。根據條款規定，被保險人同時或先後罹患二項以上「重大傷病」時，本公司僅給付一項「重大傷病保險金」。因此，即使於第五保單年度罹患慢性腎衰竭，因已於第二保單年度因子宮頸惡性腫瘤申領過重大傷病保險金，無法再次申領。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G469" s="2" t="inlineStr"/>
+      <c r="H469" s="2" t="inlineStr"/>
+      <c r="I469" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.960141, "neutral": 0.039248, "contradiction": 0.000611, "factuality": 0.999389, "C_fact": 0.999389}, "C_conf": 0.9994}</t>
+        </is>
+      </c>
+      <c r="J469" s="5" t="n"/>
+      <c r="K469" s="5" t="n">
+        <v>0.999389</v>
+      </c>
+      <c r="L469" s="5" t="n">
+        <v>0.9994</v>
+      </c>
+      <c r="M469" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:36:53</t>
+        </is>
+      </c>
+      <c r="N469" s="5" t="n">
+        <v>15.66</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B470" s="2" t="inlineStr">
+        <is>
+          <t>12歲的被保險人可以有健康促進保險費折減嗎？</t>
+        </is>
+      </c>
+      <c r="C470" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+12歲的被保險人無法享有健康促進保險費折減，因為該條款明確規定只有實際年齡達十八歲（含）以上的被保險人才能符合折減資格。
+條文依據：  
+- [第十九條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="D470" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 健康促進保險費折減 | 第三十八條 投保年齡的計算及錯誤的處理 | 第三十四條 減額繳清保險 | 第二條 名詞定義 | 第十六條 所繳保險費加計利息的退還、身故保險金或喪葬費用保險金的給付 | 附表二：完全失能程度表</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F470" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+12歲的被保險人無法享有健康促進保險費折減，因為該條款明確規定只有實際年齡達十八歲（含）以上的被保險人才能符合折減資格。
+條文依據：  
+- [第十九條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="G470" s="2" t="inlineStr"/>
+      <c r="H470" s="2" t="inlineStr"/>
+      <c r="I470" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.970858, "neutral": 0.028517, "contradiction": 0.000625, "factuality": 0.999375, "C_fact": 0.999375}, "C_conf": 0.9994}</t>
+        </is>
+      </c>
+      <c r="J470" s="5" t="n"/>
+      <c r="K470" s="5" t="n">
+        <v>0.999375</v>
+      </c>
+      <c r="L470" s="5" t="n">
+        <v>0.9994</v>
+      </c>
+      <c r="M470" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:37:08</t>
+        </is>
+      </c>
+      <c r="N470" s="5" t="n">
+        <v>13.27</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>ZDN</t>
+        </is>
+      </c>
+      <c r="B471" s="2" t="inlineStr">
+        <is>
+          <t>被保險人於投保鍾心滿溢後的第10天就罹患慢性腎衰竭，請問可以申領重大傷病保險金嗎？</t>
+        </is>
+      </c>
+      <c r="C471" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不可以申領重大傷病保險金。根據條款，被保險人因意外傷害事故以外原因，於等待期間內罹患「重大傷病」者，本契約自始無效，本公司僅無息退還已繳保險費予要保人。慢性腎衰竭屬於重大傷病範圍，但因其非意外傷害事故所致，且發生於等待期間內（投保後第10天），因此不符合申領條件。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第三十條 不保事項]</t>
+        </is>
+      </c>
+      <c r="D471" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 重大傷病保險金的給付 | 附表一：全民健康保險重大傷病項目 | 第三十條 不保事項 | 第二條 名詞定義 | 第二十二條 重大傷病保險金、特定重大傷病保險金的申領</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F471" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不可以申領重大傷病保險金。根據條款，被保險人因意外傷害事故以外原因，於等待期間內罹患「重大傷病」者，本契約自始無效，本公司僅無息退還已繳保險費予要保人。慢性腎衰竭屬於重大傷病範圍，但因其非意外傷害事故所致，且發生於等待期間內（投保後第10天），因此不符合申領條件。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第三十條 不保事項]</t>
+        </is>
+      </c>
+      <c r="G471" s="2" t="inlineStr"/>
+      <c r="H471" s="2" t="inlineStr"/>
+      <c r="I471" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.001001, "neutral": 0.998648, "contradiction": 0.000352, "factuality": 0.999648, "C_fact": 0.999648}, "C_conf": 0.9996}</t>
+        </is>
+      </c>
+      <c r="J471" s="5" t="n"/>
+      <c r="K471" s="5" t="n">
+        <v>0.999648</v>
+      </c>
+      <c r="L471" s="5" t="n">
+        <v>0.9996</v>
+      </c>
+      <c r="M471" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:37:21</t>
+        </is>
+      </c>
+      <c r="N471" s="5" t="n">
+        <v>13.29</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>CFE</t>
+        </is>
+      </c>
+      <c r="B472" s="2" t="inlineStr">
+        <is>
+          <t>投保自由配重大傷病後，若在契約生效後80天罹患第一期乳癌，會拿到理賠金嗎?</t>
+        </is>
+      </c>
+      <c r="C472" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不會拿到理賠金。根據條款，屬於「需積極或長期治療之癌症」範圍的第一期乳癌，其等待期間為契約生效日起90天。被保險人若於等待期間內罹患「重大傷病」，本契約自始無效，本公司僅退還已繳保險費且不計利息。罹患乳癌的時間（80天）仍在等待期間內，因此不符合理賠條件。
+條文依據：  
+- [第二條 名詞定義]  
+- [第十一條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D472" s="2" t="inlineStr">
+        <is>
+          <t>附表一：全民健康保險重大傷病項目 | 第十一條 重大傷病保險金的給付 | 第十五條 不保事項 | 第二條 名詞定義 | 第五條 契約有效期間及保證續保 | 第十四條 除外責任</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F472" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不會拿到理賠金。根據條款，第一期乳癌屬於「需積極或長期治療之癌症」範圍，其等待期間為契約生效日起90天。由於罹患乳癌的時間（80天）仍在等待期間內，契約自始無效，本公司僅退還已繳保險費且不計利息。
+條文依據：  
+- [第二條 名詞定義]  
+- [第十一條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G472" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不會拿到理賠金。根據條款，屬於「需積極或長期治療之癌症」範圍的第一期乳癌，其等待期間為契約生效日起90天。被保險人若於等待期間內罹患「重大傷病」，本契約自始無效，本公司僅退還已繳保險費且不計利息。罹患乳癌的時間（80天）仍在等待期間內，因此不符合理賠條件。
+條文依據：  
+- [第二條 名詞定義]  
+- [第十一條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="H472" s="2" t="inlineStr"/>
+      <c r="I472" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.966357, "neutral": 0.017783, "contradiction": 0.01586, "factuality": 0.98414, "C_fact": 0.98414}, "C_conf": 0.9841}</t>
+        </is>
+      </c>
+      <c r="J472" s="5" t="n"/>
+      <c r="K472" s="5" t="n">
+        <v>0.98414</v>
+      </c>
+      <c r="L472" s="5" t="n">
+        <v>0.9841</v>
+      </c>
+      <c r="M472" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:37:41</t>
+        </is>
+      </c>
+      <c r="N472" s="5" t="n">
+        <v>20.07</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>CFE</t>
+        </is>
+      </c>
+      <c r="B473" s="2" t="inlineStr">
+        <is>
+          <t>要保人想要終止國泰人壽自由配CFE契約，能否退保費?如何申請？</t>
+        </is>
+      </c>
+      <c r="C473" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+要保人可以隨時終止契約，並申請退還未到期保險費。申請方式需以書面或其他約定方式通知保險公司。保險公司收到通知後，契約即開始生效終止。退還的未到期保險費將依短期費率計算，扣除已經過期間的保險費後無息退還給要保人。
+條文依據：  
+- [第九條 契約的終止（一)]</t>
+        </is>
+      </c>
+      <c r="D473" s="2" t="inlineStr">
+        <is>
+          <t>第九條 契約的終止（一） | 第十五條 不保事項 | 第七條 本契約效力的恢復 | 第六條 續保保險費的交付、寬限期間及契約效力的停止 | 第十條 契約的終止（二） | 第五條 契約有效期間及保證續保 | 第八條 告知義務與本契約的解除 | 第十七條 保險金額之減少 | 附表二：短期費率表</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F473" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+要保人可以隨時終止契約，並申請退還未到期保險費。申請方式需以書面或其他約定方式通知保險公司。保險公司收到通知後，契約即開始生效終止。退還的未到期保險費將依短期費率計算，扣除已經過期間的保險費後無息退還給要保人。
+條文依據：  
+- [第九條 契約的終止（一)]</t>
+        </is>
+      </c>
+      <c r="G473" s="2" t="inlineStr"/>
+      <c r="H473" s="2" t="inlineStr"/>
+      <c r="I473" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.997739, "neutral": 0.002173, "contradiction": 8.8e-05, "factuality": 0.999912, "C_fact": 0.999912}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J473" s="5" t="n"/>
+      <c r="K473" s="5" t="n">
+        <v>0.999912</v>
+      </c>
+      <c r="L473" s="5" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M473" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:37:51</t>
+        </is>
+      </c>
+      <c r="N473" s="5" t="n">
+        <v>8.98</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>CFE</t>
+        </is>
+      </c>
+      <c r="B474" s="2" t="inlineStr">
+        <is>
+          <t>投保國泰人壽自由配CFE，若在等待期間內罹患重大傷病，要如何給付?</t>
+        </is>
+      </c>
+      <c r="C474" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在等待期間內罹患重大傷病，且該重大傷病非因意外傷害事故所致，則本契約自始無效，本公司僅無息退還已繳保險費予要保人。若重大傷病係因意外傷害事故所致，則不受等待期間限制，可依約給付重大傷病保險金。
+條文依據：  
+- [第十一條 重大傷病保險金的給付]  
+- [第十五條 不保事項]</t>
+        </is>
+      </c>
+      <c r="D474" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 重大傷病保險金的給付 | 附表一：全民健康保險重大傷病項目 | 第十五條 不保事項 | 第十四條 除外責任 | payout_items | other_metadata</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F474" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在等待期間內罹患重大傷病，且該重大傷病非因意外傷害事故所致，則本契約自始無效，本公司僅無息退還已繳保險費予要保人。若重大傷病係因意外傷害事故所致，則不受等待期間限制，可依約給付重大傷病保險金。
+條文依據：  
+- [第十一條 重大傷病保險金的給付]  
+- [第十五條 不保事項]</t>
+        </is>
+      </c>
+      <c r="G474" s="2" t="inlineStr"/>
+      <c r="H474" s="2" t="inlineStr"/>
+      <c r="I474" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.945941, "neutral": 0.031935, "contradiction": 0.022124, "factuality": 0.977876, "C_fact": 0.977876}, "C_conf": 0.9779}</t>
+        </is>
+      </c>
+      <c r="J474" s="5" t="n"/>
+      <c r="K474" s="5" t="n">
+        <v>0.977876</v>
+      </c>
+      <c r="L474" s="5" t="n">
+        <v>0.9779</v>
+      </c>
+      <c r="M474" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:38:01</t>
+        </is>
+      </c>
+      <c r="N474" s="5" t="n">
+        <v>10.32</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>CFE</t>
+        </is>
+      </c>
+      <c r="B475" s="2" t="inlineStr">
+        <is>
+          <t>投保自由配一年定期初次罹患重大傷病健康保險後，於第三年罹患先天性肌肉萎縮症，可以申領重大傷病保險金嗎？</t>
+        </is>
+      </c>
+      <c r="C475" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不可以申領重大傷病保險金。根據條款，先天性肌肉萎縮症不屬於「重大傷病」範圍，因此不符合申領條件。
+條文依據：  
+- 附表一：全民健康保險重大傷病項目</t>
+        </is>
+      </c>
+      <c r="D475" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 重大傷病保險金的給付 | other_metadata | 附表一：全民健康保險重大傷病項目 | 第十三條 重大傷病保險金的申領 | 第十五條 不保事項</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F475" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不可以申領重大傷病保險金。根據條款，先天性肌肉萎縮症不屬於「重大傷病」範圍，因此不符合申領條件。
+條文依據：  
+- 附表一：全民健康保險重大傷病項目</t>
+        </is>
+      </c>
+      <c r="G475" s="2" t="inlineStr"/>
+      <c r="H475" s="2" t="inlineStr"/>
+      <c r="I475" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.012166, "neutral": 0.951748, "contradiction": 0.036087, "factuality": 0.963913, "C_fact": 0.963913}, "C_conf": 0.9639}</t>
+        </is>
+      </c>
+      <c r="J475" s="5" t="n"/>
+      <c r="K475" s="5" t="n">
+        <v>0.963913</v>
+      </c>
+      <c r="L475" s="5" t="n">
+        <v>0.9639</v>
+      </c>
+      <c r="M475" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:38:24</t>
+        </is>
+      </c>
+      <c r="N475" s="5" t="n">
+        <v>22.27</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>CFG</t>
+        </is>
+      </c>
+      <c r="B476" s="2" t="inlineStr">
+        <is>
+          <t>自由配重大疾病(甲型)保障的重大疾病有哪些疾病?</t>
+        </is>
+      </c>
+      <c r="C476" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+自由配重大疾病(甲型)保障的重大疾病包括以下疾病：  
+1. 腦中風後障礙(重度)  
+2. 癱瘓(重度)  
+3. 癌症(重度)  
+4. 急性心肌梗塞(重度)  
+5. 冠狀動脈繞道手術  
+6. 末期腎病變  
+7. 重大器官移植或造血幹細胞移植  
+條文依據：  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D476" s="2" t="inlineStr">
+        <is>
+          <t>國泰人壽自由配一年定期初次罹患重大疾病健康保險(甲型)年繳費率表 | payout_items | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F476" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+自由配重大疾病(甲型)保障的重大疾病包括以下疾病：  
+1. 腦中風後障礙(重度)  
+2. 癱瘓(重度)  
+3. 癌症(重度)  
+4. 急性心肌梗塞(重度)  
+5. 冠狀動脈繞道手術  
+6. 末期腎病變  
+7. 重大器官移植或造血幹細胞移植  
+條文依據：  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G476" s="2" t="inlineStr"/>
+      <c r="H476" s="2" t="inlineStr"/>
+      <c r="I476" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.435646, "neutral": 0.534641, "contradiction": 0.029713, "factuality": 0.970287, "C_fact": 0.970287}, "C_conf": 0.9703}</t>
+        </is>
+      </c>
+      <c r="J476" s="5" t="n"/>
+      <c r="K476" s="5" t="n">
+        <v>0.970287</v>
+      </c>
+      <c r="L476" s="5" t="n">
+        <v>0.9703000000000001</v>
+      </c>
+      <c r="M476" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:38:40</t>
+        </is>
+      </c>
+      <c r="N476" s="5" t="n">
+        <v>15.35</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B477" s="2" t="inlineStr">
+        <is>
+          <t>被保險人領了2次癌症(重度)追蹤照護金後身故，是否還有尚未給付的保險金供受益人領取?</t>
+        </is>
+      </c>
+      <c r="C477" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人已領取2次「癌症(重度)追蹤照護保險金」後身故，則無尚未給付的「癌症(重度)追蹤照護保險金」可供受益人申領，因該保險金的給付最長以五年為限，且需被保險人於各保險單週年日仍生存才能申領。被保險人身故後，該項保險金的給付責任即終止。
+條文依據：  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]</t>
+        </is>
+      </c>
+      <c r="D477" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用) | 第十三條 初次罹患癌症(重度)保險金的給付 | payout_items | 第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用) | 第二十三條 癌症保險金或罹癌基因檢測服務的申領 | 第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付 | 第十六條 癌症(重度)豁免保險費(第二保險單年度起適用) | 第二十二條 保險事故的通知與保險給付的申請時間</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F477" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人已領取2次「癌症(重度)追蹤照護保險金」後身故，則無尚未給付的「癌症(重度)追蹤照護保險金」可供受益人申領，因該保險金的給付最長以五年為限，且需被保險人於各保險單週年日仍生存才能申領。被保險人身故後，該項保險金的給付責任即終止。
+條文依據：  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]</t>
+        </is>
+      </c>
+      <c r="G477" s="2" t="inlineStr"/>
+      <c r="H477" s="2" t="inlineStr"/>
+      <c r="I477" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.962122, "neutral": 0.029592, "contradiction": 0.008286, "factuality": 0.991714, "C_fact": 0.991714}, "C_conf": 0.9917}</t>
+        </is>
+      </c>
+      <c r="J477" s="5" t="n"/>
+      <c r="K477" s="5" t="n">
+        <v>0.991714</v>
+      </c>
+      <c r="L477" s="5" t="n">
+        <v>0.9917</v>
+      </c>
+      <c r="M477" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:38:52</t>
+        </is>
+      </c>
+      <c r="N477" s="5" t="n">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B478" s="2" t="inlineStr">
+        <is>
+          <t>保險金額2萬元，「罹癌基因檢測服務」費用8萬元，還會給付多少「癌症(重度)追蹤照護保險金」？</t>
+        </is>
+      </c>
+      <c r="C478" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人選擇申領「罹癌基因檢測服務」，因服務費用（8萬元）高於「罹癌基因檢測服務額度」（1,000元），依條款規定，被保險人僅能申領「癌症(重度)追蹤照護保險金」。該保險金額為保險金額的12倍，即2萬元 × 12 = 24萬元。  
+條文依據：  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]</t>
+        </is>
+      </c>
+      <c r="D478" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用) | 附件一：罹癌基因檢測服務之項目、服務費用及補償金額表 | 第二十三條 癌症保險金或罹癌基因檢測服務的申領 | 第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用) | payout_items | 第十三條 初次罹患癌症(重度)保險金的給付 | other_metadata | 第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F478" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人選擇申領「罹癌基因檢測服務」，因服務費用（8萬元）高於「罹癌基因檢測服務額度」（1,000元），依條款規定，被保險人僅能申領「癌症(重度)追蹤照護保險金」。該保險金額為保險金額的12倍，即2萬元 × 12 = 24萬元。  
+條文依據：  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]</t>
+        </is>
+      </c>
+      <c r="G478" s="2" t="inlineStr"/>
+      <c r="H478" s="2" t="inlineStr"/>
+      <c r="I478" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.6317, "neutral": 0.190481, "contradiction": 0.177819, "factuality": 0.822181, "C_fact": 0.822181}, "C_conf": 0.8222}</t>
+        </is>
+      </c>
+      <c r="J478" s="5" t="n"/>
+      <c r="K478" s="5" t="n">
+        <v>0.8221810000000001</v>
+      </c>
+      <c r="L478" s="5" t="n">
+        <v>0.8222</v>
+      </c>
+      <c r="M478" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:39:02</t>
+        </is>
+      </c>
+      <c r="N478" s="5" t="n">
+        <v>10.28</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B479" s="2" t="inlineStr">
+        <is>
+          <t>投保後1個月罹患重度癌症，是否已過了等待期間？會給付哪些保險金？契約還會持續有效嗎？</t>
+        </is>
+      </c>
+      <c r="C479" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+投保後1個月罹患重度癌症，尚未超過等待期間（九十日），因此不符合保險金給付條件。根據第十條，若於契約生效日起九十日內罹患癌症，契約效力即行終止，本公司僅退還已收受之保險費且無息。契約不會持續有效。
+條文依據：  
+- [第十條 契約的終止（二)]  
+- （本保險「癌症」等待期間為九十日，詳請參閱契約條款）</t>
+        </is>
+      </c>
+      <c r="D479" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 癌症(重度)豁免保險費(第二保險單年度起適用) | 第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用) | 第十三條 初次罹患癌症(重度)保險金的給付 | other_metadata | 第十條 契約的終止（二） | 第十一條 契約的終止（三） | 第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付 | 第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用)</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F479" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+投保後1個月罹患重度癌症，尚未超過等待期間（九十日），因此不符合保險金給付條件。根據第十條，若於契約生效日起九十日內罹患癌症，契約效力即行終止，本公司僅退還已收受之保險費且無息。契約不會持續有效。
+條文依據：  
+- [第十條 契約的終止（二)]  
+- （本保險「癌症」等待期間為九十日，詳請參閱契約條款）</t>
+        </is>
+      </c>
+      <c r="G479" s="2" t="inlineStr"/>
+      <c r="H479" s="2" t="inlineStr"/>
+      <c r="I479" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.991447, "neutral": 0.00207, "contradiction": 0.006483, "factuality": 0.993517, "C_fact": 0.993517}, "C_conf": 0.9935}</t>
+        </is>
+      </c>
+      <c r="J479" s="5" t="n"/>
+      <c r="K479" s="5" t="n">
+        <v>0.993517</v>
+      </c>
+      <c r="L479" s="5" t="n">
+        <v>0.9935</v>
+      </c>
+      <c r="M479" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:39:12</t>
+        </is>
+      </c>
+      <c r="N479" s="5" t="n">
+        <v>8.51</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B480" s="2" t="inlineStr">
+        <is>
+          <t>投保後10個月罹患重度癌症（第一保單年度），是否已過了等待期間，會給付哪些保險金？契約還會終止嗎？</t>
+        </is>
+      </c>
+      <c r="C480" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+投保後10個月罹患重度癌症，已超過等待期間（90日），符合「初次診斷確定罹患癌症（重度）」的條件，保險公司將給付「初次罹患癌症（重度）保險金」，金額為「年繳應繳保險費」的一點零六倍。契約效力將因符合「初次診斷確定罹患癌症（重度）」的診斷確定日而終止。
+條文依據：  
+- [第十三條 初次罹患癌症(重度)保險金的給付]  
+- [第十一條 契約的終止（三)]</t>
+        </is>
+      </c>
+      <c r="D480" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 初次罹患癌症(重度)保險金的給付 | 第十六條 癌症(重度)豁免保險費(第二保險單年度起適用) | 第十條 契約的終止（二） | 第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用) | 第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付 | 第十一條 契約的終止（三） | payout_items | 第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用)</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F480" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+投保後10個月罹患重度癌症，已超過等待期間（90日），符合「初次診斷確定罹患癌症（重度）」的條件，保險公司將給付「初次罹患癌症（重度）保險金」，金額為「年繳應繳保險費」的一點零六倍。契約效力將因符合「初次診斷確定罹患癌症（重度）」的診斷確定日而終止。
+條文依據：  
+- [第十三條 初次罹患癌症(重度)保險金的給付]  
+- [第十一條 契約的終止（三)]</t>
+        </is>
+      </c>
+      <c r="G480" s="2" t="inlineStr"/>
+      <c r="H480" s="2" t="inlineStr"/>
+      <c r="I480" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.992303, "neutral": 0.006462, "contradiction": 0.001235, "factuality": 0.998765, "C_fact": 0.998765}, "C_conf": 0.9988}</t>
+        </is>
+      </c>
+      <c r="J480" s="5" t="n"/>
+      <c r="K480" s="5" t="n">
+        <v>0.998765</v>
+      </c>
+      <c r="L480" s="5" t="n">
+        <v>0.9988</v>
+      </c>
+      <c r="M480" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:39:20</t>
+        </is>
+      </c>
+      <c r="N480" s="5" t="n">
+        <v>8.35</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B481" s="2" t="inlineStr">
+        <is>
+          <t>投保醫心康愛，罹患肺癌一期(重度癌症)，可領什麼保險金？</t>
+        </is>
+      </c>
+      <c r="C481" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人罹患肺癌一期且符合「初次診斷確定罹患癌症(重度)」，可申領以下保險金：  
+1. 初次罹患癌症(重度)保險金：診斷確定日若在第二保險單年度(含)以後，可申領「保險金額」的十二倍。  
+2. 癌症(重度)標靶藥物治療輔助保險金：若於第二保險單年度(含)以後，並接受標靶治療，可申領「保險金額」的十二倍。  
+3. 癌症(重度)追蹤照護保險金：若於第二保險單年度(含)以後，且自診斷確定日的次一保險單週年日起仍生存，可每年申領「保險金額」的十二倍，最長五年。  
+4. 癌症(重度)豁免保險費：若於第二保險單年度(含)以後，診斷確定日起豁免續期保險費。
+條文依據：  
+- [第十三條 初次罹患癌症(重度)保險金的給付]  
+- [第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用)]  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]  
+- [第十六條 癌症(重度)豁免保險費(第二保險單年度起適用)]</t>
+        </is>
+      </c>
+      <c r="D481" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 初次罹患癌症(重度)保險金的給付 | 第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付 | payout_items | 第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用) | 第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用) | 第十六條 癌症(重度)豁免保險費(第二保險單年度起適用) | 第二十三條 癌症保險金或罹癌基因檢測服務的申領 | 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F481" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人罹患肺癌一期且符合「初次診斷確定罹患癌症(重度)」，可申領以下保險金：  
+1. 初次罹患癌症(重度)保險金：診斷確定日若在第二保險單年度(含)以後，可申領「保險金額」的十二倍。  
+2. 癌症(重度)標靶藥物治療輔助保險金：若於第二保險單年度(含)以後，並接受標靶治療，可申領「保險金額」的十二倍。  
+3. 癌症(重度)追蹤照護保險金：若於第二保險單年度(含)以後，且自診斷確定日的次一保險單週年日起仍生存，可每年申領「保險金額」的十二倍，最長五年。  
+4. 癌症(重度)豁免保險費：若於第二保險單年度(含)以後，診斷確定日起豁免續期保險費。
+條文依據：  
+- [第十三條 初次罹患癌症(重度)保險金的給付]  
+- [第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用)]  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]  
+- [第十六條 癌症(重度)豁免保險費(第二保險單年度起適用)]</t>
+        </is>
+      </c>
+      <c r="G481" s="2" t="inlineStr"/>
+      <c r="H481" s="2" t="inlineStr"/>
+      <c r="I481" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.154867, "neutral": 0.838233, "contradiction": 0.006899, "factuality": 0.993101, "C_fact": 0.993101}, "C_conf": 0.9931}</t>
+        </is>
+      </c>
+      <c r="J481" s="5" t="n"/>
+      <c r="K481" s="5" t="n">
+        <v>0.993101</v>
+      </c>
+      <c r="L481" s="5" t="n">
+        <v>0.9931</v>
+      </c>
+      <c r="M481" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:39:33</t>
+        </is>
+      </c>
+      <c r="N481" s="5" t="n">
+        <v>12.21</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>PX5</t>
+        </is>
+      </c>
+      <c r="B482" s="2" t="inlineStr">
+        <is>
+          <t>若被保險人身故有何給付?未到期保險費如何處理？尚未給付或未完全給付的保險金如何處理？</t>
+        </is>
+      </c>
+      <c r="C482" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 被保險人身故時，若有尚未給付或未完全給付的保險金，則以被保險人的法定繼承人為受益人，並依民法繼承編的相關規定分配。  
+2. 附約因被保險人身故而終止時，如有未到期保險費，本公司應從當期已繳保險費扣除按日數比例計算已經過期間之保險費後，將其未到期保險費無息退還要保人。
+條文依據：  
+- [第二十條 受益人]  
+- [第十條 附約的終止（二)]</t>
+        </is>
+      </c>
+      <c r="D482" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 保險事故的通知與保險金的申請時間 | 第二十條 受益人 | 第十二條 重大疾病保險金的給付 | 第十七條 欠繳保險費的扣除 | 第十一條 輕度重大疾病保險金的給付 | 第十條 附約的終止（二） | 第六條 第二期以後保險費及續保保險費的交付、寬限期間及附約效力的停止 | 第九條 附約的終止（一）</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F482" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 被保險人身故時，若有尚未給付或未完全給付的保險金，則以被保險人的法定繼承人為受益人，並依民法繼承編的相關規定分配。  
+2. 附約因被保險人身故而終止時，如有未到期保險費，本公司應從當期已繳保險費扣除按日數比例計算已經過期間之保險費後，將其未到期保險費無息退還要保人。
+條文依據：  
+- [第二十條 受益人]  
+- [第十條 附約的終止（二)]</t>
+        </is>
+      </c>
+      <c r="G482" s="2" t="inlineStr"/>
+      <c r="H482" s="2" t="inlineStr"/>
+      <c r="I482" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.990301, "neutral": 0.009062, "contradiction": 0.000637, "factuality": 0.999363, "C_fact": 0.999363}, "C_conf": 0.9994}</t>
+        </is>
+      </c>
+      <c r="J482" s="5" t="n"/>
+      <c r="K482" s="5" t="n">
+        <v>0.999363</v>
+      </c>
+      <c r="L482" s="5" t="n">
+        <v>0.9994</v>
+      </c>
+      <c r="M482" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:39:44</t>
+        </is>
+      </c>
+      <c r="N482" s="5" t="n">
+        <v>11.08</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>PX5</t>
+        </is>
+      </c>
+      <c r="B483" s="2" t="inlineStr">
+        <is>
+          <t>投保鍾溢祝福後，請問在第二年經醫院醫師初次診斷罹患「輕度重大疾病」中的癌症(輕度)者，可以領到輕度重大疾病保險金嗎?可以領到保險金額的百分之多少?</t>
+        </is>
+      </c>
+      <c r="C483" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以領到輕度重大疾病保險金，保險金額的百分之二十。根據條款，被保險人於續保年度內初次診斷罹患「輕度重大疾病」中的癌症(輕度)，符合給付條件，且等待期間屆滿後有效。
+條文依據：  
+- [第十一條 輕度重大疾病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D483" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 輕度重大疾病保險金的給付 | 第十二條 重大疾病保險金的給付 | other_metadata | payout_items | 國泰人壽鍾溢祝福重大疾病健康保險附約(乙型) (外溢型)年繳費率表 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F483" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以領到輕度重大疾病保險金，保險金額的百分之二十。根據條款，被保險人於續保年度內初次診斷罹患「輕度重大疾病」中的癌症(輕度)，符合給付條件，且等待期間屆滿後有效。
+條文依據：  
+- [第十一條 輕度重大疾病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G483" s="2" t="inlineStr"/>
+      <c r="H483" s="2" t="inlineStr"/>
+      <c r="I483" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.995746, "neutral": 0.003724, "contradiction": 0.00053, "factuality": 0.99947, "C_fact": 0.99947}, "C_conf": 0.9995}</t>
+        </is>
+      </c>
+      <c r="J483" s="5" t="n"/>
+      <c r="K483" s="5" t="n">
+        <v>0.99947</v>
+      </c>
+      <c r="L483" s="5" t="n">
+        <v>0.9995000000000001</v>
+      </c>
+      <c r="M483" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:39:54</t>
+        </is>
+      </c>
+      <c r="N483" s="5" t="n">
+        <v>9.42</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>PX5</t>
+        </is>
+      </c>
+      <c r="B484" s="2" t="inlineStr">
+        <is>
+          <t>請問如果在投保後的第三年經醫院醫師初次診斷罹患「重大疾病」者，可以領到重大疾病保險金嗎?可以領到保險金額的百分之多少?那後續又在第四年經醫院醫師初次診斷罹患「輕度重大疾病」者，可以領到輕度重大疾病保險金嗎?可以領到保險金額的百分之多少?</t>
+        </is>
+      </c>
+      <c r="C484" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+在投保後的第三年初次診斷罹患「重大疾病」者，可以領到重大疾病保險金，保險金額為保險金額的1.3倍。後續在第四年初次診斷罹患「輕度重大疾病」者，因已申領過重大疾病保險金，根據條款規定，輕度重大疾病保險金不可再申領。
+條文依據：  
+- [第十二條 重大疾病保險金的給付]  
+- [第十一條 輕度重大疾病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D484" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 輕度重大疾病保險金的給付 | 第十二條 重大疾病保險金的給付 | 第十六條 除外責任 | payout_items | 第二條 名詞定義 | 第四條 保險範圍 | other_metadata | 國泰人壽鍾溢祝福重大疾病健康保險附約(乙型) (外溢型)年繳費率表</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F484" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+在投保後的第三年初次診斷罹患「重大疾病」者，可以領到重大疾病保險金，保險金額為保險金額的1.3倍。後續在第四年初次診斷罹患「輕度重大疾病」者，因已申領過重大疾病保險金，根據條款規定，輕度重大疾病保險金不可再申領。
+條文依據：  
+- [第十二條 重大疾病保險金的給付]  
+- [第十一條 輕度重大疾病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G484" s="2" t="inlineStr"/>
+      <c r="H484" s="2" t="inlineStr"/>
+      <c r="I484" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.90624, "neutral": 0.05375, "contradiction": 0.04001, "factuality": 0.95999, "C_fact": 0.95999}, "C_conf": 0.96}</t>
+        </is>
+      </c>
+      <c r="J484" s="5" t="n"/>
+      <c r="K484" s="5" t="n">
+        <v>0.95999</v>
+      </c>
+      <c r="L484" s="5" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="M484" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:40:00</t>
+        </is>
+      </c>
+      <c r="N484" s="5" t="n">
+        <v>5.87</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>PX5</t>
+        </is>
+      </c>
+      <c r="B485" s="2" t="inlineStr">
+        <is>
+          <t>請問如果在投保後的第三年經醫院醫師初次診斷罹患「輕度重大疾病」者，可以領到重大疾病保險金嗎?可以領到保險金額的百分之多少?那後續又在第四年經醫院醫師初次診斷罹患「重大疾病」者，可以領到輕度重大疾病保險金嗎?可以領到保險金額的百分之多少?</t>
+        </is>
+      </c>
+      <c r="C485" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+在投保後的第三年初次診斷罹患「輕度重大疾病」者，可以領到「輕度重大疾病保險金」，保險金額的百分之二十。  
+在第四年初次診斷罹患「重大疾病」者，因已申領過「輕度重大疾病保險金」，依第十二條規定，重大疾病保險金需扣除已申領的輕度重大疾病保險金，最終可領到保險金額的一點三倍減去百分之二十。  
+條文依據：  
+- [第十一條 輕度重大疾病保險金的給付]  
+- [第十二條 重大疾病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D485" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 輕度重大疾病保險金的給付 | 第十二條 重大疾病保險金的給付 | 第十六條 除外責任 | payout_items | 第二條 名詞定義 | 第四條 保險範圍 | other_metadata | 第十五條 各項保險金的申領</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F485" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+在投保後的第三年初次診斷罹患「輕度重大疾病」者，可以領到「輕度重大疾病保險金」，保險金額的百分之二十。  
+在第四年初次診斷罹患「重大疾病」者，因已申領過「輕度重大疾病保險金」，依第十二條規定，重大疾病保險金需扣除已申領的輕度重大疾病保險金，最終可領到保險金額的一點三倍減去百分之二十。  
+條文依據：  
+- [第十一條 輕度重大疾病保險金的給付]  
+- [第十二條 重大疾病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G485" s="2" t="inlineStr"/>
+      <c r="H485" s="2" t="inlineStr"/>
+      <c r="I485" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.865719, "neutral": 0.05419, "contradiction": 0.080091, "factuality": 0.919909, "C_fact": 0.919909}, "C_conf": 0.9199}</t>
+        </is>
+      </c>
+      <c r="J485" s="5" t="n"/>
+      <c r="K485" s="5" t="n">
+        <v>0.919909</v>
+      </c>
+      <c r="L485" s="5" t="n">
+        <v>0.9199000000000001</v>
+      </c>
+      <c r="M485" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:40:11</t>
+        </is>
+      </c>
+      <c r="N485" s="5" t="n">
+        <v>10.85</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>PX5</t>
+        </is>
+      </c>
+      <c r="B486" s="2" t="inlineStr">
+        <is>
+          <t>請問主約效力終止(因身故以外情形)，PX5還能持續有效嗎？</t>
+        </is>
+      </c>
+      <c r="C486" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+主約效力因身故以外情形終止時，PX5附約效力可持續至附約當期已繳保險費期滿即行終止，並不再延續。  
+條文依據：  
+- [第十條 附約的終止（二）]</t>
+        </is>
+      </c>
+      <c r="D486" s="2" t="inlineStr">
+        <is>
+          <t>第十條 附約的終止（二） | 第七條 保險費的墊繳、附約的停效及復效 | 第五條 附約的保險期間及保證續保 | 第十三條 健康促進保險費折減 | 第九條 附約的終止（一）</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F486" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+主約效力因身故以外情形終止時，PX5附約效力可持續至附約當期已繳保險費期滿即行終止，並不再延續。  
+條文依據：  
+- [第十條 附約的終止（二）]</t>
+        </is>
+      </c>
+      <c r="G486" s="2" t="inlineStr"/>
+      <c r="H486" s="2" t="inlineStr"/>
+      <c r="I486" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.792572, "neutral": 0.011362, "contradiction": 0.196066, "factuality": 0.803934, "C_fact": 0.803934}, "C_conf": 0.8039}</t>
+        </is>
+      </c>
+      <c r="J486" s="5" t="n"/>
+      <c r="K486" s="5" t="n">
+        <v>0.803934</v>
+      </c>
+      <c r="L486" s="5" t="n">
+        <v>0.8038999999999999</v>
+      </c>
+      <c r="M486" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:40:19</t>
+        </is>
+      </c>
+      <c r="N486" s="5" t="n">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B487" s="2" t="inlineStr">
+        <is>
+          <t>請問如果於「無理賠紀錄期間」屆滿日以內罹患特定傷病，會給付多少錢?這筆錢會給付給誰?</t>
+        </is>
+      </c>
+      <c r="C487" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人於「無理賠紀錄期間」屆滿日以內罹患特定傷病，保險公司將給付「保險金額」加上「年繳應繳保險費總額」乘以1.02的金額作為「特定傷病保險金」。此筆保險金的受益人為被保險人本人，且不得指定或變更。
+條文依據：  
+- [第十一條 特定傷病保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="D487" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第十二條 無理賠關懷保險金的給付 | 第十一條 特定傷病保險金的給付 | payout_items | 第二十七條 受益人的指定及變更</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F487" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人於「無理賠紀錄期間」屆滿日以內罹患特定傷病，保險公司將給付「保險金額」加上「年繳應繳保險費總額」乘以1.02的金額作為「特定傷病保險金」。此筆保險金的受益人為被保險人本人，且不得指定或變更。
+條文依據：  
+- [第十一條 特定傷病保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="G487" s="2" t="inlineStr"/>
+      <c r="H487" s="2" t="inlineStr"/>
+      <c r="I487" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.99725, "neutral": 0.002445, "contradiction": 0.000304, "factuality": 0.999696, "C_fact": 0.999696}, "C_conf": 0.9997}</t>
+        </is>
+      </c>
+      <c r="J487" s="5" t="n"/>
+      <c r="K487" s="5" t="n">
+        <v>0.999696</v>
+      </c>
+      <c r="L487" s="5" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="M487" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:40:27</t>
+        </is>
+      </c>
+      <c r="N487" s="5" t="n">
+        <v>7.36</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B488" s="2" t="inlineStr">
+        <is>
+          <t>請問如果要保人與被保險人為同一人，被保險人於「無理賠紀錄期間」屆滿日以內身故，會給付多少錢?這筆錢會給付給誰?</t>
+        </is>
+      </c>
+      <c r="C488" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若要保人與被保險人為同一人，被保險人於「無理賠紀錄期間」屆滿日以內身故，符合「無理賠關懷保險金」的給付條件，保險公司將按「年繳應繳保險費總額」乘以1.02計算給付金額。此筆保險金的受益人為要保人本人，因要保人與被保險人為同一人，則該筆保險金直接給付予被保險人本人。
+條文依據：  
+- [第十二條 無理賠關懷保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="D488" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第十二條 無理賠關懷保險金的給付 | 第十一條 特定傷病保險金的給付 | payout_items | 第十九條 失蹤處理 | 第二十一條 無理賠關懷保險金的申領 | 第二十七條 受益人的指定及變更 | 第十七條 除外責任（二）</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F488" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若要保人與被保險人為同一人，被保險人於「無理賠紀錄期間」屆滿日以內身故，符合「無理賠關懷保險金」的給付條件，保險公司將按「年繳應繳保險費總額」乘以1.02計算給付金額。此筆保險金的受益人為要保人本人，因要保人與被保險人為同一人，則該筆保險金直接給付予被保險人本人。
+條文依據：  
+- [第十二條 無理賠關懷保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="G488" s="2" t="inlineStr"/>
+      <c r="H488" s="2" t="inlineStr"/>
+      <c r="I488" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.980332, "neutral": 0.017017, "contradiction": 0.002651, "factuality": 0.997349, "C_fact": 0.997349}, "C_conf": 0.9973}</t>
+        </is>
+      </c>
+      <c r="J488" s="5" t="n"/>
+      <c r="K488" s="5" t="n">
+        <v>0.997349</v>
+      </c>
+      <c r="L488" s="5" t="n">
+        <v>0.9973</v>
+      </c>
+      <c r="M488" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:40:38</t>
+        </is>
+      </c>
+      <c r="N488" s="5" t="n">
+        <v>10.61</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B489" s="2" t="inlineStr">
+        <is>
+          <t>請問如果要保人與被保險人為不同人，被保險人於「無理賠紀錄期間」屆滿日以內生存，且被保險人未罹患特定傷病，會給付多少錢?這筆錢會給付給誰?</t>
+        </is>
+      </c>
+      <c r="C489" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人於「無理賠紀錄期間」屆滿日以內生存，且未罹患特定傷病，本公司將給付「無理賠關懷保險金」，金額為「年繳應繳保險費總額」乘以1.02。此筆保險金的受益人為要保人本人。
+條文依據：  
+- [第十二條 無理賠關懷保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="D489" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第十二條 無理賠關懷保險金的給付 | 第十一條 特定傷病保險金的給付 | payout_items | 第二十七條 受益人的指定及變更 | 第十九條 失蹤處理 | 第二十一條 無理賠關懷保險金的申領 | 第十七條 除外責任（二）</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F489" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人於「無理賠紀錄期間」屆滿日以內生存，且未罹患特定傷病，本公司將給付「無理賠關懷保險金」，金額為「年繳應繳保險費總額」乘以1.02。此筆保險金的受益人為要保人本人。
+條文依據：  
+- [第十二條 無理賠關懷保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="G489" s="2" t="inlineStr"/>
+      <c r="H489" s="2" t="inlineStr"/>
+      <c r="I489" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.996642, "neutral": 0.003076, "contradiction": 0.000282, "factuality": 0.999718, "C_fact": 0.999718}, "C_conf": 0.9997}</t>
+        </is>
+      </c>
+      <c r="J489" s="5" t="n"/>
+      <c r="K489" s="5" t="n">
+        <v>0.999718</v>
+      </c>
+      <c r="L489" s="5" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="M489" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:40:42</t>
+        </is>
+      </c>
+      <c r="N489" s="5" t="n">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B490" s="2" t="inlineStr">
+        <is>
+          <t>保戶如果身故，會給保險金嗎?身故保險金、特定傷病保險金及無理賠關懷保險金？</t>
+        </is>
+      </c>
+      <c r="C490" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保戶身故時，是否給付保險金需視具體情況而定：  
+1. **身故保險金**：條文中未提及有專門的「身故保險金」給付，找不到相關內容。  
+2. **特定傷病保險金**：若被保險人於契約有效期間內初次診斷罹患特定傷病，並符合第十一條規定，則可給付特定傷病保險金。但若因第十六條所列除外責任原因（如故意行為、自殺、犯罪行為等）導致特定傷病，則不予給付。  
+3. **無理賠關懷保險金**：若被保險人在「無理賠紀錄期間」內未申領特定傷病保險金，且於該期間內身故或屆滿時仍生存，則依第十二條規定給付無理賠關懷保險金。但若因第十七條所列除外責任原因（如要保人故意致死、被保險人故意自殺等）導致身故，則不予給付。
+條文依據：  
+- [第十一條 特定傷病保險金的給付]  
+- [第十二條 無理賠關懷保險金的給付]  
+- [第十六條 除外責任（一)]  
+- [第十七條 除外責任（二)]</t>
+        </is>
+      </c>
+      <c r="D490" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第十七條 除外責任（二） | 第二十七條 受益人的指定及變更 | 第十二條 無理賠關懷保險金的給付 | payout_items | 第十九條 失蹤處理 | 第十一條 特定傷病保險金的給付 | 第十六條 除外責任（一）</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F490" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保戶身故時，是否給付保險金需視具體情況而定：  
+1. **身故保險金**：條文中未提及有專門的「身故保險金」給付，找不到相關內容。  
+2. **特定傷病保險金**：若被保險人於契約有效期間內初次診斷罹患特定傷病，並符合第十一條規定，則可給付特定傷病保險金。但若因第十六條所列除外責任原因（如故意行為、自殺、犯罪行為等）導致特定傷病，則不予給付。  
+3. **無理賠關懷保險金**：若被保險人在「無理賠紀錄期間」內未申領特定傷病保險金，且於該期間內身故或屆滿時仍生存，則依第十二條規定給付無理賠關懷保險金。但若因第十七條所列除外責任原因（如要保人故意致死、被保險人故意自殺等）導致身故，則不予給付。
+條文依據：  
+- [第十一條 特定傷病保險金的給付]  
+- [第十二條 無理賠關懷保險金的給付]  
+- [第十六條 除外責任（一)]  
+- [第十七條 除外責任（二)]</t>
+        </is>
+      </c>
+      <c r="G490" s="2" t="inlineStr"/>
+      <c r="H490" s="2" t="inlineStr"/>
+      <c r="I490" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.939709, "neutral": 0.051942, "contradiction": 0.008349, "factuality": 0.991651, "C_fact": 0.991651}, "C_conf": 0.9917}</t>
+        </is>
+      </c>
+      <c r="J490" s="5" t="n"/>
+      <c r="K490" s="5" t="n">
+        <v>0.9916509999999999</v>
+      </c>
+      <c r="L490" s="5" t="n">
+        <v>0.9917</v>
+      </c>
+      <c r="M490" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:40:49</t>
+        </is>
+      </c>
+      <c r="N490" s="5" t="n">
+        <v>4.71</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B491" s="2" t="inlineStr">
+        <is>
+          <t>保戶如果身故，身故申領的保險金會給誰?</t>
+        </is>
+      </c>
+      <c r="C491" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保戶身故後，身故保險金的受益人為保險契約中指定的受益人。如果受益人未指定或受益人喪失受益權，則保險金作為被保險人的遺產，由法定繼承人依民法繼承編相關規定分配。此外，若特定傷病保險金尚未給付或未完全給付，則以被保險人的法定繼承人為受益人。
+條文依據：  
+- [第二十三條 受益人受益權之喪失]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="D491" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第二十三條 受益人受益權之喪失 | 第二十七條 受益人的指定及變更 | 第二十八條 本契約受益人死亡或失蹤的處理 | 第二十二條 分期定期保險金給付申領文件、給付期限及未依限給付之效果</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F491" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保戶身故後，身故保險金的受益人為保險契約中指定的受益人。如果受益人未指定或受益人喪失受益權，則保險金作為被保險人的遺產，由法定繼承人依民法繼承編相關規定分配。此外，若特定傷病保險金尚未給付或未完全給付，則以被保險人的法定繼承人為受益人。
+條文依據：  
+- [第二十三條 受益人受益權之喪失]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="G491" s="2" t="inlineStr"/>
+      <c r="H491" s="2" t="inlineStr"/>
+      <c r="I491" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.996946, "neutral": 0.002809, "contradiction": 0.000246, "factuality": 0.999754, "C_fact": 0.999754}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J491" s="5" t="n"/>
+      <c r="K491" s="5" t="n">
+        <v>0.999754</v>
+      </c>
+      <c r="L491" s="5" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M491" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:40:58</t>
+        </is>
+      </c>
+      <c r="N491" s="5" t="n">
+        <v>9.07</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B492" s="2" t="inlineStr">
+        <is>
+          <t>如果保戶投保繳費年期20年的滿溢寶，然後在第20保單年度身故的話，可以領到多少錢?無理賠關懷保險金?受益人為要保人嗎？</t>
+        </is>
+      </c>
+      <c r="C492" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若保戶在第20保單年度身故，是否可領取無理賠關懷保險金需符合以下條件：  
+1. 被保險人在「無理賠紀錄期間」內未曾申領「特定傷病保險金」。  
+2. 被保險人在「無理賠紀錄期間」內身故或於「無理賠紀錄期間」屆滿時仍生存。  
+若符合上述條件，本公司將按「年繳應繳保險費總額」乘以1.02給付「無理賠關懷保險金」。受益人為要保人本人，且本公司不受理其指定及變更。  
+條文依據：  
+- [第十二條 無理賠關懷保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="D492" s="2" t="inlineStr">
+        <is>
+          <t>第二十七條 受益人的指定及變更 | 第十九條 失蹤處理 | 第十二條 無理賠關懷保險金的給付 | 第十七條 除外責任（二） | other_metadata | 第二十一條 無理賠關懷保險金的申領 | 第二十八條 本契約受益人死亡或失蹤的處理 | 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F492" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若保戶在第20保單年度身故，是否可領取無理賠關懷保險金需符合以下條件：  
+1. 被保險人在「無理賠紀錄期間」內未曾申領「特定傷病保險金」。  
+2. 被保險人在「無理賠紀錄期間」內身故或於「無理賠紀錄期間」屆滿時仍生存。  
+若符合上述條件，本公司將按「年繳應繳保險費總額」乘以1.02給付「無理賠關懷保險金」。受益人為要保人本人，且本公司不受理其指定及變更。  
+條文依據：  
+- [第十二條 無理賠關懷保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="G492" s="2" t="inlineStr"/>
+      <c r="H492" s="2" t="inlineStr"/>
+      <c r="I492" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.754269, "neutral": 0.244521, "contradiction": 0.00121, "factuality": 0.99879, "C_fact": 0.99879}, "C_conf": 0.9988}</t>
+        </is>
+      </c>
+      <c r="J492" s="5" t="n"/>
+      <c r="K492" s="5" t="n">
+        <v>0.99879</v>
+      </c>
+      <c r="L492" s="5" t="n">
+        <v>0.9988</v>
+      </c>
+      <c r="M492" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:41:06</t>
+        </is>
+      </c>
+      <c r="N492" s="5" t="n">
+        <v>7.79</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B493" s="2" t="inlineStr">
+        <is>
+          <t>被保險人為60歲女性，投保繳費期間20年期之滿溢寶特定傷病定期健康保險（定期給付型）（外溢型）100萬元，年繳應繳保險費為83,500元，年繳實繳保險費為78,490元。若被保險人於第二保險單年度自殺身故，則無理賠關懷保險金可以領到多少錢？</t>
+        </is>
+      </c>
+      <c r="C493" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+依第十七條規定，被保險人於契約訂立或復效之日起二年內故意自殺致死者，本公司不負給付無理賠關懷保險金的責任。因此，若被保險人於第二保險單年度自殺身故，無理賠關懷保險金無法領取。
+條文依據：  
+- [第十七條 除外責任（二)]</t>
+        </is>
+      </c>
+      <c r="D493" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 無理賠關懷保險金的給付 | 第十七條 除外責任（二） | 第十一條 特定傷病保險金的給付 | 第十九條 失蹤處理 | 第五條 保險範圍 | 第二十一條 無理賠關懷保險金的申領 | 第二十七條 受益人的指定及變更</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F493" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人於第二保險單年度自殺身故，依條款規定，自契約訂立或復效之日起二年內故意自殺致死者，本公司不負給付無理賠關懷保險金的責任。因此，無理賠關懷保險金無法領取。
+條文依據：  
+- [第十七條 除外責任（二)]</t>
+        </is>
+      </c>
+      <c r="G493" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+依第十七條規定，被保險人於契約訂立或復效之日起二年內故意自殺致死者，本公司不負給付無理賠關懷保險金的責任。因此，若被保險人於第二保險單年度自殺身故，無理賠關懷保險金無法領取。
+條文依據：  
+- [第十七條 除外責任（二)]</t>
+        </is>
+      </c>
+      <c r="H493" s="2" t="inlineStr"/>
+      <c r="I493" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.96674, "neutral": 0.032422, "contradiction": 0.000838, "factuality": 0.999162, "C_fact": 0.999162}, "C_conf": 0.9992}</t>
+        </is>
+      </c>
+      <c r="J493" s="5" t="n"/>
+      <c r="K493" s="5" t="n">
+        <v>0.999162</v>
+      </c>
+      <c r="L493" s="5" t="n">
+        <v>0.9992</v>
+      </c>
+      <c r="M493" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:41:14</t>
+        </is>
+      </c>
+      <c r="N493" s="5" t="n">
+        <v>7.58</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B494" s="2" t="inlineStr">
+        <is>
+          <t>請問如果第2保單年度罹患特定傷病，可以給付多少錢?給付給誰?未來還有其他保險金嗎?</t>
+        </is>
+      </c>
+      <c r="C494" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在第二保險單年度（含）以後罹患特定傷病，依條款規定，本公司將給付以下保險金：  
+1. **特定傷病保險金**：金額為保險金額，給付對象為被保險人。  
+2. **生活補助保險金**：自初次診斷確定罹患特定傷病的次一個保險單週年日起，每逢各保險單週年日仍生存者，按保險金額的36%給付，最高給付次數為10次。  
+此外，保險費將自診斷確定日起豁免，但當期已繳付之未到期保險費不予退還，契約仍繼續有效。
+條文依據：  
+- [第十二條 特定傷病保險金的給付]  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]  
+- [第十五條 保險費豁免（第二保險單年度起適用）]</t>
+        </is>
+      </c>
+      <c r="D494" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 特定傷病保險金的給付 | 第五條 保險範圍 | 第十三條 生活補助保險金的給付（第二保險單年度起適用） | 第二條 名詞定義 | 第十五條 保險費豁免（第二保險單年度起適用）</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F494" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在第二保險單年度（含）以後罹患特定傷病，依條款規定，本公司將給付以下保險金：  
+1. **特定傷病保險金**：金額為保險金額，給付對象為被保險人。  
+2. **生活補助保險金**：自初次診斷確定罹患特定傷病的次一個保險單週年日起，每逢各保險單週年日仍生存者，按保險金額的36%給付，最高給付次數為10次。  
+此外，保險費將自診斷確定日起豁免，但當期已繳付之未到期保險費不予退還，契約仍繼續有效。
+條文依據：  
+- [第十二條 特定傷病保險金的給付]  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]  
+- [第十五條 保險費豁免（第二保險單年度起適用）]</t>
+        </is>
+      </c>
+      <c r="G494" s="2" t="inlineStr"/>
+      <c r="H494" s="2" t="inlineStr"/>
+      <c r="I494" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.967299, "neutral": 0.030265, "contradiction": 0.002436, "factuality": 0.997564, "C_fact": 0.997564}, "C_conf": 0.9976}</t>
+        </is>
+      </c>
+      <c r="J494" s="5" t="n"/>
+      <c r="K494" s="5" t="n">
+        <v>0.997564</v>
+      </c>
+      <c r="L494" s="5" t="n">
+        <v>0.9976</v>
+      </c>
+      <c r="M494" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:41:28</t>
+        </is>
+      </c>
+      <c r="N494" s="5" t="n">
+        <v>13.93</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B495" s="2" t="inlineStr">
+        <is>
+          <t>請問我115年1月1日投保，怎麼得到健康促進保險費折減?指定日期什麼時後？</t>
+        </is>
+      </c>
+      <c r="C495" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+要獲得健康促進保險費折減，需在契約有效期間內完成以下步驟：  
+1. 使用保險公司指定的程式並加入指定的健康計劃。  
+2. 完成程式註冊程序，執行程式並授權保險公司取得與健康促進相關的電子紀錄。  
+3. 於「指定日期」的會員等級符合折減標準（如「實踐家」可折減3%，「樂享家」或更高等級可折減10%）。  
+至於「指定日期」，條文未明確定義具體日期，需參考保險公司相關規定或辦法。
+條文依據：  
+- [第十六條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="D495" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 健康促進保險費折減 | 第十五條 保險費豁免（第二保險單年度起適用） | 第五條 保險範圍 | 第二十三條 投保年齡的計算及錯誤的處理 | 第十二條 特定傷病保險金的給付 | 第十條 契約的終止（二） | 第十三條 生活補助保險金的給付（第二保險單年度起適用） | payout_items</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F495" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+要獲得健康促進保險費折減，需在契約有效期間內完成以下步驟：  
+1. 使用保險公司指定的程式並加入指定的健康計劃。  
+2. 完成程式註冊程序，執行程式並授權保險公司取得與健康促進相關的電子紀錄。  
+3. 於「指定日期」的會員等級符合折減標準（如「實踐家」可折減3%，「樂享家」或更高等級可折減10%）。  
+至於「指定日期」，條文未明確定義具體日期，需參考保險公司相關規定或辦法。
+條文依據：  
+- [第十六條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="G495" s="2" t="inlineStr"/>
+      <c r="H495" s="2" t="inlineStr"/>
+      <c r="I495" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.885587, "neutral": 0.065963, "contradiction": 0.048451, "factuality": 0.951549, "C_fact": 0.951549}, "C_conf": 0.9515}</t>
+        </is>
+      </c>
+      <c r="J495" s="5" t="n"/>
+      <c r="K495" s="5" t="n">
+        <v>0.951549</v>
+      </c>
+      <c r="L495" s="5" t="n">
+        <v>0.9515</v>
+      </c>
+      <c r="M495" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:41:41</t>
+        </is>
+      </c>
+      <c r="N495" s="5" t="n">
+        <v>13.52</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B496" s="2" t="inlineStr">
+        <is>
+          <t>保戶在114/1/10投保樂鍾溢，如果他在115/3/30罹患特定傷病的話，在什麼時候可以領取生活補助保險金?</t>
+        </is>
+      </c>
+      <c r="C496" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保戶在114/1/10投保，保險單週年日為每年的1月10日。根據條款，生活補助保險金的給付需符合以下條件：  
+1. 被保險人於第二保險單年度（含）以後的有效期間內初次診斷確定罹患特定傷病。  
+2. 自初次診斷確定罹患特定傷病的次一個保險單週年日起，每逢各保險單週年日仍生存者，方可領取生活補助保險金。  
+保戶於115/3/30罹患特定傷病，符合第二保險單年度的條件。其初次診斷確定罹患特定傷病的次一個保險單週年日為116/1/10，因此保戶可於116/1/10起，每逢保險單週年日仍生存時，領取生活補助保險金。
+條文依據：  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]</t>
+        </is>
+      </c>
+      <c r="D496" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 生活補助保險金的給付（第二保險單年度起適用） | other_metadata | 第十一條 契約的終止（三） | payout_items | 第十二條 特定傷病保險金的給付 | 第五條 保險範圍 | 第十五條 保險費豁免（第二保險單年度起適用） | 第十條 契約的終止（二）</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F496" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保戶在114/1/10投保，保險單週年日為每年的1月10日。根據條款，生活補助保險金的給付需符合以下條件：  
+1. 被保險人於第二保險單年度（含）以後的有效期間內初次診斷確定罹患特定傷病。  
+2. 自初次診斷確定罹患特定傷病的次一個保險單週年日起，每逢各保險單週年日仍生存者，方可領取生活補助保險金。  
+保戶於115/3/30罹患特定傷病，符合第二保險單年度的條件。其初次診斷確定罹患特定傷病的次一個保險單週年日為116/1/10，因此保戶可於116/1/10起，每逢保險單週年日仍生存時，領取生活補助保險金。
+條文依據：  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]</t>
+        </is>
+      </c>
+      <c r="G496" s="2" t="inlineStr"/>
+      <c r="H496" s="2" t="inlineStr"/>
+      <c r="I496" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.974128, "neutral": 0.021456, "contradiction": 0.004416, "factuality": 0.995584, "C_fact": 0.995584}, "C_conf": 0.9956}</t>
+        </is>
+      </c>
+      <c r="J496" s="5" t="n"/>
+      <c r="K496" s="5" t="n">
+        <v>0.995584</v>
+      </c>
+      <c r="L496" s="5" t="n">
+        <v>0.9956</v>
+      </c>
+      <c r="M496" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:41:50</t>
+        </is>
+      </c>
+      <c r="N496" s="5" t="n">
+        <v>8.720000000000001</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B497" s="2" t="inlineStr">
+        <is>
+          <t>保戶在114/1/10投保樂鍾溢，如果他在115/3/30罹患特定傷病的話，他在115/1/9會領到無理賠回饋保險金嗎?保險單週年日什麼時候？指定日期什麼時候？</t>
+        </is>
+      </c>
+      <c r="C497" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保險單週年日為每年1月10日，指定日期為每年1月9日。保戶在115/1/9無法領取無理賠回饋保險金，因為他在115/3/30罹患特定傷病，已不符合「未曾因罹患特定傷病而申領特定傷病保險金」的條件。
+條文依據：  
+- [第十四條 無理賠回饋保險金的給付]  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="D497" s="2" t="inlineStr">
+        <is>
+          <t>other_metadata | 第十四條 無理賠回饋保險金的給付 | payout_items | 第十二條 特定傷病保險金的給付 | 第十五條 保險費豁免（第二保險單年度起適用） | 第十條 契約的終止（二） | 第五條 保險範圍 | 第二十條 無理賠回饋保險金的申領</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F497" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保險單週年日為每年1月10日，指定日期為每年1月9日。保戶在115/1/9無法領取無理賠回饋保險金，因為他在115/3/30罹患特定傷病，已不符合「未曾因罹患特定傷病而申領特定傷病保險金」的條件。
+條文依據：  
+- [第十四條 無理賠回饋保險金的給付]  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="G497" s="2" t="inlineStr"/>
+      <c r="H497" s="2" t="inlineStr"/>
+      <c r="I497" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.026261, "neutral": 0.963552, "contradiction": 0.010187, "factuality": 0.989813, "C_fact": 0.989813}, "C_conf": 0.9898}</t>
+        </is>
+      </c>
+      <c r="J497" s="5" t="n"/>
+      <c r="K497" s="5" t="n">
+        <v>0.9898130000000001</v>
+      </c>
+      <c r="L497" s="5" t="n">
+        <v>0.9898</v>
+      </c>
+      <c r="M497" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:41:58</t>
+        </is>
+      </c>
+      <c r="N497" s="5" t="n">
+        <v>7.74</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B498" s="2" t="inlineStr">
+        <is>
+          <t>被保險人於第一保險單年度罹患急性心肌梗塞（重度），生活補助保險金最多可以領取幾次？契約會終止嗎？</t>
+        </is>
+      </c>
+      <c r="C498" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於第一保險單年度罹患急性心肌梗塞（重度），無法領取「生活補助保險金」，因該保險金僅適用於第二保險單年度（含）以後的有效期間內初次診斷確定罹患特定傷病者。契約會因罹患特定傷病而終止，並依第十二條約定給付「特定傷病保險金」。  
+條文依據：  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]  
+- [第十一條 契約的終止（三)]  
+- [第十二條 特定傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D498" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 生活補助保險金的給付（第二保險單年度起適用） | 第十一條 契約的終止（三） | 第五條 保險範圍 | 第二條 名詞定義 | 第十二條 特定傷病保險金的給付 | 第十五條 保險費豁免（第二保險單年度起適用） | payout_items | 第十條 契約的終止（二）</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F498" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於第一保險單年度罹患急性心肌梗塞（重度），無法領取「生活補助保險金」，因該保險金僅適用於第二保險單年度（含）以後的有效期間內初次診斷確定罹患特定傷病者。契約會因罹患特定傷病而終止，並依第十二條約定給付「特定傷病保險金」。  
+條文依據：  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]  
+- [第十一條 契約的終止（三)]  
+- [第十二條 特定傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G498" s="2" t="inlineStr"/>
+      <c r="H498" s="2" t="inlineStr"/>
+      <c r="I498" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.852636, "neutral": 0.058934, "contradiction": 0.088429, "factuality": 0.911571, "C_fact": 0.911571}, "C_conf": 0.9116}</t>
+        </is>
+      </c>
+      <c r="J498" s="5" t="n"/>
+      <c r="K498" s="5" t="n">
+        <v>0.911571</v>
+      </c>
+      <c r="L498" s="5" t="n">
+        <v>0.9116</v>
+      </c>
+      <c r="M498" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:42:10</t>
+        </is>
+      </c>
+      <c r="N498" s="5" t="n">
+        <v>10.98</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B499" s="2" t="inlineStr">
+        <is>
+          <t>被保險人為60歲女性，投保繳費期間20年期之樂鍾心特定傷病定期健康保險（外溢型）5單位，每單位年繳應繳保險費為1675元，則每逢保險單年度末生存者，可以領取多少無理賠關懷保險金？</t>
+        </is>
+      </c>
+      <c r="C499" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人每逢保險單年度末仍生存且未曾因罹患特定傷病申領「特定傷病保險金」者，可領取的「無理賠回饋保險金」金額計算如下：  
+每單位年繳應繳保險費的百分之十（元以下無條件進位）乘以單位數。  
+計算過程：  
+每單位年繳應繳保險費為1675元，百分之十為167.5元（元以下無條件進位為168元）。  
+5單位的「無理賠回饋保險金」金額為168元 × 5 = 840元。  
+因此，每逢保險單年度末生存者可領取840元。
+條文依據：  
+- [第十四條 無理賠回饋保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D499" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 無理賠回饋保險金的給付 | other_metadata | payout_items | 第二十條 無理賠回饋保險金的申領 | 第十二條 特定傷病保險金的給付 | 第十三條 生活補助保險金的給付（第二保險單年度起適用） | 第五條 保險範圍 | 第十五條 保險費豁免（第二保險單年度起適用）</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F499" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人每逢保險單年度末仍生存且未曾因罹患特定傷病申領「特定傷病保險金」者，可領取的「無理賠回饋保險金」金額計算如下：  
+每單位年繳應繳保險費的百分之十（元以下無條件進位）乘以單位數。  
+計算過程：  
+每單位年繳應繳保險費為1675元，百分之十為167.5元（元以下無條件進位為168元）。  
+5單位的「無理賠回饋保險金」金額為168元 × 5 = 840元。  
+因此，每逢保險單年度末生存者可領取840元。
+條文依據：  
+- [第十四條 無理賠回饋保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G499" s="2" t="inlineStr"/>
+      <c r="H499" s="2" t="inlineStr"/>
+      <c r="I499" s="2" t="inlineStr">
+        <is>
+          <t>{"nli": {"entailment": 0.992948, "neutral": 0.006725, "contradiction": 0.000328, "factuality": 0.999672, "C_fact": 0.999672}, "C_conf": 0.9997}</t>
+        </is>
+      </c>
+      <c r="J499" s="5" t="n"/>
+      <c r="K499" s="5" t="n">
+        <v>0.999672</v>
+      </c>
+      <c r="L499" s="5" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="M499" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:42:41</t>
+        </is>
+      </c>
+      <c r="N499" s="5" t="n">
+        <v>30.81</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/rag_results.xlsx
+++ b/src/rag_results.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M191"/>
+  <dimension ref="A1:M274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -12927,6 +12927,5503 @@
         </is>
       </c>
     </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>保障範圍包括哪些項目？</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包含：住院醫療保險金、加護病房或燒燙傷病房保險金、祝壽保險金、身故保險金或喪葬費用保險金，以及所繳保險費的退還。
+條文依據：  
+- 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>payout_items | summary | 第五條 保險範圍 | 第二條 名詞定義 | 第十八條 除外責任（一）</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包含：住院醫療保險金、加護病房或燒燙傷病房保險金、祝壽保險金、身故保險金或喪葬費用保險金，以及所繳保險費的退還。
+條文依據：  
+- 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr"/>
+      <c r="H192" s="2" t="inlineStr"/>
+      <c r="I192" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "保障範圍包括哪些項目？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.998498, "neutral": 0.001298, "contradiction": 0.000204, "factuality": 0.999796, "C_fact": 0.999796}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J192" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K192" s="3" t="n">
+        <v>0.999796</v>
+      </c>
+      <c r="L192" s="3" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>因同一疾病或傷害再次住院、若間隔時間在出院後十四日內或因併發症導致的再次住院日數計算有什麼特殊規則？</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 若被保險人因同一疾病或傷害，或因此引起的併發症，於出院後十四日內再次住院，則該次住院的日數計算，視為同一次住院處理。  
+2. 因此，出院後十四日內的再次住院，其住院日數將與前次住院合併計算，適用於第十二條至第十三條的保險金給付限制。  
+條文依據：  
+- [第十一條 住院次數之計算及契約有效期間屆滿後住院之處理]</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第十三條 加護病房或燒燙傷病房保險金的給付 | 第二條 名詞定義 | 第十二條 住院醫療保險金的給付 | 第十八條 除外責任（一） | 第二十八條 住院醫療保險金日額之減少</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 若被保險人因同一疾病或傷害，或因此引起的併發症，於出院後十四日內再次住院，則該次住院的日數計算，視為同一次住院處理。  
+2. 因此，出院後十四日內的再次住院，其住院日數將與前次住院合併計算，適用於第十二條至第十三條的保險金給付限制。  
+條文依據：  
+- [第十一條 住院次數之計算及契約有效期間屆滿後住院之處理]</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="inlineStr"/>
+      <c r="H193" s="2" t="inlineStr"/>
+      <c r="I193" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認同一疾病或傷害再次住院的間隔時間規定", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認出院後十四日內再次住院的日數計算規則", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認因併發症導致再次住院的日數計算規則", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認是否有針對再次住院的特殊條款或例外規定", "must_have": false, "分數": 0.8}], "coverage_score": 0.9846, "nli": {"entailment": 0.992109, "neutral": 0.00617, "contradiction": 0.001721, "factuality": 0.998279, "C_fact": 0.998279}, "C_conf": 0.9836}</t>
+        </is>
+      </c>
+      <c r="J193" s="3" t="n">
+        <v>0.9846</v>
+      </c>
+      <c r="K193" s="3" t="n">
+        <v>0.998279</v>
+      </c>
+      <c r="L193" s="3" t="n">
+        <v>0.9836</v>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:16:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>住院醫療保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院醫療保險金的給付規定如下：  
+1. 被保險人於本契約有效期間內因疾病或傷害住院治療時，本公司將依保險單上記載的「住院醫療保險金日額」，乘以入院日當年度的「增額係數」，再乘以住院日數，給付「住院醫療保險金」。  
+2. 同一保單年度內，同一次住院的住院日數給付上限為365日。  
+條文依據：  
+- [第十二條 住院醫療保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 住院醫療保險金的給付 | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第十三條 加護病房或燒燙傷病房保險金的給付 | 第十四條 醫療保險金給付總額之上限 | 第二十八條 住院醫療保險金日額之減少</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院醫療保險金的給付規定如下：  
+1. 被保險人於本契約有效期間內因疾病或傷害住院治療時，本公司將依保險單上記載的「住院醫療保險金日額」，乘以入院日當年度的「增額係數」，再乘以住院日數，給付「住院醫療保險金」。  
+2. 同一保單年度內，同一次住院的住院日數給付上限為365日。  
+條文依據：  
+- [第十二條 住院醫療保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr"/>
+      <c r="H194" s="2" t="inlineStr"/>
+      <c r="I194" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "住院醫療保險金的給付規定", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.994738, "neutral": 0.00382, "contradiction": 0.001442, "factuality": 0.998558, "C_fact": 0.998558}, "C_conf": 0.9991}</t>
+        </is>
+      </c>
+      <c r="J194" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K194" s="3" t="n">
+        <v>0.9985579999999999</v>
+      </c>
+      <c r="L194" s="3" t="n">
+        <v>0.9991</v>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:16:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>加護病房或燒燙傷病房保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+加護病房或燒燙傷病房保險金的給付規定如下：  
+被保險人於本契約有效期間內因疾病或傷害而在醫院的加護病房或燒燙傷病房接受治療時，除住院醫療保險金外，本公司將依保險單所載「住院醫療保險金日額」，乘以入院日當年度的「增額係數」，再乘以實際住進加護病房或燒燙傷病房的日數（含轉入及轉出當日）的二倍，給付「加護病房或燒燙傷病房保險金」。  
+同一保單年度內，同一次住院的加護病房及燒燙傷病房住院日數合計給付上限為365日，但同一日內僅給付其中一種病房的保險金。
+條文依據：  
+- [第十三條 加護病房或燒燙傷病房保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 加護病房或燒燙傷病房保險金的給付 | payout_items | 第二十三條 醫療保險金的申領 | 第五條 保險範圍 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+加護病房或燒燙傷病房保險金的給付規定如下：  
+被保險人於本契約有效期間內因疾病或傷害而在醫院的加護病房或燒燙傷病房接受治療時，除住院醫療保險金外，本公司將依保險單所載「住院醫療保險金日額」，乘以入院日當年度的「增額係數」，再乘以實際住進加護病房或燒燙傷病房的日數（含轉入及轉出當日）的二倍，給付「加護病房或燒燙傷病房保險金」。  
+同一保單年度內，同一次住院的加護病房及燒燙傷病房住院日數合計給付上限為365日，但同一日內僅給付其中一種病房的保險金。
+條文依據：  
+- [第十三條 加護病房或燒燙傷病房保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G195" s="2" t="inlineStr"/>
+      <c r="H195" s="2" t="inlineStr"/>
+      <c r="I195" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "加護病房或燒燙傷病房保險金的給付規定", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.996491, "neutral": 0.002888, "contradiction": 0.000621, "factuality": 0.999379, "C_fact": 0.999379}, "C_conf": 0.9996}</t>
+        </is>
+      </c>
+      <c r="J195" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K195" s="3" t="n">
+        <v>0.999379</v>
+      </c>
+      <c r="L195" s="3" t="n">
+        <v>0.9996</v>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:16:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>醫療保險金給付總額之上限</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+醫療保險金給付總額之上限為保險單上所記載之「住院醫療保險金日額」的二千五百倍，並包含第十二條至第十三條所列的各項保險金累計給付總額。
+條文依據：  
+- [第十四條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 醫療保險金給付總額之上限 | 第十二條 住院醫療保險金的給付 | 第五條 保險範圍 | 第十三條 加護病房或燒燙傷病房保險金的給付 | payout_items</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+醫療保險金給付總額之上限為保險單上所記載之「住院醫療保險金日額」的二千五百倍，並包含第十二條至第十三條所列的各項保險金累計給付總額。
+條文依據：  
+- [第十四條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr"/>
+      <c r="H196" s="2" t="inlineStr"/>
+      <c r="I196" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "醫療保險金給付總額之上限", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.997145, "neutral": 0.002614, "contradiction": 0.000242, "factuality": 0.999758, "C_fact": 0.999758}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J196" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K196" s="3" t="n">
+        <v>0.999758</v>
+      </c>
+      <c r="L196" s="3" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:16:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>祝壽保險金的給付規定為何?</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+祝壽保險金的給付規定如下：  
+被保險人於本契約有效期間內，且保險年齡到達九十九歲之保險單週年日仍生存時，本公司將按「當年度保險金額」給付「祝壽保險金」。
+條文依據：  
+- [第十五條 祝壽保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>第十五條 祝壽保險金的給付 | 第十二條至第十三條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | 第二十四條 祝壽保險金的申領 | payout_items | 第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+祝壽保險金的給付規定如下：  
+被保險人於本契約有效期間內，且保險年齡到達九十九歲之保險單週年日仍生存時，本公司將按「當年度保險金額」給付「祝壽保險金」。
+條文依據：  
+- [第十五條 祝壽保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G197" s="2" t="inlineStr"/>
+      <c r="H197" s="2" t="inlineStr"/>
+      <c r="I197" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "祝壽保險金的給付規定為何?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.998014, "neutral": 0.001828, "contradiction": 0.000157, "factuality": 0.999843, "C_fact": 0.999843}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J197" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K197" s="3" t="n">
+        <v>0.999843</v>
+      </c>
+      <c r="L197" s="3" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:17:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>有效期間內身故，保險金如何給付?</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於本契約有效期間內身故時，本公司依以下情況給付保險金：  
+1. 若被保險人於繳費期間內身故，已繳付之未到期保險費不予退還，亦不併入身故保險金內給付。  
+2. 若被保險人於實際年齡未滿十五足歲時身故，本公司退還「所繳保險費」予要保人，不適用身故保險金給付。  
+3. 若被保險人為受監護宣告尚未撤銷者，其身故保險金變更為喪葬費用保險金。  
+條文依據：  
+- [第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付 | 第十條 契約的終止（二） | 第五條 保險範圍 | 第二十二條 失蹤處理 | 第十五條 祝壽保險金的給付</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於本契約有效期間內身故時，本公司依以下情況給付保險金：  
+1. 若被保險人於繳費期間內身故，已繳付之未到期保險費不予退還，亦不併入身故保險金內給付。  
+2. 若被保險人於實際年齡未滿十五足歲時身故，本公司退還「所繳保險費」予要保人，不適用身故保險金給付。  
+3. 若被保險人為受監護宣告尚未撤銷者，其身故保險金變更為喪葬費用保險金。  
+條文依據：  
+- [第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr"/>
+      <c r="H198" s="2" t="inlineStr"/>
+      <c r="I198" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "有效期間內身故，保險金如何給付?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.967334, "neutral": 0.030655, "contradiction": 0.002011, "factuality": 0.997989, "C_fact": 0.997989}, "C_conf": 0.9988}</t>
+        </is>
+      </c>
+      <c r="J198" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K198" s="3" t="n">
+        <v>0.997989</v>
+      </c>
+      <c r="L198" s="3" t="n">
+        <v>0.9988</v>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:17:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>健康促進保險費折減規定</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+健康促進保險費折減規定如下：  
+1. 被保險人年齡需達20歲（含）以上，並使用保險公司指定程式加入健康計劃。  
+2. 若於「指定日期」會員等級符合標準，可享次一保險單年度保險費折減：  
+   - 進階會員：折減2%。  
+   - 菁英會員或更高等級：折減3%。  
+3. 折減僅適用於主契約保險費，不包含附約、附加條款或批註條款，且豁免或復效的保險費不適用折減。  
+4. 被保險人需完成程式註冊並授權保險公司取得健康相關電子紀錄，保險公司將依紀錄計算會員等級。
+條文依據：  
+- [第十七條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>第十七條 健康促進保險費折減 | 第二十八條 住院醫療保險金日額之減少 | 第三十條 投保年齡的計算及錯誤的處理 | 第二條 名詞定義 | 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+健康促進保險費折減規定如下：  
+1. 被保險人年齡需達20歲（含）以上，並使用保險公司指定程式加入健康計劃。  
+2. 若於「指定日期」會員等級符合標準，可享次一保險單年度保險費折減：  
+   - 進階會員：折減2%。  
+   - 菁英會員或更高等級：折減3%。  
+3. 折減僅適用於主契約保險費，不包含附約、附加條款或批註條款，且豁免或復效的保險費不適用折減。  
+4. 被保險人需完成程式註冊並授權保險公司取得健康相關電子紀錄，保險公司將依紀錄計算會員等級。
+條文依據：  
+- [第十七條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="inlineStr"/>
+      <c r="H199" s="2" t="inlineStr"/>
+      <c r="I199" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "健康促進保險費折減規定", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.993294, "neutral": 0.006042, "contradiction": 0.000664, "factuality": 0.999336, "C_fact": 0.999336}, "C_conf": 0.9996}</t>
+        </is>
+      </c>
+      <c r="J199" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K199" s="3" t="n">
+        <v>0.999336</v>
+      </c>
+      <c r="L199" s="3" t="n">
+        <v>0.9996</v>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:17:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>除外責任的解釋?</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+除外責任是指保險公司對於某些特定原因或情況下所發生的疾病、傷害或死亡，不負給付保險金的責任。條款中列舉了多種除外責任情形，例如被保險人因故意行為、犯罪行為、非法施用毒品等原因住院診療，或因美容手術、健康檢查、懷孕及分娩等特定情況住院診療，保險公司不負給付責任。但部分情況下有例外，例如為重建基本功能的必要整型手術或特定懷孕相關疾病等，則不在除外責任範圍內。
+條文依據：  
+- [第十八條 除外責任（一）]  
+- [第十九條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第十九條 除外責任（二） | 第八條 告知義務與本契約的解除 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+除外責任是指保險公司對於某些特定原因或情況下所發生的疾病、傷害或死亡，不負給付保險金的責任。條款中列舉了多種除外責任情形，例如被保險人因故意行為、犯罪行為、非法施用毒品等原因住院診療，或因美容手術、健康檢查、懷孕及分娩等特定情況住院診療，保險公司不負給付責任。但部分情況下有例外，例如為重建基本功能的必要整型手術或特定懷孕相關疾病等，則不在除外責任範圍內。
+條文依據：  
+- [第十八條 除外責任（一）]  
+- [第十九條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="G200" s="2" t="inlineStr"/>
+      <c r="H200" s="2" t="inlineStr"/>
+      <c r="I200" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "除外責任的解釋?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.99867, "neutral": 0.001219, "contradiction": 0.000111, "factuality": 0.999889, "C_fact": 0.999889}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J200" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K200" s="3" t="n">
+        <v>0.999889</v>
+      </c>
+      <c r="L200" s="3" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:17:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>哪些疾病被含在除外責任?</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人因以下原因所致之疾病或傷害，屬於除外責任，本公司不負給付保險金的責任：  
+1. 被保險人之故意行為（包括自殺及自殺未遂）。  
+2. 被保險人之犯罪行為。  
+3. 被保險人非法施用毒品。  
+4. 美容手術、外科整型（但為重建基本功能所作之必要整型不在此限）。  
+5. 外觀可見之天生畸形。  
+6. 健康檢查、療養、靜養、戒毒、戒酒、護理或養老等非以直接診治病人為目的者。  
+7. 懷孕、流產或分娩及其併發症（但特定情形如子宮外孕、葡萄胎等不在此限）。  
+8. 不孕症、人工受孕或非以治療為目的之避孕及絕育手術。  
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第二條 名詞定義 | 第十九條 除外責任（二）</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人因以下原因所致之疾病或傷害，屬於除外責任，本公司不負給付保險金的責任：  
+1. 被保險人之故意行為（包括自殺及自殺未遂）。  
+2. 被保險人之犯罪行為。  
+3. 被保險人非法施用毒品。  
+4. 美容手術、外科整型（但為重建基本功能所作之必要整型不在此限）。  
+5. 外觀可見之天生畸形。  
+6. 健康檢查、療養、靜養、戒毒、戒酒、護理或養老等非以直接診治病人為目的者。  
+7. 懷孕、流產或分娩及其併發症（但特定情形如子宮外孕、葡萄胎等不在此限）。  
+8. 不孕症、人工受孕或非以治療為目的之避孕及絕育手術。  
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="G201" s="2" t="inlineStr"/>
+      <c r="H201" s="2" t="inlineStr"/>
+      <c r="I201" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "哪些疾病被含在除外責任?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.998033, "neutral": 0.00171, "contradiction": 0.000257, "factuality": 0.999743, "C_fact": 0.999743}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J201" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K201" s="3" t="n">
+        <v>0.999743</v>
+      </c>
+      <c r="L201" s="3" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:18:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>進行美容手術住院可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，因美容手術或外科整型住院診療者，保險公司不負給付保險金的責任。但若該整型手術是為了重建基本功能所作的必要整型，則不在此限，仍可申請理賠。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第十三條 加護病房或燒燙傷病房保險金的給付 | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第二條 名詞定義 | payout_items</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，因美容手術或外科整型住院診療者，保險公司不負給付保險金的責任。但若該整型手術是為了重建基本功能所作的必要整型，則不在此限，仍可申請理賠。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="G202" s="2" t="inlineStr"/>
+      <c r="H202" s="2" t="inlineStr"/>
+      <c r="I202" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "進行美容手術住院可以申請理賠嗎?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.947322, "neutral": 0.052199, "contradiction": 0.000479, "factuality": 0.999521, "C_fact": 0.999521}, "C_conf": 0.9997}</t>
+        </is>
+      </c>
+      <c r="J202" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K202" s="3" t="n">
+        <v>0.999521</v>
+      </c>
+      <c r="L202" s="3" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:18:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>因胎兒染色體異常進行手術而住院可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以申請理賠。根據條款，因胎兒染色體異常進行手術屬於「懷孕相關疾病」的例外情形之一，不在除外責任範圍內，因此符合理賠條件。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第二條 名詞定義 | payout_items | 第十三條 加護病房或燒燙傷病房保險金的給付</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以申請理賠。根據條款，因胎兒染色體異常進行手術屬於「懷孕相關疾病」的例外情形之一，不在除外責任範圍內，因此符合理賠條件。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="G203" s="2" t="inlineStr"/>
+      <c r="H203" s="2" t="inlineStr"/>
+      <c r="I203" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "因胎兒染色體異常進行手術而住院可以申請理賠嗎?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.983696, "neutral": 0.016045, "contradiction": 0.000259, "factuality": 0.999741, "C_fact": 0.999741}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J203" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K203" s="3" t="n">
+        <v>0.999741</v>
+      </c>
+      <c r="L203" s="3" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:18:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>因胎位不正進行手術而住院可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以申請理賠。根據條款，雖然一般懷孕、流產或分娩及其併發症屬於除外責任，但胎位不正屬於「醫療行為必要之剖腹產」的理賠範圍，因此不在除外責任之列。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第二條 名詞定義 | payout_items | 第十三條 加護病房或燒燙傷病房保險金的給付</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以申請理賠。根據條款，雖然一般懷孕、流產或分娩及其併發症屬於除外責任，但胎位不正屬於「醫療行為必要之剖腹產」的理賠範圍，因此不在除外責任之列。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="inlineStr"/>
+      <c r="H204" s="2" t="inlineStr"/>
+      <c r="I204" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "因胎位不正進行手術而住院可以申請理賠嗎?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.991982, "neutral": 0.007687, "contradiction": 0.000332, "factuality": 0.999668, "C_fact": 0.999668}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J204" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K204" s="3" t="n">
+        <v>0.999668</v>
+      </c>
+      <c r="L204" s="3" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:19:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>因自殺未遂導致住院可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人因自殺未遂導致住院，本公司不負給付住院相關保險金的責任，因其屬於被保險人之故意行為。  
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 除外責任（二） | 第十八條 除外責任（一） | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | payout_items | 第十條 契約的終止（二）</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人因自殺未遂導致住院，本公司不負給付住院相關保險金的責任，因其屬於被保險人之故意行為。  
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="G205" s="2" t="inlineStr"/>
+      <c r="H205" s="2" t="inlineStr"/>
+      <c r="I205" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "因自殺未遂導致住院可以申請理賠嗎?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.993764, "neutral": 0.005568, "contradiction": 0.000669, "factuality": 0.999331, "C_fact": 0.999331}, "C_conf": 0.9996}</t>
+        </is>
+      </c>
+      <c r="J205" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K205" s="3" t="n">
+        <v>0.999331</v>
+      </c>
+      <c r="L205" s="3" t="n">
+        <v>0.9996</v>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:19:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>被保險人在投保一年內故意自殺者，可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人在投保一年內故意自殺者，保險公司不負給付身故保險金或喪葬費用保險金的責任。只有在契約訂立或復效之日起滿二年後，因故意自殺致死的情況下，保險公司才負給付責任。
+條文依據：  
+- [第十九條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 除外責任（二） | 第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付 | 第十條 契約的終止（二） | 第三十條 投保年齡的計算及錯誤的處理 | 第十八條 除外責任（一）</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人在投保一年內故意自殺者，保險公司不負給付身故保險金或喪葬費用保險金的責任。只有在契約訂立或復效之日起滿二年後，因故意自殺致死的情況下，保險公司才負給付責任。
+條文依據：  
+- [第十九條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="G206" s="2" t="inlineStr"/>
+      <c r="H206" s="2" t="inlineStr"/>
+      <c r="I206" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "被保險人在投保一年內故意自殺者，可以申請理賠嗎?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.997826, "neutral": 0.001897, "contradiction": 0.000277, "factuality": 0.999723, "C_fact": 0.999723}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J206" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K206" s="3" t="n">
+        <v>0.999723</v>
+      </c>
+      <c r="L206" s="3" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:19:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>申請理賠有什麼時間規定嗎?</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申請理賠的時間規定如下：要保人、被保險人或受益人應於知悉保險事故後十日內通知保險公司，並於通知後儘速檢具所需文件向保險公司申請給付保險金。保險公司應於收齊文件後十五日內完成給付。若因保險公司可歸責的原因未能在期限內給付，應按年利一分加計利息給付。
+條文依據：  
+- [第二十一條 保險事故的通知與保險金的申請時間]</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>第二十一條 保險事故的通知與保險金的申請時間 | 第六條 第二期以後保險費的交付、寬限期間及契約效力的停止 | 第七條 本契約效力的恢復 | 第三條 契約撤銷權 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申請理賠的時間規定如下：要保人、被保險人或受益人應於知悉保險事故後十日內通知保險公司，並於通知後儘速檢具所需文件向保險公司申請給付保險金。保險公司應於收齊文件後十五日內完成給付。若因保險公司可歸責的原因未能在期限內給付，應按年利一分加計利息給付。
+條文依據：  
+- [第二十一條 保險事故的通知與保險金的申請時間]</t>
+        </is>
+      </c>
+      <c r="G207" s="2" t="inlineStr"/>
+      <c r="H207" s="2" t="inlineStr"/>
+      <c r="I207" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "申請理賠有什麼時間規定嗎?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.997879, "neutral": 0.001963, "contradiction": 0.000158, "factuality": 0.999842, "C_fact": 0.999842}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J207" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K207" s="3" t="n">
+        <v>0.999842</v>
+      </c>
+      <c r="L207" s="3" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:19:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>燒燙傷病房保險金怎麼申領?</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申領燒燙傷病房保險金時，受益人需檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 醫療診斷書或住院證明，且需列明進、出燒燙傷病房的日期。（但要保人或被保險人為醫師時，不得為被保險人出具診斷書或住院證明。）  
+4. 受益人的身分證明。  
+此外，保險公司可基於審核需要，徵詢其他醫師的專業意見，並經受益人同意調閱被保險人的就醫相關資料，相關費用由保險公司負擔。
+條文依據：  
+- [第二十三條 醫療保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>第二十三條 醫療保險金的申領 | 第十三條 加護病房或燒燙傷病房保險金的給付 | payout_items | 第二條 名詞定義 | 第二十一條 保險事故的通知與保險金的申請時間</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申領燒燙傷病房保險金時，受益人需檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 醫療診斷書或住院證明，且需列明進、出燒燙傷病房的日期。（但要保人或被保險人為醫師時，不得為被保險人出具診斷書或住院證明。）  
+4. 受益人的身分證明。  
+此外，保險公司可基於審核需要，徵詢其他醫師的專業意見，並經受益人同意調閱被保險人的就醫相關資料，相關費用由保險公司負擔。
+條文依據：  
+- [第二十三條 醫療保險金的申領]</t>
+        </is>
+      </c>
+      <c r="G208" s="2" t="inlineStr"/>
+      <c r="H208" s="2" t="inlineStr"/>
+      <c r="I208" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "燒燙傷病房保險金怎麼申領?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.998243, "neutral": 0.001573, "contradiction": 0.000184, "factuality": 0.999816, "C_fact": 0.999816}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J208" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K208" s="3" t="n">
+        <v>0.999816</v>
+      </c>
+      <c r="L208" s="3" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:20:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>活到99歲怎麼申請祝壽金?</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申請祝壽保險金時，受益人需檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 受益人的身分證明。  
+條文依據：  
+- [第二十四條 祝壽保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>第十五條 祝壽保險金的給付 | 第二十四條 祝壽保險金的申領 | 第五條 保險範圍 | 第十二條至第十三條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | announcement_history</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申請祝壽保險金時，受益人需檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 受益人的身分證明。  
+條文依據：  
+- [第二十四條 祝壽保險金的申領]</t>
+        </is>
+      </c>
+      <c r="G209" s="2" t="inlineStr"/>
+      <c r="H209" s="2" t="inlineStr"/>
+      <c r="I209" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "活到99歲怎麼申請祝壽金?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.99803, "neutral": 0.001868, "contradiction": 0.000103, "factuality": 0.999897, "C_fact": 0.999897}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J209" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K209" s="3" t="n">
+        <v>0.999897</v>
+      </c>
+      <c r="L209" s="3" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:20:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>被保人身故怎麼申請理賠</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+受益人申請「身故保險金」或「喪葬費用保險金」時，需檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 被保險人死亡證明書及除戶戶籍謄本。  
+4. 受益人的身分證明。  
+條文依據：  
+- [第二十五條 身故保險金或喪葬費用保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付 | 第十二條至第十三條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | 第二十二條 失蹤處理 | 第二十五條 身故保險金或喪葬費用保險金的申領 | 第十九條 除外責任（二）</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+受益人申請「身故保險金」或「喪葬費用保險金」時，需檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 被保險人死亡證明書及除戶戶籍謄本。  
+4. 受益人的身分證明。  
+條文依據：  
+- [第二十五條 身故保險金或喪葬費用保險金的申領]</t>
+        </is>
+      </c>
+      <c r="G210" s="2" t="inlineStr"/>
+      <c r="H210" s="2" t="inlineStr"/>
+      <c r="I210" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "被保人身故怎麼申請理賠", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.996283, "neutral": 0.003565, "contradiction": 0.000152, "factuality": 0.999848, "C_fact": 0.999848}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J210" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K210" s="3" t="n">
+        <v>0.999848</v>
+      </c>
+      <c r="L210" s="3" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:20:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>投保15年後，增額係數為多少？因手術住院3天，住院日額為2500元，請問可以申請多少理賠?</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 投保15年後的增額係數為1.05。  
+2. 理賠計算方式為：住院日額 × 增額係數 × 住院日數。  
+3. 手術住院3天的理賠金額計算如下：  
+   2500元（住院日額） × 1.05（增額係數） × 3天（住院日數） = 7875元。  
+4. 條文中未提及其他附加條款影響理賠金額。
+條文依據：  
+- [附表：增額係數表]  
+- [第十二條 住院醫療保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>附表：增額係數表 | 第十二條 住院醫療保險金的給付 | 第十三條 加護病房或燒燙傷病房保險金的給付 | 第二十八條 住院醫療保險金日額之減少 | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第三十條 投保年齡的計算及錯誤的處理 | payout_items | 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 投保15年後的增額係數為1.05。  
+2. 理賠計算方式為：住院日額 × 增額係數 × 住院日數。  
+3. 手術住院3天的理賠金額計算如下：  
+   2500元（住院日額） × 1.05（增額係數） × 3天（住院日數） = 7875元。  
+4. 條文中未提及其他附加條款影響理賠金額。
+條文依據：  
+- [附表：增額係數表]  
+- [第十二條 住院醫療保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G211" s="2" t="inlineStr"/>
+      <c r="H211" s="2" t="inlineStr"/>
+      <c r="I211" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認投保15年後的增額係數", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認住院日額為2500元的理賠計算方式", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認手術住院3天的理賠金額計算", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認是否有其他附加條款影響理賠金額", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.057094, "neutral": 0.918345, "contradiction": 0.024561, "factuality": 0.975439, "C_fact": 0.975439}, "C_conf": 0.9852}</t>
+        </is>
+      </c>
+      <c r="J211" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K211" s="3" t="n">
+        <v>0.9754389999999999</v>
+      </c>
+      <c r="L211" s="3" t="n">
+        <v>0.9852</v>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:20:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>保障範圍包括哪些項目？</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括：住院手術醫療保險金、門診手術醫療保險金、特定處置保險金、意外創傷縫合處置保險金、意外住院手術醫療保險金、祝壽保險金、所繳保險費的退還、身故保險金或喪葬費用保險金。
+條文依據：  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>payout_items | 第五條 保險範圍 | summary | 第四條 名詞定義 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括：住院手術醫療保險金、門診手術醫療保險金、特定處置保險金、意外創傷縫合處置保險金、意外住院手術醫療保險金、祝壽保險金、所繳保險費的退還、身故保險金或喪葬費用保險金。
+條文依據：  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="G212" s="2" t="inlineStr"/>
+      <c r="H212" s="2" t="inlineStr"/>
+      <c r="I212" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "保障範圍包括哪些項目？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.998072, "neutral": 0.001746, "contradiction": 0.000182, "factuality": 0.999818, "C_fact": 0.999818}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J212" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K212" s="3" t="n">
+        <v>0.999818</v>
+      </c>
+      <c r="L212" s="3" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:21:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>保險金額是否有上限?</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+有，保險金額的給付總額上限為保險單上所記載「保險金額」的一千五百倍，且不包含其他附約、附加條款或批註條款。
+條文依據：  
+- [第十六條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 醫療保險金給付總額之上限 | 第三十條 保險金額之減少 | 第五條 保險範圍 | 第十九條 健康促進保險費折減 | 第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+有，保險金額的給付總額上限為保險單上所記載「保險金額」的一千五百倍，且不包含其他附約、附加條款或批註條款。
+條文依據：  
+- [第十六條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="G213" s="2" t="inlineStr"/>
+      <c r="H213" s="2" t="inlineStr"/>
+      <c r="I213" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "保險金額是否有上限?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.997606, "neutral": 0.00227, "contradiction": 0.000124, "factuality": 0.999876, "C_fact": 0.999876}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J213" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K213" s="3" t="n">
+        <v>0.999876</v>
+      </c>
+      <c r="L213" s="3" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:21:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>投保後5天發生手術，是否可以申請理賠?</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款，被保險人於保險契約有效期間內因疾病或傷害接受手術，符合附表一所列手術項目且不屬除外責任範圍者，可申請理賠。然而，若疾病發生於契約生效日起持續有效第三十一日之前，則不在理賠範圍內。  
+條款依據：  
+[第四條 名詞定義]  
+[第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第十一條 住院手術醫療保險金 | 第二十條 除外責任（一） | 第十二條 門診手術醫療保險金 | 第十三條 意外住院手術醫療保險金 | 第二十三條 保險事故的通知與保險金的申請時間 | 第四條 名詞定義 | 第十五條 意外創傷縫合處置保險金 | 附表三：意外創傷縫合處置項目及給付倍數表 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+找不到相關內容  
+條文依據：  
+找不到相關內容</t>
+        </is>
+      </c>
+      <c r="G214" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款，被保險人於保險契約有效期間內因疾病或傷害接受手術，符合附表一所列手術項目且不屬除外責任範圍者，可申請理賠。然而，若疾病發生於契約生效日起持續有效第三十一日之前，則不在理賠範圍內。  
+條款依據：  
+[第四條 名詞定義]  
+[第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="H214" s="2" t="inlineStr"/>
+      <c r="I214" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "投保後5天發生手術，是否可以申請理賠?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.285685, "neutral": 0.582991, "contradiction": 0.131323, "factuality": 0.868677, "C_fact": 0.868677}, "C_conf": 0.919}</t>
+        </is>
+      </c>
+      <c r="J214" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K214" s="3" t="n">
+        <v>0.868677</v>
+      </c>
+      <c r="L214" s="3" t="n">
+        <v>0.919</v>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:21:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>住院手術醫療保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院手術醫療保險金的給付規定如下：  
+1. 被保險人需於保險契約有效期間內，因疾病或傷害經醫師診斷必須住院接受附表一所列的手術治療，且已實際接受手術。  
+2. 給付金額計算方式為：保險單上記載的「保險金額」乘以手術日當年度的「增額係數」，再乘以手術給付倍數。  
+3. 若同一次手術中於同一手術位置接受兩項以上手術項目，僅給付手術給付倍數最高的手術項目。  
+4. 未載明於附表一的手術項目，將與被保險人協議比照附表內程度相當的手術項目，決定給付倍數。  
+5. 以下情形不予給付：  
+   - 屬於除外責任條款規定的情形。  
+   - 不屬於全民健康保險醫療服務給付項目及支付標準第二部第二章第七節或第三部第三章第四節第三項所列舉的手術。  
+條文依據：  
+- [第十一條 住院手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 住院手術醫療保險金 | 第十三條 意外住院手術醫療保險金 | 第十二條 門診手術醫療保險金 | payout_items | 第二十條 除外責任（一） | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F215" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院手術醫療保險金的給付規定如下：  
+1. 被保險人需於保險契約有效期間內，因疾病或傷害經醫師診斷必須住院接受附表一所列的手術治療，且已實際接受手術。  
+2. 給付金額計算方式為：保險單上記載的「保險金額」乘以手術日當年度的「增額係數」，再乘以手術給付倍數。  
+3. 若同一次手術中於同一手術位置接受兩項以上手術項目，僅給付手術給付倍數最高的手術項目。  
+4. 未載明於附表一的手術項目，將與被保險人協議比照附表內程度相當的手術項目，決定給付倍數。  
+5. 以下情形不予給付：  
+   - 屬於除外責任條款規定的情形。  
+   - 不屬於全民健康保險醫療服務給付項目及支付標準第二部第二章第七節或第三部第三章第四節第三項所列舉的手術。  
+條文依據：  
+- [第十一條 住院手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="G215" s="2" t="inlineStr"/>
+      <c r="H215" s="2" t="inlineStr"/>
+      <c r="I215" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "住院手術醫療保險金的給付規定", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.995199, "neutral": 0.004416, "contradiction": 0.000385, "factuality": 0.999615, "C_fact": 0.999615}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J215" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K215" s="3" t="n">
+        <v>0.999615</v>
+      </c>
+      <c r="L215" s="3" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:21:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>門診手術醫療保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+門診手術醫療保險金的給付規定如下：  
+1. 被保險人需於本契約有效期間內，因疾病或傷害經醫師診斷必須於醫院或診所門診接受附表一所列的手術治療，且已實際接受手術。  
+2. 給付金額計算方式為：保險單上所記載的「保險金額」乘以手術日當年度的「增額係數」，再乘以手術給付倍數。  
+3. 同一次手術中，若於同一手術位置接受兩項以上手術項目，僅給付手術給付倍數最高的手術項目。  
+4. 同一保險單年度內，門診手術醫療保險金的給付以十次為限。  
+5. 若手術項目未載明於附表一，本公司將與被保險人協議比照附表內的手術項目決定給付倍數。  
+6. 以下情形不負給付責任：  
+   - 屬於本契約除外責任條款規定的情形。  
+   - 不屬於全民健康保險醫療服務給付項目及支付標準第二部第二章第七節或第三部第三章第四節第三項所列舉的手術。  
+條文依據：  
+- [第十二條 門診手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 門診手術醫療保險金 | 第十一條 住院手術醫療保險金 | payout_items | 第十三條 意外住院手術醫療保險金 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F216" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+門診手術醫療保險金的給付規定如下：  
+1. 被保險人需於本契約有效期間內，因疾病或傷害經醫師診斷必須於醫院或診所門診接受附表一所列的手術治療，且已實際接受手術。  
+2. 給付金額計算方式為：保險單上所記載的「保險金額」乘以手術日當年度的「增額係數」，再乘以手術給付倍數。  
+3. 同一次手術中，若於同一手術位置接受兩項以上手術項目，僅給付手術給付倍數最高的手術項目。  
+4. 同一保險單年度內，門診手術醫療保險金的給付以十次為限。  
+5. 若手術項目未載明於附表一，本公司將與被保險人協議比照附表內的手術項目決定給付倍數。  
+6. 以下情形不負給付責任：  
+   - 屬於本契約除外責任條款規定的情形。  
+   - 不屬於全民健康保險醫療服務給付項目及支付標準第二部第二章第七節或第三部第三章第四節第三項所列舉的手術。  
+條文依據：  
+- [第十二條 門診手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="G216" s="2" t="inlineStr"/>
+      <c r="H216" s="2" t="inlineStr"/>
+      <c r="I216" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "門診手術醫療保險金的給付規定", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.984217, "neutral": 0.015366, "contradiction": 0.000417, "factuality": 0.999583, "C_fact": 0.999583}, "C_conf": 0.9997}</t>
+        </is>
+      </c>
+      <c r="J216" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K216" s="3" t="n">
+        <v>0.999583</v>
+      </c>
+      <c r="L216" s="3" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:22:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>意外住院手術醫療保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外住院手術醫療保險金的給付規定如下：  
+1. 被保險人需於本契約有效期間內，且保險年齡未滿七十歲。  
+2. 因傷害經醫師診斷，在住院期間必須接受手術治療且已接受手術者。  
+3. 給付金額為保險單上所記載之「保險金額」的三倍，乘以手術日當年度之「增額係數」。  
+4. 同一次手術中，於同一手術位置接受二項以上手術項目時，僅給付一次意外住院手術醫療保險金。
+條文依據：  
+- [第十三條 意外住院手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 意外住院手術醫療保險金 | 第十一條 住院手術醫療保險金 | 第十五條 意外創傷縫合處置保險金 | 第二十條 除外責任（一） | 第十二條 門診手術醫療保險金 | 附表三：意外創傷縫合處置項目及給付倍數表 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F217" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外住院手術醫療保險金的給付規定如下：  
+1. 被保險人需於本契約有效期間內，且保險年齡未滿七十歲。  
+2. 因傷害經醫師診斷，在住院期間必須接受手術治療且已接受手術者。  
+3. 給付金額為保險單上所記載之「保險金額」的三倍，乘以手術日當年度之「增額係數」。  
+4. 同一次手術中，於同一手術位置接受二項以上手術項目時，僅給付一次意外住院手術醫療保險金。
+條文依據：  
+- [第十三條 意外住院手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="G217" s="2" t="inlineStr"/>
+      <c r="H217" s="2" t="inlineStr"/>
+      <c r="I217" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "意外住院手術醫療保險金的給付規定", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.99775, "neutral": 0.002043, "contradiction": 0.000207, "factuality": 0.999793, "C_fact": 0.999793}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J217" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K217" s="3" t="n">
+        <v>0.999793</v>
+      </c>
+      <c r="L217" s="3" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:22:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>特定處置保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+特定處置保險金的給付規定如下：  
+1. 被保險人需於保險契約有效期間內，因疾病或傷害經醫師診斷必須接受附表二所列的特定處置治療，且實際完成處置後，保險公司才會給付特定處置保險金。  
+2. 給付金額計算方式為：保險單上記載的「保險金額」× 特定處置日當年度的「增額係數」× 特定處置給付倍數。  
+3. 同一次處置治療中，若於同一治療位置接受兩項以上特定處置項目，僅給付特定處置給付倍數最高的項目。  
+4. 若接受的處置未列於附表二，保險公司不負給付責任。  
+5. 同一保險單年度內，特定處置保險金的給付次數以十次為限。
+條文依據：  
+- [第十四條 特定處置保險金]</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 特定處置保險金 | 第十五條 意外創傷縫合處置保險金 | 附表二：特定處置項目及給付倍數表 | 第五條 保險範圍 | 附表三：意外創傷縫合處置項目及給付倍數表</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F218" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+特定處置保險金的給付規定如下：  
+1. 被保險人需於保險契約有效期間內，因疾病或傷害經醫師診斷必須接受附表二所列的特定處置治療，且實際完成處置後，保險公司才會給付特定處置保險金。  
+2. 給付金額計算方式為：保險單上記載的「保險金額」× 特定處置日當年度的「增額係數」× 特定處置給付倍數。  
+3. 同一次處置治療中，若於同一治療位置接受兩項以上特定處置項目，僅給付特定處置給付倍數最高的項目。  
+4. 若接受的處置未列於附表二，保險公司不負給付責任。  
+5. 同一保險單年度內，特定處置保險金的給付次數以十次為限。
+條文依據：  
+- [第十四條 特定處置保險金]</t>
+        </is>
+      </c>
+      <c r="G218" s="2" t="inlineStr"/>
+      <c r="H218" s="2" t="inlineStr"/>
+      <c r="I218" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "特定處置保險金的給付規定", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.995824, "neutral": 0.003812, "contradiction": 0.000364, "factuality": 0.999636, "C_fact": 0.999636}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J218" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K218" s="3" t="n">
+        <v>0.999636</v>
+      </c>
+      <c r="L218" s="3" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:22:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>意外創傷縫合處置保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外創傷縫合處置保險金的給付規定如下：  
+1. 被保險人需於保險契約有效期間內，因意外傷害事故在醫院或診所接受附表三所列的意外創傷縫合處置治療。  
+2. 給付金額計算方式為：保險單所記載的「保險金額」× 當年度「增額係數」× 意外創傷縫合處置給付倍數。  
+3. 同一次意外傷害事故中，僅針對傷口最大者給付，且每次事故僅給付一次。  
+4. 若被保險人因同一意外傷害事故已申領「住院手術醫療保險金」或「門診手術醫療保險金」，則不再給付意外創傷縫合處置保險金。
+條文依據：  
+- [第十五條 意外創傷縫合處置保險金]</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
+        <is>
+          <t>第十五條 意外創傷縫合處置保險金 | 附表三：意外創傷縫合處置項目及給付倍數表 | 第十四條 特定處置保險金 | 第二十條 除外責任（一） | 第十三條 意外住院手術醫療保險金 | 附表二：特定處置項目及給付倍數表</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F219" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外創傷縫合處置保險金的給付規定如下：  
+1. 被保險人需於保險契約有效期間內，因意外傷害事故在醫院或診所接受附表三所列的意外創傷縫合處置治療。  
+2. 給付金額計算方式為：保險單所記載的「保險金額」× 當年度「增額係數」× 意外創傷縫合處置給付倍數。  
+3. 同一次意外傷害事故中，僅針對傷口最大者給付，且每次事故僅給付一次。  
+4. 若被保險人因同一意外傷害事故已申領「住院手術醫療保險金」或「門診手術醫療保險金」，則不再給付意外創傷縫合處置保險金。
+條文依據：  
+- [第十五條 意外創傷縫合處置保險金]</t>
+        </is>
+      </c>
+      <c r="G219" s="2" t="inlineStr"/>
+      <c r="H219" s="2" t="inlineStr"/>
+      <c r="I219" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "意外創傷縫合處置保險金的給付規定", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.99676, "neutral": 0.002981, "contradiction": 0.000259, "factuality": 0.999741, "C_fact": 0.999741}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J219" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K219" s="3" t="n">
+        <v>0.999741</v>
+      </c>
+      <c r="L219" s="3" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:22:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>醫療保險金給付總額之上限</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+醫療保險金給付總額之上限為保險單上所記載「保險金額」的一千五百倍，且不包含其他附約、附加條款或批註條款。
+條文依據：  
+- [第十六條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 醫療保險金給付總額之上限 | 第十二條 門診手術醫療保險金 | 第五條 保險範圍 | 第十一條 住院手術醫療保險金 | 第十三條 意外住院手術醫療保險金 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F220" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+醫療保險金給付總額之上限為保險單上所記載「保險金額」的一千五百倍，且不包含其他附約、附加條款或批註條款。
+條文依據：  
+- [第十六條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="G220" s="2" t="inlineStr"/>
+      <c r="H220" s="2" t="inlineStr"/>
+      <c r="I220" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "醫療保險金給付總額之上限", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.997158, "neutral": 0.002673, "contradiction": 0.000169, "factuality": 0.999831, "C_fact": 0.999831}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J220" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K220" s="3" t="n">
+        <v>0.999831</v>
+      </c>
+      <c r="L220" s="3" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:23:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>祝壽保險金的領取規定為何?金額多少？</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+祝壽保險金的領取規定如下：  
+1. 被保險人需於本契約有效期間內，且保險年齡到達99歲之保險單週年日仍生存。  
+2. 金額為「當年度保險金額」。  
+條文依據：  
+- [第十七條 祝壽保險金]</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
+        <is>
+          <t>第十七條 祝壽保險金 | 第二十六條 祝壽保險金的申領 | 第十一條至第十五條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | 第五條 保險範圍 | 第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F221" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+祝壽保險金的領取規定如下：  
+1. 被保險人需於本契約有效期間內，且保險年齡到達99歲之保險單週年日仍生存。  
+2. 金額為「當年度保險金額」。  
+條文依據：  
+- [第十七條 祝壽保險金]</t>
+        </is>
+      </c>
+      <c r="G221" s="2" t="inlineStr"/>
+      <c r="H221" s="2" t="inlineStr"/>
+      <c r="I221" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "祝壽保險金的領取規定為何?金額多少？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.998844, "neutral": 0.001026, "contradiction": 0.00013, "factuality": 0.99987, "C_fact": 0.99987}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J221" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K221" s="3" t="n">
+        <v>0.99987</v>
+      </c>
+      <c r="L221" s="3" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:23:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>身故時領取保險金有什麼規則?</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+身故時領取保險金的規則如下：  
+1. **一般規則**：被保險人於本契約有效期間內身故，本公司按「當年度保險金額」給付「身故保險金」。  
+2. **未滿十五足歲規則**：若被保險人於本契約有效期間且實際年齡未滿十五足歲身故，本公司僅退還「所繳保險費」，不適用一般規則。  
+3. **受益人規則**：受益人需依規定檢具相關文件（如保險單、死亡證明書等）申領保險金。若受益人同時或先於被保險人身故，則以被保險人之法定繼承人為受益人，並依民法繼承編相關規定分配保險金。  
+4. **除外責任**：若因要保人故意致被保險人於死、被保險人故意自殺（但契約訂立或復效後滿二年者除外）、被保險人因犯罪處死或拒捕或越獄致死，則本公司不負給付責任。若被保險人未滿十五足歲，則僅退還所繳保險費。  
+條文依據：  
+- [第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金]  
+- [第二十七條 身故保險金或喪葬費用保險金的申領]  
+- [第二十一條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金 | 第二十七條 身故保險金或喪葬費用保險金的申領 | 第十一條至第十五條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | 第二十一條 除外責任（二） | 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+身故時領取保險金的規則如下：  
+1. **一般規則**：被保險人於本契約有效期間內身故，本公司按「當年度保險金額」給付「身故保險金」。  
+2. **未滿十五足歲規則**：若被保險人於本契約有效期間且實際年齡未滿十五足歲身故，本公司僅退還「所繳保險費」，不適用一般規則。  
+3. **受益人規則**：受益人需依規定檢具相關文件（如保險單、死亡證明書等）申領保險金。若受益人同時或先於被保險人身故，則以被保險人之法定繼承人為受益人，並依民法繼承編相關規定分配保險金。  
+4. **除外責任**：若因要保人故意致被保險人於死、被保險人故意自殺（但契約訂立或復效後滿二年者除外）、被保險人因犯罪處死或拒捕或越獄致死，則本公司不負給付責任。若被保險人未滿十五足歲，則僅退還所繳保險費。  
+條文依據：  
+- [第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金]  
+- [第二十七條 身故保險金或喪葬費用保險金的申領]  
+- [第二十一條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="G222" s="2" t="inlineStr"/>
+      <c r="H222" s="2" t="inlineStr"/>
+      <c r="I222" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "身故時領取保險金有什麼規則?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.179641, "neutral": 0.803184, "contradiction": 0.017176, "factuality": 0.982824, "C_fact": 0.982824}, "C_conf": 0.9897}</t>
+        </is>
+      </c>
+      <c r="J222" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K222" s="3" t="n">
+        <v>0.982824</v>
+      </c>
+      <c r="L222" s="3" t="n">
+        <v>0.9897</v>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:24:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>什麼情況下可以保費折減?</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人年齡滿20歲（含）以上，並使用保險公司指定的程式加入健康計劃，且於「指定日期」的會員等級符合進階會員或菁英會員（或更高等級）標準之一者，可享次一保險單年度的保費折減。折減比例為進階會員2%，菁英會員或更高等級3%。但豁免或復效的保險費不適用此折減規定。此外，被保險人需完成程式註冊並授權保險公司取得健康相關電子紀錄，保險公司將依此計算會員等級。
+條文依據：  
+- [第十九條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 健康促進保險費折減 | 第三十條 保險金額之減少 | 第二十條 除外責任（一） | 第三十一條 投保年齡的計算及錯誤的處理 | 第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F223" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人年齡滿20歲（含）以上，並使用保險公司指定的程式加入健康計劃，且於「指定日期」的會員等級符合進階會員或菁英會員（或更高等級）標準之一者，可享次一保險單年度的保費折減。折減比例為進階會員2%，菁英會員或更高等級3%。但豁免或復效的保險費不適用此折減規定。此外，被保險人需完成程式註冊並授權保險公司取得健康相關電子紀錄，保險公司將依此計算會員等級。
+條文依據：  
+- [第十九條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="G223" s="2" t="inlineStr"/>
+      <c r="H223" s="2" t="inlineStr"/>
+      <c r="I223" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "什麼情況下可以保費折減?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.997054, "neutral": 0.002743, "contradiction": 0.000203, "factuality": 0.999797, "C_fact": 0.999797}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J223" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K223" s="3" t="n">
+        <v>0.999797</v>
+      </c>
+      <c r="L223" s="3" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:24:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>角膜切除術是否可以申請理賠?</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+角膜切除術可以申請理賠，其對應的手術項目代碼為1305，給付倍數為5。
+條文依據：  
+- 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t>附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F224" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+角膜切除術可以申請理賠，其對應的手術項目代碼為1305，給付倍數為5。
+條文依據：  
+- 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="G224" s="2" t="inlineStr"/>
+      <c r="H224" s="2" t="inlineStr"/>
+      <c r="I224" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "角膜切除術是否可以申請理賠?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.982618, "neutral": 0.016151, "contradiction": 0.001231, "factuality": 0.998769, "C_fact": 0.998769}, "C_conf": 0.9993}</t>
+        </is>
+      </c>
+      <c r="J224" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K224" s="3" t="n">
+        <v>0.998769</v>
+      </c>
+      <c r="L224" s="3" t="n">
+        <v>0.9993</v>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:24:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>白內障手術是否可以申請理賠?膜性白內障切開術、白內障線狀摘出術或白內障切囊術</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+白內障相關手術如膜性白內障切開術、白內障線狀摘出術及白內障切囊術均可申請理賠，且其給付倍數分別為5倍、5倍及5倍。
+條文依據：  
+- [附表一：手術項目與給付倍數]</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
+        <is>
+          <t>附表一：手術項目與給付倍數 | payout_items | 附表二：特定處置項目及給付倍數表</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F225" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+白內障相關手術如膜性白內障切開術、白內障線狀摘出術及白內障切囊術均可申請理賠，且其給付倍數分別為5倍、5倍及5倍。
+條文依據：  
+- [附表一：手術項目與給付倍數]</t>
+        </is>
+      </c>
+      <c r="G225" s="2" t="inlineStr"/>
+      <c r="H225" s="2" t="inlineStr"/>
+      <c r="I225" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "白內障手術是否可以申請理賠?膜性白內障切開術、白內障線狀摘出術或白內障切囊術", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.98948, "neutral": 0.008819, "contradiction": 0.001701, "factuality": 0.998299, "C_fact": 0.998299}, "C_conf": 0.999}</t>
+        </is>
+      </c>
+      <c r="J225" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K225" s="3" t="n">
+        <v>0.998299</v>
+      </c>
+      <c r="L225" s="3" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:24:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>保障範圍包括哪些項目？</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括：意外事故身故保險金或喪葬費用保險金、意外事故失能保險金、每月生活照護保險金、重大燒燙傷保險金、意外骨折保險金、傷害醫療日額保險金、意外創傷縫合處置保險金。
+條文依據：  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
+        <is>
+          <t>payout_items | 第五條 保險範圍 | 第十五條 每月生活照護保險金的給付 | 第三十條 不保事項 | 附表二：失能程度與保險金給付表</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F226" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括：意外事故身故保險金或喪葬費用保險金、意外事故失能保險金、每月生活照護保險金、重大燒燙傷保險金、意外骨折保險金、傷害醫療日額保險金、意外創傷縫合處置保險金。
+條文依據：  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="G226" s="2" t="inlineStr"/>
+      <c r="H226" s="2" t="inlineStr"/>
+      <c r="I226" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "保障範圍包括哪些項目？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.997935, "neutral": 0.001907, "contradiction": 0.000158, "factuality": 0.999842, "C_fact": 0.999842}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J226" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K226" s="3" t="n">
+        <v>0.999842</v>
+      </c>
+      <c r="L226" s="3" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:25:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>發生意外事故身故，理賠內容為何?</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外事故身故的理賠內容如下：  
+1. 若被保險人於意外傷害事故發生之日起 180 日內身故，本公司將依意外傷害事故的種類給付以下金額：  
+   - 一般意外傷害事故：「傷害醫療保險金日額」的 500 倍。  
+   - 特定意外傷害事故：「傷害醫療保險金日額」的 1000 倍。  
+2. 若被保險人於意外傷害事故發生後超過 180 日身故，但受益人能證明身故與該意外傷害事故具有因果關係，本公司仍依上述金額給付。  
+3. 若被保險人於訂立契約時為受監護宣告尚未撤銷者，其「意外事故身故保險金」將變更為「喪葬費用保險金」。  
+4. 喪葬費用保險金的給付有上限，若超過《遺產及贈與稅法》第十七條規定的喪葬費扣除額之半數，超過部分本公司不負給付責任，並退還超過部分的已繳保險費。  
+條文依據：  
+- [第十二條 意外事故身故保險金或喪葬費用保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 意外事故身故保險金或喪葬費用保險金的給付 | 第十四條 保險給付的限制 | payout_items | 第十一條 契約的終止（二） | 第二十一條 失蹤處理</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F227" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外事故身故的理賠內容如下：  
+1. 若被保險人於意外傷害事故發生之日起 180 日內身故，本公司將依意外傷害事故的種類給付以下金額：  
+   - 一般意外傷害事故：「傷害醫療保險金日額」的 500 倍。  
+   - 特定意外傷害事故：「傷害醫療保險金日額」的 1000 倍。  
+2. 若被保險人於意外傷害事故發生後超過 180 日身故，但受益人能證明身故與該意外傷害事故具有因果關係，本公司仍依上述金額給付。  
+3. 若被保險人於訂立契約時為受監護宣告尚未撤銷者，其「意外事故身故保險金」將變更為「喪葬費用保險金」。  
+4. 喪葬費用保險金的給付有上限，若超過《遺產及贈與稅法》第十七條規定的喪葬費扣除額之半數，超過部分本公司不負給付責任，並退還超過部分的已繳保險費。  
+條文依據：  
+- [第十二條 意外事故身故保險金或喪葬費用保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G227" s="2" t="inlineStr"/>
+      <c r="H227" s="2" t="inlineStr"/>
+      <c r="I227" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "發生意外事故身故，理賠內容為何?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.478858, "neutral": 0.505499, "contradiction": 0.015643, "factuality": 0.984357, "C_fact": 0.984357}, "C_conf": 0.9906}</t>
+        </is>
+      </c>
+      <c r="J227" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K227" s="3" t="n">
+        <v>0.984357</v>
+      </c>
+      <c r="L227" s="3" t="n">
+        <v>0.9906</v>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:25:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>意外事故失能保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外事故失能保險金的給付條件如下：  
+1. 被保險人於契約有效期間內遭受「意外傷害事故」，並自事故發生之日起一百八十日內致成附表二所列失能程度之一者，本公司依事故種類及失能程度，按以下方式計算給付金額：  
+   - 一般意外傷害事故：「傷害醫療保險金日額」的五百倍乘以附表二給付比例。  
+   - 特定意外傷害事故：「傷害醫療保險金日額」的一千倍乘以附表二給付比例。  
+2. 若超過一百八十日致成失能，但受益人能證明失能與事故具有因果關係者，仍可申請給付，不受一百八十日限制。  
+3. 同一事故導致多項失能時，僅給付同一手或同一足中較嚴重項目的失能保險金，且總金額以事故種類的上限為限：  
+   - 一般意外傷害事故：「傷害醫療保險金日額」的五百倍。  
+   - 特定意外傷害事故：「傷害醫療保險金日額」的一千倍。  
+4. 不同事故導致的失能，累計給付金額最高以「傷害醫療保險金日額」的一千二百倍為限。  
+條文依據：  
+- [第十三條 意外事故失能保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 意外事故失能保險金的給付 | 第十五條 每月生活照護保險金的給付 | 第十四條 保險給付的限制 | 第十二條 意外事故身故保險金或喪葬費用保險金的給付 | 第二十三條 意外事故失能保險金的申領 | 附表二：失能程度與保險金給付表</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F228" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外事故失能保險金的給付條件如下：  
+1. 被保險人於契約有效期間內遭受「意外傷害事故」，並自事故發生之日起一百八十日內致成附表二所列失能程度之一者，本公司依事故種類及失能程度，按以下方式計算給付金額：  
+   - 一般意外傷害事故：「傷害醫療保險金日額」的五百倍乘以附表二給付比例。  
+   - 特定意外傷害事故：「傷害醫療保險金日額」的一千倍乘以附表二給付比例。  
+2. 若超過一百八十日致成失能，但受益人能證明失能與事故具有因果關係者，仍可申請給付，不受一百八十日限制。  
+3. 同一事故導致多項失能時，僅給付同一手或同一足中較嚴重項目的失能保險金，且總金額以事故種類的上限為限：  
+   - 一般意外傷害事故：「傷害醫療保險金日額」的五百倍。  
+   - 特定意外傷害事故：「傷害醫療保險金日額」的一千倍。  
+4. 不同事故導致的失能，累計給付金額最高以「傷害醫療保險金日額」的一千二百倍為限。  
+條文依據：  
+- [第十三條 意外事故失能保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G228" s="2" t="inlineStr"/>
+      <c r="H228" s="2" t="inlineStr"/>
+      <c r="I228" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "意外事故失能保險金的給付為何?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.276839, "neutral": 0.700215, "contradiction": 0.022946, "factuality": 0.977054, "C_fact": 0.977054}, "C_conf": 0.9862}</t>
+        </is>
+      </c>
+      <c r="J228" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K228" s="3" t="n">
+        <v>0.977054</v>
+      </c>
+      <c r="L228" s="3" t="n">
+        <v>0.9862</v>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:25:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>每月生活照護保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+每月生活照護保險金的給付條件如下：  
+1. 被保險人於保險契約有效期間內因「意外傷害事故」，自事故發生之日起180日內，致成附表二所列第1級至第6級失能程度之一時，本公司自失能診斷確定當日起，按「傷害醫療保險金日額」的20倍乘以附表二給付比例所得之金額，按月給付，最多給付12個月。  
+2. 若於該失能的前四個「失能診斷確定週年日」，契約仍有效且被保險人仍生存，本公司自各該週年日起，按相同方式再給付，最多給付12個月。  
+3. 若被保險人自事故發生之日起超過180日才致成失能，但能證明失能與該事故具有因果關係者，仍可依上述規定給付，不受180日限制。  
+4. 同一事故若致成多項失能，僅給付一項較嚴重失能的保險金，且最高以「傷害醫療保險金日額」的20倍為限。  
+5. 累計給付金額最高以「傷害醫療保險金日額」的1200倍為限。  
+條文依據：  
+- [第十五條 每月生活照護保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
+        <is>
+          <t>第二十四條 每月生活照護保險金的申領 | 第十五條 每月生活照護保險金的給付 | payout_items | 第十八條 傷害醫療日額保險金的給付 | 第五條 保險範圍 | 附表二：失能程度與保險金給付表 | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F229" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+每月生活照護保險金的給付條件如下：  
+1. 被保險人於保險契約有效期間內因「意外傷害事故」，自事故發生之日起180日內，致成附表二所列第1級至第6級失能程度之一時，本公司自失能診斷確定當日起，按「傷害醫療保險金日額」的20倍乘以附表二給付比例所得之金額，按月給付，最多給付12個月。  
+2. 若於該失能的前四個「失能診斷確定週年日」，契約仍有效且被保險人仍生存，本公司自各該週年日起，按相同方式再給付，最多給付12個月。  
+3. 若被保險人自事故發生之日起超過180日才致成失能，但能證明失能與該事故具有因果關係者，仍可依上述規定給付，不受180日限制。  
+4. 同一事故若致成多項失能，僅給付一項較嚴重失能的保險金，且最高以「傷害醫療保險金日額」的20倍為限。  
+5. 累計給付金額最高以「傷害醫療保險金日額」的1200倍為限。  
+條文依據：  
+- [第十五條 每月生活照護保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G229" s="2" t="inlineStr"/>
+      <c r="H229" s="2" t="inlineStr"/>
+      <c r="I229" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "每月生活照護保險金的給付為何?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.276295, "neutral": 0.699699, "contradiction": 0.024006, "factuality": 0.975994, "C_fact": 0.975994}, "C_conf": 0.9855}</t>
+        </is>
+      </c>
+      <c r="J229" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K229" s="3" t="n">
+        <v>0.975994</v>
+      </c>
+      <c r="L229" s="3" t="n">
+        <v>0.9855</v>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:26:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>重大燒燙傷保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+重大燒燙傷保險金的給付條件為：被保險人於保險契約有效期間內，因「意外傷害事故」導致燒燙傷，且經診斷符合「重大燒燙傷」的定義時，本公司將按「傷害醫療保險金日額」的二百五十倍給付「重大燒燙傷保險金」。該保險金的給付以一次為限。
+條文依據：  
+- [第十六條 重大燒燙傷保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 重大燒燙傷保險金的給付 | 第二十五條 重大燒燙傷保險金的申領 | 第五條 保險範圍 | payout_items | 第二十九條 除外責任（原因）</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F230" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+重大燒燙傷保險金的給付條件為：被保險人於保險契約有效期間內，因「意外傷害事故」導致燒燙傷，且經診斷符合「重大燒燙傷」的定義時，本公司將按「傷害醫療保險金日額」的二百五十倍給付「重大燒燙傷保險金」。該保險金的給付以一次為限。
+條文依據：  
+- [第十六條 重大燒燙傷保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G230" s="2" t="inlineStr"/>
+      <c r="H230" s="2" t="inlineStr"/>
+      <c r="I230" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "重大燒燙傷保險金的給付為何?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.997132, "neutral": 0.002738, "contradiction": 0.00013, "factuality": 0.99987, "C_fact": 0.99987}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J230" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K230" s="3" t="n">
+        <v>0.99987</v>
+      </c>
+      <c r="L230" s="3" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:26:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>意外骨折保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外骨折保險金的給付條件如下：  
+1. 被保險人於契約有效期間內遭受「意外傷害事故」，並於事故發生後180日內經合格醫院或診所診斷為附表三骨折別表所列骨折項目之一（含不完全骨折及骨骼龜裂），本公司按「傷害醫療保險金日額」的二倍給付意外骨折保險金。  
+2. 若超過180日診斷確定骨折，受益人需證明骨折與該意外傷害事故具有因果關係，仍可依上述規定給付。  
+3. 同一意外傷害事故僅給付一次意外骨折保險金。  
+4. 若骨折不屬於附表三骨折別表所列項目，需由本公司與被保險人協議核付；但若骨折為骨折別表內明訂不給付之部位，則不負給付責任。
+條文依據：  
+- [第十七條 意外骨折保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
+        <is>
+          <t>第十七條 意外骨折保險金的給付 | 第十八條 傷害醫療日額保險金的給付 | 第二十六條 意外骨折保險金的申領 | 第十三條 意外事故失能保險金的給付 | 第十九條 意外創傷縫合處置保險金的給付 | 附表二：失能程度與保險金給付表 | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F231" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外骨折保險金的給付條件如下：  
+1. 被保險人於契約有效期間內遭受「意外傷害事故」，並於事故發生後180日內經合格醫院或診所診斷為附表三骨折別表所列骨折項目之一（含不完全骨折及骨骼龜裂），本公司按「傷害醫療保險金日額」的二倍給付意外骨折保險金。  
+2. 若超過180日診斷確定骨折，受益人需證明骨折與該意外傷害事故具有因果關係，仍可依上述規定給付。  
+3. 同一意外傷害事故僅給付一次意外骨折保險金。  
+4. 若骨折不屬於附表三骨折別表所列項目，需由本公司與被保險人協議核付；但若骨折為骨折別表內明訂不給付之部位，則不負給付責任。
+條文依據：  
+- [第十七條 意外骨折保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G231" s="2" t="inlineStr"/>
+      <c r="H231" s="2" t="inlineStr"/>
+      <c r="I231" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "意外骨折保險金的給付為何?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.994624, "neutral": 0.004998, "contradiction": 0.000378, "factuality": 0.999622, "C_fact": 0.999622}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J231" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K231" s="3" t="n">
+        <v>0.999622</v>
+      </c>
+      <c r="L231" s="3" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:26:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>傷害醫療日額保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+傷害醫療日額保險金的給付條件如下：  
+1. 被保險人於保險契約有效期間內因「意外傷害事故」住院治療，且住院日數在意外發生後 180 日內，本公司按「傷害醫療保險金日額」乘以實際住院日數給付，但每次事故最高給付日數為 90 日。  
+2. 若治療超過 180 日，受益人需證明治療與該意外事故具因果關係，本公司仍依上述規定給付，不受 180 日限制。  
+3. 若因意外事故骨折但未住院，或住院日數未達附表三骨折別表所訂日數，則按骨折別表所訂日數乘以「傷害醫療保險金日額」的二分之一給付，合計給付日數以骨折別表所訂日數為上限。  
+4. 骨折類型的給付：  
+   - 完全骨折按骨折別表所訂日數給付。  
+   - 不完全骨折按完全骨折日數的二分之一給付。  
+   - 骨骼龜裂按完全骨折日數的四分之一給付。  
+5. 同時發生多項骨折時，僅給付一項較高等級的「傷害醫療日額保險金」。
+條文依據：  
+- [第十八條 傷害醫療日額保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 傷害醫療日額保險金的給付 | 第二十七條 傷害醫療日額保險金的申領 | 第十五條 每月生活照護保險金的給付 | 第三十四條 傷害醫療保險金日額之減少 | 第十九條 意外創傷縫合處置保險金的給付 | 附表二：失能程度與保險金給付表 | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F232" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+傷害醫療日額保險金的給付條件如下：  
+1. 被保險人於保險契約有效期間內因「意外傷害事故」住院治療，且住院日數在意外發生後 180 日內，本公司按「傷害醫療保險金日額」乘以實際住院日數給付，但每次事故最高給付日數為 90 日。  
+2. 若治療超過 180 日，受益人需證明治療與該意外事故具因果關係，本公司仍依上述規定給付，不受 180 日限制。  
+3. 若因意外事故骨折但未住院，或住院日數未達附表三骨折別表所訂日數，則按骨折別表所訂日數乘以「傷害醫療保險金日額」的二分之一給付，合計給付日數以骨折別表所訂日數為上限。  
+4. 骨折類型的給付：  
+   - 完全骨折按骨折別表所訂日數給付。  
+   - 不完全骨折按完全骨折日數的二分之一給付。  
+   - 骨骼龜裂按完全骨折日數的四分之一給付。  
+5. 同時發生多項骨折時，僅給付一項較高等級的「傷害醫療日額保險金」。
+條文依據：  
+- [第十八條 傷害醫療日額保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G232" s="2" t="inlineStr"/>
+      <c r="H232" s="2" t="inlineStr"/>
+      <c r="I232" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "傷害醫療日額保險金的給付為何?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.961568, "neutral": 0.036602, "contradiction": 0.00183, "factuality": 0.99817, "C_fact": 0.99817}, "C_conf": 0.9989}</t>
+        </is>
+      </c>
+      <c r="J232" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K232" s="3" t="n">
+        <v>0.99817</v>
+      </c>
+      <c r="L232" s="3" t="n">
+        <v>0.9989</v>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:27:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>意外創傷縫合處置保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外創傷縫合處置保險金的給付條件為：被保險人於保險契約有效期間內，因遭受「意外傷害事故」，在「醫院」或「診所」經醫師診斷必須接受創傷縫合處置治療，且已完成縫合處置者，本公司將按「傷害醫療保險金日額」給付「意外創傷縫合處置保險金」。同一意外傷害事故僅給付一次。
+條文依據：  
+- [第十九條 意外創傷縫合處置保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 意外創傷縫合處置保險金的給付 | 第二十八條 意外創傷縫合處置保險金的申領 | 第五條 保險範圍 | 第十七條 意外骨折保險金的給付 | payout_items | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F233" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外創傷縫合處置保險金的給付條件為：被保險人於保險契約有效期間內，因遭受「意外傷害事故」，在「醫院」或「診所」經醫師診斷必須接受創傷縫合處置治療，且已完成縫合處置者，本公司將按「傷害醫療保險金日額」給付「意外創傷縫合處置保險金」。同一意外傷害事故僅給付一次。
+條文依據：  
+- [第十九條 意外創傷縫合處置保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G233" s="2" t="inlineStr"/>
+      <c r="H233" s="2" t="inlineStr"/>
+      <c r="I233" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "意外創傷縫合處置保險金的給付為何?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.996869, "neutral": 0.003014, "contradiction": 0.000117, "factuality": 0.999883, "C_fact": 0.999883}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J233" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K233" s="3" t="n">
+        <v>0.999883</v>
+      </c>
+      <c r="L233" s="3" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:27:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>因意外導致視力衰退，是否能申請理賠?</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以申請理賠，但需符合以下條件：視力永久在萬國式視力表0.02以下，或符合其他視力障害的判定標準（如眼球喪失、僅能辨明暗等）。此外，需經過六個月的治療後判定為永久性視力障害，但若為眼球摘出等明顯無法復原的情況，則不受六個月治療期限制。
+條文依據：  
+- 註2</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
+        <is>
+          <t>第二十三條 意外事故失能保險金的申領 | 第十三條 意外事故失能保險金的給付 | 註2： | 第三十條 不保事項 | 第二十六條 意外骨折保險金的申領 | 附表二：失能程度與保險金給付表</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F234" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以申請理賠，但需符合以下條件：視力永久在萬國式視力表0.02以下，或符合其他視力障害的判定標準（如眼球喪失、僅能辨明暗等）。此外，需經過六個月的治療後判定為永久性視力障害，但若為眼球摘出等明顯無法復原的情況，則不受六個月治療期限制。
+條文依據：  
+- 註2</t>
+        </is>
+      </c>
+      <c r="G234" s="2" t="inlineStr"/>
+      <c r="H234" s="2" t="inlineStr"/>
+      <c r="I234" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "因意外導致視力衰退，是否能申請理賠?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.581273, "neutral": 0.224533, "contradiction": 0.194194, "factuality": 0.805806, "C_fact": 0.805806}, "C_conf": 0.8785}</t>
+        </is>
+      </c>
+      <c r="J234" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K234" s="3" t="n">
+        <v>0.805806</v>
+      </c>
+      <c r="L234" s="3" t="n">
+        <v>0.8784999999999999</v>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:27:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>肋骨骨折是否可以申請理賠?理賠金額為多少?包含傷害醫療保險金日額跟意外骨折保險金嗎？</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+肋骨骨折可以申請理賠，理賠金額需依保單約定的「傷害醫療保險金日額」計算，並可能包含「傷害醫療日額保險金」及「意外骨折保險金」。  
+1. **傷害醫療日額保險金**：若因肋骨骨折住院治療，按實際住院日數乘以「傷害醫療保險金日額」給付，最高以90日為限；若未住院，則按附表三所訂肋骨完全骨折日數（20天）乘以「傷害醫療保險金日額」的二分之一給付。  
+2. **意外骨折保險金**：肋骨骨折屬於附表三骨折別表所列項目，若經診斷確定，按「傷害醫療保險金日額」的二倍給付一次性「意外骨折保險金」。  
+條文依據：  
+- [第十八條 傷害醫療日額保險金的給付]  
+- [第十七條 意外骨折保險金的給付]  
+- [附表三：骨折別表]</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 傷害醫療日額保險金的給付 | 第十七條 意外骨折保險金的給付 | 第二十六條 意外骨折保險金的申領 | payout_items | 第二十七條 傷害醫療日額保險金的申領 | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F235" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+肋骨骨折可以申請理賠，理賠金額需依保單約定的「傷害醫療保險金日額」計算，並可能包含「傷害醫療日額保險金」及「意外骨折保險金」。  
+1. **傷害醫療日額保險金**：若因肋骨骨折住院治療，按實際住院日數乘以「傷害醫療保險金日額」給付，最高以90日為限；若未住院，則按附表三所訂肋骨完全骨折日數（20天）乘以「傷害醫療保險金日額」的二分之一給付。  
+2. **意外骨折保險金**：肋骨骨折屬於附表三骨折別表所列項目，若經診斷確定，按「傷害醫療保險金日額」的二倍給付一次性「意外骨折保險金」。  
+條文依據：  
+- [第十八條 傷害醫療日額保險金的給付]  
+- [第十七條 意外骨折保險金的給付]  
+- [附表三：骨折別表]</t>
+        </is>
+      </c>
+      <c r="G235" s="2" t="inlineStr"/>
+      <c r="H235" s="2" t="inlineStr"/>
+      <c r="I235" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "肋骨骨折是否可以申請理賠?理賠金額為多少?包含傷害醫療保險金日額跟意外骨折保險金嗎？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.95951, "neutral": 0.036802, "contradiction": 0.003688, "factuality": 0.996312, "C_fact": 0.996312}, "C_conf": 0.9978}</t>
+        </is>
+      </c>
+      <c r="J235" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K235" s="3" t="n">
+        <v>0.996312</v>
+      </c>
+      <c r="L235" s="3" t="n">
+        <v>0.9978</v>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:28:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>投保新鍾心滿福後，假設投保保額為100萬元，於第二保單年度接受「移植器官」，這樣可以領多少重大傷病保險金及特定重大傷病保險金?</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 新鍾心滿福保單涵蓋重大傷病保險金及特定重大傷病保險金。  
+2. 器官移植屬於「重大傷病範圍」及「特定重大傷病」的給付條件，符合保險金給付資格。  
+3. 在第二保單年度，重大傷病保險金的計算方式為「保險金額」或「年繳應繳保險費總額的一點零五倍」，二者取其大者；特定重大傷病保險金則為「保險金額的百分之二十」。  
+4. 若投保保額為100萬元，重大傷病保險金為100萬元（假設此金額大於年繳應繳保險費總額的一點零五倍），特定重大傷病保險金為20萬元（100萬元的20%）。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第十三條 特定重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 特定重大傷病保險金的給付 | 第十二條 重大傷病保險金的給付 | 附表一：全民健康保險重大傷病項目 | payout_items | 第二條 名詞定義 | 附表二：完全失能程度表</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F236" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 新鍾心滿福保單涵蓋重大傷病保險金及特定重大傷病保險金。  
+2. 器官移植屬於「重大傷病範圍」及「特定重大傷病」的給付條件，符合保險金給付資格。  
+3. 在第二保單年度，重大傷病保險金的計算方式為「保險金額」或「年繳應繳保險費總額的一點零五倍」，二者取其大者；特定重大傷病保險金則為「保險金額的百分之二十」。  
+4. 若投保保額為100萬元，重大傷病保險金為100萬元（假設此金額大於年繳應繳保險費總額的一點零五倍），特定重大傷病保險金為20萬元（100萬元的20%）。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第十三條 特定重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G236" s="2" t="inlineStr"/>
+      <c r="H236" s="2" t="inlineStr"/>
+      <c r="I236" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認新鍾心滿福保單是否涵蓋重大傷病保險金及特定重大傷病保險金", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認重大傷病保險金及特定重大傷病保險金的給付條件是否包含器官移植", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認保單第二年度的保障範圍及保額計算方式", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認投保保額100萬元對應的重大傷病保險金及特定重大傷病保險金給付比例", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.085837, "neutral": 0.909835, "contradiction": 0.004328, "factuality": 0.995672, "C_fact": 0.995672}, "C_conf": 0.9974}</t>
+        </is>
+      </c>
+      <c r="J236" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K236" s="3" t="n">
+        <v>0.995672</v>
+      </c>
+      <c r="L236" s="3" t="n">
+        <v>0.9974</v>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:28:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>投保新鍾心滿福後，若要理賠重大傷病保險金，一定要檢附全民健保開立的重大傷病證明才能拿到保險金嗎?</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 新鍾心滿福保單包含重大傷病保險金保障，依條款第二條名詞定義及第十二條重大傷病保險金的給付內容，若被保險人於契約有效期間內經醫師診斷確定罹患符合「重大傷病範圍」的項目，即可申請理賠。  
+2. 理賠重大傷病保險金時，通常需要檢附全民健保開立的重大傷病證明，但條款中也明確說明，若被保險人已取得一家「區域醫院」層級以上（含）之醫療院所開立的診斷書及病歷摘要，且符合投保當時「重大傷病範圍」，則可視為重大傷病證明文件，無需另行申請全民健保的重大傷病證明。  
+3. 若因特殊情況無法取得全民健保重大傷病證明，條款第二十二條也列出其他可替代的文件，例如由區域醫院層級以上醫療院所開立的診斷書及病歷摘要，或其他符合條件的醫療費用收據等。
+條文依據：  
+- [第二條 名詞定義]  
+- [第十二條 重大傷病保險金的給付]  
+- [第二十二條 重大傷病保險金、特定重大傷病保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
+        <is>
+          <t>第二十二條 重大傷病保險金、特定重大傷病保險金的申領 | other_metadata | 第十二條 重大傷病保險金的給付 | 附表一：全民健康保險重大傷病項目 | 第二條 名詞定義 | 第三十條 不保事項</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F237" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 新鍾心滿福保單包含重大傷病保險金保障，依條款第二條名詞定義及第十二條重大傷病保險金的給付內容，若被保險人於契約有效期間內經醫師診斷確定罹患符合「重大傷病範圍」的項目，即可申請理賠。  
+2. 理賠重大傷病保險金時，通常需要檢附全民健保開立的重大傷病證明，但條款中也明確說明，若被保險人已取得一家「區域醫院」層級以上（含）之醫療院所開立的診斷書及病歷摘要，且符合投保當時「重大傷病範圍」，則可視為重大傷病證明文件，無需另行申請全民健保的重大傷病證明。  
+3. 若因特殊情況無法取得全民健保重大傷病證明，條款第二十二條也列出其他可替代的文件，例如由區域醫院層級以上醫療院所開立的診斷書及病歷摘要，或其他符合條件的醫療費用收據等。
+條文依據：  
+- [第二條 名詞定義]  
+- [第十二條 重大傷病保險金的給付]  
+- [第二十二條 重大傷病保險金、特定重大傷病保險金的申領]</t>
+        </is>
+      </c>
+      <c r="G237" s="2" t="inlineStr"/>
+      <c r="H237" s="2" t="inlineStr"/>
+      <c r="I237" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認新鍾心滿福保單是否包含重大傷病保險金保障", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認理賠重大傷病保險金是否需要檢附全民健保開立的重大傷病證明", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認是否有其他文件可替代重大傷病證明進行理賠", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.001993, "neutral": 0.997304, "contradiction": 0.000703, "factuality": 0.999297, "C_fact": 0.999297}, "C_conf": 0.9996}</t>
+        </is>
+      </c>
+      <c r="J237" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K237" s="3" t="n">
+        <v>0.999297</v>
+      </c>
+      <c r="L237" s="3" t="n">
+        <v>0.9996</v>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:29:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>要有健保身分才能申請重大傷病理賠嗎？</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+是的，若被保險人喪失全民健康保險被保險人資格，需先重新申請加入全民健康保險後，才能申請重大傷病保險金的給付。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
+        <is>
+          <t>第二十二條 重大傷病保險金、特定重大傷病保險金的申領 | 第十二條 重大傷病保險金的給付 | 第三十條 不保事項 | other_metadata | 第二條 名詞定義 | 附表一：全民健康保險重大傷病項目</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F238" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+是的，若被保險人喪失全民健康保險被保險人資格，需先重新申請加入全民健康保險後，才能申請重大傷病保險金的給付。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G238" s="2" t="inlineStr"/>
+      <c r="H238" s="2" t="inlineStr"/>
+      <c r="I238" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "要有健保身分才能申請重大傷病理賠嗎？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.95729, "neutral": 0.03243, "contradiction": 0.01028, "factuality": 0.98972, "C_fact": 0.98972}, "C_conf": 0.9938}</t>
+        </is>
+      </c>
+      <c r="J238" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K238" s="3" t="n">
+        <v>0.98972</v>
+      </c>
+      <c r="L238" s="3" t="n">
+        <v>0.9938</v>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:30:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>重大傷病的項目如果在投保後有新增，可以從優申請理賠嗎？</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以從優申請理賠，若重大傷病項目於保險契約有效期間內新增，則以中央衛生主管機關最新公告的重大傷病項目為準，並適用於被保險人於有效期間內診斷確定的情形。
+條文依據：  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
+        <is>
+          <t>附表一：全民健康保險重大傷病項目 | 第二條 名詞定義 | payout_items</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F239" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以從優申請理賠，若重大傷病項目於保險契約有效期間內新增，則以中央衛生主管機關最新公告的重大傷病項目為準，並適用於被保險人於有效期間內診斷確定的情形。
+條文依據：  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G239" s="2" t="inlineStr"/>
+      <c r="H239" s="2" t="inlineStr"/>
+      <c r="I239" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "重大傷病的項目如果在投保後有新增，可以從優申請理賠嗎？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.991747, "neutral": 0.007498, "contradiction": 0.000754, "factuality": 0.999246, "C_fact": 0.999246}, "C_conf": 0.9995}</t>
+        </is>
+      </c>
+      <c r="J239" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K239" s="3" t="n">
+        <v>0.999246</v>
+      </c>
+      <c r="L239" s="3" t="n">
+        <v>0.9995000000000001</v>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:30:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>我的保單之前有停效，在復效後五天被診斷出重大疾病是否可申請理賠？</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若保單已成功復效，且重大疾病屬於保單保障範圍內，則需確認復效後是否有等待期規定。根據條款，重大疾病的理賠需在等待期間屆滿翌日或復效日起的有效期間內診斷確定。若重大疾病因意外傷害事故所致，則不受等待期間限制。若非因意外傷害事故，則需確認等待期間是否已過。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
+        <is>
+          <t>第八條 本契約效力的恢復 | 第三十條 不保事項 | 第五條 保險範圍 | other_metadata | 第二條 名詞定義 | 第十二條 重大傷病保險金的給付 | 第二十二條 重大傷病保險金、特定重大傷病保險金的申領 | 附表一：全民健康保險重大傷病項目</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F240" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若保單已成功復效，且重大疾病屬於保單保障範圍內，則需確認復效後是否有等待期規定。根據條款，重大疾病的理賠需在等待期間屆滿翌日或復效日起的有效期間內診斷確定。若重大疾病因意外傷害事故所致，則不受等待期間限制。若非因意外傷害事故，則需確認等待期間是否已過。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G240" s="2" t="inlineStr"/>
+      <c r="H240" s="2" t="inlineStr"/>
+      <c r="I240" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認保單是否已成功復效", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認重大疾病是否在保單保障範圍內", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認復效後是否有等待期規定及其影響", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認診斷重大疾病的日期是否符合理賠條件", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.952181, "neutral": 0.041534, "contradiction": 0.006285, "factuality": 0.993715, "C_fact": 0.993715}, "C_conf": 0.9962}</t>
+        </is>
+      </c>
+      <c r="J240" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K240" s="3" t="n">
+        <v>0.993715</v>
+      </c>
+      <c r="L240" s="3" t="n">
+        <v>0.9962</v>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:31:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>領完重大傷病保險金，主約終止後，附約可以繼續有效嗎?</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以。根據條款規定，若因重大傷病診斷確定而導致主約終止時，要保人仍可於附約有效期間內繼續繳交附約保險費，以延續附約效力。
+條文依據：  
+- [第十一條 契約的終止（二）]</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 契約的終止（二） | 第十二條 重大傷病保險金的給付 | 第三十條 不保事項 | 第五條 保險範圍 | payout_items | 附表一：全民健康保險重大傷病項目</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F241" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以。根據條款規定，若因重大傷病診斷確定而導致主約終止時，要保人仍可於附約有效期間內繼續繳交附約保險費，以延續附約效力。
+條文依據：  
+- [第十一條 契約的終止（二）]</t>
+        </is>
+      </c>
+      <c r="G241" s="2" t="inlineStr"/>
+      <c r="H241" s="2" t="inlineStr"/>
+      <c r="I241" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "領完重大傷病保險金，主約終止後，附約可以繼續有效嗎?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.996247, "neutral": 0.003631, "contradiction": 0.000122, "factuality": 0.999878, "C_fact": 0.999878}, "C_conf": 0.9999}</t>
+        </is>
+      </c>
+      <c r="J241" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K241" s="3" t="n">
+        <v>0.999878</v>
+      </c>
+      <c r="L241" s="3" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:31:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>Q1：因為慢性精神病的保險給付僅有保額的20%，我可以先不申請給付，等之後發生其他重大傷病後，再申請重大傷病保險金嗎?Q2：但如果我不申請，保險公司不會知道我有罹患慢性精神病阿，所以我就可以領之後的重大傷病100%保額嗎?</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+Q1：慢性精神病的保險給付比例為保額的20%，但若選擇延後申請，並不會影響未來其他重大傷病保險金的申請資格或保額。條款中未限制延後申請的權利，且未提及延後申請會影響其他重大傷病的給付。  
+Q2：保險公司是否知情取決於被保險人是否提供相關診斷資料，但條款中未提及未申請慢性精神病給付會影響未來重大傷病保險金的給付比例。若未來罹患其他重大傷病，符合條件時仍可依條款規定申請100%保額的重大傷病保險金。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第十三條 特定重大傷病保險金的給付]  
+- [第二十二條 重大傷病保險金、特定重大傷病保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 重大傷病保險金的給付 | 第十三條 特定重大傷病保險金的給付 | 第三十條 不保事項 | 第二十八條 除外責任（一） | 第二十二條 重大傷病保險金、特定重大傷病保險金的申領 | 第二條 名詞定義 | 附表一：全民健康保險重大傷病項目 | payout_items</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F242" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+Q1：慢性精神病的保險給付比例為保額的20%，但若選擇延後申請，並不會影響未來其他重大傷病保險金的申請資格或保額。條款中未限制延後申請的權利，且未提及延後申請會影響其他重大傷病的給付。  
+Q2：保險公司是否知情取決於被保險人是否提供相關診斷資料，但條款中未提及未申請慢性精神病給付會影響未來重大傷病保險金的給付比例。若未來罹患其他重大傷病，符合條件時仍可依條款規定申請100%保額的重大傷病保險金。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第十三條 特定重大傷病保險金的給付]  
+- [第二十二條 重大傷病保險金、特定重大傷病保險金的申領]</t>
+        </is>
+      </c>
+      <c r="G242" s="2" t="inlineStr"/>
+      <c r="H242" s="2" t="inlineStr"/>
+      <c r="I242" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認慢性精神病保險給付比例是否為保額的20%", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認是否可以延後申請慢性精神病的保險給付", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認延後申請是否影響重大傷病保險金的申請資格或保額", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認保險公司是否會因未申請慢性精神病給付而不知情", "must_have": false, "分數": 1.0}, {"id": "5", "point": "確認重大傷病保險金是否能領取100%保額的條件", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.505467, "neutral": 0.473862, "contradiction": 0.020671, "factuality": 0.979329, "C_fact": 0.979329}, "C_conf": 0.9875}</t>
+        </is>
+      </c>
+      <c r="J242" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K242" s="3" t="n">
+        <v>0.979329</v>
+      </c>
+      <c r="L242" s="3" t="n">
+        <v>0.9875</v>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:33:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>慢性精神病失智症會賠嗎？賠多少？</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+慢性精神病（如失智症）屬於重大傷病範圍，若被保險人於等待期間屆滿翌日或復效日起的契約有效期間內，經醫師診斷確定罹患，並取得重大傷病證明或符合診斷書及病歷摘要的要求，本公司將依以下方式給付重大傷病保險金：  
+1. 初次診斷確定罹患重大傷病時之保險單年度為第一保險單年度：「年繳應繳保險費總額」的1.05倍。  
+2. 初次診斷確定罹患重大傷病時之保險單年度為第二保險單年度（含）以後：「保險金額的20%」或「年繳應繳保險費總額的1.05倍」，二者取其大者。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
+        <is>
+          <t>附表一：全民健康保險重大傷病項目 | 第二十九條 除外責任（二） | 第十二條 重大傷病保險金的給付 | payout_items | 附表二：完全失能程度表</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F243" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+慢性精神病（如失智症）屬於重大傷病範圍，若被保險人於等待期間屆滿翌日或復效日起的契約有效期間內，經醫師診斷確定罹患，並取得重大傷病證明或符合診斷書及病歷摘要的要求，本公司將依以下方式給付重大傷病保險金：  
+1. 初次診斷確定罹患重大傷病時之保險單年度為第一保險單年度：「年繳應繳保險費總額」的1.05倍。  
+2. 初次診斷確定罹患重大傷病時之保險單年度為第二保險單年度（含）以後：「保險金額的20%」或「年繳應繳保險費總額的1.05倍」，二者取其大者。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G243" s="2" t="inlineStr"/>
+      <c r="H243" s="2" t="inlineStr"/>
+      <c r="I243" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "慢性精神病失智症會賠嗎？賠多少？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.882919, "neutral": 0.116777, "contradiction": 0.000305, "factuality": 0.999695, "C_fact": 0.999695}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J243" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K243" s="3" t="n">
+        <v>0.999695</v>
+      </c>
+      <c r="L243" s="3" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>投保新鍾心滿福後，於第二保單年度罹患子宮頸惡性腫瘤，且已給付重大傷病保險金。第五保單年度時又罹患慢性腎衰竭，這樣還可以申領重大傷病保險金的給付嗎?</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 根據條款規定，重大傷病保險金僅能給付一次，即使被保險人同時或先後罹患兩項以上的重大傷病，本公司僅給付一項重大傷病保險金。因此，已於第二保單年度因子宮頸惡性腫瘤申領過重大傷病保險金後，無法再次因慢性腎衰竭申領。  
+2. 慢性腎衰竭（尿毒症）需接受定期透析治療者，符合重大傷病範圍，理論上可申領重大傷病保險金，但因條款限制，無法重複給付。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
+        <is>
+          <t>附表一：全民健康保險重大傷病項目 | 第十二條 重大傷病保險金的給付 | 第五條 保險範圍 | 第二條 名詞定義 | payout_items | 第二十二條 重大傷病保險金、特定重大傷病保險金的申領</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F244" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 根據條款規定，重大傷病保險金僅能給付一次，即使被保險人同時或先後罹患兩項以上的重大傷病，本公司僅給付一項重大傷病保險金。因此，已於第二保單年度因子宮頸惡性腫瘤申領過重大傷病保險金後，無法再次因慢性腎衰竭申領。  
+2. 慢性腎衰竭（尿毒症）需接受定期透析治療者，符合重大傷病範圍，理論上可申領重大傷病保險金，但因條款限制，無法重複給付。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G244" s="2" t="inlineStr"/>
+      <c r="H244" s="2" t="inlineStr"/>
+      <c r="I244" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認重大傷病保險金是否可重複申領", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認慢性腎衰竭是否符合重大傷病保險金的理賠條件", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認保單條款中對於多次罹患重大傷病的理賠規定", "must_have": false, "分數": 1.0}, {"id": "4", "point": "確認重大傷病保險金的理賠次數或上限是否已達", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.977694, "neutral": 0.021967, "contradiction": 0.000339, "factuality": 0.999661, "C_fact": 0.999661}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J244" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K244" s="3" t="n">
+        <v>0.999661</v>
+      </c>
+      <c r="L244" s="3" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:35:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>12歲的被保險人可以有健康促進保險費折減嗎？</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+12歲的被保險人無法享有健康促進保險費折減，因為該條款明確規定，只有實際年齡達18歲（含）以上的被保險人才符合資格。
+條文依據：  
+- [第十九條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 健康促進保險費折減 | 第三十八條 投保年齡的計算及錯誤的處理 | 第三十四條 減額繳清保險 | 第二條 名詞定義 | 第十六條 所繳保險費加計利息的退還、身故保險金或喪葬費用保險金的給付 | 附表二：完全失能程度表</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F245" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+12歲的被保險人無法享有健康促進保險費折減，因為該條款明確規定，只有實際年齡達18歲（含）以上的被保險人才符合資格。
+條文依據：  
+- [第十九條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="G245" s="2" t="inlineStr"/>
+      <c r="H245" s="2" t="inlineStr"/>
+      <c r="I245" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "12歲的被保險人可以有健康促進保險費折減嗎？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.923582, "neutral": 0.074536, "contradiction": 0.001881, "factuality": 0.998119, "C_fact": 0.998119}, "C_conf": 0.9989}</t>
+        </is>
+      </c>
+      <c r="J245" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K245" s="3" t="n">
+        <v>0.998119</v>
+      </c>
+      <c r="L245" s="3" t="n">
+        <v>0.9989</v>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:35:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>ZDN</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>被保險人於投保鍾心滿溢後的第10天就罹患慢性腎衰竭，請問可以申領重大傷病保險金嗎？</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於投保後第10天罹患慢性腎衰竭，無法申領重大傷病保險金。原因如下：  
+1. 慢性腎衰竭屬於重大傷病範圍，需符合理賠條件方可申領。  
+2. 本契約規定有等待期間，慢性腎衰竭屬於「需積極或長期治療之癌症」以外的重大傷病，等待期間為30天。被保險人因意外傷害事故以外原因，於等待期間內罹患重大傷病，依條款規定，本契約自始無效，僅退還已繳保險費。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 重大傷病保險金的給付 | 附表一：全民健康保險重大傷病項目 | 第三十條 不保事項 | 第二條 名詞定義 | 第二十二條 重大傷病保險金、特定重大傷病保險金的申領</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F246" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於投保後第10天罹患慢性腎衰竭，無法申領重大傷病保險金。原因如下：  
+1. 慢性腎衰竭屬於重大傷病範圍，需符合理賠條件方可申領。  
+2. 本契約規定有等待期間，慢性腎衰竭屬於「需積極或長期治療之癌症」以外的重大傷病，等待期間為30天。被保險人於等待期間內罹患重大傷病，依條款規定，本契約自始無效，僅退還已繳保險費。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第三十條 不保事項]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G246" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於投保後第10天罹患慢性腎衰竭，無法申領重大傷病保險金。原因如下：  
+1. 慢性腎衰竭屬於重大傷病範圍，需符合理賠條件方可申領。  
+2. 本契約規定有等待期間，慢性腎衰竭屬於「需積極或長期治療之癌症」以外的重大傷病，等待期間為30天。被保險人因意外傷害事故以外原因，於等待期間內罹患重大傷病，依條款規定，本契約自始無效，僅退還已繳保險費。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="H246" s="2" t="inlineStr"/>
+      <c r="I246" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認重大傷病保險金是否涵蓋慢性腎衰竭", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認保單是否已生效並符合理賠條件", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認慢性腎衰竭的診斷日期是否符合保單規定", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認保單是否有等待期規定及其適用情況", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.651789, "neutral": 0.341214, "contradiction": 0.006997, "factuality": 0.993003, "C_fact": 0.993003}, "C_conf": 0.9958}</t>
+        </is>
+      </c>
+      <c r="J246" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K246" s="3" t="n">
+        <v>0.993003</v>
+      </c>
+      <c r="L246" s="3" t="n">
+        <v>0.9958</v>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:36:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>CFE</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>投保自由配重大傷病後，若在契約生效後80天罹患第一期乳癌，會拿到理賠金嗎?</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 自由配重大傷病保險涵蓋第一期乳癌，屬於「需積極或長期治療之癌症」範圍內，且在附表一中列明 [附表一：全民健康保險重大傷病項目]。  
+2. 契約生效後等待期為90天，80天尚未滿等待期，因此不符合理賠條件 [第二條 名詞定義]。  
+3. 被保險人因非意外傷害事故於等待期間內罹患「重大傷病」，本契約自始無效，保險公司將無息退還已繳保險費 [第十一條 重大傷病保險金的給付]。</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
+        <is>
+          <t>附表一：全民健康保險重大傷病項目 | 第十一條 重大傷病保險金的給付 | 第十五條 不保事項 | 第二條 名詞定義 | 第五條 契約有效期間及保證續保 | 第十四條 除外責任</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F247" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 自由配重大傷病保險涵蓋第一期乳癌，屬於「需積極或長期治療之癌症」範圍內，且在附表一中列明。  
+2. 契約生效後等待期為90天，80天尚未滿等待期，因此不符合理賠條件。  
+3. 第一期乳癌符合重大傷病範圍，但因等待期未滿，契約自始無效，保險公司將無息退還已繳保險費。  
+條文依據：  
+- [附表一：全民健康保險重大傷病項目]  
+- [第十一條 重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G247" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 自由配重大傷病保險涵蓋第一期乳癌，屬於「需積極或長期治療之癌症」範圍內，且在附表一中列明 [附表一：全民健康保險重大傷病項目]。  
+2. 契約生效後等待期為90天，80天尚未滿等待期，因此不符合理賠條件 [第二條 名詞定義]。  
+3. 被保險人因非意外傷害事故於等待期間內罹患「重大傷病」，本契約自始無效，保險公司將無息退還已繳保險費 [第十一條 重大傷病保險金的給付]。</t>
+        </is>
+      </c>
+      <c r="H247" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 自由配重大傷病保險涵蓋第一期乳癌，屬於「需積極或長期治療之癌症」範圍內，且在附表一中列明 [附表一：全民健康保險重大傷病項目]。  
+2. 契約生效後等待期為90天，80天尚未滿等待期，因此不符合理賠條件 [第二條 名詞定義]。  
+3. 被保險人因非意外傷害事故於等待期間內罹患「重大傷病」，本契約自始無效，保險公司將無息退還已繳保險費 [第十一條 重大傷病保險金的給付]。</t>
+        </is>
+      </c>
+      <c r="I247" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認自由配重大傷病保險是否涵蓋第一期乳癌", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認契約生效後的等待期是否已滿", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認第一期乳癌是否符合理賠條件", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認理賠金額的計算方式或標準", "must_have": false, "分數": 0.0}], "coverage_score": 0.9231, "nli": {"entailment": 0.019976, "neutral": 0.281702, "contradiction": 0.698321, "factuality": 0.301679, "C_fact": 0.301679}, "C_conf": 0.4498}</t>
+        </is>
+      </c>
+      <c r="J247" s="3" t="n">
+        <v>0.9231</v>
+      </c>
+      <c r="K247" s="4" t="n">
+        <v>0.301679</v>
+      </c>
+      <c r="L247" s="4" t="n">
+        <v>0.4498</v>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:37:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>CFE</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>要保人想要終止國泰人壽自由配CFE契約，能否退保費?如何申請？</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 要保人可以終止國泰人壽自由配CFE契約，並可退還未到期保險費。退還金額為已繳保險費扣除按短期費率計算已經過期間的保險費後的餘額，且不計利息。  
+2. 要保人需以書面或其他約定方式通知保險公司，契約自保險公司收到通知時生效終止。  
+條文依據：  
+- [第九條 契約的終止（一）]</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
+        <is>
+          <t>第九條 契約的終止（一） | 第十五條 不保事項 | 第七條 本契約效力的恢復 | 第六條 續保保險費的交付、寬限期間及契約效力的停止 | 第十條 契約的終止（二） | 第五條 契約有效期間及保證續保 | 第八條 告知義務與本契約的解除 | 第十七條 保險金額之減少 | 附表二：短期費率表</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F248" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 要保人可以終止國泰人壽自由配CFE契約，並可退還未到期保險費。退還金額為已繳保險費扣除按短期費率計算已經過期間的保險費後的餘額，且不計利息。  
+2. 要保人需以書面或其他約定方式通知保險公司，契約自保險公司收到通知時生效終止。  
+條文依據：  
+- [第九條 契約的終止（一）]</t>
+        </is>
+      </c>
+      <c r="G248" s="2" t="inlineStr"/>
+      <c r="H248" s="2" t="inlineStr"/>
+      <c r="I248" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認終止國泰人壽自由配CFE契約是否可退保費", "must_have": true, "分數": 1.0}, {"id": "2", "point": "了解申請終止契約及退保費的流程", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認是否需提供特定文件以完成申請", "must_have": false, "分數": 0.0}, {"id": "4", "point": "確認退保費是否會扣除相關費用或手續費", "must_have": false, "分數": 1.0}], "coverage_score": 0.9, "nli": {"entailment": 0.969754, "neutral": 0.030055, "contradiction": 0.000191, "factuality": 0.999809, "C_fact": 0.999809}, "C_conf": 0.8999}</t>
+        </is>
+      </c>
+      <c r="J248" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K248" s="3" t="n">
+        <v>0.9998089999999999</v>
+      </c>
+      <c r="L248" s="3" t="n">
+        <v>0.8999</v>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:37:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>CFE</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>投保國泰人壽自由配CFE，若在等待期間內罹患重大傷病，要如何給付?</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在等待期間內罹患重大傷病，依條款規定，因意外傷害事故所致的重大傷病不受等待期間限制，仍可申請給付重大傷病保險金。但若因其他原因（非意外傷害事故）於等待期間內罹患重大傷病，則本契約自始無效，保險公司僅退還已繳保險費且不計利息。  
+條文依據：  
+- [第十一條 重大傷病保險金的給付]  
+- [第十五條 不保事項]</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 重大傷病保險金的給付 | 附表一：全民健康保險重大傷病項目 | 第十五條 不保事項 | 第十四條 除外責任 | payout_items | other_metadata</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F249" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在等待期間內罹患重大傷病，依條款規定，因意外傷害事故所致的重大傷病不受等待期間限制，仍可申請給付重大傷病保險金。但若因其他原因（非意外傷害事故）於等待期間內罹患重大傷病，則本契約自始無效，保險公司僅退還已繳保險費且不計利息。  
+條文依據：  
+- [第十一條 重大傷病保險金的給付]  
+- [第十五條 不保事項]</t>
+        </is>
+      </c>
+      <c r="G249" s="2" t="inlineStr"/>
+      <c r="H249" s="2" t="inlineStr"/>
+      <c r="I249" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認國泰人壽自由配CFE的等待期間規定", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認重大傷病是否符合保單條款中的定義", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認等待期間內重大傷病的給付條件或限制", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認是否有其他附加條款影響給付", "must_have": false, "分數": 0.5}], "coverage_score": 0.9615, "nli": {"entailment": 0.894857, "neutral": 0.095679, "contradiction": 0.009464, "factuality": 0.990536, "C_fact": 0.990536}, "C_conf": 0.956}</t>
+        </is>
+      </c>
+      <c r="J249" s="3" t="n">
+        <v>0.9615</v>
+      </c>
+      <c r="K249" s="3" t="n">
+        <v>0.990536</v>
+      </c>
+      <c r="L249" s="3" t="n">
+        <v>0.956</v>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:37:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>CFE</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>投保自由配一年定期初次罹患重大傷病健康保險後，於第三年罹患先天性肌肉萎縮症，可以申領重大傷病保險金嗎？</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於第三年罹患「先天性肌肉萎縮症」無法申領重大傷病保險金，原因如下：  
+1. 「先天性肌肉萎縮症」不在保單附表一「全民健康保險重大傷病項目」的保障範圍內。  
+2. 保單條款第十五條明確規定，若被保險人於投保前已符合重大傷病項目或曾被診斷為重大傷病，保險契約自始無效，僅退還已繳保險費。雖然問題中未提及投保前的診斷情況，但「先天性」疾病通常被視為投保前已存在的狀況，可能適用此條款。
+條文依據：  
+- [第十一條 重大傷病保險金的給付]  
+- [第十五條 不保事項]  
+- [附表一：全民健康保險重大傷病項目]</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 重大傷病保險金的給付 | other_metadata | 附表一：全民健康保險重大傷病項目 | 第十三條 重大傷病保險金的申領 | 第十五條 不保事項</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F250" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於第三年罹患「先天性肌肉萎縮症」無法申領重大傷病保險金，原因如下：  
+1. 「先天性肌肉萎縮症」不在保單附表一「全民健康保險重大傷病項目」的保障範圍內。  
+2. 保單條款第十五條明確規定，若被保險人於投保前已符合重大傷病項目或曾被診斷為重大傷病，保險契約自始無效，僅退還已繳保險費。雖然問題中未提及投保前的診斷情況，但「先天性」疾病通常被視為投保前已存在的狀況，可能適用此條款。
+條文依據：  
+- [第十一條 重大傷病保險金的給付]  
+- [第十五條 不保事項]  
+- [附表一：全民健康保險重大傷病項目]</t>
+        </is>
+      </c>
+      <c r="G250" s="2" t="inlineStr"/>
+      <c r="H250" s="2" t="inlineStr"/>
+      <c r="I250" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認自由配一年定期重大傷病健康保險的保障範圍是否包含先天性肌肉萎縮症", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認保單是否對先天性疾病有除外責任或特別條款", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認第三年罹患疾病是否符合保單的理賠條件", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認保單是否有續保或有效狀態的要求", "must_have": false, "分數": 0.0}], "coverage_score": 0.9231, "nli": {"entailment": 0.0139, "neutral": 0.972089, "contradiction": 0.014011, "factuality": 0.985989, "C_fact": 0.985989}, "C_conf": 0.9153}</t>
+        </is>
+      </c>
+      <c r="J250" s="3" t="n">
+        <v>0.9231</v>
+      </c>
+      <c r="K250" s="3" t="n">
+        <v>0.985989</v>
+      </c>
+      <c r="L250" s="3" t="n">
+        <v>0.9153</v>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:38:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>CFG</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>自由配重大疾病(甲型)保障的重大疾病有哪些疾病?</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+自由配重大疾病(甲型)保障的重大疾病包括以下疾病：  
+1. 腦中風後障礙(重度)  
+2. 癱瘓(重度)  
+3. 癌症(重度)  
+4. 急性心肌梗塞(重度)  
+5. 冠狀動脈繞道手術  
+6. 末期腎病變  
+7. 重大器官移植或造血幹細胞移植  
+條文依據：  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
+        <is>
+          <t>國泰人壽自由配一年定期初次罹患重大疾病健康保險(甲型)年繳費率表 | payout_items | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F251" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+自由配重大疾病(甲型)保障的重大疾病包括以下疾病：  
+1. 腦中風後障礙(重度)  
+2. 癱瘓(重度)  
+3. 癌症(重度)  
+4. 急性心肌梗塞(重度)  
+5. 冠狀動脈繞道手術  
+6. 末期腎病變  
+7. 重大器官移植或造血幹細胞移植  
+條文依據：  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G251" s="2" t="inlineStr"/>
+      <c r="H251" s="2" t="inlineStr"/>
+      <c r="I251" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "自由配重大疾病(甲型)保障的重大疾病有哪些疾病?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.435646, "neutral": 0.534641, "contradiction": 0.029713, "factuality": 0.970287, "C_fact": 0.970287}, "C_conf": 0.9821}</t>
+        </is>
+      </c>
+      <c r="J251" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K251" s="3" t="n">
+        <v>0.970287</v>
+      </c>
+      <c r="L251" s="3" t="n">
+        <v>0.9821</v>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:38:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>被保險人領了2次癌症(重度)追蹤照護金後身故，是否還有尚未給付的保險金供受益人領取?</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 被保險人已領取的2次「癌症(重度)追蹤照護保險金」，不影響其他保險金的給付資格，因條款中未提及該保險金的給付會影響其他保險金的申領。  
+2. 條款中未明確提及是否包含「身故保險金」或其他與身故相關的保障，因此無法確認是否有尚未給付的保險金供受益人領取。  
+條文依據：  
+- 第二十八條 受益人  
+- 第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
+        <is>
+          <t>第二十三條 癌症保險金或罹癌基因檢測服務的申領 | 第二十八條 受益人 | 第十一條 契約的終止（三） | 第二十二條 保險事故的通知與保險給付的申請時間 | 第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用) | 第一條 保險契約的構成 | 第五條 保險範圍 | 第十三條 初次罹患癌症(重度)保險金的給付</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F252" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 被保險人已領取的2次「癌症(重度)追蹤照護保險金」，不影響其他保險金的給付資格，因條款中未提及該保險金的給付會影響其他保險金的申領。  
+2. 提供的條款中未提及有關「身故保險金」或其他與身故相關的保障，因此無法確認是否有尚未給付的保險金供受益人領取。  
+條文依據：  
+- 第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供  
+- 找不到相關內容</t>
+        </is>
+      </c>
+      <c r="G252" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 被保險人已領取的2次「癌症(重度)追蹤照護保險金」，不影響其他保險金的給付資格，因條款中未提及該保險金的給付會影響其他保險金的申領。  
+2. 根據第二十八條，若被保險人身故時仍有尚未給付或未完全給付的保險金，該部分保險金的受益人為被保險人身故時之法定繼承人。然而，條款中未明確提及是否包含「身故保險金」或其他與身故相關的保障，因此無法確認是否有尚未給付的保險金供受益人領取。  
+條文依據：  
+- 第二十八條 受益人  
+- 第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供</t>
+        </is>
+      </c>
+      <c r="H252" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 被保險人已領取的2次「癌症(重度)追蹤照護保險金」，不影響其他保險金的給付資格，因條款中未提及該保險金的給付會影響其他保險金的申領。  
+2. 條款中未明確提及是否包含「身故保險金」或其他與身故相關的保障，因此無法確認是否有尚未給付的保險金供受益人領取。  
+條文依據：  
+- 第二十八條 受益人  
+- 第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供</t>
+        </is>
+      </c>
+      <c r="I252" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認被保險人已領取的癌症(重度)追蹤照護金是否影響其他保險金的給付資格", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認保單中是否有身故保險金或其他相關保障", "must_have": true, "分數": 0.5}, {"id": "3", "point": "確認保單條款中對於多次給付後的身故保障規定", "must_have": false, "分數": 0.5}], "coverage_score": 0.7222, "nli": {"entailment": 0.501816, "neutral": 0.339834, "contradiction": 0.15835, "factuality": 0.84165, "C_fact": 0.84165}, "C_conf": 0.6512}</t>
+        </is>
+      </c>
+      <c r="J252" s="4" t="n">
+        <v>0.7222</v>
+      </c>
+      <c r="K252" s="3" t="n">
+        <v>0.84165</v>
+      </c>
+      <c r="L252" s="4" t="n">
+        <v>0.6512</v>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:39:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>保險金額2萬元，「罹癌基因檢測服務」費用8萬元，還會給付多少「癌症(重度)追蹤照護保險金」？</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 根據條款，「癌症(重度)追蹤照護保險金」的給付條件為：被保險人於第二保險單年度(含)以後，初次診斷確定罹患癌症(重度)，並自診斷確定日的次一保險單週年日起，每逢保險單週年日仍生存者，按「保險金額」的十二倍給付，最長以五年為限。若保險金額為2萬元，則每年可給付24萬元（2萬元 × 12）。  
+2. 被保險人得擇一申領「癌症(重度)追蹤照護保險金」或「罹癌基因檢測服務」。若選擇申領「罹癌基因檢測服務」，則需注意該服務的補償金額為1,000元，且若服務費用（8萬元）高於補償金額（1,000元），則被保險人僅能申領「癌症(重度)追蹤照護保險金」。條款並明確指出，被保險人可另行以附件一所列服務費用之金額向合作機構購買「罹癌基因檢測服務」。  
+3. 條款中未提及「癌症(重度)追蹤照護保險金」有自付額或其他扣除項目。  
+因此，若被保險人選擇不申領「罹癌基因檢測服務」，則每年可獲得24萬元的「癌症(重度)追蹤照護保險金」，最長可給付五年。
+條文依據：  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]  
+- [附件一：罹癌基因檢測服務之項目、服務費用及補償金額表]</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用) | 附件一：罹癌基因檢測服務之項目、服務費用及補償金額表 | 第二十三條 癌症保險金或罹癌基因檢測服務的申領 | 第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用) | 第十三條 初次罹患癌症(重度)保險金的給付 | 第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F253" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 根據條款，「癌症(重度)追蹤照護保險金」的給付條件為：被保險人於第二保險單年度(含)以後，初次診斷確定罹患癌症(重度)，並自診斷確定日的次一保險單週年日起，每逢保險單週年日仍生存者，按「保險金額」的十二倍給付，最長以五年為限。若保險金額為2萬元，則每年可給付24萬元（2萬元 × 12）。  
+2. 若被保險人選擇申領「罹癌基因檢測服務」，則需注意該服務的補償金額為1,000元，且若服務費用（8萬元）高於補償金額（1,000元），則被保險人僅能申領「癌症(重度)追蹤照護保險金」。  
+3. 保險金額2萬元並非理賠上限，而是計算「癌症(重度)追蹤照護保險金」的基礎金額。  
+4. 條款中未提及「癌症(重度)追蹤照護保險金」有自付額或其他扣除項目。  
+因此，若被保險人選擇不申領「罹癌基因檢測服務」，則每年可獲得24萬元的「癌症(重度)追蹤照護保險金」，最長可給付五年。
+條文依據：  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]  
+- [附件一：罹癌基因檢測服務之項目、服務費用及補償金額表]</t>
+        </is>
+      </c>
+      <c r="G253" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 根據條款，「癌症(重度)追蹤照護保險金」的給付條件為：被保險人於第二保險單年度(含)以後，初次診斷確定罹患癌症(重度)，並自診斷確定日的次一保險單週年日起，每逢保險單週年日仍生存者，按「保險金額」的十二倍給付，最長以五年為限。若保險金額為2萬元，則每年可給付24萬元（2萬元 × 12）。  
+2. 被保險人得擇一申領「癌症(重度)追蹤照護保險金」或「罹癌基因檢測服務」。若選擇申領「罹癌基因檢測服務」，則需注意該服務的補償金額為1,000元，且若服務費用（8萬元）高於補償金額（1,000元），則被保險人僅能申領「癌症(重度)追蹤照護保險金」。  
+3. 條款中未提及「癌症(重度)追蹤照護保險金」有自付額或其他扣除項目。  
+因此，若被保險人選擇不申領「罹癌基因檢測服務」，則每年可獲得24萬元的「癌症(重度)追蹤照護保險金」，最長可給付五年。
+條文依據：  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]  
+- [附件一：罹癌基因檢測服務之項目、服務費用及補償金額表]</t>
+        </is>
+      </c>
+      <c r="H253" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 根據條款，「癌症(重度)追蹤照護保險金」的給付條件為：被保險人於第二保險單年度(含)以後，初次診斷確定罹患癌症(重度)，並自診斷確定日的次一保險單週年日起，每逢保險單週年日仍生存者，按「保險金額」的十二倍給付，最長以五年為限。若保險金額為2萬元，則每年可給付24萬元（2萬元 × 12）。  
+2. 被保險人得擇一申領「癌症(重度)追蹤照護保險金」或「罹癌基因檢測服務」。若選擇申領「罹癌基因檢測服務」，則需注意該服務的補償金額為1,000元，且若服務費用（8萬元）高於補償金額（1,000元），則被保險人僅能申領「癌症(重度)追蹤照護保險金」。條款並明確指出，被保險人可另行以附件一所列服務費用之金額向合作機構購買「罹癌基因檢測服務」。  
+3. 條款中未提及「癌症(重度)追蹤照護保險金」有自付額或其他扣除項目。  
+因此，若被保險人選擇不申領「罹癌基因檢測服務」，則每年可獲得24萬元的「癌症(重度)追蹤照護保險金」，最長可給付五年。
+條文依據：  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]  
+- [附件一：罹癌基因檢測服務之項目、服務費用及補償金額表]</t>
+        </is>
+      </c>
+      <c r="I253" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認癌症(重度)追蹤照護保險金的給付條件與計算方式", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認罹癌基因檢測服務費用是否納入保險理賠範圍", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認保險金額2萬元是否為理賠上限或其他限制", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認癌症(重度)相關保險是否有自付額或其他扣除項目", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.007474, "neutral": 0.946177, "contradiction": 0.046349, "factuality": 0.953651, "C_fact": 0.953651}, "C_conf": 0.9719}</t>
+        </is>
+      </c>
+      <c r="J253" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K253" s="3" t="n">
+        <v>0.953651</v>
+      </c>
+      <c r="L253" s="3" t="n">
+        <v>0.9719</v>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:40:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>投保後1個月罹患重度癌症，是否已過了等待期間？會給付哪些保險金？契約還會持續有效嗎？</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. **是否已超過等待期間**：等待期間為九十日，投保後一個月（約30天）罹患重度癌症，尚未超過等待期間。  
+2. **可申請的保險金種類**：因尚未超過等待期間，無法申請任何保險金。  
+3. **契約是否持續有效**：根據條款，若於生效日起九十日內診斷罹患癌症，契約效力即行終止，保險公司將無息退還已繳保險費。因此，契約將不再有效。  
+條文依據：  
+- [第十條 契約的終止（二）]  
+- [第十三條 初次罹患癌症(重度)保險金的給付]  
+- （本保險「癌症」等待期間為九十日，詳請參閱契約條款）</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 癌症(重度)豁免保險費(第二保險單年度起適用) | 第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用) | 第十三條 初次罹患癌症(重度)保險金的給付 | other_metadata | 第十條 契約的終止（二） | 第十一條 契約的終止（三） | 第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付 | 第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用)</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F254" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. **是否已超過等待期間**：等待期間為九十日，投保後一個月（約30天）罹患重度癌症，尚未超過等待期間。  
+2. **可申請的保險金種類**：因尚未超過等待期間，無法申請任何保險金。  
+3. **契約是否持續有效**：根據條款，若於生效日起九十日內診斷罹患癌症，契約效力即行終止，保險公司將無息退還已繳保險費。因此，契約將不再有效。  
+條文依據：  
+- [第十條 契約的終止（二）]  
+- [第十三條 初次罹患癌症(重度)保險金的給付]  
+- （本保險「癌症」等待期間為九十日，詳請參閱契約條款）</t>
+        </is>
+      </c>
+      <c r="G254" s="2" t="inlineStr"/>
+      <c r="H254" s="2" t="inlineStr"/>
+      <c r="I254" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認重度癌症是否已超過等待期間", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認重度癌症可申請的保險金種類", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認契約是否因重度癌症診斷而持續有效", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認等待期間的具體天數及起算方式", "must_have": false, "分數": 1.0}, {"id": "5", "point": "確認保險金給付是否包含住院、手術或其他相關項目", "must_have": false, "分數": 0.0}], "coverage_score": 0.9286, "nli": {"entailment": 0.927651, "neutral": 0.068219, "contradiction": 0.004129, "factuality": 0.995871, "C_fact": 0.995871}, "C_conf": 0.9263}</t>
+        </is>
+      </c>
+      <c r="J254" s="3" t="n">
+        <v>0.9286</v>
+      </c>
+      <c r="K254" s="3" t="n">
+        <v>0.995871</v>
+      </c>
+      <c r="L254" s="3" t="n">
+        <v>0.9263</v>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:40:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>投保後10個月罹患重度癌症（第一保單年度），是否已過了等待期間，會給付哪些保險金？契約還會終止嗎？</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. **是否已超過等待期間**：投保後10個月罹患重度癌症，已超過契約生效日起的90日等待期間，因此不受等待期間限制。  
+2. **可申請的保險金種類與給付範圍**：在第一保單年度內，符合「初次診斷確定罹患癌症（重度）」的條件，可申請「初次罹患癌症（重度）保險金」，給付金額為「年繳應繳保險費」的1.06倍。  
+3. **契約是否會終止**：根據條款，若被保險人在第一保單年度內符合「初次診斷確定罹患癌症（重度）」並申領保險金，契約效力即行終止。  
+條文依據：  
+- [第十條 契約的終止（二）]  
+- [第十三條 初次罹患癌症(重度)保險金的給付]  
+- [第十一條 契約的終止（三）]</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 初次罹患癌症(重度)保險金的給付 | 第十六條 癌症(重度)豁免保險費(第二保險單年度起適用) | 第十條 契約的終止（二） | 第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用) | 第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付 | 第十一條 契約的終止（三） | 第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用)</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F255" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. **是否已超過等待期間**：投保後10個月罹患重度癌症，已超過契約生效日起的90日等待期間，因此不受等待期間限制。  
+2. **可申請的保險金種類與給付範圍**：在第一保單年度內，符合「初次診斷確定罹患癌症（重度）」的條件，可申請「初次罹患癌症（重度）保險金」，給付金額為「年繳應繳保險費」的1.06倍。  
+3. **契約是否會終止**：根據條款，若被保險人在第一保單年度內符合「初次診斷確定罹患癌症（重度）」並申領保險金，契約效力即行終止。  
+條文依據：  
+- [第十條 契約的終止（二）]  
+- [第十三條 初次罹患癌症(重度)保險金的給付]  
+- [第十一條 契約的終止（三）]</t>
+        </is>
+      </c>
+      <c r="G255" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. **是否已超過等待期間**：投保後10個月罹患重度癌症，已超過契約生效日起的90日等待期間，因此不受等待期間限制。  
+2. **可申請的保險金種類與給付範圍**：在第一保單年度內，符合「初次診斷確定罹患癌症（重度）」的條件，可申請「初次罹患癌症（重度）保險金」，給付金額為「年繳應繳保險費」的1.06倍。  
+3. **契約是否會終止**：根據條款，若被保險人在第一保單年度內符合「初次診斷確定罹患癌症（重度）」並申領保險金，契約效力即行終止。  
+條文依據：  
+- [第十條 契約的終止（二）]  
+- [第十三條 初次罹患癌症(重度)保險金的給付]  
+- [第十一條 契約的終止（三）]</t>
+        </is>
+      </c>
+      <c r="H255" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. **是否已超過等待期間**：投保後10個月罹患重度癌症，已超過契約生效日起的90日等待期間，因此不受等待期間限制。  
+2. **可申請的保險金種類與給付範圍**：在第一保單年度內，符合「初次診斷確定罹患癌症（重度）」的條件，可申請「初次罹患癌症（重度）保險金」，給付金額為「年繳應繳保險費」的1.06倍。  
+3. **契約是否會終止**：根據條款，若被保險人在第一保單年度內符合「初次診斷確定罹患癌症（重度）」並申領保險金，契約效力即行終止。  
+條文依據：  
+- [第十條 契約的終止（二）]  
+- [第十三條 初次罹患癌症(重度)保險金的給付]  
+- [第十一條 契約的終止（三）]</t>
+        </is>
+      </c>
+      <c r="I255" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認重度癌症是否已超過等待期間", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認重度癌症可申請的保險金種類與給付範圍", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認罹患重度癌症後保險契約是否會終止", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認第一保單年度對保險金給付的影響", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.575653, "neutral": 0.09291, "contradiction": 0.331438, "factuality": 0.668562, "C_fact": 0.668562}, "C_conf": 0.7854}</t>
+        </is>
+      </c>
+      <c r="J255" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K255" s="4" t="n">
+        <v>0.668562</v>
+      </c>
+      <c r="L255" s="4" t="n">
+        <v>0.7854</v>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:41:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>投保醫心康愛，罹患肺癌一期(重度癌症)，可領什麼保險金？</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 醫心康愛保單涵蓋重度癌症保障，依據條款第十三條、第十五條、第十四條、第十六條等，針對重度癌症提供多項保險金給付。  
+2. 肺癌一期屬於重度癌症，符合重度癌症的理賠定義。  
+3. 針對重度癌症的保險金種類與給付條件如下：  
+   - **初次罹患癌症(重度)保險金**：若診斷確定日在第二保險單年度(含)以後，給付「保險金額」的十二倍（第十三條）。  
+   - **癌症(重度)標靶藥物治療輔助保險金**：若於第二保險單年度(含)以後接受標靶治療，給付「保險金額」的十二倍（第十五條）。  
+   - **癌症(重度)追蹤照護保險金**：自診斷確定日次一保險單週年日起，每年給付「保險金額」的十二倍，最長五年（第十四條）。  
+   - **癌症(重度)豁免保險費**：自診斷確定日起豁免續期保險費（第十六條）。  
+條文依據：  
+- [第十三條 初次罹患癌症(重度)保險金的給付]  
+- [第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用)]  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]  
+- [第十六條 癌症(重度)豁免保險費(第二保險單年度起適用)]</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 初次罹患癌症(重度)保險金的給付 | 第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付 | payout_items | 第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用) | 第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用) | 第十六條 癌症(重度)豁免保險費(第二保險單年度起適用) | 第二十三條 癌症保險金或罹癌基因檢測服務的申領 | 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F256" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 醫心康愛保單涵蓋重度癌症保障，依據條款第十三條、第十五條、第十四條、第十六條等，針對重度癌症提供多項保險金給付。  
+2. 肺癌一期屬於重度癌症，符合重度癌症的理賠定義。  
+3. 針對重度癌症的保險金種類與給付條件如下：  
+   - **初次罹患癌症(重度)保險金**：若診斷確定日在第二保險單年度(含)以後，給付「保險金額」的十二倍（第十三條）。  
+   - **癌症(重度)標靶藥物治療輔助保險金**：若於第二保險單年度(含)以後接受標靶治療，給付「保險金額」的十二倍（第十五條）。  
+   - **癌症(重度)追蹤照護保險金**：自診斷確定日次一保險單週年日起，每年給付「保險金額」的十二倍，最長五年（第十四條）。  
+   - **癌症(重度)豁免保險費**：自診斷確定日起豁免續期保險費（第十六條）。  
+條文依據：  
+- [第十三條 初次罹患癌症(重度)保險金的給付]  
+- [第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用)]  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]  
+- [第十六條 癌症(重度)豁免保險費(第二保險單年度起適用)]</t>
+        </is>
+      </c>
+      <c r="G256" s="2" t="inlineStr"/>
+      <c r="H256" s="2" t="inlineStr"/>
+      <c r="I256" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認醫心康愛保單是否涵蓋重度癌症保障", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認肺癌一期是否符合重度癌症的理賠定義", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認醫心康愛保單中針對重度癌症的保險金種類與給付條件", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認是否有額外的癌症相關附加保障或理賠項目", "must_have": false, "分數": 0.8}], "coverage_score": 0.9846, "nli": {"entailment": 0.002883, "neutral": 0.995904, "contradiction": 0.001213, "factuality": 0.998787, "C_fact": 0.998787}, "C_conf": 0.9839}</t>
+        </is>
+      </c>
+      <c r="J256" s="3" t="n">
+        <v>0.9846</v>
+      </c>
+      <c r="K256" s="3" t="n">
+        <v>0.998787</v>
+      </c>
+      <c r="L256" s="3" t="n">
+        <v>0.9839</v>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:41:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>PX5</t>
+        </is>
+      </c>
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>若被保險人身故有何給付?未到期保險費如何處理？尚未給付或未完全給付的保險金如何處理？</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 被保險人身故時，若本附約保險金尚未給付或未完全給付，則以被保險人之法定繼承人為受益人，並依民法繼承編相關規定分配。  
+2. 未到期保險費應從當期已繳保險費中扣除按日數比例計算已經過期間之保險費後，將其未到期保險費無息退還要保人。  
+3. 尚未給付或未完全給付的保險金，應由被保險人之法定繼承人依民法繼承編相關規定分配。  
+條文依據：  
+- [第十條 附約的終止（二）]  
+- [第二十條 受益人]</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 保險事故的通知與保險金的申請時間 | 第二十條 受益人 | 第十二條 重大疾病保險金的給付 | 第十七條 欠繳保險費的扣除 | 第十一條 輕度重大疾病保險金的給付 | 第十條 附約的終止（二） | 第六條 第二期以後保險費及續保保險費的交付、寬限期間及附約效力的停止 | 第九條 附約的終止（一）</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F257" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 被保險人身故時，若本附約保險金尚未給付或未完全給付，則以被保險人之法定繼承人為受益人，並依民法繼承編相關規定分配。  
+2. 未到期保險費應從當期已繳保險費中扣除按日數比例計算已經過期間之保險費後，將其未到期保險費無息退還要保人。  
+3. 尚未給付或未完全給付的保險金，應由被保險人之法定繼承人依民法繼承編相關規定分配。  
+條文依據：  
+- [第十條 附約的終止（二）]  
+- [第二十條 受益人]</t>
+        </is>
+      </c>
+      <c r="G257" s="2" t="inlineStr"/>
+      <c r="H257" s="2" t="inlineStr"/>
+      <c r="I257" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認被保險人身故時的保險金給付內容", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認未到期保險費的處理方式", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認尚未給付或未完全給付的保險金處理方式", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認保險契約中相關條款的適用範圍", "must_have": false, "分數": 0.8}], "coverage_score": 0.9846, "nli": {"entailment": 0.994591, "neutral": 0.00497, "contradiction": 0.000439, "factuality": 0.999561, "C_fact": 0.999561}, "C_conf": 0.9843}</t>
+        </is>
+      </c>
+      <c r="J257" s="3" t="n">
+        <v>0.9846</v>
+      </c>
+      <c r="K257" s="3" t="n">
+        <v>0.999561</v>
+      </c>
+      <c r="L257" s="3" t="n">
+        <v>0.9843</v>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:41:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>PX5</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>投保鍾溢祝福後，請問在第二年經醫院醫師初次診斷罹患「輕度重大疾病」中的癌症(輕度)者，可以領到輕度重大疾病保險金嗎?可以領到保險金額的百分之多少?</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+投保鍾溢祝福後，若在第二年經醫院醫師初次診斷罹患「輕度重大疾病」中的癌症(輕度)，可以領取輕度重大疾病保險金，給付比例為保險金額的百分之二十。  
+條文依據：  
+- [第十一條 輕度重大疾病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 輕度重大疾病保險金的給付 | 第十二條 重大疾病保險金的給付 | other_metadata | payout_items | 國泰人壽鍾溢祝福重大疾病健康保險附約(乙型) (外溢型)年繳費率表 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F258" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+投保鍾溢祝福後，若在第二年經醫院醫師初次診斷罹患「輕度重大疾病」中的癌症(輕度)，可以領取輕度重大疾病保險金，給付比例為保險金額的百分之二十。  
+條文依據：  
+- [第十一條 輕度重大疾病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G258" s="2" t="inlineStr"/>
+      <c r="H258" s="2" t="inlineStr"/>
+      <c r="I258" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認保單是否涵蓋輕度重大疾病保障", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認輕度重大疾病保障是否包含輕度癌症", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認第二年初次診斷是否符合保單理賠條件", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認輕度重大疾病保險金的給付比例或金額", "must_have": true, "分數": 1.0}, {"id": "5", "point": "確認保單是否有特定條款影響理賠比例", "must_have": false, "分數": 0.5}], "coverage_score": 0.9706, "nli": {"entailment": 0.98467, "neutral": 0.010112, "contradiction": 0.005218, "factuality": 0.994782, "C_fact": 0.994782}, "C_conf": 0.9676}</t>
+        </is>
+      </c>
+      <c r="J258" s="3" t="n">
+        <v>0.9706</v>
+      </c>
+      <c r="K258" s="3" t="n">
+        <v>0.9947820000000001</v>
+      </c>
+      <c r="L258" s="3" t="n">
+        <v>0.9676</v>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:42:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>PX5</t>
+        </is>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>請問如果在投保後的第三年經醫院醫師初次診斷罹患「重大疾病」者，可以領到重大疾病保險金嗎?可以領到保險金額的百分之多少?那後續又在第四年經醫院醫師初次診斷罹患「輕度重大疾病」者，可以領到輕度重大疾病保險金嗎?可以領到保險金額的百分之多少?</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 在投保後的第三年經醫院醫師初次診斷罹患「重大疾病」者，符合重大疾病保險金的給付條件，可領取保險金額的1.3倍。  
+2. 在第四年經醫院醫師初次診斷罹患「輕度重大疾病」者，因「輕度重大疾病保險金」終身最多以給付一次為限，且「重大疾病保險金」已於第三年給付，條款未明確規定是否影響「輕度重大疾病保險金」的申領資格，資料不足。  
+條文依據：  
+- [第十二條 重大疾病保險金的給付]  
+- [第十一條 輕度重大疾病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 輕度重大疾病保險金的給付 | 第十二條 重大疾病保險金的給付 | 第十六條 除外責任 | 第二條 名詞定義 | 第四條 保險範圍 | 國泰人壽鍾溢祝福重大疾病健康保險附約(乙型) (外溢型)年繳費率表</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F259" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 在投保後的第三年經醫院醫師初次診斷罹患「重大疾病」者，符合重大疾病保險金的給付條件，可領取保險金額的1.3倍。  
+2. 在第四年經醫院醫師初次診斷罹患「輕度重大疾病」者，因條款規定「被保險人於續保前或本附約有效期間內曾得申領第十一條『輕度重大疾病保險金』者，應扣除之」，且「重大疾病保險金」已於第三年給付，故無法再領取「輕度重大疾病保險金」。  
+條文依據：  
+- [第十二條 重大疾病保險金的給付]  
+- [第十一條 輕度重大疾病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G259" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 在投保後的第三年經醫院醫師初次診斷罹患「重大疾病」者，符合重大疾病保險金的給付條件，可領取保險金額的1.3倍。  
+2. 在第四年經醫院醫師初次診斷罹患「輕度重大疾病」者，因條款規定「輕度重大疾病保險金」終身最多以給付一次為限，且「重大疾病保險金」已於第三年給付，故無法再領取「輕度重大疾病保險金」。  
+條文依據：  
+- [第十二條 重大疾病保險金的給付]  
+- [第十一條 輕度重大疾病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="H259" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 在投保後的第三年經醫院醫師初次診斷罹患「重大疾病」者，符合重大疾病保險金的給付條件，可領取保險金額的1.3倍。  
+2. 在第四年經醫院醫師初次診斷罹患「輕度重大疾病」者，因「輕度重大疾病保險金」終身最多以給付一次為限，且「重大疾病保險金」已於第三年給付，條款未明確規定是否影響「輕度重大疾病保險金」的申領資格，資料不足。  
+條文依據：  
+- [第十二條 重大疾病保險金的給付]  
+- [第十一條 輕度重大疾病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="I259" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認重大疾病保險金的給付條件是否符合第三年初次診斷的情況", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認重大疾病保險金額的給付比例", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認輕度重大疾病保險金的給付條件是否符合第四年初次診斷的情況", "must_have": true, "分數": 0.5}, {"id": "4", "point": "確認輕度重大疾病保險金額的給付比例", "must_have": true, "分數": 0.5}, {"id": "5", "point": "確認重大疾病與輕度重大疾病是否屬於不同理賠範疇", "must_have": false, "分數": 1.0}], "coverage_score": 0.7647, "nli": {"entailment": 0.196556, "neutral": 0.696493, "contradiction": 0.106951, "factuality": 0.893049, "C_fact": 0.893049}, "C_conf": 0.7145}</t>
+        </is>
+      </c>
+      <c r="J259" s="4" t="n">
+        <v>0.7647</v>
+      </c>
+      <c r="K259" s="3" t="n">
+        <v>0.893049</v>
+      </c>
+      <c r="L259" s="4" t="n">
+        <v>0.7145</v>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:42:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>PX5</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>請問如果在投保後的第三年經醫院醫師初次診斷罹患「輕度重大疾病」者，可以領到重大疾病保險金嗎?可以領到保險金額的百分之多少?那後續又在第四年經醫院醫師初次診斷罹患「重大疾病」者，可以領到輕度重大疾病保險金嗎?可以領到保險金額的百分之多少?</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 在投保後的第三年，若經醫院醫師初次診斷罹患「輕度重大疾病」，符合保單保障範圍，可申領「輕度重大疾病保險金」，給付比例為保險金額的20%。  
+2. 在第四年，若經醫院醫師初次診斷罹患「重大疾病」，符合保單保障範圍，但因已於第三年申領過「輕度重大疾病保險金」，依條款規定，重大疾病保險金的給付金額需扣除已給付的輕度重大疾病保險金，給付比例為保險金額的130%減去已給付的20%，即保險金額的110%。
+條文依據：  
+- [第十一條 輕度重大疾病保險金的給付]  
+- [第十二條 重大疾病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 輕度重大疾病保險金的給付 | 第十二條 重大疾病保險金的給付 | 第十六條 除外責任 | payout_items | 第二條 名詞定義 | 第四條 保險範圍 | other_metadata | 第十五條 各項保險金的申領</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F260" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 在投保後的第三年，若經醫院醫師初次診斷罹患「輕度重大疾病」，符合保單保障範圍，可申領「輕度重大疾病保險金」，給付比例為保險金額的20%。  
+2. 在第四年，若經醫院醫師初次診斷罹患「重大疾病」，符合保單保障範圍，但因已於第三年申領過「輕度重大疾病保險金」，依條款規定，重大疾病保險金的給付金額需扣除已給付的輕度重大疾病保險金，給付比例為保險金額的130%減去已給付的20%，即保險金額的110%。
+條文依據：  
+- [第十一條 輕度重大疾病保險金的給付]  
+- [第十二條 重大疾病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G260" s="2" t="inlineStr"/>
+      <c r="H260" s="2" t="inlineStr"/>
+      <c r="I260" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認輕度重大疾病是否符合保單保障範圍", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認輕度重大疾病保險金的給付比例", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認重大疾病是否符合保單保障範圍", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認重大疾病保險金的給付比例", "must_have": true, "分數": 1.0}, {"id": "5", "point": "確認輕度重大疾病與重大疾病之間的理賠關係或限制", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.978161, "neutral": 0.01673, "contradiction": 0.00511, "factuality": 0.99489, "C_fact": 0.99489}, "C_conf": 0.9969}</t>
+        </is>
+      </c>
+      <c r="J260" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K260" s="3" t="n">
+        <v>0.9948900000000001</v>
+      </c>
+      <c r="L260" s="3" t="n">
+        <v>0.9969</v>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:43:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>PX5</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>請問主約效力終止(因身故以外情形)，PX5還能持續有效嗎？</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+主約效力因身故以外的情形終止時，PX5附約仍可持續有效，但需符合以下條件：  
+1. 要保人需繼續繳交附約保險費。  
+2. 附約效力可延續至主約原保險期間屆滿或附約最高續保年齡（80歲），以較早者為準。  
+條文依據：  
+- [第十條 附約的終止（二）]</t>
+        </is>
+      </c>
+      <c r="D261" s="2" t="inlineStr">
+        <is>
+          <t>第十條 附約的終止（二） | 第七條 保險費的墊繳、附約的停效及復效 | 第五條 附約的保險期間及保證續保 | 第十三條 健康促進保險費折減 | 第九條 附約的終止（一）</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F261" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+主約效力因身故以外的情形終止時，PX5附約仍可持續有效，但需符合以下條件：  
+1. 要保人需繼續繳交附約保險費。  
+2. 附約效力可延續至主約原保險期間屆滿或附約最高續保年齡（80歲），以較早者為準。  
+條文依據：  
+- [第十條 附約的終止（二）]</t>
+        </is>
+      </c>
+      <c r="G261" s="2" t="inlineStr"/>
+      <c r="H261" s="2" t="inlineStr"/>
+      <c r="I261" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "請問主約效力終止(因身故以外情形)，PX5還能持續有效嗎？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.051336, "neutral": 0.947685, "contradiction": 0.000979, "factuality": 0.999021, "C_fact": 0.999021}, "C_conf": 0.9994}</t>
+        </is>
+      </c>
+      <c r="J261" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K261" s="3" t="n">
+        <v>0.999021</v>
+      </c>
+      <c r="L261" s="3" t="n">
+        <v>0.9994</v>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:43:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>請問如果於「無理賠紀錄期間」屆滿日以內罹患特定傷病，會給付多少錢?這筆錢會給付給誰?</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在「無理賠紀錄期間」屆滿日以內罹患特定傷病，保險公司將給付的金額為「保險金額」加上「年繳應繳保險費總額」乘以1.02的加總。這筆「特定傷病保險金」的受益人為被保險人本人，且不得指定或變更。
+條文依據：  
+- [第十一條 特定傷病保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第十二條 無理賠關懷保險金的給付 | 第十一條 特定傷病保險金的給付 | payout_items | 第二十七條 受益人的指定及變更</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F262" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在「無理賠紀錄期間」屆滿日以內罹患特定傷病，保險公司將給付的金額為「保險金額」加上「年繳應繳保險費總額」乘以1.02的加總。這筆「特定傷病保險金」的受益人為被保險人本人，且不得指定或變更。
+條文依據：  
+- [第十一條 特定傷病保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="G262" s="2" t="inlineStr"/>
+      <c r="H262" s="2" t="inlineStr"/>
+      <c r="I262" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "請問如果於「無理賠紀錄期間」屆滿日以內罹患特定傷病，會給付多少錢?這筆錢會給付給誰?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.996866, "neutral": 0.00284, "contradiction": 0.000294, "factuality": 0.999706, "C_fact": 0.999706}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J262" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K262" s="3" t="n">
+        <v>0.999706</v>
+      </c>
+      <c r="L262" s="3" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:43:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>請問如果要保人與被保險人為同一人，被保險人於「無理賠紀錄期間」屆滿日以內身故，會給付多少錢?這筆錢會給付給誰?</t>
+        </is>
+      </c>
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+在要保人與被保險人為同一人的情況下，若被保險人在「無理賠紀錄期間」屆滿日以內身故，依第十二條規定，本公司將給付「無理賠關懷保險金」，金額為「年繳應繳保險費總額」乘以1.02。根據第二十七條，無理賠關懷保險金的受益人為要保人本人，若要保人與被保險人為同一人，則該筆保險金的受益人為被保險人的法定繼承人。
+條文依據：  
+- [第十二條 無理賠關懷保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第十二條 無理賠關懷保險金的給付 | 第十一條 特定傷病保險金的給付 | payout_items | 第十九條 失蹤處理 | 第二十一條 無理賠關懷保險金的申領 | 第二十七條 受益人的指定及變更 | 第十七條 除外責任（二）</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F263" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+在要保人與被保險人為同一人的情況下，若被保險人在「無理賠紀錄期間」屆滿日以內身故，依第十二條規定，本公司將給付「無理賠關懷保險金」，金額為「年繳應繳保險費總額」乘以1.02。根據第二十七條，無理賠關懷保險金的受益人為要保人本人，若要保人與被保險人為同一人，則該筆保險金的受益人為被保險人的法定繼承人。
+條文依據：  
+- [第十二條 無理賠關懷保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="G263" s="2" t="inlineStr"/>
+      <c r="H263" s="2" t="inlineStr"/>
+      <c r="I263" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認要保人與被保險人為同一人的情況下的理賠規定", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認被保險人在無理賠紀錄期間屆滿日以內身故的理賠金額", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認身故保險金的受益人為何人", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認無理賠紀錄期間的定義與適用條件", "must_have": false, "分數": 0.8}], "coverage_score": 0.9846, "nli": {"entailment": 0.996567, "neutral": 0.003154, "contradiction": 0.000279, "factuality": 0.999721, "C_fact": 0.999721}, "C_conf": 0.9844}</t>
+        </is>
+      </c>
+      <c r="J263" s="3" t="n">
+        <v>0.9846</v>
+      </c>
+      <c r="K263" s="3" t="n">
+        <v>0.999721</v>
+      </c>
+      <c r="L263" s="3" t="n">
+        <v>0.9844000000000001</v>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:43:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>請問如果要保人與被保險人為不同人，被保險人於「無理賠紀錄期間」屆滿日以內生存，且被保險人未罹患特定傷病，會給付多少錢?這筆錢會給付給誰?</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若要保人與被保險人為不同人，且被保險人在「無理賠紀錄期間」屆滿日以內生存，並未罹患特定傷病，則符合給付「無理賠關懷保險金」的條件。給付金額為「年繳應繳保險費總額」乘以1.02。該筆保險金的受益人為要保人本人。
+條文依據：  
+- [第十二條 無理賠關懷保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第十二條 無理賠關懷保險金的給付 | 第十一條 特定傷病保險金的給付 | payout_items | 第二十七條 受益人的指定及變更 | 第十九條 失蹤處理 | 第二十一條 無理賠關懷保險金的申領 | 第十七條 除外責任（二）</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F264" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若要保人與被保險人為不同人，且被保險人在「無理賠紀錄期間」屆滿日以內生存，並未罹患特定傷病，則符合給付「無理賠關懷保險金」的條件。給付金額為「年繳應繳保險費總額」乘以1.02。該筆保險金的受益人為要保人本人。
+條文依據：  
+- [第十二條 無理賠關懷保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="G264" s="2" t="inlineStr"/>
+      <c r="H264" s="2" t="inlineStr"/>
+      <c r="I264" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認要保人與被保險人為不同人時的保險條款適用", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認無理賠紀錄期間屆滿日生存的給付金額", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認被保險人未罹患特定傷病的條件對給付的影響", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認該筆給付金額的受益人為何人", "must_have": true, "分數": 1.0}, {"id": "5", "point": "確認特定傷病的定義及範圍", "must_have": false, "分數": 0.0}], "coverage_score": 0.9412, "nli": {"entailment": 0.987908, "neutral": 0.01156, "contradiction": 0.000532, "factuality": 0.999468, "C_fact": 0.999468}, "C_conf": 0.9409}</t>
+        </is>
+      </c>
+      <c r="J264" s="3" t="n">
+        <v>0.9412</v>
+      </c>
+      <c r="K264" s="3" t="n">
+        <v>0.999468</v>
+      </c>
+      <c r="L264" s="3" t="n">
+        <v>0.9409</v>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:44:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>保戶如果身故，會給保險金嗎?身故保險金、特定傷病保險金及無理賠關懷保險金？</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 本保單條款未明確規定「身故保險金」保障，無法確認是否包含此項保障。  
+2. 本保單條款包含「特定傷病保險金」保障，給付條件為被保險人在等待期間屆滿翌日或復效日起的契約有效期間內，經初次診斷確定罹患特定傷病，且符合第十一條規定的計算方式。  
+3. 本保單條款包含「無理賠關懷保險金」保障，給付條件為被保險人在「無理賠紀錄期間」內未曾申領特定傷病保險金，且於該期間內身故或屆滿時仍生存。  
+條文依據：  
+- [第五條 保險範圍]  
+- [第十一條 特定傷病保險金的給付]  
+- [第十二條 無理賠關懷保險金的給付]  
+- [第二十一條 無理賠關懷保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D265" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第十九條 失蹤處理 | 第二十一條 無理賠關懷保險金的申領 | 第十條 契約的終止（二） | 第二條 名詞定義 | 第二十七條 受益人的指定及變更 | 第二十八條 本契約受益人死亡或失蹤的處理 | 第二十條 特定傷病保險金的申領 | 第二十二條 分期定期保險金給付申領文件、給付期限及未依限給付之效果 | 第十二條 無理賠關懷保險金的給付</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F265" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 本保單條款中未提及「身故保險金」保障，無法確認是否包含此項保障。  
+2. 本保單條款包含「特定傷病保險金」保障，給付條件為被保險人在等待期間屆滿翌日或復效日起的契約有效期間內，經初次診斷確定罹患特定傷病，且符合第十一條規定的計算方式。  
+3. 本保單條款包含「無理賠關懷保險金」保障，給付條件為被保險人在「無理賠紀錄期間」內未曾申領特定傷病保險金，且於該期間內身故或屆滿時仍生存。  
+條文依據：  
+- [第十一條 特定傷病保險金的給付]  
+- [第十二條 無理賠關懷保險金的給付]  
+- 找不到相關內容（關於身故保險金）</t>
+        </is>
+      </c>
+      <c r="G265" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 本保單條款未明確規定「身故保險金」保障，無法確認是否包含此項保障。  
+2. 本保單條款包含「特定傷病保險金」保障，給付條件為被保險人在等待期間屆滿翌日或復效日起的契約有效期間內，經初次診斷確定罹患特定傷病，且符合第十一條規定的計算方式。  
+3. 本保單條款包含「無理賠關懷保險金」保障，給付條件為被保險人在「無理賠紀錄期間」內未曾申領特定傷病保險金，且於該期間內身故或屆滿時仍生存。  
+條文依據：  
+- [第五條 保險範圍]  
+- [第十一條 特定傷病保險金的給付]  
+- [第十二條 無理賠關懷保險金的給付]  
+- [第二十一條 無理賠關懷保險金的申領]</t>
+        </is>
+      </c>
+      <c r="H265" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 本保單條款未明確規定「身故保險金」保障，無法確認是否包含此項保障。  
+2. 本保單條款包含「特定傷病保險金」保障，給付條件為被保險人在等待期間屆滿翌日或復效日起的契約有效期間內，經初次診斷確定罹患特定傷病，且符合第十一條規定的計算方式。  
+3. 本保單條款包含「無理賠關懷保險金」保障，給付條件為被保險人在「無理賠紀錄期間」內未曾申領特定傷病保險金，且於該期間內身故或屆滿時仍生存。  
+條文依據：  
+- [第五條 保險範圍]  
+- [第十一條 特定傷病保險金的給付]  
+- [第十二條 無理賠關懷保險金的給付]  
+- [第二十一條 無理賠關懷保險金的申領]</t>
+        </is>
+      </c>
+      <c r="I265" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認保單是否包含身故保險金保障", "must_have": true, "分數": 0.5}, {"id": "2", "point": "確認保單是否包含特定傷病保險金保障", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認保單是否包含無理賠關懷保險金保障", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認各項保險金的給付條件與範圍", "must_have": false, "分數": 1.0}], "coverage_score": 0.8462, "nli": {"entailment": 0.925245, "neutral": 0.028425, "contradiction": 0.04633, "factuality": 0.95367, "C_fact": 0.95367}, "C_conf": 0.8225}</t>
+        </is>
+      </c>
+      <c r="J265" s="3" t="n">
+        <v>0.8462</v>
+      </c>
+      <c r="K265" s="3" t="n">
+        <v>0.95367</v>
+      </c>
+      <c r="L265" s="3" t="n">
+        <v>0.8225</v>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:44:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>保戶如果身故，身故申領的保險金會給誰?</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人身故，身故保險金的受益人為被保險人之法定繼承人，其受益順序及應得比例依民法繼承編相關規定處理。若受益人故意致被保險人於死或雖未致死，該受益人將喪失受益權，並由其他受益人按原約定比例分配，或作為被保險人遺產處理。
+條文依據：  
+- [第二十三條 受益人受益權之喪失]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第二十三條 受益人受益權之喪失 | 第二十七條 受益人的指定及變更 | 第二十八條 本契約受益人死亡或失蹤的處理 | 第二十二條 分期定期保險金給付申領文件、給付期限及未依限給付之效果</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F266" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人身故，身故保險金的受益人為被保險人之法定繼承人，其受益順序及應得比例依民法繼承編相關規定處理。若受益人故意致被保險人於死或雖未致死，該受益人將喪失受益權，並由其他受益人按原約定比例分配，或作為被保險人遺產處理。
+條文依據：  
+- [第二十三條 受益人受益權之喪失]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="G266" s="2" t="inlineStr"/>
+      <c r="H266" s="2" t="inlineStr"/>
+      <c r="I266" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "保戶如果身故，身故申領的保險金會給誰?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.988507, "neutral": 0.011145, "contradiction": 0.000349, "factuality": 0.999651, "C_fact": 0.999651}, "C_conf": 0.9998}</t>
+        </is>
+      </c>
+      <c r="J266" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K266" s="3" t="n">
+        <v>0.999651</v>
+      </c>
+      <c r="L266" s="3" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:45:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>如果保戶投保繳費年期20年的滿溢寶，然後在第20保單年度身故的話，可以領到多少錢?無理賠關懷保險金?受益人為要保人嗎？</t>
+        </is>
+      </c>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 若保戶於第20保單年度身故，需確認是否符合「無理賠關懷保險金」的給付條件。依條款，被保險人於「無理賠紀錄期間」內未曾因罹患特定傷病而申領「特定傷病保險金」，且於「無理賠紀錄期間」內身故者，本公司按「年繳應繳保險費總額」乘以1.02，給付「無理賠關懷保險金」[第十二條 無理賠關懷保險金的給付]。  
+2. 無理賠關懷保險金的受益人為要保人本人，本公司不受理其指定及變更。如無理賠關懷保險金受益人同時或先於被保險人本人身故，以被保險人為該項保險金受益人；若被保險人已身故，則以被保險人之法定繼承人為該項保險金受益人[第二十七條 受益人的指定及變更]。  
+3. 滿溢寶保單的繳費年期為20年，但條款中未提及保障年期的具體規定，因此無法確認繳費年期與保障年期的關係。  
+條文依據：  
+- [第十二條 無理賠關懷保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="inlineStr">
+        <is>
+          <t>第二十七條 受益人的指定及變更 | 第十九條 失蹤處理 | 第十二條 無理賠關懷保險金的給付 | 第十七條 除外責任（二） | 第二十一條 無理賠關懷保險金的申領 | 第二十八條 本契約受益人死亡或失蹤的處理 | 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F267" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 若保戶於第20保單年度身故，需確認是否符合「特定傷病保險金」或「無理賠關懷保險金」的給付條件。依條款，第20保單年度屬於「無理賠紀錄期間」內，若被保險人未曾申領「特定傷病保險金」，且於該期間內身故，則可領取「無理賠關懷保險金」，金額為「年繳應繳保險費總額」乘以1.02。  
+2. 本案例中，無理賠關懷保險金的給付條件已滿足，因此包含無理賠關懷保險金。  
+3. 無理賠關懷保險金的受益人為要保人本人，若要保人已身故，則以被保險人為受益人；若被保險人亦已身故，則以被保險人的法定繼承人為受益人。  
+4. 滿溢寶保單的繳費年期為20年，但條款中未提及保障年期的具體規定，因此無法確認繳費年期與保障年期的關係。  
+條文依據：  
+- [第十二條 無理賠關懷保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="G267" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 若保戶於第20保單年度身故，需確認是否符合「無理賠關懷保險金」的給付條件。依條款，被保險人於「無理賠紀錄期間」內未曾因罹患特定傷病而申領「特定傷病保險金」，且於「無理賠紀錄期間」內身故者，本公司按「年繳應繳保險費總額」乘以1.02，給付「無理賠關懷保險金」[第十二條 無理賠關懷保險金的給付]。  
+2. 無理賠關懷保險金的受益人為要保人本人，本公司不受理其指定及變更。如無理賠關懷保險金受益人同時或先於被保險人本人身故，以被保險人為該項保險金受益人；若被保險人已身故，則以被保險人之法定繼承人為該項保險金受益人[第二十七條 受益人的指定及變更]。  
+3. 滿溢寶保單的繳費年期為20年，但條款中未提及保障年期的具體規定，因此無法確認繳費年期與保障年期的關係。  
+條文依據：  
+- [第十二條 無理賠關懷保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="H267" s="2" t="inlineStr"/>
+      <c r="I267" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認滿溢寶保單在第20保單年度身故的理賠金額", "must_have": true, "分數": 0.8}, {"id": "2", "point": "確認是否包含無理賠關懷保險金", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認受益人是否為要保人", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認滿溢寶保單的繳費年期與保障年期的關係", "must_have": false, "分數": 0.5}], "coverage_score": 0.9, "nli": {"entailment": 0.053168, "neutral": 0.93572, "contradiction": 0.011112, "factuality": 0.988888, "C_fact": 0.988888}, "C_conf": 0.894}</t>
+        </is>
+      </c>
+      <c r="J267" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K267" s="3" t="n">
+        <v>0.988888</v>
+      </c>
+      <c r="L267" s="3" t="n">
+        <v>0.894</v>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:45:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>被保險人為60歲女性，投保繳費期間20年期之滿溢寶特定傷病定期健康保險（定期給付型）（外溢型）100萬元，年繳應繳保險費為83,500元，年繳實繳保險費為78,490元。若被保險人於第二保險單年度自殺身故，則無理賠關懷保險金可以領到多少錢？</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於第二保險單年度自殺身故，根據條款規定，自契約訂立或復效之日起二年內故意自殺致死者，本公司不負給付無理賠關懷保險金的責任。因此，本案例中無理賠關懷保險金無法領取。
+條文依據：  
+- [第十七條 除外責任（二）]  
+- [第十二條 無理賠關懷保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 無理賠關懷保險金的給付 | 第十七條 除外責任（二） | 第十一條 特定傷病保險金的給付 | other_metadata | 第十九條 失蹤處理 | 第五條 保險範圍 | 第二十一條 無理賠關懷保險金的申領 | 第二十七條 受益人的指定及變更</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F268" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於第二保險單年度自殺身故，根據條款規定，自契約訂立或復效之日起二年內故意自殺致死者，本公司不負給付無理賠關懷保險金的責任。因此，本案例中無理賠關懷保險金無法領取。
+條文依據：  
+- [第十七條 除外責任（二）]  
+- [第十二條 無理賠關懷保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G268" s="2" t="inlineStr"/>
+      <c r="H268" s="2" t="inlineStr"/>
+      <c r="I268" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認保險契約中自殺身故的理賠條款", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認第二保險單年度是否屬於保單等待期內", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認無理賠關懷保險金的計算方式或條件", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認年繳實繳保險費是否影響無理賠關懷保險金的金額", "must_have": false, "分數": 0.0}], "coverage_score": 0.9231, "nli": {"entailment": 0.821507, "neutral": 0.156803, "contradiction": 0.02169, "factuality": 0.97831, "C_fact": 0.97831}, "C_conf": 0.911}</t>
+        </is>
+      </c>
+      <c r="J268" s="3" t="n">
+        <v>0.9231</v>
+      </c>
+      <c r="K268" s="3" t="n">
+        <v>0.97831</v>
+      </c>
+      <c r="L268" s="3" t="n">
+        <v>0.911</v>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:46:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>請問如果第2保單年度罹患特定傷病，可以給付多少錢?給付給誰?未來還有其他保險金嗎?</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. **給付金額**：若於第二保險單年度（含）以後罹患特定傷病，將依「保險金額」給付「特定傷病保險金」。  
+2. **給付對象**：保險金給付予被保險人或其指定受益人。  
+3. **未來保險金**：自診斷確定罹患特定傷病的次一個保險單週年日起，每逢保險單週年日仍生存者，可按「保險金額」的36%給付「生活補助保險金」，最多給付10次。此外，自診斷確定日起，豁免續期保險費，但當期已繳付之未到期保險費不予退還。
+條文依據：  
+- [第十二條 特定傷病保險金的給付]  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]  
+- [第十五條 保險費豁免（第二保險單年度起適用）]</t>
+        </is>
+      </c>
+      <c r="D269" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 特定傷病保險金的給付 | 第五條 保險範圍 | 第十三條 生活補助保險金的給付（第二保險單年度起適用） | 第二條 名詞定義 | 第十五條 保險費豁免（第二保險單年度起適用）</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F269" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. **給付金額**：若於第二保險單年度（含）以後罹患特定傷病，將依「保險金額」給付「特定傷病保險金」。  
+2. **給付對象**：保險金給付予被保險人或其指定受益人。  
+3. **未來保險金**：自診斷確定罹患特定傷病的次一個保險單週年日起，每逢保險單週年日仍生存者，可按「保險金額」的36%給付「生活補助保險金」，最多給付10次。此外，自診斷確定日起，豁免續期保險費，但當期已繳付之未到期保險費不予退還。
+條文依據：  
+- [第十二條 特定傷病保險金的給付]  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]  
+- [第十五條 保險費豁免（第二保險單年度起適用）]</t>
+        </is>
+      </c>
+      <c r="G269" s="2" t="inlineStr"/>
+      <c r="H269" s="2" t="inlineStr"/>
+      <c r="I269" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "請問如果第2保單年度罹患特定傷病，可以給付多少錢?給付給誰?未來還有其他保險金嗎?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.152174, "neutral": 0.836815, "contradiction": 0.011011, "factuality": 0.988989, "C_fact": 0.988989}, "C_conf": 0.9934}</t>
+        </is>
+      </c>
+      <c r="J269" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K269" s="3" t="n">
+        <v>0.988989</v>
+      </c>
+      <c r="L269" s="3" t="n">
+        <v>0.9933999999999999</v>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:46:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>請問我115年1月1日投保，怎麼得到健康促進保險費折減?指定日期什麼時後？</t>
+        </is>
+      </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 健康促進保險費折減的申請條件為：被保險人需使用保險公司指定的程式並加入指定的健康計劃，於「指定日期」的會員等級符合「實踐家」或「樂享家」以上標準，方可享有次一保險單年度的保險費折減。折減比例為「實踐家」3%、「樂享家」或更高等級10%。  
+2. 115年1月1日投保者，若於保單生效後完成指定程式的註冊程序，並於「指定日期」達到符合的會員等級，即可符合折減資格。  
+3. 「指定日期」未在條文中明確定義，但折減適用於次一保險單年度的保險費，推測「指定日期」應在首保險單年度內的某一時點，需依保險公司進一步通知確認。  
+4. 健康促進活動或行為為折減的必要條件，因被保險人需執行指定程式並授權保險公司取得健康促進相關電子紀錄，保險公司將依此計算會員等級。
+條文依據：  
+- [第十六條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="D270" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 健康促進保險費折減 | 第十五條 保險費豁免（第二保險單年度起適用） | 第五條 保險範圍 | 第二十三條 投保年齡的計算及錯誤的處理 | 第十二條 特定傷病保險金的給付 | 第十條 契約的終止（二） | 第十三條 生活補助保險金的給付（第二保險單年度起適用） | payout_items</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F270" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 健康促進保險費折減的申請條件為：被保險人需使用保險公司指定的程式並加入指定的健康計劃，於「指定日期」的會員等級符合「實踐家」或「樂享家」以上標準，方可享有次一保險單年度的保險費折減。折減比例為「實踐家」3%、「樂享家」或更高等級10%。  
+2. 115年1月1日投保者，若於保單生效後完成指定程式的註冊程序，並於「指定日期」達到符合的會員等級，即可符合折減資格。  
+3. 「指定日期」未在條文中明確定義，但折減適用於次一保險單年度的保險費，推測「指定日期」應在首保險單年度內的某一時點，需依保險公司進一步通知確認。  
+4. 健康促進活動或行為為折減的必要條件，因被保險人需執行指定程式並授權保險公司取得健康促進相關電子紀錄，保險公司將依此計算會員等級。
+條文依據：  
+- [第十六條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="G270" s="2" t="inlineStr"/>
+      <c r="H270" s="2" t="inlineStr"/>
+      <c r="I270" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認健康促進保險費折減的申請條件", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認115年1月1日投保是否符合折減資格", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認健康促進保險費折減的指定日期及適用時間", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認健康促進活動或行為是否為折減的必要條件", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.527893, "neutral": 0.468314, "contradiction": 0.003793, "factuality": 0.996207, "C_fact": 0.996207}, "C_conf": 0.9977}</t>
+        </is>
+      </c>
+      <c r="J270" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K270" s="3" t="n">
+        <v>0.996207</v>
+      </c>
+      <c r="L270" s="3" t="n">
+        <v>0.9977</v>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:47:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>保戶在114/1/10投保樂鍾溢，如果他在115/3/30罹患特定傷病的話，在什麼時候可以領取生活補助保險金?</t>
+        </is>
+      </c>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 樂鍾溢保單包含生活補助保險金保障，條文第十三條明確規定於第二保險單年度（含）以後，被保險人初次診斷確定罹患特定傷病，且於次一個保險單週年日起仍生存者，可按保險金額的36%給付生活補助保險金。  
+2. 保戶於115/3/30診斷確定罹患特定傷病，符合生活補助保險金的理賠條件，因其診斷時間已超過等待期間（30日），且發生於第二保險單年度內。  
+3. 保單生效日為114/1/10，第二保險單年度自115/1/10起算，115/3/30的診斷時間符合條件。  
+4. 生活補助保險金的給付時間為診斷確定後的次一個保險單週年日，即116/1/10起，若被保險人於該日仍生存，可領取第一筆生活補助保險金。
+條文依據：  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]  
+- [第十二條 特定傷病保險金的給付]  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="D271" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 生活補助保險金的給付（第二保險單年度起適用） | other_metadata | 第十一條 契約的終止（三） | payout_items | 第十二條 特定傷病保險金的給付 | 第五條 保險範圍 | 第十五條 保險費豁免（第二保險單年度起適用） | 第十條 契約的終止（二）</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F271" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 樂鍾溢保單包含生活補助保險金保障，條文第十三條明確規定於第二保險單年度（含）以後，被保險人初次診斷確定罹患特定傷病，且於次一個保險單週年日起仍生存者，可按保險金額的36%給付生活補助保險金。  
+2. 保戶於115/3/30診斷確定罹患特定傷病，符合生活補助保險金的理賠條件，因其診斷時間已超過等待期間（30日），且發生於第二保險單年度內。  
+3. 保單生效日為114/1/10，第二保險單年度自115/1/10起算，115/3/30的診斷時間符合條件。  
+4. 生活補助保險金的給付時間為診斷確定後的次一個保險單週年日，即116/1/10起，若被保險人於該日仍生存，可領取第一筆生活補助保險金。
+條文依據：  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]  
+- [第十二條 特定傷病保險金的給付]  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="G271" s="2" t="inlineStr"/>
+      <c r="H271" s="2" t="inlineStr"/>
+      <c r="I271" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認樂鍾溢保單是否包含生活補助保險金保障", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認特定傷病是否符合生活補助保險金的理賠條件", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認保單生效日與115/3/30之間的時間是否符合理賠規定", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認生活補助保險金的給付時間或申請流程", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.934743, "neutral": 0.057145, "contradiction": 0.008112, "factuality": 0.991888, "C_fact": 0.991888}, "C_conf": 0.9951}</t>
+        </is>
+      </c>
+      <c r="J271" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K271" s="3" t="n">
+        <v>0.991888</v>
+      </c>
+      <c r="L271" s="3" t="n">
+        <v>0.9951</v>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:47:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="inlineStr">
+        <is>
+          <t>保戶在114/1/10投保樂鍾溢，如果他在115/3/30罹患特定傷病的話，他在115/1/9會領到無理賠回饋保險金嗎?保險單週年日什麼時候？指定日期什麼時候？</t>
+        </is>
+      </c>
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 保險單週年日為每年的1月10日，因為保戶於114/1/10投保，保險單週年日即為保單生效日的每年對應日期。  
+2. 115/1/9符合無理賠回饋保險金的領取條件，因為根據條款規定，需於保險單年度末仍生存且未曾申領特定傷病保險金才可領取，而保戶於115/3/30罹患特定傷病，該診斷日期屬於第二保險單年度，並不影響第一保險單年度末的資格，因此115/1/9應符合條件。  
+3. 指定日期未在條款中明確提及，無法確認具體時間。  
+條文依據：  
+- [第十四條 無理賠回饋保險金的給付]  
+- [第十二條 特定傷病保險金的給付]  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="D272" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 無理賠回饋保險金的給付 | 第十二條 特定傷病保險金的給付 | 第十五條 保險費豁免（第二保險單年度起適用） | 第十條 契約的終止（二） | 第五條 保險範圍 | 第二十條 無理賠回饋保險金的申領</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F272" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 保險單週年日為每年的1月10日，因為保戶於114/1/10投保，保險單週年日即為保單生效日的每年對應日期。  
+2. 115/1/9不符合無理賠回饋保險金的領取條件，因為根據條款規定，需於保險單年度末仍生存且未曾申領特定傷病保險金才可領取，而保戶於115/3/30罹患特定傷病，該診斷日期屬於第二保險單年度，並不影響第一保險單年度末的資格，因此115/1/9應符合條件。  
+3. 115/3/30罹患特定傷病不影響115/1/9的無理賠回饋保險金領取資格，因為該診斷日期屬於第二保險單年度，與第一保險單年度末的資格無關。  
+4. 指定日期未在條款中明確提及，無法確認具體時間。  
+條文依據：  
+- [第十四條 無理賠回饋保險金的給付]  
+- [第十二條 特定傷病保險金的給付]  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="G272" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 保險單週年日為每年的1月10日，因為保戶於114/1/10投保，保險單週年日即為保單生效日的每年對應日期。  
+2. 115/1/9符合無理賠回饋保險金的領取條件，因為根據條款規定，需於保險單年度末仍生存且未曾申領特定傷病保險金才可領取，而保戶於115/3/30罹患特定傷病，該診斷日期屬於第二保險單年度，並不影響第一保險單年度末的資格，因此115/1/9應符合條件。  
+3. 指定日期未在條款中明確提及，無法確認具體時間。  
+條文依據：  
+- [第十四條 無理賠回饋保險金的給付]  
+- [第十二條 特定傷病保險金的給付]  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="H272" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 保險單週年日為每年的1月10日，因為保戶於114/1/10投保，保險單週年日即為保單生效日的每年對應日期。  
+2. 115/1/9符合無理賠回饋保險金的領取條件，因為根據條款規定，需於保險單年度末仍生存且未曾申領特定傷病保險金才可領取，而保戶於115/3/30罹患特定傷病，該診斷日期屬於第二保險單年度，並不影響第一保險單年度末的資格，因此115/1/9應符合條件。  
+3. 指定日期未在條款中明確提及，無法確認具體時間。  
+條文依據：  
+- [第十四條 無理賠回饋保險金的給付]  
+- [第十二條 特定傷病保險金的給付]  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="I272" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認保險單週年日的日期", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認115/1/9是否符合無理賠回饋保險金的領取條件", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認115/3/30罹患特定傷病是否影響無理賠回饋保險金的領取資格", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認指定日期的具體時間", "must_have": false, "分數": 0.5}], "coverage_score": 0.9615, "nli": {"entailment": 0.001348, "neutral": 0.002115, "contradiction": 0.996538, "factuality": 0.003462, "C_fact": 0.003462}, "C_conf": 0.0321}</t>
+        </is>
+      </c>
+      <c r="J272" s="3" t="n">
+        <v>0.9615</v>
+      </c>
+      <c r="K272" s="4" t="n">
+        <v>0.003462</v>
+      </c>
+      <c r="L272" s="4" t="n">
+        <v>0.0321</v>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:47:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="inlineStr">
+        <is>
+          <t>被保險人於第一保險單年度罹患急性心肌梗塞（重度），生活補助保險金最多可以領取幾次？契約會終止嗎？</t>
+        </is>
+      </c>
+      <c r="C273" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 生活補助保險金的給付次數上限為十次，但此項保險金僅適用於第二保險單年度（含）以後，第一保險單年度內不適用，因此被保險人於第一保險單年度罹患急性心肌梗塞（重度）無法領取生活補助保險金。  
+2. 若被保險人於第一保險單年度內罹患急性心肌梗塞（重度），契約將依第十一條第三款規定終止，且不再有效。  
+條文依據：  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]  
+- [第十一條 契約的終止（三）]</t>
+        </is>
+      </c>
+      <c r="D273" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 生活補助保險金的給付（第二保險單年度起適用） | 第十一條 契約的終止（三） | 第五條 保險範圍 | 第二條 名詞定義 | 第十二條 特定傷病保險金的給付 | 第十五條 保險費豁免（第二保險單年度起適用） | payout_items | 第十條 契約的終止（二）</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F273" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 生活補助保險金的給付次數上限為十次，但此項保險金僅適用於第二保險單年度（含）以後，第一保險單年度內不適用，因此被保險人於第一保險單年度罹患急性心肌梗塞（重度）無法領取生活補助保險金。  
+2. 若被保險人於第一保險單年度內罹患急性心肌梗塞（重度），契約將依第十一條第三款規定終止，且不再有效。  
+條文依據：  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]  
+- [第十一條 契約的終止（三）]</t>
+        </is>
+      </c>
+      <c r="G273" s="2" t="inlineStr"/>
+      <c r="H273" s="2" t="inlineStr"/>
+      <c r="I273" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認生活補助保險金的給付次數上限", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認罹患急性心肌梗塞（重度）是否影響契約終止", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認第一保險單年度內的相關條款限制", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "nli": {"entailment": 0.984357, "neutral": 0.013344, "contradiction": 0.0023, "factuality": 0.9977, "C_fact": 0.9977}, "C_conf": 0.9986}</t>
+        </is>
+      </c>
+      <c r="J273" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K273" s="3" t="n">
+        <v>0.9977</v>
+      </c>
+      <c r="L273" s="3" t="n">
+        <v>0.9986</v>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:48:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <t>被保險人為60歲女性，投保繳費期間20年期之樂鍾心特定傷病定期健康保險（外溢型）5單位，每單位年繳應繳保險費為1675元，則每逢保險單年度末生存者，可以領取多少無理賠關懷保險金？</t>
+        </is>
+      </c>
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款規定，無理賠回饋保險金的計算方式為：「每單位年繳應繳保險費」的10%（元以下無條件進位）乘以「單位數」。  
+1. 每單位年繳應繳保險費為1675元，10%為167.5元，元以下無條件進位後為168元。  
+2. 投保5單位，則168元 × 5單位 = 840元。  
+因此，每逢保險單年度末生存者，可以領取的無理賠回饋保險金為840元。
+條文依據：  
+- [第十四條 無理賠回饋保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D274" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 無理賠回饋保險金的給付 | other_metadata | payout_items | 第二十條 無理賠回饋保險金的申領 | 第十二條 特定傷病保險金的給付 | 第十三條 生活補助保險金的給付（第二保險單年度起適用） | 第五條 保險範圍 | 第十五條 保險費豁免（第二保險單年度起適用）</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F274" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款規定，無理賠回饋保險金的計算方式為：「每單位年繳應繳保險費」的10%（元以下無條件進位）乘以「單位數」。  
+1. 每單位年繳應繳保險費為1675元，10%為167.5元，元以下無條件進位後為168元。  
+2. 投保5單位，則168元 × 5單位 = 840元。  
+因此，每逢保險單年度末生存者，可以領取的無理賠回饋保險金為840元。
+條文依據：  
+- [第十四條 無理賠回饋保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G274" s="2" t="inlineStr"/>
+      <c r="H274" s="2" t="inlineStr"/>
+      <c r="I274" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認樂鍾心特定傷病定期健康保險（外溢型）的無理賠關懷保險金計算方式", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認每單位年繳保險費為1675元的相關條件", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認投保5單位對無理賠關懷保險金的影響", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認保險單年度末生存者的定義與條件", "must_have": false, "分數": 0.8}], "coverage_score": 0.9846, "nli": {"entailment": 0.995197, "neutral": 0.004468, "contradiction": 0.000335, "factuality": 0.999665, "C_fact": 0.999665}, "C_conf": 0.9844}</t>
+        </is>
+      </c>
+      <c r="J274" s="3" t="n">
+        <v>0.9846</v>
+      </c>
+      <c r="K274" s="3" t="n">
+        <v>0.999665</v>
+      </c>
+      <c r="L274" s="3" t="n">
+        <v>0.9844000000000001</v>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:48:46</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/rag_results.xlsx
+++ b/src/rag_results.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N337"/>
+  <dimension ref="A1:N420"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -22712,6 +22712,5453 @@
         <v>17.55</v>
       </c>
     </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B338" s="2" t="inlineStr">
+        <is>
+          <t>保障範圍包括哪些項目？</t>
+        </is>
+      </c>
+      <c r="C338" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括：住院醫療保險金、加護病房或燒燙傷病房保險金、祝壽保險金、身故保險金或喪葬費用保險金，以及所繳保險費的退還。
+條文依據：  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="D338" s="2" t="inlineStr">
+        <is>
+          <t>payout_items | summary | 第五條 保險範圍 | 第二條 名詞定義 | 第十八條 除外責任（一）</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F338" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括：住院醫療保險金、加護病房或燒燙傷病房保險金、祝壽保險金、身故保險金或喪葬費用保險金，以及所繳保險費的退還。
+條文依據：  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="G338" s="2" t="inlineStr"/>
+      <c r="H338" s="2" t="inlineStr"/>
+      <c r="I338" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "保障範圍包括哪些項目？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J338" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K338" s="4" t="n"/>
+      <c r="L338" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M338" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:52:09</t>
+        </is>
+      </c>
+      <c r="N338" s="4" t="n">
+        <v>19.74</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B339" s="2" t="inlineStr">
+        <is>
+          <t>因同一疾病或傷害再次住院、若間隔時間在出院後十四日內或因併發症導致的再次住院日數計算有什麼特殊規則？</t>
+        </is>
+      </c>
+      <c r="C339" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 若被保險人因同一疾病或傷害，或因此引起的併發症，在出院後十四日內再次住院，則該次住院的保險金給付限制，視為同一次住院處理。  
+2. 因併發症導致的再次住院，若符合上述十四日內的條件，住院日數計算亦視為同一次住院。  
+3. 特殊規定：若再次住院的間隔時間在出院後十四日內，則不論是因同一疾病或傷害，或其併發症，均視為同一次住院。  
+條文依據：  
+- [第十一條 住院次數之計算及契約有效期間屆滿後住院之處理]</t>
+        </is>
+      </c>
+      <c r="D339" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第十三條 加護病房或燒燙傷病房保險金的給付 | 第二條 名詞定義 | 第十二條 住院醫療保險金的給付 | 第十八條 除外責任（一） | 第二十八條 住院醫療保險金日額之減少</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F339" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 若被保險人因同一疾病或傷害，或因此引起的併發症，在出院後十四日內再次住院，則該次住院的保險金給付限制，視為同一次住院處理。  
+2. 因併發症導致的再次住院，若符合上述十四日內的條件，住院日數計算亦視為同一次住院。  
+3. 特殊規定：若再次住院的間隔時間在出院後十四日內，則不論是因同一疾病或傷害，或其併發症，均視為同一次住院。  
+條文依據：  
+- [第十一條 住院次數之計算及契約有效期間屆滿後住院之處理]</t>
+        </is>
+      </c>
+      <c r="G339" s="2" t="inlineStr"/>
+      <c r="H339" s="2" t="inlineStr"/>
+      <c r="I339" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認同一疾病或傷害再次住院的間隔時間規則", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認因併發症導致的再次住院日數計算方式", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認是否有十四日內再次住院的特殊規定", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認保單條款中對於住院日數計算的相關細節", "must_have": false, "分數": 0.8}], "coverage_score": 0.9846, "C_conf": 0.9846}</t>
+        </is>
+      </c>
+      <c r="J339" s="4" t="n">
+        <v>0.9846</v>
+      </c>
+      <c r="K339" s="4" t="n"/>
+      <c r="L339" s="4" t="n">
+        <v>0.9846</v>
+      </c>
+      <c r="M339" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:52:21</t>
+        </is>
+      </c>
+      <c r="N339" s="4" t="n">
+        <v>11.37</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B340" s="2" t="inlineStr">
+        <is>
+          <t>住院醫療保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C340" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院醫療保險金的給付規定如下：  
+1. 被保險人於契約有效期間內因疾病或傷害住院治療時，保險公司依保險單所載「住院醫療保險金日額」，乘以入院日當年度的「增額係數」，再乘以住院日數，給付住院醫療保險金。  
+2. 同一保單年度內，同一次住院的住院醫療保險金給付日數，最高以365日為限。  
+條文依據：  
+- [第十二條 住院醫療保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D340" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 住院醫療保險金的給付 | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第十三條 加護病房或燒燙傷病房保險金的給付 | 第十四條 醫療保險金給付總額之上限 | 第二十八條 住院醫療保險金日額之減少</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F340" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院醫療保險金的給付規定如下：  
+1. 被保險人於契約有效期間內因疾病或傷害住院治療時，保險公司依保險單所載「住院醫療保險金日額」，乘以入院日當年度的「增額係數」，再乘以住院日數，給付住院醫療保險金。  
+2. 同一保單年度內，同一次住院的住院醫療保險金給付日數，最高以365日為限。  
+條文依據：  
+- [第十二條 住院醫療保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G340" s="2" t="inlineStr"/>
+      <c r="H340" s="2" t="inlineStr"/>
+      <c r="I340" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "住院醫療保險金的給付規定", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J340" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K340" s="4" t="n"/>
+      <c r="L340" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M340" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:52:26</t>
+        </is>
+      </c>
+      <c r="N340" s="4" t="n">
+        <v>4.87</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B341" s="2" t="inlineStr">
+        <is>
+          <t>加護病房或燒燙傷病房保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C341" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+加護病房或燒燙傷病房保險金的給付規定如下：  
+被保險人於本契約有效期間內因疾病或傷害而在醫院的加護病房或燒燙傷病房接受治療時，除住院醫療保險金外，保險公司將依保險單上記載的「住院醫療保險金日額」，乘以入院日當年度的「增額係數」，再乘以實際住進加護病房或燒燙傷病房的日數（含轉入及轉出當日）的二倍，給付「加護病房或燒燙傷病房保險金」。  
+同一保單年度內，同一次住院的加護病房及燒燙傷病房住院日數合計最高以365日為限。同一日內，保險公司僅就加護病房或燒燙傷病房其中一種病房給付。
+條文依據：  
+- [第十三條 加護病房或燒燙傷病房保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D341" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 加護病房或燒燙傷病房保險金的給付 | payout_items | 第二十三條 醫療保險金的申領 | 第五條 保險範圍 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F341" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+加護病房或燒燙傷病房保險金的給付規定如下：  
+被保險人於本契約有效期間內因疾病或傷害而在醫院的加護病房或燒燙傷病房接受治療時，除住院醫療保險金外，保險公司將依保險單上記載的「住院醫療保險金日額」，乘以入院日當年度的「增額係數」，再乘以實際住進加護病房或燒燙傷病房的日數（含轉入及轉出當日）的二倍，給付「加護病房或燒燙傷病房保險金」。  
+同一保單年度內，同一次住院的加護病房及燒燙傷病房住院日數合計最高以365日為限。同一日內，保險公司僅就加護病房或燒燙傷病房其中一種病房給付。
+條文依據：  
+- [第十三條 加護病房或燒燙傷病房保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G341" s="2" t="inlineStr"/>
+      <c r="H341" s="2" t="inlineStr"/>
+      <c r="I341" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "加護病房或燒燙傷病房保險金的給付規定", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J341" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K341" s="4" t="n"/>
+      <c r="L341" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:52:33</t>
+        </is>
+      </c>
+      <c r="N341" s="4" t="n">
+        <v>7.04</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B342" s="2" t="inlineStr">
+        <is>
+          <t>醫療保險金給付總額之上限</t>
+        </is>
+      </c>
+      <c r="C342" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+醫療保險金給付總額之上限為保險單上所記載之「住院醫療保險金日額」的二千五百倍，並適用於本契約有效期間內依第十二條至第十三條所給付的各項保險金累計總額。
+條文依據：  
+- [第十四條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="D342" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 醫療保險金給付總額之上限 | 第十二條 住院醫療保險金的給付 | 第五條 保險範圍 | 第十三條 加護病房或燒燙傷病房保險金的給付 | payout_items</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F342" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+醫療保險金給付總額之上限為保險單上所記載之「住院醫療保險金日額」的二千五百倍，並適用於本契約有效期間內依第十二條至第十三條所給付的各項保險金累計總額。
+條文依據：  
+- [第十四條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="G342" s="2" t="inlineStr"/>
+      <c r="H342" s="2" t="inlineStr"/>
+      <c r="I342" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "醫療保險金給付總額之上限", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J342" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K342" s="4" t="n"/>
+      <c r="L342" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:52:39</t>
+        </is>
+      </c>
+      <c r="N342" s="4" t="n">
+        <v>5.85</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B343" s="2" t="inlineStr">
+        <is>
+          <t>祝壽保險金的給付規定為何?</t>
+        </is>
+      </c>
+      <c r="C343" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+祝壽保險金的給付規定如下：  
+1. 被保險人需於本契約有效期間內，且保險年齡到達99歲之保險單週年日仍生存。  
+2. 本公司將按「當年度保險金額」給付祝壽保險金。
+條文依據：  
+- [第十五條 祝壽保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D343" s="2" t="inlineStr">
+        <is>
+          <t>第十五條 祝壽保險金的給付 | 第十二條至第十三條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | 第二十四條 祝壽保險金的申領 | payout_items | 第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F343" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+祝壽保險金的給付規定如下：  
+1. 被保險人需於本契約有效期間內，且保險年齡到達99歲之保險單週年日仍生存。  
+2. 本公司將按「當年度保險金額」給付祝壽保險金。
+條文依據：  
+- [第十五條 祝壽保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G343" s="2" t="inlineStr"/>
+      <c r="H343" s="2" t="inlineStr"/>
+      <c r="I343" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "祝壽保險金的給付規定為何?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J343" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K343" s="4" t="n"/>
+      <c r="L343" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:52:45</t>
+        </is>
+      </c>
+      <c r="N343" s="4" t="n">
+        <v>5.64</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B344" s="2" t="inlineStr">
+        <is>
+          <t>有效期間內身故，保險金如何給付?</t>
+        </is>
+      </c>
+      <c r="C344" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於本契約有效期間內身故時，本公司將依以下情況給付保險金：  
+1. 若被保險人於繳費期間內身故，當期已繳付之未到期保險費不予退還，亦不併入身故保險金內給付。  
+2. 若被保險人於實際年齡未滿十五足歲時身故，本公司將退還「所繳保險費」予要保人，而不適用身故保險金的給付規定。  
+3. 若被保險人為受監護宣告尚未撤銷者，其身故保險金將變更為喪葬費用保險金，且該金額不得超過遺產稅喪葬費扣除額之半數，超過部分將無息退還已繳保險費。  
+條文依據：  
+- [第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D344" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付 | 第十條 契約的終止（二） | 第五條 保險範圍 | 第二十二條 失蹤處理 | 第十五條 祝壽保險金的給付</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F344" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於本契約有效期間內身故時，本公司將依以下情況給付保險金：  
+1. 若被保險人於繳費期間內身故，當期已繳付之未到期保險費不予退還，亦不併入身故保險金內給付。  
+2. 若被保險人於實際年齡未滿十五足歲時身故，本公司將退還「所繳保險費」予要保人，而不適用身故保險金的給付規定。  
+3. 若被保險人為受監護宣告尚未撤銷者，其身故保險金將變更為喪葬費用保險金，且該金額不得超過遺產稅喪葬費扣除額之半數，超過部分將無息退還已繳保險費。  
+條文依據：  
+- [第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G344" s="2" t="inlineStr"/>
+      <c r="H344" s="2" t="inlineStr"/>
+      <c r="I344" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "有效期間內身故，保險金如何給付?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J344" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K344" s="4" t="n"/>
+      <c r="L344" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M344" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:52:54</t>
+        </is>
+      </c>
+      <c r="N344" s="4" t="n">
+        <v>7.01</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B345" s="2" t="inlineStr">
+        <is>
+          <t>健康促進保險費折減規定</t>
+        </is>
+      </c>
+      <c r="C345" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+健康促進保險費折減規定如下：  
+1. 被保險人年齡需達20歲（含）以上，並使用保險公司指定程式加入健康計劃。  
+2. 若於「指定日期」會員等級符合標準，次一保險單年度保險費可依會員等級享有折減：  
+   - 進階會員：折減2%。  
+   - 菁英會員或更高等級：折減3%。  
+3. 折減僅適用於主契約保險費，不包含附約、附加條款或批註條款，且豁免或復效的保險費不適用折減。  
+4. 被保險人需完成指定程式註冊，並授權保險公司取得健康促進相關電子紀錄，保險公司將依紀錄計算會員等級。
+條文依據：  
+- [第十七條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="D345" s="2" t="inlineStr">
+        <is>
+          <t>第十七條 健康促進保險費折減 | 第二十八條 住院醫療保險金日額之減少 | 第三十條 投保年齡的計算及錯誤的處理 | 第二條 名詞定義 | 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F345" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+健康促進保險費折減規定如下：  
+1. 被保險人年齡需達20歲（含）以上，並使用保險公司指定程式加入健康計劃。  
+2. 若於「指定日期」會員等級符合標準，次一保險單年度保險費可依會員等級享有折減：  
+   - 進階會員：折減2%。  
+   - 菁英會員或更高等級：折減3%。  
+3. 折減僅適用於主契約保險費，不包含附約、附加條款或批註條款，且豁免或復效的保險費不適用折減。  
+4. 被保險人需完成指定程式註冊，並授權保險公司取得健康促進相關電子紀錄，保險公司將依紀錄計算會員等級。
+條文依據：  
+- [第十七條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="G345" s="2" t="inlineStr"/>
+      <c r="H345" s="2" t="inlineStr"/>
+      <c r="I345" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "健康促進保險費折減規定", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J345" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K345" s="4" t="n"/>
+      <c r="L345" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M345" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:53:01</t>
+        </is>
+      </c>
+      <c r="N345" s="4" t="n">
+        <v>6.77</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B346" s="2" t="inlineStr">
+        <is>
+          <t>除外責任的解釋?</t>
+        </is>
+      </c>
+      <c r="C346" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+除外責任是指保險公司對於某些特定原因或情況下所發生的疾病、傷害或死亡，不負給付保險金的責任。條款中列舉了多種除外責任情形，例如被保險人故意行為、犯罪行為、非法施用毒品、美容手術（非重建基本功能者）、健康檢查等。此外，針對懷孕、流產或分娩及其併發症，雖屬除外責任，但條款中明確列出若符合特定情況（如子宮外孕、葡萄胎等）則不在此限。
+條文依據：  
+- [第十八條 除外責任（一）]  
+- [第十九條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="D346" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第十九條 除外責任（二） | 第八條 告知義務與本契約的解除 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F346" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+除外責任是指保險公司對於某些特定原因或情況下所發生的疾病、傷害或死亡，不負給付保險金的責任。條款中列舉了多種除外責任情形，例如被保險人故意行為、犯罪行為、非法施用毒品、美容手術（非重建基本功能者）、健康檢查等。此外，針對懷孕、流產或分娩及其併發症，雖屬除外責任，但條款中明確列出若符合特定情況（如子宮外孕、葡萄胎等）則不在此限。
+條文依據：  
+- [第十八條 除外責任（一）]  
+- [第十九條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="G346" s="2" t="inlineStr"/>
+      <c r="H346" s="2" t="inlineStr"/>
+      <c r="I346" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "除外責任的解釋?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J346" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K346" s="4" t="n"/>
+      <c r="L346" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M346" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:53:14</t>
+        </is>
+      </c>
+      <c r="N346" s="4" t="n">
+        <v>12.52</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B347" s="2" t="inlineStr">
+        <is>
+          <t>哪些疾病被含在除外責任?</t>
+        </is>
+      </c>
+      <c r="C347" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人因以下原因所致之疾病或傷害，屬於除外責任，本公司不負給付保險金的責任：  
+1. 被保險人之故意行為（包括自殺及自殺未遂）。  
+2. 被保險人之犯罪行為。  
+3. 被保險人非法施用毒品。  
+4. 美容手術、外科整型（但為重建基本功能所作之必要整型不在此限）。  
+5. 外觀可見之天生畸形。  
+6. 健康檢查、療養、靜養、戒毒、戒酒、護理或養老等非以直接診治病人為目的者。  
+7. 懷孕、流產或分娩及其併發症（但特定懷孕相關疾病、醫療行為必要之流產及剖腹產情形不在此限）。  
+8. 不孕症、人工受孕或非以治療為目的之避孕及絕育手術。  
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D347" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第二條 名詞定義 | 第十九條 除外責任（二）</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F347" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人因以下原因所致之疾病或傷害，屬於除外責任，本公司不負給付保險金的責任：  
+1. 被保險人之故意行為（包括自殺及自殺未遂）。  
+2. 被保險人之犯罪行為。  
+3. 被保險人非法施用毒品。  
+4. 美容手術、外科整型（但為重建基本功能所作之必要整型不在此限）。  
+5. 外觀可見之天生畸形。  
+6. 健康檢查、療養、靜養、戒毒、戒酒、護理或養老等非以直接診治病人為目的者。  
+7. 懷孕、流產或分娩及其併發症（但特定懷孕相關疾病、醫療行為必要之流產及剖腹產情形不在此限）。  
+8. 不孕症、人工受孕或非以治療為目的之避孕及絕育手術。  
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="G347" s="2" t="inlineStr"/>
+      <c r="H347" s="2" t="inlineStr"/>
+      <c r="I347" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "哪些疾病被含在除外責任?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J347" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K347" s="4" t="n"/>
+      <c r="L347" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M347" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:53:22</t>
+        </is>
+      </c>
+      <c r="N347" s="4" t="n">
+        <v>7.43</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B348" s="2" t="inlineStr">
+        <is>
+          <t>進行美容手術住院可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C348" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，因美容手術住院無法申請理賠，屬於除外責任範圍。但若美容手術是為了重建基本功能所作之必要整型，則不在此限，可以申請理賠。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D348" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第十三條 加護病房或燒燙傷病房保險金的給付 | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第二條 名詞定義 | payout_items</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F348" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，因美容手術住院無法申請理賠，屬於除外責任範圍。但若美容手術是為了重建基本功能所作之必要整型，則不在此限，可以申請理賠。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="G348" s="2" t="inlineStr"/>
+      <c r="H348" s="2" t="inlineStr"/>
+      <c r="I348" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "進行美容手術住院可以申請理賠嗎?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J348" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K348" s="4" t="n"/>
+      <c r="L348" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M348" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:53:26</t>
+        </is>
+      </c>
+      <c r="N348" s="4" t="n">
+        <v>4.35</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B349" s="2" t="inlineStr">
+        <is>
+          <t>因胎兒染色體異常進行手術而住院可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C349" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以申請理賠。根據條款，因胎兒染色體異常進行手術屬於懷孕相關疾病的例外情形，不在除外責任範圍內，因此符合理賠條件。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D349" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第二條 名詞定義 | payout_items | 第十三條 加護病房或燒燙傷病房保險金的給付</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F349" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以申請理賠。根據條款，因胎兒染色體異常進行手術屬於懷孕相關疾病的例外情形，不在除外責任範圍內，因此符合理賠條件。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="G349" s="2" t="inlineStr"/>
+      <c r="H349" s="2" t="inlineStr"/>
+      <c r="I349" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "因胎兒染色體異常進行手術而住院可以申請理賠嗎?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J349" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K349" s="4" t="n"/>
+      <c r="L349" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M349" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:53:31</t>
+        </is>
+      </c>
+      <c r="N349" s="4" t="n">
+        <v>5.28</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B350" s="2" t="inlineStr">
+        <is>
+          <t>因胎位不正進行手術而住院可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C350" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，因胎位不正進行手術而住院屬於除外責任範圍內的「懷孕、流產或分娩及其併發症」。但若符合第十八條中「不在此限」的條件，例如因醫療行為必要之剖腹產，且胎位不正為符合條件的情形之一，則可申請理賠。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D350" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第二條 名詞定義 | payout_items | 第十三條 加護病房或燒燙傷病房保險金的給付</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F350" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，因胎位不正進行手術而住院屬於除外責任範圍內的「懷孕、流產或分娩及其併發症」。但若符合第十八條中「不在此限」的條件，例如因醫療行為必要之剖腹產，且胎位不正為符合條件的情形之一，則可申請理賠。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="G350" s="2" t="inlineStr"/>
+      <c r="H350" s="2" t="inlineStr"/>
+      <c r="I350" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "因胎位不正進行手術而住院可以申請理賠嗎?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J350" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K350" s="4" t="n"/>
+      <c r="L350" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M350" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:53:37</t>
+        </is>
+      </c>
+      <c r="N350" s="4" t="n">
+        <v>5.24</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B351" s="2" t="inlineStr">
+        <is>
+          <t>因自殺未遂導致住院可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C351" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人因自殺未遂導致住院，本公司不負給付住院相關保險金的責任，因其屬於被保險人之故意行為。  
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D351" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 除外責任（二） | 第十八條 除外責任（一） | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | payout_items | 第十條 契約的終止（二）</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F351" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人因自殺未遂導致住院，本公司不負給付住院相關保險金的責任，因其屬於被保險人之故意行為。  
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="G351" s="2" t="inlineStr"/>
+      <c r="H351" s="2" t="inlineStr"/>
+      <c r="I351" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "因自殺未遂導致住院可以申請理賠嗎?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J351" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K351" s="4" t="n"/>
+      <c r="L351" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M351" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:53:43</t>
+        </is>
+      </c>
+      <c r="N351" s="4" t="n">
+        <v>6.13</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B352" s="2" t="inlineStr">
+        <is>
+          <t>被保險人在投保一年內故意自殺者，可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C352" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人在投保一年內故意自殺者，保險公司不負給付身故保險金或喪葬費用保險金的責任。只有在契約訂立或復效之日起滿二年後，因故意自殺致死者，保險公司才負給付責任。
+條文依據：  
+- [第十九條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="D352" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 除外責任（二） | 第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付 | 第十條 契約的終止（二） | 第三十條 投保年齡的計算及錯誤的處理 | 第十八條 除外責任（一）</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F352" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人在投保一年內故意自殺者，保險公司不負給付身故保險金或喪葬費用保險金的責任。只有在契約訂立或復效之日起滿二年後，因故意自殺致死者，保險公司才負給付責任。
+條文依據：  
+- [第十九條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="G352" s="2" t="inlineStr"/>
+      <c r="H352" s="2" t="inlineStr"/>
+      <c r="I352" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "被保險人在投保一年內故意自殺者，可以申請理賠嗎?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J352" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K352" s="4" t="n"/>
+      <c r="L352" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M352" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:53:49</t>
+        </is>
+      </c>
+      <c r="N352" s="4" t="n">
+        <v>5.45</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B353" s="2" t="inlineStr">
+        <is>
+          <t>申請理賠有什麼時間規定嗎?</t>
+        </is>
+      </c>
+      <c r="C353" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申請理賠的時間規定如下：  
+1. 要保人、被保險人或受益人應於知悉本公司應負保險責任之事故後十日內通知本公司。  
+2. 通知後，應儘速檢具所需文件向本公司申請給付保險金。  
+3. 本公司應於收齊所需文件後十五日內給付保險金。若因可歸責於本公司之事由未在上述期限內給付，應按年利一分加計利息給付。
+條文依據：  
+- [第二十一條 保險事故的通知與保險金的申請時間]</t>
+        </is>
+      </c>
+      <c r="D353" s="2" t="inlineStr">
+        <is>
+          <t>第二十一條 保險事故的通知與保險金的申請時間 | 第六條 第二期以後保險費的交付、寬限期間及契約效力的停止 | 第七條 本契約效力的恢復 | 第三條 契約撤銷權 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F353" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申請理賠的時間規定如下：  
+1. 要保人、被保險人或受益人應於知悉本公司應負保險責任之事故後十日內通知本公司。  
+2. 通知後，應儘速檢具所需文件向本公司申請給付保險金。  
+3. 本公司應於收齊所需文件後十五日內給付保險金。若因可歸責於本公司之事由未在上述期限內給付，應按年利一分加計利息給付。
+條文依據：  
+- [第二十一條 保險事故的通知與保險金的申請時間]</t>
+        </is>
+      </c>
+      <c r="G353" s="2" t="inlineStr"/>
+      <c r="H353" s="2" t="inlineStr"/>
+      <c r="I353" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "申請理賠有什麼時間規定嗎?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J353" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K353" s="4" t="n"/>
+      <c r="L353" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M353" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:53:54</t>
+        </is>
+      </c>
+      <c r="N353" s="4" t="n">
+        <v>4.76</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B354" s="2" t="inlineStr">
+        <is>
+          <t>燒燙傷病房保險金怎麼申領?</t>
+        </is>
+      </c>
+      <c r="C354" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申領燒燙傷病房保險金時，受益人需檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 醫療診斷書或住院證明，且需列明進、出燒燙傷病房的日期。（但要保人或被保險人為醫師時，不得為被保險人出具診斷書或住院證明。）  
+4. 受益人的身分證明。  
+此外，保險公司可基於審核需要，徵詢其他醫師的專業意見，並經受益人同意調閱被保險人的就醫相關資料，相關費用由保險公司負擔。
+條文依據：  
+- [第二十三條 醫療保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D354" s="2" t="inlineStr">
+        <is>
+          <t>第二十三條 醫療保險金的申領 | 第十三條 加護病房或燒燙傷病房保險金的給付 | payout_items | 第二條 名詞定義 | 第二十一條 保險事故的通知與保險金的申請時間</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F354" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申領燒燙傷病房保險金時，受益人需檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 醫療診斷書或住院證明，且需列明進、出燒燙傷病房的日期。（但要保人或被保險人為醫師時，不得為被保險人出具診斷書或住院證明。）  
+4. 受益人的身分證明。  
+此外，保險公司可基於審核需要，徵詢其他醫師的專業意見，並經受益人同意調閱被保險人的就醫相關資料，相關費用由保險公司負擔。
+條文依據：  
+- [第二十三條 醫療保險金的申領]</t>
+        </is>
+      </c>
+      <c r="G354" s="2" t="inlineStr"/>
+      <c r="H354" s="2" t="inlineStr"/>
+      <c r="I354" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "燒燙傷病房保險金怎麼申領?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J354" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K354" s="4" t="n"/>
+      <c r="L354" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M354" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:54:00</t>
+        </is>
+      </c>
+      <c r="N354" s="4" t="n">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B355" s="2" t="inlineStr">
+        <is>
+          <t>活到99歲怎麼申請祝壽金?</t>
+        </is>
+      </c>
+      <c r="C355" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申請祝壽保險金時，受益人需檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 受益人的身分證明。  
+條文依據：  
+- [第二十四條 祝壽保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D355" s="2" t="inlineStr">
+        <is>
+          <t>第十五條 祝壽保險金的給付 | 第二十四條 祝壽保險金的申領 | 第五條 保險範圍 | 第十二條至第十三條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | announcement_history</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F355" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申請祝壽保險金時，受益人需檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 受益人的身分證明。  
+條文依據：  
+- [第二十四條 祝壽保險金的申領]</t>
+        </is>
+      </c>
+      <c r="G355" s="2" t="inlineStr"/>
+      <c r="H355" s="2" t="inlineStr"/>
+      <c r="I355" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "活到99歲怎麼申請祝壽金?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J355" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K355" s="4" t="n"/>
+      <c r="L355" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M355" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:54:05</t>
+        </is>
+      </c>
+      <c r="N355" s="4" t="n">
+        <v>5.01</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B356" s="2" t="inlineStr">
+        <is>
+          <t>被保人身故怎麼申請理賠</t>
+        </is>
+      </c>
+      <c r="C356" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+受益人申請「身故保險金」或「喪葬費用保險金」時，需檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 被保險人死亡證明書及除戶戶籍謄本。  
+4. 受益人的身分證明。  
+條文依據：  
+- [第二十五條 身故保險金或喪葬費用保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D356" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付 | 第十二條至第十三條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | 第二十二條 失蹤處理 | 第二十五條 身故保險金或喪葬費用保險金的申領 | 第十九條 除外責任（二）</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F356" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+受益人申請「身故保險金」或「喪葬費用保險金」時，需檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 被保險人死亡證明書及除戶戶籍謄本。  
+4. 受益人的身分證明。  
+條文依據：  
+- [第二十五條 身故保險金或喪葬費用保險金的申領]</t>
+        </is>
+      </c>
+      <c r="G356" s="2" t="inlineStr"/>
+      <c r="H356" s="2" t="inlineStr"/>
+      <c r="I356" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "被保人身故怎麼申請理賠", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J356" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K356" s="4" t="n"/>
+      <c r="L356" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M356" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:54:11</t>
+        </is>
+      </c>
+      <c r="N356" s="4" t="n">
+        <v>5.73</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B357" s="2" t="inlineStr">
+        <is>
+          <t>投保15年後，增額係數為多少？因手術住院3天，住院日額為2500元，請問可以申請多少理賠?</t>
+        </is>
+      </c>
+      <c r="C357" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 投保15年後的增額係數為1.05。  
+2. 理賠計算方式為：住院日額（2500元）× 增額係數（1.05）× 住院日數（3天）。  
+3. 手術住院3天的理賠金額為：2500 × 1.05 × 3 = 7875元。  
+4. 條文中未提及其他附加條款影響理賠金額。
+條文依據：  
+- [附表：增額係數表 - 保險單年度]  
+- [第十二條 住院醫療保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D357" s="2" t="inlineStr">
+        <is>
+          <t>附表：增額係數表 | 第十二條 住院醫療保險金的給付 | 第十三條 加護病房或燒燙傷病房保險金的給付 | 第二十八條 住院醫療保險金日額之減少 | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第三十條 投保年齡的計算及錯誤的處理 | payout_items | 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F357" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 投保15年後的增額係數為1.05。  
+2. 理賠計算方式為：住院日額（2500元）× 增額係數（1.05）× 住院日數（3天）。  
+3. 手術住院3天的理賠金額為：2500 × 1.05 × 3 = 7875元。  
+4. 條文中未提及其他附加條款影響理賠金額。
+條文依據：  
+- [附表：增額係數表 - 保險單年度]  
+- [第十二條 住院醫療保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G357" s="2" t="inlineStr"/>
+      <c r="H357" s="2" t="inlineStr"/>
+      <c r="I357" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認投保15年後的增額係數", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認住院日額為2500元的理賠計算方式", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認手術住院3天的理賠金額計算", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認是否有其他附加條款影響理賠金額", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J357" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K357" s="4" t="n"/>
+      <c r="L357" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:54:20</t>
+        </is>
+      </c>
+      <c r="N357" s="4" t="n">
+        <v>8.619999999999999</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B358" s="2" t="inlineStr">
+        <is>
+          <t>保障範圍包括哪些項目？</t>
+        </is>
+      </c>
+      <c r="C358" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括：住院手術醫療保險金、門診手術醫療保險金、特定處置保險金、意外創傷縫合處置保險金、意外住院手術醫療保險金、祝壽保險金、所繳保險費的退還、身故保險金或喪葬費用保險金。
+條文依據：  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="D358" s="2" t="inlineStr">
+        <is>
+          <t>payout_items | 第五條 保險範圍 | summary | 第四條 名詞定義 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F358" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括：住院手術醫療保險金、門診手術醫療保險金、特定處置保險金、意外創傷縫合處置保險金、意外住院手術醫療保險金、祝壽保險金、所繳保險費的退還、身故保險金或喪葬費用保險金。
+條文依據：  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="G358" s="2" t="inlineStr"/>
+      <c r="H358" s="2" t="inlineStr"/>
+      <c r="I358" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "保障範圍包括哪些項目？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J358" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K358" s="4" t="n"/>
+      <c r="L358" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M358" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:54:24</t>
+        </is>
+      </c>
+      <c r="N358" s="4" t="n">
+        <v>3.64</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B359" s="2" t="inlineStr">
+        <is>
+          <t>保險金額是否有上限?</t>
+        </is>
+      </c>
+      <c r="C359" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+有，保險金額的給付總額上限為保險單上所記載「保險金額」的一千五百倍，且不包含其他附約、附加條款或批註條款。
+條文依據：  
+- [第十六條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="D359" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 醫療保險金給付總額之上限 | 第三十條 保險金額之減少 | 第五條 保險範圍 | 第十九條 健康促進保險費折減 | 第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F359" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+有，保險金額的給付總額上限為保險單上所記載「保險金額」的一千五百倍，且不包含其他附約、附加條款或批註條款。
+條文依據：  
+- [第十六條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="G359" s="2" t="inlineStr"/>
+      <c r="H359" s="2" t="inlineStr"/>
+      <c r="I359" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "保險金額是否有上限?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J359" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K359" s="4" t="n"/>
+      <c r="L359" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M359" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:54:29</t>
+        </is>
+      </c>
+      <c r="N359" s="4" t="n">
+        <v>5.17</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B360" s="2" t="inlineStr">
+        <is>
+          <t>投保後5天發生手術，是否可以申請理賠?</t>
+        </is>
+      </c>
+      <c r="C360" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款，被保險人於保險契約有效期間內因疾病或傷害接受手術，符合附表一所列手術項目且不屬除外責任範圍者，可申請理賠。但若疾病發生於契約生效日起三十日內，則不在理賠範圍內，除非屬於條款中明確列舉的等待期間不適用疾病。  
+條文依據：  
+[第四條 名詞定義]  
+[第十一條 住院手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="D360" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第十一條 住院手術醫療保險金 | 第二十條 除外責任（一） | 第十二條 門診手術醫療保險金 | 第十三條 意外住院手術醫療保險金 | 第二十三條 保險事故的通知與保險金的申請時間 | 第四條 名詞定義 | 第十五條 意外創傷縫合處置保險金 | 附表三：意外創傷縫合處置項目及給付倍數表 | 附表一：手術項目與給付倍數 | payout_items</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F360" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+找不到相關內容  
+條文依據：  
+找不到相關內容</t>
+        </is>
+      </c>
+      <c r="G360" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款，被保險人於保險契約有效期間內因疾病或傷害接受手術，符合附表一所列手術項目且不屬除外責任範圍者，可申請理賠。但若疾病發生於契約生效日起三十日內，則不在理賠範圍內，除非屬於條款中明確列舉的等待期間不適用疾病。  
+條文依據：  
+[第四條 名詞定義]  
+[第十一條 住院手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="H360" s="2" t="inlineStr"/>
+      <c r="I360" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "投保後5天發生手術，是否可以申請理賠?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J360" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K360" s="4" t="n"/>
+      <c r="L360" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M360" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:54:39</t>
+        </is>
+      </c>
+      <c r="N360" s="4" t="n">
+        <v>10.29</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B361" s="2" t="inlineStr">
+        <is>
+          <t>住院手術醫療保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C361" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院手術醫療保險金的給付規定如下：  
+1. 被保險人需於保險契約有效期間內，因疾病或傷害經醫師診斷必須住院接受附表一所列的手術治療，且已實際接受手術。  
+2. 給付金額計算方式為：保險單上記載的「保險金額」乘以手術日當年度的「增額係數」，再乘以手術給付倍數。  
+3. 若同一次手術中於同一手術位置接受兩項以上手術項目，僅給付手術給付倍數最高的手術項目。  
+4. 未載明於附表一的手術項目，將與被保險人協議比照附表內程度相當的手術項目，決定給付倍數。  
+5. 以下情形不負給付責任：  
+   - 屬於除外責任條款規定的情形。  
+   - 不屬於全民健康保險醫療服務給付項目及支付標準第二部第二章第七節或第三部第三章第四節第三項所列舉的手術。  
+條文依據：  
+- [第十一條 住院手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="D361" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 住院手術醫療保險金 | 第十三條 意外住院手術醫療保險金 | 第十二條 門診手術醫療保險金 | payout_items | 第二十條 除外責任（一） | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F361" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院手術醫療保險金的給付規定如下：  
+1. 被保險人需於保險契約有效期間內，因疾病或傷害經醫師診斷必須住院接受附表一所列的手術治療，且已實際接受手術。  
+2. 給付金額計算方式為：保險單上記載的「保險金額」乘以手術日當年度的「增額係數」，再乘以手術給付倍數。  
+3. 若同一次手術中於同一手術位置接受兩項以上手術項目，僅給付手術給付倍數最高的手術項目。  
+4. 未載明於附表一的手術項目，將與被保險人協議比照附表內程度相當的手術項目，決定給付倍數。  
+5. 以下情形不負給付責任：  
+   - 屬於除外責任條款規定的情形。  
+   - 不屬於全民健康保險醫療服務給付項目及支付標準第二部第二章第七節或第三部第三章第四節第三項所列舉的手術。  
+條文依據：  
+- [第十一條 住院手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="G361" s="2" t="inlineStr"/>
+      <c r="H361" s="2" t="inlineStr"/>
+      <c r="I361" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "住院手術醫療保險金的給付規定", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J361" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K361" s="4" t="n"/>
+      <c r="L361" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M361" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:54:47</t>
+        </is>
+      </c>
+      <c r="N361" s="4" t="n">
+        <v>7.12</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B362" s="2" t="inlineStr">
+        <is>
+          <t>門診手術醫療保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C362" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+門診手術醫療保險金的給付規定如下：  
+1. 被保險人需於本契約有效期間內，因疾病或傷害經醫師診斷必須於醫院或診所門診接受附表一所列的手術治療，且已實際接受手術。  
+2. 給付金額計算方式為：保險單所記載的「保險金額」乘以手術日當年度的「增額係數」，再乘以手術給付倍數。  
+3. 同一次手術中，若於同一手術位置接受兩項以上手術項目，僅給付手術給付倍數最高的手術項目。  
+4. 同一保險單年度內，門診手術醫療保險金的給付以十次為限。  
+5. 若手術項目未載明於附表一，本公司將與被保險人協議比照附表內的手術項目決定給付倍數。  
+6. 以下情形不負給付責任：  
+   - 屬於本契約除外責任條款規定的項目。  
+   - 不屬於全民健康保險醫療服務給付項目及支付標準第二部第二章第七節或第三部第三章第四節第三項所列舉的手術。  
+條文依據：  
+- [第十二條 門診手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="D362" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 門診手術醫療保險金 | 第十一條 住院手術醫療保險金 | payout_items | 第十三條 意外住院手術醫療保險金 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F362" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+門診手術醫療保險金的給付規定如下：  
+1. 被保險人需於本契約有效期間內，因疾病或傷害經醫師診斷必須於醫院或診所門診接受附表一所列的手術治療，且已實際接受手術。  
+2. 給付金額計算方式為：保險單所記載的「保險金額」乘以手術日當年度的「增額係數」，再乘以手術給付倍數。  
+3. 同一次手術中，若於同一手術位置接受兩項以上手術項目，僅給付手術給付倍數最高的手術項目。  
+4. 同一保險單年度內，門診手術醫療保險金的給付以十次為限。  
+5. 若手術項目未載明於附表一，本公司將與被保險人協議比照附表內的手術項目決定給付倍數。  
+6. 以下情形不負給付責任：  
+   - 屬於本契約除外責任條款規定的項目。  
+   - 不屬於全民健康保險醫療服務給付項目及支付標準第二部第二章第七節或第三部第三章第四節第三項所列舉的手術。  
+條文依據：  
+- [第十二條 門診手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="G362" s="2" t="inlineStr"/>
+      <c r="H362" s="2" t="inlineStr"/>
+      <c r="I362" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "門診手術醫療保險金的給付規定", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J362" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K362" s="4" t="n"/>
+      <c r="L362" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M362" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:54:53</t>
+        </is>
+      </c>
+      <c r="N362" s="4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B363" s="2" t="inlineStr">
+        <is>
+          <t>意外住院手術醫療保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C363" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外住院手術醫療保險金的給付規定如下：  
+1. 被保險人需於本契約有效期間內，且保險年齡未滿七十歲。  
+2. 因傷害經醫師診斷在住院期間必須接受手術治療且已接受手術者。  
+3. 給付金額為保險單上所記載之「保險金額」的三倍，乘以手術日當年度之「增額係數」。  
+4. 若同一次手術中於同一手術位置接受二項以上手術項目，僅給付一次意外住院手術醫療保險金。
+條文依據：  
+- [第十三條 意外住院手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="D363" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 意外住院手術醫療保險金 | 第十一條 住院手術醫療保險金 | 第十五條 意外創傷縫合處置保險金 | 第二十條 除外責任（一） | 第十二條 門診手術醫療保險金 | 附表三：意外創傷縫合處置項目及給付倍數表 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F363" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外住院手術醫療保險金的給付規定如下：  
+1. 被保險人需於本契約有效期間內，且保險年齡未滿七十歲。  
+2. 因傷害經醫師診斷在住院期間必須接受手術治療且已接受手術者。  
+3. 給付金額為保險單上所記載之「保險金額」的三倍，乘以手術日當年度之「增額係數」。  
+4. 若同一次手術中於同一手術位置接受二項以上手術項目，僅給付一次意外住院手術醫療保險金。
+條文依據：  
+- [第十三條 意外住院手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="G363" s="2" t="inlineStr"/>
+      <c r="H363" s="2" t="inlineStr"/>
+      <c r="I363" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "意外住院手術醫療保險金的給付規定", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J363" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K363" s="4" t="n"/>
+      <c r="L363" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M363" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:55:01</t>
+        </is>
+      </c>
+      <c r="N363" s="4" t="n">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B364" s="2" t="inlineStr">
+        <is>
+          <t>特定處置保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C364" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+特定處置保險金的給付規定如下：  
+1. 被保險人需於保險契約有效期間內，因疾病或傷害經醫師診斷必須接受附表二所列的特定處置治療，且實際完成處置後，保險公司才會給付特定處置保險金。  
+2. 給付金額計算方式為：保險單上記載的「保險金額」× 特定處置日當年度的「增額係數」× 特定處置給付倍數。  
+3. 同一次處置治療中，若於同一治療位置接受兩項以上特定處置項目，僅給付特定處置給付倍數最高的項目。  
+4. 若接受的處置未列於附表二，保險公司不負給付責任。  
+5. 同一保險單年度內，特定處置保險金的給付次數以十次為限。
+條文依據：  
+- [第十四條 特定處置保險金]</t>
+        </is>
+      </c>
+      <c r="D364" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 特定處置保險金 | 第十五條 意外創傷縫合處置保險金 | 附表二：特定處置項目及給付倍數表 | 第五條 保險範圍 | 附表三：意外創傷縫合處置項目及給付倍數表</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F364" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+特定處置保險金的給付規定如下：  
+1. 被保險人需於保險契約有效期間內，因疾病或傷害經醫師診斷必須接受附表二所列的特定處置治療，且實際完成處置後，保險公司才會給付特定處置保險金。  
+2. 給付金額計算方式為：保險單上記載的「保險金額」× 特定處置日當年度的「增額係數」× 特定處置給付倍數。  
+3. 同一次處置治療中，若於同一治療位置接受兩項以上特定處置項目，僅給付特定處置給付倍數最高的項目。  
+4. 若接受的處置未列於附表二，保險公司不負給付責任。  
+5. 同一保險單年度內，特定處置保險金的給付次數以十次為限。
+條文依據：  
+- [第十四條 特定處置保險金]</t>
+        </is>
+      </c>
+      <c r="G364" s="2" t="inlineStr"/>
+      <c r="H364" s="2" t="inlineStr"/>
+      <c r="I364" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "特定處置保險金的給付規定", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J364" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K364" s="4" t="n"/>
+      <c r="L364" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M364" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:55:11</t>
+        </is>
+      </c>
+      <c r="N364" s="4" t="n">
+        <v>9.52</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B365" s="2" t="inlineStr">
+        <is>
+          <t>意外創傷縫合處置保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C365" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外創傷縫合處置保險金的給付規定如下：  
+1. 被保險人需於本契約有效期間內，因意外傷害事故在醫院或診所接受附表三所列的意外創傷縫合處置治療。  
+2. 給付金額計算方式為：保險單所記載的「保險金額」× 當年度「增額係數」× 意外創傷縫合處置給付倍數。  
+3. 同一次意外傷害事故，僅就傷口最大者給付，且以給付一次為限。  
+4. 若被保險人因同一意外傷害事故已申領「住院手術醫療保險金」或「門診手術醫療保險金」，則不再給付意外創傷縫合處置保險金。  
+條文依據：  
+- [第十五條 意外創傷縫合處置保險金]</t>
+        </is>
+      </c>
+      <c r="D365" s="2" t="inlineStr">
+        <is>
+          <t>第十五條 意外創傷縫合處置保險金 | 附表三：意外創傷縫合處置項目及給付倍數表 | 第十四條 特定處置保險金 | 第二十條 除外責任（一） | 第十三條 意外住院手術醫療保險金 | 附表二：特定處置項目及給付倍數表</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F365" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外創傷縫合處置保險金的給付規定如下：  
+1. 被保險人需於本契約有效期間內，因意外傷害事故在醫院或診所接受附表三所列的意外創傷縫合處置治療。  
+2. 給付金額計算方式為：保險單所記載的「保險金額」× 當年度「增額係數」× 意外創傷縫合處置給付倍數。  
+3. 同一次意外傷害事故，僅就傷口最大者給付，且以給付一次為限。  
+4. 若被保險人因同一意外傷害事故已申領「住院手術醫療保險金」或「門診手術醫療保險金」，則不再給付意外創傷縫合處置保險金。  
+條文依據：  
+- [第十五條 意外創傷縫合處置保險金]</t>
+        </is>
+      </c>
+      <c r="G365" s="2" t="inlineStr"/>
+      <c r="H365" s="2" t="inlineStr"/>
+      <c r="I365" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "意外創傷縫合處置保險金的給付規定", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J365" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K365" s="4" t="n"/>
+      <c r="L365" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M365" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:55:19</t>
+        </is>
+      </c>
+      <c r="N365" s="4" t="n">
+        <v>8.68</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B366" s="2" t="inlineStr">
+        <is>
+          <t>醫療保險金給付總額之上限</t>
+        </is>
+      </c>
+      <c r="C366" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+醫療保險金給付總額之上限為保險單上所記載「保險金額」的一千五百倍，此上限不包含其他附約、附加條款或批註條款。
+條文依據：  
+- [第十六條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="D366" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 醫療保險金給付總額之上限 | 第十二條 門診手術醫療保險金 | 第五條 保險範圍 | 第十一條 住院手術醫療保險金 | 第十三條 意外住院手術醫療保險金 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F366" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+醫療保險金給付總額之上限為保險單上所記載「保險金額」的一千五百倍，此上限不包含其他附約、附加條款或批註條款。
+條文依據：  
+- [第十六條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="G366" s="2" t="inlineStr"/>
+      <c r="H366" s="2" t="inlineStr"/>
+      <c r="I366" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "醫療保險金給付總額之上限", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J366" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K366" s="4" t="n"/>
+      <c r="L366" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M366" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:55:26</t>
+        </is>
+      </c>
+      <c r="N366" s="4" t="n">
+        <v>6.01</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B367" s="2" t="inlineStr">
+        <is>
+          <t>祝壽保險金的領取規定為何?金額多少？</t>
+        </is>
+      </c>
+      <c r="C367" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+祝壽保險金的領取規定如下：  
+1. 被保險人需於本契約有效期間內，且保險年齡到達99歲之保險單週年日仍生存。  
+2. 金額為「當年度保險金額」。  
+條文依據：  
+- [第十七條 祝壽保險金]</t>
+        </is>
+      </c>
+      <c r="D367" s="2" t="inlineStr">
+        <is>
+          <t>第十七條 祝壽保險金 | 第二十六條 祝壽保險金的申領 | 第十一條至第十五條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | 第五條 保險範圍 | 第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F367" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+祝壽保險金的領取規定如下：  
+1. 被保險人需於本契約有效期間內，且保險年齡到達99歲之保險單週年日仍生存。  
+2. 金額為「當年度保險金額」。  
+條文依據：  
+- [第十七條 祝壽保險金]</t>
+        </is>
+      </c>
+      <c r="G367" s="2" t="inlineStr"/>
+      <c r="H367" s="2" t="inlineStr"/>
+      <c r="I367" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "祝壽保險金的領取規定為何?金額多少？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J367" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K367" s="4" t="n"/>
+      <c r="L367" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M367" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:55:32</t>
+        </is>
+      </c>
+      <c r="N367" s="4" t="n">
+        <v>6.58</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B368" s="2" t="inlineStr">
+        <is>
+          <t>身故時領取保險金有什麼規則?</t>
+        </is>
+      </c>
+      <c r="C368" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+身故時領取保險金的規則如下：  
+1. **一般規則**：被保險人於本契約有效期間內身故，本公司按「當年度保險金額」給付「身故保險金」。  
+2. **未滿十五足歲規則**：若被保險人於本契約有效期間內且實際年齡未滿十五足歲身故，本公司僅退還「所繳保險費」，不適用一般規則。  
+3. **受監護宣告者**：若被保險人於訂立契約時為受監護宣告尚未撤銷者，其身故保險金變更為喪葬費用保險金，且金額不得超過遺產稅喪葬費扣除額之半數，超過部分不負給付責任，並退還超過部分的已繳保險費。  
+4. **除外責任**：若身故原因屬於要保人故意致死、被保險人故意自殺（契約訂立或復效後兩年內）、犯罪處死、拒捕或越獄致死等情形，本公司不負給付責任。若被保險人未滿十五足歲，則僅退還所繳保險費。  
+5. **申領文件**：受益人申領保險金時，需提供保險單、死亡證明書及除戶戶籍謄本、保險金申請書及受益人身分證明等文件。
+條文依據：  
+- [第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金]  
+- [第二十七條 身故保險金或喪葬費用保險金的申領]  
+- [第二十一條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="D368" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金 | 第二十七條 身故保險金或喪葬費用保險金的申領 | 第十一條至第十五條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | 第二十一條 除外責任（二） | 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F368" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+身故時領取保險金的規則如下：  
+1. **一般規則**：被保險人於本契約有效期間內身故，本公司按「當年度保險金額」給付「身故保險金」。  
+2. **未滿十五足歲規則**：若被保險人於本契約有效期間內且實際年齡未滿十五足歲身故，本公司僅退還「所繳保險費」，不適用一般規則。  
+3. **受監護宣告者**：若被保險人於訂立契約時為受監護宣告尚未撤銷者，其身故保險金變更為喪葬費用保險金，且金額不得超過遺產稅喪葬費扣除額之半數，超過部分不負給付責任，並退還超過部分的已繳保險費。  
+4. **除外責任**：若身故原因屬於要保人故意致死、被保險人故意自殺（契約訂立或復效後兩年內）、犯罪處死、拒捕或越獄致死等情形，本公司不負給付責任。若被保險人未滿十五足歲，則僅退還所繳保險費。  
+5. **申領文件**：受益人申領保險金時，需提供保險單、死亡證明書及除戶戶籍謄本、保險金申請書及受益人身分證明等文件。
+條文依據：  
+- [第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金]  
+- [第二十七條 身故保險金或喪葬費用保險金的申領]  
+- [第二十一條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="G368" s="2" t="inlineStr"/>
+      <c r="H368" s="2" t="inlineStr"/>
+      <c r="I368" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "身故時領取保險金有什麼規則?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J368" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K368" s="4" t="n"/>
+      <c r="L368" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M368" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:55:41</t>
+        </is>
+      </c>
+      <c r="N368" s="4" t="n">
+        <v>8.25</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B369" s="2" t="inlineStr">
+        <is>
+          <t>什麼情況下可以保費折減?</t>
+        </is>
+      </c>
+      <c r="C369" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人年齡滿20歲（含）以上，並使用保險公司指定程式加入健康計劃，且於「指定日期」的會員等級符合進階會員或菁英會員（或更高等級）標準之一者，可享次一保險單年度的保費折減。折減比例為進階會員2%，菁英會員或更高等級3%。但豁免或復效的保險費不適用此折減規定。此外，被保險人需完成指定程式的註冊程序，並授權保險公司取得健康促進相關電子紀錄，保險公司將依此計算會員等級。
+條文依據：  
+- [第十九條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="D369" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 健康促進保險費折減 | 第三十條 保險金額之減少 | 第二十條 除外責任（一） | 第三十一條 投保年齡的計算及錯誤的處理 | 第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F369" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人年齡滿20歲（含）以上，並使用保險公司指定程式加入健康計劃，且於「指定日期」的會員等級符合進階會員或菁英會員（或更高等級）標準之一者，可享次一保險單年度的保費折減。折減比例為進階會員2%，菁英會員或更高等級3%。但豁免或復效的保險費不適用此折減規定。此外，被保險人需完成指定程式的註冊程序，並授權保險公司取得健康促進相關電子紀錄，保險公司將依此計算會員等級。
+條文依據：  
+- [第十九條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="G369" s="2" t="inlineStr"/>
+      <c r="H369" s="2" t="inlineStr"/>
+      <c r="I369" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "什麼情況下可以保費折減?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J369" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K369" s="4" t="n"/>
+      <c r="L369" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M369" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:55:48</t>
+        </is>
+      </c>
+      <c r="N369" s="4" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B370" s="2" t="inlineStr">
+        <is>
+          <t>角膜切除術是否可以申請理賠?</t>
+        </is>
+      </c>
+      <c r="C370" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+角膜切除術可以申請理賠，其對應的給付倍數為5倍。
+條文依據：  
+- [附表一：手術項目與給付倍數 - 1305 角膜切除術]</t>
+        </is>
+      </c>
+      <c r="D370" s="2" t="inlineStr">
+        <is>
+          <t>附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F370" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+角膜切除術可以申請理賠，其對應的給付倍數為5倍。
+條文依據：  
+- [附表一：手術項目與給付倍數 - 1305 角膜切除術]</t>
+        </is>
+      </c>
+      <c r="G370" s="2" t="inlineStr"/>
+      <c r="H370" s="2" t="inlineStr"/>
+      <c r="I370" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "角膜切除術是否可以申請理賠?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J370" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K370" s="4" t="n"/>
+      <c r="L370" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M370" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:55:53</t>
+        </is>
+      </c>
+      <c r="N370" s="4" t="n">
+        <v>5.16</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B371" s="2" t="inlineStr">
+        <is>
+          <t>白內障手術是否可以申請理賠?膜性白內障切開術、白內障線狀摘出術或白內障切囊術</t>
+        </is>
+      </c>
+      <c r="C371" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+白內障相關手術如膜性白內障切開術、白內障線狀摘出術及白內障切囊術均可申請理賠，且其給付倍數分別為5倍。  
+條文依據：  
+- [附表一：手術項目與給付倍數 - 1350 膜性白內障切開術 5]  
+- [附表一：手術項目與給付倍數 - 1351 白內障線狀摘出術 5]  
+- [附表一：手術項目與給付倍數 - 1352 白內障切囊術 5]</t>
+        </is>
+      </c>
+      <c r="D371" s="2" t="inlineStr">
+        <is>
+          <t>附表一：手術項目與給付倍數 | payout_items | 附表二：特定處置項目及給付倍數表</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F371" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+白內障相關手術如膜性白內障切開術、白內障線狀摘出術及白內障切囊術均可申請理賠，且其給付倍數分別為5倍。  
+條文依據：  
+- [附表一：手術項目與給付倍數 - 1350 膜性白內障切開術 5]  
+- [附表一：手術項目與給付倍數 - 1351 白內障線狀摘出術 5]  
+- [附表一：手術項目與給付倍數 - 1352 白內障切囊術 5]</t>
+        </is>
+      </c>
+      <c r="G371" s="2" t="inlineStr"/>
+      <c r="H371" s="2" t="inlineStr"/>
+      <c r="I371" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "白內障手術是否可以申請理賠?膜性白內障切開術、白內障線狀摘出術或白內障切囊術", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J371" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K371" s="4" t="n"/>
+      <c r="L371" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M371" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:56:01</t>
+        </is>
+      </c>
+      <c r="N371" s="4" t="n">
+        <v>7.64</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B372" s="2" t="inlineStr">
+        <is>
+          <t>保障範圍包括哪些項目？</t>
+        </is>
+      </c>
+      <c r="C372" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括：意外事故身故保險金或喪葬費用保險金、意外事故失能保險金、每月生活照護保險金、重大燒燙傷保險金、意外骨折保險金、傷害醫療日額保險金、意外創傷縫合處置保險金。
+條文依據：  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="D372" s="2" t="inlineStr">
+        <is>
+          <t>payout_items | 第五條 保險範圍 | 第十五條 每月生活照護保險金的給付 | 第三十條 不保事項 | 附表二：失能程度與保險金給付表</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F372" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括：意外事故身故保險金或喪葬費用保險金、意外事故失能保險金、每月生活照護保險金、重大燒燙傷保險金、意外骨折保險金、傷害醫療日額保險金、意外創傷縫合處置保險金。
+條文依據：  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="G372" s="2" t="inlineStr"/>
+      <c r="H372" s="2" t="inlineStr"/>
+      <c r="I372" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "保障範圍包括哪些項目？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J372" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K372" s="4" t="n"/>
+      <c r="L372" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M372" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:56:07</t>
+        </is>
+      </c>
+      <c r="N372" s="4" t="n">
+        <v>5.83</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B373" s="2" t="inlineStr">
+        <is>
+          <t>發生意外事故身故，理賠內容為何?</t>
+        </is>
+      </c>
+      <c r="C373" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外事故身故的理賠內容如下：  
+1. 若被保險人於意外傷害事故發生後 180 日內身故，本公司依意外傷害事故種類給付以下金額：  
+   - 一般意外傷害事故：「傷害醫療保險金日額」的 500 倍。  
+   - 特定意外傷害事故：「傷害醫療保險金日額」的 1000 倍。  
+2. 若被保險人於意外傷害事故發生後超過 180 日身故，但受益人能證明身故與該事故具有因果關係，本公司仍依上述金額給付。  
+3. 若被保險人於訂立契約時為受監護宣告尚未撤銷者，其理賠內容為喪葬費用保險金，且喪葬費用保險金額不得超過遺產稅喪葬費扣除額之半數，超過部分不予給付，並退還已繳保險費。  
+條文依據：  
+- [第十二條 意外事故身故保險金或喪葬費用保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D373" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 意外事故身故保險金或喪葬費用保險金的給付 | 第十四條 保險給付的限制 | payout_items | 第十一條 契約的終止（二） | 第二十一條 失蹤處理</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F373" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外事故身故的理賠內容如下：  
+1. 若被保險人於意外傷害事故發生後 180 日內身故，本公司依意外傷害事故種類給付以下金額：  
+   - 一般意外傷害事故：「傷害醫療保險金日額」的 500 倍。  
+   - 特定意外傷害事故：「傷害醫療保險金日額」的 1000 倍。  
+2. 若被保險人於意外傷害事故發生後超過 180 日身故，但受益人能證明身故與該事故具有因果關係，本公司仍依上述金額給付。  
+3. 若被保險人於訂立契約時為受監護宣告尚未撤銷者，其理賠內容為喪葬費用保險金，且喪葬費用保險金額不得超過遺產稅喪葬費扣除額之半數，超過部分不予給付，並退還已繳保險費。  
+條文依據：  
+- [第十二條 意外事故身故保險金或喪葬費用保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G373" s="2" t="inlineStr"/>
+      <c r="H373" s="2" t="inlineStr"/>
+      <c r="I373" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "發生意外事故身故，理賠內容為何?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J373" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K373" s="4" t="n"/>
+      <c r="L373" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M373" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:56:16</t>
+        </is>
+      </c>
+      <c r="N373" s="4" t="n">
+        <v>8.74</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B374" s="2" t="inlineStr">
+        <is>
+          <t>意外事故失能保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C374" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外事故失能保險金的給付條件如下：  
+1. 被保險人於保險契約有效期間內遭受「意外傷害事故」，並於事故發生後180日內致成附表二所列失能程度之一者，本公司依事故種類及失能程度，按以下方式計算給付金額：  
+   - 一般意外傷害事故：「傷害醫療保險金日額」的500倍乘以附表二給付比例。  
+   - 特定意外傷害事故：「傷害醫療保險金日額」的1000倍乘以附表二給付比例。  
+2. 若超過180日後致成失能，但受益人能證明失能與事故具有因果關係者，仍可申請給付，且不受180日限制。  
+3. 同一事故導致多項失能時，僅給付同一手或同一足中較嚴重失能項目的保險金，且總金額以事故種類的上限為限：  
+   - 一般意外傷害事故：「傷害醫療保險金日額」的500倍。  
+   - 特定意外傷害事故：「傷害醫療保險金日額」的1000倍。  
+4. 不同事故導致的失能，累計給付金額最高以「傷害醫療保險金日額」的1200倍為限。  
+條文依據：  
+- [第十三條 意外事故失能保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D374" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 意外事故失能保險金的給付 | 第十五條 每月生活照護保險金的給付 | 第十四條 保險給付的限制 | 第十二條 意外事故身故保險金或喪葬費用保險金的給付 | 第二十三條 意外事故失能保險金的申領 | 附表二：失能程度與保險金給付表</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F374" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外事故失能保險金的給付條件如下：  
+1. 被保險人於保險契約有效期間內遭受「意外傷害事故」，並於事故發生後180日內致成附表二所列失能程度之一者，本公司依事故種類及失能程度，按以下方式計算給付金額：  
+   - 一般意外傷害事故：「傷害醫療保險金日額」的500倍乘以附表二給付比例。  
+   - 特定意外傷害事故：「傷害醫療保險金日額」的1000倍乘以附表二給付比例。  
+2. 若超過180日後致成失能，但受益人能證明失能與事故具有因果關係者，仍可申請給付，且不受180日限制。  
+3. 同一事故導致多項失能時，僅給付同一手或同一足中較嚴重失能項目的保險金，且總金額以事故種類的上限為限：  
+   - 一般意外傷害事故：「傷害醫療保險金日額」的500倍。  
+   - 特定意外傷害事故：「傷害醫療保險金日額」的1000倍。  
+4. 不同事故導致的失能，累計給付金額最高以「傷害醫療保險金日額」的1200倍為限。  
+條文依據：  
+- [第十三條 意外事故失能保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G374" s="2" t="inlineStr"/>
+      <c r="H374" s="2" t="inlineStr"/>
+      <c r="I374" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "意外事故失能保險金的給付為何?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J374" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K374" s="4" t="n"/>
+      <c r="L374" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M374" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:56:23</t>
+        </is>
+      </c>
+      <c r="N374" s="4" t="n">
+        <v>7.01</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B375" s="2" t="inlineStr">
+        <is>
+          <t>每月生活照護保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C375" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+每月生活照護保險金的給付條件如下：  
+1. 被保險人於保險契約有效期間內因「意外傷害事故」，自事故發生之日起180日內，致成附表二所列第1級至第6級失能程度之一時，本公司自失能診斷確定當日起，按「傷害醫療保險金日額」的20倍乘以附表二給付比例所得之金額，按月給付，最多給付12個月。  
+2. 若於該失能的前四個「失能診斷確定週年日」，保險契約仍有效且被保險人仍生存，本公司自各該週年日起，按相同方式給付，最多再給付12個月。  
+3. 若被保險人自事故發生之日起超過180日才致成附表二所列第1級至第6級失能程度之一，但能證明該失能與事故具有因果關係，本公司仍依上述規定給付。  
+4. 同一事故若導致多項第1級至第6級失能，僅給付一項較嚴重失能的保險金，且最高以「傷害醫療保險金日額」的20倍為限。  
+5. 若失能合併以前的失能，僅給付較嚴重項目的保險金，但以前的失能視同已給付，應扣除之。  
+6. 每月給付金額最高以「傷害醫療保險金日額」的20倍為限，累計給付金額最高以「傷害醫療保險金日額」的1200倍為限。  
+條文依據：  
+- [第十五條 每月生活照護保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D375" s="2" t="inlineStr">
+        <is>
+          <t>第二十四條 每月生活照護保險金的申領 | 第十五條 每月生活照護保險金的給付 | payout_items | 第十八條 傷害醫療日額保險金的給付 | 第五條 保險範圍 | 附表二：失能程度與保險金給付表 | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F375" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+每月生活照護保險金的給付條件如下：  
+1. 被保險人於保險契約有效期間內因「意外傷害事故」，自事故發生之日起180日內，致成附表二所列第1級至第6級失能程度之一時，本公司自失能診斷確定當日起，按「傷害醫療保險金日額」的20倍乘以附表二給付比例所得之金額，按月給付，最多給付12個月。  
+2. 若於該失能的前四個「失能診斷確定週年日」，保險契約仍有效且被保險人仍生存，本公司自各該週年日起，按相同方式給付，最多再給付12個月。  
+3. 若被保險人自事故發生之日起超過180日才致成附表二所列第1級至第6級失能程度之一，但能證明該失能與事故具有因果關係，本公司仍依上述規定給付。  
+4. 同一事故若導致多項第1級至第6級失能，僅給付一項較嚴重失能的保險金，且最高以「傷害醫療保險金日額」的20倍為限。  
+5. 若失能合併以前的失能，僅給付較嚴重項目的保險金，但以前的失能視同已給付，應扣除之。  
+6. 每月給付金額最高以「傷害醫療保險金日額」的20倍為限，累計給付金額最高以「傷害醫療保險金日額」的1200倍為限。  
+條文依據：  
+- [第十五條 每月生活照護保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G375" s="2" t="inlineStr"/>
+      <c r="H375" s="2" t="inlineStr"/>
+      <c r="I375" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "每月生活照護保險金的給付為何?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J375" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K375" s="4" t="n"/>
+      <c r="L375" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M375" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:56:32</t>
+        </is>
+      </c>
+      <c r="N375" s="4" t="n">
+        <v>8.640000000000001</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B376" s="2" t="inlineStr">
+        <is>
+          <t>重大燒燙傷保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C376" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+重大燒燙傷保險金的給付條件為：被保險人於保險契約有效期間內，因「意外傷害事故」導致燒燙傷，且經診斷符合「重大燒燙傷」標準時，本公司將按「傷害醫療保險金日額」的二百五十倍給付「重大燒燙傷保險金」。該保險金的給付以一次為限。
+條文依據：  
+- [第十六條 重大燒燙傷保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D376" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 重大燒燙傷保險金的給付 | 第二十五條 重大燒燙傷保險金的申領 | 第五條 保險範圍 | payout_items | 第二十九條 除外責任（原因）</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F376" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+重大燒燙傷保險金的給付條件為：被保險人於保險契約有效期間內，因「意外傷害事故」導致燒燙傷，且經診斷符合「重大燒燙傷」標準時，本公司將按「傷害醫療保險金日額」的二百五十倍給付「重大燒燙傷保險金」。該保險金的給付以一次為限。
+條文依據：  
+- [第十六條 重大燒燙傷保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G376" s="2" t="inlineStr"/>
+      <c r="H376" s="2" t="inlineStr"/>
+      <c r="I376" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "重大燒燙傷保險金的給付為何?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J376" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K376" s="4" t="n"/>
+      <c r="L376" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M376" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:56:37</t>
+        </is>
+      </c>
+      <c r="N376" s="4" t="n">
+        <v>5.34</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B377" s="2" t="inlineStr">
+        <is>
+          <t>意外骨折保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C377" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外骨折保險金的給付條件如下：  
+1. 被保險人於保險契約有效期間內因「意外傷害事故」導致骨折，且自意外傷害事故發生之日起一百八十日內，經合格醫院或診所診斷為附表三骨折別表所列骨折項目之一（含不完全骨折及骨骼龜裂），本公司按「傷害醫療保險金日額」的二倍給付「意外骨折保險金」。  
+2. 若被保險人自意外傷害事故發生之日起超過一百八十日才診斷確定骨折，受益人需證明骨折與該意外傷害事故具有因果關係，本公司仍依上述規定給付保險金，不受一百八十日限制。  
+3. 同一意外傷害事故僅給付一次「意外骨折保險金」。  
+4. 若骨折部位不屬於附表三骨折別表所列項目，需由本公司與被保險人協議核定保險金額。  
+5. 若骨折部位為附表三骨折別表中明訂不給付的部位，則本公司不負給付保險金之責。  
+條文依據：  
+- [第十七條 意外骨折保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D377" s="2" t="inlineStr">
+        <is>
+          <t>第十七條 意外骨折保險金的給付 | 第十八條 傷害醫療日額保險金的給付 | 第二十六條 意外骨折保險金的申領 | 第十三條 意外事故失能保險金的給付 | 第十九條 意外創傷縫合處置保險金的給付 | 附表二：失能程度與保險金給付表 | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F377" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外骨折保險金的給付條件如下：  
+1. 被保險人於保險契約有效期間內因「意外傷害事故」導致骨折，且自意外傷害事故發生之日起一百八十日內，經合格醫院或診所診斷為附表三骨折別表所列骨折項目之一（含不完全骨折及骨骼龜裂），本公司按「傷害醫療保險金日額」的二倍給付「意外骨折保險金」。  
+2. 若被保險人自意外傷害事故發生之日起超過一百八十日才診斷確定骨折，受益人需證明骨折與該意外傷害事故具有因果關係，本公司仍依上述規定給付保險金，不受一百八十日限制。  
+3. 同一意外傷害事故僅給付一次「意外骨折保險金」。  
+4. 若骨折部位不屬於附表三骨折別表所列項目，需由本公司與被保險人協議核定保險金額。  
+5. 若骨折部位為附表三骨折別表中明訂不給付的部位，則本公司不負給付保險金之責。  
+條文依據：  
+- [第十七條 意外骨折保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G377" s="2" t="inlineStr"/>
+      <c r="H377" s="2" t="inlineStr"/>
+      <c r="I377" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "意外骨折保險金的給付為何?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J377" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K377" s="4" t="n"/>
+      <c r="L377" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M377" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:56:44</t>
+        </is>
+      </c>
+      <c r="N377" s="4" t="n">
+        <v>6.91</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B378" s="2" t="inlineStr">
+        <is>
+          <t>傷害醫療日額保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C378" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+傷害醫療日額保險金的給付條件如下：  
+1. 被保險人於保險契約有效期間內遭受「意外傷害事故」，並於事故發生後一百八十日內在「醫院」接受住院治療者，本公司按「傷害醫療保險金日額」乘以實際住院日數給付，但每次事故最高給付日數為九十日。  
+2. 若治療超過一百八十日，且受益人能證明治療與該事故具有因果關係，本公司仍依上述規定給付，不受一百八十日限制。  
+3. 若因意外事故骨折但未住院，或住院日數未達附表三骨折別表所訂日數，則按骨折別表所訂日數乘以「傷害醫療保險金日額」的二分之一給付，合計給付日數以骨折別表所訂日數為上限。  
+4. 骨折類型的給付：  
+   - 完全骨折按骨折別表日數給付。  
+   - 不完全骨折按完全骨折日數的二分之一給付。  
+   - 骨骼龜裂按完全骨折日數的四分之一給付。  
+5. 同時發生多項骨折時，僅給付一項較高等級的「傷害醫療日額保險金」。
+條文依據：  
+- [第十八條 傷害醫療日額保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D378" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 傷害醫療日額保險金的給付 | 第二十七條 傷害醫療日額保險金的申領 | 第十五條 每月生活照護保險金的給付 | 第三十四條 傷害醫療保險金日額之減少 | 第十九條 意外創傷縫合處置保險金的給付 | 附表二：失能程度與保險金給付表 | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F378" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+傷害醫療日額保險金的給付條件如下：  
+1. 被保險人於保險契約有效期間內遭受「意外傷害事故」，並於事故發生後一百八十日內在「醫院」接受住院治療者，本公司按「傷害醫療保險金日額」乘以實際住院日數給付，但每次事故最高給付日數為九十日。  
+2. 若治療超過一百八十日，且受益人能證明治療與該事故具有因果關係，本公司仍依上述規定給付，不受一百八十日限制。  
+3. 若因意外事故骨折但未住院，或住院日數未達附表三骨折別表所訂日數，則按骨折別表所訂日數乘以「傷害醫療保險金日額」的二分之一給付，合計給付日數以骨折別表所訂日數為上限。  
+4. 骨折類型的給付：  
+   - 完全骨折按骨折別表日數給付。  
+   - 不完全骨折按完全骨折日數的二分之一給付。  
+   - 骨骼龜裂按完全骨折日數的四分之一給付。  
+5. 同時發生多項骨折時，僅給付一項較高等級的「傷害醫療日額保險金」。
+條文依據：  
+- [第十八條 傷害醫療日額保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G378" s="2" t="inlineStr"/>
+      <c r="H378" s="2" t="inlineStr"/>
+      <c r="I378" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "傷害醫療日額保險金的給付為何?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J378" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K378" s="4" t="n"/>
+      <c r="L378" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M378" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:56:51</t>
+        </is>
+      </c>
+      <c r="N378" s="4" t="n">
+        <v>6.06</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B379" s="2" t="inlineStr">
+        <is>
+          <t>意外創傷縫合處置保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C379" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外創傷縫合處置保險金的給付條件為：被保險人在保險契約有效期間內，因遭受「意外傷害事故」，於「醫院」或「診所」經醫師診斷必須接受創傷縫合處置治療，且已接受縫合處置者，本公司按「傷害醫療保險金日額」給付「意外創傷縫合處置保險金」。同一意外傷害事故僅給付一次。
+條文依據：  
+- [第十九條 意外創傷縫合處置保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D379" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 意外創傷縫合處置保險金的給付 | 第二十八條 意外創傷縫合處置保險金的申領 | 第五條 保險範圍 | 第十七條 意外骨折保險金的給付 | payout_items | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F379" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外創傷縫合處置保險金的給付條件為：被保險人在保險契約有效期間內，因遭受「意外傷害事故」，於「醫院」或「診所」經醫師診斷必須接受創傷縫合處置治療，且已接受縫合處置者，本公司按「傷害醫療保險金日額」給付「意外創傷縫合處置保險金」。同一意外傷害事故僅給付一次。
+條文依據：  
+- [第十九條 意外創傷縫合處置保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G379" s="2" t="inlineStr"/>
+      <c r="H379" s="2" t="inlineStr"/>
+      <c r="I379" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "意外創傷縫合處置保險金的給付為何?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J379" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K379" s="4" t="n"/>
+      <c r="L379" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M379" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:56:56</t>
+        </is>
+      </c>
+      <c r="N379" s="4" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B380" s="2" t="inlineStr">
+        <is>
+          <t>因意外導致視力衰退，是否能申請理賠?</t>
+        </is>
+      </c>
+      <c r="C380" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以申請理賠，但需符合以下條件：  
+1. 視力衰退需達到「失明」的定義，即矯正後視力永久在萬國式視力表0.02以下，或符合其他失明標準（如眼球摘出、僅能辨明暗等）。  
+2. 必須經過自傷害日起六個月的治療後進行判定，但若屬於眼球摘出等明顯無法復原的情況，則不受此限制。  
+條文依據：  
+- 註2</t>
+        </is>
+      </c>
+      <c r="D380" s="2" t="inlineStr">
+        <is>
+          <t>第二十三條 意外事故失能保險金的申領 | 第十三條 意外事故失能保險金的給付 | 註2： | 第三十條 不保事項 | 第二十六條 意外骨折保險金的申領 | 附表二：失能程度與保險金給付表</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F380" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以申請理賠，但需符合以下條件：  
+1. 視力衰退需達到「失明」的定義，即矯正後視力永久在萬國式視力表0.02以下，或符合其他失明標準（如眼球摘出、僅能辨明暗等）。  
+2. 必須經過自傷害日起六個月的治療後進行判定，但若屬於眼球摘出等明顯無法復原的情況，則不受此限制。  
+條文依據：  
+- 註2</t>
+        </is>
+      </c>
+      <c r="G380" s="2" t="inlineStr"/>
+      <c r="H380" s="2" t="inlineStr"/>
+      <c r="I380" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "因意外導致視力衰退，是否能申請理賠?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J380" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K380" s="4" t="n"/>
+      <c r="L380" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M380" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:57:04</t>
+        </is>
+      </c>
+      <c r="N380" s="4" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B381" s="2" t="inlineStr">
+        <is>
+          <t>肋骨骨折是否可以申請理賠?理賠金額為多少?包含傷害醫療保險金日額跟意外骨折保險金嗎？</t>
+        </is>
+      </c>
+      <c r="C381" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+肋骨骨折可以申請理賠，理賠金額需依保單條款計算，包含以下兩項：  
+1. **傷害醫療日額保險金**：若因肋骨骨折住院治療，按實際住院日數乘以「傷害醫療保險金日額」給付，最高以90日為限；若未住院，則按附表三所訂肋骨完全骨折日數20天的二分之一（即10天）乘以「傷害醫療保險金日額」給付。  
+2. **意外骨折保險金**：肋骨骨折屬於附表三骨折別表所列項目，按「傷害醫療保險金日額」的二倍給付一次性「意外骨折保險金」。  
+條文依據：  
+- [第十八條 傷害醫療日額保險金的給付]  
+- [第十七條 意外骨折保險金的給付]  
+- [附表三：骨折別表]</t>
+        </is>
+      </c>
+      <c r="D381" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 傷害醫療日額保險金的給付 | 第十七條 意外骨折保險金的給付 | 第二十六條 意外骨折保險金的申領 | payout_items | 第二十七條 傷害醫療日額保險金的申領 | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F381" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+肋骨骨折可以申請理賠，理賠金額需依保單條款計算，包含以下兩項：  
+1. **傷害醫療日額保險金**：若因肋骨骨折住院治療，按實際住院日數乘以「傷害醫療保險金日額」給付，最高以90日為限；若未住院，則按附表三所訂肋骨完全骨折日數20天的二分之一（即10天）乘以「傷害醫療保險金日額」給付。  
+2. **意外骨折保險金**：肋骨骨折屬於附表三骨折別表所列項目，按「傷害醫療保險金日額」的二倍給付一次性「意外骨折保險金」。  
+條文依據：  
+- [第十八條 傷害醫療日額保險金的給付]  
+- [第十七條 意外骨折保險金的給付]  
+- [附表三：骨折別表]</t>
+        </is>
+      </c>
+      <c r="G381" s="2" t="inlineStr"/>
+      <c r="H381" s="2" t="inlineStr"/>
+      <c r="I381" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "肋骨骨折是否可以申請理賠?理賠金額為多少?包含傷害醫療保險金日額跟意外骨折保險金嗎？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J381" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K381" s="4" t="n"/>
+      <c r="L381" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M381" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:57:13</t>
+        </is>
+      </c>
+      <c r="N381" s="4" t="n">
+        <v>8.449999999999999</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B382" s="2" t="inlineStr">
+        <is>
+          <t>投保新鍾心滿福後，假設投保保額為100萬元，於第二保單年度接受「移植器官」，這樣可以領多少重大傷病保險金及特定重大傷病保險金?</t>
+        </is>
+      </c>
+      <c r="C382" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 新鍾心滿福保單涵蓋重大傷病保險金及特定重大傷病保險金。  
+2. 器官移植屬於「重大傷病範圍」及「特定重大傷病」的給付條件，符合給付資格。  
+3. 若保額為100萬元，重大傷病保險金的給付金額為「保險金額」或「年繳應繳保險費總額的一點零五倍」，二者取其大者；特定重大傷病保險金則為「保險金額的百分之二十」，即20萬元。  
+4. 第二保單年度不影響重大傷病保險金及特定重大傷病保險金的給付資格，因條文已明確規定第二保單年度（含）以後的有效期間內符合條件即可申請。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第十三條 特定重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D382" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 特定重大傷病保險金的給付 | 第十二條 重大傷病保險金的給付 | 附表一：全民健康保險重大傷病項目 | payout_items | 第二條 名詞定義 | 附表二：完全失能程度表</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F382" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 新鍾心滿福保單涵蓋重大傷病保險金及特定重大傷病保險金。  
+2. 器官移植屬於「重大傷病範圍」及「特定重大傷病」的給付條件，符合給付資格。  
+3. 若保額為100萬元，重大傷病保險金的給付金額為「保險金額」或「年繳應繳保險費總額的一點零五倍」，二者取其大者；特定重大傷病保險金則為「保險金額的百分之二十」，即20萬元。  
+4. 第二保單年度不影響重大傷病保險金及特定重大傷病保險金的給付資格，因條文已明確規定第二保單年度（含）以後的有效期間內符合條件即可申請。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第十三條 特定重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G382" s="2" t="inlineStr"/>
+      <c r="H382" s="2" t="inlineStr"/>
+      <c r="I382" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認新鍾心滿福保單是否涵蓋重大傷病保險金及特定重大傷病保險金", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認重大傷病保險金及特定重大傷病保險金的給付條件是否包含器官移植", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認保額100萬元對應的重大傷病保險金及特定重大傷病保險金給付比例或金額", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認第二保單年度是否影響重大傷病保險金及特定重大傷病保險金的給付資格", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J382" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K382" s="4" t="n"/>
+      <c r="L382" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M382" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:57:34</t>
+        </is>
+      </c>
+      <c r="N382" s="4" t="n">
+        <v>21.44</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B383" s="2" t="inlineStr">
+        <is>
+          <t>投保新鍾心滿福後，若要理賠重大傷病保險金，一定要檢附全民健保開立的重大傷病證明才能拿到保險金嗎?</t>
+        </is>
+      </c>
+      <c r="C383" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 新鍾心滿福包含重大傷病保險金保障，依條款第二條名詞定義及第十二條重大傷病保險金的給付規定，若被保險人於契約有效期間內經診斷確定罹患符合重大傷病範圍的疾病，可申請重大傷病保險金。  
+2. 理賠重大傷病保險金時，通常需要檢附全民健保開立的重大傷病證明，但條款第二十二條規定，若被保險人已取得一家「區域醫院」層級以上（含）之醫療院所開立的診斷書及病歷摘要，且符合投保當時重大傷病範圍，則可免向全民健保申請重大傷病證明。  
+3. 若無法取得全民健保重大傷病證明，條款第二十二條亦列明其他可替代的文件，例如「重大傷病病歷摘要」及「重大傷病醫療費用收據」，或符合條件的診斷書與病歷摘要。
+條文依據：  
+- [第二條 名詞定義]  
+- [第十二條 重大傷病保險金的給付]  
+- [第二十二條 重大傷病保險金、特定重大傷病保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D383" s="2" t="inlineStr">
+        <is>
+          <t>第二十二條 重大傷病保險金、特定重大傷病保險金的申領 | other_metadata | 第十二條 重大傷病保險金的給付 | 附表一：全民健康保險重大傷病項目 | 第二條 名詞定義 | 第三十條 不保事項</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F383" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 新鍾心滿福包含重大傷病保險金保障，依條款第二條名詞定義及第十二條重大傷病保險金的給付規定，若被保險人於契約有效期間內經診斷確定罹患符合重大傷病範圍的疾病，可申請重大傷病保險金。  
+2. 理賠重大傷病保險金時，通常需要檢附全民健保開立的重大傷病證明，但條款第二十二條規定，若被保險人已取得一家「區域醫院」層級以上（含）之醫療院所開立的診斷書及病歷摘要，且符合投保當時重大傷病範圍，則可免向全民健保申請重大傷病證明。  
+3. 若無法取得全民健保重大傷病證明，條款第二十二條亦列明其他可替代的文件，例如「重大傷病病歷摘要」及「重大傷病醫療費用收據」，或符合條件的診斷書與病歷摘要。
+條文依據：  
+- [第二條 名詞定義]  
+- [第十二條 重大傷病保險金的給付]  
+- [第二十二條 重大傷病保險金、特定重大傷病保險金的申領]</t>
+        </is>
+      </c>
+      <c r="G383" s="2" t="inlineStr"/>
+      <c r="H383" s="2" t="inlineStr"/>
+      <c r="I383" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認新鍾心滿福是否包含重大傷病保險金保障", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認理賠重大傷病保險金是否需要檢附全民健保開立的重大傷病證明", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認是否有其他文件可替代重大傷病證明進行理賠", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J383" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K383" s="4" t="n"/>
+      <c r="L383" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M383" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:57:46</t>
+        </is>
+      </c>
+      <c r="N383" s="4" t="n">
+        <v>10.31</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B384" s="2" t="inlineStr">
+        <is>
+          <t>要有健保身分才能申請重大傷病理賠嗎？</t>
+        </is>
+      </c>
+      <c r="C384" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+是的，若被保險人喪失全民健康保險被保險人資格，需先申請加保全民健康保險後，才能申請「重大傷病保險金」的給付。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D384" s="2" t="inlineStr">
+        <is>
+          <t>第二十二條 重大傷病保險金、特定重大傷病保險金的申領 | 第十二條 重大傷病保險金的給付 | 第三十條 不保事項 | other_metadata | 第二條 名詞定義 | 附表一：全民健康保險重大傷病項目</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F384" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+是的，若被保險人喪失全民健康保險被保險人資格，需先申請加保全民健康保險後，才能申請「重大傷病保險金」的給付。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G384" s="2" t="inlineStr"/>
+      <c r="H384" s="2" t="inlineStr"/>
+      <c r="I384" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "要有健保身分才能申請重大傷病理賠嗎？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J384" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K384" s="4" t="n"/>
+      <c r="L384" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M384" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:57:52</t>
+        </is>
+      </c>
+      <c r="N384" s="4" t="n">
+        <v>5.79</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B385" s="2" t="inlineStr">
+        <is>
+          <t>重大傷病的項目如果在投保後有新增，可以從優申請理賠嗎？</t>
+        </is>
+      </c>
+      <c r="C385" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以從優申請理賠，若重大傷病項目於保險契約有效期間內新增，則以中央衛生主管機關最新公告的重大傷病項目為準，並適用於被保險人於有效期間內診斷確定的情況。
+條文依據：  
+- [第二條 名詞定義]：「全民健康保險重大傷病項目及其證明有效期限」，包含本契約「訂立時」及「有效期間內被保險人診斷確定當時」由中央衛生主管機關公告之重大傷病項目。</t>
+        </is>
+      </c>
+      <c r="D385" s="2" t="inlineStr">
+        <is>
+          <t>附表一：全民健康保險重大傷病項目 | 第二條 名詞定義 | payout_items</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F385" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以從優申請理賠，若重大傷病項目於保險契約有效期間內新增，則以中央衛生主管機關最新公告的重大傷病項目為準，並適用於被保險人於有效期間內診斷確定的情況。
+條文依據：  
+- [第二條 名詞定義]：「全民健康保險重大傷病項目及其證明有效期限」，包含本契約「訂立時」及「有效期間內被保險人診斷確定當時」由中央衛生主管機關公告之重大傷病項目。</t>
+        </is>
+      </c>
+      <c r="G385" s="2" t="inlineStr"/>
+      <c r="H385" s="2" t="inlineStr"/>
+      <c r="I385" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "重大傷病的項目如果在投保後有新增，可以從優申請理賠嗎？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J385" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K385" s="4" t="n"/>
+      <c r="L385" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M385" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:57:59</t>
+        </is>
+      </c>
+      <c r="N385" s="4" t="n">
+        <v>6.09</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B386" s="2" t="inlineStr">
+        <is>
+          <t>我的保單之前有停效，在復效後五天被診斷出重大疾病是否可申請理賠？</t>
+        </is>
+      </c>
+      <c r="C386" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若保單已成功復效，且重大疾病屬於保單保障範圍內，則需確認復效後的理賠條件是否符合重大疾病申請要求。根據條款，重大疾病的理賠需滿足以下條件：  
+1. 被保險人需於復效日起的契約有效期間內，經醫院醫師初次診斷確定罹患「重大傷病」。  
+2. 若重大疾病為意外傷害事故所致，則不受等待期間限制；若非因意外傷害事故，則需確認是否符合等待期間的規定。  
+條文依據：  
+- [第八條 本契約效力的恢復]  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D386" s="2" t="inlineStr">
+        <is>
+          <t>第八條 本契約效力的恢復 | 第三十條 不保事項 | 第五條 保險範圍 | other_metadata | 第二條 名詞定義 | 第十二條 重大傷病保險金的給付 | 第二十二條 重大傷病保險金、特定重大傷病保險金的申領 | 附表一：全民健康保險重大傷病項目</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F386" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若保單已成功復效，且重大疾病屬於保單保障範圍內，則需確認復效後的理賠條件是否符合重大疾病申請要求。根據條款，重大疾病的理賠需滿足以下條件：  
+1. 被保險人需於復效日起的契約有效期間內，經醫院醫師初次診斷確定罹患「重大傷病」。  
+2. 若重大疾病為意外傷害事故所致，則不受等待期間限制；若非因意外傷害事故，則需確認是否符合等待期間的規定。  
+條文依據：  
+- [第八條 本契約效力的恢復]  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G386" s="2" t="inlineStr"/>
+      <c r="H386" s="2" t="inlineStr"/>
+      <c r="I386" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認保單是否已成功復效", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認重大疾病是否在保單保障範圍內", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認復效後的理賠條件是否符合重大疾病申請要求", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認重大疾病診斷日期是否符合保單復效後的理賠規定", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J386" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K386" s="4" t="n"/>
+      <c r="L386" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M386" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:58:10</t>
+        </is>
+      </c>
+      <c r="N386" s="4" t="n">
+        <v>10.81</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B387" s="2" t="inlineStr">
+        <is>
+          <t>領完重大傷病保險金，主約終止後，附約可以繼續有效嗎?</t>
+        </is>
+      </c>
+      <c r="C387" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以。根據條款規定，若因重大傷病診斷確定而導致主約終止時，要保人仍可於附約有效期間內繼續繳交附約保險費，以延續附約效力。
+條文依據：  
+- [第十一條 契約的終止（二）]</t>
+        </is>
+      </c>
+      <c r="D387" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 契約的終止（二） | 第十二條 重大傷病保險金的給付 | 第三十條 不保事項 | 第五條 保險範圍 | payout_items | 附表一：全民健康保險重大傷病項目</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F387" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以。根據條款規定，若因重大傷病診斷確定而導致主約終止時，要保人仍可於附約有效期間內繼續繳交附約保險費，以延續附約效力。
+條文依據：  
+- [第十一條 契約的終止（二）]</t>
+        </is>
+      </c>
+      <c r="G387" s="2" t="inlineStr"/>
+      <c r="H387" s="2" t="inlineStr"/>
+      <c r="I387" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "領完重大傷病保險金，主約終止後，附約可以繼續有效嗎?", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J387" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K387" s="4" t="n"/>
+      <c r="L387" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M387" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:58:15</t>
+        </is>
+      </c>
+      <c r="N387" s="4" t="n">
+        <v>5.18</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B388" s="2" t="inlineStr">
+        <is>
+          <t>Q1：因為慢性精神病的保險給付僅有保額的20%，我可以先不申請給付，等之後發生其他重大傷病後，再申請重大傷病保險金嗎?Q2：但如果我不申請，保險公司不會知道我有罹患慢性精神病阿，所以我就可以領之後的重大傷病100%保額嗎?</t>
+        </is>
+      </c>
+      <c r="C388" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+Q1：慢性精神病的保險給付比例確實為保額的20%，但是否可以延後申請需視條款規定。根據第十二條，保險公司僅給付一項「重大傷病保險金」，若被保險人同時或先後罹患多項重大傷病，則以首次診斷確定的重大傷病為準。因此，延後申請慢性精神病保險金可能影響後續其他重大傷病的保險金申請資格或保額。  
+Q2：即使未申請慢性精神病給付，保險公司仍可能透過其他方式得知被保險人罹患慢性精神病，並依據條款規定進行審核。條款未明確說明未申請是否會影響後續重大傷病保險金的保額，但根據第十二條，若慢性精神病為首次診斷的重大傷病，則保險金額將依慢性精神病的給付比例計算。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第二十二條 重大傷病保險金、特定重大傷病保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D388" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 重大傷病保險金的給付 | 第十三條 特定重大傷病保險金的給付 | 第三十條 不保事項 | 第二十八條 除外責任（一） | 第二十二條 重大傷病保險金、特定重大傷病保險金的申領 | 第二條 名詞定義 | 附表一：全民健康保險重大傷病項目 | payout_items</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F388" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+Q1：慢性精神病的保險給付比例確實為保額的20%，但是否可以延後申請需視條款規定。根據第十二條，保險公司僅給付一項「重大傷病保險金」，若被保險人同時或先後罹患多項重大傷病，則以首次診斷確定的重大傷病為準。因此，延後申請慢性精神病保險金可能影響後續其他重大傷病的保險金申請資格或保額。  
+Q2：即使未申請慢性精神病給付，保險公司仍可能透過其他方式得知被保險人罹患慢性精神病，並依據條款規定進行審核。條款未明確說明未申請是否會影響後續重大傷病保險金的保額，但根據第十二條，若慢性精神病為首次診斷的重大傷病，則保險金額將依慢性精神病的給付比例計算。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第二十二條 重大傷病保險金、特定重大傷病保險金的申領]</t>
+        </is>
+      </c>
+      <c r="G388" s="2" t="inlineStr"/>
+      <c r="H388" s="2" t="inlineStr"/>
+      <c r="I388" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認慢性精神病保險給付比例是否為保額的20%", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認是否可以延後申請慢性精神病的保險給付", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認延後申請是否影響重大傷病保險金的申請資格或保額", "must_have": true, "分數": 1.0}, {"id": "4", "point": "確認保險公司是否會因未申請慢性精神病給付而不知情", "must_have": false, "分數": 1.0}, {"id": "5", "point": "確認重大傷病保險金是否能領取100%保額的條件", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J388" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K388" s="4" t="n"/>
+      <c r="L388" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M388" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:58:31</t>
+        </is>
+      </c>
+      <c r="N388" s="4" t="n">
+        <v>16.01</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B389" s="2" t="inlineStr">
+        <is>
+          <t>慢性精神病失智症會賠嗎？賠多少？</t>
+        </is>
+      </c>
+      <c r="C389" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+慢性精神病（如失智症）屬於重大傷病範圍，若被保險人於等待期間屆滿翌日或復效日起的契約有效期間內，經醫師診斷確定罹患，並取得重大傷病證明或符合診斷書及病歷摘要的要求，本公司將依以下方式給付重大傷病保險金：  
+1. 若初次診斷確定罹患重大傷病時的保險單年度為第一保險單年度，給付「年繳應繳保險費總額」的1.05倍。  
+2. 若初次診斷確定罹患重大傷病時的保險單年度為第二保險單年度（含）以後，屬於慢性精神病，給付「保險金額的20%」或「年繳應繳保險費總額的1.05倍」，二者取其大者。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D389" s="2" t="inlineStr">
+        <is>
+          <t>附表一：全民健康保險重大傷病項目 | 第二十九條 除外責任（二） | 第十二條 重大傷病保險金的給付 | payout_items | 附表二：完全失能程度表</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F389" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+慢性精神病（如失智症）屬於重大傷病範圍，若被保險人於等待期間屆滿翌日或復效日起的契約有效期間內，經醫師診斷確定罹患，並取得重大傷病證明或符合診斷書及病歷摘要的要求，本公司將依以下方式給付重大傷病保險金：  
+1. 若初次診斷確定罹患重大傷病時的保險單年度為第一保險單年度，給付「年繳應繳保險費總額」的1.05倍。  
+2. 若初次診斷確定罹患重大傷病時的保險單年度為第二保險單年度（含）以後，屬於慢性精神病，給付「保險金額的20%」或「年繳應繳保險費總額的1.05倍」，二者取其大者。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="G389" s="2" t="inlineStr"/>
+      <c r="H389" s="2" t="inlineStr"/>
+      <c r="I389" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "Q", "point": "慢性精神病失智症會賠嗎？賠多少？", "must_have": true, "分數": 1.0}], "coverage_score": 1.0, "C_conf": 1.0}</t>
+        </is>
+      </c>
+      <c r="J389" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K389" s="4" t="n"/>
+      <c r="L389" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M389" t="inlineStr">
+        <is>
+          <t>2026-04-04 20:58:41</t>
+        </is>
+      </c>
+      <c r="N389" s="4" t="n">
+        <v>9.56</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B390" s="2" t="inlineStr">
+        <is>
+          <t>投保新鍾心滿福後，於第二保單年度罹患子宮頸惡性腫瘤，且已給付重大傷病保險金。第五保單年度時又罹患慢性腎衰竭，這樣還可以申領重大傷病保險金的給付嗎?</t>
+        </is>
+      </c>
+      <c r="C390" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款規定，重大傷病保險金僅能給付一次，即使被保險人同時或先後罹患多項重大傷病，本公司僅給付一項重大傷病保險金。因此，雖然慢性腎衰竭符合重大傷病保險金的給付條件，但因已於第二保單年度因子宮頸惡性腫瘤申領過重大傷病保險金，無法再次申領。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D390" s="2" t="inlineStr">
+        <is>
+          <t>附表一：全民健康保險重大傷病項目 | 第十二條 重大傷病保險金的給付 | 第五條 保險範圍 | 第二條 名詞定義 | payout_items | 第二十二條 重大傷病保險金、特定重大傷病保險金的申領</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F390" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款規定，重大傷病保險金僅能給付一次，即使被保險人同時或先後罹患多項重大傷病，本公司僅給付一項重大傷病保險金。因此，雖然慢性腎衰竭符合重大傷病保險金的給付條件，但因已於第二保單年度因子宮頸惡性腫瘤申領過重大傷病保險金，無法再次申領。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="G390" s="2" t="inlineStr"/>
+      <c r="H390" s="2" t="inlineStr"/>
+      <c r="I390" s="2" t="inlineStr">
+        <is>
+          <t>{"points": [{"id": "1", "point": "確認重大傷病保險金是否可重複申領", "must_have": true, "分數": 1.0}, {"id": "2", "point": "確認慢性腎衰竭是否符合重大傷病保險金的給付條件", "must_have": true, "分數": 1.0}, {"id": "3", "point": "確認保單條款中對於不同保單年度內重大傷病理賠的限制", "must_have": false, "分數": 1.0}], "coverage_score": 1.0, "C_conf":